--- a/report_2410.xlsx
+++ b/report_2410.xlsx
@@ -800,7 +800,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1059,11 +1059,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3891,7 +3886,7 @@
         </is>
       </c>
       <c r="B25" s="88" t="n">
-        <v>7.06</v>
+        <v>7.07</v>
       </c>
       <c r="C25" s="88" t="n">
         <v>7.01</v>
@@ -3988,7 +3983,7 @@
         </is>
       </c>
       <c r="B26" s="89" t="n">
-        <v>0.68</v>
+        <v>0.92</v>
       </c>
       <c r="C26" s="89" t="n">
         <v>0.42</v>
@@ -4085,7 +4080,7 @@
         </is>
       </c>
       <c r="B27" s="89" t="n">
-        <v>-0.43</v>
+        <v>-0.19</v>
       </c>
       <c r="C27" s="89" t="n">
         <v>-1.11</v>
@@ -6327,7 +6322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE52"/>
+  <dimension ref="A1:AE49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col width="19.5925925925926" customWidth="1" style="34" min="1" max="1"/>
@@ -6335,5551 +6330,1937 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="76" t="inlineStr">
+      <c r="A1" s="58" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="77" t="inlineStr">
-        <is>
-          <t>241008</t>
-        </is>
-      </c>
-      <c r="C1" s="77" t="inlineStr">
-        <is>
-          <t>241007</t>
-        </is>
-      </c>
-      <c r="D1" s="77" t="inlineStr">
-        <is>
-          <t>241004</t>
-        </is>
-      </c>
-      <c r="E1" s="77" t="inlineStr">
+      <c r="B1" s="59" t="inlineStr">
         <is>
           <t>241003</t>
         </is>
       </c>
-      <c r="F1" s="77" t="inlineStr">
+      <c r="C1" s="59" t="inlineStr">
         <is>
           <t>241002</t>
         </is>
       </c>
-      <c r="G1" s="77" t="inlineStr">
+      <c r="D1" s="59" t="inlineStr">
         <is>
           <t>241001</t>
         </is>
       </c>
-      <c r="H1" s="77" t="inlineStr">
+      <c r="E1" s="59" t="inlineStr">
         <is>
           <t>240930</t>
         </is>
       </c>
-      <c r="I1" s="77" t="inlineStr">
+      <c r="F1" s="59" t="inlineStr">
         <is>
           <t>240927</t>
         </is>
       </c>
-      <c r="J1" s="77" t="inlineStr">
+      <c r="G1" s="59" t="inlineStr">
         <is>
           <t>240926</t>
         </is>
       </c>
-      <c r="K1" s="77" t="inlineStr">
+      <c r="H1" s="59" t="inlineStr">
         <is>
           <t>240925</t>
         </is>
       </c>
-      <c r="L1" s="77" t="inlineStr">
+      <c r="I1" s="59" t="inlineStr">
         <is>
           <t>240924</t>
         </is>
       </c>
-      <c r="M1" s="77" t="inlineStr">
+      <c r="J1" s="59" t="inlineStr">
         <is>
           <t>240923</t>
         </is>
       </c>
-      <c r="N1" s="77" t="inlineStr">
+      <c r="K1" s="59" t="inlineStr">
         <is>
           <t>240920</t>
         </is>
       </c>
-      <c r="O1" s="77" t="inlineStr">
+      <c r="L1" s="59" t="inlineStr">
         <is>
           <t>240919</t>
         </is>
       </c>
-      <c r="P1" s="77" t="inlineStr">
+      <c r="M1" s="59" t="inlineStr">
         <is>
           <t>240918</t>
         </is>
       </c>
-      <c r="Q1" s="77" t="inlineStr">
+      <c r="N1" s="59" t="inlineStr">
         <is>
           <t>240917</t>
         </is>
       </c>
-      <c r="R1" s="77" t="inlineStr">
+      <c r="O1" s="59" t="inlineStr">
         <is>
           <t>240916</t>
         </is>
       </c>
-      <c r="S1" s="77" t="inlineStr">
+      <c r="P1" s="59" t="inlineStr">
         <is>
           <t>240913</t>
         </is>
       </c>
-      <c r="T1" s="77" t="inlineStr">
+      <c r="Q1" s="59" t="inlineStr">
         <is>
           <t>240912</t>
         </is>
       </c>
-      <c r="U1" s="77" t="inlineStr">
+      <c r="R1" s="59" t="inlineStr">
         <is>
           <t>240911</t>
         </is>
       </c>
-      <c r="V1" s="77" t="inlineStr">
+      <c r="S1" s="59" t="inlineStr">
         <is>
           <t>240910</t>
         </is>
       </c>
-      <c r="W1" s="77" t="inlineStr">
+      <c r="T1" s="59" t="inlineStr">
         <is>
           <t>240909</t>
         </is>
       </c>
-      <c r="X1" s="77" t="inlineStr">
+      <c r="U1" s="59" t="inlineStr">
         <is>
           <t>240906</t>
         </is>
       </c>
-      <c r="Y1" s="77" t="inlineStr">
+      <c r="V1" s="59" t="inlineStr">
         <is>
           <t>240905</t>
         </is>
       </c>
-      <c r="Z1" s="77" t="inlineStr">
+      <c r="W1" s="59" t="inlineStr">
         <is>
           <t>240904</t>
         </is>
       </c>
-      <c r="AA1" s="77" t="inlineStr">
+      <c r="X1" s="59" t="inlineStr">
         <is>
           <t>240903</t>
         </is>
       </c>
-      <c r="AB1" s="77" t="inlineStr">
+      <c r="Y1" s="59" t="inlineStr">
         <is>
           <t>240902</t>
         </is>
       </c>
-      <c r="AC1" s="77" t="inlineStr">
+      <c r="Z1" s="59" t="inlineStr">
         <is>
           <t>240830</t>
         </is>
       </c>
-      <c r="AD1" s="77" t="inlineStr">
+      <c r="AA1" s="59" t="inlineStr">
         <is>
           <t>240829</t>
         </is>
       </c>
-      <c r="AE1" s="77" t="inlineStr">
+      <c r="AB1" s="59" t="inlineStr">
         <is>
           <t>240828</t>
         </is>
       </c>
+      <c r="AC1" s="59" t="inlineStr">
+        <is>
+          <t>240827</t>
+        </is>
+      </c>
+      <c r="AD1" s="59" t="inlineStr">
+        <is>
+          <t>240826</t>
+        </is>
+      </c>
+      <c r="AE1" s="59" t="inlineStr">
+        <is>
+          <t>240823</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="76" t="inlineStr">
+      <c r="A2" s="58" t="inlineStr">
         <is>
           <t>sh:EIDE</t>
         </is>
       </c>
-      <c r="B2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="C2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="D2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="E2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="F2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="G2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="H2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="I2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M2" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N2" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O2" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P2" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q2" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="R2" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="S2" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="T2" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="U2" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="V2" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="W2" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="X2" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y2" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z2" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA2" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB2" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC2" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD2" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE2" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
+      <c r="B2" s="60" t="n"/>
+      <c r="C2" s="60" t="n"/>
+      <c r="D2" s="60" t="n"/>
+      <c r="E2" s="60" t="n"/>
+      <c r="F2" s="60" t="n"/>
+      <c r="G2" s="60" t="n"/>
+      <c r="H2" s="60" t="n"/>
+      <c r="I2" s="60" t="n"/>
+      <c r="J2" s="60" t="n"/>
+      <c r="K2" s="60" t="n"/>
+      <c r="L2" s="60" t="n"/>
+      <c r="M2" s="60" t="n"/>
+      <c r="N2" s="60" t="n"/>
+      <c r="O2" s="60" t="n"/>
+      <c r="P2" s="60" t="n"/>
+      <c r="Q2" s="60" t="n"/>
+      <c r="R2" s="60" t="n"/>
+      <c r="S2" s="60" t="n"/>
+      <c r="T2" s="60" t="n"/>
+      <c r="U2" s="60" t="n"/>
+      <c r="V2" s="60" t="n"/>
+      <c r="W2" s="60" t="n"/>
+      <c r="X2" s="60" t="n"/>
+      <c r="Y2" s="60" t="n"/>
+      <c r="Z2" s="60" t="n"/>
+      <c r="AA2" s="60" t="n"/>
+      <c r="AB2" s="60" t="n"/>
+      <c r="AC2" s="60" t="n"/>
+      <c r="AD2" s="60" t="n"/>
+      <c r="AE2" s="60" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="82" t="inlineStr">
+      <c r="A3" s="58" t="inlineStr">
         <is>
           <t>sh:RNG60</t>
         </is>
       </c>
-      <c r="B3" s="95" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="C3" s="95" t="n">
-        <v>12.81</v>
-      </c>
-      <c r="D3" s="95" t="n">
-        <v>12.81</v>
-      </c>
-      <c r="E3" s="95" t="n">
-        <v>12.81</v>
-      </c>
-      <c r="F3" s="95" t="n">
-        <v>12.81</v>
-      </c>
-      <c r="G3" s="95" t="n">
-        <v>12.81</v>
-      </c>
-      <c r="H3" s="95" t="n">
-        <v>12.81</v>
-      </c>
-      <c r="I3" s="95" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="J3" s="95" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="K3" s="95" t="n">
-        <v>-3.29</v>
-      </c>
-      <c r="L3" s="95" t="n">
-        <v>-3.51</v>
-      </c>
-      <c r="M3" s="95" t="n">
-        <v>-6.68</v>
-      </c>
-      <c r="N3" s="95" t="n">
-        <v>-7.93</v>
-      </c>
-      <c r="O3" s="95" t="n">
-        <v>-7.25</v>
-      </c>
-      <c r="P3" s="95" t="n">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="Q3" s="95" t="n">
-        <v>-9.81</v>
-      </c>
-      <c r="R3" s="95" t="n">
-        <v>-9.81</v>
-      </c>
-      <c r="S3" s="95" t="n">
-        <v>-9.81</v>
-      </c>
-      <c r="T3" s="95" t="n">
-        <v>-9.59</v>
-      </c>
-      <c r="U3" s="95" t="n">
-        <v>-9.82</v>
-      </c>
-      <c r="V3" s="95" t="n">
-        <v>-9.44</v>
-      </c>
-      <c r="W3" s="95" t="n">
-        <v>-9.26</v>
-      </c>
-      <c r="X3" s="95" t="n">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="Y3" s="95" t="n">
-        <v>-7.94</v>
-      </c>
-      <c r="Z3" s="95" t="n">
-        <v>-8.34</v>
-      </c>
-      <c r="AA3" s="95" t="n">
-        <v>-7.43</v>
-      </c>
-      <c r="AB3" s="95" t="n">
-        <v>-7.87</v>
-      </c>
-      <c r="AC3" s="95" t="n">
-        <v>-6.78</v>
-      </c>
-      <c r="AD3" s="95" t="n">
-        <v>-7.9</v>
-      </c>
-      <c r="AE3" s="95" t="n">
-        <v>-8.210000000000001</v>
-      </c>
+      <c r="B3" s="60" t="n"/>
+      <c r="C3" s="60" t="n"/>
+      <c r="D3" s="60" t="n"/>
+      <c r="E3" s="60" t="n"/>
+      <c r="F3" s="60" t="n"/>
+      <c r="G3" s="60" t="n"/>
+      <c r="H3" s="60" t="n"/>
+      <c r="I3" s="60" t="n"/>
+      <c r="J3" s="60" t="n"/>
+      <c r="K3" s="60" t="n"/>
+      <c r="L3" s="60" t="n"/>
+      <c r="M3" s="60" t="n"/>
+      <c r="N3" s="60" t="n"/>
+      <c r="O3" s="60" t="n"/>
+      <c r="P3" s="60" t="n"/>
+      <c r="Q3" s="60" t="n"/>
+      <c r="R3" s="60" t="n"/>
+      <c r="S3" s="60" t="n"/>
+      <c r="T3" s="60" t="n"/>
+      <c r="U3" s="60" t="n"/>
+      <c r="V3" s="60" t="n"/>
+      <c r="W3" s="60" t="n"/>
+      <c r="X3" s="60" t="n"/>
+      <c r="Y3" s="60" t="n"/>
+      <c r="Z3" s="60" t="n"/>
+      <c r="AA3" s="60" t="n"/>
+      <c r="AB3" s="60" t="n"/>
+      <c r="AC3" s="60" t="n"/>
+      <c r="AD3" s="60" t="n"/>
+      <c r="AE3" s="60" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="76" t="inlineStr">
+      <c r="A4" s="58" t="inlineStr">
         <is>
           <t>sh:RNG120</t>
         </is>
       </c>
-      <c r="B4" s="95" t="n">
-        <v>14.53</v>
-      </c>
-      <c r="C4" s="95" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="D4" s="95" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="E4" s="95" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="F4" s="95" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="G4" s="95" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="H4" s="95" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="I4" s="95" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="J4" s="95" t="n">
-        <v>-2.48</v>
-      </c>
-      <c r="K4" s="95" t="n">
-        <v>-4.76</v>
-      </c>
-      <c r="L4" s="95" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="M4" s="95" t="n">
-        <v>-8.16</v>
-      </c>
-      <c r="N4" s="95" t="n">
-        <v>-9.720000000000001</v>
-      </c>
-      <c r="O4" s="95" t="n">
-        <v>-9.59</v>
-      </c>
-      <c r="P4" s="95" t="n">
-        <v>-10.85</v>
-      </c>
-      <c r="Q4" s="95" t="n">
-        <v>-12.12</v>
-      </c>
-      <c r="R4" s="95" t="n">
-        <v>-12.12</v>
-      </c>
-      <c r="S4" s="95" t="n">
-        <v>-12.12</v>
-      </c>
-      <c r="T4" s="95" t="n">
-        <v>-11.77</v>
-      </c>
-      <c r="U4" s="95" t="n">
-        <v>-11.13</v>
-      </c>
-      <c r="V4" s="95" t="n">
-        <v>-11.05</v>
-      </c>
-      <c r="W4" s="95" t="n">
-        <v>-10.42</v>
-      </c>
-      <c r="X4" s="95" t="n">
-        <v>-8.970000000000001</v>
-      </c>
-      <c r="Y4" s="95" t="n">
-        <v>-8.390000000000001</v>
-      </c>
-      <c r="Z4" s="95" t="n">
-        <v>-8.890000000000001</v>
-      </c>
-      <c r="AA4" s="95" t="n">
-        <v>-8.65</v>
-      </c>
-      <c r="AB4" s="95" t="n">
-        <v>-7.71</v>
-      </c>
-      <c r="AC4" s="95" t="n">
-        <v>-6.12</v>
-      </c>
-      <c r="AD4" s="95" t="n">
-        <v>-7.13</v>
-      </c>
-      <c r="AE4" s="95" t="n">
-        <v>-6.9</v>
-      </c>
+      <c r="B4" s="60" t="n"/>
+      <c r="C4" s="60" t="n"/>
+      <c r="D4" s="60" t="n"/>
+      <c r="E4" s="60" t="n"/>
+      <c r="F4" s="60" t="n"/>
+      <c r="G4" s="60" t="n"/>
+      <c r="H4" s="60" t="n"/>
+      <c r="I4" s="60" t="n"/>
+      <c r="J4" s="60" t="n"/>
+      <c r="K4" s="60" t="n"/>
+      <c r="L4" s="60" t="n"/>
+      <c r="M4" s="60" t="n"/>
+      <c r="N4" s="60" t="n"/>
+      <c r="O4" s="60" t="n"/>
+      <c r="P4" s="60" t="n"/>
+      <c r="Q4" s="60" t="n"/>
+      <c r="R4" s="60" t="n"/>
+      <c r="S4" s="60" t="n"/>
+      <c r="T4" s="60" t="n"/>
+      <c r="U4" s="60" t="n"/>
+      <c r="V4" s="60" t="n"/>
+      <c r="W4" s="60" t="n"/>
+      <c r="X4" s="60" t="n"/>
+      <c r="Y4" s="60" t="n"/>
+      <c r="Z4" s="60" t="n"/>
+      <c r="AA4" s="60" t="n"/>
+      <c r="AB4" s="60" t="n"/>
+      <c r="AC4" s="60" t="n"/>
+      <c r="AD4" s="60" t="n"/>
+      <c r="AE4" s="60" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="82" t="inlineStr">
-        <is>
-          <t>sh:RS3</t>
-        </is>
-      </c>
-      <c r="B5" s="95" t="n">
-        <v>99.84</v>
-      </c>
-      <c r="C5" s="95" t="n">
-        <v>99.75</v>
-      </c>
-      <c r="D5" s="95" t="n">
-        <v>99.75</v>
-      </c>
-      <c r="E5" s="95" t="n">
-        <v>99.75</v>
-      </c>
-      <c r="F5" s="95" t="n">
-        <v>99.75</v>
-      </c>
-      <c r="G5" s="95" t="n">
-        <v>99.75</v>
-      </c>
-      <c r="H5" s="95" t="n">
-        <v>99.75</v>
-      </c>
-      <c r="I5" s="95" t="n">
-        <v>99.31</v>
-      </c>
-      <c r="J5" s="95" t="n">
-        <v>98.83</v>
-      </c>
-      <c r="K5" s="95" t="n">
-        <v>97.34999999999999</v>
-      </c>
-      <c r="L5" s="95" t="n">
-        <v>96.38</v>
-      </c>
-      <c r="M5" s="95" t="n">
-        <v>77.51000000000001</v>
-      </c>
-      <c r="N5" s="95" t="n">
-        <v>64.38</v>
-      </c>
-      <c r="O5" s="95" t="n">
-        <v>63.45</v>
-      </c>
-      <c r="P5" s="95" t="n">
-        <v>37.85</v>
-      </c>
-      <c r="Q5" s="95" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="R5" s="95" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="S5" s="95" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="T5" s="95" t="n">
-        <v>10.95</v>
-      </c>
-      <c r="U5" s="95" t="n">
-        <v>12.36</v>
-      </c>
-      <c r="V5" s="95" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="W5" s="95" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="X5" s="95" t="n">
-        <v>11.48</v>
-      </c>
-      <c r="Y5" s="95" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="Z5" s="95" t="n">
-        <v>12.41</v>
-      </c>
-      <c r="AA5" s="95" t="n">
-        <v>19.88</v>
-      </c>
-      <c r="AB5" s="95" t="n">
-        <v>24.04</v>
-      </c>
-      <c r="AC5" s="95" t="n">
-        <v>52.18</v>
-      </c>
-      <c r="AD5" s="95" t="n">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="AE5" s="95" t="n">
-        <v>15.44</v>
-      </c>
+      <c r="A5" s="58" t="inlineStr">
+        <is>
+          <t>sh:RSI11</t>
+        </is>
+      </c>
+      <c r="B5" s="60" t="n"/>
+      <c r="C5" s="60" t="n"/>
+      <c r="D5" s="60" t="n"/>
+      <c r="E5" s="60" t="n"/>
+      <c r="F5" s="60" t="n"/>
+      <c r="G5" s="60" t="n"/>
+      <c r="H5" s="60" t="n"/>
+      <c r="I5" s="60" t="n"/>
+      <c r="J5" s="60" t="n"/>
+      <c r="K5" s="60" t="n"/>
+      <c r="L5" s="60" t="n"/>
+      <c r="M5" s="60" t="n"/>
+      <c r="N5" s="60" t="n"/>
+      <c r="O5" s="60" t="n"/>
+      <c r="P5" s="60" t="n"/>
+      <c r="Q5" s="60" t="n"/>
+      <c r="R5" s="60" t="n"/>
+      <c r="S5" s="60" t="n"/>
+      <c r="T5" s="60" t="n"/>
+      <c r="U5" s="60" t="n"/>
+      <c r="V5" s="60" t="n"/>
+      <c r="W5" s="60" t="n"/>
+      <c r="X5" s="60" t="n"/>
+      <c r="Y5" s="60" t="n"/>
+      <c r="Z5" s="60" t="n"/>
+      <c r="AA5" s="60" t="n"/>
+      <c r="AB5" s="60" t="n"/>
+      <c r="AC5" s="60" t="n"/>
+      <c r="AD5" s="60" t="n"/>
+      <c r="AE5" s="60" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="76" t="inlineStr">
+      <c r="A6" s="58" t="inlineStr">
         <is>
           <t>kc:EIDE</t>
         </is>
       </c>
-      <c r="B6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="C6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="D6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="E6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="F6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="G6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="H6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="I6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M6" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N6" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O6" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P6" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Q6" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R6" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S6" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T6" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U6" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V6" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W6" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="X6" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y6" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z6" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA6" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB6" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD6" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE6" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
+      <c r="B6" s="60" t="n"/>
+      <c r="C6" s="60" t="n"/>
+      <c r="D6" s="60" t="n"/>
+      <c r="E6" s="60" t="n"/>
+      <c r="F6" s="60" t="n"/>
+      <c r="G6" s="60" t="n"/>
+      <c r="H6" s="60" t="n"/>
+      <c r="I6" s="60" t="n"/>
+      <c r="J6" s="60" t="n"/>
+      <c r="K6" s="60" t="n"/>
+      <c r="L6" s="60" t="n"/>
+      <c r="M6" s="60" t="n"/>
+      <c r="N6" s="60" t="n"/>
+      <c r="O6" s="60" t="n"/>
+      <c r="P6" s="60" t="n"/>
+      <c r="Q6" s="60" t="n"/>
+      <c r="R6" s="60" t="n"/>
+      <c r="S6" s="60" t="n"/>
+      <c r="T6" s="60" t="n"/>
+      <c r="U6" s="60" t="n"/>
+      <c r="V6" s="60" t="n"/>
+      <c r="W6" s="60" t="n"/>
+      <c r="X6" s="60" t="n"/>
+      <c r="Y6" s="60" t="n"/>
+      <c r="Z6" s="60" t="n"/>
+      <c r="AA6" s="60" t="n"/>
+      <c r="AB6" s="60" t="n"/>
+      <c r="AC6" s="60" t="n"/>
+      <c r="AD6" s="60" t="n"/>
+      <c r="AE6" s="60" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="82" t="inlineStr">
+      <c r="A7" s="58" t="inlineStr">
         <is>
           <t>kc:RNG60</t>
         </is>
       </c>
-      <c r="B7" s="95" t="n">
-        <v>46.52</v>
-      </c>
-      <c r="C7" s="95" t="n">
-        <v>26.36</v>
-      </c>
-      <c r="D7" s="95" t="n">
-        <v>26.36</v>
-      </c>
-      <c r="E7" s="95" t="n">
-        <v>26.36</v>
-      </c>
-      <c r="F7" s="95" t="n">
-        <v>26.36</v>
-      </c>
-      <c r="G7" s="95" t="n">
-        <v>26.36</v>
-      </c>
-      <c r="H7" s="95" t="n">
-        <v>26.36</v>
-      </c>
-      <c r="I7" s="95" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="J7" s="95" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="K7" s="95" t="n">
-        <v>-5.96</v>
-      </c>
-      <c r="L7" s="95" t="n">
-        <v>-6.32</v>
-      </c>
-      <c r="M7" s="95" t="n">
-        <v>-10.11</v>
-      </c>
-      <c r="N7" s="95" t="n">
-        <v>-11.14</v>
-      </c>
-      <c r="O7" s="95" t="n">
-        <v>-9.23</v>
-      </c>
-      <c r="P7" s="95" t="n">
-        <v>-12.41</v>
-      </c>
-      <c r="Q7" s="95" t="n">
-        <v>-13.62</v>
-      </c>
-      <c r="R7" s="95" t="n">
-        <v>-13.62</v>
-      </c>
-      <c r="S7" s="95" t="n">
-        <v>-13.62</v>
-      </c>
-      <c r="T7" s="95" t="n">
-        <v>-12.75</v>
-      </c>
-      <c r="U7" s="95" t="n">
-        <v>-11.62</v>
-      </c>
-      <c r="V7" s="95" t="n">
-        <v>-12.8</v>
-      </c>
-      <c r="W7" s="95" t="n">
-        <v>-13.49</v>
-      </c>
-      <c r="X7" s="95" t="n">
-        <v>-12.19</v>
-      </c>
-      <c r="Y7" s="95" t="n">
-        <v>-11.56</v>
-      </c>
-      <c r="Z7" s="95" t="n">
-        <v>-10.95</v>
-      </c>
-      <c r="AA7" s="95" t="n">
-        <v>-10.7</v>
-      </c>
-      <c r="AB7" s="95" t="n">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="AC7" s="95" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AD7" s="95" t="n">
-        <v>-9.630000000000001</v>
-      </c>
-      <c r="AE7" s="95" t="n">
-        <v>-10.94</v>
-      </c>
+      <c r="B7" s="60" t="n"/>
+      <c r="C7" s="60" t="n"/>
+      <c r="D7" s="60" t="n"/>
+      <c r="E7" s="60" t="n"/>
+      <c r="F7" s="60" t="n"/>
+      <c r="G7" s="60" t="n"/>
+      <c r="H7" s="60" t="n"/>
+      <c r="I7" s="60" t="n"/>
+      <c r="J7" s="60" t="n"/>
+      <c r="K7" s="60" t="n"/>
+      <c r="L7" s="60" t="n"/>
+      <c r="M7" s="60" t="n"/>
+      <c r="N7" s="60" t="n"/>
+      <c r="O7" s="60" t="n"/>
+      <c r="P7" s="60" t="n"/>
+      <c r="Q7" s="60" t="n"/>
+      <c r="R7" s="60" t="n"/>
+      <c r="S7" s="60" t="n"/>
+      <c r="T7" s="60" t="n"/>
+      <c r="U7" s="60" t="n"/>
+      <c r="V7" s="60" t="n"/>
+      <c r="W7" s="60" t="n"/>
+      <c r="X7" s="60" t="n"/>
+      <c r="Y7" s="60" t="n"/>
+      <c r="Z7" s="60" t="n"/>
+      <c r="AA7" s="60" t="n"/>
+      <c r="AB7" s="60" t="n"/>
+      <c r="AC7" s="60" t="n"/>
+      <c r="AD7" s="60" t="n"/>
+      <c r="AE7" s="60" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="82" t="inlineStr">
+      <c r="A8" s="58" t="inlineStr">
         <is>
           <t>kc:RNG120</t>
         </is>
       </c>
-      <c r="B8" s="95" t="n">
-        <v>38.25</v>
-      </c>
-      <c r="C8" s="95" t="n">
-        <v>15.28</v>
-      </c>
-      <c r="D8" s="95" t="n">
-        <v>15.28</v>
-      </c>
-      <c r="E8" s="95" t="n">
-        <v>15.28</v>
-      </c>
-      <c r="F8" s="95" t="n">
-        <v>15.28</v>
-      </c>
-      <c r="G8" s="95" t="n">
-        <v>15.28</v>
-      </c>
-      <c r="H8" s="95" t="n">
-        <v>15.28</v>
-      </c>
-      <c r="I8" s="95" t="n">
-        <v>-3.74</v>
-      </c>
-      <c r="J8" s="95" t="n">
-        <v>-10.62</v>
-      </c>
-      <c r="K8" s="95" t="n">
-        <v>-12.51</v>
-      </c>
-      <c r="L8" s="95" t="n">
-        <v>-12.61</v>
-      </c>
-      <c r="M8" s="95" t="n">
-        <v>-14.58</v>
-      </c>
-      <c r="N8" s="95" t="n">
-        <v>-16.03</v>
-      </c>
-      <c r="O8" s="95" t="n">
-        <v>-16.65</v>
-      </c>
-      <c r="P8" s="95" t="n">
-        <v>-18.48</v>
-      </c>
-      <c r="Q8" s="95" t="n">
-        <v>-18.74</v>
-      </c>
-      <c r="R8" s="95" t="n">
-        <v>-18.74</v>
-      </c>
-      <c r="S8" s="95" t="n">
-        <v>-18.74</v>
-      </c>
-      <c r="T8" s="95" t="n">
-        <v>-19.06</v>
-      </c>
-      <c r="U8" s="95" t="n">
-        <v>-18.16</v>
-      </c>
-      <c r="V8" s="95" t="n">
-        <v>-20.04</v>
-      </c>
-      <c r="W8" s="95" t="n">
-        <v>-19.01</v>
-      </c>
-      <c r="X8" s="95" t="n">
-        <v>-17.71</v>
-      </c>
-      <c r="Y8" s="95" t="n">
-        <v>-17.63</v>
-      </c>
-      <c r="Z8" s="95" t="n">
-        <v>-17.79</v>
-      </c>
-      <c r="AA8" s="95" t="n">
-        <v>-17.53</v>
-      </c>
-      <c r="AB8" s="95" t="n">
-        <v>-16.58</v>
-      </c>
-      <c r="AC8" s="95" t="n">
-        <v>-12.6</v>
-      </c>
-      <c r="AD8" s="95" t="n">
-        <v>-16.3</v>
-      </c>
-      <c r="AE8" s="95" t="n">
-        <v>-17.92</v>
-      </c>
+      <c r="B8" s="60" t="n"/>
+      <c r="C8" s="60" t="n"/>
+      <c r="D8" s="60" t="n"/>
+      <c r="E8" s="60" t="n"/>
+      <c r="F8" s="60" t="n"/>
+      <c r="G8" s="60" t="n"/>
+      <c r="H8" s="60" t="n"/>
+      <c r="I8" s="60" t="n"/>
+      <c r="J8" s="60" t="n"/>
+      <c r="K8" s="60" t="n"/>
+      <c r="L8" s="60" t="n"/>
+      <c r="M8" s="60" t="n"/>
+      <c r="N8" s="60" t="n"/>
+      <c r="O8" s="60" t="n"/>
+      <c r="P8" s="60" t="n"/>
+      <c r="Q8" s="60" t="n"/>
+      <c r="R8" s="60" t="n"/>
+      <c r="S8" s="60" t="n"/>
+      <c r="T8" s="60" t="n"/>
+      <c r="U8" s="60" t="n"/>
+      <c r="V8" s="60" t="n"/>
+      <c r="W8" s="60" t="n"/>
+      <c r="X8" s="60" t="n"/>
+      <c r="Y8" s="60" t="n"/>
+      <c r="Z8" s="60" t="n"/>
+      <c r="AA8" s="60" t="n"/>
+      <c r="AB8" s="60" t="n"/>
+      <c r="AC8" s="60" t="n"/>
+      <c r="AD8" s="60" t="n"/>
+      <c r="AE8" s="60" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="82" t="inlineStr">
-        <is>
-          <t>kc:RS5</t>
-        </is>
-      </c>
-      <c r="B9" s="95" t="n">
-        <v>98.36</v>
-      </c>
-      <c r="C9" s="95" t="n">
-        <v>96.84</v>
-      </c>
-      <c r="D9" s="95" t="n">
-        <v>96.84</v>
-      </c>
-      <c r="E9" s="95" t="n">
-        <v>96.84</v>
-      </c>
-      <c r="F9" s="95" t="n">
-        <v>96.84</v>
-      </c>
-      <c r="G9" s="95" t="n">
-        <v>96.84</v>
-      </c>
-      <c r="H9" s="95" t="n">
-        <v>96.84</v>
-      </c>
-      <c r="I9" s="95" t="n">
-        <v>91.06999999999999</v>
-      </c>
-      <c r="J9" s="95" t="n">
-        <v>81.48999999999999</v>
-      </c>
-      <c r="K9" s="95" t="n">
-        <v>64.94</v>
-      </c>
-      <c r="L9" s="95" t="n">
-        <v>64.66</v>
-      </c>
-      <c r="M9" s="95" t="n">
-        <v>23.69</v>
-      </c>
-      <c r="N9" s="95" t="n">
-        <v>29.81</v>
-      </c>
-      <c r="O9" s="95" t="n">
-        <v>33.91</v>
-      </c>
-      <c r="P9" s="95" t="n">
-        <v>22.82</v>
-      </c>
-      <c r="Q9" s="95" t="n">
-        <v>30.54</v>
-      </c>
-      <c r="R9" s="95" t="n">
-        <v>30.54</v>
-      </c>
-      <c r="S9" s="95" t="n">
-        <v>30.54</v>
-      </c>
-      <c r="T9" s="95" t="n">
-        <v>35.28</v>
-      </c>
-      <c r="U9" s="95" t="n">
-        <v>42.99</v>
-      </c>
-      <c r="V9" s="95" t="n">
-        <v>33.88</v>
-      </c>
-      <c r="W9" s="95" t="n">
-        <v>22.22</v>
-      </c>
-      <c r="X9" s="95" t="n">
-        <v>27.98</v>
-      </c>
-      <c r="Y9" s="95" t="n">
-        <v>37.32</v>
-      </c>
-      <c r="Z9" s="95" t="n">
-        <v>38.49</v>
-      </c>
-      <c r="AA9" s="95" t="n">
-        <v>41.22</v>
-      </c>
-      <c r="AB9" s="95" t="n">
-        <v>34.35</v>
-      </c>
-      <c r="AC9" s="95" t="n">
-        <v>63.18</v>
-      </c>
-      <c r="AD9" s="95" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="AE9" s="95" t="n">
-        <v>9.880000000000001</v>
-      </c>
+      <c r="A9" s="58" t="inlineStr">
+        <is>
+          <t>kc:RSI10</t>
+        </is>
+      </c>
+      <c r="B9" s="60" t="n"/>
+      <c r="C9" s="60" t="n"/>
+      <c r="D9" s="60" t="n"/>
+      <c r="E9" s="60" t="n"/>
+      <c r="F9" s="60" t="n"/>
+      <c r="G9" s="60" t="n"/>
+      <c r="H9" s="60" t="n"/>
+      <c r="I9" s="60" t="n"/>
+      <c r="J9" s="60" t="n"/>
+      <c r="K9" s="60" t="n"/>
+      <c r="L9" s="60" t="n"/>
+      <c r="M9" s="60" t="n"/>
+      <c r="N9" s="60" t="n"/>
+      <c r="O9" s="60" t="n"/>
+      <c r="P9" s="60" t="n"/>
+      <c r="Q9" s="60" t="n"/>
+      <c r="R9" s="60" t="n"/>
+      <c r="S9" s="60" t="n"/>
+      <c r="T9" s="60" t="n"/>
+      <c r="U9" s="60" t="n"/>
+      <c r="V9" s="60" t="n"/>
+      <c r="W9" s="60" t="n"/>
+      <c r="X9" s="60" t="n"/>
+      <c r="Y9" s="60" t="n"/>
+      <c r="Z9" s="60" t="n"/>
+      <c r="AA9" s="60" t="n"/>
+      <c r="AB9" s="60" t="n"/>
+      <c r="AC9" s="60" t="n"/>
+      <c r="AD9" s="60" t="n"/>
+      <c r="AE9" s="60" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="76" t="inlineStr">
+      <c r="A10" s="58" t="inlineStr">
         <is>
           <t>cy:EIDE</t>
         </is>
       </c>
-      <c r="B10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="C10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="D10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="E10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="F10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="G10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="H10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="I10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M10" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N10" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="O10" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P10" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Q10" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="R10" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="S10" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="T10" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V10" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="W10" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="X10" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z10" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA10" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB10" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD10" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE10" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
+      <c r="B10" s="60" t="n"/>
+      <c r="C10" s="60" t="n"/>
+      <c r="D10" s="60" t="n"/>
+      <c r="E10" s="60" t="n"/>
+      <c r="F10" s="60" t="n"/>
+      <c r="G10" s="60" t="n"/>
+      <c r="H10" s="60" t="n"/>
+      <c r="I10" s="60" t="n"/>
+      <c r="J10" s="60" t="n"/>
+      <c r="K10" s="60" t="n"/>
+      <c r="L10" s="60" t="n"/>
+      <c r="M10" s="60" t="n"/>
+      <c r="N10" s="60" t="n"/>
+      <c r="O10" s="60" t="n"/>
+      <c r="P10" s="60" t="n"/>
+      <c r="Q10" s="60" t="n"/>
+      <c r="R10" s="60" t="n"/>
+      <c r="S10" s="60" t="n"/>
+      <c r="T10" s="60" t="n"/>
+      <c r="U10" s="60" t="n"/>
+      <c r="V10" s="60" t="n"/>
+      <c r="W10" s="60" t="n"/>
+      <c r="X10" s="60" t="n"/>
+      <c r="Y10" s="60" t="n"/>
+      <c r="Z10" s="60" t="n"/>
+      <c r="AA10" s="60" t="n"/>
+      <c r="AB10" s="60" t="n"/>
+      <c r="AC10" s="60" t="n"/>
+      <c r="AD10" s="60" t="n"/>
+      <c r="AE10" s="60" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="82" t="inlineStr">
+      <c r="A11" s="58" t="inlineStr">
         <is>
           <t>cy:RNG60</t>
         </is>
       </c>
-      <c r="B11" s="95" t="n">
-        <v>54.04</v>
-      </c>
-      <c r="C11" s="95" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="D11" s="95" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="E11" s="95" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="F11" s="95" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="G11" s="95" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="H11" s="95" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="I11" s="95" t="n">
-        <v>13.58</v>
-      </c>
-      <c r="J11" s="95" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="K11" s="95" t="n">
-        <v>-2.45</v>
-      </c>
-      <c r="L11" s="95" t="n">
-        <v>-4.05</v>
-      </c>
-      <c r="M11" s="95" t="n">
-        <v>-10.14</v>
-      </c>
-      <c r="N11" s="95" t="n">
-        <v>-11.21</v>
-      </c>
-      <c r="O11" s="95" t="n">
-        <v>-9.029999999999999</v>
-      </c>
-      <c r="P11" s="95" t="n">
-        <v>-11.44</v>
-      </c>
-      <c r="Q11" s="95" t="n">
-        <v>-12.57</v>
-      </c>
-      <c r="R11" s="95" t="n">
-        <v>-12.57</v>
-      </c>
-      <c r="S11" s="95" t="n">
-        <v>-12.57</v>
-      </c>
-      <c r="T11" s="95" t="n">
-        <v>-11.96</v>
-      </c>
-      <c r="U11" s="95" t="n">
-        <v>-12.87</v>
-      </c>
-      <c r="V11" s="95" t="n">
-        <v>-14.98</v>
-      </c>
-      <c r="W11" s="95" t="n">
-        <v>-14.79</v>
-      </c>
-      <c r="X11" s="95" t="n">
-        <v>-14.14</v>
-      </c>
-      <c r="Y11" s="95" t="n">
-        <v>-11.99</v>
-      </c>
-      <c r="Z11" s="95" t="n">
-        <v>-12.63</v>
-      </c>
-      <c r="AA11" s="95" t="n">
-        <v>-12.92</v>
-      </c>
-      <c r="AB11" s="95" t="n">
-        <v>-13.71</v>
-      </c>
-      <c r="AC11" s="95" t="n">
-        <v>-13.18</v>
-      </c>
-      <c r="AD11" s="95" t="n">
-        <v>-15.93</v>
-      </c>
-      <c r="AE11" s="95" t="n">
-        <v>-16.93</v>
-      </c>
+      <c r="B11" s="60" t="n"/>
+      <c r="C11" s="60" t="n"/>
+      <c r="D11" s="60" t="n"/>
+      <c r="E11" s="60" t="n"/>
+      <c r="F11" s="60" t="n"/>
+      <c r="G11" s="60" t="n"/>
+      <c r="H11" s="60" t="n"/>
+      <c r="I11" s="60" t="n"/>
+      <c r="J11" s="60" t="n"/>
+      <c r="K11" s="60" t="n"/>
+      <c r="L11" s="60" t="n"/>
+      <c r="M11" s="60" t="n"/>
+      <c r="N11" s="60" t="n"/>
+      <c r="O11" s="60" t="n"/>
+      <c r="P11" s="60" t="n"/>
+      <c r="Q11" s="60" t="n"/>
+      <c r="R11" s="60" t="n"/>
+      <c r="S11" s="60" t="n"/>
+      <c r="T11" s="60" t="n"/>
+      <c r="U11" s="60" t="n"/>
+      <c r="V11" s="60" t="n"/>
+      <c r="W11" s="60" t="n"/>
+      <c r="X11" s="60" t="n"/>
+      <c r="Y11" s="60" t="n"/>
+      <c r="Z11" s="60" t="n"/>
+      <c r="AA11" s="60" t="n"/>
+      <c r="AB11" s="60" t="n"/>
+      <c r="AC11" s="60" t="n"/>
+      <c r="AD11" s="60" t="n"/>
+      <c r="AE11" s="60" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="82" t="inlineStr">
+      <c r="A12" s="58" t="inlineStr">
         <is>
           <t>cy:RNG120</t>
         </is>
       </c>
-      <c r="B12" s="95" t="n">
-        <v>41.13</v>
-      </c>
-      <c r="C12" s="95" t="n">
-        <v>18.19</v>
-      </c>
-      <c r="D12" s="95" t="n">
-        <v>18.19</v>
-      </c>
-      <c r="E12" s="95" t="n">
-        <v>18.19</v>
-      </c>
-      <c r="F12" s="95" t="n">
-        <v>18.19</v>
-      </c>
-      <c r="G12" s="95" t="n">
-        <v>18.19</v>
-      </c>
-      <c r="H12" s="95" t="n">
-        <v>18.19</v>
-      </c>
-      <c r="I12" s="95" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="J12" s="95" t="n">
-        <v>-8.44</v>
-      </c>
-      <c r="K12" s="95" t="n">
-        <v>-9.720000000000001</v>
-      </c>
-      <c r="L12" s="95" t="n">
-        <v>-10.6</v>
-      </c>
-      <c r="M12" s="95" t="n">
-        <v>-14.49</v>
-      </c>
-      <c r="N12" s="95" t="n">
-        <v>-16.56</v>
-      </c>
-      <c r="O12" s="95" t="n">
-        <v>-15.65</v>
-      </c>
-      <c r="P12" s="95" t="n">
-        <v>-17.96</v>
-      </c>
-      <c r="Q12" s="95" t="n">
-        <v>-19.08</v>
-      </c>
-      <c r="R12" s="95" t="n">
-        <v>-19.08</v>
-      </c>
-      <c r="S12" s="95" t="n">
-        <v>-19.08</v>
-      </c>
-      <c r="T12" s="95" t="n">
-        <v>-18.72</v>
-      </c>
-      <c r="U12" s="95" t="n">
-        <v>-18.28</v>
-      </c>
-      <c r="V12" s="95" t="n">
-        <v>-20.06</v>
-      </c>
-      <c r="W12" s="95" t="n">
-        <v>-18.31</v>
-      </c>
-      <c r="X12" s="95" t="n">
-        <v>-18.32</v>
-      </c>
-      <c r="Y12" s="95" t="n">
-        <v>-17.44</v>
-      </c>
-      <c r="Z12" s="95" t="n">
-        <v>-18.44</v>
-      </c>
-      <c r="AA12" s="95" t="n">
-        <v>-17.67</v>
-      </c>
-      <c r="AB12" s="95" t="n">
-        <v>-14.96</v>
-      </c>
-      <c r="AC12" s="95" t="n">
-        <v>-11.7</v>
-      </c>
-      <c r="AD12" s="95" t="n">
-        <v>-15.89</v>
-      </c>
-      <c r="AE12" s="95" t="n">
-        <v>-16.48</v>
-      </c>
+      <c r="B12" s="60" t="n"/>
+      <c r="C12" s="60" t="n"/>
+      <c r="D12" s="60" t="n"/>
+      <c r="E12" s="60" t="n"/>
+      <c r="F12" s="60" t="n"/>
+      <c r="G12" s="60" t="n"/>
+      <c r="H12" s="60" t="n"/>
+      <c r="I12" s="60" t="n"/>
+      <c r="J12" s="60" t="n"/>
+      <c r="K12" s="60" t="n"/>
+      <c r="L12" s="60" t="n"/>
+      <c r="M12" s="60" t="n"/>
+      <c r="N12" s="60" t="n"/>
+      <c r="O12" s="60" t="n"/>
+      <c r="P12" s="60" t="n"/>
+      <c r="Q12" s="60" t="n"/>
+      <c r="R12" s="60" t="n"/>
+      <c r="S12" s="60" t="n"/>
+      <c r="T12" s="60" t="n"/>
+      <c r="U12" s="60" t="n"/>
+      <c r="V12" s="60" t="n"/>
+      <c r="W12" s="60" t="n"/>
+      <c r="X12" s="60" t="n"/>
+      <c r="Y12" s="60" t="n"/>
+      <c r="Z12" s="60" t="n"/>
+      <c r="AA12" s="60" t="n"/>
+      <c r="AB12" s="60" t="n"/>
+      <c r="AC12" s="60" t="n"/>
+      <c r="AD12" s="60" t="n"/>
+      <c r="AE12" s="60" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="82" t="inlineStr">
-        <is>
-          <t>cy:RS3</t>
-        </is>
-      </c>
-      <c r="B13" s="95" t="n">
-        <v>99.77</v>
-      </c>
-      <c r="C13" s="95" t="n">
-        <v>99.48</v>
-      </c>
-      <c r="D13" s="95" t="n">
-        <v>99.48</v>
-      </c>
-      <c r="E13" s="95" t="n">
-        <v>99.48</v>
-      </c>
-      <c r="F13" s="95" t="n">
-        <v>99.48</v>
-      </c>
-      <c r="G13" s="95" t="n">
-        <v>99.48</v>
-      </c>
-      <c r="H13" s="95" t="n">
-        <v>99.48</v>
-      </c>
-      <c r="I13" s="95" t="n">
-        <v>98.62</v>
-      </c>
-      <c r="J13" s="95" t="n">
-        <v>96</v>
-      </c>
-      <c r="K13" s="95" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="L13" s="95" t="n">
-        <v>88.09</v>
-      </c>
-      <c r="M13" s="95" t="n">
-        <v>30.34</v>
-      </c>
-      <c r="N13" s="95" t="n">
-        <v>39.51</v>
-      </c>
-      <c r="O13" s="95" t="n">
-        <v>58.67</v>
-      </c>
-      <c r="P13" s="95" t="n">
-        <v>28.04</v>
-      </c>
-      <c r="Q13" s="95" t="n">
-        <v>29.98</v>
-      </c>
-      <c r="R13" s="95" t="n">
-        <v>29.98</v>
-      </c>
-      <c r="S13" s="95" t="n">
-        <v>29.98</v>
-      </c>
-      <c r="T13" s="95" t="n">
-        <v>54.57</v>
-      </c>
-      <c r="U13" s="95" t="n">
-        <v>69.45</v>
-      </c>
-      <c r="V13" s="95" t="n">
-        <v>37.43</v>
-      </c>
-      <c r="W13" s="95" t="n">
-        <v>35.11</v>
-      </c>
-      <c r="X13" s="95" t="n">
-        <v>33.41</v>
-      </c>
-      <c r="Y13" s="95" t="n">
-        <v>64.26000000000001</v>
-      </c>
-      <c r="Z13" s="95" t="n">
-        <v>53.41</v>
-      </c>
-      <c r="AA13" s="95" t="n">
-        <v>55.28</v>
-      </c>
-      <c r="AB13" s="95" t="n">
-        <v>38.88</v>
-      </c>
-      <c r="AC13" s="95" t="n">
-        <v>86.18000000000001</v>
-      </c>
-      <c r="AD13" s="95" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="AE13" s="95" t="n">
-        <v>6.86</v>
-      </c>
+      <c r="A13" s="58" t="inlineStr">
+        <is>
+          <t>cy:RSI10</t>
+        </is>
+      </c>
+      <c r="B13" s="60" t="n"/>
+      <c r="C13" s="60" t="n"/>
+      <c r="D13" s="60" t="n"/>
+      <c r="E13" s="60" t="n"/>
+      <c r="F13" s="60" t="n"/>
+      <c r="G13" s="60" t="n"/>
+      <c r="H13" s="60" t="n"/>
+      <c r="I13" s="60" t="n"/>
+      <c r="J13" s="60" t="n"/>
+      <c r="K13" s="60" t="n"/>
+      <c r="L13" s="60" t="n"/>
+      <c r="M13" s="60" t="n"/>
+      <c r="N13" s="60" t="n"/>
+      <c r="O13" s="60" t="n"/>
+      <c r="P13" s="60" t="n"/>
+      <c r="Q13" s="60" t="n"/>
+      <c r="R13" s="60" t="n"/>
+      <c r="S13" s="60" t="n"/>
+      <c r="T13" s="60" t="n"/>
+      <c r="U13" s="60" t="n"/>
+      <c r="V13" s="60" t="n"/>
+      <c r="W13" s="60" t="n"/>
+      <c r="X13" s="60" t="n"/>
+      <c r="Y13" s="60" t="n"/>
+      <c r="Z13" s="60" t="n"/>
+      <c r="AA13" s="60" t="n"/>
+      <c r="AB13" s="60" t="n"/>
+      <c r="AC13" s="60" t="n"/>
+      <c r="AD13" s="60" t="n"/>
+      <c r="AE13" s="60" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="76" t="inlineStr">
+      <c r="A14" s="58" t="inlineStr">
         <is>
           <t>hk50:EIDE</t>
         </is>
       </c>
-      <c r="B14" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="C14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="D14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="E14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="F14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="G14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="H14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="I14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S14" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T14" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U14" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="V14" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="W14" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="X14" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y14" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z14" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA14" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB14" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD14" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE14" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
+      <c r="B14" s="60" t="n"/>
+      <c r="C14" s="60" t="n"/>
+      <c r="D14" s="60" t="n"/>
+      <c r="E14" s="60" t="n"/>
+      <c r="F14" s="60" t="n"/>
+      <c r="G14" s="60" t="n"/>
+      <c r="H14" s="60" t="n"/>
+      <c r="I14" s="60" t="n"/>
+      <c r="J14" s="60" t="n"/>
+      <c r="K14" s="60" t="n"/>
+      <c r="L14" s="60" t="n"/>
+      <c r="M14" s="60" t="n"/>
+      <c r="N14" s="60" t="n"/>
+      <c r="O14" s="60" t="n"/>
+      <c r="P14" s="60" t="n"/>
+      <c r="Q14" s="60" t="n"/>
+      <c r="R14" s="60" t="n"/>
+      <c r="S14" s="60" t="n"/>
+      <c r="T14" s="60" t="n"/>
+      <c r="U14" s="60" t="n"/>
+      <c r="V14" s="60" t="n"/>
+      <c r="W14" s="60" t="n"/>
+      <c r="X14" s="60" t="n"/>
+      <c r="Y14" s="60" t="n"/>
+      <c r="Z14" s="60" t="n"/>
+      <c r="AA14" s="60" t="n"/>
+      <c r="AB14" s="60" t="n"/>
+      <c r="AC14" s="60" t="n"/>
+      <c r="AD14" s="60" t="n"/>
+      <c r="AE14" s="60" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="82" t="inlineStr">
+      <c r="A15" s="58" t="inlineStr">
         <is>
           <t>hk50:RNG60</t>
         </is>
       </c>
-      <c r="B15" s="95" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="C15" s="95" t="n">
-        <v>32.21</v>
-      </c>
-      <c r="D15" s="95" t="n">
-        <v>29.75</v>
-      </c>
-      <c r="E15" s="95" t="n">
-        <v>26.19</v>
-      </c>
-      <c r="F15" s="95" t="n">
-        <v>26.09</v>
-      </c>
-      <c r="G15" s="95" t="n">
-        <v>17.23</v>
-      </c>
-      <c r="H15" s="95" t="n">
-        <v>17.23</v>
-      </c>
-      <c r="I15" s="95" t="n">
-        <v>14.76</v>
-      </c>
-      <c r="J15" s="95" t="n">
-        <v>12.13</v>
-      </c>
-      <c r="K15" s="95" t="n">
-        <v>7.96</v>
-      </c>
-      <c r="L15" s="95" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="M15" s="95" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="N15" s="95" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="O15" s="95" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="P15" s="95" t="n">
-        <v>-2.04</v>
-      </c>
-      <c r="Q15" s="95" t="n">
-        <v>-2.04</v>
-      </c>
-      <c r="R15" s="95" t="n">
-        <v>-4.98</v>
-      </c>
-      <c r="S15" s="95" t="n">
-        <v>-5.76</v>
-      </c>
-      <c r="T15" s="95" t="n">
-        <v>-3.77</v>
-      </c>
-      <c r="U15" s="95" t="n">
-        <v>-4.61</v>
-      </c>
-      <c r="V15" s="95" t="n">
-        <v>-3.94</v>
-      </c>
-      <c r="W15" s="95" t="n">
-        <v>-5.06</v>
-      </c>
-      <c r="X15" s="95" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="Y15" s="95" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="Z15" s="95" t="n">
-        <v>-3.96</v>
-      </c>
-      <c r="AA15" s="95" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="AB15" s="95" t="n">
-        <v>-4.25</v>
-      </c>
-      <c r="AC15" s="95" t="n">
-        <v>-2.37</v>
-      </c>
-      <c r="AD15" s="95" t="n">
-        <v>-3.57</v>
-      </c>
-      <c r="AE15" s="95" t="n">
-        <v>-3.86</v>
-      </c>
+      <c r="B15" s="60" t="n"/>
+      <c r="C15" s="60" t="n"/>
+      <c r="D15" s="60" t="n"/>
+      <c r="E15" s="60" t="n"/>
+      <c r="F15" s="60" t="n"/>
+      <c r="G15" s="60" t="n"/>
+      <c r="H15" s="60" t="n"/>
+      <c r="I15" s="60" t="n"/>
+      <c r="J15" s="60" t="n"/>
+      <c r="K15" s="60" t="n"/>
+      <c r="L15" s="60" t="n"/>
+      <c r="M15" s="60" t="n"/>
+      <c r="N15" s="60" t="n"/>
+      <c r="O15" s="60" t="n"/>
+      <c r="P15" s="60" t="n"/>
+      <c r="Q15" s="60" t="n"/>
+      <c r="R15" s="60" t="n"/>
+      <c r="S15" s="60" t="n"/>
+      <c r="T15" s="60" t="n"/>
+      <c r="U15" s="60" t="n"/>
+      <c r="V15" s="60" t="n"/>
+      <c r="W15" s="60" t="n"/>
+      <c r="X15" s="60" t="n"/>
+      <c r="Y15" s="60" t="n"/>
+      <c r="Z15" s="60" t="n"/>
+      <c r="AA15" s="60" t="n"/>
+      <c r="AB15" s="60" t="n"/>
+      <c r="AC15" s="60" t="n"/>
+      <c r="AD15" s="60" t="n"/>
+      <c r="AE15" s="60" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="82" t="inlineStr">
+      <c r="A16" s="58" t="inlineStr">
         <is>
           <t>hk50:RNG120</t>
         </is>
       </c>
-      <c r="B16" s="95" t="n">
-        <v>25.15</v>
-      </c>
-      <c r="C16" s="95" t="n">
-        <v>35.13</v>
-      </c>
-      <c r="D16" s="95" t="n">
-        <v>32.66</v>
-      </c>
-      <c r="E16" s="95" t="n">
-        <v>31.41</v>
-      </c>
-      <c r="F16" s="95" t="n">
-        <v>34.13</v>
-      </c>
-      <c r="G16" s="95" t="n">
-        <v>26.37</v>
-      </c>
-      <c r="H16" s="95" t="n">
-        <v>26.37</v>
-      </c>
-      <c r="I16" s="95" t="n">
-        <v>23.36</v>
-      </c>
-      <c r="J16" s="95" t="n">
-        <v>17.68</v>
-      </c>
-      <c r="K16" s="95" t="n">
-        <v>15.64</v>
-      </c>
-      <c r="L16" s="95" t="n">
-        <v>15.91</v>
-      </c>
-      <c r="M16" s="95" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="N16" s="95" t="n">
-        <v>10.84</v>
-      </c>
-      <c r="O16" s="95" t="n">
-        <v>9.17</v>
-      </c>
-      <c r="P16" s="95" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="Q16" s="95" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="R16" s="95" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="S16" s="95" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="T16" s="95" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="U16" s="95" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V16" s="95" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W16" s="95" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="X16" s="95" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y16" s="95" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z16" s="95" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="AA16" s="95" t="n">
-        <v>7.94</v>
-      </c>
-      <c r="AB16" s="95" t="n">
-        <v>9.01</v>
-      </c>
-      <c r="AC16" s="95" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="AD16" s="95" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="AE16" s="95" t="n">
-        <v>6.61</v>
-      </c>
+      <c r="B16" s="60" t="n"/>
+      <c r="C16" s="60" t="n"/>
+      <c r="D16" s="60" t="n"/>
+      <c r="E16" s="60" t="n"/>
+      <c r="F16" s="60" t="n"/>
+      <c r="G16" s="60" t="n"/>
+      <c r="H16" s="60" t="n"/>
+      <c r="I16" s="60" t="n"/>
+      <c r="J16" s="60" t="n"/>
+      <c r="K16" s="60" t="n"/>
+      <c r="L16" s="60" t="n"/>
+      <c r="M16" s="60" t="n"/>
+      <c r="N16" s="60" t="n"/>
+      <c r="O16" s="60" t="n"/>
+      <c r="P16" s="60" t="n"/>
+      <c r="Q16" s="60" t="n"/>
+      <c r="R16" s="60" t="n"/>
+      <c r="S16" s="60" t="n"/>
+      <c r="T16" s="60" t="n"/>
+      <c r="U16" s="60" t="n"/>
+      <c r="V16" s="60" t="n"/>
+      <c r="W16" s="60" t="n"/>
+      <c r="X16" s="60" t="n"/>
+      <c r="Y16" s="60" t="n"/>
+      <c r="Z16" s="60" t="n"/>
+      <c r="AA16" s="60" t="n"/>
+      <c r="AB16" s="60" t="n"/>
+      <c r="AC16" s="60" t="n"/>
+      <c r="AD16" s="60" t="n"/>
+      <c r="AE16" s="60" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="76" t="inlineStr">
-        <is>
-          <t>hk50:RS4</t>
-        </is>
-      </c>
-      <c r="B17" s="95" t="n">
-        <v>39.14</v>
-      </c>
-      <c r="C17" s="95" t="n">
-        <v>91.23999999999999</v>
-      </c>
-      <c r="D17" s="95" t="n">
-        <v>89.48999999999999</v>
-      </c>
-      <c r="E17" s="95" t="n">
-        <v>85.84</v>
-      </c>
-      <c r="F17" s="95" t="n">
-        <v>99.56999999999999</v>
-      </c>
-      <c r="G17" s="95" t="n">
-        <v>99.18000000000001</v>
-      </c>
-      <c r="H17" s="95" t="n">
-        <v>99.18000000000001</v>
-      </c>
-      <c r="I17" s="95" t="n">
-        <v>98.89</v>
-      </c>
-      <c r="J17" s="95" t="n">
-        <v>98.23</v>
-      </c>
-      <c r="K17" s="95" t="n">
-        <v>96.44</v>
-      </c>
-      <c r="L17" s="95" t="n">
-        <v>95.94</v>
-      </c>
-      <c r="M17" s="95" t="n">
-        <v>89.48</v>
-      </c>
-      <c r="N17" s="95" t="n">
-        <v>91.13</v>
-      </c>
-      <c r="O17" s="95" t="n">
-        <v>87.39</v>
-      </c>
-      <c r="P17" s="95" t="n">
-        <v>76.86</v>
-      </c>
-      <c r="Q17" s="95" t="n">
-        <v>76.86</v>
-      </c>
-      <c r="R17" s="95" t="n">
-        <v>59.96</v>
-      </c>
-      <c r="S17" s="95" t="n">
-        <v>54.39</v>
-      </c>
-      <c r="T17" s="95" t="n">
-        <v>38.93</v>
-      </c>
-      <c r="U17" s="95" t="n">
-        <v>17.46</v>
-      </c>
-      <c r="V17" s="95" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="W17" s="95" t="n">
-        <v>17.15</v>
-      </c>
-      <c r="X17" s="95" t="n">
-        <v>28.67</v>
-      </c>
-      <c r="Y17" s="95" t="n">
-        <v>28.67</v>
-      </c>
-      <c r="Z17" s="95" t="n">
-        <v>29.45</v>
-      </c>
-      <c r="AA17" s="95" t="n">
-        <v>42.37</v>
-      </c>
-      <c r="AB17" s="95" t="n">
-        <v>45.49</v>
-      </c>
-      <c r="AC17" s="95" t="n">
-        <v>76.48999999999999</v>
-      </c>
-      <c r="AD17" s="95" t="n">
-        <v>63.9</v>
-      </c>
-      <c r="AE17" s="95" t="n">
-        <v>55.65</v>
-      </c>
+      <c r="A17" s="58" t="inlineStr">
+        <is>
+          <t>hk50:RSI6</t>
+        </is>
+      </c>
+      <c r="B17" s="60" t="n"/>
+      <c r="C17" s="60" t="n"/>
+      <c r="D17" s="60" t="n"/>
+      <c r="E17" s="60" t="n"/>
+      <c r="F17" s="60" t="n"/>
+      <c r="G17" s="60" t="n"/>
+      <c r="H17" s="60" t="n"/>
+      <c r="I17" s="60" t="n"/>
+      <c r="J17" s="60" t="n"/>
+      <c r="K17" s="60" t="n"/>
+      <c r="L17" s="60" t="n"/>
+      <c r="M17" s="60" t="n"/>
+      <c r="N17" s="60" t="n"/>
+      <c r="O17" s="60" t="n"/>
+      <c r="P17" s="60" t="n"/>
+      <c r="Q17" s="60" t="n"/>
+      <c r="R17" s="60" t="n"/>
+      <c r="S17" s="60" t="n"/>
+      <c r="T17" s="60" t="n"/>
+      <c r="U17" s="60" t="n"/>
+      <c r="V17" s="60" t="n"/>
+      <c r="W17" s="60" t="n"/>
+      <c r="X17" s="60" t="n"/>
+      <c r="Y17" s="60" t="n"/>
+      <c r="Z17" s="60" t="n"/>
+      <c r="AA17" s="60" t="n"/>
+      <c r="AB17" s="60" t="n"/>
+      <c r="AC17" s="60" t="n"/>
+      <c r="AD17" s="60" t="n"/>
+      <c r="AE17" s="60" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="76" t="inlineStr">
+      <c r="A18" s="58" t="inlineStr">
         <is>
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="C18" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="D18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="E18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="F18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="G18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="H18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="I18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="J18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="K18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="L18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W18" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="X18" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y18" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z18" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA18" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
+      <c r="B18" s="60" t="n"/>
+      <c r="C18" s="60" t="n"/>
+      <c r="D18" s="60" t="n"/>
+      <c r="E18" s="60" t="n"/>
+      <c r="F18" s="60" t="n"/>
+      <c r="G18" s="60" t="n"/>
+      <c r="H18" s="60" t="n"/>
+      <c r="I18" s="60" t="n"/>
+      <c r="J18" s="60" t="n"/>
+      <c r="K18" s="60" t="n"/>
+      <c r="L18" s="60" t="n"/>
+      <c r="M18" s="60" t="n"/>
+      <c r="N18" s="60" t="n"/>
+      <c r="O18" s="60" t="n"/>
+      <c r="P18" s="60" t="n"/>
+      <c r="Q18" s="60" t="n"/>
+      <c r="R18" s="60" t="n"/>
+      <c r="S18" s="60" t="n"/>
+      <c r="T18" s="60" t="n"/>
+      <c r="U18" s="60" t="n"/>
+      <c r="V18" s="60" t="n"/>
+      <c r="W18" s="60" t="n"/>
+      <c r="X18" s="60" t="n"/>
+      <c r="Y18" s="60" t="n"/>
+      <c r="Z18" s="60" t="n"/>
+      <c r="AA18" s="60" t="n"/>
+      <c r="AB18" s="60" t="n"/>
+      <c r="AC18" s="60" t="n"/>
+      <c r="AD18" s="60" t="n"/>
+      <c r="AE18" s="60" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="76" t="inlineStr">
+      <c r="A19" s="58" t="inlineStr">
         <is>
           <t>us500:RNG60</t>
         </is>
       </c>
-      <c r="B19" s="95" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="C19" s="95" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="D19" s="95" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="E19" s="95" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="F19" s="95" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="G19" s="95" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="H19" s="95" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="I19" s="95" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="J19" s="95" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="K19" s="95" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="L19" s="95" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="M19" s="95" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N19" s="95" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O19" s="95" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="P19" s="95" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="Q19" s="95" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="R19" s="95" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="S19" s="95" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T19" s="95" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U19" s="95" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V19" s="95" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W19" s="95" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="X19" s="95" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="Y19" s="95" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Z19" s="95" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA19" s="95" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AB19" s="95" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AC19" s="95" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD19" s="95" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="AE19" s="95" t="n">
-        <v>5.84</v>
-      </c>
+      <c r="B19" s="60" t="n"/>
+      <c r="C19" s="60" t="n"/>
+      <c r="D19" s="60" t="n"/>
+      <c r="E19" s="60" t="n"/>
+      <c r="F19" s="60" t="n"/>
+      <c r="G19" s="60" t="n"/>
+      <c r="H19" s="60" t="n"/>
+      <c r="I19" s="60" t="n"/>
+      <c r="J19" s="60" t="n"/>
+      <c r="K19" s="60" t="n"/>
+      <c r="L19" s="60" t="n"/>
+      <c r="M19" s="60" t="n"/>
+      <c r="N19" s="60" t="n"/>
+      <c r="O19" s="60" t="n"/>
+      <c r="P19" s="60" t="n"/>
+      <c r="Q19" s="60" t="n"/>
+      <c r="R19" s="60" t="n"/>
+      <c r="S19" s="60" t="n"/>
+      <c r="T19" s="60" t="n"/>
+      <c r="U19" s="60" t="n"/>
+      <c r="V19" s="60" t="n"/>
+      <c r="W19" s="60" t="n"/>
+      <c r="X19" s="60" t="n"/>
+      <c r="Y19" s="60" t="n"/>
+      <c r="Z19" s="60" t="n"/>
+      <c r="AA19" s="60" t="n"/>
+      <c r="AB19" s="60" t="n"/>
+      <c r="AC19" s="60" t="n"/>
+      <c r="AD19" s="60" t="n"/>
+      <c r="AE19" s="60" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="76" t="inlineStr">
+      <c r="A20" s="58" t="inlineStr">
         <is>
           <t>us500:RNG120</t>
         </is>
       </c>
-      <c r="B20" s="95" t="n">
-        <v>12.76</v>
-      </c>
-      <c r="C20" s="95" t="n">
-        <v>12.76</v>
-      </c>
-      <c r="D20" s="95" t="n">
-        <v>13.62</v>
-      </c>
-      <c r="E20" s="95" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="F20" s="95" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="G20" s="95" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="H20" s="95" t="n">
-        <v>10.61</v>
-      </c>
-      <c r="I20" s="95" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J20" s="95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="K20" s="95" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="L20" s="95" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="M20" s="95" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="N20" s="95" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="O20" s="95" t="n">
-        <v>8.74</v>
-      </c>
-      <c r="P20" s="95" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="Q20" s="95" t="n">
-        <v>8.279999999999999</v>
-      </c>
-      <c r="R20" s="95" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="S20" s="95" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="T20" s="95" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="U20" s="95" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="V20" s="95" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="W20" s="95" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="X20" s="95" t="n">
-        <v>5.69</v>
-      </c>
-      <c r="Y20" s="95" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="Z20" s="95" t="n">
-        <v>6.87</v>
-      </c>
-      <c r="AA20" s="95" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="AB20" s="95" t="n">
-        <v>10.36</v>
-      </c>
-      <c r="AC20" s="95" t="n">
-        <v>10.36</v>
-      </c>
-      <c r="AD20" s="95" t="n">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="AE20" s="95" t="n">
-        <v>8.43</v>
-      </c>
+      <c r="B20" s="60" t="n"/>
+      <c r="C20" s="60" t="n"/>
+      <c r="D20" s="60" t="n"/>
+      <c r="E20" s="60" t="n"/>
+      <c r="F20" s="60" t="n"/>
+      <c r="G20" s="60" t="n"/>
+      <c r="H20" s="60" t="n"/>
+      <c r="I20" s="60" t="n"/>
+      <c r="J20" s="60" t="n"/>
+      <c r="K20" s="60" t="n"/>
+      <c r="L20" s="60" t="n"/>
+      <c r="M20" s="60" t="n"/>
+      <c r="N20" s="60" t="n"/>
+      <c r="O20" s="60" t="n"/>
+      <c r="P20" s="60" t="n"/>
+      <c r="Q20" s="60" t="n"/>
+      <c r="R20" s="60" t="n"/>
+      <c r="S20" s="60" t="n"/>
+      <c r="T20" s="60" t="n"/>
+      <c r="U20" s="60" t="n"/>
+      <c r="V20" s="60" t="n"/>
+      <c r="W20" s="60" t="n"/>
+      <c r="X20" s="60" t="n"/>
+      <c r="Y20" s="60" t="n"/>
+      <c r="Z20" s="60" t="n"/>
+      <c r="AA20" s="60" t="n"/>
+      <c r="AB20" s="60" t="n"/>
+      <c r="AC20" s="60" t="n"/>
+      <c r="AD20" s="60" t="n"/>
+      <c r="AE20" s="60" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="76" t="inlineStr">
-        <is>
-          <t>us500:RS2</t>
-        </is>
-      </c>
-      <c r="B21" s="95" t="n">
-        <v>30.41</v>
-      </c>
-      <c r="C21" s="95" t="n">
-        <v>30.41</v>
-      </c>
-      <c r="D21" s="95" t="n">
-        <v>81.84</v>
-      </c>
-      <c r="E21" s="95" t="n">
-        <v>15.76</v>
-      </c>
-      <c r="F21" s="95" t="n">
-        <v>23.93</v>
-      </c>
-      <c r="G21" s="95" t="n">
-        <v>22.27</v>
-      </c>
-      <c r="H21" s="95" t="n">
-        <v>86.19</v>
-      </c>
-      <c r="I21" s="95" t="n">
-        <v>60.63</v>
-      </c>
-      <c r="J21" s="95" t="n">
-        <v>83.51000000000001</v>
-      </c>
-      <c r="K21" s="95" t="n">
-        <v>58.19</v>
-      </c>
-      <c r="L21" s="95" t="n">
-        <v>90.16</v>
-      </c>
-      <c r="M21" s="95" t="n">
-        <v>84.39</v>
-      </c>
-      <c r="N21" s="95" t="n">
-        <v>76.79000000000001</v>
-      </c>
-      <c r="O21" s="95" t="n">
-        <v>92.34</v>
-      </c>
-      <c r="P21" s="95" t="n">
-        <v>40.89</v>
-      </c>
-      <c r="Q21" s="95" t="n">
-        <v>96.09</v>
-      </c>
-      <c r="R21" s="95" t="n">
-        <v>95.83</v>
-      </c>
-      <c r="S21" s="95" t="n">
-        <v>95.06</v>
-      </c>
-      <c r="T21" s="95" t="n">
-        <v>91.83</v>
-      </c>
-      <c r="U21" s="95" t="n">
-        <v>85.17</v>
-      </c>
-      <c r="V21" s="95" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="W21" s="95" t="n">
-        <v>51.58</v>
-      </c>
-      <c r="X21" s="95" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y21" s="95" t="n">
-        <v>12.54</v>
-      </c>
-      <c r="Z21" s="95" t="n">
-        <v>17.38</v>
-      </c>
-      <c r="AA21" s="95" t="n">
-        <v>19.37</v>
-      </c>
-      <c r="AB21" s="95" t="n">
-        <v>85.14</v>
-      </c>
-      <c r="AC21" s="95" t="n">
-        <v>85.14</v>
-      </c>
-      <c r="AD21" s="95" t="n">
-        <v>24.99</v>
-      </c>
-      <c r="AE21" s="95" t="n">
-        <v>25.19</v>
-      </c>
+      <c r="A21" s="58" t="inlineStr">
+        <is>
+          <t>us500:RSI2</t>
+        </is>
+      </c>
+      <c r="B21" s="60" t="n"/>
+      <c r="C21" s="60" t="n"/>
+      <c r="D21" s="60" t="n"/>
+      <c r="E21" s="60" t="n"/>
+      <c r="F21" s="60" t="n"/>
+      <c r="G21" s="60" t="n"/>
+      <c r="H21" s="60" t="n"/>
+      <c r="I21" s="60" t="n"/>
+      <c r="J21" s="60" t="n"/>
+      <c r="K21" s="60" t="n"/>
+      <c r="L21" s="60" t="n"/>
+      <c r="M21" s="60" t="n"/>
+      <c r="N21" s="60" t="n"/>
+      <c r="O21" s="60" t="n"/>
+      <c r="P21" s="60" t="n"/>
+      <c r="Q21" s="60" t="n"/>
+      <c r="R21" s="60" t="n"/>
+      <c r="S21" s="60" t="n"/>
+      <c r="T21" s="60" t="n"/>
+      <c r="U21" s="60" t="n"/>
+      <c r="V21" s="60" t="n"/>
+      <c r="W21" s="60" t="n"/>
+      <c r="X21" s="60" t="n"/>
+      <c r="Y21" s="60" t="n"/>
+      <c r="Z21" s="60" t="n"/>
+      <c r="AA21" s="60" t="n"/>
+      <c r="AB21" s="60" t="n"/>
+      <c r="AC21" s="60" t="n"/>
+      <c r="AD21" s="60" t="n"/>
+      <c r="AE21" s="60" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="76" t="inlineStr">
+      <c r="A22" s="58" t="inlineStr">
         <is>
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="C22" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="D22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="E22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="F22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="G22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="H22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="I22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="J22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="K22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="L22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V22" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="W22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X22" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y22" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
+      <c r="B22" s="60" t="n"/>
+      <c r="C22" s="60" t="n"/>
+      <c r="D22" s="60" t="n"/>
+      <c r="E22" s="60" t="n"/>
+      <c r="F22" s="60" t="n"/>
+      <c r="G22" s="60" t="n"/>
+      <c r="H22" s="60" t="n"/>
+      <c r="I22" s="60" t="n"/>
+      <c r="J22" s="60" t="n"/>
+      <c r="K22" s="60" t="n"/>
+      <c r="L22" s="60" t="n"/>
+      <c r="M22" s="60" t="n"/>
+      <c r="N22" s="60" t="n"/>
+      <c r="O22" s="60" t="n"/>
+      <c r="P22" s="60" t="n"/>
+      <c r="Q22" s="60" t="n"/>
+      <c r="R22" s="60" t="n"/>
+      <c r="S22" s="60" t="n"/>
+      <c r="T22" s="60" t="n"/>
+      <c r="U22" s="60" t="n"/>
+      <c r="V22" s="60" t="n"/>
+      <c r="W22" s="60" t="n"/>
+      <c r="X22" s="60" t="n"/>
+      <c r="Y22" s="60" t="n"/>
+      <c r="Z22" s="60" t="n"/>
+      <c r="AA22" s="60" t="n"/>
+      <c r="AB22" s="60" t="n"/>
+      <c r="AC22" s="60" t="n"/>
+      <c r="AD22" s="60" t="n"/>
+      <c r="AE22" s="60" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="76" t="inlineStr">
+      <c r="A23" s="58" t="inlineStr">
         <is>
           <t>us30:RNG60</t>
         </is>
       </c>
-      <c r="B23" s="95" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="C23" s="95" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="D23" s="95" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="E23" s="95" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="F23" s="95" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="G23" s="95" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="H23" s="95" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I23" s="95" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="J23" s="95" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="K23" s="95" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="L23" s="95" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="M23" s="95" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="N23" s="95" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O23" s="95" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="P23" s="95" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="Q23" s="95" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="R23" s="95" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="S23" s="95" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="T23" s="95" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="U23" s="95" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="V23" s="95" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="W23" s="95" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="X23" s="95" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="Y23" s="95" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="Z23" s="95" t="n">
-        <v>5.61</v>
-      </c>
-      <c r="AA23" s="95" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AB23" s="95" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AC23" s="95" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AD23" s="95" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="AE23" s="95" t="n">
-        <v>6.53</v>
-      </c>
+      <c r="B23" s="60" t="n"/>
+      <c r="C23" s="60" t="n"/>
+      <c r="D23" s="60" t="n"/>
+      <c r="E23" s="60" t="n"/>
+      <c r="F23" s="60" t="n"/>
+      <c r="G23" s="60" t="n"/>
+      <c r="H23" s="60" t="n"/>
+      <c r="I23" s="60" t="n"/>
+      <c r="J23" s="60" t="n"/>
+      <c r="K23" s="60" t="n"/>
+      <c r="L23" s="60" t="n"/>
+      <c r="M23" s="60" t="n"/>
+      <c r="N23" s="60" t="n"/>
+      <c r="O23" s="60" t="n"/>
+      <c r="P23" s="60" t="n"/>
+      <c r="Q23" s="60" t="n"/>
+      <c r="R23" s="60" t="n"/>
+      <c r="S23" s="60" t="n"/>
+      <c r="T23" s="60" t="n"/>
+      <c r="U23" s="60" t="n"/>
+      <c r="V23" s="60" t="n"/>
+      <c r="W23" s="60" t="n"/>
+      <c r="X23" s="60" t="n"/>
+      <c r="Y23" s="60" t="n"/>
+      <c r="Z23" s="60" t="n"/>
+      <c r="AA23" s="60" t="n"/>
+      <c r="AB23" s="60" t="n"/>
+      <c r="AC23" s="60" t="n"/>
+      <c r="AD23" s="60" t="n"/>
+      <c r="AE23" s="60" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="76" t="inlineStr">
+      <c r="A24" s="58" t="inlineStr">
         <is>
           <t>us30:RNG120</t>
         </is>
       </c>
-      <c r="B24" s="95" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="C24" s="95" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="D24" s="95" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="E24" s="95" t="n">
-        <v>10.61</v>
-      </c>
-      <c r="F24" s="95" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="G24" s="95" t="n">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="H24" s="95" t="n">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="I24" s="95" t="n">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="J24" s="95" t="n">
-        <v>8.41</v>
-      </c>
-      <c r="K24" s="95" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L24" s="95" t="n">
-        <v>7.87</v>
-      </c>
-      <c r="M24" s="95" t="n">
-        <v>7.54</v>
-      </c>
-      <c r="N24" s="95" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="O24" s="95" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="P24" s="95" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="Q24" s="95" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="R24" s="95" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="S24" s="95" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="T24" s="95" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="U24" s="95" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="V24" s="95" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="W24" s="95" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="X24" s="95" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="Y24" s="95" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="Z24" s="95" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AA24" s="95" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AB24" s="95" t="n">
-        <v>7.21</v>
-      </c>
-      <c r="AC24" s="95" t="n">
-        <v>7.21</v>
-      </c>
-      <c r="AD24" s="95" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AE24" s="95" t="n">
-        <v>5.93</v>
-      </c>
+      <c r="B24" s="60" t="n"/>
+      <c r="C24" s="60" t="n"/>
+      <c r="D24" s="60" t="n"/>
+      <c r="E24" s="60" t="n"/>
+      <c r="F24" s="60" t="n"/>
+      <c r="G24" s="60" t="n"/>
+      <c r="H24" s="60" t="n"/>
+      <c r="I24" s="60" t="n"/>
+      <c r="J24" s="60" t="n"/>
+      <c r="K24" s="60" t="n"/>
+      <c r="L24" s="60" t="n"/>
+      <c r="M24" s="60" t="n"/>
+      <c r="N24" s="60" t="n"/>
+      <c r="O24" s="60" t="n"/>
+      <c r="P24" s="60" t="n"/>
+      <c r="Q24" s="60" t="n"/>
+      <c r="R24" s="60" t="n"/>
+      <c r="S24" s="60" t="n"/>
+      <c r="T24" s="60" t="n"/>
+      <c r="U24" s="60" t="n"/>
+      <c r="V24" s="60" t="n"/>
+      <c r="W24" s="60" t="n"/>
+      <c r="X24" s="60" t="n"/>
+      <c r="Y24" s="60" t="n"/>
+      <c r="Z24" s="60" t="n"/>
+      <c r="AA24" s="60" t="n"/>
+      <c r="AB24" s="60" t="n"/>
+      <c r="AC24" s="60" t="n"/>
+      <c r="AD24" s="60" t="n"/>
+      <c r="AE24" s="60" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="76" t="inlineStr">
-        <is>
-          <t>us30:RS3</t>
-        </is>
-      </c>
-      <c r="B25" s="95" t="n">
-        <v>34.52</v>
-      </c>
-      <c r="C25" s="95" t="n">
-        <v>34.52</v>
-      </c>
-      <c r="D25" s="95" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="E25" s="95" t="n">
-        <v>28.19</v>
-      </c>
-      <c r="F25" s="95" t="n">
-        <v>52.09</v>
-      </c>
-      <c r="G25" s="95" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="H25" s="95" t="n">
-        <v>76.02</v>
-      </c>
-      <c r="I25" s="95" t="n">
-        <v>74.91</v>
-      </c>
-      <c r="J25" s="95" t="n">
-        <v>66.62</v>
-      </c>
-      <c r="K25" s="95" t="n">
-        <v>42.84</v>
-      </c>
-      <c r="L25" s="95" t="n">
-        <v>92.18000000000001</v>
-      </c>
-      <c r="M25" s="95" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="N25" s="95" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="O25" s="95" t="n">
-        <v>87.58</v>
-      </c>
-      <c r="P25" s="95" t="n">
-        <v>65.31</v>
-      </c>
-      <c r="Q25" s="95" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="R25" s="95" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="S25" s="95" t="n">
-        <v>82.94</v>
-      </c>
-      <c r="T25" s="95" t="n">
-        <v>71.68000000000001</v>
-      </c>
-      <c r="U25" s="95" t="n">
-        <v>56.57</v>
-      </c>
-      <c r="V25" s="95" t="n">
-        <v>46.45</v>
-      </c>
-      <c r="W25" s="95" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="X25" s="95" t="n">
-        <v>13.02</v>
-      </c>
-      <c r="Y25" s="95" t="n">
-        <v>24.55</v>
-      </c>
-      <c r="Z25" s="95" t="n">
-        <v>35.87</v>
-      </c>
-      <c r="AA25" s="95" t="n">
-        <v>32.25</v>
-      </c>
-      <c r="AB25" s="95" t="n">
-        <v>84.45999999999999</v>
-      </c>
-      <c r="AC25" s="95" t="n">
-        <v>84.45999999999999</v>
-      </c>
-      <c r="AD25" s="95" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="AE25" s="95" t="n">
-        <v>52.49</v>
-      </c>
+      <c r="A25" s="58" t="inlineStr">
+        <is>
+          <t>us30:RSI3</t>
+        </is>
+      </c>
+      <c r="B25" s="60" t="n"/>
+      <c r="C25" s="60" t="n"/>
+      <c r="D25" s="60" t="n"/>
+      <c r="E25" s="60" t="n"/>
+      <c r="F25" s="60" t="n"/>
+      <c r="G25" s="60" t="n"/>
+      <c r="H25" s="60" t="n"/>
+      <c r="I25" s="60" t="n"/>
+      <c r="J25" s="60" t="n"/>
+      <c r="K25" s="60" t="n"/>
+      <c r="L25" s="60" t="n"/>
+      <c r="M25" s="60" t="n"/>
+      <c r="N25" s="60" t="n"/>
+      <c r="O25" s="60" t="n"/>
+      <c r="P25" s="60" t="n"/>
+      <c r="Q25" s="60" t="n"/>
+      <c r="R25" s="60" t="n"/>
+      <c r="S25" s="60" t="n"/>
+      <c r="T25" s="60" t="n"/>
+      <c r="U25" s="60" t="n"/>
+      <c r="V25" s="60" t="n"/>
+      <c r="W25" s="60" t="n"/>
+      <c r="X25" s="60" t="n"/>
+      <c r="Y25" s="60" t="n"/>
+      <c r="Z25" s="60" t="n"/>
+      <c r="AA25" s="60" t="n"/>
+      <c r="AB25" s="60" t="n"/>
+      <c r="AC25" s="60" t="n"/>
+      <c r="AD25" s="60" t="n"/>
+      <c r="AE25" s="60" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="76" t="inlineStr">
+      <c r="A26" s="58" t="inlineStr">
         <is>
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="C26" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="D26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="E26" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="F26" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="G26" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="H26" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="I26" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="J26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K26" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="L26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P26" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V26" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W26" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="X26" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y26" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z26" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA26" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB26" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC26" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD26" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE26" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
+      <c r="B26" s="60" t="n"/>
+      <c r="C26" s="60" t="n"/>
+      <c r="D26" s="60" t="n"/>
+      <c r="E26" s="60" t="n"/>
+      <c r="F26" s="60" t="n"/>
+      <c r="G26" s="60" t="n"/>
+      <c r="H26" s="60" t="n"/>
+      <c r="I26" s="60" t="n"/>
+      <c r="J26" s="60" t="n"/>
+      <c r="K26" s="60" t="n"/>
+      <c r="L26" s="60" t="n"/>
+      <c r="M26" s="60" t="n"/>
+      <c r="N26" s="60" t="n"/>
+      <c r="O26" s="60" t="n"/>
+      <c r="P26" s="60" t="n"/>
+      <c r="Q26" s="60" t="n"/>
+      <c r="R26" s="60" t="n"/>
+      <c r="S26" s="60" t="n"/>
+      <c r="T26" s="60" t="n"/>
+      <c r="U26" s="60" t="n"/>
+      <c r="V26" s="60" t="n"/>
+      <c r="W26" s="60" t="n"/>
+      <c r="X26" s="60" t="n"/>
+      <c r="Y26" s="60" t="n"/>
+      <c r="Z26" s="60" t="n"/>
+      <c r="AA26" s="60" t="n"/>
+      <c r="AB26" s="60" t="n"/>
+      <c r="AC26" s="60" t="n"/>
+      <c r="AD26" s="60" t="n"/>
+      <c r="AE26" s="60" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="76" t="inlineStr">
+      <c r="A27" s="58" t="inlineStr">
         <is>
           <t>ixic:RNG60</t>
         </is>
       </c>
-      <c r="B27" s="95" t="n">
-        <v>-2.58</v>
-      </c>
-      <c r="C27" s="95" t="n">
-        <v>-2.58</v>
-      </c>
-      <c r="D27" s="95" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="E27" s="95" t="n">
-        <v>-3.91</v>
-      </c>
-      <c r="F27" s="95" t="n">
-        <v>-2.74</v>
-      </c>
-      <c r="G27" s="95" t="n">
-        <v>-2.68</v>
-      </c>
-      <c r="H27" s="95" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="I27" s="95" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="J27" s="95" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K27" s="95" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="L27" s="95" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="M27" s="95" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="N27" s="95" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O27" s="95" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P27" s="95" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="Q27" s="95" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="R27" s="95" t="n">
-        <v>-0.73</v>
-      </c>
-      <c r="S27" s="95" t="n">
-        <v>-1</v>
-      </c>
-      <c r="T27" s="95" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="U27" s="95" t="n">
-        <v>-1.66</v>
-      </c>
-      <c r="V27" s="95" t="n">
-        <v>-3.63</v>
-      </c>
-      <c r="W27" s="95" t="n">
-        <v>-4.11</v>
-      </c>
-      <c r="X27" s="95" t="n">
-        <v>-3.76</v>
-      </c>
-      <c r="Y27" s="95" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="Z27" s="95" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="AA27" s="95" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="AB27" s="95" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="AC27" s="95" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="AD27" s="95" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="AE27" s="95" t="n">
-        <v>4.32</v>
-      </c>
+      <c r="B27" s="60" t="n"/>
+      <c r="C27" s="60" t="n"/>
+      <c r="D27" s="60" t="n"/>
+      <c r="E27" s="60" t="n"/>
+      <c r="F27" s="60" t="n"/>
+      <c r="G27" s="60" t="n"/>
+      <c r="H27" s="60" t="n"/>
+      <c r="I27" s="60" t="n"/>
+      <c r="J27" s="60" t="n"/>
+      <c r="K27" s="60" t="n"/>
+      <c r="L27" s="60" t="n"/>
+      <c r="M27" s="60" t="n"/>
+      <c r="N27" s="60" t="n"/>
+      <c r="O27" s="60" t="n"/>
+      <c r="P27" s="60" t="n"/>
+      <c r="Q27" s="60" t="n"/>
+      <c r="R27" s="60" t="n"/>
+      <c r="S27" s="60" t="n"/>
+      <c r="T27" s="60" t="n"/>
+      <c r="U27" s="60" t="n"/>
+      <c r="V27" s="60" t="n"/>
+      <c r="W27" s="60" t="n"/>
+      <c r="X27" s="60" t="n"/>
+      <c r="Y27" s="60" t="n"/>
+      <c r="Z27" s="60" t="n"/>
+      <c r="AA27" s="60" t="n"/>
+      <c r="AB27" s="60" t="n"/>
+      <c r="AC27" s="60" t="n"/>
+      <c r="AD27" s="60" t="n"/>
+      <c r="AE27" s="60" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="76" t="inlineStr">
+      <c r="A28" s="58" t="inlineStr">
         <is>
           <t>ixic:RNG120</t>
         </is>
       </c>
-      <c r="B28" s="95" t="n">
-        <v>12.98</v>
-      </c>
-      <c r="C28" s="95" t="n">
-        <v>12.98</v>
-      </c>
-      <c r="D28" s="95" t="n">
-        <v>14.18</v>
-      </c>
-      <c r="E28" s="95" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="F28" s="95" t="n">
-        <v>9.02</v>
-      </c>
-      <c r="G28" s="95" t="n">
-        <v>10.76</v>
-      </c>
-      <c r="H28" s="95" t="n">
-        <v>11.54</v>
-      </c>
-      <c r="I28" s="95" t="n">
-        <v>11.48</v>
-      </c>
-      <c r="J28" s="95" t="n">
-        <v>11.95</v>
-      </c>
-      <c r="K28" s="95" t="n">
-        <v>12.67</v>
-      </c>
-      <c r="L28" s="95" t="n">
-        <v>11.04</v>
-      </c>
-      <c r="M28" s="95" t="n">
-        <v>10.68</v>
-      </c>
-      <c r="N28" s="95" t="n">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="O28" s="95" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="P28" s="95" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="Q28" s="95" t="n">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="R28" s="95" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="S28" s="95" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="T28" s="95" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="U28" s="95" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="V28" s="95" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="W28" s="95" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="X28" s="95" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="Y28" s="95" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="Z28" s="95" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA28" s="95" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AB28" s="95" t="n">
-        <v>10.58</v>
-      </c>
-      <c r="AC28" s="95" t="n">
-        <v>10.58</v>
-      </c>
-      <c r="AD28" s="95" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AE28" s="95" t="n">
-        <v>7.88</v>
-      </c>
+      <c r="B28" s="60" t="n"/>
+      <c r="C28" s="60" t="n"/>
+      <c r="D28" s="60" t="n"/>
+      <c r="E28" s="60" t="n"/>
+      <c r="F28" s="60" t="n"/>
+      <c r="G28" s="60" t="n"/>
+      <c r="H28" s="60" t="n"/>
+      <c r="I28" s="60" t="n"/>
+      <c r="J28" s="60" t="n"/>
+      <c r="K28" s="60" t="n"/>
+      <c r="L28" s="60" t="n"/>
+      <c r="M28" s="60" t="n"/>
+      <c r="N28" s="60" t="n"/>
+      <c r="O28" s="60" t="n"/>
+      <c r="P28" s="60" t="n"/>
+      <c r="Q28" s="60" t="n"/>
+      <c r="R28" s="60" t="n"/>
+      <c r="S28" s="60" t="n"/>
+      <c r="T28" s="60" t="n"/>
+      <c r="U28" s="60" t="n"/>
+      <c r="V28" s="60" t="n"/>
+      <c r="W28" s="60" t="n"/>
+      <c r="X28" s="60" t="n"/>
+      <c r="Y28" s="60" t="n"/>
+      <c r="Z28" s="60" t="n"/>
+      <c r="AA28" s="60" t="n"/>
+      <c r="AB28" s="60" t="n"/>
+      <c r="AC28" s="60" t="n"/>
+      <c r="AD28" s="60" t="n"/>
+      <c r="AE28" s="60" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="96" t="inlineStr">
-        <is>
-          <t>ixic:RS2</t>
-        </is>
-      </c>
-      <c r="B29" s="95" t="n">
-        <v>32.92</v>
-      </c>
-      <c r="C29" s="95" t="n">
-        <v>32.92</v>
-      </c>
-      <c r="D29" s="95" t="n">
-        <v>85.03</v>
-      </c>
-      <c r="E29" s="95" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="F29" s="95" t="n">
-        <v>21.97</v>
-      </c>
-      <c r="G29" s="95" t="n">
-        <v>15.42</v>
-      </c>
-      <c r="H29" s="95" t="n">
-        <v>74.7</v>
-      </c>
-      <c r="I29" s="95" t="n">
-        <v>51.35</v>
-      </c>
-      <c r="J29" s="95" t="n">
-        <v>96.66</v>
-      </c>
-      <c r="K29" s="95" t="n">
-        <v>89.75</v>
-      </c>
-      <c r="L29" s="95" t="n">
-        <v>88.93000000000001</v>
-      </c>
-      <c r="M29" s="95" t="n">
-        <v>77.02</v>
-      </c>
-      <c r="N29" s="95" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="O29" s="95" t="n">
-        <v>92.18000000000001</v>
-      </c>
-      <c r="P29" s="95" t="n">
-        <v>42.32</v>
-      </c>
-      <c r="Q29" s="95" t="n">
-        <v>70.06</v>
-      </c>
-      <c r="R29" s="95" t="n">
-        <v>61.86</v>
-      </c>
-      <c r="S29" s="95" t="n">
-        <v>95.17</v>
-      </c>
-      <c r="T29" s="95" t="n">
-        <v>92.73999999999999</v>
-      </c>
-      <c r="U29" s="95" t="n">
-        <v>88.20999999999999</v>
-      </c>
-      <c r="V29" s="95" t="n">
-        <v>65.19</v>
-      </c>
-      <c r="W29" s="95" t="n">
-        <v>44.48</v>
-      </c>
-      <c r="X29" s="95" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Y29" s="95" t="n">
-        <v>27.81</v>
-      </c>
-      <c r="Z29" s="95" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="AA29" s="95" t="n">
-        <v>14.52</v>
-      </c>
-      <c r="AB29" s="95" t="n">
-        <v>71.48999999999999</v>
-      </c>
-      <c r="AC29" s="95" t="n">
-        <v>71.48999999999999</v>
-      </c>
-      <c r="AD29" s="95" t="n">
-        <v>13.66</v>
-      </c>
-      <c r="AE29" s="95" t="n">
-        <v>17.16</v>
-      </c>
+      <c r="A29" s="58" t="inlineStr">
+        <is>
+          <t>ixic:RSI2</t>
+        </is>
+      </c>
+      <c r="B29" s="60" t="n"/>
+      <c r="C29" s="60" t="n"/>
+      <c r="D29" s="60" t="n"/>
+      <c r="E29" s="60" t="n"/>
+      <c r="F29" s="60" t="n"/>
+      <c r="G29" s="60" t="n"/>
+      <c r="H29" s="60" t="n"/>
+      <c r="I29" s="60" t="n"/>
+      <c r="J29" s="60" t="n"/>
+      <c r="K29" s="60" t="n"/>
+      <c r="L29" s="60" t="n"/>
+      <c r="M29" s="60" t="n"/>
+      <c r="N29" s="60" t="n"/>
+      <c r="O29" s="60" t="n"/>
+      <c r="P29" s="60" t="n"/>
+      <c r="Q29" s="60" t="n"/>
+      <c r="R29" s="60" t="n"/>
+      <c r="S29" s="60" t="n"/>
+      <c r="T29" s="60" t="n"/>
+      <c r="U29" s="60" t="n"/>
+      <c r="V29" s="60" t="n"/>
+      <c r="W29" s="60" t="n"/>
+      <c r="X29" s="60" t="n"/>
+      <c r="Y29" s="60" t="n"/>
+      <c r="Z29" s="60" t="n"/>
+      <c r="AA29" s="60" t="n"/>
+      <c r="AB29" s="60" t="n"/>
+      <c r="AC29" s="60" t="n"/>
+      <c r="AD29" s="60" t="n"/>
+      <c r="AE29" s="60" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="76" t="inlineStr">
+      <c r="A30" s="58" t="inlineStr">
         <is>
           <t>jp225:EIDE</t>
         </is>
       </c>
-      <c r="B30" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="C30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="D30" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="E30" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="F30" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="G30" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="H30" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="I30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P30" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q30" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R30" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S30" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T30" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U30" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="V30" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="W30" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="X30" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y30" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z30" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA30" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB30" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC30" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD30" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE30" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
+      <c r="B30" s="60" t="n"/>
+      <c r="C30" s="60" t="n"/>
+      <c r="D30" s="60" t="n"/>
+      <c r="E30" s="60" t="n"/>
+      <c r="F30" s="60" t="n"/>
+      <c r="G30" s="60" t="n"/>
+      <c r="H30" s="60" t="n"/>
+      <c r="I30" s="60" t="n"/>
+      <c r="J30" s="60" t="n"/>
+      <c r="K30" s="60" t="n"/>
+      <c r="L30" s="60" t="n"/>
+      <c r="M30" s="60" t="n"/>
+      <c r="N30" s="60" t="n"/>
+      <c r="O30" s="60" t="n"/>
+      <c r="P30" s="60" t="n"/>
+      <c r="Q30" s="60" t="n"/>
+      <c r="R30" s="60" t="n"/>
+      <c r="S30" s="60" t="n"/>
+      <c r="T30" s="60" t="n"/>
+      <c r="U30" s="60" t="n"/>
+      <c r="V30" s="60" t="n"/>
+      <c r="W30" s="60" t="n"/>
+      <c r="X30" s="60" t="n"/>
+      <c r="Y30" s="60" t="n"/>
+      <c r="Z30" s="60" t="n"/>
+      <c r="AA30" s="60" t="n"/>
+      <c r="AB30" s="60" t="n"/>
+      <c r="AC30" s="60" t="n"/>
+      <c r="AD30" s="60" t="n"/>
+      <c r="AE30" s="60" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="76" t="inlineStr">
+      <c r="A31" s="58" t="inlineStr">
         <is>
           <t>jp225:RNG60</t>
         </is>
       </c>
-      <c r="B31" s="95" t="n">
-        <v>-5.47</v>
-      </c>
-      <c r="C31" s="95" t="n">
-        <v>-6.85</v>
-      </c>
-      <c r="D31" s="95" t="n">
-        <v>-7.64</v>
-      </c>
-      <c r="E31" s="95" t="n">
-        <v>-7.28</v>
-      </c>
-      <c r="F31" s="95" t="n">
-        <v>-7.29</v>
-      </c>
-      <c r="G31" s="95" t="n">
-        <v>-5.52</v>
-      </c>
-      <c r="H31" s="95" t="n">
-        <v>-7.32</v>
-      </c>
-      <c r="I31" s="95" t="n">
-        <v>-1.85</v>
-      </c>
-      <c r="J31" s="95" t="n">
-        <v>-2.87</v>
-      </c>
-      <c r="K31" s="95" t="n">
-        <v>-4.44</v>
-      </c>
-      <c r="L31" s="95" t="n">
-        <v>-4.15</v>
-      </c>
-      <c r="M31" s="95" t="n">
-        <v>-4.11</v>
-      </c>
-      <c r="N31" s="95" t="n">
-        <v>-4.11</v>
-      </c>
-      <c r="O31" s="95" t="n">
-        <v>-6.33</v>
-      </c>
-      <c r="P31" s="95" t="n">
-        <v>-7.13</v>
-      </c>
-      <c r="Q31" s="95" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="R31" s="95" t="n">
-        <v>-5.28</v>
-      </c>
-      <c r="S31" s="95" t="n">
-        <v>-5.31</v>
-      </c>
-      <c r="T31" s="95" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="U31" s="95" t="n">
-        <v>-7.44</v>
-      </c>
-      <c r="V31" s="95" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="W31" s="95" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="X31" s="95" t="n">
-        <v>-6.01</v>
-      </c>
-      <c r="Y31" s="95" t="n">
-        <v>-5.71</v>
-      </c>
-      <c r="Z31" s="95" t="n">
-        <v>-5.33</v>
-      </c>
-      <c r="AA31" s="95" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AB31" s="95" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AC31" s="95" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="AD31" s="95" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="AE31" s="95" t="n">
-        <v>-1.2</v>
-      </c>
+      <c r="B31" s="60" t="n"/>
+      <c r="C31" s="60" t="n"/>
+      <c r="D31" s="60" t="n"/>
+      <c r="E31" s="60" t="n"/>
+      <c r="F31" s="60" t="n"/>
+      <c r="G31" s="60" t="n"/>
+      <c r="H31" s="60" t="n"/>
+      <c r="I31" s="60" t="n"/>
+      <c r="J31" s="60" t="n"/>
+      <c r="K31" s="60" t="n"/>
+      <c r="L31" s="60" t="n"/>
+      <c r="M31" s="60" t="n"/>
+      <c r="N31" s="60" t="n"/>
+      <c r="O31" s="60" t="n"/>
+      <c r="P31" s="60" t="n"/>
+      <c r="Q31" s="60" t="n"/>
+      <c r="R31" s="60" t="n"/>
+      <c r="S31" s="60" t="n"/>
+      <c r="T31" s="60" t="n"/>
+      <c r="U31" s="60" t="n"/>
+      <c r="V31" s="60" t="n"/>
+      <c r="W31" s="60" t="n"/>
+      <c r="X31" s="60" t="n"/>
+      <c r="Y31" s="60" t="n"/>
+      <c r="Z31" s="60" t="n"/>
+      <c r="AA31" s="60" t="n"/>
+      <c r="AB31" s="60" t="n"/>
+      <c r="AC31" s="60" t="n"/>
+      <c r="AD31" s="60" t="n"/>
+      <c r="AE31" s="60" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="76" t="inlineStr">
+      <c r="A32" s="58" t="inlineStr">
         <is>
           <t>jp225:RNG120</t>
         </is>
       </c>
-      <c r="B32" s="95" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="C32" s="95" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D32" s="95" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="E32" s="95" t="n">
-        <v>-2.26</v>
-      </c>
-      <c r="F32" s="95" t="n">
-        <v>-4.48</v>
-      </c>
-      <c r="G32" s="95" t="n">
-        <v>-2.82</v>
-      </c>
-      <c r="H32" s="95" t="n">
-        <v>-3.63</v>
-      </c>
-      <c r="I32" s="95" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="J32" s="95" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="K32" s="95" t="n">
-        <v>-4.01</v>
-      </c>
-      <c r="L32" s="95" t="n">
-        <v>-4.76</v>
-      </c>
-      <c r="M32" s="95" t="n">
-        <v>-5.22</v>
-      </c>
-      <c r="N32" s="95" t="n">
-        <v>-5.22</v>
-      </c>
-      <c r="O32" s="95" t="n">
-        <v>-7.96</v>
-      </c>
-      <c r="P32" s="95" t="n">
-        <v>-9.43</v>
-      </c>
-      <c r="Q32" s="95" t="n">
-        <v>-11.19</v>
-      </c>
-      <c r="R32" s="95" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="S32" s="95" t="n">
-        <v>-9.48</v>
-      </c>
-      <c r="T32" s="95" t="n">
-        <v>-9.92</v>
-      </c>
-      <c r="U32" s="95" t="n">
-        <v>-12.73</v>
-      </c>
-      <c r="V32" s="95" t="n">
-        <v>-9.609999999999999</v>
-      </c>
-      <c r="W32" s="95" t="n">
-        <v>-8.869999999999999</v>
-      </c>
-      <c r="X32" s="95" t="n">
-        <v>-5.98</v>
-      </c>
-      <c r="Y32" s="95" t="n">
-        <v>-5.54</v>
-      </c>
-      <c r="Z32" s="95" t="n">
-        <v>-4.26</v>
-      </c>
-      <c r="AA32" s="95" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="AB32" s="95" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="AC32" s="95" t="n">
-        <v>-2.62</v>
-      </c>
-      <c r="AD32" s="95" t="n">
-        <v>-3.12</v>
-      </c>
-      <c r="AE32" s="95" t="n">
-        <v>-4.29</v>
-      </c>
+      <c r="B32" s="60" t="n"/>
+      <c r="C32" s="60" t="n"/>
+      <c r="D32" s="60" t="n"/>
+      <c r="E32" s="60" t="n"/>
+      <c r="F32" s="60" t="n"/>
+      <c r="G32" s="60" t="n"/>
+      <c r="H32" s="60" t="n"/>
+      <c r="I32" s="60" t="n"/>
+      <c r="J32" s="60" t="n"/>
+      <c r="K32" s="60" t="n"/>
+      <c r="L32" s="60" t="n"/>
+      <c r="M32" s="60" t="n"/>
+      <c r="N32" s="60" t="n"/>
+      <c r="O32" s="60" t="n"/>
+      <c r="P32" s="60" t="n"/>
+      <c r="Q32" s="60" t="n"/>
+      <c r="R32" s="60" t="n"/>
+      <c r="S32" s="60" t="n"/>
+      <c r="T32" s="60" t="n"/>
+      <c r="U32" s="60" t="n"/>
+      <c r="V32" s="60" t="n"/>
+      <c r="W32" s="60" t="n"/>
+      <c r="X32" s="60" t="n"/>
+      <c r="Y32" s="60" t="n"/>
+      <c r="Z32" s="60" t="n"/>
+      <c r="AA32" s="60" t="n"/>
+      <c r="AB32" s="60" t="n"/>
+      <c r="AC32" s="60" t="n"/>
+      <c r="AD32" s="60" t="n"/>
+      <c r="AE32" s="60" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="76" t="inlineStr">
-        <is>
-          <t>jp225:RS9</t>
-        </is>
-      </c>
-      <c r="B33" s="95" t="n">
-        <v>57.64</v>
-      </c>
-      <c r="C33" s="95" t="n">
-        <v>62.13</v>
-      </c>
-      <c r="D33" s="95" t="n">
-        <v>56.86</v>
-      </c>
-      <c r="E33" s="95" t="n">
-        <v>56.21</v>
-      </c>
-      <c r="F33" s="95" t="n">
-        <v>50.28</v>
-      </c>
-      <c r="G33" s="95" t="n">
-        <v>58.22</v>
-      </c>
-      <c r="H33" s="95" t="n">
-        <v>52.42</v>
-      </c>
-      <c r="I33" s="95" t="n">
-        <v>77.31</v>
-      </c>
-      <c r="J33" s="95" t="n">
-        <v>71.64</v>
-      </c>
-      <c r="K33" s="95" t="n">
-        <v>61.74</v>
-      </c>
-      <c r="L33" s="95" t="n">
-        <v>63.04</v>
-      </c>
-      <c r="M33" s="95" t="n">
-        <v>60.77</v>
-      </c>
-      <c r="N33" s="95" t="n">
-        <v>60.77</v>
-      </c>
-      <c r="O33" s="95" t="n">
-        <v>54.21</v>
-      </c>
-      <c r="P33" s="95" t="n">
-        <v>42.56</v>
-      </c>
-      <c r="Q33" s="95" t="n">
-        <v>39.44</v>
-      </c>
-      <c r="R33" s="95" t="n">
-        <v>43.68</v>
-      </c>
-      <c r="S33" s="95" t="n">
-        <v>43.96</v>
-      </c>
-      <c r="T33" s="95" t="n">
-        <v>46.79</v>
-      </c>
-      <c r="U33" s="95" t="n">
-        <v>26.47</v>
-      </c>
-      <c r="V33" s="95" t="n">
-        <v>31.18</v>
-      </c>
-      <c r="W33" s="95" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="X33" s="95" t="n">
-        <v>33.25</v>
-      </c>
-      <c r="Y33" s="95" t="n">
-        <v>35.58</v>
-      </c>
-      <c r="Z33" s="95" t="n">
-        <v>39.17</v>
-      </c>
-      <c r="AA33" s="95" t="n">
-        <v>62.79</v>
-      </c>
-      <c r="AB33" s="95" t="n">
-        <v>63.09</v>
-      </c>
-      <c r="AC33" s="95" t="n">
-        <v>62.51</v>
-      </c>
-      <c r="AD33" s="95" t="n">
-        <v>59.46</v>
-      </c>
-      <c r="AE33" s="95" t="n">
-        <v>59.6</v>
-      </c>
+      <c r="A33" s="58" t="inlineStr">
+        <is>
+          <t>jp225:RSI5</t>
+        </is>
+      </c>
+      <c r="B33" s="60" t="n"/>
+      <c r="C33" s="60" t="n"/>
+      <c r="D33" s="60" t="n"/>
+      <c r="E33" s="60" t="n"/>
+      <c r="F33" s="60" t="n"/>
+      <c r="G33" s="60" t="n"/>
+      <c r="H33" s="60" t="n"/>
+      <c r="I33" s="60" t="n"/>
+      <c r="J33" s="60" t="n"/>
+      <c r="K33" s="60" t="n"/>
+      <c r="L33" s="60" t="n"/>
+      <c r="M33" s="60" t="n"/>
+      <c r="N33" s="60" t="n"/>
+      <c r="O33" s="60" t="n"/>
+      <c r="P33" s="60" t="n"/>
+      <c r="Q33" s="60" t="n"/>
+      <c r="R33" s="60" t="n"/>
+      <c r="S33" s="60" t="n"/>
+      <c r="T33" s="60" t="n"/>
+      <c r="U33" s="60" t="n"/>
+      <c r="V33" s="60" t="n"/>
+      <c r="W33" s="60" t="n"/>
+      <c r="X33" s="60" t="n"/>
+      <c r="Y33" s="60" t="n"/>
+      <c r="Z33" s="60" t="n"/>
+      <c r="AA33" s="60" t="n"/>
+      <c r="AB33" s="60" t="n"/>
+      <c r="AC33" s="60" t="n"/>
+      <c r="AD33" s="60" t="n"/>
+      <c r="AE33" s="60" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="76" t="inlineStr">
+      <c r="A34" s="58" t="inlineStr">
         <is>
           <t>vn:EIDE</t>
         </is>
       </c>
-      <c r="B34" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="C34" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="D34" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="E34" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="F34" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="G34" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="H34" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="I34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q34" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R34" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="S34" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="T34" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="U34" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="V34" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="W34" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="X34" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y34" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z34" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA34" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB34" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC34" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD34" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE34" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
+      <c r="B34" s="60" t="n"/>
+      <c r="C34" s="60" t="n"/>
+      <c r="D34" s="60" t="n"/>
+      <c r="E34" s="60" t="n"/>
+      <c r="F34" s="60" t="n"/>
+      <c r="G34" s="60" t="n"/>
+      <c r="H34" s="60" t="n"/>
+      <c r="I34" s="60" t="n"/>
+      <c r="J34" s="60" t="n"/>
+      <c r="K34" s="60" t="n"/>
+      <c r="L34" s="60" t="n"/>
+      <c r="M34" s="60" t="n"/>
+      <c r="N34" s="60" t="n"/>
+      <c r="O34" s="60" t="n"/>
+      <c r="P34" s="60" t="n"/>
+      <c r="Q34" s="60" t="n"/>
+      <c r="R34" s="60" t="n"/>
+      <c r="S34" s="60" t="n"/>
+      <c r="T34" s="60" t="n"/>
+      <c r="U34" s="60" t="n"/>
+      <c r="V34" s="60" t="n"/>
+      <c r="W34" s="60" t="n"/>
+      <c r="X34" s="60" t="n"/>
+      <c r="Y34" s="60" t="n"/>
+      <c r="Z34" s="60" t="n"/>
+      <c r="AA34" s="60" t="n"/>
+      <c r="AB34" s="60" t="n"/>
+      <c r="AC34" s="60" t="n"/>
+      <c r="AD34" s="60" t="n"/>
+      <c r="AE34" s="60" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="76" t="inlineStr">
+      <c r="A35" s="58" t="inlineStr">
         <is>
           <t>vn:RNG60</t>
         </is>
       </c>
-      <c r="B35" s="95" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C35" s="95" t="n">
-        <v>-1.08</v>
-      </c>
-      <c r="D35" s="95" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="E35" s="95" t="n">
-        <v>-1.21</v>
-      </c>
-      <c r="F35" s="95" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G35" s="95" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H35" s="95" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="I35" s="95" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J35" s="95" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="K35" s="95" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="L35" s="95" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="M35" s="95" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="N35" s="95" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="O35" s="95" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P35" s="95" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="Q35" s="95" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="R35" s="95" t="n">
-        <v>-3.34</v>
-      </c>
-      <c r="S35" s="95" t="n">
-        <v>-2.39</v>
-      </c>
-      <c r="T35" s="95" t="n">
-        <v>-1.83</v>
-      </c>
-      <c r="U35" s="95" t="n">
-        <v>-2.05</v>
-      </c>
-      <c r="V35" s="95" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="W35" s="95" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="X35" s="95" t="n">
-        <v>-2.12</v>
-      </c>
-      <c r="Y35" s="95" t="n">
-        <v>-2.46</v>
-      </c>
-      <c r="Z35" s="95" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="AA35" s="95" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="AB35" s="95" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="AC35" s="95" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="AD35" s="95" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="AE35" s="95" t="n">
-        <v>-0.17</v>
-      </c>
+      <c r="B35" s="60" t="n"/>
+      <c r="C35" s="60" t="n"/>
+      <c r="D35" s="60" t="n"/>
+      <c r="E35" s="60" t="n"/>
+      <c r="F35" s="60" t="n"/>
+      <c r="G35" s="60" t="n"/>
+      <c r="H35" s="60" t="n"/>
+      <c r="I35" s="60" t="n"/>
+      <c r="J35" s="60" t="n"/>
+      <c r="K35" s="60" t="n"/>
+      <c r="L35" s="60" t="n"/>
+      <c r="M35" s="60" t="n"/>
+      <c r="N35" s="60" t="n"/>
+      <c r="O35" s="60" t="n"/>
+      <c r="P35" s="60" t="n"/>
+      <c r="Q35" s="60" t="n"/>
+      <c r="R35" s="60" t="n"/>
+      <c r="S35" s="60" t="n"/>
+      <c r="T35" s="60" t="n"/>
+      <c r="U35" s="60" t="n"/>
+      <c r="V35" s="60" t="n"/>
+      <c r="W35" s="60" t="n"/>
+      <c r="X35" s="60" t="n"/>
+      <c r="Y35" s="60" t="n"/>
+      <c r="Z35" s="60" t="n"/>
+      <c r="AA35" s="60" t="n"/>
+      <c r="AB35" s="60" t="n"/>
+      <c r="AC35" s="60" t="n"/>
+      <c r="AD35" s="60" t="n"/>
+      <c r="AE35" s="60" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="76" t="inlineStr">
+      <c r="A36" s="58" t="inlineStr">
         <is>
           <t>vn:RNG120</t>
         </is>
       </c>
-      <c r="B36" s="95" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="C36" s="95" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="D36" s="95" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="E36" s="95" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="F36" s="95" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="G36" s="95" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="H36" s="95" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="I36" s="95" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="J36" s="95" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="K36" s="95" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="L36" s="95" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="M36" s="95" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="N36" s="95" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="O36" s="95" t="n">
-        <v>-1.47</v>
-      </c>
-      <c r="P36" s="95" t="n">
-        <v>-1.42</v>
-      </c>
-      <c r="Q36" s="95" t="n">
-        <v>-1.81</v>
-      </c>
-      <c r="R36" s="95" t="n">
-        <v>-2.26</v>
-      </c>
-      <c r="S36" s="95" t="n">
-        <v>-2.35</v>
-      </c>
-      <c r="T36" s="95" t="n">
-        <v>-1.57</v>
-      </c>
-      <c r="U36" s="95" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="V36" s="95" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W36" s="95" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="X36" s="95" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="Y36" s="95" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="Z36" s="95" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AA36" s="95" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AB36" s="95" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AC36" s="95" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD36" s="95" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AE36" s="95" t="n">
-        <v>2.73</v>
-      </c>
+      <c r="B36" s="60" t="n"/>
+      <c r="C36" s="60" t="n"/>
+      <c r="D36" s="60" t="n"/>
+      <c r="E36" s="60" t="n"/>
+      <c r="F36" s="60" t="n"/>
+      <c r="G36" s="60" t="n"/>
+      <c r="H36" s="60" t="n"/>
+      <c r="I36" s="60" t="n"/>
+      <c r="J36" s="60" t="n"/>
+      <c r="K36" s="60" t="n"/>
+      <c r="L36" s="60" t="n"/>
+      <c r="M36" s="60" t="n"/>
+      <c r="N36" s="60" t="n"/>
+      <c r="O36" s="60" t="n"/>
+      <c r="P36" s="60" t="n"/>
+      <c r="Q36" s="60" t="n"/>
+      <c r="R36" s="60" t="n"/>
+      <c r="S36" s="60" t="n"/>
+      <c r="T36" s="60" t="n"/>
+      <c r="U36" s="60" t="n"/>
+      <c r="V36" s="60" t="n"/>
+      <c r="W36" s="60" t="n"/>
+      <c r="X36" s="60" t="n"/>
+      <c r="Y36" s="60" t="n"/>
+      <c r="Z36" s="60" t="n"/>
+      <c r="AA36" s="60" t="n"/>
+      <c r="AB36" s="60" t="n"/>
+      <c r="AC36" s="60" t="n"/>
+      <c r="AD36" s="60" t="n"/>
+      <c r="AE36" s="60" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="76" t="inlineStr">
-        <is>
-          <t>vn:RS3</t>
-        </is>
-      </c>
-      <c r="B37" s="95" t="n">
-        <v>46.98</v>
-      </c>
-      <c r="C37" s="95" t="n">
-        <v>13.62</v>
-      </c>
-      <c r="D37" s="95" t="n">
-        <v>14.32</v>
-      </c>
-      <c r="E37" s="95" t="n">
-        <v>23.23</v>
-      </c>
-      <c r="F37" s="95" t="n">
-        <v>50.34</v>
-      </c>
-      <c r="G37" s="95" t="n">
-        <v>77.23999999999999</v>
-      </c>
-      <c r="H37" s="95" t="n">
-        <v>65.09</v>
-      </c>
-      <c r="I37" s="95" t="n">
-        <v>86.66</v>
-      </c>
-      <c r="J37" s="95" t="n">
-        <v>90.48999999999999</v>
-      </c>
-      <c r="K37" s="95" t="n">
-        <v>88</v>
-      </c>
-      <c r="L37" s="95" t="n">
-        <v>77.98</v>
-      </c>
-      <c r="M37" s="95" t="n">
-        <v>59.82</v>
-      </c>
-      <c r="N37" s="95" t="n">
-        <v>77.68000000000001</v>
-      </c>
-      <c r="O37" s="95" t="n">
-        <v>76.68000000000001</v>
-      </c>
-      <c r="P37" s="95" t="n">
-        <v>68.98</v>
-      </c>
-      <c r="Q37" s="95" t="n">
-        <v>60.96</v>
-      </c>
-      <c r="R37" s="95" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="S37" s="95" t="n">
-        <v>20.58</v>
-      </c>
-      <c r="T37" s="95" t="n">
-        <v>30.12</v>
-      </c>
-      <c r="U37" s="95" t="n">
-        <v>12.08</v>
-      </c>
-      <c r="V37" s="95" t="n">
-        <v>13.57</v>
-      </c>
-      <c r="W37" s="95" t="n">
-        <v>28.44</v>
-      </c>
-      <c r="X37" s="95" t="n">
-        <v>44.72</v>
-      </c>
-      <c r="Y37" s="95" t="n">
-        <v>14.66</v>
-      </c>
-      <c r="Z37" s="95" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="AA37" s="95" t="n">
-        <v>80.38</v>
-      </c>
-      <c r="AB37" s="95" t="n">
-        <v>80.38</v>
-      </c>
-      <c r="AC37" s="95" t="n">
-        <v>80.38</v>
-      </c>
-      <c r="AD37" s="95" t="n">
-        <v>68.92</v>
-      </c>
-      <c r="AE37" s="95" t="n">
-        <v>68.76000000000001</v>
-      </c>
+      <c r="A37" s="58" t="inlineStr">
+        <is>
+          <t>vn:RSI3</t>
+        </is>
+      </c>
+      <c r="B37" s="60" t="n"/>
+      <c r="C37" s="60" t="n"/>
+      <c r="D37" s="60" t="n"/>
+      <c r="E37" s="60" t="n"/>
+      <c r="F37" s="60" t="n"/>
+      <c r="G37" s="60" t="n"/>
+      <c r="H37" s="60" t="n"/>
+      <c r="I37" s="60" t="n"/>
+      <c r="J37" s="60" t="n"/>
+      <c r="K37" s="60" t="n"/>
+      <c r="L37" s="60" t="n"/>
+      <c r="M37" s="60" t="n"/>
+      <c r="N37" s="60" t="n"/>
+      <c r="O37" s="60" t="n"/>
+      <c r="P37" s="60" t="n"/>
+      <c r="Q37" s="60" t="n"/>
+      <c r="R37" s="60" t="n"/>
+      <c r="S37" s="60" t="n"/>
+      <c r="T37" s="60" t="n"/>
+      <c r="U37" s="60" t="n"/>
+      <c r="V37" s="60" t="n"/>
+      <c r="W37" s="60" t="n"/>
+      <c r="X37" s="60" t="n"/>
+      <c r="Y37" s="60" t="n"/>
+      <c r="Z37" s="60" t="n"/>
+      <c r="AA37" s="60" t="n"/>
+      <c r="AB37" s="60" t="n"/>
+      <c r="AC37" s="60" t="n"/>
+      <c r="AD37" s="60" t="n"/>
+      <c r="AE37" s="60" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="76" t="inlineStr">
+      <c r="A38" s="58" t="inlineStr">
         <is>
           <t>sensex:EIDE</t>
         </is>
       </c>
-      <c r="B38" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="C38" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="D38" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="E38" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="F38" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="G38" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="H38" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="I38" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="J38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P38" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U38" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="V38" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W38" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="X38" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y38" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z38" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA38" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
+      <c r="B38" s="60" t="n"/>
+      <c r="C38" s="60" t="n"/>
+      <c r="D38" s="60" t="n"/>
+      <c r="E38" s="60" t="n"/>
+      <c r="F38" s="60" t="n"/>
+      <c r="G38" s="60" t="n"/>
+      <c r="H38" s="60" t="n"/>
+      <c r="I38" s="60" t="n"/>
+      <c r="J38" s="60" t="n"/>
+      <c r="K38" s="60" t="n"/>
+      <c r="L38" s="60" t="n"/>
+      <c r="M38" s="60" t="n"/>
+      <c r="N38" s="60" t="n"/>
+      <c r="O38" s="60" t="n"/>
+      <c r="P38" s="60" t="n"/>
+      <c r="Q38" s="60" t="n"/>
+      <c r="R38" s="60" t="n"/>
+      <c r="S38" s="60" t="n"/>
+      <c r="T38" s="60" t="n"/>
+      <c r="U38" s="60" t="n"/>
+      <c r="V38" s="60" t="n"/>
+      <c r="W38" s="60" t="n"/>
+      <c r="X38" s="60" t="n"/>
+      <c r="Y38" s="60" t="n"/>
+      <c r="Z38" s="60" t="n"/>
+      <c r="AA38" s="60" t="n"/>
+      <c r="AB38" s="60" t="n"/>
+      <c r="AC38" s="60" t="n"/>
+      <c r="AD38" s="60" t="n"/>
+      <c r="AE38" s="60" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="76" t="inlineStr">
+      <c r="A39" s="58" t="inlineStr">
         <is>
           <t>sensex:RNG60</t>
         </is>
       </c>
-      <c r="B39" s="95" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="C39" s="95" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="D39" s="95" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E39" s="95" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="F39" s="95" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="G39" s="95" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="H39" s="95" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="I39" s="95" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J39" s="95" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="K39" s="95" t="n">
-        <v>7.21</v>
-      </c>
-      <c r="L39" s="95" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="M39" s="95" t="n">
-        <v>7.46</v>
-      </c>
-      <c r="N39" s="95" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="O39" s="95" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="P39" s="95" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="Q39" s="95" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="R39" s="95" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="S39" s="95" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="T39" s="95" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="U39" s="95" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="V39" s="95" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W39" s="95" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="X39" s="95" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="Y39" s="95" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="Z39" s="95" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="AA39" s="95" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="AB39" s="95" t="n">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="AC39" s="95" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="AD39" s="95" t="n">
-        <v>13.95</v>
-      </c>
-      <c r="AE39" s="95" t="n">
-        <v>6.95</v>
-      </c>
+      <c r="B39" s="60" t="n"/>
+      <c r="C39" s="60" t="n"/>
+      <c r="D39" s="60" t="n"/>
+      <c r="E39" s="60" t="n"/>
+      <c r="F39" s="60" t="n"/>
+      <c r="G39" s="60" t="n"/>
+      <c r="H39" s="60" t="n"/>
+      <c r="I39" s="60" t="n"/>
+      <c r="J39" s="60" t="n"/>
+      <c r="K39" s="60" t="n"/>
+      <c r="L39" s="60" t="n"/>
+      <c r="M39" s="60" t="n"/>
+      <c r="N39" s="60" t="n"/>
+      <c r="O39" s="60" t="n"/>
+      <c r="P39" s="60" t="n"/>
+      <c r="Q39" s="60" t="n"/>
+      <c r="R39" s="60" t="n"/>
+      <c r="S39" s="60" t="n"/>
+      <c r="T39" s="60" t="n"/>
+      <c r="U39" s="60" t="n"/>
+      <c r="V39" s="60" t="n"/>
+      <c r="W39" s="60" t="n"/>
+      <c r="X39" s="60" t="n"/>
+      <c r="Y39" s="60" t="n"/>
+      <c r="Z39" s="60" t="n"/>
+      <c r="AA39" s="60" t="n"/>
+      <c r="AB39" s="60" t="n"/>
+      <c r="AC39" s="60" t="n"/>
+      <c r="AD39" s="60" t="n"/>
+      <c r="AE39" s="60" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="76" t="inlineStr">
+      <c r="A40" s="58" t="inlineStr">
         <is>
           <t>sensex:RNG120</t>
         </is>
       </c>
-      <c r="B40" s="95" t="n">
-        <v>11.87</v>
-      </c>
-      <c r="C40" s="95" t="n">
-        <v>10.42</v>
-      </c>
-      <c r="D40" s="95" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="E40" s="95" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="F40" s="95" t="n">
-        <v>12.83</v>
-      </c>
-      <c r="G40" s="95" t="n">
-        <v>12.83</v>
-      </c>
-      <c r="H40" s="95" t="n">
-        <v>12.79</v>
-      </c>
-      <c r="I40" s="95" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="J40" s="95" t="n">
-        <v>15.64</v>
-      </c>
-      <c r="K40" s="95" t="n">
-        <v>15.29</v>
-      </c>
-      <c r="L40" s="95" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="M40" s="95" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="N40" s="95" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="O40" s="95" t="n">
-        <v>13.96</v>
-      </c>
-      <c r="P40" s="95" t="n">
-        <v>14.46</v>
-      </c>
-      <c r="Q40" s="95" t="n">
-        <v>14.07</v>
-      </c>
-      <c r="R40" s="95" t="n">
-        <v>14.24</v>
-      </c>
-      <c r="S40" s="95" t="n">
-        <v>14.96</v>
-      </c>
-      <c r="T40" s="95" t="n">
-        <v>15.21</v>
-      </c>
-      <c r="U40" s="95" t="n">
-        <v>12.06</v>
-      </c>
-      <c r="V40" s="95" t="n">
-        <v>12.77</v>
-      </c>
-      <c r="W40" s="95" t="n">
-        <v>11.58</v>
-      </c>
-      <c r="X40" s="95" t="n">
-        <v>11.57</v>
-      </c>
-      <c r="Y40" s="95" t="n">
-        <v>11.58</v>
-      </c>
-      <c r="Z40" s="95" t="n">
-        <v>12.04</v>
-      </c>
-      <c r="AA40" s="95" t="n">
-        <v>11.38</v>
-      </c>
-      <c r="AB40" s="95" t="n">
-        <v>11.44</v>
-      </c>
-      <c r="AC40" s="95" t="n">
-        <v>11.79</v>
-      </c>
-      <c r="AD40" s="95" t="n">
-        <v>11.18</v>
-      </c>
-      <c r="AE40" s="95" t="n">
-        <v>10.81</v>
-      </c>
+      <c r="B40" s="60" t="n"/>
+      <c r="C40" s="60" t="n"/>
+      <c r="D40" s="60" t="n"/>
+      <c r="E40" s="60" t="n"/>
+      <c r="F40" s="60" t="n"/>
+      <c r="G40" s="60" t="n"/>
+      <c r="H40" s="60" t="n"/>
+      <c r="I40" s="60" t="n"/>
+      <c r="J40" s="60" t="n"/>
+      <c r="K40" s="60" t="n"/>
+      <c r="L40" s="60" t="n"/>
+      <c r="M40" s="60" t="n"/>
+      <c r="N40" s="60" t="n"/>
+      <c r="O40" s="60" t="n"/>
+      <c r="P40" s="60" t="n"/>
+      <c r="Q40" s="60" t="n"/>
+      <c r="R40" s="60" t="n"/>
+      <c r="S40" s="60" t="n"/>
+      <c r="T40" s="60" t="n"/>
+      <c r="U40" s="60" t="n"/>
+      <c r="V40" s="60" t="n"/>
+      <c r="W40" s="60" t="n"/>
+      <c r="X40" s="60" t="n"/>
+      <c r="Y40" s="60" t="n"/>
+      <c r="Z40" s="60" t="n"/>
+      <c r="AA40" s="60" t="n"/>
+      <c r="AB40" s="60" t="n"/>
+      <c r="AC40" s="60" t="n"/>
+      <c r="AD40" s="60" t="n"/>
+      <c r="AE40" s="60" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="96" t="inlineStr">
-        <is>
-          <t>sensex:RS10</t>
-        </is>
-      </c>
-      <c r="B41" s="95" t="n">
-        <v>36.52</v>
-      </c>
-      <c r="C41" s="95" t="n">
-        <v>29.96</v>
-      </c>
-      <c r="D41" s="95" t="n">
-        <v>33.56</v>
-      </c>
-      <c r="E41" s="95" t="n">
-        <v>38.91</v>
-      </c>
-      <c r="F41" s="95" t="n">
-        <v>56.68</v>
-      </c>
-      <c r="G41" s="95" t="n">
-        <v>56.68</v>
-      </c>
-      <c r="H41" s="95" t="n">
-        <v>57.12</v>
-      </c>
-      <c r="I41" s="95" t="n">
-        <v>78.04000000000001</v>
-      </c>
-      <c r="J41" s="95" t="n">
-        <v>83.77</v>
-      </c>
-      <c r="K41" s="95" t="n">
-        <v>80.52</v>
-      </c>
-      <c r="L41" s="95" t="n">
-        <v>79.08</v>
-      </c>
-      <c r="M41" s="95" t="n">
-        <v>79.38</v>
-      </c>
-      <c r="N41" s="95" t="n">
-        <v>77.31999999999999</v>
-      </c>
-      <c r="O41" s="95" t="n">
-        <v>66.75</v>
-      </c>
-      <c r="P41" s="95" t="n">
-        <v>64.14</v>
-      </c>
-      <c r="Q41" s="95" t="n">
-        <v>66.76000000000001</v>
-      </c>
-      <c r="R41" s="95" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="S41" s="95" t="n">
-        <v>65.01000000000001</v>
-      </c>
-      <c r="T41" s="95" t="n">
-        <v>66.14</v>
-      </c>
-      <c r="U41" s="95" t="n">
-        <v>50.55</v>
-      </c>
-      <c r="V41" s="95" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="W41" s="95" t="n">
-        <v>52.02</v>
-      </c>
-      <c r="X41" s="95" t="n">
-        <v>46.05</v>
-      </c>
-      <c r="Y41" s="95" t="n">
-        <v>66.09</v>
-      </c>
-      <c r="Z41" s="95" t="n">
-        <v>70.18000000000001</v>
-      </c>
-      <c r="AA41" s="95" t="n">
-        <v>75.84999999999999</v>
-      </c>
-      <c r="AB41" s="95" t="n">
-        <v>75.97</v>
-      </c>
-      <c r="AC41" s="95" t="n">
-        <v>74.36</v>
-      </c>
-      <c r="AD41" s="95" t="n">
-        <v>72.38</v>
-      </c>
-      <c r="AE41" s="95" t="n">
-        <v>69.15000000000001</v>
-      </c>
+      <c r="A41" s="58" t="inlineStr">
+        <is>
+          <t>sensex:RSI7</t>
+        </is>
+      </c>
+      <c r="B41" s="60" t="n"/>
+      <c r="C41" s="60" t="n"/>
+      <c r="D41" s="60" t="n"/>
+      <c r="E41" s="60" t="n"/>
+      <c r="F41" s="60" t="n"/>
+      <c r="G41" s="60" t="n"/>
+      <c r="H41" s="60" t="n"/>
+      <c r="I41" s="60" t="n"/>
+      <c r="J41" s="60" t="n"/>
+      <c r="K41" s="60" t="n"/>
+      <c r="L41" s="60" t="n"/>
+      <c r="M41" s="60" t="n"/>
+      <c r="N41" s="60" t="n"/>
+      <c r="O41" s="60" t="n"/>
+      <c r="P41" s="60" t="n"/>
+      <c r="Q41" s="60" t="n"/>
+      <c r="R41" s="60" t="n"/>
+      <c r="S41" s="60" t="n"/>
+      <c r="T41" s="60" t="n"/>
+      <c r="U41" s="60" t="n"/>
+      <c r="V41" s="60" t="n"/>
+      <c r="W41" s="60" t="n"/>
+      <c r="X41" s="60" t="n"/>
+      <c r="Y41" s="60" t="n"/>
+      <c r="Z41" s="60" t="n"/>
+      <c r="AA41" s="60" t="n"/>
+      <c r="AB41" s="60" t="n"/>
+      <c r="AC41" s="60" t="n"/>
+      <c r="AD41" s="60" t="n"/>
+      <c r="AE41" s="60" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="76" t="inlineStr">
+      <c r="A42" s="58" t="inlineStr">
         <is>
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="C42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="D42" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="E42" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="F42" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="G42" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="H42" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="I42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M42" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N42" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P42" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R42" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T42" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U42" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="V42" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="W42" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="X42" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y42" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z42" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA42" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB42" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC42" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE42" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
+      <c r="B42" s="60" t="n"/>
+      <c r="C42" s="60" t="n"/>
+      <c r="D42" s="60" t="n"/>
+      <c r="E42" s="60" t="n"/>
+      <c r="F42" s="60" t="n"/>
+      <c r="G42" s="60" t="n"/>
+      <c r="H42" s="60" t="n"/>
+      <c r="I42" s="60" t="n"/>
+      <c r="J42" s="60" t="n"/>
+      <c r="K42" s="60" t="n"/>
+      <c r="L42" s="60" t="n"/>
+      <c r="M42" s="60" t="n"/>
+      <c r="N42" s="60" t="n"/>
+      <c r="O42" s="60" t="n"/>
+      <c r="P42" s="60" t="n"/>
+      <c r="Q42" s="60" t="n"/>
+      <c r="R42" s="60" t="n"/>
+      <c r="S42" s="60" t="n"/>
+      <c r="T42" s="60" t="n"/>
+      <c r="U42" s="60" t="n"/>
+      <c r="V42" s="60" t="n"/>
+      <c r="W42" s="60" t="n"/>
+      <c r="X42" s="60" t="n"/>
+      <c r="Y42" s="60" t="n"/>
+      <c r="Z42" s="60" t="n"/>
+      <c r="AA42" s="60" t="n"/>
+      <c r="AB42" s="60" t="n"/>
+      <c r="AC42" s="60" t="n"/>
+      <c r="AD42" s="60" t="n"/>
+      <c r="AE42" s="60" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="76" t="inlineStr">
+      <c r="A43" s="58" t="inlineStr">
         <is>
           <t>fr40:RNG60</t>
         </is>
       </c>
-      <c r="B43" s="95" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="C43" s="95" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="D43" s="95" t="n">
-        <v>-2.37</v>
-      </c>
-      <c r="E43" s="95" t="n">
-        <v>-1.96</v>
-      </c>
-      <c r="F43" s="95" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G43" s="95" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="H43" s="95" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I43" s="95" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="J43" s="95" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K43" s="95" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="L43" s="95" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="M43" s="95" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="N43" s="95" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="O43" s="95" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P43" s="95" t="n">
-        <v>-2.16</v>
-      </c>
-      <c r="Q43" s="95" t="n">
-        <v>-2.28</v>
-      </c>
-      <c r="R43" s="95" t="n">
-        <v>-3.34</v>
-      </c>
-      <c r="S43" s="95" t="n">
-        <v>-2.14</v>
-      </c>
-      <c r="T43" s="95" t="n">
-        <v>-3.08</v>
-      </c>
-      <c r="U43" s="95" t="n">
-        <v>-2.29</v>
-      </c>
-      <c r="V43" s="95" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="W43" s="95" t="n">
-        <v>-1.93</v>
-      </c>
-      <c r="X43" s="95" t="n">
-        <v>-2.01</v>
-      </c>
-      <c r="Y43" s="95" t="n">
-        <v>-3.58</v>
-      </c>
-      <c r="Z43" s="95" t="n">
-        <v>-4.62</v>
-      </c>
-      <c r="AA43" s="95" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="AB43" s="95" t="n">
-        <v>-3.14</v>
-      </c>
-      <c r="AC43" s="95" t="n">
-        <v>-4.63</v>
-      </c>
-      <c r="AD43" s="95" t="n">
-        <v>-4.96</v>
-      </c>
-      <c r="AE43" s="95" t="n">
-        <v>-5.36</v>
-      </c>
+      <c r="B43" s="60" t="n"/>
+      <c r="C43" s="60" t="n"/>
+      <c r="D43" s="60" t="n"/>
+      <c r="E43" s="60" t="n"/>
+      <c r="F43" s="60" t="n"/>
+      <c r="G43" s="60" t="n"/>
+      <c r="H43" s="60" t="n"/>
+      <c r="I43" s="60" t="n"/>
+      <c r="J43" s="60" t="n"/>
+      <c r="K43" s="60" t="n"/>
+      <c r="L43" s="60" t="n"/>
+      <c r="M43" s="60" t="n"/>
+      <c r="N43" s="60" t="n"/>
+      <c r="O43" s="60" t="n"/>
+      <c r="P43" s="60" t="n"/>
+      <c r="Q43" s="60" t="n"/>
+      <c r="R43" s="60" t="n"/>
+      <c r="S43" s="60" t="n"/>
+      <c r="T43" s="60" t="n"/>
+      <c r="U43" s="60" t="n"/>
+      <c r="V43" s="60" t="n"/>
+      <c r="W43" s="60" t="n"/>
+      <c r="X43" s="60" t="n"/>
+      <c r="Y43" s="60" t="n"/>
+      <c r="Z43" s="60" t="n"/>
+      <c r="AA43" s="60" t="n"/>
+      <c r="AB43" s="60" t="n"/>
+      <c r="AC43" s="60" t="n"/>
+      <c r="AD43" s="60" t="n"/>
+      <c r="AE43" s="60" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="76" t="inlineStr">
+      <c r="A44" s="58" t="inlineStr">
         <is>
           <t>fr40:RNG120</t>
         </is>
       </c>
-      <c r="B44" s="95" t="n">
-        <v>-6.76</v>
-      </c>
-      <c r="C44" s="95" t="n">
-        <v>-5.56</v>
-      </c>
-      <c r="D44" s="95" t="n">
-        <v>-6.01</v>
-      </c>
-      <c r="E44" s="95" t="n">
-        <v>-6.31</v>
-      </c>
-      <c r="F44" s="95" t="n">
-        <v>-4.48</v>
-      </c>
-      <c r="G44" s="95" t="n">
-        <v>-5.85</v>
-      </c>
-      <c r="H44" s="95" t="n">
-        <v>-4.68</v>
-      </c>
-      <c r="I44" s="95" t="n">
-        <v>-2.89</v>
-      </c>
-      <c r="J44" s="95" t="n">
-        <v>-3.77</v>
-      </c>
-      <c r="K44" s="95" t="n">
-        <v>-6.01</v>
-      </c>
-      <c r="L44" s="95" t="n">
-        <v>-6.35</v>
-      </c>
-      <c r="M44" s="95" t="n">
-        <v>-6.86</v>
-      </c>
-      <c r="N44" s="95" t="n">
-        <v>-7.99</v>
-      </c>
-      <c r="O44" s="95" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="P44" s="95" t="n">
-        <v>-8.43</v>
-      </c>
-      <c r="Q44" s="95" t="n">
-        <v>-8.75</v>
-      </c>
-      <c r="R44" s="95" t="n">
-        <v>-9.210000000000001</v>
-      </c>
-      <c r="S44" s="95" t="n">
-        <v>-8.789999999999999</v>
-      </c>
-      <c r="T44" s="95" t="n">
-        <v>-8.789999999999999</v>
-      </c>
-      <c r="U44" s="95" t="n">
-        <v>-9.26</v>
-      </c>
-      <c r="V44" s="95" t="n">
-        <v>-9.44</v>
-      </c>
-      <c r="W44" s="95" t="n">
-        <v>-9.02</v>
-      </c>
-      <c r="X44" s="95" t="n">
-        <v>-10.35</v>
-      </c>
-      <c r="Y44" s="95" t="n">
-        <v>-8.789999999999999</v>
-      </c>
-      <c r="Z44" s="95" t="n">
-        <v>-8.130000000000001</v>
-      </c>
-      <c r="AA44" s="95" t="n">
-        <v>-7.18</v>
-      </c>
-      <c r="AB44" s="95" t="n">
-        <v>-6.04</v>
-      </c>
-      <c r="AC44" s="95" t="n">
-        <v>-5.64</v>
-      </c>
-      <c r="AD44" s="95" t="n">
-        <v>-4.72</v>
-      </c>
-      <c r="AE44" s="95" t="n">
-        <v>-5.61</v>
-      </c>
+      <c r="B44" s="60" t="n"/>
+      <c r="C44" s="60" t="n"/>
+      <c r="D44" s="60" t="n"/>
+      <c r="E44" s="60" t="n"/>
+      <c r="F44" s="60" t="n"/>
+      <c r="G44" s="60" t="n"/>
+      <c r="H44" s="60" t="n"/>
+      <c r="I44" s="60" t="n"/>
+      <c r="J44" s="60" t="n"/>
+      <c r="K44" s="60" t="n"/>
+      <c r="L44" s="60" t="n"/>
+      <c r="M44" s="60" t="n"/>
+      <c r="N44" s="60" t="n"/>
+      <c r="O44" s="60" t="n"/>
+      <c r="P44" s="60" t="n"/>
+      <c r="Q44" s="60" t="n"/>
+      <c r="R44" s="60" t="n"/>
+      <c r="S44" s="60" t="n"/>
+      <c r="T44" s="60" t="n"/>
+      <c r="U44" s="60" t="n"/>
+      <c r="V44" s="60" t="n"/>
+      <c r="W44" s="60" t="n"/>
+      <c r="X44" s="60" t="n"/>
+      <c r="Y44" s="60" t="n"/>
+      <c r="Z44" s="60" t="n"/>
+      <c r="AA44" s="60" t="n"/>
+      <c r="AB44" s="60" t="n"/>
+      <c r="AC44" s="60" t="n"/>
+      <c r="AD44" s="60" t="n"/>
+      <c r="AE44" s="60" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="76" t="inlineStr">
-        <is>
-          <t>fr40:RS5</t>
-        </is>
-      </c>
-      <c r="B45" s="95" t="n">
-        <v>39.08</v>
-      </c>
-      <c r="C45" s="95" t="n">
-        <v>50.81</v>
-      </c>
-      <c r="D45" s="95" t="n">
-        <v>45.03</v>
-      </c>
-      <c r="E45" s="95" t="n">
-        <v>33.57</v>
-      </c>
-      <c r="F45" s="95" t="n">
-        <v>45.48</v>
-      </c>
-      <c r="G45" s="95" t="n">
-        <v>44.93</v>
-      </c>
-      <c r="H45" s="95" t="n">
-        <v>52.35</v>
-      </c>
-      <c r="I45" s="95" t="n">
-        <v>78.61</v>
-      </c>
-      <c r="J45" s="95" t="n">
-        <v>75.48</v>
-      </c>
-      <c r="K45" s="95" t="n">
-        <v>57.98</v>
-      </c>
-      <c r="L45" s="95" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="M45" s="95" t="n">
-        <v>52.83</v>
-      </c>
-      <c r="N45" s="95" t="n">
-        <v>51.58</v>
-      </c>
-      <c r="O45" s="95" t="n">
-        <v>74.97</v>
-      </c>
-      <c r="P45" s="95" t="n">
-        <v>45.92</v>
-      </c>
-      <c r="Q45" s="95" t="n">
-        <v>59.76</v>
-      </c>
-      <c r="R45" s="95" t="n">
-        <v>48.71</v>
-      </c>
-      <c r="S45" s="95" t="n">
-        <v>53.61</v>
-      </c>
-      <c r="T45" s="95" t="n">
-        <v>45.19</v>
-      </c>
-      <c r="U45" s="95" t="n">
-        <v>32.83</v>
-      </c>
-      <c r="V45" s="95" t="n">
-        <v>34.58</v>
-      </c>
-      <c r="W45" s="95" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="X45" s="95" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="Y45" s="95" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="Z45" s="95" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="AA45" s="95" t="n">
-        <v>48.66</v>
-      </c>
-      <c r="AB45" s="95" t="n">
-        <v>80.73</v>
-      </c>
-      <c r="AC45" s="95" t="n">
-        <v>78.23999999999999</v>
-      </c>
-      <c r="AD45" s="95" t="n">
-        <v>83.84</v>
-      </c>
-      <c r="AE45" s="95" t="n">
-        <v>74.67</v>
-      </c>
+      <c r="A45" s="58" t="inlineStr">
+        <is>
+          <t>fr40:RSI3</t>
+        </is>
+      </c>
+      <c r="B45" s="60" t="n"/>
+      <c r="C45" s="60" t="n"/>
+      <c r="D45" s="60" t="n"/>
+      <c r="E45" s="60" t="n"/>
+      <c r="F45" s="60" t="n"/>
+      <c r="G45" s="60" t="n"/>
+      <c r="H45" s="60" t="n"/>
+      <c r="I45" s="60" t="n"/>
+      <c r="J45" s="60" t="n"/>
+      <c r="K45" s="60" t="n"/>
+      <c r="L45" s="60" t="n"/>
+      <c r="M45" s="60" t="n"/>
+      <c r="N45" s="60" t="n"/>
+      <c r="O45" s="60" t="n"/>
+      <c r="P45" s="60" t="n"/>
+      <c r="Q45" s="60" t="n"/>
+      <c r="R45" s="60" t="n"/>
+      <c r="S45" s="60" t="n"/>
+      <c r="T45" s="60" t="n"/>
+      <c r="U45" s="60" t="n"/>
+      <c r="V45" s="60" t="n"/>
+      <c r="W45" s="60" t="n"/>
+      <c r="X45" s="60" t="n"/>
+      <c r="Y45" s="60" t="n"/>
+      <c r="Z45" s="60" t="n"/>
+      <c r="AA45" s="60" t="n"/>
+      <c r="AB45" s="60" t="n"/>
+      <c r="AC45" s="60" t="n"/>
+      <c r="AD45" s="60" t="n"/>
+      <c r="AE45" s="60" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="76" t="inlineStr">
+      <c r="A46" s="58" t="inlineStr">
         <is>
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="C46" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="D46" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="E46" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="F46" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="G46" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="H46" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="I46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K46" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="L46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N46" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U46" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="V46" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="W46" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="X46" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y46" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z46" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA46" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB46" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC46" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE46" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
+      <c r="B46" s="60" t="n"/>
+      <c r="C46" s="60" t="n"/>
+      <c r="D46" s="60" t="n"/>
+      <c r="E46" s="60" t="n"/>
+      <c r="F46" s="60" t="n"/>
+      <c r="G46" s="60" t="n"/>
+      <c r="H46" s="60" t="n"/>
+      <c r="I46" s="60" t="n"/>
+      <c r="J46" s="60" t="n"/>
+      <c r="K46" s="60" t="n"/>
+      <c r="L46" s="60" t="n"/>
+      <c r="M46" s="60" t="n"/>
+      <c r="N46" s="60" t="n"/>
+      <c r="O46" s="60" t="n"/>
+      <c r="P46" s="60" t="n"/>
+      <c r="Q46" s="60" t="n"/>
+      <c r="R46" s="60" t="n"/>
+      <c r="S46" s="60" t="n"/>
+      <c r="T46" s="60" t="n"/>
+      <c r="U46" s="60" t="n"/>
+      <c r="V46" s="60" t="n"/>
+      <c r="W46" s="60" t="n"/>
+      <c r="X46" s="60" t="n"/>
+      <c r="Y46" s="60" t="n"/>
+      <c r="Z46" s="60" t="n"/>
+      <c r="AA46" s="60" t="n"/>
+      <c r="AB46" s="60" t="n"/>
+      <c r="AC46" s="60" t="n"/>
+      <c r="AD46" s="60" t="n"/>
+      <c r="AE46" s="60" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="76" t="inlineStr">
+      <c r="A47" s="58" t="inlineStr">
         <is>
           <t>dax30:RNG60</t>
         </is>
       </c>
-      <c r="B47" s="95" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="C47" s="95" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="D47" s="95" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="E47" s="95" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="F47" s="95" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="G47" s="95" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="H47" s="95" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="I47" s="95" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J47" s="95" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="K47" s="95" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="L47" s="95" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="M47" s="95" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="N47" s="95" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O47" s="95" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="P47" s="95" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="Q47" s="95" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="R47" s="95" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S47" s="95" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T47" s="95" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="U47" s="95" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V47" s="95" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="W47" s="95" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="X47" s="95" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Y47" s="95" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z47" s="95" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="AA47" s="95" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB47" s="95" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AC47" s="95" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD47" s="95" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE47" s="95" t="n">
-        <v>1.11</v>
-      </c>
+      <c r="B47" s="60" t="n"/>
+      <c r="C47" s="60" t="n"/>
+      <c r="D47" s="60" t="n"/>
+      <c r="E47" s="60" t="n"/>
+      <c r="F47" s="60" t="n"/>
+      <c r="G47" s="60" t="n"/>
+      <c r="H47" s="60" t="n"/>
+      <c r="I47" s="60" t="n"/>
+      <c r="J47" s="60" t="n"/>
+      <c r="K47" s="60" t="n"/>
+      <c r="L47" s="60" t="n"/>
+      <c r="M47" s="60" t="n"/>
+      <c r="N47" s="60" t="n"/>
+      <c r="O47" s="60" t="n"/>
+      <c r="P47" s="60" t="n"/>
+      <c r="Q47" s="60" t="n"/>
+      <c r="R47" s="60" t="n"/>
+      <c r="S47" s="60" t="n"/>
+      <c r="T47" s="60" t="n"/>
+      <c r="U47" s="60" t="n"/>
+      <c r="V47" s="60" t="n"/>
+      <c r="W47" s="60" t="n"/>
+      <c r="X47" s="60" t="n"/>
+      <c r="Y47" s="60" t="n"/>
+      <c r="Z47" s="60" t="n"/>
+      <c r="AA47" s="60" t="n"/>
+      <c r="AB47" s="60" t="n"/>
+      <c r="AC47" s="60" t="n"/>
+      <c r="AD47" s="60" t="n"/>
+      <c r="AE47" s="60" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="76" t="inlineStr">
+      <c r="A48" s="58" t="inlineStr">
         <is>
           <t>dax30:RNG120</t>
         </is>
       </c>
-      <c r="B48" s="95" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="C48" s="95" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="D48" s="95" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="E48" s="95" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="F48" s="95" t="n">
-        <v>7.87</v>
-      </c>
-      <c r="G48" s="95" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="H48" s="95" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="I48" s="95" t="n">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="J48" s="95" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="K48" s="95" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="L48" s="95" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M48" s="95" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N48" s="95" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="O48" s="95" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="P48" s="95" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q48" s="95" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="R48" s="95" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S48" s="95" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="T48" s="95" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="U48" s="95" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="V48" s="95" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="W48" s="95" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="X48" s="95" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Y48" s="95" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="Z48" s="95" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA48" s="95" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="AB48" s="95" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AC48" s="95" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="AD48" s="95" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="AE48" s="95" t="n">
-        <v>5.43</v>
-      </c>
+      <c r="B48" s="60" t="n"/>
+      <c r="C48" s="60" t="n"/>
+      <c r="D48" s="60" t="n"/>
+      <c r="E48" s="60" t="n"/>
+      <c r="F48" s="60" t="n"/>
+      <c r="G48" s="60" t="n"/>
+      <c r="H48" s="60" t="n"/>
+      <c r="I48" s="60" t="n"/>
+      <c r="J48" s="60" t="n"/>
+      <c r="K48" s="60" t="n"/>
+      <c r="L48" s="60" t="n"/>
+      <c r="M48" s="60" t="n"/>
+      <c r="N48" s="60" t="n"/>
+      <c r="O48" s="60" t="n"/>
+      <c r="P48" s="60" t="n"/>
+      <c r="Q48" s="60" t="n"/>
+      <c r="R48" s="60" t="n"/>
+      <c r="S48" s="60" t="n"/>
+      <c r="T48" s="60" t="n"/>
+      <c r="U48" s="60" t="n"/>
+      <c r="V48" s="60" t="n"/>
+      <c r="W48" s="60" t="n"/>
+      <c r="X48" s="60" t="n"/>
+      <c r="Y48" s="60" t="n"/>
+      <c r="Z48" s="60" t="n"/>
+      <c r="AA48" s="60" t="n"/>
+      <c r="AB48" s="60" t="n"/>
+      <c r="AC48" s="60" t="n"/>
+      <c r="AD48" s="60" t="n"/>
+      <c r="AE48" s="60" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="76" t="inlineStr">
-        <is>
-          <t>dax30:RS6</t>
-        </is>
-      </c>
-      <c r="B49" s="95" t="n">
-        <v>41.06</v>
-      </c>
-      <c r="C49" s="95" t="n">
-        <v>52.29</v>
-      </c>
-      <c r="D49" s="95" t="n">
-        <v>53.55</v>
-      </c>
-      <c r="E49" s="95" t="n">
-        <v>46.86</v>
-      </c>
-      <c r="F49" s="95" t="n">
-        <v>56.45</v>
-      </c>
-      <c r="G49" s="95" t="n">
-        <v>59.76</v>
-      </c>
-      <c r="H49" s="95" t="n">
-        <v>67.34999999999999</v>
-      </c>
-      <c r="I49" s="95" t="n">
-        <v>78.38</v>
-      </c>
-      <c r="J49" s="95" t="n">
-        <v>72.42</v>
-      </c>
-      <c r="K49" s="95" t="n">
-        <v>59.91</v>
-      </c>
-      <c r="L49" s="95" t="n">
-        <v>66</v>
-      </c>
-      <c r="M49" s="95" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="N49" s="95" t="n">
-        <v>52.95</v>
-      </c>
-      <c r="O49" s="95" t="n">
-        <v>75.06999999999999</v>
-      </c>
-      <c r="P49" s="95" t="n">
-        <v>61.14</v>
-      </c>
-      <c r="Q49" s="95" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="R49" s="95" t="n">
-        <v>57.16</v>
-      </c>
-      <c r="S49" s="95" t="n">
-        <v>62.56</v>
-      </c>
-      <c r="T49" s="95" t="n">
-        <v>52.29</v>
-      </c>
-      <c r="U49" s="95" t="n">
-        <v>37.42</v>
-      </c>
-      <c r="V49" s="95" t="n">
-        <v>31.32</v>
-      </c>
-      <c r="W49" s="95" t="n">
-        <v>40.38</v>
-      </c>
-      <c r="X49" s="95" t="n">
-        <v>26.19</v>
-      </c>
-      <c r="Y49" s="95" t="n">
-        <v>42.54</v>
-      </c>
-      <c r="Z49" s="95" t="n">
-        <v>43.82</v>
-      </c>
-      <c r="AA49" s="95" t="n">
-        <v>58.62</v>
-      </c>
-      <c r="AB49" s="95" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="AC49" s="95" t="n">
-        <v>87.20999999999999</v>
-      </c>
-      <c r="AD49" s="95" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="AE49" s="95" t="n">
-        <v>84.89</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="91" t="inlineStr">
-        <is>
-          <t>今日买报：ixic:RS2:32.92&lt;=38;sensex:RS10:36.52&lt;=39</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="91" t="inlineStr">
-        <is>
-          <t>今日卖报：sh:RNG60:18.3&gt;=10;sh:RS3:99.84&gt;=66;kc:RNG60:46.52&gt;=25;kc:RNG120:38.25&gt;=30;kc:RS5:98.36&gt;=65;cy:RNG60:54.04&gt;=25;cy:RNG120:41.13&gt;=40;cy:RS3:99.77&gt;=93;hk50:RNG60:17.35&gt;=15;hk50:RNG120:25.15&gt;=25</t>
-        </is>
-      </c>
+      <c r="A49" s="58" t="inlineStr">
+        <is>
+          <t>dax30:RSI4</t>
+        </is>
+      </c>
+      <c r="B49" s="60" t="n"/>
+      <c r="C49" s="60" t="n"/>
+      <c r="D49" s="60" t="n"/>
+      <c r="E49" s="60" t="n"/>
+      <c r="F49" s="60" t="n"/>
+      <c r="G49" s="60" t="n"/>
+      <c r="H49" s="60" t="n"/>
+      <c r="I49" s="60" t="n"/>
+      <c r="J49" s="60" t="n"/>
+      <c r="K49" s="60" t="n"/>
+      <c r="L49" s="60" t="n"/>
+      <c r="M49" s="60" t="n"/>
+      <c r="N49" s="60" t="n"/>
+      <c r="O49" s="60" t="n"/>
+      <c r="P49" s="60" t="n"/>
+      <c r="Q49" s="60" t="n"/>
+      <c r="R49" s="60" t="n"/>
+      <c r="S49" s="60" t="n"/>
+      <c r="T49" s="60" t="n"/>
+      <c r="U49" s="60" t="n"/>
+      <c r="V49" s="60" t="n"/>
+      <c r="W49" s="60" t="n"/>
+      <c r="X49" s="60" t="n"/>
+      <c r="Y49" s="60" t="n"/>
+      <c r="Z49" s="60" t="n"/>
+      <c r="AA49" s="60" t="n"/>
+      <c r="AB49" s="60" t="n"/>
+      <c r="AC49" s="60" t="n"/>
+      <c r="AD49" s="60" t="n"/>
+      <c r="AE49" s="60" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:AE1">
@@ -11891,12 +8272,6 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="50">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:AE2">
     <cfRule type="colorScale" priority="2">
@@ -11907,12 +8282,6 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="51">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:AE3">
     <cfRule type="colorScale" priority="3">
@@ -11923,14 +8292,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="52">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:AE4">
     <cfRule type="colorScale" priority="4">
@@ -11941,14 +8302,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="53">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:AE5">
     <cfRule type="colorScale" priority="5">
@@ -11959,14 +8312,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="54">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:AE6">
     <cfRule type="colorScale" priority="7">
@@ -11977,12 +8322,6 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="55">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:AE7">
     <cfRule type="colorScale" priority="8">
@@ -11993,14 +8332,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="56">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:AE8">
     <cfRule type="colorScale" priority="9">
@@ -12011,14 +8342,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="57">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:AE9">
     <cfRule type="colorScale" priority="10">
@@ -12029,14 +8352,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="58">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10:AE10">
     <cfRule type="colorScale" priority="12">
@@ -12047,12 +8362,6 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="59">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:AE11">
     <cfRule type="colorScale" priority="13">
@@ -12063,14 +8372,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="60">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:AE12">
     <cfRule type="colorScale" priority="14">
@@ -12081,14 +8382,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="61">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:AE13">
     <cfRule type="colorScale" priority="15">
@@ -12099,14 +8392,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="62">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:AE14">
     <cfRule type="colorScale" priority="17">
@@ -12117,12 +8402,6 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="63">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:AE15">
     <cfRule type="colorScale" priority="18">
@@ -12133,14 +8412,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="64">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:AE16">
     <cfRule type="colorScale" priority="19">
@@ -12151,14 +8422,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="65">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:AE17">
     <cfRule type="colorScale" priority="20">
@@ -12169,14 +8432,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="66">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:AE18">
     <cfRule type="colorScale" priority="22">
@@ -12187,12 +8442,6 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="67">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:AE19">
     <cfRule type="colorScale" priority="23">
@@ -12203,14 +8452,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="68">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20:AE20">
     <cfRule type="colorScale" priority="24">
@@ -12221,14 +8462,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="69">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:AE21">
     <cfRule type="colorScale" priority="25">
@@ -12239,14 +8472,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="70">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:AE22">
     <cfRule type="colorScale" priority="27">
@@ -12257,12 +8482,6 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="71">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:AE23">
     <cfRule type="colorScale" priority="28">
@@ -12273,14 +8492,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="72">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24:AE24">
     <cfRule type="colorScale" priority="29">
@@ -12291,14 +8502,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="73">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25:AE25">
     <cfRule type="colorScale" priority="30">
@@ -12309,14 +8512,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="74">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:AE26">
     <cfRule type="colorScale" priority="32">
@@ -12327,12 +8522,6 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="75">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27:AE27">
     <cfRule type="colorScale" priority="33">
@@ -12343,14 +8532,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="76">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:AE28">
     <cfRule type="colorScale" priority="34">
@@ -12361,14 +8542,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="77">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29:AE29">
     <cfRule type="colorScale" priority="35">
@@ -12379,14 +8552,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="78">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30:AE30">
     <cfRule type="colorScale" priority="37">
@@ -12397,12 +8562,6 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="79">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:AE31">
     <cfRule type="colorScale" priority="38">
@@ -12413,14 +8572,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="80">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32:AE32">
     <cfRule type="colorScale" priority="39">
@@ -12431,14 +8582,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="81">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:AE33">
     <cfRule type="colorScale" priority="40">
@@ -12449,14 +8592,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="82">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34:AE34">
     <cfRule type="colorScale" priority="42">
@@ -12467,12 +8602,6 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="83">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35:AE35">
     <cfRule type="colorScale" priority="43">
@@ -12483,14 +8612,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="84">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36:AE36">
     <cfRule type="colorScale" priority="44">
@@ -12501,14 +8622,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="85">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37:AE37">
     <cfRule type="colorScale" priority="45">
@@ -12519,14 +8632,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="86">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:AE38">
     <cfRule type="colorScale" priority="47">
@@ -12537,12 +8642,6 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="87">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B39:AE39">
     <cfRule type="colorScale" priority="48">
@@ -12553,14 +8652,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="88">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B40:AE40">
     <cfRule type="colorScale" priority="49">
@@ -12571,14 +8662,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="89">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41:AE41">
     <cfRule type="colorScale" priority="50">
@@ -12589,14 +8672,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="90">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42:AE42">
     <cfRule type="colorScale" priority="52">
@@ -12607,12 +8682,6 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="91">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43:AE43">
     <cfRule type="colorScale" priority="53">
@@ -12623,14 +8692,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="92">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44:AE44">
     <cfRule type="colorScale" priority="54">
@@ -12641,14 +8702,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="93">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45:AE45">
     <cfRule type="colorScale" priority="55">
@@ -12659,14 +8712,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="94">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:AE46">
     <cfRule type="colorScale" priority="57">
@@ -12677,12 +8722,6 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="95">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47:AE47">
     <cfRule type="colorScale" priority="58">
@@ -12693,14 +8732,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="96">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:AE48">
     <cfRule type="colorScale" priority="59">
@@ -12711,14 +8742,6 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="97">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49:AE49">
     <cfRule type="colorScale" priority="60">
@@ -12727,14 +8750,6 @@
         <cfvo type="max"/>
         <color rgb="FFF8544C"/>
         <color rgb="FF9AE854"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="98">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00F8544C"/>
-        <color rgb="009AE854"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -15478,13 +11493,13 @@
       <c r="G2" s="36" t="n">
         <v>66</v>
       </c>
-      <c r="H2" s="97" t="n">
+      <c r="H2" s="92" t="n">
         <v>22.3514585</v>
       </c>
       <c r="I2" s="36" t="n">
         <v>7.06</v>
       </c>
-      <c r="J2" s="98">
+      <c r="J2" s="93">
         <f>(1+H2/100)^(1/(YEAR(D2)-YEAR(C2)))-1</f>
         <v/>
       </c>
@@ -15516,13 +11531,13 @@
       <c r="G3" s="39" t="n">
         <v>73</v>
       </c>
-      <c r="H3" s="99" t="n">
+      <c r="H3" s="94" t="n">
         <v>35.0298984</v>
       </c>
       <c r="I3" s="39" t="n">
         <v>11.41</v>
       </c>
-      <c r="J3" s="98">
+      <c r="J3" s="93">
         <f>(1+H3/100)^(1/(YEAR(D3)-YEAR(C3)))-1</f>
         <v/>
       </c>
@@ -15554,13 +11569,13 @@
       <c r="G4" s="39" t="n">
         <v>85</v>
       </c>
-      <c r="H4" s="99" t="n">
+      <c r="H4" s="94" t="n">
         <v>122.4911655</v>
       </c>
       <c r="I4" s="39" t="n">
         <v>76.98</v>
       </c>
-      <c r="J4" s="100">
+      <c r="J4" s="95">
         <f>(1+H4/100)^(1/(YEAR(D4)-YEAR(C4)))-1</f>
         <v/>
       </c>
@@ -15592,13 +11607,13 @@
       <c r="G5" s="39" t="n">
         <v>96</v>
       </c>
-      <c r="H5" s="99" t="n">
+      <c r="H5" s="94" t="n">
         <v>136.13543</v>
       </c>
       <c r="I5" s="39" t="n">
         <v>100.05</v>
       </c>
-      <c r="J5" s="100">
+      <c r="J5" s="95">
         <f>(1+H5/100)^(1/(YEAR(D5)-YEAR(C5)))-1</f>
         <v/>
       </c>
@@ -15630,13 +11645,13 @@
       <c r="G6" s="39" t="n">
         <v>95</v>
       </c>
-      <c r="H6" s="99" t="n">
+      <c r="H6" s="94" t="n">
         <v>95.7546074</v>
       </c>
       <c r="I6" s="39" t="n">
         <v>44.37</v>
       </c>
-      <c r="J6" s="100">
+      <c r="J6" s="95">
         <f>(1+H6/100)^(1/(YEAR(D6)-YEAR(C6)))-1</f>
         <v/>
       </c>
@@ -15668,13 +11683,13 @@
       <c r="G7" s="39" t="n">
         <v>86</v>
       </c>
-      <c r="H7" s="99" t="n">
+      <c r="H7" s="94" t="n">
         <v>123.8525927</v>
       </c>
       <c r="I7" s="39" t="n">
         <v>63.41</v>
       </c>
-      <c r="J7" s="100">
+      <c r="J7" s="95">
         <f>(1+H7/100)^(1/(YEAR(D7)-YEAR(C7)))-1</f>
         <v/>
       </c>
@@ -15706,13 +11721,13 @@
       <c r="G8" s="39" t="n">
         <v>87</v>
       </c>
-      <c r="H8" s="99" t="n">
+      <c r="H8" s="94" t="n">
         <v>81.41461922000001</v>
       </c>
       <c r="I8" s="39" t="n">
         <v>26.39</v>
       </c>
-      <c r="J8" s="100">
+      <c r="J8" s="95">
         <f>(1+H8/100)^(1/(YEAR(D8)-YEAR(C8)))-1</f>
         <v/>
       </c>
@@ -15744,13 +11759,13 @@
       <c r="G9" s="39" t="n">
         <v>83</v>
       </c>
-      <c r="H9" s="99" t="n">
+      <c r="H9" s="94" t="n">
         <v>47.02060524</v>
       </c>
       <c r="I9" s="39" t="n">
         <v>37.82</v>
       </c>
-      <c r="J9" s="100">
+      <c r="J9" s="95">
         <f>(1+H9/100)^(1/(YEAR(D9)-YEAR(C9)))-1</f>
         <v/>
       </c>
@@ -15781,13 +11796,13 @@
       <c r="G10" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="H10" s="101" t="n">
+      <c r="H10" s="96" t="n">
         <v>27.8860732</v>
       </c>
       <c r="I10" s="24" t="n">
         <v>-10.97</v>
       </c>
-      <c r="J10" s="102" t="n">
+      <c r="J10" s="97" t="n">
         <v>0.278860732</v>
       </c>
     </row>
@@ -15818,13 +11833,13 @@
       <c r="G11" s="24" t="n">
         <v>93</v>
       </c>
-      <c r="H11" s="101" t="n">
+      <c r="H11" s="96" t="n">
         <v>17.4948656</v>
       </c>
       <c r="I11" s="24" t="n">
         <v>-7.7</v>
       </c>
-      <c r="J11" s="102">
+      <c r="J11" s="97">
         <f>(1+H11/100)^(1/(YEAR(D11)-YEAR(C11)))-1</f>
         <v/>
       </c>

--- a/report_2410.xlsx
+++ b/report_2410.xlsx
@@ -486,12 +486,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ff0000"/>
+        <fgColor rgb="000000ff"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000000ff"/>
+        <fgColor rgb="00ff0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -1439,152 +1439,152 @@
       </c>
       <c r="B1" s="77" t="inlineStr">
         <is>
+          <t>241009</t>
+        </is>
+      </c>
+      <c r="C1" s="77" t="inlineStr">
+        <is>
           <t>241008</t>
         </is>
       </c>
-      <c r="C1" s="77" t="inlineStr">
+      <c r="D1" s="77" t="inlineStr">
         <is>
           <t>240930</t>
         </is>
       </c>
-      <c r="D1" s="77" t="inlineStr">
+      <c r="E1" s="77" t="inlineStr">
         <is>
           <t>240927</t>
         </is>
       </c>
-      <c r="E1" s="77" t="inlineStr">
+      <c r="F1" s="77" t="inlineStr">
         <is>
           <t>240926</t>
         </is>
       </c>
-      <c r="F1" s="77" t="inlineStr">
+      <c r="G1" s="77" t="inlineStr">
         <is>
           <t>240925</t>
         </is>
       </c>
-      <c r="G1" s="77" t="inlineStr">
+      <c r="H1" s="77" t="inlineStr">
         <is>
           <t>240924</t>
         </is>
       </c>
-      <c r="H1" s="77" t="inlineStr">
+      <c r="I1" s="77" t="inlineStr">
         <is>
           <t>240923</t>
         </is>
       </c>
-      <c r="I1" s="77" t="inlineStr">
+      <c r="J1" s="77" t="inlineStr">
         <is>
           <t>240920</t>
         </is>
       </c>
-      <c r="J1" s="77" t="inlineStr">
+      <c r="K1" s="77" t="inlineStr">
         <is>
           <t>240919</t>
         </is>
       </c>
-      <c r="K1" s="77" t="inlineStr">
+      <c r="L1" s="77" t="inlineStr">
         <is>
           <t>240918</t>
         </is>
       </c>
-      <c r="L1" s="77" t="inlineStr">
+      <c r="M1" s="77" t="inlineStr">
         <is>
           <t>240913</t>
         </is>
       </c>
-      <c r="M1" s="77" t="inlineStr">
+      <c r="N1" s="77" t="inlineStr">
         <is>
           <t>240912</t>
         </is>
       </c>
-      <c r="N1" s="77" t="inlineStr">
+      <c r="O1" s="77" t="inlineStr">
         <is>
           <t>240911</t>
         </is>
       </c>
-      <c r="O1" s="77" t="inlineStr">
+      <c r="P1" s="77" t="inlineStr">
         <is>
           <t>240910</t>
         </is>
       </c>
-      <c r="P1" s="77" t="inlineStr">
+      <c r="Q1" s="77" t="inlineStr">
         <is>
           <t>240909</t>
         </is>
       </c>
-      <c r="Q1" s="77" t="inlineStr">
+      <c r="R1" s="77" t="inlineStr">
         <is>
           <t>240906</t>
         </is>
       </c>
-      <c r="R1" s="77" t="inlineStr">
+      <c r="S1" s="77" t="inlineStr">
         <is>
           <t>240905</t>
         </is>
       </c>
-      <c r="S1" s="77" t="inlineStr">
+      <c r="T1" s="77" t="inlineStr">
         <is>
           <t>240904</t>
         </is>
       </c>
-      <c r="T1" s="77" t="inlineStr">
+      <c r="U1" s="77" t="inlineStr">
         <is>
           <t>240903</t>
         </is>
       </c>
-      <c r="U1" s="77" t="inlineStr">
+      <c r="V1" s="77" t="inlineStr">
         <is>
           <t>240902</t>
         </is>
       </c>
-      <c r="V1" s="77" t="inlineStr">
+      <c r="W1" s="77" t="inlineStr">
         <is>
           <t>240830</t>
         </is>
       </c>
-      <c r="W1" s="77" t="inlineStr">
+      <c r="X1" s="77" t="inlineStr">
         <is>
           <t>240829</t>
         </is>
       </c>
-      <c r="X1" s="77" t="inlineStr">
+      <c r="Y1" s="77" t="inlineStr">
         <is>
           <t>240828</t>
         </is>
       </c>
-      <c r="Y1" s="77" t="inlineStr">
+      <c r="Z1" s="77" t="inlineStr">
         <is>
           <t>240827</t>
         </is>
       </c>
-      <c r="Z1" s="77" t="inlineStr">
+      <c r="AA1" s="77" t="inlineStr">
         <is>
           <t>240826</t>
         </is>
       </c>
-      <c r="AA1" s="77" t="inlineStr">
+      <c r="AB1" s="77" t="inlineStr">
         <is>
           <t>240823</t>
         </is>
       </c>
-      <c r="AB1" s="77" t="inlineStr">
+      <c r="AC1" s="77" t="inlineStr">
         <is>
           <t>240822</t>
         </is>
       </c>
-      <c r="AC1" s="77" t="inlineStr">
+      <c r="AD1" s="77" t="inlineStr">
         <is>
           <t>240821</t>
         </is>
       </c>
-      <c r="AD1" s="77" t="inlineStr">
+      <c r="AE1" s="77" t="inlineStr">
         <is>
           <t>240820</t>
-        </is>
-      </c>
-      <c r="AE1" s="77" t="inlineStr">
-        <is>
-          <t>240819</t>
         </is>
       </c>
     </row>
@@ -1595,94 +1595,94 @@
         </is>
       </c>
       <c r="B2" s="78" t="n">
+        <v>3258.86</v>
+      </c>
+      <c r="C2" s="78" t="n">
         <v>3489.78</v>
       </c>
-      <c r="C2" s="78" t="n">
+      <c r="D2" s="78" t="n">
         <v>3336.5</v>
       </c>
-      <c r="D2" s="78" t="n">
+      <c r="E2" s="78" t="n">
         <v>3087.53</v>
       </c>
-      <c r="E2" s="78" t="n">
+      <c r="F2" s="78" t="n">
         <v>3000.95</v>
       </c>
-      <c r="F2" s="78" t="n">
+      <c r="G2" s="78" t="n">
         <v>2896.31</v>
       </c>
-      <c r="G2" s="78" t="n">
+      <c r="H2" s="78" t="n">
         <v>2863.13</v>
       </c>
-      <c r="H2" s="78" t="n">
+      <c r="I2" s="78" t="n">
         <v>2748.92</v>
       </c>
-      <c r="I2" s="78" t="n">
+      <c r="J2" s="78" t="n">
         <v>2736.81</v>
       </c>
-      <c r="J2" s="78" t="n">
+      <c r="K2" s="78" t="n">
         <v>2736.02</v>
       </c>
-      <c r="K2" s="78" t="n">
+      <c r="L2" s="78" t="n">
         <v>2717.28</v>
       </c>
-      <c r="L2" s="78" t="n">
+      <c r="M2" s="78" t="n">
         <v>2704.09</v>
       </c>
-      <c r="M2" s="78" t="n">
+      <c r="N2" s="78" t="n">
         <v>2717.12</v>
       </c>
-      <c r="N2" s="78" t="n">
+      <c r="O2" s="78" t="n">
         <v>2721.8</v>
       </c>
-      <c r="O2" s="78" t="n">
+      <c r="P2" s="78" t="n">
         <v>2744.19</v>
       </c>
-      <c r="P2" s="78" t="n">
+      <c r="Q2" s="78" t="n">
         <v>2736.49</v>
       </c>
-      <c r="Q2" s="78" t="n">
+      <c r="R2" s="78" t="n">
         <v>2765.81</v>
       </c>
-      <c r="R2" s="78" t="n">
+      <c r="S2" s="78" t="n">
         <v>2788.31</v>
       </c>
-      <c r="S2" s="78" t="n">
+      <c r="T2" s="78" t="n">
         <v>2784.28</v>
       </c>
-      <c r="T2" s="78" t="n">
+      <c r="U2" s="78" t="n">
         <v>2802.98</v>
       </c>
-      <c r="U2" s="78" t="n">
+      <c r="V2" s="78" t="n">
         <v>2811.03</v>
       </c>
-      <c r="V2" s="78" t="n">
+      <c r="W2" s="78" t="n">
         <v>2842.21</v>
       </c>
-      <c r="W2" s="78" t="n">
+      <c r="X2" s="78" t="n">
         <v>2823.11</v>
       </c>
-      <c r="X2" s="78" t="n">
+      <c r="Y2" s="78" t="n">
         <v>2837.43</v>
       </c>
-      <c r="Y2" s="78" t="n">
+      <c r="Z2" s="78" t="n">
         <v>2848.73</v>
       </c>
-      <c r="Z2" s="78" t="n">
+      <c r="AA2" s="78" t="n">
         <v>2855.52</v>
       </c>
-      <c r="AA2" s="78" t="n">
+      <c r="AB2" s="78" t="n">
         <v>2854.37</v>
       </c>
-      <c r="AB2" s="78" t="n">
+      <c r="AC2" s="78" t="n">
         <v>2848.77</v>
       </c>
-      <c r="AC2" s="78" t="n">
+      <c r="AD2" s="78" t="n">
         <v>2856.58</v>
       </c>
-      <c r="AD2" s="78" t="n">
+      <c r="AE2" s="78" t="n">
         <v>2866.66</v>
-      </c>
-      <c r="AE2" s="78" t="n">
-        <v>2893.67</v>
       </c>
     </row>
     <row r="3">
@@ -1693,152 +1693,152 @@
       </c>
       <c r="B3" s="79" t="inlineStr">
         <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C3" s="80" t="inlineStr">
+        <is>
           <t>red</t>
         </is>
       </c>
-      <c r="C3" s="79" t="inlineStr">
+      <c r="D3" s="80" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D3" s="79" t="inlineStr">
+      <c r="E3" s="80" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E3" s="79" t="inlineStr">
+      <c r="F3" s="80" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F3" s="79" t="inlineStr">
+      <c r="G3" s="80" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G3" s="79" t="inlineStr">
+      <c r="H3" s="80" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H3" s="80" t="inlineStr">
+      <c r="I3" s="79" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I3" s="80" t="inlineStr">
+      <c r="J3" s="79" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J3" s="80" t="inlineStr">
+      <c r="K3" s="79" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K3" s="80" t="inlineStr">
+      <c r="L3" s="79" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L3" s="81" t="inlineStr">
+      <c r="M3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M3" s="81" t="inlineStr">
+      <c r="N3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N3" s="81" t="inlineStr">
+      <c r="O3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O3" s="81" t="inlineStr">
+      <c r="P3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P3" s="81" t="inlineStr">
+      <c r="Q3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q3" s="81" t="inlineStr">
+      <c r="R3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R3" s="81" t="inlineStr">
+      <c r="S3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S3" s="81" t="inlineStr">
+      <c r="T3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T3" s="81" t="inlineStr">
+      <c r="U3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U3" s="81" t="inlineStr">
+      <c r="V3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V3" s="80" t="inlineStr">
+      <c r="W3" s="79" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W3" s="81" t="inlineStr">
+      <c r="X3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X3" s="81" t="inlineStr">
+      <c r="Y3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y3" s="81" t="inlineStr">
+      <c r="Z3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z3" s="80" t="inlineStr">
+      <c r="AA3" s="79" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA3" s="81" t="inlineStr">
+      <c r="AB3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB3" s="81" t="inlineStr">
+      <c r="AC3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC3" s="81" t="inlineStr">
+      <c r="AD3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD3" s="81" t="inlineStr">
+      <c r="AE3" s="81" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AE3" s="79" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -1849,94 +1849,94 @@
         </is>
       </c>
       <c r="B4" s="78" t="n">
+        <v>-6.62</v>
+      </c>
+      <c r="C4" s="78" t="n">
         <v>4.59</v>
       </c>
-      <c r="C4" s="78" t="n">
+      <c r="D4" s="78" t="n">
         <v>8.06</v>
       </c>
-      <c r="D4" s="78" t="n">
+      <c r="E4" s="78" t="n">
         <v>2.89</v>
       </c>
-      <c r="E4" s="78" t="n">
+      <c r="F4" s="78" t="n">
         <v>3.61</v>
       </c>
-      <c r="F4" s="78" t="n">
+      <c r="G4" s="78" t="n">
         <v>1.16</v>
       </c>
-      <c r="G4" s="78" t="n">
+      <c r="H4" s="78" t="n">
         <v>4.15</v>
       </c>
-      <c r="H4" s="78" t="n">
+      <c r="I4" s="78" t="n">
         <v>0.44</v>
       </c>
-      <c r="I4" s="78" t="n">
+      <c r="J4" s="78" t="n">
         <v>0.03</v>
       </c>
-      <c r="J4" s="78" t="n">
+      <c r="K4" s="78" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="K4" s="78" t="n">
+      <c r="L4" s="78" t="n">
         <v>0.49</v>
       </c>
-      <c r="L4" s="78" t="n">
+      <c r="M4" s="78" t="n">
         <v>-0.48</v>
       </c>
-      <c r="M4" s="78" t="n">
+      <c r="N4" s="78" t="n">
         <v>-0.17</v>
       </c>
-      <c r="N4" s="78" t="n">
+      <c r="O4" s="78" t="n">
         <v>-0.82</v>
       </c>
-      <c r="O4" s="78" t="n">
+      <c r="P4" s="78" t="n">
         <v>0.28</v>
       </c>
-      <c r="P4" s="78" t="n">
+      <c r="Q4" s="78" t="n">
         <v>-1.06</v>
       </c>
-      <c r="Q4" s="78" t="n">
+      <c r="R4" s="78" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="R4" s="78" t="n">
+      <c r="S4" s="78" t="n">
         <v>0.14</v>
       </c>
-      <c r="S4" s="78" t="n">
+      <c r="T4" s="78" t="n">
         <v>-0.67</v>
       </c>
-      <c r="T4" s="78" t="n">
+      <c r="U4" s="78" t="n">
         <v>-0.29</v>
       </c>
-      <c r="U4" s="78" t="n">
+      <c r="V4" s="78" t="n">
         <v>-1.1</v>
       </c>
-      <c r="V4" s="78" t="n">
+      <c r="W4" s="78" t="n">
         <v>0.68</v>
       </c>
-      <c r="W4" s="78" t="n">
+      <c r="X4" s="78" t="n">
         <v>-0.5</v>
       </c>
-      <c r="X4" s="78" t="n">
+      <c r="Y4" s="78" t="n">
         <v>-0.4</v>
       </c>
-      <c r="Y4" s="78" t="n">
+      <c r="Z4" s="78" t="n">
         <v>-0.24</v>
       </c>
-      <c r="Z4" s="78" t="n">
+      <c r="AA4" s="78" t="n">
         <v>0.04</v>
       </c>
-      <c r="AA4" s="78" t="n">
+      <c r="AB4" s="78" t="n">
         <v>0.2</v>
       </c>
-      <c r="AB4" s="78" t="n">
+      <c r="AC4" s="78" t="n">
         <v>-0.27</v>
       </c>
-      <c r="AC4" s="78" t="n">
+      <c r="AD4" s="78" t="n">
         <v>-0.35</v>
       </c>
-      <c r="AD4" s="78" t="n">
+      <c r="AE4" s="78" t="n">
         <v>-0.93</v>
-      </c>
-      <c r="AE4" s="78" t="n">
-        <v>0.49</v>
       </c>
     </row>
     <row r="5">
@@ -1946,94 +1946,94 @@
         </is>
       </c>
       <c r="B5" s="78" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="C5" s="78" t="n">
         <v>18.3</v>
       </c>
-      <c r="C5" s="78" t="n">
+      <c r="D5" s="78" t="n">
         <v>12.81</v>
       </c>
-      <c r="D5" s="78" t="n">
+      <c r="E5" s="78" t="n">
         <v>3.53</v>
       </c>
-      <c r="E5" s="78" t="n">
+      <c r="F5" s="78" t="n">
         <v>0.13</v>
       </c>
-      <c r="F5" s="78" t="n">
+      <c r="G5" s="78" t="n">
         <v>-3.29</v>
       </c>
-      <c r="G5" s="78" t="n">
+      <c r="H5" s="78" t="n">
         <v>-3.51</v>
       </c>
-      <c r="H5" s="78" t="n">
+      <c r="I5" s="78" t="n">
         <v>-6.68</v>
       </c>
-      <c r="I5" s="78" t="n">
+      <c r="J5" s="78" t="n">
         <v>-7.93</v>
       </c>
-      <c r="J5" s="78" t="n">
+      <c r="K5" s="78" t="n">
         <v>-7.25</v>
       </c>
-      <c r="K5" s="78" t="n">
+      <c r="L5" s="78" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="L5" s="78" t="n">
+      <c r="M5" s="78" t="n">
         <v>-9.81</v>
       </c>
-      <c r="M5" s="78" t="n">
+      <c r="N5" s="78" t="n">
         <v>-9.59</v>
       </c>
-      <c r="N5" s="78" t="n">
+      <c r="O5" s="78" t="n">
         <v>-9.82</v>
       </c>
-      <c r="O5" s="78" t="n">
+      <c r="P5" s="78" t="n">
         <v>-9.44</v>
       </c>
-      <c r="P5" s="78" t="n">
+      <c r="Q5" s="78" t="n">
         <v>-9.26</v>
       </c>
-      <c r="Q5" s="78" t="n">
+      <c r="R5" s="78" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="R5" s="78" t="n">
+      <c r="S5" s="78" t="n">
         <v>-7.94</v>
       </c>
-      <c r="S5" s="78" t="n">
+      <c r="T5" s="78" t="n">
         <v>-8.34</v>
       </c>
-      <c r="T5" s="78" t="n">
+      <c r="U5" s="78" t="n">
         <v>-7.43</v>
       </c>
-      <c r="U5" s="78" t="n">
+      <c r="V5" s="78" t="n">
         <v>-7.87</v>
       </c>
-      <c r="V5" s="78" t="n">
+      <c r="W5" s="78" t="n">
         <v>-6.78</v>
       </c>
-      <c r="W5" s="78" t="n">
+      <c r="X5" s="78" t="n">
         <v>-7.9</v>
       </c>
-      <c r="X5" s="78" t="n">
+      <c r="Y5" s="78" t="n">
         <v>-8.210000000000001</v>
       </c>
-      <c r="Y5" s="78" t="n">
+      <c r="Z5" s="78" t="n">
         <v>-7.46</v>
       </c>
-      <c r="Z5" s="78" t="n">
+      <c r="AA5" s="78" t="n">
         <v>-7.49</v>
       </c>
-      <c r="AA5" s="78" t="n">
+      <c r="AB5" s="78" t="n">
         <v>-7.68</v>
       </c>
-      <c r="AB5" s="78" t="n">
+      <c r="AC5" s="78" t="n">
         <v>-8.43</v>
       </c>
-      <c r="AC5" s="78" t="n">
+      <c r="AD5" s="78" t="n">
         <v>-8.140000000000001</v>
       </c>
-      <c r="AD5" s="78" t="n">
+      <c r="AE5" s="78" t="n">
         <v>-8.24</v>
-      </c>
-      <c r="AE5" s="78" t="n">
-        <v>-6.32</v>
       </c>
     </row>
     <row r="6">
@@ -2043,94 +2043,94 @@
         </is>
       </c>
       <c r="B6" s="78" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C6" s="78" t="n">
         <v>14.53</v>
       </c>
-      <c r="C6" s="78" t="n">
+      <c r="D6" s="78" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="D6" s="78" t="n">
+      <c r="E6" s="78" t="n">
         <v>0.41</v>
       </c>
-      <c r="E6" s="78" t="n">
+      <c r="F6" s="78" t="n">
         <v>-2.48</v>
       </c>
-      <c r="F6" s="78" t="n">
+      <c r="G6" s="78" t="n">
         <v>-4.76</v>
       </c>
-      <c r="G6" s="78" t="n">
+      <c r="H6" s="78" t="n">
         <v>-4.9</v>
       </c>
-      <c r="H6" s="78" t="n">
+      <c r="I6" s="78" t="n">
         <v>-8.16</v>
       </c>
-      <c r="I6" s="78" t="n">
+      <c r="J6" s="78" t="n">
         <v>-9.720000000000001</v>
       </c>
-      <c r="J6" s="78" t="n">
+      <c r="K6" s="78" t="n">
         <v>-9.59</v>
       </c>
-      <c r="K6" s="78" t="n">
+      <c r="L6" s="78" t="n">
         <v>-10.85</v>
       </c>
-      <c r="L6" s="78" t="n">
+      <c r="M6" s="78" t="n">
         <v>-12.12</v>
       </c>
-      <c r="M6" s="78" t="n">
+      <c r="N6" s="78" t="n">
         <v>-11.77</v>
       </c>
-      <c r="N6" s="78" t="n">
+      <c r="O6" s="78" t="n">
         <v>-11.13</v>
       </c>
-      <c r="O6" s="78" t="n">
+      <c r="P6" s="78" t="n">
         <v>-11.05</v>
       </c>
-      <c r="P6" s="78" t="n">
+      <c r="Q6" s="78" t="n">
         <v>-10.42</v>
       </c>
-      <c r="Q6" s="78" t="n">
+      <c r="R6" s="78" t="n">
         <v>-8.970000000000001</v>
       </c>
-      <c r="R6" s="78" t="n">
+      <c r="S6" s="78" t="n">
         <v>-8.390000000000001</v>
       </c>
-      <c r="S6" s="78" t="n">
+      <c r="T6" s="78" t="n">
         <v>-8.890000000000001</v>
       </c>
-      <c r="T6" s="78" t="n">
+      <c r="U6" s="78" t="n">
         <v>-8.65</v>
       </c>
-      <c r="U6" s="78" t="n">
+      <c r="V6" s="78" t="n">
         <v>-7.71</v>
       </c>
-      <c r="V6" s="78" t="n">
+      <c r="W6" s="78" t="n">
         <v>-6.12</v>
       </c>
-      <c r="W6" s="78" t="n">
+      <c r="X6" s="78" t="n">
         <v>-7.13</v>
       </c>
-      <c r="X6" s="78" t="n">
+      <c r="Y6" s="78" t="n">
         <v>-6.9</v>
       </c>
-      <c r="Y6" s="78" t="n">
+      <c r="Z6" s="78" t="n">
         <v>-6.27</v>
       </c>
-      <c r="Z6" s="78" t="n">
+      <c r="AA6" s="78" t="n">
         <v>-5.67</v>
       </c>
-      <c r="AA6" s="78" t="n">
+      <c r="AB6" s="78" t="n">
         <v>-5.33</v>
       </c>
-      <c r="AB6" s="78" t="n">
+      <c r="AC6" s="78" t="n">
         <v>-3.69</v>
       </c>
-      <c r="AC6" s="78" t="n">
+      <c r="AD6" s="78" t="n">
         <v>-5.27</v>
       </c>
-      <c r="AD6" s="78" t="n">
+      <c r="AE6" s="78" t="n">
         <v>-3.71</v>
-      </c>
-      <c r="AE6" s="78" t="n">
-        <v>-3.7</v>
       </c>
     </row>
     <row r="7">
@@ -2140,94 +2140,94 @@
         </is>
       </c>
       <c r="B7" s="78" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="C7" s="78" t="n">
         <v>4.34</v>
       </c>
-      <c r="C7" s="78" t="n">
+      <c r="D7" s="78" t="n">
         <v>3.45</v>
       </c>
-      <c r="D7" s="78" t="n">
+      <c r="E7" s="78" t="n">
         <v>2.09</v>
       </c>
-      <c r="E7" s="78" t="n">
+      <c r="F7" s="78" t="n">
         <v>1.75</v>
       </c>
-      <c r="F7" s="78" t="n">
-        <v>1.8</v>
-      </c>
       <c r="G7" s="78" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H7" s="78" t="n">
         <v>1.53</v>
       </c>
-      <c r="H7" s="78" t="n">
+      <c r="I7" s="78" t="n">
         <v>0.91</v>
       </c>
-      <c r="I7" s="78" t="n">
+      <c r="J7" s="78" t="n">
         <v>0.95</v>
       </c>
-      <c r="J7" s="78" t="n">
+      <c r="K7" s="78" t="n">
         <v>1.03</v>
       </c>
-      <c r="K7" s="78" t="n">
+      <c r="L7" s="78" t="n">
         <v>0.8</v>
       </c>
-      <c r="L7" s="78" t="n">
+      <c r="M7" s="78" t="n">
         <v>0.88</v>
       </c>
-      <c r="M7" s="78" t="n">
+      <c r="N7" s="78" t="n">
         <v>0.86</v>
       </c>
-      <c r="N7" s="78" t="n">
+      <c r="O7" s="78" t="n">
         <v>0.83</v>
       </c>
-      <c r="O7" s="78" t="n">
+      <c r="P7" s="78" t="n">
         <v>0.87</v>
       </c>
-      <c r="P7" s="78" t="n">
+      <c r="Q7" s="78" t="n">
         <v>0.86</v>
       </c>
-      <c r="Q7" s="78" t="n">
+      <c r="R7" s="78" t="n">
         <v>0.89</v>
       </c>
-      <c r="R7" s="78" t="n">
+      <c r="S7" s="78" t="n">
         <v>0.87</v>
       </c>
-      <c r="S7" s="78" t="n">
+      <c r="T7" s="78" t="n">
         <v>0.91</v>
       </c>
-      <c r="T7" s="78" t="n">
+      <c r="U7" s="78" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="U7" s="78" t="n">
+      <c r="V7" s="78" t="n">
         <v>1.14</v>
       </c>
-      <c r="V7" s="78" t="n">
+      <c r="W7" s="78" t="n">
         <v>1.4</v>
       </c>
-      <c r="W7" s="78" t="n">
+      <c r="X7" s="78" t="n">
         <v>0.98</v>
       </c>
-      <c r="X7" s="78" t="n">
+      <c r="Y7" s="78" t="n">
         <v>0.8</v>
       </c>
-      <c r="Y7" s="78" t="n">
+      <c r="Z7" s="78" t="n">
         <v>0.82</v>
       </c>
-      <c r="Z7" s="78" t="n">
+      <c r="AA7" s="78" t="n">
         <v>0.84</v>
       </c>
-      <c r="AA7" s="78" t="n">
+      <c r="AB7" s="78" t="n">
         <v>0.82</v>
       </c>
-      <c r="AB7" s="78" t="n">
+      <c r="AC7" s="78" t="n">
         <v>0.88</v>
       </c>
-      <c r="AC7" s="78" t="n">
+      <c r="AD7" s="78" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AD7" s="78" t="n">
+      <c r="AE7" s="78" t="n">
         <v>0.89</v>
-      </c>
-      <c r="AE7" s="78" t="n">
-        <v>0.9</v>
       </c>
     </row>
     <row r="8">
@@ -2237,191 +2237,191 @@
         </is>
       </c>
       <c r="B8" s="78" t="n">
+        <v>29398.22</v>
+      </c>
+      <c r="C8" s="78" t="n">
         <v>34519.39</v>
       </c>
-      <c r="C8" s="78" t="n">
+      <c r="D8" s="78" t="n">
         <v>25930.37</v>
       </c>
-      <c r="D8" s="78" t="n">
+      <c r="E8" s="78" t="n">
         <v>14460.05</v>
       </c>
-      <c r="E8" s="78" t="n">
+      <c r="F8" s="78" t="n">
         <v>11624.35</v>
       </c>
-      <c r="F8" s="78" t="n">
+      <c r="G8" s="78" t="n">
         <v>11573.71</v>
       </c>
-      <c r="G8" s="78" t="n">
+      <c r="H8" s="78" t="n">
         <v>9713.43</v>
       </c>
-      <c r="H8" s="78" t="n">
+      <c r="I8" s="78" t="n">
         <v>5510.02</v>
       </c>
-      <c r="I8" s="78" t="n">
+      <c r="J8" s="78" t="n">
         <v>5747.48</v>
       </c>
-      <c r="J8" s="78" t="n">
+      <c r="K8" s="78" t="n">
         <v>6270.01</v>
       </c>
-      <c r="K8" s="78" t="n">
+      <c r="L8" s="78" t="n">
         <v>4793.28</v>
       </c>
-      <c r="L8" s="78" t="n">
+      <c r="M8" s="78" t="n">
         <v>5247.59</v>
       </c>
-      <c r="M8" s="78" t="n">
+      <c r="N8" s="78" t="n">
         <v>5155.67</v>
       </c>
-      <c r="N8" s="78" t="n">
+      <c r="O8" s="78" t="n">
         <v>4995.56</v>
       </c>
-      <c r="O8" s="78" t="n">
+      <c r="P8" s="78" t="n">
         <v>5276.48</v>
       </c>
-      <c r="P8" s="78" t="n">
+      <c r="Q8" s="78" t="n">
         <v>5186.37</v>
       </c>
-      <c r="Q8" s="78" t="n">
+      <c r="R8" s="78" t="n">
         <v>5426.32</v>
       </c>
-      <c r="R8" s="78" t="n">
+      <c r="S8" s="78" t="n">
         <v>5348.38</v>
       </c>
-      <c r="S8" s="78" t="n">
+      <c r="T8" s="78" t="n">
         <v>5593.8</v>
       </c>
-      <c r="T8" s="78" t="n">
+      <c r="U8" s="78" t="n">
         <v>5806.01</v>
       </c>
-      <c r="U8" s="78" t="n">
+      <c r="V8" s="78" t="n">
         <v>7057.33</v>
       </c>
-      <c r="V8" s="78" t="n">
+      <c r="W8" s="78" t="n">
         <v>8765.889999999999</v>
       </c>
-      <c r="W8" s="78" t="n">
+      <c r="X8" s="78" t="n">
         <v>6072.48</v>
       </c>
-      <c r="X8" s="78" t="n">
+      <c r="Y8" s="78" t="n">
         <v>4966.07</v>
       </c>
-      <c r="Y8" s="78" t="n">
+      <c r="Z8" s="78" t="n">
         <v>5114.57</v>
       </c>
-      <c r="Z8" s="78" t="n">
+      <c r="AA8" s="78" t="n">
         <v>5265.26</v>
       </c>
-      <c r="AA8" s="78" t="n">
+      <c r="AB8" s="78" t="n">
         <v>5102.25</v>
       </c>
-      <c r="AB8" s="78" t="n">
+      <c r="AC8" s="78" t="n">
         <v>5491.53</v>
       </c>
-      <c r="AC8" s="78" t="n">
+      <c r="AD8" s="78" t="n">
         <v>5095.55</v>
       </c>
-      <c r="AD8" s="78" t="n">
+      <c r="AE8" s="78" t="n">
         <v>5577.82</v>
       </c>
-      <c r="AE8" s="78" t="n">
-        <v>5706.17</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="82" t="inlineStr">
+      <c r="A9" s="76" t="inlineStr">
         <is>
           <t>获利比(加权)</t>
         </is>
       </c>
       <c r="B9" s="83" t="n">
-        <v>0.8612</v>
+        <v>0.6112</v>
       </c>
       <c r="C9" s="83" t="n">
-        <v>0.8766</v>
+        <v>0.8611</v>
       </c>
       <c r="D9" s="83" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="E9" s="83" t="n">
-        <v>0.6278</v>
+        <v>0.7141</v>
       </c>
       <c r="F9" s="83" t="n">
-        <v>0.5172</v>
+        <v>0.6276</v>
       </c>
       <c r="G9" s="83" t="n">
-        <v>0.4915</v>
+        <v>0.517</v>
       </c>
       <c r="H9" s="83" t="n">
-        <v>0.3702</v>
+        <v>0.4914</v>
       </c>
       <c r="I9" s="83" t="n">
-        <v>0.3497</v>
+        <v>0.37</v>
       </c>
       <c r="J9" s="83" t="n">
-        <v>0.3444</v>
+        <v>0.3495</v>
       </c>
       <c r="K9" s="83" t="n">
-        <v>0.316</v>
+        <v>0.3442</v>
       </c>
       <c r="L9" s="83" t="n">
-        <v>0.2888</v>
+        <v>0.3158</v>
       </c>
       <c r="M9" s="83" t="n">
-        <v>0.3022</v>
+        <v>0.2886</v>
       </c>
       <c r="N9" s="83" t="n">
-        <v>0.304</v>
+        <v>0.302</v>
       </c>
       <c r="O9" s="83" t="n">
-        <v>0.3233</v>
+        <v>0.3038</v>
       </c>
       <c r="P9" s="83" t="n">
-        <v>0.3078</v>
+        <v>0.3231</v>
       </c>
       <c r="Q9" s="83" t="n">
-        <v>0.3338</v>
+        <v>0.3076</v>
       </c>
       <c r="R9" s="83" t="n">
-        <v>0.3652</v>
+        <v>0.3336</v>
       </c>
       <c r="S9" s="83" t="n">
-        <v>0.3568</v>
+        <v>0.365</v>
       </c>
       <c r="T9" s="83" t="n">
-        <v>0.3732</v>
+        <v>0.3566</v>
       </c>
       <c r="U9" s="83" t="n">
-        <v>0.3754</v>
+        <v>0.373</v>
       </c>
       <c r="V9" s="83" t="n">
-        <v>0.4091</v>
+        <v>0.3752</v>
       </c>
       <c r="W9" s="83" t="n">
-        <v>0.3803</v>
+        <v>0.4089</v>
       </c>
       <c r="X9" s="83" t="n">
-        <v>0.3858</v>
+        <v>0.3801</v>
       </c>
       <c r="Y9" s="83" t="n">
-        <v>0.3895</v>
+        <v>0.3856</v>
       </c>
       <c r="Z9" s="83" t="n">
-        <v>0.4026</v>
+        <v>0.3894</v>
       </c>
       <c r="AA9" s="83" t="n">
-        <v>0.3991</v>
+        <v>0.4024</v>
       </c>
       <c r="AB9" s="83" t="n">
-        <v>0.3862</v>
+        <v>0.3989</v>
       </c>
       <c r="AC9" s="83" t="n">
-        <v>0.3914</v>
+        <v>0.386</v>
       </c>
       <c r="AD9" s="83" t="n">
-        <v>0.3981</v>
+        <v>0.3912</v>
       </c>
       <c r="AE9" s="83" t="n">
-        <v>0.4236</v>
+        <v>0.3979</v>
       </c>
     </row>
     <row r="10">
@@ -2431,94 +2431,94 @@
         </is>
       </c>
       <c r="B10" s="83" t="n">
+        <v>0.439026</v>
+      </c>
+      <c r="C10" s="83" t="n">
         <v>0.834885</v>
       </c>
-      <c r="C10" s="83" t="n">
+      <c r="D10" s="83" t="n">
         <v>0.995366</v>
       </c>
-      <c r="D10" s="83" t="n">
+      <c r="E10" s="83" t="n">
         <v>0.881059</v>
       </c>
-      <c r="E10" s="83" t="n">
+      <c r="F10" s="83" t="n">
         <v>0.668977</v>
       </c>
-      <c r="F10" s="83" t="n">
+      <c r="G10" s="83" t="n">
         <v>0.377668</v>
       </c>
-      <c r="G10" s="83" t="n">
+      <c r="H10" s="83" t="n">
         <v>0.290923</v>
       </c>
-      <c r="H10" s="83" t="n">
+      <c r="I10" s="83" t="n">
         <v>0.078874</v>
       </c>
-      <c r="I10" s="83" t="n">
+      <c r="J10" s="83" t="n">
         <v>0.06608</v>
       </c>
-      <c r="J10" s="83" t="n">
+      <c r="K10" s="83" t="n">
         <v>0.057833</v>
       </c>
-      <c r="K10" s="83" t="n">
+      <c r="L10" s="83" t="n">
         <v>0.017712</v>
       </c>
-      <c r="L10" s="83" t="n">
+      <c r="M10" s="83" t="n">
         <v>0.000532</v>
       </c>
-      <c r="M10" s="83" t="n">
+      <c r="N10" s="83" t="n">
         <v>0.003474</v>
       </c>
-      <c r="N10" s="83" t="n">
+      <c r="O10" s="83" t="n">
         <v>0.006562</v>
       </c>
-      <c r="O10" s="83" t="n">
+      <c r="P10" s="83" t="n">
         <v>0.015835</v>
       </c>
-      <c r="P10" s="83" t="n">
+      <c r="Q10" s="83" t="n">
         <v>0.004763</v>
       </c>
-      <c r="Q10" s="83" t="n">
+      <c r="R10" s="83" t="n">
         <v>0.000513</v>
       </c>
-      <c r="R10" s="83" t="n">
+      <c r="S10" s="83" t="n">
         <v>0.006747</v>
       </c>
-      <c r="S10" s="83" t="n">
+      <c r="T10" s="83" t="n">
         <v>0.001473</v>
       </c>
-      <c r="T10" s="83" t="n">
+      <c r="U10" s="83" t="n">
         <v>0.004212</v>
       </c>
-      <c r="U10" s="83" t="n">
+      <c r="V10" s="83" t="n">
         <v>0.0008899999999999999</v>
       </c>
-      <c r="V10" s="83" t="n">
+      <c r="W10" s="83" t="n">
         <v>0.034869</v>
       </c>
-      <c r="W10" s="83" t="n">
+      <c r="X10" s="83" t="n">
         <v>0.003664</v>
       </c>
-      <c r="X10" s="83" t="n">
+      <c r="Y10" s="83" t="n">
         <v>0.002424</v>
       </c>
-      <c r="Y10" s="83" t="n">
+      <c r="Z10" s="83" t="n">
         <v>0.017205</v>
       </c>
-      <c r="Z10" s="83" t="n">
+      <c r="AA10" s="83" t="n">
         <v>0.036324</v>
       </c>
-      <c r="AA10" s="83" t="n">
+      <c r="AB10" s="83" t="n">
         <v>0.029327</v>
       </c>
-      <c r="AB10" s="83" t="n">
+      <c r="AC10" s="83" t="n">
         <v>0.010431</v>
       </c>
-      <c r="AC10" s="83" t="n">
+      <c r="AD10" s="83" t="n">
         <v>0.027288</v>
       </c>
-      <c r="AD10" s="83" t="n">
+      <c r="AE10" s="83" t="n">
         <v>0.053794</v>
-      </c>
-      <c r="AE10" s="83" t="n">
-        <v>0.125844</v>
       </c>
     </row>
     <row r="11" ht="19" customFormat="1" customHeight="1" s="31">
@@ -2528,94 +2528,94 @@
         </is>
       </c>
       <c r="B11" s="85" t="n">
-        <v>-0.04590000000000002</v>
+        <v>0.0184</v>
       </c>
       <c r="C11" s="85" t="n">
-        <v>-0.02969999999999998</v>
+        <v>-0.04580000000000004</v>
       </c>
       <c r="D11" s="85" t="n">
+        <v>-0.0295</v>
+      </c>
+      <c r="E11" s="85" t="n">
         <v>-0.0413</v>
       </c>
-      <c r="E11" s="85" t="n">
-        <v>-0.03169999999999998</v>
-      </c>
       <c r="F11" s="85" t="n">
-        <v>-0.02779999999999999</v>
+        <v>-0.03179999999999997</v>
       </c>
       <c r="G11" s="85" t="n">
-        <v>-0.0227</v>
+        <v>-0.02789999999999998</v>
       </c>
       <c r="H11" s="85" t="n">
+        <v>-0.02280000000000001</v>
+      </c>
+      <c r="I11" s="85" t="n">
         <v>-0.01820000000000002</v>
       </c>
-      <c r="I11" s="85" t="n">
+      <c r="J11" s="85" t="n">
         <v>-0.01699999999999999</v>
       </c>
-      <c r="J11" s="85" t="n">
+      <c r="K11" s="85" t="n">
         <v>-0.01799999999999999</v>
       </c>
-      <c r="K11" s="85" t="n">
+      <c r="L11" s="85" t="n">
         <v>-0.01619999999999999</v>
       </c>
-      <c r="L11" s="85" t="n">
-        <v>-0.02360000000000001</v>
-      </c>
       <c r="M11" s="85" t="n">
-        <v>-0.0325</v>
+        <v>-0.0237</v>
       </c>
       <c r="N11" s="85" t="n">
-        <v>-0.033</v>
+        <v>-0.03259999999999999</v>
       </c>
       <c r="O11" s="85" t="n">
-        <v>-0.03220000000000001</v>
+        <v>-0.03309999999999999</v>
       </c>
       <c r="P11" s="85" t="n">
-        <v>-0.0343</v>
+        <v>-0.03230000000000002</v>
       </c>
       <c r="Q11" s="85" t="n">
+        <v>-0.03439999999999999</v>
+      </c>
+      <c r="R11" s="85" t="n">
         <v>-0.03160000000000002</v>
       </c>
-      <c r="R11" s="85" t="n">
+      <c r="S11" s="85" t="n">
         <v>-0.04029999999999997</v>
       </c>
-      <c r="S11" s="85" t="n">
-        <v>-0.03609999999999999</v>
-      </c>
       <c r="T11" s="85" t="n">
-        <v>-0.03559999999999997</v>
+        <v>-0.03620000000000001</v>
       </c>
       <c r="U11" s="85" t="n">
-        <v>-0.03369999999999998</v>
+        <v>-0.03569999999999998</v>
       </c>
       <c r="V11" s="85" t="n">
+        <v>-0.03379999999999997</v>
+      </c>
+      <c r="W11" s="85" t="n">
         <v>-0.03430000000000002</v>
       </c>
-      <c r="W11" s="85" t="n">
-        <v>-0.03409999999999999</v>
-      </c>
       <c r="X11" s="85" t="n">
-        <v>-0.03550000000000003</v>
+        <v>-0.03420000000000001</v>
       </c>
       <c r="Y11" s="85" t="n">
+        <v>-0.03560000000000002</v>
+      </c>
+      <c r="Z11" s="85" t="n">
+        <v>-0.03490000000000001</v>
+      </c>
+      <c r="AA11" s="85" t="n">
+        <v>-0.03160000000000002</v>
+      </c>
+      <c r="AB11" s="85" t="n">
+        <v>-0.03200000000000003</v>
+      </c>
+      <c r="AC11" s="85" t="n">
+        <v>-0.03209999999999999</v>
+      </c>
+      <c r="AD11" s="85" t="n">
+        <v>-0.03489999999999999</v>
+      </c>
+      <c r="AE11" s="85" t="n">
         <v>-0.0348</v>
-      </c>
-      <c r="Z11" s="85" t="n">
-        <v>-0.03150000000000003</v>
-      </c>
-      <c r="AA11" s="85" t="n">
-        <v>-0.03190000000000001</v>
-      </c>
-      <c r="AB11" s="85" t="n">
-        <v>-0.032</v>
-      </c>
-      <c r="AC11" s="85" t="n">
-        <v>-0.0348</v>
-      </c>
-      <c r="AD11" s="85" t="n">
-        <v>-0.0348</v>
-      </c>
-      <c r="AE11" s="85" t="n">
-        <v>-0.03700000000000003</v>
       </c>
     </row>
     <row r="12">
@@ -2625,94 +2625,94 @@
         </is>
       </c>
       <c r="B12" s="78" t="n">
+        <v>46.75</v>
+      </c>
+      <c r="C12" s="78" t="n">
         <v>49.53</v>
       </c>
-      <c r="C12" s="78" t="n">
+      <c r="D12" s="78" t="n">
         <v>56.35</v>
       </c>
-      <c r="D12" s="78" t="n">
+      <c r="E12" s="78" t="n">
         <v>66.34</v>
       </c>
-      <c r="E12" s="78" t="n">
+      <c r="F12" s="78" t="n">
         <v>77.88</v>
       </c>
-      <c r="F12" s="78" t="n">
+      <c r="G12" s="78" t="n">
         <v>88.77</v>
       </c>
-      <c r="G12" s="78" t="n">
+      <c r="H12" s="78" t="n">
         <v>96.05</v>
       </c>
-      <c r="H12" s="78" t="n">
+      <c r="I12" s="78" t="n">
         <v>102.11</v>
       </c>
-      <c r="I12" s="78" t="n">
+      <c r="J12" s="78" t="n">
         <v>103.88</v>
       </c>
-      <c r="J12" s="78" t="n">
+      <c r="K12" s="78" t="n">
         <v>105.24</v>
       </c>
-      <c r="K12" s="78" t="n">
+      <c r="L12" s="78" t="n">
         <v>106.67</v>
       </c>
-      <c r="L12" s="78" t="n">
+      <c r="M12" s="78" t="n">
         <v>107.48</v>
       </c>
-      <c r="M12" s="78" t="n">
+      <c r="N12" s="78" t="n">
         <v>107.3</v>
       </c>
-      <c r="N12" s="78" t="n">
+      <c r="O12" s="78" t="n">
         <v>107.29</v>
       </c>
-      <c r="O12" s="78" t="n">
+      <c r="P12" s="78" t="n">
         <v>107.42</v>
       </c>
-      <c r="P12" s="78" t="n">
+      <c r="Q12" s="78" t="n">
         <v>108.09</v>
       </c>
-      <c r="Q12" s="78" t="n">
+      <c r="R12" s="78" t="n">
         <v>108.17</v>
       </c>
-      <c r="R12" s="78" t="n">
+      <c r="S12" s="78" t="n">
         <v>107.87</v>
       </c>
-      <c r="S12" s="78" t="n">
+      <c r="T12" s="78" t="n">
         <v>107.94</v>
       </c>
-      <c r="T12" s="78" t="n">
+      <c r="U12" s="78" t="n">
         <v>107.63</v>
       </c>
-      <c r="U12" s="78" t="n">
+      <c r="V12" s="78" t="n">
         <v>107.48</v>
       </c>
-      <c r="V12" s="78" t="n">
+      <c r="W12" s="78" t="n">
         <v>106.97</v>
       </c>
-      <c r="W12" s="78" t="n">
+      <c r="X12" s="78" t="n">
         <v>107.52</v>
       </c>
-      <c r="X12" s="78" t="n">
+      <c r="Y12" s="78" t="n">
         <v>107.24</v>
       </c>
-      <c r="Y12" s="78" t="n">
+      <c r="Z12" s="78" t="n">
         <v>106.85</v>
       </c>
-      <c r="Z12" s="78" t="n">
+      <c r="AA12" s="78" t="n">
         <v>106.52</v>
       </c>
-      <c r="AA12" s="78" t="n">
+      <c r="AB12" s="78" t="n">
         <v>106.44</v>
       </c>
-      <c r="AB12" s="78" t="n">
+      <c r="AC12" s="78" t="n">
         <v>106.24</v>
       </c>
-      <c r="AC12" s="78" t="n">
+      <c r="AD12" s="78" t="n">
         <v>105.72</v>
       </c>
-      <c r="AD12" s="78" t="n">
+      <c r="AE12" s="78" t="n">
         <v>105.46</v>
-      </c>
-      <c r="AE12" s="78" t="n">
-        <v>105.61</v>
       </c>
     </row>
     <row r="13">
@@ -2731,85 +2731,85 @@
         <v>0</v>
       </c>
       <c r="E13" s="86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="86" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="86" t="n">
+      <c r="G13" s="86" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="86" t="n">
-        <v>35</v>
-      </c>
       <c r="H13" s="86" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I13" s="86" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" s="86" t="n">
         <v>19</v>
       </c>
-      <c r="J13" s="86" t="n">
-        <v>32</v>
-      </c>
       <c r="K13" s="86" t="n">
-        <v>122</v>
+        <v>33</v>
       </c>
       <c r="L13" s="86" t="n">
+        <v>136</v>
+      </c>
+      <c r="M13" s="86" t="n">
         <v>8</v>
       </c>
-      <c r="M13" s="86" t="n">
+      <c r="N13" s="86" t="n">
         <v>1</v>
       </c>
-      <c r="N13" s="86" t="n">
+      <c r="O13" s="86" t="n">
         <v>17</v>
       </c>
-      <c r="O13" s="86" t="n">
-        <v>177</v>
-      </c>
       <c r="P13" s="86" t="n">
+        <v>192</v>
+      </c>
+      <c r="Q13" s="86" t="n">
         <v>15</v>
       </c>
-      <c r="Q13" s="86" t="n">
+      <c r="R13" s="86" t="n">
         <v>4</v>
       </c>
-      <c r="R13" s="86" t="n">
+      <c r="S13" s="86" t="n">
         <v>2</v>
       </c>
-      <c r="S13" s="86" t="n">
+      <c r="T13" s="86" t="n">
         <v>6</v>
       </c>
-      <c r="T13" s="86" t="n">
-        <v>3</v>
-      </c>
       <c r="U13" s="86" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V13" s="86" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="W13" s="86" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="X13" s="86" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Y13" s="86" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="Z13" s="86" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA13" s="86" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB13" s="86" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC13" s="86" t="n">
         <v>16</v>
       </c>
-      <c r="AA13" s="86" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB13" s="86" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC13" s="86" t="n">
+      <c r="AD13" s="86" t="n">
         <v>26</v>
       </c>
-      <c r="AD13" s="86" t="n">
-        <v>9</v>
-      </c>
       <c r="AE13" s="86" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -2837,76 +2837,76 @@
         <v>0</v>
       </c>
       <c r="H14" s="86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="86" t="n">
+        <v>18</v>
+      </c>
+      <c r="J14" s="86" t="n">
+        <v>13</v>
+      </c>
+      <c r="K14" s="86" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" s="86" t="n">
+        <v>13</v>
+      </c>
+      <c r="M14" s="86" t="n">
+        <v>40</v>
+      </c>
+      <c r="N14" s="86" t="n">
+        <v>38</v>
+      </c>
+      <c r="O14" s="86" t="n">
+        <v>20</v>
+      </c>
+      <c r="P14" s="86" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="86" t="n">
+        <v>11</v>
+      </c>
+      <c r="R14" s="86" t="n">
+        <v>20</v>
+      </c>
+      <c r="S14" s="86" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" s="86" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" s="86" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" s="86" t="n">
+        <v>19</v>
+      </c>
+      <c r="W14" s="86" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" s="86" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="86" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z14" s="86" t="n">
+        <v>76</v>
+      </c>
+      <c r="AA14" s="86" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB14" s="86" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC14" s="86" t="n">
+        <v>56</v>
+      </c>
+      <c r="AD14" s="86" t="n">
         <v>17</v>
       </c>
-      <c r="I14" s="86" t="n">
-        <v>13</v>
-      </c>
-      <c r="J14" s="86" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="86" t="n">
-        <v>13</v>
-      </c>
-      <c r="L14" s="86" t="n">
-        <v>37</v>
-      </c>
-      <c r="M14" s="86" t="n">
-        <v>36</v>
-      </c>
-      <c r="N14" s="86" t="n">
-        <v>20</v>
-      </c>
-      <c r="O14" s="86" t="n">
-        <v>4</v>
-      </c>
-      <c r="P14" s="86" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q14" s="86" t="n">
-        <v>18</v>
-      </c>
-      <c r="R14" s="86" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" s="86" t="n">
-        <v>6</v>
-      </c>
-      <c r="T14" s="86" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" s="86" t="n">
-        <v>17</v>
-      </c>
-      <c r="V14" s="86" t="n">
-        <v>2</v>
-      </c>
-      <c r="W14" s="86" t="n">
-        <v>4</v>
-      </c>
-      <c r="X14" s="86" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y14" s="86" t="n">
-        <v>73</v>
-      </c>
-      <c r="Z14" s="86" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA14" s="86" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB14" s="86" t="n">
-        <v>53</v>
-      </c>
-      <c r="AC14" s="86" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD14" s="86" t="n">
-        <v>19</v>
-      </c>
       <c r="AE14" s="86" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -2934,76 +2934,76 @@
         <v>0</v>
       </c>
       <c r="H15" s="86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="86" t="n">
         <v>34</v>
       </c>
-      <c r="I15" s="86" t="n">
+      <c r="J15" s="86" t="n">
         <v>15</v>
       </c>
-      <c r="J15" s="86" t="n">
+      <c r="K15" s="86" t="n">
         <v>1</v>
       </c>
-      <c r="K15" s="86" t="n">
+      <c r="L15" s="86" t="n">
         <v>27</v>
       </c>
-      <c r="L15" s="86" t="n">
-        <v>75</v>
-      </c>
       <c r="M15" s="86" t="n">
+        <v>76</v>
+      </c>
+      <c r="N15" s="86" t="n">
         <v>105</v>
       </c>
-      <c r="N15" s="86" t="n">
+      <c r="O15" s="86" t="n">
         <v>80</v>
       </c>
-      <c r="O15" s="86" t="n">
+      <c r="P15" s="86" t="n">
         <v>4</v>
       </c>
-      <c r="P15" s="86" t="n">
+      <c r="Q15" s="86" t="n">
         <v>23</v>
       </c>
-      <c r="Q15" s="86" t="n">
+      <c r="R15" s="86" t="n">
         <v>36</v>
       </c>
-      <c r="R15" s="86" t="n">
+      <c r="S15" s="86" t="n">
         <v>2</v>
       </c>
-      <c r="S15" s="86" t="n">
+      <c r="T15" s="86" t="n">
         <v>22</v>
       </c>
-      <c r="T15" s="86" t="n">
+      <c r="U15" s="86" t="n">
         <v>13</v>
       </c>
-      <c r="U15" s="86" t="n">
+      <c r="V15" s="86" t="n">
         <v>30</v>
       </c>
-      <c r="V15" s="86" t="n">
+      <c r="W15" s="86" t="n">
         <v>6</v>
       </c>
-      <c r="W15" s="86" t="n">
+      <c r="X15" s="86" t="n">
         <v>12</v>
       </c>
-      <c r="X15" s="86" t="n">
+      <c r="Y15" s="86" t="n">
         <v>51</v>
       </c>
-      <c r="Y15" s="86" t="n">
+      <c r="Z15" s="86" t="n">
         <v>127</v>
       </c>
-      <c r="Z15" s="86" t="n">
+      <c r="AA15" s="86" t="n">
         <v>20</v>
       </c>
-      <c r="AA15" s="86" t="n">
+      <c r="AB15" s="86" t="n">
         <v>36</v>
       </c>
-      <c r="AB15" s="86" t="n">
+      <c r="AC15" s="86" t="n">
         <v>85</v>
       </c>
-      <c r="AC15" s="86" t="n">
+      <c r="AD15" s="86" t="n">
         <v>26</v>
       </c>
-      <c r="AD15" s="86" t="n">
+      <c r="AE15" s="86" t="n">
         <v>25</v>
-      </c>
-      <c r="AE15" s="86" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -3016,91 +3016,91 @@
         <v>0</v>
       </c>
       <c r="C16" s="86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="86" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="86" t="n">
+      <c r="E16" s="86" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="86" t="n">
+      <c r="F16" s="86" t="n">
         <v>27</v>
       </c>
-      <c r="F16" s="86" t="n">
+      <c r="G16" s="86" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="86" t="n">
-        <v>271</v>
-      </c>
       <c r="H16" s="86" t="n">
+        <v>272</v>
+      </c>
+      <c r="I16" s="86" t="n">
         <v>16</v>
       </c>
-      <c r="I16" s="86" t="n">
+      <c r="J16" s="86" t="n">
         <v>159</v>
       </c>
-      <c r="J16" s="86" t="n">
-        <v>233</v>
-      </c>
       <c r="K16" s="86" t="n">
-        <v>508</v>
+        <v>234</v>
       </c>
       <c r="L16" s="86" t="n">
+        <v>510</v>
+      </c>
+      <c r="M16" s="86" t="n">
         <v>28</v>
       </c>
-      <c r="M16" s="86" t="n">
+      <c r="N16" s="86" t="n">
         <v>4</v>
       </c>
-      <c r="N16" s="86" t="n">
-        <v>479</v>
-      </c>
       <c r="O16" s="86" t="n">
-        <v>708</v>
+        <v>480</v>
       </c>
       <c r="P16" s="86" t="n">
+        <v>709</v>
+      </c>
+      <c r="Q16" s="86" t="n">
         <v>99</v>
       </c>
-      <c r="Q16" s="86" t="n">
+      <c r="R16" s="86" t="n">
         <v>22</v>
       </c>
-      <c r="R16" s="86" t="n">
+      <c r="S16" s="86" t="n">
         <v>16</v>
       </c>
-      <c r="S16" s="86" t="n">
+      <c r="T16" s="86" t="n">
         <v>26</v>
       </c>
-      <c r="T16" s="86" t="n">
+      <c r="U16" s="86" t="n">
         <v>11</v>
       </c>
-      <c r="U16" s="86" t="n">
+      <c r="V16" s="86" t="n">
         <v>35</v>
       </c>
-      <c r="V16" s="86" t="n">
+      <c r="W16" s="86" t="n">
         <v>157</v>
       </c>
-      <c r="W16" s="86" t="n">
-        <v>350</v>
-      </c>
       <c r="X16" s="86" t="n">
+        <v>351</v>
+      </c>
+      <c r="Y16" s="86" t="n">
         <v>258</v>
-      </c>
-      <c r="Y16" s="86" t="n">
-        <v>84</v>
       </c>
       <c r="Z16" s="86" t="n">
         <v>84</v>
       </c>
       <c r="AA16" s="86" t="n">
+        <v>84</v>
+      </c>
+      <c r="AB16" s="86" t="n">
         <v>143</v>
       </c>
-      <c r="AB16" s="86" t="n">
+      <c r="AC16" s="86" t="n">
         <v>122</v>
       </c>
-      <c r="AC16" s="86" t="n">
+      <c r="AD16" s="86" t="n">
         <v>144</v>
       </c>
-      <c r="AD16" s="86" t="n">
+      <c r="AE16" s="86" t="n">
         <v>56</v>
-      </c>
-      <c r="AE16" s="86" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="B17" s="86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C17" s="86" t="n">
         <v>0</v>
@@ -3119,85 +3119,85 @@
         <v>0</v>
       </c>
       <c r="E17" s="86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="86" t="n">
         <v>8</v>
       </c>
-      <c r="F17" s="86" t="n">
+      <c r="G17" s="86" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="86" t="n">
+      <c r="H17" s="86" t="n">
         <v>132</v>
       </c>
-      <c r="H17" s="86" t="n">
+      <c r="I17" s="86" t="n">
         <v>178</v>
       </c>
-      <c r="I17" s="86" t="n">
+      <c r="J17" s="86" t="n">
         <v>243</v>
       </c>
-      <c r="J17" s="86" t="n">
-        <v>465</v>
-      </c>
       <c r="K17" s="86" t="n">
-        <v>1309</v>
+        <v>466</v>
       </c>
       <c r="L17" s="86" t="n">
-        <v>859</v>
+        <v>1311</v>
       </c>
       <c r="M17" s="86" t="n">
-        <v>617</v>
+        <v>861</v>
       </c>
       <c r="N17" s="86" t="n">
-        <v>1033</v>
+        <v>618</v>
       </c>
       <c r="O17" s="86" t="n">
-        <v>1149</v>
+        <v>1034</v>
       </c>
       <c r="P17" s="86" t="n">
-        <v>1286</v>
+        <v>1151</v>
       </c>
       <c r="Q17" s="86" t="n">
-        <v>494</v>
+        <v>1288</v>
       </c>
       <c r="R17" s="86" t="n">
-        <v>473</v>
+        <v>495</v>
       </c>
       <c r="S17" s="86" t="n">
-        <v>604</v>
+        <v>474</v>
       </c>
       <c r="T17" s="86" t="n">
+        <v>605</v>
+      </c>
+      <c r="U17" s="86" t="n">
         <v>345</v>
       </c>
-      <c r="U17" s="86" t="n">
+      <c r="V17" s="86" t="n">
         <v>260</v>
       </c>
-      <c r="V17" s="86" t="n">
+      <c r="W17" s="86" t="n">
         <v>243</v>
       </c>
-      <c r="W17" s="86" t="n">
-        <v>584</v>
-      </c>
       <c r="X17" s="86" t="n">
-        <v>866</v>
+        <v>585</v>
       </c>
       <c r="Y17" s="86" t="n">
-        <v>834</v>
+        <v>867</v>
       </c>
       <c r="Z17" s="86" t="n">
+        <v>835</v>
+      </c>
+      <c r="AA17" s="86" t="n">
         <v>536</v>
       </c>
-      <c r="AA17" s="86" t="n">
-        <v>849</v>
-      </c>
       <c r="AB17" s="86" t="n">
-        <v>918</v>
+        <v>850</v>
       </c>
       <c r="AC17" s="86" t="n">
-        <v>780</v>
+        <v>919</v>
       </c>
       <c r="AD17" s="86" t="n">
-        <v>666</v>
+        <v>781</v>
       </c>
       <c r="AE17" s="86" t="n">
-        <v>261</v>
+        <v>667</v>
       </c>
     </row>
     <row r="18">
@@ -3207,94 +3207,94 @@
         </is>
       </c>
       <c r="B18" s="86" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" s="86" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="86" t="n">
+      <c r="D18" s="86" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="86" t="n">
+      <c r="E18" s="86" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="86" t="n">
+      <c r="F18" s="86" t="n">
         <v>2</v>
       </c>
-      <c r="F18" s="86" t="n">
+      <c r="G18" s="86" t="n">
         <v>4</v>
       </c>
-      <c r="G18" s="86" t="n">
+      <c r="H18" s="86" t="n">
         <v>3</v>
       </c>
-      <c r="H18" s="86" t="n">
+      <c r="I18" s="86" t="n">
         <v>357</v>
       </c>
-      <c r="I18" s="86" t="n">
+      <c r="J18" s="86" t="n">
         <v>342</v>
       </c>
-      <c r="J18" s="86" t="n">
+      <c r="K18" s="86" t="n">
         <v>70</v>
       </c>
-      <c r="K18" s="86" t="n">
+      <c r="L18" s="86" t="n">
         <v>1544</v>
       </c>
-      <c r="L18" s="86" t="n">
+      <c r="M18" s="86" t="n">
         <v>1420</v>
       </c>
-      <c r="M18" s="86" t="n">
+      <c r="N18" s="86" t="n">
         <v>700</v>
       </c>
-      <c r="N18" s="86" t="n">
+      <c r="O18" s="86" t="n">
         <v>660</v>
       </c>
-      <c r="O18" s="86" t="n">
+      <c r="P18" s="86" t="n">
         <v>449</v>
       </c>
-      <c r="P18" s="86" t="n">
+      <c r="Q18" s="86" t="n">
         <v>835</v>
       </c>
-      <c r="Q18" s="86" t="n">
+      <c r="R18" s="86" t="n">
         <v>792</v>
       </c>
-      <c r="R18" s="86" t="n">
+      <c r="S18" s="86" t="n">
         <v>137</v>
       </c>
-      <c r="S18" s="86" t="n">
+      <c r="T18" s="86" t="n">
         <v>436</v>
       </c>
-      <c r="T18" s="86" t="n">
+      <c r="U18" s="86" t="n">
         <v>205</v>
       </c>
-      <c r="U18" s="86" t="n">
+      <c r="V18" s="86" t="n">
         <v>460</v>
       </c>
-      <c r="V18" s="86" t="n">
+      <c r="W18" s="86" t="n">
         <v>47</v>
       </c>
-      <c r="W18" s="86" t="n">
+      <c r="X18" s="86" t="n">
         <v>174</v>
       </c>
-      <c r="X18" s="86" t="n">
+      <c r="Y18" s="86" t="n">
         <v>570</v>
       </c>
-      <c r="Y18" s="86" t="n">
+      <c r="Z18" s="86" t="n">
         <v>1284</v>
       </c>
-      <c r="Z18" s="86" t="n">
+      <c r="AA18" s="86" t="n">
         <v>384</v>
       </c>
-      <c r="AA18" s="86" t="n">
+      <c r="AB18" s="86" t="n">
         <v>1435</v>
       </c>
-      <c r="AB18" s="86" t="n">
+      <c r="AC18" s="86" t="n">
         <v>1700</v>
       </c>
-      <c r="AC18" s="86" t="n">
+      <c r="AD18" s="86" t="n">
         <v>953</v>
       </c>
-      <c r="AD18" s="86" t="n">
+      <c r="AE18" s="86" t="n">
         <v>1203</v>
-      </c>
-      <c r="AE18" s="86" t="n">
-        <v>525</v>
       </c>
     </row>
     <row r="19">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="B19" s="86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C19" s="86" t="n">
         <v>0</v>
@@ -3322,76 +3322,76 @@
         <v>0</v>
       </c>
       <c r="H19" s="86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="86" t="n">
         <v>65</v>
       </c>
-      <c r="I19" s="86" t="n">
+      <c r="J19" s="86" t="n">
         <v>54</v>
       </c>
-      <c r="J19" s="86" t="n">
+      <c r="K19" s="86" t="n">
         <v>13</v>
       </c>
-      <c r="K19" s="86" t="n">
+      <c r="L19" s="86" t="n">
         <v>114</v>
       </c>
-      <c r="L19" s="86" t="n">
+      <c r="M19" s="86" t="n">
         <v>147</v>
       </c>
-      <c r="M19" s="86" t="n">
+      <c r="N19" s="86" t="n">
         <v>75</v>
       </c>
-      <c r="N19" s="86" t="n">
+      <c r="O19" s="86" t="n">
         <v>104</v>
       </c>
-      <c r="O19" s="86" t="n">
+      <c r="P19" s="86" t="n">
         <v>102</v>
       </c>
-      <c r="P19" s="86" t="n">
+      <c r="Q19" s="86" t="n">
         <v>127</v>
       </c>
-      <c r="Q19" s="86" t="n">
+      <c r="R19" s="86" t="n">
         <v>91</v>
       </c>
-      <c r="R19" s="86" t="n">
+      <c r="S19" s="86" t="n">
         <v>36</v>
       </c>
-      <c r="S19" s="86" t="n">
+      <c r="T19" s="86" t="n">
         <v>60</v>
       </c>
-      <c r="T19" s="86" t="n">
+      <c r="U19" s="86" t="n">
         <v>41</v>
       </c>
-      <c r="U19" s="86" t="n">
+      <c r="V19" s="86" t="n">
         <v>81</v>
       </c>
-      <c r="V19" s="86" t="n">
+      <c r="W19" s="86" t="n">
         <v>15</v>
       </c>
-      <c r="W19" s="86" t="n">
+      <c r="X19" s="86" t="n">
         <v>35</v>
       </c>
-      <c r="X19" s="86" t="n">
+      <c r="Y19" s="86" t="n">
         <v>84</v>
       </c>
-      <c r="Y19" s="86" t="n">
+      <c r="Z19" s="86" t="n">
         <v>162</v>
       </c>
-      <c r="Z19" s="86" t="n">
+      <c r="AA19" s="86" t="n">
         <v>76</v>
       </c>
-      <c r="AA19" s="86" t="n">
+      <c r="AB19" s="86" t="n">
         <v>118</v>
       </c>
-      <c r="AB19" s="86" t="n">
+      <c r="AC19" s="86" t="n">
         <v>201</v>
       </c>
-      <c r="AC19" s="86" t="n">
+      <c r="AD19" s="86" t="n">
         <v>146</v>
       </c>
-      <c r="AD19" s="86" t="n">
+      <c r="AE19" s="86" t="n">
         <v>163</v>
-      </c>
-      <c r="AE19" s="86" t="n">
-        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -3401,385 +3401,385 @@
         </is>
       </c>
       <c r="B20" s="86" t="n">
-        <v>1172</v>
+        <v>290</v>
       </c>
       <c r="C20" s="86" t="n">
-        <v>858</v>
+        <v>1243</v>
       </c>
       <c r="D20" s="86" t="n">
-        <v>562</v>
+        <v>907</v>
       </c>
       <c r="E20" s="86" t="n">
-        <v>300</v>
+        <v>587</v>
       </c>
       <c r="F20" s="86" t="n">
-        <v>258</v>
+        <v>311</v>
       </c>
       <c r="G20" s="86" t="n">
-        <v>126</v>
+        <v>273</v>
       </c>
       <c r="H20" s="86" t="n">
+        <v>133</v>
+      </c>
+      <c r="I20" s="86" t="n">
+        <v>57</v>
+      </c>
+      <c r="J20" s="86" t="n">
+        <v>48</v>
+      </c>
+      <c r="K20" s="86" t="n">
+        <v>53</v>
+      </c>
+      <c r="L20" s="86" t="n">
+        <v>34</v>
+      </c>
+      <c r="M20" s="86" t="n">
+        <v>23</v>
+      </c>
+      <c r="N20" s="86" t="n">
+        <v>52</v>
+      </c>
+      <c r="O20" s="86" t="n">
+        <v>42</v>
+      </c>
+      <c r="P20" s="86" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q20" s="86" t="n">
+        <v>16</v>
+      </c>
+      <c r="R20" s="86" t="n">
+        <v>43</v>
+      </c>
+      <c r="S20" s="86" t="n">
+        <v>59</v>
+      </c>
+      <c r="T20" s="86" t="n">
         <v>51</v>
       </c>
-      <c r="I20" s="86" t="n">
-        <v>43</v>
-      </c>
-      <c r="J20" s="86" t="n">
+      <c r="U20" s="86" t="n">
+        <v>61</v>
+      </c>
+      <c r="V20" s="86" t="n">
         <v>49</v>
       </c>
-      <c r="K20" s="86" t="n">
-        <v>31</v>
-      </c>
-      <c r="L20" s="86" t="n">
-        <v>20</v>
-      </c>
-      <c r="M20" s="86" t="n">
+      <c r="W20" s="86" t="n">
+        <v>53</v>
+      </c>
+      <c r="X20" s="86" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y20" s="86" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z20" s="86" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA20" s="86" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB20" s="86" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC20" s="86" t="n">
+        <v>35</v>
+      </c>
+      <c r="AD20" s="86" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE20" s="86" t="n">
         <v>49</v>
       </c>
-      <c r="N20" s="86" t="n">
-        <v>41</v>
-      </c>
-      <c r="O20" s="86" t="n">
-        <v>20</v>
-      </c>
-      <c r="P20" s="86" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q20" s="86" t="n">
-        <v>40</v>
-      </c>
-      <c r="R20" s="86" t="n">
-        <v>51</v>
-      </c>
-      <c r="S20" s="86" t="n">
-        <v>45</v>
-      </c>
-      <c r="T20" s="86" t="n">
-        <v>57</v>
-      </c>
-      <c r="U20" s="86" t="n">
+    </row>
+    <row r="21">
+      <c r="A21" s="76" t="inlineStr">
+        <is>
+          <t>新高数120d(avg)</t>
+        </is>
+      </c>
+      <c r="B21" s="86" t="n">
+        <v>734</v>
+      </c>
+      <c r="C21" s="86" t="n">
+        <v>4681</v>
+      </c>
+      <c r="D21" s="86" t="n">
+        <v>3737</v>
+      </c>
+      <c r="E21" s="86" t="n">
+        <v>2351</v>
+      </c>
+      <c r="F21" s="86" t="n">
+        <v>1154</v>
+      </c>
+      <c r="G21" s="86" t="n">
+        <v>1106</v>
+      </c>
+      <c r="H21" s="86" t="n">
+        <v>618</v>
+      </c>
+      <c r="I21" s="86" t="n">
+        <v>240</v>
+      </c>
+      <c r="J21" s="86" t="n">
+        <v>113</v>
+      </c>
+      <c r="K21" s="86" t="n">
+        <v>105</v>
+      </c>
+      <c r="L21" s="86" t="n">
+        <v>147</v>
+      </c>
+      <c r="M21" s="86" t="n">
         <v>44</v>
       </c>
-      <c r="V20" s="86" t="n">
-        <v>47</v>
-      </c>
-      <c r="W20" s="86" t="n">
-        <v>29</v>
-      </c>
-      <c r="X20" s="86" t="n">
-        <v>33</v>
-      </c>
-      <c r="Y20" s="86" t="n">
-        <v>33</v>
-      </c>
-      <c r="Z20" s="86" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA20" s="86" t="n">
-        <v>22</v>
-      </c>
-      <c r="AB20" s="86" t="n">
-        <v>35</v>
-      </c>
-      <c r="AC20" s="86" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD20" s="86" t="n">
-        <v>47</v>
-      </c>
-      <c r="AE20" s="86" t="n">
+      <c r="N21" s="86" t="n">
+        <v>125</v>
+      </c>
+      <c r="O21" s="86" t="n">
+        <v>115</v>
+      </c>
+      <c r="P21" s="86" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q21" s="86" t="n">
+        <v>61</v>
+      </c>
+      <c r="R21" s="86" t="n">
+        <v>116</v>
+      </c>
+      <c r="S21" s="86" t="n">
+        <v>95</v>
+      </c>
+      <c r="T21" s="86" t="n">
+        <v>226</v>
+      </c>
+      <c r="U21" s="86" t="n">
+        <v>162</v>
+      </c>
+      <c r="V21" s="86" t="n">
+        <v>183</v>
+      </c>
+      <c r="W21" s="86" t="n">
+        <v>236</v>
+      </c>
+      <c r="X21" s="86" t="n">
+        <v>140</v>
+      </c>
+      <c r="Y21" s="86" t="n">
+        <v>568</v>
+      </c>
+      <c r="Z21" s="86" t="n">
+        <v>670</v>
+      </c>
+      <c r="AA21" s="86" t="n">
+        <v>318</v>
+      </c>
+      <c r="AB21" s="86" t="n">
+        <v>502</v>
+      </c>
+      <c r="AC21" s="86" t="n">
+        <v>595</v>
+      </c>
+      <c r="AD21" s="86" t="n">
+        <v>133</v>
+      </c>
+      <c r="AE21" s="86" t="n">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="76" t="inlineStr">
+        <is>
+          <t>新高数60d</t>
+        </is>
+      </c>
+      <c r="B22" s="86" t="n">
+        <v>255</v>
+      </c>
+      <c r="C22" s="86" t="n">
+        <v>4449</v>
+      </c>
+      <c r="D22" s="86" t="n">
+        <v>4061</v>
+      </c>
+      <c r="E22" s="86" t="n">
+        <v>2268</v>
+      </c>
+      <c r="F22" s="86" t="n">
+        <v>1284</v>
+      </c>
+      <c r="G22" s="86" t="n">
+        <v>570</v>
+      </c>
+      <c r="H22" s="86" t="n">
+        <v>438</v>
+      </c>
+      <c r="I22" s="86" t="n">
+        <v>175</v>
+      </c>
+      <c r="J22" s="86" t="n">
+        <v>170</v>
+      </c>
+      <c r="K22" s="86" t="n">
+        <v>173</v>
+      </c>
+      <c r="L22" s="86" t="n">
+        <v>94</v>
+      </c>
+      <c r="M22" s="86" t="n">
+        <v>86</v>
+      </c>
+      <c r="N22" s="86" t="n">
+        <v>97</v>
+      </c>
+      <c r="O22" s="86" t="n">
+        <v>106</v>
+      </c>
+      <c r="P22" s="86" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q22" s="86" t="n">
+        <v>68</v>
+      </c>
+      <c r="R22" s="86" t="n">
+        <v>76</v>
+      </c>
+      <c r="S22" s="86" t="n">
+        <v>135</v>
+      </c>
+      <c r="T22" s="86" t="n">
+        <v>92</v>
+      </c>
+      <c r="U22" s="86" t="n">
+        <v>162</v>
+      </c>
+      <c r="V22" s="86" t="n">
+        <v>121</v>
+      </c>
+      <c r="W22" s="86" t="n">
+        <v>138</v>
+      </c>
+      <c r="X22" s="86" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y22" s="86" t="n">
         <v>52</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="82" t="inlineStr">
-        <is>
-          <t>新高数120d(avg)</t>
-        </is>
-      </c>
-      <c r="B21" s="86" t="n">
-        <v>4676</v>
-      </c>
-      <c r="C21" s="86" t="n">
-        <v>3733</v>
-      </c>
-      <c r="D21" s="86" t="n">
-        <v>2349</v>
-      </c>
-      <c r="E21" s="86" t="n">
-        <v>1153</v>
-      </c>
-      <c r="F21" s="86" t="n">
-        <v>1105</v>
-      </c>
-      <c r="G21" s="86" t="n">
-        <v>617</v>
-      </c>
-      <c r="H21" s="86" t="n">
-        <v>240</v>
-      </c>
-      <c r="I21" s="86" t="n">
-        <v>113</v>
-      </c>
-      <c r="J21" s="86" t="n">
-        <v>105</v>
-      </c>
-      <c r="K21" s="86" t="n">
-        <v>147</v>
-      </c>
-      <c r="L21" s="86" t="n">
-        <v>44</v>
-      </c>
-      <c r="M21" s="86" t="n">
-        <v>125</v>
-      </c>
-      <c r="N21" s="86" t="n">
-        <v>114</v>
-      </c>
-      <c r="O21" s="86" t="n">
-        <v>37</v>
-      </c>
-      <c r="P21" s="86" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q21" s="86" t="n">
-        <v>116</v>
-      </c>
-      <c r="R21" s="86" t="n">
-        <v>95</v>
-      </c>
-      <c r="S21" s="86" t="n">
-        <v>226</v>
-      </c>
-      <c r="T21" s="86" t="n">
-        <v>162</v>
-      </c>
-      <c r="U21" s="86" t="n">
-        <v>183</v>
-      </c>
-      <c r="V21" s="86" t="n">
-        <v>235</v>
-      </c>
-      <c r="W21" s="86" t="n">
-        <v>140</v>
-      </c>
-      <c r="X21" s="86" t="n">
-        <v>567</v>
-      </c>
-      <c r="Y21" s="86" t="n">
-        <v>669</v>
-      </c>
-      <c r="Z21" s="86" t="n">
-        <v>317</v>
-      </c>
-      <c r="AA21" s="86" t="n">
-        <v>502</v>
-      </c>
-      <c r="AB21" s="86" t="n">
-        <v>594</v>
-      </c>
-      <c r="AC21" s="86" t="n">
-        <v>133</v>
-      </c>
-      <c r="AD21" s="86" t="n">
-        <v>544</v>
-      </c>
-      <c r="AE21" s="86" t="n">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="82" t="inlineStr">
-        <is>
-          <t>新高数60d</t>
-        </is>
-      </c>
-      <c r="B22" s="86" t="n">
-        <v>4449</v>
-      </c>
-      <c r="C22" s="86" t="n">
-        <v>4061</v>
-      </c>
-      <c r="D22" s="86" t="n">
-        <v>2268</v>
-      </c>
-      <c r="E22" s="86" t="n">
-        <v>1284</v>
-      </c>
-      <c r="F22" s="86" t="n">
-        <v>570</v>
-      </c>
-      <c r="G22" s="86" t="n">
-        <v>438</v>
-      </c>
-      <c r="H22" s="86" t="n">
-        <v>175</v>
-      </c>
-      <c r="I22" s="86" t="n">
-        <v>170</v>
-      </c>
-      <c r="J22" s="86" t="n">
-        <v>173</v>
-      </c>
-      <c r="K22" s="86" t="n">
-        <v>94</v>
-      </c>
-      <c r="L22" s="86" t="n">
-        <v>86</v>
-      </c>
-      <c r="M22" s="86" t="n">
-        <v>97</v>
-      </c>
-      <c r="N22" s="86" t="n">
-        <v>106</v>
-      </c>
-      <c r="O22" s="86" t="n">
-        <v>92</v>
-      </c>
-      <c r="P22" s="86" t="n">
-        <v>68</v>
-      </c>
-      <c r="Q22" s="86" t="n">
-        <v>76</v>
-      </c>
-      <c r="R22" s="86" t="n">
-        <v>135</v>
-      </c>
-      <c r="S22" s="86" t="n">
-        <v>92</v>
-      </c>
-      <c r="T22" s="86" t="n">
-        <v>162</v>
-      </c>
-      <c r="U22" s="86" t="n">
-        <v>121</v>
-      </c>
-      <c r="V22" s="86" t="n">
-        <v>138</v>
-      </c>
-      <c r="W22" s="86" t="n">
-        <v>85</v>
-      </c>
-      <c r="X22" s="86" t="n">
-        <v>52</v>
-      </c>
-      <c r="Y22" s="86" t="n">
+      <c r="Z22" s="86" t="n">
         <v>64</v>
       </c>
-      <c r="Z22" s="86" t="n">
+      <c r="AA22" s="86" t="n">
         <v>78</v>
       </c>
-      <c r="AA22" s="86" t="n">
+      <c r="AB22" s="86" t="n">
         <v>63</v>
-      </c>
-      <c r="AB22" s="86" t="n">
-        <v>47</v>
       </c>
       <c r="AC22" s="86" t="n">
         <v>47</v>
       </c>
       <c r="AD22" s="86" t="n">
+        <v>47</v>
+      </c>
+      <c r="AE22" s="86" t="n">
         <v>49</v>
       </c>
-      <c r="AE22" s="86" t="n">
-        <v>91</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23" s="82" t="inlineStr">
+      <c r="A23" s="76" t="inlineStr">
         <is>
           <t>新高数60d(zz500)</t>
         </is>
       </c>
       <c r="B23" s="86" t="n">
+        <v>32</v>
+      </c>
+      <c r="C23" s="86" t="n">
         <v>415</v>
       </c>
-      <c r="C23" s="86" t="n">
+      <c r="D23" s="86" t="n">
         <v>409</v>
       </c>
-      <c r="D23" s="86" t="n">
+      <c r="E23" s="86" t="n">
         <v>250</v>
       </c>
-      <c r="E23" s="86" t="n">
+      <c r="F23" s="86" t="n">
         <v>146</v>
       </c>
-      <c r="F23" s="86" t="n">
+      <c r="G23" s="86" t="n">
         <v>67</v>
       </c>
-      <c r="G23" s="86" t="n">
+      <c r="H23" s="86" t="n">
         <v>57</v>
       </c>
-      <c r="H23" s="86" t="n">
+      <c r="I23" s="86" t="n">
         <v>8</v>
-      </c>
-      <c r="I23" s="86" t="n">
-        <v>11</v>
       </c>
       <c r="J23" s="86" t="n">
         <v>11</v>
       </c>
       <c r="K23" s="86" t="n">
+        <v>11</v>
+      </c>
+      <c r="L23" s="86" t="n">
         <v>14</v>
       </c>
-      <c r="L23" s="86" t="n">
+      <c r="M23" s="86" t="n">
         <v>4</v>
       </c>
-      <c r="M23" s="86" t="n">
+      <c r="N23" s="86" t="n">
         <v>6</v>
       </c>
-      <c r="N23" s="86" t="n">
+      <c r="O23" s="86" t="n">
         <v>19</v>
       </c>
-      <c r="O23" s="86" t="n">
+      <c r="P23" s="86" t="n">
         <v>12</v>
       </c>
-      <c r="P23" s="86" t="n">
+      <c r="Q23" s="86" t="n">
         <v>5</v>
       </c>
-      <c r="Q23" s="86" t="n">
+      <c r="R23" s="86" t="n">
         <v>4</v>
       </c>
-      <c r="R23" s="86" t="n">
+      <c r="S23" s="86" t="n">
         <v>11</v>
       </c>
-      <c r="S23" s="86" t="n">
+      <c r="T23" s="86" t="n">
         <v>9</v>
       </c>
-      <c r="T23" s="86" t="n">
+      <c r="U23" s="86" t="n">
         <v>14</v>
       </c>
-      <c r="U23" s="86" t="n">
+      <c r="V23" s="86" t="n">
         <v>9</v>
       </c>
-      <c r="V23" s="86" t="n">
+      <c r="W23" s="86" t="n">
         <v>7</v>
-      </c>
-      <c r="W23" s="86" t="n">
-        <v>6</v>
       </c>
       <c r="X23" s="86" t="n">
         <v>6</v>
       </c>
       <c r="Y23" s="86" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z23" s="86" t="n">
         <v>5</v>
       </c>
-      <c r="Z23" s="86" t="n">
+      <c r="AA23" s="86" t="n">
         <v>6</v>
       </c>
-      <c r="AA23" s="86" t="n">
+      <c r="AB23" s="86" t="n">
         <v>3</v>
       </c>
-      <c r="AB23" s="86" t="n">
+      <c r="AC23" s="86" t="n">
         <v>4</v>
       </c>
-      <c r="AC23" s="86" t="n">
+      <c r="AD23" s="86" t="n">
         <v>1</v>
       </c>
-      <c r="AD23" s="86" t="n">
+      <c r="AE23" s="86" t="n">
         <v>2</v>
-      </c>
-      <c r="AE23" s="86" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -3889,91 +3889,91 @@
         <v>7.07</v>
       </c>
       <c r="C25" s="88" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="D25" s="88" t="n">
         <v>7.01</v>
-      </c>
-      <c r="D25" s="88" t="n">
-        <v>6.98</v>
       </c>
       <c r="E25" s="88" t="n">
         <v>6.98</v>
       </c>
       <c r="F25" s="88" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="G25" s="88" t="n">
         <v>7.03</v>
       </c>
-      <c r="G25" s="88" t="n">
+      <c r="H25" s="88" t="n">
         <v>7</v>
       </c>
-      <c r="H25" s="88" t="n">
+      <c r="I25" s="88" t="n">
         <v>7.06</v>
       </c>
-      <c r="I25" s="88" t="n">
+      <c r="J25" s="88" t="n">
         <v>7.04</v>
       </c>
-      <c r="J25" s="88" t="n">
+      <c r="K25" s="88" t="n">
         <v>7.07</v>
-      </c>
-      <c r="K25" s="88" t="n">
-        <v>7.1</v>
       </c>
       <c r="L25" s="88" t="n">
         <v>7.1</v>
       </c>
       <c r="M25" s="88" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="N25" s="88" t="n">
         <v>7.12</v>
-      </c>
-      <c r="N25" s="88" t="n">
-        <v>7.13</v>
       </c>
       <c r="O25" s="88" t="n">
         <v>7.13</v>
       </c>
       <c r="P25" s="88" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="Q25" s="88" t="n">
         <v>7.12</v>
-      </c>
-      <c r="Q25" s="88" t="n">
-        <v>7.09</v>
       </c>
       <c r="R25" s="88" t="n">
         <v>7.09</v>
       </c>
       <c r="S25" s="88" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="T25" s="88" t="n">
         <v>7.11</v>
-      </c>
-      <c r="T25" s="88" t="n">
-        <v>7.12</v>
       </c>
       <c r="U25" s="88" t="n">
         <v>7.12</v>
       </c>
       <c r="V25" s="88" t="n">
-        <v>7.09</v>
+        <v>7.12</v>
       </c>
       <c r="W25" s="88" t="n">
         <v>7.09</v>
       </c>
       <c r="X25" s="88" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="Y25" s="88" t="n">
         <v>7.13</v>
       </c>
-      <c r="Y25" s="88" t="n">
+      <c r="Z25" s="88" t="n">
         <v>7.12</v>
       </c>
-      <c r="Z25" s="88" t="n">
+      <c r="AA25" s="88" t="n">
         <v>7.13</v>
       </c>
-      <c r="AA25" s="88" t="n">
+      <c r="AB25" s="88" t="n">
         <v>7.11</v>
       </c>
-      <c r="AB25" s="88" t="n">
+      <c r="AC25" s="88" t="n">
         <v>7.15</v>
       </c>
-      <c r="AC25" s="88" t="n">
+      <c r="AD25" s="88" t="n">
         <v>7.13</v>
       </c>
-      <c r="AD25" s="88" t="n">
+      <c r="AE25" s="88" t="n">
         <v>7.11</v>
-      </c>
-      <c r="AE25" s="88" t="n">
-        <v>7.13</v>
       </c>
     </row>
     <row r="26">
@@ -3983,94 +3983,94 @@
         </is>
       </c>
       <c r="B26" s="89" t="n">
-        <v>0.92</v>
+        <v>-0.04</v>
       </c>
       <c r="C26" s="89" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D26" s="88" t="n">
         <v>0.42</v>
       </c>
-      <c r="D26" s="88" t="n">
+      <c r="E26" s="88" t="n">
         <v>0.02</v>
       </c>
-      <c r="E26" s="88" t="n">
+      <c r="F26" s="88" t="n">
         <v>-0.79</v>
       </c>
-      <c r="F26" s="88" t="n">
+      <c r="G26" s="88" t="n">
         <v>0.49</v>
       </c>
-      <c r="G26" s="88" t="n">
+      <c r="H26" s="88" t="n">
         <v>-0.84</v>
       </c>
-      <c r="H26" s="88" t="n">
+      <c r="I26" s="88" t="n">
         <v>0.27</v>
       </c>
-      <c r="I26" s="88" t="n">
+      <c r="J26" s="88" t="n">
         <v>-0.44</v>
       </c>
-      <c r="J26" s="88" t="n">
+      <c r="K26" s="88" t="n">
         <v>-0.34</v>
       </c>
-      <c r="K26" s="88" t="n">
+      <c r="L26" s="88" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L26" s="88" t="n">
+      <c r="M26" s="88" t="n">
         <v>-0.25</v>
       </c>
-      <c r="M26" s="88" t="n">
+      <c r="N26" s="88" t="n">
         <v>-0.15</v>
       </c>
-      <c r="N26" s="88" t="n">
+      <c r="O26" s="88" t="n">
         <v>-0.1</v>
       </c>
-      <c r="O26" s="88" t="n">
+      <c r="P26" s="88" t="n">
         <v>0.18</v>
       </c>
-      <c r="P26" s="88" t="n">
+      <c r="Q26" s="88" t="n">
         <v>0.43</v>
       </c>
-      <c r="Q26" s="88" t="n">
+      <c r="R26" s="88" t="n">
         <v>0.03</v>
       </c>
-      <c r="R26" s="88" t="n">
+      <c r="S26" s="88" t="n">
         <v>-0.24</v>
       </c>
-      <c r="S26" s="88" t="n">
+      <c r="T26" s="88" t="n">
         <v>-0.18</v>
       </c>
-      <c r="T26" s="88" t="n">
+      <c r="U26" s="88" t="n">
         <v>0.02</v>
       </c>
-      <c r="U26" s="88" t="n">
+      <c r="V26" s="88" t="n">
         <v>0.41</v>
       </c>
-      <c r="V26" s="88" t="n">
+      <c r="W26" s="88" t="n">
         <v>-0.01</v>
       </c>
-      <c r="W26" s="88" t="n">
+      <c r="X26" s="88" t="n">
         <v>-0.59</v>
       </c>
-      <c r="X26" s="88" t="n">
+      <c r="Y26" s="88" t="n">
         <v>0.13</v>
       </c>
-      <c r="Y26" s="88" t="n">
+      <c r="Z26" s="88" t="n">
         <v>-0.05</v>
       </c>
-      <c r="Z26" s="88" t="n">
+      <c r="AA26" s="88" t="n">
         <v>0.15</v>
       </c>
-      <c r="AA26" s="88" t="n">
+      <c r="AB26" s="88" t="n">
         <v>-0.43</v>
       </c>
-      <c r="AB26" s="88" t="n">
+      <c r="AC26" s="88" t="n">
         <v>0.21</v>
       </c>
-      <c r="AC26" s="88" t="n">
+      <c r="AD26" s="88" t="n">
         <v>0.23</v>
       </c>
-      <c r="AD26" s="88" t="n">
+      <c r="AE26" s="88" t="n">
         <v>-0.23</v>
-      </c>
-      <c r="AE26" s="88" t="n">
-        <v>-0.44</v>
       </c>
     </row>
     <row r="27">
@@ -4080,94 +4080,94 @@
         </is>
       </c>
       <c r="B27" s="89" t="n">
-        <v>-0.19</v>
+        <v>-0.64</v>
       </c>
       <c r="C27" s="89" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="D27" s="88" t="n">
         <v>-1.11</v>
       </c>
-      <c r="D27" s="88" t="n">
+      <c r="E27" s="88" t="n">
         <v>-2.1</v>
       </c>
-      <c r="E27" s="88" t="n">
+      <c r="F27" s="88" t="n">
         <v>-2</v>
       </c>
-      <c r="F27" s="88" t="n">
+      <c r="G27" s="88" t="n">
         <v>-1.27</v>
       </c>
-      <c r="G27" s="88" t="n">
+      <c r="H27" s="88" t="n">
         <v>-1.61</v>
       </c>
-      <c r="H27" s="88" t="n">
+      <c r="I27" s="88" t="n">
         <v>-1.2</v>
       </c>
-      <c r="I27" s="88" t="n">
+      <c r="J27" s="88" t="n">
         <v>-1.26</v>
       </c>
-      <c r="J27" s="88" t="n">
+      <c r="K27" s="88" t="n">
         <v>-0.59</v>
       </c>
-      <c r="K27" s="88" t="n">
+      <c r="L27" s="88" t="n">
         <v>-0.47</v>
       </c>
-      <c r="L27" s="88" t="n">
+      <c r="M27" s="88" t="n">
         <v>-0.88</v>
       </c>
-      <c r="M27" s="88" t="n">
+      <c r="N27" s="88" t="n">
         <v>-0.93</v>
       </c>
-      <c r="N27" s="88" t="n">
+      <c r="O27" s="88" t="n">
         <v>-0.29</v>
       </c>
-      <c r="O27" s="88" t="n">
+      <c r="P27" s="88" t="n">
         <v>-0.21</v>
       </c>
-      <c r="P27" s="88" t="n">
+      <c r="Q27" s="88" t="n">
         <v>-0.79</v>
       </c>
-      <c r="Q27" s="88" t="n">
+      <c r="R27" s="88" t="n">
         <v>-1.17</v>
       </c>
-      <c r="R27" s="88" t="n">
+      <c r="S27" s="88" t="n">
         <v>-1.35</v>
       </c>
-      <c r="S27" s="88" t="n">
+      <c r="T27" s="88" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="T27" s="88" t="n">
+      <c r="U27" s="88" t="n">
         <v>-0.58</v>
       </c>
-      <c r="U27" s="88" t="n">
+      <c r="V27" s="88" t="n">
         <v>-0.41</v>
       </c>
-      <c r="V27" s="88" t="n">
+      <c r="W27" s="88" t="n">
         <v>-1.02</v>
       </c>
-      <c r="W27" s="88" t="n">
+      <c r="X27" s="88" t="n">
         <v>-2.2</v>
       </c>
-      <c r="X27" s="88" t="n">
+      <c r="Y27" s="88" t="n">
         <v>-1.3</v>
       </c>
-      <c r="Y27" s="88" t="n">
+      <c r="Z27" s="88" t="n">
         <v>-1.66</v>
       </c>
-      <c r="Z27" s="88" t="n">
+      <c r="AA27" s="88" t="n">
         <v>-1.96</v>
       </c>
-      <c r="AA27" s="88" t="n">
+      <c r="AB27" s="88" t="n">
         <v>-2.03</v>
       </c>
-      <c r="AB27" s="88" t="n">
+      <c r="AC27" s="88" t="n">
         <v>-1.31</v>
       </c>
-      <c r="AC27" s="88" t="n">
+      <c r="AD27" s="88" t="n">
         <v>-1.91</v>
       </c>
-      <c r="AD27" s="88" t="n">
+      <c r="AE27" s="88" t="n">
         <v>-2.42</v>
-      </c>
-      <c r="AE27" s="88" t="n">
-        <v>-2.28</v>
       </c>
     </row>
     <row r="28">
@@ -4177,94 +4177,94 @@
         </is>
       </c>
       <c r="B28" s="86" t="n">
+        <v>2996</v>
+      </c>
+      <c r="C28" s="86" t="n">
         <v>3217</v>
       </c>
-      <c r="C28" s="86" t="n">
+      <c r="D28" s="86" t="n">
         <v>3100</v>
       </c>
-      <c r="D28" s="86" t="n">
+      <c r="E28" s="86" t="n">
         <v>2851</v>
       </c>
-      <c r="E28" s="86" t="n">
+      <c r="F28" s="86" t="n">
         <v>2646</v>
       </c>
-      <c r="F28" s="86" t="n">
+      <c r="G28" s="86" t="n">
         <v>2505</v>
       </c>
-      <c r="G28" s="86" t="n">
+      <c r="H28" s="86" t="n">
         <v>2483</v>
       </c>
-      <c r="H28" s="86" t="n">
+      <c r="I28" s="86" t="n">
         <v>2363</v>
       </c>
-      <c r="I28" s="86" t="n">
+      <c r="J28" s="86" t="n">
         <v>2355</v>
       </c>
-      <c r="J28" s="86" t="n">
+      <c r="K28" s="86" t="n">
         <v>2365</v>
       </c>
-      <c r="K28" s="86" t="n">
+      <c r="L28" s="86" t="n">
         <v>2330</v>
       </c>
-      <c r="L28" s="86" t="n">
+      <c r="M28" s="86" t="n">
         <v>2328</v>
       </c>
-      <c r="M28" s="86" t="n">
+      <c r="N28" s="86" t="n">
         <v>2349</v>
       </c>
-      <c r="N28" s="86" t="n">
+      <c r="O28" s="86" t="n">
         <v>2354</v>
       </c>
-      <c r="O28" s="86" t="n">
+      <c r="P28" s="86" t="n">
         <v>2355</v>
       </c>
-      <c r="P28" s="86" t="n">
+      <c r="Q28" s="86" t="n">
         <v>2353</v>
       </c>
-      <c r="Q28" s="86" t="n">
+      <c r="R28" s="86" t="n">
         <v>2375</v>
       </c>
-      <c r="R28" s="86" t="n">
+      <c r="S28" s="86" t="n">
         <v>2407</v>
       </c>
-      <c r="S28" s="86" t="n">
+      <c r="T28" s="86" t="n">
         <v>2395</v>
       </c>
-      <c r="T28" s="86" t="n">
+      <c r="U28" s="86" t="n">
         <v>2404</v>
       </c>
-      <c r="U28" s="86" t="n">
+      <c r="V28" s="86" t="n">
         <v>2392</v>
       </c>
-      <c r="V28" s="86" t="n">
+      <c r="W28" s="86" t="n">
         <v>2443</v>
       </c>
-      <c r="W28" s="86" t="n">
+      <c r="X28" s="86" t="n">
         <v>2401</v>
       </c>
-      <c r="X28" s="86" t="n">
+      <c r="Y28" s="86" t="n">
         <v>2379</v>
       </c>
-      <c r="Y28" s="86" t="n">
+      <c r="Z28" s="86" t="n">
         <v>2384</v>
       </c>
-      <c r="Z28" s="86" t="n">
+      <c r="AA28" s="86" t="n">
         <v>2403</v>
       </c>
-      <c r="AA28" s="86" t="n">
+      <c r="AB28" s="86" t="n">
         <v>2400</v>
       </c>
-      <c r="AB28" s="86" t="n">
+      <c r="AC28" s="86" t="n">
         <v>2392</v>
       </c>
-      <c r="AC28" s="86" t="n">
+      <c r="AD28" s="86" t="n">
         <v>2412</v>
       </c>
-      <c r="AD28" s="86" t="n">
+      <c r="AE28" s="86" t="n">
         <v>2417</v>
-      </c>
-      <c r="AE28" s="86" t="n">
-        <v>2454</v>
       </c>
     </row>
     <row r="29">
@@ -4274,94 +4274,94 @@
         </is>
       </c>
       <c r="B29" s="86" t="n">
+        <v>18196.08</v>
+      </c>
+      <c r="C29" s="86" t="n">
         <v>18342.9</v>
       </c>
-      <c r="C29" s="86" t="n">
+      <c r="D29" s="86" t="n">
         <v>17606.93</v>
       </c>
-      <c r="D29" s="86" t="n">
+      <c r="E29" s="86" t="n">
         <v>15998.63</v>
       </c>
-      <c r="E29" s="86" t="n">
+      <c r="F29" s="86" t="n">
         <v>14768.14</v>
       </c>
-      <c r="F29" s="86" t="n">
+      <c r="G29" s="86" t="n">
         <v>13526.64</v>
       </c>
-      <c r="G29" s="86" t="n">
+      <c r="H29" s="86" t="n">
         <v>13800.9</v>
       </c>
-      <c r="H29" s="86" t="n">
+      <c r="I29" s="86" t="n">
         <v>11544.58</v>
       </c>
-      <c r="I29" s="86" t="n">
+      <c r="J29" s="86" t="n">
         <v>11616.2</v>
       </c>
-      <c r="J29" s="86" t="n">
+      <c r="K29" s="86" t="n">
         <v>13089.88</v>
       </c>
-      <c r="K29" s="86" t="n">
+      <c r="L29" s="86" t="n">
         <v>12465.83</v>
       </c>
-      <c r="L29" s="86" t="n">
+      <c r="M29" s="86" t="n">
         <v>11938.76</v>
       </c>
-      <c r="M29" s="86" t="n">
+      <c r="N29" s="86" t="n">
         <v>12054.01</v>
       </c>
-      <c r="N29" s="86" t="n">
+      <c r="O29" s="86" t="n">
         <v>11859.62</v>
       </c>
-      <c r="O29" s="86" t="n">
+      <c r="P29" s="86" t="n">
         <v>12309.48</v>
       </c>
-      <c r="P29" s="86" t="n">
+      <c r="Q29" s="86" t="n">
         <v>11892.59</v>
       </c>
-      <c r="Q29" s="86" t="n">
+      <c r="R29" s="86" t="n">
         <v>11776.47</v>
       </c>
-      <c r="R29" s="86" t="n">
+      <c r="S29" s="86" t="n">
         <v>11675.78</v>
       </c>
-      <c r="S29" s="86" t="n">
+      <c r="T29" s="86" t="n">
         <v>11602.92</v>
       </c>
-      <c r="T29" s="86" t="n">
+      <c r="U29" s="86" t="n">
         <v>11818.73</v>
       </c>
-      <c r="U29" s="86" t="n">
+      <c r="V29" s="86" t="n">
         <v>11478</v>
       </c>
-      <c r="V29" s="86" t="n">
+      <c r="W29" s="86" t="n">
         <v>12471.49</v>
       </c>
-      <c r="W29" s="86" t="n">
+      <c r="X29" s="86" t="n">
         <v>11718.02</v>
       </c>
-      <c r="X29" s="86" t="n">
+      <c r="Y29" s="86" t="n">
         <v>11315.57</v>
       </c>
-      <c r="Y29" s="86" t="n">
+      <c r="Z29" s="86" t="n">
         <v>11020.76</v>
       </c>
-      <c r="Z29" s="86" t="n">
+      <c r="AA29" s="86" t="n">
         <v>11193.66</v>
       </c>
-      <c r="AA29" s="86" t="n">
+      <c r="AB29" s="86" t="n">
         <v>11195.74</v>
       </c>
-      <c r="AB29" s="86" t="n">
+      <c r="AC29" s="86" t="n">
         <v>11410.71</v>
       </c>
-      <c r="AC29" s="86" t="n">
+      <c r="AD29" s="86" t="n">
         <v>11122.46</v>
       </c>
-      <c r="AD29" s="86" t="n">
+      <c r="AE29" s="86" t="n">
         <v>11439.39</v>
-      </c>
-      <c r="AE29" s="86" t="n">
-        <v>11516.31</v>
       </c>
     </row>
     <row r="30">
@@ -4371,94 +4371,94 @@
         </is>
       </c>
       <c r="B30" s="90" t="n">
+        <v>46.16</v>
+      </c>
+      <c r="C30" s="90" t="n">
         <v>45.91</v>
       </c>
-      <c r="C30" s="90" t="n">
+      <c r="D30" s="90" t="n">
         <v>46.49</v>
       </c>
-      <c r="D30" s="90" t="n">
+      <c r="E30" s="90" t="n">
         <v>46.8</v>
       </c>
-      <c r="E30" s="90" t="n">
+      <c r="F30" s="90" t="n">
         <v>46.99</v>
       </c>
-      <c r="F30" s="90" t="n">
+      <c r="G30" s="90" t="n">
         <v>47.26</v>
       </c>
-      <c r="G30" s="90" t="n">
+      <c r="H30" s="90" t="n">
         <v>47.47</v>
       </c>
-      <c r="H30" s="90" t="n">
+      <c r="I30" s="90" t="n">
         <v>47.52</v>
       </c>
-      <c r="I30" s="90" t="n">
+      <c r="J30" s="90" t="n">
         <v>47.5</v>
       </c>
-      <c r="J30" s="90" t="n">
+      <c r="K30" s="90" t="n">
         <v>47.39</v>
       </c>
-      <c r="K30" s="90" t="n">
+      <c r="L30" s="90" t="n">
         <v>47.54</v>
       </c>
-      <c r="L30" s="90" t="n">
+      <c r="M30" s="90" t="n">
         <v>47.31</v>
       </c>
-      <c r="M30" s="90" t="n">
+      <c r="N30" s="90" t="n">
         <v>47.24</v>
       </c>
-      <c r="N30" s="90" t="n">
+      <c r="O30" s="90" t="n">
         <v>47.26</v>
       </c>
-      <c r="O30" s="90" t="n">
+      <c r="P30" s="90" t="n">
         <v>47.5</v>
       </c>
-      <c r="P30" s="90" t="n">
+      <c r="Q30" s="90" t="n">
         <v>47.4</v>
       </c>
-      <c r="Q30" s="90" t="n">
+      <c r="R30" s="90" t="n">
         <v>47.44</v>
       </c>
-      <c r="R30" s="90" t="n">
+      <c r="S30" s="90" t="n">
         <v>47.35</v>
       </c>
-      <c r="S30" s="90" t="n">
+      <c r="T30" s="90" t="n">
         <v>47.37</v>
       </c>
-      <c r="T30" s="90" t="n">
+      <c r="U30" s="90" t="n">
         <v>47.36</v>
       </c>
-      <c r="U30" s="90" t="n">
+      <c r="V30" s="90" t="n">
         <v>47.2</v>
       </c>
-      <c r="V30" s="90" t="n">
+      <c r="W30" s="90" t="n">
         <v>47.19</v>
       </c>
-      <c r="W30" s="90" t="n">
+      <c r="X30" s="90" t="n">
         <v>47.18</v>
       </c>
-      <c r="X30" s="90" t="n">
+      <c r="Y30" s="90" t="n">
         <v>47.17</v>
       </c>
-      <c r="Y30" s="90" t="n">
+      <c r="Z30" s="90" t="n">
         <v>47.11</v>
       </c>
-      <c r="Z30" s="90" t="n">
+      <c r="AA30" s="90" t="n">
         <v>47.04</v>
       </c>
-      <c r="AA30" s="90" t="n">
+      <c r="AB30" s="90" t="n">
         <v>47.06</v>
       </c>
-      <c r="AB30" s="90" t="n">
+      <c r="AC30" s="90" t="n">
         <v>47.22</v>
       </c>
-      <c r="AC30" s="90" t="n">
+      <c r="AD30" s="90" t="n">
         <v>47.19</v>
       </c>
-      <c r="AD30" s="90" t="n">
+      <c r="AE30" s="90" t="n">
         <v>47.14</v>
-      </c>
-      <c r="AE30" s="90" t="n">
-        <v>47.03</v>
       </c>
     </row>
     <row r="31">
@@ -4468,94 +4468,94 @@
         </is>
       </c>
       <c r="B31" s="86" t="n">
+        <v>-1398.16</v>
+      </c>
+      <c r="C31" s="86" t="n">
         <v>-1500.31</v>
       </c>
-      <c r="C31" s="86" t="n">
+      <c r="D31" s="86" t="n">
         <v>-1237.26</v>
       </c>
-      <c r="D31" s="86" t="n">
+      <c r="E31" s="86" t="n">
         <v>-1024.13</v>
       </c>
-      <c r="E31" s="86" t="n">
+      <c r="F31" s="86" t="n">
         <v>-890.33</v>
       </c>
-      <c r="F31" s="86" t="n">
+      <c r="G31" s="86" t="n">
         <v>-741.6799999999999</v>
       </c>
-      <c r="G31" s="86" t="n">
+      <c r="H31" s="86" t="n">
         <v>-697.09</v>
       </c>
-      <c r="H31" s="86" t="n">
+      <c r="I31" s="86" t="n">
         <v>-571.89</v>
       </c>
-      <c r="I31" s="86" t="n">
+      <c r="J31" s="86" t="n">
         <v>-579.7</v>
       </c>
-      <c r="J31" s="86" t="n">
+      <c r="K31" s="86" t="n">
         <v>-683.6</v>
       </c>
-      <c r="K31" s="86" t="n">
+      <c r="L31" s="86" t="n">
         <v>-612.92</v>
       </c>
-      <c r="L31" s="86" t="n">
+      <c r="M31" s="86" t="n">
         <v>-641.25</v>
       </c>
-      <c r="M31" s="86" t="n">
+      <c r="N31" s="86" t="n">
         <v>-665.05</v>
       </c>
-      <c r="N31" s="86" t="n">
+      <c r="O31" s="86" t="n">
         <v>-650.98</v>
       </c>
-      <c r="O31" s="86" t="n">
+      <c r="P31" s="86" t="n">
         <v>-615.41</v>
       </c>
-      <c r="P31" s="86" t="n">
+      <c r="Q31" s="86" t="n">
         <v>-618.52</v>
       </c>
-      <c r="Q31" s="86" t="n">
+      <c r="R31" s="86" t="n">
         <v>-603.8099999999999</v>
       </c>
-      <c r="R31" s="86" t="n">
+      <c r="S31" s="86" t="n">
         <v>-618.02</v>
       </c>
-      <c r="S31" s="86" t="n">
+      <c r="T31" s="86" t="n">
         <v>-609.3200000000001</v>
       </c>
-      <c r="T31" s="86" t="n">
+      <c r="U31" s="86" t="n">
         <v>-623.89</v>
       </c>
-      <c r="U31" s="86" t="n">
+      <c r="V31" s="86" t="n">
         <v>-641.9299999999999</v>
       </c>
-      <c r="V31" s="86" t="n">
+      <c r="W31" s="86" t="n">
         <v>-700.54</v>
       </c>
-      <c r="W31" s="86" t="n">
+      <c r="X31" s="86" t="n">
         <v>-661.59</v>
       </c>
-      <c r="X31" s="86" t="n">
+      <c r="Y31" s="86" t="n">
         <v>-641.1</v>
       </c>
-      <c r="Y31" s="86" t="n">
+      <c r="Z31" s="86" t="n">
         <v>-637.14</v>
       </c>
-      <c r="Z31" s="86" t="n">
+      <c r="AA31" s="86" t="n">
         <v>-663.05</v>
       </c>
-      <c r="AA31" s="86" t="n">
+      <c r="AB31" s="86" t="n">
         <v>-659.14</v>
       </c>
-      <c r="AB31" s="86" t="n">
+      <c r="AC31" s="86" t="n">
         <v>-634.26</v>
       </c>
-      <c r="AC31" s="86" t="n">
+      <c r="AD31" s="86" t="n">
         <v>-625.59</v>
       </c>
-      <c r="AD31" s="86" t="n">
+      <c r="AE31" s="86" t="n">
         <v>-653.9</v>
-      </c>
-      <c r="AE31" s="86" t="n">
-        <v>-684.42</v>
       </c>
     </row>
     <row r="32">
@@ -4565,94 +4565,94 @@
         </is>
       </c>
       <c r="B32" s="86" t="n">
+        <v>-49391</v>
+      </c>
+      <c r="C32" s="86" t="n">
         <v>-59269</v>
       </c>
-      <c r="C32" s="86" t="n">
+      <c r="D32" s="86" t="n">
         <v>-36222</v>
       </c>
-      <c r="D32" s="86" t="n">
+      <c r="E32" s="86" t="n">
         <v>-42709</v>
       </c>
-      <c r="E32" s="86" t="n">
+      <c r="F32" s="86" t="n">
         <v>-39170</v>
       </c>
-      <c r="F32" s="86" t="n">
+      <c r="G32" s="86" t="n">
         <v>-25624</v>
       </c>
-      <c r="G32" s="86" t="n">
+      <c r="H32" s="86" t="n">
         <v>-27286</v>
       </c>
-      <c r="H32" s="86" t="n">
+      <c r="I32" s="86" t="n">
         <v>-15398</v>
       </c>
-      <c r="I32" s="86" t="n">
+      <c r="J32" s="86" t="n">
         <v>-19443</v>
       </c>
-      <c r="J32" s="86" t="n">
+      <c r="K32" s="86" t="n">
         <v>-32280</v>
       </c>
-      <c r="K32" s="86" t="n">
+      <c r="L32" s="86" t="n">
         <v>-23022</v>
       </c>
-      <c r="L32" s="86" t="n">
+      <c r="M32" s="86" t="n">
         <v>-25189</v>
       </c>
-      <c r="M32" s="86" t="n">
+      <c r="N32" s="86" t="n">
         <v>-28419</v>
       </c>
-      <c r="N32" s="86" t="n">
+      <c r="O32" s="86" t="n">
         <v>-28410</v>
       </c>
-      <c r="O32" s="86" t="n">
+      <c r="P32" s="86" t="n">
         <v>-26045</v>
       </c>
-      <c r="P32" s="86" t="n">
+      <c r="Q32" s="86" t="n">
         <v>-25973</v>
       </c>
-      <c r="Q32" s="86" t="n">
+      <c r="R32" s="86" t="n">
         <v>-22401</v>
       </c>
-      <c r="R32" s="86" t="n">
+      <c r="S32" s="86" t="n">
         <v>-25659</v>
       </c>
-      <c r="S32" s="86" t="n">
+      <c r="T32" s="86" t="n">
         <v>-23596</v>
       </c>
-      <c r="T32" s="86" t="n">
+      <c r="U32" s="86" t="n">
         <v>-25748</v>
       </c>
-      <c r="U32" s="86" t="n">
+      <c r="V32" s="86" t="n">
         <v>-21620</v>
       </c>
-      <c r="V32" s="86" t="n">
+      <c r="W32" s="86" t="n">
         <v>-24563</v>
       </c>
-      <c r="W32" s="86" t="n">
+      <c r="X32" s="86" t="n">
         <v>-34543</v>
       </c>
-      <c r="X32" s="86" t="n">
+      <c r="Y32" s="86" t="n">
         <v>-26728</v>
       </c>
-      <c r="Y32" s="86" t="n">
+      <c r="Z32" s="86" t="n">
         <v>-25843</v>
       </c>
-      <c r="Z32" s="86" t="n">
+      <c r="AA32" s="86" t="n">
         <v>-30256</v>
       </c>
-      <c r="AA32" s="86" t="n">
+      <c r="AB32" s="86" t="n">
         <v>-25652</v>
       </c>
-      <c r="AB32" s="86" t="n">
+      <c r="AC32" s="86" t="n">
         <v>-19237</v>
       </c>
-      <c r="AC32" s="86" t="n">
+      <c r="AD32" s="86" t="n">
         <v>-25229</v>
       </c>
-      <c r="AD32" s="86" t="n">
+      <c r="AE32" s="86" t="n">
         <v>-26744</v>
-      </c>
-      <c r="AE32" s="86" t="n">
-        <v>-26628</v>
       </c>
     </row>
     <row r="33">
@@ -4662,94 +4662,94 @@
         </is>
       </c>
       <c r="B33" s="86" t="n">
+        <v>-547</v>
+      </c>
+      <c r="C33" s="86" t="n">
         <v>1649</v>
       </c>
-      <c r="C33" s="86" t="n">
+      <c r="D33" s="86" t="n">
         <v>5979</v>
       </c>
-      <c r="D33" s="86" t="n">
+      <c r="E33" s="86" t="n">
         <v>1547</v>
       </c>
-      <c r="E33" s="86" t="n">
+      <c r="F33" s="86" t="n">
         <v>703</v>
       </c>
-      <c r="F33" s="86" t="n">
+      <c r="G33" s="86" t="n">
         <v>7134</v>
       </c>
-      <c r="G33" s="86" t="n">
+      <c r="H33" s="86" t="n">
         <v>6476</v>
       </c>
-      <c r="H33" s="86" t="n">
+      <c r="I33" s="86" t="n">
         <v>13199</v>
       </c>
-      <c r="I33" s="86" t="n">
+      <c r="J33" s="86" t="n">
         <v>12591</v>
       </c>
-      <c r="J33" s="86" t="n">
+      <c r="K33" s="86" t="n">
         <v>9543</v>
       </c>
-      <c r="K33" s="86" t="n">
+      <c r="L33" s="86" t="n">
         <v>10679</v>
       </c>
-      <c r="L33" s="86" t="n">
+      <c r="M33" s="86" t="n">
         <v>7507</v>
       </c>
-      <c r="M33" s="86" t="n">
+      <c r="N33" s="86" t="n">
         <v>-878</v>
       </c>
-      <c r="N33" s="86" t="n">
+      <c r="O33" s="86" t="n">
         <v>100</v>
       </c>
-      <c r="O33" s="86" t="n">
+      <c r="P33" s="86" t="n">
         <v>-1402</v>
       </c>
-      <c r="P33" s="86" t="n">
+      <c r="Q33" s="86" t="n">
         <v>-34</v>
       </c>
-      <c r="Q33" s="86" t="n">
+      <c r="R33" s="86" t="n">
         <v>-2376</v>
       </c>
-      <c r="R33" s="86" t="n">
+      <c r="S33" s="86" t="n">
         <v>-2051</v>
       </c>
-      <c r="S33" s="86" t="n">
+      <c r="T33" s="86" t="n">
         <v>-1952</v>
       </c>
-      <c r="T33" s="86" t="n">
+      <c r="U33" s="86" t="n">
         <v>-3278</v>
       </c>
-      <c r="U33" s="86" t="n">
+      <c r="V33" s="86" t="n">
         <v>-2459</v>
       </c>
-      <c r="V33" s="86" t="n">
+      <c r="W33" s="86" t="n">
         <v>-1710</v>
       </c>
-      <c r="W33" s="86" t="n">
+      <c r="X33" s="86" t="n">
         <v>-6016</v>
       </c>
-      <c r="X33" s="86" t="n">
+      <c r="Y33" s="86" t="n">
         <v>-3908</v>
       </c>
-      <c r="Y33" s="86" t="n">
+      <c r="Z33" s="86" t="n">
         <v>-2374</v>
       </c>
-      <c r="Z33" s="86" t="n">
+      <c r="AA33" s="86" t="n">
         <v>-4680</v>
       </c>
-      <c r="AA33" s="86" t="n">
+      <c r="AB33" s="86" t="n">
         <v>-5784</v>
       </c>
-      <c r="AB33" s="86" t="n">
+      <c r="AC33" s="86" t="n">
         <v>-4660</v>
       </c>
-      <c r="AC33" s="86" t="n">
+      <c r="AD33" s="86" t="n">
         <v>-6865</v>
       </c>
-      <c r="AD33" s="86" t="n">
+      <c r="AE33" s="86" t="n">
         <v>-8722</v>
-      </c>
-      <c r="AE33" s="86" t="n">
-        <v>-15539</v>
       </c>
     </row>
     <row r="34">
@@ -4759,94 +4759,94 @@
         </is>
       </c>
       <c r="B34" s="86" t="n">
+        <v>-33151</v>
+      </c>
+      <c r="C34" s="86" t="n">
         <v>-31667</v>
       </c>
-      <c r="C34" s="86" t="n">
+      <c r="D34" s="86" t="n">
         <v>-30115</v>
       </c>
-      <c r="D34" s="86" t="n">
+      <c r="E34" s="86" t="n">
         <v>-27126</v>
       </c>
-      <c r="E34" s="86" t="n">
+      <c r="F34" s="86" t="n">
         <v>-28243</v>
       </c>
-      <c r="F34" s="86" t="n">
+      <c r="G34" s="86" t="n">
         <v>-19887</v>
       </c>
-      <c r="G34" s="86" t="n">
+      <c r="H34" s="86" t="n">
         <v>-21792</v>
       </c>
-      <c r="H34" s="86" t="n">
+      <c r="I34" s="86" t="n">
         <v>-16942</v>
       </c>
-      <c r="I34" s="86" t="n">
+      <c r="J34" s="86" t="n">
         <v>-18355</v>
       </c>
-      <c r="J34" s="86" t="n">
+      <c r="K34" s="86" t="n">
         <v>-21603</v>
       </c>
-      <c r="K34" s="86" t="n">
+      <c r="L34" s="86" t="n">
         <v>-20550</v>
       </c>
-      <c r="L34" s="86" t="n">
+      <c r="M34" s="86" t="n">
         <v>-21729</v>
       </c>
-      <c r="M34" s="86" t="n">
+      <c r="N34" s="86" t="n">
         <v>-22380</v>
       </c>
-      <c r="N34" s="86" t="n">
+      <c r="O34" s="86" t="n">
         <v>-21704</v>
       </c>
-      <c r="O34" s="86" t="n">
+      <c r="P34" s="86" t="n">
         <v>-19910</v>
       </c>
-      <c r="P34" s="86" t="n">
+      <c r="Q34" s="86" t="n">
         <v>-20729</v>
       </c>
-      <c r="Q34" s="86" t="n">
+      <c r="R34" s="86" t="n">
         <v>-22784</v>
       </c>
-      <c r="R34" s="86" t="n">
+      <c r="S34" s="86" t="n">
         <v>-22366</v>
       </c>
-      <c r="S34" s="86" t="n">
+      <c r="T34" s="86" t="n">
         <v>-21405</v>
       </c>
-      <c r="T34" s="86" t="n">
+      <c r="U34" s="86" t="n">
         <v>-23401</v>
       </c>
-      <c r="U34" s="86" t="n">
+      <c r="V34" s="86" t="n">
         <v>-23495</v>
       </c>
-      <c r="V34" s="86" t="n">
+      <c r="W34" s="86" t="n">
         <v>-24752</v>
       </c>
-      <c r="W34" s="86" t="n">
+      <c r="X34" s="86" t="n">
         <v>-29112</v>
       </c>
-      <c r="X34" s="86" t="n">
+      <c r="Y34" s="86" t="n">
         <v>-27546</v>
       </c>
-      <c r="Y34" s="86" t="n">
+      <c r="Z34" s="86" t="n">
         <v>-28104</v>
       </c>
-      <c r="Z34" s="86" t="n">
+      <c r="AA34" s="86" t="n">
         <v>-29738</v>
       </c>
-      <c r="AA34" s="86" t="n">
+      <c r="AB34" s="86" t="n">
         <v>-28980</v>
       </c>
-      <c r="AB34" s="86" t="n">
+      <c r="AC34" s="86" t="n">
         <v>-26883</v>
       </c>
-      <c r="AC34" s="86" t="n">
+      <c r="AD34" s="86" t="n">
         <v>-25603</v>
       </c>
-      <c r="AD34" s="86" t="n">
+      <c r="AE34" s="86" t="n">
         <v>-27262</v>
-      </c>
-      <c r="AE34" s="86" t="n">
-        <v>-27452</v>
       </c>
     </row>
     <row r="35">
@@ -4856,94 +4856,94 @@
         </is>
       </c>
       <c r="B35" s="86" t="n">
+        <v>-4593</v>
+      </c>
+      <c r="C35" s="86" t="n">
         <v>-3500</v>
       </c>
-      <c r="C35" s="86" t="n">
+      <c r="D35" s="86" t="n">
         <v>-7128</v>
       </c>
-      <c r="D35" s="86" t="n">
+      <c r="E35" s="86" t="n">
         <v>-7781</v>
       </c>
-      <c r="E35" s="86" t="n">
+      <c r="F35" s="86" t="n">
         <v>-8727</v>
       </c>
-      <c r="F35" s="86" t="n">
+      <c r="G35" s="86" t="n">
         <v>-6282</v>
       </c>
-      <c r="G35" s="86" t="n">
+      <c r="H35" s="86" t="n">
         <v>-6639</v>
       </c>
-      <c r="H35" s="86" t="n">
+      <c r="I35" s="86" t="n">
         <v>-3532</v>
       </c>
-      <c r="I35" s="86" t="n">
+      <c r="J35" s="86" t="n">
         <v>-2293</v>
       </c>
-      <c r="J35" s="86" t="n">
+      <c r="K35" s="86" t="n">
         <v>-4574</v>
       </c>
-      <c r="K35" s="86" t="n">
+      <c r="L35" s="86" t="n">
         <v>-2414</v>
       </c>
-      <c r="L35" s="86" t="n">
+      <c r="M35" s="86" t="n">
         <v>-2494</v>
       </c>
-      <c r="M35" s="86" t="n">
+      <c r="N35" s="86" t="n">
         <v>-6478</v>
       </c>
-      <c r="N35" s="86" t="n">
+      <c r="O35" s="86" t="n">
         <v>-3961</v>
       </c>
-      <c r="O35" s="86" t="n">
+      <c r="P35" s="86" t="n">
         <v>-7065</v>
       </c>
-      <c r="P35" s="86" t="n">
+      <c r="Q35" s="86" t="n">
         <v>-5691</v>
       </c>
-      <c r="Q35" s="86" t="n">
+      <c r="R35" s="86" t="n">
         <v>-8542</v>
       </c>
-      <c r="R35" s="86" t="n">
+      <c r="S35" s="86" t="n">
         <v>-8285</v>
       </c>
-      <c r="S35" s="86" t="n">
+      <c r="T35" s="86" t="n">
         <v>-10101</v>
       </c>
-      <c r="T35" s="86" t="n">
+      <c r="U35" s="86" t="n">
         <v>-10429</v>
       </c>
-      <c r="U35" s="86" t="n">
+      <c r="V35" s="86" t="n">
         <v>-12108</v>
       </c>
-      <c r="V35" s="86" t="n">
+      <c r="W35" s="86" t="n">
         <v>-12524</v>
       </c>
-      <c r="W35" s="86" t="n">
+      <c r="X35" s="86" t="n">
         <v>-13507</v>
       </c>
-      <c r="X35" s="86" t="n">
+      <c r="Y35" s="86" t="n">
         <v>-12337</v>
       </c>
-      <c r="Y35" s="86" t="n">
+      <c r="Z35" s="86" t="n">
         <v>-14270</v>
       </c>
-      <c r="Z35" s="86" t="n">
+      <c r="AA35" s="86" t="n">
         <v>-15565</v>
       </c>
-      <c r="AA35" s="86" t="n">
+      <c r="AB35" s="86" t="n">
         <v>-15217</v>
       </c>
-      <c r="AB35" s="86" t="n">
+      <c r="AC35" s="86" t="n">
         <v>-13494</v>
       </c>
-      <c r="AC35" s="86" t="n">
+      <c r="AD35" s="86" t="n">
         <v>-13870</v>
       </c>
-      <c r="AD35" s="86" t="n">
+      <c r="AE35" s="86" t="n">
         <v>-14538</v>
-      </c>
-      <c r="AE35" s="86" t="n">
-        <v>-19967</v>
       </c>
     </row>
     <row r="36">
@@ -4953,94 +4953,94 @@
         </is>
       </c>
       <c r="B36" s="86" t="n">
+        <v>30833</v>
+      </c>
+      <c r="C36" s="86" t="n">
         <v>34266</v>
       </c>
-      <c r="C36" s="86" t="n">
+      <c r="D36" s="86" t="n">
         <v>44758</v>
       </c>
-      <c r="D36" s="86" t="n">
+      <c r="E36" s="86" t="n">
         <v>46864</v>
       </c>
-      <c r="E36" s="86" t="n">
+      <c r="F36" s="86" t="n">
         <v>52065</v>
       </c>
-      <c r="F36" s="86" t="n">
+      <c r="G36" s="86" t="n">
         <v>44830</v>
       </c>
-      <c r="G36" s="86" t="n">
+      <c r="H36" s="86" t="n">
         <v>44611</v>
       </c>
-      <c r="H36" s="86" t="n">
+      <c r="I36" s="86" t="n">
         <v>43465</v>
       </c>
-      <c r="I36" s="86" t="n">
+      <c r="J36" s="86" t="n">
         <v>43814</v>
       </c>
-      <c r="J36" s="86" t="n">
+      <c r="K36" s="86" t="n">
         <v>41323</v>
       </c>
-      <c r="K36" s="86" t="n">
+      <c r="L36" s="86" t="n">
         <v>33152</v>
       </c>
-      <c r="L36" s="86" t="n">
+      <c r="M36" s="86" t="n">
         <v>45049</v>
       </c>
-      <c r="M36" s="86" t="n">
+      <c r="N36" s="86" t="n">
         <v>51475</v>
       </c>
-      <c r="N36" s="86" t="n">
+      <c r="O36" s="86" t="n">
         <v>58550</v>
       </c>
-      <c r="O36" s="86" t="n">
+      <c r="P36" s="86" t="n">
         <v>59882</v>
       </c>
-      <c r="P36" s="86" t="n">
+      <c r="Q36" s="86" t="n">
         <v>62552</v>
       </c>
-      <c r="Q36" s="86" t="n">
+      <c r="R36" s="86" t="n">
         <v>60880</v>
       </c>
-      <c r="R36" s="86" t="n">
+      <c r="S36" s="86" t="n">
         <v>65490</v>
       </c>
-      <c r="S36" s="86" t="n">
+      <c r="T36" s="86" t="n">
         <v>71195</v>
       </c>
-      <c r="T36" s="86" t="n">
+      <c r="U36" s="86" t="n">
         <v>72587</v>
       </c>
-      <c r="U36" s="86" t="n">
+      <c r="V36" s="86" t="n">
         <v>77242</v>
       </c>
-      <c r="V36" s="86" t="n">
+      <c r="W36" s="86" t="n">
         <v>86343</v>
       </c>
-      <c r="W36" s="86" t="n">
+      <c r="X36" s="86" t="n">
         <v>82858</v>
       </c>
-      <c r="X36" s="86" t="n">
+      <c r="Y36" s="86" t="n">
         <v>86384</v>
       </c>
-      <c r="Y36" s="86" t="n">
+      <c r="Z36" s="86" t="n">
         <v>87972</v>
       </c>
-      <c r="Z36" s="86" t="n">
+      <c r="AA36" s="86" t="n">
         <v>91967</v>
       </c>
-      <c r="AA36" s="86" t="n">
+      <c r="AB36" s="86" t="n">
         <v>94221</v>
       </c>
-      <c r="AB36" s="86" t="n">
+      <c r="AC36" s="86" t="n">
         <v>93650</v>
       </c>
-      <c r="AC36" s="86" t="n">
+      <c r="AD36" s="86" t="n">
         <v>90571</v>
       </c>
-      <c r="AD36" s="86" t="n">
+      <c r="AE36" s="86" t="n">
         <v>94170</v>
-      </c>
-      <c r="AE36" s="86" t="n">
-        <v>95452</v>
       </c>
     </row>
     <row r="37">
@@ -5050,94 +5050,94 @@
         </is>
       </c>
       <c r="B37" s="86" t="n">
+        <v>174408</v>
+      </c>
+      <c r="C37" s="86" t="n">
         <v>173363</v>
       </c>
-      <c r="C37" s="86" t="n">
+      <c r="D37" s="86" t="n">
         <v>152297</v>
       </c>
-      <c r="D37" s="86" t="n">
+      <c r="E37" s="86" t="n">
         <v>149831</v>
       </c>
-      <c r="E37" s="86" t="n">
+      <c r="F37" s="86" t="n">
         <v>138990</v>
       </c>
-      <c r="F37" s="86" t="n">
+      <c r="G37" s="86" t="n">
         <v>124265</v>
       </c>
-      <c r="G37" s="86" t="n">
+      <c r="H37" s="86" t="n">
         <v>129855</v>
       </c>
-      <c r="H37" s="86" t="n">
+      <c r="I37" s="86" t="n">
         <v>121593</v>
       </c>
-      <c r="I37" s="86" t="n">
+      <c r="J37" s="86" t="n">
         <v>126065</v>
       </c>
-      <c r="J37" s="86" t="n">
+      <c r="K37" s="86" t="n">
         <v>114091</v>
       </c>
-      <c r="K37" s="86" t="n">
+      <c r="L37" s="86" t="n">
         <v>120465</v>
       </c>
-      <c r="L37" s="86" t="n">
+      <c r="M37" s="86" t="n">
         <v>124864</v>
       </c>
-      <c r="M37" s="86" t="n">
+      <c r="N37" s="86" t="n">
         <v>129844</v>
       </c>
-      <c r="N37" s="86" t="n">
+      <c r="O37" s="86" t="n">
         <v>125285</v>
       </c>
-      <c r="O37" s="86" t="n">
+      <c r="P37" s="86" t="n">
         <v>124136</v>
       </c>
-      <c r="P37" s="86" t="n">
+      <c r="Q37" s="86" t="n">
         <v>115543</v>
       </c>
-      <c r="Q37" s="86" t="n">
+      <c r="R37" s="86" t="n">
         <v>107325</v>
       </c>
-      <c r="R37" s="86" t="n">
+      <c r="S37" s="86" t="n">
         <v>111789</v>
       </c>
-      <c r="S37" s="86" t="n">
+      <c r="T37" s="86" t="n">
         <v>108003</v>
       </c>
-      <c r="T37" s="86" t="n">
+      <c r="U37" s="86" t="n">
         <v>110293</v>
       </c>
-      <c r="U37" s="86" t="n">
+      <c r="V37" s="86" t="n">
         <v>122598</v>
       </c>
-      <c r="V37" s="86" t="n">
+      <c r="W37" s="86" t="n">
         <v>135319</v>
       </c>
-      <c r="W37" s="86" t="n">
+      <c r="X37" s="86" t="n">
         <v>121088</v>
       </c>
-      <c r="X37" s="86" t="n">
+      <c r="Y37" s="86" t="n">
         <v>129278</v>
       </c>
-      <c r="Y37" s="86" t="n">
+      <c r="Z37" s="86" t="n">
         <v>129820</v>
       </c>
-      <c r="Z37" s="86" t="n">
+      <c r="AA37" s="86" t="n">
         <v>127965</v>
       </c>
-      <c r="AA37" s="86" t="n">
+      <c r="AB37" s="86" t="n">
         <v>129270</v>
       </c>
-      <c r="AB37" s="86" t="n">
+      <c r="AC37" s="86" t="n">
         <v>128809</v>
       </c>
-      <c r="AC37" s="86" t="n">
+      <c r="AD37" s="86" t="n">
         <v>122462</v>
       </c>
-      <c r="AD37" s="86" t="n">
+      <c r="AE37" s="86" t="n">
         <v>128844</v>
-      </c>
-      <c r="AE37" s="86" t="n">
-        <v>127468</v>
       </c>
     </row>
     <row r="38">
@@ -5147,94 +5147,94 @@
         </is>
       </c>
       <c r="B38" s="86" t="n">
+        <v>70900</v>
+      </c>
+      <c r="C38" s="86" t="n">
         <v>68886</v>
       </c>
-      <c r="C38" s="86" t="n">
+      <c r="D38" s="86" t="n">
         <v>64718</v>
       </c>
-      <c r="D38" s="86" t="n">
+      <c r="E38" s="86" t="n">
         <v>59845</v>
       </c>
-      <c r="E38" s="86" t="n">
+      <c r="F38" s="86" t="n">
         <v>57916</v>
       </c>
-      <c r="F38" s="86" t="n">
+      <c r="G38" s="86" t="n">
         <v>54008</v>
       </c>
-      <c r="G38" s="86" t="n">
+      <c r="H38" s="86" t="n">
         <v>52754</v>
       </c>
-      <c r="H38" s="86" t="n">
+      <c r="I38" s="86" t="n">
         <v>49457</v>
       </c>
-      <c r="I38" s="86" t="n">
+      <c r="J38" s="86" t="n">
         <v>49214</v>
       </c>
-      <c r="J38" s="86" t="n">
+      <c r="K38" s="86" t="n">
         <v>51881</v>
       </c>
-      <c r="K38" s="86" t="n">
+      <c r="L38" s="86" t="n">
         <v>48370</v>
       </c>
-      <c r="L38" s="86" t="n">
+      <c r="M38" s="86" t="n">
         <v>53900</v>
       </c>
-      <c r="M38" s="86" t="n">
+      <c r="N38" s="86" t="n">
         <v>59063</v>
       </c>
-      <c r="N38" s="86" t="n">
+      <c r="O38" s="86" t="n">
         <v>58132</v>
       </c>
-      <c r="O38" s="86" t="n">
+      <c r="P38" s="86" t="n">
         <v>57844</v>
       </c>
-      <c r="P38" s="86" t="n">
+      <c r="Q38" s="86" t="n">
         <v>51375</v>
       </c>
-      <c r="Q38" s="86" t="n">
+      <c r="R38" s="86" t="n">
         <v>50883</v>
       </c>
-      <c r="R38" s="86" t="n">
+      <c r="S38" s="86" t="n">
         <v>50688</v>
       </c>
-      <c r="S38" s="86" t="n">
+      <c r="T38" s="86" t="n">
         <v>50309</v>
       </c>
-      <c r="T38" s="86" t="n">
+      <c r="U38" s="86" t="n">
         <v>51034</v>
       </c>
-      <c r="U38" s="86" t="n">
+      <c r="V38" s="86" t="n">
         <v>50972</v>
       </c>
-      <c r="V38" s="86" t="n">
+      <c r="W38" s="86" t="n">
         <v>51615</v>
       </c>
-      <c r="W38" s="86" t="n">
+      <c r="X38" s="86" t="n">
         <v>51739</v>
       </c>
-      <c r="X38" s="86" t="n">
+      <c r="Y38" s="86" t="n">
         <v>51534</v>
       </c>
-      <c r="Y38" s="86" t="n">
+      <c r="Z38" s="86" t="n">
         <v>50630</v>
       </c>
-      <c r="Z38" s="86" t="n">
+      <c r="AA38" s="86" t="n">
         <v>51651</v>
       </c>
-      <c r="AA38" s="86" t="n">
+      <c r="AB38" s="86" t="n">
         <v>51493</v>
       </c>
-      <c r="AB38" s="86" t="n">
+      <c r="AC38" s="86" t="n">
         <v>52808</v>
       </c>
-      <c r="AC38" s="86" t="n">
+      <c r="AD38" s="86" t="n">
         <v>48360</v>
       </c>
-      <c r="AD38" s="86" t="n">
+      <c r="AE38" s="86" t="n">
         <v>51975</v>
-      </c>
-      <c r="AE38" s="86" t="n">
-        <v>52065</v>
       </c>
     </row>
     <row r="39">
@@ -5244,94 +5244,94 @@
         </is>
       </c>
       <c r="B39" s="86" t="n">
+        <v>11204</v>
+      </c>
+      <c r="C39" s="86" t="n">
         <v>11717</v>
       </c>
-      <c r="C39" s="86" t="n">
+      <c r="D39" s="86" t="n">
         <v>14251</v>
       </c>
-      <c r="D39" s="86" t="n">
+      <c r="E39" s="86" t="n">
         <v>15075</v>
       </c>
-      <c r="E39" s="86" t="n">
+      <c r="F39" s="86" t="n">
         <v>16231</v>
       </c>
-      <c r="F39" s="86" t="n">
+      <c r="G39" s="86" t="n">
         <v>13658</v>
       </c>
-      <c r="G39" s="86" t="n">
+      <c r="H39" s="86" t="n">
         <v>16239</v>
       </c>
-      <c r="H39" s="86" t="n">
+      <c r="I39" s="86" t="n">
         <v>13971</v>
       </c>
-      <c r="I39" s="86" t="n">
+      <c r="J39" s="86" t="n">
         <v>15254</v>
       </c>
-      <c r="J39" s="86" t="n">
+      <c r="K39" s="86" t="n">
         <v>13966</v>
       </c>
-      <c r="K39" s="86" t="n">
+      <c r="L39" s="86" t="n">
         <v>9839</v>
       </c>
-      <c r="L39" s="86" t="n">
+      <c r="M39" s="86" t="n">
         <v>16729</v>
       </c>
-      <c r="M39" s="86" t="n">
+      <c r="N39" s="86" t="n">
         <v>21354</v>
       </c>
-      <c r="N39" s="86" t="n">
+      <c r="O39" s="86" t="n">
         <v>24129</v>
       </c>
-      <c r="O39" s="86" t="n">
+      <c r="P39" s="86" t="n">
         <v>23841</v>
       </c>
-      <c r="P39" s="86" t="n">
+      <c r="Q39" s="86" t="n">
         <v>25383</v>
       </c>
-      <c r="Q39" s="86" t="n">
+      <c r="R39" s="86" t="n">
         <v>28150</v>
       </c>
-      <c r="R39" s="86" t="n">
+      <c r="S39" s="86" t="n">
         <v>29036</v>
       </c>
-      <c r="S39" s="86" t="n">
+      <c r="T39" s="86" t="n">
         <v>29878</v>
       </c>
-      <c r="T39" s="86" t="n">
+      <c r="U39" s="86" t="n">
         <v>31317</v>
       </c>
-      <c r="U39" s="86" t="n">
+      <c r="V39" s="86" t="n">
         <v>31225</v>
       </c>
-      <c r="V39" s="86" t="n">
+      <c r="W39" s="86" t="n">
         <v>32000</v>
       </c>
-      <c r="W39" s="86" t="n">
+      <c r="X39" s="86" t="n">
         <v>33502</v>
       </c>
-      <c r="X39" s="86" t="n">
+      <c r="Y39" s="86" t="n">
         <v>33944</v>
       </c>
-      <c r="Y39" s="86" t="n">
+      <c r="Z39" s="86" t="n">
         <v>34381</v>
       </c>
-      <c r="Z39" s="86" t="n">
+      <c r="AA39" s="86" t="n">
         <v>35985</v>
       </c>
-      <c r="AA39" s="86" t="n">
+      <c r="AB39" s="86" t="n">
         <v>35567</v>
       </c>
-      <c r="AB39" s="86" t="n">
+      <c r="AC39" s="86" t="n">
         <v>37588</v>
       </c>
-      <c r="AC39" s="86" t="n">
+      <c r="AD39" s="86" t="n">
         <v>35094</v>
       </c>
-      <c r="AD39" s="86" t="n">
+      <c r="AE39" s="86" t="n">
         <v>35849</v>
-      </c>
-      <c r="AE39" s="86" t="n">
-        <v>36254</v>
       </c>
     </row>
     <row r="41">
@@ -5344,7 +5344,7 @@
     <row r="42">
       <c r="A42" s="91" t="inlineStr">
         <is>
-          <t>今日卖报：市值交换率(p):4.34&gt;=3.564;获利比(加权):86.12%&gt;=0.823;主力拉高数:1172.0&gt;=213.0;新高数120d(avg):4676.0&gt;=1165.963;新高数60d:4449.0&gt;=661.0;新高数60d(zz500):415.0&gt;=71.0</t>
+          <t>今日卖报：市值交换率(p):3.98&gt;=3.564;主力拉高数:290.0&gt;=213.0</t>
         </is>
       </c>
     </row>

--- a/report_2410.xlsx
+++ b/report_2410.xlsx
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="B25" s="88" t="n">
-        <v>7.07</v>
+        <v>7.09</v>
       </c>
       <c r="C25" s="88" t="n">
         <v>7.07</v>
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="B26" s="89" t="n">
-        <v>-0.04</v>
+        <v>0.28</v>
       </c>
       <c r="C26" s="89" t="n">
         <v>0.9</v>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="B27" s="89" t="n">
-        <v>-0.64</v>
+        <v>-0.33</v>
       </c>
       <c r="C27" s="89" t="n">
         <v>-0.21</v>

--- a/report_2410.xlsx
+++ b/report_2410.xlsx
@@ -800,7 +800,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1033,7 +1033,6 @@
     <xf numFmtId="0" fontId="0" fillId="47" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -1439,152 +1438,152 @@
       </c>
       <c r="B1" s="77" t="inlineStr">
         <is>
+          <t>241010</t>
+        </is>
+      </c>
+      <c r="C1" s="77" t="inlineStr">
+        <is>
           <t>241009</t>
         </is>
       </c>
-      <c r="C1" s="77" t="inlineStr">
+      <c r="D1" s="77" t="inlineStr">
         <is>
           <t>241008</t>
         </is>
       </c>
-      <c r="D1" s="77" t="inlineStr">
+      <c r="E1" s="77" t="inlineStr">
         <is>
           <t>240930</t>
         </is>
       </c>
-      <c r="E1" s="77" t="inlineStr">
+      <c r="F1" s="77" t="inlineStr">
         <is>
           <t>240927</t>
         </is>
       </c>
-      <c r="F1" s="77" t="inlineStr">
+      <c r="G1" s="77" t="inlineStr">
         <is>
           <t>240926</t>
         </is>
       </c>
-      <c r="G1" s="77" t="inlineStr">
+      <c r="H1" s="77" t="inlineStr">
         <is>
           <t>240925</t>
         </is>
       </c>
-      <c r="H1" s="77" t="inlineStr">
+      <c r="I1" s="77" t="inlineStr">
         <is>
           <t>240924</t>
         </is>
       </c>
-      <c r="I1" s="77" t="inlineStr">
+      <c r="J1" s="77" t="inlineStr">
         <is>
           <t>240923</t>
         </is>
       </c>
-      <c r="J1" s="77" t="inlineStr">
+      <c r="K1" s="77" t="inlineStr">
         <is>
           <t>240920</t>
         </is>
       </c>
-      <c r="K1" s="77" t="inlineStr">
+      <c r="L1" s="77" t="inlineStr">
         <is>
           <t>240919</t>
         </is>
       </c>
-      <c r="L1" s="77" t="inlineStr">
+      <c r="M1" s="77" t="inlineStr">
         <is>
           <t>240918</t>
         </is>
       </c>
-      <c r="M1" s="77" t="inlineStr">
+      <c r="N1" s="77" t="inlineStr">
         <is>
           <t>240913</t>
         </is>
       </c>
-      <c r="N1" s="77" t="inlineStr">
+      <c r="O1" s="77" t="inlineStr">
         <is>
           <t>240912</t>
         </is>
       </c>
-      <c r="O1" s="77" t="inlineStr">
+      <c r="P1" s="77" t="inlineStr">
         <is>
           <t>240911</t>
         </is>
       </c>
-      <c r="P1" s="77" t="inlineStr">
+      <c r="Q1" s="77" t="inlineStr">
         <is>
           <t>240910</t>
         </is>
       </c>
-      <c r="Q1" s="77" t="inlineStr">
+      <c r="R1" s="77" t="inlineStr">
         <is>
           <t>240909</t>
         </is>
       </c>
-      <c r="R1" s="77" t="inlineStr">
+      <c r="S1" s="77" t="inlineStr">
         <is>
           <t>240906</t>
         </is>
       </c>
-      <c r="S1" s="77" t="inlineStr">
+      <c r="T1" s="77" t="inlineStr">
         <is>
           <t>240905</t>
         </is>
       </c>
-      <c r="T1" s="77" t="inlineStr">
+      <c r="U1" s="77" t="inlineStr">
         <is>
           <t>240904</t>
         </is>
       </c>
-      <c r="U1" s="77" t="inlineStr">
+      <c r="V1" s="77" t="inlineStr">
         <is>
           <t>240903</t>
         </is>
       </c>
-      <c r="V1" s="77" t="inlineStr">
+      <c r="W1" s="77" t="inlineStr">
         <is>
           <t>240902</t>
         </is>
       </c>
-      <c r="W1" s="77" t="inlineStr">
+      <c r="X1" s="77" t="inlineStr">
         <is>
           <t>240830</t>
         </is>
       </c>
-      <c r="X1" s="77" t="inlineStr">
+      <c r="Y1" s="77" t="inlineStr">
         <is>
           <t>240829</t>
         </is>
       </c>
-      <c r="Y1" s="77" t="inlineStr">
+      <c r="Z1" s="77" t="inlineStr">
         <is>
           <t>240828</t>
         </is>
       </c>
-      <c r="Z1" s="77" t="inlineStr">
+      <c r="AA1" s="77" t="inlineStr">
         <is>
           <t>240827</t>
         </is>
       </c>
-      <c r="AA1" s="77" t="inlineStr">
+      <c r="AB1" s="77" t="inlineStr">
         <is>
           <t>240826</t>
         </is>
       </c>
-      <c r="AB1" s="77" t="inlineStr">
+      <c r="AC1" s="77" t="inlineStr">
         <is>
           <t>240823</t>
         </is>
       </c>
-      <c r="AC1" s="77" t="inlineStr">
+      <c r="AD1" s="77" t="inlineStr">
         <is>
           <t>240822</t>
         </is>
       </c>
-      <c r="AD1" s="77" t="inlineStr">
+      <c r="AE1" s="77" t="inlineStr">
         <is>
           <t>240821</t>
-        </is>
-      </c>
-      <c r="AE1" s="77" t="inlineStr">
-        <is>
-          <t>240820</t>
         </is>
       </c>
     </row>
@@ -1595,94 +1594,94 @@
         </is>
       </c>
       <c r="B2" s="78" t="n">
+        <v>3301.93</v>
+      </c>
+      <c r="C2" s="78" t="n">
         <v>3258.86</v>
       </c>
-      <c r="C2" s="78" t="n">
+      <c r="D2" s="78" t="n">
         <v>3489.78</v>
       </c>
-      <c r="D2" s="78" t="n">
+      <c r="E2" s="78" t="n">
         <v>3336.5</v>
       </c>
-      <c r="E2" s="78" t="n">
+      <c r="F2" s="78" t="n">
         <v>3087.53</v>
       </c>
-      <c r="F2" s="78" t="n">
+      <c r="G2" s="78" t="n">
         <v>3000.95</v>
       </c>
-      <c r="G2" s="78" t="n">
+      <c r="H2" s="78" t="n">
         <v>2896.31</v>
       </c>
-      <c r="H2" s="78" t="n">
+      <c r="I2" s="78" t="n">
         <v>2863.13</v>
       </c>
-      <c r="I2" s="78" t="n">
+      <c r="J2" s="78" t="n">
         <v>2748.92</v>
       </c>
-      <c r="J2" s="78" t="n">
+      <c r="K2" s="78" t="n">
         <v>2736.81</v>
       </c>
-      <c r="K2" s="78" t="n">
+      <c r="L2" s="78" t="n">
         <v>2736.02</v>
       </c>
-      <c r="L2" s="78" t="n">
+      <c r="M2" s="78" t="n">
         <v>2717.28</v>
       </c>
-      <c r="M2" s="78" t="n">
+      <c r="N2" s="78" t="n">
         <v>2704.09</v>
       </c>
-      <c r="N2" s="78" t="n">
+      <c r="O2" s="78" t="n">
         <v>2717.12</v>
       </c>
-      <c r="O2" s="78" t="n">
+      <c r="P2" s="78" t="n">
         <v>2721.8</v>
       </c>
-      <c r="P2" s="78" t="n">
+      <c r="Q2" s="78" t="n">
         <v>2744.19</v>
       </c>
-      <c r="Q2" s="78" t="n">
+      <c r="R2" s="78" t="n">
         <v>2736.49</v>
       </c>
-      <c r="R2" s="78" t="n">
+      <c r="S2" s="78" t="n">
         <v>2765.81</v>
       </c>
-      <c r="S2" s="78" t="n">
+      <c r="T2" s="78" t="n">
         <v>2788.31</v>
       </c>
-      <c r="T2" s="78" t="n">
+      <c r="U2" s="78" t="n">
         <v>2784.28</v>
       </c>
-      <c r="U2" s="78" t="n">
+      <c r="V2" s="78" t="n">
         <v>2802.98</v>
       </c>
-      <c r="V2" s="78" t="n">
+      <c r="W2" s="78" t="n">
         <v>2811.03</v>
       </c>
-      <c r="W2" s="78" t="n">
+      <c r="X2" s="78" t="n">
         <v>2842.21</v>
       </c>
-      <c r="X2" s="78" t="n">
+      <c r="Y2" s="78" t="n">
         <v>2823.11</v>
       </c>
-      <c r="Y2" s="78" t="n">
+      <c r="Z2" s="78" t="n">
         <v>2837.43</v>
       </c>
-      <c r="Z2" s="78" t="n">
+      <c r="AA2" s="78" t="n">
         <v>2848.73</v>
       </c>
-      <c r="AA2" s="78" t="n">
+      <c r="AB2" s="78" t="n">
         <v>2855.52</v>
       </c>
-      <c r="AB2" s="78" t="n">
+      <c r="AC2" s="78" t="n">
         <v>2854.37</v>
       </c>
-      <c r="AC2" s="78" t="n">
+      <c r="AD2" s="78" t="n">
         <v>2848.77</v>
       </c>
-      <c r="AD2" s="78" t="n">
+      <c r="AE2" s="78" t="n">
         <v>2856.58</v>
-      </c>
-      <c r="AE2" s="78" t="n">
-        <v>2866.66</v>
       </c>
     </row>
     <row r="3">
@@ -1696,134 +1695,134 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="C3" s="80" t="inlineStr">
+      <c r="C3" s="79" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D3" s="80" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D3" s="80" t="inlineStr">
+      <c r="E3" s="80" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E3" s="80" t="inlineStr">
+      <c r="F3" s="80" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F3" s="80" t="inlineStr">
+      <c r="G3" s="80" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G3" s="80" t="inlineStr">
+      <c r="H3" s="80" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H3" s="80" t="inlineStr">
+      <c r="I3" s="80" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I3" s="79" t="inlineStr">
+      <c r="J3" s="79" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J3" s="79" t="inlineStr">
+      <c r="K3" s="79" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K3" s="79" t="inlineStr">
+      <c r="L3" s="79" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L3" s="79" t="inlineStr">
+      <c r="M3" s="79" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M3" s="81" t="inlineStr">
+      <c r="N3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N3" s="81" t="inlineStr">
+      <c r="O3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O3" s="81" t="inlineStr">
+      <c r="P3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P3" s="81" t="inlineStr">
+      <c r="Q3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q3" s="81" t="inlineStr">
+      <c r="R3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R3" s="81" t="inlineStr">
+      <c r="S3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S3" s="81" t="inlineStr">
+      <c r="T3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T3" s="81" t="inlineStr">
+      <c r="U3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U3" s="81" t="inlineStr">
+      <c r="V3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V3" s="81" t="inlineStr">
+      <c r="W3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W3" s="79" t="inlineStr">
+      <c r="X3" s="79" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X3" s="81" t="inlineStr">
+      <c r="Y3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y3" s="81" t="inlineStr">
+      <c r="Z3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z3" s="81" t="inlineStr">
+      <c r="AA3" s="81" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA3" s="79" t="inlineStr">
+      <c r="AB3" s="79" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AB3" s="81" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AC3" s="81" t="inlineStr">
@@ -1849,94 +1848,94 @@
         </is>
       </c>
       <c r="B4" s="78" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C4" s="78" t="n">
         <v>-6.62</v>
       </c>
-      <c r="C4" s="78" t="n">
+      <c r="D4" s="78" t="n">
         <v>4.59</v>
       </c>
-      <c r="D4" s="78" t="n">
+      <c r="E4" s="78" t="n">
         <v>8.06</v>
       </c>
-      <c r="E4" s="78" t="n">
+      <c r="F4" s="78" t="n">
         <v>2.89</v>
       </c>
-      <c r="F4" s="78" t="n">
+      <c r="G4" s="78" t="n">
         <v>3.61</v>
       </c>
-      <c r="G4" s="78" t="n">
+      <c r="H4" s="78" t="n">
         <v>1.16</v>
       </c>
-      <c r="H4" s="78" t="n">
+      <c r="I4" s="78" t="n">
         <v>4.15</v>
       </c>
-      <c r="I4" s="78" t="n">
+      <c r="J4" s="78" t="n">
         <v>0.44</v>
       </c>
-      <c r="J4" s="78" t="n">
+      <c r="K4" s="78" t="n">
         <v>0.03</v>
       </c>
-      <c r="K4" s="78" t="n">
+      <c r="L4" s="78" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="L4" s="78" t="n">
+      <c r="M4" s="78" t="n">
         <v>0.49</v>
       </c>
-      <c r="M4" s="78" t="n">
+      <c r="N4" s="78" t="n">
         <v>-0.48</v>
       </c>
-      <c r="N4" s="78" t="n">
+      <c r="O4" s="78" t="n">
         <v>-0.17</v>
       </c>
-      <c r="O4" s="78" t="n">
+      <c r="P4" s="78" t="n">
         <v>-0.82</v>
       </c>
-      <c r="P4" s="78" t="n">
+      <c r="Q4" s="78" t="n">
         <v>0.28</v>
       </c>
-      <c r="Q4" s="78" t="n">
+      <c r="R4" s="78" t="n">
         <v>-1.06</v>
       </c>
-      <c r="R4" s="78" t="n">
+      <c r="S4" s="78" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="S4" s="78" t="n">
+      <c r="T4" s="78" t="n">
         <v>0.14</v>
       </c>
-      <c r="T4" s="78" t="n">
+      <c r="U4" s="78" t="n">
         <v>-0.67</v>
       </c>
-      <c r="U4" s="78" t="n">
+      <c r="V4" s="78" t="n">
         <v>-0.29</v>
       </c>
-      <c r="V4" s="78" t="n">
+      <c r="W4" s="78" t="n">
         <v>-1.1</v>
       </c>
-      <c r="W4" s="78" t="n">
+      <c r="X4" s="78" t="n">
         <v>0.68</v>
       </c>
-      <c r="X4" s="78" t="n">
+      <c r="Y4" s="78" t="n">
         <v>-0.5</v>
       </c>
-      <c r="Y4" s="78" t="n">
+      <c r="Z4" s="78" t="n">
         <v>-0.4</v>
       </c>
-      <c r="Z4" s="78" t="n">
+      <c r="AA4" s="78" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AA4" s="78" t="n">
+      <c r="AB4" s="78" t="n">
         <v>0.04</v>
       </c>
-      <c r="AB4" s="78" t="n">
+      <c r="AC4" s="78" t="n">
         <v>0.2</v>
       </c>
-      <c r="AC4" s="78" t="n">
+      <c r="AD4" s="78" t="n">
         <v>-0.27</v>
       </c>
-      <c r="AD4" s="78" t="n">
+      <c r="AE4" s="78" t="n">
         <v>-0.35</v>
-      </c>
-      <c r="AE4" s="78" t="n">
-        <v>-0.93</v>
       </c>
     </row>
     <row r="5">
@@ -1946,94 +1945,94 @@
         </is>
       </c>
       <c r="B5" s="78" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="C5" s="78" t="n">
         <v>11.51</v>
       </c>
-      <c r="C5" s="78" t="n">
+      <c r="D5" s="78" t="n">
         <v>18.3</v>
       </c>
-      <c r="D5" s="78" t="n">
+      <c r="E5" s="78" t="n">
         <v>12.81</v>
       </c>
-      <c r="E5" s="78" t="n">
+      <c r="F5" s="78" t="n">
         <v>3.53</v>
       </c>
-      <c r="F5" s="78" t="n">
+      <c r="G5" s="78" t="n">
         <v>0.13</v>
       </c>
-      <c r="G5" s="78" t="n">
+      <c r="H5" s="78" t="n">
         <v>-3.29</v>
       </c>
-      <c r="H5" s="78" t="n">
+      <c r="I5" s="78" t="n">
         <v>-3.51</v>
       </c>
-      <c r="I5" s="78" t="n">
+      <c r="J5" s="78" t="n">
         <v>-6.68</v>
       </c>
-      <c r="J5" s="78" t="n">
+      <c r="K5" s="78" t="n">
         <v>-7.93</v>
       </c>
-      <c r="K5" s="78" t="n">
+      <c r="L5" s="78" t="n">
         <v>-7.25</v>
       </c>
-      <c r="L5" s="78" t="n">
+      <c r="M5" s="78" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="M5" s="78" t="n">
+      <c r="N5" s="78" t="n">
         <v>-9.81</v>
       </c>
-      <c r="N5" s="78" t="n">
+      <c r="O5" s="78" t="n">
         <v>-9.59</v>
       </c>
-      <c r="O5" s="78" t="n">
+      <c r="P5" s="78" t="n">
         <v>-9.82</v>
       </c>
-      <c r="P5" s="78" t="n">
+      <c r="Q5" s="78" t="n">
         <v>-9.44</v>
       </c>
-      <c r="Q5" s="78" t="n">
+      <c r="R5" s="78" t="n">
         <v>-9.26</v>
       </c>
-      <c r="R5" s="78" t="n">
+      <c r="S5" s="78" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="S5" s="78" t="n">
+      <c r="T5" s="78" t="n">
         <v>-7.94</v>
       </c>
-      <c r="T5" s="78" t="n">
+      <c r="U5" s="78" t="n">
         <v>-8.34</v>
       </c>
-      <c r="U5" s="78" t="n">
+      <c r="V5" s="78" t="n">
         <v>-7.43</v>
       </c>
-      <c r="V5" s="78" t="n">
+      <c r="W5" s="78" t="n">
         <v>-7.87</v>
       </c>
-      <c r="W5" s="78" t="n">
+      <c r="X5" s="78" t="n">
         <v>-6.78</v>
       </c>
-      <c r="X5" s="78" t="n">
+      <c r="Y5" s="78" t="n">
         <v>-7.9</v>
       </c>
-      <c r="Y5" s="78" t="n">
+      <c r="Z5" s="78" t="n">
         <v>-8.210000000000001</v>
       </c>
-      <c r="Z5" s="78" t="n">
+      <c r="AA5" s="78" t="n">
         <v>-7.46</v>
       </c>
-      <c r="AA5" s="78" t="n">
+      <c r="AB5" s="78" t="n">
         <v>-7.49</v>
       </c>
-      <c r="AB5" s="78" t="n">
+      <c r="AC5" s="78" t="n">
         <v>-7.68</v>
       </c>
-      <c r="AC5" s="78" t="n">
+      <c r="AD5" s="78" t="n">
         <v>-8.43</v>
       </c>
-      <c r="AD5" s="78" t="n">
+      <c r="AE5" s="78" t="n">
         <v>-8.140000000000001</v>
-      </c>
-      <c r="AE5" s="78" t="n">
-        <v>-8.24</v>
       </c>
     </row>
     <row r="6">
@@ -2043,191 +2042,191 @@
         </is>
       </c>
       <c r="B6" s="78" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="C6" s="78" t="n">
         <v>6.9</v>
       </c>
-      <c r="C6" s="78" t="n">
+      <c r="D6" s="78" t="n">
         <v>14.53</v>
       </c>
-      <c r="D6" s="78" t="n">
+      <c r="E6" s="78" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="E6" s="78" t="n">
+      <c r="F6" s="78" t="n">
         <v>0.41</v>
       </c>
-      <c r="F6" s="78" t="n">
+      <c r="G6" s="78" t="n">
         <v>-2.48</v>
       </c>
-      <c r="G6" s="78" t="n">
+      <c r="H6" s="78" t="n">
         <v>-4.76</v>
       </c>
-      <c r="H6" s="78" t="n">
+      <c r="I6" s="78" t="n">
         <v>-4.9</v>
       </c>
-      <c r="I6" s="78" t="n">
+      <c r="J6" s="78" t="n">
         <v>-8.16</v>
       </c>
-      <c r="J6" s="78" t="n">
+      <c r="K6" s="78" t="n">
         <v>-9.720000000000001</v>
       </c>
-      <c r="K6" s="78" t="n">
+      <c r="L6" s="78" t="n">
         <v>-9.59</v>
       </c>
-      <c r="L6" s="78" t="n">
+      <c r="M6" s="78" t="n">
         <v>-10.85</v>
       </c>
-      <c r="M6" s="78" t="n">
+      <c r="N6" s="78" t="n">
         <v>-12.12</v>
       </c>
-      <c r="N6" s="78" t="n">
+      <c r="O6" s="78" t="n">
         <v>-11.77</v>
       </c>
-      <c r="O6" s="78" t="n">
+      <c r="P6" s="78" t="n">
         <v>-11.13</v>
       </c>
-      <c r="P6" s="78" t="n">
+      <c r="Q6" s="78" t="n">
         <v>-11.05</v>
       </c>
-      <c r="Q6" s="78" t="n">
+      <c r="R6" s="78" t="n">
         <v>-10.42</v>
       </c>
-      <c r="R6" s="78" t="n">
+      <c r="S6" s="78" t="n">
         <v>-8.970000000000001</v>
       </c>
-      <c r="S6" s="78" t="n">
+      <c r="T6" s="78" t="n">
         <v>-8.390000000000001</v>
       </c>
-      <c r="T6" s="78" t="n">
+      <c r="U6" s="78" t="n">
         <v>-8.890000000000001</v>
       </c>
-      <c r="U6" s="78" t="n">
+      <c r="V6" s="78" t="n">
         <v>-8.65</v>
       </c>
-      <c r="V6" s="78" t="n">
+      <c r="W6" s="78" t="n">
         <v>-7.71</v>
       </c>
-      <c r="W6" s="78" t="n">
+      <c r="X6" s="78" t="n">
         <v>-6.12</v>
       </c>
-      <c r="X6" s="78" t="n">
+      <c r="Y6" s="78" t="n">
         <v>-7.13</v>
       </c>
-      <c r="Y6" s="78" t="n">
+      <c r="Z6" s="78" t="n">
         <v>-6.9</v>
       </c>
-      <c r="Z6" s="78" t="n">
+      <c r="AA6" s="78" t="n">
         <v>-6.27</v>
       </c>
-      <c r="AA6" s="78" t="n">
+      <c r="AB6" s="78" t="n">
         <v>-5.67</v>
       </c>
-      <c r="AB6" s="78" t="n">
+      <c r="AC6" s="78" t="n">
         <v>-5.33</v>
       </c>
-      <c r="AC6" s="78" t="n">
+      <c r="AD6" s="78" t="n">
         <v>-3.69</v>
       </c>
-      <c r="AD6" s="78" t="n">
+      <c r="AE6" s="78" t="n">
         <v>-5.27</v>
       </c>
-      <c r="AE6" s="78" t="n">
-        <v>-3.71</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="82" t="inlineStr">
+      <c r="A7" s="76" t="inlineStr">
         <is>
           <t>市值交换率(p)</t>
         </is>
       </c>
       <c r="B7" s="78" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C7" s="78" t="n">
         <v>3.98</v>
       </c>
-      <c r="C7" s="78" t="n">
+      <c r="D7" s="78" t="n">
         <v>4.34</v>
       </c>
-      <c r="D7" s="78" t="n">
+      <c r="E7" s="78" t="n">
         <v>3.45</v>
       </c>
-      <c r="E7" s="78" t="n">
+      <c r="F7" s="78" t="n">
         <v>2.09</v>
       </c>
-      <c r="F7" s="78" t="n">
+      <c r="G7" s="78" t="n">
         <v>1.75</v>
       </c>
-      <c r="G7" s="78" t="n">
+      <c r="H7" s="78" t="n">
         <v>1.81</v>
       </c>
-      <c r="H7" s="78" t="n">
+      <c r="I7" s="78" t="n">
         <v>1.53</v>
       </c>
-      <c r="I7" s="78" t="n">
+      <c r="J7" s="78" t="n">
         <v>0.91</v>
       </c>
-      <c r="J7" s="78" t="n">
+      <c r="K7" s="78" t="n">
         <v>0.95</v>
       </c>
-      <c r="K7" s="78" t="n">
-        <v>1.03</v>
-      </c>
       <c r="L7" s="78" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="M7" s="78" t="n">
         <v>0.8</v>
       </c>
-      <c r="M7" s="78" t="n">
+      <c r="N7" s="78" t="n">
         <v>0.88</v>
       </c>
-      <c r="N7" s="78" t="n">
+      <c r="O7" s="78" t="n">
         <v>0.86</v>
       </c>
-      <c r="O7" s="78" t="n">
+      <c r="P7" s="78" t="n">
         <v>0.83</v>
       </c>
-      <c r="P7" s="78" t="n">
+      <c r="Q7" s="78" t="n">
         <v>0.87</v>
       </c>
-      <c r="Q7" s="78" t="n">
+      <c r="R7" s="78" t="n">
         <v>0.86</v>
       </c>
-      <c r="R7" s="78" t="n">
+      <c r="S7" s="78" t="n">
         <v>0.89</v>
       </c>
-      <c r="S7" s="78" t="n">
+      <c r="T7" s="78" t="n">
         <v>0.87</v>
       </c>
-      <c r="T7" s="78" t="n">
+      <c r="U7" s="78" t="n">
         <v>0.91</v>
       </c>
-      <c r="U7" s="78" t="n">
+      <c r="V7" s="78" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="V7" s="78" t="n">
+      <c r="W7" s="78" t="n">
         <v>1.14</v>
       </c>
-      <c r="W7" s="78" t="n">
+      <c r="X7" s="78" t="n">
         <v>1.4</v>
       </c>
-      <c r="X7" s="78" t="n">
+      <c r="Y7" s="78" t="n">
         <v>0.98</v>
       </c>
-      <c r="Y7" s="78" t="n">
+      <c r="Z7" s="78" t="n">
         <v>0.8</v>
       </c>
-      <c r="Z7" s="78" t="n">
+      <c r="AA7" s="78" t="n">
         <v>0.82</v>
       </c>
-      <c r="AA7" s="78" t="n">
+      <c r="AB7" s="78" t="n">
         <v>0.84</v>
       </c>
-      <c r="AB7" s="78" t="n">
+      <c r="AC7" s="78" t="n">
         <v>0.82</v>
       </c>
-      <c r="AC7" s="78" t="n">
+      <c r="AD7" s="78" t="n">
         <v>0.88</v>
       </c>
-      <c r="AD7" s="78" t="n">
+      <c r="AE7" s="78" t="n">
         <v>0.8100000000000001</v>
-      </c>
-      <c r="AE7" s="78" t="n">
-        <v>0.89</v>
       </c>
     </row>
     <row r="8">
@@ -2237,94 +2236,94 @@
         </is>
       </c>
       <c r="B8" s="78" t="n">
+        <v>21429.89</v>
+      </c>
+      <c r="C8" s="78" t="n">
         <v>29398.22</v>
       </c>
-      <c r="C8" s="78" t="n">
+      <c r="D8" s="78" t="n">
         <v>34519.39</v>
       </c>
-      <c r="D8" s="78" t="n">
+      <c r="E8" s="78" t="n">
         <v>25930.37</v>
       </c>
-      <c r="E8" s="78" t="n">
+      <c r="F8" s="78" t="n">
         <v>14460.05</v>
       </c>
-      <c r="F8" s="78" t="n">
+      <c r="G8" s="78" t="n">
         <v>11624.35</v>
       </c>
-      <c r="G8" s="78" t="n">
+      <c r="H8" s="78" t="n">
         <v>11573.71</v>
       </c>
-      <c r="H8" s="78" t="n">
+      <c r="I8" s="78" t="n">
         <v>9713.43</v>
       </c>
-      <c r="I8" s="78" t="n">
+      <c r="J8" s="78" t="n">
         <v>5510.02</v>
       </c>
-      <c r="J8" s="78" t="n">
+      <c r="K8" s="78" t="n">
         <v>5747.48</v>
       </c>
-      <c r="K8" s="78" t="n">
+      <c r="L8" s="78" t="n">
         <v>6270.01</v>
       </c>
-      <c r="L8" s="78" t="n">
+      <c r="M8" s="78" t="n">
         <v>4793.28</v>
       </c>
-      <c r="M8" s="78" t="n">
+      <c r="N8" s="78" t="n">
         <v>5247.59</v>
       </c>
-      <c r="N8" s="78" t="n">
+      <c r="O8" s="78" t="n">
         <v>5155.67</v>
       </c>
-      <c r="O8" s="78" t="n">
+      <c r="P8" s="78" t="n">
         <v>4995.56</v>
       </c>
-      <c r="P8" s="78" t="n">
+      <c r="Q8" s="78" t="n">
         <v>5276.48</v>
       </c>
-      <c r="Q8" s="78" t="n">
+      <c r="R8" s="78" t="n">
         <v>5186.37</v>
       </c>
-      <c r="R8" s="78" t="n">
+      <c r="S8" s="78" t="n">
         <v>5426.32</v>
       </c>
-      <c r="S8" s="78" t="n">
+      <c r="T8" s="78" t="n">
         <v>5348.38</v>
       </c>
-      <c r="T8" s="78" t="n">
+      <c r="U8" s="78" t="n">
         <v>5593.8</v>
       </c>
-      <c r="U8" s="78" t="n">
+      <c r="V8" s="78" t="n">
         <v>5806.01</v>
       </c>
-      <c r="V8" s="78" t="n">
+      <c r="W8" s="78" t="n">
         <v>7057.33</v>
       </c>
-      <c r="W8" s="78" t="n">
+      <c r="X8" s="78" t="n">
         <v>8765.889999999999</v>
       </c>
-      <c r="X8" s="78" t="n">
+      <c r="Y8" s="78" t="n">
         <v>6072.48</v>
       </c>
-      <c r="Y8" s="78" t="n">
+      <c r="Z8" s="78" t="n">
         <v>4966.07</v>
       </c>
-      <c r="Z8" s="78" t="n">
+      <c r="AA8" s="78" t="n">
         <v>5114.57</v>
       </c>
-      <c r="AA8" s="78" t="n">
+      <c r="AB8" s="78" t="n">
         <v>5265.26</v>
       </c>
-      <c r="AB8" s="78" t="n">
+      <c r="AC8" s="78" t="n">
         <v>5102.25</v>
       </c>
-      <c r="AC8" s="78" t="n">
+      <c r="AD8" s="78" t="n">
         <v>5491.53</v>
       </c>
-      <c r="AD8" s="78" t="n">
+      <c r="AE8" s="78" t="n">
         <v>5095.55</v>
-      </c>
-      <c r="AE8" s="78" t="n">
-        <v>5577.82</v>
       </c>
     </row>
     <row r="9">
@@ -2333,95 +2332,95 @@
           <t>获利比(加权)</t>
         </is>
       </c>
-      <c r="B9" s="83" t="n">
-        <v>0.6112</v>
-      </c>
-      <c r="C9" s="83" t="n">
+      <c r="B9" s="82" t="n">
+        <v>0.6454</v>
+      </c>
+      <c r="C9" s="82" t="n">
+        <v>0.6107</v>
+      </c>
+      <c r="D9" s="82" t="n">
         <v>0.8611</v>
       </c>
-      <c r="D9" s="83" t="n">
-        <v>0.8764999999999999</v>
-      </c>
-      <c r="E9" s="83" t="n">
-        <v>0.7141</v>
-      </c>
-      <c r="F9" s="83" t="n">
-        <v>0.6276</v>
-      </c>
-      <c r="G9" s="83" t="n">
-        <v>0.517</v>
-      </c>
-      <c r="H9" s="83" t="n">
-        <v>0.4914</v>
-      </c>
-      <c r="I9" s="83" t="n">
+      <c r="E9" s="82" t="n">
+        <v>0.8767</v>
+      </c>
+      <c r="F9" s="82" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="G9" s="82" t="n">
+        <v>0.6279</v>
+      </c>
+      <c r="H9" s="82" t="n">
+        <v>0.5172</v>
+      </c>
+      <c r="I9" s="82" t="n">
+        <v>0.4918</v>
+      </c>
+      <c r="J9" s="82" t="n">
         <v>0.37</v>
       </c>
-      <c r="J9" s="83" t="n">
-        <v>0.3495</v>
-      </c>
-      <c r="K9" s="83" t="n">
-        <v>0.3442</v>
-      </c>
-      <c r="L9" s="83" t="n">
-        <v>0.3158</v>
-      </c>
-      <c r="M9" s="83" t="n">
-        <v>0.2886</v>
-      </c>
-      <c r="N9" s="83" t="n">
-        <v>0.302</v>
-      </c>
-      <c r="O9" s="83" t="n">
-        <v>0.3038</v>
-      </c>
-      <c r="P9" s="83" t="n">
-        <v>0.3231</v>
-      </c>
-      <c r="Q9" s="83" t="n">
-        <v>0.3076</v>
-      </c>
-      <c r="R9" s="83" t="n">
-        <v>0.3336</v>
-      </c>
-      <c r="S9" s="83" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="T9" s="83" t="n">
+      <c r="K9" s="82" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="L9" s="82" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="M9" s="82" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="N9" s="82" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="O9" s="82" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="P9" s="82" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="Q9" s="82" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="R9" s="82" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="S9" s="82" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="T9" s="82" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="U9" s="82" t="n">
         <v>0.3566</v>
       </c>
-      <c r="U9" s="83" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="V9" s="83" t="n">
-        <v>0.3752</v>
-      </c>
-      <c r="W9" s="83" t="n">
-        <v>0.4089</v>
-      </c>
-      <c r="X9" s="83" t="n">
-        <v>0.3801</v>
-      </c>
-      <c r="Y9" s="83" t="n">
-        <v>0.3856</v>
-      </c>
-      <c r="Z9" s="83" t="n">
-        <v>0.3894</v>
-      </c>
-      <c r="AA9" s="83" t="n">
-        <v>0.4024</v>
-      </c>
-      <c r="AB9" s="83" t="n">
-        <v>0.3989</v>
-      </c>
-      <c r="AC9" s="83" t="n">
+      <c r="V9" s="82" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="W9" s="82" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="X9" s="82" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="Y9" s="82" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="Z9" s="82" t="n">
         <v>0.386</v>
       </c>
-      <c r="AD9" s="83" t="n">
-        <v>0.3912</v>
-      </c>
-      <c r="AE9" s="83" t="n">
-        <v>0.3979</v>
+      <c r="AA9" s="82" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="AB9" s="82" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="AC9" s="82" t="n">
+        <v>0.3992</v>
+      </c>
+      <c r="AD9" s="82" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="AE9" s="82" t="n">
+        <v>0.3916</v>
       </c>
     </row>
     <row r="10">
@@ -2430,192 +2429,192 @@
           <t>获利比(sh)</t>
         </is>
       </c>
-      <c r="B10" s="83" t="n">
+      <c r="B10" s="82" t="n">
+        <v>0.545983</v>
+      </c>
+      <c r="C10" s="82" t="n">
         <v>0.439026</v>
       </c>
-      <c r="C10" s="83" t="n">
+      <c r="D10" s="82" t="n">
         <v>0.834885</v>
       </c>
-      <c r="D10" s="83" t="n">
+      <c r="E10" s="82" t="n">
         <v>0.995366</v>
       </c>
-      <c r="E10" s="83" t="n">
+      <c r="F10" s="82" t="n">
         <v>0.881059</v>
       </c>
-      <c r="F10" s="83" t="n">
+      <c r="G10" s="82" t="n">
         <v>0.668977</v>
       </c>
-      <c r="G10" s="83" t="n">
+      <c r="H10" s="82" t="n">
         <v>0.377668</v>
       </c>
-      <c r="H10" s="83" t="n">
+      <c r="I10" s="82" t="n">
         <v>0.290923</v>
       </c>
-      <c r="I10" s="83" t="n">
+      <c r="J10" s="82" t="n">
         <v>0.078874</v>
       </c>
-      <c r="J10" s="83" t="n">
+      <c r="K10" s="82" t="n">
         <v>0.06608</v>
       </c>
-      <c r="K10" s="83" t="n">
+      <c r="L10" s="82" t="n">
         <v>0.057833</v>
       </c>
-      <c r="L10" s="83" t="n">
+      <c r="M10" s="82" t="n">
         <v>0.017712</v>
       </c>
-      <c r="M10" s="83" t="n">
+      <c r="N10" s="82" t="n">
         <v>0.000532</v>
       </c>
-      <c r="N10" s="83" t="n">
+      <c r="O10" s="82" t="n">
         <v>0.003474</v>
       </c>
-      <c r="O10" s="83" t="n">
+      <c r="P10" s="82" t="n">
         <v>0.006562</v>
       </c>
-      <c r="P10" s="83" t="n">
+      <c r="Q10" s="82" t="n">
         <v>0.015835</v>
       </c>
-      <c r="Q10" s="83" t="n">
+      <c r="R10" s="82" t="n">
         <v>0.004763</v>
       </c>
-      <c r="R10" s="83" t="n">
+      <c r="S10" s="82" t="n">
         <v>0.000513</v>
       </c>
-      <c r="S10" s="83" t="n">
+      <c r="T10" s="82" t="n">
         <v>0.006747</v>
       </c>
-      <c r="T10" s="83" t="n">
+      <c r="U10" s="82" t="n">
         <v>0.001473</v>
       </c>
-      <c r="U10" s="83" t="n">
+      <c r="V10" s="82" t="n">
         <v>0.004212</v>
       </c>
-      <c r="V10" s="83" t="n">
+      <c r="W10" s="82" t="n">
         <v>0.0008899999999999999</v>
       </c>
-      <c r="W10" s="83" t="n">
+      <c r="X10" s="82" t="n">
         <v>0.034869</v>
       </c>
-      <c r="X10" s="83" t="n">
+      <c r="Y10" s="82" t="n">
         <v>0.003664</v>
       </c>
-      <c r="Y10" s="83" t="n">
+      <c r="Z10" s="82" t="n">
         <v>0.002424</v>
       </c>
-      <c r="Z10" s="83" t="n">
+      <c r="AA10" s="82" t="n">
         <v>0.017205</v>
       </c>
-      <c r="AA10" s="83" t="n">
+      <c r="AB10" s="82" t="n">
         <v>0.036324</v>
       </c>
-      <c r="AB10" s="83" t="n">
+      <c r="AC10" s="82" t="n">
         <v>0.029327</v>
       </c>
-      <c r="AC10" s="83" t="n">
+      <c r="AD10" s="82" t="n">
         <v>0.010431</v>
       </c>
-      <c r="AD10" s="83" t="n">
+      <c r="AE10" s="82" t="n">
         <v>0.027288</v>
       </c>
-      <c r="AE10" s="83" t="n">
-        <v>0.053794</v>
-      </c>
     </row>
     <row r="11" ht="19" customFormat="1" customHeight="1" s="31">
-      <c r="A11" s="84" t="inlineStr">
+      <c r="A11" s="83" t="inlineStr">
         <is>
           <t>顶底获利差(加权)</t>
         </is>
       </c>
-      <c r="B11" s="85" t="n">
-        <v>0.0184</v>
-      </c>
-      <c r="C11" s="85" t="n">
-        <v>-0.04580000000000004</v>
-      </c>
-      <c r="D11" s="85" t="n">
-        <v>-0.0295</v>
-      </c>
-      <c r="E11" s="85" t="n">
-        <v>-0.0413</v>
-      </c>
-      <c r="F11" s="85" t="n">
-        <v>-0.03179999999999997</v>
-      </c>
-      <c r="G11" s="85" t="n">
-        <v>-0.02789999999999998</v>
-      </c>
-      <c r="H11" s="85" t="n">
-        <v>-0.02280000000000001</v>
-      </c>
-      <c r="I11" s="85" t="n">
-        <v>-0.01820000000000002</v>
-      </c>
-      <c r="J11" s="85" t="n">
-        <v>-0.01699999999999999</v>
-      </c>
-      <c r="K11" s="85" t="n">
-        <v>-0.01799999999999999</v>
-      </c>
-      <c r="L11" s="85" t="n">
-        <v>-0.01619999999999999</v>
-      </c>
-      <c r="M11" s="85" t="n">
-        <v>-0.0237</v>
-      </c>
-      <c r="N11" s="85" t="n">
-        <v>-0.03259999999999999</v>
-      </c>
-      <c r="O11" s="85" t="n">
-        <v>-0.03309999999999999</v>
-      </c>
-      <c r="P11" s="85" t="n">
-        <v>-0.03230000000000002</v>
-      </c>
-      <c r="Q11" s="85" t="n">
-        <v>-0.03439999999999999</v>
-      </c>
-      <c r="R11" s="85" t="n">
-        <v>-0.03160000000000002</v>
-      </c>
-      <c r="S11" s="85" t="n">
-        <v>-0.04029999999999997</v>
-      </c>
-      <c r="T11" s="85" t="n">
-        <v>-0.03620000000000001</v>
-      </c>
-      <c r="U11" s="85" t="n">
-        <v>-0.03569999999999998</v>
-      </c>
-      <c r="V11" s="85" t="n">
-        <v>-0.03379999999999997</v>
-      </c>
-      <c r="W11" s="85" t="n">
-        <v>-0.03430000000000002</v>
-      </c>
-      <c r="X11" s="85" t="n">
-        <v>-0.03420000000000001</v>
-      </c>
-      <c r="Y11" s="85" t="n">
-        <v>-0.03560000000000002</v>
-      </c>
-      <c r="Z11" s="85" t="n">
-        <v>-0.03490000000000001</v>
-      </c>
-      <c r="AA11" s="85" t="n">
-        <v>-0.03160000000000002</v>
-      </c>
-      <c r="AB11" s="85" t="n">
-        <v>-0.03200000000000003</v>
-      </c>
-      <c r="AC11" s="85" t="n">
-        <v>-0.03209999999999999</v>
-      </c>
-      <c r="AD11" s="85" t="n">
-        <v>-0.03489999999999999</v>
-      </c>
-      <c r="AE11" s="85" t="n">
-        <v>-0.0348</v>
+      <c r="B11" s="84" t="n">
+        <v>0.04390000000000002</v>
+      </c>
+      <c r="C11" s="84" t="n">
+        <v>0.01980000000000001</v>
+      </c>
+      <c r="D11" s="84" t="n">
+        <v>-0.04449999999999998</v>
+      </c>
+      <c r="E11" s="84" t="n">
+        <v>-0.02860000000000001</v>
+      </c>
+      <c r="F11" s="84" t="n">
+        <v>-0.04049999999999998</v>
+      </c>
+      <c r="G11" s="84" t="n">
+        <v>-0.03050000000000003</v>
+      </c>
+      <c r="H11" s="84" t="n">
+        <v>-0.0265</v>
+      </c>
+      <c r="I11" s="84" t="n">
+        <v>-0.02129999999999999</v>
+      </c>
+      <c r="J11" s="84" t="n">
+        <v>-0.01669999999999999</v>
+      </c>
+      <c r="K11" s="84" t="n">
+        <v>-0.01549999999999999</v>
+      </c>
+      <c r="L11" s="84" t="n">
+        <v>-0.0166</v>
+      </c>
+      <c r="M11" s="84" t="n">
+        <v>-0.01480000000000001</v>
+      </c>
+      <c r="N11" s="84" t="n">
+        <v>-0.02229999999999999</v>
+      </c>
+      <c r="O11" s="84" t="n">
+        <v>-0.03109999999999999</v>
+      </c>
+      <c r="P11" s="84" t="n">
+        <v>-0.03159999999999999</v>
+      </c>
+      <c r="Q11" s="84" t="n">
+        <v>-0.03079999999999999</v>
+      </c>
+      <c r="R11" s="84" t="n">
+        <v>-0.03300000000000003</v>
+      </c>
+      <c r="S11" s="84" t="n">
+        <v>-0.03029999999999999</v>
+      </c>
+      <c r="T11" s="84" t="n">
+        <v>-0.03850000000000001</v>
+      </c>
+      <c r="U11" s="84" t="n">
+        <v>-0.03459999999999999</v>
+      </c>
+      <c r="V11" s="84" t="n">
+        <v>-0.03410000000000002</v>
+      </c>
+      <c r="W11" s="84" t="n">
+        <v>-0.03220000000000001</v>
+      </c>
+      <c r="X11" s="84" t="n">
+        <v>-0.0328</v>
+      </c>
+      <c r="Y11" s="84" t="n">
+        <v>-0.03269999999999998</v>
+      </c>
+      <c r="Z11" s="84" t="n">
+        <v>-0.03409999999999999</v>
+      </c>
+      <c r="AA11" s="84" t="n">
+        <v>-0.03339999999999999</v>
+      </c>
+      <c r="AB11" s="84" t="n">
+        <v>-0.03010000000000002</v>
+      </c>
+      <c r="AC11" s="84" t="n">
+        <v>-0.03040000000000001</v>
+      </c>
+      <c r="AD11" s="84" t="n">
+        <v>-0.03049999999999997</v>
+      </c>
+      <c r="AE11" s="84" t="n">
+        <v>-0.033</v>
       </c>
     </row>
     <row r="12">
@@ -2625,94 +2624,94 @@
         </is>
       </c>
       <c r="B12" s="78" t="n">
+        <v>43.63</v>
+      </c>
+      <c r="C12" s="78" t="n">
         <v>46.75</v>
       </c>
-      <c r="C12" s="78" t="n">
+      <c r="D12" s="78" t="n">
         <v>49.53</v>
       </c>
-      <c r="D12" s="78" t="n">
+      <c r="E12" s="78" t="n">
         <v>56.35</v>
       </c>
-      <c r="E12" s="78" t="n">
+      <c r="F12" s="78" t="n">
         <v>66.34</v>
       </c>
-      <c r="F12" s="78" t="n">
+      <c r="G12" s="78" t="n">
         <v>77.88</v>
       </c>
-      <c r="G12" s="78" t="n">
+      <c r="H12" s="78" t="n">
         <v>88.77</v>
       </c>
-      <c r="H12" s="78" t="n">
+      <c r="I12" s="78" t="n">
         <v>96.05</v>
       </c>
-      <c r="I12" s="78" t="n">
+      <c r="J12" s="78" t="n">
         <v>102.11</v>
       </c>
-      <c r="J12" s="78" t="n">
+      <c r="K12" s="78" t="n">
         <v>103.88</v>
       </c>
-      <c r="K12" s="78" t="n">
+      <c r="L12" s="78" t="n">
         <v>105.24</v>
       </c>
-      <c r="L12" s="78" t="n">
+      <c r="M12" s="78" t="n">
         <v>106.67</v>
       </c>
-      <c r="M12" s="78" t="n">
+      <c r="N12" s="78" t="n">
         <v>107.48</v>
       </c>
-      <c r="N12" s="78" t="n">
+      <c r="O12" s="78" t="n">
         <v>107.3</v>
       </c>
-      <c r="O12" s="78" t="n">
+      <c r="P12" s="78" t="n">
         <v>107.29</v>
       </c>
-      <c r="P12" s="78" t="n">
+      <c r="Q12" s="78" t="n">
         <v>107.42</v>
       </c>
-      <c r="Q12" s="78" t="n">
+      <c r="R12" s="78" t="n">
         <v>108.09</v>
       </c>
-      <c r="R12" s="78" t="n">
+      <c r="S12" s="78" t="n">
         <v>108.17</v>
       </c>
-      <c r="S12" s="78" t="n">
+      <c r="T12" s="78" t="n">
         <v>107.87</v>
       </c>
-      <c r="T12" s="78" t="n">
+      <c r="U12" s="78" t="n">
         <v>107.94</v>
       </c>
-      <c r="U12" s="78" t="n">
+      <c r="V12" s="78" t="n">
         <v>107.63</v>
       </c>
-      <c r="V12" s="78" t="n">
+      <c r="W12" s="78" t="n">
         <v>107.48</v>
       </c>
-      <c r="W12" s="78" t="n">
+      <c r="X12" s="78" t="n">
         <v>106.97</v>
       </c>
-      <c r="X12" s="78" t="n">
+      <c r="Y12" s="78" t="n">
         <v>107.52</v>
       </c>
-      <c r="Y12" s="78" t="n">
+      <c r="Z12" s="78" t="n">
         <v>107.24</v>
       </c>
-      <c r="Z12" s="78" t="n">
+      <c r="AA12" s="78" t="n">
         <v>106.85</v>
       </c>
-      <c r="AA12" s="78" t="n">
+      <c r="AB12" s="78" t="n">
         <v>106.52</v>
       </c>
-      <c r="AB12" s="78" t="n">
+      <c r="AC12" s="78" t="n">
         <v>106.44</v>
       </c>
-      <c r="AC12" s="78" t="n">
+      <c r="AD12" s="78" t="n">
         <v>106.24</v>
       </c>
-      <c r="AD12" s="78" t="n">
+      <c r="AE12" s="78" t="n">
         <v>105.72</v>
-      </c>
-      <c r="AE12" s="78" t="n">
-        <v>105.46</v>
       </c>
     </row>
     <row r="13">
@@ -2721,95 +2720,95 @@
           <t>下影线数</t>
         </is>
       </c>
-      <c r="B13" s="86" t="n">
+      <c r="B13" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="86" t="n">
+      <c r="C13" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="86" t="n">
+      <c r="D13" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="86" t="n">
+      <c r="E13" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="86" t="n">
+      <c r="F13" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="85" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="86" t="n">
+      <c r="H13" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="86" t="n">
-        <v>36</v>
-      </c>
-      <c r="I13" s="86" t="n">
+      <c r="I13" s="85" t="n">
+        <v>35</v>
+      </c>
+      <c r="J13" s="85" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" s="85" t="n">
+        <v>19</v>
+      </c>
+      <c r="L13" s="85" t="n">
+        <v>31</v>
+      </c>
+      <c r="M13" s="85" t="n">
+        <v>120</v>
+      </c>
+      <c r="N13" s="85" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" s="85" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="85" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q13" s="85" t="n">
+        <v>171</v>
+      </c>
+      <c r="R13" s="85" t="n">
+        <v>15</v>
+      </c>
+      <c r="S13" s="85" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" s="85" t="n">
         <v>6</v>
       </c>
-      <c r="J13" s="86" t="n">
-        <v>19</v>
-      </c>
-      <c r="K13" s="86" t="n">
-        <v>33</v>
-      </c>
-      <c r="L13" s="86" t="n">
-        <v>136</v>
-      </c>
-      <c r="M13" s="86" t="n">
-        <v>8</v>
-      </c>
-      <c r="N13" s="86" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" s="86" t="n">
-        <v>17</v>
-      </c>
-      <c r="P13" s="86" t="n">
-        <v>192</v>
-      </c>
-      <c r="Q13" s="86" t="n">
+      <c r="V13" s="85" t="n">
+        <v>4</v>
+      </c>
+      <c r="W13" s="85" t="n">
+        <v>7</v>
+      </c>
+      <c r="X13" s="85" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y13" s="85" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z13" s="85" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA13" s="85" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB13" s="85" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC13" s="85" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD13" s="85" t="n">
         <v>15</v>
       </c>
-      <c r="R13" s="86" t="n">
-        <v>4</v>
-      </c>
-      <c r="S13" s="86" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" s="86" t="n">
-        <v>6</v>
-      </c>
-      <c r="U13" s="86" t="n">
-        <v>4</v>
-      </c>
-      <c r="V13" s="86" t="n">
-        <v>7</v>
-      </c>
-      <c r="W13" s="86" t="n">
-        <v>28</v>
-      </c>
-      <c r="X13" s="86" t="n">
-        <v>46</v>
-      </c>
-      <c r="Y13" s="86" t="n">
-        <v>42</v>
-      </c>
-      <c r="Z13" s="86" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA13" s="86" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB13" s="86" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC13" s="86" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD13" s="86" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE13" s="86" t="n">
-        <v>10</v>
+      <c r="AE13" s="85" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -2818,95 +2817,95 @@
           <t>主力建仓数</t>
         </is>
       </c>
-      <c r="B14" s="87" t="n">
+      <c r="B14" s="86" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="86" t="n">
+      <c r="C14" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="86" t="n">
+      <c r="D14" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="86" t="n">
+      <c r="E14" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="86" t="n">
+      <c r="F14" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="86" t="n">
+      <c r="G14" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="86" t="n">
+      <c r="H14" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="86" t="n">
+      <c r="I14" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="85" t="n">
+        <v>17</v>
+      </c>
+      <c r="K14" s="85" t="n">
+        <v>12</v>
+      </c>
+      <c r="L14" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" s="85" t="n">
+        <v>13</v>
+      </c>
+      <c r="N14" s="85" t="n">
+        <v>38</v>
+      </c>
+      <c r="O14" s="85" t="n">
+        <v>35</v>
+      </c>
+      <c r="P14" s="85" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q14" s="85" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" s="85" t="n">
+        <v>11</v>
+      </c>
+      <c r="S14" s="85" t="n">
+        <v>19</v>
+      </c>
+      <c r="T14" s="85" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" s="85" t="n">
+        <v>6</v>
+      </c>
+      <c r="V14" s="85" t="n">
+        <v>3</v>
+      </c>
+      <c r="W14" s="85" t="n">
+        <v>16</v>
+      </c>
+      <c r="X14" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y14" s="85" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z14" s="85" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA14" s="85" t="n">
+        <v>72</v>
+      </c>
+      <c r="AB14" s="85" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC14" s="85" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD14" s="85" t="n">
+        <v>53</v>
+      </c>
+      <c r="AE14" s="85" t="n">
         <v>18</v>
-      </c>
-      <c r="J14" s="86" t="n">
-        <v>13</v>
-      </c>
-      <c r="K14" s="86" t="n">
-        <v>2</v>
-      </c>
-      <c r="L14" s="86" t="n">
-        <v>13</v>
-      </c>
-      <c r="M14" s="86" t="n">
-        <v>40</v>
-      </c>
-      <c r="N14" s="86" t="n">
-        <v>38</v>
-      </c>
-      <c r="O14" s="86" t="n">
-        <v>20</v>
-      </c>
-      <c r="P14" s="86" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q14" s="86" t="n">
-        <v>11</v>
-      </c>
-      <c r="R14" s="86" t="n">
-        <v>20</v>
-      </c>
-      <c r="S14" s="86" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" s="86" t="n">
-        <v>6</v>
-      </c>
-      <c r="U14" s="86" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" s="86" t="n">
-        <v>19</v>
-      </c>
-      <c r="W14" s="86" t="n">
-        <v>2</v>
-      </c>
-      <c r="X14" s="86" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y14" s="86" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z14" s="86" t="n">
-        <v>76</v>
-      </c>
-      <c r="AA14" s="86" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB14" s="86" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC14" s="86" t="n">
-        <v>56</v>
-      </c>
-      <c r="AD14" s="86" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE14" s="86" t="n">
-        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -2915,95 +2914,95 @@
           <t>主力建仓(avg)</t>
         </is>
       </c>
-      <c r="B15" s="87" t="n">
+      <c r="B15" s="86" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="86" t="n">
+      <c r="C15" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="86" t="n">
+      <c r="D15" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="86" t="n">
+      <c r="E15" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="86" t="n">
+      <c r="F15" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="86" t="n">
+      <c r="G15" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="86" t="n">
+      <c r="H15" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="86" t="n">
+      <c r="I15" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="85" t="n">
         <v>34</v>
       </c>
-      <c r="J15" s="86" t="n">
+      <c r="K15" s="85" t="n">
         <v>15</v>
       </c>
-      <c r="K15" s="86" t="n">
+      <c r="L15" s="85" t="n">
         <v>1</v>
       </c>
-      <c r="L15" s="86" t="n">
+      <c r="M15" s="85" t="n">
         <v>27</v>
       </c>
-      <c r="M15" s="86" t="n">
-        <v>76</v>
-      </c>
-      <c r="N15" s="86" t="n">
+      <c r="N15" s="85" t="n">
+        <v>75</v>
+      </c>
+      <c r="O15" s="85" t="n">
         <v>105</v>
       </c>
-      <c r="O15" s="86" t="n">
+      <c r="P15" s="85" t="n">
         <v>80</v>
       </c>
-      <c r="P15" s="86" t="n">
+      <c r="Q15" s="85" t="n">
         <v>4</v>
       </c>
-      <c r="Q15" s="86" t="n">
+      <c r="R15" s="85" t="n">
         <v>23</v>
       </c>
-      <c r="R15" s="86" t="n">
+      <c r="S15" s="85" t="n">
         <v>36</v>
       </c>
-      <c r="S15" s="86" t="n">
+      <c r="T15" s="85" t="n">
         <v>2</v>
       </c>
-      <c r="T15" s="86" t="n">
+      <c r="U15" s="85" t="n">
         <v>22</v>
       </c>
-      <c r="U15" s="86" t="n">
+      <c r="V15" s="85" t="n">
         <v>13</v>
       </c>
-      <c r="V15" s="86" t="n">
+      <c r="W15" s="85" t="n">
         <v>30</v>
       </c>
-      <c r="W15" s="86" t="n">
+      <c r="X15" s="85" t="n">
         <v>6</v>
       </c>
-      <c r="X15" s="86" t="n">
+      <c r="Y15" s="85" t="n">
         <v>12</v>
       </c>
-      <c r="Y15" s="86" t="n">
+      <c r="Z15" s="85" t="n">
         <v>51</v>
       </c>
-      <c r="Z15" s="86" t="n">
+      <c r="AA15" s="85" t="n">
         <v>127</v>
       </c>
-      <c r="AA15" s="86" t="n">
+      <c r="AB15" s="85" t="n">
         <v>20</v>
       </c>
-      <c r="AB15" s="86" t="n">
+      <c r="AC15" s="85" t="n">
         <v>36</v>
       </c>
-      <c r="AC15" s="86" t="n">
+      <c r="AD15" s="85" t="n">
         <v>85</v>
       </c>
-      <c r="AD15" s="86" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE15" s="86" t="n">
-        <v>25</v>
+      <c r="AE15" s="85" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="16">
@@ -3012,95 +3011,95 @@
           <t>下影线数120d(avg)</t>
         </is>
       </c>
-      <c r="B16" s="86" t="n">
+      <c r="B16" s="85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="86" t="n">
+      <c r="D16" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="86" t="n">
+      <c r="E16" s="85" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="86" t="n">
+      <c r="F16" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="86" t="n">
+      <c r="G16" s="85" t="n">
         <v>27</v>
       </c>
-      <c r="G16" s="86" t="n">
+      <c r="H16" s="85" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="86" t="n">
-        <v>272</v>
-      </c>
-      <c r="I16" s="86" t="n">
+      <c r="I16" s="85" t="n">
+        <v>271</v>
+      </c>
+      <c r="J16" s="85" t="n">
         <v>16</v>
       </c>
-      <c r="J16" s="86" t="n">
+      <c r="K16" s="85" t="n">
         <v>159</v>
       </c>
-      <c r="K16" s="86" t="n">
-        <v>234</v>
-      </c>
-      <c r="L16" s="86" t="n">
-        <v>510</v>
-      </c>
-      <c r="M16" s="86" t="n">
+      <c r="L16" s="85" t="n">
+        <v>233</v>
+      </c>
+      <c r="M16" s="85" t="n">
+        <v>509</v>
+      </c>
+      <c r="N16" s="85" t="n">
         <v>28</v>
       </c>
-      <c r="N16" s="86" t="n">
+      <c r="O16" s="85" t="n">
         <v>4</v>
       </c>
-      <c r="O16" s="86" t="n">
-        <v>480</v>
-      </c>
-      <c r="P16" s="86" t="n">
-        <v>709</v>
-      </c>
-      <c r="Q16" s="86" t="n">
+      <c r="P16" s="85" t="n">
+        <v>479</v>
+      </c>
+      <c r="Q16" s="85" t="n">
+        <v>708</v>
+      </c>
+      <c r="R16" s="85" t="n">
         <v>99</v>
       </c>
-      <c r="R16" s="86" t="n">
+      <c r="S16" s="85" t="n">
         <v>22</v>
       </c>
-      <c r="S16" s="86" t="n">
+      <c r="T16" s="85" t="n">
         <v>16</v>
       </c>
-      <c r="T16" s="86" t="n">
+      <c r="U16" s="85" t="n">
         <v>26</v>
       </c>
-      <c r="U16" s="86" t="n">
+      <c r="V16" s="85" t="n">
         <v>11</v>
       </c>
-      <c r="V16" s="86" t="n">
+      <c r="W16" s="85" t="n">
         <v>35</v>
       </c>
-      <c r="W16" s="86" t="n">
+      <c r="X16" s="85" t="n">
         <v>157</v>
       </c>
-      <c r="X16" s="86" t="n">
-        <v>351</v>
-      </c>
-      <c r="Y16" s="86" t="n">
+      <c r="Y16" s="85" t="n">
+        <v>350</v>
+      </c>
+      <c r="Z16" s="85" t="n">
         <v>258</v>
       </c>
-      <c r="Z16" s="86" t="n">
+      <c r="AA16" s="85" t="n">
         <v>84</v>
       </c>
-      <c r="AA16" s="86" t="n">
+      <c r="AB16" s="85" t="n">
         <v>84</v>
       </c>
-      <c r="AB16" s="86" t="n">
+      <c r="AC16" s="85" t="n">
         <v>143</v>
       </c>
-      <c r="AC16" s="86" t="n">
+      <c r="AD16" s="85" t="n">
         <v>122</v>
       </c>
-      <c r="AD16" s="86" t="n">
+      <c r="AE16" s="85" t="n">
         <v>144</v>
-      </c>
-      <c r="AE16" s="86" t="n">
-        <v>56</v>
       </c>
     </row>
     <row r="17">
@@ -3109,95 +3108,95 @@
           <t>新低数120d(avg)</t>
         </is>
       </c>
-      <c r="B17" s="86" t="n">
+      <c r="B17" s="85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="85" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="86" t="n">
+      <c r="D17" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="86" t="n">
+      <c r="E17" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="86" t="n">
+      <c r="F17" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="86" t="n">
+      <c r="G17" s="85" t="n">
         <v>8</v>
       </c>
-      <c r="G17" s="86" t="n">
+      <c r="H17" s="85" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="86" t="n">
+      <c r="I17" s="85" t="n">
         <v>132</v>
       </c>
-      <c r="I17" s="86" t="n">
+      <c r="J17" s="85" t="n">
         <v>178</v>
       </c>
-      <c r="J17" s="86" t="n">
+      <c r="K17" s="85" t="n">
         <v>243</v>
       </c>
-      <c r="K17" s="86" t="n">
-        <v>466</v>
-      </c>
-      <c r="L17" s="86" t="n">
-        <v>1311</v>
-      </c>
-      <c r="M17" s="86" t="n">
-        <v>861</v>
-      </c>
-      <c r="N17" s="86" t="n">
-        <v>618</v>
-      </c>
-      <c r="O17" s="86" t="n">
-        <v>1034</v>
-      </c>
-      <c r="P17" s="86" t="n">
-        <v>1151</v>
-      </c>
-      <c r="Q17" s="86" t="n">
-        <v>1288</v>
-      </c>
-      <c r="R17" s="86" t="n">
-        <v>495</v>
-      </c>
-      <c r="S17" s="86" t="n">
-        <v>474</v>
-      </c>
-      <c r="T17" s="86" t="n">
-        <v>605</v>
-      </c>
-      <c r="U17" s="86" t="n">
-        <v>345</v>
-      </c>
-      <c r="V17" s="86" t="n">
+      <c r="L17" s="85" t="n">
+        <v>465</v>
+      </c>
+      <c r="M17" s="85" t="n">
+        <v>1308</v>
+      </c>
+      <c r="N17" s="85" t="n">
+        <v>859</v>
+      </c>
+      <c r="O17" s="85" t="n">
+        <v>617</v>
+      </c>
+      <c r="P17" s="85" t="n">
+        <v>1031</v>
+      </c>
+      <c r="Q17" s="85" t="n">
+        <v>1148</v>
+      </c>
+      <c r="R17" s="85" t="n">
+        <v>1285</v>
+      </c>
+      <c r="S17" s="85" t="n">
+        <v>493</v>
+      </c>
+      <c r="T17" s="85" t="n">
+        <v>473</v>
+      </c>
+      <c r="U17" s="85" t="n">
+        <v>604</v>
+      </c>
+      <c r="V17" s="85" t="n">
+        <v>344</v>
+      </c>
+      <c r="W17" s="85" t="n">
         <v>260</v>
       </c>
-      <c r="W17" s="86" t="n">
+      <c r="X17" s="85" t="n">
         <v>243</v>
       </c>
-      <c r="X17" s="86" t="n">
-        <v>585</v>
-      </c>
-      <c r="Y17" s="86" t="n">
-        <v>867</v>
-      </c>
-      <c r="Z17" s="86" t="n">
-        <v>835</v>
-      </c>
-      <c r="AA17" s="86" t="n">
-        <v>536</v>
-      </c>
-      <c r="AB17" s="86" t="n">
-        <v>850</v>
-      </c>
-      <c r="AC17" s="86" t="n">
-        <v>919</v>
-      </c>
-      <c r="AD17" s="86" t="n">
-        <v>781</v>
-      </c>
-      <c r="AE17" s="86" t="n">
-        <v>667</v>
+      <c r="Y17" s="85" t="n">
+        <v>583</v>
+      </c>
+      <c r="Z17" s="85" t="n">
+        <v>865</v>
+      </c>
+      <c r="AA17" s="85" t="n">
+        <v>834</v>
+      </c>
+      <c r="AB17" s="85" t="n">
+        <v>535</v>
+      </c>
+      <c r="AC17" s="85" t="n">
+        <v>849</v>
+      </c>
+      <c r="AD17" s="85" t="n">
+        <v>918</v>
+      </c>
+      <c r="AE17" s="85" t="n">
+        <v>779</v>
       </c>
     </row>
     <row r="18">
@@ -3206,95 +3205,95 @@
           <t>新低数60d</t>
         </is>
       </c>
-      <c r="B18" s="86" t="n">
+      <c r="B18" s="85" t="n">
         <v>6</v>
       </c>
-      <c r="C18" s="86" t="n">
+      <c r="C18" s="85" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" s="85" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="86" t="n">
+      <c r="E18" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="86" t="n">
+      <c r="F18" s="85" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="86" t="n">
+      <c r="G18" s="85" t="n">
         <v>2</v>
       </c>
-      <c r="G18" s="86" t="n">
+      <c r="H18" s="85" t="n">
         <v>4</v>
       </c>
-      <c r="H18" s="86" t="n">
+      <c r="I18" s="85" t="n">
         <v>3</v>
       </c>
-      <c r="I18" s="86" t="n">
+      <c r="J18" s="85" t="n">
         <v>357</v>
       </c>
-      <c r="J18" s="86" t="n">
+      <c r="K18" s="85" t="n">
         <v>342</v>
       </c>
-      <c r="K18" s="86" t="n">
+      <c r="L18" s="85" t="n">
         <v>70</v>
       </c>
-      <c r="L18" s="86" t="n">
+      <c r="M18" s="85" t="n">
         <v>1544</v>
       </c>
-      <c r="M18" s="86" t="n">
+      <c r="N18" s="85" t="n">
         <v>1420</v>
       </c>
-      <c r="N18" s="86" t="n">
+      <c r="O18" s="85" t="n">
         <v>700</v>
       </c>
-      <c r="O18" s="86" t="n">
+      <c r="P18" s="85" t="n">
         <v>660</v>
       </c>
-      <c r="P18" s="86" t="n">
+      <c r="Q18" s="85" t="n">
         <v>449</v>
       </c>
-      <c r="Q18" s="86" t="n">
+      <c r="R18" s="85" t="n">
         <v>835</v>
       </c>
-      <c r="R18" s="86" t="n">
+      <c r="S18" s="85" t="n">
         <v>792</v>
       </c>
-      <c r="S18" s="86" t="n">
+      <c r="T18" s="85" t="n">
         <v>137</v>
       </c>
-      <c r="T18" s="86" t="n">
+      <c r="U18" s="85" t="n">
         <v>436</v>
       </c>
-      <c r="U18" s="86" t="n">
+      <c r="V18" s="85" t="n">
         <v>205</v>
       </c>
-      <c r="V18" s="86" t="n">
+      <c r="W18" s="85" t="n">
         <v>460</v>
       </c>
-      <c r="W18" s="86" t="n">
+      <c r="X18" s="85" t="n">
         <v>47</v>
       </c>
-      <c r="X18" s="86" t="n">
+      <c r="Y18" s="85" t="n">
         <v>174</v>
       </c>
-      <c r="Y18" s="86" t="n">
+      <c r="Z18" s="85" t="n">
         <v>570</v>
       </c>
-      <c r="Z18" s="86" t="n">
+      <c r="AA18" s="85" t="n">
         <v>1284</v>
       </c>
-      <c r="AA18" s="86" t="n">
+      <c r="AB18" s="85" t="n">
         <v>384</v>
       </c>
-      <c r="AB18" s="86" t="n">
+      <c r="AC18" s="85" t="n">
         <v>1435</v>
       </c>
-      <c r="AC18" s="86" t="n">
+      <c r="AD18" s="85" t="n">
         <v>1700</v>
       </c>
-      <c r="AD18" s="86" t="n">
+      <c r="AE18" s="85" t="n">
         <v>953</v>
-      </c>
-      <c r="AE18" s="86" t="n">
-        <v>1203</v>
       </c>
     </row>
     <row r="19">
@@ -3303,192 +3302,192 @@
           <t>新低数60d(zz500)</t>
         </is>
       </c>
-      <c r="B19" s="86" t="n">
+      <c r="B19" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="85" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="86" t="n">
+      <c r="D19" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="86" t="n">
+      <c r="E19" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="86" t="n">
+      <c r="F19" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="86" t="n">
+      <c r="G19" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="86" t="n">
+      <c r="H19" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="86" t="n">
+      <c r="I19" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="86" t="n">
+      <c r="J19" s="85" t="n">
         <v>65</v>
       </c>
-      <c r="J19" s="86" t="n">
+      <c r="K19" s="85" t="n">
         <v>54</v>
       </c>
-      <c r="K19" s="86" t="n">
+      <c r="L19" s="85" t="n">
         <v>13</v>
       </c>
-      <c r="L19" s="86" t="n">
+      <c r="M19" s="85" t="n">
         <v>114</v>
       </c>
-      <c r="M19" s="86" t="n">
+      <c r="N19" s="85" t="n">
         <v>147</v>
       </c>
-      <c r="N19" s="86" t="n">
+      <c r="O19" s="85" t="n">
         <v>75</v>
       </c>
-      <c r="O19" s="86" t="n">
+      <c r="P19" s="85" t="n">
         <v>104</v>
       </c>
-      <c r="P19" s="86" t="n">
+      <c r="Q19" s="85" t="n">
         <v>102</v>
       </c>
-      <c r="Q19" s="86" t="n">
+      <c r="R19" s="85" t="n">
         <v>127</v>
       </c>
-      <c r="R19" s="86" t="n">
+      <c r="S19" s="85" t="n">
         <v>91</v>
       </c>
-      <c r="S19" s="86" t="n">
+      <c r="T19" s="85" t="n">
         <v>36</v>
       </c>
-      <c r="T19" s="86" t="n">
+      <c r="U19" s="85" t="n">
         <v>60</v>
       </c>
-      <c r="U19" s="86" t="n">
+      <c r="V19" s="85" t="n">
         <v>41</v>
       </c>
-      <c r="V19" s="86" t="n">
+      <c r="W19" s="85" t="n">
         <v>81</v>
       </c>
-      <c r="W19" s="86" t="n">
+      <c r="X19" s="85" t="n">
         <v>15</v>
       </c>
-      <c r="X19" s="86" t="n">
+      <c r="Y19" s="85" t="n">
         <v>35</v>
       </c>
-      <c r="Y19" s="86" t="n">
+      <c r="Z19" s="85" t="n">
         <v>84</v>
       </c>
-      <c r="Z19" s="86" t="n">
+      <c r="AA19" s="85" t="n">
         <v>162</v>
       </c>
-      <c r="AA19" s="86" t="n">
+      <c r="AB19" s="85" t="n">
         <v>76</v>
       </c>
-      <c r="AB19" s="86" t="n">
+      <c r="AC19" s="85" t="n">
         <v>118</v>
       </c>
-      <c r="AC19" s="86" t="n">
+      <c r="AD19" s="85" t="n">
         <v>201</v>
       </c>
-      <c r="AD19" s="86" t="n">
+      <c r="AE19" s="85" t="n">
         <v>146</v>
       </c>
-      <c r="AE19" s="86" t="n">
-        <v>163</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="82" t="inlineStr">
+      <c r="A20" s="76" t="inlineStr">
         <is>
           <t>主力拉高数</t>
         </is>
       </c>
-      <c r="B20" s="86" t="n">
-        <v>290</v>
-      </c>
-      <c r="C20" s="86" t="n">
-        <v>1243</v>
-      </c>
-      <c r="D20" s="86" t="n">
-        <v>907</v>
-      </c>
-      <c r="E20" s="86" t="n">
-        <v>587</v>
-      </c>
-      <c r="F20" s="86" t="n">
-        <v>311</v>
-      </c>
-      <c r="G20" s="86" t="n">
-        <v>273</v>
-      </c>
-      <c r="H20" s="86" t="n">
-        <v>133</v>
-      </c>
-      <c r="I20" s="86" t="n">
+      <c r="B20" s="85" t="n">
+        <v>42</v>
+      </c>
+      <c r="C20" s="85" t="n">
+        <v>285</v>
+      </c>
+      <c r="D20" s="85" t="n">
+        <v>1161</v>
+      </c>
+      <c r="E20" s="85" t="n">
+        <v>848</v>
+      </c>
+      <c r="F20" s="85" t="n">
+        <v>553</v>
+      </c>
+      <c r="G20" s="85" t="n">
+        <v>294</v>
+      </c>
+      <c r="H20" s="85" t="n">
+        <v>259</v>
+      </c>
+      <c r="I20" s="85" t="n">
+        <v>131</v>
+      </c>
+      <c r="J20" s="85" t="n">
         <v>57</v>
       </c>
-      <c r="J20" s="86" t="n">
+      <c r="K20" s="85" t="n">
+        <v>47</v>
+      </c>
+      <c r="L20" s="85" t="n">
+        <v>52</v>
+      </c>
+      <c r="M20" s="85" t="n">
+        <v>34</v>
+      </c>
+      <c r="N20" s="85" t="n">
+        <v>22</v>
+      </c>
+      <c r="O20" s="85" t="n">
+        <v>50</v>
+      </c>
+      <c r="P20" s="85" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q20" s="85" t="n">
+        <v>21</v>
+      </c>
+      <c r="R20" s="85" t="n">
+        <v>14</v>
+      </c>
+      <c r="S20" s="85" t="n">
+        <v>40</v>
+      </c>
+      <c r="T20" s="85" t="n">
+        <v>54</v>
+      </c>
+      <c r="U20" s="85" t="n">
+        <v>46</v>
+      </c>
+      <c r="V20" s="85" t="n">
+        <v>58</v>
+      </c>
+      <c r="W20" s="85" t="n">
+        <v>46</v>
+      </c>
+      <c r="X20" s="85" t="n">
         <v>48</v>
       </c>
-      <c r="K20" s="86" t="n">
-        <v>53</v>
-      </c>
-      <c r="L20" s="86" t="n">
+      <c r="Y20" s="85" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z20" s="85" t="n">
         <v>34</v>
       </c>
-      <c r="M20" s="86" t="n">
-        <v>23</v>
-      </c>
-      <c r="N20" s="86" t="n">
-        <v>52</v>
-      </c>
-      <c r="O20" s="86" t="n">
-        <v>42</v>
-      </c>
-      <c r="P20" s="86" t="n">
+      <c r="AA20" s="85" t="n">
+        <v>33</v>
+      </c>
+      <c r="AB20" s="85" t="n">
+        <v>31</v>
+      </c>
+      <c r="AC20" s="85" t="n">
         <v>22</v>
       </c>
-      <c r="Q20" s="86" t="n">
-        <v>16</v>
-      </c>
-      <c r="R20" s="86" t="n">
-        <v>43</v>
-      </c>
-      <c r="S20" s="86" t="n">
-        <v>59</v>
-      </c>
-      <c r="T20" s="86" t="n">
-        <v>51</v>
-      </c>
-      <c r="U20" s="86" t="n">
-        <v>61</v>
-      </c>
-      <c r="V20" s="86" t="n">
-        <v>49</v>
-      </c>
-      <c r="W20" s="86" t="n">
-        <v>53</v>
-      </c>
-      <c r="X20" s="86" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y20" s="86" t="n">
+      <c r="AD20" s="85" t="n">
         <v>35</v>
       </c>
-      <c r="Z20" s="86" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA20" s="86" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB20" s="86" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC20" s="86" t="n">
-        <v>35</v>
-      </c>
-      <c r="AD20" s="86" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE20" s="86" t="n">
-        <v>49</v>
+      <c r="AE20" s="85" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -3497,95 +3496,95 @@
           <t>新高数120d(avg)</t>
         </is>
       </c>
-      <c r="B21" s="86" t="n">
-        <v>734</v>
-      </c>
-      <c r="C21" s="86" t="n">
-        <v>4681</v>
-      </c>
-      <c r="D21" s="86" t="n">
-        <v>3737</v>
-      </c>
-      <c r="E21" s="86" t="n">
-        <v>2351</v>
-      </c>
-      <c r="F21" s="86" t="n">
-        <v>1154</v>
-      </c>
-      <c r="G21" s="86" t="n">
-        <v>1106</v>
-      </c>
-      <c r="H21" s="86" t="n">
-        <v>618</v>
-      </c>
-      <c r="I21" s="86" t="n">
-        <v>240</v>
-      </c>
-      <c r="J21" s="86" t="n">
+      <c r="B21" s="85" t="n">
+        <v>100</v>
+      </c>
+      <c r="C21" s="85" t="n">
+        <v>733</v>
+      </c>
+      <c r="D21" s="85" t="n">
+        <v>4672</v>
+      </c>
+      <c r="E21" s="85" t="n">
+        <v>3730</v>
+      </c>
+      <c r="F21" s="85" t="n">
+        <v>2346</v>
+      </c>
+      <c r="G21" s="85" t="n">
+        <v>1152</v>
+      </c>
+      <c r="H21" s="85" t="n">
+        <v>1104</v>
+      </c>
+      <c r="I21" s="85" t="n">
+        <v>617</v>
+      </c>
+      <c r="J21" s="85" t="n">
+        <v>239</v>
+      </c>
+      <c r="K21" s="85" t="n">
         <v>113</v>
       </c>
-      <c r="K21" s="86" t="n">
+      <c r="L21" s="85" t="n">
         <v>105</v>
       </c>
-      <c r="L21" s="86" t="n">
+      <c r="M21" s="85" t="n">
         <v>147</v>
       </c>
-      <c r="M21" s="86" t="n">
+      <c r="N21" s="85" t="n">
         <v>44</v>
       </c>
-      <c r="N21" s="86" t="n">
+      <c r="O21" s="85" t="n">
         <v>125</v>
       </c>
-      <c r="O21" s="86" t="n">
-        <v>115</v>
-      </c>
-      <c r="P21" s="86" t="n">
+      <c r="P21" s="85" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q21" s="85" t="n">
         <v>37</v>
       </c>
-      <c r="Q21" s="86" t="n">
+      <c r="R21" s="85" t="n">
         <v>61</v>
       </c>
-      <c r="R21" s="86" t="n">
+      <c r="S21" s="85" t="n">
         <v>116</v>
       </c>
-      <c r="S21" s="86" t="n">
+      <c r="T21" s="85" t="n">
         <v>95</v>
       </c>
-      <c r="T21" s="86" t="n">
+      <c r="U21" s="85" t="n">
         <v>226</v>
       </c>
-      <c r="U21" s="86" t="n">
+      <c r="V21" s="85" t="n">
         <v>162</v>
       </c>
-      <c r="V21" s="86" t="n">
+      <c r="W21" s="85" t="n">
         <v>183</v>
       </c>
-      <c r="W21" s="86" t="n">
-        <v>236</v>
-      </c>
-      <c r="X21" s="86" t="n">
+      <c r="X21" s="85" t="n">
+        <v>235</v>
+      </c>
+      <c r="Y21" s="85" t="n">
         <v>140</v>
       </c>
-      <c r="Y21" s="86" t="n">
-        <v>568</v>
-      </c>
-      <c r="Z21" s="86" t="n">
-        <v>670</v>
-      </c>
-      <c r="AA21" s="86" t="n">
-        <v>318</v>
-      </c>
-      <c r="AB21" s="86" t="n">
-        <v>502</v>
-      </c>
-      <c r="AC21" s="86" t="n">
-        <v>595</v>
-      </c>
-      <c r="AD21" s="86" t="n">
+      <c r="Z21" s="85" t="n">
+        <v>567</v>
+      </c>
+      <c r="AA21" s="85" t="n">
+        <v>669</v>
+      </c>
+      <c r="AB21" s="85" t="n">
+        <v>317</v>
+      </c>
+      <c r="AC21" s="85" t="n">
+        <v>501</v>
+      </c>
+      <c r="AD21" s="85" t="n">
+        <v>594</v>
+      </c>
+      <c r="AE21" s="85" t="n">
         <v>133</v>
-      </c>
-      <c r="AE21" s="86" t="n">
-        <v>545</v>
       </c>
     </row>
     <row r="22">
@@ -3594,95 +3593,95 @@
           <t>新高数60d</t>
         </is>
       </c>
-      <c r="B22" s="86" t="n">
+      <c r="B22" s="85" t="n">
+        <v>121</v>
+      </c>
+      <c r="C22" s="85" t="n">
         <v>255</v>
       </c>
-      <c r="C22" s="86" t="n">
+      <c r="D22" s="85" t="n">
         <v>4449</v>
       </c>
-      <c r="D22" s="86" t="n">
+      <c r="E22" s="85" t="n">
         <v>4061</v>
       </c>
-      <c r="E22" s="86" t="n">
+      <c r="F22" s="85" t="n">
         <v>2268</v>
       </c>
-      <c r="F22" s="86" t="n">
+      <c r="G22" s="85" t="n">
         <v>1284</v>
       </c>
-      <c r="G22" s="86" t="n">
+      <c r="H22" s="85" t="n">
         <v>570</v>
       </c>
-      <c r="H22" s="86" t="n">
+      <c r="I22" s="85" t="n">
         <v>438</v>
       </c>
-      <c r="I22" s="86" t="n">
+      <c r="J22" s="85" t="n">
         <v>175</v>
       </c>
-      <c r="J22" s="86" t="n">
+      <c r="K22" s="85" t="n">
         <v>170</v>
       </c>
-      <c r="K22" s="86" t="n">
+      <c r="L22" s="85" t="n">
         <v>173</v>
       </c>
-      <c r="L22" s="86" t="n">
+      <c r="M22" s="85" t="n">
         <v>94</v>
       </c>
-      <c r="M22" s="86" t="n">
+      <c r="N22" s="85" t="n">
         <v>86</v>
       </c>
-      <c r="N22" s="86" t="n">
+      <c r="O22" s="85" t="n">
         <v>97</v>
       </c>
-      <c r="O22" s="86" t="n">
+      <c r="P22" s="85" t="n">
         <v>106</v>
       </c>
-      <c r="P22" s="86" t="n">
+      <c r="Q22" s="85" t="n">
         <v>92</v>
       </c>
-      <c r="Q22" s="86" t="n">
+      <c r="R22" s="85" t="n">
         <v>68</v>
       </c>
-      <c r="R22" s="86" t="n">
+      <c r="S22" s="85" t="n">
         <v>76</v>
       </c>
-      <c r="S22" s="86" t="n">
+      <c r="T22" s="85" t="n">
         <v>135</v>
       </c>
-      <c r="T22" s="86" t="n">
+      <c r="U22" s="85" t="n">
         <v>92</v>
       </c>
-      <c r="U22" s="86" t="n">
+      <c r="V22" s="85" t="n">
         <v>162</v>
       </c>
-      <c r="V22" s="86" t="n">
+      <c r="W22" s="85" t="n">
         <v>121</v>
       </c>
-      <c r="W22" s="86" t="n">
+      <c r="X22" s="85" t="n">
         <v>138</v>
       </c>
-      <c r="X22" s="86" t="n">
+      <c r="Y22" s="85" t="n">
         <v>85</v>
       </c>
-      <c r="Y22" s="86" t="n">
+      <c r="Z22" s="85" t="n">
         <v>52</v>
       </c>
-      <c r="Z22" s="86" t="n">
+      <c r="AA22" s="85" t="n">
         <v>64</v>
       </c>
-      <c r="AA22" s="86" t="n">
+      <c r="AB22" s="85" t="n">
         <v>78</v>
       </c>
-      <c r="AB22" s="86" t="n">
+      <c r="AC22" s="85" t="n">
         <v>63</v>
       </c>
-      <c r="AC22" s="86" t="n">
+      <c r="AD22" s="85" t="n">
         <v>47</v>
       </c>
-      <c r="AD22" s="86" t="n">
+      <c r="AE22" s="85" t="n">
         <v>47</v>
-      </c>
-      <c r="AE22" s="86" t="n">
-        <v>49</v>
       </c>
     </row>
     <row r="23">
@@ -3691,95 +3690,95 @@
           <t>新高数60d(zz500)</t>
         </is>
       </c>
-      <c r="B23" s="86" t="n">
+      <c r="B23" s="85" t="n">
+        <v>9</v>
+      </c>
+      <c r="C23" s="85" t="n">
         <v>32</v>
       </c>
-      <c r="C23" s="86" t="n">
+      <c r="D23" s="85" t="n">
         <v>415</v>
       </c>
-      <c r="D23" s="86" t="n">
+      <c r="E23" s="85" t="n">
         <v>409</v>
       </c>
-      <c r="E23" s="86" t="n">
+      <c r="F23" s="85" t="n">
         <v>250</v>
       </c>
-      <c r="F23" s="86" t="n">
+      <c r="G23" s="85" t="n">
         <v>146</v>
       </c>
-      <c r="G23" s="86" t="n">
+      <c r="H23" s="85" t="n">
         <v>67</v>
       </c>
-      <c r="H23" s="86" t="n">
+      <c r="I23" s="85" t="n">
         <v>57</v>
       </c>
-      <c r="I23" s="86" t="n">
+      <c r="J23" s="85" t="n">
         <v>8</v>
       </c>
-      <c r="J23" s="86" t="n">
+      <c r="K23" s="85" t="n">
         <v>11</v>
       </c>
-      <c r="K23" s="86" t="n">
+      <c r="L23" s="85" t="n">
         <v>11</v>
       </c>
-      <c r="L23" s="86" t="n">
+      <c r="M23" s="85" t="n">
         <v>14</v>
       </c>
-      <c r="M23" s="86" t="n">
+      <c r="N23" s="85" t="n">
         <v>4</v>
       </c>
-      <c r="N23" s="86" t="n">
+      <c r="O23" s="85" t="n">
         <v>6</v>
       </c>
-      <c r="O23" s="86" t="n">
+      <c r="P23" s="85" t="n">
         <v>19</v>
       </c>
-      <c r="P23" s="86" t="n">
+      <c r="Q23" s="85" t="n">
         <v>12</v>
       </c>
-      <c r="Q23" s="86" t="n">
+      <c r="R23" s="85" t="n">
         <v>5</v>
       </c>
-      <c r="R23" s="86" t="n">
+      <c r="S23" s="85" t="n">
         <v>4</v>
       </c>
-      <c r="S23" s="86" t="n">
+      <c r="T23" s="85" t="n">
         <v>11</v>
       </c>
-      <c r="T23" s="86" t="n">
+      <c r="U23" s="85" t="n">
         <v>9</v>
       </c>
-      <c r="U23" s="86" t="n">
+      <c r="V23" s="85" t="n">
         <v>14</v>
       </c>
-      <c r="V23" s="86" t="n">
+      <c r="W23" s="85" t="n">
         <v>9</v>
       </c>
-      <c r="W23" s="86" t="n">
+      <c r="X23" s="85" t="n">
         <v>7</v>
       </c>
-      <c r="X23" s="86" t="n">
+      <c r="Y23" s="85" t="n">
         <v>6</v>
       </c>
-      <c r="Y23" s="86" t="n">
+      <c r="Z23" s="85" t="n">
         <v>6</v>
       </c>
-      <c r="Z23" s="86" t="n">
+      <c r="AA23" s="85" t="n">
         <v>5</v>
       </c>
-      <c r="AA23" s="86" t="n">
+      <c r="AB23" s="85" t="n">
         <v>6</v>
       </c>
-      <c r="AB23" s="86" t="n">
+      <c r="AC23" s="85" t="n">
         <v>3</v>
       </c>
-      <c r="AC23" s="86" t="n">
+      <c r="AD23" s="85" t="n">
         <v>4</v>
       </c>
-      <c r="AD23" s="86" t="n">
+      <c r="AE23" s="85" t="n">
         <v>1</v>
-      </c>
-      <c r="AE23" s="86" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -3788,94 +3787,94 @@
           <t>升息概率</t>
         </is>
       </c>
-      <c r="B24" s="86" t="n">
+      <c r="B24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="86" t="n">
+      <c r="C24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="86" t="n">
+      <c r="D24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="86" t="n">
+      <c r="E24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="86" t="n">
+      <c r="F24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="86" t="n">
+      <c r="G24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="86" t="n">
+      <c r="H24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="86" t="n">
+      <c r="I24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="86" t="n">
+      <c r="J24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="86" t="n">
+      <c r="K24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="86" t="n">
+      <c r="L24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="86" t="n">
+      <c r="M24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="86" t="n">
+      <c r="N24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="O24" s="86" t="n">
+      <c r="O24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="P24" s="86" t="n">
+      <c r="P24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" s="86" t="n">
+      <c r="Q24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="R24" s="86" t="n">
+      <c r="R24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="S24" s="86" t="n">
+      <c r="S24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="T24" s="86" t="n">
+      <c r="T24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="U24" s="86" t="n">
+      <c r="U24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="86" t="n">
+      <c r="V24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="W24" s="86" t="n">
+      <c r="W24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="X24" s="86" t="n">
+      <c r="X24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="Y24" s="86" t="n">
+      <c r="Y24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="Z24" s="86" t="n">
+      <c r="Z24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="AA24" s="86" t="n">
+      <c r="AA24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="AB24" s="86" t="n">
+      <c r="AB24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="AC24" s="86" t="n">
+      <c r="AC24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="AD24" s="86" t="n">
+      <c r="AD24" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="AE24" s="86" t="n">
+      <c r="AE24" s="85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3885,95 +3884,95 @@
           <t>人民币</t>
         </is>
       </c>
-      <c r="B25" s="88" t="n">
+      <c r="B25" s="87" t="n">
         <v>7.09</v>
       </c>
-      <c r="C25" s="88" t="n">
+      <c r="C25" s="87" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="D25" s="87" t="n">
         <v>7.07</v>
       </c>
-      <c r="D25" s="88" t="n">
+      <c r="E25" s="87" t="n">
         <v>7.01</v>
       </c>
-      <c r="E25" s="88" t="n">
+      <c r="F25" s="87" t="n">
         <v>6.98</v>
       </c>
-      <c r="F25" s="88" t="n">
+      <c r="G25" s="87" t="n">
         <v>6.98</v>
       </c>
-      <c r="G25" s="88" t="n">
+      <c r="H25" s="87" t="n">
         <v>7.03</v>
       </c>
-      <c r="H25" s="88" t="n">
+      <c r="I25" s="87" t="n">
         <v>7</v>
       </c>
-      <c r="I25" s="88" t="n">
+      <c r="J25" s="87" t="n">
         <v>7.06</v>
       </c>
-      <c r="J25" s="88" t="n">
+      <c r="K25" s="87" t="n">
         <v>7.04</v>
       </c>
-      <c r="K25" s="88" t="n">
+      <c r="L25" s="87" t="n">
         <v>7.07</v>
       </c>
-      <c r="L25" s="88" t="n">
+      <c r="M25" s="87" t="n">
         <v>7.1</v>
       </c>
-      <c r="M25" s="88" t="n">
+      <c r="N25" s="87" t="n">
         <v>7.1</v>
       </c>
-      <c r="N25" s="88" t="n">
+      <c r="O25" s="87" t="n">
         <v>7.12</v>
       </c>
-      <c r="O25" s="88" t="n">
+      <c r="P25" s="87" t="n">
         <v>7.13</v>
       </c>
-      <c r="P25" s="88" t="n">
+      <c r="Q25" s="87" t="n">
         <v>7.13</v>
       </c>
-      <c r="Q25" s="88" t="n">
+      <c r="R25" s="87" t="n">
         <v>7.12</v>
       </c>
-      <c r="R25" s="88" t="n">
+      <c r="S25" s="87" t="n">
         <v>7.09</v>
       </c>
-      <c r="S25" s="88" t="n">
+      <c r="T25" s="87" t="n">
         <v>7.09</v>
       </c>
-      <c r="T25" s="88" t="n">
+      <c r="U25" s="87" t="n">
         <v>7.11</v>
       </c>
-      <c r="U25" s="88" t="n">
+      <c r="V25" s="87" t="n">
         <v>7.12</v>
       </c>
-      <c r="V25" s="88" t="n">
+      <c r="W25" s="87" t="n">
         <v>7.12</v>
       </c>
-      <c r="W25" s="88" t="n">
+      <c r="X25" s="87" t="n">
         <v>7.09</v>
       </c>
-      <c r="X25" s="88" t="n">
+      <c r="Y25" s="87" t="n">
         <v>7.09</v>
       </c>
-      <c r="Y25" s="88" t="n">
+      <c r="Z25" s="87" t="n">
         <v>7.13</v>
       </c>
-      <c r="Z25" s="88" t="n">
+      <c r="AA25" s="87" t="n">
         <v>7.12</v>
       </c>
-      <c r="AA25" s="88" t="n">
+      <c r="AB25" s="87" t="n">
         <v>7.13</v>
       </c>
-      <c r="AB25" s="88" t="n">
+      <c r="AC25" s="87" t="n">
         <v>7.11</v>
       </c>
-      <c r="AC25" s="88" t="n">
+      <c r="AD25" s="87" t="n">
         <v>7.15</v>
       </c>
-      <c r="AD25" s="88" t="n">
+      <c r="AE25" s="87" t="n">
         <v>7.13</v>
-      </c>
-      <c r="AE25" s="88" t="n">
-        <v>7.11</v>
       </c>
     </row>
     <row r="26">
@@ -3982,95 +3981,95 @@
           <t>人民币涨跌幅</t>
         </is>
       </c>
-      <c r="B26" s="89" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="C26" s="89" t="n">
+      <c r="B26" s="88" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="C26" s="88" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D26" s="87" t="n">
         <v>0.9</v>
       </c>
-      <c r="D26" s="88" t="n">
+      <c r="E26" s="87" t="n">
         <v>0.42</v>
       </c>
-      <c r="E26" s="88" t="n">
+      <c r="F26" s="87" t="n">
         <v>0.02</v>
       </c>
-      <c r="F26" s="88" t="n">
+      <c r="G26" s="87" t="n">
         <v>-0.79</v>
       </c>
-      <c r="G26" s="88" t="n">
+      <c r="H26" s="87" t="n">
         <v>0.49</v>
       </c>
-      <c r="H26" s="88" t="n">
+      <c r="I26" s="87" t="n">
         <v>-0.84</v>
       </c>
-      <c r="I26" s="88" t="n">
+      <c r="J26" s="87" t="n">
         <v>0.27</v>
       </c>
-      <c r="J26" s="88" t="n">
+      <c r="K26" s="87" t="n">
         <v>-0.44</v>
       </c>
-      <c r="K26" s="88" t="n">
+      <c r="L26" s="87" t="n">
         <v>-0.34</v>
       </c>
-      <c r="L26" s="88" t="n">
+      <c r="M26" s="87" t="n">
         <v>-0.02</v>
       </c>
-      <c r="M26" s="88" t="n">
+      <c r="N26" s="87" t="n">
         <v>-0.25</v>
       </c>
-      <c r="N26" s="88" t="n">
+      <c r="O26" s="87" t="n">
         <v>-0.15</v>
       </c>
-      <c r="O26" s="88" t="n">
+      <c r="P26" s="87" t="n">
         <v>-0.1</v>
       </c>
-      <c r="P26" s="88" t="n">
+      <c r="Q26" s="87" t="n">
         <v>0.18</v>
       </c>
-      <c r="Q26" s="88" t="n">
+      <c r="R26" s="87" t="n">
         <v>0.43</v>
       </c>
-      <c r="R26" s="88" t="n">
+      <c r="S26" s="87" t="n">
         <v>0.03</v>
       </c>
-      <c r="S26" s="88" t="n">
+      <c r="T26" s="87" t="n">
         <v>-0.24</v>
       </c>
-      <c r="T26" s="88" t="n">
+      <c r="U26" s="87" t="n">
         <v>-0.18</v>
       </c>
-      <c r="U26" s="88" t="n">
+      <c r="V26" s="87" t="n">
         <v>0.02</v>
       </c>
-      <c r="V26" s="88" t="n">
+      <c r="W26" s="87" t="n">
         <v>0.41</v>
       </c>
-      <c r="W26" s="88" t="n">
+      <c r="X26" s="87" t="n">
         <v>-0.01</v>
       </c>
-      <c r="X26" s="88" t="n">
+      <c r="Y26" s="87" t="n">
         <v>-0.59</v>
       </c>
-      <c r="Y26" s="88" t="n">
+      <c r="Z26" s="87" t="n">
         <v>0.13</v>
       </c>
-      <c r="Z26" s="88" t="n">
+      <c r="AA26" s="87" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AA26" s="88" t="n">
+      <c r="AB26" s="87" t="n">
         <v>0.15</v>
       </c>
-      <c r="AB26" s="88" t="n">
+      <c r="AC26" s="87" t="n">
         <v>-0.43</v>
       </c>
-      <c r="AC26" s="88" t="n">
+      <c r="AD26" s="87" t="n">
         <v>0.21</v>
       </c>
-      <c r="AD26" s="88" t="n">
+      <c r="AE26" s="87" t="n">
         <v>0.23</v>
-      </c>
-      <c r="AE26" s="88" t="n">
-        <v>-0.23</v>
       </c>
     </row>
     <row r="27">
@@ -4079,95 +4078,95 @@
           <t>人民币20日涨跌幅</t>
         </is>
       </c>
-      <c r="B27" s="89" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="C27" s="89" t="n">
+      <c r="B27" s="88" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="C27" s="88" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="D27" s="87" t="n">
         <v>-0.21</v>
       </c>
-      <c r="D27" s="88" t="n">
+      <c r="E27" s="87" t="n">
         <v>-1.11</v>
       </c>
-      <c r="E27" s="88" t="n">
+      <c r="F27" s="87" t="n">
         <v>-2.1</v>
       </c>
-      <c r="F27" s="88" t="n">
+      <c r="G27" s="87" t="n">
         <v>-2</v>
       </c>
-      <c r="G27" s="88" t="n">
+      <c r="H27" s="87" t="n">
         <v>-1.27</v>
       </c>
-      <c r="H27" s="88" t="n">
+      <c r="I27" s="87" t="n">
         <v>-1.61</v>
       </c>
-      <c r="I27" s="88" t="n">
+      <c r="J27" s="87" t="n">
         <v>-1.2</v>
       </c>
-      <c r="J27" s="88" t="n">
+      <c r="K27" s="87" t="n">
         <v>-1.26</v>
       </c>
-      <c r="K27" s="88" t="n">
+      <c r="L27" s="87" t="n">
         <v>-0.59</v>
       </c>
-      <c r="L27" s="88" t="n">
+      <c r="M27" s="87" t="n">
         <v>-0.47</v>
       </c>
-      <c r="M27" s="88" t="n">
+      <c r="N27" s="87" t="n">
         <v>-0.88</v>
       </c>
-      <c r="N27" s="88" t="n">
+      <c r="O27" s="87" t="n">
         <v>-0.93</v>
       </c>
-      <c r="O27" s="88" t="n">
+      <c r="P27" s="87" t="n">
         <v>-0.29</v>
       </c>
-      <c r="P27" s="88" t="n">
+      <c r="Q27" s="87" t="n">
         <v>-0.21</v>
       </c>
-      <c r="Q27" s="88" t="n">
+      <c r="R27" s="87" t="n">
         <v>-0.79</v>
       </c>
-      <c r="R27" s="88" t="n">
+      <c r="S27" s="87" t="n">
         <v>-1.17</v>
       </c>
-      <c r="S27" s="88" t="n">
+      <c r="T27" s="87" t="n">
         <v>-1.35</v>
       </c>
-      <c r="T27" s="88" t="n">
+      <c r="U27" s="87" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="U27" s="88" t="n">
+      <c r="V27" s="87" t="n">
         <v>-0.58</v>
       </c>
-      <c r="V27" s="88" t="n">
+      <c r="W27" s="87" t="n">
         <v>-0.41</v>
       </c>
-      <c r="W27" s="88" t="n">
+      <c r="X27" s="87" t="n">
         <v>-1.02</v>
       </c>
-      <c r="X27" s="88" t="n">
+      <c r="Y27" s="87" t="n">
         <v>-2.2</v>
       </c>
-      <c r="Y27" s="88" t="n">
+      <c r="Z27" s="87" t="n">
         <v>-1.3</v>
       </c>
-      <c r="Z27" s="88" t="n">
+      <c r="AA27" s="87" t="n">
         <v>-1.66</v>
       </c>
-      <c r="AA27" s="88" t="n">
+      <c r="AB27" s="87" t="n">
         <v>-1.96</v>
       </c>
-      <c r="AB27" s="88" t="n">
+      <c r="AC27" s="87" t="n">
         <v>-2.03</v>
       </c>
-      <c r="AC27" s="88" t="n">
+      <c r="AD27" s="87" t="n">
         <v>-1.31</v>
       </c>
-      <c r="AD27" s="88" t="n">
+      <c r="AE27" s="87" t="n">
         <v>-1.91</v>
-      </c>
-      <c r="AE27" s="88" t="n">
-        <v>-2.42</v>
       </c>
     </row>
     <row r="28">
@@ -4176,95 +4175,95 @@
           <t>奇货股指(qhkch)</t>
         </is>
       </c>
-      <c r="B28" s="86" t="n">
+      <c r="B28" s="85" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C28" s="85" t="n">
         <v>2996</v>
       </c>
-      <c r="C28" s="86" t="n">
+      <c r="D28" s="85" t="n">
         <v>3217</v>
       </c>
-      <c r="D28" s="86" t="n">
+      <c r="E28" s="85" t="n">
         <v>3100</v>
       </c>
-      <c r="E28" s="86" t="n">
+      <c r="F28" s="85" t="n">
         <v>2851</v>
       </c>
-      <c r="F28" s="86" t="n">
+      <c r="G28" s="85" t="n">
         <v>2646</v>
       </c>
-      <c r="G28" s="86" t="n">
+      <c r="H28" s="85" t="n">
         <v>2505</v>
       </c>
-      <c r="H28" s="86" t="n">
+      <c r="I28" s="85" t="n">
         <v>2483</v>
       </c>
-      <c r="I28" s="86" t="n">
+      <c r="J28" s="85" t="n">
         <v>2363</v>
       </c>
-      <c r="J28" s="86" t="n">
+      <c r="K28" s="85" t="n">
         <v>2355</v>
       </c>
-      <c r="K28" s="86" t="n">
+      <c r="L28" s="85" t="n">
         <v>2365</v>
       </c>
-      <c r="L28" s="86" t="n">
+      <c r="M28" s="85" t="n">
         <v>2330</v>
       </c>
-      <c r="M28" s="86" t="n">
+      <c r="N28" s="85" t="n">
         <v>2328</v>
       </c>
-      <c r="N28" s="86" t="n">
+      <c r="O28" s="85" t="n">
         <v>2349</v>
       </c>
-      <c r="O28" s="86" t="n">
+      <c r="P28" s="85" t="n">
         <v>2354</v>
       </c>
-      <c r="P28" s="86" t="n">
+      <c r="Q28" s="85" t="n">
         <v>2355</v>
       </c>
-      <c r="Q28" s="86" t="n">
+      <c r="R28" s="85" t="n">
         <v>2353</v>
       </c>
-      <c r="R28" s="86" t="n">
+      <c r="S28" s="85" t="n">
         <v>2375</v>
       </c>
-      <c r="S28" s="86" t="n">
+      <c r="T28" s="85" t="n">
         <v>2407</v>
       </c>
-      <c r="T28" s="86" t="n">
+      <c r="U28" s="85" t="n">
         <v>2395</v>
       </c>
-      <c r="U28" s="86" t="n">
+      <c r="V28" s="85" t="n">
         <v>2404</v>
       </c>
-      <c r="V28" s="86" t="n">
+      <c r="W28" s="85" t="n">
         <v>2392</v>
       </c>
-      <c r="W28" s="86" t="n">
+      <c r="X28" s="85" t="n">
         <v>2443</v>
       </c>
-      <c r="X28" s="86" t="n">
+      <c r="Y28" s="85" t="n">
         <v>2401</v>
       </c>
-      <c r="Y28" s="86" t="n">
+      <c r="Z28" s="85" t="n">
         <v>2379</v>
       </c>
-      <c r="Z28" s="86" t="n">
+      <c r="AA28" s="85" t="n">
         <v>2384</v>
       </c>
-      <c r="AA28" s="86" t="n">
+      <c r="AB28" s="85" t="n">
         <v>2403</v>
       </c>
-      <c r="AB28" s="86" t="n">
+      <c r="AC28" s="85" t="n">
         <v>2400</v>
       </c>
-      <c r="AC28" s="86" t="n">
+      <c r="AD28" s="85" t="n">
         <v>2392</v>
       </c>
-      <c r="AD28" s="86" t="n">
+      <c r="AE28" s="85" t="n">
         <v>2412</v>
-      </c>
-      <c r="AE28" s="86" t="n">
-        <v>2417</v>
       </c>
     </row>
     <row r="29">
@@ -4273,95 +4272,95 @@
           <t>股指持仓市值(亿)</t>
         </is>
       </c>
-      <c r="B29" s="86" t="n">
+      <c r="B29" s="85" t="n">
+        <v>18188.38</v>
+      </c>
+      <c r="C29" s="85" t="n">
         <v>18196.08</v>
       </c>
-      <c r="C29" s="86" t="n">
+      <c r="D29" s="85" t="n">
         <v>18342.9</v>
       </c>
-      <c r="D29" s="86" t="n">
+      <c r="E29" s="85" t="n">
         <v>17606.93</v>
       </c>
-      <c r="E29" s="86" t="n">
+      <c r="F29" s="85" t="n">
         <v>15998.63</v>
       </c>
-      <c r="F29" s="86" t="n">
+      <c r="G29" s="85" t="n">
         <v>14768.14</v>
       </c>
-      <c r="G29" s="86" t="n">
+      <c r="H29" s="85" t="n">
         <v>13526.64</v>
       </c>
-      <c r="H29" s="86" t="n">
+      <c r="I29" s="85" t="n">
         <v>13800.9</v>
       </c>
-      <c r="I29" s="86" t="n">
+      <c r="J29" s="85" t="n">
         <v>11544.58</v>
       </c>
-      <c r="J29" s="86" t="n">
+      <c r="K29" s="85" t="n">
         <v>11616.2</v>
       </c>
-      <c r="K29" s="86" t="n">
+      <c r="L29" s="85" t="n">
         <v>13089.88</v>
       </c>
-      <c r="L29" s="86" t="n">
+      <c r="M29" s="85" t="n">
         <v>12465.83</v>
       </c>
-      <c r="M29" s="86" t="n">
+      <c r="N29" s="85" t="n">
         <v>11938.76</v>
       </c>
-      <c r="N29" s="86" t="n">
+      <c r="O29" s="85" t="n">
         <v>12054.01</v>
       </c>
-      <c r="O29" s="86" t="n">
+      <c r="P29" s="85" t="n">
         <v>11859.62</v>
       </c>
-      <c r="P29" s="86" t="n">
+      <c r="Q29" s="85" t="n">
         <v>12309.48</v>
       </c>
-      <c r="Q29" s="86" t="n">
+      <c r="R29" s="85" t="n">
         <v>11892.59</v>
       </c>
-      <c r="R29" s="86" t="n">
+      <c r="S29" s="85" t="n">
         <v>11776.47</v>
       </c>
-      <c r="S29" s="86" t="n">
+      <c r="T29" s="85" t="n">
         <v>11675.78</v>
       </c>
-      <c r="T29" s="86" t="n">
+      <c r="U29" s="85" t="n">
         <v>11602.92</v>
       </c>
-      <c r="U29" s="86" t="n">
+      <c r="V29" s="85" t="n">
         <v>11818.73</v>
       </c>
-      <c r="V29" s="86" t="n">
+      <c r="W29" s="85" t="n">
         <v>11478</v>
       </c>
-      <c r="W29" s="86" t="n">
+      <c r="X29" s="85" t="n">
         <v>12471.49</v>
       </c>
-      <c r="X29" s="86" t="n">
+      <c r="Y29" s="85" t="n">
         <v>11718.02</v>
       </c>
-      <c r="Y29" s="86" t="n">
+      <c r="Z29" s="85" t="n">
         <v>11315.57</v>
       </c>
-      <c r="Z29" s="86" t="n">
+      <c r="AA29" s="85" t="n">
         <v>11020.76</v>
       </c>
-      <c r="AA29" s="86" t="n">
+      <c r="AB29" s="85" t="n">
         <v>11193.66</v>
       </c>
-      <c r="AB29" s="86" t="n">
+      <c r="AC29" s="85" t="n">
         <v>11195.74</v>
       </c>
-      <c r="AC29" s="86" t="n">
+      <c r="AD29" s="85" t="n">
         <v>11410.71</v>
       </c>
-      <c r="AD29" s="86" t="n">
+      <c r="AE29" s="85" t="n">
         <v>11122.46</v>
-      </c>
-      <c r="AE29" s="86" t="n">
-        <v>11439.39</v>
       </c>
     </row>
     <row r="30">
@@ -4370,95 +4369,95 @@
           <t>多空比</t>
         </is>
       </c>
-      <c r="B30" s="90" t="n">
+      <c r="B30" s="89" t="n">
+        <v>46.19</v>
+      </c>
+      <c r="C30" s="89" t="n">
         <v>46.16</v>
       </c>
-      <c r="C30" s="90" t="n">
+      <c r="D30" s="89" t="n">
         <v>45.91</v>
       </c>
-      <c r="D30" s="90" t="n">
+      <c r="E30" s="89" t="n">
         <v>46.49</v>
       </c>
-      <c r="E30" s="90" t="n">
+      <c r="F30" s="89" t="n">
         <v>46.8</v>
       </c>
-      <c r="F30" s="90" t="n">
+      <c r="G30" s="89" t="n">
         <v>46.99</v>
       </c>
-      <c r="G30" s="90" t="n">
+      <c r="H30" s="89" t="n">
         <v>47.26</v>
       </c>
-      <c r="H30" s="90" t="n">
+      <c r="I30" s="89" t="n">
         <v>47.47</v>
       </c>
-      <c r="I30" s="90" t="n">
+      <c r="J30" s="89" t="n">
         <v>47.52</v>
       </c>
-      <c r="J30" s="90" t="n">
+      <c r="K30" s="89" t="n">
         <v>47.5</v>
       </c>
-      <c r="K30" s="90" t="n">
+      <c r="L30" s="89" t="n">
         <v>47.39</v>
       </c>
-      <c r="L30" s="90" t="n">
+      <c r="M30" s="89" t="n">
         <v>47.54</v>
       </c>
-      <c r="M30" s="90" t="n">
+      <c r="N30" s="89" t="n">
         <v>47.31</v>
       </c>
-      <c r="N30" s="90" t="n">
+      <c r="O30" s="89" t="n">
         <v>47.24</v>
       </c>
-      <c r="O30" s="90" t="n">
+      <c r="P30" s="89" t="n">
         <v>47.26</v>
       </c>
-      <c r="P30" s="90" t="n">
+      <c r="Q30" s="89" t="n">
         <v>47.5</v>
       </c>
-      <c r="Q30" s="90" t="n">
+      <c r="R30" s="89" t="n">
         <v>47.4</v>
       </c>
-      <c r="R30" s="90" t="n">
+      <c r="S30" s="89" t="n">
         <v>47.44</v>
       </c>
-      <c r="S30" s="90" t="n">
+      <c r="T30" s="89" t="n">
         <v>47.35</v>
       </c>
-      <c r="T30" s="90" t="n">
+      <c r="U30" s="89" t="n">
         <v>47.37</v>
       </c>
-      <c r="U30" s="90" t="n">
+      <c r="V30" s="89" t="n">
         <v>47.36</v>
       </c>
-      <c r="V30" s="90" t="n">
+      <c r="W30" s="89" t="n">
         <v>47.2</v>
       </c>
-      <c r="W30" s="90" t="n">
+      <c r="X30" s="89" t="n">
         <v>47.19</v>
       </c>
-      <c r="X30" s="90" t="n">
+      <c r="Y30" s="89" t="n">
         <v>47.18</v>
       </c>
-      <c r="Y30" s="90" t="n">
+      <c r="Z30" s="89" t="n">
         <v>47.17</v>
       </c>
-      <c r="Z30" s="90" t="n">
+      <c r="AA30" s="89" t="n">
         <v>47.11</v>
       </c>
-      <c r="AA30" s="90" t="n">
+      <c r="AB30" s="89" t="n">
         <v>47.04</v>
       </c>
-      <c r="AB30" s="90" t="n">
+      <c r="AC30" s="89" t="n">
         <v>47.06</v>
       </c>
-      <c r="AC30" s="90" t="n">
+      <c r="AD30" s="89" t="n">
         <v>47.22</v>
       </c>
-      <c r="AD30" s="90" t="n">
+      <c r="AE30" s="89" t="n">
         <v>47.19</v>
-      </c>
-      <c r="AE30" s="90" t="n">
-        <v>47.14</v>
       </c>
     </row>
     <row r="31">
@@ -4467,95 +4466,95 @@
           <t>多空差(亿)</t>
         </is>
       </c>
-      <c r="B31" s="86" t="n">
+      <c r="B31" s="85" t="n">
+        <v>-1385.94</v>
+      </c>
+      <c r="C31" s="85" t="n">
         <v>-1398.16</v>
       </c>
-      <c r="C31" s="86" t="n">
+      <c r="D31" s="85" t="n">
         <v>-1500.31</v>
       </c>
-      <c r="D31" s="86" t="n">
+      <c r="E31" s="85" t="n">
         <v>-1237.26</v>
       </c>
-      <c r="E31" s="86" t="n">
+      <c r="F31" s="85" t="n">
         <v>-1024.13</v>
       </c>
-      <c r="F31" s="86" t="n">
+      <c r="G31" s="85" t="n">
         <v>-890.33</v>
       </c>
-      <c r="G31" s="86" t="n">
+      <c r="H31" s="85" t="n">
         <v>-741.6799999999999</v>
       </c>
-      <c r="H31" s="86" t="n">
+      <c r="I31" s="85" t="n">
         <v>-697.09</v>
       </c>
-      <c r="I31" s="86" t="n">
+      <c r="J31" s="85" t="n">
         <v>-571.89</v>
       </c>
-      <c r="J31" s="86" t="n">
+      <c r="K31" s="85" t="n">
         <v>-579.7</v>
       </c>
-      <c r="K31" s="86" t="n">
+      <c r="L31" s="85" t="n">
         <v>-683.6</v>
       </c>
-      <c r="L31" s="86" t="n">
+      <c r="M31" s="85" t="n">
         <v>-612.92</v>
       </c>
-      <c r="M31" s="86" t="n">
+      <c r="N31" s="85" t="n">
         <v>-641.25</v>
       </c>
-      <c r="N31" s="86" t="n">
+      <c r="O31" s="85" t="n">
         <v>-665.05</v>
       </c>
-      <c r="O31" s="86" t="n">
+      <c r="P31" s="85" t="n">
         <v>-650.98</v>
       </c>
-      <c r="P31" s="86" t="n">
+      <c r="Q31" s="85" t="n">
         <v>-615.41</v>
       </c>
-      <c r="Q31" s="86" t="n">
+      <c r="R31" s="85" t="n">
         <v>-618.52</v>
       </c>
-      <c r="R31" s="86" t="n">
+      <c r="S31" s="85" t="n">
         <v>-603.8099999999999</v>
       </c>
-      <c r="S31" s="86" t="n">
+      <c r="T31" s="85" t="n">
         <v>-618.02</v>
       </c>
-      <c r="T31" s="86" t="n">
+      <c r="U31" s="85" t="n">
         <v>-609.3200000000001</v>
       </c>
-      <c r="U31" s="86" t="n">
+      <c r="V31" s="85" t="n">
         <v>-623.89</v>
       </c>
-      <c r="V31" s="86" t="n">
+      <c r="W31" s="85" t="n">
         <v>-641.9299999999999</v>
       </c>
-      <c r="W31" s="86" t="n">
+      <c r="X31" s="85" t="n">
         <v>-700.54</v>
       </c>
-      <c r="X31" s="86" t="n">
+      <c r="Y31" s="85" t="n">
         <v>-661.59</v>
       </c>
-      <c r="Y31" s="86" t="n">
+      <c r="Z31" s="85" t="n">
         <v>-641.1</v>
       </c>
-      <c r="Z31" s="86" t="n">
+      <c r="AA31" s="85" t="n">
         <v>-637.14</v>
       </c>
-      <c r="AA31" s="86" t="n">
+      <c r="AB31" s="85" t="n">
         <v>-663.05</v>
       </c>
-      <c r="AB31" s="86" t="n">
+      <c r="AC31" s="85" t="n">
         <v>-659.14</v>
       </c>
-      <c r="AC31" s="86" t="n">
+      <c r="AD31" s="85" t="n">
         <v>-634.26</v>
       </c>
-      <c r="AD31" s="86" t="n">
+      <c r="AE31" s="85" t="n">
         <v>-625.59</v>
-      </c>
-      <c r="AE31" s="86" t="n">
-        <v>-653.9</v>
       </c>
     </row>
     <row r="32">
@@ -4564,95 +4563,95 @@
           <t>累计净多单</t>
         </is>
       </c>
-      <c r="B32" s="86" t="n">
+      <c r="B32" s="85" t="n">
+        <v>-43535</v>
+      </c>
+      <c r="C32" s="85" t="n">
         <v>-49391</v>
       </c>
-      <c r="C32" s="86" t="n">
+      <c r="D32" s="85" t="n">
         <v>-59269</v>
       </c>
-      <c r="D32" s="86" t="n">
+      <c r="E32" s="85" t="n">
         <v>-36222</v>
       </c>
-      <c r="E32" s="86" t="n">
+      <c r="F32" s="85" t="n">
         <v>-42709</v>
       </c>
-      <c r="F32" s="86" t="n">
+      <c r="G32" s="85" t="n">
         <v>-39170</v>
       </c>
-      <c r="G32" s="86" t="n">
+      <c r="H32" s="85" t="n">
         <v>-25624</v>
       </c>
-      <c r="H32" s="86" t="n">
+      <c r="I32" s="85" t="n">
         <v>-27286</v>
       </c>
-      <c r="I32" s="86" t="n">
+      <c r="J32" s="85" t="n">
         <v>-15398</v>
       </c>
-      <c r="J32" s="86" t="n">
+      <c r="K32" s="85" t="n">
         <v>-19443</v>
       </c>
-      <c r="K32" s="86" t="n">
+      <c r="L32" s="85" t="n">
         <v>-32280</v>
       </c>
-      <c r="L32" s="86" t="n">
+      <c r="M32" s="85" t="n">
         <v>-23022</v>
       </c>
-      <c r="M32" s="86" t="n">
+      <c r="N32" s="85" t="n">
         <v>-25189</v>
       </c>
-      <c r="N32" s="86" t="n">
+      <c r="O32" s="85" t="n">
         <v>-28419</v>
       </c>
-      <c r="O32" s="86" t="n">
+      <c r="P32" s="85" t="n">
         <v>-28410</v>
       </c>
-      <c r="P32" s="86" t="n">
+      <c r="Q32" s="85" t="n">
         <v>-26045</v>
       </c>
-      <c r="Q32" s="86" t="n">
+      <c r="R32" s="85" t="n">
         <v>-25973</v>
       </c>
-      <c r="R32" s="86" t="n">
+      <c r="S32" s="85" t="n">
         <v>-22401</v>
       </c>
-      <c r="S32" s="86" t="n">
+      <c r="T32" s="85" t="n">
         <v>-25659</v>
       </c>
-      <c r="T32" s="86" t="n">
+      <c r="U32" s="85" t="n">
         <v>-23596</v>
       </c>
-      <c r="U32" s="86" t="n">
+      <c r="V32" s="85" t="n">
         <v>-25748</v>
       </c>
-      <c r="V32" s="86" t="n">
+      <c r="W32" s="85" t="n">
         <v>-21620</v>
       </c>
-      <c r="W32" s="86" t="n">
+      <c r="X32" s="85" t="n">
         <v>-24563</v>
       </c>
-      <c r="X32" s="86" t="n">
+      <c r="Y32" s="85" t="n">
         <v>-34543</v>
       </c>
-      <c r="Y32" s="86" t="n">
+      <c r="Z32" s="85" t="n">
         <v>-26728</v>
       </c>
-      <c r="Z32" s="86" t="n">
+      <c r="AA32" s="85" t="n">
         <v>-25843</v>
       </c>
-      <c r="AA32" s="86" t="n">
+      <c r="AB32" s="85" t="n">
         <v>-30256</v>
       </c>
-      <c r="AB32" s="86" t="n">
+      <c r="AC32" s="85" t="n">
         <v>-25652</v>
       </c>
-      <c r="AC32" s="86" t="n">
+      <c r="AD32" s="85" t="n">
         <v>-19237</v>
       </c>
-      <c r="AD32" s="86" t="n">
+      <c r="AE32" s="85" t="n">
         <v>-25229</v>
-      </c>
-      <c r="AE32" s="86" t="n">
-        <v>-26744</v>
       </c>
     </row>
     <row r="33">
@@ -4661,95 +4660,95 @@
           <t>当月净多单</t>
         </is>
       </c>
-      <c r="B33" s="86" t="n">
+      <c r="B33" s="85" t="n">
+        <v>3538</v>
+      </c>
+      <c r="C33" s="85" t="n">
         <v>-547</v>
       </c>
-      <c r="C33" s="86" t="n">
+      <c r="D33" s="85" t="n">
         <v>1649</v>
       </c>
-      <c r="D33" s="86" t="n">
+      <c r="E33" s="85" t="n">
         <v>5979</v>
       </c>
-      <c r="E33" s="86" t="n">
+      <c r="F33" s="85" t="n">
         <v>1547</v>
       </c>
-      <c r="F33" s="86" t="n">
+      <c r="G33" s="85" t="n">
         <v>703</v>
       </c>
-      <c r="G33" s="86" t="n">
+      <c r="H33" s="85" t="n">
         <v>7134</v>
       </c>
-      <c r="H33" s="86" t="n">
+      <c r="I33" s="85" t="n">
         <v>6476</v>
       </c>
-      <c r="I33" s="86" t="n">
+      <c r="J33" s="85" t="n">
         <v>13199</v>
       </c>
-      <c r="J33" s="86" t="n">
+      <c r="K33" s="85" t="n">
         <v>12591</v>
       </c>
-      <c r="K33" s="86" t="n">
+      <c r="L33" s="85" t="n">
         <v>9543</v>
       </c>
-      <c r="L33" s="86" t="n">
+      <c r="M33" s="85" t="n">
         <v>10679</v>
       </c>
-      <c r="M33" s="86" t="n">
+      <c r="N33" s="85" t="n">
         <v>7507</v>
       </c>
-      <c r="N33" s="86" t="n">
+      <c r="O33" s="85" t="n">
         <v>-878</v>
       </c>
-      <c r="O33" s="86" t="n">
+      <c r="P33" s="85" t="n">
         <v>100</v>
       </c>
-      <c r="P33" s="86" t="n">
+      <c r="Q33" s="85" t="n">
         <v>-1402</v>
       </c>
-      <c r="Q33" s="86" t="n">
+      <c r="R33" s="85" t="n">
         <v>-34</v>
       </c>
-      <c r="R33" s="86" t="n">
+      <c r="S33" s="85" t="n">
         <v>-2376</v>
       </c>
-      <c r="S33" s="86" t="n">
+      <c r="T33" s="85" t="n">
         <v>-2051</v>
       </c>
-      <c r="T33" s="86" t="n">
+      <c r="U33" s="85" t="n">
         <v>-1952</v>
       </c>
-      <c r="U33" s="86" t="n">
+      <c r="V33" s="85" t="n">
         <v>-3278</v>
       </c>
-      <c r="V33" s="86" t="n">
+      <c r="W33" s="85" t="n">
         <v>-2459</v>
       </c>
-      <c r="W33" s="86" t="n">
+      <c r="X33" s="85" t="n">
         <v>-1710</v>
       </c>
-      <c r="X33" s="86" t="n">
+      <c r="Y33" s="85" t="n">
         <v>-6016</v>
       </c>
-      <c r="Y33" s="86" t="n">
+      <c r="Z33" s="85" t="n">
         <v>-3908</v>
       </c>
-      <c r="Z33" s="86" t="n">
+      <c r="AA33" s="85" t="n">
         <v>-2374</v>
       </c>
-      <c r="AA33" s="86" t="n">
+      <c r="AB33" s="85" t="n">
         <v>-4680</v>
       </c>
-      <c r="AB33" s="86" t="n">
+      <c r="AC33" s="85" t="n">
         <v>-5784</v>
       </c>
-      <c r="AC33" s="86" t="n">
+      <c r="AD33" s="85" t="n">
         <v>-4660</v>
       </c>
-      <c r="AD33" s="86" t="n">
+      <c r="AE33" s="85" t="n">
         <v>-6865</v>
-      </c>
-      <c r="AE33" s="86" t="n">
-        <v>-8722</v>
       </c>
     </row>
     <row r="34">
@@ -4758,95 +4757,95 @@
           <t>沪深300累计多单</t>
         </is>
       </c>
-      <c r="B34" s="86" t="n">
+      <c r="B34" s="85" t="n">
+        <v>-31243</v>
+      </c>
+      <c r="C34" s="85" t="n">
         <v>-33151</v>
       </c>
-      <c r="C34" s="86" t="n">
+      <c r="D34" s="85" t="n">
         <v>-31667</v>
       </c>
-      <c r="D34" s="86" t="n">
+      <c r="E34" s="85" t="n">
         <v>-30115</v>
       </c>
-      <c r="E34" s="86" t="n">
+      <c r="F34" s="85" t="n">
         <v>-27126</v>
       </c>
-      <c r="F34" s="86" t="n">
+      <c r="G34" s="85" t="n">
         <v>-28243</v>
       </c>
-      <c r="G34" s="86" t="n">
+      <c r="H34" s="85" t="n">
         <v>-19887</v>
       </c>
-      <c r="H34" s="86" t="n">
+      <c r="I34" s="85" t="n">
         <v>-21792</v>
       </c>
-      <c r="I34" s="86" t="n">
+      <c r="J34" s="85" t="n">
         <v>-16942</v>
       </c>
-      <c r="J34" s="86" t="n">
+      <c r="K34" s="85" t="n">
         <v>-18355</v>
       </c>
-      <c r="K34" s="86" t="n">
+      <c r="L34" s="85" t="n">
         <v>-21603</v>
       </c>
-      <c r="L34" s="86" t="n">
+      <c r="M34" s="85" t="n">
         <v>-20550</v>
       </c>
-      <c r="M34" s="86" t="n">
+      <c r="N34" s="85" t="n">
         <v>-21729</v>
       </c>
-      <c r="N34" s="86" t="n">
+      <c r="O34" s="85" t="n">
         <v>-22380</v>
       </c>
-      <c r="O34" s="86" t="n">
+      <c r="P34" s="85" t="n">
         <v>-21704</v>
       </c>
-      <c r="P34" s="86" t="n">
+      <c r="Q34" s="85" t="n">
         <v>-19910</v>
       </c>
-      <c r="Q34" s="86" t="n">
+      <c r="R34" s="85" t="n">
         <v>-20729</v>
       </c>
-      <c r="R34" s="86" t="n">
+      <c r="S34" s="85" t="n">
         <v>-22784</v>
       </c>
-      <c r="S34" s="86" t="n">
+      <c r="T34" s="85" t="n">
         <v>-22366</v>
       </c>
-      <c r="T34" s="86" t="n">
+      <c r="U34" s="85" t="n">
         <v>-21405</v>
       </c>
-      <c r="U34" s="86" t="n">
+      <c r="V34" s="85" t="n">
         <v>-23401</v>
       </c>
-      <c r="V34" s="86" t="n">
+      <c r="W34" s="85" t="n">
         <v>-23495</v>
       </c>
-      <c r="W34" s="86" t="n">
+      <c r="X34" s="85" t="n">
         <v>-24752</v>
       </c>
-      <c r="X34" s="86" t="n">
+      <c r="Y34" s="85" t="n">
         <v>-29112</v>
       </c>
-      <c r="Y34" s="86" t="n">
+      <c r="Z34" s="85" t="n">
         <v>-27546</v>
       </c>
-      <c r="Z34" s="86" t="n">
+      <c r="AA34" s="85" t="n">
         <v>-28104</v>
       </c>
-      <c r="AA34" s="86" t="n">
+      <c r="AB34" s="85" t="n">
         <v>-29738</v>
       </c>
-      <c r="AB34" s="86" t="n">
+      <c r="AC34" s="85" t="n">
         <v>-28980</v>
       </c>
-      <c r="AC34" s="86" t="n">
+      <c r="AD34" s="85" t="n">
         <v>-26883</v>
       </c>
-      <c r="AD34" s="86" t="n">
+      <c r="AE34" s="85" t="n">
         <v>-25603</v>
-      </c>
-      <c r="AE34" s="86" t="n">
-        <v>-27262</v>
       </c>
     </row>
     <row r="35">
@@ -4855,95 +4854,95 @@
           <t>沪深300当月多单</t>
         </is>
       </c>
-      <c r="B35" s="86" t="n">
+      <c r="B35" s="85" t="n">
+        <v>-2950</v>
+      </c>
+      <c r="C35" s="85" t="n">
         <v>-4593</v>
       </c>
-      <c r="C35" s="86" t="n">
+      <c r="D35" s="85" t="n">
         <v>-3500</v>
       </c>
-      <c r="D35" s="86" t="n">
+      <c r="E35" s="85" t="n">
         <v>-7128</v>
       </c>
-      <c r="E35" s="86" t="n">
+      <c r="F35" s="85" t="n">
         <v>-7781</v>
       </c>
-      <c r="F35" s="86" t="n">
+      <c r="G35" s="85" t="n">
         <v>-8727</v>
       </c>
-      <c r="G35" s="86" t="n">
+      <c r="H35" s="85" t="n">
         <v>-6282</v>
       </c>
-      <c r="H35" s="86" t="n">
+      <c r="I35" s="85" t="n">
         <v>-6639</v>
       </c>
-      <c r="I35" s="86" t="n">
+      <c r="J35" s="85" t="n">
         <v>-3532</v>
       </c>
-      <c r="J35" s="86" t="n">
+      <c r="K35" s="85" t="n">
         <v>-2293</v>
       </c>
-      <c r="K35" s="86" t="n">
+      <c r="L35" s="85" t="n">
         <v>-4574</v>
       </c>
-      <c r="L35" s="86" t="n">
+      <c r="M35" s="85" t="n">
         <v>-2414</v>
       </c>
-      <c r="M35" s="86" t="n">
+      <c r="N35" s="85" t="n">
         <v>-2494</v>
       </c>
-      <c r="N35" s="86" t="n">
+      <c r="O35" s="85" t="n">
         <v>-6478</v>
       </c>
-      <c r="O35" s="86" t="n">
+      <c r="P35" s="85" t="n">
         <v>-3961</v>
       </c>
-      <c r="P35" s="86" t="n">
+      <c r="Q35" s="85" t="n">
         <v>-7065</v>
       </c>
-      <c r="Q35" s="86" t="n">
+      <c r="R35" s="85" t="n">
         <v>-5691</v>
       </c>
-      <c r="R35" s="86" t="n">
+      <c r="S35" s="85" t="n">
         <v>-8542</v>
       </c>
-      <c r="S35" s="86" t="n">
+      <c r="T35" s="85" t="n">
         <v>-8285</v>
       </c>
-      <c r="T35" s="86" t="n">
+      <c r="U35" s="85" t="n">
         <v>-10101</v>
       </c>
-      <c r="U35" s="86" t="n">
+      <c r="V35" s="85" t="n">
         <v>-10429</v>
       </c>
-      <c r="V35" s="86" t="n">
+      <c r="W35" s="85" t="n">
         <v>-12108</v>
       </c>
-      <c r="W35" s="86" t="n">
+      <c r="X35" s="85" t="n">
         <v>-12524</v>
       </c>
-      <c r="X35" s="86" t="n">
+      <c r="Y35" s="85" t="n">
         <v>-13507</v>
       </c>
-      <c r="Y35" s="86" t="n">
+      <c r="Z35" s="85" t="n">
         <v>-12337</v>
       </c>
-      <c r="Z35" s="86" t="n">
+      <c r="AA35" s="85" t="n">
         <v>-14270</v>
       </c>
-      <c r="AA35" s="86" t="n">
+      <c r="AB35" s="85" t="n">
         <v>-15565</v>
       </c>
-      <c r="AB35" s="86" t="n">
+      <c r="AC35" s="85" t="n">
         <v>-15217</v>
       </c>
-      <c r="AC35" s="86" t="n">
+      <c r="AD35" s="85" t="n">
         <v>-13494</v>
       </c>
-      <c r="AD35" s="86" t="n">
+      <c r="AE35" s="85" t="n">
         <v>-13870</v>
-      </c>
-      <c r="AE35" s="86" t="n">
-        <v>-14538</v>
       </c>
     </row>
     <row r="36">
@@ -4952,95 +4951,95 @@
           <t>当月净空单</t>
         </is>
       </c>
-      <c r="B36" s="86" t="n">
+      <c r="B36" s="85" t="n">
+        <v>30252</v>
+      </c>
+      <c r="C36" s="85" t="n">
         <v>30833</v>
       </c>
-      <c r="C36" s="86" t="n">
+      <c r="D36" s="85" t="n">
         <v>34266</v>
       </c>
-      <c r="D36" s="86" t="n">
+      <c r="E36" s="85" t="n">
         <v>44758</v>
       </c>
-      <c r="E36" s="86" t="n">
+      <c r="F36" s="85" t="n">
         <v>46864</v>
       </c>
-      <c r="F36" s="86" t="n">
+      <c r="G36" s="85" t="n">
         <v>52065</v>
       </c>
-      <c r="G36" s="86" t="n">
+      <c r="H36" s="85" t="n">
         <v>44830</v>
       </c>
-      <c r="H36" s="86" t="n">
+      <c r="I36" s="85" t="n">
         <v>44611</v>
       </c>
-      <c r="I36" s="86" t="n">
+      <c r="J36" s="85" t="n">
         <v>43465</v>
       </c>
-      <c r="J36" s="86" t="n">
+      <c r="K36" s="85" t="n">
         <v>43814</v>
       </c>
-      <c r="K36" s="86" t="n">
+      <c r="L36" s="85" t="n">
         <v>41323</v>
       </c>
-      <c r="L36" s="86" t="n">
+      <c r="M36" s="85" t="n">
         <v>33152</v>
       </c>
-      <c r="M36" s="86" t="n">
+      <c r="N36" s="85" t="n">
         <v>45049</v>
       </c>
-      <c r="N36" s="86" t="n">
+      <c r="O36" s="85" t="n">
         <v>51475</v>
       </c>
-      <c r="O36" s="86" t="n">
+      <c r="P36" s="85" t="n">
         <v>58550</v>
       </c>
-      <c r="P36" s="86" t="n">
+      <c r="Q36" s="85" t="n">
         <v>59882</v>
       </c>
-      <c r="Q36" s="86" t="n">
+      <c r="R36" s="85" t="n">
         <v>62552</v>
       </c>
-      <c r="R36" s="86" t="n">
+      <c r="S36" s="85" t="n">
         <v>60880</v>
       </c>
-      <c r="S36" s="86" t="n">
+      <c r="T36" s="85" t="n">
         <v>65490</v>
       </c>
-      <c r="T36" s="86" t="n">
+      <c r="U36" s="85" t="n">
         <v>71195</v>
       </c>
-      <c r="U36" s="86" t="n">
+      <c r="V36" s="85" t="n">
         <v>72587</v>
       </c>
-      <c r="V36" s="86" t="n">
+      <c r="W36" s="85" t="n">
         <v>77242</v>
       </c>
-      <c r="W36" s="86" t="n">
+      <c r="X36" s="85" t="n">
         <v>86343</v>
       </c>
-      <c r="X36" s="86" t="n">
+      <c r="Y36" s="85" t="n">
         <v>82858</v>
       </c>
-      <c r="Y36" s="86" t="n">
+      <c r="Z36" s="85" t="n">
         <v>86384</v>
       </c>
-      <c r="Z36" s="86" t="n">
+      <c r="AA36" s="85" t="n">
         <v>87972</v>
       </c>
-      <c r="AA36" s="86" t="n">
+      <c r="AB36" s="85" t="n">
         <v>91967</v>
       </c>
-      <c r="AB36" s="86" t="n">
+      <c r="AC36" s="85" t="n">
         <v>94221</v>
       </c>
-      <c r="AC36" s="86" t="n">
+      <c r="AD36" s="85" t="n">
         <v>93650</v>
       </c>
-      <c r="AD36" s="86" t="n">
+      <c r="AE36" s="85" t="n">
         <v>90571</v>
-      </c>
-      <c r="AE36" s="86" t="n">
-        <v>94170</v>
       </c>
     </row>
     <row r="37">
@@ -5049,95 +5048,95 @@
           <t>累计净空单</t>
         </is>
       </c>
-      <c r="B37" s="86" t="n">
+      <c r="B37" s="85" t="n">
+        <v>173289</v>
+      </c>
+      <c r="C37" s="85" t="n">
         <v>174408</v>
       </c>
-      <c r="C37" s="86" t="n">
+      <c r="D37" s="85" t="n">
         <v>173363</v>
       </c>
-      <c r="D37" s="86" t="n">
+      <c r="E37" s="85" t="n">
         <v>152297</v>
       </c>
-      <c r="E37" s="86" t="n">
+      <c r="F37" s="85" t="n">
         <v>149831</v>
       </c>
-      <c r="F37" s="86" t="n">
+      <c r="G37" s="85" t="n">
         <v>138990</v>
       </c>
-      <c r="G37" s="86" t="n">
+      <c r="H37" s="85" t="n">
         <v>124265</v>
       </c>
-      <c r="H37" s="86" t="n">
+      <c r="I37" s="85" t="n">
         <v>129855</v>
       </c>
-      <c r="I37" s="86" t="n">
+      <c r="J37" s="85" t="n">
         <v>121593</v>
       </c>
-      <c r="J37" s="86" t="n">
+      <c r="K37" s="85" t="n">
         <v>126065</v>
       </c>
-      <c r="K37" s="86" t="n">
+      <c r="L37" s="85" t="n">
         <v>114091</v>
       </c>
-      <c r="L37" s="86" t="n">
+      <c r="M37" s="85" t="n">
         <v>120465</v>
       </c>
-      <c r="M37" s="86" t="n">
+      <c r="N37" s="85" t="n">
         <v>124864</v>
       </c>
-      <c r="N37" s="86" t="n">
+      <c r="O37" s="85" t="n">
         <v>129844</v>
       </c>
-      <c r="O37" s="86" t="n">
+      <c r="P37" s="85" t="n">
         <v>125285</v>
       </c>
-      <c r="P37" s="86" t="n">
+      <c r="Q37" s="85" t="n">
         <v>124136</v>
       </c>
-      <c r="Q37" s="86" t="n">
+      <c r="R37" s="85" t="n">
         <v>115543</v>
       </c>
-      <c r="R37" s="86" t="n">
+      <c r="S37" s="85" t="n">
         <v>107325</v>
       </c>
-      <c r="S37" s="86" t="n">
+      <c r="T37" s="85" t="n">
         <v>111789</v>
       </c>
-      <c r="T37" s="86" t="n">
+      <c r="U37" s="85" t="n">
         <v>108003</v>
       </c>
-      <c r="U37" s="86" t="n">
+      <c r="V37" s="85" t="n">
         <v>110293</v>
       </c>
-      <c r="V37" s="86" t="n">
+      <c r="W37" s="85" t="n">
         <v>122598</v>
       </c>
-      <c r="W37" s="86" t="n">
+      <c r="X37" s="85" t="n">
         <v>135319</v>
       </c>
-      <c r="X37" s="86" t="n">
+      <c r="Y37" s="85" t="n">
         <v>121088</v>
       </c>
-      <c r="Y37" s="86" t="n">
+      <c r="Z37" s="85" t="n">
         <v>129278</v>
       </c>
-      <c r="Z37" s="86" t="n">
+      <c r="AA37" s="85" t="n">
         <v>129820</v>
       </c>
-      <c r="AA37" s="86" t="n">
+      <c r="AB37" s="85" t="n">
         <v>127965</v>
       </c>
-      <c r="AB37" s="86" t="n">
+      <c r="AC37" s="85" t="n">
         <v>129270</v>
       </c>
-      <c r="AC37" s="86" t="n">
+      <c r="AD37" s="85" t="n">
         <v>128809</v>
       </c>
-      <c r="AD37" s="86" t="n">
+      <c r="AE37" s="85" t="n">
         <v>122462</v>
-      </c>
-      <c r="AE37" s="86" t="n">
-        <v>128844</v>
       </c>
     </row>
     <row r="38">
@@ -5146,95 +5145,95 @@
           <t>沪深300累计空单</t>
         </is>
       </c>
-      <c r="B38" s="86" t="n">
+      <c r="B38" s="85" t="n">
+        <v>66830</v>
+      </c>
+      <c r="C38" s="85" t="n">
         <v>70900</v>
       </c>
-      <c r="C38" s="86" t="n">
+      <c r="D38" s="85" t="n">
         <v>68886</v>
       </c>
-      <c r="D38" s="86" t="n">
+      <c r="E38" s="85" t="n">
         <v>64718</v>
       </c>
-      <c r="E38" s="86" t="n">
+      <c r="F38" s="85" t="n">
         <v>59845</v>
       </c>
-      <c r="F38" s="86" t="n">
+      <c r="G38" s="85" t="n">
         <v>57916</v>
       </c>
-      <c r="G38" s="86" t="n">
+      <c r="H38" s="85" t="n">
         <v>54008</v>
       </c>
-      <c r="H38" s="86" t="n">
+      <c r="I38" s="85" t="n">
         <v>52754</v>
       </c>
-      <c r="I38" s="86" t="n">
+      <c r="J38" s="85" t="n">
         <v>49457</v>
       </c>
-      <c r="J38" s="86" t="n">
+      <c r="K38" s="85" t="n">
         <v>49214</v>
       </c>
-      <c r="K38" s="86" t="n">
+      <c r="L38" s="85" t="n">
         <v>51881</v>
       </c>
-      <c r="L38" s="86" t="n">
+      <c r="M38" s="85" t="n">
         <v>48370</v>
       </c>
-      <c r="M38" s="86" t="n">
+      <c r="N38" s="85" t="n">
         <v>53900</v>
       </c>
-      <c r="N38" s="86" t="n">
+      <c r="O38" s="85" t="n">
         <v>59063</v>
       </c>
-      <c r="O38" s="86" t="n">
+      <c r="P38" s="85" t="n">
         <v>58132</v>
       </c>
-      <c r="P38" s="86" t="n">
+      <c r="Q38" s="85" t="n">
         <v>57844</v>
       </c>
-      <c r="Q38" s="86" t="n">
+      <c r="R38" s="85" t="n">
         <v>51375</v>
       </c>
-      <c r="R38" s="86" t="n">
+      <c r="S38" s="85" t="n">
         <v>50883</v>
       </c>
-      <c r="S38" s="86" t="n">
+      <c r="T38" s="85" t="n">
         <v>50688</v>
       </c>
-      <c r="T38" s="86" t="n">
+      <c r="U38" s="85" t="n">
         <v>50309</v>
       </c>
-      <c r="U38" s="86" t="n">
+      <c r="V38" s="85" t="n">
         <v>51034</v>
       </c>
-      <c r="V38" s="86" t="n">
+      <c r="W38" s="85" t="n">
         <v>50972</v>
       </c>
-      <c r="W38" s="86" t="n">
+      <c r="X38" s="85" t="n">
         <v>51615</v>
       </c>
-      <c r="X38" s="86" t="n">
+      <c r="Y38" s="85" t="n">
         <v>51739</v>
       </c>
-      <c r="Y38" s="86" t="n">
+      <c r="Z38" s="85" t="n">
         <v>51534</v>
       </c>
-      <c r="Z38" s="86" t="n">
+      <c r="AA38" s="85" t="n">
         <v>50630</v>
       </c>
-      <c r="AA38" s="86" t="n">
+      <c r="AB38" s="85" t="n">
         <v>51651</v>
       </c>
-      <c r="AB38" s="86" t="n">
+      <c r="AC38" s="85" t="n">
         <v>51493</v>
       </c>
-      <c r="AC38" s="86" t="n">
+      <c r="AD38" s="85" t="n">
         <v>52808</v>
       </c>
-      <c r="AD38" s="86" t="n">
+      <c r="AE38" s="85" t="n">
         <v>48360</v>
-      </c>
-      <c r="AE38" s="86" t="n">
-        <v>51975</v>
       </c>
     </row>
     <row r="39">
@@ -5243,108 +5242,108 @@
           <t>沪深300当月空单</t>
         </is>
       </c>
-      <c r="B39" s="86" t="n">
+      <c r="B39" s="85" t="n">
+        <v>9546</v>
+      </c>
+      <c r="C39" s="85" t="n">
         <v>11204</v>
       </c>
-      <c r="C39" s="86" t="n">
+      <c r="D39" s="85" t="n">
         <v>11717</v>
       </c>
-      <c r="D39" s="86" t="n">
+      <c r="E39" s="85" t="n">
         <v>14251</v>
       </c>
-      <c r="E39" s="86" t="n">
+      <c r="F39" s="85" t="n">
         <v>15075</v>
       </c>
-      <c r="F39" s="86" t="n">
+      <c r="G39" s="85" t="n">
         <v>16231</v>
       </c>
-      <c r="G39" s="86" t="n">
+      <c r="H39" s="85" t="n">
         <v>13658</v>
       </c>
-      <c r="H39" s="86" t="n">
+      <c r="I39" s="85" t="n">
         <v>16239</v>
       </c>
-      <c r="I39" s="86" t="n">
+      <c r="J39" s="85" t="n">
         <v>13971</v>
       </c>
-      <c r="J39" s="86" t="n">
+      <c r="K39" s="85" t="n">
         <v>15254</v>
       </c>
-      <c r="K39" s="86" t="n">
+      <c r="L39" s="85" t="n">
         <v>13966</v>
       </c>
-      <c r="L39" s="86" t="n">
+      <c r="M39" s="85" t="n">
         <v>9839</v>
       </c>
-      <c r="M39" s="86" t="n">
+      <c r="N39" s="85" t="n">
         <v>16729</v>
       </c>
-      <c r="N39" s="86" t="n">
+      <c r="O39" s="85" t="n">
         <v>21354</v>
       </c>
-      <c r="O39" s="86" t="n">
+      <c r="P39" s="85" t="n">
         <v>24129</v>
       </c>
-      <c r="P39" s="86" t="n">
+      <c r="Q39" s="85" t="n">
         <v>23841</v>
       </c>
-      <c r="Q39" s="86" t="n">
+      <c r="R39" s="85" t="n">
         <v>25383</v>
       </c>
-      <c r="R39" s="86" t="n">
+      <c r="S39" s="85" t="n">
         <v>28150</v>
       </c>
-      <c r="S39" s="86" t="n">
+      <c r="T39" s="85" t="n">
         <v>29036</v>
       </c>
-      <c r="T39" s="86" t="n">
+      <c r="U39" s="85" t="n">
         <v>29878</v>
       </c>
-      <c r="U39" s="86" t="n">
+      <c r="V39" s="85" t="n">
         <v>31317</v>
       </c>
-      <c r="V39" s="86" t="n">
+      <c r="W39" s="85" t="n">
         <v>31225</v>
       </c>
-      <c r="W39" s="86" t="n">
+      <c r="X39" s="85" t="n">
         <v>32000</v>
       </c>
-      <c r="X39" s="86" t="n">
+      <c r="Y39" s="85" t="n">
         <v>33502</v>
       </c>
-      <c r="Y39" s="86" t="n">
+      <c r="Z39" s="85" t="n">
         <v>33944</v>
       </c>
-      <c r="Z39" s="86" t="n">
+      <c r="AA39" s="85" t="n">
         <v>34381</v>
       </c>
-      <c r="AA39" s="86" t="n">
+      <c r="AB39" s="85" t="n">
         <v>35985</v>
       </c>
-      <c r="AB39" s="86" t="n">
+      <c r="AC39" s="85" t="n">
         <v>35567</v>
       </c>
-      <c r="AC39" s="86" t="n">
+      <c r="AD39" s="85" t="n">
         <v>37588</v>
       </c>
-      <c r="AD39" s="86" t="n">
+      <c r="AE39" s="85" t="n">
         <v>35094</v>
       </c>
-      <c r="AE39" s="86" t="n">
-        <v>35849</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" s="91" t="inlineStr">
+      <c r="A41" s="90" t="inlineStr">
         <is>
           <t>今日买报：</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="91" t="inlineStr">
-        <is>
-          <t>今日卖报：市值交换率(p):3.98&gt;=3.564;主力拉高数:290.0&gt;=213.0</t>
+      <c r="A42" s="90" t="inlineStr">
+        <is>
+          <t>今日卖报：</t>
         </is>
       </c>
     </row>
@@ -11493,13 +11492,13 @@
       <c r="G2" s="36" t="n">
         <v>66</v>
       </c>
-      <c r="H2" s="92" t="n">
+      <c r="H2" s="91" t="n">
         <v>22.3514585</v>
       </c>
       <c r="I2" s="36" t="n">
         <v>7.06</v>
       </c>
-      <c r="J2" s="93">
+      <c r="J2" s="92">
         <f>(1+H2/100)^(1/(YEAR(D2)-YEAR(C2)))-1</f>
         <v/>
       </c>
@@ -11531,13 +11530,13 @@
       <c r="G3" s="39" t="n">
         <v>73</v>
       </c>
-      <c r="H3" s="94" t="n">
+      <c r="H3" s="93" t="n">
         <v>35.0298984</v>
       </c>
       <c r="I3" s="39" t="n">
         <v>11.41</v>
       </c>
-      <c r="J3" s="93">
+      <c r="J3" s="92">
         <f>(1+H3/100)^(1/(YEAR(D3)-YEAR(C3)))-1</f>
         <v/>
       </c>
@@ -11569,13 +11568,13 @@
       <c r="G4" s="39" t="n">
         <v>85</v>
       </c>
-      <c r="H4" s="94" t="n">
+      <c r="H4" s="93" t="n">
         <v>122.4911655</v>
       </c>
       <c r="I4" s="39" t="n">
         <v>76.98</v>
       </c>
-      <c r="J4" s="95">
+      <c r="J4" s="94">
         <f>(1+H4/100)^(1/(YEAR(D4)-YEAR(C4)))-1</f>
         <v/>
       </c>
@@ -11607,13 +11606,13 @@
       <c r="G5" s="39" t="n">
         <v>96</v>
       </c>
-      <c r="H5" s="94" t="n">
+      <c r="H5" s="93" t="n">
         <v>136.13543</v>
       </c>
       <c r="I5" s="39" t="n">
         <v>100.05</v>
       </c>
-      <c r="J5" s="95">
+      <c r="J5" s="94">
         <f>(1+H5/100)^(1/(YEAR(D5)-YEAR(C5)))-1</f>
         <v/>
       </c>
@@ -11645,13 +11644,13 @@
       <c r="G6" s="39" t="n">
         <v>95</v>
       </c>
-      <c r="H6" s="94" t="n">
+      <c r="H6" s="93" t="n">
         <v>95.7546074</v>
       </c>
       <c r="I6" s="39" t="n">
         <v>44.37</v>
       </c>
-      <c r="J6" s="95">
+      <c r="J6" s="94">
         <f>(1+H6/100)^(1/(YEAR(D6)-YEAR(C6)))-1</f>
         <v/>
       </c>
@@ -11683,13 +11682,13 @@
       <c r="G7" s="39" t="n">
         <v>86</v>
       </c>
-      <c r="H7" s="94" t="n">
+      <c r="H7" s="93" t="n">
         <v>123.8525927</v>
       </c>
       <c r="I7" s="39" t="n">
         <v>63.41</v>
       </c>
-      <c r="J7" s="95">
+      <c r="J7" s="94">
         <f>(1+H7/100)^(1/(YEAR(D7)-YEAR(C7)))-1</f>
         <v/>
       </c>
@@ -11721,13 +11720,13 @@
       <c r="G8" s="39" t="n">
         <v>87</v>
       </c>
-      <c r="H8" s="94" t="n">
+      <c r="H8" s="93" t="n">
         <v>81.41461922000001</v>
       </c>
       <c r="I8" s="39" t="n">
         <v>26.39</v>
       </c>
-      <c r="J8" s="95">
+      <c r="J8" s="94">
         <f>(1+H8/100)^(1/(YEAR(D8)-YEAR(C8)))-1</f>
         <v/>
       </c>
@@ -11759,13 +11758,13 @@
       <c r="G9" s="39" t="n">
         <v>83</v>
       </c>
-      <c r="H9" s="94" t="n">
+      <c r="H9" s="93" t="n">
         <v>47.02060524</v>
       </c>
       <c r="I9" s="39" t="n">
         <v>37.82</v>
       </c>
-      <c r="J9" s="95">
+      <c r="J9" s="94">
         <f>(1+H9/100)^(1/(YEAR(D9)-YEAR(C9)))-1</f>
         <v/>
       </c>
@@ -11796,13 +11795,13 @@
       <c r="G10" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="H10" s="96" t="n">
+      <c r="H10" s="95" t="n">
         <v>27.8860732</v>
       </c>
       <c r="I10" s="24" t="n">
         <v>-10.97</v>
       </c>
-      <c r="J10" s="97" t="n">
+      <c r="J10" s="96" t="n">
         <v>0.278860732</v>
       </c>
     </row>
@@ -11833,13 +11832,13 @@
       <c r="G11" s="24" t="n">
         <v>93</v>
       </c>
-      <c r="H11" s="96" t="n">
+      <c r="H11" s="95" t="n">
         <v>17.4948656</v>
       </c>
       <c r="I11" s="24" t="n">
         <v>-7.7</v>
       </c>
-      <c r="J11" s="97">
+      <c r="J11" s="96">
         <f>(1+H11/100)^(1/(YEAR(D11)-YEAR(C11)))-1</f>
         <v/>
       </c>

--- a/report_2410.xlsx
+++ b/report_2410.xlsx
@@ -800,7 +800,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1058,6 +1058,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3982,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.26</v>
@@ -4079,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>-0.39</v>
+        <v>-0.41</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>-0.35</v>
@@ -6321,7 +6327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE49"/>
+  <dimension ref="A1:AE52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col width="19.5925925925926" customWidth="1" style="34" min="1" max="1"/>
@@ -6329,1937 +6335,5547 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="76" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="59" t="inlineStr">
+      <c r="B1" s="77" t="inlineStr">
+        <is>
+          <t>241010</t>
+        </is>
+      </c>
+      <c r="C1" s="77" t="inlineStr">
+        <is>
+          <t>241009</t>
+        </is>
+      </c>
+      <c r="D1" s="77" t="inlineStr">
+        <is>
+          <t>241008</t>
+        </is>
+      </c>
+      <c r="E1" s="77" t="inlineStr">
+        <is>
+          <t>241007</t>
+        </is>
+      </c>
+      <c r="F1" s="77" t="inlineStr">
+        <is>
+          <t>241006</t>
+        </is>
+      </c>
+      <c r="G1" s="77" t="inlineStr">
+        <is>
+          <t>241004</t>
+        </is>
+      </c>
+      <c r="H1" s="77" t="inlineStr">
         <is>
           <t>241003</t>
         </is>
       </c>
-      <c r="C1" s="59" t="inlineStr">
+      <c r="I1" s="77" t="inlineStr">
         <is>
           <t>241002</t>
         </is>
       </c>
-      <c r="D1" s="59" t="inlineStr">
+      <c r="J1" s="77" t="inlineStr">
         <is>
           <t>241001</t>
         </is>
       </c>
-      <c r="E1" s="59" t="inlineStr">
+      <c r="K1" s="77" t="inlineStr">
         <is>
           <t>240930</t>
         </is>
       </c>
-      <c r="F1" s="59" t="inlineStr">
+      <c r="L1" s="77" t="inlineStr">
+        <is>
+          <t>240929</t>
+        </is>
+      </c>
+      <c r="M1" s="77" t="inlineStr">
         <is>
           <t>240927</t>
         </is>
       </c>
-      <c r="G1" s="59" t="inlineStr">
+      <c r="N1" s="77" t="inlineStr">
         <is>
           <t>240926</t>
         </is>
       </c>
-      <c r="H1" s="59" t="inlineStr">
+      <c r="O1" s="77" t="inlineStr">
         <is>
           <t>240925</t>
         </is>
       </c>
-      <c r="I1" s="59" t="inlineStr">
+      <c r="P1" s="77" t="inlineStr">
         <is>
           <t>240924</t>
         </is>
       </c>
-      <c r="J1" s="59" t="inlineStr">
+      <c r="Q1" s="77" t="inlineStr">
         <is>
           <t>240923</t>
         </is>
       </c>
-      <c r="K1" s="59" t="inlineStr">
+      <c r="R1" s="77" t="inlineStr">
+        <is>
+          <t>240922</t>
+        </is>
+      </c>
+      <c r="S1" s="77" t="inlineStr">
         <is>
           <t>240920</t>
         </is>
       </c>
-      <c r="L1" s="59" t="inlineStr">
+      <c r="T1" s="77" t="inlineStr">
         <is>
           <t>240919</t>
         </is>
       </c>
-      <c r="M1" s="59" t="inlineStr">
+      <c r="U1" s="77" t="inlineStr">
         <is>
           <t>240918</t>
         </is>
       </c>
-      <c r="N1" s="59" t="inlineStr">
+      <c r="V1" s="77" t="inlineStr">
         <is>
           <t>240917</t>
         </is>
       </c>
-      <c r="O1" s="59" t="inlineStr">
+      <c r="W1" s="77" t="inlineStr">
         <is>
           <t>240916</t>
         </is>
       </c>
-      <c r="P1" s="59" t="inlineStr">
+      <c r="X1" s="77" t="inlineStr">
+        <is>
+          <t>240915</t>
+        </is>
+      </c>
+      <c r="Y1" s="77" t="inlineStr">
         <is>
           <t>240913</t>
         </is>
       </c>
-      <c r="Q1" s="59" t="inlineStr">
+      <c r="Z1" s="77" t="inlineStr">
         <is>
           <t>240912</t>
         </is>
       </c>
-      <c r="R1" s="59" t="inlineStr">
+      <c r="AA1" s="77" t="inlineStr">
         <is>
           <t>240911</t>
         </is>
       </c>
-      <c r="S1" s="59" t="inlineStr">
+      <c r="AB1" s="77" t="inlineStr">
         <is>
           <t>240910</t>
         </is>
       </c>
-      <c r="T1" s="59" t="inlineStr">
+      <c r="AC1" s="77" t="inlineStr">
         <is>
           <t>240909</t>
         </is>
       </c>
-      <c r="U1" s="59" t="inlineStr">
+      <c r="AD1" s="77" t="inlineStr">
+        <is>
+          <t>240908</t>
+        </is>
+      </c>
+      <c r="AE1" s="77" t="inlineStr">
         <is>
           <t>240906</t>
         </is>
       </c>
-      <c r="V1" s="59" t="inlineStr">
-        <is>
-          <t>240905</t>
-        </is>
-      </c>
-      <c r="W1" s="59" t="inlineStr">
-        <is>
-          <t>240904</t>
-        </is>
-      </c>
-      <c r="X1" s="59" t="inlineStr">
-        <is>
-          <t>240903</t>
-        </is>
-      </c>
-      <c r="Y1" s="59" t="inlineStr">
-        <is>
-          <t>240902</t>
-        </is>
-      </c>
-      <c r="Z1" s="59" t="inlineStr">
-        <is>
-          <t>240830</t>
-        </is>
-      </c>
-      <c r="AA1" s="59" t="inlineStr">
-        <is>
-          <t>240829</t>
-        </is>
-      </c>
-      <c r="AB1" s="59" t="inlineStr">
-        <is>
-          <t>240828</t>
-        </is>
-      </c>
-      <c r="AC1" s="59" t="inlineStr">
-        <is>
-          <t>240827</t>
-        </is>
-      </c>
-      <c r="AD1" s="59" t="inlineStr">
-        <is>
-          <t>240826</t>
-        </is>
-      </c>
-      <c r="AE1" s="59" t="inlineStr">
-        <is>
-          <t>240823</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr">
+      <c r="A2" s="76" t="inlineStr">
         <is>
           <t>sh:EIDE</t>
         </is>
       </c>
-      <c r="B2" s="60" t="n"/>
-      <c r="C2" s="60" t="n"/>
-      <c r="D2" s="60" t="n"/>
-      <c r="E2" s="60" t="n"/>
-      <c r="F2" s="60" t="n"/>
-      <c r="G2" s="60" t="n"/>
-      <c r="H2" s="60" t="n"/>
-      <c r="I2" s="60" t="n"/>
-      <c r="J2" s="60" t="n"/>
-      <c r="K2" s="60" t="n"/>
-      <c r="L2" s="60" t="n"/>
-      <c r="M2" s="60" t="n"/>
-      <c r="N2" s="60" t="n"/>
-      <c r="O2" s="60" t="n"/>
-      <c r="P2" s="60" t="n"/>
-      <c r="Q2" s="60" t="n"/>
-      <c r="R2" s="60" t="n"/>
-      <c r="S2" s="60" t="n"/>
-      <c r="T2" s="60" t="n"/>
-      <c r="U2" s="60" t="n"/>
-      <c r="V2" s="60" t="n"/>
-      <c r="W2" s="60" t="n"/>
-      <c r="X2" s="60" t="n"/>
-      <c r="Y2" s="60" t="n"/>
-      <c r="Z2" s="60" t="n"/>
-      <c r="AA2" s="60" t="n"/>
-      <c r="AB2" s="60" t="n"/>
-      <c r="AC2" s="60" t="n"/>
-      <c r="AD2" s="60" t="n"/>
-      <c r="AE2" s="60" t="n"/>
+      <c r="B2" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C2" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="E2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q2" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R2" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S2" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T2" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U2" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="W2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="X2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Y2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="58" t="inlineStr">
+      <c r="A3" s="94" t="inlineStr">
         <is>
           <t>sh:RNG60</t>
         </is>
       </c>
-      <c r="B3" s="60" t="n"/>
-      <c r="C3" s="60" t="n"/>
-      <c r="D3" s="60" t="n"/>
-      <c r="E3" s="60" t="n"/>
-      <c r="F3" s="60" t="n"/>
-      <c r="G3" s="60" t="n"/>
-      <c r="H3" s="60" t="n"/>
-      <c r="I3" s="60" t="n"/>
-      <c r="J3" s="60" t="n"/>
-      <c r="K3" s="60" t="n"/>
-      <c r="L3" s="60" t="n"/>
-      <c r="M3" s="60" t="n"/>
-      <c r="N3" s="60" t="n"/>
-      <c r="O3" s="60" t="n"/>
-      <c r="P3" s="60" t="n"/>
-      <c r="Q3" s="60" t="n"/>
-      <c r="R3" s="60" t="n"/>
-      <c r="S3" s="60" t="n"/>
-      <c r="T3" s="60" t="n"/>
-      <c r="U3" s="60" t="n"/>
-      <c r="V3" s="60" t="n"/>
-      <c r="W3" s="60" t="n"/>
-      <c r="X3" s="60" t="n"/>
-      <c r="Y3" s="60" t="n"/>
-      <c r="Z3" s="60" t="n"/>
-      <c r="AA3" s="60" t="n"/>
-      <c r="AB3" s="60" t="n"/>
-      <c r="AC3" s="60" t="n"/>
-      <c r="AD3" s="60" t="n"/>
-      <c r="AE3" s="60" t="n"/>
+      <c r="B3" s="95" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="C3" s="95" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="D3" s="95" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="E3" s="95" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="F3" s="95" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="G3" s="95" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="H3" s="95" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="I3" s="95" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="J3" s="95" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="K3" s="95" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="L3" s="95" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="M3" s="95" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="N3" s="95" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="O3" s="95" t="n">
+        <v>-3.29</v>
+      </c>
+      <c r="P3" s="95" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="Q3" s="95" t="n">
+        <v>-6.68</v>
+      </c>
+      <c r="R3" s="95" t="n">
+        <v>-7.93</v>
+      </c>
+      <c r="S3" s="95" t="n">
+        <v>-7.93</v>
+      </c>
+      <c r="T3" s="95" t="n">
+        <v>-7.25</v>
+      </c>
+      <c r="U3" s="95" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="V3" s="95" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="W3" s="95" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="X3" s="95" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="Y3" s="95" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="Z3" s="95" t="n">
+        <v>-9.59</v>
+      </c>
+      <c r="AA3" s="95" t="n">
+        <v>-9.82</v>
+      </c>
+      <c r="AB3" s="95" t="n">
+        <v>-9.44</v>
+      </c>
+      <c r="AC3" s="95" t="n">
+        <v>-9.26</v>
+      </c>
+      <c r="AD3" s="95" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="AE3" s="95" t="n">
+        <v>-8.800000000000001</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="58" t="inlineStr">
+      <c r="A4" s="76" t="inlineStr">
         <is>
           <t>sh:RNG120</t>
         </is>
       </c>
-      <c r="B4" s="60" t="n"/>
-      <c r="C4" s="60" t="n"/>
-      <c r="D4" s="60" t="n"/>
-      <c r="E4" s="60" t="n"/>
-      <c r="F4" s="60" t="n"/>
-      <c r="G4" s="60" t="n"/>
-      <c r="H4" s="60" t="n"/>
-      <c r="I4" s="60" t="n"/>
-      <c r="J4" s="60" t="n"/>
-      <c r="K4" s="60" t="n"/>
-      <c r="L4" s="60" t="n"/>
-      <c r="M4" s="60" t="n"/>
-      <c r="N4" s="60" t="n"/>
-      <c r="O4" s="60" t="n"/>
-      <c r="P4" s="60" t="n"/>
-      <c r="Q4" s="60" t="n"/>
-      <c r="R4" s="60" t="n"/>
-      <c r="S4" s="60" t="n"/>
-      <c r="T4" s="60" t="n"/>
-      <c r="U4" s="60" t="n"/>
-      <c r="V4" s="60" t="n"/>
-      <c r="W4" s="60" t="n"/>
-      <c r="X4" s="60" t="n"/>
-      <c r="Y4" s="60" t="n"/>
-      <c r="Z4" s="60" t="n"/>
-      <c r="AA4" s="60" t="n"/>
-      <c r="AB4" s="60" t="n"/>
-      <c r="AC4" s="60" t="n"/>
-      <c r="AD4" s="60" t="n"/>
-      <c r="AE4" s="60" t="n"/>
+      <c r="B4" s="95" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="C4" s="95" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D4" s="95" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="E4" s="95" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="F4" s="95" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="G4" s="95" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H4" s="95" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="I4" s="95" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="J4" s="95" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="K4" s="95" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="L4" s="95" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M4" s="95" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="N4" s="95" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="O4" s="95" t="n">
+        <v>-4.76</v>
+      </c>
+      <c r="P4" s="95" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="Q4" s="95" t="n">
+        <v>-8.16</v>
+      </c>
+      <c r="R4" s="95" t="n">
+        <v>-9.720000000000001</v>
+      </c>
+      <c r="S4" s="95" t="n">
+        <v>-9.720000000000001</v>
+      </c>
+      <c r="T4" s="95" t="n">
+        <v>-9.59</v>
+      </c>
+      <c r="U4" s="95" t="n">
+        <v>-10.85</v>
+      </c>
+      <c r="V4" s="95" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="W4" s="95" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="X4" s="95" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="Y4" s="95" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="Z4" s="95" t="n">
+        <v>-11.77</v>
+      </c>
+      <c r="AA4" s="95" t="n">
+        <v>-11.13</v>
+      </c>
+      <c r="AB4" s="95" t="n">
+        <v>-11.05</v>
+      </c>
+      <c r="AC4" s="95" t="n">
+        <v>-10.42</v>
+      </c>
+      <c r="AD4" s="95" t="n">
+        <v>-8.970000000000001</v>
+      </c>
+      <c r="AE4" s="95" t="n">
+        <v>-8.970000000000001</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="58" t="inlineStr">
-        <is>
-          <t>sh:RSI11</t>
-        </is>
-      </c>
-      <c r="B5" s="60" t="n"/>
-      <c r="C5" s="60" t="n"/>
-      <c r="D5" s="60" t="n"/>
-      <c r="E5" s="60" t="n"/>
-      <c r="F5" s="60" t="n"/>
-      <c r="G5" s="60" t="n"/>
-      <c r="H5" s="60" t="n"/>
-      <c r="I5" s="60" t="n"/>
-      <c r="J5" s="60" t="n"/>
-      <c r="K5" s="60" t="n"/>
-      <c r="L5" s="60" t="n"/>
-      <c r="M5" s="60" t="n"/>
-      <c r="N5" s="60" t="n"/>
-      <c r="O5" s="60" t="n"/>
-      <c r="P5" s="60" t="n"/>
-      <c r="Q5" s="60" t="n"/>
-      <c r="R5" s="60" t="n"/>
-      <c r="S5" s="60" t="n"/>
-      <c r="T5" s="60" t="n"/>
-      <c r="U5" s="60" t="n"/>
-      <c r="V5" s="60" t="n"/>
-      <c r="W5" s="60" t="n"/>
-      <c r="X5" s="60" t="n"/>
-      <c r="Y5" s="60" t="n"/>
-      <c r="Z5" s="60" t="n"/>
-      <c r="AA5" s="60" t="n"/>
-      <c r="AB5" s="60" t="n"/>
-      <c r="AC5" s="60" t="n"/>
-      <c r="AD5" s="60" t="n"/>
-      <c r="AE5" s="60" t="n"/>
+      <c r="A5" s="76" t="inlineStr">
+        <is>
+          <t>sh:RS3</t>
+        </is>
+      </c>
+      <c r="B5" s="95" t="n">
+        <v>59.48</v>
+      </c>
+      <c r="C5" s="95" t="n">
+        <v>54.31</v>
+      </c>
+      <c r="D5" s="95" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="E5" s="95" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="F5" s="95" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="G5" s="95" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="H5" s="95" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="I5" s="95" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="J5" s="95" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="K5" s="95" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="L5" s="95" t="n">
+        <v>99.31</v>
+      </c>
+      <c r="M5" s="95" t="n">
+        <v>99.31</v>
+      </c>
+      <c r="N5" s="95" t="n">
+        <v>98.83</v>
+      </c>
+      <c r="O5" s="95" t="n">
+        <v>97.34999999999999</v>
+      </c>
+      <c r="P5" s="95" t="n">
+        <v>96.38</v>
+      </c>
+      <c r="Q5" s="95" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="R5" s="95" t="n">
+        <v>64.38</v>
+      </c>
+      <c r="S5" s="95" t="n">
+        <v>64.38</v>
+      </c>
+      <c r="T5" s="95" t="n">
+        <v>63.45</v>
+      </c>
+      <c r="U5" s="95" t="n">
+        <v>37.85</v>
+      </c>
+      <c r="V5" s="95" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="W5" s="95" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="X5" s="95" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="Y5" s="95" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="Z5" s="95" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="AA5" s="95" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="AB5" s="95" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="AC5" s="95" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AD5" s="95" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="AE5" s="95" t="n">
+        <v>11.48</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="58" t="inlineStr">
+      <c r="A6" s="76" t="inlineStr">
         <is>
           <t>kc:EIDE</t>
         </is>
       </c>
-      <c r="B6" s="60" t="n"/>
-      <c r="C6" s="60" t="n"/>
-      <c r="D6" s="60" t="n"/>
-      <c r="E6" s="60" t="n"/>
-      <c r="F6" s="60" t="n"/>
-      <c r="G6" s="60" t="n"/>
-      <c r="H6" s="60" t="n"/>
-      <c r="I6" s="60" t="n"/>
-      <c r="J6" s="60" t="n"/>
-      <c r="K6" s="60" t="n"/>
-      <c r="L6" s="60" t="n"/>
-      <c r="M6" s="60" t="n"/>
-      <c r="N6" s="60" t="n"/>
-      <c r="O6" s="60" t="n"/>
-      <c r="P6" s="60" t="n"/>
-      <c r="Q6" s="60" t="n"/>
-      <c r="R6" s="60" t="n"/>
-      <c r="S6" s="60" t="n"/>
-      <c r="T6" s="60" t="n"/>
-      <c r="U6" s="60" t="n"/>
-      <c r="V6" s="60" t="n"/>
-      <c r="W6" s="60" t="n"/>
-      <c r="X6" s="60" t="n"/>
-      <c r="Y6" s="60" t="n"/>
-      <c r="Z6" s="60" t="n"/>
-      <c r="AA6" s="60" t="n"/>
-      <c r="AB6" s="60" t="n"/>
-      <c r="AC6" s="60" t="n"/>
-      <c r="AD6" s="60" t="n"/>
-      <c r="AE6" s="60" t="n"/>
+      <c r="B6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="D6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="E6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="V6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Z6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AB6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AC6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="58" t="inlineStr">
+      <c r="A7" s="94" t="inlineStr">
         <is>
           <t>kc:RNG60</t>
         </is>
       </c>
-      <c r="B7" s="60" t="n"/>
-      <c r="C7" s="60" t="n"/>
-      <c r="D7" s="60" t="n"/>
-      <c r="E7" s="60" t="n"/>
-      <c r="F7" s="60" t="n"/>
-      <c r="G7" s="60" t="n"/>
-      <c r="H7" s="60" t="n"/>
-      <c r="I7" s="60" t="n"/>
-      <c r="J7" s="60" t="n"/>
-      <c r="K7" s="60" t="n"/>
-      <c r="L7" s="60" t="n"/>
-      <c r="M7" s="60" t="n"/>
-      <c r="N7" s="60" t="n"/>
-      <c r="O7" s="60" t="n"/>
-      <c r="P7" s="60" t="n"/>
-      <c r="Q7" s="60" t="n"/>
-      <c r="R7" s="60" t="n"/>
-      <c r="S7" s="60" t="n"/>
-      <c r="T7" s="60" t="n"/>
-      <c r="U7" s="60" t="n"/>
-      <c r="V7" s="60" t="n"/>
-      <c r="W7" s="60" t="n"/>
-      <c r="X7" s="60" t="n"/>
-      <c r="Y7" s="60" t="n"/>
-      <c r="Z7" s="60" t="n"/>
-      <c r="AA7" s="60" t="n"/>
-      <c r="AB7" s="60" t="n"/>
-      <c r="AC7" s="60" t="n"/>
-      <c r="AD7" s="60" t="n"/>
-      <c r="AE7" s="60" t="n"/>
+      <c r="B7" s="95" t="n">
+        <v>34.41</v>
+      </c>
+      <c r="C7" s="95" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="D7" s="95" t="n">
+        <v>46.52</v>
+      </c>
+      <c r="E7" s="95" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="F7" s="95" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="G7" s="95" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="H7" s="95" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="I7" s="95" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="J7" s="95" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="K7" s="95" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="L7" s="95" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="M7" s="95" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="N7" s="95" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="O7" s="95" t="n">
+        <v>-5.96</v>
+      </c>
+      <c r="P7" s="95" t="n">
+        <v>-6.32</v>
+      </c>
+      <c r="Q7" s="95" t="n">
+        <v>-10.11</v>
+      </c>
+      <c r="R7" s="95" t="n">
+        <v>-11.14</v>
+      </c>
+      <c r="S7" s="95" t="n">
+        <v>-11.14</v>
+      </c>
+      <c r="T7" s="95" t="n">
+        <v>-9.23</v>
+      </c>
+      <c r="U7" s="95" t="n">
+        <v>-12.41</v>
+      </c>
+      <c r="V7" s="95" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="W7" s="95" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="X7" s="95" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="Y7" s="95" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="Z7" s="95" t="n">
+        <v>-12.75</v>
+      </c>
+      <c r="AA7" s="95" t="n">
+        <v>-11.62</v>
+      </c>
+      <c r="AB7" s="95" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="AC7" s="95" t="n">
+        <v>-13.49</v>
+      </c>
+      <c r="AD7" s="95" t="n">
+        <v>-12.19</v>
+      </c>
+      <c r="AE7" s="95" t="n">
+        <v>-12.19</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="58" t="inlineStr">
+      <c r="A8" s="76" t="inlineStr">
         <is>
           <t>kc:RNG120</t>
         </is>
       </c>
-      <c r="B8" s="60" t="n"/>
-      <c r="C8" s="60" t="n"/>
-      <c r="D8" s="60" t="n"/>
-      <c r="E8" s="60" t="n"/>
-      <c r="F8" s="60" t="n"/>
-      <c r="G8" s="60" t="n"/>
-      <c r="H8" s="60" t="n"/>
-      <c r="I8" s="60" t="n"/>
-      <c r="J8" s="60" t="n"/>
-      <c r="K8" s="60" t="n"/>
-      <c r="L8" s="60" t="n"/>
-      <c r="M8" s="60" t="n"/>
-      <c r="N8" s="60" t="n"/>
-      <c r="O8" s="60" t="n"/>
-      <c r="P8" s="60" t="n"/>
-      <c r="Q8" s="60" t="n"/>
-      <c r="R8" s="60" t="n"/>
-      <c r="S8" s="60" t="n"/>
-      <c r="T8" s="60" t="n"/>
-      <c r="U8" s="60" t="n"/>
-      <c r="V8" s="60" t="n"/>
-      <c r="W8" s="60" t="n"/>
-      <c r="X8" s="60" t="n"/>
-      <c r="Y8" s="60" t="n"/>
-      <c r="Z8" s="60" t="n"/>
-      <c r="AA8" s="60" t="n"/>
-      <c r="AB8" s="60" t="n"/>
-      <c r="AC8" s="60" t="n"/>
-      <c r="AD8" s="60" t="n"/>
-      <c r="AE8" s="60" t="n"/>
+      <c r="B8" s="95" t="n">
+        <v>29.69</v>
+      </c>
+      <c r="C8" s="95" t="n">
+        <v>33.11</v>
+      </c>
+      <c r="D8" s="95" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="E8" s="95" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="F8" s="95" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="G8" s="95" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="H8" s="95" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="I8" s="95" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="J8" s="95" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="K8" s="95" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="L8" s="95" t="n">
+        <v>-3.74</v>
+      </c>
+      <c r="M8" s="95" t="n">
+        <v>-3.74</v>
+      </c>
+      <c r="N8" s="95" t="n">
+        <v>-10.62</v>
+      </c>
+      <c r="O8" s="95" t="n">
+        <v>-12.51</v>
+      </c>
+      <c r="P8" s="95" t="n">
+        <v>-12.61</v>
+      </c>
+      <c r="Q8" s="95" t="n">
+        <v>-14.58</v>
+      </c>
+      <c r="R8" s="95" t="n">
+        <v>-16.03</v>
+      </c>
+      <c r="S8" s="95" t="n">
+        <v>-16.03</v>
+      </c>
+      <c r="T8" s="95" t="n">
+        <v>-16.65</v>
+      </c>
+      <c r="U8" s="95" t="n">
+        <v>-18.48</v>
+      </c>
+      <c r="V8" s="95" t="n">
+        <v>-18.74</v>
+      </c>
+      <c r="W8" s="95" t="n">
+        <v>-18.74</v>
+      </c>
+      <c r="X8" s="95" t="n">
+        <v>-18.74</v>
+      </c>
+      <c r="Y8" s="95" t="n">
+        <v>-18.74</v>
+      </c>
+      <c r="Z8" s="95" t="n">
+        <v>-19.06</v>
+      </c>
+      <c r="AA8" s="95" t="n">
+        <v>-18.16</v>
+      </c>
+      <c r="AB8" s="95" t="n">
+        <v>-20.04</v>
+      </c>
+      <c r="AC8" s="95" t="n">
+        <v>-19.01</v>
+      </c>
+      <c r="AD8" s="95" t="n">
+        <v>-17.71</v>
+      </c>
+      <c r="AE8" s="95" t="n">
+        <v>-17.71</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="58" t="inlineStr">
-        <is>
-          <t>kc:RSI10</t>
-        </is>
-      </c>
-      <c r="B9" s="60" t="n"/>
-      <c r="C9" s="60" t="n"/>
-      <c r="D9" s="60" t="n"/>
-      <c r="E9" s="60" t="n"/>
-      <c r="F9" s="60" t="n"/>
-      <c r="G9" s="60" t="n"/>
-      <c r="H9" s="60" t="n"/>
-      <c r="I9" s="60" t="n"/>
-      <c r="J9" s="60" t="n"/>
-      <c r="K9" s="60" t="n"/>
-      <c r="L9" s="60" t="n"/>
-      <c r="M9" s="60" t="n"/>
-      <c r="N9" s="60" t="n"/>
-      <c r="O9" s="60" t="n"/>
-      <c r="P9" s="60" t="n"/>
-      <c r="Q9" s="60" t="n"/>
-      <c r="R9" s="60" t="n"/>
-      <c r="S9" s="60" t="n"/>
-      <c r="T9" s="60" t="n"/>
-      <c r="U9" s="60" t="n"/>
-      <c r="V9" s="60" t="n"/>
-      <c r="W9" s="60" t="n"/>
-      <c r="X9" s="60" t="n"/>
-      <c r="Y9" s="60" t="n"/>
-      <c r="Z9" s="60" t="n"/>
-      <c r="AA9" s="60" t="n"/>
-      <c r="AB9" s="60" t="n"/>
-      <c r="AC9" s="60" t="n"/>
-      <c r="AD9" s="60" t="n"/>
-      <c r="AE9" s="60" t="n"/>
+      <c r="A9" s="94" t="inlineStr">
+        <is>
+          <t>kc:RS5</t>
+        </is>
+      </c>
+      <c r="B9" s="95" t="n">
+        <v>74.52</v>
+      </c>
+      <c r="C9" s="95" t="n">
+        <v>89.13</v>
+      </c>
+      <c r="D9" s="95" t="n">
+        <v>98.36</v>
+      </c>
+      <c r="E9" s="95" t="n">
+        <v>96.84</v>
+      </c>
+      <c r="F9" s="95" t="n">
+        <v>96.84</v>
+      </c>
+      <c r="G9" s="95" t="n">
+        <v>96.84</v>
+      </c>
+      <c r="H9" s="95" t="n">
+        <v>96.84</v>
+      </c>
+      <c r="I9" s="95" t="n">
+        <v>96.84</v>
+      </c>
+      <c r="J9" s="95" t="n">
+        <v>96.84</v>
+      </c>
+      <c r="K9" s="95" t="n">
+        <v>96.84</v>
+      </c>
+      <c r="L9" s="95" t="n">
+        <v>91.06999999999999</v>
+      </c>
+      <c r="M9" s="95" t="n">
+        <v>91.06999999999999</v>
+      </c>
+      <c r="N9" s="95" t="n">
+        <v>81.48999999999999</v>
+      </c>
+      <c r="O9" s="95" t="n">
+        <v>64.94</v>
+      </c>
+      <c r="P9" s="95" t="n">
+        <v>64.66</v>
+      </c>
+      <c r="Q9" s="95" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="R9" s="95" t="n">
+        <v>29.81</v>
+      </c>
+      <c r="S9" s="95" t="n">
+        <v>29.81</v>
+      </c>
+      <c r="T9" s="95" t="n">
+        <v>33.91</v>
+      </c>
+      <c r="U9" s="95" t="n">
+        <v>22.82</v>
+      </c>
+      <c r="V9" s="95" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="W9" s="95" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="X9" s="95" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="Y9" s="95" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="Z9" s="95" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="AA9" s="95" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="AB9" s="95" t="n">
+        <v>33.88</v>
+      </c>
+      <c r="AC9" s="95" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="AD9" s="95" t="n">
+        <v>27.98</v>
+      </c>
+      <c r="AE9" s="95" t="n">
+        <v>27.98</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="58" t="inlineStr">
+      <c r="A10" s="76" t="inlineStr">
         <is>
           <t>cy:EIDE</t>
         </is>
       </c>
-      <c r="B10" s="60" t="n"/>
-      <c r="C10" s="60" t="n"/>
-      <c r="D10" s="60" t="n"/>
-      <c r="E10" s="60" t="n"/>
-      <c r="F10" s="60" t="n"/>
-      <c r="G10" s="60" t="n"/>
-      <c r="H10" s="60" t="n"/>
-      <c r="I10" s="60" t="n"/>
-      <c r="J10" s="60" t="n"/>
-      <c r="K10" s="60" t="n"/>
-      <c r="L10" s="60" t="n"/>
-      <c r="M10" s="60" t="n"/>
-      <c r="N10" s="60" t="n"/>
-      <c r="O10" s="60" t="n"/>
-      <c r="P10" s="60" t="n"/>
-      <c r="Q10" s="60" t="n"/>
-      <c r="R10" s="60" t="n"/>
-      <c r="S10" s="60" t="n"/>
-      <c r="T10" s="60" t="n"/>
-      <c r="U10" s="60" t="n"/>
-      <c r="V10" s="60" t="n"/>
-      <c r="W10" s="60" t="n"/>
-      <c r="X10" s="60" t="n"/>
-      <c r="Y10" s="60" t="n"/>
-      <c r="Z10" s="60" t="n"/>
-      <c r="AA10" s="60" t="n"/>
-      <c r="AB10" s="60" t="n"/>
-      <c r="AC10" s="60" t="n"/>
-      <c r="AD10" s="60" t="n"/>
-      <c r="AE10" s="60" t="n"/>
+      <c r="B10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="D10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="E10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="S10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="T10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="V10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="W10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="X10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Y10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="58" t="inlineStr">
+      <c r="A11" s="94" t="inlineStr">
         <is>
           <t>cy:RNG60</t>
         </is>
       </c>
-      <c r="B11" s="60" t="n"/>
-      <c r="C11" s="60" t="n"/>
-      <c r="D11" s="60" t="n"/>
-      <c r="E11" s="60" t="n"/>
-      <c r="F11" s="60" t="n"/>
-      <c r="G11" s="60" t="n"/>
-      <c r="H11" s="60" t="n"/>
-      <c r="I11" s="60" t="n"/>
-      <c r="J11" s="60" t="n"/>
-      <c r="K11" s="60" t="n"/>
-      <c r="L11" s="60" t="n"/>
-      <c r="M11" s="60" t="n"/>
-      <c r="N11" s="60" t="n"/>
-      <c r="O11" s="60" t="n"/>
-      <c r="P11" s="60" t="n"/>
-      <c r="Q11" s="60" t="n"/>
-      <c r="R11" s="60" t="n"/>
-      <c r="S11" s="60" t="n"/>
-      <c r="T11" s="60" t="n"/>
-      <c r="U11" s="60" t="n"/>
-      <c r="V11" s="60" t="n"/>
-      <c r="W11" s="60" t="n"/>
-      <c r="X11" s="60" t="n"/>
-      <c r="Y11" s="60" t="n"/>
-      <c r="Z11" s="60" t="n"/>
-      <c r="AA11" s="60" t="n"/>
-      <c r="AB11" s="60" t="n"/>
-      <c r="AC11" s="60" t="n"/>
-      <c r="AD11" s="60" t="n"/>
-      <c r="AE11" s="60" t="n"/>
+      <c r="B11" s="95" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="C11" s="95" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="D11" s="95" t="n">
+        <v>54.04</v>
+      </c>
+      <c r="E11" s="95" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="F11" s="95" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="G11" s="95" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="H11" s="95" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="I11" s="95" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="J11" s="95" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="K11" s="95" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="L11" s="95" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="M11" s="95" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="N11" s="95" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O11" s="95" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="P11" s="95" t="n">
+        <v>-4.05</v>
+      </c>
+      <c r="Q11" s="95" t="n">
+        <v>-10.14</v>
+      </c>
+      <c r="R11" s="95" t="n">
+        <v>-11.21</v>
+      </c>
+      <c r="S11" s="95" t="n">
+        <v>-11.21</v>
+      </c>
+      <c r="T11" s="95" t="n">
+        <v>-9.029999999999999</v>
+      </c>
+      <c r="U11" s="95" t="n">
+        <v>-11.44</v>
+      </c>
+      <c r="V11" s="95" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="W11" s="95" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="X11" s="95" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="Y11" s="95" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="Z11" s="95" t="n">
+        <v>-11.96</v>
+      </c>
+      <c r="AA11" s="95" t="n">
+        <v>-12.87</v>
+      </c>
+      <c r="AB11" s="95" t="n">
+        <v>-14.98</v>
+      </c>
+      <c r="AC11" s="95" t="n">
+        <v>-14.79</v>
+      </c>
+      <c r="AD11" s="95" t="n">
+        <v>-14.14</v>
+      </c>
+      <c r="AE11" s="95" t="n">
+        <v>-14.14</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="58" t="inlineStr">
+      <c r="A12" s="76" t="inlineStr">
         <is>
           <t>cy:RNG120</t>
         </is>
       </c>
-      <c r="B12" s="60" t="n"/>
-      <c r="C12" s="60" t="n"/>
-      <c r="D12" s="60" t="n"/>
-      <c r="E12" s="60" t="n"/>
-      <c r="F12" s="60" t="n"/>
-      <c r="G12" s="60" t="n"/>
-      <c r="H12" s="60" t="n"/>
-      <c r="I12" s="60" t="n"/>
-      <c r="J12" s="60" t="n"/>
-      <c r="K12" s="60" t="n"/>
-      <c r="L12" s="60" t="n"/>
-      <c r="M12" s="60" t="n"/>
-      <c r="N12" s="60" t="n"/>
-      <c r="O12" s="60" t="n"/>
-      <c r="P12" s="60" t="n"/>
-      <c r="Q12" s="60" t="n"/>
-      <c r="R12" s="60" t="n"/>
-      <c r="S12" s="60" t="n"/>
-      <c r="T12" s="60" t="n"/>
-      <c r="U12" s="60" t="n"/>
-      <c r="V12" s="60" t="n"/>
-      <c r="W12" s="60" t="n"/>
-      <c r="X12" s="60" t="n"/>
-      <c r="Y12" s="60" t="n"/>
-      <c r="Z12" s="60" t="n"/>
-      <c r="AA12" s="60" t="n"/>
-      <c r="AB12" s="60" t="n"/>
-      <c r="AC12" s="60" t="n"/>
-      <c r="AD12" s="60" t="n"/>
-      <c r="AE12" s="60" t="n"/>
+      <c r="B12" s="95" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="C12" s="95" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="D12" s="95" t="n">
+        <v>41.13</v>
+      </c>
+      <c r="E12" s="95" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="F12" s="95" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="G12" s="95" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="H12" s="95" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="I12" s="95" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="J12" s="95" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="K12" s="95" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="L12" s="95" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M12" s="95" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="N12" s="95" t="n">
+        <v>-8.44</v>
+      </c>
+      <c r="O12" s="95" t="n">
+        <v>-9.720000000000001</v>
+      </c>
+      <c r="P12" s="95" t="n">
+        <v>-10.6</v>
+      </c>
+      <c r="Q12" s="95" t="n">
+        <v>-14.49</v>
+      </c>
+      <c r="R12" s="95" t="n">
+        <v>-16.56</v>
+      </c>
+      <c r="S12" s="95" t="n">
+        <v>-16.56</v>
+      </c>
+      <c r="T12" s="95" t="n">
+        <v>-15.65</v>
+      </c>
+      <c r="U12" s="95" t="n">
+        <v>-17.96</v>
+      </c>
+      <c r="V12" s="95" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="W12" s="95" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="X12" s="95" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="Y12" s="95" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="Z12" s="95" t="n">
+        <v>-18.72</v>
+      </c>
+      <c r="AA12" s="95" t="n">
+        <v>-18.28</v>
+      </c>
+      <c r="AB12" s="95" t="n">
+        <v>-20.06</v>
+      </c>
+      <c r="AC12" s="95" t="n">
+        <v>-18.31</v>
+      </c>
+      <c r="AD12" s="95" t="n">
+        <v>-18.32</v>
+      </c>
+      <c r="AE12" s="95" t="n">
+        <v>-18.32</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="58" t="inlineStr">
-        <is>
-          <t>cy:RSI10</t>
-        </is>
-      </c>
-      <c r="B13" s="60" t="n"/>
-      <c r="C13" s="60" t="n"/>
-      <c r="D13" s="60" t="n"/>
-      <c r="E13" s="60" t="n"/>
-      <c r="F13" s="60" t="n"/>
-      <c r="G13" s="60" t="n"/>
-      <c r="H13" s="60" t="n"/>
-      <c r="I13" s="60" t="n"/>
-      <c r="J13" s="60" t="n"/>
-      <c r="K13" s="60" t="n"/>
-      <c r="L13" s="60" t="n"/>
-      <c r="M13" s="60" t="n"/>
-      <c r="N13" s="60" t="n"/>
-      <c r="O13" s="60" t="n"/>
-      <c r="P13" s="60" t="n"/>
-      <c r="Q13" s="60" t="n"/>
-      <c r="R13" s="60" t="n"/>
-      <c r="S13" s="60" t="n"/>
-      <c r="T13" s="60" t="n"/>
-      <c r="U13" s="60" t="n"/>
-      <c r="V13" s="60" t="n"/>
-      <c r="W13" s="60" t="n"/>
-      <c r="X13" s="60" t="n"/>
-      <c r="Y13" s="60" t="n"/>
-      <c r="Z13" s="60" t="n"/>
-      <c r="AA13" s="60" t="n"/>
-      <c r="AB13" s="60" t="n"/>
-      <c r="AC13" s="60" t="n"/>
-      <c r="AD13" s="60" t="n"/>
-      <c r="AE13" s="60" t="n"/>
+      <c r="A13" s="76" t="inlineStr">
+        <is>
+          <t>cy:RS3</t>
+        </is>
+      </c>
+      <c r="B13" s="95" t="n">
+        <v>55.03</v>
+      </c>
+      <c r="C13" s="95" t="n">
+        <v>62.67</v>
+      </c>
+      <c r="D13" s="95" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="E13" s="95" t="n">
+        <v>99.48</v>
+      </c>
+      <c r="F13" s="95" t="n">
+        <v>99.48</v>
+      </c>
+      <c r="G13" s="95" t="n">
+        <v>99.48</v>
+      </c>
+      <c r="H13" s="95" t="n">
+        <v>99.48</v>
+      </c>
+      <c r="I13" s="95" t="n">
+        <v>99.48</v>
+      </c>
+      <c r="J13" s="95" t="n">
+        <v>99.48</v>
+      </c>
+      <c r="K13" s="95" t="n">
+        <v>99.48</v>
+      </c>
+      <c r="L13" s="95" t="n">
+        <v>98.62</v>
+      </c>
+      <c r="M13" s="95" t="n">
+        <v>98.62</v>
+      </c>
+      <c r="N13" s="95" t="n">
+        <v>96</v>
+      </c>
+      <c r="O13" s="95" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="P13" s="95" t="n">
+        <v>88.09</v>
+      </c>
+      <c r="Q13" s="95" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="R13" s="95" t="n">
+        <v>39.51</v>
+      </c>
+      <c r="S13" s="95" t="n">
+        <v>39.51</v>
+      </c>
+      <c r="T13" s="95" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="U13" s="95" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="V13" s="95" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="W13" s="95" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="X13" s="95" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="Y13" s="95" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="Z13" s="95" t="n">
+        <v>54.57</v>
+      </c>
+      <c r="AA13" s="95" t="n">
+        <v>69.45</v>
+      </c>
+      <c r="AB13" s="95" t="n">
+        <v>37.43</v>
+      </c>
+      <c r="AC13" s="95" t="n">
+        <v>35.11</v>
+      </c>
+      <c r="AD13" s="95" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="AE13" s="95" t="n">
+        <v>33.41</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="58" t="inlineStr">
+      <c r="A14" s="76" t="inlineStr">
         <is>
           <t>hk50:EIDE</t>
         </is>
       </c>
-      <c r="B14" s="60" t="n"/>
-      <c r="C14" s="60" t="n"/>
-      <c r="D14" s="60" t="n"/>
-      <c r="E14" s="60" t="n"/>
-      <c r="F14" s="60" t="n"/>
-      <c r="G14" s="60" t="n"/>
-      <c r="H14" s="60" t="n"/>
-      <c r="I14" s="60" t="n"/>
-      <c r="J14" s="60" t="n"/>
-      <c r="K14" s="60" t="n"/>
-      <c r="L14" s="60" t="n"/>
-      <c r="M14" s="60" t="n"/>
-      <c r="N14" s="60" t="n"/>
-      <c r="O14" s="60" t="n"/>
-      <c r="P14" s="60" t="n"/>
-      <c r="Q14" s="60" t="n"/>
-      <c r="R14" s="60" t="n"/>
-      <c r="S14" s="60" t="n"/>
-      <c r="T14" s="60" t="n"/>
-      <c r="U14" s="60" t="n"/>
-      <c r="V14" s="60" t="n"/>
-      <c r="W14" s="60" t="n"/>
-      <c r="X14" s="60" t="n"/>
-      <c r="Y14" s="60" t="n"/>
-      <c r="Z14" s="60" t="n"/>
-      <c r="AA14" s="60" t="n"/>
-      <c r="AB14" s="60" t="n"/>
-      <c r="AC14" s="60" t="n"/>
-      <c r="AD14" s="60" t="n"/>
-      <c r="AE14" s="60" t="n"/>
+      <c r="B14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Z14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD14" s="91" t="n">
+        <v/>
+      </c>
+      <c r="AE14" s="91" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="58" t="inlineStr">
+      <c r="A15" s="94" t="inlineStr">
         <is>
           <t>hk50:RNG60</t>
         </is>
       </c>
-      <c r="B15" s="60" t="n"/>
-      <c r="C15" s="60" t="n"/>
-      <c r="D15" s="60" t="n"/>
-      <c r="E15" s="60" t="n"/>
-      <c r="F15" s="60" t="n"/>
-      <c r="G15" s="60" t="n"/>
-      <c r="H15" s="60" t="n"/>
-      <c r="I15" s="60" t="n"/>
-      <c r="J15" s="60" t="n"/>
-      <c r="K15" s="60" t="n"/>
-      <c r="L15" s="60" t="n"/>
-      <c r="M15" s="60" t="n"/>
-      <c r="N15" s="60" t="n"/>
-      <c r="O15" s="60" t="n"/>
-      <c r="P15" s="60" t="n"/>
-      <c r="Q15" s="60" t="n"/>
-      <c r="R15" s="60" t="n"/>
-      <c r="S15" s="60" t="n"/>
-      <c r="T15" s="60" t="n"/>
-      <c r="U15" s="60" t="n"/>
-      <c r="V15" s="60" t="n"/>
-      <c r="W15" s="60" t="n"/>
-      <c r="X15" s="60" t="n"/>
-      <c r="Y15" s="60" t="n"/>
-      <c r="Z15" s="60" t="n"/>
-      <c r="AA15" s="60" t="n"/>
-      <c r="AB15" s="60" t="n"/>
-      <c r="AC15" s="60" t="n"/>
-      <c r="AD15" s="60" t="n"/>
-      <c r="AE15" s="60" t="n"/>
+      <c r="B15" s="95" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="C15" s="95" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="D15" s="95" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="E15" s="95" t="n">
+        <v>32.21</v>
+      </c>
+      <c r="F15" s="95" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="G15" s="95" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="H15" s="95" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="I15" s="95" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="J15" s="95" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="K15" s="95" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="L15" s="95" t="n">
+        <v>14.76</v>
+      </c>
+      <c r="M15" s="95" t="n">
+        <v>14.76</v>
+      </c>
+      <c r="N15" s="95" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="O15" s="95" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="P15" s="95" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="Q15" s="95" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="R15" s="95" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="S15" s="95" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="T15" s="95" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="U15" s="95" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="V15" s="95" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="W15" s="95" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="X15" s="95" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="Y15" s="95" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="Z15" s="95" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="AA15" s="95" t="n">
+        <v>-4.61</v>
+      </c>
+      <c r="AB15" s="95" t="n">
+        <v>-3.94</v>
+      </c>
+      <c r="AC15" s="95" t="n">
+        <v>-5.06</v>
+      </c>
+      <c r="AD15" s="95" t="n">
+        <v/>
+      </c>
+      <c r="AE15" s="95" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="58" t="inlineStr">
+      <c r="A16" s="94" t="inlineStr">
         <is>
           <t>hk50:RNG120</t>
         </is>
       </c>
-      <c r="B16" s="60" t="n"/>
-      <c r="C16" s="60" t="n"/>
-      <c r="D16" s="60" t="n"/>
-      <c r="E16" s="60" t="n"/>
-      <c r="F16" s="60" t="n"/>
-      <c r="G16" s="60" t="n"/>
-      <c r="H16" s="60" t="n"/>
-      <c r="I16" s="60" t="n"/>
-      <c r="J16" s="60" t="n"/>
-      <c r="K16" s="60" t="n"/>
-      <c r="L16" s="60" t="n"/>
-      <c r="M16" s="60" t="n"/>
-      <c r="N16" s="60" t="n"/>
-      <c r="O16" s="60" t="n"/>
-      <c r="P16" s="60" t="n"/>
-      <c r="Q16" s="60" t="n"/>
-      <c r="R16" s="60" t="n"/>
-      <c r="S16" s="60" t="n"/>
-      <c r="T16" s="60" t="n"/>
-      <c r="U16" s="60" t="n"/>
-      <c r="V16" s="60" t="n"/>
-      <c r="W16" s="60" t="n"/>
-      <c r="X16" s="60" t="n"/>
-      <c r="Y16" s="60" t="n"/>
-      <c r="Z16" s="60" t="n"/>
-      <c r="AA16" s="60" t="n"/>
-      <c r="AB16" s="60" t="n"/>
-      <c r="AC16" s="60" t="n"/>
-      <c r="AD16" s="60" t="n"/>
-      <c r="AE16" s="60" t="n"/>
+      <c r="B16" s="95" t="n">
+        <v>30.79</v>
+      </c>
+      <c r="C16" s="95" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="D16" s="95" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="E16" s="95" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="F16" s="95" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="G16" s="95" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="H16" s="95" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="I16" s="95" t="n">
+        <v>34.13</v>
+      </c>
+      <c r="J16" s="95" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="K16" s="95" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="L16" s="95" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="M16" s="95" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="N16" s="95" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="O16" s="95" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="P16" s="95" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="Q16" s="95" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="R16" s="95" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="S16" s="95" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="T16" s="95" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="U16" s="95" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="V16" s="95" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="W16" s="95" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="X16" s="95" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="Y16" s="95" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="Z16" s="95" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AA16" s="95" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB16" s="95" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC16" s="95" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AD16" s="95" t="n">
+        <v/>
+      </c>
+      <c r="AE16" s="95" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="58" t="inlineStr">
-        <is>
-          <t>hk50:RSI6</t>
-        </is>
-      </c>
-      <c r="B17" s="60" t="n"/>
-      <c r="C17" s="60" t="n"/>
-      <c r="D17" s="60" t="n"/>
-      <c r="E17" s="60" t="n"/>
-      <c r="F17" s="60" t="n"/>
-      <c r="G17" s="60" t="n"/>
-      <c r="H17" s="60" t="n"/>
-      <c r="I17" s="60" t="n"/>
-      <c r="J17" s="60" t="n"/>
-      <c r="K17" s="60" t="n"/>
-      <c r="L17" s="60" t="n"/>
-      <c r="M17" s="60" t="n"/>
-      <c r="N17" s="60" t="n"/>
-      <c r="O17" s="60" t="n"/>
-      <c r="P17" s="60" t="n"/>
-      <c r="Q17" s="60" t="n"/>
-      <c r="R17" s="60" t="n"/>
-      <c r="S17" s="60" t="n"/>
-      <c r="T17" s="60" t="n"/>
-      <c r="U17" s="60" t="n"/>
-      <c r="V17" s="60" t="n"/>
-      <c r="W17" s="60" t="n"/>
-      <c r="X17" s="60" t="n"/>
-      <c r="Y17" s="60" t="n"/>
-      <c r="Z17" s="60" t="n"/>
-      <c r="AA17" s="60" t="n"/>
-      <c r="AB17" s="60" t="n"/>
-      <c r="AC17" s="60" t="n"/>
-      <c r="AD17" s="60" t="n"/>
-      <c r="AE17" s="60" t="n"/>
+      <c r="A17" s="76" t="inlineStr">
+        <is>
+          <t>hk50:RS4</t>
+        </is>
+      </c>
+      <c r="B17" s="95" t="n">
+        <v>48.87</v>
+      </c>
+      <c r="C17" s="95" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="D17" s="95" t="n">
+        <v>39.14</v>
+      </c>
+      <c r="E17" s="95" t="n">
+        <v>91.23999999999999</v>
+      </c>
+      <c r="F17" s="95" t="n">
+        <v>89.48999999999999</v>
+      </c>
+      <c r="G17" s="95" t="n">
+        <v>89.48999999999999</v>
+      </c>
+      <c r="H17" s="95" t="n">
+        <v>85.84</v>
+      </c>
+      <c r="I17" s="95" t="n">
+        <v>99.56999999999999</v>
+      </c>
+      <c r="J17" s="95" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="K17" s="95" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="L17" s="95" t="n">
+        <v>98.89</v>
+      </c>
+      <c r="M17" s="95" t="n">
+        <v>98.89</v>
+      </c>
+      <c r="N17" s="95" t="n">
+        <v>98.23</v>
+      </c>
+      <c r="O17" s="95" t="n">
+        <v>96.44</v>
+      </c>
+      <c r="P17" s="95" t="n">
+        <v>95.94</v>
+      </c>
+      <c r="Q17" s="95" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="R17" s="95" t="n">
+        <v>91.13</v>
+      </c>
+      <c r="S17" s="95" t="n">
+        <v>91.13</v>
+      </c>
+      <c r="T17" s="95" t="n">
+        <v>87.39</v>
+      </c>
+      <c r="U17" s="95" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="V17" s="95" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="W17" s="95" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="X17" s="95" t="n">
+        <v>54.39</v>
+      </c>
+      <c r="Y17" s="95" t="n">
+        <v>54.39</v>
+      </c>
+      <c r="Z17" s="95" t="n">
+        <v>38.93</v>
+      </c>
+      <c r="AA17" s="95" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="AB17" s="95" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="AC17" s="95" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="AD17" s="95" t="n">
+        <v/>
+      </c>
+      <c r="AE17" s="95" t="n">
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="58" t="inlineStr">
+      <c r="A18" s="76" t="inlineStr">
         <is>
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="60" t="n"/>
-      <c r="C18" s="60" t="n"/>
-      <c r="D18" s="60" t="n"/>
-      <c r="E18" s="60" t="n"/>
-      <c r="F18" s="60" t="n"/>
-      <c r="G18" s="60" t="n"/>
-      <c r="H18" s="60" t="n"/>
-      <c r="I18" s="60" t="n"/>
-      <c r="J18" s="60" t="n"/>
-      <c r="K18" s="60" t="n"/>
-      <c r="L18" s="60" t="n"/>
-      <c r="M18" s="60" t="n"/>
-      <c r="N18" s="60" t="n"/>
-      <c r="O18" s="60" t="n"/>
-      <c r="P18" s="60" t="n"/>
-      <c r="Q18" s="60" t="n"/>
-      <c r="R18" s="60" t="n"/>
-      <c r="S18" s="60" t="n"/>
-      <c r="T18" s="60" t="n"/>
-      <c r="U18" s="60" t="n"/>
-      <c r="V18" s="60" t="n"/>
-      <c r="W18" s="60" t="n"/>
-      <c r="X18" s="60" t="n"/>
-      <c r="Y18" s="60" t="n"/>
-      <c r="Z18" s="60" t="n"/>
-      <c r="AA18" s="60" t="n"/>
-      <c r="AB18" s="60" t="n"/>
-      <c r="AC18" s="60" t="n"/>
-      <c r="AD18" s="60" t="n"/>
-      <c r="AE18" s="60" t="n"/>
+      <c r="B18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="D18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="E18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AC18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="58" t="inlineStr">
+      <c r="A19" s="76" t="inlineStr">
         <is>
           <t>us500:RNG60</t>
         </is>
       </c>
-      <c r="B19" s="60" t="n"/>
-      <c r="C19" s="60" t="n"/>
-      <c r="D19" s="60" t="n"/>
-      <c r="E19" s="60" t="n"/>
-      <c r="F19" s="60" t="n"/>
-      <c r="G19" s="60" t="n"/>
-      <c r="H19" s="60" t="n"/>
-      <c r="I19" s="60" t="n"/>
-      <c r="J19" s="60" t="n"/>
-      <c r="K19" s="60" t="n"/>
-      <c r="L19" s="60" t="n"/>
-      <c r="M19" s="60" t="n"/>
-      <c r="N19" s="60" t="n"/>
-      <c r="O19" s="60" t="n"/>
-      <c r="P19" s="60" t="n"/>
-      <c r="Q19" s="60" t="n"/>
-      <c r="R19" s="60" t="n"/>
-      <c r="S19" s="60" t="n"/>
-      <c r="T19" s="60" t="n"/>
-      <c r="U19" s="60" t="n"/>
-      <c r="V19" s="60" t="n"/>
-      <c r="W19" s="60" t="n"/>
-      <c r="X19" s="60" t="n"/>
-      <c r="Y19" s="60" t="n"/>
-      <c r="Z19" s="60" t="n"/>
-      <c r="AA19" s="60" t="n"/>
-      <c r="AB19" s="60" t="n"/>
-      <c r="AC19" s="60" t="n"/>
-      <c r="AD19" s="60" t="n"/>
-      <c r="AE19" s="60" t="n"/>
+      <c r="B19" s="95" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C19" s="95" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D19" s="95" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E19" s="95" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="F19" s="95" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G19" s="95" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H19" s="95" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I19" s="95" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J19" s="95" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="K19" s="95" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="L19" s="95" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="M19" s="95" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="N19" s="95" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="O19" s="95" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="P19" s="95" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="Q19" s="95" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R19" s="95" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="S19" s="95" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T19" s="95" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="U19" s="95" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="V19" s="95" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="W19" s="95" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X19" s="95" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y19" s="95" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Z19" s="95" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA19" s="95" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB19" s="95" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC19" s="95" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AD19" s="95" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AE19" s="95" t="n">
+        <v>0.62</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="58" t="inlineStr">
+      <c r="A20" s="76" t="inlineStr">
         <is>
           <t>us500:RNG120</t>
         </is>
       </c>
-      <c r="B20" s="60" t="n"/>
-      <c r="C20" s="60" t="n"/>
-      <c r="D20" s="60" t="n"/>
-      <c r="E20" s="60" t="n"/>
-      <c r="F20" s="60" t="n"/>
-      <c r="G20" s="60" t="n"/>
-      <c r="H20" s="60" t="n"/>
-      <c r="I20" s="60" t="n"/>
-      <c r="J20" s="60" t="n"/>
-      <c r="K20" s="60" t="n"/>
-      <c r="L20" s="60" t="n"/>
-      <c r="M20" s="60" t="n"/>
-      <c r="N20" s="60" t="n"/>
-      <c r="O20" s="60" t="n"/>
-      <c r="P20" s="60" t="n"/>
-      <c r="Q20" s="60" t="n"/>
-      <c r="R20" s="60" t="n"/>
-      <c r="S20" s="60" t="n"/>
-      <c r="T20" s="60" t="n"/>
-      <c r="U20" s="60" t="n"/>
-      <c r="V20" s="60" t="n"/>
-      <c r="W20" s="60" t="n"/>
-      <c r="X20" s="60" t="n"/>
-      <c r="Y20" s="60" t="n"/>
-      <c r="Z20" s="60" t="n"/>
-      <c r="AA20" s="60" t="n"/>
-      <c r="AB20" s="60" t="n"/>
-      <c r="AC20" s="60" t="n"/>
-      <c r="AD20" s="60" t="n"/>
-      <c r="AE20" s="60" t="n"/>
+      <c r="B20" s="95" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="C20" s="95" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="D20" s="95" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="E20" s="95" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="F20" s="95" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="G20" s="95" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="H20" s="95" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="I20" s="95" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="J20" s="95" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="K20" s="95" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="L20" s="95" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="M20" s="95" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="N20" s="95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="O20" s="95" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="P20" s="95" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="Q20" s="95" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="R20" s="95" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="S20" s="95" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="T20" s="95" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="U20" s="95" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="V20" s="95" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="W20" s="95" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="X20" s="95" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="Y20" s="95" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="Z20" s="95" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="AA20" s="95" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="AB20" s="95" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="AC20" s="95" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AD20" s="95" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="AE20" s="95" t="n">
+        <v>5.69</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="58" t="inlineStr">
-        <is>
-          <t>us500:RSI2</t>
-        </is>
-      </c>
-      <c r="B21" s="60" t="n"/>
-      <c r="C21" s="60" t="n"/>
-      <c r="D21" s="60" t="n"/>
-      <c r="E21" s="60" t="n"/>
-      <c r="F21" s="60" t="n"/>
-      <c r="G21" s="60" t="n"/>
-      <c r="H21" s="60" t="n"/>
-      <c r="I21" s="60" t="n"/>
-      <c r="J21" s="60" t="n"/>
-      <c r="K21" s="60" t="n"/>
-      <c r="L21" s="60" t="n"/>
-      <c r="M21" s="60" t="n"/>
-      <c r="N21" s="60" t="n"/>
-      <c r="O21" s="60" t="n"/>
-      <c r="P21" s="60" t="n"/>
-      <c r="Q21" s="60" t="n"/>
-      <c r="R21" s="60" t="n"/>
-      <c r="S21" s="60" t="n"/>
-      <c r="T21" s="60" t="n"/>
-      <c r="U21" s="60" t="n"/>
-      <c r="V21" s="60" t="n"/>
-      <c r="W21" s="60" t="n"/>
-      <c r="X21" s="60" t="n"/>
-      <c r="Y21" s="60" t="n"/>
-      <c r="Z21" s="60" t="n"/>
-      <c r="AA21" s="60" t="n"/>
-      <c r="AB21" s="60" t="n"/>
-      <c r="AC21" s="60" t="n"/>
-      <c r="AD21" s="60" t="n"/>
-      <c r="AE21" s="60" t="n"/>
+      <c r="A21" s="76" t="inlineStr">
+        <is>
+          <t>us500:RS2</t>
+        </is>
+      </c>
+      <c r="B21" s="95" t="n">
+        <v>83.12</v>
+      </c>
+      <c r="C21" s="95" t="n">
+        <v>83.12</v>
+      </c>
+      <c r="D21" s="95" t="n">
+        <v>69.18000000000001</v>
+      </c>
+      <c r="E21" s="95" t="n">
+        <v>30.41</v>
+      </c>
+      <c r="F21" s="95" t="n">
+        <v>81.84</v>
+      </c>
+      <c r="G21" s="95" t="n">
+        <v>81.84</v>
+      </c>
+      <c r="H21" s="95" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="I21" s="95" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="J21" s="95" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="K21" s="95" t="n">
+        <v>86.19</v>
+      </c>
+      <c r="L21" s="95" t="n">
+        <v>60.63</v>
+      </c>
+      <c r="M21" s="95" t="n">
+        <v>60.63</v>
+      </c>
+      <c r="N21" s="95" t="n">
+        <v>83.51000000000001</v>
+      </c>
+      <c r="O21" s="95" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="P21" s="95" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="Q21" s="95" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="R21" s="95" t="n">
+        <v>76.79000000000001</v>
+      </c>
+      <c r="S21" s="95" t="n">
+        <v>76.79000000000001</v>
+      </c>
+      <c r="T21" s="95" t="n">
+        <v>92.34</v>
+      </c>
+      <c r="U21" s="95" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="V21" s="95" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="W21" s="95" t="n">
+        <v>95.83</v>
+      </c>
+      <c r="X21" s="95" t="n">
+        <v>95.06</v>
+      </c>
+      <c r="Y21" s="95" t="n">
+        <v>95.06</v>
+      </c>
+      <c r="Z21" s="95" t="n">
+        <v>91.83</v>
+      </c>
+      <c r="AA21" s="95" t="n">
+        <v>85.17</v>
+      </c>
+      <c r="AB21" s="95" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AC21" s="95" t="n">
+        <v>51.58</v>
+      </c>
+      <c r="AD21" s="95" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE21" s="95" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="58" t="inlineStr">
+      <c r="A22" s="76" t="inlineStr">
         <is>
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="60" t="n"/>
-      <c r="C22" s="60" t="n"/>
-      <c r="D22" s="60" t="n"/>
-      <c r="E22" s="60" t="n"/>
-      <c r="F22" s="60" t="n"/>
-      <c r="G22" s="60" t="n"/>
-      <c r="H22" s="60" t="n"/>
-      <c r="I22" s="60" t="n"/>
-      <c r="J22" s="60" t="n"/>
-      <c r="K22" s="60" t="n"/>
-      <c r="L22" s="60" t="n"/>
-      <c r="M22" s="60" t="n"/>
-      <c r="N22" s="60" t="n"/>
-      <c r="O22" s="60" t="n"/>
-      <c r="P22" s="60" t="n"/>
-      <c r="Q22" s="60" t="n"/>
-      <c r="R22" s="60" t="n"/>
-      <c r="S22" s="60" t="n"/>
-      <c r="T22" s="60" t="n"/>
-      <c r="U22" s="60" t="n"/>
-      <c r="V22" s="60" t="n"/>
-      <c r="W22" s="60" t="n"/>
-      <c r="X22" s="60" t="n"/>
-      <c r="Y22" s="60" t="n"/>
-      <c r="Z22" s="60" t="n"/>
-      <c r="AA22" s="60" t="n"/>
-      <c r="AB22" s="60" t="n"/>
-      <c r="AC22" s="60" t="n"/>
-      <c r="AD22" s="60" t="n"/>
-      <c r="AE22" s="60" t="n"/>
+      <c r="B22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="D22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AD22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="58" t="inlineStr">
+      <c r="A23" s="76" t="inlineStr">
         <is>
           <t>us30:RNG60</t>
         </is>
       </c>
-      <c r="B23" s="60" t="n"/>
-      <c r="C23" s="60" t="n"/>
-      <c r="D23" s="60" t="n"/>
-      <c r="E23" s="60" t="n"/>
-      <c r="F23" s="60" t="n"/>
-      <c r="G23" s="60" t="n"/>
-      <c r="H23" s="60" t="n"/>
-      <c r="I23" s="60" t="n"/>
-      <c r="J23" s="60" t="n"/>
-      <c r="K23" s="60" t="n"/>
-      <c r="L23" s="60" t="n"/>
-      <c r="M23" s="60" t="n"/>
-      <c r="N23" s="60" t="n"/>
-      <c r="O23" s="60" t="n"/>
-      <c r="P23" s="60" t="n"/>
-      <c r="Q23" s="60" t="n"/>
-      <c r="R23" s="60" t="n"/>
-      <c r="S23" s="60" t="n"/>
-      <c r="T23" s="60" t="n"/>
-      <c r="U23" s="60" t="n"/>
-      <c r="V23" s="60" t="n"/>
-      <c r="W23" s="60" t="n"/>
-      <c r="X23" s="60" t="n"/>
-      <c r="Y23" s="60" t="n"/>
-      <c r="Z23" s="60" t="n"/>
-      <c r="AA23" s="60" t="n"/>
-      <c r="AB23" s="60" t="n"/>
-      <c r="AC23" s="60" t="n"/>
-      <c r="AD23" s="60" t="n"/>
-      <c r="AE23" s="60" t="n"/>
+      <c r="B23" s="95" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C23" s="95" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D23" s="95" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="E23" s="95" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="F23" s="95" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="G23" s="95" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="H23" s="95" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="I23" s="95" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="J23" s="95" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="K23" s="95" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L23" s="95" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="M23" s="95" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="N23" s="95" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="O23" s="95" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="P23" s="95" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q23" s="95" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="R23" s="95" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="S23" s="95" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="T23" s="95" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="U23" s="95" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="V23" s="95" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="W23" s="95" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="X23" s="95" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="Y23" s="95" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="Z23" s="95" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AA23" s="95" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AB23" s="95" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="AC23" s="95" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="AD23" s="95" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AE23" s="95" t="n">
+        <v>4.12</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="58" t="inlineStr">
+      <c r="A24" s="76" t="inlineStr">
         <is>
           <t>us30:RNG120</t>
         </is>
       </c>
-      <c r="B24" s="60" t="n"/>
-      <c r="C24" s="60" t="n"/>
-      <c r="D24" s="60" t="n"/>
-      <c r="E24" s="60" t="n"/>
-      <c r="F24" s="60" t="n"/>
-      <c r="G24" s="60" t="n"/>
-      <c r="H24" s="60" t="n"/>
-      <c r="I24" s="60" t="n"/>
-      <c r="J24" s="60" t="n"/>
-      <c r="K24" s="60" t="n"/>
-      <c r="L24" s="60" t="n"/>
-      <c r="M24" s="60" t="n"/>
-      <c r="N24" s="60" t="n"/>
-      <c r="O24" s="60" t="n"/>
-      <c r="P24" s="60" t="n"/>
-      <c r="Q24" s="60" t="n"/>
-      <c r="R24" s="60" t="n"/>
-      <c r="S24" s="60" t="n"/>
-      <c r="T24" s="60" t="n"/>
-      <c r="U24" s="60" t="n"/>
-      <c r="V24" s="60" t="n"/>
-      <c r="W24" s="60" t="n"/>
-      <c r="X24" s="60" t="n"/>
-      <c r="Y24" s="60" t="n"/>
-      <c r="Z24" s="60" t="n"/>
-      <c r="AA24" s="60" t="n"/>
-      <c r="AB24" s="60" t="n"/>
-      <c r="AC24" s="60" t="n"/>
-      <c r="AD24" s="60" t="n"/>
-      <c r="AE24" s="60" t="n"/>
+      <c r="B24" s="95" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="C24" s="95" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="D24" s="95" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="E24" s="95" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="F24" s="95" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="G24" s="95" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="H24" s="95" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="I24" s="95" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="J24" s="95" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="K24" s="95" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="L24" s="95" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="M24" s="95" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="N24" s="95" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="O24" s="95" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="P24" s="95" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="Q24" s="95" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="R24" s="95" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="S24" s="95" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="T24" s="95" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="U24" s="95" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="V24" s="95" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="W24" s="95" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="X24" s="95" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="Y24" s="95" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="Z24" s="95" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AA24" s="95" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AB24" s="95" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="AC24" s="95" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AD24" s="95" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AE24" s="95" t="n">
+        <v>4.21</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="58" t="inlineStr">
-        <is>
-          <t>us30:RSI3</t>
-        </is>
-      </c>
-      <c r="B25" s="60" t="n"/>
-      <c r="C25" s="60" t="n"/>
-      <c r="D25" s="60" t="n"/>
-      <c r="E25" s="60" t="n"/>
-      <c r="F25" s="60" t="n"/>
-      <c r="G25" s="60" t="n"/>
-      <c r="H25" s="60" t="n"/>
-      <c r="I25" s="60" t="n"/>
-      <c r="J25" s="60" t="n"/>
-      <c r="K25" s="60" t="n"/>
-      <c r="L25" s="60" t="n"/>
-      <c r="M25" s="60" t="n"/>
-      <c r="N25" s="60" t="n"/>
-      <c r="O25" s="60" t="n"/>
-      <c r="P25" s="60" t="n"/>
-      <c r="Q25" s="60" t="n"/>
-      <c r="R25" s="60" t="n"/>
-      <c r="S25" s="60" t="n"/>
-      <c r="T25" s="60" t="n"/>
-      <c r="U25" s="60" t="n"/>
-      <c r="V25" s="60" t="n"/>
-      <c r="W25" s="60" t="n"/>
-      <c r="X25" s="60" t="n"/>
-      <c r="Y25" s="60" t="n"/>
-      <c r="Z25" s="60" t="n"/>
-      <c r="AA25" s="60" t="n"/>
-      <c r="AB25" s="60" t="n"/>
-      <c r="AC25" s="60" t="n"/>
-      <c r="AD25" s="60" t="n"/>
-      <c r="AE25" s="60" t="n"/>
+      <c r="A25" s="76" t="inlineStr">
+        <is>
+          <t>us30:RS3</t>
+        </is>
+      </c>
+      <c r="B25" s="95" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="C25" s="95" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="D25" s="95" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="E25" s="95" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="F25" s="95" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="G25" s="95" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="H25" s="95" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="I25" s="95" t="n">
+        <v>52.09</v>
+      </c>
+      <c r="J25" s="95" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="K25" s="95" t="n">
+        <v>76.02</v>
+      </c>
+      <c r="L25" s="95" t="n">
+        <v>74.91</v>
+      </c>
+      <c r="M25" s="95" t="n">
+        <v>74.91</v>
+      </c>
+      <c r="N25" s="95" t="n">
+        <v>66.62</v>
+      </c>
+      <c r="O25" s="95" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="P25" s="95" t="n">
+        <v>92.18000000000001</v>
+      </c>
+      <c r="Q25" s="95" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="R25" s="95" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="S25" s="95" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="T25" s="95" t="n">
+        <v>87.58</v>
+      </c>
+      <c r="U25" s="95" t="n">
+        <v>65.31</v>
+      </c>
+      <c r="V25" s="95" t="n">
+        <v>85.48999999999999</v>
+      </c>
+      <c r="W25" s="95" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="X25" s="95" t="n">
+        <v>82.94</v>
+      </c>
+      <c r="Y25" s="95" t="n">
+        <v>82.94</v>
+      </c>
+      <c r="Z25" s="95" t="n">
+        <v>71.68000000000001</v>
+      </c>
+      <c r="AA25" s="95" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="AB25" s="95" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="AC25" s="95" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="AD25" s="95" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="AE25" s="95" t="n">
+        <v>13.02</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="58" t="inlineStr">
+      <c r="A26" s="76" t="inlineStr">
         <is>
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="60" t="n"/>
-      <c r="C26" s="60" t="n"/>
-      <c r="D26" s="60" t="n"/>
-      <c r="E26" s="60" t="n"/>
-      <c r="F26" s="60" t="n"/>
-      <c r="G26" s="60" t="n"/>
-      <c r="H26" s="60" t="n"/>
-      <c r="I26" s="60" t="n"/>
-      <c r="J26" s="60" t="n"/>
-      <c r="K26" s="60" t="n"/>
-      <c r="L26" s="60" t="n"/>
-      <c r="M26" s="60" t="n"/>
-      <c r="N26" s="60" t="n"/>
-      <c r="O26" s="60" t="n"/>
-      <c r="P26" s="60" t="n"/>
-      <c r="Q26" s="60" t="n"/>
-      <c r="R26" s="60" t="n"/>
-      <c r="S26" s="60" t="n"/>
-      <c r="T26" s="60" t="n"/>
-      <c r="U26" s="60" t="n"/>
-      <c r="V26" s="60" t="n"/>
-      <c r="W26" s="60" t="n"/>
-      <c r="X26" s="60" t="n"/>
-      <c r="Y26" s="60" t="n"/>
-      <c r="Z26" s="60" t="n"/>
-      <c r="AA26" s="60" t="n"/>
-      <c r="AB26" s="60" t="n"/>
-      <c r="AC26" s="60" t="n"/>
-      <c r="AD26" s="60" t="n"/>
-      <c r="AE26" s="60" t="n"/>
+      <c r="B26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="D26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="E26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AC26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="58" t="inlineStr">
+      <c r="A27" s="76" t="inlineStr">
         <is>
           <t>ixic:RNG60</t>
         </is>
       </c>
-      <c r="B27" s="60" t="n"/>
-      <c r="C27" s="60" t="n"/>
-      <c r="D27" s="60" t="n"/>
-      <c r="E27" s="60" t="n"/>
-      <c r="F27" s="60" t="n"/>
-      <c r="G27" s="60" t="n"/>
-      <c r="H27" s="60" t="n"/>
-      <c r="I27" s="60" t="n"/>
-      <c r="J27" s="60" t="n"/>
-      <c r="K27" s="60" t="n"/>
-      <c r="L27" s="60" t="n"/>
-      <c r="M27" s="60" t="n"/>
-      <c r="N27" s="60" t="n"/>
-      <c r="O27" s="60" t="n"/>
-      <c r="P27" s="60" t="n"/>
-      <c r="Q27" s="60" t="n"/>
-      <c r="R27" s="60" t="n"/>
-      <c r="S27" s="60" t="n"/>
-      <c r="T27" s="60" t="n"/>
-      <c r="U27" s="60" t="n"/>
-      <c r="V27" s="60" t="n"/>
-      <c r="W27" s="60" t="n"/>
-      <c r="X27" s="60" t="n"/>
-      <c r="Y27" s="60" t="n"/>
-      <c r="Z27" s="60" t="n"/>
-      <c r="AA27" s="60" t="n"/>
-      <c r="AB27" s="60" t="n"/>
-      <c r="AC27" s="60" t="n"/>
-      <c r="AD27" s="60" t="n"/>
-      <c r="AE27" s="60" t="n"/>
+      <c r="B27" s="95" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="C27" s="95" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="D27" s="95" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="E27" s="95" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="F27" s="95" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="G27" s="95" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="H27" s="95" t="n">
+        <v>-3.91</v>
+      </c>
+      <c r="I27" s="95" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="J27" s="95" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="K27" s="95" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="L27" s="95" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="M27" s="95" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="N27" s="95" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O27" s="95" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P27" s="95" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q27" s="95" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R27" s="95" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S27" s="95" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T27" s="95" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U27" s="95" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="V27" s="95" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="W27" s="95" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="X27" s="95" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y27" s="95" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z27" s="95" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="AA27" s="95" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="AB27" s="95" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="AC27" s="95" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="AD27" s="95" t="n">
+        <v>-3.76</v>
+      </c>
+      <c r="AE27" s="95" t="n">
+        <v>-3.76</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="58" t="inlineStr">
+      <c r="A28" s="76" t="inlineStr">
         <is>
           <t>ixic:RNG120</t>
         </is>
       </c>
-      <c r="B28" s="60" t="n"/>
-      <c r="C28" s="60" t="n"/>
-      <c r="D28" s="60" t="n"/>
-      <c r="E28" s="60" t="n"/>
-      <c r="F28" s="60" t="n"/>
-      <c r="G28" s="60" t="n"/>
-      <c r="H28" s="60" t="n"/>
-      <c r="I28" s="60" t="n"/>
-      <c r="J28" s="60" t="n"/>
-      <c r="K28" s="60" t="n"/>
-      <c r="L28" s="60" t="n"/>
-      <c r="M28" s="60" t="n"/>
-      <c r="N28" s="60" t="n"/>
-      <c r="O28" s="60" t="n"/>
-      <c r="P28" s="60" t="n"/>
-      <c r="Q28" s="60" t="n"/>
-      <c r="R28" s="60" t="n"/>
-      <c r="S28" s="60" t="n"/>
-      <c r="T28" s="60" t="n"/>
-      <c r="U28" s="60" t="n"/>
-      <c r="V28" s="60" t="n"/>
-      <c r="W28" s="60" t="n"/>
-      <c r="X28" s="60" t="n"/>
-      <c r="Y28" s="60" t="n"/>
-      <c r="Z28" s="60" t="n"/>
-      <c r="AA28" s="60" t="n"/>
-      <c r="AB28" s="60" t="n"/>
-      <c r="AC28" s="60" t="n"/>
-      <c r="AD28" s="60" t="n"/>
-      <c r="AE28" s="60" t="n"/>
+      <c r="B28" s="95" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="C28" s="95" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="D28" s="95" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="E28" s="95" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="F28" s="95" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G28" s="95" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="H28" s="95" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="I28" s="95" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="J28" s="95" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="K28" s="95" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="L28" s="95" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="M28" s="95" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="N28" s="95" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="O28" s="95" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="P28" s="95" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="Q28" s="95" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="R28" s="95" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="S28" s="95" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="T28" s="95" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="U28" s="95" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="V28" s="95" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="W28" s="95" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="X28" s="95" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="Y28" s="95" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="Z28" s="95" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="AA28" s="95" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="AB28" s="95" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="AC28" s="95" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AD28" s="95" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="AE28" s="95" t="n">
+        <v>4.49</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="58" t="inlineStr">
-        <is>
-          <t>ixic:RSI2</t>
-        </is>
-      </c>
-      <c r="B29" s="60" t="n"/>
-      <c r="C29" s="60" t="n"/>
-      <c r="D29" s="60" t="n"/>
-      <c r="E29" s="60" t="n"/>
-      <c r="F29" s="60" t="n"/>
-      <c r="G29" s="60" t="n"/>
-      <c r="H29" s="60" t="n"/>
-      <c r="I29" s="60" t="n"/>
-      <c r="J29" s="60" t="n"/>
-      <c r="K29" s="60" t="n"/>
-      <c r="L29" s="60" t="n"/>
-      <c r="M29" s="60" t="n"/>
-      <c r="N29" s="60" t="n"/>
-      <c r="O29" s="60" t="n"/>
-      <c r="P29" s="60" t="n"/>
-      <c r="Q29" s="60" t="n"/>
-      <c r="R29" s="60" t="n"/>
-      <c r="S29" s="60" t="n"/>
-      <c r="T29" s="60" t="n"/>
-      <c r="U29" s="60" t="n"/>
-      <c r="V29" s="60" t="n"/>
-      <c r="W29" s="60" t="n"/>
-      <c r="X29" s="60" t="n"/>
-      <c r="Y29" s="60" t="n"/>
-      <c r="Z29" s="60" t="n"/>
-      <c r="AA29" s="60" t="n"/>
-      <c r="AB29" s="60" t="n"/>
-      <c r="AC29" s="60" t="n"/>
-      <c r="AD29" s="60" t="n"/>
-      <c r="AE29" s="60" t="n"/>
+      <c r="A29" s="76" t="inlineStr">
+        <is>
+          <t>ixic:RS2</t>
+        </is>
+      </c>
+      <c r="B29" s="95" t="n">
+        <v>82.01000000000001</v>
+      </c>
+      <c r="C29" s="95" t="n">
+        <v>82.01000000000001</v>
+      </c>
+      <c r="D29" s="95" t="n">
+        <v>72.98999999999999</v>
+      </c>
+      <c r="E29" s="95" t="n">
+        <v>32.92</v>
+      </c>
+      <c r="F29" s="95" t="n">
+        <v>85.03</v>
+      </c>
+      <c r="G29" s="95" t="n">
+        <v>85.03</v>
+      </c>
+      <c r="H29" s="95" t="n">
+        <v>20.54</v>
+      </c>
+      <c r="I29" s="95" t="n">
+        <v>21.97</v>
+      </c>
+      <c r="J29" s="95" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="K29" s="95" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="L29" s="95" t="n">
+        <v>51.35</v>
+      </c>
+      <c r="M29" s="95" t="n">
+        <v>51.35</v>
+      </c>
+      <c r="N29" s="95" t="n">
+        <v>96.66</v>
+      </c>
+      <c r="O29" s="95" t="n">
+        <v>89.75</v>
+      </c>
+      <c r="P29" s="95" t="n">
+        <v>88.93000000000001</v>
+      </c>
+      <c r="Q29" s="95" t="n">
+        <v>77.02</v>
+      </c>
+      <c r="R29" s="95" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="S29" s="95" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="T29" s="95" t="n">
+        <v>92.18000000000001</v>
+      </c>
+      <c r="U29" s="95" t="n">
+        <v>42.32</v>
+      </c>
+      <c r="V29" s="95" t="n">
+        <v>70.06</v>
+      </c>
+      <c r="W29" s="95" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="X29" s="95" t="n">
+        <v>95.17</v>
+      </c>
+      <c r="Y29" s="95" t="n">
+        <v>95.17</v>
+      </c>
+      <c r="Z29" s="95" t="n">
+        <v>92.73999999999999</v>
+      </c>
+      <c r="AA29" s="95" t="n">
+        <v>88.20999999999999</v>
+      </c>
+      <c r="AB29" s="95" t="n">
+        <v>65.19</v>
+      </c>
+      <c r="AC29" s="95" t="n">
+        <v>44.48</v>
+      </c>
+      <c r="AD29" s="95" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AE29" s="95" t="n">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="58" t="inlineStr">
+      <c r="A30" s="76" t="inlineStr">
         <is>
           <t>jp225:EIDE</t>
         </is>
       </c>
-      <c r="B30" s="60" t="n"/>
-      <c r="C30" s="60" t="n"/>
-      <c r="D30" s="60" t="n"/>
-      <c r="E30" s="60" t="n"/>
-      <c r="F30" s="60" t="n"/>
-      <c r="G30" s="60" t="n"/>
-      <c r="H30" s="60" t="n"/>
-      <c r="I30" s="60" t="n"/>
-      <c r="J30" s="60" t="n"/>
-      <c r="K30" s="60" t="n"/>
-      <c r="L30" s="60" t="n"/>
-      <c r="M30" s="60" t="n"/>
-      <c r="N30" s="60" t="n"/>
-      <c r="O30" s="60" t="n"/>
-      <c r="P30" s="60" t="n"/>
-      <c r="Q30" s="60" t="n"/>
-      <c r="R30" s="60" t="n"/>
-      <c r="S30" s="60" t="n"/>
-      <c r="T30" s="60" t="n"/>
-      <c r="U30" s="60" t="n"/>
-      <c r="V30" s="60" t="n"/>
-      <c r="W30" s="60" t="n"/>
-      <c r="X30" s="60" t="n"/>
-      <c r="Y30" s="60" t="n"/>
-      <c r="Z30" s="60" t="n"/>
-      <c r="AA30" s="60" t="n"/>
-      <c r="AB30" s="60" t="n"/>
-      <c r="AC30" s="60" t="n"/>
-      <c r="AD30" s="60" t="n"/>
-      <c r="AE30" s="60" t="n"/>
+      <c r="B30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Z30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="58" t="inlineStr">
+      <c r="A31" s="76" t="inlineStr">
         <is>
           <t>jp225:RNG60</t>
         </is>
       </c>
-      <c r="B31" s="60" t="n"/>
-      <c r="C31" s="60" t="n"/>
-      <c r="D31" s="60" t="n"/>
-      <c r="E31" s="60" t="n"/>
-      <c r="F31" s="60" t="n"/>
-      <c r="G31" s="60" t="n"/>
-      <c r="H31" s="60" t="n"/>
-      <c r="I31" s="60" t="n"/>
-      <c r="J31" s="60" t="n"/>
-      <c r="K31" s="60" t="n"/>
-      <c r="L31" s="60" t="n"/>
-      <c r="M31" s="60" t="n"/>
-      <c r="N31" s="60" t="n"/>
-      <c r="O31" s="60" t="n"/>
-      <c r="P31" s="60" t="n"/>
-      <c r="Q31" s="60" t="n"/>
-      <c r="R31" s="60" t="n"/>
-      <c r="S31" s="60" t="n"/>
-      <c r="T31" s="60" t="n"/>
-      <c r="U31" s="60" t="n"/>
-      <c r="V31" s="60" t="n"/>
-      <c r="W31" s="60" t="n"/>
-      <c r="X31" s="60" t="n"/>
-      <c r="Y31" s="60" t="n"/>
-      <c r="Z31" s="60" t="n"/>
-      <c r="AA31" s="60" t="n"/>
-      <c r="AB31" s="60" t="n"/>
-      <c r="AC31" s="60" t="n"/>
-      <c r="AD31" s="60" t="n"/>
-      <c r="AE31" s="60" t="n"/>
+      <c r="B31" s="95" t="n">
+        <v>-4.18</v>
+      </c>
+      <c r="C31" s="95" t="n">
+        <v>-4.84</v>
+      </c>
+      <c r="D31" s="95" t="n">
+        <v>-5.47</v>
+      </c>
+      <c r="E31" s="95" t="n">
+        <v>-6.85</v>
+      </c>
+      <c r="F31" s="95" t="n">
+        <v>-7.64</v>
+      </c>
+      <c r="G31" s="95" t="n">
+        <v>-7.64</v>
+      </c>
+      <c r="H31" s="95" t="n">
+        <v>-7.28</v>
+      </c>
+      <c r="I31" s="95" t="n">
+        <v>-7.29</v>
+      </c>
+      <c r="J31" s="95" t="n">
+        <v>-5.52</v>
+      </c>
+      <c r="K31" s="95" t="n">
+        <v>-7.32</v>
+      </c>
+      <c r="L31" s="95" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="M31" s="95" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="N31" s="95" t="n">
+        <v>-2.87</v>
+      </c>
+      <c r="O31" s="95" t="n">
+        <v>-4.44</v>
+      </c>
+      <c r="P31" s="95" t="n">
+        <v>-4.15</v>
+      </c>
+      <c r="Q31" s="95" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="R31" s="95" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="S31" s="95" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="T31" s="95" t="n">
+        <v>-6.33</v>
+      </c>
+      <c r="U31" s="95" t="n">
+        <v>-7.13</v>
+      </c>
+      <c r="V31" s="95" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="W31" s="95" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="X31" s="95" t="n">
+        <v>-5.31</v>
+      </c>
+      <c r="Y31" s="95" t="n">
+        <v>-5.31</v>
+      </c>
+      <c r="Z31" s="95" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AA31" s="95" t="n">
+        <v>-7.44</v>
+      </c>
+      <c r="AB31" s="95" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="AC31" s="95" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="AD31" s="95" t="n">
+        <v>-6.01</v>
+      </c>
+      <c r="AE31" s="95" t="n">
+        <v>-6.01</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="58" t="inlineStr">
+      <c r="A32" s="76" t="inlineStr">
         <is>
           <t>jp225:RNG120</t>
         </is>
       </c>
-      <c r="B32" s="60" t="n"/>
-      <c r="C32" s="60" t="n"/>
-      <c r="D32" s="60" t="n"/>
-      <c r="E32" s="60" t="n"/>
-      <c r="F32" s="60" t="n"/>
-      <c r="G32" s="60" t="n"/>
-      <c r="H32" s="60" t="n"/>
-      <c r="I32" s="60" t="n"/>
-      <c r="J32" s="60" t="n"/>
-      <c r="K32" s="60" t="n"/>
-      <c r="L32" s="60" t="n"/>
-      <c r="M32" s="60" t="n"/>
-      <c r="N32" s="60" t="n"/>
-      <c r="O32" s="60" t="n"/>
-      <c r="P32" s="60" t="n"/>
-      <c r="Q32" s="60" t="n"/>
-      <c r="R32" s="60" t="n"/>
-      <c r="S32" s="60" t="n"/>
-      <c r="T32" s="60" t="n"/>
-      <c r="U32" s="60" t="n"/>
-      <c r="V32" s="60" t="n"/>
-      <c r="W32" s="60" t="n"/>
-      <c r="X32" s="60" t="n"/>
-      <c r="Y32" s="60" t="n"/>
-      <c r="Z32" s="60" t="n"/>
-      <c r="AA32" s="60" t="n"/>
-      <c r="AB32" s="60" t="n"/>
-      <c r="AC32" s="60" t="n"/>
-      <c r="AD32" s="60" t="n"/>
-      <c r="AE32" s="60" t="n"/>
+      <c r="B32" s="95" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="C32" s="95" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="D32" s="95" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E32" s="95" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F32" s="95" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="G32" s="95" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="H32" s="95" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="I32" s="95" t="n">
+        <v>-4.48</v>
+      </c>
+      <c r="J32" s="95" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="K32" s="95" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="L32" s="95" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M32" s="95" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N32" s="95" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="O32" s="95" t="n">
+        <v>-4.01</v>
+      </c>
+      <c r="P32" s="95" t="n">
+        <v>-4.76</v>
+      </c>
+      <c r="Q32" s="95" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="R32" s="95" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="S32" s="95" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="T32" s="95" t="n">
+        <v>-7.96</v>
+      </c>
+      <c r="U32" s="95" t="n">
+        <v>-9.43</v>
+      </c>
+      <c r="V32" s="95" t="n">
+        <v>-11.19</v>
+      </c>
+      <c r="W32" s="95" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="X32" s="95" t="n">
+        <v>-9.48</v>
+      </c>
+      <c r="Y32" s="95" t="n">
+        <v>-9.48</v>
+      </c>
+      <c r="Z32" s="95" t="n">
+        <v>-9.92</v>
+      </c>
+      <c r="AA32" s="95" t="n">
+        <v>-12.73</v>
+      </c>
+      <c r="AB32" s="95" t="n">
+        <v>-9.609999999999999</v>
+      </c>
+      <c r="AC32" s="95" t="n">
+        <v>-8.869999999999999</v>
+      </c>
+      <c r="AD32" s="95" t="n">
+        <v>-5.98</v>
+      </c>
+      <c r="AE32" s="95" t="n">
+        <v>-5.98</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="58" t="inlineStr">
-        <is>
-          <t>jp225:RSI5</t>
-        </is>
-      </c>
-      <c r="B33" s="60" t="n"/>
-      <c r="C33" s="60" t="n"/>
-      <c r="D33" s="60" t="n"/>
-      <c r="E33" s="60" t="n"/>
-      <c r="F33" s="60" t="n"/>
-      <c r="G33" s="60" t="n"/>
-      <c r="H33" s="60" t="n"/>
-      <c r="I33" s="60" t="n"/>
-      <c r="J33" s="60" t="n"/>
-      <c r="K33" s="60" t="n"/>
-      <c r="L33" s="60" t="n"/>
-      <c r="M33" s="60" t="n"/>
-      <c r="N33" s="60" t="n"/>
-      <c r="O33" s="60" t="n"/>
-      <c r="P33" s="60" t="n"/>
-      <c r="Q33" s="60" t="n"/>
-      <c r="R33" s="60" t="n"/>
-      <c r="S33" s="60" t="n"/>
-      <c r="T33" s="60" t="n"/>
-      <c r="U33" s="60" t="n"/>
-      <c r="V33" s="60" t="n"/>
-      <c r="W33" s="60" t="n"/>
-      <c r="X33" s="60" t="n"/>
-      <c r="Y33" s="60" t="n"/>
-      <c r="Z33" s="60" t="n"/>
-      <c r="AA33" s="60" t="n"/>
-      <c r="AB33" s="60" t="n"/>
-      <c r="AC33" s="60" t="n"/>
-      <c r="AD33" s="60" t="n"/>
-      <c r="AE33" s="60" t="n"/>
+      <c r="A33" s="76" t="inlineStr">
+        <is>
+          <t>jp225:RS9</t>
+        </is>
+      </c>
+      <c r="B33" s="95" t="n">
+        <v>61.28</v>
+      </c>
+      <c r="C33" s="95" t="n">
+        <v>60.41</v>
+      </c>
+      <c r="D33" s="95" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="E33" s="95" t="n">
+        <v>62.13</v>
+      </c>
+      <c r="F33" s="95" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="G33" s="95" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="H33" s="95" t="n">
+        <v>56.21</v>
+      </c>
+      <c r="I33" s="95" t="n">
+        <v>50.28</v>
+      </c>
+      <c r="J33" s="95" t="n">
+        <v>58.22</v>
+      </c>
+      <c r="K33" s="95" t="n">
+        <v>52.42</v>
+      </c>
+      <c r="L33" s="95" t="n">
+        <v>77.31</v>
+      </c>
+      <c r="M33" s="95" t="n">
+        <v>77.31</v>
+      </c>
+      <c r="N33" s="95" t="n">
+        <v>71.64</v>
+      </c>
+      <c r="O33" s="95" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="P33" s="95" t="n">
+        <v>63.04</v>
+      </c>
+      <c r="Q33" s="95" t="n">
+        <v>60.77</v>
+      </c>
+      <c r="R33" s="95" t="n">
+        <v>60.77</v>
+      </c>
+      <c r="S33" s="95" t="n">
+        <v>60.77</v>
+      </c>
+      <c r="T33" s="95" t="n">
+        <v>54.21</v>
+      </c>
+      <c r="U33" s="95" t="n">
+        <v>42.56</v>
+      </c>
+      <c r="V33" s="95" t="n">
+        <v>39.44</v>
+      </c>
+      <c r="W33" s="95" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="X33" s="95" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="Y33" s="95" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="Z33" s="95" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="AA33" s="95" t="n">
+        <v>26.47</v>
+      </c>
+      <c r="AB33" s="95" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="AC33" s="95" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="AD33" s="95" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="AE33" s="95" t="n">
+        <v>33.25</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="58" t="inlineStr">
+      <c r="A34" s="76" t="inlineStr">
         <is>
           <t>vn:EIDE</t>
         </is>
       </c>
-      <c r="B34" s="60" t="n"/>
-      <c r="C34" s="60" t="n"/>
-      <c r="D34" s="60" t="n"/>
-      <c r="E34" s="60" t="n"/>
-      <c r="F34" s="60" t="n"/>
-      <c r="G34" s="60" t="n"/>
-      <c r="H34" s="60" t="n"/>
-      <c r="I34" s="60" t="n"/>
-      <c r="J34" s="60" t="n"/>
-      <c r="K34" s="60" t="n"/>
-      <c r="L34" s="60" t="n"/>
-      <c r="M34" s="60" t="n"/>
-      <c r="N34" s="60" t="n"/>
-      <c r="O34" s="60" t="n"/>
-      <c r="P34" s="60" t="n"/>
-      <c r="Q34" s="60" t="n"/>
-      <c r="R34" s="60" t="n"/>
-      <c r="S34" s="60" t="n"/>
-      <c r="T34" s="60" t="n"/>
-      <c r="U34" s="60" t="n"/>
-      <c r="V34" s="60" t="n"/>
-      <c r="W34" s="60" t="n"/>
-      <c r="X34" s="60" t="n"/>
-      <c r="Y34" s="60" t="n"/>
-      <c r="Z34" s="60" t="n"/>
-      <c r="AA34" s="60" t="n"/>
-      <c r="AB34" s="60" t="n"/>
-      <c r="AC34" s="60" t="n"/>
-      <c r="AD34" s="60" t="n"/>
-      <c r="AE34" s="60" t="n"/>
+      <c r="B34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="D34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="X34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Y34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AE34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="58" t="inlineStr">
+      <c r="A35" s="76" t="inlineStr">
         <is>
           <t>vn:RNG60</t>
         </is>
       </c>
-      <c r="B35" s="60" t="n"/>
-      <c r="C35" s="60" t="n"/>
-      <c r="D35" s="60" t="n"/>
-      <c r="E35" s="60" t="n"/>
-      <c r="F35" s="60" t="n"/>
-      <c r="G35" s="60" t="n"/>
-      <c r="H35" s="60" t="n"/>
-      <c r="I35" s="60" t="n"/>
-      <c r="J35" s="60" t="n"/>
-      <c r="K35" s="60" t="n"/>
-      <c r="L35" s="60" t="n"/>
-      <c r="M35" s="60" t="n"/>
-      <c r="N35" s="60" t="n"/>
-      <c r="O35" s="60" t="n"/>
-      <c r="P35" s="60" t="n"/>
-      <c r="Q35" s="60" t="n"/>
-      <c r="R35" s="60" t="n"/>
-      <c r="S35" s="60" t="n"/>
-      <c r="T35" s="60" t="n"/>
-      <c r="U35" s="60" t="n"/>
-      <c r="V35" s="60" t="n"/>
-      <c r="W35" s="60" t="n"/>
-      <c r="X35" s="60" t="n"/>
-      <c r="Y35" s="60" t="n"/>
-      <c r="Z35" s="60" t="n"/>
-      <c r="AA35" s="60" t="n"/>
-      <c r="AB35" s="60" t="n"/>
-      <c r="AC35" s="60" t="n"/>
-      <c r="AD35" s="60" t="n"/>
-      <c r="AE35" s="60" t="n"/>
+      <c r="B35" s="95" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C35" s="95" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D35" s="95" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="E35" s="95" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="F35" s="95" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="G35" s="95" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="H35" s="95" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="I35" s="95" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J35" s="95" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K35" s="95" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L35" s="95" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M35" s="95" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N35" s="95" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="O35" s="95" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P35" s="95" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q35" s="95" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R35" s="95" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="S35" s="95" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="T35" s="95" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U35" s="95" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="V35" s="95" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="W35" s="95" t="n">
+        <v>-3.34</v>
+      </c>
+      <c r="X35" s="95" t="n">
+        <v>-2.39</v>
+      </c>
+      <c r="Y35" s="95" t="n">
+        <v>-2.39</v>
+      </c>
+      <c r="Z35" s="95" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="AA35" s="95" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="AB35" s="95" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="AC35" s="95" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="AD35" s="95" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="AE35" s="95" t="n">
+        <v>-2.12</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="58" t="inlineStr">
+      <c r="A36" s="76" t="inlineStr">
         <is>
           <t>vn:RNG120</t>
         </is>
       </c>
-      <c r="B36" s="60" t="n"/>
-      <c r="C36" s="60" t="n"/>
-      <c r="D36" s="60" t="n"/>
-      <c r="E36" s="60" t="n"/>
-      <c r="F36" s="60" t="n"/>
-      <c r="G36" s="60" t="n"/>
-      <c r="H36" s="60" t="n"/>
-      <c r="I36" s="60" t="n"/>
-      <c r="J36" s="60" t="n"/>
-      <c r="K36" s="60" t="n"/>
-      <c r="L36" s="60" t="n"/>
-      <c r="M36" s="60" t="n"/>
-      <c r="N36" s="60" t="n"/>
-      <c r="O36" s="60" t="n"/>
-      <c r="P36" s="60" t="n"/>
-      <c r="Q36" s="60" t="n"/>
-      <c r="R36" s="60" t="n"/>
-      <c r="S36" s="60" t="n"/>
-      <c r="T36" s="60" t="n"/>
-      <c r="U36" s="60" t="n"/>
-      <c r="V36" s="60" t="n"/>
-      <c r="W36" s="60" t="n"/>
-      <c r="X36" s="60" t="n"/>
-      <c r="Y36" s="60" t="n"/>
-      <c r="Z36" s="60" t="n"/>
-      <c r="AA36" s="60" t="n"/>
-      <c r="AB36" s="60" t="n"/>
-      <c r="AC36" s="60" t="n"/>
-      <c r="AD36" s="60" t="n"/>
-      <c r="AE36" s="60" t="n"/>
+      <c r="B36" s="95" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="C36" s="95" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="D36" s="95" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="E36" s="95" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="F36" s="95" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="G36" s="95" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="H36" s="95" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I36" s="95" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="J36" s="95" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="K36" s="95" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="L36" s="95" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M36" s="95" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N36" s="95" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O36" s="95" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P36" s="95" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="Q36" s="95" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="R36" s="95" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="S36" s="95" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="T36" s="95" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="U36" s="95" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="V36" s="95" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="W36" s="95" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="X36" s="95" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="Y36" s="95" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="Z36" s="95" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="AA36" s="95" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="AB36" s="95" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC36" s="95" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD36" s="95" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AE36" s="95" t="n">
+        <v>0.8100000000000001</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="58" t="inlineStr">
-        <is>
-          <t>vn:RSI3</t>
-        </is>
-      </c>
-      <c r="B37" s="60" t="n"/>
-      <c r="C37" s="60" t="n"/>
-      <c r="D37" s="60" t="n"/>
-      <c r="E37" s="60" t="n"/>
-      <c r="F37" s="60" t="n"/>
-      <c r="G37" s="60" t="n"/>
-      <c r="H37" s="60" t="n"/>
-      <c r="I37" s="60" t="n"/>
-      <c r="J37" s="60" t="n"/>
-      <c r="K37" s="60" t="n"/>
-      <c r="L37" s="60" t="n"/>
-      <c r="M37" s="60" t="n"/>
-      <c r="N37" s="60" t="n"/>
-      <c r="O37" s="60" t="n"/>
-      <c r="P37" s="60" t="n"/>
-      <c r="Q37" s="60" t="n"/>
-      <c r="R37" s="60" t="n"/>
-      <c r="S37" s="60" t="n"/>
-      <c r="T37" s="60" t="n"/>
-      <c r="U37" s="60" t="n"/>
-      <c r="V37" s="60" t="n"/>
-      <c r="W37" s="60" t="n"/>
-      <c r="X37" s="60" t="n"/>
-      <c r="Y37" s="60" t="n"/>
-      <c r="Z37" s="60" t="n"/>
-      <c r="AA37" s="60" t="n"/>
-      <c r="AB37" s="60" t="n"/>
-      <c r="AC37" s="60" t="n"/>
-      <c r="AD37" s="60" t="n"/>
-      <c r="AE37" s="60" t="n"/>
+      <c r="A37" s="76" t="inlineStr">
+        <is>
+          <t>vn:RS3</t>
+        </is>
+      </c>
+      <c r="B37" s="95" t="n">
+        <v>78.16</v>
+      </c>
+      <c r="C37" s="95" t="n">
+        <v>69.63</v>
+      </c>
+      <c r="D37" s="95" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="E37" s="95" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="F37" s="95" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="G37" s="95" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="H37" s="95" t="n">
+        <v>23.23</v>
+      </c>
+      <c r="I37" s="95" t="n">
+        <v>50.34</v>
+      </c>
+      <c r="J37" s="95" t="n">
+        <v>77.23999999999999</v>
+      </c>
+      <c r="K37" s="95" t="n">
+        <v>65.09</v>
+      </c>
+      <c r="L37" s="95" t="n">
+        <v>86.66</v>
+      </c>
+      <c r="M37" s="95" t="n">
+        <v>86.66</v>
+      </c>
+      <c r="N37" s="95" t="n">
+        <v>90.48999999999999</v>
+      </c>
+      <c r="O37" s="95" t="n">
+        <v>88</v>
+      </c>
+      <c r="P37" s="95" t="n">
+        <v>77.98</v>
+      </c>
+      <c r="Q37" s="95" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="R37" s="95" t="n">
+        <v>77.68000000000001</v>
+      </c>
+      <c r="S37" s="95" t="n">
+        <v>77.68000000000001</v>
+      </c>
+      <c r="T37" s="95" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="U37" s="95" t="n">
+        <v>68.98</v>
+      </c>
+      <c r="V37" s="95" t="n">
+        <v>60.96</v>
+      </c>
+      <c r="W37" s="95" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="X37" s="95" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="Y37" s="95" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="Z37" s="95" t="n">
+        <v>30.12</v>
+      </c>
+      <c r="AA37" s="95" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="AB37" s="95" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="AC37" s="95" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="AD37" s="95" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="AE37" s="95" t="n">
+        <v>44.72</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="58" t="inlineStr">
+      <c r="A38" s="76" t="inlineStr">
         <is>
           <t>sensex:EIDE</t>
         </is>
       </c>
-      <c r="B38" s="60" t="n"/>
-      <c r="C38" s="60" t="n"/>
-      <c r="D38" s="60" t="n"/>
-      <c r="E38" s="60" t="n"/>
-      <c r="F38" s="60" t="n"/>
-      <c r="G38" s="60" t="n"/>
-      <c r="H38" s="60" t="n"/>
-      <c r="I38" s="60" t="n"/>
-      <c r="J38" s="60" t="n"/>
-      <c r="K38" s="60" t="n"/>
-      <c r="L38" s="60" t="n"/>
-      <c r="M38" s="60" t="n"/>
-      <c r="N38" s="60" t="n"/>
-      <c r="O38" s="60" t="n"/>
-      <c r="P38" s="60" t="n"/>
-      <c r="Q38" s="60" t="n"/>
-      <c r="R38" s="60" t="n"/>
-      <c r="S38" s="60" t="n"/>
-      <c r="T38" s="60" t="n"/>
-      <c r="U38" s="60" t="n"/>
-      <c r="V38" s="60" t="n"/>
-      <c r="W38" s="60" t="n"/>
-      <c r="X38" s="60" t="n"/>
-      <c r="Y38" s="60" t="n"/>
-      <c r="Z38" s="60" t="n"/>
-      <c r="AA38" s="60" t="n"/>
-      <c r="AB38" s="60" t="n"/>
-      <c r="AC38" s="60" t="n"/>
-      <c r="AD38" s="60" t="n"/>
-      <c r="AE38" s="60" t="n"/>
+      <c r="B38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AC38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="58" t="inlineStr">
+      <c r="A39" s="76" t="inlineStr">
         <is>
           <t>sensex:RNG60</t>
         </is>
       </c>
-      <c r="B39" s="60" t="n"/>
-      <c r="C39" s="60" t="n"/>
-      <c r="D39" s="60" t="n"/>
-      <c r="E39" s="60" t="n"/>
-      <c r="F39" s="60" t="n"/>
-      <c r="G39" s="60" t="n"/>
-      <c r="H39" s="60" t="n"/>
-      <c r="I39" s="60" t="n"/>
-      <c r="J39" s="60" t="n"/>
-      <c r="K39" s="60" t="n"/>
-      <c r="L39" s="60" t="n"/>
-      <c r="M39" s="60" t="n"/>
-      <c r="N39" s="60" t="n"/>
-      <c r="O39" s="60" t="n"/>
-      <c r="P39" s="60" t="n"/>
-      <c r="Q39" s="60" t="n"/>
-      <c r="R39" s="60" t="n"/>
-      <c r="S39" s="60" t="n"/>
-      <c r="T39" s="60" t="n"/>
-      <c r="U39" s="60" t="n"/>
-      <c r="V39" s="60" t="n"/>
-      <c r="W39" s="60" t="n"/>
-      <c r="X39" s="60" t="n"/>
-      <c r="Y39" s="60" t="n"/>
-      <c r="Z39" s="60" t="n"/>
-      <c r="AA39" s="60" t="n"/>
-      <c r="AB39" s="60" t="n"/>
-      <c r="AC39" s="60" t="n"/>
-      <c r="AD39" s="60" t="n"/>
-      <c r="AE39" s="60" t="n"/>
+      <c r="B39" s="95" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C39" s="95" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D39" s="95" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E39" s="95" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="F39" s="95" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="G39" s="95" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="H39" s="95" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="I39" s="95" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="J39" s="95" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="K39" s="95" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="L39" s="95" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M39" s="95" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="N39" s="95" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="O39" s="95" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="P39" s="95" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="Q39" s="95" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="R39" s="95" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="S39" s="95" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="T39" s="95" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="U39" s="95" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="V39" s="95" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="W39" s="95" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="X39" s="95" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="Y39" s="95" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="Z39" s="95" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="AA39" s="95" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="AB39" s="95" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC39" s="95" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="AD39" s="95" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AE39" s="95" t="n">
+        <v>5.98</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="58" t="inlineStr">
+      <c r="A40" s="76" t="inlineStr">
         <is>
           <t>sensex:RNG120</t>
         </is>
       </c>
-      <c r="B40" s="60" t="n"/>
-      <c r="C40" s="60" t="n"/>
-      <c r="D40" s="60" t="n"/>
-      <c r="E40" s="60" t="n"/>
-      <c r="F40" s="60" t="n"/>
-      <c r="G40" s="60" t="n"/>
-      <c r="H40" s="60" t="n"/>
-      <c r="I40" s="60" t="n"/>
-      <c r="J40" s="60" t="n"/>
-      <c r="K40" s="60" t="n"/>
-      <c r="L40" s="60" t="n"/>
-      <c r="M40" s="60" t="n"/>
-      <c r="N40" s="60" t="n"/>
-      <c r="O40" s="60" t="n"/>
-      <c r="P40" s="60" t="n"/>
-      <c r="Q40" s="60" t="n"/>
-      <c r="R40" s="60" t="n"/>
-      <c r="S40" s="60" t="n"/>
-      <c r="T40" s="60" t="n"/>
-      <c r="U40" s="60" t="n"/>
-      <c r="V40" s="60" t="n"/>
-      <c r="W40" s="60" t="n"/>
-      <c r="X40" s="60" t="n"/>
-      <c r="Y40" s="60" t="n"/>
-      <c r="Z40" s="60" t="n"/>
-      <c r="AA40" s="60" t="n"/>
-      <c r="AB40" s="60" t="n"/>
-      <c r="AC40" s="60" t="n"/>
-      <c r="AD40" s="60" t="n"/>
-      <c r="AE40" s="60" t="n"/>
+      <c r="B40" s="95" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="C40" s="95" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="D40" s="95" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="E40" s="95" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="F40" s="95" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="G40" s="95" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="H40" s="95" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="I40" s="95" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="J40" s="95" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="K40" s="95" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="L40" s="95" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="M40" s="95" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="N40" s="95" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="O40" s="95" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="P40" s="95" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="Q40" s="95" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="R40" s="95" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="S40" s="95" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="T40" s="95" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="U40" s="95" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="V40" s="95" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="W40" s="95" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="X40" s="95" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="Y40" s="95" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="Z40" s="95" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="AA40" s="95" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="AB40" s="95" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="AC40" s="95" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="AD40" s="95" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="AE40" s="95" t="n">
+        <v>11.57</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="58" t="inlineStr">
-        <is>
-          <t>sensex:RSI7</t>
-        </is>
-      </c>
-      <c r="B41" s="60" t="n"/>
-      <c r="C41" s="60" t="n"/>
-      <c r="D41" s="60" t="n"/>
-      <c r="E41" s="60" t="n"/>
-      <c r="F41" s="60" t="n"/>
-      <c r="G41" s="60" t="n"/>
-      <c r="H41" s="60" t="n"/>
-      <c r="I41" s="60" t="n"/>
-      <c r="J41" s="60" t="n"/>
-      <c r="K41" s="60" t="n"/>
-      <c r="L41" s="60" t="n"/>
-      <c r="M41" s="60" t="n"/>
-      <c r="N41" s="60" t="n"/>
-      <c r="O41" s="60" t="n"/>
-      <c r="P41" s="60" t="n"/>
-      <c r="Q41" s="60" t="n"/>
-      <c r="R41" s="60" t="n"/>
-      <c r="S41" s="60" t="n"/>
-      <c r="T41" s="60" t="n"/>
-      <c r="U41" s="60" t="n"/>
-      <c r="V41" s="60" t="n"/>
-      <c r="W41" s="60" t="n"/>
-      <c r="X41" s="60" t="n"/>
-      <c r="Y41" s="60" t="n"/>
-      <c r="Z41" s="60" t="n"/>
-      <c r="AA41" s="60" t="n"/>
-      <c r="AB41" s="60" t="n"/>
-      <c r="AC41" s="60" t="n"/>
-      <c r="AD41" s="60" t="n"/>
-      <c r="AE41" s="60" t="n"/>
+      <c r="A41" s="96" t="inlineStr">
+        <is>
+          <t>sensex:RS10</t>
+        </is>
+      </c>
+      <c r="B41" s="95" t="n">
+        <v>37.56</v>
+      </c>
+      <c r="C41" s="95" t="n">
+        <v>35.74</v>
+      </c>
+      <c r="D41" s="95" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="E41" s="95" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="F41" s="95" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="G41" s="95" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="H41" s="95" t="n">
+        <v>38.91</v>
+      </c>
+      <c r="I41" s="95" t="n">
+        <v>56.68</v>
+      </c>
+      <c r="J41" s="95" t="n">
+        <v>56.68</v>
+      </c>
+      <c r="K41" s="95" t="n">
+        <v>57.12</v>
+      </c>
+      <c r="L41" s="95" t="n">
+        <v>78.04000000000001</v>
+      </c>
+      <c r="M41" s="95" t="n">
+        <v>78.04000000000001</v>
+      </c>
+      <c r="N41" s="95" t="n">
+        <v>83.77</v>
+      </c>
+      <c r="O41" s="95" t="n">
+        <v>80.52</v>
+      </c>
+      <c r="P41" s="95" t="n">
+        <v>79.08</v>
+      </c>
+      <c r="Q41" s="95" t="n">
+        <v>79.38</v>
+      </c>
+      <c r="R41" s="95" t="n">
+        <v>77.31999999999999</v>
+      </c>
+      <c r="S41" s="95" t="n">
+        <v>77.31999999999999</v>
+      </c>
+      <c r="T41" s="95" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="U41" s="95" t="n">
+        <v>64.14</v>
+      </c>
+      <c r="V41" s="95" t="n">
+        <v>66.76000000000001</v>
+      </c>
+      <c r="W41" s="95" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="X41" s="95" t="n">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="Y41" s="95" t="n">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="Z41" s="95" t="n">
+        <v>66.14</v>
+      </c>
+      <c r="AA41" s="95" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="AB41" s="95" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="AC41" s="95" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="AD41" s="95" t="n">
+        <v>46.05</v>
+      </c>
+      <c r="AE41" s="95" t="n">
+        <v>46.05</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="58" t="inlineStr">
+      <c r="A42" s="76" t="inlineStr">
         <is>
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="60" t="n"/>
-      <c r="C42" s="60" t="n"/>
-      <c r="D42" s="60" t="n"/>
-      <c r="E42" s="60" t="n"/>
-      <c r="F42" s="60" t="n"/>
-      <c r="G42" s="60" t="n"/>
-      <c r="H42" s="60" t="n"/>
-      <c r="I42" s="60" t="n"/>
-      <c r="J42" s="60" t="n"/>
-      <c r="K42" s="60" t="n"/>
-      <c r="L42" s="60" t="n"/>
-      <c r="M42" s="60" t="n"/>
-      <c r="N42" s="60" t="n"/>
-      <c r="O42" s="60" t="n"/>
-      <c r="P42" s="60" t="n"/>
-      <c r="Q42" s="60" t="n"/>
-      <c r="R42" s="60" t="n"/>
-      <c r="S42" s="60" t="n"/>
-      <c r="T42" s="60" t="n"/>
-      <c r="U42" s="60" t="n"/>
-      <c r="V42" s="60" t="n"/>
-      <c r="W42" s="60" t="n"/>
-      <c r="X42" s="60" t="n"/>
-      <c r="Y42" s="60" t="n"/>
-      <c r="Z42" s="60" t="n"/>
-      <c r="AA42" s="60" t="n"/>
-      <c r="AB42" s="60" t="n"/>
-      <c r="AC42" s="60" t="n"/>
-      <c r="AD42" s="60" t="n"/>
-      <c r="AE42" s="60" t="n"/>
+      <c r="B42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="58" t="inlineStr">
+      <c r="A43" s="76" t="inlineStr">
         <is>
           <t>fr40:RNG60</t>
         </is>
       </c>
-      <c r="B43" s="60" t="n"/>
-      <c r="C43" s="60" t="n"/>
-      <c r="D43" s="60" t="n"/>
-      <c r="E43" s="60" t="n"/>
-      <c r="F43" s="60" t="n"/>
-      <c r="G43" s="60" t="n"/>
-      <c r="H43" s="60" t="n"/>
-      <c r="I43" s="60" t="n"/>
-      <c r="J43" s="60" t="n"/>
-      <c r="K43" s="60" t="n"/>
-      <c r="L43" s="60" t="n"/>
-      <c r="M43" s="60" t="n"/>
-      <c r="N43" s="60" t="n"/>
-      <c r="O43" s="60" t="n"/>
-      <c r="P43" s="60" t="n"/>
-      <c r="Q43" s="60" t="n"/>
-      <c r="R43" s="60" t="n"/>
-      <c r="S43" s="60" t="n"/>
-      <c r="T43" s="60" t="n"/>
-      <c r="U43" s="60" t="n"/>
-      <c r="V43" s="60" t="n"/>
-      <c r="W43" s="60" t="n"/>
-      <c r="X43" s="60" t="n"/>
-      <c r="Y43" s="60" t="n"/>
-      <c r="Z43" s="60" t="n"/>
-      <c r="AA43" s="60" t="n"/>
-      <c r="AB43" s="60" t="n"/>
-      <c r="AC43" s="60" t="n"/>
-      <c r="AD43" s="60" t="n"/>
-      <c r="AE43" s="60" t="n"/>
+      <c r="B43" s="95" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="C43" s="95" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="D43" s="95" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="E43" s="95" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="F43" s="95" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="G43" s="95" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="H43" s="95" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="I43" s="95" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J43" s="95" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K43" s="95" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L43" s="95" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M43" s="95" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="N43" s="95" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O43" s="95" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="P43" s="95" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="Q43" s="95" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="R43" s="95" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="S43" s="95" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="T43" s="95" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="U43" s="95" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="V43" s="95" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="W43" s="95" t="n">
+        <v>-3.34</v>
+      </c>
+      <c r="X43" s="95" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="Y43" s="95" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="Z43" s="95" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="AA43" s="95" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="AB43" s="95" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="AC43" s="95" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="AD43" s="95" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="AE43" s="95" t="n">
+        <v>-2.01</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="58" t="inlineStr">
+      <c r="A44" s="76" t="inlineStr">
         <is>
           <t>fr40:RNG120</t>
         </is>
       </c>
-      <c r="B44" s="60" t="n"/>
-      <c r="C44" s="60" t="n"/>
-      <c r="D44" s="60" t="n"/>
-      <c r="E44" s="60" t="n"/>
-      <c r="F44" s="60" t="n"/>
-      <c r="G44" s="60" t="n"/>
-      <c r="H44" s="60" t="n"/>
-      <c r="I44" s="60" t="n"/>
-      <c r="J44" s="60" t="n"/>
-      <c r="K44" s="60" t="n"/>
-      <c r="L44" s="60" t="n"/>
-      <c r="M44" s="60" t="n"/>
-      <c r="N44" s="60" t="n"/>
-      <c r="O44" s="60" t="n"/>
-      <c r="P44" s="60" t="n"/>
-      <c r="Q44" s="60" t="n"/>
-      <c r="R44" s="60" t="n"/>
-      <c r="S44" s="60" t="n"/>
-      <c r="T44" s="60" t="n"/>
-      <c r="U44" s="60" t="n"/>
-      <c r="V44" s="60" t="n"/>
-      <c r="W44" s="60" t="n"/>
-      <c r="X44" s="60" t="n"/>
-      <c r="Y44" s="60" t="n"/>
-      <c r="Z44" s="60" t="n"/>
-      <c r="AA44" s="60" t="n"/>
-      <c r="AB44" s="60" t="n"/>
-      <c r="AC44" s="60" t="n"/>
-      <c r="AD44" s="60" t="n"/>
-      <c r="AE44" s="60" t="n"/>
+      <c r="B44" s="95" t="n">
+        <v>-6.83</v>
+      </c>
+      <c r="C44" s="95" t="n">
+        <v>-6.73</v>
+      </c>
+      <c r="D44" s="95" t="n">
+        <v>-6.46</v>
+      </c>
+      <c r="E44" s="95" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="F44" s="95" t="n">
+        <v>-6.01</v>
+      </c>
+      <c r="G44" s="95" t="n">
+        <v>-6.01</v>
+      </c>
+      <c r="H44" s="95" t="n">
+        <v>-6.31</v>
+      </c>
+      <c r="I44" s="95" t="n">
+        <v>-4.48</v>
+      </c>
+      <c r="J44" s="95" t="n">
+        <v>-5.85</v>
+      </c>
+      <c r="K44" s="95" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="L44" s="95" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="M44" s="95" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="N44" s="95" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="O44" s="95" t="n">
+        <v>-6.01</v>
+      </c>
+      <c r="P44" s="95" t="n">
+        <v>-6.35</v>
+      </c>
+      <c r="Q44" s="95" t="n">
+        <v>-6.86</v>
+      </c>
+      <c r="R44" s="95" t="n">
+        <v>-7.99</v>
+      </c>
+      <c r="S44" s="95" t="n">
+        <v>-7.99</v>
+      </c>
+      <c r="T44" s="95" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="U44" s="95" t="n">
+        <v>-8.43</v>
+      </c>
+      <c r="V44" s="95" t="n">
+        <v>-8.75</v>
+      </c>
+      <c r="W44" s="95" t="n">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="X44" s="95" t="n">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="Y44" s="95" t="n">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="Z44" s="95" t="n">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="AA44" s="95" t="n">
+        <v>-9.26</v>
+      </c>
+      <c r="AB44" s="95" t="n">
+        <v>-9.44</v>
+      </c>
+      <c r="AC44" s="95" t="n">
+        <v>-9.02</v>
+      </c>
+      <c r="AD44" s="95" t="n">
+        <v>-10.35</v>
+      </c>
+      <c r="AE44" s="95" t="n">
+        <v>-10.35</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="58" t="inlineStr">
-        <is>
-          <t>fr40:RSI3</t>
-        </is>
-      </c>
-      <c r="B45" s="60" t="n"/>
-      <c r="C45" s="60" t="n"/>
-      <c r="D45" s="60" t="n"/>
-      <c r="E45" s="60" t="n"/>
-      <c r="F45" s="60" t="n"/>
-      <c r="G45" s="60" t="n"/>
-      <c r="H45" s="60" t="n"/>
-      <c r="I45" s="60" t="n"/>
-      <c r="J45" s="60" t="n"/>
-      <c r="K45" s="60" t="n"/>
-      <c r="L45" s="60" t="n"/>
-      <c r="M45" s="60" t="n"/>
-      <c r="N45" s="60" t="n"/>
-      <c r="O45" s="60" t="n"/>
-      <c r="P45" s="60" t="n"/>
-      <c r="Q45" s="60" t="n"/>
-      <c r="R45" s="60" t="n"/>
-      <c r="S45" s="60" t="n"/>
-      <c r="T45" s="60" t="n"/>
-      <c r="U45" s="60" t="n"/>
-      <c r="V45" s="60" t="n"/>
-      <c r="W45" s="60" t="n"/>
-      <c r="X45" s="60" t="n"/>
-      <c r="Y45" s="60" t="n"/>
-      <c r="Z45" s="60" t="n"/>
-      <c r="AA45" s="60" t="n"/>
-      <c r="AB45" s="60" t="n"/>
-      <c r="AC45" s="60" t="n"/>
-      <c r="AD45" s="60" t="n"/>
-      <c r="AE45" s="60" t="n"/>
+      <c r="A45" s="76" t="inlineStr">
+        <is>
+          <t>fr40:RS5</t>
+        </is>
+      </c>
+      <c r="B45" s="95" t="n">
+        <v>45.63</v>
+      </c>
+      <c r="C45" s="95" t="n">
+        <v>49.74</v>
+      </c>
+      <c r="D45" s="95" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="E45" s="95" t="n">
+        <v>50.81</v>
+      </c>
+      <c r="F45" s="95" t="n">
+        <v>45.03</v>
+      </c>
+      <c r="G45" s="95" t="n">
+        <v>45.03</v>
+      </c>
+      <c r="H45" s="95" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="I45" s="95" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="J45" s="95" t="n">
+        <v>44.93</v>
+      </c>
+      <c r="K45" s="95" t="n">
+        <v>52.35</v>
+      </c>
+      <c r="L45" s="95" t="n">
+        <v>78.61</v>
+      </c>
+      <c r="M45" s="95" t="n">
+        <v>78.61</v>
+      </c>
+      <c r="N45" s="95" t="n">
+        <v>75.48</v>
+      </c>
+      <c r="O45" s="95" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="P45" s="95" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="Q45" s="95" t="n">
+        <v>52.83</v>
+      </c>
+      <c r="R45" s="95" t="n">
+        <v>51.58</v>
+      </c>
+      <c r="S45" s="95" t="n">
+        <v>51.58</v>
+      </c>
+      <c r="T45" s="95" t="n">
+        <v>74.97</v>
+      </c>
+      <c r="U45" s="95" t="n">
+        <v>45.92</v>
+      </c>
+      <c r="V45" s="95" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="W45" s="95" t="n">
+        <v>48.71</v>
+      </c>
+      <c r="X45" s="95" t="n">
+        <v>53.61</v>
+      </c>
+      <c r="Y45" s="95" t="n">
+        <v>53.61</v>
+      </c>
+      <c r="Z45" s="95" t="n">
+        <v>45.19</v>
+      </c>
+      <c r="AA45" s="95" t="n">
+        <v>32.83</v>
+      </c>
+      <c r="AB45" s="95" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="AC45" s="95" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="AD45" s="95" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="AE45" s="95" t="n">
+        <v>16.31</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="58" t="inlineStr">
+      <c r="A46" s="76" t="inlineStr">
         <is>
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="60" t="n"/>
-      <c r="C46" s="60" t="n"/>
-      <c r="D46" s="60" t="n"/>
-      <c r="E46" s="60" t="n"/>
-      <c r="F46" s="60" t="n"/>
-      <c r="G46" s="60" t="n"/>
-      <c r="H46" s="60" t="n"/>
-      <c r="I46" s="60" t="n"/>
-      <c r="J46" s="60" t="n"/>
-      <c r="K46" s="60" t="n"/>
-      <c r="L46" s="60" t="n"/>
-      <c r="M46" s="60" t="n"/>
-      <c r="N46" s="60" t="n"/>
-      <c r="O46" s="60" t="n"/>
-      <c r="P46" s="60" t="n"/>
-      <c r="Q46" s="60" t="n"/>
-      <c r="R46" s="60" t="n"/>
-      <c r="S46" s="60" t="n"/>
-      <c r="T46" s="60" t="n"/>
-      <c r="U46" s="60" t="n"/>
-      <c r="V46" s="60" t="n"/>
-      <c r="W46" s="60" t="n"/>
-      <c r="X46" s="60" t="n"/>
-      <c r="Y46" s="60" t="n"/>
-      <c r="Z46" s="60" t="n"/>
-      <c r="AA46" s="60" t="n"/>
-      <c r="AB46" s="60" t="n"/>
-      <c r="AC46" s="60" t="n"/>
-      <c r="AD46" s="60" t="n"/>
-      <c r="AE46" s="60" t="n"/>
+      <c r="B46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="D46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="58" t="inlineStr">
+      <c r="A47" s="76" t="inlineStr">
         <is>
           <t>dax30:RNG60</t>
         </is>
       </c>
-      <c r="B47" s="60" t="n"/>
-      <c r="C47" s="60" t="n"/>
-      <c r="D47" s="60" t="n"/>
-      <c r="E47" s="60" t="n"/>
-      <c r="F47" s="60" t="n"/>
-      <c r="G47" s="60" t="n"/>
-      <c r="H47" s="60" t="n"/>
-      <c r="I47" s="60" t="n"/>
-      <c r="J47" s="60" t="n"/>
-      <c r="K47" s="60" t="n"/>
-      <c r="L47" s="60" t="n"/>
-      <c r="M47" s="60" t="n"/>
-      <c r="N47" s="60" t="n"/>
-      <c r="O47" s="60" t="n"/>
-      <c r="P47" s="60" t="n"/>
-      <c r="Q47" s="60" t="n"/>
-      <c r="R47" s="60" t="n"/>
-      <c r="S47" s="60" t="n"/>
-      <c r="T47" s="60" t="n"/>
-      <c r="U47" s="60" t="n"/>
-      <c r="V47" s="60" t="n"/>
-      <c r="W47" s="60" t="n"/>
-      <c r="X47" s="60" t="n"/>
-      <c r="Y47" s="60" t="n"/>
-      <c r="Z47" s="60" t="n"/>
-      <c r="AA47" s="60" t="n"/>
-      <c r="AB47" s="60" t="n"/>
-      <c r="AC47" s="60" t="n"/>
-      <c r="AD47" s="60" t="n"/>
-      <c r="AE47" s="60" t="n"/>
+      <c r="B47" s="95" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="C47" s="95" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="D47" s="95" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E47" s="95" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="F47" s="95" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G47" s="95" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H47" s="95" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="I47" s="95" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="J47" s="95" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="K47" s="95" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="L47" s="95" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M47" s="95" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N47" s="95" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="O47" s="95" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="P47" s="95" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="Q47" s="95" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R47" s="95" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="S47" s="95" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T47" s="95" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="U47" s="95" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="V47" s="95" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W47" s="95" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X47" s="95" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y47" s="95" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Z47" s="95" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA47" s="95" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AB47" s="95" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AC47" s="95" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD47" s="95" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE47" s="95" t="n">
+        <v>1.67</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="58" t="inlineStr">
+      <c r="A48" s="76" t="inlineStr">
         <is>
           <t>dax30:RNG120</t>
         </is>
       </c>
-      <c r="B48" s="60" t="n"/>
-      <c r="C48" s="60" t="n"/>
-      <c r="D48" s="60" t="n"/>
-      <c r="E48" s="60" t="n"/>
-      <c r="F48" s="60" t="n"/>
-      <c r="G48" s="60" t="n"/>
-      <c r="H48" s="60" t="n"/>
-      <c r="I48" s="60" t="n"/>
-      <c r="J48" s="60" t="n"/>
-      <c r="K48" s="60" t="n"/>
-      <c r="L48" s="60" t="n"/>
-      <c r="M48" s="60" t="n"/>
-      <c r="N48" s="60" t="n"/>
-      <c r="O48" s="60" t="n"/>
-      <c r="P48" s="60" t="n"/>
-      <c r="Q48" s="60" t="n"/>
-      <c r="R48" s="60" t="n"/>
-      <c r="S48" s="60" t="n"/>
-      <c r="T48" s="60" t="n"/>
-      <c r="U48" s="60" t="n"/>
-      <c r="V48" s="60" t="n"/>
-      <c r="W48" s="60" t="n"/>
-      <c r="X48" s="60" t="n"/>
-      <c r="Y48" s="60" t="n"/>
-      <c r="Z48" s="60" t="n"/>
-      <c r="AA48" s="60" t="n"/>
-      <c r="AB48" s="60" t="n"/>
-      <c r="AC48" s="60" t="n"/>
-      <c r="AD48" s="60" t="n"/>
-      <c r="AE48" s="60" t="n"/>
+      <c r="B48" s="95" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="C48" s="95" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="D48" s="95" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E48" s="95" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="F48" s="95" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G48" s="95" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H48" s="95" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="I48" s="95" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="J48" s="95" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="K48" s="95" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="L48" s="95" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="M48" s="95" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="N48" s="95" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="O48" s="95" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="P48" s="95" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q48" s="95" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R48" s="95" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S48" s="95" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="T48" s="95" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="U48" s="95" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V48" s="95" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W48" s="95" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="X48" s="95" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Y48" s="95" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z48" s="95" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AA48" s="95" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AB48" s="95" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AC48" s="95" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD48" s="95" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE48" s="95" t="n">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="58" t="inlineStr">
-        <is>
-          <t>dax30:RSI4</t>
-        </is>
-      </c>
-      <c r="B49" s="60" t="n"/>
-      <c r="C49" s="60" t="n"/>
-      <c r="D49" s="60" t="n"/>
-      <c r="E49" s="60" t="n"/>
-      <c r="F49" s="60" t="n"/>
-      <c r="G49" s="60" t="n"/>
-      <c r="H49" s="60" t="n"/>
-      <c r="I49" s="60" t="n"/>
-      <c r="J49" s="60" t="n"/>
-      <c r="K49" s="60" t="n"/>
-      <c r="L49" s="60" t="n"/>
-      <c r="M49" s="60" t="n"/>
-      <c r="N49" s="60" t="n"/>
-      <c r="O49" s="60" t="n"/>
-      <c r="P49" s="60" t="n"/>
-      <c r="Q49" s="60" t="n"/>
-      <c r="R49" s="60" t="n"/>
-      <c r="S49" s="60" t="n"/>
-      <c r="T49" s="60" t="n"/>
-      <c r="U49" s="60" t="n"/>
-      <c r="V49" s="60" t="n"/>
-      <c r="W49" s="60" t="n"/>
-      <c r="X49" s="60" t="n"/>
-      <c r="Y49" s="60" t="n"/>
-      <c r="Z49" s="60" t="n"/>
-      <c r="AA49" s="60" t="n"/>
-      <c r="AB49" s="60" t="n"/>
-      <c r="AC49" s="60" t="n"/>
-      <c r="AD49" s="60" t="n"/>
-      <c r="AE49" s="60" t="n"/>
+      <c r="A49" s="76" t="inlineStr">
+        <is>
+          <t>dax30:RS6</t>
+        </is>
+      </c>
+      <c r="B49" s="95" t="n">
+        <v>60.76</v>
+      </c>
+      <c r="C49" s="95" t="n">
+        <v>62.55</v>
+      </c>
+      <c r="D49" s="95" t="n">
+        <v>49.18</v>
+      </c>
+      <c r="E49" s="95" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="F49" s="95" t="n">
+        <v>53.55</v>
+      </c>
+      <c r="G49" s="95" t="n">
+        <v>53.55</v>
+      </c>
+      <c r="H49" s="95" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="I49" s="95" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="J49" s="95" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="K49" s="95" t="n">
+        <v>67.34999999999999</v>
+      </c>
+      <c r="L49" s="95" t="n">
+        <v>78.38</v>
+      </c>
+      <c r="M49" s="95" t="n">
+        <v>78.38</v>
+      </c>
+      <c r="N49" s="95" t="n">
+        <v>72.42</v>
+      </c>
+      <c r="O49" s="95" t="n">
+        <v>59.91</v>
+      </c>
+      <c r="P49" s="95" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q49" s="95" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="R49" s="95" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="S49" s="95" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="T49" s="95" t="n">
+        <v>75.06999999999999</v>
+      </c>
+      <c r="U49" s="95" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="V49" s="95" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="W49" s="95" t="n">
+        <v>57.16</v>
+      </c>
+      <c r="X49" s="95" t="n">
+        <v>62.56</v>
+      </c>
+      <c r="Y49" s="95" t="n">
+        <v>62.56</v>
+      </c>
+      <c r="Z49" s="95" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="AA49" s="95" t="n">
+        <v>37.42</v>
+      </c>
+      <c r="AB49" s="95" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="AC49" s="95" t="n">
+        <v>40.38</v>
+      </c>
+      <c r="AD49" s="95" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="AE49" s="95" t="n">
+        <v>26.19</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="90" t="inlineStr">
+        <is>
+          <t>今日买报：sensex:RS10:37.56&lt;=39</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="90" t="inlineStr">
+        <is>
+          <t>今日卖报：sh:RNG60:11.58&gt;=10;kc:RNG60:34.41&gt;=25;kc:RS5:74.52&gt;=65;cy:RNG60:33.94&gt;=25;hk50:RNG60:17.96&gt;=15;hk50:RNG120:30.79&gt;=25</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:AE1">
@@ -8271,6 +11887,12 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:AE2">
     <cfRule type="colorScale" priority="2">
@@ -8281,6 +11903,12 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="51">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:AE3">
     <cfRule type="colorScale" priority="3">
@@ -8291,6 +11919,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:AE4">
     <cfRule type="colorScale" priority="4">
@@ -8301,6 +11937,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="53">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:AE5">
     <cfRule type="colorScale" priority="5">
@@ -8311,6 +11955,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:AE6">
     <cfRule type="colorScale" priority="7">
@@ -8321,6 +11973,12 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="55">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:AE7">
     <cfRule type="colorScale" priority="8">
@@ -8331,6 +11989,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:AE8">
     <cfRule type="colorScale" priority="9">
@@ -8341,6 +12007,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="57">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:AE9">
     <cfRule type="colorScale" priority="10">
@@ -8351,6 +12025,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10:AE10">
     <cfRule type="colorScale" priority="12">
@@ -8361,6 +12043,12 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="59">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:AE11">
     <cfRule type="colorScale" priority="13">
@@ -8371,6 +12059,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:AE12">
     <cfRule type="colorScale" priority="14">
@@ -8381,6 +12077,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="61">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:AE13">
     <cfRule type="colorScale" priority="15">
@@ -8391,6 +12095,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:AE14">
     <cfRule type="colorScale" priority="17">
@@ -8401,6 +12113,12 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="63">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:AE15">
     <cfRule type="colorScale" priority="18">
@@ -8411,6 +12129,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:AE16">
     <cfRule type="colorScale" priority="19">
@@ -8421,6 +12147,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="65">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:AE17">
     <cfRule type="colorScale" priority="20">
@@ -8431,6 +12165,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="66">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:AE18">
     <cfRule type="colorScale" priority="22">
@@ -8441,6 +12183,12 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="67">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:AE19">
     <cfRule type="colorScale" priority="23">
@@ -8451,6 +12199,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20:AE20">
     <cfRule type="colorScale" priority="24">
@@ -8461,6 +12217,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="69">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:AE21">
     <cfRule type="colorScale" priority="25">
@@ -8471,6 +12235,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="70">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:AE22">
     <cfRule type="colorScale" priority="27">
@@ -8481,6 +12253,12 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="71">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:AE23">
     <cfRule type="colorScale" priority="28">
@@ -8491,6 +12269,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="72">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24:AE24">
     <cfRule type="colorScale" priority="29">
@@ -8501,6 +12287,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="73">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25:AE25">
     <cfRule type="colorScale" priority="30">
@@ -8511,6 +12305,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:AE26">
     <cfRule type="colorScale" priority="32">
@@ -8521,6 +12323,12 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="75">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27:AE27">
     <cfRule type="colorScale" priority="33">
@@ -8531,6 +12339,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="76">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:AE28">
     <cfRule type="colorScale" priority="34">
@@ -8541,6 +12357,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="77">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29:AE29">
     <cfRule type="colorScale" priority="35">
@@ -8551,6 +12375,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="78">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30:AE30">
     <cfRule type="colorScale" priority="37">
@@ -8561,6 +12393,12 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="79">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:AE31">
     <cfRule type="colorScale" priority="38">
@@ -8571,6 +12409,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="80">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32:AE32">
     <cfRule type="colorScale" priority="39">
@@ -8581,6 +12427,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="81">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:AE33">
     <cfRule type="colorScale" priority="40">
@@ -8591,6 +12445,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="82">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34:AE34">
     <cfRule type="colorScale" priority="42">
@@ -8601,6 +12463,12 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="83">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35:AE35">
     <cfRule type="colorScale" priority="43">
@@ -8611,6 +12479,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="84">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36:AE36">
     <cfRule type="colorScale" priority="44">
@@ -8621,6 +12497,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="85">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37:AE37">
     <cfRule type="colorScale" priority="45">
@@ -8631,6 +12515,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="86">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:AE38">
     <cfRule type="colorScale" priority="47">
@@ -8641,6 +12533,12 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="87">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B39:AE39">
     <cfRule type="colorScale" priority="48">
@@ -8651,6 +12549,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="88">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B40:AE40">
     <cfRule type="colorScale" priority="49">
@@ -8661,6 +12567,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="89">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41:AE41">
     <cfRule type="colorScale" priority="50">
@@ -8671,6 +12585,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="90">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42:AE42">
     <cfRule type="colorScale" priority="52">
@@ -8681,6 +12603,12 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="91">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43:AE43">
     <cfRule type="colorScale" priority="53">
@@ -8691,6 +12619,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="92">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44:AE44">
     <cfRule type="colorScale" priority="54">
@@ -8701,6 +12637,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="93">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45:AE45">
     <cfRule type="colorScale" priority="55">
@@ -8711,6 +12655,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="94">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:AE46">
     <cfRule type="colorScale" priority="57">
@@ -8721,6 +12673,12 @@
         <color indexed="65"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="95">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47:AE47">
     <cfRule type="colorScale" priority="58">
@@ -8731,6 +12689,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="96">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:AE48">
     <cfRule type="colorScale" priority="59">
@@ -8741,6 +12707,14 @@
         <color rgb="FF9AE854"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="97">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49:AE49">
     <cfRule type="colorScale" priority="60">
@@ -8749,6 +12723,14 @@
         <cfvo type="max"/>
         <color rgb="FFF8544C"/>
         <color rgb="FF9AE854"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="98">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00F8544C"/>
+        <color rgb="009AE854"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -11492,13 +15474,13 @@
       <c r="G2" s="36" t="n">
         <v>66</v>
       </c>
-      <c r="H2" s="91" t="n">
+      <c r="H2" s="97" t="n">
         <v>22.3514585</v>
       </c>
       <c r="I2" s="36" t="n">
         <v>7.06</v>
       </c>
-      <c r="J2" s="92">
+      <c r="J2" s="98">
         <f>(1+H2/100)^(1/(YEAR(D2)-YEAR(C2)))-1</f>
         <v/>
       </c>
@@ -11530,13 +15512,13 @@
       <c r="G3" s="39" t="n">
         <v>73</v>
       </c>
-      <c r="H3" s="93" t="n">
+      <c r="H3" s="99" t="n">
         <v>35.0298984</v>
       </c>
       <c r="I3" s="39" t="n">
         <v>11.41</v>
       </c>
-      <c r="J3" s="92">
+      <c r="J3" s="98">
         <f>(1+H3/100)^(1/(YEAR(D3)-YEAR(C3)))-1</f>
         <v/>
       </c>
@@ -11568,13 +15550,13 @@
       <c r="G4" s="39" t="n">
         <v>85</v>
       </c>
-      <c r="H4" s="93" t="n">
+      <c r="H4" s="99" t="n">
         <v>122.4911655</v>
       </c>
       <c r="I4" s="39" t="n">
         <v>76.98</v>
       </c>
-      <c r="J4" s="94">
+      <c r="J4" s="100">
         <f>(1+H4/100)^(1/(YEAR(D4)-YEAR(C4)))-1</f>
         <v/>
       </c>
@@ -11606,13 +15588,13 @@
       <c r="G5" s="39" t="n">
         <v>96</v>
       </c>
-      <c r="H5" s="93" t="n">
+      <c r="H5" s="99" t="n">
         <v>136.13543</v>
       </c>
       <c r="I5" s="39" t="n">
         <v>100.05</v>
       </c>
-      <c r="J5" s="94">
+      <c r="J5" s="100">
         <f>(1+H5/100)^(1/(YEAR(D5)-YEAR(C5)))-1</f>
         <v/>
       </c>
@@ -11644,13 +15626,13 @@
       <c r="G6" s="39" t="n">
         <v>95</v>
       </c>
-      <c r="H6" s="93" t="n">
+      <c r="H6" s="99" t="n">
         <v>95.7546074</v>
       </c>
       <c r="I6" s="39" t="n">
         <v>44.37</v>
       </c>
-      <c r="J6" s="94">
+      <c r="J6" s="100">
         <f>(1+H6/100)^(1/(YEAR(D6)-YEAR(C6)))-1</f>
         <v/>
       </c>
@@ -11682,13 +15664,13 @@
       <c r="G7" s="39" t="n">
         <v>86</v>
       </c>
-      <c r="H7" s="93" t="n">
+      <c r="H7" s="99" t="n">
         <v>123.8525927</v>
       </c>
       <c r="I7" s="39" t="n">
         <v>63.41</v>
       </c>
-      <c r="J7" s="94">
+      <c r="J7" s="100">
         <f>(1+H7/100)^(1/(YEAR(D7)-YEAR(C7)))-1</f>
         <v/>
       </c>
@@ -11720,13 +15702,13 @@
       <c r="G8" s="39" t="n">
         <v>87</v>
       </c>
-      <c r="H8" s="93" t="n">
+      <c r="H8" s="99" t="n">
         <v>81.41461922000001</v>
       </c>
       <c r="I8" s="39" t="n">
         <v>26.39</v>
       </c>
-      <c r="J8" s="94">
+      <c r="J8" s="100">
         <f>(1+H8/100)^(1/(YEAR(D8)-YEAR(C8)))-1</f>
         <v/>
       </c>
@@ -11758,13 +15740,13 @@
       <c r="G9" s="39" t="n">
         <v>83</v>
       </c>
-      <c r="H9" s="93" t="n">
+      <c r="H9" s="99" t="n">
         <v>47.02060524</v>
       </c>
       <c r="I9" s="39" t="n">
         <v>37.82</v>
       </c>
-      <c r="J9" s="94">
+      <c r="J9" s="100">
         <f>(1+H9/100)^(1/(YEAR(D9)-YEAR(C9)))-1</f>
         <v/>
       </c>
@@ -11795,13 +15777,13 @@
       <c r="G10" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="H10" s="95" t="n">
+      <c r="H10" s="101" t="n">
         <v>27.8860732</v>
       </c>
       <c r="I10" s="24" t="n">
         <v>-10.97</v>
       </c>
-      <c r="J10" s="96" t="n">
+      <c r="J10" s="102" t="n">
         <v>0.278860732</v>
       </c>
     </row>
@@ -11832,13 +15814,13 @@
       <c r="G11" s="24" t="n">
         <v>93</v>
       </c>
-      <c r="H11" s="95" t="n">
+      <c r="H11" s="101" t="n">
         <v>17.4948656</v>
       </c>
       <c r="I11" s="24" t="n">
         <v>-7.7</v>
       </c>
-      <c r="J11" s="96">
+      <c r="J11" s="102">
         <f>(1+H11/100)^(1/(YEAR(D11)-YEAR(C11)))-1</f>
         <v/>
       </c>

--- a/report_2410.xlsx
+++ b/report_2410.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.09</v>
+        <v>7.08</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.09</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.26</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>-0.41</v>
+        <v>-0.5</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>-0.35</v>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>2.2</v>
+        <v>3.43</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>2.2</v>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>15.58</v>
+        <v>16.36</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>15.58</v>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>83.12</v>
+        <v>65.7</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>83.12</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>3.8</v>
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>12.54</v>
+        <v>11.76</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>12.54</v>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>73.18000000000001</v>
+        <v>66.56</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>73.18000000000001</v>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>-1.18</v>
+        <v>1.58</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>-1.18</v>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>17.24</v>
+        <v>19.63</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>17.24</v>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>82.01000000000001</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>82.01000000000001</v>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-0.63</v>
+        <v>-0.59</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-0.14</v>
@@ -11228,7 +11228,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-6.83</v>
+        <v>-6.8</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-6.73</v>
@@ -11325,7 +11325,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>45.63</v>
+        <v>46.1</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>49.74</v>
@@ -11421,9 +11421,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C46" s="92" t="inlineStr">
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>4.81</v>
+        <v>4.66</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>4.43</v>
@@ -11676,7 +11676,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>6.35</v>
+        <v>6.2</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>6.16</v>
@@ -11773,7 +11773,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>60.76</v>
+        <v>58.26</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>62.55</v>

--- a/report_2410.xlsx
+++ b/report_2410.xlsx
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.15</v>
+        <v>-0.23</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.11</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>-0.46</v>
+        <v>-0.54</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>-0.49</v>
@@ -6367,127 +6367,127 @@
       </c>
       <c r="G1" s="77" t="inlineStr">
         <is>
-          <t>241006</t>
+          <t>241004</t>
         </is>
       </c>
       <c r="H1" s="77" t="inlineStr">
         <is>
-          <t>241004</t>
+          <t>241003</t>
         </is>
       </c>
       <c r="I1" s="77" t="inlineStr">
         <is>
-          <t>241003</t>
+          <t>241002</t>
         </is>
       </c>
       <c r="J1" s="77" t="inlineStr">
         <is>
-          <t>241002</t>
+          <t>241001</t>
         </is>
       </c>
       <c r="K1" s="77" t="inlineStr">
         <is>
-          <t>241001</t>
+          <t>240930</t>
         </is>
       </c>
       <c r="L1" s="77" t="inlineStr">
         <is>
-          <t>240930</t>
+          <t>240927</t>
         </is>
       </c>
       <c r="M1" s="77" t="inlineStr">
         <is>
-          <t>240929</t>
+          <t>240926</t>
         </is>
       </c>
       <c r="N1" s="77" t="inlineStr">
         <is>
-          <t>240927</t>
+          <t>240925</t>
         </is>
       </c>
       <c r="O1" s="77" t="inlineStr">
         <is>
-          <t>240926</t>
+          <t>240924</t>
         </is>
       </c>
       <c r="P1" s="77" t="inlineStr">
         <is>
-          <t>240925</t>
+          <t>240923</t>
         </is>
       </c>
       <c r="Q1" s="77" t="inlineStr">
         <is>
-          <t>240924</t>
+          <t>240920</t>
         </is>
       </c>
       <c r="R1" s="77" t="inlineStr">
         <is>
-          <t>240923</t>
+          <t>240919</t>
         </is>
       </c>
       <c r="S1" s="77" t="inlineStr">
         <is>
-          <t>240922</t>
+          <t>240918</t>
         </is>
       </c>
       <c r="T1" s="77" t="inlineStr">
         <is>
-          <t>240920</t>
+          <t>240917</t>
         </is>
       </c>
       <c r="U1" s="77" t="inlineStr">
         <is>
-          <t>240919</t>
+          <t>240916</t>
         </is>
       </c>
       <c r="V1" s="77" t="inlineStr">
         <is>
-          <t>240918</t>
+          <t>240913</t>
         </is>
       </c>
       <c r="W1" s="77" t="inlineStr">
         <is>
-          <t>240917</t>
+          <t>240912</t>
         </is>
       </c>
       <c r="X1" s="77" t="inlineStr">
         <is>
-          <t>240916</t>
+          <t>240911</t>
         </is>
       </c>
       <c r="Y1" s="77" t="inlineStr">
         <is>
-          <t>240915</t>
+          <t>240910</t>
         </is>
       </c>
       <c r="Z1" s="77" t="inlineStr">
         <is>
-          <t>240913</t>
+          <t>240909</t>
         </is>
       </c>
       <c r="AA1" s="77" t="inlineStr">
         <is>
-          <t>240912</t>
+          <t>240906</t>
         </is>
       </c>
       <c r="AB1" s="77" t="inlineStr">
         <is>
-          <t>240911</t>
+          <t>240905</t>
         </is>
       </c>
       <c r="AC1" s="77" t="inlineStr">
         <is>
-          <t>240910</t>
+          <t>240904</t>
         </is>
       </c>
       <c r="AD1" s="77" t="inlineStr">
         <is>
-          <t>240909</t>
+          <t>240903</t>
         </is>
       </c>
       <c r="AE1" s="77" t="inlineStr">
         <is>
-          <t>240908</t>
+          <t>240902</t>
         </is>
       </c>
     </row>
@@ -6567,14 +6567,14 @@
           <t>red</t>
         </is>
       </c>
-      <c r="P2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="P2" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q2" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="R2" s="91" t="inlineStr">
@@ -6587,19 +6587,19 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="T2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="T2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="U2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="V2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="W2" s="93" t="inlineStr">
@@ -6642,8 +6642,10 @@
           <t>green</t>
         </is>
       </c>
-      <c r="AE2" s="91" t="n">
-        <v/>
+      <c r="AE2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -6683,64 +6685,64 @@
         <v>12.81</v>
       </c>
       <c r="L3" s="94" t="n">
-        <v>12.81</v>
+        <v>3.53</v>
       </c>
       <c r="M3" s="94" t="n">
-        <v>3.53</v>
+        <v>0.13</v>
       </c>
       <c r="N3" s="94" t="n">
-        <v>3.53</v>
+        <v>-3.29</v>
       </c>
       <c r="O3" s="94" t="n">
-        <v>0.13</v>
+        <v>-3.51</v>
       </c>
       <c r="P3" s="94" t="n">
-        <v>-3.29</v>
+        <v>-6.68</v>
       </c>
       <c r="Q3" s="94" t="n">
-        <v>-3.51</v>
+        <v>-7.93</v>
       </c>
       <c r="R3" s="94" t="n">
-        <v>-6.68</v>
+        <v>-7.25</v>
       </c>
       <c r="S3" s="94" t="n">
-        <v>-7.93</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="T3" s="94" t="n">
-        <v>-7.93</v>
+        <v>-9.81</v>
       </c>
       <c r="U3" s="94" t="n">
-        <v>-7.25</v>
+        <v>-9.81</v>
       </c>
       <c r="V3" s="94" t="n">
-        <v>-8.300000000000001</v>
+        <v>-9.81</v>
       </c>
       <c r="W3" s="94" t="n">
-        <v>-9.81</v>
+        <v>-9.59</v>
       </c>
       <c r="X3" s="94" t="n">
-        <v>-9.81</v>
+        <v>-9.82</v>
       </c>
       <c r="Y3" s="94" t="n">
-        <v>-9.81</v>
+        <v>-9.44</v>
       </c>
       <c r="Z3" s="94" t="n">
-        <v>-9.81</v>
+        <v>-9.26</v>
       </c>
       <c r="AA3" s="94" t="n">
-        <v>-9.59</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="AB3" s="94" t="n">
-        <v>-9.82</v>
+        <v>-7.94</v>
       </c>
       <c r="AC3" s="94" t="n">
-        <v>-9.44</v>
+        <v>-8.34</v>
       </c>
       <c r="AD3" s="94" t="n">
-        <v>-9.26</v>
+        <v>-7.43</v>
       </c>
       <c r="AE3" s="94" t="n">
-        <v/>
+        <v>-7.87</v>
       </c>
     </row>
     <row r="4">
@@ -6780,64 +6782,64 @@
         <v>8.710000000000001</v>
       </c>
       <c r="L4" s="94" t="n">
-        <v>8.710000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="M4" s="94" t="n">
-        <v>0.41</v>
+        <v>-2.48</v>
       </c>
       <c r="N4" s="94" t="n">
-        <v>0.41</v>
+        <v>-4.76</v>
       </c>
       <c r="O4" s="94" t="n">
-        <v>-2.48</v>
+        <v>-4.9</v>
       </c>
       <c r="P4" s="94" t="n">
-        <v>-4.76</v>
+        <v>-8.16</v>
       </c>
       <c r="Q4" s="94" t="n">
-        <v>-4.9</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="R4" s="94" t="n">
-        <v>-8.16</v>
+        <v>-9.59</v>
       </c>
       <c r="S4" s="94" t="n">
-        <v>-9.720000000000001</v>
+        <v>-10.85</v>
       </c>
       <c r="T4" s="94" t="n">
-        <v>-9.720000000000001</v>
+        <v>-12.12</v>
       </c>
       <c r="U4" s="94" t="n">
-        <v>-9.59</v>
+        <v>-12.12</v>
       </c>
       <c r="V4" s="94" t="n">
-        <v>-10.85</v>
+        <v>-12.12</v>
       </c>
       <c r="W4" s="94" t="n">
-        <v>-12.12</v>
+        <v>-11.77</v>
       </c>
       <c r="X4" s="94" t="n">
-        <v>-12.12</v>
+        <v>-11.13</v>
       </c>
       <c r="Y4" s="94" t="n">
-        <v>-12.12</v>
+        <v>-11.05</v>
       </c>
       <c r="Z4" s="94" t="n">
-        <v>-12.12</v>
+        <v>-10.42</v>
       </c>
       <c r="AA4" s="94" t="n">
-        <v>-11.77</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="AB4" s="94" t="n">
-        <v>-11.13</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="AC4" s="94" t="n">
-        <v>-11.05</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="AD4" s="94" t="n">
-        <v>-10.42</v>
+        <v>-8.65</v>
       </c>
       <c r="AE4" s="94" t="n">
-        <v/>
+        <v>-7.71</v>
       </c>
     </row>
     <row r="5">
@@ -6877,64 +6879,64 @@
         <v>99.75</v>
       </c>
       <c r="L5" s="94" t="n">
-        <v>99.75</v>
+        <v>99.31</v>
       </c>
       <c r="M5" s="94" t="n">
-        <v>99.31</v>
+        <v>98.83</v>
       </c>
       <c r="N5" s="94" t="n">
-        <v>99.31</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="O5" s="94" t="n">
-        <v>98.83</v>
+        <v>96.38</v>
       </c>
       <c r="P5" s="94" t="n">
-        <v>97.34999999999999</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="Q5" s="94" t="n">
-        <v>96.38</v>
+        <v>64.38</v>
       </c>
       <c r="R5" s="94" t="n">
-        <v>77.51000000000001</v>
+        <v>63.45</v>
       </c>
       <c r="S5" s="94" t="n">
-        <v>64.38</v>
+        <v>37.85</v>
       </c>
       <c r="T5" s="94" t="n">
-        <v>64.38</v>
+        <v>7.42</v>
       </c>
       <c r="U5" s="94" t="n">
-        <v>63.45</v>
+        <v>7.42</v>
       </c>
       <c r="V5" s="94" t="n">
-        <v>37.85</v>
+        <v>7.42</v>
       </c>
       <c r="W5" s="94" t="n">
-        <v>7.42</v>
+        <v>10.95</v>
       </c>
       <c r="X5" s="94" t="n">
-        <v>7.42</v>
+        <v>12.36</v>
       </c>
       <c r="Y5" s="94" t="n">
-        <v>7.42</v>
+        <v>20.95</v>
       </c>
       <c r="Z5" s="94" t="n">
-        <v>7.42</v>
+        <v>5.95</v>
       </c>
       <c r="AA5" s="94" t="n">
-        <v>10.95</v>
+        <v>11.48</v>
       </c>
       <c r="AB5" s="94" t="n">
-        <v>12.36</v>
+        <v>21.9</v>
       </c>
       <c r="AC5" s="94" t="n">
-        <v>20.95</v>
+        <v>12.41</v>
       </c>
       <c r="AD5" s="94" t="n">
-        <v>5.95</v>
+        <v>19.88</v>
       </c>
       <c r="AE5" s="94" t="n">
-        <v/>
+        <v>24.04</v>
       </c>
     </row>
     <row r="6">
@@ -7013,26 +7015,26 @@
           <t>red</t>
         </is>
       </c>
-      <c r="P6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R6" s="93" t="inlineStr">
+      <c r="P6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S6" s="91" t="inlineStr">
+      <c r="Q6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
+      <c r="R6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
       <c r="T6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
@@ -7043,53 +7045,55 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="V6" s="93" t="inlineStr">
+      <c r="V6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Z6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W6" s="91" t="inlineStr">
+      <c r="AA6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X6" s="91" t="inlineStr">
+      <c r="AC6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y6" s="91" t="inlineStr">
+      <c r="AD6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD6" s="93" t="inlineStr">
+      <c r="AE6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
-      </c>
-      <c r="AE6" s="91" t="n">
-        <v/>
       </c>
     </row>
     <row r="7">
@@ -7129,64 +7133,64 @@
         <v>26.36</v>
       </c>
       <c r="L7" s="94" t="n">
-        <v>26.36</v>
+        <v>5.45</v>
       </c>
       <c r="M7" s="94" t="n">
-        <v>5.45</v>
+        <v>-0.85</v>
       </c>
       <c r="N7" s="94" t="n">
-        <v>5.45</v>
+        <v>-5.96</v>
       </c>
       <c r="O7" s="94" t="n">
-        <v>-0.85</v>
+        <v>-6.32</v>
       </c>
       <c r="P7" s="94" t="n">
-        <v>-5.96</v>
+        <v>-10.11</v>
       </c>
       <c r="Q7" s="94" t="n">
-        <v>-6.32</v>
+        <v>-11.14</v>
       </c>
       <c r="R7" s="94" t="n">
-        <v>-10.11</v>
+        <v>-9.23</v>
       </c>
       <c r="S7" s="94" t="n">
-        <v>-11.14</v>
+        <v>-12.41</v>
       </c>
       <c r="T7" s="94" t="n">
-        <v>-11.14</v>
+        <v>-13.62</v>
       </c>
       <c r="U7" s="94" t="n">
-        <v>-9.23</v>
+        <v>-13.62</v>
       </c>
       <c r="V7" s="94" t="n">
-        <v>-12.41</v>
+        <v>-13.62</v>
       </c>
       <c r="W7" s="94" t="n">
-        <v>-13.62</v>
+        <v>-12.75</v>
       </c>
       <c r="X7" s="94" t="n">
-        <v>-13.62</v>
+        <v>-11.62</v>
       </c>
       <c r="Y7" s="94" t="n">
-        <v>-13.62</v>
+        <v>-12.8</v>
       </c>
       <c r="Z7" s="94" t="n">
-        <v>-13.62</v>
+        <v>-13.49</v>
       </c>
       <c r="AA7" s="94" t="n">
-        <v>-12.75</v>
+        <v>-12.19</v>
       </c>
       <c r="AB7" s="94" t="n">
-        <v>-11.62</v>
+        <v>-11.56</v>
       </c>
       <c r="AC7" s="94" t="n">
-        <v>-12.8</v>
+        <v>-10.95</v>
       </c>
       <c r="AD7" s="94" t="n">
-        <v>-13.49</v>
+        <v>-10.7</v>
       </c>
       <c r="AE7" s="94" t="n">
-        <v/>
+        <v>-9.199999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -7226,64 +7230,64 @@
         <v>15.28</v>
       </c>
       <c r="L8" s="94" t="n">
-        <v>15.28</v>
+        <v>-3.74</v>
       </c>
       <c r="M8" s="94" t="n">
-        <v>-3.74</v>
+        <v>-10.62</v>
       </c>
       <c r="N8" s="94" t="n">
-        <v>-3.74</v>
+        <v>-12.51</v>
       </c>
       <c r="O8" s="94" t="n">
-        <v>-10.62</v>
+        <v>-12.61</v>
       </c>
       <c r="P8" s="94" t="n">
-        <v>-12.51</v>
+        <v>-14.58</v>
       </c>
       <c r="Q8" s="94" t="n">
-        <v>-12.61</v>
+        <v>-16.03</v>
       </c>
       <c r="R8" s="94" t="n">
-        <v>-14.58</v>
+        <v>-16.65</v>
       </c>
       <c r="S8" s="94" t="n">
-        <v>-16.03</v>
+        <v>-18.48</v>
       </c>
       <c r="T8" s="94" t="n">
-        <v>-16.03</v>
+        <v>-18.74</v>
       </c>
       <c r="U8" s="94" t="n">
-        <v>-16.65</v>
+        <v>-18.74</v>
       </c>
       <c r="V8" s="94" t="n">
-        <v>-18.48</v>
+        <v>-18.74</v>
       </c>
       <c r="W8" s="94" t="n">
-        <v>-18.74</v>
+        <v>-19.06</v>
       </c>
       <c r="X8" s="94" t="n">
-        <v>-18.74</v>
+        <v>-18.16</v>
       </c>
       <c r="Y8" s="94" t="n">
-        <v>-18.74</v>
+        <v>-20.04</v>
       </c>
       <c r="Z8" s="94" t="n">
-        <v>-18.74</v>
+        <v>-19.01</v>
       </c>
       <c r="AA8" s="94" t="n">
-        <v>-19.06</v>
+        <v>-17.71</v>
       </c>
       <c r="AB8" s="94" t="n">
-        <v>-18.16</v>
+        <v>-17.63</v>
       </c>
       <c r="AC8" s="94" t="n">
-        <v>-20.04</v>
+        <v>-17.79</v>
       </c>
       <c r="AD8" s="94" t="n">
-        <v>-19.01</v>
+        <v>-17.53</v>
       </c>
       <c r="AE8" s="94" t="n">
-        <v/>
+        <v>-16.58</v>
       </c>
     </row>
     <row r="9">
@@ -7323,64 +7327,64 @@
         <v>96.84</v>
       </c>
       <c r="L9" s="94" t="n">
-        <v>96.84</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="M9" s="94" t="n">
-        <v>91.06999999999999</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="N9" s="94" t="n">
-        <v>91.06999999999999</v>
+        <v>64.94</v>
       </c>
       <c r="O9" s="94" t="n">
-        <v>81.48999999999999</v>
+        <v>64.66</v>
       </c>
       <c r="P9" s="94" t="n">
-        <v>64.94</v>
+        <v>23.69</v>
       </c>
       <c r="Q9" s="94" t="n">
-        <v>64.66</v>
+        <v>29.81</v>
       </c>
       <c r="R9" s="94" t="n">
-        <v>23.69</v>
+        <v>33.91</v>
       </c>
       <c r="S9" s="94" t="n">
-        <v>29.81</v>
+        <v>22.82</v>
       </c>
       <c r="T9" s="94" t="n">
-        <v>29.81</v>
+        <v>30.54</v>
       </c>
       <c r="U9" s="94" t="n">
-        <v>33.91</v>
+        <v>30.54</v>
       </c>
       <c r="V9" s="94" t="n">
-        <v>22.82</v>
+        <v>30.54</v>
       </c>
       <c r="W9" s="94" t="n">
-        <v>30.54</v>
+        <v>35.28</v>
       </c>
       <c r="X9" s="94" t="n">
-        <v>30.54</v>
+        <v>42.99</v>
       </c>
       <c r="Y9" s="94" t="n">
-        <v>30.54</v>
+        <v>33.88</v>
       </c>
       <c r="Z9" s="94" t="n">
-        <v>30.54</v>
+        <v>22.22</v>
       </c>
       <c r="AA9" s="94" t="n">
-        <v>35.28</v>
+        <v>27.98</v>
       </c>
       <c r="AB9" s="94" t="n">
-        <v>42.99</v>
+        <v>37.32</v>
       </c>
       <c r="AC9" s="94" t="n">
-        <v>33.88</v>
+        <v>38.49</v>
       </c>
       <c r="AD9" s="94" t="n">
-        <v>22.22</v>
+        <v>41.22</v>
       </c>
       <c r="AE9" s="94" t="n">
-        <v/>
+        <v>34.35</v>
       </c>
     </row>
     <row r="10">
@@ -7459,83 +7463,85 @@
           <t>red</t>
         </is>
       </c>
-      <c r="P10" s="92" t="inlineStr">
+      <c r="P10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="T10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="U10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="V10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="W10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q10" s="92" t="inlineStr">
+      <c r="Y10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R10" s="93" t="inlineStr">
+      <c r="AC10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AD10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AE10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
-      </c>
-      <c r="S10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="T10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="U10" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="W10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="X10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA10" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE10" s="91" t="n">
-        <v/>
       </c>
     </row>
     <row r="11">
@@ -7575,64 +7581,64 @@
         <v>32.05</v>
       </c>
       <c r="L11" s="94" t="n">
-        <v>32.05</v>
+        <v>13.58</v>
       </c>
       <c r="M11" s="94" t="n">
-        <v>13.58</v>
+        <v>2.95</v>
       </c>
       <c r="N11" s="94" t="n">
-        <v>13.58</v>
+        <v>-2.45</v>
       </c>
       <c r="O11" s="94" t="n">
-        <v>2.95</v>
+        <v>-4.05</v>
       </c>
       <c r="P11" s="94" t="n">
-        <v>-2.45</v>
+        <v>-10.14</v>
       </c>
       <c r="Q11" s="94" t="n">
-        <v>-4.05</v>
+        <v>-11.21</v>
       </c>
       <c r="R11" s="94" t="n">
-        <v>-10.14</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="S11" s="94" t="n">
-        <v>-11.21</v>
+        <v>-11.44</v>
       </c>
       <c r="T11" s="94" t="n">
-        <v>-11.21</v>
+        <v>-12.57</v>
       </c>
       <c r="U11" s="94" t="n">
-        <v>-9.029999999999999</v>
+        <v>-12.57</v>
       </c>
       <c r="V11" s="94" t="n">
-        <v>-11.44</v>
+        <v>-12.57</v>
       </c>
       <c r="W11" s="94" t="n">
-        <v>-12.57</v>
+        <v>-11.96</v>
       </c>
       <c r="X11" s="94" t="n">
-        <v>-12.57</v>
+        <v>-12.87</v>
       </c>
       <c r="Y11" s="94" t="n">
-        <v>-12.57</v>
+        <v>-14.98</v>
       </c>
       <c r="Z11" s="94" t="n">
-        <v>-12.57</v>
+        <v>-14.79</v>
       </c>
       <c r="AA11" s="94" t="n">
-        <v>-11.96</v>
+        <v>-14.14</v>
       </c>
       <c r="AB11" s="94" t="n">
-        <v>-12.87</v>
+        <v>-11.99</v>
       </c>
       <c r="AC11" s="94" t="n">
-        <v>-14.98</v>
+        <v>-12.63</v>
       </c>
       <c r="AD11" s="94" t="n">
-        <v>-14.79</v>
+        <v>-12.92</v>
       </c>
       <c r="AE11" s="94" t="n">
-        <v/>
+        <v>-13.71</v>
       </c>
     </row>
     <row r="12">
@@ -7672,64 +7678,64 @@
         <v>18.19</v>
       </c>
       <c r="L12" s="94" t="n">
-        <v>18.19</v>
+        <v>1.34</v>
       </c>
       <c r="M12" s="94" t="n">
-        <v>1.34</v>
+        <v>-8.44</v>
       </c>
       <c r="N12" s="94" t="n">
-        <v>1.34</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="O12" s="94" t="n">
-        <v>-8.44</v>
+        <v>-10.6</v>
       </c>
       <c r="P12" s="94" t="n">
-        <v>-9.720000000000001</v>
+        <v>-14.49</v>
       </c>
       <c r="Q12" s="94" t="n">
-        <v>-10.6</v>
+        <v>-16.56</v>
       </c>
       <c r="R12" s="94" t="n">
-        <v>-14.49</v>
+        <v>-15.65</v>
       </c>
       <c r="S12" s="94" t="n">
-        <v>-16.56</v>
+        <v>-17.96</v>
       </c>
       <c r="T12" s="94" t="n">
-        <v>-16.56</v>
+        <v>-19.08</v>
       </c>
       <c r="U12" s="94" t="n">
-        <v>-15.65</v>
+        <v>-19.08</v>
       </c>
       <c r="V12" s="94" t="n">
-        <v>-17.96</v>
+        <v>-19.08</v>
       </c>
       <c r="W12" s="94" t="n">
-        <v>-19.08</v>
+        <v>-18.72</v>
       </c>
       <c r="X12" s="94" t="n">
-        <v>-19.08</v>
+        <v>-18.28</v>
       </c>
       <c r="Y12" s="94" t="n">
-        <v>-19.08</v>
+        <v>-20.06</v>
       </c>
       <c r="Z12" s="94" t="n">
-        <v>-19.08</v>
+        <v>-18.31</v>
       </c>
       <c r="AA12" s="94" t="n">
-        <v>-18.72</v>
+        <v>-18.32</v>
       </c>
       <c r="AB12" s="94" t="n">
-        <v>-18.28</v>
+        <v>-17.44</v>
       </c>
       <c r="AC12" s="94" t="n">
-        <v>-20.06</v>
+        <v>-18.44</v>
       </c>
       <c r="AD12" s="94" t="n">
-        <v>-18.31</v>
+        <v>-17.67</v>
       </c>
       <c r="AE12" s="94" t="n">
-        <v/>
+        <v>-14.96</v>
       </c>
     </row>
     <row r="13">
@@ -7769,64 +7775,64 @@
         <v>99.48</v>
       </c>
       <c r="L13" s="94" t="n">
-        <v>99.48</v>
+        <v>98.62</v>
       </c>
       <c r="M13" s="94" t="n">
-        <v>98.62</v>
+        <v>96</v>
       </c>
       <c r="N13" s="94" t="n">
-        <v>98.62</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="O13" s="94" t="n">
-        <v>96</v>
+        <v>88.09</v>
       </c>
       <c r="P13" s="94" t="n">
-        <v>91.40000000000001</v>
+        <v>30.34</v>
       </c>
       <c r="Q13" s="94" t="n">
-        <v>88.09</v>
+        <v>39.51</v>
       </c>
       <c r="R13" s="94" t="n">
-        <v>30.34</v>
+        <v>58.67</v>
       </c>
       <c r="S13" s="94" t="n">
-        <v>39.51</v>
+        <v>28.04</v>
       </c>
       <c r="T13" s="94" t="n">
-        <v>39.51</v>
+        <v>29.98</v>
       </c>
       <c r="U13" s="94" t="n">
-        <v>58.67</v>
+        <v>29.98</v>
       </c>
       <c r="V13" s="94" t="n">
-        <v>28.04</v>
+        <v>29.98</v>
       </c>
       <c r="W13" s="94" t="n">
-        <v>29.98</v>
+        <v>54.57</v>
       </c>
       <c r="X13" s="94" t="n">
-        <v>29.98</v>
+        <v>69.45</v>
       </c>
       <c r="Y13" s="94" t="n">
-        <v>29.98</v>
+        <v>37.43</v>
       </c>
       <c r="Z13" s="94" t="n">
-        <v>29.98</v>
+        <v>35.11</v>
       </c>
       <c r="AA13" s="94" t="n">
-        <v>54.57</v>
+        <v>33.41</v>
       </c>
       <c r="AB13" s="94" t="n">
-        <v>69.45</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="AC13" s="94" t="n">
-        <v>37.43</v>
+        <v>53.41</v>
       </c>
       <c r="AD13" s="94" t="n">
-        <v>35.11</v>
+        <v>55.28</v>
       </c>
       <c r="AE13" s="94" t="n">
-        <v/>
+        <v>38.88</v>
       </c>
     </row>
     <row r="14">
@@ -7935,53 +7941,55 @@
           <t>red</t>
         </is>
       </c>
-      <c r="V14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y14" s="91" t="inlineStr">
+      <c r="V14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z14" s="91" t="inlineStr">
+      <c r="W14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA14" s="91" t="inlineStr">
+      <c r="X14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Y14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB14" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC14" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD14" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE14" s="91" t="n">
-        <v/>
+      <c r="AE14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -8009,76 +8017,76 @@
         <v>29.75</v>
       </c>
       <c r="H15" s="94" t="n">
-        <v>29.75</v>
+        <v>26.19</v>
       </c>
       <c r="I15" s="94" t="n">
-        <v>26.19</v>
+        <v>26.09</v>
       </c>
       <c r="J15" s="94" t="n">
-        <v>26.09</v>
+        <v>17.23</v>
       </c>
       <c r="K15" s="94" t="n">
         <v>17.23</v>
       </c>
       <c r="L15" s="94" t="n">
-        <v>17.23</v>
+        <v>14.76</v>
       </c>
       <c r="M15" s="94" t="n">
-        <v>14.76</v>
+        <v>12.13</v>
       </c>
       <c r="N15" s="94" t="n">
-        <v>14.76</v>
+        <v>7.96</v>
       </c>
       <c r="O15" s="94" t="n">
-        <v>12.13</v>
+        <v>7.25</v>
       </c>
       <c r="P15" s="94" t="n">
-        <v>7.96</v>
+        <v>0.87</v>
       </c>
       <c r="Q15" s="94" t="n">
-        <v>7.25</v>
+        <v>1.03</v>
       </c>
       <c r="R15" s="94" t="n">
-        <v>0.87</v>
+        <v>-0.08</v>
       </c>
       <c r="S15" s="94" t="n">
-        <v>1.03</v>
+        <v>-2.04</v>
       </c>
       <c r="T15" s="94" t="n">
-        <v>1.03</v>
+        <v>-2.04</v>
       </c>
       <c r="U15" s="94" t="n">
-        <v>-0.08</v>
+        <v>-4.98</v>
       </c>
       <c r="V15" s="94" t="n">
-        <v>-2.04</v>
+        <v>-5.76</v>
       </c>
       <c r="W15" s="94" t="n">
-        <v>-2.04</v>
+        <v>-3.77</v>
       </c>
       <c r="X15" s="94" t="n">
-        <v>-4.98</v>
+        <v>-4.61</v>
       </c>
       <c r="Y15" s="94" t="n">
-        <v>-5.76</v>
+        <v>-3.94</v>
       </c>
       <c r="Z15" s="94" t="n">
-        <v>-5.76</v>
+        <v>-5.06</v>
       </c>
       <c r="AA15" s="94" t="n">
-        <v>-3.77</v>
+        <v>-2.75</v>
       </c>
       <c r="AB15" s="94" t="n">
-        <v>-4.61</v>
+        <v>-2.75</v>
       </c>
       <c r="AC15" s="94" t="n">
-        <v>-3.94</v>
+        <v>-3.96</v>
       </c>
       <c r="AD15" s="94" t="n">
-        <v>-5.06</v>
+        <v>-3.9</v>
       </c>
       <c r="AE15" s="94" t="n">
-        <v/>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="16">
@@ -8106,76 +8114,76 @@
         <v>32.66</v>
       </c>
       <c r="H16" s="94" t="n">
-        <v>32.66</v>
+        <v>31.41</v>
       </c>
       <c r="I16" s="94" t="n">
-        <v>31.41</v>
+        <v>34.13</v>
       </c>
       <c r="J16" s="94" t="n">
-        <v>34.13</v>
+        <v>26.37</v>
       </c>
       <c r="K16" s="94" t="n">
         <v>26.37</v>
       </c>
       <c r="L16" s="94" t="n">
-        <v>26.37</v>
+        <v>23.36</v>
       </c>
       <c r="M16" s="94" t="n">
-        <v>23.36</v>
+        <v>17.68</v>
       </c>
       <c r="N16" s="94" t="n">
-        <v>23.36</v>
+        <v>15.64</v>
       </c>
       <c r="O16" s="94" t="n">
-        <v>17.68</v>
+        <v>15.91</v>
       </c>
       <c r="P16" s="94" t="n">
-        <v>15.64</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q16" s="94" t="n">
-        <v>15.91</v>
+        <v>10.84</v>
       </c>
       <c r="R16" s="94" t="n">
-        <v>9.800000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="S16" s="94" t="n">
-        <v>10.84</v>
+        <v>4.73</v>
       </c>
       <c r="T16" s="94" t="n">
-        <v>10.84</v>
+        <v>4.73</v>
       </c>
       <c r="U16" s="94" t="n">
-        <v>9.17</v>
+        <v>5.31</v>
       </c>
       <c r="V16" s="94" t="n">
-        <v>4.73</v>
+        <v>5.08</v>
       </c>
       <c r="W16" s="94" t="n">
-        <v>4.73</v>
+        <v>3.01</v>
       </c>
       <c r="X16" s="94" t="n">
-        <v>5.31</v>
+        <v>2.32</v>
       </c>
       <c r="Y16" s="94" t="n">
-        <v>5.08</v>
+        <v>1.61</v>
       </c>
       <c r="Z16" s="94" t="n">
-        <v>5.08</v>
+        <v>0.67</v>
       </c>
       <c r="AA16" s="94" t="n">
-        <v>3.01</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" s="94" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="AC16" s="94" t="n">
-        <v>1.61</v>
+        <v>5.24</v>
       </c>
       <c r="AD16" s="94" t="n">
-        <v>0.67</v>
+        <v>7.94</v>
       </c>
       <c r="AE16" s="94" t="n">
-        <v/>
+        <v>9.01</v>
       </c>
     </row>
     <row r="17">
@@ -8203,76 +8211,76 @@
         <v>89.48999999999999</v>
       </c>
       <c r="H17" s="94" t="n">
-        <v>89.48999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="I17" s="94" t="n">
-        <v>85.84</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="J17" s="94" t="n">
-        <v>99.56999999999999</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="K17" s="94" t="n">
         <v>99.18000000000001</v>
       </c>
       <c r="L17" s="94" t="n">
-        <v>99.18000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="M17" s="94" t="n">
-        <v>98.89</v>
+        <v>98.23</v>
       </c>
       <c r="N17" s="94" t="n">
-        <v>98.89</v>
+        <v>96.44</v>
       </c>
       <c r="O17" s="94" t="n">
-        <v>98.23</v>
+        <v>95.94</v>
       </c>
       <c r="P17" s="94" t="n">
-        <v>96.44</v>
+        <v>89.48</v>
       </c>
       <c r="Q17" s="94" t="n">
-        <v>95.94</v>
+        <v>91.13</v>
       </c>
       <c r="R17" s="94" t="n">
-        <v>89.48</v>
+        <v>87.39</v>
       </c>
       <c r="S17" s="94" t="n">
-        <v>91.13</v>
+        <v>76.86</v>
       </c>
       <c r="T17" s="94" t="n">
-        <v>91.13</v>
+        <v>76.86</v>
       </c>
       <c r="U17" s="94" t="n">
-        <v>87.39</v>
+        <v>59.96</v>
       </c>
       <c r="V17" s="94" t="n">
-        <v>76.86</v>
+        <v>54.39</v>
       </c>
       <c r="W17" s="94" t="n">
-        <v>76.86</v>
+        <v>38.93</v>
       </c>
       <c r="X17" s="94" t="n">
-        <v>59.96</v>
+        <v>17.46</v>
       </c>
       <c r="Y17" s="94" t="n">
-        <v>54.39</v>
+        <v>23.32</v>
       </c>
       <c r="Z17" s="94" t="n">
-        <v>54.39</v>
+        <v>17.15</v>
       </c>
       <c r="AA17" s="94" t="n">
-        <v>38.93</v>
+        <v>28.67</v>
       </c>
       <c r="AB17" s="94" t="n">
-        <v>17.46</v>
+        <v>28.67</v>
       </c>
       <c r="AC17" s="94" t="n">
-        <v>23.32</v>
+        <v>29.45</v>
       </c>
       <c r="AD17" s="94" t="n">
-        <v>17.15</v>
+        <v>42.37</v>
       </c>
       <c r="AE17" s="94" t="n">
-        <v/>
+        <v>45.49</v>
       </c>
     </row>
     <row r="18">
@@ -8311,114 +8319,114 @@
           <t>red</t>
         </is>
       </c>
-      <c r="H18" s="92" t="inlineStr">
+      <c r="H18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I18" s="91" t="inlineStr">
+      <c r="P18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J18" s="91" t="inlineStr">
+      <c r="T18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="L18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="M18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="Z18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="AD18" s="93" t="inlineStr">
@@ -8437,7 +8445,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>3.43</v>
+        <v>4.88</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>3.43</v>
@@ -8455,73 +8463,73 @@
         <v>2.98</v>
       </c>
       <c r="H19" s="94" t="n">
-        <v>2.98</v>
+        <v>1.17</v>
       </c>
       <c r="I19" s="94" t="n">
-        <v>1.17</v>
+        <v>2.38</v>
       </c>
       <c r="J19" s="94" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="K19" s="94" t="n">
-        <v>2.44</v>
+        <v>3.51</v>
       </c>
       <c r="L19" s="94" t="n">
-        <v>3.51</v>
+        <v>3.63</v>
       </c>
       <c r="M19" s="94" t="n">
-        <v>3.63</v>
+        <v>4.29</v>
       </c>
       <c r="N19" s="94" t="n">
-        <v>3.63</v>
+        <v>4.51</v>
       </c>
       <c r="O19" s="94" t="n">
-        <v>4.29</v>
+        <v>4.99</v>
       </c>
       <c r="P19" s="94" t="n">
-        <v>4.51</v>
+        <v>4.3</v>
       </c>
       <c r="Q19" s="94" t="n">
-        <v>4.99</v>
+        <v>4.1</v>
       </c>
       <c r="R19" s="94" t="n">
-        <v>4.3</v>
+        <v>4.47</v>
       </c>
       <c r="S19" s="94" t="n">
-        <v>4.1</v>
+        <v>3.13</v>
       </c>
       <c r="T19" s="94" t="n">
-        <v>4.1</v>
+        <v>3.11</v>
       </c>
       <c r="U19" s="94" t="n">
-        <v>4.47</v>
+        <v>2.92</v>
       </c>
       <c r="V19" s="94" t="n">
-        <v>3.13</v>
+        <v>2.53</v>
       </c>
       <c r="W19" s="94" t="n">
-        <v>3.11</v>
+        <v>2.24</v>
       </c>
       <c r="X19" s="94" t="n">
-        <v>2.92</v>
+        <v>2.26</v>
       </c>
       <c r="Y19" s="94" t="n">
-        <v>2.53</v>
+        <v>1.14</v>
       </c>
       <c r="Z19" s="94" t="n">
-        <v>2.53</v>
+        <v>0.92</v>
       </c>
       <c r="AA19" s="94" t="n">
-        <v>2.24</v>
+        <v>0.62</v>
       </c>
       <c r="AB19" s="94" t="n">
-        <v>2.26</v>
+        <v>2.66</v>
       </c>
       <c r="AC19" s="94" t="n">
-        <v>1.14</v>
+        <v>3.24</v>
       </c>
       <c r="AD19" s="94" t="n">
-        <v>0.92</v>
+        <v>3.29</v>
       </c>
       <c r="AE19" s="94" t="n">
         <v/>
@@ -8534,7 +8542,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>16.36</v>
+        <v>16.05</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>16.36</v>
@@ -8552,73 +8560,73 @@
         <v>13.62</v>
       </c>
       <c r="H20" s="94" t="n">
-        <v>13.62</v>
+        <v>11.25</v>
       </c>
       <c r="I20" s="94" t="n">
-        <v>11.25</v>
+        <v>9.82</v>
       </c>
       <c r="J20" s="94" t="n">
-        <v>9.82</v>
+        <v>10.62</v>
       </c>
       <c r="K20" s="94" t="n">
-        <v>10.62</v>
+        <v>10.61</v>
       </c>
       <c r="L20" s="94" t="n">
-        <v>10.61</v>
+        <v>10.3</v>
       </c>
       <c r="M20" s="94" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="N20" s="94" t="n">
-        <v>10.3</v>
+        <v>11.17</v>
       </c>
       <c r="O20" s="94" t="n">
-        <v>10.4</v>
+        <v>10.01</v>
       </c>
       <c r="P20" s="94" t="n">
-        <v>11.17</v>
+        <v>9.85</v>
       </c>
       <c r="Q20" s="94" t="n">
-        <v>10.01</v>
+        <v>8.75</v>
       </c>
       <c r="R20" s="94" t="n">
-        <v>9.85</v>
+        <v>8.74</v>
       </c>
       <c r="S20" s="94" t="n">
-        <v>8.75</v>
+        <v>7.05</v>
       </c>
       <c r="T20" s="94" t="n">
-        <v>8.75</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="U20" s="94" t="n">
-        <v>8.74</v>
+        <v>7.95</v>
       </c>
       <c r="V20" s="94" t="n">
-        <v>7.05</v>
+        <v>7.49</v>
       </c>
       <c r="W20" s="94" t="n">
-        <v>8.279999999999999</v>
+        <v>6.76</v>
       </c>
       <c r="X20" s="94" t="n">
-        <v>7.95</v>
+        <v>6.31</v>
       </c>
       <c r="Y20" s="94" t="n">
-        <v>7.49</v>
+        <v>6.12</v>
       </c>
       <c r="Z20" s="94" t="n">
-        <v>7.49</v>
+        <v>6.25</v>
       </c>
       <c r="AA20" s="94" t="n">
-        <v>6.76</v>
+        <v>5.69</v>
       </c>
       <c r="AB20" s="94" t="n">
-        <v>6.31</v>
+        <v>6.85</v>
       </c>
       <c r="AC20" s="94" t="n">
-        <v>6.12</v>
+        <v>6.87</v>
       </c>
       <c r="AD20" s="94" t="n">
-        <v>6.25</v>
+        <v>6.83</v>
       </c>
       <c r="AE20" s="94" t="n">
         <v/>
@@ -8631,7 +8639,7 @@
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>65.7</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>65.7</v>
@@ -8649,73 +8657,73 @@
         <v>81.84</v>
       </c>
       <c r="H21" s="94" t="n">
-        <v>81.84</v>
+        <v>15.76</v>
       </c>
       <c r="I21" s="94" t="n">
-        <v>15.76</v>
+        <v>23.93</v>
       </c>
       <c r="J21" s="94" t="n">
-        <v>23.93</v>
+        <v>22.27</v>
       </c>
       <c r="K21" s="94" t="n">
-        <v>22.27</v>
+        <v>86.19</v>
       </c>
       <c r="L21" s="94" t="n">
-        <v>86.19</v>
+        <v>60.63</v>
       </c>
       <c r="M21" s="94" t="n">
-        <v>60.63</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="N21" s="94" t="n">
-        <v>60.63</v>
+        <v>58.19</v>
       </c>
       <c r="O21" s="94" t="n">
-        <v>83.51000000000001</v>
+        <v>90.16</v>
       </c>
       <c r="P21" s="94" t="n">
-        <v>58.19</v>
+        <v>84.39</v>
       </c>
       <c r="Q21" s="94" t="n">
-        <v>90.16</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="R21" s="94" t="n">
-        <v>84.39</v>
+        <v>92.34</v>
       </c>
       <c r="S21" s="94" t="n">
-        <v>76.79000000000001</v>
+        <v>40.89</v>
       </c>
       <c r="T21" s="94" t="n">
-        <v>76.79000000000001</v>
+        <v>96.09</v>
       </c>
       <c r="U21" s="94" t="n">
-        <v>92.34</v>
+        <v>95.83</v>
       </c>
       <c r="V21" s="94" t="n">
-        <v>40.89</v>
+        <v>95.06</v>
       </c>
       <c r="W21" s="94" t="n">
-        <v>96.09</v>
+        <v>91.83</v>
       </c>
       <c r="X21" s="94" t="n">
-        <v>95.83</v>
+        <v>85.17</v>
       </c>
       <c r="Y21" s="94" t="n">
-        <v>95.06</v>
+        <v>65.2</v>
       </c>
       <c r="Z21" s="94" t="n">
-        <v>95.06</v>
+        <v>51.58</v>
       </c>
       <c r="AA21" s="94" t="n">
-        <v>91.83</v>
+        <v>3</v>
       </c>
       <c r="AB21" s="94" t="n">
-        <v>85.17</v>
+        <v>12.54</v>
       </c>
       <c r="AC21" s="94" t="n">
-        <v>65.2</v>
+        <v>17.38</v>
       </c>
       <c r="AD21" s="94" t="n">
-        <v>51.58</v>
+        <v>19.37</v>
       </c>
       <c r="AE21" s="94" t="n">
         <v/>
@@ -8757,114 +8765,114 @@
           <t>red</t>
         </is>
       </c>
-      <c r="H22" s="92" t="inlineStr">
+      <c r="H22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I22" s="91" t="inlineStr">
+      <c r="P22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J22" s="91" t="inlineStr">
+      <c r="AA22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="K22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="L22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="M22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC22" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AD22" s="91" t="inlineStr">
@@ -8883,7 +8891,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>3.05</v>
+        <v>5.41</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>3.05</v>
@@ -8901,73 +8909,73 @@
         <v>6.54</v>
       </c>
       <c r="H23" s="94" t="n">
-        <v>6.54</v>
+        <v>5.77</v>
       </c>
       <c r="I23" s="94" t="n">
-        <v>5.77</v>
+        <v>7.39</v>
       </c>
       <c r="J23" s="94" t="n">
-        <v>7.39</v>
+        <v>7.15</v>
       </c>
       <c r="K23" s="94" t="n">
-        <v>7.15</v>
+        <v>7.5</v>
       </c>
       <c r="L23" s="94" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="M23" s="94" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="N23" s="94" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="O23" s="94" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="P23" s="94" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="Q23" s="94" t="n">
         <v>7.5</v>
       </c>
-      <c r="M23" s="94" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="N23" s="94" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="O23" s="94" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="P23" s="94" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="Q23" s="94" t="n">
-        <v>7.9</v>
-      </c>
       <c r="R23" s="94" t="n">
-        <v>7.56</v>
+        <v>7.45</v>
       </c>
       <c r="S23" s="94" t="n">
-        <v>7.5</v>
+        <v>5.31</v>
       </c>
       <c r="T23" s="94" t="n">
-        <v>7.5</v>
+        <v>6.27</v>
       </c>
       <c r="U23" s="94" t="n">
-        <v>7.45</v>
+        <v>6.36</v>
       </c>
       <c r="V23" s="94" t="n">
-        <v>5.31</v>
+        <v>6.59</v>
       </c>
       <c r="W23" s="94" t="n">
-        <v>6.27</v>
+        <v>5.98</v>
       </c>
       <c r="X23" s="94" t="n">
-        <v>6.36</v>
+        <v>5.89</v>
       </c>
       <c r="Y23" s="94" t="n">
-        <v>6.59</v>
+        <v>5.41</v>
       </c>
       <c r="Z23" s="94" t="n">
-        <v>6.59</v>
+        <v>5.47</v>
       </c>
       <c r="AA23" s="94" t="n">
-        <v>5.98</v>
+        <v>4.12</v>
       </c>
       <c r="AB23" s="94" t="n">
-        <v>5.89</v>
+        <v>4.86</v>
       </c>
       <c r="AC23" s="94" t="n">
-        <v>5.41</v>
+        <v>5.61</v>
       </c>
       <c r="AD23" s="94" t="n">
-        <v>5.47</v>
+        <v>5.27</v>
       </c>
       <c r="AE23" s="94" t="n">
         <v/>
@@ -8980,7 +8988,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>11.76</v>
+        <v>12.09</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>11.76</v>
@@ -8998,73 +9006,73 @@
         <v>12.24</v>
       </c>
       <c r="H24" s="94" t="n">
-        <v>12.24</v>
+        <v>10.61</v>
       </c>
       <c r="I24" s="94" t="n">
-        <v>10.61</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="J24" s="94" t="n">
-        <v>9.720000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="K24" s="94" t="n">
-        <v>9.609999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="L24" s="94" t="n">
-        <v>8.859999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="M24" s="94" t="n">
-        <v>8.789999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="N24" s="94" t="n">
-        <v>8.789999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O24" s="94" t="n">
-        <v>8.41</v>
+        <v>7.87</v>
       </c>
       <c r="P24" s="94" t="n">
-        <v>8.6</v>
+        <v>7.54</v>
       </c>
       <c r="Q24" s="94" t="n">
-        <v>7.87</v>
+        <v>6.31</v>
       </c>
       <c r="R24" s="94" t="n">
-        <v>7.54</v>
+        <v>5.57</v>
       </c>
       <c r="S24" s="94" t="n">
-        <v>6.31</v>
+        <v>4.38</v>
       </c>
       <c r="T24" s="94" t="n">
-        <v>6.31</v>
+        <v>5.92</v>
       </c>
       <c r="U24" s="94" t="n">
-        <v>5.57</v>
+        <v>5.87</v>
       </c>
       <c r="V24" s="94" t="n">
-        <v>4.38</v>
+        <v>4.86</v>
       </c>
       <c r="W24" s="94" t="n">
-        <v>5.92</v>
+        <v>3.31</v>
       </c>
       <c r="X24" s="94" t="n">
-        <v>5.87</v>
+        <v>3.42</v>
       </c>
       <c r="Y24" s="94" t="n">
-        <v>4.86</v>
+        <v>4.16</v>
       </c>
       <c r="Z24" s="94" t="n">
-        <v>4.86</v>
+        <v>5.26</v>
       </c>
       <c r="AA24" s="94" t="n">
-        <v>3.31</v>
+        <v>4.21</v>
       </c>
       <c r="AB24" s="94" t="n">
-        <v>3.42</v>
+        <v>4.76</v>
       </c>
       <c r="AC24" s="94" t="n">
-        <v>4.16</v>
+        <v>4.95</v>
       </c>
       <c r="AD24" s="94" t="n">
-        <v>5.26</v>
+        <v>4.95</v>
       </c>
       <c r="AE24" s="94" t="n">
         <v/>
@@ -9077,7 +9085,7 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>66.56</v>
+        <v>82.94</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>66.56</v>
@@ -9095,73 +9103,73 @@
         <v>68.36</v>
       </c>
       <c r="H25" s="94" t="n">
-        <v>68.36</v>
+        <v>28.19</v>
       </c>
       <c r="I25" s="94" t="n">
-        <v>28.19</v>
+        <v>52.09</v>
       </c>
       <c r="J25" s="94" t="n">
-        <v>52.09</v>
+        <v>45.5</v>
       </c>
       <c r="K25" s="94" t="n">
-        <v>45.5</v>
+        <v>76.02</v>
       </c>
       <c r="L25" s="94" t="n">
-        <v>76.02</v>
+        <v>74.91</v>
       </c>
       <c r="M25" s="94" t="n">
-        <v>74.91</v>
+        <v>66.62</v>
       </c>
       <c r="N25" s="94" t="n">
-        <v>74.91</v>
+        <v>42.84</v>
       </c>
       <c r="O25" s="94" t="n">
-        <v>66.62</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="P25" s="94" t="n">
-        <v>42.84</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="Q25" s="94" t="n">
-        <v>92.18000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="R25" s="94" t="n">
-        <v>89.98999999999999</v>
+        <v>87.58</v>
       </c>
       <c r="S25" s="94" t="n">
-        <v>88.40000000000001</v>
+        <v>65.31</v>
       </c>
       <c r="T25" s="94" t="n">
-        <v>88.40000000000001</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="U25" s="94" t="n">
-        <v>87.58</v>
+        <v>88.3</v>
       </c>
       <c r="V25" s="94" t="n">
-        <v>65.31</v>
+        <v>82.94</v>
       </c>
       <c r="W25" s="94" t="n">
-        <v>85.48999999999999</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="X25" s="94" t="n">
-        <v>88.3</v>
+        <v>56.57</v>
       </c>
       <c r="Y25" s="94" t="n">
-        <v>82.94</v>
+        <v>46.45</v>
       </c>
       <c r="Z25" s="94" t="n">
-        <v>82.94</v>
+        <v>52.5</v>
       </c>
       <c r="AA25" s="94" t="n">
-        <v>71.68000000000001</v>
+        <v>13.02</v>
       </c>
       <c r="AB25" s="94" t="n">
-        <v>56.57</v>
+        <v>24.55</v>
       </c>
       <c r="AC25" s="94" t="n">
-        <v>46.45</v>
+        <v>35.87</v>
       </c>
       <c r="AD25" s="94" t="n">
-        <v>52.5</v>
+        <v>32.25</v>
       </c>
       <c r="AE25" s="94" t="n">
         <v/>
@@ -9203,114 +9211,114 @@
           <t>red</t>
         </is>
       </c>
-      <c r="H26" s="92" t="inlineStr">
+      <c r="H26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I26" s="91" t="inlineStr">
+      <c r="N26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J26" s="91" t="inlineStr">
+      <c r="O26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K26" s="91" t="inlineStr">
+      <c r="T26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="M26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="Z26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="AD26" s="93" t="inlineStr">
@@ -9329,7 +9337,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>1.58</v>
+        <v>2.64</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>1.58</v>
@@ -9347,73 +9355,73 @@
         <v>-0.8</v>
       </c>
       <c r="H27" s="94" t="n">
-        <v>-0.8</v>
+        <v>-3.91</v>
       </c>
       <c r="I27" s="94" t="n">
-        <v>-3.91</v>
+        <v>-2.74</v>
       </c>
       <c r="J27" s="94" t="n">
-        <v>-2.74</v>
+        <v>-2.68</v>
       </c>
       <c r="K27" s="94" t="n">
-        <v>-2.68</v>
+        <v>-0.89</v>
       </c>
       <c r="L27" s="94" t="n">
-        <v>-0.89</v>
+        <v>-0.38</v>
       </c>
       <c r="M27" s="94" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N27" s="94" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="O27" s="94" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P27" s="94" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="Q27" s="94" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R27" s="94" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S27" s="94" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="T27" s="94" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="U27" s="94" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="V27" s="94" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W27" s="94" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="X27" s="94" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="Y27" s="94" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="Z27" s="94" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="AA27" s="94" t="n">
+        <v>-3.76</v>
+      </c>
+      <c r="AB27" s="94" t="n">
         <v>-0.38</v>
       </c>
-      <c r="N27" s="94" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="O27" s="94" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="P27" s="94" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Q27" s="94" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R27" s="94" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="S27" s="94" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="T27" s="94" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U27" s="94" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V27" s="94" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="W27" s="94" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="X27" s="94" t="n">
-        <v>-0.73</v>
-      </c>
-      <c r="Y27" s="94" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z27" s="94" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AA27" s="94" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="AB27" s="94" t="n">
-        <v>-1.66</v>
-      </c>
       <c r="AC27" s="94" t="n">
-        <v>-3.63</v>
+        <v>-0.28</v>
       </c>
       <c r="AD27" s="94" t="n">
-        <v>-4.11</v>
+        <v>-0.21</v>
       </c>
       <c r="AE27" s="94" t="n">
         <v/>
@@ -9426,7 +9434,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>19.63</v>
+        <v>18.71</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>19.63</v>
@@ -9444,73 +9452,73 @@
         <v>14.18</v>
       </c>
       <c r="H28" s="94" t="n">
-        <v>14.18</v>
+        <v>10.78</v>
       </c>
       <c r="I28" s="94" t="n">
-        <v>10.78</v>
+        <v>9.02</v>
       </c>
       <c r="J28" s="94" t="n">
-        <v>9.02</v>
+        <v>10.76</v>
       </c>
       <c r="K28" s="94" t="n">
-        <v>10.76</v>
+        <v>11.54</v>
       </c>
       <c r="L28" s="94" t="n">
-        <v>11.54</v>
+        <v>11.48</v>
       </c>
       <c r="M28" s="94" t="n">
-        <v>11.48</v>
+        <v>11.95</v>
       </c>
       <c r="N28" s="94" t="n">
-        <v>11.48</v>
+        <v>12.67</v>
       </c>
       <c r="O28" s="94" t="n">
-        <v>11.95</v>
+        <v>11.04</v>
       </c>
       <c r="P28" s="94" t="n">
-        <v>12.67</v>
+        <v>10.68</v>
       </c>
       <c r="Q28" s="94" t="n">
-        <v>11.04</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="R28" s="94" t="n">
-        <v>10.68</v>
+        <v>9.98</v>
       </c>
       <c r="S28" s="94" t="n">
-        <v>9.460000000000001</v>
+        <v>7.16</v>
       </c>
       <c r="T28" s="94" t="n">
-        <v>9.460000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="U28" s="94" t="n">
-        <v>9.98</v>
+        <v>7.37</v>
       </c>
       <c r="V28" s="94" t="n">
-        <v>7.16</v>
+        <v>7.64</v>
       </c>
       <c r="W28" s="94" t="n">
-        <v>8.039999999999999</v>
+        <v>7.12</v>
       </c>
       <c r="X28" s="94" t="n">
-        <v>7.37</v>
+        <v>6.27</v>
       </c>
       <c r="Y28" s="94" t="n">
-        <v>7.64</v>
+        <v>5.31</v>
       </c>
       <c r="Z28" s="94" t="n">
-        <v>7.64</v>
+        <v>4.85</v>
       </c>
       <c r="AA28" s="94" t="n">
-        <v>7.12</v>
+        <v>4.49</v>
       </c>
       <c r="AB28" s="94" t="n">
-        <v>6.27</v>
+        <v>6.19</v>
       </c>
       <c r="AC28" s="94" t="n">
-        <v>5.31</v>
+        <v>5.6</v>
       </c>
       <c r="AD28" s="94" t="n">
-        <v>4.85</v>
+        <v>5.35</v>
       </c>
       <c r="AE28" s="94" t="n">
         <v/>
@@ -9523,7 +9531,7 @@
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>77.45999999999999</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>77.45999999999999</v>
@@ -9541,73 +9549,73 @@
         <v>85.03</v>
       </c>
       <c r="H29" s="94" t="n">
-        <v>85.03</v>
+        <v>20.54</v>
       </c>
       <c r="I29" s="94" t="n">
-        <v>20.54</v>
+        <v>21.97</v>
       </c>
       <c r="J29" s="94" t="n">
-        <v>21.97</v>
+        <v>15.42</v>
       </c>
       <c r="K29" s="94" t="n">
-        <v>15.42</v>
+        <v>74.7</v>
       </c>
       <c r="L29" s="94" t="n">
-        <v>74.7</v>
+        <v>51.35</v>
       </c>
       <c r="M29" s="94" t="n">
-        <v>51.35</v>
+        <v>96.66</v>
       </c>
       <c r="N29" s="94" t="n">
-        <v>51.35</v>
+        <v>89.75</v>
       </c>
       <c r="O29" s="94" t="n">
-        <v>96.66</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="P29" s="94" t="n">
-        <v>89.75</v>
+        <v>77.02</v>
       </c>
       <c r="Q29" s="94" t="n">
-        <v>88.93000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="R29" s="94" t="n">
-        <v>77.02</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="S29" s="94" t="n">
-        <v>73.3</v>
+        <v>42.32</v>
       </c>
       <c r="T29" s="94" t="n">
-        <v>73.3</v>
+        <v>70.06</v>
       </c>
       <c r="U29" s="94" t="n">
-        <v>92.18000000000001</v>
+        <v>61.86</v>
       </c>
       <c r="V29" s="94" t="n">
-        <v>42.32</v>
+        <v>95.17</v>
       </c>
       <c r="W29" s="94" t="n">
-        <v>70.06</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="X29" s="94" t="n">
-        <v>61.86</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="Y29" s="94" t="n">
-        <v>95.17</v>
+        <v>65.19</v>
       </c>
       <c r="Z29" s="94" t="n">
-        <v>95.17</v>
+        <v>44.48</v>
       </c>
       <c r="AA29" s="94" t="n">
-        <v>92.73999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AB29" s="94" t="n">
-        <v>88.20999999999999</v>
+        <v>27.81</v>
       </c>
       <c r="AC29" s="94" t="n">
-        <v>65.19</v>
+        <v>12.7</v>
       </c>
       <c r="AD29" s="94" t="n">
-        <v>44.48</v>
+        <v>14.52</v>
       </c>
       <c r="AE29" s="94" t="n">
         <v/>
@@ -9654,118 +9662,120 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="I30" s="91" t="inlineStr">
+      <c r="I30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J30" s="93" t="inlineStr">
+      <c r="K30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K30" s="91" t="inlineStr">
+      <c r="Y30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L30" s="91" t="inlineStr">
+      <c r="AE30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
-      </c>
-      <c r="M30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB30" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC30" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD30" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE30" s="91" t="n">
-        <v/>
       </c>
     </row>
     <row r="31">
@@ -9793,76 +9803,76 @@
         <v>-7.64</v>
       </c>
       <c r="H31" s="94" t="n">
-        <v>-7.64</v>
+        <v>-7.28</v>
       </c>
       <c r="I31" s="94" t="n">
-        <v>-7.28</v>
+        <v>-7.29</v>
       </c>
       <c r="J31" s="94" t="n">
-        <v>-7.29</v>
+        <v>-5.52</v>
       </c>
       <c r="K31" s="94" t="n">
-        <v>-5.52</v>
+        <v>-7.32</v>
       </c>
       <c r="L31" s="94" t="n">
-        <v>-7.32</v>
+        <v>-1.85</v>
       </c>
       <c r="M31" s="94" t="n">
-        <v>-1.85</v>
+        <v>-2.87</v>
       </c>
       <c r="N31" s="94" t="n">
-        <v>-1.85</v>
+        <v>-4.44</v>
       </c>
       <c r="O31" s="94" t="n">
-        <v>-2.87</v>
+        <v>-4.15</v>
       </c>
       <c r="P31" s="94" t="n">
-        <v>-4.44</v>
+        <v>-4.11</v>
       </c>
       <c r="Q31" s="94" t="n">
-        <v>-4.15</v>
+        <v>-4.11</v>
       </c>
       <c r="R31" s="94" t="n">
-        <v>-4.11</v>
+        <v>-6.33</v>
       </c>
       <c r="S31" s="94" t="n">
-        <v>-4.11</v>
+        <v>-7.13</v>
       </c>
       <c r="T31" s="94" t="n">
-        <v>-4.11</v>
+        <v>-6.7</v>
       </c>
       <c r="U31" s="94" t="n">
-        <v>-6.33</v>
+        <v>-5.28</v>
       </c>
       <c r="V31" s="94" t="n">
-        <v>-7.13</v>
+        <v>-5.31</v>
       </c>
       <c r="W31" s="94" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="X31" s="94" t="n">
+        <v>-7.44</v>
+      </c>
+      <c r="Y31" s="94" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="Z31" s="94" t="n">
         <v>-6.7</v>
       </c>
-      <c r="X31" s="94" t="n">
-        <v>-5.28</v>
-      </c>
-      <c r="Y31" s="94" t="n">
-        <v>-5.31</v>
-      </c>
-      <c r="Z31" s="94" t="n">
-        <v>-5.31</v>
-      </c>
       <c r="AA31" s="94" t="n">
-        <v>-4.5</v>
+        <v>-6.01</v>
       </c>
       <c r="AB31" s="94" t="n">
-        <v>-7.44</v>
+        <v>-5.71</v>
       </c>
       <c r="AC31" s="94" t="n">
-        <v>-5.1</v>
+        <v>-5.33</v>
       </c>
       <c r="AD31" s="94" t="n">
-        <v>-6.7</v>
+        <v>-0.9</v>
       </c>
       <c r="AE31" s="94" t="n">
-        <v/>
+        <v>0.04</v>
       </c>
     </row>
     <row r="32">
@@ -9890,76 +9900,76 @@
         <v>-2.25</v>
       </c>
       <c r="H32" s="94" t="n">
-        <v>-2.25</v>
+        <v>-2.26</v>
       </c>
       <c r="I32" s="94" t="n">
-        <v>-2.26</v>
+        <v>-4.48</v>
       </c>
       <c r="J32" s="94" t="n">
-        <v>-4.48</v>
+        <v>-2.82</v>
       </c>
       <c r="K32" s="94" t="n">
-        <v>-2.82</v>
+        <v>-3.63</v>
       </c>
       <c r="L32" s="94" t="n">
-        <v>-3.63</v>
+        <v>2.15</v>
       </c>
       <c r="M32" s="94" t="n">
-        <v>2.15</v>
+        <v>-2.13</v>
       </c>
       <c r="N32" s="94" t="n">
-        <v>2.15</v>
+        <v>-4.01</v>
       </c>
       <c r="O32" s="94" t="n">
-        <v>-2.13</v>
+        <v>-4.76</v>
       </c>
       <c r="P32" s="94" t="n">
-        <v>-4.01</v>
+        <v>-5.22</v>
       </c>
       <c r="Q32" s="94" t="n">
-        <v>-4.76</v>
+        <v>-5.22</v>
       </c>
       <c r="R32" s="94" t="n">
-        <v>-5.22</v>
+        <v>-7.96</v>
       </c>
       <c r="S32" s="94" t="n">
-        <v>-5.22</v>
+        <v>-9.43</v>
       </c>
       <c r="T32" s="94" t="n">
-        <v>-5.22</v>
+        <v>-11.19</v>
       </c>
       <c r="U32" s="94" t="n">
-        <v>-7.96</v>
+        <v>-9.5</v>
       </c>
       <c r="V32" s="94" t="n">
-        <v>-9.43</v>
+        <v>-9.48</v>
       </c>
       <c r="W32" s="94" t="n">
-        <v>-11.19</v>
+        <v>-9.92</v>
       </c>
       <c r="X32" s="94" t="n">
-        <v>-9.5</v>
+        <v>-12.73</v>
       </c>
       <c r="Y32" s="94" t="n">
-        <v>-9.48</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="Z32" s="94" t="n">
-        <v>-9.48</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="AA32" s="94" t="n">
-        <v>-9.92</v>
+        <v>-5.98</v>
       </c>
       <c r="AB32" s="94" t="n">
-        <v>-12.73</v>
+        <v>-5.54</v>
       </c>
       <c r="AC32" s="94" t="n">
-        <v>-9.609999999999999</v>
+        <v>-4.26</v>
       </c>
       <c r="AD32" s="94" t="n">
-        <v>-8.869999999999999</v>
+        <v>-0.29</v>
       </c>
       <c r="AE32" s="94" t="n">
-        <v/>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="33">
@@ -9987,76 +9997,76 @@
         <v>56.86</v>
       </c>
       <c r="H33" s="94" t="n">
-        <v>56.86</v>
+        <v>56.21</v>
       </c>
       <c r="I33" s="94" t="n">
-        <v>56.21</v>
+        <v>50.28</v>
       </c>
       <c r="J33" s="94" t="n">
-        <v>50.28</v>
+        <v>58.22</v>
       </c>
       <c r="K33" s="94" t="n">
-        <v>58.22</v>
+        <v>52.42</v>
       </c>
       <c r="L33" s="94" t="n">
-        <v>52.42</v>
+        <v>77.31</v>
       </c>
       <c r="M33" s="94" t="n">
-        <v>77.31</v>
+        <v>71.64</v>
       </c>
       <c r="N33" s="94" t="n">
-        <v>77.31</v>
+        <v>61.74</v>
       </c>
       <c r="O33" s="94" t="n">
-        <v>71.64</v>
+        <v>63.04</v>
       </c>
       <c r="P33" s="94" t="n">
-        <v>61.74</v>
+        <v>60.77</v>
       </c>
       <c r="Q33" s="94" t="n">
-        <v>63.04</v>
+        <v>60.77</v>
       </c>
       <c r="R33" s="94" t="n">
-        <v>60.77</v>
+        <v>54.21</v>
       </c>
       <c r="S33" s="94" t="n">
-        <v>60.77</v>
+        <v>42.56</v>
       </c>
       <c r="T33" s="94" t="n">
-        <v>60.77</v>
+        <v>39.44</v>
       </c>
       <c r="U33" s="94" t="n">
-        <v>54.21</v>
+        <v>43.68</v>
       </c>
       <c r="V33" s="94" t="n">
-        <v>42.56</v>
+        <v>43.96</v>
       </c>
       <c r="W33" s="94" t="n">
-        <v>39.44</v>
+        <v>46.79</v>
       </c>
       <c r="X33" s="94" t="n">
-        <v>43.68</v>
+        <v>26.47</v>
       </c>
       <c r="Y33" s="94" t="n">
-        <v>43.96</v>
+        <v>31.18</v>
       </c>
       <c r="Z33" s="94" t="n">
-        <v>43.96</v>
+        <v>31.7</v>
       </c>
       <c r="AA33" s="94" t="n">
-        <v>46.79</v>
+        <v>33.25</v>
       </c>
       <c r="AB33" s="94" t="n">
-        <v>26.47</v>
+        <v>35.58</v>
       </c>
       <c r="AC33" s="94" t="n">
-        <v>31.18</v>
+        <v>39.17</v>
       </c>
       <c r="AD33" s="94" t="n">
-        <v>31.7</v>
+        <v>62.79</v>
       </c>
       <c r="AE33" s="94" t="n">
-        <v/>
+        <v>63.09</v>
       </c>
     </row>
     <row r="34">
@@ -10100,115 +10110,113 @@
           <t>green</t>
         </is>
       </c>
-      <c r="I34" s="93" t="inlineStr">
+      <c r="I34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J34" s="91" t="inlineStr">
+      <c r="V34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="W34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="X34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Y34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K34" s="91" t="inlineStr">
+      <c r="AB34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="M34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
+      <c r="AD34" s="91" t="n">
+        <v/>
       </c>
       <c r="AE34" s="91" t="n">
         <v/>
@@ -10239,73 +10247,73 @@
         <v>-1.19</v>
       </c>
       <c r="H35" s="94" t="n">
-        <v>-1.19</v>
+        <v>-1.21</v>
       </c>
       <c r="I35" s="94" t="n">
-        <v>-1.21</v>
+        <v>0.33</v>
       </c>
       <c r="J35" s="94" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="K35" s="94" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="L35" s="94" t="n">
-        <v>0.63</v>
+        <v>1.1</v>
       </c>
       <c r="M35" s="94" t="n">
-        <v>1.1</v>
+        <v>1.71</v>
       </c>
       <c r="N35" s="94" t="n">
-        <v>1.1</v>
+        <v>2.62</v>
       </c>
       <c r="O35" s="94" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="P35" s="94" t="n">
-        <v>2.62</v>
+        <v>1.86</v>
       </c>
       <c r="Q35" s="94" t="n">
-        <v>1.79</v>
+        <v>1.03</v>
       </c>
       <c r="R35" s="94" t="n">
-        <v>1.86</v>
+        <v>0.8</v>
       </c>
       <c r="S35" s="94" t="n">
-        <v>1.03</v>
+        <v>0.66</v>
       </c>
       <c r="T35" s="94" t="n">
-        <v>1.03</v>
+        <v>0.39</v>
       </c>
       <c r="U35" s="94" t="n">
-        <v>0.8</v>
+        <v>-3.34</v>
       </c>
       <c r="V35" s="94" t="n">
-        <v>0.66</v>
+        <v>-2.39</v>
       </c>
       <c r="W35" s="94" t="n">
-        <v>0.39</v>
+        <v>-1.83</v>
       </c>
       <c r="X35" s="94" t="n">
-        <v>-3.34</v>
+        <v>-2.05</v>
       </c>
       <c r="Y35" s="94" t="n">
-        <v>-2.39</v>
+        <v>-1.53</v>
       </c>
       <c r="Z35" s="94" t="n">
-        <v>-2.39</v>
+        <v>-0.95</v>
       </c>
       <c r="AA35" s="94" t="n">
-        <v>-1.83</v>
+        <v>-2.12</v>
       </c>
       <c r="AB35" s="94" t="n">
-        <v>-2.05</v>
+        <v>-2.46</v>
       </c>
       <c r="AC35" s="94" t="n">
-        <v>-1.53</v>
+        <v>-0.67</v>
       </c>
       <c r="AD35" s="94" t="n">
-        <v>-0.95</v>
+        <v/>
       </c>
       <c r="AE35" s="94" t="n">
         <v/>
@@ -10336,73 +10344,73 @@
         <v>-0.47</v>
       </c>
       <c r="H36" s="94" t="n">
-        <v>-0.47</v>
+        <v>1.58</v>
       </c>
       <c r="I36" s="94" t="n">
-        <v>1.58</v>
+        <v>2.33</v>
       </c>
       <c r="J36" s="94" t="n">
         <v>2.33</v>
       </c>
       <c r="K36" s="94" t="n">
-        <v>2.33</v>
+        <v>3.01</v>
       </c>
       <c r="L36" s="94" t="n">
-        <v>3.01</v>
+        <v>2.85</v>
       </c>
       <c r="M36" s="94" t="n">
-        <v>2.85</v>
+        <v>1.83</v>
       </c>
       <c r="N36" s="94" t="n">
-        <v>2.85</v>
+        <v>1.26</v>
       </c>
       <c r="O36" s="94" t="n">
-        <v>1.83</v>
+        <v>-0.78</v>
       </c>
       <c r="P36" s="94" t="n">
-        <v>1.26</v>
+        <v>-1.02</v>
       </c>
       <c r="Q36" s="94" t="n">
-        <v>-0.78</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="R36" s="94" t="n">
-        <v>-1.02</v>
+        <v>-1.47</v>
       </c>
       <c r="S36" s="94" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.42</v>
       </c>
       <c r="T36" s="94" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.81</v>
       </c>
       <c r="U36" s="94" t="n">
-        <v>-1.47</v>
+        <v>-2.26</v>
       </c>
       <c r="V36" s="94" t="n">
-        <v>-1.42</v>
+        <v>-2.35</v>
       </c>
       <c r="W36" s="94" t="n">
-        <v>-1.81</v>
+        <v>-1.57</v>
       </c>
       <c r="X36" s="94" t="n">
-        <v>-2.26</v>
+        <v>-0.54</v>
       </c>
       <c r="Y36" s="94" t="n">
-        <v>-2.35</v>
+        <v>1.03</v>
       </c>
       <c r="Z36" s="94" t="n">
-        <v>-2.35</v>
+        <v>1.94</v>
       </c>
       <c r="AA36" s="94" t="n">
-        <v>-1.57</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AB36" s="94" t="n">
-        <v>-0.54</v>
+        <v>0.31</v>
       </c>
       <c r="AC36" s="94" t="n">
-        <v>1.03</v>
+        <v>0.42</v>
       </c>
       <c r="AD36" s="94" t="n">
-        <v>1.94</v>
+        <v/>
       </c>
       <c r="AE36" s="94" t="n">
         <v/>
@@ -10433,73 +10441,73 @@
         <v>14.32</v>
       </c>
       <c r="H37" s="94" t="n">
-        <v>14.32</v>
+        <v>23.23</v>
       </c>
       <c r="I37" s="94" t="n">
-        <v>23.23</v>
+        <v>50.34</v>
       </c>
       <c r="J37" s="94" t="n">
-        <v>50.34</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="K37" s="94" t="n">
-        <v>77.23999999999999</v>
+        <v>65.09</v>
       </c>
       <c r="L37" s="94" t="n">
-        <v>65.09</v>
+        <v>86.66</v>
       </c>
       <c r="M37" s="94" t="n">
-        <v>86.66</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="N37" s="94" t="n">
-        <v>86.66</v>
+        <v>88</v>
       </c>
       <c r="O37" s="94" t="n">
-        <v>90.48999999999999</v>
+        <v>77.98</v>
       </c>
       <c r="P37" s="94" t="n">
-        <v>88</v>
+        <v>59.82</v>
       </c>
       <c r="Q37" s="94" t="n">
-        <v>77.98</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="R37" s="94" t="n">
-        <v>59.82</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="S37" s="94" t="n">
-        <v>77.68000000000001</v>
+        <v>68.98</v>
       </c>
       <c r="T37" s="94" t="n">
-        <v>77.68000000000001</v>
+        <v>60.96</v>
       </c>
       <c r="U37" s="94" t="n">
-        <v>76.68000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="V37" s="94" t="n">
-        <v>68.98</v>
+        <v>20.58</v>
       </c>
       <c r="W37" s="94" t="n">
-        <v>60.96</v>
+        <v>30.12</v>
       </c>
       <c r="X37" s="94" t="n">
-        <v>9.050000000000001</v>
+        <v>12.08</v>
       </c>
       <c r="Y37" s="94" t="n">
-        <v>20.58</v>
+        <v>13.57</v>
       </c>
       <c r="Z37" s="94" t="n">
-        <v>20.58</v>
+        <v>28.44</v>
       </c>
       <c r="AA37" s="94" t="n">
-        <v>30.12</v>
+        <v>44.72</v>
       </c>
       <c r="AB37" s="94" t="n">
-        <v>12.08</v>
+        <v>14.66</v>
       </c>
       <c r="AC37" s="94" t="n">
-        <v>13.57</v>
+        <v>28.1</v>
       </c>
       <c r="AD37" s="94" t="n">
-        <v>28.44</v>
+        <v/>
       </c>
       <c r="AE37" s="94" t="n">
         <v/>
@@ -10546,118 +10554,120 @@
           <t>green</t>
         </is>
       </c>
-      <c r="I38" s="93" t="inlineStr">
+      <c r="I38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J38" s="91" t="inlineStr">
+      <c r="Y38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K38" s="91" t="inlineStr">
+      <c r="Z38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L38" s="91" t="inlineStr">
+      <c r="AC38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M38" s="91" t="inlineStr">
+      <c r="AD38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O38" s="92" t="inlineStr">
+      <c r="AE38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
-      </c>
-      <c r="P38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB38" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD38" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE38" s="91" t="n">
-        <v/>
       </c>
     </row>
     <row r="39">
@@ -10667,7 +10677,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>1.11</v>
@@ -10685,76 +10695,76 @@
         <v>2.21</v>
       </c>
       <c r="H39" s="94" t="n">
-        <v>2.21</v>
+        <v>2.67</v>
       </c>
       <c r="I39" s="94" t="n">
-        <v>2.67</v>
+        <v>5.39</v>
       </c>
       <c r="J39" s="94" t="n">
         <v>5.39</v>
       </c>
       <c r="K39" s="94" t="n">
-        <v>5.39</v>
+        <v>5.38</v>
       </c>
       <c r="L39" s="94" t="n">
-        <v>5.38</v>
+        <v>6.9</v>
       </c>
       <c r="M39" s="94" t="n">
-        <v>6.9</v>
+        <v>7.31</v>
       </c>
       <c r="N39" s="94" t="n">
-        <v>6.9</v>
+        <v>7.21</v>
       </c>
       <c r="O39" s="94" t="n">
-        <v>7.31</v>
+        <v>6.84</v>
       </c>
       <c r="P39" s="94" t="n">
-        <v>7.21</v>
+        <v>7.46</v>
       </c>
       <c r="Q39" s="94" t="n">
-        <v>6.84</v>
+        <v>6.69</v>
       </c>
       <c r="R39" s="94" t="n">
-        <v>7.46</v>
+        <v>5.73</v>
       </c>
       <c r="S39" s="94" t="n">
-        <v>6.69</v>
+        <v>6.27</v>
       </c>
       <c r="T39" s="94" t="n">
-        <v>6.69</v>
+        <v>7.42</v>
       </c>
       <c r="U39" s="94" t="n">
-        <v>5.73</v>
+        <v>7.48</v>
       </c>
       <c r="V39" s="94" t="n">
-        <v>6.27</v>
+        <v>6.99</v>
       </c>
       <c r="W39" s="94" t="n">
-        <v>7.42</v>
+        <v>7.27</v>
       </c>
       <c r="X39" s="94" t="n">
-        <v>7.48</v>
+        <v>5.46</v>
       </c>
       <c r="Y39" s="94" t="n">
-        <v>6.99</v>
+        <v>6.4</v>
       </c>
       <c r="Z39" s="94" t="n">
-        <v>6.99</v>
+        <v>6.18</v>
       </c>
       <c r="AA39" s="94" t="n">
-        <v>7.27</v>
+        <v>5.98</v>
       </c>
       <c r="AB39" s="94" t="n">
-        <v>5.46</v>
+        <v>7.51</v>
       </c>
       <c r="AC39" s="94" t="n">
-        <v>6.4</v>
+        <v>7.66</v>
       </c>
       <c r="AD39" s="94" t="n">
-        <v>6.18</v>
+        <v>7.64</v>
       </c>
       <c r="AE39" s="94" t="n">
-        <v/>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -10764,7 +10774,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>10.49</v>
+        <v>10.5</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>11.66</v>
@@ -10782,76 +10792,76 @@
         <v>10.03</v>
       </c>
       <c r="H40" s="94" t="n">
-        <v>10.03</v>
+        <v>9.94</v>
       </c>
       <c r="I40" s="94" t="n">
-        <v>9.94</v>
+        <v>12.83</v>
       </c>
       <c r="J40" s="94" t="n">
         <v>12.83</v>
       </c>
       <c r="K40" s="94" t="n">
-        <v>12.83</v>
+        <v>12.79</v>
       </c>
       <c r="L40" s="94" t="n">
-        <v>12.79</v>
+        <v>15.25</v>
       </c>
       <c r="M40" s="94" t="n">
-        <v>15.25</v>
+        <v>15.64</v>
       </c>
       <c r="N40" s="94" t="n">
-        <v>15.25</v>
+        <v>15.29</v>
       </c>
       <c r="O40" s="94" t="n">
-        <v>15.64</v>
+        <v>14.9</v>
       </c>
       <c r="P40" s="94" t="n">
-        <v>15.29</v>
+        <v>14.75</v>
       </c>
       <c r="Q40" s="94" t="n">
-        <v>14.9</v>
+        <v>14.79</v>
       </c>
       <c r="R40" s="94" t="n">
-        <v>14.75</v>
+        <v>13.96</v>
       </c>
       <c r="S40" s="94" t="n">
-        <v>14.79</v>
+        <v>14.46</v>
       </c>
       <c r="T40" s="94" t="n">
-        <v>14.79</v>
+        <v>14.07</v>
       </c>
       <c r="U40" s="94" t="n">
-        <v>13.96</v>
+        <v>14.24</v>
       </c>
       <c r="V40" s="94" t="n">
-        <v>14.46</v>
+        <v>14.96</v>
       </c>
       <c r="W40" s="94" t="n">
-        <v>14.07</v>
+        <v>15.21</v>
       </c>
       <c r="X40" s="94" t="n">
-        <v>14.24</v>
+        <v>12.06</v>
       </c>
       <c r="Y40" s="94" t="n">
-        <v>14.96</v>
+        <v>12.77</v>
       </c>
       <c r="Z40" s="94" t="n">
-        <v>14.96</v>
+        <v>11.58</v>
       </c>
       <c r="AA40" s="94" t="n">
-        <v>15.21</v>
+        <v>11.57</v>
       </c>
       <c r="AB40" s="94" t="n">
-        <v>12.06</v>
+        <v>11.58</v>
       </c>
       <c r="AC40" s="94" t="n">
-        <v>12.77</v>
+        <v>12.04</v>
       </c>
       <c r="AD40" s="94" t="n">
-        <v>11.58</v>
+        <v>11.38</v>
       </c>
       <c r="AE40" s="94" t="n">
-        <v/>
+        <v>11.44</v>
       </c>
     </row>
     <row r="41">
@@ -10861,7 +10871,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>35.7</v>
+        <v>35.77</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>37.56</v>
@@ -10879,76 +10889,76 @@
         <v>33.56</v>
       </c>
       <c r="H41" s="94" t="n">
-        <v>33.56</v>
+        <v>38.91</v>
       </c>
       <c r="I41" s="94" t="n">
-        <v>38.91</v>
+        <v>56.68</v>
       </c>
       <c r="J41" s="94" t="n">
         <v>56.68</v>
       </c>
       <c r="K41" s="94" t="n">
-        <v>56.68</v>
+        <v>57.12</v>
       </c>
       <c r="L41" s="94" t="n">
-        <v>57.12</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="M41" s="94" t="n">
-        <v>78.04000000000001</v>
+        <v>83.77</v>
       </c>
       <c r="N41" s="94" t="n">
-        <v>78.04000000000001</v>
+        <v>80.52</v>
       </c>
       <c r="O41" s="94" t="n">
-        <v>83.77</v>
+        <v>79.08</v>
       </c>
       <c r="P41" s="94" t="n">
-        <v>80.52</v>
+        <v>79.38</v>
       </c>
       <c r="Q41" s="94" t="n">
-        <v>79.08</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="R41" s="94" t="n">
-        <v>79.38</v>
+        <v>66.75</v>
       </c>
       <c r="S41" s="94" t="n">
-        <v>77.31999999999999</v>
+        <v>64.14</v>
       </c>
       <c r="T41" s="94" t="n">
-        <v>77.31999999999999</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="U41" s="94" t="n">
-        <v>66.75</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="V41" s="94" t="n">
-        <v>64.14</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="W41" s="94" t="n">
-        <v>66.76000000000001</v>
+        <v>66.14</v>
       </c>
       <c r="X41" s="94" t="n">
-        <v>65.90000000000001</v>
+        <v>50.55</v>
       </c>
       <c r="Y41" s="94" t="n">
-        <v>65.01000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="Z41" s="94" t="n">
-        <v>65.01000000000001</v>
+        <v>52.02</v>
       </c>
       <c r="AA41" s="94" t="n">
-        <v>66.14</v>
+        <v>46.05</v>
       </c>
       <c r="AB41" s="94" t="n">
-        <v>50.55</v>
+        <v>66.09</v>
       </c>
       <c r="AC41" s="94" t="n">
-        <v>57.1</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="AD41" s="94" t="n">
-        <v>52.02</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="AE41" s="94" t="n">
-        <v/>
+        <v>75.97</v>
       </c>
     </row>
     <row r="42">
@@ -10957,153 +10967,155 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="93" t="inlineStr">
+      <c r="B42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C42" s="93" t="inlineStr">
+      <c r="D42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D42" s="91" t="inlineStr">
+      <c r="F42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K42" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E42" s="93" t="inlineStr">
+      <c r="L42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="G42" s="93" t="inlineStr">
+      <c r="Y42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H42" s="93" t="inlineStr">
+      <c r="Z42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I42" s="93" t="inlineStr">
+      <c r="AA42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J42" s="93" t="inlineStr">
+      <c r="AB42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K42" s="93" t="inlineStr">
+      <c r="AC42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L42" s="91" t="inlineStr">
+      <c r="AD42" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R42" s="91" t="inlineStr">
+      <c r="AE42" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
-      </c>
-      <c r="S42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE42" s="91" t="n">
-        <v/>
       </c>
     </row>
     <row r="43">
@@ -11113,7 +11125,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>-0.14</v>
+        <v>0.58</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>-0.59</v>
@@ -11131,76 +11143,76 @@
         <v>-2.37</v>
       </c>
       <c r="H43" s="94" t="n">
-        <v>-2.37</v>
+        <v>-1.96</v>
       </c>
       <c r="I43" s="94" t="n">
-        <v>-1.96</v>
+        <v>0.05</v>
       </c>
       <c r="J43" s="94" t="n">
-        <v>0.05</v>
+        <v>0.87</v>
       </c>
       <c r="K43" s="94" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L43" s="94" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M43" s="94" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N43" s="94" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="O43" s="94" t="n">
         <v>0.87</v>
       </c>
-      <c r="L43" s="94" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="M43" s="94" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="N43" s="94" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="O43" s="94" t="n">
-        <v>0.6</v>
-      </c>
       <c r="P43" s="94" t="n">
-        <v>-0.87</v>
+        <v>-0.7</v>
       </c>
       <c r="Q43" s="94" t="n">
-        <v>0.87</v>
+        <v>0.28</v>
       </c>
       <c r="R43" s="94" t="n">
-        <v>-0.7</v>
+        <v>1.12</v>
       </c>
       <c r="S43" s="94" t="n">
-        <v>0.28</v>
+        <v>-2.16</v>
       </c>
       <c r="T43" s="94" t="n">
-        <v>0.28</v>
+        <v>-2.28</v>
       </c>
       <c r="U43" s="94" t="n">
-        <v>1.12</v>
+        <v>-3.34</v>
       </c>
       <c r="V43" s="94" t="n">
-        <v>-2.16</v>
+        <v>-2.14</v>
       </c>
       <c r="W43" s="94" t="n">
-        <v>-2.28</v>
+        <v>-3.08</v>
       </c>
       <c r="X43" s="94" t="n">
-        <v>-3.34</v>
+        <v>-2.29</v>
       </c>
       <c r="Y43" s="94" t="n">
-        <v>-2.14</v>
+        <v>-2.9</v>
       </c>
       <c r="Z43" s="94" t="n">
-        <v>-2.14</v>
+        <v>-1.93</v>
       </c>
       <c r="AA43" s="94" t="n">
-        <v>-3.08</v>
+        <v>-2.01</v>
       </c>
       <c r="AB43" s="94" t="n">
-        <v>-2.29</v>
+        <v>-3.58</v>
       </c>
       <c r="AC43" s="94" t="n">
-        <v>-2.9</v>
+        <v>-4.62</v>
       </c>
       <c r="AD43" s="94" t="n">
-        <v>-1.93</v>
+        <v>-2.75</v>
       </c>
       <c r="AE43" s="94" t="n">
-        <v/>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="44">
@@ -11210,7 +11222,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>-6.14</v>
+        <v>-5.47</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>-6.8</v>
@@ -11228,76 +11240,76 @@
         <v>-6.01</v>
       </c>
       <c r="H44" s="94" t="n">
+        <v>-6.31</v>
+      </c>
+      <c r="I44" s="94" t="n">
+        <v>-4.48</v>
+      </c>
+      <c r="J44" s="94" t="n">
+        <v>-5.85</v>
+      </c>
+      <c r="K44" s="94" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="L44" s="94" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="M44" s="94" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="N44" s="94" t="n">
         <v>-6.01</v>
       </c>
-      <c r="I44" s="94" t="n">
-        <v>-6.31</v>
-      </c>
-      <c r="J44" s="94" t="n">
-        <v>-4.48</v>
-      </c>
-      <c r="K44" s="94" t="n">
-        <v>-5.85</v>
-      </c>
-      <c r="L44" s="94" t="n">
-        <v>-4.68</v>
-      </c>
-      <c r="M44" s="94" t="n">
-        <v>-2.89</v>
-      </c>
-      <c r="N44" s="94" t="n">
-        <v>-2.89</v>
-      </c>
       <c r="O44" s="94" t="n">
-        <v>-3.77</v>
+        <v>-6.35</v>
       </c>
       <c r="P44" s="94" t="n">
-        <v>-6.01</v>
+        <v>-6.86</v>
       </c>
       <c r="Q44" s="94" t="n">
-        <v>-6.35</v>
+        <v>-7.99</v>
       </c>
       <c r="R44" s="94" t="n">
-        <v>-6.86</v>
+        <v>-6.6</v>
       </c>
       <c r="S44" s="94" t="n">
-        <v>-7.99</v>
+        <v>-8.43</v>
       </c>
       <c r="T44" s="94" t="n">
-        <v>-7.99</v>
+        <v>-8.75</v>
       </c>
       <c r="U44" s="94" t="n">
-        <v>-6.6</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="V44" s="94" t="n">
-        <v>-8.43</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="W44" s="94" t="n">
-        <v>-8.75</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="X44" s="94" t="n">
-        <v>-9.210000000000001</v>
+        <v>-9.26</v>
       </c>
       <c r="Y44" s="94" t="n">
+        <v>-9.44</v>
+      </c>
+      <c r="Z44" s="94" t="n">
+        <v>-9.02</v>
+      </c>
+      <c r="AA44" s="94" t="n">
+        <v>-10.35</v>
+      </c>
+      <c r="AB44" s="94" t="n">
         <v>-8.789999999999999</v>
       </c>
-      <c r="Z44" s="94" t="n">
-        <v>-8.789999999999999</v>
-      </c>
-      <c r="AA44" s="94" t="n">
-        <v>-8.789999999999999</v>
-      </c>
-      <c r="AB44" s="94" t="n">
-        <v>-9.26</v>
-      </c>
       <c r="AC44" s="94" t="n">
-        <v>-9.44</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="AD44" s="94" t="n">
-        <v>-9.02</v>
+        <v>-7.18</v>
       </c>
       <c r="AE44" s="94" t="n">
-        <v/>
+        <v>-6.04</v>
       </c>
     </row>
     <row r="45">
@@ -11307,7 +11319,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>42.47</v>
+        <v>54.29</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>46.1</v>
@@ -11325,76 +11337,76 @@
         <v>45.03</v>
       </c>
       <c r="H45" s="94" t="n">
-        <v>45.03</v>
+        <v>33.57</v>
       </c>
       <c r="I45" s="94" t="n">
-        <v>33.57</v>
+        <v>45.48</v>
       </c>
       <c r="J45" s="94" t="n">
-        <v>45.48</v>
+        <v>44.93</v>
       </c>
       <c r="K45" s="94" t="n">
-        <v>44.93</v>
+        <v>52.35</v>
       </c>
       <c r="L45" s="94" t="n">
-        <v>52.35</v>
+        <v>78.61</v>
       </c>
       <c r="M45" s="94" t="n">
-        <v>78.61</v>
+        <v>75.48</v>
       </c>
       <c r="N45" s="94" t="n">
-        <v>78.61</v>
+        <v>57.98</v>
       </c>
       <c r="O45" s="94" t="n">
-        <v>75.48</v>
+        <v>66.2</v>
       </c>
       <c r="P45" s="94" t="n">
-        <v>57.98</v>
+        <v>52.83</v>
       </c>
       <c r="Q45" s="94" t="n">
-        <v>66.2</v>
+        <v>51.58</v>
       </c>
       <c r="R45" s="94" t="n">
-        <v>52.83</v>
+        <v>74.97</v>
       </c>
       <c r="S45" s="94" t="n">
-        <v>51.58</v>
+        <v>45.92</v>
       </c>
       <c r="T45" s="94" t="n">
-        <v>51.58</v>
+        <v>59.76</v>
       </c>
       <c r="U45" s="94" t="n">
-        <v>74.97</v>
+        <v>48.71</v>
       </c>
       <c r="V45" s="94" t="n">
-        <v>45.92</v>
+        <v>53.61</v>
       </c>
       <c r="W45" s="94" t="n">
-        <v>59.76</v>
+        <v>45.19</v>
       </c>
       <c r="X45" s="94" t="n">
-        <v>48.71</v>
+        <v>32.83</v>
       </c>
       <c r="Y45" s="94" t="n">
-        <v>53.61</v>
+        <v>34.58</v>
       </c>
       <c r="Z45" s="94" t="n">
-        <v>53.61</v>
+        <v>37.2</v>
       </c>
       <c r="AA45" s="94" t="n">
-        <v>45.19</v>
+        <v>16.31</v>
       </c>
       <c r="AB45" s="94" t="n">
-        <v>32.83</v>
+        <v>22.99</v>
       </c>
       <c r="AC45" s="94" t="n">
-        <v>34.58</v>
+        <v>32.1</v>
       </c>
       <c r="AD45" s="94" t="n">
-        <v>37.2</v>
+        <v>48.66</v>
       </c>
       <c r="AE45" s="94" t="n">
-        <v/>
+        <v>80.73</v>
       </c>
     </row>
     <row r="46">
@@ -11403,153 +11415,155 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="91" t="inlineStr">
+      <c r="B46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C46" s="91" t="inlineStr">
+      <c r="D46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="E46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D46" s="92" t="inlineStr">
+      <c r="F46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E46" s="91" t="inlineStr">
+      <c r="M46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F46" s="91" t="inlineStr">
+      <c r="O46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G46" s="91" t="inlineStr">
+      <c r="R46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Y46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H46" s="91" t="inlineStr">
+      <c r="AE46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
-      </c>
-      <c r="I46" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="J46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="K46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="L46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="M46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB46" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC46" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD46" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE46" s="91" t="n">
-        <v/>
       </c>
     </row>
     <row r="47">
@@ -11559,7 +11573,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>5.73</v>
+        <v>6.61</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>4.66</v>
@@ -11577,76 +11591,76 @@
         <v>1.99</v>
       </c>
       <c r="H47" s="94" t="n">
-        <v>1.99</v>
+        <v>2.59</v>
       </c>
       <c r="I47" s="94" t="n">
-        <v>2.59</v>
+        <v>4.12</v>
       </c>
       <c r="J47" s="94" t="n">
-        <v>4.12</v>
+        <v>5.36</v>
       </c>
       <c r="K47" s="94" t="n">
-        <v>5.36</v>
+        <v>4.62</v>
       </c>
       <c r="L47" s="94" t="n">
-        <v>4.62</v>
+        <v>5.4</v>
       </c>
       <c r="M47" s="94" t="n">
-        <v>5.4</v>
+        <v>4.27</v>
       </c>
       <c r="N47" s="94" t="n">
-        <v>5.4</v>
+        <v>2.96</v>
       </c>
       <c r="O47" s="94" t="n">
-        <v>4.27</v>
+        <v>4.58</v>
       </c>
       <c r="P47" s="94" t="n">
-        <v>2.96</v>
+        <v>3.04</v>
       </c>
       <c r="Q47" s="94" t="n">
-        <v>4.58</v>
+        <v>2.66</v>
       </c>
       <c r="R47" s="94" t="n">
-        <v>3.04</v>
+        <v>4.35</v>
       </c>
       <c r="S47" s="94" t="n">
-        <v>2.66</v>
+        <v>3.06</v>
       </c>
       <c r="T47" s="94" t="n">
-        <v>2.66</v>
+        <v>3.02</v>
       </c>
       <c r="U47" s="94" t="n">
-        <v>4.35</v>
+        <v>1.68</v>
       </c>
       <c r="V47" s="94" t="n">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="W47" s="94" t="n">
-        <v>3.02</v>
+        <v>1.45</v>
       </c>
       <c r="X47" s="94" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="Y47" s="94" t="n">
-        <v>2.95</v>
+        <v>0.74</v>
       </c>
       <c r="Z47" s="94" t="n">
-        <v>2.95</v>
+        <v>2.08</v>
       </c>
       <c r="AA47" s="94" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AB47" s="94" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AC47" s="94" t="n">
-        <v>0.74</v>
+        <v>-0.21</v>
       </c>
       <c r="AD47" s="94" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AE47" s="94" t="n">
-        <v/>
+        <v>2.36</v>
       </c>
     </row>
     <row r="48">
@@ -11656,7 +11670,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>7.23</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>6.2</v>
@@ -11674,76 +11688,76 @@
         <v>7.2</v>
       </c>
       <c r="H48" s="94" t="n">
-        <v>7.2</v>
+        <v>7.01</v>
       </c>
       <c r="I48" s="94" t="n">
-        <v>7.01</v>
+        <v>7.87</v>
       </c>
       <c r="J48" s="94" t="n">
-        <v>7.87</v>
+        <v>6.58</v>
       </c>
       <c r="K48" s="94" t="n">
-        <v>6.58</v>
+        <v>7.78</v>
       </c>
       <c r="L48" s="94" t="n">
-        <v>7.78</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M48" s="94" t="n">
-        <v>8.460000000000001</v>
+        <v>6.31</v>
       </c>
       <c r="N48" s="94" t="n">
-        <v>8.460000000000001</v>
+        <v>4.66</v>
       </c>
       <c r="O48" s="94" t="n">
-        <v>6.31</v>
+        <v>3.7</v>
       </c>
       <c r="P48" s="94" t="n">
-        <v>4.66</v>
+        <v>3.7</v>
       </c>
       <c r="Q48" s="94" t="n">
-        <v>3.7</v>
+        <v>1.72</v>
       </c>
       <c r="R48" s="94" t="n">
-        <v>3.7</v>
+        <v>3.46</v>
       </c>
       <c r="S48" s="94" t="n">
-        <v>1.72</v>
+        <v>2.34</v>
       </c>
       <c r="T48" s="94" t="n">
-        <v>1.72</v>
+        <v>1.26</v>
       </c>
       <c r="U48" s="94" t="n">
-        <v>3.46</v>
+        <v>0.84</v>
       </c>
       <c r="V48" s="94" t="n">
-        <v>2.34</v>
+        <v>1.71</v>
       </c>
       <c r="W48" s="94" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="X48" s="94" t="n">
-        <v>0.84</v>
+        <v>0.68</v>
       </c>
       <c r="Y48" s="94" t="n">
-        <v>1.71</v>
+        <v>0.48</v>
       </c>
       <c r="Z48" s="94" t="n">
-        <v>1.71</v>
+        <v>2.38</v>
       </c>
       <c r="AA48" s="94" t="n">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="AB48" s="94" t="n">
-        <v>0.68</v>
+        <v>3.59</v>
       </c>
       <c r="AC48" s="94" t="n">
-        <v>0.48</v>
+        <v>3.65</v>
       </c>
       <c r="AD48" s="94" t="n">
-        <v>2.38</v>
+        <v>4.49</v>
       </c>
       <c r="AE48" s="94" t="n">
-        <v/>
+        <v>5.4</v>
       </c>
     </row>
     <row r="49">
@@ -11753,7 +11767,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>58.46</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>58.26</v>
@@ -11771,82 +11785,82 @@
         <v>53.55</v>
       </c>
       <c r="H49" s="94" t="n">
-        <v>53.55</v>
+        <v>46.86</v>
       </c>
       <c r="I49" s="94" t="n">
-        <v>46.86</v>
+        <v>56.45</v>
       </c>
       <c r="J49" s="94" t="n">
-        <v>56.45</v>
+        <v>59.76</v>
       </c>
       <c r="K49" s="94" t="n">
-        <v>59.76</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="L49" s="94" t="n">
-        <v>67.34999999999999</v>
+        <v>78.38</v>
       </c>
       <c r="M49" s="94" t="n">
-        <v>78.38</v>
+        <v>72.42</v>
       </c>
       <c r="N49" s="94" t="n">
-        <v>78.38</v>
+        <v>59.91</v>
       </c>
       <c r="O49" s="94" t="n">
-        <v>72.42</v>
+        <v>66</v>
       </c>
       <c r="P49" s="94" t="n">
-        <v>59.91</v>
+        <v>59.4</v>
       </c>
       <c r="Q49" s="94" t="n">
-        <v>66</v>
+        <v>52.95</v>
       </c>
       <c r="R49" s="94" t="n">
-        <v>59.4</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="S49" s="94" t="n">
-        <v>52.95</v>
+        <v>61.14</v>
       </c>
       <c r="T49" s="94" t="n">
-        <v>52.95</v>
+        <v>62.6</v>
       </c>
       <c r="U49" s="94" t="n">
-        <v>75.06999999999999</v>
+        <v>57.16</v>
       </c>
       <c r="V49" s="94" t="n">
-        <v>61.14</v>
+        <v>62.56</v>
       </c>
       <c r="W49" s="94" t="n">
-        <v>62.6</v>
+        <v>52.29</v>
       </c>
       <c r="X49" s="94" t="n">
-        <v>57.16</v>
+        <v>37.42</v>
       </c>
       <c r="Y49" s="94" t="n">
-        <v>62.56</v>
+        <v>31.32</v>
       </c>
       <c r="Z49" s="94" t="n">
-        <v>62.56</v>
+        <v>40.38</v>
       </c>
       <c r="AA49" s="94" t="n">
-        <v>52.29</v>
+        <v>26.19</v>
       </c>
       <c r="AB49" s="94" t="n">
-        <v>37.42</v>
+        <v>42.54</v>
       </c>
       <c r="AC49" s="94" t="n">
-        <v>31.32</v>
+        <v>43.82</v>
       </c>
       <c r="AD49" s="94" t="n">
-        <v>40.38</v>
+        <v>58.62</v>
       </c>
       <c r="AE49" s="94" t="n">
-        <v/>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：sensex:RS10:35.7&lt;=39</t>
+          <t>今日买报：sensex:RS10:35.77&lt;=39</t>
         </is>
       </c>
     </row>

--- a/report_2410.xlsx
+++ b/report_2410.xlsx
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>-0.54</v>
@@ -6346,147 +6346,147 @@
       </c>
       <c r="C1" s="77" t="inlineStr">
         <is>
-          <t>241013</t>
+          <t>241011</t>
         </is>
       </c>
       <c r="D1" s="77" t="inlineStr">
         <is>
-          <t>241011</t>
+          <t>241010</t>
         </is>
       </c>
       <c r="E1" s="77" t="inlineStr">
         <is>
-          <t>241010</t>
+          <t>241009</t>
         </is>
       </c>
       <c r="F1" s="77" t="inlineStr">
         <is>
-          <t>241009</t>
+          <t>241008</t>
         </is>
       </c>
       <c r="G1" s="77" t="inlineStr">
         <is>
-          <t>241008</t>
+          <t>241007</t>
         </is>
       </c>
       <c r="H1" s="77" t="inlineStr">
         <is>
-          <t>241007</t>
+          <t>241004</t>
         </is>
       </c>
       <c r="I1" s="77" t="inlineStr">
         <is>
-          <t>241006</t>
+          <t>241003</t>
         </is>
       </c>
       <c r="J1" s="77" t="inlineStr">
         <is>
-          <t>241004</t>
+          <t>241002</t>
         </is>
       </c>
       <c r="K1" s="77" t="inlineStr">
         <is>
-          <t>241003</t>
+          <t>241001</t>
         </is>
       </c>
       <c r="L1" s="77" t="inlineStr">
         <is>
-          <t>241002</t>
+          <t>240930</t>
         </is>
       </c>
       <c r="M1" s="77" t="inlineStr">
         <is>
-          <t>241001</t>
+          <t>240927</t>
         </is>
       </c>
       <c r="N1" s="77" t="inlineStr">
         <is>
-          <t>240930</t>
+          <t>240926</t>
         </is>
       </c>
       <c r="O1" s="77" t="inlineStr">
         <is>
-          <t>240929</t>
+          <t>240925</t>
         </is>
       </c>
       <c r="P1" s="77" t="inlineStr">
         <is>
-          <t>240927</t>
+          <t>240924</t>
         </is>
       </c>
       <c r="Q1" s="77" t="inlineStr">
         <is>
-          <t>240926</t>
+          <t>240923</t>
         </is>
       </c>
       <c r="R1" s="77" t="inlineStr">
         <is>
-          <t>240925</t>
+          <t>240920</t>
         </is>
       </c>
       <c r="S1" s="77" t="inlineStr">
         <is>
-          <t>240924</t>
+          <t>240919</t>
         </is>
       </c>
       <c r="T1" s="77" t="inlineStr">
         <is>
-          <t>240923</t>
+          <t>240918</t>
         </is>
       </c>
       <c r="U1" s="77" t="inlineStr">
         <is>
-          <t>240922</t>
+          <t>240917</t>
         </is>
       </c>
       <c r="V1" s="77" t="inlineStr">
         <is>
-          <t>240920</t>
+          <t>240916</t>
         </is>
       </c>
       <c r="W1" s="77" t="inlineStr">
         <is>
-          <t>240919</t>
+          <t>240913</t>
         </is>
       </c>
       <c r="X1" s="77" t="inlineStr">
         <is>
-          <t>240918</t>
+          <t>240912</t>
         </is>
       </c>
       <c r="Y1" s="77" t="inlineStr">
         <is>
-          <t>240917</t>
+          <t>240911</t>
         </is>
       </c>
       <c r="Z1" s="77" t="inlineStr">
         <is>
-          <t>240916</t>
+          <t>240910</t>
         </is>
       </c>
       <c r="AA1" s="77" t="inlineStr">
         <is>
-          <t>240915</t>
+          <t>240909</t>
         </is>
       </c>
       <c r="AB1" s="77" t="inlineStr">
         <is>
-          <t>240913</t>
+          <t>240906</t>
         </is>
       </c>
       <c r="AC1" s="77" t="inlineStr">
         <is>
-          <t>240912</t>
+          <t>240905</t>
         </is>
       </c>
       <c r="AD1" s="77" t="inlineStr">
         <is>
-          <t>240911</t>
+          <t>240904</t>
         </is>
       </c>
       <c r="AE1" s="77" t="inlineStr">
         <is>
-          <t>240910</t>
+          <t>240903</t>
         </is>
       </c>
     </row>
@@ -6516,74 +6516,74 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="F2" s="91" t="inlineStr">
+      <c r="F2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="H2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="I2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="R2" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S2" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="T2" s="91" t="inlineStr">
@@ -6591,24 +6591,24 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="U2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="U2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="V2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="W2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="X2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="Y2" s="93" t="inlineStr">
@@ -6660,16 +6660,16 @@
         <v>9.470000000000001</v>
       </c>
       <c r="D3" s="95" t="n">
-        <v>9.470000000000001</v>
+        <v>11.58</v>
       </c>
       <c r="E3" s="95" t="n">
-        <v>11.58</v>
+        <v>11.51</v>
       </c>
       <c r="F3" s="95" t="n">
-        <v>11.51</v>
+        <v>18.3</v>
       </c>
       <c r="G3" s="95" t="n">
-        <v>18.3</v>
+        <v>12.81</v>
       </c>
       <c r="H3" s="95" t="n">
         <v>12.81</v>
@@ -6687,61 +6687,61 @@
         <v>12.81</v>
       </c>
       <c r="M3" s="95" t="n">
-        <v>12.81</v>
+        <v>3.53</v>
       </c>
       <c r="N3" s="95" t="n">
-        <v>12.81</v>
+        <v>0.13</v>
       </c>
       <c r="O3" s="95" t="n">
-        <v>3.53</v>
+        <v>-3.29</v>
       </c>
       <c r="P3" s="95" t="n">
-        <v>3.53</v>
+        <v>-3.51</v>
       </c>
       <c r="Q3" s="95" t="n">
-        <v>0.13</v>
+        <v>-6.68</v>
       </c>
       <c r="R3" s="95" t="n">
-        <v>-3.29</v>
+        <v>-7.93</v>
       </c>
       <c r="S3" s="95" t="n">
-        <v>-3.51</v>
+        <v>-7.25</v>
       </c>
       <c r="T3" s="95" t="n">
-        <v>-6.68</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="U3" s="95" t="n">
-        <v>-7.93</v>
+        <v>-9.81</v>
       </c>
       <c r="V3" s="95" t="n">
-        <v>-7.93</v>
+        <v>-9.81</v>
       </c>
       <c r="W3" s="95" t="n">
-        <v>-7.25</v>
+        <v>-9.81</v>
       </c>
       <c r="X3" s="95" t="n">
-        <v>-8.300000000000001</v>
+        <v>-9.59</v>
       </c>
       <c r="Y3" s="95" t="n">
-        <v>-9.81</v>
+        <v>-9.82</v>
       </c>
       <c r="Z3" s="95" t="n">
-        <v>-9.81</v>
+        <v>-9.44</v>
       </c>
       <c r="AA3" s="95" t="n">
-        <v>-9.81</v>
+        <v>-9.26</v>
       </c>
       <c r="AB3" s="95" t="n">
-        <v>-9.81</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="AC3" s="95" t="n">
-        <v>-9.59</v>
+        <v>-7.94</v>
       </c>
       <c r="AD3" s="95" t="n">
-        <v>-9.82</v>
+        <v>-8.34</v>
       </c>
       <c r="AE3" s="95" t="n">
-        <v>-9.44</v>
+        <v>-7.43</v>
       </c>
     </row>
     <row r="4">
@@ -6757,16 +6757,16 @@
         <v>6.05</v>
       </c>
       <c r="D4" s="95" t="n">
-        <v>6.05</v>
+        <v>9.07</v>
       </c>
       <c r="E4" s="95" t="n">
-        <v>9.07</v>
+        <v>6.9</v>
       </c>
       <c r="F4" s="95" t="n">
-        <v>6.9</v>
+        <v>14.53</v>
       </c>
       <c r="G4" s="95" t="n">
-        <v>14.53</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H4" s="95" t="n">
         <v>8.710000000000001</v>
@@ -6784,61 +6784,61 @@
         <v>8.710000000000001</v>
       </c>
       <c r="M4" s="95" t="n">
-        <v>8.710000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="N4" s="95" t="n">
-        <v>8.710000000000001</v>
+        <v>-2.48</v>
       </c>
       <c r="O4" s="95" t="n">
-        <v>0.41</v>
+        <v>-4.76</v>
       </c>
       <c r="P4" s="95" t="n">
-        <v>0.41</v>
+        <v>-4.9</v>
       </c>
       <c r="Q4" s="95" t="n">
-        <v>-2.48</v>
+        <v>-8.16</v>
       </c>
       <c r="R4" s="95" t="n">
-        <v>-4.76</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="S4" s="95" t="n">
-        <v>-4.9</v>
+        <v>-9.59</v>
       </c>
       <c r="T4" s="95" t="n">
-        <v>-8.16</v>
+        <v>-10.85</v>
       </c>
       <c r="U4" s="95" t="n">
-        <v>-9.720000000000001</v>
+        <v>-12.12</v>
       </c>
       <c r="V4" s="95" t="n">
-        <v>-9.720000000000001</v>
+        <v>-12.12</v>
       </c>
       <c r="W4" s="95" t="n">
-        <v>-9.59</v>
+        <v>-12.12</v>
       </c>
       <c r="X4" s="95" t="n">
-        <v>-10.85</v>
+        <v>-11.77</v>
       </c>
       <c r="Y4" s="95" t="n">
-        <v>-12.12</v>
+        <v>-11.13</v>
       </c>
       <c r="Z4" s="95" t="n">
-        <v>-12.12</v>
+        <v>-11.05</v>
       </c>
       <c r="AA4" s="95" t="n">
-        <v>-12.12</v>
+        <v>-10.42</v>
       </c>
       <c r="AB4" s="95" t="n">
-        <v>-12.12</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="AC4" s="95" t="n">
-        <v>-11.77</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="AD4" s="95" t="n">
-        <v>-11.13</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="AE4" s="95" t="n">
-        <v>-11.05</v>
+        <v>-8.65</v>
       </c>
     </row>
     <row r="5">
@@ -6854,16 +6854,16 @@
         <v>44.67</v>
       </c>
       <c r="D5" s="95" t="n">
-        <v>44.67</v>
+        <v>59.48</v>
       </c>
       <c r="E5" s="95" t="n">
-        <v>59.48</v>
+        <v>54.31</v>
       </c>
       <c r="F5" s="95" t="n">
-        <v>54.31</v>
+        <v>99.84</v>
       </c>
       <c r="G5" s="95" t="n">
-        <v>99.84</v>
+        <v>99.75</v>
       </c>
       <c r="H5" s="95" t="n">
         <v>99.75</v>
@@ -6881,61 +6881,61 @@
         <v>99.75</v>
       </c>
       <c r="M5" s="95" t="n">
-        <v>99.75</v>
+        <v>99.31</v>
       </c>
       <c r="N5" s="95" t="n">
-        <v>99.75</v>
+        <v>98.83</v>
       </c>
       <c r="O5" s="95" t="n">
-        <v>99.31</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="P5" s="95" t="n">
-        <v>99.31</v>
+        <v>96.38</v>
       </c>
       <c r="Q5" s="95" t="n">
-        <v>98.83</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="R5" s="95" t="n">
-        <v>97.34999999999999</v>
+        <v>64.38</v>
       </c>
       <c r="S5" s="95" t="n">
-        <v>96.38</v>
+        <v>63.45</v>
       </c>
       <c r="T5" s="95" t="n">
-        <v>77.51000000000001</v>
+        <v>37.85</v>
       </c>
       <c r="U5" s="95" t="n">
-        <v>64.38</v>
+        <v>7.42</v>
       </c>
       <c r="V5" s="95" t="n">
-        <v>64.38</v>
+        <v>7.42</v>
       </c>
       <c r="W5" s="95" t="n">
-        <v>63.45</v>
+        <v>7.42</v>
       </c>
       <c r="X5" s="95" t="n">
-        <v>37.85</v>
+        <v>10.95</v>
       </c>
       <c r="Y5" s="95" t="n">
-        <v>7.42</v>
+        <v>12.36</v>
       </c>
       <c r="Z5" s="95" t="n">
-        <v>7.42</v>
+        <v>20.95</v>
       </c>
       <c r="AA5" s="95" t="n">
-        <v>7.42</v>
+        <v>5.95</v>
       </c>
       <c r="AB5" s="95" t="n">
-        <v>7.42</v>
+        <v>11.48</v>
       </c>
       <c r="AC5" s="95" t="n">
-        <v>10.95</v>
+        <v>21.9</v>
       </c>
       <c r="AD5" s="95" t="n">
-        <v>12.36</v>
+        <v>12.41</v>
       </c>
       <c r="AE5" s="95" t="n">
-        <v>20.95</v>
+        <v>19.88</v>
       </c>
     </row>
     <row r="6">
@@ -6959,79 +6959,79 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="E6" s="91" t="inlineStr">
+      <c r="E6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="G6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="H6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="I6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="S6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="T6" s="93" t="inlineStr">
@@ -7054,29 +7054,29 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="X6" s="93" t="inlineStr">
+      <c r="X6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Z6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="AB6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="AC6" s="91" t="inlineStr">
@@ -7108,16 +7108,16 @@
         <v>26.54</v>
       </c>
       <c r="D7" s="95" t="n">
-        <v>26.54</v>
+        <v>34.41</v>
       </c>
       <c r="E7" s="95" t="n">
-        <v>34.41</v>
+        <v>44.1</v>
       </c>
       <c r="F7" s="95" t="n">
-        <v>44.1</v>
+        <v>46.52</v>
       </c>
       <c r="G7" s="95" t="n">
-        <v>46.52</v>
+        <v>26.36</v>
       </c>
       <c r="H7" s="95" t="n">
         <v>26.36</v>
@@ -7135,61 +7135,61 @@
         <v>26.36</v>
       </c>
       <c r="M7" s="95" t="n">
-        <v>26.36</v>
+        <v>5.45</v>
       </c>
       <c r="N7" s="95" t="n">
-        <v>26.36</v>
+        <v>-0.85</v>
       </c>
       <c r="O7" s="95" t="n">
-        <v>5.45</v>
+        <v>-5.96</v>
       </c>
       <c r="P7" s="95" t="n">
-        <v>5.45</v>
+        <v>-6.32</v>
       </c>
       <c r="Q7" s="95" t="n">
-        <v>-0.85</v>
+        <v>-10.11</v>
       </c>
       <c r="R7" s="95" t="n">
-        <v>-5.96</v>
+        <v>-11.14</v>
       </c>
       <c r="S7" s="95" t="n">
-        <v>-6.32</v>
+        <v>-9.23</v>
       </c>
       <c r="T7" s="95" t="n">
-        <v>-10.11</v>
+        <v>-12.41</v>
       </c>
       <c r="U7" s="95" t="n">
-        <v>-11.14</v>
+        <v>-13.62</v>
       </c>
       <c r="V7" s="95" t="n">
-        <v>-11.14</v>
+        <v>-13.62</v>
       </c>
       <c r="W7" s="95" t="n">
-        <v>-9.23</v>
+        <v>-13.62</v>
       </c>
       <c r="X7" s="95" t="n">
-        <v>-12.41</v>
+        <v>-12.75</v>
       </c>
       <c r="Y7" s="95" t="n">
-        <v>-13.62</v>
+        <v>-11.62</v>
       </c>
       <c r="Z7" s="95" t="n">
-        <v>-13.62</v>
+        <v>-12.8</v>
       </c>
       <c r="AA7" s="95" t="n">
-        <v>-13.62</v>
+        <v>-13.49</v>
       </c>
       <c r="AB7" s="95" t="n">
-        <v>-13.62</v>
+        <v>-12.19</v>
       </c>
       <c r="AC7" s="95" t="n">
-        <v>-12.75</v>
+        <v>-11.56</v>
       </c>
       <c r="AD7" s="95" t="n">
-        <v>-11.62</v>
+        <v>-10.95</v>
       </c>
       <c r="AE7" s="95" t="n">
-        <v>-12.8</v>
+        <v>-10.7</v>
       </c>
     </row>
     <row r="8">
@@ -7205,16 +7205,16 @@
         <v>21.69</v>
       </c>
       <c r="D8" s="95" t="n">
-        <v>21.69</v>
+        <v>29.69</v>
       </c>
       <c r="E8" s="95" t="n">
-        <v>29.69</v>
+        <v>33.11</v>
       </c>
       <c r="F8" s="95" t="n">
-        <v>33.11</v>
+        <v>38.25</v>
       </c>
       <c r="G8" s="95" t="n">
-        <v>38.25</v>
+        <v>15.28</v>
       </c>
       <c r="H8" s="95" t="n">
         <v>15.28</v>
@@ -7232,61 +7232,61 @@
         <v>15.28</v>
       </c>
       <c r="M8" s="95" t="n">
-        <v>15.28</v>
+        <v>-3.74</v>
       </c>
       <c r="N8" s="95" t="n">
-        <v>15.28</v>
+        <v>-10.62</v>
       </c>
       <c r="O8" s="95" t="n">
-        <v>-3.74</v>
+        <v>-12.51</v>
       </c>
       <c r="P8" s="95" t="n">
-        <v>-3.74</v>
+        <v>-12.61</v>
       </c>
       <c r="Q8" s="95" t="n">
-        <v>-10.62</v>
+        <v>-14.58</v>
       </c>
       <c r="R8" s="95" t="n">
-        <v>-12.51</v>
+        <v>-16.03</v>
       </c>
       <c r="S8" s="95" t="n">
-        <v>-12.61</v>
+        <v>-16.65</v>
       </c>
       <c r="T8" s="95" t="n">
-        <v>-14.58</v>
+        <v>-18.48</v>
       </c>
       <c r="U8" s="95" t="n">
-        <v>-16.03</v>
+        <v>-18.74</v>
       </c>
       <c r="V8" s="95" t="n">
-        <v>-16.03</v>
+        <v>-18.74</v>
       </c>
       <c r="W8" s="95" t="n">
-        <v>-16.65</v>
+        <v>-18.74</v>
       </c>
       <c r="X8" s="95" t="n">
-        <v>-18.48</v>
+        <v>-19.06</v>
       </c>
       <c r="Y8" s="95" t="n">
-        <v>-18.74</v>
+        <v>-18.16</v>
       </c>
       <c r="Z8" s="95" t="n">
-        <v>-18.74</v>
+        <v>-20.04</v>
       </c>
       <c r="AA8" s="95" t="n">
-        <v>-18.74</v>
+        <v>-19.01</v>
       </c>
       <c r="AB8" s="95" t="n">
-        <v>-18.74</v>
+        <v>-17.71</v>
       </c>
       <c r="AC8" s="95" t="n">
-        <v>-19.06</v>
+        <v>-17.63</v>
       </c>
       <c r="AD8" s="95" t="n">
-        <v>-18.16</v>
+        <v>-17.79</v>
       </c>
       <c r="AE8" s="95" t="n">
-        <v>-20.04</v>
+        <v>-17.53</v>
       </c>
     </row>
     <row r="9">
@@ -7302,16 +7302,16 @@
         <v>59.18</v>
       </c>
       <c r="D9" s="95" t="n">
-        <v>59.18</v>
+        <v>74.52</v>
       </c>
       <c r="E9" s="95" t="n">
-        <v>74.52</v>
+        <v>89.13</v>
       </c>
       <c r="F9" s="95" t="n">
-        <v>89.13</v>
+        <v>98.36</v>
       </c>
       <c r="G9" s="95" t="n">
-        <v>98.36</v>
+        <v>96.84</v>
       </c>
       <c r="H9" s="95" t="n">
         <v>96.84</v>
@@ -7329,61 +7329,61 @@
         <v>96.84</v>
       </c>
       <c r="M9" s="95" t="n">
-        <v>96.84</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="N9" s="95" t="n">
-        <v>96.84</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="O9" s="95" t="n">
-        <v>91.06999999999999</v>
+        <v>64.94</v>
       </c>
       <c r="P9" s="95" t="n">
-        <v>91.06999999999999</v>
+        <v>64.66</v>
       </c>
       <c r="Q9" s="95" t="n">
-        <v>81.48999999999999</v>
+        <v>23.69</v>
       </c>
       <c r="R9" s="95" t="n">
-        <v>64.94</v>
+        <v>29.81</v>
       </c>
       <c r="S9" s="95" t="n">
-        <v>64.66</v>
+        <v>33.91</v>
       </c>
       <c r="T9" s="95" t="n">
-        <v>23.69</v>
+        <v>22.82</v>
       </c>
       <c r="U9" s="95" t="n">
-        <v>29.81</v>
+        <v>30.54</v>
       </c>
       <c r="V9" s="95" t="n">
-        <v>29.81</v>
+        <v>30.54</v>
       </c>
       <c r="W9" s="95" t="n">
-        <v>33.91</v>
+        <v>30.54</v>
       </c>
       <c r="X9" s="95" t="n">
-        <v>22.82</v>
+        <v>35.28</v>
       </c>
       <c r="Y9" s="95" t="n">
-        <v>30.54</v>
+        <v>42.99</v>
       </c>
       <c r="Z9" s="95" t="n">
-        <v>30.54</v>
+        <v>33.88</v>
       </c>
       <c r="AA9" s="95" t="n">
-        <v>30.54</v>
+        <v>22.22</v>
       </c>
       <c r="AB9" s="95" t="n">
-        <v>30.54</v>
+        <v>27.98</v>
       </c>
       <c r="AC9" s="95" t="n">
-        <v>35.28</v>
+        <v>37.32</v>
       </c>
       <c r="AD9" s="95" t="n">
-        <v>42.99</v>
+        <v>38.49</v>
       </c>
       <c r="AE9" s="95" t="n">
-        <v>33.88</v>
+        <v>41.22</v>
       </c>
     </row>
     <row r="10">
@@ -7407,139 +7407,139 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="E10" s="91" t="inlineStr">
+      <c r="E10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="S10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F10" s="92" t="inlineStr">
+      <c r="T10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="U10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="V10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="W10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="X10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G10" s="92" t="inlineStr">
+      <c r="Z10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="I10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="U10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="V10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="W10" s="91" t="inlineStr">
+      <c r="AD10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC10" s="91" t="inlineStr">
+      <c r="AE10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AD10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -7556,16 +7556,16 @@
         <v>27.24</v>
       </c>
       <c r="D11" s="95" t="n">
-        <v>27.24</v>
+        <v>33.94</v>
       </c>
       <c r="E11" s="95" t="n">
-        <v>33.94</v>
+        <v>39.99</v>
       </c>
       <c r="F11" s="95" t="n">
-        <v>39.99</v>
+        <v>54.04</v>
       </c>
       <c r="G11" s="95" t="n">
-        <v>54.04</v>
+        <v>32.05</v>
       </c>
       <c r="H11" s="95" t="n">
         <v>32.05</v>
@@ -7583,61 +7583,61 @@
         <v>32.05</v>
       </c>
       <c r="M11" s="95" t="n">
-        <v>32.05</v>
+        <v>13.58</v>
       </c>
       <c r="N11" s="95" t="n">
-        <v>32.05</v>
+        <v>2.95</v>
       </c>
       <c r="O11" s="95" t="n">
-        <v>13.58</v>
+        <v>-2.45</v>
       </c>
       <c r="P11" s="95" t="n">
-        <v>13.58</v>
+        <v>-4.05</v>
       </c>
       <c r="Q11" s="95" t="n">
-        <v>2.95</v>
+        <v>-10.14</v>
       </c>
       <c r="R11" s="95" t="n">
-        <v>-2.45</v>
+        <v>-11.21</v>
       </c>
       <c r="S11" s="95" t="n">
-        <v>-4.05</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="T11" s="95" t="n">
-        <v>-10.14</v>
+        <v>-11.44</v>
       </c>
       <c r="U11" s="95" t="n">
-        <v>-11.21</v>
+        <v>-12.57</v>
       </c>
       <c r="V11" s="95" t="n">
-        <v>-11.21</v>
+        <v>-12.57</v>
       </c>
       <c r="W11" s="95" t="n">
-        <v>-9.029999999999999</v>
+        <v>-12.57</v>
       </c>
       <c r="X11" s="95" t="n">
-        <v>-11.44</v>
+        <v>-11.96</v>
       </c>
       <c r="Y11" s="95" t="n">
-        <v>-12.57</v>
+        <v>-12.87</v>
       </c>
       <c r="Z11" s="95" t="n">
-        <v>-12.57</v>
+        <v>-14.98</v>
       </c>
       <c r="AA11" s="95" t="n">
-        <v>-12.57</v>
+        <v>-14.79</v>
       </c>
       <c r="AB11" s="95" t="n">
-        <v>-12.57</v>
+        <v>-14.14</v>
       </c>
       <c r="AC11" s="95" t="n">
-        <v>-11.96</v>
+        <v>-11.99</v>
       </c>
       <c r="AD11" s="95" t="n">
-        <v>-12.87</v>
+        <v>-12.63</v>
       </c>
       <c r="AE11" s="95" t="n">
-        <v>-14.98</v>
+        <v>-12.92</v>
       </c>
     </row>
     <row r="12">
@@ -7653,16 +7653,16 @@
         <v>17.89</v>
       </c>
       <c r="D12" s="95" t="n">
-        <v>17.89</v>
+        <v>23.63</v>
       </c>
       <c r="E12" s="95" t="n">
-        <v>23.63</v>
+        <v>24.76</v>
       </c>
       <c r="F12" s="95" t="n">
-        <v>24.76</v>
+        <v>41.13</v>
       </c>
       <c r="G12" s="95" t="n">
-        <v>41.13</v>
+        <v>18.19</v>
       </c>
       <c r="H12" s="95" t="n">
         <v>18.19</v>
@@ -7680,61 +7680,61 @@
         <v>18.19</v>
       </c>
       <c r="M12" s="95" t="n">
-        <v>18.19</v>
+        <v>1.34</v>
       </c>
       <c r="N12" s="95" t="n">
-        <v>18.19</v>
+        <v>-8.44</v>
       </c>
       <c r="O12" s="95" t="n">
-        <v>1.34</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="P12" s="95" t="n">
-        <v>1.34</v>
+        <v>-10.6</v>
       </c>
       <c r="Q12" s="95" t="n">
-        <v>-8.44</v>
+        <v>-14.49</v>
       </c>
       <c r="R12" s="95" t="n">
-        <v>-9.720000000000001</v>
+        <v>-16.56</v>
       </c>
       <c r="S12" s="95" t="n">
-        <v>-10.6</v>
+        <v>-15.65</v>
       </c>
       <c r="T12" s="95" t="n">
-        <v>-14.49</v>
+        <v>-17.96</v>
       </c>
       <c r="U12" s="95" t="n">
-        <v>-16.56</v>
+        <v>-19.08</v>
       </c>
       <c r="V12" s="95" t="n">
-        <v>-16.56</v>
+        <v>-19.08</v>
       </c>
       <c r="W12" s="95" t="n">
-        <v>-15.65</v>
+        <v>-19.08</v>
       </c>
       <c r="X12" s="95" t="n">
-        <v>-17.96</v>
+        <v>-18.72</v>
       </c>
       <c r="Y12" s="95" t="n">
-        <v>-19.08</v>
+        <v>-18.28</v>
       </c>
       <c r="Z12" s="95" t="n">
-        <v>-19.08</v>
+        <v>-20.06</v>
       </c>
       <c r="AA12" s="95" t="n">
-        <v>-19.08</v>
+        <v>-18.31</v>
       </c>
       <c r="AB12" s="95" t="n">
-        <v>-19.08</v>
+        <v>-18.32</v>
       </c>
       <c r="AC12" s="95" t="n">
-        <v>-18.72</v>
+        <v>-17.44</v>
       </c>
       <c r="AD12" s="95" t="n">
-        <v>-18.28</v>
+        <v>-18.44</v>
       </c>
       <c r="AE12" s="95" t="n">
-        <v>-20.06</v>
+        <v>-17.67</v>
       </c>
     </row>
     <row r="13">
@@ -7750,16 +7750,16 @@
         <v>42.18</v>
       </c>
       <c r="D13" s="95" t="n">
-        <v>42.18</v>
+        <v>55.03</v>
       </c>
       <c r="E13" s="95" t="n">
-        <v>55.03</v>
+        <v>62.67</v>
       </c>
       <c r="F13" s="95" t="n">
-        <v>62.67</v>
+        <v>99.77</v>
       </c>
       <c r="G13" s="95" t="n">
-        <v>99.77</v>
+        <v>99.48</v>
       </c>
       <c r="H13" s="95" t="n">
         <v>99.48</v>
@@ -7777,61 +7777,61 @@
         <v>99.48</v>
       </c>
       <c r="M13" s="95" t="n">
-        <v>99.48</v>
+        <v>98.62</v>
       </c>
       <c r="N13" s="95" t="n">
-        <v>99.48</v>
+        <v>96</v>
       </c>
       <c r="O13" s="95" t="n">
-        <v>98.62</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="P13" s="95" t="n">
-        <v>98.62</v>
+        <v>88.09</v>
       </c>
       <c r="Q13" s="95" t="n">
-        <v>96</v>
+        <v>30.34</v>
       </c>
       <c r="R13" s="95" t="n">
-        <v>91.40000000000001</v>
+        <v>39.51</v>
       </c>
       <c r="S13" s="95" t="n">
-        <v>88.09</v>
+        <v>58.67</v>
       </c>
       <c r="T13" s="95" t="n">
-        <v>30.34</v>
+        <v>28.04</v>
       </c>
       <c r="U13" s="95" t="n">
-        <v>39.51</v>
+        <v>29.98</v>
       </c>
       <c r="V13" s="95" t="n">
-        <v>39.51</v>
+        <v>29.98</v>
       </c>
       <c r="W13" s="95" t="n">
-        <v>58.67</v>
+        <v>29.98</v>
       </c>
       <c r="X13" s="95" t="n">
-        <v>28.04</v>
+        <v>54.57</v>
       </c>
       <c r="Y13" s="95" t="n">
-        <v>29.98</v>
+        <v>69.45</v>
       </c>
       <c r="Z13" s="95" t="n">
-        <v>29.98</v>
+        <v>37.43</v>
       </c>
       <c r="AA13" s="95" t="n">
-        <v>29.98</v>
+        <v>35.11</v>
       </c>
       <c r="AB13" s="95" t="n">
-        <v>29.98</v>
+        <v>33.41</v>
       </c>
       <c r="AC13" s="95" t="n">
-        <v>54.57</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="AD13" s="95" t="n">
-        <v>69.45</v>
+        <v>53.41</v>
       </c>
       <c r="AE13" s="95" t="n">
-        <v>37.43</v>
+        <v>55.28</v>
       </c>
     </row>
     <row r="14">
@@ -7855,139 +7855,139 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="E14" s="91" t="inlineStr">
+      <c r="E14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F14" s="93" t="inlineStr">
+      <c r="G14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G14" s="91" t="inlineStr">
+      <c r="Z14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="H14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="I14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD14" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE14" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -8007,85 +8007,85 @@
         <v>17.96</v>
       </c>
       <c r="E15" s="95" t="n">
-        <v>17.96</v>
+        <v>12.81</v>
       </c>
       <c r="F15" s="95" t="n">
-        <v>12.81</v>
+        <v>17.35</v>
       </c>
       <c r="G15" s="95" t="n">
-        <v>17.35</v>
+        <v>32.21</v>
       </c>
       <c r="H15" s="95" t="n">
-        <v>32.21</v>
+        <v>29.75</v>
       </c>
       <c r="I15" s="95" t="n">
-        <v>29.75</v>
+        <v>26.19</v>
       </c>
       <c r="J15" s="95" t="n">
-        <v>29.75</v>
+        <v>26.09</v>
       </c>
       <c r="K15" s="95" t="n">
-        <v>26.19</v>
+        <v>17.23</v>
       </c>
       <c r="L15" s="95" t="n">
-        <v>26.09</v>
+        <v>17.23</v>
       </c>
       <c r="M15" s="95" t="n">
-        <v>17.23</v>
+        <v>14.76</v>
       </c>
       <c r="N15" s="95" t="n">
-        <v>17.23</v>
+        <v>12.13</v>
       </c>
       <c r="O15" s="95" t="n">
-        <v>14.76</v>
+        <v>7.96</v>
       </c>
       <c r="P15" s="95" t="n">
-        <v>14.76</v>
+        <v>7.25</v>
       </c>
       <c r="Q15" s="95" t="n">
-        <v>12.13</v>
+        <v>0.87</v>
       </c>
       <c r="R15" s="95" t="n">
-        <v>7.96</v>
+        <v>1.03</v>
       </c>
       <c r="S15" s="95" t="n">
-        <v>7.25</v>
+        <v>-0.08</v>
       </c>
       <c r="T15" s="95" t="n">
-        <v>0.87</v>
+        <v>-2.04</v>
       </c>
       <c r="U15" s="95" t="n">
-        <v>1.03</v>
+        <v>-2.04</v>
       </c>
       <c r="V15" s="95" t="n">
-        <v>1.03</v>
+        <v>-4.98</v>
       </c>
       <c r="W15" s="95" t="n">
-        <v>-0.08</v>
+        <v>-5.76</v>
       </c>
       <c r="X15" s="95" t="n">
-        <v>-2.04</v>
+        <v>-3.77</v>
       </c>
       <c r="Y15" s="95" t="n">
-        <v>-2.04</v>
+        <v>-4.61</v>
       </c>
       <c r="Z15" s="95" t="n">
-        <v>-4.98</v>
+        <v>-3.94</v>
       </c>
       <c r="AA15" s="95" t="n">
-        <v>-5.76</v>
+        <v>-5.06</v>
       </c>
       <c r="AB15" s="95" t="n">
-        <v>-5.76</v>
+        <v>-2.75</v>
       </c>
       <c r="AC15" s="95" t="n">
-        <v>-3.77</v>
+        <v>-2.75</v>
       </c>
       <c r="AD15" s="95" t="n">
-        <v>-4.61</v>
+        <v>-3.96</v>
       </c>
       <c r="AE15" s="95" t="n">
-        <v>-3.94</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="16">
@@ -8104,85 +8104,85 @@
         <v>30.79</v>
       </c>
       <c r="E16" s="95" t="n">
-        <v>30.79</v>
+        <v>24.32</v>
       </c>
       <c r="F16" s="95" t="n">
-        <v>24.32</v>
+        <v>25.15</v>
       </c>
       <c r="G16" s="95" t="n">
-        <v>25.15</v>
+        <v>35.13</v>
       </c>
       <c r="H16" s="95" t="n">
-        <v>35.13</v>
+        <v>32.66</v>
       </c>
       <c r="I16" s="95" t="n">
-        <v>32.66</v>
+        <v>31.41</v>
       </c>
       <c r="J16" s="95" t="n">
-        <v>32.66</v>
+        <v>34.13</v>
       </c>
       <c r="K16" s="95" t="n">
-        <v>31.41</v>
+        <v>26.37</v>
       </c>
       <c r="L16" s="95" t="n">
-        <v>34.13</v>
+        <v>26.37</v>
       </c>
       <c r="M16" s="95" t="n">
-        <v>26.37</v>
+        <v>23.36</v>
       </c>
       <c r="N16" s="95" t="n">
-        <v>26.37</v>
+        <v>17.68</v>
       </c>
       <c r="O16" s="95" t="n">
-        <v>23.36</v>
+        <v>15.64</v>
       </c>
       <c r="P16" s="95" t="n">
-        <v>23.36</v>
+        <v>15.91</v>
       </c>
       <c r="Q16" s="95" t="n">
-        <v>17.68</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R16" s="95" t="n">
-        <v>15.64</v>
+        <v>10.84</v>
       </c>
       <c r="S16" s="95" t="n">
-        <v>15.91</v>
+        <v>9.17</v>
       </c>
       <c r="T16" s="95" t="n">
-        <v>9.800000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="U16" s="95" t="n">
-        <v>10.84</v>
+        <v>4.73</v>
       </c>
       <c r="V16" s="95" t="n">
-        <v>10.84</v>
+        <v>5.31</v>
       </c>
       <c r="W16" s="95" t="n">
-        <v>9.17</v>
+        <v>5.08</v>
       </c>
       <c r="X16" s="95" t="n">
-        <v>4.73</v>
+        <v>3.01</v>
       </c>
       <c r="Y16" s="95" t="n">
-        <v>4.73</v>
+        <v>2.32</v>
       </c>
       <c r="Z16" s="95" t="n">
-        <v>5.31</v>
+        <v>1.61</v>
       </c>
       <c r="AA16" s="95" t="n">
-        <v>5.08</v>
+        <v>0.67</v>
       </c>
       <c r="AB16" s="95" t="n">
-        <v>5.08</v>
+        <v>2.05</v>
       </c>
       <c r="AC16" s="95" t="n">
-        <v>3.01</v>
+        <v>2.05</v>
       </c>
       <c r="AD16" s="95" t="n">
-        <v>2.32</v>
+        <v>5.24</v>
       </c>
       <c r="AE16" s="95" t="n">
-        <v>1.61</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="17">
@@ -8201,85 +8201,85 @@
         <v>48.87</v>
       </c>
       <c r="E17" s="95" t="n">
-        <v>48.87</v>
+        <v>35.54</v>
       </c>
       <c r="F17" s="95" t="n">
-        <v>35.54</v>
+        <v>39.14</v>
       </c>
       <c r="G17" s="95" t="n">
-        <v>39.14</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="H17" s="95" t="n">
-        <v>91.23999999999999</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="I17" s="95" t="n">
-        <v>89.48999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="J17" s="95" t="n">
-        <v>89.48999999999999</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="K17" s="95" t="n">
-        <v>85.84</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="L17" s="95" t="n">
-        <v>99.56999999999999</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="M17" s="95" t="n">
-        <v>99.18000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="N17" s="95" t="n">
-        <v>99.18000000000001</v>
+        <v>98.23</v>
       </c>
       <c r="O17" s="95" t="n">
-        <v>98.89</v>
+        <v>96.44</v>
       </c>
       <c r="P17" s="95" t="n">
-        <v>98.89</v>
+        <v>95.94</v>
       </c>
       <c r="Q17" s="95" t="n">
-        <v>98.23</v>
+        <v>89.48</v>
       </c>
       <c r="R17" s="95" t="n">
-        <v>96.44</v>
+        <v>91.13</v>
       </c>
       <c r="S17" s="95" t="n">
-        <v>95.94</v>
+        <v>87.39</v>
       </c>
       <c r="T17" s="95" t="n">
-        <v>89.48</v>
+        <v>76.86</v>
       </c>
       <c r="U17" s="95" t="n">
-        <v>91.13</v>
+        <v>76.86</v>
       </c>
       <c r="V17" s="95" t="n">
-        <v>91.13</v>
+        <v>59.96</v>
       </c>
       <c r="W17" s="95" t="n">
-        <v>87.39</v>
+        <v>54.39</v>
       </c>
       <c r="X17" s="95" t="n">
-        <v>76.86</v>
+        <v>38.93</v>
       </c>
       <c r="Y17" s="95" t="n">
-        <v>76.86</v>
+        <v>17.46</v>
       </c>
       <c r="Z17" s="95" t="n">
-        <v>59.96</v>
+        <v>23.32</v>
       </c>
       <c r="AA17" s="95" t="n">
-        <v>54.39</v>
+        <v>17.15</v>
       </c>
       <c r="AB17" s="95" t="n">
-        <v>54.39</v>
+        <v>28.67</v>
       </c>
       <c r="AC17" s="95" t="n">
-        <v>38.93</v>
+        <v>28.67</v>
       </c>
       <c r="AD17" s="95" t="n">
-        <v>17.46</v>
+        <v>29.45</v>
       </c>
       <c r="AE17" s="95" t="n">
-        <v>23.32</v>
+        <v>42.37</v>
       </c>
     </row>
     <row r="18">
@@ -8313,129 +8313,129 @@
           <t>red</t>
         </is>
       </c>
-      <c r="G18" s="92" t="inlineStr">
+      <c r="G18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H18" s="93" t="inlineStr">
+      <c r="I18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="L18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="M18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="AB18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -8446,94 +8446,94 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>4.88</v>
+        <v>6.45</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>4.88</v>
       </c>
       <c r="D19" s="95" t="n">
-        <v>4.88</v>
+        <v>3.43</v>
       </c>
       <c r="E19" s="95" t="n">
-        <v>3.43</v>
+        <v>2.2</v>
       </c>
       <c r="F19" s="95" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="G19" s="95" t="n">
-        <v>2.13</v>
+        <v>1.44</v>
       </c>
       <c r="H19" s="95" t="n">
-        <v>1.44</v>
+        <v>2.98</v>
       </c>
       <c r="I19" s="95" t="n">
-        <v>2.98</v>
+        <v>1.17</v>
       </c>
       <c r="J19" s="95" t="n">
-        <v>2.98</v>
+        <v>2.38</v>
       </c>
       <c r="K19" s="95" t="n">
-        <v>1.17</v>
+        <v>2.44</v>
       </c>
       <c r="L19" s="95" t="n">
-        <v>2.38</v>
+        <v>3.51</v>
       </c>
       <c r="M19" s="95" t="n">
-        <v>2.44</v>
+        <v>3.63</v>
       </c>
       <c r="N19" s="95" t="n">
-        <v>3.51</v>
+        <v>4.29</v>
       </c>
       <c r="O19" s="95" t="n">
-        <v>3.63</v>
+        <v>4.51</v>
       </c>
       <c r="P19" s="95" t="n">
-        <v>3.63</v>
+        <v>4.99</v>
       </c>
       <c r="Q19" s="95" t="n">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="R19" s="95" t="n">
-        <v>4.51</v>
+        <v>4.1</v>
       </c>
       <c r="S19" s="95" t="n">
-        <v>4.99</v>
+        <v>4.47</v>
       </c>
       <c r="T19" s="95" t="n">
-        <v>4.3</v>
+        <v>3.13</v>
       </c>
       <c r="U19" s="95" t="n">
-        <v>4.1</v>
+        <v>3.11</v>
       </c>
       <c r="V19" s="95" t="n">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="W19" s="95" t="n">
-        <v>4.47</v>
+        <v>2.53</v>
       </c>
       <c r="X19" s="95" t="n">
-        <v>3.13</v>
+        <v>2.24</v>
       </c>
       <c r="Y19" s="95" t="n">
-        <v>3.11</v>
+        <v>2.26</v>
       </c>
       <c r="Z19" s="95" t="n">
-        <v>2.92</v>
+        <v>1.14</v>
       </c>
       <c r="AA19" s="95" t="n">
-        <v>2.53</v>
+        <v>0.92</v>
       </c>
       <c r="AB19" s="95" t="n">
-        <v>2.53</v>
+        <v>0.62</v>
       </c>
       <c r="AC19" s="95" t="n">
-        <v>2.24</v>
+        <v>2.66</v>
       </c>
       <c r="AD19" s="95" t="n">
-        <v>2.26</v>
+        <v>3.24</v>
       </c>
       <c r="AE19" s="95" t="n">
-        <v>1.14</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="20">
@@ -8543,191 +8543,191 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>16.05</v>
+        <v>15.57</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>16.05</v>
       </c>
       <c r="D20" s="95" t="n">
-        <v>16.05</v>
+        <v>16.36</v>
       </c>
       <c r="E20" s="95" t="n">
-        <v>16.36</v>
+        <v>15.58</v>
       </c>
       <c r="F20" s="95" t="n">
-        <v>15.58</v>
+        <v>14.51</v>
       </c>
       <c r="G20" s="95" t="n">
-        <v>14.51</v>
+        <v>12.76</v>
       </c>
       <c r="H20" s="95" t="n">
-        <v>12.76</v>
+        <v>13.62</v>
       </c>
       <c r="I20" s="95" t="n">
-        <v>13.62</v>
+        <v>11.25</v>
       </c>
       <c r="J20" s="95" t="n">
-        <v>13.62</v>
+        <v>9.82</v>
       </c>
       <c r="K20" s="95" t="n">
-        <v>11.25</v>
+        <v>10.62</v>
       </c>
       <c r="L20" s="95" t="n">
-        <v>9.82</v>
+        <v>10.61</v>
       </c>
       <c r="M20" s="95" t="n">
-        <v>10.62</v>
+        <v>10.3</v>
       </c>
       <c r="N20" s="95" t="n">
-        <v>10.61</v>
+        <v>10.4</v>
       </c>
       <c r="O20" s="95" t="n">
-        <v>10.3</v>
+        <v>11.17</v>
       </c>
       <c r="P20" s="95" t="n">
-        <v>10.3</v>
+        <v>10.01</v>
       </c>
       <c r="Q20" s="95" t="n">
-        <v>10.4</v>
+        <v>9.85</v>
       </c>
       <c r="R20" s="95" t="n">
-        <v>11.17</v>
+        <v>8.75</v>
       </c>
       <c r="S20" s="95" t="n">
-        <v>10.01</v>
+        <v>8.74</v>
       </c>
       <c r="T20" s="95" t="n">
-        <v>9.85</v>
+        <v>7.05</v>
       </c>
       <c r="U20" s="95" t="n">
-        <v>8.75</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="V20" s="95" t="n">
-        <v>8.75</v>
+        <v>7.95</v>
       </c>
       <c r="W20" s="95" t="n">
-        <v>8.74</v>
+        <v>7.49</v>
       </c>
       <c r="X20" s="95" t="n">
-        <v>7.05</v>
+        <v>6.76</v>
       </c>
       <c r="Y20" s="95" t="n">
-        <v>8.279999999999999</v>
+        <v>6.31</v>
       </c>
       <c r="Z20" s="95" t="n">
-        <v>7.95</v>
+        <v>6.12</v>
       </c>
       <c r="AA20" s="95" t="n">
-        <v>7.49</v>
+        <v>6.25</v>
       </c>
       <c r="AB20" s="95" t="n">
-        <v>7.49</v>
+        <v>5.69</v>
       </c>
       <c r="AC20" s="95" t="n">
-        <v>6.76</v>
+        <v>6.85</v>
       </c>
       <c r="AD20" s="95" t="n">
-        <v>6.31</v>
+        <v>6.87</v>
       </c>
       <c r="AE20" s="95" t="n">
-        <v>6.12</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="94" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>84.56999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>84.56999999999999</v>
       </c>
       <c r="D21" s="95" t="n">
-        <v>84.56999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="E21" s="95" t="n">
-        <v>65.7</v>
+        <v>83.12</v>
       </c>
       <c r="F21" s="95" t="n">
-        <v>83.12</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="G21" s="95" t="n">
-        <v>69.18000000000001</v>
+        <v>30.41</v>
       </c>
       <c r="H21" s="95" t="n">
-        <v>30.41</v>
+        <v>81.84</v>
       </c>
       <c r="I21" s="95" t="n">
-        <v>81.84</v>
+        <v>15.76</v>
       </c>
       <c r="J21" s="95" t="n">
-        <v>81.84</v>
+        <v>23.93</v>
       </c>
       <c r="K21" s="95" t="n">
-        <v>15.76</v>
+        <v>22.27</v>
       </c>
       <c r="L21" s="95" t="n">
-        <v>23.93</v>
+        <v>86.19</v>
       </c>
       <c r="M21" s="95" t="n">
-        <v>22.27</v>
+        <v>60.63</v>
       </c>
       <c r="N21" s="95" t="n">
-        <v>86.19</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="O21" s="95" t="n">
-        <v>60.63</v>
+        <v>58.19</v>
       </c>
       <c r="P21" s="95" t="n">
-        <v>60.63</v>
+        <v>90.16</v>
       </c>
       <c r="Q21" s="95" t="n">
-        <v>83.51000000000001</v>
+        <v>84.39</v>
       </c>
       <c r="R21" s="95" t="n">
-        <v>58.19</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="S21" s="95" t="n">
-        <v>90.16</v>
+        <v>92.34</v>
       </c>
       <c r="T21" s="95" t="n">
-        <v>84.39</v>
+        <v>40.89</v>
       </c>
       <c r="U21" s="95" t="n">
-        <v>76.79000000000001</v>
+        <v>96.09</v>
       </c>
       <c r="V21" s="95" t="n">
-        <v>76.79000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="W21" s="95" t="n">
-        <v>92.34</v>
+        <v>95.06</v>
       </c>
       <c r="X21" s="95" t="n">
-        <v>40.89</v>
+        <v>91.83</v>
       </c>
       <c r="Y21" s="95" t="n">
-        <v>96.09</v>
+        <v>85.17</v>
       </c>
       <c r="Z21" s="95" t="n">
-        <v>95.83</v>
+        <v>65.2</v>
       </c>
       <c r="AA21" s="95" t="n">
-        <v>95.06</v>
+        <v>51.58</v>
       </c>
       <c r="AB21" s="95" t="n">
-        <v>95.06</v>
+        <v>3</v>
       </c>
       <c r="AC21" s="95" t="n">
-        <v>91.83</v>
+        <v>12.54</v>
       </c>
       <c r="AD21" s="95" t="n">
-        <v>85.17</v>
+        <v>17.38</v>
       </c>
       <c r="AE21" s="95" t="n">
-        <v>65.2</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="22">
@@ -8756,134 +8756,134 @@
           <t>red</t>
         </is>
       </c>
-      <c r="F22" s="92" t="inlineStr">
+      <c r="F22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G22" s="91" t="inlineStr">
+      <c r="I22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H22" s="93" t="inlineStr">
+      <c r="J22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K22" s="91" t="inlineStr">
+      <c r="AA22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L22" s="91" t="inlineStr">
+      <c r="AB22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M22" s="91" t="inlineStr">
+      <c r="AE22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="N22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE22" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -8894,94 +8894,94 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>5.41</v>
+        <v>6.89</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>5.41</v>
       </c>
       <c r="D23" s="95" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E23" s="95" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F23" s="95" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="G23" s="95" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="H23" s="95" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="I23" s="95" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="J23" s="95" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="K23" s="95" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="L23" s="95" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M23" s="95" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="N23" s="95" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="O23" s="95" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="P23" s="95" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q23" s="95" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="R23" s="95" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="S23" s="95" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="T23" s="95" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="U23" s="95" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="V23" s="95" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="W23" s="95" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="X23" s="95" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="Y23" s="95" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="Z23" s="95" t="n">
         <v>5.41</v>
       </c>
-      <c r="E23" s="95" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="F23" s="95" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G23" s="95" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="H23" s="95" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="I23" s="95" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="J23" s="95" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="K23" s="95" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="L23" s="95" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="M23" s="95" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="N23" s="95" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O23" s="95" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="P23" s="95" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="Q23" s="95" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="R23" s="95" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="S23" s="95" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="T23" s="95" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="U23" s="95" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="V23" s="95" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W23" s="95" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="X23" s="95" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="Y23" s="95" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="Z23" s="95" t="n">
-        <v>6.36</v>
-      </c>
       <c r="AA23" s="95" t="n">
-        <v>6.59</v>
+        <v>5.47</v>
       </c>
       <c r="AB23" s="95" t="n">
-        <v>6.59</v>
+        <v>4.12</v>
       </c>
       <c r="AC23" s="95" t="n">
-        <v>5.98</v>
+        <v>4.86</v>
       </c>
       <c r="AD23" s="95" t="n">
-        <v>5.89</v>
+        <v>5.61</v>
       </c>
       <c r="AE23" s="95" t="n">
-        <v>5.41</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="24">
@@ -8991,191 +8991,191 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>12.09</v>
+        <v>11.85</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>12.09</v>
       </c>
       <c r="D24" s="95" t="n">
-        <v>12.09</v>
+        <v>11.76</v>
       </c>
       <c r="E24" s="95" t="n">
-        <v>11.76</v>
+        <v>12.54</v>
       </c>
       <c r="F24" s="95" t="n">
-        <v>12.54</v>
+        <v>11.46</v>
       </c>
       <c r="G24" s="95" t="n">
-        <v>11.46</v>
+        <v>10.99</v>
       </c>
       <c r="H24" s="95" t="n">
-        <v>10.99</v>
+        <v>12.24</v>
       </c>
       <c r="I24" s="95" t="n">
-        <v>12.24</v>
+        <v>10.61</v>
       </c>
       <c r="J24" s="95" t="n">
-        <v>12.24</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K24" s="95" t="n">
-        <v>10.61</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="L24" s="95" t="n">
-        <v>9.720000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="M24" s="95" t="n">
-        <v>9.609999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="N24" s="95" t="n">
-        <v>8.859999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="O24" s="95" t="n">
-        <v>8.789999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="P24" s="95" t="n">
-        <v>8.789999999999999</v>
+        <v>7.87</v>
       </c>
       <c r="Q24" s="95" t="n">
-        <v>8.41</v>
+        <v>7.54</v>
       </c>
       <c r="R24" s="95" t="n">
-        <v>8.6</v>
+        <v>6.31</v>
       </c>
       <c r="S24" s="95" t="n">
-        <v>7.87</v>
+        <v>5.57</v>
       </c>
       <c r="T24" s="95" t="n">
-        <v>7.54</v>
+        <v>4.38</v>
       </c>
       <c r="U24" s="95" t="n">
-        <v>6.31</v>
+        <v>5.92</v>
       </c>
       <c r="V24" s="95" t="n">
-        <v>6.31</v>
+        <v>5.87</v>
       </c>
       <c r="W24" s="95" t="n">
-        <v>5.57</v>
+        <v>4.86</v>
       </c>
       <c r="X24" s="95" t="n">
-        <v>4.38</v>
+        <v>3.31</v>
       </c>
       <c r="Y24" s="95" t="n">
-        <v>5.92</v>
+        <v>3.42</v>
       </c>
       <c r="Z24" s="95" t="n">
-        <v>5.87</v>
+        <v>4.16</v>
       </c>
       <c r="AA24" s="95" t="n">
-        <v>4.86</v>
+        <v>5.26</v>
       </c>
       <c r="AB24" s="95" t="n">
-        <v>4.86</v>
+        <v>4.21</v>
       </c>
       <c r="AC24" s="95" t="n">
-        <v>3.31</v>
+        <v>4.76</v>
       </c>
       <c r="AD24" s="95" t="n">
-        <v>3.42</v>
+        <v>4.95</v>
       </c>
       <c r="AE24" s="95" t="n">
-        <v>4.16</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="76" t="inlineStr">
+      <c r="A25" s="94" t="inlineStr">
         <is>
           <t>us30:RS3</t>
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>82.94</v>
+        <v>87.47</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>82.94</v>
       </c>
       <c r="D25" s="95" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="E25" s="95" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="F25" s="95" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="G25" s="95" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="H25" s="95" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="I25" s="95" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="J25" s="95" t="n">
+        <v>52.09</v>
+      </c>
+      <c r="K25" s="95" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="L25" s="95" t="n">
+        <v>76.02</v>
+      </c>
+      <c r="M25" s="95" t="n">
+        <v>74.91</v>
+      </c>
+      <c r="N25" s="95" t="n">
+        <v>66.62</v>
+      </c>
+      <c r="O25" s="95" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="P25" s="95" t="n">
+        <v>92.18000000000001</v>
+      </c>
+      <c r="Q25" s="95" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="R25" s="95" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="S25" s="95" t="n">
+        <v>87.58</v>
+      </c>
+      <c r="T25" s="95" t="n">
+        <v>65.31</v>
+      </c>
+      <c r="U25" s="95" t="n">
+        <v>85.48999999999999</v>
+      </c>
+      <c r="V25" s="95" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="W25" s="95" t="n">
         <v>82.94</v>
       </c>
-      <c r="E25" s="95" t="n">
-        <v>66.56</v>
-      </c>
-      <c r="F25" s="95" t="n">
-        <v>73.18000000000001</v>
-      </c>
-      <c r="G25" s="95" t="n">
-        <v>46.98</v>
-      </c>
-      <c r="H25" s="95" t="n">
-        <v>34.52</v>
-      </c>
-      <c r="I25" s="95" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="J25" s="95" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="K25" s="95" t="n">
-        <v>28.19</v>
-      </c>
-      <c r="L25" s="95" t="n">
-        <v>52.09</v>
-      </c>
-      <c r="M25" s="95" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="N25" s="95" t="n">
-        <v>76.02</v>
-      </c>
-      <c r="O25" s="95" t="n">
-        <v>74.91</v>
-      </c>
-      <c r="P25" s="95" t="n">
-        <v>74.91</v>
-      </c>
-      <c r="Q25" s="95" t="n">
-        <v>66.62</v>
-      </c>
-      <c r="R25" s="95" t="n">
-        <v>42.84</v>
-      </c>
-      <c r="S25" s="95" t="n">
-        <v>92.18000000000001</v>
-      </c>
-      <c r="T25" s="95" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="U25" s="95" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="V25" s="95" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="W25" s="95" t="n">
-        <v>87.58</v>
-      </c>
       <c r="X25" s="95" t="n">
-        <v>65.31</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="Y25" s="95" t="n">
-        <v>85.48999999999999</v>
+        <v>56.57</v>
       </c>
       <c r="Z25" s="95" t="n">
-        <v>88.3</v>
+        <v>46.45</v>
       </c>
       <c r="AA25" s="95" t="n">
-        <v>82.94</v>
+        <v>52.5</v>
       </c>
       <c r="AB25" s="95" t="n">
-        <v>82.94</v>
+        <v>13.02</v>
       </c>
       <c r="AC25" s="95" t="n">
-        <v>71.68000000000001</v>
+        <v>24.55</v>
       </c>
       <c r="AD25" s="95" t="n">
-        <v>56.57</v>
+        <v>35.87</v>
       </c>
       <c r="AE25" s="95" t="n">
-        <v>46.45</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="26">
@@ -9209,129 +9209,129 @@
           <t>red</t>
         </is>
       </c>
-      <c r="G26" s="92" t="inlineStr">
+      <c r="G26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H26" s="93" t="inlineStr">
+      <c r="I26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="L26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="M26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="AB26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -9342,94 +9342,94 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>2.64</v>
+        <v>4.38</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>2.64</v>
       </c>
       <c r="D27" s="95" t="n">
-        <v>2.64</v>
+        <v>1.58</v>
       </c>
       <c r="E27" s="95" t="n">
-        <v>1.58</v>
+        <v>-1.18</v>
       </c>
       <c r="F27" s="95" t="n">
-        <v>-1.18</v>
+        <v>-1.57</v>
       </c>
       <c r="G27" s="95" t="n">
-        <v>-1.57</v>
+        <v>-2.58</v>
       </c>
       <c r="H27" s="95" t="n">
-        <v>-2.58</v>
+        <v>-0.8</v>
       </c>
       <c r="I27" s="95" t="n">
-        <v>-0.8</v>
+        <v>-3.91</v>
       </c>
       <c r="J27" s="95" t="n">
-        <v>-0.8</v>
+        <v>-2.74</v>
       </c>
       <c r="K27" s="95" t="n">
-        <v>-3.91</v>
+        <v>-2.68</v>
       </c>
       <c r="L27" s="95" t="n">
-        <v>-2.74</v>
+        <v>-0.89</v>
       </c>
       <c r="M27" s="95" t="n">
-        <v>-2.68</v>
+        <v>-0.38</v>
       </c>
       <c r="N27" s="95" t="n">
-        <v>-0.89</v>
+        <v>0.9</v>
       </c>
       <c r="O27" s="95" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P27" s="95" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q27" s="95" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R27" s="95" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S27" s="95" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="T27" s="95" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="U27" s="95" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="V27" s="95" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="W27" s="95" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X27" s="95" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="Y27" s="95" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="Z27" s="95" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="AA27" s="95" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="AB27" s="95" t="n">
+        <v>-3.76</v>
+      </c>
+      <c r="AC27" s="95" t="n">
         <v>-0.38</v>
       </c>
-      <c r="P27" s="95" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="Q27" s="95" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="R27" s="95" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S27" s="95" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="T27" s="95" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="U27" s="95" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="V27" s="95" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W27" s="95" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X27" s="95" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="Y27" s="95" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="Z27" s="95" t="n">
-        <v>-0.73</v>
-      </c>
-      <c r="AA27" s="95" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AB27" s="95" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC27" s="95" t="n">
-        <v>-1.61</v>
-      </c>
       <c r="AD27" s="95" t="n">
-        <v>-1.66</v>
+        <v>-0.28</v>
       </c>
       <c r="AE27" s="95" t="n">
-        <v>-3.63</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="28">
@@ -9439,94 +9439,94 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>18.71</v>
+        <v>17.88</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>18.71</v>
       </c>
       <c r="D28" s="95" t="n">
-        <v>18.71</v>
+        <v>19.63</v>
       </c>
       <c r="E28" s="95" t="n">
-        <v>19.63</v>
+        <v>17.24</v>
       </c>
       <c r="F28" s="95" t="n">
-        <v>17.24</v>
+        <v>15.94</v>
       </c>
       <c r="G28" s="95" t="n">
-        <v>15.94</v>
+        <v>12.98</v>
       </c>
       <c r="H28" s="95" t="n">
-        <v>12.98</v>
+        <v>14.18</v>
       </c>
       <c r="I28" s="95" t="n">
-        <v>14.18</v>
+        <v>10.78</v>
       </c>
       <c r="J28" s="95" t="n">
-        <v>14.18</v>
+        <v>9.02</v>
       </c>
       <c r="K28" s="95" t="n">
-        <v>10.78</v>
+        <v>10.76</v>
       </c>
       <c r="L28" s="95" t="n">
-        <v>9.02</v>
+        <v>11.54</v>
       </c>
       <c r="M28" s="95" t="n">
-        <v>10.76</v>
+        <v>11.48</v>
       </c>
       <c r="N28" s="95" t="n">
-        <v>11.54</v>
+        <v>11.95</v>
       </c>
       <c r="O28" s="95" t="n">
-        <v>11.48</v>
+        <v>12.67</v>
       </c>
       <c r="P28" s="95" t="n">
-        <v>11.48</v>
+        <v>11.04</v>
       </c>
       <c r="Q28" s="95" t="n">
-        <v>11.95</v>
+        <v>10.68</v>
       </c>
       <c r="R28" s="95" t="n">
-        <v>12.67</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="S28" s="95" t="n">
-        <v>11.04</v>
+        <v>9.98</v>
       </c>
       <c r="T28" s="95" t="n">
-        <v>10.68</v>
+        <v>7.16</v>
       </c>
       <c r="U28" s="95" t="n">
-        <v>9.460000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="V28" s="95" t="n">
-        <v>9.460000000000001</v>
+        <v>7.37</v>
       </c>
       <c r="W28" s="95" t="n">
-        <v>9.98</v>
+        <v>7.64</v>
       </c>
       <c r="X28" s="95" t="n">
-        <v>7.16</v>
+        <v>7.12</v>
       </c>
       <c r="Y28" s="95" t="n">
-        <v>8.039999999999999</v>
+        <v>6.27</v>
       </c>
       <c r="Z28" s="95" t="n">
-        <v>7.37</v>
+        <v>5.31</v>
       </c>
       <c r="AA28" s="95" t="n">
-        <v>7.64</v>
+        <v>4.85</v>
       </c>
       <c r="AB28" s="95" t="n">
-        <v>7.64</v>
+        <v>4.49</v>
       </c>
       <c r="AC28" s="95" t="n">
-        <v>7.12</v>
+        <v>6.19</v>
       </c>
       <c r="AD28" s="95" t="n">
-        <v>6.27</v>
+        <v>5.6</v>
       </c>
       <c r="AE28" s="95" t="n">
-        <v>5.31</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="29">
@@ -9536,94 +9536,94 @@
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>86.79000000000001</v>
+        <v>95.84</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>86.79000000000001</v>
       </c>
       <c r="D29" s="95" t="n">
-        <v>86.79000000000001</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="E29" s="95" t="n">
-        <v>77.45999999999999</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="F29" s="95" t="n">
-        <v>82.01000000000001</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="G29" s="95" t="n">
-        <v>72.98999999999999</v>
+        <v>32.92</v>
       </c>
       <c r="H29" s="95" t="n">
-        <v>32.92</v>
+        <v>85.03</v>
       </c>
       <c r="I29" s="95" t="n">
-        <v>85.03</v>
+        <v>20.54</v>
       </c>
       <c r="J29" s="95" t="n">
-        <v>85.03</v>
+        <v>21.97</v>
       </c>
       <c r="K29" s="95" t="n">
-        <v>20.54</v>
+        <v>15.42</v>
       </c>
       <c r="L29" s="95" t="n">
-        <v>21.97</v>
+        <v>74.7</v>
       </c>
       <c r="M29" s="95" t="n">
-        <v>15.42</v>
+        <v>51.35</v>
       </c>
       <c r="N29" s="95" t="n">
-        <v>74.7</v>
+        <v>96.66</v>
       </c>
       <c r="O29" s="95" t="n">
-        <v>51.35</v>
+        <v>89.75</v>
       </c>
       <c r="P29" s="95" t="n">
-        <v>51.35</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="Q29" s="95" t="n">
-        <v>96.66</v>
+        <v>77.02</v>
       </c>
       <c r="R29" s="95" t="n">
-        <v>89.75</v>
+        <v>73.3</v>
       </c>
       <c r="S29" s="95" t="n">
-        <v>88.93000000000001</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="T29" s="95" t="n">
-        <v>77.02</v>
+        <v>42.32</v>
       </c>
       <c r="U29" s="95" t="n">
-        <v>73.3</v>
+        <v>70.06</v>
       </c>
       <c r="V29" s="95" t="n">
-        <v>73.3</v>
+        <v>61.86</v>
       </c>
       <c r="W29" s="95" t="n">
-        <v>92.18000000000001</v>
+        <v>95.17</v>
       </c>
       <c r="X29" s="95" t="n">
-        <v>42.32</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="Y29" s="95" t="n">
-        <v>70.06</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="Z29" s="95" t="n">
-        <v>61.86</v>
+        <v>65.19</v>
       </c>
       <c r="AA29" s="95" t="n">
-        <v>95.17</v>
+        <v>44.48</v>
       </c>
       <c r="AB29" s="95" t="n">
-        <v>95.17</v>
+        <v>6.2</v>
       </c>
       <c r="AC29" s="95" t="n">
-        <v>92.73999999999999</v>
+        <v>27.81</v>
       </c>
       <c r="AD29" s="95" t="n">
-        <v>88.20999999999999</v>
+        <v>12.7</v>
       </c>
       <c r="AE29" s="95" t="n">
-        <v>65.19</v>
+        <v>14.52</v>
       </c>
     </row>
     <row r="30">
@@ -9642,144 +9642,144 @@
           <t>red</t>
         </is>
       </c>
-      <c r="D30" s="92" t="inlineStr">
+      <c r="D30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E30" s="91" t="inlineStr">
+      <c r="H30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F30" s="91" t="inlineStr">
+      <c r="I30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G30" s="91" t="inlineStr">
+      <c r="J30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H30" s="92" t="inlineStr">
+      <c r="L30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I30" s="91" t="inlineStr">
+      <c r="N30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J30" s="91" t="inlineStr">
+      <c r="U30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K30" s="91" t="inlineStr">
+      <c r="V30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L30" s="93" t="inlineStr">
+      <c r="W30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M30" s="91" t="inlineStr">
+      <c r="Z30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="N30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD30" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE30" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -9796,88 +9796,88 @@
         <v>-1.3</v>
       </c>
       <c r="D31" s="95" t="n">
-        <v>-1.3</v>
+        <v>-4.18</v>
       </c>
       <c r="E31" s="95" t="n">
-        <v>-4.18</v>
+        <v>-4.84</v>
       </c>
       <c r="F31" s="95" t="n">
-        <v>-4.84</v>
+        <v>-5.47</v>
       </c>
       <c r="G31" s="95" t="n">
-        <v>-5.47</v>
+        <v>-6.85</v>
       </c>
       <c r="H31" s="95" t="n">
-        <v>-6.85</v>
+        <v>-7.64</v>
       </c>
       <c r="I31" s="95" t="n">
-        <v>-7.64</v>
+        <v>-7.28</v>
       </c>
       <c r="J31" s="95" t="n">
-        <v>-7.64</v>
+        <v>-7.29</v>
       </c>
       <c r="K31" s="95" t="n">
-        <v>-7.28</v>
+        <v>-5.52</v>
       </c>
       <c r="L31" s="95" t="n">
-        <v>-7.29</v>
+        <v>-7.32</v>
       </c>
       <c r="M31" s="95" t="n">
-        <v>-5.52</v>
+        <v>-1.85</v>
       </c>
       <c r="N31" s="95" t="n">
-        <v>-7.32</v>
+        <v>-2.87</v>
       </c>
       <c r="O31" s="95" t="n">
-        <v>-1.85</v>
+        <v>-4.44</v>
       </c>
       <c r="P31" s="95" t="n">
-        <v>-1.85</v>
+        <v>-4.15</v>
       </c>
       <c r="Q31" s="95" t="n">
-        <v>-2.87</v>
+        <v>-4.11</v>
       </c>
       <c r="R31" s="95" t="n">
-        <v>-4.44</v>
+        <v>-4.11</v>
       </c>
       <c r="S31" s="95" t="n">
-        <v>-4.15</v>
+        <v>-6.33</v>
       </c>
       <c r="T31" s="95" t="n">
-        <v>-4.11</v>
+        <v>-7.13</v>
       </c>
       <c r="U31" s="95" t="n">
-        <v>-4.11</v>
+        <v>-6.7</v>
       </c>
       <c r="V31" s="95" t="n">
-        <v>-4.11</v>
+        <v>-5.28</v>
       </c>
       <c r="W31" s="95" t="n">
-        <v>-6.33</v>
+        <v>-5.31</v>
       </c>
       <c r="X31" s="95" t="n">
-        <v>-7.13</v>
+        <v>-4.5</v>
       </c>
       <c r="Y31" s="95" t="n">
+        <v>-7.44</v>
+      </c>
+      <c r="Z31" s="95" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="AA31" s="95" t="n">
         <v>-6.7</v>
       </c>
-      <c r="Z31" s="95" t="n">
-        <v>-5.28</v>
-      </c>
-      <c r="AA31" s="95" t="n">
-        <v>-5.31</v>
-      </c>
       <c r="AB31" s="95" t="n">
-        <v>-5.31</v>
+        <v>-6.01</v>
       </c>
       <c r="AC31" s="95" t="n">
-        <v>-4.5</v>
+        <v>-5.71</v>
       </c>
       <c r="AD31" s="95" t="n">
-        <v>-7.44</v>
+        <v>-5.33</v>
       </c>
       <c r="AE31" s="95" t="n">
-        <v>-5.1</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="32">
@@ -9893,88 +9893,88 @@
         <v>6.85</v>
       </c>
       <c r="D32" s="95" t="n">
-        <v>6.85</v>
+        <v>3.42</v>
       </c>
       <c r="E32" s="95" t="n">
-        <v>3.42</v>
+        <v>3.47</v>
       </c>
       <c r="F32" s="95" t="n">
-        <v>3.47</v>
+        <v>1.21</v>
       </c>
       <c r="G32" s="95" t="n">
-        <v>1.21</v>
+        <v>0.25</v>
       </c>
       <c r="H32" s="95" t="n">
-        <v>0.25</v>
+        <v>-2.25</v>
       </c>
       <c r="I32" s="95" t="n">
-        <v>-2.25</v>
+        <v>-2.26</v>
       </c>
       <c r="J32" s="95" t="n">
-        <v>-2.25</v>
+        <v>-4.48</v>
       </c>
       <c r="K32" s="95" t="n">
-        <v>-2.26</v>
+        <v>-2.82</v>
       </c>
       <c r="L32" s="95" t="n">
-        <v>-4.48</v>
+        <v>-3.63</v>
       </c>
       <c r="M32" s="95" t="n">
-        <v>-2.82</v>
+        <v>2.15</v>
       </c>
       <c r="N32" s="95" t="n">
-        <v>-3.63</v>
+        <v>-2.13</v>
       </c>
       <c r="O32" s="95" t="n">
-        <v>2.15</v>
+        <v>-4.01</v>
       </c>
       <c r="P32" s="95" t="n">
-        <v>2.15</v>
+        <v>-4.76</v>
       </c>
       <c r="Q32" s="95" t="n">
-        <v>-2.13</v>
+        <v>-5.22</v>
       </c>
       <c r="R32" s="95" t="n">
-        <v>-4.01</v>
+        <v>-5.22</v>
       </c>
       <c r="S32" s="95" t="n">
-        <v>-4.76</v>
+        <v>-7.96</v>
       </c>
       <c r="T32" s="95" t="n">
-        <v>-5.22</v>
+        <v>-9.43</v>
       </c>
       <c r="U32" s="95" t="n">
-        <v>-5.22</v>
+        <v>-11.19</v>
       </c>
       <c r="V32" s="95" t="n">
-        <v>-5.22</v>
+        <v>-9.5</v>
       </c>
       <c r="W32" s="95" t="n">
-        <v>-7.96</v>
+        <v>-9.48</v>
       </c>
       <c r="X32" s="95" t="n">
-        <v>-9.43</v>
+        <v>-9.92</v>
       </c>
       <c r="Y32" s="95" t="n">
-        <v>-11.19</v>
+        <v>-12.73</v>
       </c>
       <c r="Z32" s="95" t="n">
-        <v>-9.5</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="AA32" s="95" t="n">
-        <v>-9.48</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="AB32" s="95" t="n">
-        <v>-9.48</v>
+        <v>-5.98</v>
       </c>
       <c r="AC32" s="95" t="n">
-        <v>-9.92</v>
+        <v>-5.54</v>
       </c>
       <c r="AD32" s="95" t="n">
-        <v>-12.73</v>
+        <v>-4.26</v>
       </c>
       <c r="AE32" s="95" t="n">
-        <v>-9.609999999999999</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="33">
@@ -9990,88 +9990,88 @@
         <v>63.24</v>
       </c>
       <c r="D33" s="95" t="n">
-        <v>63.24</v>
+        <v>61.28</v>
       </c>
       <c r="E33" s="95" t="n">
-        <v>61.28</v>
+        <v>60.41</v>
       </c>
       <c r="F33" s="95" t="n">
-        <v>60.41</v>
+        <v>57.64</v>
       </c>
       <c r="G33" s="95" t="n">
-        <v>57.64</v>
+        <v>62.13</v>
       </c>
       <c r="H33" s="95" t="n">
-        <v>62.13</v>
+        <v>56.86</v>
       </c>
       <c r="I33" s="95" t="n">
-        <v>56.86</v>
+        <v>56.21</v>
       </c>
       <c r="J33" s="95" t="n">
-        <v>56.86</v>
+        <v>50.28</v>
       </c>
       <c r="K33" s="95" t="n">
-        <v>56.21</v>
+        <v>58.22</v>
       </c>
       <c r="L33" s="95" t="n">
-        <v>50.28</v>
+        <v>52.42</v>
       </c>
       <c r="M33" s="95" t="n">
-        <v>58.22</v>
+        <v>77.31</v>
       </c>
       <c r="N33" s="95" t="n">
-        <v>52.42</v>
+        <v>71.64</v>
       </c>
       <c r="O33" s="95" t="n">
-        <v>77.31</v>
+        <v>61.74</v>
       </c>
       <c r="P33" s="95" t="n">
-        <v>77.31</v>
+        <v>63.04</v>
       </c>
       <c r="Q33" s="95" t="n">
-        <v>71.64</v>
+        <v>60.77</v>
       </c>
       <c r="R33" s="95" t="n">
-        <v>61.74</v>
+        <v>60.77</v>
       </c>
       <c r="S33" s="95" t="n">
-        <v>63.04</v>
+        <v>54.21</v>
       </c>
       <c r="T33" s="95" t="n">
-        <v>60.77</v>
+        <v>42.56</v>
       </c>
       <c r="U33" s="95" t="n">
-        <v>60.77</v>
+        <v>39.44</v>
       </c>
       <c r="V33" s="95" t="n">
-        <v>60.77</v>
+        <v>43.68</v>
       </c>
       <c r="W33" s="95" t="n">
-        <v>54.21</v>
+        <v>43.96</v>
       </c>
       <c r="X33" s="95" t="n">
-        <v>42.56</v>
+        <v>46.79</v>
       </c>
       <c r="Y33" s="95" t="n">
-        <v>39.44</v>
+        <v>26.47</v>
       </c>
       <c r="Z33" s="95" t="n">
-        <v>43.68</v>
+        <v>31.18</v>
       </c>
       <c r="AA33" s="95" t="n">
-        <v>43.96</v>
+        <v>31.7</v>
       </c>
       <c r="AB33" s="95" t="n">
-        <v>43.96</v>
+        <v>33.25</v>
       </c>
       <c r="AC33" s="95" t="n">
-        <v>46.79</v>
+        <v>35.58</v>
       </c>
       <c r="AD33" s="95" t="n">
-        <v>26.47</v>
+        <v>39.17</v>
       </c>
       <c r="AE33" s="95" t="n">
-        <v>31.18</v>
+        <v>62.79</v>
       </c>
     </row>
     <row r="34">
@@ -10100,135 +10100,133 @@
           <t>red</t>
         </is>
       </c>
-      <c r="F34" s="92" t="inlineStr">
+      <c r="F34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G34" s="93" t="inlineStr">
+      <c r="N34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H34" s="93" t="inlineStr">
+      <c r="W34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I34" s="93" t="inlineStr">
+      <c r="X34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J34" s="93" t="inlineStr">
+      <c r="Y34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K34" s="93" t="inlineStr">
+      <c r="Z34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L34" s="91" t="inlineStr">
+      <c r="AA34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M34" s="91" t="inlineStr">
+      <c r="AC34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
+      <c r="AE34" s="91" t="n">
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -10238,94 +10236,94 @@
         </is>
       </c>
       <c r="B35" s="95" t="n">
-        <v>1.24</v>
+        <v>0.93</v>
       </c>
       <c r="C35" s="95" t="n">
         <v>1.56</v>
       </c>
       <c r="D35" s="95" t="n">
-        <v>1.56</v>
+        <v>0.4</v>
       </c>
       <c r="E35" s="95" t="n">
-        <v>0.4</v>
+        <v>0.16</v>
       </c>
       <c r="F35" s="95" t="n">
-        <v>0.16</v>
+        <v>-0.68</v>
       </c>
       <c r="G35" s="95" t="n">
-        <v>-0.68</v>
+        <v>-1.08</v>
       </c>
       <c r="H35" s="95" t="n">
-        <v>-1.08</v>
+        <v>-1.19</v>
       </c>
       <c r="I35" s="95" t="n">
-        <v>-1.19</v>
+        <v>-1.21</v>
       </c>
       <c r="J35" s="95" t="n">
-        <v>-1.19</v>
+        <v>0.33</v>
       </c>
       <c r="K35" s="95" t="n">
-        <v>-1.21</v>
+        <v>0.71</v>
       </c>
       <c r="L35" s="95" t="n">
-        <v>0.33</v>
+        <v>0.63</v>
       </c>
       <c r="M35" s="95" t="n">
-        <v>0.71</v>
+        <v>1.1</v>
       </c>
       <c r="N35" s="95" t="n">
-        <v>0.63</v>
+        <v>1.71</v>
       </c>
       <c r="O35" s="95" t="n">
-        <v>1.1</v>
+        <v>2.62</v>
       </c>
       <c r="P35" s="95" t="n">
-        <v>1.1</v>
+        <v>1.79</v>
       </c>
       <c r="Q35" s="95" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="R35" s="95" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="S35" s="95" t="n">
-        <v>1.79</v>
+        <v>0.8</v>
       </c>
       <c r="T35" s="95" t="n">
-        <v>1.86</v>
+        <v>0.66</v>
       </c>
       <c r="U35" s="95" t="n">
-        <v>1.03</v>
+        <v>0.39</v>
       </c>
       <c r="V35" s="95" t="n">
-        <v>1.03</v>
+        <v>-3.34</v>
       </c>
       <c r="W35" s="95" t="n">
-        <v>0.8</v>
+        <v>-2.39</v>
       </c>
       <c r="X35" s="95" t="n">
-        <v>0.66</v>
+        <v>-1.83</v>
       </c>
       <c r="Y35" s="95" t="n">
-        <v>0.39</v>
+        <v>-2.05</v>
       </c>
       <c r="Z35" s="95" t="n">
-        <v>-3.34</v>
+        <v>-1.53</v>
       </c>
       <c r="AA35" s="95" t="n">
-        <v>-2.39</v>
+        <v>-0.95</v>
       </c>
       <c r="AB35" s="95" t="n">
-        <v>-2.39</v>
+        <v>-2.12</v>
       </c>
       <c r="AC35" s="95" t="n">
-        <v>-1.83</v>
+        <v>-2.46</v>
       </c>
       <c r="AD35" s="95" t="n">
-        <v>-2.05</v>
+        <v>-0.67</v>
       </c>
       <c r="AE35" s="95" t="n">
-        <v>-1.53</v>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -10335,94 +10333,94 @@
         </is>
       </c>
       <c r="B36" s="95" t="n">
-        <v>9.58</v>
+        <v>9.25</v>
       </c>
       <c r="C36" s="95" t="n">
         <v>8.25</v>
       </c>
       <c r="D36" s="95" t="n">
-        <v>8.25</v>
+        <v>9.49</v>
       </c>
       <c r="E36" s="95" t="n">
-        <v>9.49</v>
+        <v>7.45</v>
       </c>
       <c r="F36" s="95" t="n">
-        <v>7.45</v>
+        <v>4.63</v>
       </c>
       <c r="G36" s="95" t="n">
-        <v>4.63</v>
+        <v>4.38</v>
       </c>
       <c r="H36" s="95" t="n">
-        <v>4.38</v>
+        <v>-0.47</v>
       </c>
       <c r="I36" s="95" t="n">
-        <v>-0.47</v>
+        <v>1.58</v>
       </c>
       <c r="J36" s="95" t="n">
-        <v>-0.47</v>
+        <v>2.33</v>
       </c>
       <c r="K36" s="95" t="n">
-        <v>1.58</v>
+        <v>2.33</v>
       </c>
       <c r="L36" s="95" t="n">
-        <v>2.33</v>
+        <v>3.01</v>
       </c>
       <c r="M36" s="95" t="n">
-        <v>2.33</v>
+        <v>2.85</v>
       </c>
       <c r="N36" s="95" t="n">
-        <v>3.01</v>
+        <v>1.83</v>
       </c>
       <c r="O36" s="95" t="n">
-        <v>2.85</v>
+        <v>1.26</v>
       </c>
       <c r="P36" s="95" t="n">
-        <v>2.85</v>
+        <v>-0.78</v>
       </c>
       <c r="Q36" s="95" t="n">
-        <v>1.83</v>
+        <v>-1.02</v>
       </c>
       <c r="R36" s="95" t="n">
-        <v>1.26</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S36" s="95" t="n">
-        <v>-0.78</v>
+        <v>-1.47</v>
       </c>
       <c r="T36" s="95" t="n">
-        <v>-1.02</v>
+        <v>-1.42</v>
       </c>
       <c r="U36" s="95" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.81</v>
       </c>
       <c r="V36" s="95" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.26</v>
       </c>
       <c r="W36" s="95" t="n">
-        <v>-1.47</v>
+        <v>-2.35</v>
       </c>
       <c r="X36" s="95" t="n">
-        <v>-1.42</v>
+        <v>-1.57</v>
       </c>
       <c r="Y36" s="95" t="n">
-        <v>-1.81</v>
+        <v>-0.54</v>
       </c>
       <c r="Z36" s="95" t="n">
-        <v>-2.26</v>
+        <v>1.03</v>
       </c>
       <c r="AA36" s="95" t="n">
-        <v>-2.35</v>
+        <v>1.94</v>
       </c>
       <c r="AB36" s="95" t="n">
-        <v>-2.35</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AC36" s="95" t="n">
-        <v>-1.57</v>
+        <v>0.31</v>
       </c>
       <c r="AD36" s="95" t="n">
-        <v>-0.54</v>
+        <v>0.42</v>
       </c>
       <c r="AE36" s="95" t="n">
-        <v>1.03</v>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -10432,94 +10430,94 @@
         </is>
       </c>
       <c r="B37" s="95" t="n">
-        <v>84.86</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="C37" s="95" t="n">
         <v>81.64</v>
       </c>
       <c r="D37" s="95" t="n">
-        <v>81.64</v>
+        <v>78.16</v>
       </c>
       <c r="E37" s="95" t="n">
-        <v>78.16</v>
+        <v>69.63</v>
       </c>
       <c r="F37" s="95" t="n">
-        <v>69.63</v>
+        <v>29.45</v>
       </c>
       <c r="G37" s="95" t="n">
-        <v>29.45</v>
+        <v>13.62</v>
       </c>
       <c r="H37" s="95" t="n">
-        <v>13.62</v>
+        <v>14.32</v>
       </c>
       <c r="I37" s="95" t="n">
-        <v>14.32</v>
+        <v>23.23</v>
       </c>
       <c r="J37" s="95" t="n">
-        <v>14.32</v>
+        <v>50.34</v>
       </c>
       <c r="K37" s="95" t="n">
-        <v>23.23</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="L37" s="95" t="n">
-        <v>50.34</v>
+        <v>65.09</v>
       </c>
       <c r="M37" s="95" t="n">
-        <v>77.23999999999999</v>
+        <v>86.66</v>
       </c>
       <c r="N37" s="95" t="n">
-        <v>65.09</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="O37" s="95" t="n">
-        <v>86.66</v>
+        <v>88</v>
       </c>
       <c r="P37" s="95" t="n">
-        <v>86.66</v>
+        <v>77.98</v>
       </c>
       <c r="Q37" s="95" t="n">
-        <v>90.48999999999999</v>
+        <v>59.82</v>
       </c>
       <c r="R37" s="95" t="n">
-        <v>88</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="S37" s="95" t="n">
-        <v>77.98</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="T37" s="95" t="n">
-        <v>59.82</v>
+        <v>68.98</v>
       </c>
       <c r="U37" s="95" t="n">
-        <v>77.68000000000001</v>
+        <v>60.96</v>
       </c>
       <c r="V37" s="95" t="n">
-        <v>77.68000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="W37" s="95" t="n">
-        <v>76.68000000000001</v>
+        <v>20.58</v>
       </c>
       <c r="X37" s="95" t="n">
-        <v>68.98</v>
+        <v>30.12</v>
       </c>
       <c r="Y37" s="95" t="n">
-        <v>60.96</v>
+        <v>12.08</v>
       </c>
       <c r="Z37" s="95" t="n">
-        <v>9.050000000000001</v>
+        <v>13.57</v>
       </c>
       <c r="AA37" s="95" t="n">
-        <v>20.58</v>
+        <v>28.44</v>
       </c>
       <c r="AB37" s="95" t="n">
-        <v>20.58</v>
+        <v>44.72</v>
       </c>
       <c r="AC37" s="95" t="n">
-        <v>30.12</v>
+        <v>14.66</v>
       </c>
       <c r="AD37" s="95" t="n">
-        <v>12.08</v>
+        <v>28.1</v>
       </c>
       <c r="AE37" s="95" t="n">
-        <v>13.57</v>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -10543,134 +10541,134 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="E38" s="91" t="inlineStr">
+      <c r="E38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F38" s="93" t="inlineStr">
+      <c r="K38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G38" s="93" t="inlineStr">
+      <c r="Z38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H38" s="93" t="inlineStr">
+      <c r="AB38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I38" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="J38" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="K38" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="L38" s="91" t="inlineStr">
+      <c r="AC38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M38" s="91" t="inlineStr">
+      <c r="AD38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="N38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD38" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AE38" s="91" t="inlineStr">
@@ -10686,94 +10684,94 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>0.05</v>
       </c>
       <c r="D39" s="95" t="n">
-        <v>0.05</v>
+        <v>1.11</v>
       </c>
       <c r="E39" s="95" t="n">
-        <v>1.11</v>
+        <v>0.99</v>
       </c>
       <c r="F39" s="95" t="n">
-        <v>0.99</v>
+        <v>1.39</v>
       </c>
       <c r="G39" s="95" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="H39" s="95" t="n">
-        <v>1.44</v>
+        <v>2.21</v>
       </c>
       <c r="I39" s="95" t="n">
-        <v>2.21</v>
+        <v>2.67</v>
       </c>
       <c r="J39" s="95" t="n">
-        <v>2.21</v>
+        <v>5.39</v>
       </c>
       <c r="K39" s="95" t="n">
-        <v>2.67</v>
+        <v>5.39</v>
       </c>
       <c r="L39" s="95" t="n">
-        <v>5.39</v>
+        <v>5.38</v>
       </c>
       <c r="M39" s="95" t="n">
-        <v>5.39</v>
+        <v>6.9</v>
       </c>
       <c r="N39" s="95" t="n">
-        <v>5.38</v>
+        <v>7.31</v>
       </c>
       <c r="O39" s="95" t="n">
-        <v>6.9</v>
+        <v>7.21</v>
       </c>
       <c r="P39" s="95" t="n">
-        <v>6.9</v>
+        <v>6.84</v>
       </c>
       <c r="Q39" s="95" t="n">
-        <v>7.31</v>
+        <v>7.46</v>
       </c>
       <c r="R39" s="95" t="n">
-        <v>7.21</v>
+        <v>6.69</v>
       </c>
       <c r="S39" s="95" t="n">
-        <v>6.84</v>
+        <v>5.73</v>
       </c>
       <c r="T39" s="95" t="n">
-        <v>7.46</v>
+        <v>6.27</v>
       </c>
       <c r="U39" s="95" t="n">
-        <v>6.69</v>
+        <v>7.42</v>
       </c>
       <c r="V39" s="95" t="n">
-        <v>6.69</v>
+        <v>7.48</v>
       </c>
       <c r="W39" s="95" t="n">
-        <v>5.73</v>
+        <v>6.99</v>
       </c>
       <c r="X39" s="95" t="n">
-        <v>6.27</v>
+        <v>7.27</v>
       </c>
       <c r="Y39" s="95" t="n">
-        <v>7.42</v>
+        <v>5.46</v>
       </c>
       <c r="Z39" s="95" t="n">
-        <v>7.48</v>
+        <v>6.4</v>
       </c>
       <c r="AA39" s="95" t="n">
-        <v>6.99</v>
+        <v>6.18</v>
       </c>
       <c r="AB39" s="95" t="n">
-        <v>6.99</v>
+        <v>5.98</v>
       </c>
       <c r="AC39" s="95" t="n">
-        <v>7.27</v>
+        <v>7.51</v>
       </c>
       <c r="AD39" s="95" t="n">
-        <v>5.46</v>
+        <v>7.66</v>
       </c>
       <c r="AE39" s="95" t="n">
-        <v>6.4</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="40">
@@ -10783,94 +10781,94 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>11.14</v>
+        <v>11.17</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>10.5</v>
       </c>
       <c r="D40" s="95" t="n">
-        <v>10.5</v>
+        <v>11.66</v>
       </c>
       <c r="E40" s="95" t="n">
-        <v>11.66</v>
+        <v>12.39</v>
       </c>
       <c r="F40" s="95" t="n">
-        <v>12.39</v>
+        <v>11.91</v>
       </c>
       <c r="G40" s="95" t="n">
-        <v>11.91</v>
+        <v>10.42</v>
       </c>
       <c r="H40" s="95" t="n">
-        <v>10.42</v>
+        <v>10.03</v>
       </c>
       <c r="I40" s="95" t="n">
-        <v>10.03</v>
+        <v>9.94</v>
       </c>
       <c r="J40" s="95" t="n">
-        <v>10.03</v>
+        <v>12.83</v>
       </c>
       <c r="K40" s="95" t="n">
-        <v>9.94</v>
+        <v>12.83</v>
       </c>
       <c r="L40" s="95" t="n">
-        <v>12.83</v>
+        <v>12.79</v>
       </c>
       <c r="M40" s="95" t="n">
-        <v>12.83</v>
+        <v>15.25</v>
       </c>
       <c r="N40" s="95" t="n">
-        <v>12.79</v>
+        <v>15.64</v>
       </c>
       <c r="O40" s="95" t="n">
-        <v>15.25</v>
+        <v>15.29</v>
       </c>
       <c r="P40" s="95" t="n">
-        <v>15.25</v>
+        <v>14.9</v>
       </c>
       <c r="Q40" s="95" t="n">
-        <v>15.64</v>
+        <v>14.75</v>
       </c>
       <c r="R40" s="95" t="n">
-        <v>15.29</v>
+        <v>14.79</v>
       </c>
       <c r="S40" s="95" t="n">
-        <v>14.9</v>
+        <v>13.96</v>
       </c>
       <c r="T40" s="95" t="n">
-        <v>14.75</v>
+        <v>14.46</v>
       </c>
       <c r="U40" s="95" t="n">
-        <v>14.79</v>
+        <v>14.07</v>
       </c>
       <c r="V40" s="95" t="n">
-        <v>14.79</v>
+        <v>14.24</v>
       </c>
       <c r="W40" s="95" t="n">
-        <v>13.96</v>
+        <v>14.96</v>
       </c>
       <c r="X40" s="95" t="n">
-        <v>14.46</v>
+        <v>15.21</v>
       </c>
       <c r="Y40" s="95" t="n">
-        <v>14.07</v>
+        <v>12.06</v>
       </c>
       <c r="Z40" s="95" t="n">
-        <v>14.24</v>
+        <v>12.77</v>
       </c>
       <c r="AA40" s="95" t="n">
-        <v>14.96</v>
+        <v>11.58</v>
       </c>
       <c r="AB40" s="95" t="n">
-        <v>14.96</v>
+        <v>11.57</v>
       </c>
       <c r="AC40" s="95" t="n">
-        <v>15.21</v>
+        <v>11.58</v>
       </c>
       <c r="AD40" s="95" t="n">
-        <v>12.06</v>
+        <v>12.04</v>
       </c>
       <c r="AE40" s="95" t="n">
-        <v>12.77</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="41">
@@ -10880,94 +10878,94 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>43.21</v>
+        <v>43.48</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>35.77</v>
       </c>
       <c r="D41" s="95" t="n">
-        <v>35.77</v>
+        <v>37.56</v>
       </c>
       <c r="E41" s="95" t="n">
-        <v>37.56</v>
+        <v>35.74</v>
       </c>
       <c r="F41" s="95" t="n">
-        <v>35.74</v>
+        <v>36.86</v>
       </c>
       <c r="G41" s="95" t="n">
-        <v>36.86</v>
+        <v>29.96</v>
       </c>
       <c r="H41" s="95" t="n">
-        <v>29.96</v>
+        <v>33.56</v>
       </c>
       <c r="I41" s="95" t="n">
-        <v>33.56</v>
+        <v>38.91</v>
       </c>
       <c r="J41" s="95" t="n">
-        <v>33.56</v>
+        <v>56.68</v>
       </c>
       <c r="K41" s="95" t="n">
-        <v>38.91</v>
+        <v>56.68</v>
       </c>
       <c r="L41" s="95" t="n">
-        <v>56.68</v>
+        <v>57.12</v>
       </c>
       <c r="M41" s="95" t="n">
-        <v>56.68</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="N41" s="95" t="n">
-        <v>57.12</v>
+        <v>83.77</v>
       </c>
       <c r="O41" s="95" t="n">
-        <v>78.04000000000001</v>
+        <v>80.52</v>
       </c>
       <c r="P41" s="95" t="n">
-        <v>78.04000000000001</v>
+        <v>79.08</v>
       </c>
       <c r="Q41" s="95" t="n">
-        <v>83.77</v>
+        <v>79.38</v>
       </c>
       <c r="R41" s="95" t="n">
-        <v>80.52</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="S41" s="95" t="n">
-        <v>79.08</v>
+        <v>66.75</v>
       </c>
       <c r="T41" s="95" t="n">
-        <v>79.38</v>
+        <v>64.14</v>
       </c>
       <c r="U41" s="95" t="n">
-        <v>77.31999999999999</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="V41" s="95" t="n">
-        <v>77.31999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="W41" s="95" t="n">
-        <v>66.75</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="X41" s="95" t="n">
-        <v>64.14</v>
+        <v>66.14</v>
       </c>
       <c r="Y41" s="95" t="n">
-        <v>66.76000000000001</v>
+        <v>50.55</v>
       </c>
       <c r="Z41" s="95" t="n">
-        <v>65.90000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="AA41" s="95" t="n">
-        <v>65.01000000000001</v>
+        <v>52.02</v>
       </c>
       <c r="AB41" s="95" t="n">
-        <v>65.01000000000001</v>
+        <v>46.05</v>
       </c>
       <c r="AC41" s="95" t="n">
-        <v>66.14</v>
+        <v>66.09</v>
       </c>
       <c r="AD41" s="95" t="n">
-        <v>50.55</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="AE41" s="95" t="n">
-        <v>57.1</v>
+        <v>75.84999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -10976,154 +10974,154 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="91" t="inlineStr">
+      <c r="B42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="D42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E42" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C42" s="92" t="inlineStr">
+      <c r="F42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D42" s="92" t="inlineStr">
+      <c r="H42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E42" s="93" t="inlineStr">
+      <c r="N42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F42" s="91" t="inlineStr">
+      <c r="Z42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE42" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="G42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="H42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="I42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="J42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="K42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="L42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="M42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -11134,94 +11132,94 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-0.85</v>
+        <v>-0.26</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>0.58</v>
       </c>
       <c r="D43" s="95" t="n">
-        <v>0.58</v>
+        <v>-0.59</v>
       </c>
       <c r="E43" s="95" t="n">
-        <v>-0.59</v>
+        <v>-0.14</v>
       </c>
       <c r="F43" s="95" t="n">
-        <v>-0.14</v>
+        <v>-0.77</v>
       </c>
       <c r="G43" s="95" t="n">
-        <v>-0.77</v>
+        <v>-0.74</v>
       </c>
       <c r="H43" s="95" t="n">
-        <v>-0.74</v>
+        <v>-2.37</v>
       </c>
       <c r="I43" s="95" t="n">
-        <v>-2.37</v>
+        <v>-1.96</v>
       </c>
       <c r="J43" s="95" t="n">
-        <v>-2.37</v>
+        <v>0.05</v>
       </c>
       <c r="K43" s="95" t="n">
-        <v>-1.96</v>
+        <v>0.87</v>
       </c>
       <c r="L43" s="95" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="M43" s="95" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="N43" s="95" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O43" s="95" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="P43" s="95" t="n">
         <v>0.87</v>
       </c>
-      <c r="N43" s="95" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="O43" s="95" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P43" s="95" t="n">
-        <v>1.51</v>
-      </c>
       <c r="Q43" s="95" t="n">
-        <v>0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="R43" s="95" t="n">
-        <v>-0.87</v>
+        <v>0.28</v>
       </c>
       <c r="S43" s="95" t="n">
-        <v>0.87</v>
+        <v>1.12</v>
       </c>
       <c r="T43" s="95" t="n">
-        <v>-0.7</v>
+        <v>-2.16</v>
       </c>
       <c r="U43" s="95" t="n">
-        <v>0.28</v>
+        <v>-2.28</v>
       </c>
       <c r="V43" s="95" t="n">
-        <v>0.28</v>
+        <v>-3.34</v>
       </c>
       <c r="W43" s="95" t="n">
-        <v>1.12</v>
+        <v>-2.14</v>
       </c>
       <c r="X43" s="95" t="n">
-        <v>-2.16</v>
+        <v>-3.08</v>
       </c>
       <c r="Y43" s="95" t="n">
-        <v>-2.28</v>
+        <v>-2.29</v>
       </c>
       <c r="Z43" s="95" t="n">
-        <v>-3.34</v>
+        <v>-2.9</v>
       </c>
       <c r="AA43" s="95" t="n">
-        <v>-2.14</v>
+        <v>-1.93</v>
       </c>
       <c r="AB43" s="95" t="n">
-        <v>-2.14</v>
+        <v>-2.01</v>
       </c>
       <c r="AC43" s="95" t="n">
-        <v>-3.08</v>
+        <v>-3.58</v>
       </c>
       <c r="AD43" s="95" t="n">
-        <v>-2.29</v>
+        <v>-4.62</v>
       </c>
       <c r="AE43" s="95" t="n">
-        <v>-2.9</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="44">
@@ -11231,94 +11229,94 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-6.57</v>
+        <v>-6.01</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-5.47</v>
       </c>
       <c r="D44" s="95" t="n">
-        <v>-5.47</v>
+        <v>-6.8</v>
       </c>
       <c r="E44" s="95" t="n">
-        <v>-6.8</v>
+        <v>-6.73</v>
       </c>
       <c r="F44" s="95" t="n">
-        <v>-6.73</v>
+        <v>-6.46</v>
       </c>
       <c r="G44" s="95" t="n">
-        <v>-6.46</v>
+        <v>-5.56</v>
       </c>
       <c r="H44" s="95" t="n">
-        <v>-5.56</v>
+        <v>-6.01</v>
       </c>
       <c r="I44" s="95" t="n">
+        <v>-6.31</v>
+      </c>
+      <c r="J44" s="95" t="n">
+        <v>-4.48</v>
+      </c>
+      <c r="K44" s="95" t="n">
+        <v>-5.85</v>
+      </c>
+      <c r="L44" s="95" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="M44" s="95" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="N44" s="95" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="O44" s="95" t="n">
         <v>-6.01</v>
       </c>
-      <c r="J44" s="95" t="n">
-        <v>-6.01</v>
-      </c>
-      <c r="K44" s="95" t="n">
-        <v>-6.31</v>
-      </c>
-      <c r="L44" s="95" t="n">
-        <v>-4.48</v>
-      </c>
-      <c r="M44" s="95" t="n">
-        <v>-5.85</v>
-      </c>
-      <c r="N44" s="95" t="n">
-        <v>-4.68</v>
-      </c>
-      <c r="O44" s="95" t="n">
-        <v>-2.89</v>
-      </c>
       <c r="P44" s="95" t="n">
-        <v>-2.89</v>
+        <v>-6.35</v>
       </c>
       <c r="Q44" s="95" t="n">
-        <v>-3.77</v>
+        <v>-6.86</v>
       </c>
       <c r="R44" s="95" t="n">
-        <v>-6.01</v>
+        <v>-7.99</v>
       </c>
       <c r="S44" s="95" t="n">
-        <v>-6.35</v>
+        <v>-6.6</v>
       </c>
       <c r="T44" s="95" t="n">
-        <v>-6.86</v>
+        <v>-8.43</v>
       </c>
       <c r="U44" s="95" t="n">
-        <v>-7.99</v>
+        <v>-8.75</v>
       </c>
       <c r="V44" s="95" t="n">
-        <v>-7.99</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="W44" s="95" t="n">
-        <v>-6.6</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="X44" s="95" t="n">
-        <v>-8.43</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="Y44" s="95" t="n">
-        <v>-8.75</v>
+        <v>-9.26</v>
       </c>
       <c r="Z44" s="95" t="n">
-        <v>-9.210000000000001</v>
+        <v>-9.44</v>
       </c>
       <c r="AA44" s="95" t="n">
-        <v>-8.789999999999999</v>
+        <v>-9.02</v>
       </c>
       <c r="AB44" s="95" t="n">
-        <v>-8.789999999999999</v>
+        <v>-10.35</v>
       </c>
       <c r="AC44" s="95" t="n">
         <v>-8.789999999999999</v>
       </c>
       <c r="AD44" s="95" t="n">
-        <v>-9.26</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="AE44" s="95" t="n">
-        <v>-9.44</v>
+        <v>-7.18</v>
       </c>
     </row>
     <row r="45">
@@ -11328,94 +11326,94 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>48.99</v>
+        <v>59.42</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>54.29</v>
       </c>
       <c r="D45" s="95" t="n">
-        <v>54.29</v>
+        <v>46.1</v>
       </c>
       <c r="E45" s="95" t="n">
-        <v>46.1</v>
+        <v>49.74</v>
       </c>
       <c r="F45" s="95" t="n">
-        <v>49.74</v>
+        <v>42.08</v>
       </c>
       <c r="G45" s="95" t="n">
-        <v>42.08</v>
+        <v>50.81</v>
       </c>
       <c r="H45" s="95" t="n">
-        <v>50.81</v>
+        <v>45.03</v>
       </c>
       <c r="I45" s="95" t="n">
-        <v>45.03</v>
+        <v>33.57</v>
       </c>
       <c r="J45" s="95" t="n">
-        <v>45.03</v>
+        <v>45.48</v>
       </c>
       <c r="K45" s="95" t="n">
-        <v>33.57</v>
+        <v>44.93</v>
       </c>
       <c r="L45" s="95" t="n">
-        <v>45.48</v>
+        <v>52.35</v>
       </c>
       <c r="M45" s="95" t="n">
-        <v>44.93</v>
+        <v>78.61</v>
       </c>
       <c r="N45" s="95" t="n">
-        <v>52.35</v>
+        <v>75.48</v>
       </c>
       <c r="O45" s="95" t="n">
-        <v>78.61</v>
+        <v>57.98</v>
       </c>
       <c r="P45" s="95" t="n">
-        <v>78.61</v>
+        <v>66.2</v>
       </c>
       <c r="Q45" s="95" t="n">
-        <v>75.48</v>
+        <v>52.83</v>
       </c>
       <c r="R45" s="95" t="n">
-        <v>57.98</v>
+        <v>51.58</v>
       </c>
       <c r="S45" s="95" t="n">
-        <v>66.2</v>
+        <v>74.97</v>
       </c>
       <c r="T45" s="95" t="n">
-        <v>52.83</v>
+        <v>45.92</v>
       </c>
       <c r="U45" s="95" t="n">
-        <v>51.58</v>
+        <v>59.76</v>
       </c>
       <c r="V45" s="95" t="n">
-        <v>51.58</v>
+        <v>48.71</v>
       </c>
       <c r="W45" s="95" t="n">
-        <v>74.97</v>
+        <v>53.61</v>
       </c>
       <c r="X45" s="95" t="n">
-        <v>45.92</v>
+        <v>45.19</v>
       </c>
       <c r="Y45" s="95" t="n">
-        <v>59.76</v>
+        <v>32.83</v>
       </c>
       <c r="Z45" s="95" t="n">
-        <v>48.71</v>
+        <v>34.58</v>
       </c>
       <c r="AA45" s="95" t="n">
-        <v>53.61</v>
+        <v>37.2</v>
       </c>
       <c r="AB45" s="95" t="n">
-        <v>53.61</v>
+        <v>16.31</v>
       </c>
       <c r="AC45" s="95" t="n">
-        <v>45.19</v>
+        <v>22.99</v>
       </c>
       <c r="AD45" s="95" t="n">
-        <v>32.83</v>
+        <v>32.1</v>
       </c>
       <c r="AE45" s="95" t="n">
-        <v>34.58</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="46">
@@ -11434,144 +11432,144 @@
           <t>red</t>
         </is>
       </c>
-      <c r="D46" s="92" t="inlineStr">
+      <c r="D46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E46" s="91" t="inlineStr">
+      <c r="F46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F46" s="92" t="inlineStr">
+      <c r="G46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G46" s="91" t="inlineStr">
+      <c r="N46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H46" s="91" t="inlineStr">
+      <c r="P46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I46" s="91" t="inlineStr">
+      <c r="S46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="J46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="K46" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="L46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="M46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD46" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE46" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -11582,94 +11580,94 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>6.61</v>
+        <v>5.95</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>6.61</v>
       </c>
       <c r="D47" s="95" t="n">
-        <v>6.61</v>
+        <v>4.66</v>
       </c>
       <c r="E47" s="95" t="n">
-        <v>4.66</v>
+        <v>4.43</v>
       </c>
       <c r="F47" s="95" t="n">
-        <v>4.43</v>
+        <v>2.96</v>
       </c>
       <c r="G47" s="95" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H47" s="95" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I47" s="95" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J47" s="95" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="K47" s="95" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="L47" s="95" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="M47" s="95" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N47" s="95" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="O47" s="95" t="n">
         <v>2.96</v>
       </c>
-      <c r="H47" s="95" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="I47" s="95" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="J47" s="95" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="K47" s="95" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="L47" s="95" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="M47" s="95" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="N47" s="95" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="O47" s="95" t="n">
-        <v>5.4</v>
-      </c>
       <c r="P47" s="95" t="n">
-        <v>5.4</v>
+        <v>4.58</v>
       </c>
       <c r="Q47" s="95" t="n">
-        <v>4.27</v>
+        <v>3.04</v>
       </c>
       <c r="R47" s="95" t="n">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="S47" s="95" t="n">
-        <v>4.58</v>
+        <v>4.35</v>
       </c>
       <c r="T47" s="95" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="U47" s="95" t="n">
-        <v>2.66</v>
+        <v>3.02</v>
       </c>
       <c r="V47" s="95" t="n">
-        <v>2.66</v>
+        <v>1.68</v>
       </c>
       <c r="W47" s="95" t="n">
-        <v>4.35</v>
+        <v>2.95</v>
       </c>
       <c r="X47" s="95" t="n">
-        <v>3.06</v>
+        <v>1.45</v>
       </c>
       <c r="Y47" s="95" t="n">
-        <v>3.02</v>
+        <v>1.45</v>
       </c>
       <c r="Z47" s="95" t="n">
-        <v>1.68</v>
+        <v>0.74</v>
       </c>
       <c r="AA47" s="95" t="n">
-        <v>2.95</v>
+        <v>2.08</v>
       </c>
       <c r="AB47" s="95" t="n">
-        <v>2.95</v>
+        <v>1.67</v>
       </c>
       <c r="AC47" s="95" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AD47" s="95" t="n">
-        <v>1.45</v>
+        <v>-0.21</v>
       </c>
       <c r="AE47" s="95" t="n">
-        <v>0.74</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="48">
@@ -11679,94 +11677,94 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>8.130000000000001</v>
+        <v>7.38</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>8.130000000000001</v>
       </c>
       <c r="D48" s="95" t="n">
-        <v>8.130000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="E48" s="95" t="n">
-        <v>6.2</v>
+        <v>6.16</v>
       </c>
       <c r="F48" s="95" t="n">
-        <v>6.16</v>
+        <v>6.75</v>
       </c>
       <c r="G48" s="95" t="n">
-        <v>6.75</v>
+        <v>7.71</v>
       </c>
       <c r="H48" s="95" t="n">
-        <v>7.71</v>
+        <v>7.2</v>
       </c>
       <c r="I48" s="95" t="n">
-        <v>7.2</v>
+        <v>7.01</v>
       </c>
       <c r="J48" s="95" t="n">
-        <v>7.2</v>
+        <v>7.87</v>
       </c>
       <c r="K48" s="95" t="n">
-        <v>7.01</v>
+        <v>6.58</v>
       </c>
       <c r="L48" s="95" t="n">
-        <v>7.87</v>
+        <v>7.78</v>
       </c>
       <c r="M48" s="95" t="n">
-        <v>6.58</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="N48" s="95" t="n">
-        <v>7.78</v>
+        <v>6.31</v>
       </c>
       <c r="O48" s="95" t="n">
-        <v>8.460000000000001</v>
+        <v>4.66</v>
       </c>
       <c r="P48" s="95" t="n">
-        <v>8.460000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="Q48" s="95" t="n">
-        <v>6.31</v>
+        <v>3.7</v>
       </c>
       <c r="R48" s="95" t="n">
-        <v>4.66</v>
+        <v>1.72</v>
       </c>
       <c r="S48" s="95" t="n">
-        <v>3.7</v>
+        <v>3.46</v>
       </c>
       <c r="T48" s="95" t="n">
-        <v>3.7</v>
+        <v>2.34</v>
       </c>
       <c r="U48" s="95" t="n">
-        <v>1.72</v>
+        <v>1.26</v>
       </c>
       <c r="V48" s="95" t="n">
-        <v>1.72</v>
+        <v>0.84</v>
       </c>
       <c r="W48" s="95" t="n">
-        <v>3.46</v>
+        <v>1.71</v>
       </c>
       <c r="X48" s="95" t="n">
-        <v>2.34</v>
+        <v>1.41</v>
       </c>
       <c r="Y48" s="95" t="n">
-        <v>1.26</v>
+        <v>0.68</v>
       </c>
       <c r="Z48" s="95" t="n">
-        <v>0.84</v>
+        <v>0.48</v>
       </c>
       <c r="AA48" s="95" t="n">
-        <v>1.71</v>
+        <v>2.38</v>
       </c>
       <c r="AB48" s="95" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" s="95" t="n">
-        <v>1.41</v>
+        <v>3.59</v>
       </c>
       <c r="AD48" s="95" t="n">
-        <v>0.68</v>
+        <v>3.65</v>
       </c>
       <c r="AE48" s="95" t="n">
-        <v>0.48</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="49">
@@ -11776,94 +11774,94 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>68.01000000000001</v>
+        <v>73.77</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>68.01000000000001</v>
       </c>
       <c r="D49" s="95" t="n">
-        <v>68.01000000000001</v>
+        <v>58.26</v>
       </c>
       <c r="E49" s="95" t="n">
-        <v>58.26</v>
+        <v>62.55</v>
       </c>
       <c r="F49" s="95" t="n">
-        <v>62.55</v>
+        <v>49.18</v>
       </c>
       <c r="G49" s="95" t="n">
-        <v>49.18</v>
+        <v>52.29</v>
       </c>
       <c r="H49" s="95" t="n">
+        <v>53.55</v>
+      </c>
+      <c r="I49" s="95" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="J49" s="95" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="K49" s="95" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="L49" s="95" t="n">
+        <v>67.34999999999999</v>
+      </c>
+      <c r="M49" s="95" t="n">
+        <v>78.38</v>
+      </c>
+      <c r="N49" s="95" t="n">
+        <v>72.42</v>
+      </c>
+      <c r="O49" s="95" t="n">
+        <v>59.91</v>
+      </c>
+      <c r="P49" s="95" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q49" s="95" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="R49" s="95" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="S49" s="95" t="n">
+        <v>75.06999999999999</v>
+      </c>
+      <c r="T49" s="95" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="U49" s="95" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="V49" s="95" t="n">
+        <v>57.16</v>
+      </c>
+      <c r="W49" s="95" t="n">
+        <v>62.56</v>
+      </c>
+      <c r="X49" s="95" t="n">
         <v>52.29</v>
       </c>
-      <c r="I49" s="95" t="n">
-        <v>53.55</v>
-      </c>
-      <c r="J49" s="95" t="n">
-        <v>53.55</v>
-      </c>
-      <c r="K49" s="95" t="n">
-        <v>46.86</v>
-      </c>
-      <c r="L49" s="95" t="n">
-        <v>56.45</v>
-      </c>
-      <c r="M49" s="95" t="n">
-        <v>59.76</v>
-      </c>
-      <c r="N49" s="95" t="n">
-        <v>67.34999999999999</v>
-      </c>
-      <c r="O49" s="95" t="n">
-        <v>78.38</v>
-      </c>
-      <c r="P49" s="95" t="n">
-        <v>78.38</v>
-      </c>
-      <c r="Q49" s="95" t="n">
-        <v>72.42</v>
-      </c>
-      <c r="R49" s="95" t="n">
-        <v>59.91</v>
-      </c>
-      <c r="S49" s="95" t="n">
-        <v>66</v>
-      </c>
-      <c r="T49" s="95" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="U49" s="95" t="n">
-        <v>52.95</v>
-      </c>
-      <c r="V49" s="95" t="n">
-        <v>52.95</v>
-      </c>
-      <c r="W49" s="95" t="n">
-        <v>75.06999999999999</v>
-      </c>
-      <c r="X49" s="95" t="n">
-        <v>61.14</v>
-      </c>
       <c r="Y49" s="95" t="n">
-        <v>62.6</v>
+        <v>37.42</v>
       </c>
       <c r="Z49" s="95" t="n">
-        <v>57.16</v>
+        <v>31.32</v>
       </c>
       <c r="AA49" s="95" t="n">
-        <v>62.56</v>
+        <v>40.38</v>
       </c>
       <c r="AB49" s="95" t="n">
-        <v>62.56</v>
+        <v>26.19</v>
       </c>
       <c r="AC49" s="95" t="n">
-        <v>52.29</v>
+        <v>42.54</v>
       </c>
       <c r="AD49" s="95" t="n">
-        <v>37.42</v>
+        <v>43.82</v>
       </c>
       <c r="AE49" s="95" t="n">
-        <v>31.32</v>
+        <v>58.62</v>
       </c>
     </row>
     <row r="51">
@@ -11876,7 +11874,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:10.57&gt;=10;kc:RNG60:28.96&gt;=25;cy:RNG60:27.91&gt;=25;hk50:RNG60:18.98&gt;=15;hk50:RNG120:29.79&gt;=25</t>
+          <t>今日卖报：sh:RNG60:10.57&gt;=10;kc:RNG60:28.96&gt;=25;cy:RNG60:27.91&gt;=25;hk50:RNG60:18.98&gt;=15;hk50:RNG120:29.79&gt;=25;us500:RS2:93.6&gt;=85;us30:RS3:87.47&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2410.xlsx
+++ b/report_2410.xlsx
@@ -800,7 +800,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1063,6 +1063,7 @@
     <xf numFmtId="0" fontId="0" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3890,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.12</v>
+        <v>7.14</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.09</v>
@@ -3987,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.44</v>
+        <v>0.66</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.37</v>
@@ -4084,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.48</v>
+        <v>0.7</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.07000000000000001</v>
@@ -6351,142 +6352,142 @@
       </c>
       <c r="D1" s="77" t="inlineStr">
         <is>
-          <t>241013</t>
+          <t>241011</t>
         </is>
       </c>
       <c r="E1" s="77" t="inlineStr">
         <is>
-          <t>241011</t>
+          <t>241010</t>
         </is>
       </c>
       <c r="F1" s="77" t="inlineStr">
         <is>
-          <t>241010</t>
+          <t>241009</t>
         </is>
       </c>
       <c r="G1" s="77" t="inlineStr">
         <is>
-          <t>241009</t>
+          <t>241008</t>
         </is>
       </c>
       <c r="H1" s="77" t="inlineStr">
         <is>
-          <t>241008</t>
+          <t>241007</t>
         </is>
       </c>
       <c r="I1" s="77" t="inlineStr">
         <is>
-          <t>241007</t>
+          <t>241004</t>
         </is>
       </c>
       <c r="J1" s="77" t="inlineStr">
         <is>
-          <t>241006</t>
+          <t>241003</t>
         </is>
       </c>
       <c r="K1" s="77" t="inlineStr">
         <is>
-          <t>241004</t>
+          <t>241002</t>
         </is>
       </c>
       <c r="L1" s="77" t="inlineStr">
         <is>
-          <t>241003</t>
+          <t>241001</t>
         </is>
       </c>
       <c r="M1" s="77" t="inlineStr">
         <is>
-          <t>241002</t>
+          <t>240930</t>
         </is>
       </c>
       <c r="N1" s="77" t="inlineStr">
         <is>
-          <t>241001</t>
+          <t>240927</t>
         </is>
       </c>
       <c r="O1" s="77" t="inlineStr">
         <is>
-          <t>240930</t>
+          <t>240926</t>
         </is>
       </c>
       <c r="P1" s="77" t="inlineStr">
         <is>
-          <t>240929</t>
+          <t>240925</t>
         </is>
       </c>
       <c r="Q1" s="77" t="inlineStr">
         <is>
-          <t>240927</t>
+          <t>240924</t>
         </is>
       </c>
       <c r="R1" s="77" t="inlineStr">
         <is>
-          <t>240926</t>
+          <t>240923</t>
         </is>
       </c>
       <c r="S1" s="77" t="inlineStr">
         <is>
-          <t>240925</t>
+          <t>240920</t>
         </is>
       </c>
       <c r="T1" s="77" t="inlineStr">
         <is>
-          <t>240924</t>
+          <t>240919</t>
         </is>
       </c>
       <c r="U1" s="77" t="inlineStr">
         <is>
-          <t>240923</t>
+          <t>240918</t>
         </is>
       </c>
       <c r="V1" s="77" t="inlineStr">
         <is>
-          <t>240922</t>
+          <t>240917</t>
         </is>
       </c>
       <c r="W1" s="77" t="inlineStr">
         <is>
-          <t>240920</t>
+          <t>240916</t>
         </is>
       </c>
       <c r="X1" s="77" t="inlineStr">
         <is>
-          <t>240919</t>
+          <t>240913</t>
         </is>
       </c>
       <c r="Y1" s="77" t="inlineStr">
         <is>
-          <t>240918</t>
+          <t>240912</t>
         </is>
       </c>
       <c r="Z1" s="77" t="inlineStr">
         <is>
-          <t>240917</t>
+          <t>240911</t>
         </is>
       </c>
       <c r="AA1" s="77" t="inlineStr">
         <is>
-          <t>240916</t>
+          <t>240910</t>
         </is>
       </c>
       <c r="AB1" s="77" t="inlineStr">
         <is>
-          <t>240915</t>
+          <t>240909</t>
         </is>
       </c>
       <c r="AC1" s="77" t="inlineStr">
         <is>
-          <t>240913</t>
+          <t>240906</t>
         </is>
       </c>
       <c r="AD1" s="77" t="inlineStr">
         <is>
-          <t>240912</t>
+          <t>240905</t>
         </is>
       </c>
       <c r="AE1" s="77" t="inlineStr">
         <is>
-          <t>240911</t>
+          <t>240904</t>
         </is>
       </c>
     </row>
@@ -6521,74 +6522,74 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="G2" s="91" t="inlineStr">
+      <c r="G2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="I2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="S2" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T2" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="U2" s="91" t="inlineStr">
@@ -6596,24 +6597,24 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="V2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="V2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="W2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="X2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Y2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="Z2" s="93" t="inlineStr">
@@ -6663,16 +6664,16 @@
         <v>9.470000000000001</v>
       </c>
       <c r="E3" s="94" t="n">
-        <v>9.470000000000001</v>
+        <v>11.58</v>
       </c>
       <c r="F3" s="94" t="n">
-        <v>11.58</v>
+        <v>11.51</v>
       </c>
       <c r="G3" s="94" t="n">
-        <v>11.51</v>
+        <v>18.3</v>
       </c>
       <c r="H3" s="94" t="n">
-        <v>18.3</v>
+        <v>12.81</v>
       </c>
       <c r="I3" s="94" t="n">
         <v>12.81</v>
@@ -6690,58 +6691,58 @@
         <v>12.81</v>
       </c>
       <c r="N3" s="94" t="n">
-        <v>12.81</v>
+        <v>3.53</v>
       </c>
       <c r="O3" s="94" t="n">
-        <v>12.81</v>
+        <v>0.13</v>
       </c>
       <c r="P3" s="94" t="n">
-        <v>3.53</v>
+        <v>-3.29</v>
       </c>
       <c r="Q3" s="94" t="n">
-        <v>3.53</v>
+        <v>-3.51</v>
       </c>
       <c r="R3" s="94" t="n">
-        <v>0.13</v>
+        <v>-6.68</v>
       </c>
       <c r="S3" s="94" t="n">
-        <v>-3.29</v>
+        <v>-7.93</v>
       </c>
       <c r="T3" s="94" t="n">
-        <v>-3.51</v>
+        <v>-7.25</v>
       </c>
       <c r="U3" s="94" t="n">
-        <v>-6.68</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="V3" s="94" t="n">
-        <v>-7.93</v>
+        <v>-9.81</v>
       </c>
       <c r="W3" s="94" t="n">
-        <v>-7.93</v>
+        <v>-9.81</v>
       </c>
       <c r="X3" s="94" t="n">
-        <v>-7.25</v>
+        <v>-9.81</v>
       </c>
       <c r="Y3" s="94" t="n">
-        <v>-8.300000000000001</v>
+        <v>-9.59</v>
       </c>
       <c r="Z3" s="94" t="n">
-        <v>-9.81</v>
+        <v>-9.82</v>
       </c>
       <c r="AA3" s="94" t="n">
-        <v>-9.81</v>
+        <v>-9.44</v>
       </c>
       <c r="AB3" s="94" t="n">
-        <v>-9.81</v>
+        <v>-9.26</v>
       </c>
       <c r="AC3" s="94" t="n">
-        <v>-9.81</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="AD3" s="94" t="n">
-        <v>-9.59</v>
+        <v>-7.94</v>
       </c>
       <c r="AE3" s="94" t="n">
-        <v>-9.82</v>
+        <v>-8.34</v>
       </c>
     </row>
     <row r="4">
@@ -6760,16 +6761,16 @@
         <v>6.05</v>
       </c>
       <c r="E4" s="94" t="n">
-        <v>6.05</v>
+        <v>9.07</v>
       </c>
       <c r="F4" s="94" t="n">
-        <v>9.07</v>
+        <v>6.9</v>
       </c>
       <c r="G4" s="94" t="n">
-        <v>6.9</v>
+        <v>14.53</v>
       </c>
       <c r="H4" s="94" t="n">
-        <v>14.53</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="I4" s="94" t="n">
         <v>8.710000000000001</v>
@@ -6787,58 +6788,58 @@
         <v>8.710000000000001</v>
       </c>
       <c r="N4" s="94" t="n">
-        <v>8.710000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="O4" s="94" t="n">
-        <v>8.710000000000001</v>
+        <v>-2.48</v>
       </c>
       <c r="P4" s="94" t="n">
-        <v>0.41</v>
+        <v>-4.76</v>
       </c>
       <c r="Q4" s="94" t="n">
-        <v>0.41</v>
+        <v>-4.9</v>
       </c>
       <c r="R4" s="94" t="n">
-        <v>-2.48</v>
+        <v>-8.16</v>
       </c>
       <c r="S4" s="94" t="n">
-        <v>-4.76</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="T4" s="94" t="n">
-        <v>-4.9</v>
+        <v>-9.59</v>
       </c>
       <c r="U4" s="94" t="n">
-        <v>-8.16</v>
+        <v>-10.85</v>
       </c>
       <c r="V4" s="94" t="n">
-        <v>-9.720000000000001</v>
+        <v>-12.12</v>
       </c>
       <c r="W4" s="94" t="n">
-        <v>-9.720000000000001</v>
+        <v>-12.12</v>
       </c>
       <c r="X4" s="94" t="n">
-        <v>-9.59</v>
+        <v>-12.12</v>
       </c>
       <c r="Y4" s="94" t="n">
-        <v>-10.85</v>
+        <v>-11.77</v>
       </c>
       <c r="Z4" s="94" t="n">
-        <v>-12.12</v>
+        <v>-11.13</v>
       </c>
       <c r="AA4" s="94" t="n">
-        <v>-12.12</v>
+        <v>-11.05</v>
       </c>
       <c r="AB4" s="94" t="n">
-        <v>-12.12</v>
+        <v>-10.42</v>
       </c>
       <c r="AC4" s="94" t="n">
-        <v>-12.12</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="AD4" s="94" t="n">
-        <v>-11.77</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="AE4" s="94" t="n">
-        <v>-11.13</v>
+        <v>-8.890000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -6857,16 +6858,16 @@
         <v>44.67</v>
       </c>
       <c r="E5" s="94" t="n">
-        <v>44.67</v>
+        <v>59.48</v>
       </c>
       <c r="F5" s="94" t="n">
-        <v>59.48</v>
+        <v>54.31</v>
       </c>
       <c r="G5" s="94" t="n">
-        <v>54.31</v>
+        <v>99.84</v>
       </c>
       <c r="H5" s="94" t="n">
-        <v>99.84</v>
+        <v>99.75</v>
       </c>
       <c r="I5" s="94" t="n">
         <v>99.75</v>
@@ -6884,58 +6885,58 @@
         <v>99.75</v>
       </c>
       <c r="N5" s="94" t="n">
-        <v>99.75</v>
+        <v>99.31</v>
       </c>
       <c r="O5" s="94" t="n">
-        <v>99.75</v>
+        <v>98.83</v>
       </c>
       <c r="P5" s="94" t="n">
-        <v>99.31</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="Q5" s="94" t="n">
-        <v>99.31</v>
+        <v>96.38</v>
       </c>
       <c r="R5" s="94" t="n">
-        <v>98.83</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="S5" s="94" t="n">
-        <v>97.34999999999999</v>
+        <v>64.38</v>
       </c>
       <c r="T5" s="94" t="n">
-        <v>96.38</v>
+        <v>63.45</v>
       </c>
       <c r="U5" s="94" t="n">
-        <v>77.51000000000001</v>
+        <v>37.85</v>
       </c>
       <c r="V5" s="94" t="n">
-        <v>64.38</v>
+        <v>7.42</v>
       </c>
       <c r="W5" s="94" t="n">
-        <v>64.38</v>
+        <v>7.42</v>
       </c>
       <c r="X5" s="94" t="n">
-        <v>63.45</v>
+        <v>7.42</v>
       </c>
       <c r="Y5" s="94" t="n">
-        <v>37.85</v>
+        <v>10.95</v>
       </c>
       <c r="Z5" s="94" t="n">
-        <v>7.42</v>
+        <v>12.36</v>
       </c>
       <c r="AA5" s="94" t="n">
-        <v>7.42</v>
+        <v>20.95</v>
       </c>
       <c r="AB5" s="94" t="n">
-        <v>7.42</v>
+        <v>5.95</v>
       </c>
       <c r="AC5" s="94" t="n">
-        <v>7.42</v>
+        <v>11.48</v>
       </c>
       <c r="AD5" s="94" t="n">
-        <v>10.95</v>
+        <v>21.9</v>
       </c>
       <c r="AE5" s="94" t="n">
-        <v>12.36</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="6">
@@ -6964,79 +6965,79 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="F6" s="91" t="inlineStr">
+      <c r="F6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="S6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="H6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="I6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="T6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="U6" s="93" t="inlineStr">
@@ -7059,29 +7060,29 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="Y6" s="93" t="inlineStr">
+      <c r="Y6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Z6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AB6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="AC6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="AD6" s="91" t="inlineStr">
@@ -7111,16 +7112,16 @@
         <v>26.54</v>
       </c>
       <c r="E7" s="94" t="n">
-        <v>26.54</v>
+        <v>34.41</v>
       </c>
       <c r="F7" s="94" t="n">
-        <v>34.41</v>
+        <v>44.1</v>
       </c>
       <c r="G7" s="94" t="n">
-        <v>44.1</v>
+        <v>46.52</v>
       </c>
       <c r="H7" s="94" t="n">
-        <v>46.52</v>
+        <v>26.36</v>
       </c>
       <c r="I7" s="94" t="n">
         <v>26.36</v>
@@ -7138,58 +7139,58 @@
         <v>26.36</v>
       </c>
       <c r="N7" s="94" t="n">
-        <v>26.36</v>
+        <v>5.45</v>
       </c>
       <c r="O7" s="94" t="n">
-        <v>26.36</v>
+        <v>-0.85</v>
       </c>
       <c r="P7" s="94" t="n">
-        <v>5.45</v>
+        <v>-5.96</v>
       </c>
       <c r="Q7" s="94" t="n">
-        <v>5.45</v>
+        <v>-6.32</v>
       </c>
       <c r="R7" s="94" t="n">
-        <v>-0.85</v>
+        <v>-10.11</v>
       </c>
       <c r="S7" s="94" t="n">
-        <v>-5.96</v>
+        <v>-11.14</v>
       </c>
       <c r="T7" s="94" t="n">
-        <v>-6.32</v>
+        <v>-9.23</v>
       </c>
       <c r="U7" s="94" t="n">
-        <v>-10.11</v>
+        <v>-12.41</v>
       </c>
       <c r="V7" s="94" t="n">
-        <v>-11.14</v>
+        <v>-13.62</v>
       </c>
       <c r="W7" s="94" t="n">
-        <v>-11.14</v>
+        <v>-13.62</v>
       </c>
       <c r="X7" s="94" t="n">
-        <v>-9.23</v>
+        <v>-13.62</v>
       </c>
       <c r="Y7" s="94" t="n">
-        <v>-12.41</v>
+        <v>-12.75</v>
       </c>
       <c r="Z7" s="94" t="n">
-        <v>-13.62</v>
+        <v>-11.62</v>
       </c>
       <c r="AA7" s="94" t="n">
-        <v>-13.62</v>
+        <v>-12.8</v>
       </c>
       <c r="AB7" s="94" t="n">
-        <v>-13.62</v>
+        <v>-13.49</v>
       </c>
       <c r="AC7" s="94" t="n">
-        <v>-13.62</v>
+        <v>-12.19</v>
       </c>
       <c r="AD7" s="94" t="n">
-        <v>-12.75</v>
+        <v>-11.56</v>
       </c>
       <c r="AE7" s="94" t="n">
-        <v>-11.62</v>
+        <v>-10.95</v>
       </c>
     </row>
     <row r="8">
@@ -7208,16 +7209,16 @@
         <v>21.69</v>
       </c>
       <c r="E8" s="94" t="n">
-        <v>21.69</v>
+        <v>29.69</v>
       </c>
       <c r="F8" s="94" t="n">
-        <v>29.69</v>
+        <v>33.11</v>
       </c>
       <c r="G8" s="94" t="n">
-        <v>33.11</v>
+        <v>38.25</v>
       </c>
       <c r="H8" s="94" t="n">
-        <v>38.25</v>
+        <v>15.28</v>
       </c>
       <c r="I8" s="94" t="n">
         <v>15.28</v>
@@ -7235,58 +7236,58 @@
         <v>15.28</v>
       </c>
       <c r="N8" s="94" t="n">
-        <v>15.28</v>
+        <v>-3.74</v>
       </c>
       <c r="O8" s="94" t="n">
-        <v>15.28</v>
+        <v>-10.62</v>
       </c>
       <c r="P8" s="94" t="n">
-        <v>-3.74</v>
+        <v>-12.51</v>
       </c>
       <c r="Q8" s="94" t="n">
-        <v>-3.74</v>
+        <v>-12.61</v>
       </c>
       <c r="R8" s="94" t="n">
-        <v>-10.62</v>
+        <v>-14.58</v>
       </c>
       <c r="S8" s="94" t="n">
-        <v>-12.51</v>
+        <v>-16.03</v>
       </c>
       <c r="T8" s="94" t="n">
-        <v>-12.61</v>
+        <v>-16.65</v>
       </c>
       <c r="U8" s="94" t="n">
-        <v>-14.58</v>
+        <v>-18.48</v>
       </c>
       <c r="V8" s="94" t="n">
-        <v>-16.03</v>
+        <v>-18.74</v>
       </c>
       <c r="W8" s="94" t="n">
-        <v>-16.03</v>
+        <v>-18.74</v>
       </c>
       <c r="X8" s="94" t="n">
-        <v>-16.65</v>
+        <v>-18.74</v>
       </c>
       <c r="Y8" s="94" t="n">
-        <v>-18.48</v>
+        <v>-19.06</v>
       </c>
       <c r="Z8" s="94" t="n">
-        <v>-18.74</v>
+        <v>-18.16</v>
       </c>
       <c r="AA8" s="94" t="n">
-        <v>-18.74</v>
+        <v>-20.04</v>
       </c>
       <c r="AB8" s="94" t="n">
-        <v>-18.74</v>
+        <v>-19.01</v>
       </c>
       <c r="AC8" s="94" t="n">
-        <v>-18.74</v>
+        <v>-17.71</v>
       </c>
       <c r="AD8" s="94" t="n">
-        <v>-19.06</v>
+        <v>-17.63</v>
       </c>
       <c r="AE8" s="94" t="n">
-        <v>-18.16</v>
+        <v>-17.79</v>
       </c>
     </row>
     <row r="9">
@@ -7305,16 +7306,16 @@
         <v>59.18</v>
       </c>
       <c r="E9" s="94" t="n">
-        <v>59.18</v>
+        <v>74.52</v>
       </c>
       <c r="F9" s="94" t="n">
-        <v>74.52</v>
+        <v>89.13</v>
       </c>
       <c r="G9" s="94" t="n">
-        <v>89.13</v>
+        <v>98.36</v>
       </c>
       <c r="H9" s="94" t="n">
-        <v>98.36</v>
+        <v>96.84</v>
       </c>
       <c r="I9" s="94" t="n">
         <v>96.84</v>
@@ -7332,58 +7333,58 @@
         <v>96.84</v>
       </c>
       <c r="N9" s="94" t="n">
-        <v>96.84</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="O9" s="94" t="n">
-        <v>96.84</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="P9" s="94" t="n">
-        <v>91.06999999999999</v>
+        <v>64.94</v>
       </c>
       <c r="Q9" s="94" t="n">
-        <v>91.06999999999999</v>
+        <v>64.66</v>
       </c>
       <c r="R9" s="94" t="n">
-        <v>81.48999999999999</v>
+        <v>23.69</v>
       </c>
       <c r="S9" s="94" t="n">
-        <v>64.94</v>
+        <v>29.81</v>
       </c>
       <c r="T9" s="94" t="n">
-        <v>64.66</v>
+        <v>33.91</v>
       </c>
       <c r="U9" s="94" t="n">
-        <v>23.69</v>
+        <v>22.82</v>
       </c>
       <c r="V9" s="94" t="n">
-        <v>29.81</v>
+        <v>30.54</v>
       </c>
       <c r="W9" s="94" t="n">
-        <v>29.81</v>
+        <v>30.54</v>
       </c>
       <c r="X9" s="94" t="n">
-        <v>33.91</v>
+        <v>30.54</v>
       </c>
       <c r="Y9" s="94" t="n">
-        <v>22.82</v>
+        <v>35.28</v>
       </c>
       <c r="Z9" s="94" t="n">
-        <v>30.54</v>
+        <v>42.99</v>
       </c>
       <c r="AA9" s="94" t="n">
-        <v>30.54</v>
+        <v>33.88</v>
       </c>
       <c r="AB9" s="94" t="n">
-        <v>30.54</v>
+        <v>22.22</v>
       </c>
       <c r="AC9" s="94" t="n">
-        <v>30.54</v>
+        <v>27.98</v>
       </c>
       <c r="AD9" s="94" t="n">
-        <v>35.28</v>
+        <v>37.32</v>
       </c>
       <c r="AE9" s="94" t="n">
-        <v>42.99</v>
+        <v>38.49</v>
       </c>
     </row>
     <row r="10">
@@ -7412,134 +7413,134 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="F10" s="91" t="inlineStr">
+      <c r="F10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="S10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="T10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G10" s="92" t="inlineStr">
+      <c r="U10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="V10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="W10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="X10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Y10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Z10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H10" s="92" t="inlineStr">
+      <c r="AA10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="V10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="W10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="X10" s="91" t="inlineStr">
+      <c r="AE10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="Y10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD10" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -7559,16 +7560,16 @@
         <v>27.24</v>
       </c>
       <c r="E11" s="94" t="n">
-        <v>27.24</v>
+        <v>33.94</v>
       </c>
       <c r="F11" s="94" t="n">
-        <v>33.94</v>
+        <v>39.99</v>
       </c>
       <c r="G11" s="94" t="n">
-        <v>39.99</v>
+        <v>54.04</v>
       </c>
       <c r="H11" s="94" t="n">
-        <v>54.04</v>
+        <v>32.05</v>
       </c>
       <c r="I11" s="94" t="n">
         <v>32.05</v>
@@ -7586,58 +7587,58 @@
         <v>32.05</v>
       </c>
       <c r="N11" s="94" t="n">
-        <v>32.05</v>
+        <v>13.58</v>
       </c>
       <c r="O11" s="94" t="n">
-        <v>32.05</v>
+        <v>2.95</v>
       </c>
       <c r="P11" s="94" t="n">
-        <v>13.58</v>
+        <v>-2.45</v>
       </c>
       <c r="Q11" s="94" t="n">
-        <v>13.58</v>
+        <v>-4.05</v>
       </c>
       <c r="R11" s="94" t="n">
-        <v>2.95</v>
+        <v>-10.14</v>
       </c>
       <c r="S11" s="94" t="n">
-        <v>-2.45</v>
+        <v>-11.21</v>
       </c>
       <c r="T11" s="94" t="n">
-        <v>-4.05</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="U11" s="94" t="n">
-        <v>-10.14</v>
+        <v>-11.44</v>
       </c>
       <c r="V11" s="94" t="n">
-        <v>-11.21</v>
+        <v>-12.57</v>
       </c>
       <c r="W11" s="94" t="n">
-        <v>-11.21</v>
+        <v>-12.57</v>
       </c>
       <c r="X11" s="94" t="n">
-        <v>-9.029999999999999</v>
+        <v>-12.57</v>
       </c>
       <c r="Y11" s="94" t="n">
-        <v>-11.44</v>
+        <v>-11.96</v>
       </c>
       <c r="Z11" s="94" t="n">
-        <v>-12.57</v>
+        <v>-12.87</v>
       </c>
       <c r="AA11" s="94" t="n">
-        <v>-12.57</v>
+        <v>-14.98</v>
       </c>
       <c r="AB11" s="94" t="n">
-        <v>-12.57</v>
+        <v>-14.79</v>
       </c>
       <c r="AC11" s="94" t="n">
-        <v>-12.57</v>
+        <v>-14.14</v>
       </c>
       <c r="AD11" s="94" t="n">
-        <v>-11.96</v>
+        <v>-11.99</v>
       </c>
       <c r="AE11" s="94" t="n">
-        <v>-12.87</v>
+        <v>-12.63</v>
       </c>
     </row>
     <row r="12">
@@ -7656,16 +7657,16 @@
         <v>17.89</v>
       </c>
       <c r="E12" s="94" t="n">
-        <v>17.89</v>
+        <v>23.63</v>
       </c>
       <c r="F12" s="94" t="n">
-        <v>23.63</v>
+        <v>24.76</v>
       </c>
       <c r="G12" s="94" t="n">
-        <v>24.76</v>
+        <v>41.13</v>
       </c>
       <c r="H12" s="94" t="n">
-        <v>41.13</v>
+        <v>18.19</v>
       </c>
       <c r="I12" s="94" t="n">
         <v>18.19</v>
@@ -7683,58 +7684,58 @@
         <v>18.19</v>
       </c>
       <c r="N12" s="94" t="n">
-        <v>18.19</v>
+        <v>1.34</v>
       </c>
       <c r="O12" s="94" t="n">
-        <v>18.19</v>
+        <v>-8.44</v>
       </c>
       <c r="P12" s="94" t="n">
-        <v>1.34</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="Q12" s="94" t="n">
-        <v>1.34</v>
+        <v>-10.6</v>
       </c>
       <c r="R12" s="94" t="n">
-        <v>-8.44</v>
+        <v>-14.49</v>
       </c>
       <c r="S12" s="94" t="n">
-        <v>-9.720000000000001</v>
+        <v>-16.56</v>
       </c>
       <c r="T12" s="94" t="n">
-        <v>-10.6</v>
+        <v>-15.65</v>
       </c>
       <c r="U12" s="94" t="n">
-        <v>-14.49</v>
+        <v>-17.96</v>
       </c>
       <c r="V12" s="94" t="n">
-        <v>-16.56</v>
+        <v>-19.08</v>
       </c>
       <c r="W12" s="94" t="n">
-        <v>-16.56</v>
+        <v>-19.08</v>
       </c>
       <c r="X12" s="94" t="n">
-        <v>-15.65</v>
+        <v>-19.08</v>
       </c>
       <c r="Y12" s="94" t="n">
-        <v>-17.96</v>
+        <v>-18.72</v>
       </c>
       <c r="Z12" s="94" t="n">
-        <v>-19.08</v>
+        <v>-18.28</v>
       </c>
       <c r="AA12" s="94" t="n">
-        <v>-19.08</v>
+        <v>-20.06</v>
       </c>
       <c r="AB12" s="94" t="n">
-        <v>-19.08</v>
+        <v>-18.31</v>
       </c>
       <c r="AC12" s="94" t="n">
-        <v>-19.08</v>
+        <v>-18.32</v>
       </c>
       <c r="AD12" s="94" t="n">
-        <v>-18.72</v>
+        <v>-17.44</v>
       </c>
       <c r="AE12" s="94" t="n">
-        <v>-18.28</v>
+        <v>-18.44</v>
       </c>
     </row>
     <row r="13">
@@ -7753,16 +7754,16 @@
         <v>42.18</v>
       </c>
       <c r="E13" s="94" t="n">
-        <v>42.18</v>
+        <v>55.03</v>
       </c>
       <c r="F13" s="94" t="n">
-        <v>55.03</v>
+        <v>62.67</v>
       </c>
       <c r="G13" s="94" t="n">
-        <v>62.67</v>
+        <v>99.77</v>
       </c>
       <c r="H13" s="94" t="n">
-        <v>99.77</v>
+        <v>99.48</v>
       </c>
       <c r="I13" s="94" t="n">
         <v>99.48</v>
@@ -7780,58 +7781,58 @@
         <v>99.48</v>
       </c>
       <c r="N13" s="94" t="n">
-        <v>99.48</v>
+        <v>98.62</v>
       </c>
       <c r="O13" s="94" t="n">
-        <v>99.48</v>
+        <v>96</v>
       </c>
       <c r="P13" s="94" t="n">
-        <v>98.62</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="Q13" s="94" t="n">
-        <v>98.62</v>
+        <v>88.09</v>
       </c>
       <c r="R13" s="94" t="n">
-        <v>96</v>
+        <v>30.34</v>
       </c>
       <c r="S13" s="94" t="n">
-        <v>91.40000000000001</v>
+        <v>39.51</v>
       </c>
       <c r="T13" s="94" t="n">
-        <v>88.09</v>
+        <v>58.67</v>
       </c>
       <c r="U13" s="94" t="n">
-        <v>30.34</v>
+        <v>28.04</v>
       </c>
       <c r="V13" s="94" t="n">
-        <v>39.51</v>
+        <v>29.98</v>
       </c>
       <c r="W13" s="94" t="n">
-        <v>39.51</v>
+        <v>29.98</v>
       </c>
       <c r="X13" s="94" t="n">
-        <v>58.67</v>
+        <v>29.98</v>
       </c>
       <c r="Y13" s="94" t="n">
-        <v>28.04</v>
+        <v>54.57</v>
       </c>
       <c r="Z13" s="94" t="n">
-        <v>29.98</v>
+        <v>69.45</v>
       </c>
       <c r="AA13" s="94" t="n">
-        <v>29.98</v>
+        <v>37.43</v>
       </c>
       <c r="AB13" s="94" t="n">
-        <v>29.98</v>
+        <v>35.11</v>
       </c>
       <c r="AC13" s="94" t="n">
-        <v>29.98</v>
+        <v>33.41</v>
       </c>
       <c r="AD13" s="94" t="n">
-        <v>54.57</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="AE13" s="94" t="n">
-        <v>69.45</v>
+        <v>53.41</v>
       </c>
     </row>
     <row r="14">
@@ -7860,129 +7861,129 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="F14" s="91" t="inlineStr">
+      <c r="F14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G14" s="93" t="inlineStr">
+      <c r="H14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Z14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="I14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="AA14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="AE14" s="93" t="inlineStr">
@@ -8010,82 +8011,82 @@
         <v>17.96</v>
       </c>
       <c r="F15" s="94" t="n">
-        <v>17.96</v>
+        <v>12.81</v>
       </c>
       <c r="G15" s="94" t="n">
-        <v>12.81</v>
+        <v>17.35</v>
       </c>
       <c r="H15" s="94" t="n">
-        <v>17.35</v>
+        <v>32.21</v>
       </c>
       <c r="I15" s="94" t="n">
-        <v>32.21</v>
+        <v>29.75</v>
       </c>
       <c r="J15" s="94" t="n">
-        <v>29.75</v>
+        <v>26.19</v>
       </c>
       <c r="K15" s="94" t="n">
-        <v>29.75</v>
+        <v>26.09</v>
       </c>
       <c r="L15" s="94" t="n">
-        <v>26.19</v>
+        <v>17.23</v>
       </c>
       <c r="M15" s="94" t="n">
-        <v>26.09</v>
+        <v>17.23</v>
       </c>
       <c r="N15" s="94" t="n">
-        <v>17.23</v>
+        <v>14.76</v>
       </c>
       <c r="O15" s="94" t="n">
-        <v>17.23</v>
+        <v>12.13</v>
       </c>
       <c r="P15" s="94" t="n">
-        <v>14.76</v>
+        <v>7.96</v>
       </c>
       <c r="Q15" s="94" t="n">
-        <v>14.76</v>
+        <v>7.25</v>
       </c>
       <c r="R15" s="94" t="n">
-        <v>12.13</v>
+        <v>0.87</v>
       </c>
       <c r="S15" s="94" t="n">
-        <v>7.96</v>
+        <v>1.03</v>
       </c>
       <c r="T15" s="94" t="n">
-        <v>7.25</v>
+        <v>-0.08</v>
       </c>
       <c r="U15" s="94" t="n">
-        <v>0.87</v>
+        <v>-2.04</v>
       </c>
       <c r="V15" s="94" t="n">
-        <v>1.03</v>
+        <v>-2.04</v>
       </c>
       <c r="W15" s="94" t="n">
-        <v>1.03</v>
+        <v>-4.98</v>
       </c>
       <c r="X15" s="94" t="n">
-        <v>-0.08</v>
+        <v>-5.76</v>
       </c>
       <c r="Y15" s="94" t="n">
-        <v>-2.04</v>
+        <v>-3.77</v>
       </c>
       <c r="Z15" s="94" t="n">
-        <v>-2.04</v>
+        <v>-4.61</v>
       </c>
       <c r="AA15" s="94" t="n">
-        <v>-4.98</v>
+        <v>-3.94</v>
       </c>
       <c r="AB15" s="94" t="n">
-        <v>-5.76</v>
+        <v>-5.06</v>
       </c>
       <c r="AC15" s="94" t="n">
-        <v>-5.76</v>
+        <v>-2.75</v>
       </c>
       <c r="AD15" s="94" t="n">
-        <v>-3.77</v>
+        <v>-2.75</v>
       </c>
       <c r="AE15" s="94" t="n">
-        <v>-4.61</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="16">
@@ -8107,82 +8108,82 @@
         <v>30.79</v>
       </c>
       <c r="F16" s="94" t="n">
-        <v>30.79</v>
+        <v>24.32</v>
       </c>
       <c r="G16" s="94" t="n">
-        <v>24.32</v>
+        <v>25.15</v>
       </c>
       <c r="H16" s="94" t="n">
-        <v>25.15</v>
+        <v>35.13</v>
       </c>
       <c r="I16" s="94" t="n">
-        <v>35.13</v>
+        <v>32.66</v>
       </c>
       <c r="J16" s="94" t="n">
-        <v>32.66</v>
+        <v>31.41</v>
       </c>
       <c r="K16" s="94" t="n">
-        <v>32.66</v>
+        <v>34.13</v>
       </c>
       <c r="L16" s="94" t="n">
-        <v>31.41</v>
+        <v>26.37</v>
       </c>
       <c r="M16" s="94" t="n">
-        <v>34.13</v>
+        <v>26.37</v>
       </c>
       <c r="N16" s="94" t="n">
-        <v>26.37</v>
+        <v>23.36</v>
       </c>
       <c r="O16" s="94" t="n">
-        <v>26.37</v>
+        <v>17.68</v>
       </c>
       <c r="P16" s="94" t="n">
-        <v>23.36</v>
+        <v>15.64</v>
       </c>
       <c r="Q16" s="94" t="n">
-        <v>23.36</v>
+        <v>15.91</v>
       </c>
       <c r="R16" s="94" t="n">
-        <v>17.68</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S16" s="94" t="n">
-        <v>15.64</v>
+        <v>10.84</v>
       </c>
       <c r="T16" s="94" t="n">
-        <v>15.91</v>
+        <v>9.17</v>
       </c>
       <c r="U16" s="94" t="n">
-        <v>9.800000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="V16" s="94" t="n">
-        <v>10.84</v>
+        <v>4.73</v>
       </c>
       <c r="W16" s="94" t="n">
-        <v>10.84</v>
+        <v>5.31</v>
       </c>
       <c r="X16" s="94" t="n">
-        <v>9.17</v>
+        <v>5.08</v>
       </c>
       <c r="Y16" s="94" t="n">
-        <v>4.73</v>
+        <v>3.01</v>
       </c>
       <c r="Z16" s="94" t="n">
-        <v>4.73</v>
+        <v>2.32</v>
       </c>
       <c r="AA16" s="94" t="n">
-        <v>5.31</v>
+        <v>1.61</v>
       </c>
       <c r="AB16" s="94" t="n">
-        <v>5.08</v>
+        <v>0.67</v>
       </c>
       <c r="AC16" s="94" t="n">
-        <v>5.08</v>
+        <v>2.05</v>
       </c>
       <c r="AD16" s="94" t="n">
-        <v>3.01</v>
+        <v>2.05</v>
       </c>
       <c r="AE16" s="94" t="n">
-        <v>2.32</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="17">
@@ -8204,82 +8205,82 @@
         <v>48.87</v>
       </c>
       <c r="F17" s="94" t="n">
-        <v>48.87</v>
+        <v>35.54</v>
       </c>
       <c r="G17" s="94" t="n">
-        <v>35.54</v>
+        <v>39.14</v>
       </c>
       <c r="H17" s="94" t="n">
-        <v>39.14</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="I17" s="94" t="n">
-        <v>91.23999999999999</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="J17" s="94" t="n">
-        <v>89.48999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="K17" s="94" t="n">
-        <v>89.48999999999999</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="L17" s="94" t="n">
-        <v>85.84</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="M17" s="94" t="n">
-        <v>99.56999999999999</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="N17" s="94" t="n">
-        <v>99.18000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="O17" s="94" t="n">
-        <v>99.18000000000001</v>
+        <v>98.23</v>
       </c>
       <c r="P17" s="94" t="n">
-        <v>98.89</v>
+        <v>96.44</v>
       </c>
       <c r="Q17" s="94" t="n">
-        <v>98.89</v>
+        <v>95.94</v>
       </c>
       <c r="R17" s="94" t="n">
-        <v>98.23</v>
+        <v>89.48</v>
       </c>
       <c r="S17" s="94" t="n">
-        <v>96.44</v>
+        <v>91.13</v>
       </c>
       <c r="T17" s="94" t="n">
-        <v>95.94</v>
+        <v>87.39</v>
       </c>
       <c r="U17" s="94" t="n">
-        <v>89.48</v>
+        <v>76.86</v>
       </c>
       <c r="V17" s="94" t="n">
-        <v>91.13</v>
+        <v>76.86</v>
       </c>
       <c r="W17" s="94" t="n">
-        <v>91.13</v>
+        <v>59.96</v>
       </c>
       <c r="X17" s="94" t="n">
-        <v>87.39</v>
+        <v>54.39</v>
       </c>
       <c r="Y17" s="94" t="n">
-        <v>76.86</v>
+        <v>38.93</v>
       </c>
       <c r="Z17" s="94" t="n">
-        <v>76.86</v>
+        <v>17.46</v>
       </c>
       <c r="AA17" s="94" t="n">
-        <v>59.96</v>
+        <v>23.32</v>
       </c>
       <c r="AB17" s="94" t="n">
-        <v>54.39</v>
+        <v>17.15</v>
       </c>
       <c r="AC17" s="94" t="n">
-        <v>54.39</v>
+        <v>28.67</v>
       </c>
       <c r="AD17" s="94" t="n">
-        <v>38.93</v>
+        <v>28.67</v>
       </c>
       <c r="AE17" s="94" t="n">
-        <v>17.46</v>
+        <v>29.45</v>
       </c>
     </row>
     <row r="18">
@@ -8288,154 +8289,154 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="92" t="inlineStr">
+      <c r="B18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="C18" s="92" t="inlineStr">
+      <c r="D18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D18" s="92" t="inlineStr">
+      <c r="E18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E18" s="92" t="inlineStr">
+      <c r="F18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F18" s="92" t="inlineStr">
+      <c r="G18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G18" s="92" t="inlineStr">
+      <c r="H18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H18" s="92" t="inlineStr">
+      <c r="J18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I18" s="93" t="inlineStr">
+      <c r="R18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AB18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="M18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="AC18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>6.45</v>
+        <v>4.51</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>6.45</v>
@@ -8455,85 +8456,85 @@
         <v>4.88</v>
       </c>
       <c r="E19" s="94" t="n">
-        <v>4.88</v>
+        <v>3.43</v>
       </c>
       <c r="F19" s="94" t="n">
-        <v>3.43</v>
+        <v>2.2</v>
       </c>
       <c r="G19" s="94" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="H19" s="94" t="n">
-        <v>2.13</v>
+        <v>1.44</v>
       </c>
       <c r="I19" s="94" t="n">
-        <v>1.44</v>
+        <v>2.98</v>
       </c>
       <c r="J19" s="94" t="n">
-        <v>2.98</v>
+        <v>1.17</v>
       </c>
       <c r="K19" s="94" t="n">
-        <v>2.98</v>
+        <v>2.38</v>
       </c>
       <c r="L19" s="94" t="n">
-        <v>1.17</v>
+        <v>2.44</v>
       </c>
       <c r="M19" s="94" t="n">
-        <v>2.38</v>
+        <v>3.51</v>
       </c>
       <c r="N19" s="94" t="n">
-        <v>2.44</v>
+        <v>3.63</v>
       </c>
       <c r="O19" s="94" t="n">
-        <v>3.51</v>
+        <v>4.29</v>
       </c>
       <c r="P19" s="94" t="n">
-        <v>3.63</v>
+        <v>4.51</v>
       </c>
       <c r="Q19" s="94" t="n">
-        <v>3.63</v>
+        <v>4.99</v>
       </c>
       <c r="R19" s="94" t="n">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="S19" s="94" t="n">
-        <v>4.51</v>
+        <v>4.1</v>
       </c>
       <c r="T19" s="94" t="n">
-        <v>4.99</v>
+        <v>4.47</v>
       </c>
       <c r="U19" s="94" t="n">
-        <v>4.3</v>
+        <v>3.13</v>
       </c>
       <c r="V19" s="94" t="n">
-        <v>4.1</v>
+        <v>3.11</v>
       </c>
       <c r="W19" s="94" t="n">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="X19" s="94" t="n">
-        <v>4.47</v>
+        <v>2.53</v>
       </c>
       <c r="Y19" s="94" t="n">
-        <v>3.13</v>
+        <v>2.24</v>
       </c>
       <c r="Z19" s="94" t="n">
-        <v>3.11</v>
+        <v>2.26</v>
       </c>
       <c r="AA19" s="94" t="n">
-        <v>2.92</v>
+        <v>1.14</v>
       </c>
       <c r="AB19" s="94" t="n">
-        <v>2.53</v>
+        <v>0.92</v>
       </c>
       <c r="AC19" s="94" t="n">
-        <v>2.53</v>
+        <v>0.62</v>
       </c>
       <c r="AD19" s="94" t="n">
-        <v>2.24</v>
+        <v>2.66</v>
       </c>
       <c r="AE19" s="94" t="n">
-        <v>2.26</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="20">
@@ -8543,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>15.57</v>
+        <v>14.66</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>15.57</v>
@@ -8552,95 +8553,95 @@
         <v>16.05</v>
       </c>
       <c r="E20" s="94" t="n">
-        <v>16.05</v>
+        <v>16.36</v>
       </c>
       <c r="F20" s="94" t="n">
-        <v>16.36</v>
+        <v>15.58</v>
       </c>
       <c r="G20" s="94" t="n">
-        <v>15.58</v>
+        <v>14.51</v>
       </c>
       <c r="H20" s="94" t="n">
-        <v>14.51</v>
+        <v>12.76</v>
       </c>
       <c r="I20" s="94" t="n">
-        <v>12.76</v>
+        <v>13.62</v>
       </c>
       <c r="J20" s="94" t="n">
-        <v>13.62</v>
+        <v>11.25</v>
       </c>
       <c r="K20" s="94" t="n">
-        <v>13.62</v>
+        <v>9.82</v>
       </c>
       <c r="L20" s="94" t="n">
-        <v>11.25</v>
+        <v>10.62</v>
       </c>
       <c r="M20" s="94" t="n">
-        <v>9.82</v>
+        <v>10.61</v>
       </c>
       <c r="N20" s="94" t="n">
-        <v>10.62</v>
+        <v>10.3</v>
       </c>
       <c r="O20" s="94" t="n">
-        <v>10.61</v>
+        <v>10.4</v>
       </c>
       <c r="P20" s="94" t="n">
-        <v>10.3</v>
+        <v>11.17</v>
       </c>
       <c r="Q20" s="94" t="n">
-        <v>10.3</v>
+        <v>10.01</v>
       </c>
       <c r="R20" s="94" t="n">
-        <v>10.4</v>
+        <v>9.85</v>
       </c>
       <c r="S20" s="94" t="n">
-        <v>11.17</v>
+        <v>8.75</v>
       </c>
       <c r="T20" s="94" t="n">
-        <v>10.01</v>
+        <v>8.74</v>
       </c>
       <c r="U20" s="94" t="n">
-        <v>9.85</v>
+        <v>7.05</v>
       </c>
       <c r="V20" s="94" t="n">
-        <v>8.75</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="W20" s="94" t="n">
-        <v>8.75</v>
+        <v>7.95</v>
       </c>
       <c r="X20" s="94" t="n">
-        <v>8.74</v>
+        <v>7.49</v>
       </c>
       <c r="Y20" s="94" t="n">
-        <v>7.05</v>
+        <v>6.76</v>
       </c>
       <c r="Z20" s="94" t="n">
-        <v>8.279999999999999</v>
+        <v>6.31</v>
       </c>
       <c r="AA20" s="94" t="n">
-        <v>7.95</v>
+        <v>6.12</v>
       </c>
       <c r="AB20" s="94" t="n">
-        <v>7.49</v>
+        <v>6.25</v>
       </c>
       <c r="AC20" s="94" t="n">
-        <v>7.49</v>
+        <v>5.69</v>
       </c>
       <c r="AD20" s="94" t="n">
-        <v>6.76</v>
+        <v>6.85</v>
       </c>
       <c r="AE20" s="94" t="n">
-        <v>6.31</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="95" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>93.59999999999999</v>
+        <v>43.25</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>93.59999999999999</v>
@@ -8649,85 +8650,85 @@
         <v>84.56999999999999</v>
       </c>
       <c r="E21" s="94" t="n">
-        <v>84.56999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="F21" s="94" t="n">
-        <v>65.7</v>
+        <v>83.12</v>
       </c>
       <c r="G21" s="94" t="n">
-        <v>83.12</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="H21" s="94" t="n">
-        <v>69.18000000000001</v>
+        <v>30.41</v>
       </c>
       <c r="I21" s="94" t="n">
-        <v>30.41</v>
+        <v>81.84</v>
       </c>
       <c r="J21" s="94" t="n">
-        <v>81.84</v>
+        <v>15.76</v>
       </c>
       <c r="K21" s="94" t="n">
-        <v>81.84</v>
+        <v>23.93</v>
       </c>
       <c r="L21" s="94" t="n">
-        <v>15.76</v>
+        <v>22.27</v>
       </c>
       <c r="M21" s="94" t="n">
-        <v>23.93</v>
+        <v>86.19</v>
       </c>
       <c r="N21" s="94" t="n">
-        <v>22.27</v>
+        <v>60.63</v>
       </c>
       <c r="O21" s="94" t="n">
-        <v>86.19</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="P21" s="94" t="n">
-        <v>60.63</v>
+        <v>58.19</v>
       </c>
       <c r="Q21" s="94" t="n">
-        <v>60.63</v>
+        <v>90.16</v>
       </c>
       <c r="R21" s="94" t="n">
-        <v>83.51000000000001</v>
+        <v>84.39</v>
       </c>
       <c r="S21" s="94" t="n">
-        <v>58.19</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="T21" s="94" t="n">
-        <v>90.16</v>
+        <v>92.34</v>
       </c>
       <c r="U21" s="94" t="n">
-        <v>84.39</v>
+        <v>40.89</v>
       </c>
       <c r="V21" s="94" t="n">
-        <v>76.79000000000001</v>
+        <v>96.09</v>
       </c>
       <c r="W21" s="94" t="n">
-        <v>76.79000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="X21" s="94" t="n">
-        <v>92.34</v>
+        <v>95.06</v>
       </c>
       <c r="Y21" s="94" t="n">
-        <v>40.89</v>
+        <v>91.83</v>
       </c>
       <c r="Z21" s="94" t="n">
-        <v>96.09</v>
+        <v>85.17</v>
       </c>
       <c r="AA21" s="94" t="n">
-        <v>95.83</v>
+        <v>65.2</v>
       </c>
       <c r="AB21" s="94" t="n">
-        <v>95.06</v>
+        <v>51.58</v>
       </c>
       <c r="AC21" s="94" t="n">
-        <v>95.06</v>
+        <v>3</v>
       </c>
       <c r="AD21" s="94" t="n">
-        <v>91.83</v>
+        <v>12.54</v>
       </c>
       <c r="AE21" s="94" t="n">
-        <v>85.17</v>
+        <v>17.38</v>
       </c>
     </row>
     <row r="22">
@@ -8736,154 +8737,154 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="92" t="inlineStr">
+      <c r="B22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="C22" s="92" t="inlineStr">
+      <c r="D22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D22" s="92" t="inlineStr">
+      <c r="E22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E22" s="92" t="inlineStr">
+      <c r="F22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F22" s="92" t="inlineStr">
+      <c r="G22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G22" s="92" t="inlineStr">
+      <c r="J22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H22" s="91" t="inlineStr">
+      <c r="R22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I22" s="93" t="inlineStr">
+      <c r="AC22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L22" s="91" t="inlineStr">
+      <c r="AD22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="M22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>6.89</v>
+        <v>5.75</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>6.89</v>
@@ -8903,85 +8904,85 @@
         <v>5.41</v>
       </c>
       <c r="E23" s="94" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="F23" s="94" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G23" s="94" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="H23" s="94" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="I23" s="94" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="J23" s="94" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="K23" s="94" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="L23" s="94" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="M23" s="94" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N23" s="94" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="O23" s="94" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="P23" s="94" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="Q23" s="94" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="R23" s="94" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="S23" s="94" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="T23" s="94" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="U23" s="94" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="V23" s="94" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="W23" s="94" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="X23" s="94" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="Y23" s="94" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="Z23" s="94" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AA23" s="94" t="n">
         <v>5.41</v>
       </c>
-      <c r="F23" s="94" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="G23" s="94" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H23" s="94" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="I23" s="94" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="J23" s="94" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="K23" s="94" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="L23" s="94" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="M23" s="94" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="N23" s="94" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="O23" s="94" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P23" s="94" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="Q23" s="94" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="R23" s="94" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="S23" s="94" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="T23" s="94" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="U23" s="94" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="V23" s="94" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W23" s="94" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="X23" s="94" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="Y23" s="94" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="Z23" s="94" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="AA23" s="94" t="n">
-        <v>6.36</v>
-      </c>
       <c r="AB23" s="94" t="n">
-        <v>6.59</v>
+        <v>5.47</v>
       </c>
       <c r="AC23" s="94" t="n">
-        <v>6.59</v>
+        <v>4.12</v>
       </c>
       <c r="AD23" s="94" t="n">
-        <v>5.98</v>
+        <v>4.86</v>
       </c>
       <c r="AE23" s="94" t="n">
-        <v>5.89</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="24">
@@ -8991,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>11.85</v>
+        <v>11.13</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>11.85</v>
@@ -9000,95 +9001,95 @@
         <v>12.09</v>
       </c>
       <c r="E24" s="94" t="n">
-        <v>12.09</v>
+        <v>11.76</v>
       </c>
       <c r="F24" s="94" t="n">
-        <v>11.76</v>
+        <v>12.54</v>
       </c>
       <c r="G24" s="94" t="n">
-        <v>12.54</v>
+        <v>11.46</v>
       </c>
       <c r="H24" s="94" t="n">
-        <v>11.46</v>
+        <v>10.99</v>
       </c>
       <c r="I24" s="94" t="n">
-        <v>10.99</v>
+        <v>12.24</v>
       </c>
       <c r="J24" s="94" t="n">
-        <v>12.24</v>
+        <v>10.61</v>
       </c>
       <c r="K24" s="94" t="n">
-        <v>12.24</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="L24" s="94" t="n">
-        <v>10.61</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="M24" s="94" t="n">
-        <v>9.720000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="N24" s="94" t="n">
-        <v>9.609999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="O24" s="94" t="n">
-        <v>8.859999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="P24" s="94" t="n">
-        <v>8.789999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Q24" s="94" t="n">
-        <v>8.789999999999999</v>
+        <v>7.87</v>
       </c>
       <c r="R24" s="94" t="n">
-        <v>8.41</v>
+        <v>7.54</v>
       </c>
       <c r="S24" s="94" t="n">
-        <v>8.6</v>
+        <v>6.31</v>
       </c>
       <c r="T24" s="94" t="n">
-        <v>7.87</v>
+        <v>5.57</v>
       </c>
       <c r="U24" s="94" t="n">
-        <v>7.54</v>
+        <v>4.38</v>
       </c>
       <c r="V24" s="94" t="n">
-        <v>6.31</v>
+        <v>5.92</v>
       </c>
       <c r="W24" s="94" t="n">
-        <v>6.31</v>
+        <v>5.87</v>
       </c>
       <c r="X24" s="94" t="n">
-        <v>5.57</v>
+        <v>4.86</v>
       </c>
       <c r="Y24" s="94" t="n">
-        <v>4.38</v>
+        <v>3.31</v>
       </c>
       <c r="Z24" s="94" t="n">
-        <v>5.92</v>
+        <v>3.42</v>
       </c>
       <c r="AA24" s="94" t="n">
-        <v>5.87</v>
+        <v>4.16</v>
       </c>
       <c r="AB24" s="94" t="n">
-        <v>4.86</v>
+        <v>5.26</v>
       </c>
       <c r="AC24" s="94" t="n">
-        <v>4.86</v>
+        <v>4.21</v>
       </c>
       <c r="AD24" s="94" t="n">
-        <v>3.31</v>
+        <v>4.76</v>
       </c>
       <c r="AE24" s="94" t="n">
-        <v>3.42</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="95" t="inlineStr">
+      <c r="A25" s="76" t="inlineStr">
         <is>
           <t>us30:RS3</t>
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>87.47</v>
+        <v>53.27</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>87.47</v>
@@ -9097,85 +9098,85 @@
         <v>82.94</v>
       </c>
       <c r="E25" s="94" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="F25" s="94" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="G25" s="94" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="H25" s="94" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="I25" s="94" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="J25" s="94" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="K25" s="94" t="n">
+        <v>52.09</v>
+      </c>
+      <c r="L25" s="94" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="M25" s="94" t="n">
+        <v>76.02</v>
+      </c>
+      <c r="N25" s="94" t="n">
+        <v>74.91</v>
+      </c>
+      <c r="O25" s="94" t="n">
+        <v>66.62</v>
+      </c>
+      <c r="P25" s="94" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="Q25" s="94" t="n">
+        <v>92.18000000000001</v>
+      </c>
+      <c r="R25" s="94" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="S25" s="94" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="T25" s="94" t="n">
+        <v>87.58</v>
+      </c>
+      <c r="U25" s="94" t="n">
+        <v>65.31</v>
+      </c>
+      <c r="V25" s="94" t="n">
+        <v>85.48999999999999</v>
+      </c>
+      <c r="W25" s="94" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="X25" s="94" t="n">
         <v>82.94</v>
       </c>
-      <c r="F25" s="94" t="n">
-        <v>66.56</v>
-      </c>
-      <c r="G25" s="94" t="n">
-        <v>73.18000000000001</v>
-      </c>
-      <c r="H25" s="94" t="n">
-        <v>46.98</v>
-      </c>
-      <c r="I25" s="94" t="n">
-        <v>34.52</v>
-      </c>
-      <c r="J25" s="94" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="K25" s="94" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="L25" s="94" t="n">
-        <v>28.19</v>
-      </c>
-      <c r="M25" s="94" t="n">
-        <v>52.09</v>
-      </c>
-      <c r="N25" s="94" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="O25" s="94" t="n">
-        <v>76.02</v>
-      </c>
-      <c r="P25" s="94" t="n">
-        <v>74.91</v>
-      </c>
-      <c r="Q25" s="94" t="n">
-        <v>74.91</v>
-      </c>
-      <c r="R25" s="94" t="n">
-        <v>66.62</v>
-      </c>
-      <c r="S25" s="94" t="n">
-        <v>42.84</v>
-      </c>
-      <c r="T25" s="94" t="n">
-        <v>92.18000000000001</v>
-      </c>
-      <c r="U25" s="94" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="V25" s="94" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="W25" s="94" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="X25" s="94" t="n">
-        <v>87.58</v>
-      </c>
       <c r="Y25" s="94" t="n">
-        <v>65.31</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="Z25" s="94" t="n">
-        <v>85.48999999999999</v>
+        <v>56.57</v>
       </c>
       <c r="AA25" s="94" t="n">
-        <v>88.3</v>
+        <v>46.45</v>
       </c>
       <c r="AB25" s="94" t="n">
-        <v>82.94</v>
+        <v>52.5</v>
       </c>
       <c r="AC25" s="94" t="n">
-        <v>82.94</v>
+        <v>13.02</v>
       </c>
       <c r="AD25" s="94" t="n">
-        <v>71.68000000000001</v>
+        <v>24.55</v>
       </c>
       <c r="AE25" s="94" t="n">
-        <v>56.57</v>
+        <v>35.87</v>
       </c>
     </row>
     <row r="26">
@@ -9184,154 +9185,154 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="92" t="inlineStr">
+      <c r="B26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="C26" s="92" t="inlineStr">
+      <c r="D26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D26" s="92" t="inlineStr">
+      <c r="E26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E26" s="92" t="inlineStr">
+      <c r="F26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F26" s="92" t="inlineStr">
+      <c r="G26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G26" s="92" t="inlineStr">
+      <c r="H26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H26" s="92" t="inlineStr">
+      <c r="J26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I26" s="93" t="inlineStr">
+      <c r="P26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AB26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="M26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="AC26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -9342,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>4.38</v>
+        <v>1.71</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>4.38</v>
@@ -9351,85 +9352,85 @@
         <v>2.64</v>
       </c>
       <c r="E27" s="94" t="n">
-        <v>2.64</v>
+        <v>1.58</v>
       </c>
       <c r="F27" s="94" t="n">
-        <v>1.58</v>
+        <v>-1.18</v>
       </c>
       <c r="G27" s="94" t="n">
-        <v>-1.18</v>
+        <v>-1.57</v>
       </c>
       <c r="H27" s="94" t="n">
-        <v>-1.57</v>
+        <v>-2.58</v>
       </c>
       <c r="I27" s="94" t="n">
-        <v>-2.58</v>
+        <v>-0.8</v>
       </c>
       <c r="J27" s="94" t="n">
-        <v>-0.8</v>
+        <v>-3.91</v>
       </c>
       <c r="K27" s="94" t="n">
-        <v>-0.8</v>
+        <v>-2.74</v>
       </c>
       <c r="L27" s="94" t="n">
-        <v>-3.91</v>
+        <v>-2.68</v>
       </c>
       <c r="M27" s="94" t="n">
-        <v>-2.74</v>
+        <v>-0.89</v>
       </c>
       <c r="N27" s="94" t="n">
-        <v>-2.68</v>
+        <v>-0.38</v>
       </c>
       <c r="O27" s="94" t="n">
-        <v>-0.89</v>
+        <v>0.9</v>
       </c>
       <c r="P27" s="94" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Q27" s="94" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R27" s="94" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="S27" s="94" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T27" s="94" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U27" s="94" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="V27" s="94" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="W27" s="94" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="X27" s="94" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y27" s="94" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="Z27" s="94" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="AA27" s="94" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="AB27" s="94" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="AC27" s="94" t="n">
+        <v>-3.76</v>
+      </c>
+      <c r="AD27" s="94" t="n">
         <v>-0.38</v>
       </c>
-      <c r="Q27" s="94" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="R27" s="94" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="S27" s="94" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="T27" s="94" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="U27" s="94" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="V27" s="94" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W27" s="94" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="X27" s="94" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Y27" s="94" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="Z27" s="94" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="AA27" s="94" t="n">
-        <v>-0.73</v>
-      </c>
-      <c r="AB27" s="94" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC27" s="94" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD27" s="94" t="n">
-        <v>-1.61</v>
-      </c>
       <c r="AE27" s="94" t="n">
-        <v>-1.66</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="28">
@@ -9439,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>17.88</v>
+        <v>16.57</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>17.88</v>
@@ -9448,95 +9449,95 @@
         <v>18.71</v>
       </c>
       <c r="E28" s="94" t="n">
-        <v>18.71</v>
+        <v>19.63</v>
       </c>
       <c r="F28" s="94" t="n">
-        <v>19.63</v>
+        <v>17.24</v>
       </c>
       <c r="G28" s="94" t="n">
-        <v>17.24</v>
+        <v>15.94</v>
       </c>
       <c r="H28" s="94" t="n">
-        <v>15.94</v>
+        <v>12.98</v>
       </c>
       <c r="I28" s="94" t="n">
-        <v>12.98</v>
+        <v>14.18</v>
       </c>
       <c r="J28" s="94" t="n">
-        <v>14.18</v>
+        <v>10.78</v>
       </c>
       <c r="K28" s="94" t="n">
-        <v>14.18</v>
+        <v>9.02</v>
       </c>
       <c r="L28" s="94" t="n">
-        <v>10.78</v>
+        <v>10.76</v>
       </c>
       <c r="M28" s="94" t="n">
-        <v>9.02</v>
+        <v>11.54</v>
       </c>
       <c r="N28" s="94" t="n">
-        <v>10.76</v>
+        <v>11.48</v>
       </c>
       <c r="O28" s="94" t="n">
-        <v>11.54</v>
+        <v>11.95</v>
       </c>
       <c r="P28" s="94" t="n">
-        <v>11.48</v>
+        <v>12.67</v>
       </c>
       <c r="Q28" s="94" t="n">
-        <v>11.48</v>
+        <v>11.04</v>
       </c>
       <c r="R28" s="94" t="n">
-        <v>11.95</v>
+        <v>10.68</v>
       </c>
       <c r="S28" s="94" t="n">
-        <v>12.67</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="T28" s="94" t="n">
-        <v>11.04</v>
+        <v>9.98</v>
       </c>
       <c r="U28" s="94" t="n">
-        <v>10.68</v>
+        <v>7.16</v>
       </c>
       <c r="V28" s="94" t="n">
-        <v>9.460000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="W28" s="94" t="n">
-        <v>9.460000000000001</v>
+        <v>7.37</v>
       </c>
       <c r="X28" s="94" t="n">
-        <v>9.98</v>
+        <v>7.64</v>
       </c>
       <c r="Y28" s="94" t="n">
-        <v>7.16</v>
+        <v>7.12</v>
       </c>
       <c r="Z28" s="94" t="n">
-        <v>8.039999999999999</v>
+        <v>6.27</v>
       </c>
       <c r="AA28" s="94" t="n">
-        <v>7.37</v>
+        <v>5.31</v>
       </c>
       <c r="AB28" s="94" t="n">
-        <v>7.64</v>
+        <v>4.85</v>
       </c>
       <c r="AC28" s="94" t="n">
-        <v>7.64</v>
+        <v>4.49</v>
       </c>
       <c r="AD28" s="94" t="n">
-        <v>7.12</v>
+        <v>6.19</v>
       </c>
       <c r="AE28" s="94" t="n">
-        <v>6.27</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="76" t="inlineStr">
+      <c r="A29" s="96" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>95.84</v>
+        <v>36.8</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>95.84</v>
@@ -9545,85 +9546,85 @@
         <v>86.79000000000001</v>
       </c>
       <c r="E29" s="94" t="n">
-        <v>86.79000000000001</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="F29" s="94" t="n">
-        <v>77.45999999999999</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="G29" s="94" t="n">
-        <v>82.01000000000001</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="H29" s="94" t="n">
-        <v>72.98999999999999</v>
+        <v>32.92</v>
       </c>
       <c r="I29" s="94" t="n">
-        <v>32.92</v>
+        <v>85.03</v>
       </c>
       <c r="J29" s="94" t="n">
-        <v>85.03</v>
+        <v>20.54</v>
       </c>
       <c r="K29" s="94" t="n">
-        <v>85.03</v>
+        <v>21.97</v>
       </c>
       <c r="L29" s="94" t="n">
-        <v>20.54</v>
+        <v>15.42</v>
       </c>
       <c r="M29" s="94" t="n">
-        <v>21.97</v>
+        <v>74.7</v>
       </c>
       <c r="N29" s="94" t="n">
-        <v>15.42</v>
+        <v>51.35</v>
       </c>
       <c r="O29" s="94" t="n">
-        <v>74.7</v>
+        <v>96.66</v>
       </c>
       <c r="P29" s="94" t="n">
-        <v>51.35</v>
+        <v>89.75</v>
       </c>
       <c r="Q29" s="94" t="n">
-        <v>51.35</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="R29" s="94" t="n">
-        <v>96.66</v>
+        <v>77.02</v>
       </c>
       <c r="S29" s="94" t="n">
-        <v>89.75</v>
+        <v>73.3</v>
       </c>
       <c r="T29" s="94" t="n">
-        <v>88.93000000000001</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="U29" s="94" t="n">
-        <v>77.02</v>
+        <v>42.32</v>
       </c>
       <c r="V29" s="94" t="n">
-        <v>73.3</v>
+        <v>70.06</v>
       </c>
       <c r="W29" s="94" t="n">
-        <v>73.3</v>
+        <v>61.86</v>
       </c>
       <c r="X29" s="94" t="n">
-        <v>92.18000000000001</v>
+        <v>95.17</v>
       </c>
       <c r="Y29" s="94" t="n">
-        <v>42.32</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="Z29" s="94" t="n">
-        <v>70.06</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="AA29" s="94" t="n">
-        <v>61.86</v>
+        <v>65.19</v>
       </c>
       <c r="AB29" s="94" t="n">
-        <v>95.17</v>
+        <v>44.48</v>
       </c>
       <c r="AC29" s="94" t="n">
-        <v>95.17</v>
+        <v>6.2</v>
       </c>
       <c r="AD29" s="94" t="n">
-        <v>92.73999999999999</v>
+        <v>27.81</v>
       </c>
       <c r="AE29" s="94" t="n">
-        <v>88.20999999999999</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="30">
@@ -9647,134 +9648,134 @@
           <t>red</t>
         </is>
       </c>
-      <c r="E30" s="92" t="inlineStr">
+      <c r="E30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F30" s="91" t="inlineStr">
+      <c r="I30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G30" s="91" t="inlineStr">
+      <c r="J30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H30" s="91" t="inlineStr">
+      <c r="K30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I30" s="92" t="inlineStr">
+      <c r="M30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J30" s="91" t="inlineStr">
+      <c r="O30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K30" s="91" t="inlineStr">
+      <c r="V30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L30" s="91" t="inlineStr">
+      <c r="W30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M30" s="93" t="inlineStr">
+      <c r="X30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Z30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="AA30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="AE30" s="93" t="inlineStr">
@@ -9799,85 +9800,85 @@
         <v>-1.3</v>
       </c>
       <c r="E31" s="94" t="n">
-        <v>-1.3</v>
+        <v>-4.18</v>
       </c>
       <c r="F31" s="94" t="n">
-        <v>-4.18</v>
+        <v>-4.84</v>
       </c>
       <c r="G31" s="94" t="n">
-        <v>-4.84</v>
+        <v>-5.47</v>
       </c>
       <c r="H31" s="94" t="n">
-        <v>-5.47</v>
+        <v>-6.85</v>
       </c>
       <c r="I31" s="94" t="n">
-        <v>-6.85</v>
+        <v>-7.64</v>
       </c>
       <c r="J31" s="94" t="n">
-        <v>-7.64</v>
+        <v>-7.28</v>
       </c>
       <c r="K31" s="94" t="n">
-        <v>-7.64</v>
+        <v>-7.29</v>
       </c>
       <c r="L31" s="94" t="n">
-        <v>-7.28</v>
+        <v>-5.52</v>
       </c>
       <c r="M31" s="94" t="n">
-        <v>-7.29</v>
+        <v>-7.32</v>
       </c>
       <c r="N31" s="94" t="n">
-        <v>-5.52</v>
+        <v>-1.85</v>
       </c>
       <c r="O31" s="94" t="n">
-        <v>-7.32</v>
+        <v>-2.87</v>
       </c>
       <c r="P31" s="94" t="n">
-        <v>-1.85</v>
+        <v>-4.44</v>
       </c>
       <c r="Q31" s="94" t="n">
-        <v>-1.85</v>
+        <v>-4.15</v>
       </c>
       <c r="R31" s="94" t="n">
-        <v>-2.87</v>
+        <v>-4.11</v>
       </c>
       <c r="S31" s="94" t="n">
-        <v>-4.44</v>
+        <v>-4.11</v>
       </c>
       <c r="T31" s="94" t="n">
-        <v>-4.15</v>
+        <v>-6.33</v>
       </c>
       <c r="U31" s="94" t="n">
-        <v>-4.11</v>
+        <v>-7.13</v>
       </c>
       <c r="V31" s="94" t="n">
-        <v>-4.11</v>
+        <v>-6.7</v>
       </c>
       <c r="W31" s="94" t="n">
-        <v>-4.11</v>
+        <v>-5.28</v>
       </c>
       <c r="X31" s="94" t="n">
-        <v>-6.33</v>
+        <v>-5.31</v>
       </c>
       <c r="Y31" s="94" t="n">
-        <v>-7.13</v>
+        <v>-4.5</v>
       </c>
       <c r="Z31" s="94" t="n">
+        <v>-7.44</v>
+      </c>
+      <c r="AA31" s="94" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="AB31" s="94" t="n">
         <v>-6.7</v>
       </c>
-      <c r="AA31" s="94" t="n">
-        <v>-5.28</v>
-      </c>
-      <c r="AB31" s="94" t="n">
-        <v>-5.31</v>
-      </c>
       <c r="AC31" s="94" t="n">
-        <v>-5.31</v>
+        <v>-6.01</v>
       </c>
       <c r="AD31" s="94" t="n">
-        <v>-4.5</v>
+        <v>-5.71</v>
       </c>
       <c r="AE31" s="94" t="n">
-        <v>-7.44</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="32">
@@ -9896,85 +9897,85 @@
         <v>6.85</v>
       </c>
       <c r="E32" s="94" t="n">
-        <v>6.85</v>
+        <v>3.42</v>
       </c>
       <c r="F32" s="94" t="n">
-        <v>3.42</v>
+        <v>3.47</v>
       </c>
       <c r="G32" s="94" t="n">
-        <v>3.47</v>
+        <v>1.21</v>
       </c>
       <c r="H32" s="94" t="n">
-        <v>1.21</v>
+        <v>0.25</v>
       </c>
       <c r="I32" s="94" t="n">
-        <v>0.25</v>
+        <v>-2.25</v>
       </c>
       <c r="J32" s="94" t="n">
-        <v>-2.25</v>
+        <v>-2.26</v>
       </c>
       <c r="K32" s="94" t="n">
-        <v>-2.25</v>
+        <v>-4.48</v>
       </c>
       <c r="L32" s="94" t="n">
-        <v>-2.26</v>
+        <v>-2.82</v>
       </c>
       <c r="M32" s="94" t="n">
-        <v>-4.48</v>
+        <v>-3.63</v>
       </c>
       <c r="N32" s="94" t="n">
-        <v>-2.82</v>
+        <v>2.15</v>
       </c>
       <c r="O32" s="94" t="n">
-        <v>-3.63</v>
+        <v>-2.13</v>
       </c>
       <c r="P32" s="94" t="n">
-        <v>2.15</v>
+        <v>-4.01</v>
       </c>
       <c r="Q32" s="94" t="n">
-        <v>2.15</v>
+        <v>-4.76</v>
       </c>
       <c r="R32" s="94" t="n">
-        <v>-2.13</v>
+        <v>-5.22</v>
       </c>
       <c r="S32" s="94" t="n">
-        <v>-4.01</v>
+        <v>-5.22</v>
       </c>
       <c r="T32" s="94" t="n">
-        <v>-4.76</v>
+        <v>-7.96</v>
       </c>
       <c r="U32" s="94" t="n">
-        <v>-5.22</v>
+        <v>-9.43</v>
       </c>
       <c r="V32" s="94" t="n">
-        <v>-5.22</v>
+        <v>-11.19</v>
       </c>
       <c r="W32" s="94" t="n">
-        <v>-5.22</v>
+        <v>-9.5</v>
       </c>
       <c r="X32" s="94" t="n">
-        <v>-7.96</v>
+        <v>-9.48</v>
       </c>
       <c r="Y32" s="94" t="n">
-        <v>-9.43</v>
+        <v>-9.92</v>
       </c>
       <c r="Z32" s="94" t="n">
-        <v>-11.19</v>
+        <v>-12.73</v>
       </c>
       <c r="AA32" s="94" t="n">
-        <v>-9.5</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="AB32" s="94" t="n">
-        <v>-9.48</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="AC32" s="94" t="n">
-        <v>-9.48</v>
+        <v>-5.98</v>
       </c>
       <c r="AD32" s="94" t="n">
-        <v>-9.92</v>
+        <v>-5.54</v>
       </c>
       <c r="AE32" s="94" t="n">
-        <v>-12.73</v>
+        <v>-4.26</v>
       </c>
     </row>
     <row r="33">
@@ -9993,85 +9994,85 @@
         <v>63.24</v>
       </c>
       <c r="E33" s="94" t="n">
-        <v>63.24</v>
+        <v>61.28</v>
       </c>
       <c r="F33" s="94" t="n">
-        <v>61.28</v>
+        <v>60.41</v>
       </c>
       <c r="G33" s="94" t="n">
-        <v>60.41</v>
+        <v>57.64</v>
       </c>
       <c r="H33" s="94" t="n">
-        <v>57.64</v>
+        <v>62.13</v>
       </c>
       <c r="I33" s="94" t="n">
-        <v>62.13</v>
+        <v>56.86</v>
       </c>
       <c r="J33" s="94" t="n">
-        <v>56.86</v>
+        <v>56.21</v>
       </c>
       <c r="K33" s="94" t="n">
-        <v>56.86</v>
+        <v>50.28</v>
       </c>
       <c r="L33" s="94" t="n">
-        <v>56.21</v>
+        <v>58.22</v>
       </c>
       <c r="M33" s="94" t="n">
-        <v>50.28</v>
+        <v>52.42</v>
       </c>
       <c r="N33" s="94" t="n">
-        <v>58.22</v>
+        <v>77.31</v>
       </c>
       <c r="O33" s="94" t="n">
-        <v>52.42</v>
+        <v>71.64</v>
       </c>
       <c r="P33" s="94" t="n">
-        <v>77.31</v>
+        <v>61.74</v>
       </c>
       <c r="Q33" s="94" t="n">
-        <v>77.31</v>
+        <v>63.04</v>
       </c>
       <c r="R33" s="94" t="n">
-        <v>71.64</v>
+        <v>60.77</v>
       </c>
       <c r="S33" s="94" t="n">
-        <v>61.74</v>
+        <v>60.77</v>
       </c>
       <c r="T33" s="94" t="n">
-        <v>63.04</v>
+        <v>54.21</v>
       </c>
       <c r="U33" s="94" t="n">
-        <v>60.77</v>
+        <v>42.56</v>
       </c>
       <c r="V33" s="94" t="n">
-        <v>60.77</v>
+        <v>39.44</v>
       </c>
       <c r="W33" s="94" t="n">
-        <v>60.77</v>
+        <v>43.68</v>
       </c>
       <c r="X33" s="94" t="n">
-        <v>54.21</v>
+        <v>43.96</v>
       </c>
       <c r="Y33" s="94" t="n">
-        <v>42.56</v>
+        <v>46.79</v>
       </c>
       <c r="Z33" s="94" t="n">
-        <v>39.44</v>
+        <v>26.47</v>
       </c>
       <c r="AA33" s="94" t="n">
-        <v>43.68</v>
+        <v>31.18</v>
       </c>
       <c r="AB33" s="94" t="n">
-        <v>43.96</v>
+        <v>31.7</v>
       </c>
       <c r="AC33" s="94" t="n">
-        <v>43.96</v>
+        <v>33.25</v>
       </c>
       <c r="AD33" s="94" t="n">
-        <v>46.79</v>
+        <v>35.58</v>
       </c>
       <c r="AE33" s="94" t="n">
-        <v>26.47</v>
+        <v>39.17</v>
       </c>
     </row>
     <row r="34">
@@ -10080,154 +10081,154 @@
           <t>vn:EIDE</t>
         </is>
       </c>
-      <c r="B34" s="92" t="inlineStr">
+      <c r="B34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="C34" s="92" t="inlineStr">
+      <c r="D34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D34" s="92" t="inlineStr">
+      <c r="E34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E34" s="92" t="inlineStr">
+      <c r="F34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F34" s="92" t="inlineStr">
+      <c r="G34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G34" s="92" t="inlineStr">
+      <c r="O34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H34" s="93" t="inlineStr">
+      <c r="P34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I34" s="93" t="inlineStr">
+      <c r="X34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J34" s="93" t="inlineStr">
+      <c r="Y34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K34" s="93" t="inlineStr">
+      <c r="Z34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L34" s="93" t="inlineStr">
+      <c r="AA34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M34" s="91" t="inlineStr">
+      <c r="AB34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N34" s="91" t="inlineStr">
+      <c r="AD34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="O34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -10238,7 +10239,7 @@
         </is>
       </c>
       <c r="B35" s="94" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="C35" s="94" t="n">
         <v>0.93</v>
@@ -10247,85 +10248,85 @@
         <v>1.56</v>
       </c>
       <c r="E35" s="94" t="n">
-        <v>1.56</v>
+        <v>0.4</v>
       </c>
       <c r="F35" s="94" t="n">
-        <v>0.4</v>
+        <v>0.16</v>
       </c>
       <c r="G35" s="94" t="n">
-        <v>0.16</v>
+        <v>-0.68</v>
       </c>
       <c r="H35" s="94" t="n">
-        <v>-0.68</v>
+        <v>-1.08</v>
       </c>
       <c r="I35" s="94" t="n">
-        <v>-1.08</v>
+        <v>-1.19</v>
       </c>
       <c r="J35" s="94" t="n">
-        <v>-1.19</v>
+        <v>-1.21</v>
       </c>
       <c r="K35" s="94" t="n">
-        <v>-1.19</v>
+        <v>0.33</v>
       </c>
       <c r="L35" s="94" t="n">
-        <v>-1.21</v>
+        <v>0.71</v>
       </c>
       <c r="M35" s="94" t="n">
-        <v>0.33</v>
+        <v>0.63</v>
       </c>
       <c r="N35" s="94" t="n">
-        <v>0.71</v>
+        <v>1.1</v>
       </c>
       <c r="O35" s="94" t="n">
-        <v>0.63</v>
+        <v>1.71</v>
       </c>
       <c r="P35" s="94" t="n">
-        <v>1.1</v>
+        <v>2.62</v>
       </c>
       <c r="Q35" s="94" t="n">
-        <v>1.1</v>
+        <v>1.79</v>
       </c>
       <c r="R35" s="94" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="S35" s="94" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="T35" s="94" t="n">
-        <v>1.79</v>
+        <v>0.8</v>
       </c>
       <c r="U35" s="94" t="n">
-        <v>1.86</v>
+        <v>0.66</v>
       </c>
       <c r="V35" s="94" t="n">
-        <v>1.03</v>
+        <v>0.39</v>
       </c>
       <c r="W35" s="94" t="n">
-        <v>1.03</v>
+        <v>-3.34</v>
       </c>
       <c r="X35" s="94" t="n">
-        <v>0.8</v>
+        <v>-2.39</v>
       </c>
       <c r="Y35" s="94" t="n">
-        <v>0.66</v>
+        <v>-1.83</v>
       </c>
       <c r="Z35" s="94" t="n">
-        <v>0.39</v>
+        <v>-2.05</v>
       </c>
       <c r="AA35" s="94" t="n">
-        <v>-3.34</v>
+        <v>-1.53</v>
       </c>
       <c r="AB35" s="94" t="n">
-        <v>-2.39</v>
+        <v>-0.95</v>
       </c>
       <c r="AC35" s="94" t="n">
-        <v>-2.39</v>
+        <v>-2.12</v>
       </c>
       <c r="AD35" s="94" t="n">
-        <v>-1.83</v>
+        <v>-2.46</v>
       </c>
       <c r="AE35" s="94" t="n">
-        <v>-2.05</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="36">
@@ -10335,7 +10336,7 @@
         </is>
       </c>
       <c r="B36" s="94" t="n">
-        <v>6.7</v>
+        <v>6.26</v>
       </c>
       <c r="C36" s="94" t="n">
         <v>9.25</v>
@@ -10344,85 +10345,85 @@
         <v>8.25</v>
       </c>
       <c r="E36" s="94" t="n">
-        <v>8.25</v>
+        <v>9.49</v>
       </c>
       <c r="F36" s="94" t="n">
-        <v>9.49</v>
+        <v>7.45</v>
       </c>
       <c r="G36" s="94" t="n">
-        <v>7.45</v>
+        <v>4.63</v>
       </c>
       <c r="H36" s="94" t="n">
-        <v>4.63</v>
+        <v>4.38</v>
       </c>
       <c r="I36" s="94" t="n">
-        <v>4.38</v>
+        <v>-0.47</v>
       </c>
       <c r="J36" s="94" t="n">
-        <v>-0.47</v>
+        <v>1.58</v>
       </c>
       <c r="K36" s="94" t="n">
-        <v>-0.47</v>
+        <v>2.33</v>
       </c>
       <c r="L36" s="94" t="n">
-        <v>1.58</v>
+        <v>2.33</v>
       </c>
       <c r="M36" s="94" t="n">
-        <v>2.33</v>
+        <v>3.01</v>
       </c>
       <c r="N36" s="94" t="n">
-        <v>2.33</v>
+        <v>2.85</v>
       </c>
       <c r="O36" s="94" t="n">
-        <v>3.01</v>
+        <v>1.83</v>
       </c>
       <c r="P36" s="94" t="n">
-        <v>2.85</v>
+        <v>1.26</v>
       </c>
       <c r="Q36" s="94" t="n">
-        <v>2.85</v>
+        <v>-0.78</v>
       </c>
       <c r="R36" s="94" t="n">
-        <v>1.83</v>
+        <v>-1.02</v>
       </c>
       <c r="S36" s="94" t="n">
-        <v>1.26</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="T36" s="94" t="n">
-        <v>-0.78</v>
+        <v>-1.47</v>
       </c>
       <c r="U36" s="94" t="n">
-        <v>-1.02</v>
+        <v>-1.42</v>
       </c>
       <c r="V36" s="94" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.81</v>
       </c>
       <c r="W36" s="94" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.26</v>
       </c>
       <c r="X36" s="94" t="n">
-        <v>-1.47</v>
+        <v>-2.35</v>
       </c>
       <c r="Y36" s="94" t="n">
-        <v>-1.42</v>
+        <v>-1.57</v>
       </c>
       <c r="Z36" s="94" t="n">
-        <v>-1.81</v>
+        <v>-0.54</v>
       </c>
       <c r="AA36" s="94" t="n">
-        <v>-2.26</v>
+        <v>1.03</v>
       </c>
       <c r="AB36" s="94" t="n">
-        <v>-2.35</v>
+        <v>1.94</v>
       </c>
       <c r="AC36" s="94" t="n">
-        <v>-2.35</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AD36" s="94" t="n">
-        <v>-1.57</v>
+        <v>0.31</v>
       </c>
       <c r="AE36" s="94" t="n">
-        <v>-0.54</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="37">
@@ -10432,7 +10433,7 @@
         </is>
       </c>
       <c r="B37" s="94" t="n">
-        <v>65.67</v>
+        <v>37.61</v>
       </c>
       <c r="C37" s="94" t="n">
         <v>65.76000000000001</v>
@@ -10441,85 +10442,85 @@
         <v>81.64</v>
       </c>
       <c r="E37" s="94" t="n">
-        <v>81.64</v>
+        <v>78.16</v>
       </c>
       <c r="F37" s="94" t="n">
-        <v>78.16</v>
+        <v>69.63</v>
       </c>
       <c r="G37" s="94" t="n">
-        <v>69.63</v>
+        <v>29.45</v>
       </c>
       <c r="H37" s="94" t="n">
-        <v>29.45</v>
+        <v>13.62</v>
       </c>
       <c r="I37" s="94" t="n">
-        <v>13.62</v>
+        <v>14.32</v>
       </c>
       <c r="J37" s="94" t="n">
-        <v>14.32</v>
+        <v>23.23</v>
       </c>
       <c r="K37" s="94" t="n">
-        <v>14.32</v>
+        <v>50.34</v>
       </c>
       <c r="L37" s="94" t="n">
-        <v>23.23</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="M37" s="94" t="n">
-        <v>50.34</v>
+        <v>65.09</v>
       </c>
       <c r="N37" s="94" t="n">
-        <v>77.23999999999999</v>
+        <v>86.66</v>
       </c>
       <c r="O37" s="94" t="n">
-        <v>65.09</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="P37" s="94" t="n">
-        <v>86.66</v>
+        <v>88</v>
       </c>
       <c r="Q37" s="94" t="n">
-        <v>86.66</v>
+        <v>77.98</v>
       </c>
       <c r="R37" s="94" t="n">
-        <v>90.48999999999999</v>
+        <v>59.82</v>
       </c>
       <c r="S37" s="94" t="n">
-        <v>88</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="T37" s="94" t="n">
-        <v>77.98</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="U37" s="94" t="n">
-        <v>59.82</v>
+        <v>68.98</v>
       </c>
       <c r="V37" s="94" t="n">
-        <v>77.68000000000001</v>
+        <v>60.96</v>
       </c>
       <c r="W37" s="94" t="n">
-        <v>77.68000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="X37" s="94" t="n">
-        <v>76.68000000000001</v>
+        <v>20.58</v>
       </c>
       <c r="Y37" s="94" t="n">
-        <v>68.98</v>
+        <v>30.12</v>
       </c>
       <c r="Z37" s="94" t="n">
-        <v>60.96</v>
+        <v>12.08</v>
       </c>
       <c r="AA37" s="94" t="n">
-        <v>9.050000000000001</v>
+        <v>13.57</v>
       </c>
       <c r="AB37" s="94" t="n">
-        <v>20.58</v>
+        <v>28.44</v>
       </c>
       <c r="AC37" s="94" t="n">
-        <v>20.58</v>
+        <v>44.72</v>
       </c>
       <c r="AD37" s="94" t="n">
-        <v>30.12</v>
+        <v>14.66</v>
       </c>
       <c r="AE37" s="94" t="n">
-        <v>12.08</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="38">
@@ -10548,134 +10549,134 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="F38" s="91" t="inlineStr">
+      <c r="F38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G38" s="93" t="inlineStr">
+      <c r="L38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H38" s="93" t="inlineStr">
+      <c r="AA38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AB38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I38" s="93" t="inlineStr">
+      <c r="AC38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J38" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="K38" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="L38" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="M38" s="91" t="inlineStr">
+      <c r="AD38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N38" s="91" t="inlineStr">
+      <c r="AE38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="O38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE38" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -10686,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>1.7</v>
@@ -10695,85 +10696,85 @@
         <v>0.05</v>
       </c>
       <c r="E39" s="94" t="n">
-        <v>0.05</v>
+        <v>1.11</v>
       </c>
       <c r="F39" s="94" t="n">
-        <v>1.11</v>
+        <v>0.99</v>
       </c>
       <c r="G39" s="94" t="n">
-        <v>0.99</v>
+        <v>1.39</v>
       </c>
       <c r="H39" s="94" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="I39" s="94" t="n">
-        <v>1.44</v>
+        <v>2.21</v>
       </c>
       <c r="J39" s="94" t="n">
-        <v>2.21</v>
+        <v>2.67</v>
       </c>
       <c r="K39" s="94" t="n">
-        <v>2.21</v>
+        <v>5.39</v>
       </c>
       <c r="L39" s="94" t="n">
-        <v>2.67</v>
+        <v>5.39</v>
       </c>
       <c r="M39" s="94" t="n">
-        <v>5.39</v>
+        <v>5.38</v>
       </c>
       <c r="N39" s="94" t="n">
-        <v>5.39</v>
+        <v>6.9</v>
       </c>
       <c r="O39" s="94" t="n">
-        <v>5.38</v>
+        <v>7.31</v>
       </c>
       <c r="P39" s="94" t="n">
-        <v>6.9</v>
+        <v>7.21</v>
       </c>
       <c r="Q39" s="94" t="n">
-        <v>6.9</v>
+        <v>6.84</v>
       </c>
       <c r="R39" s="94" t="n">
-        <v>7.31</v>
+        <v>7.46</v>
       </c>
       <c r="S39" s="94" t="n">
-        <v>7.21</v>
+        <v>6.69</v>
       </c>
       <c r="T39" s="94" t="n">
-        <v>6.84</v>
+        <v>5.73</v>
       </c>
       <c r="U39" s="94" t="n">
-        <v>7.46</v>
+        <v>6.27</v>
       </c>
       <c r="V39" s="94" t="n">
-        <v>6.69</v>
+        <v>7.42</v>
       </c>
       <c r="W39" s="94" t="n">
-        <v>6.69</v>
+        <v>7.48</v>
       </c>
       <c r="X39" s="94" t="n">
-        <v>5.73</v>
+        <v>6.99</v>
       </c>
       <c r="Y39" s="94" t="n">
-        <v>6.27</v>
+        <v>7.27</v>
       </c>
       <c r="Z39" s="94" t="n">
-        <v>7.42</v>
+        <v>5.46</v>
       </c>
       <c r="AA39" s="94" t="n">
-        <v>7.48</v>
+        <v>6.4</v>
       </c>
       <c r="AB39" s="94" t="n">
-        <v>6.99</v>
+        <v>6.18</v>
       </c>
       <c r="AC39" s="94" t="n">
-        <v>6.99</v>
+        <v>5.98</v>
       </c>
       <c r="AD39" s="94" t="n">
-        <v>7.27</v>
+        <v>7.51</v>
       </c>
       <c r="AE39" s="94" t="n">
-        <v>5.46</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="40">
@@ -10783,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>10.75</v>
+        <v>10.79</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>11.17</v>
@@ -10792,85 +10793,85 @@
         <v>10.5</v>
       </c>
       <c r="E40" s="94" t="n">
-        <v>10.5</v>
+        <v>11.66</v>
       </c>
       <c r="F40" s="94" t="n">
-        <v>11.66</v>
+        <v>12.39</v>
       </c>
       <c r="G40" s="94" t="n">
-        <v>12.39</v>
+        <v>11.91</v>
       </c>
       <c r="H40" s="94" t="n">
-        <v>11.91</v>
+        <v>10.42</v>
       </c>
       <c r="I40" s="94" t="n">
-        <v>10.42</v>
+        <v>10.03</v>
       </c>
       <c r="J40" s="94" t="n">
-        <v>10.03</v>
+        <v>9.94</v>
       </c>
       <c r="K40" s="94" t="n">
-        <v>10.03</v>
+        <v>12.83</v>
       </c>
       <c r="L40" s="94" t="n">
-        <v>9.94</v>
+        <v>12.83</v>
       </c>
       <c r="M40" s="94" t="n">
-        <v>12.83</v>
+        <v>12.79</v>
       </c>
       <c r="N40" s="94" t="n">
-        <v>12.83</v>
+        <v>15.25</v>
       </c>
       <c r="O40" s="94" t="n">
-        <v>12.79</v>
+        <v>15.64</v>
       </c>
       <c r="P40" s="94" t="n">
-        <v>15.25</v>
+        <v>15.29</v>
       </c>
       <c r="Q40" s="94" t="n">
-        <v>15.25</v>
+        <v>14.9</v>
       </c>
       <c r="R40" s="94" t="n">
-        <v>15.64</v>
+        <v>14.75</v>
       </c>
       <c r="S40" s="94" t="n">
-        <v>15.29</v>
+        <v>14.79</v>
       </c>
       <c r="T40" s="94" t="n">
-        <v>14.9</v>
+        <v>13.96</v>
       </c>
       <c r="U40" s="94" t="n">
-        <v>14.75</v>
+        <v>14.46</v>
       </c>
       <c r="V40" s="94" t="n">
-        <v>14.79</v>
+        <v>14.07</v>
       </c>
       <c r="W40" s="94" t="n">
-        <v>14.79</v>
+        <v>14.24</v>
       </c>
       <c r="X40" s="94" t="n">
-        <v>13.96</v>
+        <v>14.96</v>
       </c>
       <c r="Y40" s="94" t="n">
-        <v>14.46</v>
+        <v>15.21</v>
       </c>
       <c r="Z40" s="94" t="n">
-        <v>14.07</v>
+        <v>12.06</v>
       </c>
       <c r="AA40" s="94" t="n">
-        <v>14.24</v>
+        <v>12.77</v>
       </c>
       <c r="AB40" s="94" t="n">
-        <v>14.96</v>
+        <v>11.58</v>
       </c>
       <c r="AC40" s="94" t="n">
-        <v>14.96</v>
+        <v>11.57</v>
       </c>
       <c r="AD40" s="94" t="n">
-        <v>15.21</v>
+        <v>11.58</v>
       </c>
       <c r="AE40" s="94" t="n">
-        <v>12.06</v>
+        <v>12.04</v>
       </c>
     </row>
     <row r="41">
@@ -10880,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>41.77</v>
+        <v>42.03</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>43.48</v>
@@ -10889,85 +10890,85 @@
         <v>35.77</v>
       </c>
       <c r="E41" s="94" t="n">
-        <v>35.77</v>
+        <v>37.56</v>
       </c>
       <c r="F41" s="94" t="n">
-        <v>37.56</v>
+        <v>35.74</v>
       </c>
       <c r="G41" s="94" t="n">
-        <v>35.74</v>
+        <v>36.86</v>
       </c>
       <c r="H41" s="94" t="n">
-        <v>36.86</v>
+        <v>29.96</v>
       </c>
       <c r="I41" s="94" t="n">
-        <v>29.96</v>
+        <v>33.56</v>
       </c>
       <c r="J41" s="94" t="n">
-        <v>33.56</v>
+        <v>38.91</v>
       </c>
       <c r="K41" s="94" t="n">
-        <v>33.56</v>
+        <v>56.68</v>
       </c>
       <c r="L41" s="94" t="n">
-        <v>38.91</v>
+        <v>56.68</v>
       </c>
       <c r="M41" s="94" t="n">
-        <v>56.68</v>
+        <v>57.12</v>
       </c>
       <c r="N41" s="94" t="n">
-        <v>56.68</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="O41" s="94" t="n">
-        <v>57.12</v>
+        <v>83.77</v>
       </c>
       <c r="P41" s="94" t="n">
-        <v>78.04000000000001</v>
+        <v>80.52</v>
       </c>
       <c r="Q41" s="94" t="n">
-        <v>78.04000000000001</v>
+        <v>79.08</v>
       </c>
       <c r="R41" s="94" t="n">
-        <v>83.77</v>
+        <v>79.38</v>
       </c>
       <c r="S41" s="94" t="n">
-        <v>80.52</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="T41" s="94" t="n">
-        <v>79.08</v>
+        <v>66.75</v>
       </c>
       <c r="U41" s="94" t="n">
-        <v>79.38</v>
+        <v>64.14</v>
       </c>
       <c r="V41" s="94" t="n">
-        <v>77.31999999999999</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="W41" s="94" t="n">
-        <v>77.31999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="X41" s="94" t="n">
-        <v>66.75</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="Y41" s="94" t="n">
-        <v>64.14</v>
+        <v>66.14</v>
       </c>
       <c r="Z41" s="94" t="n">
-        <v>66.76000000000001</v>
+        <v>50.55</v>
       </c>
       <c r="AA41" s="94" t="n">
-        <v>65.90000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="AB41" s="94" t="n">
-        <v>65.01000000000001</v>
+        <v>52.02</v>
       </c>
       <c r="AC41" s="94" t="n">
-        <v>65.01000000000001</v>
+        <v>46.05</v>
       </c>
       <c r="AD41" s="94" t="n">
-        <v>66.14</v>
+        <v>66.09</v>
       </c>
       <c r="AE41" s="94" t="n">
-        <v>50.55</v>
+        <v>70.18000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -10976,149 +10977,149 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="92" t="inlineStr">
+      <c r="B42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="C42" s="92" t="inlineStr">
+      <c r="D42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D42" s="92" t="inlineStr">
+      <c r="E42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E42" s="92" t="inlineStr">
+      <c r="I42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F42" s="93" t="inlineStr">
+      <c r="O42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Z42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="H42" s="93" t="inlineStr">
+      <c r="AA42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J42" s="93" t="inlineStr">
+      <c r="AB42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K42" s="93" t="inlineStr">
+      <c r="AC42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L42" s="93" t="inlineStr">
+      <c r="AD42" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="M42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="O42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AE42" s="93" t="inlineStr">
@@ -11134,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>-0.26</v>
+        <v>-1.01</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>-0.26</v>
@@ -11143,85 +11144,85 @@
         <v>0.58</v>
       </c>
       <c r="E43" s="94" t="n">
-        <v>0.58</v>
+        <v>-0.59</v>
       </c>
       <c r="F43" s="94" t="n">
-        <v>-0.59</v>
+        <v>-0.14</v>
       </c>
       <c r="G43" s="94" t="n">
-        <v>-0.14</v>
+        <v>-0.77</v>
       </c>
       <c r="H43" s="94" t="n">
-        <v>-0.77</v>
+        <v>-0.74</v>
       </c>
       <c r="I43" s="94" t="n">
-        <v>-0.74</v>
+        <v>-2.37</v>
       </c>
       <c r="J43" s="94" t="n">
-        <v>-2.37</v>
+        <v>-1.96</v>
       </c>
       <c r="K43" s="94" t="n">
-        <v>-2.37</v>
+        <v>0.05</v>
       </c>
       <c r="L43" s="94" t="n">
-        <v>-1.96</v>
+        <v>0.87</v>
       </c>
       <c r="M43" s="94" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="N43" s="94" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O43" s="94" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P43" s="94" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="Q43" s="94" t="n">
         <v>0.87</v>
       </c>
-      <c r="O43" s="94" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="P43" s="94" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q43" s="94" t="n">
-        <v>1.51</v>
-      </c>
       <c r="R43" s="94" t="n">
-        <v>0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="S43" s="94" t="n">
-        <v>-0.87</v>
+        <v>0.28</v>
       </c>
       <c r="T43" s="94" t="n">
-        <v>0.87</v>
+        <v>1.12</v>
       </c>
       <c r="U43" s="94" t="n">
-        <v>-0.7</v>
+        <v>-2.16</v>
       </c>
       <c r="V43" s="94" t="n">
-        <v>0.28</v>
+        <v>-2.28</v>
       </c>
       <c r="W43" s="94" t="n">
-        <v>0.28</v>
+        <v>-3.34</v>
       </c>
       <c r="X43" s="94" t="n">
-        <v>1.12</v>
+        <v>-2.14</v>
       </c>
       <c r="Y43" s="94" t="n">
-        <v>-2.16</v>
+        <v>-3.08</v>
       </c>
       <c r="Z43" s="94" t="n">
-        <v>-2.28</v>
+        <v>-2.29</v>
       </c>
       <c r="AA43" s="94" t="n">
-        <v>-3.34</v>
+        <v>-2.9</v>
       </c>
       <c r="AB43" s="94" t="n">
-        <v>-2.14</v>
+        <v>-1.93</v>
       </c>
       <c r="AC43" s="94" t="n">
-        <v>-2.14</v>
+        <v>-2.01</v>
       </c>
       <c r="AD43" s="94" t="n">
-        <v>-3.08</v>
+        <v>-3.58</v>
       </c>
       <c r="AE43" s="94" t="n">
-        <v>-2.29</v>
+        <v>-4.62</v>
       </c>
     </row>
     <row r="44">
@@ -11231,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>-6.01</v>
+        <v>-6.73</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>-6.01</v>
@@ -11240,85 +11241,85 @@
         <v>-5.47</v>
       </c>
       <c r="E44" s="94" t="n">
-        <v>-5.47</v>
+        <v>-6.8</v>
       </c>
       <c r="F44" s="94" t="n">
-        <v>-6.8</v>
+        <v>-6.73</v>
       </c>
       <c r="G44" s="94" t="n">
-        <v>-6.73</v>
+        <v>-6.46</v>
       </c>
       <c r="H44" s="94" t="n">
-        <v>-6.46</v>
+        <v>-5.56</v>
       </c>
       <c r="I44" s="94" t="n">
-        <v>-5.56</v>
+        <v>-6.01</v>
       </c>
       <c r="J44" s="94" t="n">
+        <v>-6.31</v>
+      </c>
+      <c r="K44" s="94" t="n">
+        <v>-4.48</v>
+      </c>
+      <c r="L44" s="94" t="n">
+        <v>-5.85</v>
+      </c>
+      <c r="M44" s="94" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="N44" s="94" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="O44" s="94" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="P44" s="94" t="n">
         <v>-6.01</v>
       </c>
-      <c r="K44" s="94" t="n">
-        <v>-6.01</v>
-      </c>
-      <c r="L44" s="94" t="n">
-        <v>-6.31</v>
-      </c>
-      <c r="M44" s="94" t="n">
-        <v>-4.48</v>
-      </c>
-      <c r="N44" s="94" t="n">
-        <v>-5.85</v>
-      </c>
-      <c r="O44" s="94" t="n">
-        <v>-4.68</v>
-      </c>
-      <c r="P44" s="94" t="n">
-        <v>-2.89</v>
-      </c>
       <c r="Q44" s="94" t="n">
-        <v>-2.89</v>
+        <v>-6.35</v>
       </c>
       <c r="R44" s="94" t="n">
-        <v>-3.77</v>
+        <v>-6.86</v>
       </c>
       <c r="S44" s="94" t="n">
-        <v>-6.01</v>
+        <v>-7.99</v>
       </c>
       <c r="T44" s="94" t="n">
-        <v>-6.35</v>
+        <v>-6.6</v>
       </c>
       <c r="U44" s="94" t="n">
-        <v>-6.86</v>
+        <v>-8.43</v>
       </c>
       <c r="V44" s="94" t="n">
-        <v>-7.99</v>
+        <v>-8.75</v>
       </c>
       <c r="W44" s="94" t="n">
-        <v>-7.99</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="X44" s="94" t="n">
-        <v>-6.6</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="Y44" s="94" t="n">
-        <v>-8.43</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="Z44" s="94" t="n">
-        <v>-8.75</v>
+        <v>-9.26</v>
       </c>
       <c r="AA44" s="94" t="n">
-        <v>-9.210000000000001</v>
+        <v>-9.44</v>
       </c>
       <c r="AB44" s="94" t="n">
-        <v>-8.789999999999999</v>
+        <v>-9.02</v>
       </c>
       <c r="AC44" s="94" t="n">
-        <v>-8.789999999999999</v>
+        <v>-10.35</v>
       </c>
       <c r="AD44" s="94" t="n">
         <v>-8.789999999999999</v>
       </c>
       <c r="AE44" s="94" t="n">
-        <v>-9.26</v>
+        <v>-8.130000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -11328,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>59.42</v>
+        <v>40.56</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>59.42</v>
@@ -11337,85 +11338,85 @@
         <v>54.29</v>
       </c>
       <c r="E45" s="94" t="n">
-        <v>54.29</v>
+        <v>46.1</v>
       </c>
       <c r="F45" s="94" t="n">
-        <v>46.1</v>
+        <v>49.74</v>
       </c>
       <c r="G45" s="94" t="n">
-        <v>49.74</v>
+        <v>42.08</v>
       </c>
       <c r="H45" s="94" t="n">
-        <v>42.08</v>
+        <v>50.81</v>
       </c>
       <c r="I45" s="94" t="n">
-        <v>50.81</v>
+        <v>45.03</v>
       </c>
       <c r="J45" s="94" t="n">
-        <v>45.03</v>
+        <v>33.57</v>
       </c>
       <c r="K45" s="94" t="n">
-        <v>45.03</v>
+        <v>45.48</v>
       </c>
       <c r="L45" s="94" t="n">
-        <v>33.57</v>
+        <v>44.93</v>
       </c>
       <c r="M45" s="94" t="n">
-        <v>45.48</v>
+        <v>52.35</v>
       </c>
       <c r="N45" s="94" t="n">
-        <v>44.93</v>
+        <v>78.61</v>
       </c>
       <c r="O45" s="94" t="n">
-        <v>52.35</v>
+        <v>75.48</v>
       </c>
       <c r="P45" s="94" t="n">
-        <v>78.61</v>
+        <v>57.98</v>
       </c>
       <c r="Q45" s="94" t="n">
-        <v>78.61</v>
+        <v>66.2</v>
       </c>
       <c r="R45" s="94" t="n">
-        <v>75.48</v>
+        <v>52.83</v>
       </c>
       <c r="S45" s="94" t="n">
-        <v>57.98</v>
+        <v>51.58</v>
       </c>
       <c r="T45" s="94" t="n">
-        <v>66.2</v>
+        <v>74.97</v>
       </c>
       <c r="U45" s="94" t="n">
-        <v>52.83</v>
+        <v>45.92</v>
       </c>
       <c r="V45" s="94" t="n">
-        <v>51.58</v>
+        <v>59.76</v>
       </c>
       <c r="W45" s="94" t="n">
-        <v>51.58</v>
+        <v>48.71</v>
       </c>
       <c r="X45" s="94" t="n">
-        <v>74.97</v>
+        <v>53.61</v>
       </c>
       <c r="Y45" s="94" t="n">
-        <v>45.92</v>
+        <v>45.19</v>
       </c>
       <c r="Z45" s="94" t="n">
-        <v>59.76</v>
+        <v>32.83</v>
       </c>
       <c r="AA45" s="94" t="n">
-        <v>48.71</v>
+        <v>34.58</v>
       </c>
       <c r="AB45" s="94" t="n">
-        <v>53.61</v>
+        <v>37.2</v>
       </c>
       <c r="AC45" s="94" t="n">
-        <v>53.61</v>
+        <v>16.31</v>
       </c>
       <c r="AD45" s="94" t="n">
-        <v>45.19</v>
+        <v>22.99</v>
       </c>
       <c r="AE45" s="94" t="n">
-        <v>32.83</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="46">
@@ -11439,134 +11440,134 @@
           <t>red</t>
         </is>
       </c>
-      <c r="E46" s="92" t="inlineStr">
+      <c r="E46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F46" s="91" t="inlineStr">
+      <c r="G46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G46" s="92" t="inlineStr">
+      <c r="H46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H46" s="91" t="inlineStr">
+      <c r="O46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I46" s="91" t="inlineStr">
+      <c r="Q46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="K46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="L46" s="93" t="inlineStr">
+      <c r="T46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="AA46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="AE46" s="93" t="inlineStr">
@@ -11582,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>5.67</v>
+        <v>5.19</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>5.98</v>
@@ -11591,85 +11592,85 @@
         <v>6.61</v>
       </c>
       <c r="E47" s="94" t="n">
-        <v>6.61</v>
+        <v>4.66</v>
       </c>
       <c r="F47" s="94" t="n">
-        <v>4.66</v>
+        <v>4.43</v>
       </c>
       <c r="G47" s="94" t="n">
-        <v>4.43</v>
+        <v>2.96</v>
       </c>
       <c r="H47" s="94" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I47" s="94" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="J47" s="94" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K47" s="94" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="L47" s="94" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="M47" s="94" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="N47" s="94" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O47" s="94" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="P47" s="94" t="n">
         <v>2.96</v>
       </c>
-      <c r="I47" s="94" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J47" s="94" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="K47" s="94" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="L47" s="94" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="M47" s="94" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="N47" s="94" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="O47" s="94" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="P47" s="94" t="n">
-        <v>5.4</v>
-      </c>
       <c r="Q47" s="94" t="n">
-        <v>5.4</v>
+        <v>4.58</v>
       </c>
       <c r="R47" s="94" t="n">
-        <v>4.27</v>
+        <v>3.04</v>
       </c>
       <c r="S47" s="94" t="n">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="T47" s="94" t="n">
-        <v>4.58</v>
+        <v>4.35</v>
       </c>
       <c r="U47" s="94" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="V47" s="94" t="n">
-        <v>2.66</v>
+        <v>3.02</v>
       </c>
       <c r="W47" s="94" t="n">
-        <v>2.66</v>
+        <v>1.68</v>
       </c>
       <c r="X47" s="94" t="n">
-        <v>4.35</v>
+        <v>2.95</v>
       </c>
       <c r="Y47" s="94" t="n">
-        <v>3.06</v>
+        <v>1.45</v>
       </c>
       <c r="Z47" s="94" t="n">
-        <v>3.02</v>
+        <v>1.45</v>
       </c>
       <c r="AA47" s="94" t="n">
-        <v>1.68</v>
+        <v>0.74</v>
       </c>
       <c r="AB47" s="94" t="n">
-        <v>2.95</v>
+        <v>2.08</v>
       </c>
       <c r="AC47" s="94" t="n">
-        <v>2.95</v>
+        <v>1.67</v>
       </c>
       <c r="AD47" s="94" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AE47" s="94" t="n">
-        <v>1.45</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="48">
@@ -11679,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>8.23</v>
+        <v>7.74</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>7.42</v>
@@ -11688,85 +11689,85 @@
         <v>8.130000000000001</v>
       </c>
       <c r="E48" s="94" t="n">
-        <v>8.130000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="F48" s="94" t="n">
-        <v>6.2</v>
+        <v>6.16</v>
       </c>
       <c r="G48" s="94" t="n">
-        <v>6.16</v>
+        <v>6.75</v>
       </c>
       <c r="H48" s="94" t="n">
-        <v>6.75</v>
+        <v>7.71</v>
       </c>
       <c r="I48" s="94" t="n">
-        <v>7.71</v>
+        <v>7.2</v>
       </c>
       <c r="J48" s="94" t="n">
-        <v>7.2</v>
+        <v>7.01</v>
       </c>
       <c r="K48" s="94" t="n">
-        <v>7.2</v>
+        <v>7.87</v>
       </c>
       <c r="L48" s="94" t="n">
-        <v>7.01</v>
+        <v>6.58</v>
       </c>
       <c r="M48" s="94" t="n">
-        <v>7.87</v>
+        <v>7.78</v>
       </c>
       <c r="N48" s="94" t="n">
-        <v>6.58</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="O48" s="94" t="n">
-        <v>7.78</v>
+        <v>6.31</v>
       </c>
       <c r="P48" s="94" t="n">
-        <v>8.460000000000001</v>
+        <v>4.66</v>
       </c>
       <c r="Q48" s="94" t="n">
-        <v>8.460000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="R48" s="94" t="n">
-        <v>6.31</v>
+        <v>3.7</v>
       </c>
       <c r="S48" s="94" t="n">
-        <v>4.66</v>
+        <v>1.72</v>
       </c>
       <c r="T48" s="94" t="n">
-        <v>3.7</v>
+        <v>3.46</v>
       </c>
       <c r="U48" s="94" t="n">
-        <v>3.7</v>
+        <v>2.34</v>
       </c>
       <c r="V48" s="94" t="n">
-        <v>1.72</v>
+        <v>1.26</v>
       </c>
       <c r="W48" s="94" t="n">
-        <v>1.72</v>
+        <v>0.84</v>
       </c>
       <c r="X48" s="94" t="n">
-        <v>3.46</v>
+        <v>1.71</v>
       </c>
       <c r="Y48" s="94" t="n">
-        <v>2.34</v>
+        <v>1.41</v>
       </c>
       <c r="Z48" s="94" t="n">
-        <v>1.26</v>
+        <v>0.68</v>
       </c>
       <c r="AA48" s="94" t="n">
-        <v>0.84</v>
+        <v>0.48</v>
       </c>
       <c r="AB48" s="94" t="n">
-        <v>1.71</v>
+        <v>2.38</v>
       </c>
       <c r="AC48" s="94" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AD48" s="94" t="n">
-        <v>1.41</v>
+        <v>3.59</v>
       </c>
       <c r="AE48" s="94" t="n">
-        <v>0.68</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="49">
@@ -11776,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>77.81</v>
+        <v>74.56</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>74.03</v>
@@ -11785,98 +11786,98 @@
         <v>68.01000000000001</v>
       </c>
       <c r="E49" s="94" t="n">
-        <v>68.01000000000001</v>
+        <v>58.26</v>
       </c>
       <c r="F49" s="94" t="n">
-        <v>58.26</v>
+        <v>62.55</v>
       </c>
       <c r="G49" s="94" t="n">
-        <v>62.55</v>
+        <v>49.18</v>
       </c>
       <c r="H49" s="94" t="n">
-        <v>49.18</v>
+        <v>52.29</v>
       </c>
       <c r="I49" s="94" t="n">
+        <v>53.55</v>
+      </c>
+      <c r="J49" s="94" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="K49" s="94" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="L49" s="94" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="M49" s="94" t="n">
+        <v>67.34999999999999</v>
+      </c>
+      <c r="N49" s="94" t="n">
+        <v>78.38</v>
+      </c>
+      <c r="O49" s="94" t="n">
+        <v>72.42</v>
+      </c>
+      <c r="P49" s="94" t="n">
+        <v>59.91</v>
+      </c>
+      <c r="Q49" s="94" t="n">
+        <v>66</v>
+      </c>
+      <c r="R49" s="94" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="S49" s="94" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="T49" s="94" t="n">
+        <v>75.06999999999999</v>
+      </c>
+      <c r="U49" s="94" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="V49" s="94" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="W49" s="94" t="n">
+        <v>57.16</v>
+      </c>
+      <c r="X49" s="94" t="n">
+        <v>62.56</v>
+      </c>
+      <c r="Y49" s="94" t="n">
         <v>52.29</v>
       </c>
-      <c r="J49" s="94" t="n">
-        <v>53.55</v>
-      </c>
-      <c r="K49" s="94" t="n">
-        <v>53.55</v>
-      </c>
-      <c r="L49" s="94" t="n">
-        <v>46.86</v>
-      </c>
-      <c r="M49" s="94" t="n">
-        <v>56.45</v>
-      </c>
-      <c r="N49" s="94" t="n">
-        <v>59.76</v>
-      </c>
-      <c r="O49" s="94" t="n">
-        <v>67.34999999999999</v>
-      </c>
-      <c r="P49" s="94" t="n">
-        <v>78.38</v>
-      </c>
-      <c r="Q49" s="94" t="n">
-        <v>78.38</v>
-      </c>
-      <c r="R49" s="94" t="n">
-        <v>72.42</v>
-      </c>
-      <c r="S49" s="94" t="n">
-        <v>59.91</v>
-      </c>
-      <c r="T49" s="94" t="n">
-        <v>66</v>
-      </c>
-      <c r="U49" s="94" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="V49" s="94" t="n">
-        <v>52.95</v>
-      </c>
-      <c r="W49" s="94" t="n">
-        <v>52.95</v>
-      </c>
-      <c r="X49" s="94" t="n">
-        <v>75.06999999999999</v>
-      </c>
-      <c r="Y49" s="94" t="n">
-        <v>61.14</v>
-      </c>
       <c r="Z49" s="94" t="n">
-        <v>62.6</v>
+        <v>37.42</v>
       </c>
       <c r="AA49" s="94" t="n">
-        <v>57.16</v>
+        <v>31.32</v>
       </c>
       <c r="AB49" s="94" t="n">
-        <v>62.56</v>
+        <v>40.38</v>
       </c>
       <c r="AC49" s="94" t="n">
-        <v>62.56</v>
+        <v>26.19</v>
       </c>
       <c r="AD49" s="94" t="n">
-        <v>52.29</v>
+        <v>42.54</v>
       </c>
       <c r="AE49" s="94" t="n">
-        <v>37.42</v>
+        <v>43.82</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：</t>
+          <t>今日买报：ixic:RS2:36.8&lt;=38</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：kc:RNG60:25.12&gt;=25;us500:RS2:93.6&gt;=85;us30:RS3:87.47&gt;=85</t>
+          <t>今日卖报：kc:RNG60:25.12&gt;=25</t>
         </is>
       </c>
     </row>
@@ -15477,13 +15478,13 @@
       <c r="G2" s="36" t="n">
         <v>66</v>
       </c>
-      <c r="H2" s="96" t="n">
+      <c r="H2" s="97" t="n">
         <v>22.3514585</v>
       </c>
       <c r="I2" s="36" t="n">
         <v>7.06</v>
       </c>
-      <c r="J2" s="97">
+      <c r="J2" s="98">
         <f>(1+H2/100)^(1/(YEAR(D2)-YEAR(C2)))-1</f>
         <v/>
       </c>
@@ -15515,13 +15516,13 @@
       <c r="G3" s="39" t="n">
         <v>73</v>
       </c>
-      <c r="H3" s="98" t="n">
+      <c r="H3" s="99" t="n">
         <v>35.0298984</v>
       </c>
       <c r="I3" s="39" t="n">
         <v>11.41</v>
       </c>
-      <c r="J3" s="97">
+      <c r="J3" s="98">
         <f>(1+H3/100)^(1/(YEAR(D3)-YEAR(C3)))-1</f>
         <v/>
       </c>
@@ -15553,13 +15554,13 @@
       <c r="G4" s="39" t="n">
         <v>85</v>
       </c>
-      <c r="H4" s="98" t="n">
+      <c r="H4" s="99" t="n">
         <v>122.4911655</v>
       </c>
       <c r="I4" s="39" t="n">
         <v>76.98</v>
       </c>
-      <c r="J4" s="99">
+      <c r="J4" s="100">
         <f>(1+H4/100)^(1/(YEAR(D4)-YEAR(C4)))-1</f>
         <v/>
       </c>
@@ -15591,13 +15592,13 @@
       <c r="G5" s="39" t="n">
         <v>96</v>
       </c>
-      <c r="H5" s="98" t="n">
+      <c r="H5" s="99" t="n">
         <v>136.13543</v>
       </c>
       <c r="I5" s="39" t="n">
         <v>100.05</v>
       </c>
-      <c r="J5" s="99">
+      <c r="J5" s="100">
         <f>(1+H5/100)^(1/(YEAR(D5)-YEAR(C5)))-1</f>
         <v/>
       </c>
@@ -15629,13 +15630,13 @@
       <c r="G6" s="39" t="n">
         <v>95</v>
       </c>
-      <c r="H6" s="98" t="n">
+      <c r="H6" s="99" t="n">
         <v>95.7546074</v>
       </c>
       <c r="I6" s="39" t="n">
         <v>44.37</v>
       </c>
-      <c r="J6" s="99">
+      <c r="J6" s="100">
         <f>(1+H6/100)^(1/(YEAR(D6)-YEAR(C6)))-1</f>
         <v/>
       </c>
@@ -15667,13 +15668,13 @@
       <c r="G7" s="39" t="n">
         <v>86</v>
       </c>
-      <c r="H7" s="98" t="n">
+      <c r="H7" s="99" t="n">
         <v>123.8525927</v>
       </c>
       <c r="I7" s="39" t="n">
         <v>63.41</v>
       </c>
-      <c r="J7" s="99">
+      <c r="J7" s="100">
         <f>(1+H7/100)^(1/(YEAR(D7)-YEAR(C7)))-1</f>
         <v/>
       </c>
@@ -15705,13 +15706,13 @@
       <c r="G8" s="39" t="n">
         <v>87</v>
       </c>
-      <c r="H8" s="98" t="n">
+      <c r="H8" s="99" t="n">
         <v>81.41461922000001</v>
       </c>
       <c r="I8" s="39" t="n">
         <v>26.39</v>
       </c>
-      <c r="J8" s="99">
+      <c r="J8" s="100">
         <f>(1+H8/100)^(1/(YEAR(D8)-YEAR(C8)))-1</f>
         <v/>
       </c>
@@ -15743,13 +15744,13 @@
       <c r="G9" s="39" t="n">
         <v>83</v>
       </c>
-      <c r="H9" s="98" t="n">
+      <c r="H9" s="99" t="n">
         <v>47.02060524</v>
       </c>
       <c r="I9" s="39" t="n">
         <v>37.82</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="100">
         <f>(1+H9/100)^(1/(YEAR(D9)-YEAR(C9)))-1</f>
         <v/>
       </c>
@@ -15780,13 +15781,13 @@
       <c r="G10" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="H10" s="100" t="n">
+      <c r="H10" s="101" t="n">
         <v>27.8860732</v>
       </c>
       <c r="I10" s="24" t="n">
         <v>-10.97</v>
       </c>
-      <c r="J10" s="101" t="n">
+      <c r="J10" s="102" t="n">
         <v>0.278860732</v>
       </c>
     </row>
@@ -15817,13 +15818,13 @@
       <c r="G11" s="24" t="n">
         <v>93</v>
       </c>
-      <c r="H11" s="100" t="n">
+      <c r="H11" s="101" t="n">
         <v>17.4948656</v>
       </c>
       <c r="I11" s="24" t="n">
         <v>-7.7</v>
       </c>
-      <c r="J11" s="101">
+      <c r="J11" s="102">
         <f>(1+H11/100)^(1/(YEAR(D11)-YEAR(C11)))-1</f>
         <v/>
       </c>

--- a/report_2410.xlsx
+++ b/report_2410.xlsx
@@ -800,7 +800,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1063,7 +1063,6 @@
     <xf numFmtId="0" fontId="0" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3891,7 +3890,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.13</v>
+        <v>7.14</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.14</v>
@@ -3988,7 +3987,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.19</v>
+        <v>-0.05</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.65</v>
@@ -4085,7 +4084,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.06</v>
+        <v>0.2</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.6899999999999999</v>
@@ -6357,137 +6356,137 @@
       </c>
       <c r="E1" s="77" t="inlineStr">
         <is>
-          <t>241013</t>
+          <t>241011</t>
         </is>
       </c>
       <c r="F1" s="77" t="inlineStr">
         <is>
-          <t>241011</t>
+          <t>241010</t>
         </is>
       </c>
       <c r="G1" s="77" t="inlineStr">
         <is>
-          <t>241010</t>
+          <t>241009</t>
         </is>
       </c>
       <c r="H1" s="77" t="inlineStr">
         <is>
-          <t>241009</t>
+          <t>241008</t>
         </is>
       </c>
       <c r="I1" s="77" t="inlineStr">
         <is>
-          <t>241008</t>
+          <t>241007</t>
         </is>
       </c>
       <c r="J1" s="77" t="inlineStr">
         <is>
-          <t>241007</t>
+          <t>241004</t>
         </is>
       </c>
       <c r="K1" s="77" t="inlineStr">
         <is>
-          <t>241006</t>
+          <t>241003</t>
         </is>
       </c>
       <c r="L1" s="77" t="inlineStr">
         <is>
-          <t>241004</t>
+          <t>241002</t>
         </is>
       </c>
       <c r="M1" s="77" t="inlineStr">
         <is>
-          <t>241003</t>
+          <t>241001</t>
         </is>
       </c>
       <c r="N1" s="77" t="inlineStr">
         <is>
-          <t>241002</t>
+          <t>240930</t>
         </is>
       </c>
       <c r="O1" s="77" t="inlineStr">
         <is>
-          <t>241001</t>
+          <t>240927</t>
         </is>
       </c>
       <c r="P1" s="77" t="inlineStr">
         <is>
-          <t>240930</t>
+          <t>240926</t>
         </is>
       </c>
       <c r="Q1" s="77" t="inlineStr">
         <is>
-          <t>240929</t>
+          <t>240925</t>
         </is>
       </c>
       <c r="R1" s="77" t="inlineStr">
         <is>
-          <t>240927</t>
+          <t>240924</t>
         </is>
       </c>
       <c r="S1" s="77" t="inlineStr">
         <is>
-          <t>240926</t>
+          <t>240923</t>
         </is>
       </c>
       <c r="T1" s="77" t="inlineStr">
         <is>
-          <t>240925</t>
+          <t>240920</t>
         </is>
       </c>
       <c r="U1" s="77" t="inlineStr">
         <is>
-          <t>240924</t>
+          <t>240919</t>
         </is>
       </c>
       <c r="V1" s="77" t="inlineStr">
         <is>
-          <t>240923</t>
+          <t>240918</t>
         </is>
       </c>
       <c r="W1" s="77" t="inlineStr">
         <is>
-          <t>240922</t>
+          <t>240917</t>
         </is>
       </c>
       <c r="X1" s="77" t="inlineStr">
         <is>
-          <t>240920</t>
+          <t>240916</t>
         </is>
       </c>
       <c r="Y1" s="77" t="inlineStr">
         <is>
-          <t>240919</t>
+          <t>240913</t>
         </is>
       </c>
       <c r="Z1" s="77" t="inlineStr">
         <is>
-          <t>240918</t>
+          <t>240912</t>
         </is>
       </c>
       <c r="AA1" s="77" t="inlineStr">
         <is>
-          <t>240917</t>
+          <t>240911</t>
         </is>
       </c>
       <c r="AB1" s="77" t="inlineStr">
         <is>
-          <t>240916</t>
+          <t>240910</t>
         </is>
       </c>
       <c r="AC1" s="77" t="inlineStr">
         <is>
-          <t>240915</t>
+          <t>240909</t>
         </is>
       </c>
       <c r="AD1" s="77" t="inlineStr">
         <is>
-          <t>240913</t>
+          <t>240906</t>
         </is>
       </c>
       <c r="AE1" s="77" t="inlineStr">
         <is>
-          <t>240912</t>
+          <t>240905</t>
         </is>
       </c>
     </row>
@@ -6527,74 +6526,74 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="H2" s="91" t="inlineStr">
+      <c r="H2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="T2" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U2" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="V2" s="91" t="inlineStr">
@@ -6602,24 +6601,24 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="W2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="W2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="X2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Y2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="AA2" s="93" t="inlineStr">
@@ -6667,16 +6666,16 @@
         <v>9.470000000000001</v>
       </c>
       <c r="F3" s="94" t="n">
-        <v>9.470000000000001</v>
+        <v>11.58</v>
       </c>
       <c r="G3" s="94" t="n">
-        <v>11.58</v>
+        <v>11.51</v>
       </c>
       <c r="H3" s="94" t="n">
-        <v>11.51</v>
+        <v>18.3</v>
       </c>
       <c r="I3" s="94" t="n">
-        <v>18.3</v>
+        <v>12.81</v>
       </c>
       <c r="J3" s="94" t="n">
         <v>12.81</v>
@@ -6694,55 +6693,55 @@
         <v>12.81</v>
       </c>
       <c r="O3" s="94" t="n">
-        <v>12.81</v>
+        <v>3.53</v>
       </c>
       <c r="P3" s="94" t="n">
-        <v>12.81</v>
+        <v>0.13</v>
       </c>
       <c r="Q3" s="94" t="n">
-        <v>3.53</v>
+        <v>-3.29</v>
       </c>
       <c r="R3" s="94" t="n">
-        <v>3.53</v>
+        <v>-3.51</v>
       </c>
       <c r="S3" s="94" t="n">
-        <v>0.13</v>
+        <v>-6.68</v>
       </c>
       <c r="T3" s="94" t="n">
-        <v>-3.29</v>
+        <v>-7.93</v>
       </c>
       <c r="U3" s="94" t="n">
-        <v>-3.51</v>
+        <v>-7.25</v>
       </c>
       <c r="V3" s="94" t="n">
-        <v>-6.68</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="W3" s="94" t="n">
-        <v>-7.93</v>
+        <v>-9.81</v>
       </c>
       <c r="X3" s="94" t="n">
-        <v>-7.93</v>
+        <v>-9.81</v>
       </c>
       <c r="Y3" s="94" t="n">
-        <v>-7.25</v>
+        <v>-9.81</v>
       </c>
       <c r="Z3" s="94" t="n">
-        <v>-8.300000000000001</v>
+        <v>-9.59</v>
       </c>
       <c r="AA3" s="94" t="n">
-        <v>-9.81</v>
+        <v>-9.82</v>
       </c>
       <c r="AB3" s="94" t="n">
-        <v>-9.81</v>
+        <v>-9.44</v>
       </c>
       <c r="AC3" s="94" t="n">
-        <v>-9.81</v>
+        <v>-9.26</v>
       </c>
       <c r="AD3" s="94" t="n">
-        <v>-9.81</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="AE3" s="94" t="n">
-        <v>-9.59</v>
+        <v>-7.94</v>
       </c>
     </row>
     <row r="4">
@@ -6764,16 +6763,16 @@
         <v>6.05</v>
       </c>
       <c r="F4" s="94" t="n">
-        <v>6.05</v>
+        <v>9.07</v>
       </c>
       <c r="G4" s="94" t="n">
-        <v>9.07</v>
+        <v>6.9</v>
       </c>
       <c r="H4" s="94" t="n">
-        <v>6.9</v>
+        <v>14.53</v>
       </c>
       <c r="I4" s="94" t="n">
-        <v>14.53</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="J4" s="94" t="n">
         <v>8.710000000000001</v>
@@ -6791,55 +6790,55 @@
         <v>8.710000000000001</v>
       </c>
       <c r="O4" s="94" t="n">
-        <v>8.710000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="P4" s="94" t="n">
-        <v>8.710000000000001</v>
+        <v>-2.48</v>
       </c>
       <c r="Q4" s="94" t="n">
-        <v>0.41</v>
+        <v>-4.76</v>
       </c>
       <c r="R4" s="94" t="n">
-        <v>0.41</v>
+        <v>-4.9</v>
       </c>
       <c r="S4" s="94" t="n">
-        <v>-2.48</v>
+        <v>-8.16</v>
       </c>
       <c r="T4" s="94" t="n">
-        <v>-4.76</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="U4" s="94" t="n">
-        <v>-4.9</v>
+        <v>-9.59</v>
       </c>
       <c r="V4" s="94" t="n">
-        <v>-8.16</v>
+        <v>-10.85</v>
       </c>
       <c r="W4" s="94" t="n">
-        <v>-9.720000000000001</v>
+        <v>-12.12</v>
       </c>
       <c r="X4" s="94" t="n">
-        <v>-9.720000000000001</v>
+        <v>-12.12</v>
       </c>
       <c r="Y4" s="94" t="n">
-        <v>-9.59</v>
+        <v>-12.12</v>
       </c>
       <c r="Z4" s="94" t="n">
-        <v>-10.85</v>
+        <v>-11.77</v>
       </c>
       <c r="AA4" s="94" t="n">
-        <v>-12.12</v>
+        <v>-11.13</v>
       </c>
       <c r="AB4" s="94" t="n">
-        <v>-12.12</v>
+        <v>-11.05</v>
       </c>
       <c r="AC4" s="94" t="n">
-        <v>-12.12</v>
+        <v>-10.42</v>
       </c>
       <c r="AD4" s="94" t="n">
-        <v>-12.12</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="AE4" s="94" t="n">
-        <v>-11.77</v>
+        <v>-8.390000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -6861,16 +6860,16 @@
         <v>44.67</v>
       </c>
       <c r="F5" s="94" t="n">
-        <v>44.67</v>
+        <v>59.48</v>
       </c>
       <c r="G5" s="94" t="n">
-        <v>59.48</v>
+        <v>54.31</v>
       </c>
       <c r="H5" s="94" t="n">
-        <v>54.31</v>
+        <v>99.84</v>
       </c>
       <c r="I5" s="94" t="n">
-        <v>99.84</v>
+        <v>99.75</v>
       </c>
       <c r="J5" s="94" t="n">
         <v>99.75</v>
@@ -6888,55 +6887,55 @@
         <v>99.75</v>
       </c>
       <c r="O5" s="94" t="n">
-        <v>99.75</v>
+        <v>99.31</v>
       </c>
       <c r="P5" s="94" t="n">
-        <v>99.75</v>
+        <v>98.83</v>
       </c>
       <c r="Q5" s="94" t="n">
-        <v>99.31</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="R5" s="94" t="n">
-        <v>99.31</v>
+        <v>96.38</v>
       </c>
       <c r="S5" s="94" t="n">
-        <v>98.83</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="T5" s="94" t="n">
-        <v>97.34999999999999</v>
+        <v>64.38</v>
       </c>
       <c r="U5" s="94" t="n">
-        <v>96.38</v>
+        <v>63.45</v>
       </c>
       <c r="V5" s="94" t="n">
-        <v>77.51000000000001</v>
+        <v>37.85</v>
       </c>
       <c r="W5" s="94" t="n">
-        <v>64.38</v>
+        <v>7.42</v>
       </c>
       <c r="X5" s="94" t="n">
-        <v>64.38</v>
+        <v>7.42</v>
       </c>
       <c r="Y5" s="94" t="n">
-        <v>63.45</v>
+        <v>7.42</v>
       </c>
       <c r="Z5" s="94" t="n">
-        <v>37.85</v>
+        <v>10.95</v>
       </c>
       <c r="AA5" s="94" t="n">
-        <v>7.42</v>
+        <v>12.36</v>
       </c>
       <c r="AB5" s="94" t="n">
-        <v>7.42</v>
+        <v>20.95</v>
       </c>
       <c r="AC5" s="94" t="n">
-        <v>7.42</v>
+        <v>5.95</v>
       </c>
       <c r="AD5" s="94" t="n">
-        <v>7.42</v>
+        <v>11.48</v>
       </c>
       <c r="AE5" s="94" t="n">
-        <v>10.95</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="6">
@@ -6970,79 +6969,79 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="G6" s="91" t="inlineStr">
+      <c r="G6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="T6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="I6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="U6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="V6" s="93" t="inlineStr">
@@ -7065,29 +7064,29 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="Z6" s="93" t="inlineStr">
+      <c r="Z6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AB6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AC6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="AD6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="AE6" s="91" t="inlineStr">
@@ -7115,16 +7114,16 @@
         <v>26.54</v>
       </c>
       <c r="F7" s="94" t="n">
-        <v>26.54</v>
+        <v>34.41</v>
       </c>
       <c r="G7" s="94" t="n">
-        <v>34.41</v>
+        <v>44.1</v>
       </c>
       <c r="H7" s="94" t="n">
-        <v>44.1</v>
+        <v>46.52</v>
       </c>
       <c r="I7" s="94" t="n">
-        <v>46.52</v>
+        <v>26.36</v>
       </c>
       <c r="J7" s="94" t="n">
         <v>26.36</v>
@@ -7142,55 +7141,55 @@
         <v>26.36</v>
       </c>
       <c r="O7" s="94" t="n">
-        <v>26.36</v>
+        <v>5.45</v>
       </c>
       <c r="P7" s="94" t="n">
-        <v>26.36</v>
+        <v>-0.85</v>
       </c>
       <c r="Q7" s="94" t="n">
-        <v>5.45</v>
+        <v>-5.96</v>
       </c>
       <c r="R7" s="94" t="n">
-        <v>5.45</v>
+        <v>-6.32</v>
       </c>
       <c r="S7" s="94" t="n">
-        <v>-0.85</v>
+        <v>-10.11</v>
       </c>
       <c r="T7" s="94" t="n">
-        <v>-5.96</v>
+        <v>-11.14</v>
       </c>
       <c r="U7" s="94" t="n">
-        <v>-6.32</v>
+        <v>-9.23</v>
       </c>
       <c r="V7" s="94" t="n">
-        <v>-10.11</v>
+        <v>-12.41</v>
       </c>
       <c r="W7" s="94" t="n">
-        <v>-11.14</v>
+        <v>-13.62</v>
       </c>
       <c r="X7" s="94" t="n">
-        <v>-11.14</v>
+        <v>-13.62</v>
       </c>
       <c r="Y7" s="94" t="n">
-        <v>-9.23</v>
+        <v>-13.62</v>
       </c>
       <c r="Z7" s="94" t="n">
-        <v>-12.41</v>
+        <v>-12.75</v>
       </c>
       <c r="AA7" s="94" t="n">
-        <v>-13.62</v>
+        <v>-11.62</v>
       </c>
       <c r="AB7" s="94" t="n">
-        <v>-13.62</v>
+        <v>-12.8</v>
       </c>
       <c r="AC7" s="94" t="n">
-        <v>-13.62</v>
+        <v>-13.49</v>
       </c>
       <c r="AD7" s="94" t="n">
-        <v>-13.62</v>
+        <v>-12.19</v>
       </c>
       <c r="AE7" s="94" t="n">
-        <v>-12.75</v>
+        <v>-11.56</v>
       </c>
     </row>
     <row r="8">
@@ -7212,16 +7211,16 @@
         <v>21.69</v>
       </c>
       <c r="F8" s="94" t="n">
-        <v>21.69</v>
+        <v>29.69</v>
       </c>
       <c r="G8" s="94" t="n">
-        <v>29.69</v>
+        <v>33.11</v>
       </c>
       <c r="H8" s="94" t="n">
-        <v>33.11</v>
+        <v>38.25</v>
       </c>
       <c r="I8" s="94" t="n">
-        <v>38.25</v>
+        <v>15.28</v>
       </c>
       <c r="J8" s="94" t="n">
         <v>15.28</v>
@@ -7239,55 +7238,55 @@
         <v>15.28</v>
       </c>
       <c r="O8" s="94" t="n">
-        <v>15.28</v>
+        <v>-3.74</v>
       </c>
       <c r="P8" s="94" t="n">
-        <v>15.28</v>
+        <v>-10.62</v>
       </c>
       <c r="Q8" s="94" t="n">
-        <v>-3.74</v>
+        <v>-12.51</v>
       </c>
       <c r="R8" s="94" t="n">
-        <v>-3.74</v>
+        <v>-12.61</v>
       </c>
       <c r="S8" s="94" t="n">
-        <v>-10.62</v>
+        <v>-14.58</v>
       </c>
       <c r="T8" s="94" t="n">
-        <v>-12.51</v>
+        <v>-16.03</v>
       </c>
       <c r="U8" s="94" t="n">
-        <v>-12.61</v>
+        <v>-16.65</v>
       </c>
       <c r="V8" s="94" t="n">
-        <v>-14.58</v>
+        <v>-18.48</v>
       </c>
       <c r="W8" s="94" t="n">
-        <v>-16.03</v>
+        <v>-18.74</v>
       </c>
       <c r="X8" s="94" t="n">
-        <v>-16.03</v>
+        <v>-18.74</v>
       </c>
       <c r="Y8" s="94" t="n">
-        <v>-16.65</v>
+        <v>-18.74</v>
       </c>
       <c r="Z8" s="94" t="n">
-        <v>-18.48</v>
+        <v>-19.06</v>
       </c>
       <c r="AA8" s="94" t="n">
-        <v>-18.74</v>
+        <v>-18.16</v>
       </c>
       <c r="AB8" s="94" t="n">
-        <v>-18.74</v>
+        <v>-20.04</v>
       </c>
       <c r="AC8" s="94" t="n">
-        <v>-18.74</v>
+        <v>-19.01</v>
       </c>
       <c r="AD8" s="94" t="n">
-        <v>-18.74</v>
+        <v>-17.71</v>
       </c>
       <c r="AE8" s="94" t="n">
-        <v>-19.06</v>
+        <v>-17.63</v>
       </c>
     </row>
     <row r="9">
@@ -7309,16 +7308,16 @@
         <v>59.18</v>
       </c>
       <c r="F9" s="94" t="n">
-        <v>59.18</v>
+        <v>74.52</v>
       </c>
       <c r="G9" s="94" t="n">
-        <v>74.52</v>
+        <v>89.13</v>
       </c>
       <c r="H9" s="94" t="n">
-        <v>89.13</v>
+        <v>98.36</v>
       </c>
       <c r="I9" s="94" t="n">
-        <v>98.36</v>
+        <v>96.84</v>
       </c>
       <c r="J9" s="94" t="n">
         <v>96.84</v>
@@ -7336,55 +7335,55 @@
         <v>96.84</v>
       </c>
       <c r="O9" s="94" t="n">
-        <v>96.84</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="P9" s="94" t="n">
-        <v>96.84</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="Q9" s="94" t="n">
-        <v>91.06999999999999</v>
+        <v>64.94</v>
       </c>
       <c r="R9" s="94" t="n">
-        <v>91.06999999999999</v>
+        <v>64.66</v>
       </c>
       <c r="S9" s="94" t="n">
-        <v>81.48999999999999</v>
+        <v>23.69</v>
       </c>
       <c r="T9" s="94" t="n">
-        <v>64.94</v>
+        <v>29.81</v>
       </c>
       <c r="U9" s="94" t="n">
-        <v>64.66</v>
+        <v>33.91</v>
       </c>
       <c r="V9" s="94" t="n">
-        <v>23.69</v>
+        <v>22.82</v>
       </c>
       <c r="W9" s="94" t="n">
-        <v>29.81</v>
+        <v>30.54</v>
       </c>
       <c r="X9" s="94" t="n">
-        <v>29.81</v>
+        <v>30.54</v>
       </c>
       <c r="Y9" s="94" t="n">
-        <v>33.91</v>
+        <v>30.54</v>
       </c>
       <c r="Z9" s="94" t="n">
-        <v>22.82</v>
+        <v>35.28</v>
       </c>
       <c r="AA9" s="94" t="n">
-        <v>30.54</v>
+        <v>42.99</v>
       </c>
       <c r="AB9" s="94" t="n">
-        <v>30.54</v>
+        <v>33.88</v>
       </c>
       <c r="AC9" s="94" t="n">
-        <v>30.54</v>
+        <v>22.22</v>
       </c>
       <c r="AD9" s="94" t="n">
-        <v>30.54</v>
+        <v>27.98</v>
       </c>
       <c r="AE9" s="94" t="n">
-        <v>35.28</v>
+        <v>37.32</v>
       </c>
     </row>
     <row r="10">
@@ -7418,129 +7417,129 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="G10" s="91" t="inlineStr">
+      <c r="G10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="T10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="U10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H10" s="92" t="inlineStr">
+      <c r="V10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="W10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="X10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Y10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I10" s="92" t="inlineStr">
+      <c r="AB10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE10" s="92" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="J10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="W10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="X10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y10" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE10" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -7563,16 +7562,16 @@
         <v>27.24</v>
       </c>
       <c r="F11" s="94" t="n">
-        <v>27.24</v>
+        <v>33.94</v>
       </c>
       <c r="G11" s="94" t="n">
-        <v>33.94</v>
+        <v>39.99</v>
       </c>
       <c r="H11" s="94" t="n">
-        <v>39.99</v>
+        <v>54.04</v>
       </c>
       <c r="I11" s="94" t="n">
-        <v>54.04</v>
+        <v>32.05</v>
       </c>
       <c r="J11" s="94" t="n">
         <v>32.05</v>
@@ -7590,55 +7589,55 @@
         <v>32.05</v>
       </c>
       <c r="O11" s="94" t="n">
-        <v>32.05</v>
+        <v>13.58</v>
       </c>
       <c r="P11" s="94" t="n">
-        <v>32.05</v>
+        <v>2.95</v>
       </c>
       <c r="Q11" s="94" t="n">
-        <v>13.58</v>
+        <v>-2.45</v>
       </c>
       <c r="R11" s="94" t="n">
-        <v>13.58</v>
+        <v>-4.05</v>
       </c>
       <c r="S11" s="94" t="n">
-        <v>2.95</v>
+        <v>-10.14</v>
       </c>
       <c r="T11" s="94" t="n">
-        <v>-2.45</v>
+        <v>-11.21</v>
       </c>
       <c r="U11" s="94" t="n">
-        <v>-4.05</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="V11" s="94" t="n">
-        <v>-10.14</v>
+        <v>-11.44</v>
       </c>
       <c r="W11" s="94" t="n">
-        <v>-11.21</v>
+        <v>-12.57</v>
       </c>
       <c r="X11" s="94" t="n">
-        <v>-11.21</v>
+        <v>-12.57</v>
       </c>
       <c r="Y11" s="94" t="n">
-        <v>-9.029999999999999</v>
+        <v>-12.57</v>
       </c>
       <c r="Z11" s="94" t="n">
-        <v>-11.44</v>
+        <v>-11.96</v>
       </c>
       <c r="AA11" s="94" t="n">
-        <v>-12.57</v>
+        <v>-12.87</v>
       </c>
       <c r="AB11" s="94" t="n">
-        <v>-12.57</v>
+        <v>-14.98</v>
       </c>
       <c r="AC11" s="94" t="n">
-        <v>-12.57</v>
+        <v>-14.79</v>
       </c>
       <c r="AD11" s="94" t="n">
-        <v>-12.57</v>
+        <v>-14.14</v>
       </c>
       <c r="AE11" s="94" t="n">
-        <v>-11.96</v>
+        <v>-11.99</v>
       </c>
     </row>
     <row r="12">
@@ -7660,16 +7659,16 @@
         <v>17.89</v>
       </c>
       <c r="F12" s="94" t="n">
-        <v>17.89</v>
+        <v>23.63</v>
       </c>
       <c r="G12" s="94" t="n">
-        <v>23.63</v>
+        <v>24.76</v>
       </c>
       <c r="H12" s="94" t="n">
-        <v>24.76</v>
+        <v>41.13</v>
       </c>
       <c r="I12" s="94" t="n">
-        <v>41.13</v>
+        <v>18.19</v>
       </c>
       <c r="J12" s="94" t="n">
         <v>18.19</v>
@@ -7687,55 +7686,55 @@
         <v>18.19</v>
       </c>
       <c r="O12" s="94" t="n">
-        <v>18.19</v>
+        <v>1.34</v>
       </c>
       <c r="P12" s="94" t="n">
-        <v>18.19</v>
+        <v>-8.44</v>
       </c>
       <c r="Q12" s="94" t="n">
-        <v>1.34</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="R12" s="94" t="n">
-        <v>1.34</v>
+        <v>-10.6</v>
       </c>
       <c r="S12" s="94" t="n">
-        <v>-8.44</v>
+        <v>-14.49</v>
       </c>
       <c r="T12" s="94" t="n">
-        <v>-9.720000000000001</v>
+        <v>-16.56</v>
       </c>
       <c r="U12" s="94" t="n">
-        <v>-10.6</v>
+        <v>-15.65</v>
       </c>
       <c r="V12" s="94" t="n">
-        <v>-14.49</v>
+        <v>-17.96</v>
       </c>
       <c r="W12" s="94" t="n">
-        <v>-16.56</v>
+        <v>-19.08</v>
       </c>
       <c r="X12" s="94" t="n">
-        <v>-16.56</v>
+        <v>-19.08</v>
       </c>
       <c r="Y12" s="94" t="n">
-        <v>-15.65</v>
+        <v>-19.08</v>
       </c>
       <c r="Z12" s="94" t="n">
-        <v>-17.96</v>
+        <v>-18.72</v>
       </c>
       <c r="AA12" s="94" t="n">
-        <v>-19.08</v>
+        <v>-18.28</v>
       </c>
       <c r="AB12" s="94" t="n">
-        <v>-19.08</v>
+        <v>-20.06</v>
       </c>
       <c r="AC12" s="94" t="n">
-        <v>-19.08</v>
+        <v>-18.31</v>
       </c>
       <c r="AD12" s="94" t="n">
-        <v>-19.08</v>
+        <v>-18.32</v>
       </c>
       <c r="AE12" s="94" t="n">
-        <v>-18.72</v>
+        <v>-17.44</v>
       </c>
     </row>
     <row r="13">
@@ -7757,16 +7756,16 @@
         <v>42.18</v>
       </c>
       <c r="F13" s="94" t="n">
-        <v>42.18</v>
+        <v>55.03</v>
       </c>
       <c r="G13" s="94" t="n">
-        <v>55.03</v>
+        <v>62.67</v>
       </c>
       <c r="H13" s="94" t="n">
-        <v>62.67</v>
+        <v>99.77</v>
       </c>
       <c r="I13" s="94" t="n">
-        <v>99.77</v>
+        <v>99.48</v>
       </c>
       <c r="J13" s="94" t="n">
         <v>99.48</v>
@@ -7784,55 +7783,55 @@
         <v>99.48</v>
       </c>
       <c r="O13" s="94" t="n">
-        <v>99.48</v>
+        <v>98.62</v>
       </c>
       <c r="P13" s="94" t="n">
-        <v>99.48</v>
+        <v>96</v>
       </c>
       <c r="Q13" s="94" t="n">
-        <v>98.62</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="R13" s="94" t="n">
-        <v>98.62</v>
+        <v>88.09</v>
       </c>
       <c r="S13" s="94" t="n">
-        <v>96</v>
+        <v>30.34</v>
       </c>
       <c r="T13" s="94" t="n">
-        <v>91.40000000000001</v>
+        <v>39.51</v>
       </c>
       <c r="U13" s="94" t="n">
-        <v>88.09</v>
+        <v>58.67</v>
       </c>
       <c r="V13" s="94" t="n">
-        <v>30.34</v>
+        <v>28.04</v>
       </c>
       <c r="W13" s="94" t="n">
-        <v>39.51</v>
+        <v>29.98</v>
       </c>
       <c r="X13" s="94" t="n">
-        <v>39.51</v>
+        <v>29.98</v>
       </c>
       <c r="Y13" s="94" t="n">
-        <v>58.67</v>
+        <v>29.98</v>
       </c>
       <c r="Z13" s="94" t="n">
-        <v>28.04</v>
+        <v>54.57</v>
       </c>
       <c r="AA13" s="94" t="n">
-        <v>29.98</v>
+        <v>69.45</v>
       </c>
       <c r="AB13" s="94" t="n">
-        <v>29.98</v>
+        <v>37.43</v>
       </c>
       <c r="AC13" s="94" t="n">
-        <v>29.98</v>
+        <v>35.11</v>
       </c>
       <c r="AD13" s="94" t="n">
-        <v>29.98</v>
+        <v>33.41</v>
       </c>
       <c r="AE13" s="94" t="n">
-        <v>54.57</v>
+        <v>64.26000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -7866,129 +7865,129 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="G14" s="91" t="inlineStr">
+      <c r="G14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H14" s="93" t="inlineStr">
+      <c r="I14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Z14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="J14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="AB14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -8014,79 +8013,79 @@
         <v>17.96</v>
       </c>
       <c r="G15" s="94" t="n">
-        <v>17.96</v>
+        <v>12.81</v>
       </c>
       <c r="H15" s="94" t="n">
-        <v>12.81</v>
+        <v>17.35</v>
       </c>
       <c r="I15" s="94" t="n">
-        <v>17.35</v>
+        <v>32.21</v>
       </c>
       <c r="J15" s="94" t="n">
-        <v>32.21</v>
+        <v>29.75</v>
       </c>
       <c r="K15" s="94" t="n">
-        <v>29.75</v>
+        <v>26.19</v>
       </c>
       <c r="L15" s="94" t="n">
-        <v>29.75</v>
+        <v>26.09</v>
       </c>
       <c r="M15" s="94" t="n">
-        <v>26.19</v>
+        <v>17.23</v>
       </c>
       <c r="N15" s="94" t="n">
-        <v>26.09</v>
+        <v>17.23</v>
       </c>
       <c r="O15" s="94" t="n">
-        <v>17.23</v>
+        <v>14.76</v>
       </c>
       <c r="P15" s="94" t="n">
-        <v>17.23</v>
+        <v>12.13</v>
       </c>
       <c r="Q15" s="94" t="n">
-        <v>14.76</v>
+        <v>7.96</v>
       </c>
       <c r="R15" s="94" t="n">
-        <v>14.76</v>
+        <v>7.25</v>
       </c>
       <c r="S15" s="94" t="n">
-        <v>12.13</v>
+        <v>0.87</v>
       </c>
       <c r="T15" s="94" t="n">
-        <v>7.96</v>
+        <v>1.03</v>
       </c>
       <c r="U15" s="94" t="n">
-        <v>7.25</v>
+        <v>-0.08</v>
       </c>
       <c r="V15" s="94" t="n">
-        <v>0.87</v>
+        <v>-2.04</v>
       </c>
       <c r="W15" s="94" t="n">
-        <v>1.03</v>
+        <v>-2.04</v>
       </c>
       <c r="X15" s="94" t="n">
-        <v>1.03</v>
+        <v>-4.98</v>
       </c>
       <c r="Y15" s="94" t="n">
-        <v>-0.08</v>
+        <v>-5.76</v>
       </c>
       <c r="Z15" s="94" t="n">
-        <v>-2.04</v>
+        <v>-3.77</v>
       </c>
       <c r="AA15" s="94" t="n">
-        <v>-2.04</v>
+        <v>-4.61</v>
       </c>
       <c r="AB15" s="94" t="n">
-        <v>-4.98</v>
+        <v>-3.94</v>
       </c>
       <c r="AC15" s="94" t="n">
-        <v>-5.76</v>
+        <v>-5.06</v>
       </c>
       <c r="AD15" s="94" t="n">
-        <v>-5.76</v>
+        <v>-2.75</v>
       </c>
       <c r="AE15" s="94" t="n">
-        <v>-3.77</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="16">
@@ -8111,79 +8110,79 @@
         <v>30.79</v>
       </c>
       <c r="G16" s="94" t="n">
-        <v>30.79</v>
+        <v>24.32</v>
       </c>
       <c r="H16" s="94" t="n">
-        <v>24.32</v>
+        <v>25.15</v>
       </c>
       <c r="I16" s="94" t="n">
-        <v>25.15</v>
+        <v>35.13</v>
       </c>
       <c r="J16" s="94" t="n">
-        <v>35.13</v>
+        <v>32.66</v>
       </c>
       <c r="K16" s="94" t="n">
-        <v>32.66</v>
+        <v>31.41</v>
       </c>
       <c r="L16" s="94" t="n">
-        <v>32.66</v>
+        <v>34.13</v>
       </c>
       <c r="M16" s="94" t="n">
-        <v>31.41</v>
+        <v>26.37</v>
       </c>
       <c r="N16" s="94" t="n">
-        <v>34.13</v>
+        <v>26.37</v>
       </c>
       <c r="O16" s="94" t="n">
-        <v>26.37</v>
+        <v>23.36</v>
       </c>
       <c r="P16" s="94" t="n">
-        <v>26.37</v>
+        <v>17.68</v>
       </c>
       <c r="Q16" s="94" t="n">
-        <v>23.36</v>
+        <v>15.64</v>
       </c>
       <c r="R16" s="94" t="n">
-        <v>23.36</v>
+        <v>15.91</v>
       </c>
       <c r="S16" s="94" t="n">
-        <v>17.68</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="T16" s="94" t="n">
-        <v>15.64</v>
+        <v>10.84</v>
       </c>
       <c r="U16" s="94" t="n">
-        <v>15.91</v>
+        <v>9.17</v>
       </c>
       <c r="V16" s="94" t="n">
-        <v>9.800000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="W16" s="94" t="n">
-        <v>10.84</v>
+        <v>4.73</v>
       </c>
       <c r="X16" s="94" t="n">
-        <v>10.84</v>
+        <v>5.31</v>
       </c>
       <c r="Y16" s="94" t="n">
-        <v>9.17</v>
+        <v>5.08</v>
       </c>
       <c r="Z16" s="94" t="n">
-        <v>4.73</v>
+        <v>3.01</v>
       </c>
       <c r="AA16" s="94" t="n">
-        <v>4.73</v>
+        <v>2.32</v>
       </c>
       <c r="AB16" s="94" t="n">
-        <v>5.31</v>
+        <v>1.61</v>
       </c>
       <c r="AC16" s="94" t="n">
-        <v>5.08</v>
+        <v>0.67</v>
       </c>
       <c r="AD16" s="94" t="n">
-        <v>5.08</v>
+        <v>2.05</v>
       </c>
       <c r="AE16" s="94" t="n">
-        <v>3.01</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="17">
@@ -8208,79 +8207,79 @@
         <v>48.87</v>
       </c>
       <c r="G17" s="94" t="n">
-        <v>48.87</v>
+        <v>35.54</v>
       </c>
       <c r="H17" s="94" t="n">
-        <v>35.54</v>
+        <v>39.14</v>
       </c>
       <c r="I17" s="94" t="n">
-        <v>39.14</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="J17" s="94" t="n">
-        <v>91.23999999999999</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="K17" s="94" t="n">
-        <v>89.48999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="L17" s="94" t="n">
-        <v>89.48999999999999</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="M17" s="94" t="n">
-        <v>85.84</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="N17" s="94" t="n">
-        <v>99.56999999999999</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="O17" s="94" t="n">
-        <v>99.18000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="P17" s="94" t="n">
-        <v>99.18000000000001</v>
+        <v>98.23</v>
       </c>
       <c r="Q17" s="94" t="n">
-        <v>98.89</v>
+        <v>96.44</v>
       </c>
       <c r="R17" s="94" t="n">
-        <v>98.89</v>
+        <v>95.94</v>
       </c>
       <c r="S17" s="94" t="n">
-        <v>98.23</v>
+        <v>89.48</v>
       </c>
       <c r="T17" s="94" t="n">
-        <v>96.44</v>
+        <v>91.13</v>
       </c>
       <c r="U17" s="94" t="n">
-        <v>95.94</v>
+        <v>87.39</v>
       </c>
       <c r="V17" s="94" t="n">
-        <v>89.48</v>
+        <v>76.86</v>
       </c>
       <c r="W17" s="94" t="n">
-        <v>91.13</v>
+        <v>76.86</v>
       </c>
       <c r="X17" s="94" t="n">
-        <v>91.13</v>
+        <v>59.96</v>
       </c>
       <c r="Y17" s="94" t="n">
-        <v>87.39</v>
+        <v>54.39</v>
       </c>
       <c r="Z17" s="94" t="n">
-        <v>76.86</v>
+        <v>38.93</v>
       </c>
       <c r="AA17" s="94" t="n">
-        <v>76.86</v>
+        <v>17.46</v>
       </c>
       <c r="AB17" s="94" t="n">
-        <v>59.96</v>
+        <v>23.32</v>
       </c>
       <c r="AC17" s="94" t="n">
-        <v>54.39</v>
+        <v>17.15</v>
       </c>
       <c r="AD17" s="94" t="n">
-        <v>54.39</v>
+        <v>28.67</v>
       </c>
       <c r="AE17" s="94" t="n">
-        <v>38.93</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="18">
@@ -8289,154 +8288,154 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="91" t="inlineStr">
+      <c r="B18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C18" s="91" t="inlineStr">
+      <c r="D18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="E18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D18" s="92" t="inlineStr">
+      <c r="L18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E18" s="92" t="inlineStr">
+      <c r="S18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F18" s="92" t="inlineStr">
+      <c r="T18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G18" s="92" t="inlineStr">
+      <c r="U18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H18" s="92" t="inlineStr">
+      <c r="V18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I18" s="92" t="inlineStr">
+      <c r="X18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J18" s="93" t="inlineStr">
+      <c r="Y18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AC18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="AD18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -8447,7 +8446,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>4.51</v>
+        <v>5.16</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>4.51</v>
@@ -8459,82 +8458,82 @@
         <v>4.88</v>
       </c>
       <c r="F19" s="94" t="n">
-        <v>4.88</v>
+        <v>3.43</v>
       </c>
       <c r="G19" s="94" t="n">
-        <v>3.43</v>
+        <v>2.2</v>
       </c>
       <c r="H19" s="94" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="I19" s="94" t="n">
-        <v>2.13</v>
+        <v>1.44</v>
       </c>
       <c r="J19" s="94" t="n">
-        <v>1.44</v>
+        <v>2.98</v>
       </c>
       <c r="K19" s="94" t="n">
-        <v>2.98</v>
+        <v>1.17</v>
       </c>
       <c r="L19" s="94" t="n">
-        <v>2.98</v>
+        <v>2.38</v>
       </c>
       <c r="M19" s="94" t="n">
-        <v>1.17</v>
+        <v>2.44</v>
       </c>
       <c r="N19" s="94" t="n">
-        <v>2.38</v>
+        <v>3.51</v>
       </c>
       <c r="O19" s="94" t="n">
-        <v>2.44</v>
+        <v>3.63</v>
       </c>
       <c r="P19" s="94" t="n">
-        <v>3.51</v>
+        <v>4.29</v>
       </c>
       <c r="Q19" s="94" t="n">
-        <v>3.63</v>
+        <v>4.51</v>
       </c>
       <c r="R19" s="94" t="n">
-        <v>3.63</v>
+        <v>4.99</v>
       </c>
       <c r="S19" s="94" t="n">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="T19" s="94" t="n">
-        <v>4.51</v>
+        <v>4.1</v>
       </c>
       <c r="U19" s="94" t="n">
-        <v>4.99</v>
+        <v>4.47</v>
       </c>
       <c r="V19" s="94" t="n">
-        <v>4.3</v>
+        <v>3.13</v>
       </c>
       <c r="W19" s="94" t="n">
-        <v>4.1</v>
+        <v>3.11</v>
       </c>
       <c r="X19" s="94" t="n">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="Y19" s="94" t="n">
-        <v>4.47</v>
+        <v>2.53</v>
       </c>
       <c r="Z19" s="94" t="n">
-        <v>3.13</v>
+        <v>2.24</v>
       </c>
       <c r="AA19" s="94" t="n">
-        <v>3.11</v>
+        <v>2.26</v>
       </c>
       <c r="AB19" s="94" t="n">
-        <v>2.92</v>
+        <v>1.14</v>
       </c>
       <c r="AC19" s="94" t="n">
-        <v>2.53</v>
+        <v>0.92</v>
       </c>
       <c r="AD19" s="94" t="n">
-        <v>2.53</v>
+        <v>0.62</v>
       </c>
       <c r="AE19" s="94" t="n">
-        <v>2.24</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="20">
@@ -8544,7 +8543,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>14.66</v>
+        <v>15.73</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>14.66</v>
@@ -8556,82 +8555,82 @@
         <v>16.05</v>
       </c>
       <c r="F20" s="94" t="n">
-        <v>16.05</v>
+        <v>16.36</v>
       </c>
       <c r="G20" s="94" t="n">
-        <v>16.36</v>
+        <v>15.58</v>
       </c>
       <c r="H20" s="94" t="n">
-        <v>15.58</v>
+        <v>14.51</v>
       </c>
       <c r="I20" s="94" t="n">
-        <v>14.51</v>
+        <v>12.76</v>
       </c>
       <c r="J20" s="94" t="n">
-        <v>12.76</v>
+        <v>13.62</v>
       </c>
       <c r="K20" s="94" t="n">
-        <v>13.62</v>
+        <v>11.25</v>
       </c>
       <c r="L20" s="94" t="n">
-        <v>13.62</v>
+        <v>9.82</v>
       </c>
       <c r="M20" s="94" t="n">
-        <v>11.25</v>
+        <v>10.62</v>
       </c>
       <c r="N20" s="94" t="n">
-        <v>9.82</v>
+        <v>10.61</v>
       </c>
       <c r="O20" s="94" t="n">
-        <v>10.62</v>
+        <v>10.3</v>
       </c>
       <c r="P20" s="94" t="n">
-        <v>10.61</v>
+        <v>10.4</v>
       </c>
       <c r="Q20" s="94" t="n">
-        <v>10.3</v>
+        <v>11.17</v>
       </c>
       <c r="R20" s="94" t="n">
-        <v>10.3</v>
+        <v>10.01</v>
       </c>
       <c r="S20" s="94" t="n">
-        <v>10.4</v>
+        <v>9.85</v>
       </c>
       <c r="T20" s="94" t="n">
-        <v>11.17</v>
+        <v>8.75</v>
       </c>
       <c r="U20" s="94" t="n">
-        <v>10.01</v>
+        <v>8.74</v>
       </c>
       <c r="V20" s="94" t="n">
-        <v>9.85</v>
+        <v>7.05</v>
       </c>
       <c r="W20" s="94" t="n">
-        <v>8.75</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="X20" s="94" t="n">
-        <v>8.75</v>
+        <v>7.95</v>
       </c>
       <c r="Y20" s="94" t="n">
-        <v>8.74</v>
+        <v>7.49</v>
       </c>
       <c r="Z20" s="94" t="n">
-        <v>7.05</v>
+        <v>6.76</v>
       </c>
       <c r="AA20" s="94" t="n">
-        <v>8.279999999999999</v>
+        <v>6.31</v>
       </c>
       <c r="AB20" s="94" t="n">
-        <v>7.95</v>
+        <v>6.12</v>
       </c>
       <c r="AC20" s="94" t="n">
-        <v>7.49</v>
+        <v>6.25</v>
       </c>
       <c r="AD20" s="94" t="n">
-        <v>7.49</v>
+        <v>5.69</v>
       </c>
       <c r="AE20" s="94" t="n">
-        <v>6.76</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="21">
@@ -8641,7 +8640,7 @@
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>43.25</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>43.25</v>
@@ -8653,82 +8652,82 @@
         <v>84.56999999999999</v>
       </c>
       <c r="F21" s="94" t="n">
-        <v>84.56999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="G21" s="94" t="n">
-        <v>65.7</v>
+        <v>83.12</v>
       </c>
       <c r="H21" s="94" t="n">
-        <v>83.12</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="I21" s="94" t="n">
-        <v>69.18000000000001</v>
+        <v>30.41</v>
       </c>
       <c r="J21" s="94" t="n">
-        <v>30.41</v>
+        <v>81.84</v>
       </c>
       <c r="K21" s="94" t="n">
-        <v>81.84</v>
+        <v>15.76</v>
       </c>
       <c r="L21" s="94" t="n">
-        <v>81.84</v>
+        <v>23.93</v>
       </c>
       <c r="M21" s="94" t="n">
-        <v>15.76</v>
+        <v>22.27</v>
       </c>
       <c r="N21" s="94" t="n">
-        <v>23.93</v>
+        <v>86.19</v>
       </c>
       <c r="O21" s="94" t="n">
-        <v>22.27</v>
+        <v>60.63</v>
       </c>
       <c r="P21" s="94" t="n">
-        <v>86.19</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="Q21" s="94" t="n">
-        <v>60.63</v>
+        <v>58.19</v>
       </c>
       <c r="R21" s="94" t="n">
-        <v>60.63</v>
+        <v>90.16</v>
       </c>
       <c r="S21" s="94" t="n">
-        <v>83.51000000000001</v>
+        <v>84.39</v>
       </c>
       <c r="T21" s="94" t="n">
-        <v>58.19</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="U21" s="94" t="n">
-        <v>90.16</v>
+        <v>92.34</v>
       </c>
       <c r="V21" s="94" t="n">
-        <v>84.39</v>
+        <v>40.89</v>
       </c>
       <c r="W21" s="94" t="n">
-        <v>76.79000000000001</v>
+        <v>96.09</v>
       </c>
       <c r="X21" s="94" t="n">
-        <v>76.79000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="Y21" s="94" t="n">
-        <v>92.34</v>
+        <v>95.06</v>
       </c>
       <c r="Z21" s="94" t="n">
-        <v>40.89</v>
+        <v>91.83</v>
       </c>
       <c r="AA21" s="94" t="n">
-        <v>96.09</v>
+        <v>85.17</v>
       </c>
       <c r="AB21" s="94" t="n">
-        <v>95.83</v>
+        <v>65.2</v>
       </c>
       <c r="AC21" s="94" t="n">
-        <v>95.06</v>
+        <v>51.58</v>
       </c>
       <c r="AD21" s="94" t="n">
-        <v>95.06</v>
+        <v>3</v>
       </c>
       <c r="AE21" s="94" t="n">
-        <v>91.83</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="22">
@@ -8737,154 +8736,154 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="91" t="inlineStr">
+      <c r="B22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C22" s="91" t="inlineStr">
+      <c r="D22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="E22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D22" s="92" t="inlineStr">
+      <c r="I22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E22" s="92" t="inlineStr">
+      <c r="K22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F22" s="92" t="inlineStr">
+      <c r="S22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G22" s="92" t="inlineStr">
+      <c r="T22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H22" s="92" t="inlineStr">
+      <c r="U22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I22" s="91" t="inlineStr">
+      <c r="V22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J22" s="93" t="inlineStr">
+      <c r="AD22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="AE22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -8895,7 +8894,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>5.75</v>
+        <v>6.74</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>5.75</v>
@@ -8907,82 +8906,82 @@
         <v>5.41</v>
       </c>
       <c r="F23" s="94" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G23" s="94" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H23" s="94" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="I23" s="94" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="J23" s="94" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="K23" s="94" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="L23" s="94" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="M23" s="94" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="N23" s="94" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O23" s="94" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="P23" s="94" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="Q23" s="94" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="R23" s="94" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="S23" s="94" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="T23" s="94" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="U23" s="94" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="V23" s="94" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="W23" s="94" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="X23" s="94" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="Y23" s="94" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="Z23" s="94" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AA23" s="94" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AB23" s="94" t="n">
         <v>5.41</v>
       </c>
-      <c r="G23" s="94" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="H23" s="94" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I23" s="94" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="J23" s="94" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="K23" s="94" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="L23" s="94" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="M23" s="94" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="N23" s="94" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="O23" s="94" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="P23" s="94" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q23" s="94" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="R23" s="94" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="S23" s="94" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="T23" s="94" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="U23" s="94" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="V23" s="94" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="W23" s="94" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="X23" s="94" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y23" s="94" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="Z23" s="94" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="AA23" s="94" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="AB23" s="94" t="n">
-        <v>6.36</v>
-      </c>
       <c r="AC23" s="94" t="n">
-        <v>6.59</v>
+        <v>5.47</v>
       </c>
       <c r="AD23" s="94" t="n">
-        <v>6.59</v>
+        <v>4.12</v>
       </c>
       <c r="AE23" s="94" t="n">
-        <v>5.98</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="24">
@@ -8992,7 +8991,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>11.13</v>
+        <v>13.11</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>11.13</v>
@@ -9004,82 +9003,82 @@
         <v>12.09</v>
       </c>
       <c r="F24" s="94" t="n">
-        <v>12.09</v>
+        <v>11.76</v>
       </c>
       <c r="G24" s="94" t="n">
-        <v>11.76</v>
+        <v>12.54</v>
       </c>
       <c r="H24" s="94" t="n">
-        <v>12.54</v>
+        <v>11.46</v>
       </c>
       <c r="I24" s="94" t="n">
-        <v>11.46</v>
+        <v>10.99</v>
       </c>
       <c r="J24" s="94" t="n">
-        <v>10.99</v>
+        <v>12.24</v>
       </c>
       <c r="K24" s="94" t="n">
-        <v>12.24</v>
+        <v>10.61</v>
       </c>
       <c r="L24" s="94" t="n">
-        <v>12.24</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M24" s="94" t="n">
-        <v>10.61</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="N24" s="94" t="n">
-        <v>9.720000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="O24" s="94" t="n">
-        <v>9.609999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="P24" s="94" t="n">
-        <v>8.859999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="Q24" s="94" t="n">
-        <v>8.789999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="R24" s="94" t="n">
-        <v>8.789999999999999</v>
+        <v>7.87</v>
       </c>
       <c r="S24" s="94" t="n">
-        <v>8.41</v>
+        <v>7.54</v>
       </c>
       <c r="T24" s="94" t="n">
-        <v>8.6</v>
+        <v>6.31</v>
       </c>
       <c r="U24" s="94" t="n">
-        <v>7.87</v>
+        <v>5.57</v>
       </c>
       <c r="V24" s="94" t="n">
-        <v>7.54</v>
+        <v>4.38</v>
       </c>
       <c r="W24" s="94" t="n">
-        <v>6.31</v>
+        <v>5.92</v>
       </c>
       <c r="X24" s="94" t="n">
-        <v>6.31</v>
+        <v>5.87</v>
       </c>
       <c r="Y24" s="94" t="n">
-        <v>5.57</v>
+        <v>4.86</v>
       </c>
       <c r="Z24" s="94" t="n">
-        <v>4.38</v>
+        <v>3.31</v>
       </c>
       <c r="AA24" s="94" t="n">
-        <v>5.92</v>
+        <v>3.42</v>
       </c>
       <c r="AB24" s="94" t="n">
-        <v>5.87</v>
+        <v>4.16</v>
       </c>
       <c r="AC24" s="94" t="n">
-        <v>4.86</v>
+        <v>5.26</v>
       </c>
       <c r="AD24" s="94" t="n">
-        <v>4.86</v>
+        <v>4.21</v>
       </c>
       <c r="AE24" s="94" t="n">
-        <v>3.31</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="25">
@@ -9089,7 +9088,7 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>53.27</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>53.27</v>
@@ -9101,82 +9100,82 @@
         <v>82.94</v>
       </c>
       <c r="F25" s="94" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="G25" s="94" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="H25" s="94" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="I25" s="94" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="J25" s="94" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="K25" s="94" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="L25" s="94" t="n">
+        <v>52.09</v>
+      </c>
+      <c r="M25" s="94" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="N25" s="94" t="n">
+        <v>76.02</v>
+      </c>
+      <c r="O25" s="94" t="n">
+        <v>74.91</v>
+      </c>
+      <c r="P25" s="94" t="n">
+        <v>66.62</v>
+      </c>
+      <c r="Q25" s="94" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="R25" s="94" t="n">
+        <v>92.18000000000001</v>
+      </c>
+      <c r="S25" s="94" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="T25" s="94" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="U25" s="94" t="n">
+        <v>87.58</v>
+      </c>
+      <c r="V25" s="94" t="n">
+        <v>65.31</v>
+      </c>
+      <c r="W25" s="94" t="n">
+        <v>85.48999999999999</v>
+      </c>
+      <c r="X25" s="94" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="Y25" s="94" t="n">
         <v>82.94</v>
       </c>
-      <c r="G25" s="94" t="n">
-        <v>66.56</v>
-      </c>
-      <c r="H25" s="94" t="n">
-        <v>73.18000000000001</v>
-      </c>
-      <c r="I25" s="94" t="n">
-        <v>46.98</v>
-      </c>
-      <c r="J25" s="94" t="n">
-        <v>34.52</v>
-      </c>
-      <c r="K25" s="94" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="L25" s="94" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="M25" s="94" t="n">
-        <v>28.19</v>
-      </c>
-      <c r="N25" s="94" t="n">
-        <v>52.09</v>
-      </c>
-      <c r="O25" s="94" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="P25" s="94" t="n">
-        <v>76.02</v>
-      </c>
-      <c r="Q25" s="94" t="n">
-        <v>74.91</v>
-      </c>
-      <c r="R25" s="94" t="n">
-        <v>74.91</v>
-      </c>
-      <c r="S25" s="94" t="n">
-        <v>66.62</v>
-      </c>
-      <c r="T25" s="94" t="n">
-        <v>42.84</v>
-      </c>
-      <c r="U25" s="94" t="n">
-        <v>92.18000000000001</v>
-      </c>
-      <c r="V25" s="94" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="W25" s="94" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="X25" s="94" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="Y25" s="94" t="n">
-        <v>87.58</v>
-      </c>
       <c r="Z25" s="94" t="n">
-        <v>65.31</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="AA25" s="94" t="n">
-        <v>85.48999999999999</v>
+        <v>56.57</v>
       </c>
       <c r="AB25" s="94" t="n">
-        <v>88.3</v>
+        <v>46.45</v>
       </c>
       <c r="AC25" s="94" t="n">
-        <v>82.94</v>
+        <v>52.5</v>
       </c>
       <c r="AD25" s="94" t="n">
-        <v>82.94</v>
+        <v>13.02</v>
       </c>
       <c r="AE25" s="94" t="n">
-        <v>71.68000000000001</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="26">
@@ -9220,119 +9219,119 @@
           <t>red</t>
         </is>
       </c>
-      <c r="I26" s="92" t="inlineStr">
+      <c r="I26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J26" s="93" t="inlineStr">
+      <c r="K26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AC26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="AD26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -9343,7 +9342,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>1.71</v>
@@ -9355,82 +9354,82 @@
         <v>2.64</v>
       </c>
       <c r="F27" s="94" t="n">
-        <v>2.64</v>
+        <v>1.58</v>
       </c>
       <c r="G27" s="94" t="n">
-        <v>1.58</v>
+        <v>-1.18</v>
       </c>
       <c r="H27" s="94" t="n">
-        <v>-1.18</v>
+        <v>-1.57</v>
       </c>
       <c r="I27" s="94" t="n">
-        <v>-1.57</v>
+        <v>-2.58</v>
       </c>
       <c r="J27" s="94" t="n">
-        <v>-2.58</v>
+        <v>-0.8</v>
       </c>
       <c r="K27" s="94" t="n">
-        <v>-0.8</v>
+        <v>-3.91</v>
       </c>
       <c r="L27" s="94" t="n">
-        <v>-0.8</v>
+        <v>-2.74</v>
       </c>
       <c r="M27" s="94" t="n">
-        <v>-3.91</v>
+        <v>-2.68</v>
       </c>
       <c r="N27" s="94" t="n">
-        <v>-2.74</v>
+        <v>-0.89</v>
       </c>
       <c r="O27" s="94" t="n">
-        <v>-2.68</v>
+        <v>-0.38</v>
       </c>
       <c r="P27" s="94" t="n">
-        <v>-0.89</v>
+        <v>0.9</v>
       </c>
       <c r="Q27" s="94" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="R27" s="94" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S27" s="94" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="T27" s="94" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U27" s="94" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V27" s="94" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="W27" s="94" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="X27" s="94" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="Y27" s="94" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z27" s="94" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="AA27" s="94" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="AB27" s="94" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="AC27" s="94" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="AD27" s="94" t="n">
+        <v>-3.76</v>
+      </c>
+      <c r="AE27" s="94" t="n">
         <v>-0.38</v>
-      </c>
-      <c r="R27" s="94" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="S27" s="94" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T27" s="94" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="U27" s="94" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="V27" s="94" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="W27" s="94" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="X27" s="94" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Y27" s="94" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z27" s="94" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="AA27" s="94" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="AB27" s="94" t="n">
-        <v>-0.73</v>
-      </c>
-      <c r="AC27" s="94" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD27" s="94" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AE27" s="94" t="n">
-        <v>-1.61</v>
       </c>
     </row>
     <row r="28">
@@ -9440,7 +9439,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>16.57</v>
+        <v>17.65</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>16.57</v>
@@ -9452,92 +9451,92 @@
         <v>18.71</v>
       </c>
       <c r="F28" s="94" t="n">
-        <v>18.71</v>
+        <v>19.63</v>
       </c>
       <c r="G28" s="94" t="n">
-        <v>19.63</v>
+        <v>17.24</v>
       </c>
       <c r="H28" s="94" t="n">
-        <v>17.24</v>
+        <v>15.94</v>
       </c>
       <c r="I28" s="94" t="n">
-        <v>15.94</v>
+        <v>12.98</v>
       </c>
       <c r="J28" s="94" t="n">
-        <v>12.98</v>
+        <v>14.18</v>
       </c>
       <c r="K28" s="94" t="n">
-        <v>14.18</v>
+        <v>10.78</v>
       </c>
       <c r="L28" s="94" t="n">
-        <v>14.18</v>
+        <v>9.02</v>
       </c>
       <c r="M28" s="94" t="n">
-        <v>10.78</v>
+        <v>10.76</v>
       </c>
       <c r="N28" s="94" t="n">
-        <v>9.02</v>
+        <v>11.54</v>
       </c>
       <c r="O28" s="94" t="n">
-        <v>10.76</v>
+        <v>11.48</v>
       </c>
       <c r="P28" s="94" t="n">
-        <v>11.54</v>
+        <v>11.95</v>
       </c>
       <c r="Q28" s="94" t="n">
-        <v>11.48</v>
+        <v>12.67</v>
       </c>
       <c r="R28" s="94" t="n">
-        <v>11.48</v>
+        <v>11.04</v>
       </c>
       <c r="S28" s="94" t="n">
-        <v>11.95</v>
+        <v>10.68</v>
       </c>
       <c r="T28" s="94" t="n">
-        <v>12.67</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="U28" s="94" t="n">
-        <v>11.04</v>
+        <v>9.98</v>
       </c>
       <c r="V28" s="94" t="n">
-        <v>10.68</v>
+        <v>7.16</v>
       </c>
       <c r="W28" s="94" t="n">
-        <v>9.460000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="X28" s="94" t="n">
-        <v>9.460000000000001</v>
+        <v>7.37</v>
       </c>
       <c r="Y28" s="94" t="n">
-        <v>9.98</v>
+        <v>7.64</v>
       </c>
       <c r="Z28" s="94" t="n">
-        <v>7.16</v>
+        <v>7.12</v>
       </c>
       <c r="AA28" s="94" t="n">
-        <v>8.039999999999999</v>
+        <v>6.27</v>
       </c>
       <c r="AB28" s="94" t="n">
-        <v>7.37</v>
+        <v>5.31</v>
       </c>
       <c r="AC28" s="94" t="n">
-        <v>7.64</v>
+        <v>4.85</v>
       </c>
       <c r="AD28" s="94" t="n">
-        <v>7.64</v>
+        <v>4.49</v>
       </c>
       <c r="AE28" s="94" t="n">
-        <v>7.12</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="96" t="inlineStr">
+      <c r="A29" s="76" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>36.8</v>
+        <v>52.8</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>36.8</v>
@@ -9549,82 +9548,82 @@
         <v>86.79000000000001</v>
       </c>
       <c r="F29" s="94" t="n">
-        <v>86.79000000000001</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="G29" s="94" t="n">
-        <v>77.45999999999999</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="H29" s="94" t="n">
-        <v>82.01000000000001</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="I29" s="94" t="n">
-        <v>72.98999999999999</v>
+        <v>32.92</v>
       </c>
       <c r="J29" s="94" t="n">
-        <v>32.92</v>
+        <v>85.03</v>
       </c>
       <c r="K29" s="94" t="n">
-        <v>85.03</v>
+        <v>20.54</v>
       </c>
       <c r="L29" s="94" t="n">
-        <v>85.03</v>
+        <v>21.97</v>
       </c>
       <c r="M29" s="94" t="n">
-        <v>20.54</v>
+        <v>15.42</v>
       </c>
       <c r="N29" s="94" t="n">
-        <v>21.97</v>
+        <v>74.7</v>
       </c>
       <c r="O29" s="94" t="n">
-        <v>15.42</v>
+        <v>51.35</v>
       </c>
       <c r="P29" s="94" t="n">
-        <v>74.7</v>
+        <v>96.66</v>
       </c>
       <c r="Q29" s="94" t="n">
-        <v>51.35</v>
+        <v>89.75</v>
       </c>
       <c r="R29" s="94" t="n">
-        <v>51.35</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="S29" s="94" t="n">
-        <v>96.66</v>
+        <v>77.02</v>
       </c>
       <c r="T29" s="94" t="n">
-        <v>89.75</v>
+        <v>73.3</v>
       </c>
       <c r="U29" s="94" t="n">
-        <v>88.93000000000001</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="V29" s="94" t="n">
-        <v>77.02</v>
+        <v>42.32</v>
       </c>
       <c r="W29" s="94" t="n">
-        <v>73.3</v>
+        <v>70.06</v>
       </c>
       <c r="X29" s="94" t="n">
-        <v>73.3</v>
+        <v>61.86</v>
       </c>
       <c r="Y29" s="94" t="n">
-        <v>92.18000000000001</v>
+        <v>95.17</v>
       </c>
       <c r="Z29" s="94" t="n">
-        <v>42.32</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="AA29" s="94" t="n">
-        <v>70.06</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="AB29" s="94" t="n">
-        <v>61.86</v>
+        <v>65.19</v>
       </c>
       <c r="AC29" s="94" t="n">
-        <v>95.17</v>
+        <v>44.48</v>
       </c>
       <c r="AD29" s="94" t="n">
-        <v>95.17</v>
+        <v>6.2</v>
       </c>
       <c r="AE29" s="94" t="n">
-        <v>92.73999999999999</v>
+        <v>27.81</v>
       </c>
     </row>
     <row r="30">
@@ -9653,134 +9652,134 @@
           <t>red</t>
         </is>
       </c>
-      <c r="F30" s="92" t="inlineStr">
+      <c r="F30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G30" s="91" t="inlineStr">
+      <c r="J30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H30" s="91" t="inlineStr">
+      <c r="K30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I30" s="91" t="inlineStr">
+      <c r="L30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J30" s="92" t="inlineStr">
+      <c r="N30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K30" s="91" t="inlineStr">
+      <c r="P30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L30" s="91" t="inlineStr">
+      <c r="W30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M30" s="91" t="inlineStr">
+      <c r="X30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N30" s="93" t="inlineStr">
+      <c r="Y30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Z30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="AB30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -9803,82 +9802,82 @@
         <v>-1.3</v>
       </c>
       <c r="F31" s="94" t="n">
-        <v>-1.3</v>
+        <v>-4.18</v>
       </c>
       <c r="G31" s="94" t="n">
-        <v>-4.18</v>
+        <v>-4.84</v>
       </c>
       <c r="H31" s="94" t="n">
-        <v>-4.84</v>
+        <v>-5.47</v>
       </c>
       <c r="I31" s="94" t="n">
-        <v>-5.47</v>
+        <v>-6.85</v>
       </c>
       <c r="J31" s="94" t="n">
-        <v>-6.85</v>
+        <v>-7.64</v>
       </c>
       <c r="K31" s="94" t="n">
-        <v>-7.64</v>
+        <v>-7.28</v>
       </c>
       <c r="L31" s="94" t="n">
-        <v>-7.64</v>
+        <v>-7.29</v>
       </c>
       <c r="M31" s="94" t="n">
-        <v>-7.28</v>
+        <v>-5.52</v>
       </c>
       <c r="N31" s="94" t="n">
-        <v>-7.29</v>
+        <v>-7.32</v>
       </c>
       <c r="O31" s="94" t="n">
-        <v>-5.52</v>
+        <v>-1.85</v>
       </c>
       <c r="P31" s="94" t="n">
-        <v>-7.32</v>
+        <v>-2.87</v>
       </c>
       <c r="Q31" s="94" t="n">
-        <v>-1.85</v>
+        <v>-4.44</v>
       </c>
       <c r="R31" s="94" t="n">
-        <v>-1.85</v>
+        <v>-4.15</v>
       </c>
       <c r="S31" s="94" t="n">
-        <v>-2.87</v>
+        <v>-4.11</v>
       </c>
       <c r="T31" s="94" t="n">
-        <v>-4.44</v>
+        <v>-4.11</v>
       </c>
       <c r="U31" s="94" t="n">
-        <v>-4.15</v>
+        <v>-6.33</v>
       </c>
       <c r="V31" s="94" t="n">
-        <v>-4.11</v>
+        <v>-7.13</v>
       </c>
       <c r="W31" s="94" t="n">
-        <v>-4.11</v>
+        <v>-6.7</v>
       </c>
       <c r="X31" s="94" t="n">
-        <v>-4.11</v>
+        <v>-5.28</v>
       </c>
       <c r="Y31" s="94" t="n">
-        <v>-6.33</v>
+        <v>-5.31</v>
       </c>
       <c r="Z31" s="94" t="n">
-        <v>-7.13</v>
+        <v>-4.5</v>
       </c>
       <c r="AA31" s="94" t="n">
+        <v>-7.44</v>
+      </c>
+      <c r="AB31" s="94" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="AC31" s="94" t="n">
         <v>-6.7</v>
       </c>
-      <c r="AB31" s="94" t="n">
-        <v>-5.28</v>
-      </c>
-      <c r="AC31" s="94" t="n">
-        <v>-5.31</v>
-      </c>
       <c r="AD31" s="94" t="n">
-        <v>-5.31</v>
+        <v>-6.01</v>
       </c>
       <c r="AE31" s="94" t="n">
-        <v>-4.5</v>
+        <v>-5.71</v>
       </c>
     </row>
     <row r="32">
@@ -9900,82 +9899,82 @@
         <v>6.85</v>
       </c>
       <c r="F32" s="94" t="n">
-        <v>6.85</v>
+        <v>3.42</v>
       </c>
       <c r="G32" s="94" t="n">
-        <v>3.42</v>
+        <v>3.47</v>
       </c>
       <c r="H32" s="94" t="n">
-        <v>3.47</v>
+        <v>1.21</v>
       </c>
       <c r="I32" s="94" t="n">
-        <v>1.21</v>
+        <v>0.25</v>
       </c>
       <c r="J32" s="94" t="n">
-        <v>0.25</v>
+        <v>-2.25</v>
       </c>
       <c r="K32" s="94" t="n">
-        <v>-2.25</v>
+        <v>-2.26</v>
       </c>
       <c r="L32" s="94" t="n">
-        <v>-2.25</v>
+        <v>-4.48</v>
       </c>
       <c r="M32" s="94" t="n">
-        <v>-2.26</v>
+        <v>-2.82</v>
       </c>
       <c r="N32" s="94" t="n">
-        <v>-4.48</v>
+        <v>-3.63</v>
       </c>
       <c r="O32" s="94" t="n">
-        <v>-2.82</v>
+        <v>2.15</v>
       </c>
       <c r="P32" s="94" t="n">
-        <v>-3.63</v>
+        <v>-2.13</v>
       </c>
       <c r="Q32" s="94" t="n">
-        <v>2.15</v>
+        <v>-4.01</v>
       </c>
       <c r="R32" s="94" t="n">
-        <v>2.15</v>
+        <v>-4.76</v>
       </c>
       <c r="S32" s="94" t="n">
-        <v>-2.13</v>
+        <v>-5.22</v>
       </c>
       <c r="T32" s="94" t="n">
-        <v>-4.01</v>
+        <v>-5.22</v>
       </c>
       <c r="U32" s="94" t="n">
-        <v>-4.76</v>
+        <v>-7.96</v>
       </c>
       <c r="V32" s="94" t="n">
-        <v>-5.22</v>
+        <v>-9.43</v>
       </c>
       <c r="W32" s="94" t="n">
-        <v>-5.22</v>
+        <v>-11.19</v>
       </c>
       <c r="X32" s="94" t="n">
-        <v>-5.22</v>
+        <v>-9.5</v>
       </c>
       <c r="Y32" s="94" t="n">
-        <v>-7.96</v>
+        <v>-9.48</v>
       </c>
       <c r="Z32" s="94" t="n">
-        <v>-9.43</v>
+        <v>-9.92</v>
       </c>
       <c r="AA32" s="94" t="n">
-        <v>-11.19</v>
+        <v>-12.73</v>
       </c>
       <c r="AB32" s="94" t="n">
-        <v>-9.5</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="AC32" s="94" t="n">
-        <v>-9.48</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="AD32" s="94" t="n">
-        <v>-9.48</v>
+        <v>-5.98</v>
       </c>
       <c r="AE32" s="94" t="n">
-        <v>-9.92</v>
+        <v>-5.54</v>
       </c>
     </row>
     <row r="33">
@@ -9997,82 +9996,82 @@
         <v>63.24</v>
       </c>
       <c r="F33" s="94" t="n">
-        <v>63.24</v>
+        <v>61.28</v>
       </c>
       <c r="G33" s="94" t="n">
-        <v>61.28</v>
+        <v>60.41</v>
       </c>
       <c r="H33" s="94" t="n">
-        <v>60.41</v>
+        <v>57.64</v>
       </c>
       <c r="I33" s="94" t="n">
-        <v>57.64</v>
+        <v>62.13</v>
       </c>
       <c r="J33" s="94" t="n">
-        <v>62.13</v>
+        <v>56.86</v>
       </c>
       <c r="K33" s="94" t="n">
-        <v>56.86</v>
+        <v>56.21</v>
       </c>
       <c r="L33" s="94" t="n">
-        <v>56.86</v>
+        <v>50.28</v>
       </c>
       <c r="M33" s="94" t="n">
-        <v>56.21</v>
+        <v>58.22</v>
       </c>
       <c r="N33" s="94" t="n">
-        <v>50.28</v>
+        <v>52.42</v>
       </c>
       <c r="O33" s="94" t="n">
-        <v>58.22</v>
+        <v>77.31</v>
       </c>
       <c r="P33" s="94" t="n">
-        <v>52.42</v>
+        <v>71.64</v>
       </c>
       <c r="Q33" s="94" t="n">
-        <v>77.31</v>
+        <v>61.74</v>
       </c>
       <c r="R33" s="94" t="n">
-        <v>77.31</v>
+        <v>63.04</v>
       </c>
       <c r="S33" s="94" t="n">
-        <v>71.64</v>
+        <v>60.77</v>
       </c>
       <c r="T33" s="94" t="n">
-        <v>61.74</v>
+        <v>60.77</v>
       </c>
       <c r="U33" s="94" t="n">
-        <v>63.04</v>
+        <v>54.21</v>
       </c>
       <c r="V33" s="94" t="n">
-        <v>60.77</v>
+        <v>42.56</v>
       </c>
       <c r="W33" s="94" t="n">
-        <v>60.77</v>
+        <v>39.44</v>
       </c>
       <c r="X33" s="94" t="n">
-        <v>60.77</v>
+        <v>43.68</v>
       </c>
       <c r="Y33" s="94" t="n">
-        <v>54.21</v>
+        <v>43.96</v>
       </c>
       <c r="Z33" s="94" t="n">
-        <v>42.56</v>
+        <v>46.79</v>
       </c>
       <c r="AA33" s="94" t="n">
-        <v>39.44</v>
+        <v>26.47</v>
       </c>
       <c r="AB33" s="94" t="n">
-        <v>43.68</v>
+        <v>31.18</v>
       </c>
       <c r="AC33" s="94" t="n">
-        <v>43.96</v>
+        <v>31.7</v>
       </c>
       <c r="AD33" s="94" t="n">
-        <v>43.96</v>
+        <v>33.25</v>
       </c>
       <c r="AE33" s="94" t="n">
-        <v>46.79</v>
+        <v>35.58</v>
       </c>
     </row>
     <row r="34">
@@ -10111,119 +10110,119 @@
           <t>red</t>
         </is>
       </c>
-      <c r="H34" s="92" t="inlineStr">
+      <c r="H34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I34" s="93" t="inlineStr">
+      <c r="P34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J34" s="93" t="inlineStr">
+      <c r="Y34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K34" s="93" t="inlineStr">
+      <c r="Z34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L34" s="93" t="inlineStr">
+      <c r="AA34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M34" s="93" t="inlineStr">
+      <c r="AB34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N34" s="91" t="inlineStr">
+      <c r="AC34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="O34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AE34" s="93" t="inlineStr">
@@ -10251,82 +10250,82 @@
         <v>1.56</v>
       </c>
       <c r="F35" s="94" t="n">
-        <v>1.56</v>
+        <v>0.4</v>
       </c>
       <c r="G35" s="94" t="n">
-        <v>0.4</v>
+        <v>0.16</v>
       </c>
       <c r="H35" s="94" t="n">
-        <v>0.16</v>
+        <v>-0.68</v>
       </c>
       <c r="I35" s="94" t="n">
-        <v>-0.68</v>
+        <v>-1.08</v>
       </c>
       <c r="J35" s="94" t="n">
-        <v>-1.08</v>
+        <v>-1.19</v>
       </c>
       <c r="K35" s="94" t="n">
-        <v>-1.19</v>
+        <v>-1.21</v>
       </c>
       <c r="L35" s="94" t="n">
-        <v>-1.19</v>
+        <v>0.33</v>
       </c>
       <c r="M35" s="94" t="n">
-        <v>-1.21</v>
+        <v>0.71</v>
       </c>
       <c r="N35" s="94" t="n">
-        <v>0.33</v>
+        <v>0.63</v>
       </c>
       <c r="O35" s="94" t="n">
-        <v>0.71</v>
+        <v>1.1</v>
       </c>
       <c r="P35" s="94" t="n">
-        <v>0.63</v>
+        <v>1.71</v>
       </c>
       <c r="Q35" s="94" t="n">
-        <v>1.1</v>
+        <v>2.62</v>
       </c>
       <c r="R35" s="94" t="n">
-        <v>1.1</v>
+        <v>1.79</v>
       </c>
       <c r="S35" s="94" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="T35" s="94" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="U35" s="94" t="n">
-        <v>1.79</v>
+        <v>0.8</v>
       </c>
       <c r="V35" s="94" t="n">
-        <v>1.86</v>
+        <v>0.66</v>
       </c>
       <c r="W35" s="94" t="n">
-        <v>1.03</v>
+        <v>0.39</v>
       </c>
       <c r="X35" s="94" t="n">
-        <v>1.03</v>
+        <v>-3.34</v>
       </c>
       <c r="Y35" s="94" t="n">
-        <v>0.8</v>
+        <v>-2.39</v>
       </c>
       <c r="Z35" s="94" t="n">
-        <v>0.66</v>
+        <v>-1.83</v>
       </c>
       <c r="AA35" s="94" t="n">
-        <v>0.39</v>
+        <v>-2.05</v>
       </c>
       <c r="AB35" s="94" t="n">
-        <v>-3.34</v>
+        <v>-1.53</v>
       </c>
       <c r="AC35" s="94" t="n">
-        <v>-2.39</v>
+        <v>-0.95</v>
       </c>
       <c r="AD35" s="94" t="n">
-        <v>-2.39</v>
+        <v>-2.12</v>
       </c>
       <c r="AE35" s="94" t="n">
-        <v>-1.83</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="36">
@@ -10348,82 +10347,82 @@
         <v>8.25</v>
       </c>
       <c r="F36" s="94" t="n">
-        <v>8.25</v>
+        <v>9.49</v>
       </c>
       <c r="G36" s="94" t="n">
-        <v>9.49</v>
+        <v>7.45</v>
       </c>
       <c r="H36" s="94" t="n">
-        <v>7.45</v>
+        <v>4.63</v>
       </c>
       <c r="I36" s="94" t="n">
-        <v>4.63</v>
+        <v>4.38</v>
       </c>
       <c r="J36" s="94" t="n">
-        <v>4.38</v>
+        <v>-0.47</v>
       </c>
       <c r="K36" s="94" t="n">
-        <v>-0.47</v>
+        <v>1.58</v>
       </c>
       <c r="L36" s="94" t="n">
-        <v>-0.47</v>
+        <v>2.33</v>
       </c>
       <c r="M36" s="94" t="n">
-        <v>1.58</v>
+        <v>2.33</v>
       </c>
       <c r="N36" s="94" t="n">
-        <v>2.33</v>
+        <v>3.01</v>
       </c>
       <c r="O36" s="94" t="n">
-        <v>2.33</v>
+        <v>2.85</v>
       </c>
       <c r="P36" s="94" t="n">
-        <v>3.01</v>
+        <v>1.83</v>
       </c>
       <c r="Q36" s="94" t="n">
-        <v>2.85</v>
+        <v>1.26</v>
       </c>
       <c r="R36" s="94" t="n">
-        <v>2.85</v>
+        <v>-0.78</v>
       </c>
       <c r="S36" s="94" t="n">
-        <v>1.83</v>
+        <v>-1.02</v>
       </c>
       <c r="T36" s="94" t="n">
-        <v>1.26</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="U36" s="94" t="n">
-        <v>-0.78</v>
+        <v>-1.47</v>
       </c>
       <c r="V36" s="94" t="n">
-        <v>-1.02</v>
+        <v>-1.42</v>
       </c>
       <c r="W36" s="94" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.81</v>
       </c>
       <c r="X36" s="94" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.26</v>
       </c>
       <c r="Y36" s="94" t="n">
-        <v>-1.47</v>
+        <v>-2.35</v>
       </c>
       <c r="Z36" s="94" t="n">
-        <v>-1.42</v>
+        <v>-1.57</v>
       </c>
       <c r="AA36" s="94" t="n">
-        <v>-1.81</v>
+        <v>-0.54</v>
       </c>
       <c r="AB36" s="94" t="n">
-        <v>-2.26</v>
+        <v>1.03</v>
       </c>
       <c r="AC36" s="94" t="n">
-        <v>-2.35</v>
+        <v>1.94</v>
       </c>
       <c r="AD36" s="94" t="n">
-        <v>-2.35</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AE36" s="94" t="n">
-        <v>-1.57</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="37">
@@ -10445,82 +10444,82 @@
         <v>81.64</v>
       </c>
       <c r="F37" s="94" t="n">
-        <v>81.64</v>
+        <v>78.16</v>
       </c>
       <c r="G37" s="94" t="n">
-        <v>78.16</v>
+        <v>69.63</v>
       </c>
       <c r="H37" s="94" t="n">
-        <v>69.63</v>
+        <v>29.45</v>
       </c>
       <c r="I37" s="94" t="n">
-        <v>29.45</v>
+        <v>13.62</v>
       </c>
       <c r="J37" s="94" t="n">
-        <v>13.62</v>
+        <v>14.32</v>
       </c>
       <c r="K37" s="94" t="n">
-        <v>14.32</v>
+        <v>23.23</v>
       </c>
       <c r="L37" s="94" t="n">
-        <v>14.32</v>
+        <v>50.34</v>
       </c>
       <c r="M37" s="94" t="n">
-        <v>23.23</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="N37" s="94" t="n">
-        <v>50.34</v>
+        <v>65.09</v>
       </c>
       <c r="O37" s="94" t="n">
-        <v>77.23999999999999</v>
+        <v>86.66</v>
       </c>
       <c r="P37" s="94" t="n">
-        <v>65.09</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="Q37" s="94" t="n">
-        <v>86.66</v>
+        <v>88</v>
       </c>
       <c r="R37" s="94" t="n">
-        <v>86.66</v>
+        <v>77.98</v>
       </c>
       <c r="S37" s="94" t="n">
-        <v>90.48999999999999</v>
+        <v>59.82</v>
       </c>
       <c r="T37" s="94" t="n">
-        <v>88</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="U37" s="94" t="n">
-        <v>77.98</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="V37" s="94" t="n">
-        <v>59.82</v>
+        <v>68.98</v>
       </c>
       <c r="W37" s="94" t="n">
-        <v>77.68000000000001</v>
+        <v>60.96</v>
       </c>
       <c r="X37" s="94" t="n">
-        <v>77.68000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Y37" s="94" t="n">
-        <v>76.68000000000001</v>
+        <v>20.58</v>
       </c>
       <c r="Z37" s="94" t="n">
-        <v>68.98</v>
+        <v>30.12</v>
       </c>
       <c r="AA37" s="94" t="n">
-        <v>60.96</v>
+        <v>12.08</v>
       </c>
       <c r="AB37" s="94" t="n">
-        <v>9.050000000000001</v>
+        <v>13.57</v>
       </c>
       <c r="AC37" s="94" t="n">
-        <v>20.58</v>
+        <v>28.44</v>
       </c>
       <c r="AD37" s="94" t="n">
-        <v>20.58</v>
+        <v>44.72</v>
       </c>
       <c r="AE37" s="94" t="n">
-        <v>30.12</v>
+        <v>14.66</v>
       </c>
     </row>
     <row r="38">
@@ -10554,129 +10553,129 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="G38" s="91" t="inlineStr">
+      <c r="G38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H38" s="93" t="inlineStr">
+      <c r="M38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I38" s="93" t="inlineStr">
+      <c r="AB38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AC38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J38" s="93" t="inlineStr">
+      <c r="AD38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K38" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="L38" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="M38" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N38" s="91" t="inlineStr">
+      <c r="AE38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="O38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -10687,7 +10686,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>1.64</v>
@@ -10699,82 +10698,82 @@
         <v>0.05</v>
       </c>
       <c r="F39" s="94" t="n">
-        <v>0.05</v>
+        <v>1.11</v>
       </c>
       <c r="G39" s="94" t="n">
-        <v>1.11</v>
+        <v>0.99</v>
       </c>
       <c r="H39" s="94" t="n">
-        <v>0.99</v>
+        <v>1.39</v>
       </c>
       <c r="I39" s="94" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="J39" s="94" t="n">
-        <v>1.44</v>
+        <v>2.21</v>
       </c>
       <c r="K39" s="94" t="n">
-        <v>2.21</v>
+        <v>2.67</v>
       </c>
       <c r="L39" s="94" t="n">
-        <v>2.21</v>
+        <v>5.39</v>
       </c>
       <c r="M39" s="94" t="n">
-        <v>2.67</v>
+        <v>5.39</v>
       </c>
       <c r="N39" s="94" t="n">
-        <v>5.39</v>
+        <v>5.38</v>
       </c>
       <c r="O39" s="94" t="n">
-        <v>5.39</v>
+        <v>6.9</v>
       </c>
       <c r="P39" s="94" t="n">
-        <v>5.38</v>
+        <v>7.31</v>
       </c>
       <c r="Q39" s="94" t="n">
-        <v>6.9</v>
+        <v>7.21</v>
       </c>
       <c r="R39" s="94" t="n">
-        <v>6.9</v>
+        <v>6.84</v>
       </c>
       <c r="S39" s="94" t="n">
-        <v>7.31</v>
+        <v>7.46</v>
       </c>
       <c r="T39" s="94" t="n">
-        <v>7.21</v>
+        <v>6.69</v>
       </c>
       <c r="U39" s="94" t="n">
-        <v>6.84</v>
+        <v>5.73</v>
       </c>
       <c r="V39" s="94" t="n">
-        <v>7.46</v>
+        <v>6.27</v>
       </c>
       <c r="W39" s="94" t="n">
-        <v>6.69</v>
+        <v>7.42</v>
       </c>
       <c r="X39" s="94" t="n">
-        <v>6.69</v>
+        <v>7.48</v>
       </c>
       <c r="Y39" s="94" t="n">
-        <v>5.73</v>
+        <v>6.99</v>
       </c>
       <c r="Z39" s="94" t="n">
-        <v>6.27</v>
+        <v>7.27</v>
       </c>
       <c r="AA39" s="94" t="n">
-        <v>7.42</v>
+        <v>5.46</v>
       </c>
       <c r="AB39" s="94" t="n">
-        <v>7.48</v>
+        <v>6.4</v>
       </c>
       <c r="AC39" s="94" t="n">
-        <v>6.99</v>
+        <v>6.18</v>
       </c>
       <c r="AD39" s="94" t="n">
-        <v>6.99</v>
+        <v>5.98</v>
       </c>
       <c r="AE39" s="94" t="n">
-        <v>7.27</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="40">
@@ -10784,7 +10783,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>9.69</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>10.79</v>
@@ -10796,82 +10795,82 @@
         <v>10.5</v>
       </c>
       <c r="F40" s="94" t="n">
-        <v>10.5</v>
+        <v>11.66</v>
       </c>
       <c r="G40" s="94" t="n">
-        <v>11.66</v>
+        <v>12.39</v>
       </c>
       <c r="H40" s="94" t="n">
-        <v>12.39</v>
+        <v>11.91</v>
       </c>
       <c r="I40" s="94" t="n">
-        <v>11.91</v>
+        <v>10.42</v>
       </c>
       <c r="J40" s="94" t="n">
-        <v>10.42</v>
+        <v>10.03</v>
       </c>
       <c r="K40" s="94" t="n">
-        <v>10.03</v>
+        <v>9.94</v>
       </c>
       <c r="L40" s="94" t="n">
-        <v>10.03</v>
+        <v>12.83</v>
       </c>
       <c r="M40" s="94" t="n">
-        <v>9.94</v>
+        <v>12.83</v>
       </c>
       <c r="N40" s="94" t="n">
-        <v>12.83</v>
+        <v>12.79</v>
       </c>
       <c r="O40" s="94" t="n">
-        <v>12.83</v>
+        <v>15.25</v>
       </c>
       <c r="P40" s="94" t="n">
-        <v>12.79</v>
+        <v>15.64</v>
       </c>
       <c r="Q40" s="94" t="n">
-        <v>15.25</v>
+        <v>15.29</v>
       </c>
       <c r="R40" s="94" t="n">
-        <v>15.25</v>
+        <v>14.9</v>
       </c>
       <c r="S40" s="94" t="n">
-        <v>15.64</v>
+        <v>14.75</v>
       </c>
       <c r="T40" s="94" t="n">
-        <v>15.29</v>
+        <v>14.79</v>
       </c>
       <c r="U40" s="94" t="n">
-        <v>14.9</v>
+        <v>13.96</v>
       </c>
       <c r="V40" s="94" t="n">
-        <v>14.75</v>
+        <v>14.46</v>
       </c>
       <c r="W40" s="94" t="n">
-        <v>14.79</v>
+        <v>14.07</v>
       </c>
       <c r="X40" s="94" t="n">
-        <v>14.79</v>
+        <v>14.24</v>
       </c>
       <c r="Y40" s="94" t="n">
-        <v>13.96</v>
+        <v>14.96</v>
       </c>
       <c r="Z40" s="94" t="n">
-        <v>14.46</v>
+        <v>15.21</v>
       </c>
       <c r="AA40" s="94" t="n">
-        <v>14.07</v>
+        <v>12.06</v>
       </c>
       <c r="AB40" s="94" t="n">
-        <v>14.24</v>
+        <v>12.77</v>
       </c>
       <c r="AC40" s="94" t="n">
-        <v>14.96</v>
+        <v>11.58</v>
       </c>
       <c r="AD40" s="94" t="n">
-        <v>14.96</v>
+        <v>11.57</v>
       </c>
       <c r="AE40" s="94" t="n">
-        <v>15.21</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="41">
@@ -10881,7 +10880,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>39.41</v>
+        <v>39.02</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>42.03</v>
@@ -10893,82 +10892,82 @@
         <v>35.77</v>
       </c>
       <c r="F41" s="94" t="n">
-        <v>35.77</v>
+        <v>37.56</v>
       </c>
       <c r="G41" s="94" t="n">
-        <v>37.56</v>
+        <v>35.74</v>
       </c>
       <c r="H41" s="94" t="n">
-        <v>35.74</v>
+        <v>36.86</v>
       </c>
       <c r="I41" s="94" t="n">
-        <v>36.86</v>
+        <v>29.96</v>
       </c>
       <c r="J41" s="94" t="n">
-        <v>29.96</v>
+        <v>33.56</v>
       </c>
       <c r="K41" s="94" t="n">
-        <v>33.56</v>
+        <v>38.91</v>
       </c>
       <c r="L41" s="94" t="n">
-        <v>33.56</v>
+        <v>56.68</v>
       </c>
       <c r="M41" s="94" t="n">
-        <v>38.91</v>
+        <v>56.68</v>
       </c>
       <c r="N41" s="94" t="n">
-        <v>56.68</v>
+        <v>57.12</v>
       </c>
       <c r="O41" s="94" t="n">
-        <v>56.68</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="P41" s="94" t="n">
-        <v>57.12</v>
+        <v>83.77</v>
       </c>
       <c r="Q41" s="94" t="n">
-        <v>78.04000000000001</v>
+        <v>80.52</v>
       </c>
       <c r="R41" s="94" t="n">
-        <v>78.04000000000001</v>
+        <v>79.08</v>
       </c>
       <c r="S41" s="94" t="n">
-        <v>83.77</v>
+        <v>79.38</v>
       </c>
       <c r="T41" s="94" t="n">
-        <v>80.52</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="U41" s="94" t="n">
-        <v>79.08</v>
+        <v>66.75</v>
       </c>
       <c r="V41" s="94" t="n">
-        <v>79.38</v>
+        <v>64.14</v>
       </c>
       <c r="W41" s="94" t="n">
-        <v>77.31999999999999</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="X41" s="94" t="n">
-        <v>77.31999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="Y41" s="94" t="n">
-        <v>66.75</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="Z41" s="94" t="n">
-        <v>64.14</v>
+        <v>66.14</v>
       </c>
       <c r="AA41" s="94" t="n">
-        <v>66.76000000000001</v>
+        <v>50.55</v>
       </c>
       <c r="AB41" s="94" t="n">
-        <v>65.90000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="AC41" s="94" t="n">
-        <v>65.01000000000001</v>
+        <v>52.02</v>
       </c>
       <c r="AD41" s="94" t="n">
-        <v>65.01000000000001</v>
+        <v>46.05</v>
       </c>
       <c r="AE41" s="94" t="n">
-        <v>66.14</v>
+        <v>66.09</v>
       </c>
     </row>
     <row r="42">
@@ -10997,134 +10996,134 @@
           <t>red</t>
         </is>
       </c>
-      <c r="F42" s="92" t="inlineStr">
+      <c r="F42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G42" s="93" t="inlineStr">
+      <c r="J42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H42" s="91" t="inlineStr">
+      <c r="K42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N42" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I42" s="93" t="inlineStr">
+      <c r="O42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K42" s="93" t="inlineStr">
+      <c r="AB42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L42" s="93" t="inlineStr">
+      <c r="AC42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M42" s="93" t="inlineStr">
+      <c r="AD42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N42" s="93" t="inlineStr">
+      <c r="AE42" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="O42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="P42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -11135,7 +11134,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>-0.37</v>
+        <v>-0.29</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>-1.01</v>
@@ -11147,82 +11146,82 @@
         <v>0.58</v>
       </c>
       <c r="F43" s="94" t="n">
-        <v>0.58</v>
+        <v>-0.59</v>
       </c>
       <c r="G43" s="94" t="n">
-        <v>-0.59</v>
+        <v>-0.14</v>
       </c>
       <c r="H43" s="94" t="n">
-        <v>-0.14</v>
+        <v>-0.77</v>
       </c>
       <c r="I43" s="94" t="n">
-        <v>-0.77</v>
+        <v>-0.74</v>
       </c>
       <c r="J43" s="94" t="n">
-        <v>-0.74</v>
+        <v>-2.37</v>
       </c>
       <c r="K43" s="94" t="n">
-        <v>-2.37</v>
+        <v>-1.96</v>
       </c>
       <c r="L43" s="94" t="n">
-        <v>-2.37</v>
+        <v>0.05</v>
       </c>
       <c r="M43" s="94" t="n">
-        <v>-1.96</v>
+        <v>0.87</v>
       </c>
       <c r="N43" s="94" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="O43" s="94" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P43" s="94" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q43" s="94" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="R43" s="94" t="n">
         <v>0.87</v>
       </c>
-      <c r="P43" s="94" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Q43" s="94" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R43" s="94" t="n">
-        <v>1.51</v>
-      </c>
       <c r="S43" s="94" t="n">
-        <v>0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="T43" s="94" t="n">
-        <v>-0.87</v>
+        <v>0.28</v>
       </c>
       <c r="U43" s="94" t="n">
-        <v>0.87</v>
+        <v>1.12</v>
       </c>
       <c r="V43" s="94" t="n">
-        <v>-0.7</v>
+        <v>-2.16</v>
       </c>
       <c r="W43" s="94" t="n">
-        <v>0.28</v>
+        <v>-2.28</v>
       </c>
       <c r="X43" s="94" t="n">
-        <v>0.28</v>
+        <v>-3.34</v>
       </c>
       <c r="Y43" s="94" t="n">
-        <v>1.12</v>
+        <v>-2.14</v>
       </c>
       <c r="Z43" s="94" t="n">
-        <v>-2.16</v>
+        <v>-3.08</v>
       </c>
       <c r="AA43" s="94" t="n">
-        <v>-2.28</v>
+        <v>-2.29</v>
       </c>
       <c r="AB43" s="94" t="n">
-        <v>-3.34</v>
+        <v>-2.9</v>
       </c>
       <c r="AC43" s="94" t="n">
-        <v>-2.14</v>
+        <v>-1.93</v>
       </c>
       <c r="AD43" s="94" t="n">
-        <v>-2.14</v>
+        <v>-2.01</v>
       </c>
       <c r="AE43" s="94" t="n">
-        <v>-3.08</v>
+        <v>-3.58</v>
       </c>
     </row>
     <row r="44">
@@ -11232,7 +11231,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>-6.25</v>
+        <v>-6.17</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>-6.73</v>
@@ -11244,79 +11243,79 @@
         <v>-5.47</v>
       </c>
       <c r="F44" s="94" t="n">
-        <v>-5.47</v>
+        <v>-6.8</v>
       </c>
       <c r="G44" s="94" t="n">
-        <v>-6.8</v>
+        <v>-6.73</v>
       </c>
       <c r="H44" s="94" t="n">
-        <v>-6.73</v>
+        <v>-6.46</v>
       </c>
       <c r="I44" s="94" t="n">
-        <v>-6.46</v>
+        <v>-5.56</v>
       </c>
       <c r="J44" s="94" t="n">
-        <v>-5.56</v>
+        <v>-6.01</v>
       </c>
       <c r="K44" s="94" t="n">
+        <v>-6.31</v>
+      </c>
+      <c r="L44" s="94" t="n">
+        <v>-4.48</v>
+      </c>
+      <c r="M44" s="94" t="n">
+        <v>-5.85</v>
+      </c>
+      <c r="N44" s="94" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="O44" s="94" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="P44" s="94" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="Q44" s="94" t="n">
         <v>-6.01</v>
       </c>
-      <c r="L44" s="94" t="n">
-        <v>-6.01</v>
-      </c>
-      <c r="M44" s="94" t="n">
-        <v>-6.31</v>
-      </c>
-      <c r="N44" s="94" t="n">
-        <v>-4.48</v>
-      </c>
-      <c r="O44" s="94" t="n">
-        <v>-5.85</v>
-      </c>
-      <c r="P44" s="94" t="n">
-        <v>-4.68</v>
-      </c>
-      <c r="Q44" s="94" t="n">
-        <v>-2.89</v>
-      </c>
       <c r="R44" s="94" t="n">
-        <v>-2.89</v>
+        <v>-6.35</v>
       </c>
       <c r="S44" s="94" t="n">
-        <v>-3.77</v>
+        <v>-6.86</v>
       </c>
       <c r="T44" s="94" t="n">
-        <v>-6.01</v>
+        <v>-7.99</v>
       </c>
       <c r="U44" s="94" t="n">
-        <v>-6.35</v>
+        <v>-6.6</v>
       </c>
       <c r="V44" s="94" t="n">
-        <v>-6.86</v>
+        <v>-8.43</v>
       </c>
       <c r="W44" s="94" t="n">
-        <v>-7.99</v>
+        <v>-8.75</v>
       </c>
       <c r="X44" s="94" t="n">
-        <v>-7.99</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="Y44" s="94" t="n">
-        <v>-6.6</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="Z44" s="94" t="n">
-        <v>-8.43</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="AA44" s="94" t="n">
-        <v>-8.75</v>
+        <v>-9.26</v>
       </c>
       <c r="AB44" s="94" t="n">
-        <v>-9.210000000000001</v>
+        <v>-9.44</v>
       </c>
       <c r="AC44" s="94" t="n">
-        <v>-8.789999999999999</v>
+        <v>-9.02</v>
       </c>
       <c r="AD44" s="94" t="n">
-        <v>-8.789999999999999</v>
+        <v>-10.35</v>
       </c>
       <c r="AE44" s="94" t="n">
         <v>-8.789999999999999</v>
@@ -11329,7 +11328,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>34.38</v>
+        <v>35.32</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>40.56</v>
@@ -11341,82 +11340,82 @@
         <v>54.29</v>
       </c>
       <c r="F45" s="94" t="n">
-        <v>54.29</v>
+        <v>46.1</v>
       </c>
       <c r="G45" s="94" t="n">
-        <v>46.1</v>
+        <v>49.74</v>
       </c>
       <c r="H45" s="94" t="n">
-        <v>49.74</v>
+        <v>42.08</v>
       </c>
       <c r="I45" s="94" t="n">
-        <v>42.08</v>
+        <v>50.81</v>
       </c>
       <c r="J45" s="94" t="n">
-        <v>50.81</v>
+        <v>45.03</v>
       </c>
       <c r="K45" s="94" t="n">
-        <v>45.03</v>
+        <v>33.57</v>
       </c>
       <c r="L45" s="94" t="n">
-        <v>45.03</v>
+        <v>45.48</v>
       </c>
       <c r="M45" s="94" t="n">
-        <v>33.57</v>
+        <v>44.93</v>
       </c>
       <c r="N45" s="94" t="n">
-        <v>45.48</v>
+        <v>52.35</v>
       </c>
       <c r="O45" s="94" t="n">
-        <v>44.93</v>
+        <v>78.61</v>
       </c>
       <c r="P45" s="94" t="n">
-        <v>52.35</v>
+        <v>75.48</v>
       </c>
       <c r="Q45" s="94" t="n">
-        <v>78.61</v>
+        <v>57.98</v>
       </c>
       <c r="R45" s="94" t="n">
-        <v>78.61</v>
+        <v>66.2</v>
       </c>
       <c r="S45" s="94" t="n">
-        <v>75.48</v>
+        <v>52.83</v>
       </c>
       <c r="T45" s="94" t="n">
-        <v>57.98</v>
+        <v>51.58</v>
       </c>
       <c r="U45" s="94" t="n">
-        <v>66.2</v>
+        <v>74.97</v>
       </c>
       <c r="V45" s="94" t="n">
-        <v>52.83</v>
+        <v>45.92</v>
       </c>
       <c r="W45" s="94" t="n">
-        <v>51.58</v>
+        <v>59.76</v>
       </c>
       <c r="X45" s="94" t="n">
-        <v>51.58</v>
+        <v>48.71</v>
       </c>
       <c r="Y45" s="94" t="n">
-        <v>74.97</v>
+        <v>53.61</v>
       </c>
       <c r="Z45" s="94" t="n">
-        <v>45.92</v>
+        <v>45.19</v>
       </c>
       <c r="AA45" s="94" t="n">
-        <v>59.76</v>
+        <v>32.83</v>
       </c>
       <c r="AB45" s="94" t="n">
-        <v>48.71</v>
+        <v>34.58</v>
       </c>
       <c r="AC45" s="94" t="n">
-        <v>53.61</v>
+        <v>37.2</v>
       </c>
       <c r="AD45" s="94" t="n">
-        <v>53.61</v>
+        <v>16.31</v>
       </c>
       <c r="AE45" s="94" t="n">
-        <v>45.19</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="46">
@@ -11425,154 +11424,154 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="92" t="inlineStr">
+      <c r="B46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="C46" s="92" t="inlineStr">
+      <c r="D46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D46" s="92" t="inlineStr">
+      <c r="E46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E46" s="92" t="inlineStr">
+      <c r="F46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F46" s="92" t="inlineStr">
+      <c r="H46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G46" s="91" t="inlineStr">
+      <c r="P46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H46" s="92" t="inlineStr">
+      <c r="R46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I46" s="91" t="inlineStr">
+      <c r="S46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="K46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="L46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="M46" s="93" t="inlineStr">
+      <c r="U46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="AB46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11582,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>5</v>
+        <v>5.69</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>5</v>
@@ -11595,82 +11594,82 @@
         <v>6.61</v>
       </c>
       <c r="F47" s="94" t="n">
-        <v>6.61</v>
+        <v>4.66</v>
       </c>
       <c r="G47" s="94" t="n">
-        <v>4.66</v>
+        <v>4.43</v>
       </c>
       <c r="H47" s="94" t="n">
-        <v>4.43</v>
+        <v>2.96</v>
       </c>
       <c r="I47" s="94" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J47" s="94" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="K47" s="94" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="L47" s="94" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="M47" s="94" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="N47" s="94" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="O47" s="94" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="P47" s="94" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="Q47" s="94" t="n">
         <v>2.96</v>
       </c>
-      <c r="J47" s="94" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K47" s="94" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="L47" s="94" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="M47" s="94" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="N47" s="94" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="O47" s="94" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="P47" s="94" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="Q47" s="94" t="n">
-        <v>5.4</v>
-      </c>
       <c r="R47" s="94" t="n">
-        <v>5.4</v>
+        <v>4.58</v>
       </c>
       <c r="S47" s="94" t="n">
-        <v>4.27</v>
+        <v>3.04</v>
       </c>
       <c r="T47" s="94" t="n">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="U47" s="94" t="n">
-        <v>4.58</v>
+        <v>4.35</v>
       </c>
       <c r="V47" s="94" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="W47" s="94" t="n">
-        <v>2.66</v>
+        <v>3.02</v>
       </c>
       <c r="X47" s="94" t="n">
-        <v>2.66</v>
+        <v>1.68</v>
       </c>
       <c r="Y47" s="94" t="n">
-        <v>4.35</v>
+        <v>2.95</v>
       </c>
       <c r="Z47" s="94" t="n">
-        <v>3.06</v>
+        <v>1.45</v>
       </c>
       <c r="AA47" s="94" t="n">
-        <v>3.02</v>
+        <v>1.45</v>
       </c>
       <c r="AB47" s="94" t="n">
-        <v>1.68</v>
+        <v>0.74</v>
       </c>
       <c r="AC47" s="94" t="n">
-        <v>2.95</v>
+        <v>2.08</v>
       </c>
       <c r="AD47" s="94" t="n">
-        <v>2.95</v>
+        <v>1.67</v>
       </c>
       <c r="AE47" s="94" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="48">
@@ -11680,7 +11679,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>7.55</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>7.55</v>
@@ -11692,82 +11691,82 @@
         <v>8.130000000000001</v>
       </c>
       <c r="F48" s="94" t="n">
-        <v>8.130000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="G48" s="94" t="n">
-        <v>6.2</v>
+        <v>6.16</v>
       </c>
       <c r="H48" s="94" t="n">
-        <v>6.16</v>
+        <v>6.75</v>
       </c>
       <c r="I48" s="94" t="n">
-        <v>6.75</v>
+        <v>7.71</v>
       </c>
       <c r="J48" s="94" t="n">
-        <v>7.71</v>
+        <v>7.2</v>
       </c>
       <c r="K48" s="94" t="n">
-        <v>7.2</v>
+        <v>7.01</v>
       </c>
       <c r="L48" s="94" t="n">
-        <v>7.2</v>
+        <v>7.87</v>
       </c>
       <c r="M48" s="94" t="n">
-        <v>7.01</v>
+        <v>6.58</v>
       </c>
       <c r="N48" s="94" t="n">
-        <v>7.87</v>
+        <v>7.78</v>
       </c>
       <c r="O48" s="94" t="n">
-        <v>6.58</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="P48" s="94" t="n">
-        <v>7.78</v>
+        <v>6.31</v>
       </c>
       <c r="Q48" s="94" t="n">
-        <v>8.460000000000001</v>
+        <v>4.66</v>
       </c>
       <c r="R48" s="94" t="n">
-        <v>8.460000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="S48" s="94" t="n">
-        <v>6.31</v>
+        <v>3.7</v>
       </c>
       <c r="T48" s="94" t="n">
-        <v>4.66</v>
+        <v>1.72</v>
       </c>
       <c r="U48" s="94" t="n">
-        <v>3.7</v>
+        <v>3.46</v>
       </c>
       <c r="V48" s="94" t="n">
-        <v>3.7</v>
+        <v>2.34</v>
       </c>
       <c r="W48" s="94" t="n">
-        <v>1.72</v>
+        <v>1.26</v>
       </c>
       <c r="X48" s="94" t="n">
-        <v>1.72</v>
+        <v>0.84</v>
       </c>
       <c r="Y48" s="94" t="n">
-        <v>3.46</v>
+        <v>1.71</v>
       </c>
       <c r="Z48" s="94" t="n">
-        <v>2.34</v>
+        <v>1.41</v>
       </c>
       <c r="AA48" s="94" t="n">
-        <v>1.26</v>
+        <v>0.68</v>
       </c>
       <c r="AB48" s="94" t="n">
-        <v>0.84</v>
+        <v>0.48</v>
       </c>
       <c r="AC48" s="94" t="n">
-        <v>1.71</v>
+        <v>2.38</v>
       </c>
       <c r="AD48" s="94" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AE48" s="94" t="n">
-        <v>1.41</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="49">
@@ -11777,7 +11776,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>71.38</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>71.38</v>
@@ -11789,88 +11788,88 @@
         <v>68.01000000000001</v>
       </c>
       <c r="F49" s="94" t="n">
-        <v>68.01000000000001</v>
+        <v>58.26</v>
       </c>
       <c r="G49" s="94" t="n">
-        <v>58.26</v>
+        <v>62.55</v>
       </c>
       <c r="H49" s="94" t="n">
-        <v>62.55</v>
+        <v>49.18</v>
       </c>
       <c r="I49" s="94" t="n">
-        <v>49.18</v>
+        <v>52.29</v>
       </c>
       <c r="J49" s="94" t="n">
+        <v>53.55</v>
+      </c>
+      <c r="K49" s="94" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="L49" s="94" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="M49" s="94" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="N49" s="94" t="n">
+        <v>67.34999999999999</v>
+      </c>
+      <c r="O49" s="94" t="n">
+        <v>78.38</v>
+      </c>
+      <c r="P49" s="94" t="n">
+        <v>72.42</v>
+      </c>
+      <c r="Q49" s="94" t="n">
+        <v>59.91</v>
+      </c>
+      <c r="R49" s="94" t="n">
+        <v>66</v>
+      </c>
+      <c r="S49" s="94" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="T49" s="94" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="U49" s="94" t="n">
+        <v>75.06999999999999</v>
+      </c>
+      <c r="V49" s="94" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="W49" s="94" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="X49" s="94" t="n">
+        <v>57.16</v>
+      </c>
+      <c r="Y49" s="94" t="n">
+        <v>62.56</v>
+      </c>
+      <c r="Z49" s="94" t="n">
         <v>52.29</v>
       </c>
-      <c r="K49" s="94" t="n">
-        <v>53.55</v>
-      </c>
-      <c r="L49" s="94" t="n">
-        <v>53.55</v>
-      </c>
-      <c r="M49" s="94" t="n">
-        <v>46.86</v>
-      </c>
-      <c r="N49" s="94" t="n">
-        <v>56.45</v>
-      </c>
-      <c r="O49" s="94" t="n">
-        <v>59.76</v>
-      </c>
-      <c r="P49" s="94" t="n">
-        <v>67.34999999999999</v>
-      </c>
-      <c r="Q49" s="94" t="n">
-        <v>78.38</v>
-      </c>
-      <c r="R49" s="94" t="n">
-        <v>78.38</v>
-      </c>
-      <c r="S49" s="94" t="n">
-        <v>72.42</v>
-      </c>
-      <c r="T49" s="94" t="n">
-        <v>59.91</v>
-      </c>
-      <c r="U49" s="94" t="n">
-        <v>66</v>
-      </c>
-      <c r="V49" s="94" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="W49" s="94" t="n">
-        <v>52.95</v>
-      </c>
-      <c r="X49" s="94" t="n">
-        <v>52.95</v>
-      </c>
-      <c r="Y49" s="94" t="n">
-        <v>75.06999999999999</v>
-      </c>
-      <c r="Z49" s="94" t="n">
-        <v>61.14</v>
-      </c>
       <c r="AA49" s="94" t="n">
-        <v>62.6</v>
+        <v>37.42</v>
       </c>
       <c r="AB49" s="94" t="n">
-        <v>57.16</v>
+        <v>31.32</v>
       </c>
       <c r="AC49" s="94" t="n">
-        <v>62.56</v>
+        <v>40.38</v>
       </c>
       <c r="AD49" s="94" t="n">
-        <v>62.56</v>
+        <v>26.19</v>
       </c>
       <c r="AE49" s="94" t="n">
-        <v>52.29</v>
+        <v>42.54</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：ixic:RS2:36.8&lt;=38</t>
+          <t>今日买报：</t>
         </is>
       </c>
     </row>
@@ -15478,13 +15477,13 @@
       <c r="G2" s="36" t="n">
         <v>66</v>
       </c>
-      <c r="H2" s="97" t="n">
+      <c r="H2" s="96" t="n">
         <v>22.3514585</v>
       </c>
       <c r="I2" s="36" t="n">
         <v>7.06</v>
       </c>
-      <c r="J2" s="98">
+      <c r="J2" s="97">
         <f>(1+H2/100)^(1/(YEAR(D2)-YEAR(C2)))-1</f>
         <v/>
       </c>
@@ -15516,13 +15515,13 @@
       <c r="G3" s="39" t="n">
         <v>73</v>
       </c>
-      <c r="H3" s="99" t="n">
+      <c r="H3" s="98" t="n">
         <v>35.0298984</v>
       </c>
       <c r="I3" s="39" t="n">
         <v>11.41</v>
       </c>
-      <c r="J3" s="98">
+      <c r="J3" s="97">
         <f>(1+H3/100)^(1/(YEAR(D3)-YEAR(C3)))-1</f>
         <v/>
       </c>
@@ -15554,13 +15553,13 @@
       <c r="G4" s="39" t="n">
         <v>85</v>
       </c>
-      <c r="H4" s="99" t="n">
+      <c r="H4" s="98" t="n">
         <v>122.4911655</v>
       </c>
       <c r="I4" s="39" t="n">
         <v>76.98</v>
       </c>
-      <c r="J4" s="100">
+      <c r="J4" s="99">
         <f>(1+H4/100)^(1/(YEAR(D4)-YEAR(C4)))-1</f>
         <v/>
       </c>
@@ -15592,13 +15591,13 @@
       <c r="G5" s="39" t="n">
         <v>96</v>
       </c>
-      <c r="H5" s="99" t="n">
+      <c r="H5" s="98" t="n">
         <v>136.13543</v>
       </c>
       <c r="I5" s="39" t="n">
         <v>100.05</v>
       </c>
-      <c r="J5" s="100">
+      <c r="J5" s="99">
         <f>(1+H5/100)^(1/(YEAR(D5)-YEAR(C5)))-1</f>
         <v/>
       </c>
@@ -15630,13 +15629,13 @@
       <c r="G6" s="39" t="n">
         <v>95</v>
       </c>
-      <c r="H6" s="99" t="n">
+      <c r="H6" s="98" t="n">
         <v>95.7546074</v>
       </c>
       <c r="I6" s="39" t="n">
         <v>44.37</v>
       </c>
-      <c r="J6" s="100">
+      <c r="J6" s="99">
         <f>(1+H6/100)^(1/(YEAR(D6)-YEAR(C6)))-1</f>
         <v/>
       </c>
@@ -15668,13 +15667,13 @@
       <c r="G7" s="39" t="n">
         <v>86</v>
       </c>
-      <c r="H7" s="99" t="n">
+      <c r="H7" s="98" t="n">
         <v>123.8525927</v>
       </c>
       <c r="I7" s="39" t="n">
         <v>63.41</v>
       </c>
-      <c r="J7" s="100">
+      <c r="J7" s="99">
         <f>(1+H7/100)^(1/(YEAR(D7)-YEAR(C7)))-1</f>
         <v/>
       </c>
@@ -15706,13 +15705,13 @@
       <c r="G8" s="39" t="n">
         <v>87</v>
       </c>
-      <c r="H8" s="99" t="n">
+      <c r="H8" s="98" t="n">
         <v>81.41461922000001</v>
       </c>
       <c r="I8" s="39" t="n">
         <v>26.39</v>
       </c>
-      <c r="J8" s="100">
+      <c r="J8" s="99">
         <f>(1+H8/100)^(1/(YEAR(D8)-YEAR(C8)))-1</f>
         <v/>
       </c>
@@ -15744,13 +15743,13 @@
       <c r="G9" s="39" t="n">
         <v>83</v>
       </c>
-      <c r="H9" s="99" t="n">
+      <c r="H9" s="98" t="n">
         <v>47.02060524</v>
       </c>
       <c r="I9" s="39" t="n">
         <v>37.82</v>
       </c>
-      <c r="J9" s="100">
+      <c r="J9" s="99">
         <f>(1+H9/100)^(1/(YEAR(D9)-YEAR(C9)))-1</f>
         <v/>
       </c>
@@ -15781,13 +15780,13 @@
       <c r="G10" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="H10" s="101" t="n">
+      <c r="H10" s="100" t="n">
         <v>27.8860732</v>
       </c>
       <c r="I10" s="24" t="n">
         <v>-10.97</v>
       </c>
-      <c r="J10" s="102" t="n">
+      <c r="J10" s="101" t="n">
         <v>0.278860732</v>
       </c>
     </row>
@@ -15818,13 +15817,13 @@
       <c r="G11" s="24" t="n">
         <v>93</v>
       </c>
-      <c r="H11" s="101" t="n">
+      <c r="H11" s="100" t="n">
         <v>17.4948656</v>
       </c>
       <c r="I11" s="24" t="n">
         <v>-7.7</v>
       </c>
-      <c r="J11" s="102">
+      <c r="J11" s="101">
         <f>(1+H11/100)^(1/(YEAR(D11)-YEAR(C11)))-1</f>
         <v/>
       </c>

--- a/report_2410.xlsx
+++ b/report_2410.xlsx
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.07000000000000001</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.18</v>
@@ -6362,132 +6362,132 @@
       </c>
       <c r="F1" s="77" t="inlineStr">
         <is>
-          <t>241013</t>
+          <t>241011</t>
         </is>
       </c>
       <c r="G1" s="77" t="inlineStr">
         <is>
-          <t>241011</t>
+          <t>241010</t>
         </is>
       </c>
       <c r="H1" s="77" t="inlineStr">
         <is>
-          <t>241010</t>
+          <t>241009</t>
         </is>
       </c>
       <c r="I1" s="77" t="inlineStr">
         <is>
-          <t>241009</t>
+          <t>241008</t>
         </is>
       </c>
       <c r="J1" s="77" t="inlineStr">
         <is>
-          <t>241008</t>
+          <t>241007</t>
         </is>
       </c>
       <c r="K1" s="77" t="inlineStr">
         <is>
-          <t>241007</t>
+          <t>241004</t>
         </is>
       </c>
       <c r="L1" s="77" t="inlineStr">
         <is>
-          <t>241006</t>
+          <t>241003</t>
         </is>
       </c>
       <c r="M1" s="77" t="inlineStr">
         <is>
-          <t>241004</t>
+          <t>241002</t>
         </is>
       </c>
       <c r="N1" s="77" t="inlineStr">
         <is>
-          <t>241003</t>
+          <t>241001</t>
         </is>
       </c>
       <c r="O1" s="77" t="inlineStr">
         <is>
-          <t>241002</t>
+          <t>240930</t>
         </is>
       </c>
       <c r="P1" s="77" t="inlineStr">
         <is>
-          <t>241001</t>
+          <t>240927</t>
         </is>
       </c>
       <c r="Q1" s="77" t="inlineStr">
         <is>
-          <t>240930</t>
+          <t>240926</t>
         </is>
       </c>
       <c r="R1" s="77" t="inlineStr">
         <is>
-          <t>240929</t>
+          <t>240925</t>
         </is>
       </c>
       <c r="S1" s="77" t="inlineStr">
         <is>
-          <t>240927</t>
+          <t>240924</t>
         </is>
       </c>
       <c r="T1" s="77" t="inlineStr">
         <is>
-          <t>240926</t>
+          <t>240923</t>
         </is>
       </c>
       <c r="U1" s="77" t="inlineStr">
         <is>
-          <t>240925</t>
+          <t>240920</t>
         </is>
       </c>
       <c r="V1" s="77" t="inlineStr">
         <is>
-          <t>240924</t>
+          <t>240919</t>
         </is>
       </c>
       <c r="W1" s="77" t="inlineStr">
         <is>
-          <t>240923</t>
+          <t>240918</t>
         </is>
       </c>
       <c r="X1" s="77" t="inlineStr">
         <is>
-          <t>240922</t>
+          <t>240917</t>
         </is>
       </c>
       <c r="Y1" s="77" t="inlineStr">
         <is>
-          <t>240920</t>
+          <t>240916</t>
         </is>
       </c>
       <c r="Z1" s="77" t="inlineStr">
         <is>
-          <t>240919</t>
+          <t>240913</t>
         </is>
       </c>
       <c r="AA1" s="77" t="inlineStr">
         <is>
-          <t>240918</t>
+          <t>240912</t>
         </is>
       </c>
       <c r="AB1" s="77" t="inlineStr">
         <is>
-          <t>240917</t>
+          <t>240911</t>
         </is>
       </c>
       <c r="AC1" s="77" t="inlineStr">
         <is>
-          <t>240916</t>
+          <t>240910</t>
         </is>
       </c>
       <c r="AD1" s="77" t="inlineStr">
         <is>
-          <t>240915</t>
+          <t>240909</t>
         </is>
       </c>
       <c r="AE1" s="77" t="inlineStr">
         <is>
-          <t>240913</t>
+          <t>240906</t>
         </is>
       </c>
     </row>
@@ -6532,74 +6532,74 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="I2" s="91" t="inlineStr">
+      <c r="I2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="U2" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V2" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="W2" s="91" t="inlineStr">
@@ -6607,24 +6607,24 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="X2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="X2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Y2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="AB2" s="93" t="inlineStr">
@@ -6670,16 +6670,16 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G3" s="94" t="n">
-        <v>9.470000000000001</v>
+        <v>11.58</v>
       </c>
       <c r="H3" s="94" t="n">
-        <v>11.58</v>
+        <v>11.51</v>
       </c>
       <c r="I3" s="94" t="n">
-        <v>11.51</v>
+        <v>18.3</v>
       </c>
       <c r="J3" s="94" t="n">
-        <v>18.3</v>
+        <v>12.81</v>
       </c>
       <c r="K3" s="94" t="n">
         <v>12.81</v>
@@ -6697,52 +6697,52 @@
         <v>12.81</v>
       </c>
       <c r="P3" s="94" t="n">
-        <v>12.81</v>
+        <v>3.53</v>
       </c>
       <c r="Q3" s="94" t="n">
-        <v>12.81</v>
+        <v>0.13</v>
       </c>
       <c r="R3" s="94" t="n">
-        <v>3.53</v>
+        <v>-3.29</v>
       </c>
       <c r="S3" s="94" t="n">
-        <v>3.53</v>
+        <v>-3.51</v>
       </c>
       <c r="T3" s="94" t="n">
-        <v>0.13</v>
+        <v>-6.68</v>
       </c>
       <c r="U3" s="94" t="n">
-        <v>-3.29</v>
+        <v>-7.93</v>
       </c>
       <c r="V3" s="94" t="n">
-        <v>-3.51</v>
+        <v>-7.25</v>
       </c>
       <c r="W3" s="94" t="n">
-        <v>-6.68</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="X3" s="94" t="n">
-        <v>-7.93</v>
+        <v>-9.81</v>
       </c>
       <c r="Y3" s="94" t="n">
-        <v>-7.93</v>
+        <v>-9.81</v>
       </c>
       <c r="Z3" s="94" t="n">
-        <v>-7.25</v>
+        <v>-9.81</v>
       </c>
       <c r="AA3" s="94" t="n">
-        <v>-8.300000000000001</v>
+        <v>-9.59</v>
       </c>
       <c r="AB3" s="94" t="n">
-        <v>-9.81</v>
+        <v>-9.82</v>
       </c>
       <c r="AC3" s="94" t="n">
-        <v>-9.81</v>
+        <v>-9.44</v>
       </c>
       <c r="AD3" s="94" t="n">
-        <v>-9.81</v>
+        <v>-9.26</v>
       </c>
       <c r="AE3" s="94" t="n">
-        <v>-9.81</v>
+        <v>-8.800000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -6767,16 +6767,16 @@
         <v>6.05</v>
       </c>
       <c r="G4" s="94" t="n">
-        <v>6.05</v>
+        <v>9.07</v>
       </c>
       <c r="H4" s="94" t="n">
-        <v>9.07</v>
+        <v>6.9</v>
       </c>
       <c r="I4" s="94" t="n">
-        <v>6.9</v>
+        <v>14.53</v>
       </c>
       <c r="J4" s="94" t="n">
-        <v>14.53</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="K4" s="94" t="n">
         <v>8.710000000000001</v>
@@ -6794,52 +6794,52 @@
         <v>8.710000000000001</v>
       </c>
       <c r="P4" s="94" t="n">
-        <v>8.710000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="Q4" s="94" t="n">
-        <v>8.710000000000001</v>
+        <v>-2.48</v>
       </c>
       <c r="R4" s="94" t="n">
-        <v>0.41</v>
+        <v>-4.76</v>
       </c>
       <c r="S4" s="94" t="n">
-        <v>0.41</v>
+        <v>-4.9</v>
       </c>
       <c r="T4" s="94" t="n">
-        <v>-2.48</v>
+        <v>-8.16</v>
       </c>
       <c r="U4" s="94" t="n">
-        <v>-4.76</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="V4" s="94" t="n">
-        <v>-4.9</v>
+        <v>-9.59</v>
       </c>
       <c r="W4" s="94" t="n">
-        <v>-8.16</v>
+        <v>-10.85</v>
       </c>
       <c r="X4" s="94" t="n">
-        <v>-9.720000000000001</v>
+        <v>-12.12</v>
       </c>
       <c r="Y4" s="94" t="n">
-        <v>-9.720000000000001</v>
+        <v>-12.12</v>
       </c>
       <c r="Z4" s="94" t="n">
-        <v>-9.59</v>
+        <v>-12.12</v>
       </c>
       <c r="AA4" s="94" t="n">
-        <v>-10.85</v>
+        <v>-11.77</v>
       </c>
       <c r="AB4" s="94" t="n">
-        <v>-12.12</v>
+        <v>-11.13</v>
       </c>
       <c r="AC4" s="94" t="n">
-        <v>-12.12</v>
+        <v>-11.05</v>
       </c>
       <c r="AD4" s="94" t="n">
-        <v>-12.12</v>
+        <v>-10.42</v>
       </c>
       <c r="AE4" s="94" t="n">
-        <v>-12.12</v>
+        <v>-8.970000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -6864,16 +6864,16 @@
         <v>44.67</v>
       </c>
       <c r="G5" s="94" t="n">
-        <v>44.67</v>
+        <v>59.48</v>
       </c>
       <c r="H5" s="94" t="n">
-        <v>59.48</v>
+        <v>54.31</v>
       </c>
       <c r="I5" s="94" t="n">
-        <v>54.31</v>
+        <v>99.84</v>
       </c>
       <c r="J5" s="94" t="n">
-        <v>99.84</v>
+        <v>99.75</v>
       </c>
       <c r="K5" s="94" t="n">
         <v>99.75</v>
@@ -6891,52 +6891,52 @@
         <v>99.75</v>
       </c>
       <c r="P5" s="94" t="n">
-        <v>99.75</v>
+        <v>99.31</v>
       </c>
       <c r="Q5" s="94" t="n">
-        <v>99.75</v>
+        <v>98.83</v>
       </c>
       <c r="R5" s="94" t="n">
-        <v>99.31</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="S5" s="94" t="n">
-        <v>99.31</v>
+        <v>96.38</v>
       </c>
       <c r="T5" s="94" t="n">
-        <v>98.83</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="U5" s="94" t="n">
-        <v>97.34999999999999</v>
+        <v>64.38</v>
       </c>
       <c r="V5" s="94" t="n">
-        <v>96.38</v>
+        <v>63.45</v>
       </c>
       <c r="W5" s="94" t="n">
-        <v>77.51000000000001</v>
+        <v>37.85</v>
       </c>
       <c r="X5" s="94" t="n">
-        <v>64.38</v>
+        <v>7.42</v>
       </c>
       <c r="Y5" s="94" t="n">
-        <v>64.38</v>
+        <v>7.42</v>
       </c>
       <c r="Z5" s="94" t="n">
-        <v>63.45</v>
+        <v>7.42</v>
       </c>
       <c r="AA5" s="94" t="n">
-        <v>37.85</v>
+        <v>10.95</v>
       </c>
       <c r="AB5" s="94" t="n">
-        <v>7.42</v>
+        <v>12.36</v>
       </c>
       <c r="AC5" s="94" t="n">
-        <v>7.42</v>
+        <v>20.95</v>
       </c>
       <c r="AD5" s="94" t="n">
-        <v>7.42</v>
+        <v>5.95</v>
       </c>
       <c r="AE5" s="94" t="n">
-        <v>7.42</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="6">
@@ -6975,79 +6975,79 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="H6" s="91" t="inlineStr">
+      <c r="H6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="U6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="J6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="V6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="W6" s="93" t="inlineStr">
@@ -7070,29 +7070,29 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="AA6" s="93" t="inlineStr">
+      <c r="AA6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AB6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AC6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AD6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="AE6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -7118,16 +7118,16 @@
         <v>26.54</v>
       </c>
       <c r="G7" s="94" t="n">
-        <v>26.54</v>
+        <v>34.41</v>
       </c>
       <c r="H7" s="94" t="n">
-        <v>34.41</v>
+        <v>44.1</v>
       </c>
       <c r="I7" s="94" t="n">
-        <v>44.1</v>
+        <v>46.52</v>
       </c>
       <c r="J7" s="94" t="n">
-        <v>46.52</v>
+        <v>26.36</v>
       </c>
       <c r="K7" s="94" t="n">
         <v>26.36</v>
@@ -7145,52 +7145,52 @@
         <v>26.36</v>
       </c>
       <c r="P7" s="94" t="n">
-        <v>26.36</v>
+        <v>5.45</v>
       </c>
       <c r="Q7" s="94" t="n">
-        <v>26.36</v>
+        <v>-0.85</v>
       </c>
       <c r="R7" s="94" t="n">
-        <v>5.45</v>
+        <v>-5.96</v>
       </c>
       <c r="S7" s="94" t="n">
-        <v>5.45</v>
+        <v>-6.32</v>
       </c>
       <c r="T7" s="94" t="n">
-        <v>-0.85</v>
+        <v>-10.11</v>
       </c>
       <c r="U7" s="94" t="n">
-        <v>-5.96</v>
+        <v>-11.14</v>
       </c>
       <c r="V7" s="94" t="n">
-        <v>-6.32</v>
+        <v>-9.23</v>
       </c>
       <c r="W7" s="94" t="n">
-        <v>-10.11</v>
+        <v>-12.41</v>
       </c>
       <c r="X7" s="94" t="n">
-        <v>-11.14</v>
+        <v>-13.62</v>
       </c>
       <c r="Y7" s="94" t="n">
-        <v>-11.14</v>
+        <v>-13.62</v>
       </c>
       <c r="Z7" s="94" t="n">
-        <v>-9.23</v>
+        <v>-13.62</v>
       </c>
       <c r="AA7" s="94" t="n">
-        <v>-12.41</v>
+        <v>-12.75</v>
       </c>
       <c r="AB7" s="94" t="n">
-        <v>-13.62</v>
+        <v>-11.62</v>
       </c>
       <c r="AC7" s="94" t="n">
-        <v>-13.62</v>
+        <v>-12.8</v>
       </c>
       <c r="AD7" s="94" t="n">
-        <v>-13.62</v>
+        <v>-13.49</v>
       </c>
       <c r="AE7" s="94" t="n">
-        <v>-13.62</v>
+        <v>-12.19</v>
       </c>
     </row>
     <row r="8">
@@ -7215,16 +7215,16 @@
         <v>21.69</v>
       </c>
       <c r="G8" s="94" t="n">
-        <v>21.69</v>
+        <v>29.69</v>
       </c>
       <c r="H8" s="94" t="n">
-        <v>29.69</v>
+        <v>33.11</v>
       </c>
       <c r="I8" s="94" t="n">
-        <v>33.11</v>
+        <v>38.25</v>
       </c>
       <c r="J8" s="94" t="n">
-        <v>38.25</v>
+        <v>15.28</v>
       </c>
       <c r="K8" s="94" t="n">
         <v>15.28</v>
@@ -7242,52 +7242,52 @@
         <v>15.28</v>
       </c>
       <c r="P8" s="94" t="n">
-        <v>15.28</v>
+        <v>-3.74</v>
       </c>
       <c r="Q8" s="94" t="n">
-        <v>15.28</v>
+        <v>-10.62</v>
       </c>
       <c r="R8" s="94" t="n">
-        <v>-3.74</v>
+        <v>-12.51</v>
       </c>
       <c r="S8" s="94" t="n">
-        <v>-3.74</v>
+        <v>-12.61</v>
       </c>
       <c r="T8" s="94" t="n">
-        <v>-10.62</v>
+        <v>-14.58</v>
       </c>
       <c r="U8" s="94" t="n">
-        <v>-12.51</v>
+        <v>-16.03</v>
       </c>
       <c r="V8" s="94" t="n">
-        <v>-12.61</v>
+        <v>-16.65</v>
       </c>
       <c r="W8" s="94" t="n">
-        <v>-14.58</v>
+        <v>-18.48</v>
       </c>
       <c r="X8" s="94" t="n">
-        <v>-16.03</v>
+        <v>-18.74</v>
       </c>
       <c r="Y8" s="94" t="n">
-        <v>-16.03</v>
+        <v>-18.74</v>
       </c>
       <c r="Z8" s="94" t="n">
-        <v>-16.65</v>
+        <v>-18.74</v>
       </c>
       <c r="AA8" s="94" t="n">
-        <v>-18.48</v>
+        <v>-19.06</v>
       </c>
       <c r="AB8" s="94" t="n">
-        <v>-18.74</v>
+        <v>-18.16</v>
       </c>
       <c r="AC8" s="94" t="n">
-        <v>-18.74</v>
+        <v>-20.04</v>
       </c>
       <c r="AD8" s="94" t="n">
-        <v>-18.74</v>
+        <v>-19.01</v>
       </c>
       <c r="AE8" s="94" t="n">
-        <v>-18.74</v>
+        <v>-17.71</v>
       </c>
     </row>
     <row r="9">
@@ -7312,16 +7312,16 @@
         <v>59.18</v>
       </c>
       <c r="G9" s="94" t="n">
-        <v>59.18</v>
+        <v>74.52</v>
       </c>
       <c r="H9" s="94" t="n">
-        <v>74.52</v>
+        <v>89.13</v>
       </c>
       <c r="I9" s="94" t="n">
-        <v>89.13</v>
+        <v>98.36</v>
       </c>
       <c r="J9" s="94" t="n">
-        <v>98.36</v>
+        <v>96.84</v>
       </c>
       <c r="K9" s="94" t="n">
         <v>96.84</v>
@@ -7339,52 +7339,52 @@
         <v>96.84</v>
       </c>
       <c r="P9" s="94" t="n">
-        <v>96.84</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="Q9" s="94" t="n">
-        <v>96.84</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="R9" s="94" t="n">
-        <v>91.06999999999999</v>
+        <v>64.94</v>
       </c>
       <c r="S9" s="94" t="n">
-        <v>91.06999999999999</v>
+        <v>64.66</v>
       </c>
       <c r="T9" s="94" t="n">
-        <v>81.48999999999999</v>
+        <v>23.69</v>
       </c>
       <c r="U9" s="94" t="n">
-        <v>64.94</v>
+        <v>29.81</v>
       </c>
       <c r="V9" s="94" t="n">
-        <v>64.66</v>
+        <v>33.91</v>
       </c>
       <c r="W9" s="94" t="n">
-        <v>23.69</v>
+        <v>22.82</v>
       </c>
       <c r="X9" s="94" t="n">
-        <v>29.81</v>
+        <v>30.54</v>
       </c>
       <c r="Y9" s="94" t="n">
-        <v>29.81</v>
+        <v>30.54</v>
       </c>
       <c r="Z9" s="94" t="n">
-        <v>33.91</v>
+        <v>30.54</v>
       </c>
       <c r="AA9" s="94" t="n">
-        <v>22.82</v>
+        <v>35.28</v>
       </c>
       <c r="AB9" s="94" t="n">
-        <v>30.54</v>
+        <v>42.99</v>
       </c>
       <c r="AC9" s="94" t="n">
-        <v>30.54</v>
+        <v>33.88</v>
       </c>
       <c r="AD9" s="94" t="n">
-        <v>30.54</v>
+        <v>22.22</v>
       </c>
       <c r="AE9" s="94" t="n">
-        <v>30.54</v>
+        <v>27.98</v>
       </c>
     </row>
     <row r="10">
@@ -7423,109 +7423,109 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="H10" s="91" t="inlineStr">
+      <c r="H10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="U10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="V10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I10" s="92" t="inlineStr">
+      <c r="W10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="X10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Y10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AB10" s="92" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="J10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="X10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z10" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB10" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AC10" s="93" t="inlineStr">
@@ -7566,16 +7566,16 @@
         <v>27.24</v>
       </c>
       <c r="G11" s="94" t="n">
-        <v>27.24</v>
+        <v>33.94</v>
       </c>
       <c r="H11" s="94" t="n">
-        <v>33.94</v>
+        <v>39.99</v>
       </c>
       <c r="I11" s="94" t="n">
-        <v>39.99</v>
+        <v>54.04</v>
       </c>
       <c r="J11" s="94" t="n">
-        <v>54.04</v>
+        <v>32.05</v>
       </c>
       <c r="K11" s="94" t="n">
         <v>32.05</v>
@@ -7593,52 +7593,52 @@
         <v>32.05</v>
       </c>
       <c r="P11" s="94" t="n">
-        <v>32.05</v>
+        <v>13.58</v>
       </c>
       <c r="Q11" s="94" t="n">
-        <v>32.05</v>
+        <v>2.95</v>
       </c>
       <c r="R11" s="94" t="n">
-        <v>13.58</v>
+        <v>-2.45</v>
       </c>
       <c r="S11" s="94" t="n">
-        <v>13.58</v>
+        <v>-4.05</v>
       </c>
       <c r="T11" s="94" t="n">
-        <v>2.95</v>
+        <v>-10.14</v>
       </c>
       <c r="U11" s="94" t="n">
-        <v>-2.45</v>
+        <v>-11.21</v>
       </c>
       <c r="V11" s="94" t="n">
-        <v>-4.05</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="W11" s="94" t="n">
-        <v>-10.14</v>
+        <v>-11.44</v>
       </c>
       <c r="X11" s="94" t="n">
-        <v>-11.21</v>
+        <v>-12.57</v>
       </c>
       <c r="Y11" s="94" t="n">
-        <v>-11.21</v>
+        <v>-12.57</v>
       </c>
       <c r="Z11" s="94" t="n">
-        <v>-9.029999999999999</v>
+        <v>-12.57</v>
       </c>
       <c r="AA11" s="94" t="n">
-        <v>-11.44</v>
+        <v>-11.96</v>
       </c>
       <c r="AB11" s="94" t="n">
-        <v>-12.57</v>
+        <v>-12.87</v>
       </c>
       <c r="AC11" s="94" t="n">
-        <v>-12.57</v>
+        <v>-14.98</v>
       </c>
       <c r="AD11" s="94" t="n">
-        <v>-12.57</v>
+        <v>-14.79</v>
       </c>
       <c r="AE11" s="94" t="n">
-        <v>-12.57</v>
+        <v>-14.14</v>
       </c>
     </row>
     <row r="12">
@@ -7663,16 +7663,16 @@
         <v>17.89</v>
       </c>
       <c r="G12" s="94" t="n">
-        <v>17.89</v>
+        <v>23.63</v>
       </c>
       <c r="H12" s="94" t="n">
-        <v>23.63</v>
+        <v>24.76</v>
       </c>
       <c r="I12" s="94" t="n">
-        <v>24.76</v>
+        <v>41.13</v>
       </c>
       <c r="J12" s="94" t="n">
-        <v>41.13</v>
+        <v>18.19</v>
       </c>
       <c r="K12" s="94" t="n">
         <v>18.19</v>
@@ -7690,52 +7690,52 @@
         <v>18.19</v>
       </c>
       <c r="P12" s="94" t="n">
-        <v>18.19</v>
+        <v>1.34</v>
       </c>
       <c r="Q12" s="94" t="n">
-        <v>18.19</v>
+        <v>-8.44</v>
       </c>
       <c r="R12" s="94" t="n">
-        <v>1.34</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="S12" s="94" t="n">
-        <v>1.34</v>
+        <v>-10.6</v>
       </c>
       <c r="T12" s="94" t="n">
-        <v>-8.44</v>
+        <v>-14.49</v>
       </c>
       <c r="U12" s="94" t="n">
-        <v>-9.720000000000001</v>
+        <v>-16.56</v>
       </c>
       <c r="V12" s="94" t="n">
-        <v>-10.6</v>
+        <v>-15.65</v>
       </c>
       <c r="W12" s="94" t="n">
-        <v>-14.49</v>
+        <v>-17.96</v>
       </c>
       <c r="X12" s="94" t="n">
-        <v>-16.56</v>
+        <v>-19.08</v>
       </c>
       <c r="Y12" s="94" t="n">
-        <v>-16.56</v>
+        <v>-19.08</v>
       </c>
       <c r="Z12" s="94" t="n">
-        <v>-15.65</v>
+        <v>-19.08</v>
       </c>
       <c r="AA12" s="94" t="n">
-        <v>-17.96</v>
+        <v>-18.72</v>
       </c>
       <c r="AB12" s="94" t="n">
-        <v>-19.08</v>
+        <v>-18.28</v>
       </c>
       <c r="AC12" s="94" t="n">
-        <v>-19.08</v>
+        <v>-20.06</v>
       </c>
       <c r="AD12" s="94" t="n">
-        <v>-19.08</v>
+        <v>-18.31</v>
       </c>
       <c r="AE12" s="94" t="n">
-        <v>-19.08</v>
+        <v>-18.32</v>
       </c>
     </row>
     <row r="13">
@@ -7760,16 +7760,16 @@
         <v>42.18</v>
       </c>
       <c r="G13" s="94" t="n">
-        <v>42.18</v>
+        <v>55.03</v>
       </c>
       <c r="H13" s="94" t="n">
-        <v>55.03</v>
+        <v>62.67</v>
       </c>
       <c r="I13" s="94" t="n">
-        <v>62.67</v>
+        <v>99.77</v>
       </c>
       <c r="J13" s="94" t="n">
-        <v>99.77</v>
+        <v>99.48</v>
       </c>
       <c r="K13" s="94" t="n">
         <v>99.48</v>
@@ -7787,52 +7787,52 @@
         <v>99.48</v>
       </c>
       <c r="P13" s="94" t="n">
-        <v>99.48</v>
+        <v>98.62</v>
       </c>
       <c r="Q13" s="94" t="n">
-        <v>99.48</v>
+        <v>96</v>
       </c>
       <c r="R13" s="94" t="n">
-        <v>98.62</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="S13" s="94" t="n">
-        <v>98.62</v>
+        <v>88.09</v>
       </c>
       <c r="T13" s="94" t="n">
-        <v>96</v>
+        <v>30.34</v>
       </c>
       <c r="U13" s="94" t="n">
-        <v>91.40000000000001</v>
+        <v>39.51</v>
       </c>
       <c r="V13" s="94" t="n">
-        <v>88.09</v>
+        <v>58.67</v>
       </c>
       <c r="W13" s="94" t="n">
-        <v>30.34</v>
+        <v>28.04</v>
       </c>
       <c r="X13" s="94" t="n">
-        <v>39.51</v>
+        <v>29.98</v>
       </c>
       <c r="Y13" s="94" t="n">
-        <v>39.51</v>
+        <v>29.98</v>
       </c>
       <c r="Z13" s="94" t="n">
-        <v>58.67</v>
+        <v>29.98</v>
       </c>
       <c r="AA13" s="94" t="n">
-        <v>28.04</v>
+        <v>54.57</v>
       </c>
       <c r="AB13" s="94" t="n">
-        <v>29.98</v>
+        <v>69.45</v>
       </c>
       <c r="AC13" s="94" t="n">
-        <v>29.98</v>
+        <v>37.43</v>
       </c>
       <c r="AD13" s="94" t="n">
-        <v>29.98</v>
+        <v>35.11</v>
       </c>
       <c r="AE13" s="94" t="n">
-        <v>29.98</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="14">
@@ -7871,125 +7871,123 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="H14" s="91" t="inlineStr">
+      <c r="H14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I14" s="93" t="inlineStr">
+      <c r="J14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AB14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="K14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
+      <c r="AC14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE14" s="91" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -8017,76 +8015,76 @@
         <v>17.96</v>
       </c>
       <c r="H15" s="94" t="n">
-        <v>17.96</v>
+        <v>12.81</v>
       </c>
       <c r="I15" s="94" t="n">
-        <v>12.81</v>
+        <v>17.35</v>
       </c>
       <c r="J15" s="94" t="n">
-        <v>17.35</v>
+        <v>32.21</v>
       </c>
       <c r="K15" s="94" t="n">
-        <v>32.21</v>
+        <v>29.75</v>
       </c>
       <c r="L15" s="94" t="n">
-        <v>29.75</v>
+        <v>26.19</v>
       </c>
       <c r="M15" s="94" t="n">
-        <v>29.75</v>
+        <v>26.09</v>
       </c>
       <c r="N15" s="94" t="n">
-        <v>26.19</v>
+        <v>17.23</v>
       </c>
       <c r="O15" s="94" t="n">
-        <v>26.09</v>
+        <v>17.23</v>
       </c>
       <c r="P15" s="94" t="n">
-        <v>17.23</v>
+        <v>14.76</v>
       </c>
       <c r="Q15" s="94" t="n">
-        <v>17.23</v>
+        <v>12.13</v>
       </c>
       <c r="R15" s="94" t="n">
-        <v>14.76</v>
+        <v>7.96</v>
       </c>
       <c r="S15" s="94" t="n">
-        <v>14.76</v>
+        <v>7.25</v>
       </c>
       <c r="T15" s="94" t="n">
-        <v>12.13</v>
+        <v>0.87</v>
       </c>
       <c r="U15" s="94" t="n">
-        <v>7.96</v>
+        <v>1.03</v>
       </c>
       <c r="V15" s="94" t="n">
-        <v>7.25</v>
+        <v>-0.08</v>
       </c>
       <c r="W15" s="94" t="n">
-        <v>0.87</v>
+        <v>-2.04</v>
       </c>
       <c r="X15" s="94" t="n">
-        <v>1.03</v>
+        <v>-2.04</v>
       </c>
       <c r="Y15" s="94" t="n">
-        <v>1.03</v>
+        <v>-4.98</v>
       </c>
       <c r="Z15" s="94" t="n">
-        <v>-0.08</v>
+        <v>-5.76</v>
       </c>
       <c r="AA15" s="94" t="n">
-        <v>-2.04</v>
+        <v>-3.77</v>
       </c>
       <c r="AB15" s="94" t="n">
-        <v>-2.04</v>
+        <v>-4.61</v>
       </c>
       <c r="AC15" s="94" t="n">
-        <v>-4.98</v>
+        <v>-3.94</v>
       </c>
       <c r="AD15" s="94" t="n">
-        <v>-5.76</v>
+        <v>-5.06</v>
       </c>
       <c r="AE15" s="94" t="n">
-        <v>-5.76</v>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -8114,76 +8112,76 @@
         <v>30.79</v>
       </c>
       <c r="H16" s="94" t="n">
-        <v>30.79</v>
+        <v>24.32</v>
       </c>
       <c r="I16" s="94" t="n">
-        <v>24.32</v>
+        <v>25.15</v>
       </c>
       <c r="J16" s="94" t="n">
-        <v>25.15</v>
+        <v>35.13</v>
       </c>
       <c r="K16" s="94" t="n">
-        <v>35.13</v>
+        <v>32.66</v>
       </c>
       <c r="L16" s="94" t="n">
-        <v>32.66</v>
+        <v>31.41</v>
       </c>
       <c r="M16" s="94" t="n">
-        <v>32.66</v>
+        <v>34.13</v>
       </c>
       <c r="N16" s="94" t="n">
-        <v>31.41</v>
+        <v>26.37</v>
       </c>
       <c r="O16" s="94" t="n">
-        <v>34.13</v>
+        <v>26.37</v>
       </c>
       <c r="P16" s="94" t="n">
-        <v>26.37</v>
+        <v>23.36</v>
       </c>
       <c r="Q16" s="94" t="n">
-        <v>26.37</v>
+        <v>17.68</v>
       </c>
       <c r="R16" s="94" t="n">
-        <v>23.36</v>
+        <v>15.64</v>
       </c>
       <c r="S16" s="94" t="n">
-        <v>23.36</v>
+        <v>15.91</v>
       </c>
       <c r="T16" s="94" t="n">
-        <v>17.68</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="U16" s="94" t="n">
-        <v>15.64</v>
+        <v>10.84</v>
       </c>
       <c r="V16" s="94" t="n">
-        <v>15.91</v>
+        <v>9.17</v>
       </c>
       <c r="W16" s="94" t="n">
-        <v>9.800000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="X16" s="94" t="n">
-        <v>10.84</v>
+        <v>4.73</v>
       </c>
       <c r="Y16" s="94" t="n">
-        <v>10.84</v>
+        <v>5.31</v>
       </c>
       <c r="Z16" s="94" t="n">
-        <v>9.17</v>
+        <v>5.08</v>
       </c>
       <c r="AA16" s="94" t="n">
-        <v>4.73</v>
+        <v>3.01</v>
       </c>
       <c r="AB16" s="94" t="n">
-        <v>4.73</v>
+        <v>2.32</v>
       </c>
       <c r="AC16" s="94" t="n">
-        <v>5.31</v>
+        <v>1.61</v>
       </c>
       <c r="AD16" s="94" t="n">
-        <v>5.08</v>
+        <v>0.67</v>
       </c>
       <c r="AE16" s="94" t="n">
-        <v>5.08</v>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -8211,76 +8209,76 @@
         <v>48.87</v>
       </c>
       <c r="H17" s="94" t="n">
-        <v>48.87</v>
+        <v>35.54</v>
       </c>
       <c r="I17" s="94" t="n">
-        <v>35.54</v>
+        <v>39.14</v>
       </c>
       <c r="J17" s="94" t="n">
-        <v>39.14</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="K17" s="94" t="n">
-        <v>91.23999999999999</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="L17" s="94" t="n">
-        <v>89.48999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="M17" s="94" t="n">
-        <v>89.48999999999999</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="N17" s="94" t="n">
-        <v>85.84</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="O17" s="94" t="n">
-        <v>99.56999999999999</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="P17" s="94" t="n">
-        <v>99.18000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="Q17" s="94" t="n">
-        <v>99.18000000000001</v>
+        <v>98.23</v>
       </c>
       <c r="R17" s="94" t="n">
-        <v>98.89</v>
+        <v>96.44</v>
       </c>
       <c r="S17" s="94" t="n">
-        <v>98.89</v>
+        <v>95.94</v>
       </c>
       <c r="T17" s="94" t="n">
-        <v>98.23</v>
+        <v>89.48</v>
       </c>
       <c r="U17" s="94" t="n">
-        <v>96.44</v>
+        <v>91.13</v>
       </c>
       <c r="V17" s="94" t="n">
-        <v>95.94</v>
+        <v>87.39</v>
       </c>
       <c r="W17" s="94" t="n">
-        <v>89.48</v>
+        <v>76.86</v>
       </c>
       <c r="X17" s="94" t="n">
-        <v>91.13</v>
+        <v>76.86</v>
       </c>
       <c r="Y17" s="94" t="n">
-        <v>91.13</v>
+        <v>59.96</v>
       </c>
       <c r="Z17" s="94" t="n">
-        <v>87.39</v>
+        <v>54.39</v>
       </c>
       <c r="AA17" s="94" t="n">
-        <v>76.86</v>
+        <v>38.93</v>
       </c>
       <c r="AB17" s="94" t="n">
-        <v>76.86</v>
+        <v>17.46</v>
       </c>
       <c r="AC17" s="94" t="n">
-        <v>59.96</v>
+        <v>23.32</v>
       </c>
       <c r="AD17" s="94" t="n">
-        <v>54.39</v>
+        <v>17.15</v>
       </c>
       <c r="AE17" s="94" t="n">
-        <v>54.39</v>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -8289,154 +8287,154 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="92" t="inlineStr">
+      <c r="B18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="C18" s="92" t="inlineStr">
+      <c r="D18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D18" s="91" t="inlineStr">
+      <c r="F18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E18" s="92" t="inlineStr">
+      <c r="M18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F18" s="92" t="inlineStr">
+      <c r="T18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G18" s="92" t="inlineStr">
+      <c r="U18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H18" s="92" t="inlineStr">
+      <c r="V18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I18" s="92" t="inlineStr">
+      <c r="W18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J18" s="92" t="inlineStr">
+      <c r="Y18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K18" s="93" t="inlineStr">
+      <c r="Z18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AC18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AD18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="AE18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -8447,7 +8445,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>5.16</v>
+        <v>7.63</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>5.16</v>
@@ -8462,79 +8460,79 @@
         <v>4.88</v>
       </c>
       <c r="G19" s="94" t="n">
-        <v>4.88</v>
+        <v>3.43</v>
       </c>
       <c r="H19" s="94" t="n">
-        <v>3.43</v>
+        <v>2.2</v>
       </c>
       <c r="I19" s="94" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="J19" s="94" t="n">
-        <v>2.13</v>
+        <v>1.44</v>
       </c>
       <c r="K19" s="94" t="n">
-        <v>1.44</v>
+        <v>2.98</v>
       </c>
       <c r="L19" s="94" t="n">
-        <v>2.98</v>
+        <v>1.17</v>
       </c>
       <c r="M19" s="94" t="n">
-        <v>2.98</v>
+        <v>2.38</v>
       </c>
       <c r="N19" s="94" t="n">
-        <v>1.17</v>
+        <v>2.44</v>
       </c>
       <c r="O19" s="94" t="n">
-        <v>2.38</v>
+        <v>3.51</v>
       </c>
       <c r="P19" s="94" t="n">
-        <v>2.44</v>
+        <v>3.63</v>
       </c>
       <c r="Q19" s="94" t="n">
-        <v>3.51</v>
+        <v>4.29</v>
       </c>
       <c r="R19" s="94" t="n">
-        <v>3.63</v>
+        <v>4.51</v>
       </c>
       <c r="S19" s="94" t="n">
-        <v>3.63</v>
+        <v>4.99</v>
       </c>
       <c r="T19" s="94" t="n">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="U19" s="94" t="n">
-        <v>4.51</v>
+        <v>4.1</v>
       </c>
       <c r="V19" s="94" t="n">
-        <v>4.99</v>
+        <v>4.47</v>
       </c>
       <c r="W19" s="94" t="n">
-        <v>4.3</v>
+        <v>3.13</v>
       </c>
       <c r="X19" s="94" t="n">
-        <v>4.1</v>
+        <v>3.11</v>
       </c>
       <c r="Y19" s="94" t="n">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="Z19" s="94" t="n">
-        <v>4.47</v>
+        <v>2.53</v>
       </c>
       <c r="AA19" s="94" t="n">
-        <v>3.13</v>
+        <v>2.24</v>
       </c>
       <c r="AB19" s="94" t="n">
-        <v>3.11</v>
+        <v>2.26</v>
       </c>
       <c r="AC19" s="94" t="n">
-        <v>2.92</v>
+        <v>1.14</v>
       </c>
       <c r="AD19" s="94" t="n">
-        <v>2.53</v>
+        <v>0.92</v>
       </c>
       <c r="AE19" s="94" t="n">
-        <v>2.53</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="20">
@@ -8544,7 +8542,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>15.73</v>
+        <v>14.54</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>15.73</v>
@@ -8559,79 +8557,79 @@
         <v>16.05</v>
       </c>
       <c r="G20" s="94" t="n">
-        <v>16.05</v>
+        <v>16.36</v>
       </c>
       <c r="H20" s="94" t="n">
-        <v>16.36</v>
+        <v>15.58</v>
       </c>
       <c r="I20" s="94" t="n">
-        <v>15.58</v>
+        <v>14.51</v>
       </c>
       <c r="J20" s="94" t="n">
-        <v>14.51</v>
+        <v>12.76</v>
       </c>
       <c r="K20" s="94" t="n">
-        <v>12.76</v>
+        <v>13.62</v>
       </c>
       <c r="L20" s="94" t="n">
-        <v>13.62</v>
+        <v>11.25</v>
       </c>
       <c r="M20" s="94" t="n">
-        <v>13.62</v>
+        <v>9.82</v>
       </c>
       <c r="N20" s="94" t="n">
-        <v>11.25</v>
+        <v>10.62</v>
       </c>
       <c r="O20" s="94" t="n">
-        <v>9.82</v>
+        <v>10.61</v>
       </c>
       <c r="P20" s="94" t="n">
-        <v>10.62</v>
+        <v>10.3</v>
       </c>
       <c r="Q20" s="94" t="n">
-        <v>10.61</v>
+        <v>10.4</v>
       </c>
       <c r="R20" s="94" t="n">
-        <v>10.3</v>
+        <v>11.17</v>
       </c>
       <c r="S20" s="94" t="n">
-        <v>10.3</v>
+        <v>10.01</v>
       </c>
       <c r="T20" s="94" t="n">
-        <v>10.4</v>
+        <v>9.85</v>
       </c>
       <c r="U20" s="94" t="n">
-        <v>11.17</v>
+        <v>8.75</v>
       </c>
       <c r="V20" s="94" t="n">
-        <v>10.01</v>
+        <v>8.74</v>
       </c>
       <c r="W20" s="94" t="n">
-        <v>9.85</v>
+        <v>7.05</v>
       </c>
       <c r="X20" s="94" t="n">
-        <v>8.75</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="Y20" s="94" t="n">
-        <v>8.75</v>
+        <v>7.95</v>
       </c>
       <c r="Z20" s="94" t="n">
-        <v>8.74</v>
+        <v>7.49</v>
       </c>
       <c r="AA20" s="94" t="n">
-        <v>7.05</v>
+        <v>6.76</v>
       </c>
       <c r="AB20" s="94" t="n">
-        <v>8.279999999999999</v>
+        <v>6.31</v>
       </c>
       <c r="AC20" s="94" t="n">
-        <v>7.95</v>
+        <v>6.12</v>
       </c>
       <c r="AD20" s="94" t="n">
-        <v>7.49</v>
+        <v>6.25</v>
       </c>
       <c r="AE20" s="94" t="n">
-        <v>7.49</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="21">
@@ -8641,7 +8639,7 @@
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>65.73999999999999</v>
+        <v>63.88</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>65.73999999999999</v>
@@ -8656,79 +8654,79 @@
         <v>84.56999999999999</v>
       </c>
       <c r="G21" s="94" t="n">
-        <v>84.56999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="H21" s="94" t="n">
-        <v>65.7</v>
+        <v>83.12</v>
       </c>
       <c r="I21" s="94" t="n">
-        <v>83.12</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="J21" s="94" t="n">
-        <v>69.18000000000001</v>
+        <v>30.41</v>
       </c>
       <c r="K21" s="94" t="n">
-        <v>30.41</v>
+        <v>81.84</v>
       </c>
       <c r="L21" s="94" t="n">
-        <v>81.84</v>
+        <v>15.76</v>
       </c>
       <c r="M21" s="94" t="n">
-        <v>81.84</v>
+        <v>23.93</v>
       </c>
       <c r="N21" s="94" t="n">
-        <v>15.76</v>
+        <v>22.27</v>
       </c>
       <c r="O21" s="94" t="n">
-        <v>23.93</v>
+        <v>86.19</v>
       </c>
       <c r="P21" s="94" t="n">
-        <v>22.27</v>
+        <v>60.63</v>
       </c>
       <c r="Q21" s="94" t="n">
-        <v>86.19</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="R21" s="94" t="n">
-        <v>60.63</v>
+        <v>58.19</v>
       </c>
       <c r="S21" s="94" t="n">
-        <v>60.63</v>
+        <v>90.16</v>
       </c>
       <c r="T21" s="94" t="n">
-        <v>83.51000000000001</v>
+        <v>84.39</v>
       </c>
       <c r="U21" s="94" t="n">
-        <v>58.19</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="V21" s="94" t="n">
-        <v>90.16</v>
+        <v>92.34</v>
       </c>
       <c r="W21" s="94" t="n">
-        <v>84.39</v>
+        <v>40.89</v>
       </c>
       <c r="X21" s="94" t="n">
-        <v>76.79000000000001</v>
+        <v>96.09</v>
       </c>
       <c r="Y21" s="94" t="n">
-        <v>76.79000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="Z21" s="94" t="n">
-        <v>92.34</v>
+        <v>95.06</v>
       </c>
       <c r="AA21" s="94" t="n">
-        <v>40.89</v>
+        <v>91.83</v>
       </c>
       <c r="AB21" s="94" t="n">
-        <v>96.09</v>
+        <v>85.17</v>
       </c>
       <c r="AC21" s="94" t="n">
-        <v>95.83</v>
+        <v>65.2</v>
       </c>
       <c r="AD21" s="94" t="n">
-        <v>95.06</v>
+        <v>51.58</v>
       </c>
       <c r="AE21" s="94" t="n">
-        <v>95.06</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -8772,119 +8770,119 @@
           <t>red</t>
         </is>
       </c>
-      <c r="I22" s="92" t="inlineStr">
+      <c r="I22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J22" s="91" t="inlineStr">
+      <c r="L22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K22" s="93" t="inlineStr">
+      <c r="M22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AC22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N22" s="91" t="inlineStr">
+      <c r="AD22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="AE22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -8895,7 +8893,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>6.74</v>
+        <v>8.49</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>6.74</v>
@@ -8910,79 +8908,79 @@
         <v>5.41</v>
       </c>
       <c r="G23" s="94" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H23" s="94" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I23" s="94" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="J23" s="94" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="K23" s="94" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="L23" s="94" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="M23" s="94" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="N23" s="94" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="O23" s="94" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P23" s="94" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="Q23" s="94" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="R23" s="94" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="S23" s="94" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="T23" s="94" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="U23" s="94" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V23" s="94" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="W23" s="94" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="X23" s="94" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="Y23" s="94" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="Z23" s="94" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="AA23" s="94" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AB23" s="94" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AC23" s="94" t="n">
         <v>5.41</v>
       </c>
-      <c r="H23" s="94" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="I23" s="94" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J23" s="94" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="K23" s="94" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L23" s="94" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="M23" s="94" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="N23" s="94" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="O23" s="94" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="P23" s="94" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="Q23" s="94" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R23" s="94" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="S23" s="94" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="T23" s="94" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="U23" s="94" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="V23" s="94" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W23" s="94" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="X23" s="94" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y23" s="94" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z23" s="94" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="AA23" s="94" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="AB23" s="94" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="AC23" s="94" t="n">
-        <v>6.36</v>
-      </c>
       <c r="AD23" s="94" t="n">
-        <v>6.59</v>
+        <v>5.47</v>
       </c>
       <c r="AE23" s="94" t="n">
-        <v>6.59</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="24">
@@ -8992,7 +8990,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>13.11</v>
+        <v>13.07</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>13.11</v>
@@ -9007,79 +9005,79 @@
         <v>12.09</v>
       </c>
       <c r="G24" s="94" t="n">
-        <v>12.09</v>
+        <v>11.76</v>
       </c>
       <c r="H24" s="94" t="n">
-        <v>11.76</v>
+        <v>12.54</v>
       </c>
       <c r="I24" s="94" t="n">
-        <v>12.54</v>
+        <v>11.46</v>
       </c>
       <c r="J24" s="94" t="n">
-        <v>11.46</v>
+        <v>10.99</v>
       </c>
       <c r="K24" s="94" t="n">
-        <v>10.99</v>
+        <v>12.24</v>
       </c>
       <c r="L24" s="94" t="n">
-        <v>12.24</v>
+        <v>10.61</v>
       </c>
       <c r="M24" s="94" t="n">
-        <v>12.24</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="N24" s="94" t="n">
-        <v>10.61</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="O24" s="94" t="n">
-        <v>9.720000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="P24" s="94" t="n">
-        <v>9.609999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="Q24" s="94" t="n">
-        <v>8.859999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="R24" s="94" t="n">
-        <v>8.789999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="S24" s="94" t="n">
-        <v>8.789999999999999</v>
+        <v>7.87</v>
       </c>
       <c r="T24" s="94" t="n">
-        <v>8.41</v>
+        <v>7.54</v>
       </c>
       <c r="U24" s="94" t="n">
-        <v>8.6</v>
+        <v>6.31</v>
       </c>
       <c r="V24" s="94" t="n">
-        <v>7.87</v>
+        <v>5.57</v>
       </c>
       <c r="W24" s="94" t="n">
-        <v>7.54</v>
+        <v>4.38</v>
       </c>
       <c r="X24" s="94" t="n">
-        <v>6.31</v>
+        <v>5.92</v>
       </c>
       <c r="Y24" s="94" t="n">
-        <v>6.31</v>
+        <v>5.87</v>
       </c>
       <c r="Z24" s="94" t="n">
-        <v>5.57</v>
+        <v>4.86</v>
       </c>
       <c r="AA24" s="94" t="n">
-        <v>4.38</v>
+        <v>3.31</v>
       </c>
       <c r="AB24" s="94" t="n">
-        <v>5.92</v>
+        <v>3.42</v>
       </c>
       <c r="AC24" s="94" t="n">
-        <v>5.87</v>
+        <v>4.16</v>
       </c>
       <c r="AD24" s="94" t="n">
-        <v>4.86</v>
+        <v>5.26</v>
       </c>
       <c r="AE24" s="94" t="n">
-        <v>4.86</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="25">
@@ -9089,7 +9087,7 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>70.95999999999999</v>
+        <v>77.16</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>70.95999999999999</v>
@@ -9104,79 +9102,79 @@
         <v>82.94</v>
       </c>
       <c r="G25" s="94" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="H25" s="94" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="I25" s="94" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="J25" s="94" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="K25" s="94" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="L25" s="94" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="M25" s="94" t="n">
+        <v>52.09</v>
+      </c>
+      <c r="N25" s="94" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="O25" s="94" t="n">
+        <v>76.02</v>
+      </c>
+      <c r="P25" s="94" t="n">
+        <v>74.91</v>
+      </c>
+      <c r="Q25" s="94" t="n">
+        <v>66.62</v>
+      </c>
+      <c r="R25" s="94" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="S25" s="94" t="n">
+        <v>92.18000000000001</v>
+      </c>
+      <c r="T25" s="94" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="U25" s="94" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="V25" s="94" t="n">
+        <v>87.58</v>
+      </c>
+      <c r="W25" s="94" t="n">
+        <v>65.31</v>
+      </c>
+      <c r="X25" s="94" t="n">
+        <v>85.48999999999999</v>
+      </c>
+      <c r="Y25" s="94" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="Z25" s="94" t="n">
         <v>82.94</v>
       </c>
-      <c r="H25" s="94" t="n">
-        <v>66.56</v>
-      </c>
-      <c r="I25" s="94" t="n">
-        <v>73.18000000000001</v>
-      </c>
-      <c r="J25" s="94" t="n">
-        <v>46.98</v>
-      </c>
-      <c r="K25" s="94" t="n">
-        <v>34.52</v>
-      </c>
-      <c r="L25" s="94" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="M25" s="94" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="N25" s="94" t="n">
-        <v>28.19</v>
-      </c>
-      <c r="O25" s="94" t="n">
-        <v>52.09</v>
-      </c>
-      <c r="P25" s="94" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="Q25" s="94" t="n">
-        <v>76.02</v>
-      </c>
-      <c r="R25" s="94" t="n">
-        <v>74.91</v>
-      </c>
-      <c r="S25" s="94" t="n">
-        <v>74.91</v>
-      </c>
-      <c r="T25" s="94" t="n">
-        <v>66.62</v>
-      </c>
-      <c r="U25" s="94" t="n">
-        <v>42.84</v>
-      </c>
-      <c r="V25" s="94" t="n">
-        <v>92.18000000000001</v>
-      </c>
-      <c r="W25" s="94" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="X25" s="94" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="Y25" s="94" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="Z25" s="94" t="n">
-        <v>87.58</v>
-      </c>
       <c r="AA25" s="94" t="n">
-        <v>65.31</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="AB25" s="94" t="n">
-        <v>85.48999999999999</v>
+        <v>56.57</v>
       </c>
       <c r="AC25" s="94" t="n">
-        <v>88.3</v>
+        <v>46.45</v>
       </c>
       <c r="AD25" s="94" t="n">
-        <v>82.94</v>
+        <v>52.5</v>
       </c>
       <c r="AE25" s="94" t="n">
-        <v>82.94</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="26">
@@ -9225,114 +9223,114 @@
           <t>red</t>
         </is>
       </c>
-      <c r="J26" s="92" t="inlineStr">
+      <c r="J26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K26" s="93" t="inlineStr">
+      <c r="L26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AC26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AD26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="AE26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -9343,7 +9341,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>2.05</v>
+        <v>5.95</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>2.05</v>
@@ -9358,79 +9356,79 @@
         <v>2.64</v>
       </c>
       <c r="G27" s="94" t="n">
-        <v>2.64</v>
+        <v>1.58</v>
       </c>
       <c r="H27" s="94" t="n">
-        <v>1.58</v>
+        <v>-1.18</v>
       </c>
       <c r="I27" s="94" t="n">
-        <v>-1.18</v>
+        <v>-1.57</v>
       </c>
       <c r="J27" s="94" t="n">
-        <v>-1.57</v>
+        <v>-2.58</v>
       </c>
       <c r="K27" s="94" t="n">
-        <v>-2.58</v>
+        <v>-0.8</v>
       </c>
       <c r="L27" s="94" t="n">
-        <v>-0.8</v>
+        <v>-3.91</v>
       </c>
       <c r="M27" s="94" t="n">
-        <v>-0.8</v>
+        <v>-2.74</v>
       </c>
       <c r="N27" s="94" t="n">
-        <v>-3.91</v>
+        <v>-2.68</v>
       </c>
       <c r="O27" s="94" t="n">
-        <v>-2.74</v>
+        <v>-0.89</v>
       </c>
       <c r="P27" s="94" t="n">
-        <v>-2.68</v>
+        <v>-0.38</v>
       </c>
       <c r="Q27" s="94" t="n">
-        <v>-0.89</v>
+        <v>0.9</v>
       </c>
       <c r="R27" s="94" t="n">
-        <v>-0.38</v>
+        <v>1.13</v>
       </c>
       <c r="S27" s="94" t="n">
-        <v>-0.38</v>
+        <v>1.93</v>
       </c>
       <c r="T27" s="94" t="n">
-        <v>0.9</v>
+        <v>0.65</v>
       </c>
       <c r="U27" s="94" t="n">
-        <v>1.13</v>
+        <v>0.8</v>
       </c>
       <c r="V27" s="94" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="W27" s="94" t="n">
-        <v>0.65</v>
+        <v>0.44</v>
       </c>
       <c r="X27" s="94" t="n">
-        <v>0.8</v>
+        <v>-0.35</v>
       </c>
       <c r="Y27" s="94" t="n">
-        <v>0.8</v>
+        <v>-0.73</v>
       </c>
       <c r="Z27" s="94" t="n">
-        <v>1.67</v>
+        <v>-1</v>
       </c>
       <c r="AA27" s="94" t="n">
-        <v>0.44</v>
+        <v>-1.61</v>
       </c>
       <c r="AB27" s="94" t="n">
-        <v>-0.35</v>
+        <v>-1.66</v>
       </c>
       <c r="AC27" s="94" t="n">
-        <v>-0.73</v>
+        <v>-3.63</v>
       </c>
       <c r="AD27" s="94" t="n">
-        <v>-1</v>
+        <v>-4.11</v>
       </c>
       <c r="AE27" s="94" t="n">
-        <v>-1</v>
+        <v>-3.76</v>
       </c>
     </row>
     <row r="28">
@@ -9440,7 +9438,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>17.65</v>
+        <v>15.35</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>17.65</v>
@@ -9455,79 +9453,79 @@
         <v>18.71</v>
       </c>
       <c r="G28" s="94" t="n">
-        <v>18.71</v>
+        <v>19.63</v>
       </c>
       <c r="H28" s="94" t="n">
-        <v>19.63</v>
+        <v>17.24</v>
       </c>
       <c r="I28" s="94" t="n">
-        <v>17.24</v>
+        <v>15.94</v>
       </c>
       <c r="J28" s="94" t="n">
-        <v>15.94</v>
+        <v>12.98</v>
       </c>
       <c r="K28" s="94" t="n">
-        <v>12.98</v>
+        <v>14.18</v>
       </c>
       <c r="L28" s="94" t="n">
-        <v>14.18</v>
+        <v>10.78</v>
       </c>
       <c r="M28" s="94" t="n">
-        <v>14.18</v>
+        <v>9.02</v>
       </c>
       <c r="N28" s="94" t="n">
-        <v>10.78</v>
+        <v>10.76</v>
       </c>
       <c r="O28" s="94" t="n">
-        <v>9.02</v>
+        <v>11.54</v>
       </c>
       <c r="P28" s="94" t="n">
-        <v>10.76</v>
+        <v>11.48</v>
       </c>
       <c r="Q28" s="94" t="n">
-        <v>11.54</v>
+        <v>11.95</v>
       </c>
       <c r="R28" s="94" t="n">
-        <v>11.48</v>
+        <v>12.67</v>
       </c>
       <c r="S28" s="94" t="n">
-        <v>11.48</v>
+        <v>11.04</v>
       </c>
       <c r="T28" s="94" t="n">
-        <v>11.95</v>
+        <v>10.68</v>
       </c>
       <c r="U28" s="94" t="n">
-        <v>12.67</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="V28" s="94" t="n">
-        <v>11.04</v>
+        <v>9.98</v>
       </c>
       <c r="W28" s="94" t="n">
-        <v>10.68</v>
+        <v>7.16</v>
       </c>
       <c r="X28" s="94" t="n">
-        <v>9.460000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="Y28" s="94" t="n">
-        <v>9.460000000000001</v>
+        <v>7.37</v>
       </c>
       <c r="Z28" s="94" t="n">
-        <v>9.98</v>
+        <v>7.64</v>
       </c>
       <c r="AA28" s="94" t="n">
-        <v>7.16</v>
+        <v>7.12</v>
       </c>
       <c r="AB28" s="94" t="n">
-        <v>8.039999999999999</v>
+        <v>6.27</v>
       </c>
       <c r="AC28" s="94" t="n">
-        <v>7.37</v>
+        <v>5.31</v>
       </c>
       <c r="AD28" s="94" t="n">
-        <v>7.64</v>
+        <v>4.85</v>
       </c>
       <c r="AE28" s="94" t="n">
-        <v>7.64</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="29">
@@ -9537,7 +9535,7 @@
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>52.8</v>
+        <v>55.65</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>52.8</v>
@@ -9552,79 +9550,79 @@
         <v>86.79000000000001</v>
       </c>
       <c r="G29" s="94" t="n">
-        <v>86.79000000000001</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="H29" s="94" t="n">
-        <v>77.45999999999999</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="I29" s="94" t="n">
-        <v>82.01000000000001</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="J29" s="94" t="n">
-        <v>72.98999999999999</v>
+        <v>32.92</v>
       </c>
       <c r="K29" s="94" t="n">
-        <v>32.92</v>
+        <v>85.03</v>
       </c>
       <c r="L29" s="94" t="n">
-        <v>85.03</v>
+        <v>20.54</v>
       </c>
       <c r="M29" s="94" t="n">
-        <v>85.03</v>
+        <v>21.97</v>
       </c>
       <c r="N29" s="94" t="n">
-        <v>20.54</v>
+        <v>15.42</v>
       </c>
       <c r="O29" s="94" t="n">
-        <v>21.97</v>
+        <v>74.7</v>
       </c>
       <c r="P29" s="94" t="n">
-        <v>15.42</v>
+        <v>51.35</v>
       </c>
       <c r="Q29" s="94" t="n">
-        <v>74.7</v>
+        <v>96.66</v>
       </c>
       <c r="R29" s="94" t="n">
-        <v>51.35</v>
+        <v>89.75</v>
       </c>
       <c r="S29" s="94" t="n">
-        <v>51.35</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="T29" s="94" t="n">
-        <v>96.66</v>
+        <v>77.02</v>
       </c>
       <c r="U29" s="94" t="n">
-        <v>89.75</v>
+        <v>73.3</v>
       </c>
       <c r="V29" s="94" t="n">
-        <v>88.93000000000001</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="W29" s="94" t="n">
-        <v>77.02</v>
+        <v>42.32</v>
       </c>
       <c r="X29" s="94" t="n">
-        <v>73.3</v>
+        <v>70.06</v>
       </c>
       <c r="Y29" s="94" t="n">
-        <v>73.3</v>
+        <v>61.86</v>
       </c>
       <c r="Z29" s="94" t="n">
-        <v>92.18000000000001</v>
+        <v>95.17</v>
       </c>
       <c r="AA29" s="94" t="n">
-        <v>42.32</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="AB29" s="94" t="n">
-        <v>70.06</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="AC29" s="94" t="n">
-        <v>61.86</v>
+        <v>65.19</v>
       </c>
       <c r="AD29" s="94" t="n">
-        <v>95.17</v>
+        <v>44.48</v>
       </c>
       <c r="AE29" s="94" t="n">
-        <v>95.17</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="30">
@@ -9658,129 +9656,129 @@
           <t>red</t>
         </is>
       </c>
-      <c r="G30" s="92" t="inlineStr">
+      <c r="G30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H30" s="91" t="inlineStr">
+      <c r="K30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I30" s="91" t="inlineStr">
+      <c r="L30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J30" s="91" t="inlineStr">
+      <c r="M30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K30" s="92" t="inlineStr">
+      <c r="O30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L30" s="91" t="inlineStr">
+      <c r="Q30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M30" s="91" t="inlineStr">
+      <c r="X30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N30" s="91" t="inlineStr">
+      <c r="Y30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O30" s="93" t="inlineStr">
+      <c r="Z30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AB30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="AC30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -9806,79 +9804,79 @@
         <v>-1.3</v>
       </c>
       <c r="G31" s="94" t="n">
-        <v>-1.3</v>
+        <v>-4.18</v>
       </c>
       <c r="H31" s="94" t="n">
-        <v>-4.18</v>
+        <v>-4.84</v>
       </c>
       <c r="I31" s="94" t="n">
-        <v>-4.84</v>
+        <v>-5.47</v>
       </c>
       <c r="J31" s="94" t="n">
-        <v>-5.47</v>
+        <v>-6.85</v>
       </c>
       <c r="K31" s="94" t="n">
-        <v>-6.85</v>
+        <v>-7.64</v>
       </c>
       <c r="L31" s="94" t="n">
-        <v>-7.64</v>
+        <v>-7.28</v>
       </c>
       <c r="M31" s="94" t="n">
-        <v>-7.64</v>
+        <v>-7.29</v>
       </c>
       <c r="N31" s="94" t="n">
-        <v>-7.28</v>
+        <v>-5.52</v>
       </c>
       <c r="O31" s="94" t="n">
-        <v>-7.29</v>
+        <v>-7.32</v>
       </c>
       <c r="P31" s="94" t="n">
-        <v>-5.52</v>
+        <v>-1.85</v>
       </c>
       <c r="Q31" s="94" t="n">
-        <v>-7.32</v>
+        <v>-2.87</v>
       </c>
       <c r="R31" s="94" t="n">
-        <v>-1.85</v>
+        <v>-4.44</v>
       </c>
       <c r="S31" s="94" t="n">
-        <v>-1.85</v>
+        <v>-4.15</v>
       </c>
       <c r="T31" s="94" t="n">
-        <v>-2.87</v>
+        <v>-4.11</v>
       </c>
       <c r="U31" s="94" t="n">
-        <v>-4.44</v>
+        <v>-4.11</v>
       </c>
       <c r="V31" s="94" t="n">
-        <v>-4.15</v>
+        <v>-6.33</v>
       </c>
       <c r="W31" s="94" t="n">
-        <v>-4.11</v>
+        <v>-7.13</v>
       </c>
       <c r="X31" s="94" t="n">
-        <v>-4.11</v>
+        <v>-6.7</v>
       </c>
       <c r="Y31" s="94" t="n">
-        <v>-4.11</v>
+        <v>-5.28</v>
       </c>
       <c r="Z31" s="94" t="n">
-        <v>-6.33</v>
+        <v>-5.31</v>
       </c>
       <c r="AA31" s="94" t="n">
-        <v>-7.13</v>
+        <v>-4.5</v>
       </c>
       <c r="AB31" s="94" t="n">
+        <v>-7.44</v>
+      </c>
+      <c r="AC31" s="94" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="AD31" s="94" t="n">
         <v>-6.7</v>
       </c>
-      <c r="AC31" s="94" t="n">
-        <v>-5.28</v>
-      </c>
-      <c r="AD31" s="94" t="n">
-        <v>-5.31</v>
-      </c>
       <c r="AE31" s="94" t="n">
-        <v>-5.31</v>
+        <v>-6.01</v>
       </c>
     </row>
     <row r="32">
@@ -9903,79 +9901,79 @@
         <v>6.85</v>
       </c>
       <c r="G32" s="94" t="n">
-        <v>6.85</v>
+        <v>3.42</v>
       </c>
       <c r="H32" s="94" t="n">
-        <v>3.42</v>
+        <v>3.47</v>
       </c>
       <c r="I32" s="94" t="n">
-        <v>3.47</v>
+        <v>1.21</v>
       </c>
       <c r="J32" s="94" t="n">
-        <v>1.21</v>
+        <v>0.25</v>
       </c>
       <c r="K32" s="94" t="n">
-        <v>0.25</v>
+        <v>-2.25</v>
       </c>
       <c r="L32" s="94" t="n">
-        <v>-2.25</v>
+        <v>-2.26</v>
       </c>
       <c r="M32" s="94" t="n">
-        <v>-2.25</v>
+        <v>-4.48</v>
       </c>
       <c r="N32" s="94" t="n">
-        <v>-2.26</v>
+        <v>-2.82</v>
       </c>
       <c r="O32" s="94" t="n">
-        <v>-4.48</v>
+        <v>-3.63</v>
       </c>
       <c r="P32" s="94" t="n">
-        <v>-2.82</v>
+        <v>2.15</v>
       </c>
       <c r="Q32" s="94" t="n">
-        <v>-3.63</v>
+        <v>-2.13</v>
       </c>
       <c r="R32" s="94" t="n">
-        <v>2.15</v>
+        <v>-4.01</v>
       </c>
       <c r="S32" s="94" t="n">
-        <v>2.15</v>
+        <v>-4.76</v>
       </c>
       <c r="T32" s="94" t="n">
-        <v>-2.13</v>
+        <v>-5.22</v>
       </c>
       <c r="U32" s="94" t="n">
-        <v>-4.01</v>
+        <v>-5.22</v>
       </c>
       <c r="V32" s="94" t="n">
-        <v>-4.76</v>
+        <v>-7.96</v>
       </c>
       <c r="W32" s="94" t="n">
-        <v>-5.22</v>
+        <v>-9.43</v>
       </c>
       <c r="X32" s="94" t="n">
-        <v>-5.22</v>
+        <v>-11.19</v>
       </c>
       <c r="Y32" s="94" t="n">
-        <v>-5.22</v>
+        <v>-9.5</v>
       </c>
       <c r="Z32" s="94" t="n">
-        <v>-7.96</v>
+        <v>-9.48</v>
       </c>
       <c r="AA32" s="94" t="n">
-        <v>-9.43</v>
+        <v>-9.92</v>
       </c>
       <c r="AB32" s="94" t="n">
-        <v>-11.19</v>
+        <v>-12.73</v>
       </c>
       <c r="AC32" s="94" t="n">
-        <v>-9.5</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="AD32" s="94" t="n">
-        <v>-9.48</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="AE32" s="94" t="n">
-        <v>-9.48</v>
+        <v>-5.98</v>
       </c>
     </row>
     <row r="33">
@@ -10000,79 +9998,79 @@
         <v>63.24</v>
       </c>
       <c r="G33" s="94" t="n">
-        <v>63.24</v>
+        <v>61.28</v>
       </c>
       <c r="H33" s="94" t="n">
-        <v>61.28</v>
+        <v>60.41</v>
       </c>
       <c r="I33" s="94" t="n">
-        <v>60.41</v>
+        <v>57.64</v>
       </c>
       <c r="J33" s="94" t="n">
-        <v>57.64</v>
+        <v>62.13</v>
       </c>
       <c r="K33" s="94" t="n">
-        <v>62.13</v>
+        <v>56.86</v>
       </c>
       <c r="L33" s="94" t="n">
-        <v>56.86</v>
+        <v>56.21</v>
       </c>
       <c r="M33" s="94" t="n">
-        <v>56.86</v>
+        <v>50.28</v>
       </c>
       <c r="N33" s="94" t="n">
-        <v>56.21</v>
+        <v>58.22</v>
       </c>
       <c r="O33" s="94" t="n">
-        <v>50.28</v>
+        <v>52.42</v>
       </c>
       <c r="P33" s="94" t="n">
-        <v>58.22</v>
+        <v>77.31</v>
       </c>
       <c r="Q33" s="94" t="n">
-        <v>52.42</v>
+        <v>71.64</v>
       </c>
       <c r="R33" s="94" t="n">
-        <v>77.31</v>
+        <v>61.74</v>
       </c>
       <c r="S33" s="94" t="n">
-        <v>77.31</v>
+        <v>63.04</v>
       </c>
       <c r="T33" s="94" t="n">
-        <v>71.64</v>
+        <v>60.77</v>
       </c>
       <c r="U33" s="94" t="n">
-        <v>61.74</v>
+        <v>60.77</v>
       </c>
       <c r="V33" s="94" t="n">
-        <v>63.04</v>
+        <v>54.21</v>
       </c>
       <c r="W33" s="94" t="n">
-        <v>60.77</v>
+        <v>42.56</v>
       </c>
       <c r="X33" s="94" t="n">
-        <v>60.77</v>
+        <v>39.44</v>
       </c>
       <c r="Y33" s="94" t="n">
-        <v>60.77</v>
+        <v>43.68</v>
       </c>
       <c r="Z33" s="94" t="n">
-        <v>54.21</v>
+        <v>43.96</v>
       </c>
       <c r="AA33" s="94" t="n">
-        <v>42.56</v>
+        <v>46.79</v>
       </c>
       <c r="AB33" s="94" t="n">
-        <v>39.44</v>
+        <v>26.47</v>
       </c>
       <c r="AC33" s="94" t="n">
-        <v>43.68</v>
+        <v>31.18</v>
       </c>
       <c r="AD33" s="94" t="n">
-        <v>43.96</v>
+        <v>31.7</v>
       </c>
       <c r="AE33" s="94" t="n">
-        <v>43.96</v>
+        <v>33.25</v>
       </c>
     </row>
     <row r="34">
@@ -10081,154 +10079,154 @@
           <t>vn:EIDE</t>
         </is>
       </c>
-      <c r="B34" s="93" t="inlineStr">
+      <c r="B34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C34" s="93" t="inlineStr">
+      <c r="D34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D34" s="91" t="inlineStr">
+      <c r="J34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E34" s="92" t="inlineStr">
+      <c r="N34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F34" s="92" t="inlineStr">
+      <c r="Q34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G34" s="92" t="inlineStr">
+      <c r="R34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H34" s="92" t="inlineStr">
+      <c r="S34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I34" s="92" t="inlineStr">
+      <c r="T34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J34" s="93" t="inlineStr">
+      <c r="U34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K34" s="93" t="inlineStr">
+      <c r="Z34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L34" s="93" t="inlineStr">
+      <c r="AA34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M34" s="93" t="inlineStr">
+      <c r="AB34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N34" s="93" t="inlineStr">
+      <c r="AC34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O34" s="91" t="inlineStr">
+      <c r="AD34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="P34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE34" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -10239,7 +10237,7 @@
         </is>
       </c>
       <c r="B35" s="94" t="n">
-        <v>3.3</v>
+        <v>4.44</v>
       </c>
       <c r="C35" s="94" t="n">
         <v>1.98</v>
@@ -10254,79 +10252,79 @@
         <v>1.56</v>
       </c>
       <c r="G35" s="94" t="n">
-        <v>1.56</v>
+        <v>0.4</v>
       </c>
       <c r="H35" s="94" t="n">
-        <v>0.4</v>
+        <v>0.16</v>
       </c>
       <c r="I35" s="94" t="n">
-        <v>0.16</v>
+        <v>-0.68</v>
       </c>
       <c r="J35" s="94" t="n">
-        <v>-0.68</v>
+        <v>-1.08</v>
       </c>
       <c r="K35" s="94" t="n">
-        <v>-1.08</v>
+        <v>-1.19</v>
       </c>
       <c r="L35" s="94" t="n">
-        <v>-1.19</v>
+        <v>-1.21</v>
       </c>
       <c r="M35" s="94" t="n">
-        <v>-1.19</v>
+        <v>0.33</v>
       </c>
       <c r="N35" s="94" t="n">
-        <v>-1.21</v>
+        <v>0.71</v>
       </c>
       <c r="O35" s="94" t="n">
-        <v>0.33</v>
+        <v>0.63</v>
       </c>
       <c r="P35" s="94" t="n">
-        <v>0.71</v>
+        <v>1.1</v>
       </c>
       <c r="Q35" s="94" t="n">
-        <v>0.63</v>
+        <v>1.71</v>
       </c>
       <c r="R35" s="94" t="n">
-        <v>1.1</v>
+        <v>2.62</v>
       </c>
       <c r="S35" s="94" t="n">
-        <v>1.1</v>
+        <v>1.79</v>
       </c>
       <c r="T35" s="94" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="U35" s="94" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="V35" s="94" t="n">
-        <v>1.79</v>
+        <v>0.8</v>
       </c>
       <c r="W35" s="94" t="n">
-        <v>1.86</v>
+        <v>0.66</v>
       </c>
       <c r="X35" s="94" t="n">
-        <v>1.03</v>
+        <v>0.39</v>
       </c>
       <c r="Y35" s="94" t="n">
-        <v>1.03</v>
+        <v>-3.34</v>
       </c>
       <c r="Z35" s="94" t="n">
-        <v>0.8</v>
+        <v>-2.39</v>
       </c>
       <c r="AA35" s="94" t="n">
-        <v>0.66</v>
+        <v>-1.83</v>
       </c>
       <c r="AB35" s="94" t="n">
-        <v>0.39</v>
+        <v>-2.05</v>
       </c>
       <c r="AC35" s="94" t="n">
-        <v>-3.34</v>
+        <v>-1.53</v>
       </c>
       <c r="AD35" s="94" t="n">
-        <v>-2.39</v>
+        <v>-0.95</v>
       </c>
       <c r="AE35" s="94" t="n">
-        <v>-2.39</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="36">
@@ -10336,7 +10334,7 @@
         </is>
       </c>
       <c r="B36" s="94" t="n">
-        <v>5.2</v>
+        <v>6.37</v>
       </c>
       <c r="C36" s="94" t="n">
         <v>6.18</v>
@@ -10351,89 +10349,89 @@
         <v>8.25</v>
       </c>
       <c r="G36" s="94" t="n">
-        <v>8.25</v>
+        <v>9.49</v>
       </c>
       <c r="H36" s="94" t="n">
-        <v>9.49</v>
+        <v>7.45</v>
       </c>
       <c r="I36" s="94" t="n">
-        <v>7.45</v>
+        <v>4.63</v>
       </c>
       <c r="J36" s="94" t="n">
-        <v>4.63</v>
+        <v>4.38</v>
       </c>
       <c r="K36" s="94" t="n">
-        <v>4.38</v>
+        <v>-0.47</v>
       </c>
       <c r="L36" s="94" t="n">
-        <v>-0.47</v>
+        <v>1.58</v>
       </c>
       <c r="M36" s="94" t="n">
-        <v>-0.47</v>
+        <v>2.33</v>
       </c>
       <c r="N36" s="94" t="n">
-        <v>1.58</v>
+        <v>2.33</v>
       </c>
       <c r="O36" s="94" t="n">
-        <v>2.33</v>
+        <v>3.01</v>
       </c>
       <c r="P36" s="94" t="n">
-        <v>2.33</v>
+        <v>2.85</v>
       </c>
       <c r="Q36" s="94" t="n">
-        <v>3.01</v>
+        <v>1.83</v>
       </c>
       <c r="R36" s="94" t="n">
-        <v>2.85</v>
+        <v>1.26</v>
       </c>
       <c r="S36" s="94" t="n">
-        <v>2.85</v>
+        <v>-0.78</v>
       </c>
       <c r="T36" s="94" t="n">
-        <v>1.83</v>
+        <v>-1.02</v>
       </c>
       <c r="U36" s="94" t="n">
-        <v>1.26</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="V36" s="94" t="n">
-        <v>-0.78</v>
+        <v>-1.47</v>
       </c>
       <c r="W36" s="94" t="n">
-        <v>-1.02</v>
+        <v>-1.42</v>
       </c>
       <c r="X36" s="94" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.81</v>
       </c>
       <c r="Y36" s="94" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.26</v>
       </c>
       <c r="Z36" s="94" t="n">
-        <v>-1.47</v>
+        <v>-2.35</v>
       </c>
       <c r="AA36" s="94" t="n">
-        <v>-1.42</v>
+        <v>-1.57</v>
       </c>
       <c r="AB36" s="94" t="n">
-        <v>-1.81</v>
+        <v>-0.54</v>
       </c>
       <c r="AC36" s="94" t="n">
-        <v>-2.26</v>
+        <v>1.03</v>
       </c>
       <c r="AD36" s="94" t="n">
-        <v>-2.35</v>
+        <v>1.94</v>
       </c>
       <c r="AE36" s="94" t="n">
-        <v>-2.35</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="96" t="inlineStr">
+      <c r="A37" s="76" t="inlineStr">
         <is>
           <t>vn:RS3</t>
         </is>
       </c>
       <c r="B37" s="94" t="n">
-        <v>15.16</v>
+        <v>67.03</v>
       </c>
       <c r="C37" s="94" t="n">
         <v>31.47</v>
@@ -10448,79 +10446,79 @@
         <v>81.64</v>
       </c>
       <c r="G37" s="94" t="n">
-        <v>81.64</v>
+        <v>78.16</v>
       </c>
       <c r="H37" s="94" t="n">
-        <v>78.16</v>
+        <v>69.63</v>
       </c>
       <c r="I37" s="94" t="n">
-        <v>69.63</v>
+        <v>29.45</v>
       </c>
       <c r="J37" s="94" t="n">
-        <v>29.45</v>
+        <v>13.62</v>
       </c>
       <c r="K37" s="94" t="n">
-        <v>13.62</v>
+        <v>14.32</v>
       </c>
       <c r="L37" s="94" t="n">
-        <v>14.32</v>
+        <v>23.23</v>
       </c>
       <c r="M37" s="94" t="n">
-        <v>14.32</v>
+        <v>50.34</v>
       </c>
       <c r="N37" s="94" t="n">
-        <v>23.23</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="O37" s="94" t="n">
-        <v>50.34</v>
+        <v>65.09</v>
       </c>
       <c r="P37" s="94" t="n">
-        <v>77.23999999999999</v>
+        <v>86.66</v>
       </c>
       <c r="Q37" s="94" t="n">
-        <v>65.09</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="R37" s="94" t="n">
-        <v>86.66</v>
+        <v>88</v>
       </c>
       <c r="S37" s="94" t="n">
-        <v>86.66</v>
+        <v>77.98</v>
       </c>
       <c r="T37" s="94" t="n">
-        <v>90.48999999999999</v>
+        <v>59.82</v>
       </c>
       <c r="U37" s="94" t="n">
-        <v>88</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="V37" s="94" t="n">
-        <v>77.98</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="W37" s="94" t="n">
-        <v>59.82</v>
+        <v>68.98</v>
       </c>
       <c r="X37" s="94" t="n">
-        <v>77.68000000000001</v>
+        <v>60.96</v>
       </c>
       <c r="Y37" s="94" t="n">
-        <v>77.68000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Z37" s="94" t="n">
-        <v>76.68000000000001</v>
+        <v>20.58</v>
       </c>
       <c r="AA37" s="94" t="n">
-        <v>68.98</v>
+        <v>30.12</v>
       </c>
       <c r="AB37" s="94" t="n">
-        <v>60.96</v>
+        <v>12.08</v>
       </c>
       <c r="AC37" s="94" t="n">
-        <v>9.050000000000001</v>
+        <v>13.57</v>
       </c>
       <c r="AD37" s="94" t="n">
-        <v>20.58</v>
+        <v>28.44</v>
       </c>
       <c r="AE37" s="94" t="n">
-        <v>20.58</v>
+        <v>44.72</v>
       </c>
     </row>
     <row r="38">
@@ -10559,124 +10557,124 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="H38" s="91" t="inlineStr">
+      <c r="H38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I38" s="93" t="inlineStr">
+      <c r="N38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J38" s="93" t="inlineStr">
+      <c r="AC38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AD38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K38" s="93" t="inlineStr">
+      <c r="AE38" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="L38" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="M38" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N38" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="O38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -10687,7 +10685,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>1.33</v>
@@ -10702,79 +10700,79 @@
         <v>0.05</v>
       </c>
       <c r="G39" s="94" t="n">
-        <v>0.05</v>
+        <v>1.11</v>
       </c>
       <c r="H39" s="94" t="n">
-        <v>1.11</v>
+        <v>0.99</v>
       </c>
       <c r="I39" s="94" t="n">
-        <v>0.99</v>
+        <v>1.39</v>
       </c>
       <c r="J39" s="94" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="K39" s="94" t="n">
-        <v>1.44</v>
+        <v>2.21</v>
       </c>
       <c r="L39" s="94" t="n">
-        <v>2.21</v>
+        <v>2.67</v>
       </c>
       <c r="M39" s="94" t="n">
-        <v>2.21</v>
+        <v>5.39</v>
       </c>
       <c r="N39" s="94" t="n">
-        <v>2.67</v>
+        <v>5.39</v>
       </c>
       <c r="O39" s="94" t="n">
-        <v>5.39</v>
+        <v>5.38</v>
       </c>
       <c r="P39" s="94" t="n">
-        <v>5.39</v>
+        <v>6.9</v>
       </c>
       <c r="Q39" s="94" t="n">
-        <v>5.38</v>
+        <v>7.31</v>
       </c>
       <c r="R39" s="94" t="n">
-        <v>6.9</v>
+        <v>7.21</v>
       </c>
       <c r="S39" s="94" t="n">
-        <v>6.9</v>
+        <v>6.84</v>
       </c>
       <c r="T39" s="94" t="n">
-        <v>7.31</v>
+        <v>7.46</v>
       </c>
       <c r="U39" s="94" t="n">
-        <v>7.21</v>
+        <v>6.69</v>
       </c>
       <c r="V39" s="94" t="n">
-        <v>6.84</v>
+        <v>5.73</v>
       </c>
       <c r="W39" s="94" t="n">
-        <v>7.46</v>
+        <v>6.27</v>
       </c>
       <c r="X39" s="94" t="n">
-        <v>6.69</v>
+        <v>7.42</v>
       </c>
       <c r="Y39" s="94" t="n">
-        <v>6.69</v>
+        <v>7.48</v>
       </c>
       <c r="Z39" s="94" t="n">
-        <v>5.73</v>
+        <v>6.99</v>
       </c>
       <c r="AA39" s="94" t="n">
-        <v>6.27</v>
+        <v>7.27</v>
       </c>
       <c r="AB39" s="94" t="n">
-        <v>7.42</v>
+        <v>5.46</v>
       </c>
       <c r="AC39" s="94" t="n">
-        <v>7.48</v>
+        <v>6.4</v>
       </c>
       <c r="AD39" s="94" t="n">
-        <v>6.99</v>
+        <v>6.18</v>
       </c>
       <c r="AE39" s="94" t="n">
-        <v>6.99</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="40">
@@ -10784,7 +10782,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>9.859999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>9.630000000000001</v>
@@ -10799,79 +10797,79 @@
         <v>10.5</v>
       </c>
       <c r="G40" s="94" t="n">
-        <v>10.5</v>
+        <v>11.66</v>
       </c>
       <c r="H40" s="94" t="n">
-        <v>11.66</v>
+        <v>12.39</v>
       </c>
       <c r="I40" s="94" t="n">
-        <v>12.39</v>
+        <v>11.91</v>
       </c>
       <c r="J40" s="94" t="n">
-        <v>11.91</v>
+        <v>10.42</v>
       </c>
       <c r="K40" s="94" t="n">
-        <v>10.42</v>
+        <v>10.03</v>
       </c>
       <c r="L40" s="94" t="n">
-        <v>10.03</v>
+        <v>9.94</v>
       </c>
       <c r="M40" s="94" t="n">
-        <v>10.03</v>
+        <v>12.83</v>
       </c>
       <c r="N40" s="94" t="n">
-        <v>9.94</v>
+        <v>12.83</v>
       </c>
       <c r="O40" s="94" t="n">
-        <v>12.83</v>
+        <v>12.79</v>
       </c>
       <c r="P40" s="94" t="n">
-        <v>12.83</v>
+        <v>15.25</v>
       </c>
       <c r="Q40" s="94" t="n">
-        <v>12.79</v>
+        <v>15.64</v>
       </c>
       <c r="R40" s="94" t="n">
-        <v>15.25</v>
+        <v>15.29</v>
       </c>
       <c r="S40" s="94" t="n">
-        <v>15.25</v>
+        <v>14.9</v>
       </c>
       <c r="T40" s="94" t="n">
-        <v>15.64</v>
+        <v>14.75</v>
       </c>
       <c r="U40" s="94" t="n">
-        <v>15.29</v>
+        <v>14.79</v>
       </c>
       <c r="V40" s="94" t="n">
-        <v>14.9</v>
+        <v>13.96</v>
       </c>
       <c r="W40" s="94" t="n">
-        <v>14.75</v>
+        <v>14.46</v>
       </c>
       <c r="X40" s="94" t="n">
-        <v>14.79</v>
+        <v>14.07</v>
       </c>
       <c r="Y40" s="94" t="n">
-        <v>14.79</v>
+        <v>14.24</v>
       </c>
       <c r="Z40" s="94" t="n">
-        <v>13.96</v>
+        <v>14.96</v>
       </c>
       <c r="AA40" s="94" t="n">
-        <v>14.46</v>
+        <v>15.21</v>
       </c>
       <c r="AB40" s="94" t="n">
-        <v>14.07</v>
+        <v>12.06</v>
       </c>
       <c r="AC40" s="94" t="n">
-        <v>14.24</v>
+        <v>12.77</v>
       </c>
       <c r="AD40" s="94" t="n">
-        <v>14.96</v>
+        <v>11.58</v>
       </c>
       <c r="AE40" s="94" t="n">
-        <v>14.96</v>
+        <v>11.57</v>
       </c>
     </row>
     <row r="41">
@@ -10881,7 +10879,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>34.67</v>
+        <v>34.73</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>39.02</v>
@@ -10896,79 +10894,79 @@
         <v>35.77</v>
       </c>
       <c r="G41" s="94" t="n">
-        <v>35.77</v>
+        <v>37.56</v>
       </c>
       <c r="H41" s="94" t="n">
-        <v>37.56</v>
+        <v>35.74</v>
       </c>
       <c r="I41" s="94" t="n">
-        <v>35.74</v>
+        <v>36.86</v>
       </c>
       <c r="J41" s="94" t="n">
-        <v>36.86</v>
+        <v>29.96</v>
       </c>
       <c r="K41" s="94" t="n">
-        <v>29.96</v>
+        <v>33.56</v>
       </c>
       <c r="L41" s="94" t="n">
-        <v>33.56</v>
+        <v>38.91</v>
       </c>
       <c r="M41" s="94" t="n">
-        <v>33.56</v>
+        <v>56.68</v>
       </c>
       <c r="N41" s="94" t="n">
-        <v>38.91</v>
+        <v>56.68</v>
       </c>
       <c r="O41" s="94" t="n">
-        <v>56.68</v>
+        <v>57.12</v>
       </c>
       <c r="P41" s="94" t="n">
-        <v>56.68</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="Q41" s="94" t="n">
-        <v>57.12</v>
+        <v>83.77</v>
       </c>
       <c r="R41" s="94" t="n">
-        <v>78.04000000000001</v>
+        <v>80.52</v>
       </c>
       <c r="S41" s="94" t="n">
-        <v>78.04000000000001</v>
+        <v>79.08</v>
       </c>
       <c r="T41" s="94" t="n">
-        <v>83.77</v>
+        <v>79.38</v>
       </c>
       <c r="U41" s="94" t="n">
-        <v>80.52</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="V41" s="94" t="n">
-        <v>79.08</v>
+        <v>66.75</v>
       </c>
       <c r="W41" s="94" t="n">
-        <v>79.38</v>
+        <v>64.14</v>
       </c>
       <c r="X41" s="94" t="n">
-        <v>77.31999999999999</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="Y41" s="94" t="n">
-        <v>77.31999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="Z41" s="94" t="n">
-        <v>66.75</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="AA41" s="94" t="n">
-        <v>64.14</v>
+        <v>66.14</v>
       </c>
       <c r="AB41" s="94" t="n">
-        <v>66.76000000000001</v>
+        <v>50.55</v>
       </c>
       <c r="AC41" s="94" t="n">
-        <v>65.90000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="AD41" s="94" t="n">
-        <v>65.01000000000001</v>
+        <v>52.02</v>
       </c>
       <c r="AE41" s="94" t="n">
-        <v>65.01000000000001</v>
+        <v>46.05</v>
       </c>
     </row>
     <row r="42">
@@ -10977,154 +10975,154 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="93" t="inlineStr">
+      <c r="B42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C42" s="93" t="inlineStr">
+      <c r="D42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D42" s="93" t="inlineStr">
+      <c r="E42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E42" s="92" t="inlineStr">
+      <c r="H42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F42" s="92" t="inlineStr">
+      <c r="K42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G42" s="92" t="inlineStr">
+      <c r="Q42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H42" s="93" t="inlineStr">
+      <c r="R42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Z42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AB42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="J42" s="93" t="inlineStr">
+      <c r="AC42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L42" s="93" t="inlineStr">
+      <c r="AD42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M42" s="93" t="inlineStr">
+      <c r="AE42" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="N42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="O42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="P42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Q42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -11135,7 +11133,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>1.15</v>
+        <v>2.11</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>-0.29</v>
@@ -11150,79 +11148,79 @@
         <v>0.58</v>
       </c>
       <c r="G43" s="94" t="n">
-        <v>0.58</v>
+        <v>-0.59</v>
       </c>
       <c r="H43" s="94" t="n">
-        <v>-0.59</v>
+        <v>-0.14</v>
       </c>
       <c r="I43" s="94" t="n">
-        <v>-0.14</v>
+        <v>-0.77</v>
       </c>
       <c r="J43" s="94" t="n">
-        <v>-0.77</v>
+        <v>-0.74</v>
       </c>
       <c r="K43" s="94" t="n">
-        <v>-0.74</v>
+        <v>-2.37</v>
       </c>
       <c r="L43" s="94" t="n">
-        <v>-2.37</v>
+        <v>-1.96</v>
       </c>
       <c r="M43" s="94" t="n">
-        <v>-2.37</v>
+        <v>0.05</v>
       </c>
       <c r="N43" s="94" t="n">
-        <v>-1.96</v>
+        <v>0.87</v>
       </c>
       <c r="O43" s="94" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="P43" s="94" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q43" s="94" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R43" s="94" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="S43" s="94" t="n">
         <v>0.87</v>
       </c>
-      <c r="Q43" s="94" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="R43" s="94" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S43" s="94" t="n">
-        <v>1.51</v>
-      </c>
       <c r="T43" s="94" t="n">
-        <v>0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="U43" s="94" t="n">
-        <v>-0.87</v>
+        <v>0.28</v>
       </c>
       <c r="V43" s="94" t="n">
-        <v>0.87</v>
+        <v>1.12</v>
       </c>
       <c r="W43" s="94" t="n">
-        <v>-0.7</v>
+        <v>-2.16</v>
       </c>
       <c r="X43" s="94" t="n">
-        <v>0.28</v>
+        <v>-2.28</v>
       </c>
       <c r="Y43" s="94" t="n">
-        <v>0.28</v>
+        <v>-3.34</v>
       </c>
       <c r="Z43" s="94" t="n">
-        <v>1.12</v>
+        <v>-2.14</v>
       </c>
       <c r="AA43" s="94" t="n">
-        <v>-2.16</v>
+        <v>-3.08</v>
       </c>
       <c r="AB43" s="94" t="n">
-        <v>-2.28</v>
+        <v>-2.29</v>
       </c>
       <c r="AC43" s="94" t="n">
-        <v>-3.34</v>
+        <v>-2.9</v>
       </c>
       <c r="AD43" s="94" t="n">
-        <v>-2.14</v>
+        <v>-1.93</v>
       </c>
       <c r="AE43" s="94" t="n">
-        <v>-2.14</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="44">
@@ -11232,7 +11230,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>-5.08</v>
+        <v>-4.18</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>-6.17</v>
@@ -11247,79 +11245,79 @@
         <v>-5.47</v>
       </c>
       <c r="G44" s="94" t="n">
-        <v>-5.47</v>
+        <v>-6.8</v>
       </c>
       <c r="H44" s="94" t="n">
-        <v>-6.8</v>
+        <v>-6.73</v>
       </c>
       <c r="I44" s="94" t="n">
-        <v>-6.73</v>
+        <v>-6.46</v>
       </c>
       <c r="J44" s="94" t="n">
-        <v>-6.46</v>
+        <v>-5.56</v>
       </c>
       <c r="K44" s="94" t="n">
-        <v>-5.56</v>
+        <v>-6.01</v>
       </c>
       <c r="L44" s="94" t="n">
+        <v>-6.31</v>
+      </c>
+      <c r="M44" s="94" t="n">
+        <v>-4.48</v>
+      </c>
+      <c r="N44" s="94" t="n">
+        <v>-5.85</v>
+      </c>
+      <c r="O44" s="94" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="P44" s="94" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="Q44" s="94" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="R44" s="94" t="n">
         <v>-6.01</v>
       </c>
-      <c r="M44" s="94" t="n">
-        <v>-6.01</v>
-      </c>
-      <c r="N44" s="94" t="n">
-        <v>-6.31</v>
-      </c>
-      <c r="O44" s="94" t="n">
-        <v>-4.48</v>
-      </c>
-      <c r="P44" s="94" t="n">
-        <v>-5.85</v>
-      </c>
-      <c r="Q44" s="94" t="n">
-        <v>-4.68</v>
-      </c>
-      <c r="R44" s="94" t="n">
-        <v>-2.89</v>
-      </c>
       <c r="S44" s="94" t="n">
-        <v>-2.89</v>
+        <v>-6.35</v>
       </c>
       <c r="T44" s="94" t="n">
-        <v>-3.77</v>
+        <v>-6.86</v>
       </c>
       <c r="U44" s="94" t="n">
-        <v>-6.01</v>
+        <v>-7.99</v>
       </c>
       <c r="V44" s="94" t="n">
-        <v>-6.35</v>
+        <v>-6.6</v>
       </c>
       <c r="W44" s="94" t="n">
-        <v>-6.86</v>
+        <v>-8.43</v>
       </c>
       <c r="X44" s="94" t="n">
-        <v>-7.99</v>
+        <v>-8.75</v>
       </c>
       <c r="Y44" s="94" t="n">
-        <v>-7.99</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="Z44" s="94" t="n">
-        <v>-6.6</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="AA44" s="94" t="n">
-        <v>-8.43</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="AB44" s="94" t="n">
-        <v>-8.75</v>
+        <v>-9.26</v>
       </c>
       <c r="AC44" s="94" t="n">
-        <v>-9.210000000000001</v>
+        <v>-9.44</v>
       </c>
       <c r="AD44" s="94" t="n">
-        <v>-8.789999999999999</v>
+        <v>-9.02</v>
       </c>
       <c r="AE44" s="94" t="n">
-        <v>-8.789999999999999</v>
+        <v>-10.35</v>
       </c>
     </row>
     <row r="45">
@@ -11329,7 +11327,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>41.72</v>
+        <v>56.72</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>35.32</v>
@@ -11344,79 +11342,79 @@
         <v>54.29</v>
       </c>
       <c r="G45" s="94" t="n">
-        <v>54.29</v>
+        <v>46.1</v>
       </c>
       <c r="H45" s="94" t="n">
-        <v>46.1</v>
+        <v>49.74</v>
       </c>
       <c r="I45" s="94" t="n">
-        <v>49.74</v>
+        <v>42.08</v>
       </c>
       <c r="J45" s="94" t="n">
-        <v>42.08</v>
+        <v>50.81</v>
       </c>
       <c r="K45" s="94" t="n">
-        <v>50.81</v>
+        <v>45.03</v>
       </c>
       <c r="L45" s="94" t="n">
-        <v>45.03</v>
+        <v>33.57</v>
       </c>
       <c r="M45" s="94" t="n">
-        <v>45.03</v>
+        <v>45.48</v>
       </c>
       <c r="N45" s="94" t="n">
-        <v>33.57</v>
+        <v>44.93</v>
       </c>
       <c r="O45" s="94" t="n">
-        <v>45.48</v>
+        <v>52.35</v>
       </c>
       <c r="P45" s="94" t="n">
-        <v>44.93</v>
+        <v>78.61</v>
       </c>
       <c r="Q45" s="94" t="n">
-        <v>52.35</v>
+        <v>75.48</v>
       </c>
       <c r="R45" s="94" t="n">
-        <v>78.61</v>
+        <v>57.98</v>
       </c>
       <c r="S45" s="94" t="n">
-        <v>78.61</v>
+        <v>66.2</v>
       </c>
       <c r="T45" s="94" t="n">
-        <v>75.48</v>
+        <v>52.83</v>
       </c>
       <c r="U45" s="94" t="n">
-        <v>57.98</v>
+        <v>51.58</v>
       </c>
       <c r="V45" s="94" t="n">
-        <v>66.2</v>
+        <v>74.97</v>
       </c>
       <c r="W45" s="94" t="n">
-        <v>52.83</v>
+        <v>45.92</v>
       </c>
       <c r="X45" s="94" t="n">
-        <v>51.58</v>
+        <v>59.76</v>
       </c>
       <c r="Y45" s="94" t="n">
-        <v>51.58</v>
+        <v>48.71</v>
       </c>
       <c r="Z45" s="94" t="n">
-        <v>74.97</v>
+        <v>53.61</v>
       </c>
       <c r="AA45" s="94" t="n">
-        <v>45.92</v>
+        <v>45.19</v>
       </c>
       <c r="AB45" s="94" t="n">
-        <v>59.76</v>
+        <v>32.83</v>
       </c>
       <c r="AC45" s="94" t="n">
-        <v>48.71</v>
+        <v>34.58</v>
       </c>
       <c r="AD45" s="94" t="n">
-        <v>53.61</v>
+        <v>37.2</v>
       </c>
       <c r="AE45" s="94" t="n">
-        <v>53.61</v>
+        <v>16.31</v>
       </c>
     </row>
     <row r="46">
@@ -11425,154 +11423,154 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="91" t="inlineStr">
+      <c r="B46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C46" s="91" t="inlineStr">
+      <c r="D46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="E46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D46" s="92" t="inlineStr">
+      <c r="H46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E46" s="92" t="inlineStr">
+      <c r="I46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F46" s="92" t="inlineStr">
+      <c r="Q46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G46" s="92" t="inlineStr">
+      <c r="R46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H46" s="91" t="inlineStr">
+      <c r="T46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I46" s="92" t="inlineStr">
+      <c r="V46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="K46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="L46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="M46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N46" s="93" t="inlineStr">
+      <c r="W46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="AC46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11581,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>5.69</v>
+        <v>7.02</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>5.69</v>
@@ -11598,79 +11596,79 @@
         <v>6.61</v>
       </c>
       <c r="G47" s="94" t="n">
-        <v>6.61</v>
+        <v>4.66</v>
       </c>
       <c r="H47" s="94" t="n">
-        <v>4.66</v>
+        <v>4.43</v>
       </c>
       <c r="I47" s="94" t="n">
-        <v>4.43</v>
+        <v>2.96</v>
       </c>
       <c r="J47" s="94" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K47" s="94" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="L47" s="94" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="M47" s="94" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="N47" s="94" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="O47" s="94" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="P47" s="94" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Q47" s="94" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="R47" s="94" t="n">
         <v>2.96</v>
       </c>
-      <c r="K47" s="94" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="L47" s="94" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="M47" s="94" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="N47" s="94" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O47" s="94" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="P47" s="94" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="Q47" s="94" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="R47" s="94" t="n">
-        <v>5.4</v>
-      </c>
       <c r="S47" s="94" t="n">
-        <v>5.4</v>
+        <v>4.58</v>
       </c>
       <c r="T47" s="94" t="n">
-        <v>4.27</v>
+        <v>3.04</v>
       </c>
       <c r="U47" s="94" t="n">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="V47" s="94" t="n">
-        <v>4.58</v>
+        <v>4.35</v>
       </c>
       <c r="W47" s="94" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="X47" s="94" t="n">
-        <v>2.66</v>
+        <v>3.02</v>
       </c>
       <c r="Y47" s="94" t="n">
-        <v>2.66</v>
+        <v>1.68</v>
       </c>
       <c r="Z47" s="94" t="n">
-        <v>4.35</v>
+        <v>2.95</v>
       </c>
       <c r="AA47" s="94" t="n">
-        <v>3.06</v>
+        <v>1.45</v>
       </c>
       <c r="AB47" s="94" t="n">
-        <v>3.02</v>
+        <v>1.45</v>
       </c>
       <c r="AC47" s="94" t="n">
-        <v>1.68</v>
+        <v>0.74</v>
       </c>
       <c r="AD47" s="94" t="n">
-        <v>2.95</v>
+        <v>2.08</v>
       </c>
       <c r="AE47" s="94" t="n">
-        <v>2.95</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="48">
@@ -11680,7 +11678,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>8.369999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>8.369999999999999</v>
@@ -11695,79 +11693,79 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G48" s="94" t="n">
-        <v>8.130000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="H48" s="94" t="n">
-        <v>6.2</v>
+        <v>6.16</v>
       </c>
       <c r="I48" s="94" t="n">
-        <v>6.16</v>
+        <v>6.75</v>
       </c>
       <c r="J48" s="94" t="n">
-        <v>6.75</v>
+        <v>7.71</v>
       </c>
       <c r="K48" s="94" t="n">
-        <v>7.71</v>
+        <v>7.2</v>
       </c>
       <c r="L48" s="94" t="n">
-        <v>7.2</v>
+        <v>7.01</v>
       </c>
       <c r="M48" s="94" t="n">
-        <v>7.2</v>
+        <v>7.87</v>
       </c>
       <c r="N48" s="94" t="n">
-        <v>7.01</v>
+        <v>6.58</v>
       </c>
       <c r="O48" s="94" t="n">
-        <v>7.87</v>
+        <v>7.78</v>
       </c>
       <c r="P48" s="94" t="n">
-        <v>6.58</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="Q48" s="94" t="n">
-        <v>7.78</v>
+        <v>6.31</v>
       </c>
       <c r="R48" s="94" t="n">
-        <v>8.460000000000001</v>
+        <v>4.66</v>
       </c>
       <c r="S48" s="94" t="n">
-        <v>8.460000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="T48" s="94" t="n">
-        <v>6.31</v>
+        <v>3.7</v>
       </c>
       <c r="U48" s="94" t="n">
-        <v>4.66</v>
+        <v>1.72</v>
       </c>
       <c r="V48" s="94" t="n">
-        <v>3.7</v>
+        <v>3.46</v>
       </c>
       <c r="W48" s="94" t="n">
-        <v>3.7</v>
+        <v>2.34</v>
       </c>
       <c r="X48" s="94" t="n">
-        <v>1.72</v>
+        <v>1.26</v>
       </c>
       <c r="Y48" s="94" t="n">
-        <v>1.72</v>
+        <v>0.84</v>
       </c>
       <c r="Z48" s="94" t="n">
-        <v>3.46</v>
+        <v>1.71</v>
       </c>
       <c r="AA48" s="94" t="n">
-        <v>2.34</v>
+        <v>1.41</v>
       </c>
       <c r="AB48" s="94" t="n">
-        <v>1.26</v>
+        <v>0.68</v>
       </c>
       <c r="AC48" s="94" t="n">
-        <v>0.84</v>
+        <v>0.48</v>
       </c>
       <c r="AD48" s="94" t="n">
-        <v>1.71</v>
+        <v>2.38</v>
       </c>
       <c r="AE48" s="94" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="49">
@@ -11777,7 +11775,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>64.68000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>64.68000000000001</v>
@@ -11792,85 +11790,85 @@
         <v>68.01000000000001</v>
       </c>
       <c r="G49" s="94" t="n">
-        <v>68.01000000000001</v>
+        <v>58.26</v>
       </c>
       <c r="H49" s="94" t="n">
-        <v>58.26</v>
+        <v>62.55</v>
       </c>
       <c r="I49" s="94" t="n">
-        <v>62.55</v>
+        <v>49.18</v>
       </c>
       <c r="J49" s="94" t="n">
-        <v>49.18</v>
+        <v>52.29</v>
       </c>
       <c r="K49" s="94" t="n">
+        <v>53.55</v>
+      </c>
+      <c r="L49" s="94" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="M49" s="94" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="N49" s="94" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="O49" s="94" t="n">
+        <v>67.34999999999999</v>
+      </c>
+      <c r="P49" s="94" t="n">
+        <v>78.38</v>
+      </c>
+      <c r="Q49" s="94" t="n">
+        <v>72.42</v>
+      </c>
+      <c r="R49" s="94" t="n">
+        <v>59.91</v>
+      </c>
+      <c r="S49" s="94" t="n">
+        <v>66</v>
+      </c>
+      <c r="T49" s="94" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="U49" s="94" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="V49" s="94" t="n">
+        <v>75.06999999999999</v>
+      </c>
+      <c r="W49" s="94" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="X49" s="94" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="Y49" s="94" t="n">
+        <v>57.16</v>
+      </c>
+      <c r="Z49" s="94" t="n">
+        <v>62.56</v>
+      </c>
+      <c r="AA49" s="94" t="n">
         <v>52.29</v>
       </c>
-      <c r="L49" s="94" t="n">
-        <v>53.55</v>
-      </c>
-      <c r="M49" s="94" t="n">
-        <v>53.55</v>
-      </c>
-      <c r="N49" s="94" t="n">
-        <v>46.86</v>
-      </c>
-      <c r="O49" s="94" t="n">
-        <v>56.45</v>
-      </c>
-      <c r="P49" s="94" t="n">
-        <v>59.76</v>
-      </c>
-      <c r="Q49" s="94" t="n">
-        <v>67.34999999999999</v>
-      </c>
-      <c r="R49" s="94" t="n">
-        <v>78.38</v>
-      </c>
-      <c r="S49" s="94" t="n">
-        <v>78.38</v>
-      </c>
-      <c r="T49" s="94" t="n">
-        <v>72.42</v>
-      </c>
-      <c r="U49" s="94" t="n">
-        <v>59.91</v>
-      </c>
-      <c r="V49" s="94" t="n">
-        <v>66</v>
-      </c>
-      <c r="W49" s="94" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="X49" s="94" t="n">
-        <v>52.95</v>
-      </c>
-      <c r="Y49" s="94" t="n">
-        <v>52.95</v>
-      </c>
-      <c r="Z49" s="94" t="n">
-        <v>75.06999999999999</v>
-      </c>
-      <c r="AA49" s="94" t="n">
-        <v>61.14</v>
-      </c>
       <c r="AB49" s="94" t="n">
-        <v>62.6</v>
+        <v>37.42</v>
       </c>
       <c r="AC49" s="94" t="n">
-        <v>57.16</v>
+        <v>31.32</v>
       </c>
       <c r="AD49" s="94" t="n">
-        <v>62.56</v>
+        <v>40.38</v>
       </c>
       <c r="AE49" s="94" t="n">
-        <v>62.56</v>
+        <v>26.19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：vn:RS3:15.16&lt;=25;sensex:RS10:34.67&lt;=39</t>
+          <t>今日买报：sensex:RS10:34.73&lt;=39</t>
         </is>
       </c>
     </row>

--- a/report_2410.xlsx
+++ b/report_2410.xlsx
@@ -1060,9 +1060,9 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.26</v>
+        <v>-0.3</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.06</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>-0.1</v>
+        <v>-0.14</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.06</v>
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="B32" s="85" t="n">
-        <v>0</v>
+        <v>-45921</v>
       </c>
       <c r="C32" s="85" t="n">
         <v>-30947</v>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="B34" s="85" t="n">
-        <v>0</v>
+        <v>-30986</v>
       </c>
       <c r="C34" s="85" t="n">
         <v>-28036</v>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="B37" s="85" t="n">
-        <v>0</v>
+        <v>168313</v>
       </c>
       <c r="C37" s="85" t="n">
         <v>141939</v>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="B38" s="85" t="n">
-        <v>0</v>
+        <v>71036</v>
       </c>
       <c r="C38" s="85" t="n">
         <v>62739</v>
@@ -6367,127 +6367,127 @@
       </c>
       <c r="G1" s="77" t="inlineStr">
         <is>
-          <t>241013</t>
+          <t>241011</t>
         </is>
       </c>
       <c r="H1" s="77" t="inlineStr">
         <is>
-          <t>241011</t>
+          <t>241010</t>
         </is>
       </c>
       <c r="I1" s="77" t="inlineStr">
         <is>
-          <t>241010</t>
+          <t>241009</t>
         </is>
       </c>
       <c r="J1" s="77" t="inlineStr">
         <is>
-          <t>241009</t>
+          <t>241008</t>
         </is>
       </c>
       <c r="K1" s="77" t="inlineStr">
         <is>
-          <t>241008</t>
+          <t>241007</t>
         </is>
       </c>
       <c r="L1" s="77" t="inlineStr">
         <is>
-          <t>241007</t>
+          <t>241004</t>
         </is>
       </c>
       <c r="M1" s="77" t="inlineStr">
         <is>
-          <t>241006</t>
+          <t>241003</t>
         </is>
       </c>
       <c r="N1" s="77" t="inlineStr">
         <is>
-          <t>241004</t>
+          <t>241002</t>
         </is>
       </c>
       <c r="O1" s="77" t="inlineStr">
         <is>
-          <t>241003</t>
+          <t>241001</t>
         </is>
       </c>
       <c r="P1" s="77" t="inlineStr">
         <is>
-          <t>241002</t>
+          <t>240930</t>
         </is>
       </c>
       <c r="Q1" s="77" t="inlineStr">
         <is>
-          <t>241001</t>
+          <t>240927</t>
         </is>
       </c>
       <c r="R1" s="77" t="inlineStr">
         <is>
-          <t>240930</t>
+          <t>240926</t>
         </is>
       </c>
       <c r="S1" s="77" t="inlineStr">
         <is>
-          <t>240929</t>
+          <t>240925</t>
         </is>
       </c>
       <c r="T1" s="77" t="inlineStr">
         <is>
-          <t>240927</t>
+          <t>240924</t>
         </is>
       </c>
       <c r="U1" s="77" t="inlineStr">
         <is>
-          <t>240926</t>
+          <t>240923</t>
         </is>
       </c>
       <c r="V1" s="77" t="inlineStr">
         <is>
-          <t>240925</t>
+          <t>240920</t>
         </is>
       </c>
       <c r="W1" s="77" t="inlineStr">
         <is>
-          <t>240924</t>
+          <t>240919</t>
         </is>
       </c>
       <c r="X1" s="77" t="inlineStr">
         <is>
-          <t>240923</t>
+          <t>240918</t>
         </is>
       </c>
       <c r="Y1" s="77" t="inlineStr">
         <is>
-          <t>240922</t>
+          <t>240917</t>
         </is>
       </c>
       <c r="Z1" s="77" t="inlineStr">
         <is>
-          <t>240920</t>
+          <t>240916</t>
         </is>
       </c>
       <c r="AA1" s="77" t="inlineStr">
         <is>
-          <t>240919</t>
+          <t>240913</t>
         </is>
       </c>
       <c r="AB1" s="77" t="inlineStr">
         <is>
-          <t>240918</t>
+          <t>240912</t>
         </is>
       </c>
       <c r="AC1" s="77" t="inlineStr">
         <is>
-          <t>240917</t>
+          <t>240911</t>
         </is>
       </c>
       <c r="AD1" s="77" t="inlineStr">
         <is>
-          <t>240916</t>
+          <t>240910</t>
         </is>
       </c>
       <c r="AE1" s="77" t="inlineStr">
         <is>
-          <t>240915</t>
+          <t>240909</t>
         </is>
       </c>
     </row>
@@ -6537,74 +6537,74 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="J2" s="91" t="inlineStr">
+      <c r="J2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="V2" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W2" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="X2" s="91" t="inlineStr">
@@ -6612,131 +6612,137 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="Y2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC2" s="91" t="n">
-        <v/>
-      </c>
-      <c r="AD2" s="91" t="n">
-        <v/>
-      </c>
-      <c r="AE2" s="91" t="n">
-        <v/>
+      <c r="Y2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="93" t="inlineStr">
+      <c r="A3" s="94" t="inlineStr">
         <is>
           <t>sh:RNG60</t>
         </is>
       </c>
-      <c r="B3" s="94" t="n">
+      <c r="B3" s="95" t="n">
         <v>10.08</v>
       </c>
-      <c r="C3" s="94" t="n">
+      <c r="C3" s="95" t="n">
         <v>6.49</v>
       </c>
-      <c r="D3" s="94" t="n">
+      <c r="D3" s="95" t="n">
         <v>7.7</v>
       </c>
-      <c r="E3" s="94" t="n">
+      <c r="E3" s="95" t="n">
         <v>7.74</v>
       </c>
-      <c r="F3" s="94" t="n">
+      <c r="F3" s="95" t="n">
         <v>10.57</v>
       </c>
-      <c r="G3" s="94" t="n">
+      <c r="G3" s="95" t="n">
         <v>9.470000000000001</v>
       </c>
-      <c r="H3" s="94" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="I3" s="94" t="n">
+      <c r="H3" s="95" t="n">
         <v>11.58</v>
       </c>
-      <c r="J3" s="94" t="n">
+      <c r="I3" s="95" t="n">
         <v>11.51</v>
       </c>
-      <c r="K3" s="94" t="n">
+      <c r="J3" s="95" t="n">
         <v>18.3</v>
       </c>
-      <c r="L3" s="94" t="n">
+      <c r="K3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="M3" s="94" t="n">
+      <c r="L3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="N3" s="94" t="n">
+      <c r="M3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="O3" s="94" t="n">
+      <c r="N3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="P3" s="94" t="n">
+      <c r="O3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="Q3" s="94" t="n">
+      <c r="P3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="R3" s="94" t="n">
-        <v>12.81</v>
-      </c>
-      <c r="S3" s="94" t="n">
+      <c r="Q3" s="95" t="n">
         <v>3.53</v>
       </c>
-      <c r="T3" s="94" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="U3" s="94" t="n">
+      <c r="R3" s="95" t="n">
         <v>0.13</v>
       </c>
-      <c r="V3" s="94" t="n">
+      <c r="S3" s="95" t="n">
         <v>-3.29</v>
       </c>
-      <c r="W3" s="94" t="n">
+      <c r="T3" s="95" t="n">
         <v>-3.51</v>
       </c>
-      <c r="X3" s="94" t="n">
+      <c r="U3" s="95" t="n">
         <v>-6.68</v>
       </c>
-      <c r="Y3" s="94" t="n">
+      <c r="V3" s="95" t="n">
         <v>-7.93</v>
       </c>
-      <c r="Z3" s="94" t="n">
-        <v>-7.93</v>
-      </c>
-      <c r="AA3" s="94" t="n">
+      <c r="W3" s="95" t="n">
         <v>-7.25</v>
       </c>
-      <c r="AB3" s="94" t="n">
+      <c r="X3" s="95" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="AC3" s="94" t="n">
-        <v/>
-      </c>
-      <c r="AD3" s="94" t="n">
-        <v/>
-      </c>
-      <c r="AE3" s="94" t="n">
-        <v/>
+      <c r="Y3" s="95" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="Z3" s="95" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="AA3" s="95" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="AB3" s="95" t="n">
+        <v>-9.59</v>
+      </c>
+      <c r="AC3" s="95" t="n">
+        <v>-9.82</v>
+      </c>
+      <c r="AD3" s="95" t="n">
+        <v>-9.44</v>
+      </c>
+      <c r="AE3" s="95" t="n">
+        <v>-9.26</v>
       </c>
     </row>
     <row r="4">
@@ -6745,95 +6751,95 @@
           <t>sh:RNG120</t>
         </is>
       </c>
-      <c r="B4" s="94" t="n">
+      <c r="B4" s="95" t="n">
         <v>6.09</v>
       </c>
-      <c r="C4" s="94" t="n">
+      <c r="C4" s="95" t="n">
         <v>3.19</v>
       </c>
-      <c r="D4" s="94" t="n">
+      <c r="D4" s="95" t="n">
         <v>6.51</v>
       </c>
-      <c r="E4" s="94" t="n">
+      <c r="E4" s="95" t="n">
         <v>4.71</v>
       </c>
-      <c r="F4" s="94" t="n">
+      <c r="F4" s="95" t="n">
         <v>8.77</v>
       </c>
-      <c r="G4" s="94" t="n">
+      <c r="G4" s="95" t="n">
         <v>6.05</v>
       </c>
-      <c r="H4" s="94" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="I4" s="94" t="n">
+      <c r="H4" s="95" t="n">
         <v>9.07</v>
       </c>
-      <c r="J4" s="94" t="n">
+      <c r="I4" s="95" t="n">
         <v>6.9</v>
       </c>
-      <c r="K4" s="94" t="n">
+      <c r="J4" s="95" t="n">
         <v>14.53</v>
       </c>
-      <c r="L4" s="94" t="n">
+      <c r="K4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="M4" s="94" t="n">
+      <c r="L4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="N4" s="94" t="n">
+      <c r="M4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="O4" s="94" t="n">
+      <c r="N4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="P4" s="94" t="n">
+      <c r="O4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="Q4" s="94" t="n">
+      <c r="P4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="R4" s="94" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="S4" s="94" t="n">
+      <c r="Q4" s="95" t="n">
         <v>0.41</v>
       </c>
-      <c r="T4" s="94" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="U4" s="94" t="n">
+      <c r="R4" s="95" t="n">
         <v>-2.48</v>
       </c>
-      <c r="V4" s="94" t="n">
+      <c r="S4" s="95" t="n">
         <v>-4.76</v>
       </c>
-      <c r="W4" s="94" t="n">
+      <c r="T4" s="95" t="n">
         <v>-4.9</v>
       </c>
-      <c r="X4" s="94" t="n">
+      <c r="U4" s="95" t="n">
         <v>-8.16</v>
       </c>
-      <c r="Y4" s="94" t="n">
+      <c r="V4" s="95" t="n">
         <v>-9.720000000000001</v>
       </c>
-      <c r="Z4" s="94" t="n">
-        <v>-9.720000000000001</v>
-      </c>
-      <c r="AA4" s="94" t="n">
+      <c r="W4" s="95" t="n">
         <v>-9.59</v>
       </c>
-      <c r="AB4" s="94" t="n">
+      <c r="X4" s="95" t="n">
         <v>-10.85</v>
       </c>
-      <c r="AC4" s="94" t="n">
-        <v/>
-      </c>
-      <c r="AD4" s="94" t="n">
-        <v/>
-      </c>
-      <c r="AE4" s="94" t="n">
-        <v/>
+      <c r="Y4" s="95" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="Z4" s="95" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="AA4" s="95" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="AB4" s="95" t="n">
+        <v>-11.77</v>
+      </c>
+      <c r="AC4" s="95" t="n">
+        <v>-11.13</v>
+      </c>
+      <c r="AD4" s="95" t="n">
+        <v>-11.05</v>
+      </c>
+      <c r="AE4" s="95" t="n">
+        <v>-10.42</v>
       </c>
     </row>
     <row r="5">
@@ -6842,95 +6848,95 @@
           <t>sh:RS3</t>
         </is>
       </c>
-      <c r="B5" s="94" t="n">
+      <c r="B5" s="95" t="n">
         <v>63.75</v>
       </c>
-      <c r="C5" s="94" t="n">
+      <c r="C5" s="95" t="n">
         <v>32.04</v>
       </c>
-      <c r="D5" s="94" t="n">
+      <c r="D5" s="95" t="n">
         <v>40.69</v>
       </c>
-      <c r="E5" s="94" t="n">
+      <c r="E5" s="95" t="n">
         <v>40.15</v>
       </c>
-      <c r="F5" s="94" t="n">
+      <c r="F5" s="95" t="n">
         <v>57.29</v>
       </c>
-      <c r="G5" s="94" t="n">
+      <c r="G5" s="95" t="n">
         <v>44.67</v>
       </c>
-      <c r="H5" s="94" t="n">
-        <v>44.67</v>
-      </c>
-      <c r="I5" s="94" t="n">
+      <c r="H5" s="95" t="n">
         <v>59.48</v>
       </c>
-      <c r="J5" s="94" t="n">
+      <c r="I5" s="95" t="n">
         <v>54.31</v>
       </c>
-      <c r="K5" s="94" t="n">
+      <c r="J5" s="95" t="n">
         <v>99.84</v>
       </c>
-      <c r="L5" s="94" t="n">
+      <c r="K5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="M5" s="94" t="n">
+      <c r="L5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="N5" s="94" t="n">
+      <c r="M5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="O5" s="94" t="n">
+      <c r="N5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="P5" s="94" t="n">
+      <c r="O5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="Q5" s="94" t="n">
+      <c r="P5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="R5" s="94" t="n">
-        <v>99.75</v>
-      </c>
-      <c r="S5" s="94" t="n">
+      <c r="Q5" s="95" t="n">
         <v>99.31</v>
       </c>
-      <c r="T5" s="94" t="n">
-        <v>99.31</v>
-      </c>
-      <c r="U5" s="94" t="n">
+      <c r="R5" s="95" t="n">
         <v>98.83</v>
       </c>
-      <c r="V5" s="94" t="n">
+      <c r="S5" s="95" t="n">
         <v>97.34999999999999</v>
       </c>
-      <c r="W5" s="94" t="n">
+      <c r="T5" s="95" t="n">
         <v>96.38</v>
       </c>
-      <c r="X5" s="94" t="n">
+      <c r="U5" s="95" t="n">
         <v>77.51000000000001</v>
       </c>
-      <c r="Y5" s="94" t="n">
+      <c r="V5" s="95" t="n">
         <v>64.38</v>
       </c>
-      <c r="Z5" s="94" t="n">
-        <v>64.38</v>
-      </c>
-      <c r="AA5" s="94" t="n">
+      <c r="W5" s="95" t="n">
         <v>63.45</v>
       </c>
-      <c r="AB5" s="94" t="n">
+      <c r="X5" s="95" t="n">
         <v>37.85</v>
       </c>
-      <c r="AC5" s="94" t="n">
-        <v/>
-      </c>
-      <c r="AD5" s="94" t="n">
-        <v/>
-      </c>
-      <c r="AE5" s="94" t="n">
-        <v/>
+      <c r="Y5" s="95" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="Z5" s="95" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AA5" s="95" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AB5" s="95" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="AC5" s="95" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="AD5" s="95" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="AE5" s="95" t="n">
+        <v>5.95</v>
       </c>
     </row>
     <row r="6">
@@ -6974,82 +6980,82 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="I6" s="91" t="inlineStr">
+      <c r="I6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="V6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X6" s="95" t="inlineStr">
+      <c r="W6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -7069,310 +7075,316 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="AB6" s="95" t="inlineStr">
+      <c r="AB6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AC6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AD6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AE6" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC6" s="91" t="n">
-        <v/>
-      </c>
-      <c r="AD6" s="91" t="n">
-        <v/>
-      </c>
-      <c r="AE6" s="91" t="n">
-        <v/>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="93" t="inlineStr">
+      <c r="A7" s="94" t="inlineStr">
         <is>
           <t>kc:RNG60</t>
         </is>
       </c>
-      <c r="B7" s="94" t="n">
+      <c r="B7" s="95" t="n">
         <v>34.25</v>
       </c>
-      <c r="C7" s="94" t="n">
+      <c r="C7" s="95" t="n">
         <v>20.09</v>
       </c>
-      <c r="D7" s="94" t="n">
+      <c r="D7" s="95" t="n">
         <v>22.33</v>
       </c>
-      <c r="E7" s="94" t="n">
+      <c r="E7" s="95" t="n">
         <v>25.12</v>
       </c>
-      <c r="F7" s="94" t="n">
+      <c r="F7" s="95" t="n">
         <v>28.96</v>
       </c>
-      <c r="G7" s="94" t="n">
+      <c r="G7" s="95" t="n">
         <v>26.54</v>
       </c>
-      <c r="H7" s="94" t="n">
-        <v>26.54</v>
-      </c>
-      <c r="I7" s="94" t="n">
+      <c r="H7" s="95" t="n">
         <v>34.41</v>
       </c>
-      <c r="J7" s="94" t="n">
+      <c r="I7" s="95" t="n">
         <v>44.1</v>
       </c>
-      <c r="K7" s="94" t="n">
+      <c r="J7" s="95" t="n">
         <v>46.52</v>
       </c>
-      <c r="L7" s="94" t="n">
+      <c r="K7" s="95" t="n">
         <v>26.36</v>
       </c>
-      <c r="M7" s="94" t="n">
+      <c r="L7" s="95" t="n">
         <v>26.36</v>
       </c>
-      <c r="N7" s="94" t="n">
+      <c r="M7" s="95" t="n">
         <v>26.36</v>
       </c>
-      <c r="O7" s="94" t="n">
+      <c r="N7" s="95" t="n">
         <v>26.36</v>
       </c>
-      <c r="P7" s="94" t="n">
+      <c r="O7" s="95" t="n">
         <v>26.36</v>
       </c>
-      <c r="Q7" s="94" t="n">
+      <c r="P7" s="95" t="n">
         <v>26.36</v>
       </c>
-      <c r="R7" s="94" t="n">
-        <v>26.36</v>
-      </c>
-      <c r="S7" s="94" t="n">
+      <c r="Q7" s="95" t="n">
         <v>5.45</v>
       </c>
-      <c r="T7" s="94" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="U7" s="94" t="n">
+      <c r="R7" s="95" t="n">
         <v>-0.85</v>
       </c>
-      <c r="V7" s="94" t="n">
+      <c r="S7" s="95" t="n">
         <v>-5.96</v>
       </c>
-      <c r="W7" s="94" t="n">
+      <c r="T7" s="95" t="n">
         <v>-6.32</v>
       </c>
-      <c r="X7" s="94" t="n">
+      <c r="U7" s="95" t="n">
         <v>-10.11</v>
       </c>
-      <c r="Y7" s="94" t="n">
+      <c r="V7" s="95" t="n">
         <v>-11.14</v>
       </c>
-      <c r="Z7" s="94" t="n">
-        <v>-11.14</v>
-      </c>
-      <c r="AA7" s="94" t="n">
+      <c r="W7" s="95" t="n">
         <v>-9.23</v>
       </c>
-      <c r="AB7" s="94" t="n">
+      <c r="X7" s="95" t="n">
         <v>-12.41</v>
       </c>
-      <c r="AC7" s="94" t="n">
-        <v/>
-      </c>
-      <c r="AD7" s="94" t="n">
-        <v/>
-      </c>
-      <c r="AE7" s="94" t="n">
-        <v/>
+      <c r="Y7" s="95" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="Z7" s="95" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="AA7" s="95" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="AB7" s="95" t="n">
+        <v>-12.75</v>
+      </c>
+      <c r="AC7" s="95" t="n">
+        <v>-11.62</v>
+      </c>
+      <c r="AD7" s="95" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="AE7" s="95" t="n">
+        <v>-13.49</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="93" t="inlineStr">
+      <c r="A8" s="94" t="inlineStr">
         <is>
           <t>kc:RNG120</t>
         </is>
       </c>
-      <c r="B8" s="94" t="n">
+      <c r="B8" s="95" t="n">
         <v>31.24</v>
       </c>
-      <c r="C8" s="94" t="n">
+      <c r="C8" s="95" t="n">
         <v>17.07</v>
       </c>
-      <c r="D8" s="94" t="n">
+      <c r="D8" s="95" t="n">
         <v>19.44</v>
       </c>
-      <c r="E8" s="94" t="n">
+      <c r="E8" s="95" t="n">
         <v>19.7</v>
       </c>
-      <c r="F8" s="94" t="n">
+      <c r="F8" s="95" t="n">
         <v>25.4</v>
       </c>
-      <c r="G8" s="94" t="n">
+      <c r="G8" s="95" t="n">
         <v>21.69</v>
       </c>
-      <c r="H8" s="94" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="I8" s="94" t="n">
+      <c r="H8" s="95" t="n">
         <v>29.69</v>
       </c>
-      <c r="J8" s="94" t="n">
+      <c r="I8" s="95" t="n">
         <v>33.11</v>
       </c>
-      <c r="K8" s="94" t="n">
+      <c r="J8" s="95" t="n">
         <v>38.25</v>
       </c>
-      <c r="L8" s="94" t="n">
+      <c r="K8" s="95" t="n">
         <v>15.28</v>
       </c>
-      <c r="M8" s="94" t="n">
+      <c r="L8" s="95" t="n">
         <v>15.28</v>
       </c>
-      <c r="N8" s="94" t="n">
+      <c r="M8" s="95" t="n">
         <v>15.28</v>
       </c>
-      <c r="O8" s="94" t="n">
+      <c r="N8" s="95" t="n">
         <v>15.28</v>
       </c>
-      <c r="P8" s="94" t="n">
+      <c r="O8" s="95" t="n">
         <v>15.28</v>
       </c>
-      <c r="Q8" s="94" t="n">
+      <c r="P8" s="95" t="n">
         <v>15.28</v>
       </c>
-      <c r="R8" s="94" t="n">
-        <v>15.28</v>
-      </c>
-      <c r="S8" s="94" t="n">
+      <c r="Q8" s="95" t="n">
         <v>-3.74</v>
       </c>
-      <c r="T8" s="94" t="n">
-        <v>-3.74</v>
-      </c>
-      <c r="U8" s="94" t="n">
+      <c r="R8" s="95" t="n">
         <v>-10.62</v>
       </c>
-      <c r="V8" s="94" t="n">
+      <c r="S8" s="95" t="n">
         <v>-12.51</v>
       </c>
-      <c r="W8" s="94" t="n">
+      <c r="T8" s="95" t="n">
         <v>-12.61</v>
       </c>
-      <c r="X8" s="94" t="n">
+      <c r="U8" s="95" t="n">
         <v>-14.58</v>
       </c>
-      <c r="Y8" s="94" t="n">
+      <c r="V8" s="95" t="n">
         <v>-16.03</v>
       </c>
-      <c r="Z8" s="94" t="n">
-        <v>-16.03</v>
-      </c>
-      <c r="AA8" s="94" t="n">
+      <c r="W8" s="95" t="n">
         <v>-16.65</v>
       </c>
-      <c r="AB8" s="94" t="n">
+      <c r="X8" s="95" t="n">
         <v>-18.48</v>
       </c>
-      <c r="AC8" s="94" t="n">
-        <v/>
-      </c>
-      <c r="AD8" s="94" t="n">
-        <v/>
-      </c>
-      <c r="AE8" s="94" t="n">
-        <v/>
+      <c r="Y8" s="95" t="n">
+        <v>-18.74</v>
+      </c>
+      <c r="Z8" s="95" t="n">
+        <v>-18.74</v>
+      </c>
+      <c r="AA8" s="95" t="n">
+        <v>-18.74</v>
+      </c>
+      <c r="AB8" s="95" t="n">
+        <v>-19.06</v>
+      </c>
+      <c r="AC8" s="95" t="n">
+        <v>-18.16</v>
+      </c>
+      <c r="AD8" s="95" t="n">
+        <v>-20.04</v>
+      </c>
+      <c r="AE8" s="95" t="n">
+        <v>-19.01</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="93" t="inlineStr">
+      <c r="A9" s="94" t="inlineStr">
         <is>
           <t>kc:RS5</t>
         </is>
       </c>
-      <c r="B9" s="94" t="n">
+      <c r="B9" s="95" t="n">
         <v>71.91</v>
       </c>
-      <c r="C9" s="94" t="n">
+      <c r="C9" s="95" t="n">
         <v>50.48</v>
       </c>
-      <c r="D9" s="94" t="n">
+      <c r="D9" s="95" t="n">
         <v>49.43</v>
       </c>
-      <c r="E9" s="94" t="n">
+      <c r="E9" s="95" t="n">
         <v>55.91</v>
       </c>
-      <c r="F9" s="94" t="n">
+      <c r="F9" s="95" t="n">
         <v>63.75</v>
       </c>
-      <c r="G9" s="94" t="n">
+      <c r="G9" s="95" t="n">
         <v>59.18</v>
       </c>
-      <c r="H9" s="94" t="n">
-        <v>59.18</v>
-      </c>
-      <c r="I9" s="94" t="n">
+      <c r="H9" s="95" t="n">
         <v>74.52</v>
       </c>
-      <c r="J9" s="94" t="n">
+      <c r="I9" s="95" t="n">
         <v>89.13</v>
       </c>
-      <c r="K9" s="94" t="n">
+      <c r="J9" s="95" t="n">
         <v>98.36</v>
       </c>
-      <c r="L9" s="94" t="n">
+      <c r="K9" s="95" t="n">
         <v>96.84</v>
       </c>
-      <c r="M9" s="94" t="n">
+      <c r="L9" s="95" t="n">
         <v>96.84</v>
       </c>
-      <c r="N9" s="94" t="n">
+      <c r="M9" s="95" t="n">
         <v>96.84</v>
       </c>
-      <c r="O9" s="94" t="n">
+      <c r="N9" s="95" t="n">
         <v>96.84</v>
       </c>
-      <c r="P9" s="94" t="n">
+      <c r="O9" s="95" t="n">
         <v>96.84</v>
       </c>
-      <c r="Q9" s="94" t="n">
+      <c r="P9" s="95" t="n">
         <v>96.84</v>
       </c>
-      <c r="R9" s="94" t="n">
-        <v>96.84</v>
-      </c>
-      <c r="S9" s="94" t="n">
+      <c r="Q9" s="95" t="n">
         <v>91.06999999999999</v>
       </c>
-      <c r="T9" s="94" t="n">
-        <v>91.06999999999999</v>
-      </c>
-      <c r="U9" s="94" t="n">
+      <c r="R9" s="95" t="n">
         <v>81.48999999999999</v>
       </c>
-      <c r="V9" s="94" t="n">
+      <c r="S9" s="95" t="n">
         <v>64.94</v>
       </c>
-      <c r="W9" s="94" t="n">
+      <c r="T9" s="95" t="n">
         <v>64.66</v>
       </c>
-      <c r="X9" s="94" t="n">
+      <c r="U9" s="95" t="n">
         <v>23.69</v>
       </c>
-      <c r="Y9" s="94" t="n">
+      <c r="V9" s="95" t="n">
         <v>29.81</v>
       </c>
-      <c r="Z9" s="94" t="n">
-        <v>29.81</v>
-      </c>
-      <c r="AA9" s="94" t="n">
+      <c r="W9" s="95" t="n">
         <v>33.91</v>
       </c>
-      <c r="AB9" s="94" t="n">
+      <c r="X9" s="95" t="n">
         <v>22.82</v>
       </c>
-      <c r="AC9" s="94" t="n">
-        <v/>
-      </c>
-      <c r="AD9" s="94" t="n">
-        <v/>
-      </c>
-      <c r="AE9" s="94" t="n">
-        <v/>
+      <c r="Y9" s="95" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="Z9" s="95" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="AA9" s="95" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="AB9" s="95" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="AC9" s="95" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="AD9" s="95" t="n">
+        <v>33.88</v>
+      </c>
+      <c r="AE9" s="95" t="n">
+        <v>22.22</v>
       </c>
     </row>
     <row r="10">
@@ -7416,211 +7428,217 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="I10" s="91" t="inlineStr">
+      <c r="I10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="V10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="W10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J10" s="92" t="inlineStr">
+      <c r="X10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Y10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AC10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X10" s="95" t="inlineStr">
+      <c r="AD10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y10" s="95" t="inlineStr">
+      <c r="AE10" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z10" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA10" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB10" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC10" s="91" t="n">
-        <v/>
-      </c>
-      <c r="AD10" s="91" t="n">
-        <v/>
-      </c>
-      <c r="AE10" s="91" t="n">
-        <v/>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="93" t="inlineStr">
+      <c r="A11" s="94" t="inlineStr">
         <is>
           <t>cy:RNG60</t>
         </is>
       </c>
-      <c r="B11" s="94" t="n">
+      <c r="B11" s="95" t="n">
         <v>29.39</v>
       </c>
-      <c r="C11" s="94" t="n">
+      <c r="C11" s="95" t="n">
         <v>19.87</v>
       </c>
-      <c r="D11" s="94" t="n">
+      <c r="D11" s="95" t="n">
         <v>21.93</v>
       </c>
-      <c r="E11" s="94" t="n">
+      <c r="E11" s="95" t="n">
         <v>23.9</v>
       </c>
-      <c r="F11" s="94" t="n">
+      <c r="F11" s="95" t="n">
         <v>27.91</v>
       </c>
-      <c r="G11" s="94" t="n">
+      <c r="G11" s="95" t="n">
         <v>27.24</v>
       </c>
-      <c r="H11" s="94" t="n">
-        <v>27.24</v>
-      </c>
-      <c r="I11" s="94" t="n">
+      <c r="H11" s="95" t="n">
         <v>33.94</v>
       </c>
-      <c r="J11" s="94" t="n">
+      <c r="I11" s="95" t="n">
         <v>39.99</v>
       </c>
-      <c r="K11" s="94" t="n">
+      <c r="J11" s="95" t="n">
         <v>54.04</v>
       </c>
-      <c r="L11" s="94" t="n">
+      <c r="K11" s="95" t="n">
         <v>32.05</v>
       </c>
-      <c r="M11" s="94" t="n">
+      <c r="L11" s="95" t="n">
         <v>32.05</v>
       </c>
-      <c r="N11" s="94" t="n">
+      <c r="M11" s="95" t="n">
         <v>32.05</v>
       </c>
-      <c r="O11" s="94" t="n">
+      <c r="N11" s="95" t="n">
         <v>32.05</v>
       </c>
-      <c r="P11" s="94" t="n">
+      <c r="O11" s="95" t="n">
         <v>32.05</v>
       </c>
-      <c r="Q11" s="94" t="n">
+      <c r="P11" s="95" t="n">
         <v>32.05</v>
       </c>
-      <c r="R11" s="94" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="S11" s="94" t="n">
+      <c r="Q11" s="95" t="n">
         <v>13.58</v>
       </c>
-      <c r="T11" s="94" t="n">
-        <v>13.58</v>
-      </c>
-      <c r="U11" s="94" t="n">
+      <c r="R11" s="95" t="n">
         <v>2.95</v>
       </c>
-      <c r="V11" s="94" t="n">
+      <c r="S11" s="95" t="n">
         <v>-2.45</v>
       </c>
-      <c r="W11" s="94" t="n">
+      <c r="T11" s="95" t="n">
         <v>-4.05</v>
       </c>
-      <c r="X11" s="94" t="n">
+      <c r="U11" s="95" t="n">
         <v>-10.14</v>
       </c>
-      <c r="Y11" s="94" t="n">
+      <c r="V11" s="95" t="n">
         <v>-11.21</v>
       </c>
-      <c r="Z11" s="94" t="n">
-        <v>-11.21</v>
-      </c>
-      <c r="AA11" s="94" t="n">
+      <c r="W11" s="95" t="n">
         <v>-9.029999999999999</v>
       </c>
-      <c r="AB11" s="94" t="n">
+      <c r="X11" s="95" t="n">
         <v>-11.44</v>
       </c>
-      <c r="AC11" s="94" t="n">
-        <v/>
-      </c>
-      <c r="AD11" s="94" t="n">
-        <v/>
-      </c>
-      <c r="AE11" s="94" t="n">
-        <v/>
+      <c r="Y11" s="95" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="Z11" s="95" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="AA11" s="95" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="AB11" s="95" t="n">
+        <v>-11.96</v>
+      </c>
+      <c r="AC11" s="95" t="n">
+        <v>-12.87</v>
+      </c>
+      <c r="AD11" s="95" t="n">
+        <v>-14.98</v>
+      </c>
+      <c r="AE11" s="95" t="n">
+        <v>-14.79</v>
       </c>
     </row>
     <row r="12">
@@ -7629,95 +7647,95 @@
           <t>cy:RNG120</t>
         </is>
       </c>
-      <c r="B12" s="94" t="n">
+      <c r="B12" s="95" t="n">
         <v>22.8</v>
       </c>
-      <c r="C12" s="94" t="n">
+      <c r="C12" s="95" t="n">
         <v>13.14</v>
       </c>
-      <c r="D12" s="94" t="n">
+      <c r="D12" s="95" t="n">
         <v>15.89</v>
       </c>
-      <c r="E12" s="94" t="n">
+      <c r="E12" s="95" t="n">
         <v>16.18</v>
       </c>
-      <c r="F12" s="94" t="n">
+      <c r="F12" s="95" t="n">
         <v>22.27</v>
       </c>
-      <c r="G12" s="94" t="n">
+      <c r="G12" s="95" t="n">
         <v>17.89</v>
       </c>
-      <c r="H12" s="94" t="n">
-        <v>17.89</v>
-      </c>
-      <c r="I12" s="94" t="n">
+      <c r="H12" s="95" t="n">
         <v>23.63</v>
       </c>
-      <c r="J12" s="94" t="n">
+      <c r="I12" s="95" t="n">
         <v>24.76</v>
       </c>
-      <c r="K12" s="94" t="n">
+      <c r="J12" s="95" t="n">
         <v>41.13</v>
       </c>
-      <c r="L12" s="94" t="n">
+      <c r="K12" s="95" t="n">
         <v>18.19</v>
       </c>
-      <c r="M12" s="94" t="n">
+      <c r="L12" s="95" t="n">
         <v>18.19</v>
       </c>
-      <c r="N12" s="94" t="n">
+      <c r="M12" s="95" t="n">
         <v>18.19</v>
       </c>
-      <c r="O12" s="94" t="n">
+      <c r="N12" s="95" t="n">
         <v>18.19</v>
       </c>
-      <c r="P12" s="94" t="n">
+      <c r="O12" s="95" t="n">
         <v>18.19</v>
       </c>
-      <c r="Q12" s="94" t="n">
+      <c r="P12" s="95" t="n">
         <v>18.19</v>
       </c>
-      <c r="R12" s="94" t="n">
-        <v>18.19</v>
-      </c>
-      <c r="S12" s="94" t="n">
+      <c r="Q12" s="95" t="n">
         <v>1.34</v>
       </c>
-      <c r="T12" s="94" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="U12" s="94" t="n">
+      <c r="R12" s="95" t="n">
         <v>-8.44</v>
       </c>
-      <c r="V12" s="94" t="n">
+      <c r="S12" s="95" t="n">
         <v>-9.720000000000001</v>
       </c>
-      <c r="W12" s="94" t="n">
+      <c r="T12" s="95" t="n">
         <v>-10.6</v>
       </c>
-      <c r="X12" s="94" t="n">
+      <c r="U12" s="95" t="n">
         <v>-14.49</v>
       </c>
-      <c r="Y12" s="94" t="n">
+      <c r="V12" s="95" t="n">
         <v>-16.56</v>
       </c>
-      <c r="Z12" s="94" t="n">
-        <v>-16.56</v>
-      </c>
-      <c r="AA12" s="94" t="n">
+      <c r="W12" s="95" t="n">
         <v>-15.65</v>
       </c>
-      <c r="AB12" s="94" t="n">
+      <c r="X12" s="95" t="n">
         <v>-17.96</v>
       </c>
-      <c r="AC12" s="94" t="n">
-        <v/>
-      </c>
-      <c r="AD12" s="94" t="n">
-        <v/>
-      </c>
-      <c r="AE12" s="94" t="n">
-        <v/>
+      <c r="Y12" s="95" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="Z12" s="95" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="AA12" s="95" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="AB12" s="95" t="n">
+        <v>-18.72</v>
+      </c>
+      <c r="AC12" s="95" t="n">
+        <v>-18.28</v>
+      </c>
+      <c r="AD12" s="95" t="n">
+        <v>-20.06</v>
+      </c>
+      <c r="AE12" s="95" t="n">
+        <v>-18.31</v>
       </c>
     </row>
     <row r="13">
@@ -7726,95 +7744,95 @@
           <t>cy:RS3</t>
         </is>
       </c>
-      <c r="B13" s="94" t="n">
+      <c r="B13" s="95" t="n">
         <v>70.86</v>
       </c>
-      <c r="C13" s="94" t="n">
+      <c r="C13" s="95" t="n">
         <v>31.37</v>
       </c>
-      <c r="D13" s="94" t="n">
+      <c r="D13" s="95" t="n">
         <v>32.55</v>
       </c>
-      <c r="E13" s="94" t="n">
+      <c r="E13" s="95" t="n">
         <v>39.59</v>
       </c>
-      <c r="F13" s="94" t="n">
+      <c r="F13" s="95" t="n">
         <v>50.6</v>
       </c>
-      <c r="G13" s="94" t="n">
+      <c r="G13" s="95" t="n">
         <v>42.18</v>
       </c>
-      <c r="H13" s="94" t="n">
-        <v>42.18</v>
-      </c>
-      <c r="I13" s="94" t="n">
+      <c r="H13" s="95" t="n">
         <v>55.03</v>
       </c>
-      <c r="J13" s="94" t="n">
+      <c r="I13" s="95" t="n">
         <v>62.67</v>
       </c>
-      <c r="K13" s="94" t="n">
+      <c r="J13" s="95" t="n">
         <v>99.77</v>
       </c>
-      <c r="L13" s="94" t="n">
+      <c r="K13" s="95" t="n">
         <v>99.48</v>
       </c>
-      <c r="M13" s="94" t="n">
+      <c r="L13" s="95" t="n">
         <v>99.48</v>
       </c>
-      <c r="N13" s="94" t="n">
+      <c r="M13" s="95" t="n">
         <v>99.48</v>
       </c>
-      <c r="O13" s="94" t="n">
+      <c r="N13" s="95" t="n">
         <v>99.48</v>
       </c>
-      <c r="P13" s="94" t="n">
+      <c r="O13" s="95" t="n">
         <v>99.48</v>
       </c>
-      <c r="Q13" s="94" t="n">
+      <c r="P13" s="95" t="n">
         <v>99.48</v>
       </c>
-      <c r="R13" s="94" t="n">
-        <v>99.48</v>
-      </c>
-      <c r="S13" s="94" t="n">
+      <c r="Q13" s="95" t="n">
         <v>98.62</v>
       </c>
-      <c r="T13" s="94" t="n">
-        <v>98.62</v>
-      </c>
-      <c r="U13" s="94" t="n">
+      <c r="R13" s="95" t="n">
         <v>96</v>
       </c>
-      <c r="V13" s="94" t="n">
+      <c r="S13" s="95" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="W13" s="94" t="n">
+      <c r="T13" s="95" t="n">
         <v>88.09</v>
       </c>
-      <c r="X13" s="94" t="n">
+      <c r="U13" s="95" t="n">
         <v>30.34</v>
       </c>
-      <c r="Y13" s="94" t="n">
+      <c r="V13" s="95" t="n">
         <v>39.51</v>
       </c>
-      <c r="Z13" s="94" t="n">
-        <v>39.51</v>
-      </c>
-      <c r="AA13" s="94" t="n">
+      <c r="W13" s="95" t="n">
         <v>58.67</v>
       </c>
-      <c r="AB13" s="94" t="n">
+      <c r="X13" s="95" t="n">
         <v>28.04</v>
       </c>
-      <c r="AC13" s="94" t="n">
-        <v/>
-      </c>
-      <c r="AD13" s="94" t="n">
-        <v/>
-      </c>
-      <c r="AE13" s="94" t="n">
-        <v/>
+      <c r="Y13" s="95" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="Z13" s="95" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="AA13" s="95" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="AB13" s="95" t="n">
+        <v>54.57</v>
+      </c>
+      <c r="AC13" s="95" t="n">
+        <v>69.45</v>
+      </c>
+      <c r="AD13" s="95" t="n">
+        <v>37.43</v>
+      </c>
+      <c r="AE13" s="95" t="n">
+        <v>35.11</v>
       </c>
     </row>
     <row r="14">
@@ -7828,17 +7846,17 @@
           <t>red</t>
         </is>
       </c>
-      <c r="C14" s="95" t="inlineStr">
+      <c r="C14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D14" s="95" t="inlineStr">
+      <c r="D14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E14" s="95" t="inlineStr">
+      <c r="E14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -7858,215 +7876,217 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="I14" s="91" t="inlineStr">
+      <c r="I14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J14" s="95" t="inlineStr">
+      <c r="K14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AB14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AC14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="L14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE14" s="91" t="n">
-        <v/>
+      <c r="AD14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="93" t="inlineStr">
+      <c r="A15" s="94" t="inlineStr">
         <is>
           <t>hk50:RNG60</t>
         </is>
       </c>
-      <c r="B15" s="94" t="n">
+      <c r="B15" s="95" t="n">
         <v>17.96</v>
       </c>
-      <c r="C15" s="94" t="n">
+      <c r="C15" s="95" t="n">
         <v>15.28</v>
       </c>
-      <c r="D15" s="94" t="n">
+      <c r="D15" s="95" t="n">
         <v>14.11</v>
       </c>
-      <c r="E15" s="94" t="n">
+      <c r="E15" s="95" t="n">
         <v>14.54</v>
       </c>
-      <c r="F15" s="94" t="n">
+      <c r="F15" s="95" t="n">
         <v>18.98</v>
       </c>
-      <c r="G15" s="94" t="n">
+      <c r="G15" s="95" t="n">
         <v>17.96</v>
       </c>
-      <c r="H15" s="94" t="n">
+      <c r="H15" s="95" t="n">
         <v>17.96</v>
       </c>
-      <c r="I15" s="94" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="J15" s="94" t="n">
+      <c r="I15" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="K15" s="94" t="n">
+      <c r="J15" s="95" t="n">
         <v>17.35</v>
       </c>
-      <c r="L15" s="94" t="n">
+      <c r="K15" s="95" t="n">
         <v>32.21</v>
       </c>
-      <c r="M15" s="94" t="n">
+      <c r="L15" s="95" t="n">
         <v>29.75</v>
       </c>
-      <c r="N15" s="94" t="n">
-        <v>29.75</v>
-      </c>
-      <c r="O15" s="94" t="n">
+      <c r="M15" s="95" t="n">
         <v>26.19</v>
       </c>
-      <c r="P15" s="94" t="n">
+      <c r="N15" s="95" t="n">
         <v>26.09</v>
       </c>
-      <c r="Q15" s="94" t="n">
+      <c r="O15" s="95" t="n">
         <v>17.23</v>
       </c>
-      <c r="R15" s="94" t="n">
+      <c r="P15" s="95" t="n">
         <v>17.23</v>
       </c>
-      <c r="S15" s="94" t="n">
+      <c r="Q15" s="95" t="n">
         <v>14.76</v>
       </c>
-      <c r="T15" s="94" t="n">
-        <v>14.76</v>
-      </c>
-      <c r="U15" s="94" t="n">
+      <c r="R15" s="95" t="n">
         <v>12.13</v>
       </c>
-      <c r="V15" s="94" t="n">
+      <c r="S15" s="95" t="n">
         <v>7.96</v>
       </c>
-      <c r="W15" s="94" t="n">
+      <c r="T15" s="95" t="n">
         <v>7.25</v>
       </c>
-      <c r="X15" s="94" t="n">
+      <c r="U15" s="95" t="n">
         <v>0.87</v>
       </c>
-      <c r="Y15" s="94" t="n">
+      <c r="V15" s="95" t="n">
         <v>1.03</v>
       </c>
-      <c r="Z15" s="94" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AA15" s="94" t="n">
+      <c r="W15" s="95" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AB15" s="94" t="n">
+      <c r="X15" s="95" t="n">
         <v>-2.04</v>
       </c>
-      <c r="AC15" s="94" t="n">
+      <c r="Y15" s="95" t="n">
         <v>-2.04</v>
       </c>
-      <c r="AD15" s="94" t="n">
+      <c r="Z15" s="95" t="n">
         <v>-4.98</v>
       </c>
-      <c r="AE15" s="94" t="n">
-        <v/>
+      <c r="AA15" s="95" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="AB15" s="95" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="AC15" s="95" t="n">
+        <v>-4.61</v>
+      </c>
+      <c r="AD15" s="95" t="n">
+        <v>-3.94</v>
+      </c>
+      <c r="AE15" s="95" t="n">
+        <v>-5.06</v>
       </c>
     </row>
     <row r="16">
@@ -8075,95 +8095,95 @@
           <t>hk50:RNG120</t>
         </is>
       </c>
-      <c r="B16" s="94" t="n">
+      <c r="B16" s="95" t="n">
         <v>23.62</v>
       </c>
-      <c r="C16" s="94" t="n">
+      <c r="C16" s="95" t="n">
         <v>21.61</v>
       </c>
-      <c r="D16" s="94" t="n">
+      <c r="D16" s="95" t="n">
         <v>25.04</v>
       </c>
-      <c r="E16" s="94" t="n">
+      <c r="E16" s="95" t="n">
         <v>24</v>
       </c>
-      <c r="F16" s="94" t="n">
+      <c r="F16" s="95" t="n">
         <v>29.79</v>
       </c>
-      <c r="G16" s="94" t="n">
+      <c r="G16" s="95" t="n">
         <v>30.79</v>
       </c>
-      <c r="H16" s="94" t="n">
+      <c r="H16" s="95" t="n">
         <v>30.79</v>
       </c>
-      <c r="I16" s="94" t="n">
-        <v>30.79</v>
-      </c>
-      <c r="J16" s="94" t="n">
+      <c r="I16" s="95" t="n">
         <v>24.32</v>
       </c>
-      <c r="K16" s="94" t="n">
+      <c r="J16" s="95" t="n">
         <v>25.15</v>
       </c>
-      <c r="L16" s="94" t="n">
+      <c r="K16" s="95" t="n">
         <v>35.13</v>
       </c>
-      <c r="M16" s="94" t="n">
+      <c r="L16" s="95" t="n">
         <v>32.66</v>
       </c>
-      <c r="N16" s="94" t="n">
-        <v>32.66</v>
-      </c>
-      <c r="O16" s="94" t="n">
+      <c r="M16" s="95" t="n">
         <v>31.41</v>
       </c>
-      <c r="P16" s="94" t="n">
+      <c r="N16" s="95" t="n">
         <v>34.13</v>
       </c>
-      <c r="Q16" s="94" t="n">
+      <c r="O16" s="95" t="n">
         <v>26.37</v>
       </c>
-      <c r="R16" s="94" t="n">
+      <c r="P16" s="95" t="n">
         <v>26.37</v>
       </c>
-      <c r="S16" s="94" t="n">
+      <c r="Q16" s="95" t="n">
         <v>23.36</v>
       </c>
-      <c r="T16" s="94" t="n">
-        <v>23.36</v>
-      </c>
-      <c r="U16" s="94" t="n">
+      <c r="R16" s="95" t="n">
         <v>17.68</v>
       </c>
-      <c r="V16" s="94" t="n">
+      <c r="S16" s="95" t="n">
         <v>15.64</v>
       </c>
-      <c r="W16" s="94" t="n">
+      <c r="T16" s="95" t="n">
         <v>15.91</v>
       </c>
-      <c r="X16" s="94" t="n">
+      <c r="U16" s="95" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Y16" s="94" t="n">
+      <c r="V16" s="95" t="n">
         <v>10.84</v>
       </c>
-      <c r="Z16" s="94" t="n">
-        <v>10.84</v>
-      </c>
-      <c r="AA16" s="94" t="n">
+      <c r="W16" s="95" t="n">
         <v>9.17</v>
       </c>
-      <c r="AB16" s="94" t="n">
+      <c r="X16" s="95" t="n">
         <v>4.73</v>
       </c>
-      <c r="AC16" s="94" t="n">
+      <c r="Y16" s="95" t="n">
         <v>4.73</v>
       </c>
-      <c r="AD16" s="94" t="n">
+      <c r="Z16" s="95" t="n">
         <v>5.31</v>
       </c>
-      <c r="AE16" s="94" t="n">
-        <v/>
+      <c r="AA16" s="95" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AB16" s="95" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AC16" s="95" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD16" s="95" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE16" s="95" t="n">
+        <v>0.67</v>
       </c>
     </row>
     <row r="17">
@@ -8172,95 +8192,95 @@
           <t>hk50:RS4</t>
         </is>
       </c>
-      <c r="B17" s="94" t="n">
+      <c r="B17" s="95" t="n">
         <v>54</v>
       </c>
-      <c r="C17" s="94" t="n">
+      <c r="C17" s="95" t="n">
         <v>27.44</v>
       </c>
-      <c r="D17" s="94" t="n">
+      <c r="D17" s="95" t="n">
         <v>31.33</v>
       </c>
-      <c r="E17" s="94" t="n">
+      <c r="E17" s="95" t="n">
         <v>31.85</v>
       </c>
-      <c r="F17" s="94" t="n">
+      <c r="F17" s="95" t="n">
         <v>45.61</v>
       </c>
-      <c r="G17" s="94" t="n">
+      <c r="G17" s="95" t="n">
         <v>48.87</v>
       </c>
-      <c r="H17" s="94" t="n">
+      <c r="H17" s="95" t="n">
         <v>48.87</v>
       </c>
-      <c r="I17" s="94" t="n">
-        <v>48.87</v>
-      </c>
-      <c r="J17" s="94" t="n">
+      <c r="I17" s="95" t="n">
         <v>35.54</v>
       </c>
-      <c r="K17" s="94" t="n">
+      <c r="J17" s="95" t="n">
         <v>39.14</v>
       </c>
-      <c r="L17" s="94" t="n">
+      <c r="K17" s="95" t="n">
         <v>91.23999999999999</v>
       </c>
-      <c r="M17" s="94" t="n">
+      <c r="L17" s="95" t="n">
         <v>89.48999999999999</v>
       </c>
-      <c r="N17" s="94" t="n">
-        <v>89.48999999999999</v>
-      </c>
-      <c r="O17" s="94" t="n">
+      <c r="M17" s="95" t="n">
         <v>85.84</v>
       </c>
-      <c r="P17" s="94" t="n">
+      <c r="N17" s="95" t="n">
         <v>99.56999999999999</v>
       </c>
-      <c r="Q17" s="94" t="n">
+      <c r="O17" s="95" t="n">
         <v>99.18000000000001</v>
       </c>
-      <c r="R17" s="94" t="n">
+      <c r="P17" s="95" t="n">
         <v>99.18000000000001</v>
       </c>
-      <c r="S17" s="94" t="n">
+      <c r="Q17" s="95" t="n">
         <v>98.89</v>
       </c>
-      <c r="T17" s="94" t="n">
-        <v>98.89</v>
-      </c>
-      <c r="U17" s="94" t="n">
+      <c r="R17" s="95" t="n">
         <v>98.23</v>
       </c>
-      <c r="V17" s="94" t="n">
+      <c r="S17" s="95" t="n">
         <v>96.44</v>
       </c>
-      <c r="W17" s="94" t="n">
+      <c r="T17" s="95" t="n">
         <v>95.94</v>
       </c>
-      <c r="X17" s="94" t="n">
+      <c r="U17" s="95" t="n">
         <v>89.48</v>
       </c>
-      <c r="Y17" s="94" t="n">
+      <c r="V17" s="95" t="n">
         <v>91.13</v>
       </c>
-      <c r="Z17" s="94" t="n">
-        <v>91.13</v>
-      </c>
-      <c r="AA17" s="94" t="n">
+      <c r="W17" s="95" t="n">
         <v>87.39</v>
       </c>
-      <c r="AB17" s="94" t="n">
+      <c r="X17" s="95" t="n">
         <v>76.86</v>
       </c>
-      <c r="AC17" s="94" t="n">
+      <c r="Y17" s="95" t="n">
         <v>76.86</v>
       </c>
-      <c r="AD17" s="94" t="n">
+      <c r="Z17" s="95" t="n">
         <v>59.96</v>
       </c>
-      <c r="AE17" s="94" t="n">
-        <v/>
+      <c r="AA17" s="95" t="n">
+        <v>54.39</v>
+      </c>
+      <c r="AB17" s="95" t="n">
+        <v>38.93</v>
+      </c>
+      <c r="AC17" s="95" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="AD17" s="95" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="AE17" s="95" t="n">
+        <v>17.15</v>
       </c>
     </row>
     <row r="18">
@@ -8269,153 +8289,155 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="91" t="inlineStr">
+      <c r="B18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C18" s="91" t="inlineStr">
+      <c r="D18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="E18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D18" s="92" t="inlineStr">
+      <c r="F18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E18" s="91" t="inlineStr">
+      <c r="G18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F18" s="92" t="inlineStr">
+      <c r="N18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G18" s="92" t="inlineStr">
+      <c r="U18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H18" s="92" t="inlineStr">
+      <c r="V18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I18" s="92" t="inlineStr">
+      <c r="W18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J18" s="92" t="inlineStr">
+      <c r="X18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K18" s="92" t="inlineStr">
+      <c r="Z18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L18" s="95" t="inlineStr">
+      <c r="AA18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AC18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AD18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AE18" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
-      </c>
-      <c r="M18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE18" s="91" t="n">
-        <v/>
       </c>
     </row>
     <row r="19">
@@ -8424,95 +8446,95 @@
           <t>us500:RNG60</t>
         </is>
       </c>
-      <c r="B19" s="94" t="n">
+      <c r="B19" s="95" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="C19" s="95" t="n">
         <v>7.63</v>
       </c>
-      <c r="C19" s="94" t="n">
-        <v>7.63</v>
-      </c>
-      <c r="D19" s="94" t="n">
+      <c r="D19" s="95" t="n">
         <v>5.16</v>
       </c>
-      <c r="E19" s="94" t="n">
+      <c r="E19" s="95" t="n">
         <v>4.51</v>
       </c>
-      <c r="F19" s="94" t="n">
+      <c r="F19" s="95" t="n">
         <v>6.45</v>
       </c>
-      <c r="G19" s="94" t="n">
+      <c r="G19" s="95" t="n">
         <v>4.88</v>
       </c>
-      <c r="H19" s="94" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="I19" s="94" t="n">
+      <c r="H19" s="95" t="n">
         <v>3.43</v>
       </c>
-      <c r="J19" s="94" t="n">
+      <c r="I19" s="95" t="n">
         <v>2.2</v>
       </c>
-      <c r="K19" s="94" t="n">
+      <c r="J19" s="95" t="n">
         <v>2.13</v>
       </c>
-      <c r="L19" s="94" t="n">
+      <c r="K19" s="95" t="n">
         <v>1.44</v>
       </c>
-      <c r="M19" s="94" t="n">
+      <c r="L19" s="95" t="n">
         <v>2.98</v>
       </c>
-      <c r="N19" s="94" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O19" s="94" t="n">
+      <c r="M19" s="95" t="n">
         <v>1.17</v>
       </c>
-      <c r="P19" s="94" t="n">
+      <c r="N19" s="95" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q19" s="94" t="n">
+      <c r="O19" s="95" t="n">
         <v>2.44</v>
       </c>
-      <c r="R19" s="94" t="n">
+      <c r="P19" s="95" t="n">
         <v>3.51</v>
       </c>
-      <c r="S19" s="94" t="n">
+      <c r="Q19" s="95" t="n">
         <v>3.63</v>
       </c>
-      <c r="T19" s="94" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="U19" s="94" t="n">
+      <c r="R19" s="95" t="n">
         <v>4.29</v>
       </c>
-      <c r="V19" s="94" t="n">
+      <c r="S19" s="95" t="n">
         <v>4.51</v>
       </c>
-      <c r="W19" s="94" t="n">
+      <c r="T19" s="95" t="n">
         <v>4.99</v>
       </c>
-      <c r="X19" s="94" t="n">
+      <c r="U19" s="95" t="n">
         <v>4.3</v>
       </c>
-      <c r="Y19" s="94" t="n">
+      <c r="V19" s="95" t="n">
         <v>4.1</v>
       </c>
-      <c r="Z19" s="94" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA19" s="94" t="n">
+      <c r="W19" s="95" t="n">
         <v>4.47</v>
       </c>
-      <c r="AB19" s="94" t="n">
+      <c r="X19" s="95" t="n">
         <v>3.13</v>
       </c>
-      <c r="AC19" s="94" t="n">
+      <c r="Y19" s="95" t="n">
         <v>3.11</v>
       </c>
-      <c r="AD19" s="94" t="n">
+      <c r="Z19" s="95" t="n">
         <v>2.92</v>
       </c>
-      <c r="AE19" s="94" t="n">
-        <v/>
+      <c r="AA19" s="95" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AB19" s="95" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AC19" s="95" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AD19" s="95" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE19" s="95" t="n">
+        <v>0.92</v>
       </c>
     </row>
     <row r="20">
@@ -8521,95 +8543,95 @@
           <t>us500:RNG120</t>
         </is>
       </c>
-      <c r="B20" s="94" t="n">
+      <c r="B20" s="95" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="C20" s="95" t="n">
         <v>14.54</v>
       </c>
-      <c r="C20" s="94" t="n">
-        <v>14.54</v>
-      </c>
-      <c r="D20" s="94" t="n">
+      <c r="D20" s="95" t="n">
         <v>15.73</v>
       </c>
-      <c r="E20" s="94" t="n">
+      <c r="E20" s="95" t="n">
         <v>14.66</v>
       </c>
-      <c r="F20" s="94" t="n">
+      <c r="F20" s="95" t="n">
         <v>15.57</v>
       </c>
-      <c r="G20" s="94" t="n">
+      <c r="G20" s="95" t="n">
         <v>16.05</v>
       </c>
-      <c r="H20" s="94" t="n">
-        <v>16.05</v>
-      </c>
-      <c r="I20" s="94" t="n">
+      <c r="H20" s="95" t="n">
         <v>16.36</v>
       </c>
-      <c r="J20" s="94" t="n">
+      <c r="I20" s="95" t="n">
         <v>15.58</v>
       </c>
-      <c r="K20" s="94" t="n">
+      <c r="J20" s="95" t="n">
         <v>14.51</v>
       </c>
-      <c r="L20" s="94" t="n">
+      <c r="K20" s="95" t="n">
         <v>12.76</v>
       </c>
-      <c r="M20" s="94" t="n">
+      <c r="L20" s="95" t="n">
         <v>13.62</v>
       </c>
-      <c r="N20" s="94" t="n">
-        <v>13.62</v>
-      </c>
-      <c r="O20" s="94" t="n">
+      <c r="M20" s="95" t="n">
         <v>11.25</v>
       </c>
-      <c r="P20" s="94" t="n">
+      <c r="N20" s="95" t="n">
         <v>9.82</v>
       </c>
-      <c r="Q20" s="94" t="n">
+      <c r="O20" s="95" t="n">
         <v>10.62</v>
       </c>
-      <c r="R20" s="94" t="n">
+      <c r="P20" s="95" t="n">
         <v>10.61</v>
       </c>
-      <c r="S20" s="94" t="n">
+      <c r="Q20" s="95" t="n">
         <v>10.3</v>
       </c>
-      <c r="T20" s="94" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="U20" s="94" t="n">
+      <c r="R20" s="95" t="n">
         <v>10.4</v>
       </c>
-      <c r="V20" s="94" t="n">
+      <c r="S20" s="95" t="n">
         <v>11.17</v>
       </c>
-      <c r="W20" s="94" t="n">
+      <c r="T20" s="95" t="n">
         <v>10.01</v>
       </c>
-      <c r="X20" s="94" t="n">
+      <c r="U20" s="95" t="n">
         <v>9.85</v>
       </c>
-      <c r="Y20" s="94" t="n">
+      <c r="V20" s="95" t="n">
         <v>8.75</v>
       </c>
-      <c r="Z20" s="94" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="AA20" s="94" t="n">
+      <c r="W20" s="95" t="n">
         <v>8.74</v>
       </c>
-      <c r="AB20" s="94" t="n">
+      <c r="X20" s="95" t="n">
         <v>7.05</v>
       </c>
-      <c r="AC20" s="94" t="n">
+      <c r="Y20" s="95" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="AD20" s="94" t="n">
+      <c r="Z20" s="95" t="n">
         <v>7.95</v>
       </c>
-      <c r="AE20" s="94" t="n">
-        <v/>
+      <c r="AA20" s="95" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="AB20" s="95" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="AC20" s="95" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="AD20" s="95" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="AE20" s="95" t="n">
+        <v>6.25</v>
       </c>
     </row>
     <row r="21">
@@ -8618,95 +8640,95 @@
           <t>us500:RS2</t>
         </is>
       </c>
-      <c r="B21" s="94" t="n">
+      <c r="B21" s="95" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="C21" s="95" t="n">
         <v>63.88</v>
       </c>
-      <c r="C21" s="94" t="n">
-        <v>63.88</v>
-      </c>
-      <c r="D21" s="94" t="n">
+      <c r="D21" s="95" t="n">
         <v>65.73999999999999</v>
       </c>
-      <c r="E21" s="94" t="n">
+      <c r="E21" s="95" t="n">
         <v>43.25</v>
       </c>
-      <c r="F21" s="94" t="n">
+      <c r="F21" s="95" t="n">
         <v>93.59999999999999</v>
       </c>
-      <c r="G21" s="94" t="n">
+      <c r="G21" s="95" t="n">
         <v>84.56999999999999</v>
       </c>
-      <c r="H21" s="94" t="n">
-        <v>84.56999999999999</v>
-      </c>
-      <c r="I21" s="94" t="n">
+      <c r="H21" s="95" t="n">
         <v>65.7</v>
       </c>
-      <c r="J21" s="94" t="n">
+      <c r="I21" s="95" t="n">
         <v>83.12</v>
       </c>
-      <c r="K21" s="94" t="n">
+      <c r="J21" s="95" t="n">
         <v>69.18000000000001</v>
       </c>
-      <c r="L21" s="94" t="n">
+      <c r="K21" s="95" t="n">
         <v>30.41</v>
       </c>
-      <c r="M21" s="94" t="n">
+      <c r="L21" s="95" t="n">
         <v>81.84</v>
       </c>
-      <c r="N21" s="94" t="n">
-        <v>81.84</v>
-      </c>
-      <c r="O21" s="94" t="n">
+      <c r="M21" s="95" t="n">
         <v>15.76</v>
       </c>
-      <c r="P21" s="94" t="n">
+      <c r="N21" s="95" t="n">
         <v>23.93</v>
       </c>
-      <c r="Q21" s="94" t="n">
+      <c r="O21" s="95" t="n">
         <v>22.27</v>
       </c>
-      <c r="R21" s="94" t="n">
+      <c r="P21" s="95" t="n">
         <v>86.19</v>
       </c>
-      <c r="S21" s="94" t="n">
+      <c r="Q21" s="95" t="n">
         <v>60.63</v>
       </c>
-      <c r="T21" s="94" t="n">
-        <v>60.63</v>
-      </c>
-      <c r="U21" s="94" t="n">
+      <c r="R21" s="95" t="n">
         <v>83.51000000000001</v>
       </c>
-      <c r="V21" s="94" t="n">
+      <c r="S21" s="95" t="n">
         <v>58.19</v>
       </c>
-      <c r="W21" s="94" t="n">
+      <c r="T21" s="95" t="n">
         <v>90.16</v>
       </c>
-      <c r="X21" s="94" t="n">
+      <c r="U21" s="95" t="n">
         <v>84.39</v>
       </c>
-      <c r="Y21" s="94" t="n">
+      <c r="V21" s="95" t="n">
         <v>76.79000000000001</v>
       </c>
-      <c r="Z21" s="94" t="n">
-        <v>76.79000000000001</v>
-      </c>
-      <c r="AA21" s="94" t="n">
+      <c r="W21" s="95" t="n">
         <v>92.34</v>
       </c>
-      <c r="AB21" s="94" t="n">
+      <c r="X21" s="95" t="n">
         <v>40.89</v>
       </c>
-      <c r="AC21" s="94" t="n">
+      <c r="Y21" s="95" t="n">
         <v>96.09</v>
       </c>
-      <c r="AD21" s="94" t="n">
+      <c r="Z21" s="95" t="n">
         <v>95.83</v>
       </c>
-      <c r="AE21" s="94" t="n">
-        <v/>
+      <c r="AA21" s="95" t="n">
+        <v>95.06</v>
+      </c>
+      <c r="AB21" s="95" t="n">
+        <v>91.83</v>
+      </c>
+      <c r="AC21" s="95" t="n">
+        <v>85.17</v>
+      </c>
+      <c r="AD21" s="95" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AE21" s="95" t="n">
+        <v>51.58</v>
       </c>
     </row>
     <row r="22">
@@ -8755,113 +8777,115 @@
           <t>red</t>
         </is>
       </c>
-      <c r="J22" s="92" t="inlineStr">
+      <c r="J22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K22" s="91" t="inlineStr">
+      <c r="M22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L22" s="95" t="inlineStr">
+      <c r="N22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AC22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AD22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O22" s="91" t="inlineStr">
+      <c r="AE22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
-      </c>
-      <c r="P22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE22" s="91" t="n">
-        <v/>
       </c>
     </row>
     <row r="23">
@@ -8870,95 +8894,95 @@
           <t>us30:RNG60</t>
         </is>
       </c>
-      <c r="B23" s="94" t="n">
+      <c r="B23" s="95" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="C23" s="95" t="n">
         <v>8.49</v>
       </c>
-      <c r="C23" s="94" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="D23" s="94" t="n">
+      <c r="D23" s="95" t="n">
         <v>6.74</v>
       </c>
-      <c r="E23" s="94" t="n">
+      <c r="E23" s="95" t="n">
         <v>5.75</v>
       </c>
-      <c r="F23" s="94" t="n">
+      <c r="F23" s="95" t="n">
         <v>6.89</v>
       </c>
-      <c r="G23" s="94" t="n">
+      <c r="G23" s="95" t="n">
         <v>5.41</v>
       </c>
-      <c r="H23" s="94" t="n">
+      <c r="H23" s="95" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I23" s="95" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J23" s="95" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="K23" s="95" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="L23" s="95" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="M23" s="95" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="N23" s="95" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="O23" s="95" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="P23" s="95" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q23" s="95" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="R23" s="95" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="S23" s="95" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="T23" s="95" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="U23" s="95" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="V23" s="95" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W23" s="95" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="X23" s="95" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="Y23" s="95" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="Z23" s="95" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="AA23" s="95" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="AB23" s="95" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AC23" s="95" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AD23" s="95" t="n">
         <v>5.41</v>
       </c>
-      <c r="I23" s="94" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="J23" s="94" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K23" s="94" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="L23" s="94" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M23" s="94" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="N23" s="94" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="O23" s="94" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="P23" s="94" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="Q23" s="94" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="R23" s="94" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="S23" s="94" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="T23" s="94" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="U23" s="94" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="V23" s="94" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="W23" s="94" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="X23" s="94" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="Y23" s="94" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z23" s="94" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA23" s="94" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="AB23" s="94" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="AC23" s="94" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="AD23" s="94" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="AE23" s="94" t="n">
-        <v/>
+      <c r="AE23" s="95" t="n">
+        <v>5.47</v>
       </c>
     </row>
     <row r="24">
@@ -8967,95 +8991,95 @@
           <t>us30:RNG120</t>
         </is>
       </c>
-      <c r="B24" s="94" t="n">
+      <c r="B24" s="95" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="C24" s="95" t="n">
         <v>13.07</v>
       </c>
-      <c r="C24" s="94" t="n">
-        <v>13.07</v>
-      </c>
-      <c r="D24" s="94" t="n">
+      <c r="D24" s="95" t="n">
         <v>13.11</v>
       </c>
-      <c r="E24" s="94" t="n">
+      <c r="E24" s="95" t="n">
         <v>11.13</v>
       </c>
-      <c r="F24" s="94" t="n">
+      <c r="F24" s="95" t="n">
         <v>11.85</v>
       </c>
-      <c r="G24" s="94" t="n">
+      <c r="G24" s="95" t="n">
         <v>12.09</v>
       </c>
-      <c r="H24" s="94" t="n">
-        <v>12.09</v>
-      </c>
-      <c r="I24" s="94" t="n">
+      <c r="H24" s="95" t="n">
         <v>11.76</v>
       </c>
-      <c r="J24" s="94" t="n">
+      <c r="I24" s="95" t="n">
         <v>12.54</v>
       </c>
-      <c r="K24" s="94" t="n">
+      <c r="J24" s="95" t="n">
         <v>11.46</v>
       </c>
-      <c r="L24" s="94" t="n">
+      <c r="K24" s="95" t="n">
         <v>10.99</v>
       </c>
-      <c r="M24" s="94" t="n">
+      <c r="L24" s="95" t="n">
         <v>12.24</v>
       </c>
-      <c r="N24" s="94" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="O24" s="94" t="n">
+      <c r="M24" s="95" t="n">
         <v>10.61</v>
       </c>
-      <c r="P24" s="94" t="n">
+      <c r="N24" s="95" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="Q24" s="94" t="n">
+      <c r="O24" s="95" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="R24" s="94" t="n">
+      <c r="P24" s="95" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="S24" s="94" t="n">
+      <c r="Q24" s="95" t="n">
         <v>8.789999999999999</v>
       </c>
-      <c r="T24" s="94" t="n">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="U24" s="94" t="n">
+      <c r="R24" s="95" t="n">
         <v>8.41</v>
       </c>
-      <c r="V24" s="94" t="n">
+      <c r="S24" s="95" t="n">
         <v>8.6</v>
       </c>
-      <c r="W24" s="94" t="n">
+      <c r="T24" s="95" t="n">
         <v>7.87</v>
       </c>
-      <c r="X24" s="94" t="n">
+      <c r="U24" s="95" t="n">
         <v>7.54</v>
       </c>
-      <c r="Y24" s="94" t="n">
+      <c r="V24" s="95" t="n">
         <v>6.31</v>
       </c>
-      <c r="Z24" s="94" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="AA24" s="94" t="n">
+      <c r="W24" s="95" t="n">
         <v>5.57</v>
       </c>
-      <c r="AB24" s="94" t="n">
+      <c r="X24" s="95" t="n">
         <v>4.38</v>
       </c>
-      <c r="AC24" s="94" t="n">
+      <c r="Y24" s="95" t="n">
         <v>5.92</v>
       </c>
-      <c r="AD24" s="94" t="n">
+      <c r="Z24" s="95" t="n">
         <v>5.87</v>
       </c>
-      <c r="AE24" s="94" t="n">
-        <v/>
+      <c r="AA24" s="95" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AB24" s="95" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AC24" s="95" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD24" s="95" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="AE24" s="95" t="n">
+        <v>5.26</v>
       </c>
     </row>
     <row r="25">
@@ -9064,95 +9088,95 @@
           <t>us30:RS3</t>
         </is>
       </c>
-      <c r="B25" s="94" t="n">
+      <c r="B25" s="95" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="C25" s="95" t="n">
         <v>77.16</v>
       </c>
-      <c r="C25" s="94" t="n">
-        <v>77.16</v>
-      </c>
-      <c r="D25" s="94" t="n">
+      <c r="D25" s="95" t="n">
         <v>70.95999999999999</v>
       </c>
-      <c r="E25" s="94" t="n">
+      <c r="E25" s="95" t="n">
         <v>53.27</v>
       </c>
-      <c r="F25" s="94" t="n">
+      <c r="F25" s="95" t="n">
         <v>87.47</v>
       </c>
-      <c r="G25" s="94" t="n">
+      <c r="G25" s="95" t="n">
         <v>82.94</v>
       </c>
-      <c r="H25" s="94" t="n">
+      <c r="H25" s="95" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="I25" s="95" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="J25" s="95" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="K25" s="95" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="L25" s="95" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="M25" s="95" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="N25" s="95" t="n">
+        <v>52.09</v>
+      </c>
+      <c r="O25" s="95" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="P25" s="95" t="n">
+        <v>76.02</v>
+      </c>
+      <c r="Q25" s="95" t="n">
+        <v>74.91</v>
+      </c>
+      <c r="R25" s="95" t="n">
+        <v>66.62</v>
+      </c>
+      <c r="S25" s="95" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="T25" s="95" t="n">
+        <v>92.18000000000001</v>
+      </c>
+      <c r="U25" s="95" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="V25" s="95" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="W25" s="95" t="n">
+        <v>87.58</v>
+      </c>
+      <c r="X25" s="95" t="n">
+        <v>65.31</v>
+      </c>
+      <c r="Y25" s="95" t="n">
+        <v>85.48999999999999</v>
+      </c>
+      <c r="Z25" s="95" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="AA25" s="95" t="n">
         <v>82.94</v>
       </c>
-      <c r="I25" s="94" t="n">
-        <v>66.56</v>
-      </c>
-      <c r="J25" s="94" t="n">
-        <v>73.18000000000001</v>
-      </c>
-      <c r="K25" s="94" t="n">
-        <v>46.98</v>
-      </c>
-      <c r="L25" s="94" t="n">
-        <v>34.52</v>
-      </c>
-      <c r="M25" s="94" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="N25" s="94" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="O25" s="94" t="n">
-        <v>28.19</v>
-      </c>
-      <c r="P25" s="94" t="n">
-        <v>52.09</v>
-      </c>
-      <c r="Q25" s="94" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="R25" s="94" t="n">
-        <v>76.02</v>
-      </c>
-      <c r="S25" s="94" t="n">
-        <v>74.91</v>
-      </c>
-      <c r="T25" s="94" t="n">
-        <v>74.91</v>
-      </c>
-      <c r="U25" s="94" t="n">
-        <v>66.62</v>
-      </c>
-      <c r="V25" s="94" t="n">
-        <v>42.84</v>
-      </c>
-      <c r="W25" s="94" t="n">
-        <v>92.18000000000001</v>
-      </c>
-      <c r="X25" s="94" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="Y25" s="94" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="Z25" s="94" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="AA25" s="94" t="n">
-        <v>87.58</v>
-      </c>
-      <c r="AB25" s="94" t="n">
-        <v>65.31</v>
-      </c>
-      <c r="AC25" s="94" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AD25" s="94" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="AE25" s="94" t="n">
-        <v/>
+      <c r="AB25" s="95" t="n">
+        <v>71.68000000000001</v>
+      </c>
+      <c r="AC25" s="95" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="AD25" s="95" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="AE25" s="95" t="n">
+        <v>52.5</v>
       </c>
     </row>
     <row r="26">
@@ -9161,153 +9185,155 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="91" t="inlineStr">
+      <c r="B26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C26" s="91" t="inlineStr">
+      <c r="D26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D26" s="91" t="inlineStr">
+      <c r="E26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E26" s="91" t="inlineStr">
+      <c r="F26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F26" s="92" t="inlineStr">
+      <c r="N26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G26" s="92" t="inlineStr">
+      <c r="S26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H26" s="92" t="inlineStr">
+      <c r="U26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I26" s="92" t="inlineStr">
+      <c r="V26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J26" s="92" t="inlineStr">
+      <c r="W26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K26" s="92" t="inlineStr">
+      <c r="X26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L26" s="95" t="inlineStr">
+      <c r="Z26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AC26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AD26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AE26" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
-      </c>
-      <c r="M26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE26" s="91" t="n">
-        <v/>
       </c>
     </row>
     <row r="27">
@@ -9316,95 +9342,95 @@
           <t>ixic:RNG60</t>
         </is>
       </c>
-      <c r="B27" s="94" t="n">
+      <c r="B27" s="95" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="C27" s="95" t="n">
         <v>5.95</v>
       </c>
-      <c r="C27" s="94" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="D27" s="94" t="n">
+      <c r="D27" s="95" t="n">
         <v>2.05</v>
       </c>
-      <c r="E27" s="94" t="n">
+      <c r="E27" s="95" t="n">
         <v>1.71</v>
       </c>
-      <c r="F27" s="94" t="n">
+      <c r="F27" s="95" t="n">
         <v>4.38</v>
       </c>
-      <c r="G27" s="94" t="n">
+      <c r="G27" s="95" t="n">
         <v>2.64</v>
       </c>
-      <c r="H27" s="94" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I27" s="94" t="n">
+      <c r="H27" s="95" t="n">
         <v>1.58</v>
       </c>
-      <c r="J27" s="94" t="n">
+      <c r="I27" s="95" t="n">
         <v>-1.18</v>
       </c>
-      <c r="K27" s="94" t="n">
+      <c r="J27" s="95" t="n">
         <v>-1.57</v>
       </c>
-      <c r="L27" s="94" t="n">
+      <c r="K27" s="95" t="n">
         <v>-2.58</v>
       </c>
-      <c r="M27" s="94" t="n">
+      <c r="L27" s="95" t="n">
         <v>-0.8</v>
       </c>
-      <c r="N27" s="94" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="O27" s="94" t="n">
+      <c r="M27" s="95" t="n">
         <v>-3.91</v>
       </c>
-      <c r="P27" s="94" t="n">
+      <c r="N27" s="95" t="n">
         <v>-2.74</v>
       </c>
-      <c r="Q27" s="94" t="n">
+      <c r="O27" s="95" t="n">
         <v>-2.68</v>
       </c>
-      <c r="R27" s="94" t="n">
+      <c r="P27" s="95" t="n">
         <v>-0.89</v>
       </c>
-      <c r="S27" s="94" t="n">
+      <c r="Q27" s="95" t="n">
         <v>-0.38</v>
       </c>
-      <c r="T27" s="94" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="U27" s="94" t="n">
+      <c r="R27" s="95" t="n">
         <v>0.9</v>
       </c>
-      <c r="V27" s="94" t="n">
+      <c r="S27" s="95" t="n">
         <v>1.13</v>
       </c>
-      <c r="W27" s="94" t="n">
+      <c r="T27" s="95" t="n">
         <v>1.93</v>
       </c>
-      <c r="X27" s="94" t="n">
+      <c r="U27" s="95" t="n">
         <v>0.65</v>
       </c>
-      <c r="Y27" s="94" t="n">
+      <c r="V27" s="95" t="n">
         <v>0.8</v>
       </c>
-      <c r="Z27" s="94" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AA27" s="94" t="n">
+      <c r="W27" s="95" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB27" s="94" t="n">
+      <c r="X27" s="95" t="n">
         <v>0.44</v>
       </c>
-      <c r="AC27" s="94" t="n">
+      <c r="Y27" s="95" t="n">
         <v>-0.35</v>
       </c>
-      <c r="AD27" s="94" t="n">
+      <c r="Z27" s="95" t="n">
         <v>-0.73</v>
       </c>
-      <c r="AE27" s="94" t="n">
-        <v/>
+      <c r="AA27" s="95" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB27" s="95" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="AC27" s="95" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="AD27" s="95" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="AE27" s="95" t="n">
+        <v>-4.11</v>
       </c>
     </row>
     <row r="28">
@@ -9413,95 +9439,95 @@
           <t>ixic:RNG120</t>
         </is>
       </c>
-      <c r="B28" s="94" t="n">
+      <c r="B28" s="95" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="C28" s="95" t="n">
         <v>15.35</v>
       </c>
-      <c r="C28" s="94" t="n">
-        <v>15.35</v>
-      </c>
-      <c r="D28" s="94" t="n">
+      <c r="D28" s="95" t="n">
         <v>17.65</v>
       </c>
-      <c r="E28" s="94" t="n">
+      <c r="E28" s="95" t="n">
         <v>16.57</v>
       </c>
-      <c r="F28" s="94" t="n">
+      <c r="F28" s="95" t="n">
         <v>17.88</v>
       </c>
-      <c r="G28" s="94" t="n">
+      <c r="G28" s="95" t="n">
         <v>18.71</v>
       </c>
-      <c r="H28" s="94" t="n">
-        <v>18.71</v>
-      </c>
-      <c r="I28" s="94" t="n">
+      <c r="H28" s="95" t="n">
         <v>19.63</v>
       </c>
-      <c r="J28" s="94" t="n">
+      <c r="I28" s="95" t="n">
         <v>17.24</v>
       </c>
-      <c r="K28" s="94" t="n">
+      <c r="J28" s="95" t="n">
         <v>15.94</v>
       </c>
-      <c r="L28" s="94" t="n">
+      <c r="K28" s="95" t="n">
         <v>12.98</v>
       </c>
-      <c r="M28" s="94" t="n">
+      <c r="L28" s="95" t="n">
         <v>14.18</v>
       </c>
-      <c r="N28" s="94" t="n">
-        <v>14.18</v>
-      </c>
-      <c r="O28" s="94" t="n">
+      <c r="M28" s="95" t="n">
         <v>10.78</v>
       </c>
-      <c r="P28" s="94" t="n">
+      <c r="N28" s="95" t="n">
         <v>9.02</v>
       </c>
-      <c r="Q28" s="94" t="n">
+      <c r="O28" s="95" t="n">
         <v>10.76</v>
       </c>
-      <c r="R28" s="94" t="n">
+      <c r="P28" s="95" t="n">
         <v>11.54</v>
       </c>
-      <c r="S28" s="94" t="n">
+      <c r="Q28" s="95" t="n">
         <v>11.48</v>
       </c>
-      <c r="T28" s="94" t="n">
-        <v>11.48</v>
-      </c>
-      <c r="U28" s="94" t="n">
+      <c r="R28" s="95" t="n">
         <v>11.95</v>
       </c>
-      <c r="V28" s="94" t="n">
+      <c r="S28" s="95" t="n">
         <v>12.67</v>
       </c>
-      <c r="W28" s="94" t="n">
+      <c r="T28" s="95" t="n">
         <v>11.04</v>
       </c>
-      <c r="X28" s="94" t="n">
+      <c r="U28" s="95" t="n">
         <v>10.68</v>
       </c>
-      <c r="Y28" s="94" t="n">
+      <c r="V28" s="95" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="Z28" s="94" t="n">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="AA28" s="94" t="n">
+      <c r="W28" s="95" t="n">
         <v>9.98</v>
       </c>
-      <c r="AB28" s="94" t="n">
+      <c r="X28" s="95" t="n">
         <v>7.16</v>
       </c>
-      <c r="AC28" s="94" t="n">
+      <c r="Y28" s="95" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="AD28" s="94" t="n">
+      <c r="Z28" s="95" t="n">
         <v>7.37</v>
       </c>
-      <c r="AE28" s="94" t="n">
-        <v/>
+      <c r="AA28" s="95" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="AB28" s="95" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="AC28" s="95" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="AD28" s="95" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="AE28" s="95" t="n">
+        <v>4.85</v>
       </c>
     </row>
     <row r="29">
@@ -9510,95 +9536,95 @@
           <t>ixic:RS2</t>
         </is>
       </c>
-      <c r="B29" s="94" t="n">
+      <c r="B29" s="95" t="n">
+        <v>85.89</v>
+      </c>
+      <c r="C29" s="95" t="n">
         <v>55.65</v>
       </c>
-      <c r="C29" s="94" t="n">
-        <v>55.65</v>
-      </c>
-      <c r="D29" s="94" t="n">
+      <c r="D29" s="95" t="n">
         <v>52.8</v>
       </c>
-      <c r="E29" s="94" t="n">
+      <c r="E29" s="95" t="n">
         <v>36.8</v>
       </c>
-      <c r="F29" s="94" t="n">
+      <c r="F29" s="95" t="n">
         <v>95.84</v>
       </c>
-      <c r="G29" s="94" t="n">
+      <c r="G29" s="95" t="n">
         <v>86.79000000000001</v>
       </c>
-      <c r="H29" s="94" t="n">
-        <v>86.79000000000001</v>
-      </c>
-      <c r="I29" s="94" t="n">
+      <c r="H29" s="95" t="n">
         <v>77.45999999999999</v>
       </c>
-      <c r="J29" s="94" t="n">
+      <c r="I29" s="95" t="n">
         <v>82.01000000000001</v>
       </c>
-      <c r="K29" s="94" t="n">
+      <c r="J29" s="95" t="n">
         <v>72.98999999999999</v>
       </c>
-      <c r="L29" s="94" t="n">
+      <c r="K29" s="95" t="n">
         <v>32.92</v>
       </c>
-      <c r="M29" s="94" t="n">
+      <c r="L29" s="95" t="n">
         <v>85.03</v>
       </c>
-      <c r="N29" s="94" t="n">
-        <v>85.03</v>
-      </c>
-      <c r="O29" s="94" t="n">
+      <c r="M29" s="95" t="n">
         <v>20.54</v>
       </c>
-      <c r="P29" s="94" t="n">
+      <c r="N29" s="95" t="n">
         <v>21.97</v>
       </c>
-      <c r="Q29" s="94" t="n">
+      <c r="O29" s="95" t="n">
         <v>15.42</v>
       </c>
-      <c r="R29" s="94" t="n">
+      <c r="P29" s="95" t="n">
         <v>74.7</v>
       </c>
-      <c r="S29" s="94" t="n">
+      <c r="Q29" s="95" t="n">
         <v>51.35</v>
       </c>
-      <c r="T29" s="94" t="n">
-        <v>51.35</v>
-      </c>
-      <c r="U29" s="94" t="n">
+      <c r="R29" s="95" t="n">
         <v>96.66</v>
       </c>
-      <c r="V29" s="94" t="n">
+      <c r="S29" s="95" t="n">
         <v>89.75</v>
       </c>
-      <c r="W29" s="94" t="n">
+      <c r="T29" s="95" t="n">
         <v>88.93000000000001</v>
       </c>
-      <c r="X29" s="94" t="n">
+      <c r="U29" s="95" t="n">
         <v>77.02</v>
       </c>
-      <c r="Y29" s="94" t="n">
+      <c r="V29" s="95" t="n">
         <v>73.3</v>
       </c>
-      <c r="Z29" s="94" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="AA29" s="94" t="n">
+      <c r="W29" s="95" t="n">
         <v>92.18000000000001</v>
       </c>
-      <c r="AB29" s="94" t="n">
+      <c r="X29" s="95" t="n">
         <v>42.32</v>
       </c>
-      <c r="AC29" s="94" t="n">
+      <c r="Y29" s="95" t="n">
         <v>70.06</v>
       </c>
-      <c r="AD29" s="94" t="n">
+      <c r="Z29" s="95" t="n">
         <v>61.86</v>
       </c>
-      <c r="AE29" s="94" t="n">
-        <v/>
+      <c r="AA29" s="95" t="n">
+        <v>95.17</v>
+      </c>
+      <c r="AB29" s="95" t="n">
+        <v>92.73999999999999</v>
+      </c>
+      <c r="AC29" s="95" t="n">
+        <v>88.20999999999999</v>
+      </c>
+      <c r="AD29" s="95" t="n">
+        <v>65.19</v>
+      </c>
+      <c r="AE29" s="95" t="n">
+        <v>44.48</v>
       </c>
     </row>
     <row r="30">
@@ -9612,7 +9638,7 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="C30" s="95" t="inlineStr">
+      <c r="C30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -9637,123 +9663,125 @@
           <t>red</t>
         </is>
       </c>
-      <c r="H30" s="92" t="inlineStr">
+      <c r="H30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I30" s="91" t="inlineStr">
+      <c r="L30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J30" s="91" t="inlineStr">
+      <c r="M30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K30" s="91" t="inlineStr">
+      <c r="N30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L30" s="92" t="inlineStr">
+      <c r="P30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M30" s="91" t="inlineStr">
+      <c r="R30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N30" s="91" t="inlineStr">
+      <c r="Y30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O30" s="91" t="inlineStr">
+      <c r="Z30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P30" s="95" t="inlineStr">
+      <c r="AA30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AB30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AC30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE30" s="91" t="n">
-        <v/>
+      <c r="AD30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -9762,95 +9790,95 @@
           <t>jp225:RNG60</t>
         </is>
       </c>
-      <c r="B31" s="94" t="n">
+      <c r="B31" s="95" t="n">
         <v>-0.44</v>
       </c>
-      <c r="C31" s="94" t="n">
+      <c r="C31" s="95" t="n">
         <v>-1.73</v>
       </c>
-      <c r="D31" s="94" t="n">
+      <c r="D31" s="95" t="n">
         <v>-1.06</v>
       </c>
-      <c r="E31" s="94" t="n">
+      <c r="E31" s="95" t="n">
         <v>-0.38</v>
       </c>
-      <c r="F31" s="94" t="n">
+      <c r="F31" s="95" t="n">
         <v>-1.3</v>
       </c>
-      <c r="G31" s="94" t="n">
+      <c r="G31" s="95" t="n">
         <v>-1.3</v>
       </c>
-      <c r="H31" s="94" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="I31" s="94" t="n">
+      <c r="H31" s="95" t="n">
         <v>-4.18</v>
       </c>
-      <c r="J31" s="94" t="n">
+      <c r="I31" s="95" t="n">
         <v>-4.84</v>
       </c>
-      <c r="K31" s="94" t="n">
+      <c r="J31" s="95" t="n">
         <v>-5.47</v>
       </c>
-      <c r="L31" s="94" t="n">
+      <c r="K31" s="95" t="n">
         <v>-6.85</v>
       </c>
-      <c r="M31" s="94" t="n">
+      <c r="L31" s="95" t="n">
         <v>-7.64</v>
       </c>
-      <c r="N31" s="94" t="n">
-        <v>-7.64</v>
-      </c>
-      <c r="O31" s="94" t="n">
+      <c r="M31" s="95" t="n">
         <v>-7.28</v>
       </c>
-      <c r="P31" s="94" t="n">
+      <c r="N31" s="95" t="n">
         <v>-7.29</v>
       </c>
-      <c r="Q31" s="94" t="n">
+      <c r="O31" s="95" t="n">
         <v>-5.52</v>
       </c>
-      <c r="R31" s="94" t="n">
+      <c r="P31" s="95" t="n">
         <v>-7.32</v>
       </c>
-      <c r="S31" s="94" t="n">
+      <c r="Q31" s="95" t="n">
         <v>-1.85</v>
       </c>
-      <c r="T31" s="94" t="n">
-        <v>-1.85</v>
-      </c>
-      <c r="U31" s="94" t="n">
+      <c r="R31" s="95" t="n">
         <v>-2.87</v>
       </c>
-      <c r="V31" s="94" t="n">
+      <c r="S31" s="95" t="n">
         <v>-4.44</v>
       </c>
-      <c r="W31" s="94" t="n">
+      <c r="T31" s="95" t="n">
         <v>-4.15</v>
       </c>
-      <c r="X31" s="94" t="n">
+      <c r="U31" s="95" t="n">
         <v>-4.11</v>
       </c>
-      <c r="Y31" s="94" t="n">
+      <c r="V31" s="95" t="n">
         <v>-4.11</v>
       </c>
-      <c r="Z31" s="94" t="n">
-        <v>-4.11</v>
-      </c>
-      <c r="AA31" s="94" t="n">
+      <c r="W31" s="95" t="n">
         <v>-6.33</v>
       </c>
-      <c r="AB31" s="94" t="n">
+      <c r="X31" s="95" t="n">
         <v>-7.13</v>
       </c>
-      <c r="AC31" s="94" t="n">
+      <c r="Y31" s="95" t="n">
         <v>-6.7</v>
       </c>
-      <c r="AD31" s="94" t="n">
+      <c r="Z31" s="95" t="n">
         <v>-5.28</v>
       </c>
-      <c r="AE31" s="94" t="n">
-        <v/>
+      <c r="AA31" s="95" t="n">
+        <v>-5.31</v>
+      </c>
+      <c r="AB31" s="95" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AC31" s="95" t="n">
+        <v>-7.44</v>
+      </c>
+      <c r="AD31" s="95" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="AE31" s="95" t="n">
+        <v>-6.7</v>
       </c>
     </row>
     <row r="32">
@@ -9859,95 +9887,95 @@
           <t>jp225:RNG120</t>
         </is>
       </c>
-      <c r="B32" s="94" t="n">
+      <c r="B32" s="95" t="n">
         <v>3.6</v>
       </c>
-      <c r="C32" s="94" t="n">
+      <c r="C32" s="95" t="n">
         <v>1.17</v>
       </c>
-      <c r="D32" s="94" t="n">
+      <c r="D32" s="95" t="n">
         <v>4.34</v>
       </c>
-      <c r="E32" s="94" t="n">
+      <c r="E32" s="95" t="n">
         <v>6.6</v>
       </c>
-      <c r="F32" s="94" t="n">
+      <c r="F32" s="95" t="n">
         <v>6.85</v>
       </c>
-      <c r="G32" s="94" t="n">
+      <c r="G32" s="95" t="n">
         <v>6.85</v>
       </c>
-      <c r="H32" s="94" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="I32" s="94" t="n">
+      <c r="H32" s="95" t="n">
         <v>3.42</v>
       </c>
-      <c r="J32" s="94" t="n">
+      <c r="I32" s="95" t="n">
         <v>3.47</v>
       </c>
-      <c r="K32" s="94" t="n">
+      <c r="J32" s="95" t="n">
         <v>1.21</v>
       </c>
-      <c r="L32" s="94" t="n">
+      <c r="K32" s="95" t="n">
         <v>0.25</v>
       </c>
-      <c r="M32" s="94" t="n">
+      <c r="L32" s="95" t="n">
         <v>-2.25</v>
       </c>
-      <c r="N32" s="94" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="O32" s="94" t="n">
+      <c r="M32" s="95" t="n">
         <v>-2.26</v>
       </c>
-      <c r="P32" s="94" t="n">
+      <c r="N32" s="95" t="n">
         <v>-4.48</v>
       </c>
-      <c r="Q32" s="94" t="n">
+      <c r="O32" s="95" t="n">
         <v>-2.82</v>
       </c>
-      <c r="R32" s="94" t="n">
+      <c r="P32" s="95" t="n">
         <v>-3.63</v>
       </c>
-      <c r="S32" s="94" t="n">
+      <c r="Q32" s="95" t="n">
         <v>2.15</v>
       </c>
-      <c r="T32" s="94" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U32" s="94" t="n">
+      <c r="R32" s="95" t="n">
         <v>-2.13</v>
       </c>
-      <c r="V32" s="94" t="n">
+      <c r="S32" s="95" t="n">
         <v>-4.01</v>
       </c>
-      <c r="W32" s="94" t="n">
+      <c r="T32" s="95" t="n">
         <v>-4.76</v>
       </c>
-      <c r="X32" s="94" t="n">
+      <c r="U32" s="95" t="n">
         <v>-5.22</v>
       </c>
-      <c r="Y32" s="94" t="n">
+      <c r="V32" s="95" t="n">
         <v>-5.22</v>
       </c>
-      <c r="Z32" s="94" t="n">
-        <v>-5.22</v>
-      </c>
-      <c r="AA32" s="94" t="n">
+      <c r="W32" s="95" t="n">
         <v>-7.96</v>
       </c>
-      <c r="AB32" s="94" t="n">
+      <c r="X32" s="95" t="n">
         <v>-9.43</v>
       </c>
-      <c r="AC32" s="94" t="n">
+      <c r="Y32" s="95" t="n">
         <v>-11.19</v>
       </c>
-      <c r="AD32" s="94" t="n">
+      <c r="Z32" s="95" t="n">
         <v>-9.5</v>
       </c>
-      <c r="AE32" s="94" t="n">
-        <v/>
+      <c r="AA32" s="95" t="n">
+        <v>-9.48</v>
+      </c>
+      <c r="AB32" s="95" t="n">
+        <v>-9.92</v>
+      </c>
+      <c r="AC32" s="95" t="n">
+        <v>-12.73</v>
+      </c>
+      <c r="AD32" s="95" t="n">
+        <v>-9.609999999999999</v>
+      </c>
+      <c r="AE32" s="95" t="n">
+        <v>-8.869999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -9956,95 +9984,95 @@
           <t>jp225:RS9</t>
         </is>
       </c>
-      <c r="B33" s="94" t="n">
+      <c r="B33" s="95" t="n">
         <v>52.59</v>
       </c>
-      <c r="C33" s="94" t="n">
+      <c r="C33" s="95" t="n">
         <v>51.7</v>
       </c>
-      <c r="D33" s="94" t="n">
+      <c r="D33" s="95" t="n">
         <v>55.18</v>
       </c>
-      <c r="E33" s="94" t="n">
+      <c r="E33" s="95" t="n">
         <v>65.89</v>
       </c>
-      <c r="F33" s="94" t="n">
+      <c r="F33" s="95" t="n">
         <v>63.24</v>
       </c>
-      <c r="G33" s="94" t="n">
+      <c r="G33" s="95" t="n">
         <v>63.24</v>
       </c>
-      <c r="H33" s="94" t="n">
-        <v>63.24</v>
-      </c>
-      <c r="I33" s="94" t="n">
+      <c r="H33" s="95" t="n">
         <v>61.28</v>
       </c>
-      <c r="J33" s="94" t="n">
+      <c r="I33" s="95" t="n">
         <v>60.41</v>
       </c>
-      <c r="K33" s="94" t="n">
+      <c r="J33" s="95" t="n">
         <v>57.64</v>
       </c>
-      <c r="L33" s="94" t="n">
+      <c r="K33" s="95" t="n">
         <v>62.13</v>
       </c>
-      <c r="M33" s="94" t="n">
+      <c r="L33" s="95" t="n">
         <v>56.86</v>
       </c>
-      <c r="N33" s="94" t="n">
-        <v>56.86</v>
-      </c>
-      <c r="O33" s="94" t="n">
+      <c r="M33" s="95" t="n">
         <v>56.21</v>
       </c>
-      <c r="P33" s="94" t="n">
+      <c r="N33" s="95" t="n">
         <v>50.28</v>
       </c>
-      <c r="Q33" s="94" t="n">
+      <c r="O33" s="95" t="n">
         <v>58.22</v>
       </c>
-      <c r="R33" s="94" t="n">
+      <c r="P33" s="95" t="n">
         <v>52.42</v>
       </c>
-      <c r="S33" s="94" t="n">
+      <c r="Q33" s="95" t="n">
         <v>77.31</v>
       </c>
-      <c r="T33" s="94" t="n">
-        <v>77.31</v>
-      </c>
-      <c r="U33" s="94" t="n">
+      <c r="R33" s="95" t="n">
         <v>71.64</v>
       </c>
-      <c r="V33" s="94" t="n">
+      <c r="S33" s="95" t="n">
         <v>61.74</v>
       </c>
-      <c r="W33" s="94" t="n">
+      <c r="T33" s="95" t="n">
         <v>63.04</v>
       </c>
-      <c r="X33" s="94" t="n">
+      <c r="U33" s="95" t="n">
         <v>60.77</v>
       </c>
-      <c r="Y33" s="94" t="n">
+      <c r="V33" s="95" t="n">
         <v>60.77</v>
       </c>
-      <c r="Z33" s="94" t="n">
-        <v>60.77</v>
-      </c>
-      <c r="AA33" s="94" t="n">
+      <c r="W33" s="95" t="n">
         <v>54.21</v>
       </c>
-      <c r="AB33" s="94" t="n">
+      <c r="X33" s="95" t="n">
         <v>42.56</v>
       </c>
-      <c r="AC33" s="94" t="n">
+      <c r="Y33" s="95" t="n">
         <v>39.44</v>
       </c>
-      <c r="AD33" s="94" t="n">
+      <c r="Z33" s="95" t="n">
         <v>43.68</v>
       </c>
-      <c r="AE33" s="94" t="n">
-        <v/>
+      <c r="AA33" s="95" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="AB33" s="95" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="AC33" s="95" t="n">
+        <v>26.47</v>
+      </c>
+      <c r="AD33" s="95" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="AE33" s="95" t="n">
+        <v>31.7</v>
       </c>
     </row>
     <row r="34">
@@ -10063,7 +10091,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="D34" s="95" t="inlineStr">
+      <c r="D34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -10093,113 +10121,115 @@
           <t>red</t>
         </is>
       </c>
-      <c r="J34" s="92" t="inlineStr">
+      <c r="J34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K34" s="95" t="inlineStr">
+      <c r="R34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Z34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L34" s="95" t="inlineStr">
+      <c r="AA34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M34" s="95" t="inlineStr">
+      <c r="AB34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N34" s="95" t="inlineStr">
+      <c r="AC34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O34" s="95" t="inlineStr">
+      <c r="AD34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD34" s="95" t="inlineStr">
+      <c r="AE34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
-      </c>
-      <c r="AE34" s="91" t="n">
-        <v/>
       </c>
     </row>
     <row r="35">
@@ -10208,95 +10238,95 @@
           <t>vn:RNG60</t>
         </is>
       </c>
-      <c r="B35" s="94" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="C35" s="94" t="n">
+      <c r="B35" s="95" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="C35" s="95" t="n">
         <v>4.44</v>
       </c>
-      <c r="D35" s="94" t="n">
+      <c r="D35" s="95" t="n">
         <v>1.98</v>
       </c>
-      <c r="E35" s="94" t="n">
+      <c r="E35" s="95" t="n">
         <v>1.29</v>
       </c>
-      <c r="F35" s="94" t="n">
+      <c r="F35" s="95" t="n">
         <v>0.93</v>
       </c>
-      <c r="G35" s="94" t="n">
+      <c r="G35" s="95" t="n">
         <v>1.56</v>
       </c>
-      <c r="H35" s="94" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="I35" s="94" t="n">
+      <c r="H35" s="95" t="n">
         <v>0.4</v>
       </c>
-      <c r="J35" s="94" t="n">
+      <c r="I35" s="95" t="n">
         <v>0.16</v>
       </c>
-      <c r="K35" s="94" t="n">
+      <c r="J35" s="95" t="n">
         <v>-0.68</v>
       </c>
-      <c r="L35" s="94" t="n">
+      <c r="K35" s="95" t="n">
         <v>-1.08</v>
       </c>
-      <c r="M35" s="94" t="n">
+      <c r="L35" s="95" t="n">
         <v>-1.19</v>
       </c>
-      <c r="N35" s="94" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="O35" s="94" t="n">
+      <c r="M35" s="95" t="n">
         <v>-1.21</v>
       </c>
-      <c r="P35" s="94" t="n">
+      <c r="N35" s="95" t="n">
         <v>0.33</v>
       </c>
-      <c r="Q35" s="94" t="n">
+      <c r="O35" s="95" t="n">
         <v>0.71</v>
       </c>
-      <c r="R35" s="94" t="n">
+      <c r="P35" s="95" t="n">
         <v>0.63</v>
       </c>
-      <c r="S35" s="94" t="n">
+      <c r="Q35" s="95" t="n">
         <v>1.1</v>
       </c>
-      <c r="T35" s="94" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="U35" s="94" t="n">
+      <c r="R35" s="95" t="n">
         <v>1.71</v>
       </c>
-      <c r="V35" s="94" t="n">
+      <c r="S35" s="95" t="n">
         <v>2.62</v>
       </c>
-      <c r="W35" s="94" t="n">
+      <c r="T35" s="95" t="n">
         <v>1.79</v>
       </c>
-      <c r="X35" s="94" t="n">
+      <c r="U35" s="95" t="n">
         <v>1.86</v>
       </c>
-      <c r="Y35" s="94" t="n">
+      <c r="V35" s="95" t="n">
         <v>1.03</v>
       </c>
-      <c r="Z35" s="94" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AA35" s="94" t="n">
+      <c r="W35" s="95" t="n">
         <v>0.8</v>
       </c>
-      <c r="AB35" s="94" t="n">
+      <c r="X35" s="95" t="n">
         <v>0.66</v>
       </c>
-      <c r="AC35" s="94" t="n">
+      <c r="Y35" s="95" t="n">
         <v>0.39</v>
       </c>
-      <c r="AD35" s="94" t="n">
+      <c r="Z35" s="95" t="n">
         <v>-3.34</v>
       </c>
-      <c r="AE35" s="94" t="n">
-        <v/>
+      <c r="AA35" s="95" t="n">
+        <v>-2.39</v>
+      </c>
+      <c r="AB35" s="95" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="AC35" s="95" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="AD35" s="95" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="AE35" s="95" t="n">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="36">
@@ -10305,95 +10335,95 @@
           <t>vn:RNG120</t>
         </is>
       </c>
-      <c r="B36" s="94" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="C36" s="94" t="n">
+      <c r="B36" s="95" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="C36" s="95" t="n">
         <v>6.37</v>
       </c>
-      <c r="D36" s="94" t="n">
+      <c r="D36" s="95" t="n">
         <v>6.18</v>
       </c>
-      <c r="E36" s="94" t="n">
+      <c r="E36" s="95" t="n">
         <v>6.26</v>
       </c>
-      <c r="F36" s="94" t="n">
+      <c r="F36" s="95" t="n">
         <v>9.25</v>
       </c>
-      <c r="G36" s="94" t="n">
+      <c r="G36" s="95" t="n">
         <v>8.25</v>
       </c>
-      <c r="H36" s="94" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="I36" s="94" t="n">
+      <c r="H36" s="95" t="n">
         <v>9.49</v>
       </c>
-      <c r="J36" s="94" t="n">
+      <c r="I36" s="95" t="n">
         <v>7.45</v>
       </c>
-      <c r="K36" s="94" t="n">
+      <c r="J36" s="95" t="n">
         <v>4.63</v>
       </c>
-      <c r="L36" s="94" t="n">
+      <c r="K36" s="95" t="n">
         <v>4.38</v>
       </c>
-      <c r="M36" s="94" t="n">
+      <c r="L36" s="95" t="n">
         <v>-0.47</v>
       </c>
-      <c r="N36" s="94" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="O36" s="94" t="n">
+      <c r="M36" s="95" t="n">
         <v>1.58</v>
       </c>
-      <c r="P36" s="94" t="n">
+      <c r="N36" s="95" t="n">
         <v>2.33</v>
       </c>
-      <c r="Q36" s="94" t="n">
+      <c r="O36" s="95" t="n">
         <v>2.33</v>
       </c>
-      <c r="R36" s="94" t="n">
+      <c r="P36" s="95" t="n">
         <v>3.01</v>
       </c>
-      <c r="S36" s="94" t="n">
+      <c r="Q36" s="95" t="n">
         <v>2.85</v>
       </c>
-      <c r="T36" s="94" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U36" s="94" t="n">
+      <c r="R36" s="95" t="n">
         <v>1.83</v>
       </c>
-      <c r="V36" s="94" t="n">
+      <c r="S36" s="95" t="n">
         <v>1.26</v>
       </c>
-      <c r="W36" s="94" t="n">
+      <c r="T36" s="95" t="n">
         <v>-0.78</v>
       </c>
-      <c r="X36" s="94" t="n">
+      <c r="U36" s="95" t="n">
         <v>-1.02</v>
       </c>
-      <c r="Y36" s="94" t="n">
+      <c r="V36" s="95" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="Z36" s="94" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="AA36" s="94" t="n">
+      <c r="W36" s="95" t="n">
         <v>-1.47</v>
       </c>
-      <c r="AB36" s="94" t="n">
+      <c r="X36" s="95" t="n">
         <v>-1.42</v>
       </c>
-      <c r="AC36" s="94" t="n">
+      <c r="Y36" s="95" t="n">
         <v>-1.81</v>
       </c>
-      <c r="AD36" s="94" t="n">
+      <c r="Z36" s="95" t="n">
         <v>-2.26</v>
       </c>
-      <c r="AE36" s="94" t="n">
-        <v/>
+      <c r="AA36" s="95" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="AB36" s="95" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="AC36" s="95" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="AD36" s="95" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AE36" s="95" t="n">
+        <v>1.94</v>
       </c>
     </row>
     <row r="37">
@@ -10402,95 +10432,95 @@
           <t>vn:RS3</t>
         </is>
       </c>
-      <c r="B37" s="94" t="n">
-        <v>64.73999999999999</v>
-      </c>
-      <c r="C37" s="94" t="n">
+      <c r="B37" s="95" t="n">
+        <v>60</v>
+      </c>
+      <c r="C37" s="95" t="n">
         <v>67.03</v>
       </c>
-      <c r="D37" s="94" t="n">
+      <c r="D37" s="95" t="n">
         <v>31.47</v>
       </c>
-      <c r="E37" s="94" t="n">
+      <c r="E37" s="95" t="n">
         <v>37.61</v>
       </c>
-      <c r="F37" s="94" t="n">
+      <c r="F37" s="95" t="n">
         <v>65.76000000000001</v>
       </c>
-      <c r="G37" s="94" t="n">
+      <c r="G37" s="95" t="n">
         <v>81.64</v>
       </c>
-      <c r="H37" s="94" t="n">
-        <v>81.64</v>
-      </c>
-      <c r="I37" s="94" t="n">
+      <c r="H37" s="95" t="n">
         <v>78.16</v>
       </c>
-      <c r="J37" s="94" t="n">
+      <c r="I37" s="95" t="n">
         <v>69.63</v>
       </c>
-      <c r="K37" s="94" t="n">
+      <c r="J37" s="95" t="n">
         <v>29.45</v>
       </c>
-      <c r="L37" s="94" t="n">
+      <c r="K37" s="95" t="n">
         <v>13.62</v>
       </c>
-      <c r="M37" s="94" t="n">
+      <c r="L37" s="95" t="n">
         <v>14.32</v>
       </c>
-      <c r="N37" s="94" t="n">
-        <v>14.32</v>
-      </c>
-      <c r="O37" s="94" t="n">
+      <c r="M37" s="95" t="n">
         <v>23.23</v>
       </c>
-      <c r="P37" s="94" t="n">
+      <c r="N37" s="95" t="n">
         <v>50.34</v>
       </c>
-      <c r="Q37" s="94" t="n">
+      <c r="O37" s="95" t="n">
         <v>77.23999999999999</v>
       </c>
-      <c r="R37" s="94" t="n">
+      <c r="P37" s="95" t="n">
         <v>65.09</v>
       </c>
-      <c r="S37" s="94" t="n">
+      <c r="Q37" s="95" t="n">
         <v>86.66</v>
       </c>
-      <c r="T37" s="94" t="n">
-        <v>86.66</v>
-      </c>
-      <c r="U37" s="94" t="n">
+      <c r="R37" s="95" t="n">
         <v>90.48999999999999</v>
       </c>
-      <c r="V37" s="94" t="n">
+      <c r="S37" s="95" t="n">
         <v>88</v>
       </c>
-      <c r="W37" s="94" t="n">
+      <c r="T37" s="95" t="n">
         <v>77.98</v>
       </c>
-      <c r="X37" s="94" t="n">
+      <c r="U37" s="95" t="n">
         <v>59.82</v>
       </c>
-      <c r="Y37" s="94" t="n">
+      <c r="V37" s="95" t="n">
         <v>77.68000000000001</v>
       </c>
-      <c r="Z37" s="94" t="n">
-        <v>77.68000000000001</v>
-      </c>
-      <c r="AA37" s="94" t="n">
+      <c r="W37" s="95" t="n">
         <v>76.68000000000001</v>
       </c>
-      <c r="AB37" s="94" t="n">
+      <c r="X37" s="95" t="n">
         <v>68.98</v>
       </c>
-      <c r="AC37" s="94" t="n">
+      <c r="Y37" s="95" t="n">
         <v>60.96</v>
       </c>
-      <c r="AD37" s="94" t="n">
+      <c r="Z37" s="95" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="AE37" s="94" t="n">
-        <v/>
+      <c r="AA37" s="95" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="AB37" s="95" t="n">
+        <v>30.12</v>
+      </c>
+      <c r="AC37" s="95" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="AD37" s="95" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="AE37" s="95" t="n">
+        <v>28.44</v>
       </c>
     </row>
     <row r="38">
@@ -10534,118 +10564,120 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="I38" s="91" t="inlineStr">
+      <c r="I38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J38" s="95" t="inlineStr">
+      <c r="O38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AC38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K38" s="95" t="inlineStr">
+      <c r="AD38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AE38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
-      </c>
-      <c r="L38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="M38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="O38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="P38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE38" s="91" t="n">
-        <v/>
       </c>
     </row>
     <row r="39">
@@ -10654,95 +10686,95 @@
           <t>sensex:RNG60</t>
         </is>
       </c>
-      <c r="B39" s="94" t="n">
+      <c r="B39" s="95" t="n">
         <v>1.48</v>
       </c>
-      <c r="C39" s="94" t="n">
+      <c r="C39" s="95" t="n">
         <v>1.07</v>
       </c>
-      <c r="D39" s="94" t="n">
+      <c r="D39" s="95" t="n">
         <v>1.33</v>
       </c>
-      <c r="E39" s="94" t="n">
+      <c r="E39" s="95" t="n">
         <v>1.64</v>
       </c>
-      <c r="F39" s="94" t="n">
+      <c r="F39" s="95" t="n">
         <v>1.7</v>
       </c>
-      <c r="G39" s="94" t="n">
+      <c r="G39" s="95" t="n">
         <v>0.05</v>
       </c>
-      <c r="H39" s="94" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I39" s="94" t="n">
+      <c r="H39" s="95" t="n">
         <v>1.11</v>
       </c>
-      <c r="J39" s="94" t="n">
+      <c r="I39" s="95" t="n">
         <v>0.99</v>
       </c>
-      <c r="K39" s="94" t="n">
+      <c r="J39" s="95" t="n">
         <v>1.39</v>
       </c>
-      <c r="L39" s="94" t="n">
+      <c r="K39" s="95" t="n">
         <v>1.44</v>
       </c>
-      <c r="M39" s="94" t="n">
+      <c r="L39" s="95" t="n">
         <v>2.21</v>
       </c>
-      <c r="N39" s="94" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="O39" s="94" t="n">
+      <c r="M39" s="95" t="n">
         <v>2.67</v>
       </c>
-      <c r="P39" s="94" t="n">
+      <c r="N39" s="95" t="n">
         <v>5.39</v>
       </c>
-      <c r="Q39" s="94" t="n">
+      <c r="O39" s="95" t="n">
         <v>5.39</v>
       </c>
-      <c r="R39" s="94" t="n">
+      <c r="P39" s="95" t="n">
         <v>5.38</v>
       </c>
-      <c r="S39" s="94" t="n">
+      <c r="Q39" s="95" t="n">
         <v>6.9</v>
       </c>
-      <c r="T39" s="94" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="U39" s="94" t="n">
+      <c r="R39" s="95" t="n">
         <v>7.31</v>
       </c>
-      <c r="V39" s="94" t="n">
+      <c r="S39" s="95" t="n">
         <v>7.21</v>
       </c>
-      <c r="W39" s="94" t="n">
+      <c r="T39" s="95" t="n">
         <v>6.84</v>
       </c>
-      <c r="X39" s="94" t="n">
+      <c r="U39" s="95" t="n">
         <v>7.46</v>
       </c>
-      <c r="Y39" s="94" t="n">
+      <c r="V39" s="95" t="n">
         <v>6.69</v>
       </c>
-      <c r="Z39" s="94" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="AA39" s="94" t="n">
+      <c r="W39" s="95" t="n">
         <v>5.73</v>
       </c>
-      <c r="AB39" s="94" t="n">
+      <c r="X39" s="95" t="n">
         <v>6.27</v>
       </c>
-      <c r="AC39" s="94" t="n">
+      <c r="Y39" s="95" t="n">
         <v>7.42</v>
       </c>
-      <c r="AD39" s="94" t="n">
+      <c r="Z39" s="95" t="n">
         <v>7.48</v>
       </c>
-      <c r="AE39" s="94" t="n">
-        <v/>
+      <c r="AA39" s="95" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="AB39" s="95" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="AC39" s="95" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="AD39" s="95" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AE39" s="95" t="n">
+        <v>6.18</v>
       </c>
     </row>
     <row r="40">
@@ -10751,95 +10783,95 @@
           <t>sensex:RNG120</t>
         </is>
       </c>
-      <c r="B40" s="94" t="n">
+      <c r="B40" s="95" t="n">
         <v>8.779999999999999</v>
       </c>
-      <c r="C40" s="94" t="n">
+      <c r="C40" s="95" t="n">
         <v>9.869999999999999</v>
       </c>
-      <c r="D40" s="94" t="n">
+      <c r="D40" s="95" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="E40" s="94" t="n">
+      <c r="E40" s="95" t="n">
         <v>10.79</v>
       </c>
-      <c r="F40" s="94" t="n">
+      <c r="F40" s="95" t="n">
         <v>11.17</v>
       </c>
-      <c r="G40" s="94" t="n">
+      <c r="G40" s="95" t="n">
         <v>10.5</v>
       </c>
-      <c r="H40" s="94" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I40" s="94" t="n">
+      <c r="H40" s="95" t="n">
         <v>11.66</v>
       </c>
-      <c r="J40" s="94" t="n">
+      <c r="I40" s="95" t="n">
         <v>12.39</v>
       </c>
-      <c r="K40" s="94" t="n">
+      <c r="J40" s="95" t="n">
         <v>11.91</v>
       </c>
-      <c r="L40" s="94" t="n">
+      <c r="K40" s="95" t="n">
         <v>10.42</v>
       </c>
-      <c r="M40" s="94" t="n">
+      <c r="L40" s="95" t="n">
         <v>10.03</v>
       </c>
-      <c r="N40" s="94" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="O40" s="94" t="n">
+      <c r="M40" s="95" t="n">
         <v>9.94</v>
       </c>
-      <c r="P40" s="94" t="n">
+      <c r="N40" s="95" t="n">
         <v>12.83</v>
       </c>
-      <c r="Q40" s="94" t="n">
+      <c r="O40" s="95" t="n">
         <v>12.83</v>
       </c>
-      <c r="R40" s="94" t="n">
+      <c r="P40" s="95" t="n">
         <v>12.79</v>
       </c>
-      <c r="S40" s="94" t="n">
+      <c r="Q40" s="95" t="n">
         <v>15.25</v>
       </c>
-      <c r="T40" s="94" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="U40" s="94" t="n">
+      <c r="R40" s="95" t="n">
         <v>15.64</v>
       </c>
-      <c r="V40" s="94" t="n">
+      <c r="S40" s="95" t="n">
         <v>15.29</v>
       </c>
-      <c r="W40" s="94" t="n">
+      <c r="T40" s="95" t="n">
         <v>14.9</v>
       </c>
-      <c r="X40" s="94" t="n">
+      <c r="U40" s="95" t="n">
         <v>14.75</v>
       </c>
-      <c r="Y40" s="94" t="n">
+      <c r="V40" s="95" t="n">
         <v>14.79</v>
       </c>
-      <c r="Z40" s="94" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="AA40" s="94" t="n">
+      <c r="W40" s="95" t="n">
         <v>13.96</v>
       </c>
-      <c r="AB40" s="94" t="n">
+      <c r="X40" s="95" t="n">
         <v>14.46</v>
       </c>
-      <c r="AC40" s="94" t="n">
+      <c r="Y40" s="95" t="n">
         <v>14.07</v>
       </c>
-      <c r="AD40" s="94" t="n">
+      <c r="Z40" s="95" t="n">
         <v>14.24</v>
       </c>
-      <c r="AE40" s="94" t="n">
-        <v/>
+      <c r="AA40" s="95" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AB40" s="95" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="AC40" s="95" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="AD40" s="95" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="AE40" s="95" t="n">
+        <v>11.58</v>
       </c>
     </row>
     <row r="41">
@@ -10848,95 +10880,95 @@
           <t>sensex:RS10</t>
         </is>
       </c>
-      <c r="B41" s="94" t="n">
+      <c r="B41" s="95" t="n">
         <v>38.06</v>
       </c>
-      <c r="C41" s="94" t="n">
+      <c r="C41" s="95" t="n">
         <v>34.73</v>
       </c>
-      <c r="D41" s="94" t="n">
+      <c r="D41" s="95" t="n">
         <v>39.02</v>
       </c>
-      <c r="E41" s="94" t="n">
+      <c r="E41" s="95" t="n">
         <v>42.03</v>
       </c>
-      <c r="F41" s="94" t="n">
+      <c r="F41" s="95" t="n">
         <v>43.48</v>
       </c>
-      <c r="G41" s="94" t="n">
+      <c r="G41" s="95" t="n">
         <v>35.77</v>
       </c>
-      <c r="H41" s="94" t="n">
-        <v>35.77</v>
-      </c>
-      <c r="I41" s="94" t="n">
+      <c r="H41" s="95" t="n">
         <v>37.56</v>
       </c>
-      <c r="J41" s="94" t="n">
+      <c r="I41" s="95" t="n">
         <v>35.74</v>
       </c>
-      <c r="K41" s="94" t="n">
+      <c r="J41" s="95" t="n">
         <v>36.86</v>
       </c>
-      <c r="L41" s="94" t="n">
+      <c r="K41" s="95" t="n">
         <v>29.96</v>
       </c>
-      <c r="M41" s="94" t="n">
+      <c r="L41" s="95" t="n">
         <v>33.56</v>
       </c>
-      <c r="N41" s="94" t="n">
-        <v>33.56</v>
-      </c>
-      <c r="O41" s="94" t="n">
+      <c r="M41" s="95" t="n">
         <v>38.91</v>
       </c>
-      <c r="P41" s="94" t="n">
+      <c r="N41" s="95" t="n">
         <v>56.68</v>
       </c>
-      <c r="Q41" s="94" t="n">
+      <c r="O41" s="95" t="n">
         <v>56.68</v>
       </c>
-      <c r="R41" s="94" t="n">
+      <c r="P41" s="95" t="n">
         <v>57.12</v>
       </c>
-      <c r="S41" s="94" t="n">
+      <c r="Q41" s="95" t="n">
         <v>78.04000000000001</v>
       </c>
-      <c r="T41" s="94" t="n">
-        <v>78.04000000000001</v>
-      </c>
-      <c r="U41" s="94" t="n">
+      <c r="R41" s="95" t="n">
         <v>83.77</v>
       </c>
-      <c r="V41" s="94" t="n">
+      <c r="S41" s="95" t="n">
         <v>80.52</v>
       </c>
-      <c r="W41" s="94" t="n">
+      <c r="T41" s="95" t="n">
         <v>79.08</v>
       </c>
-      <c r="X41" s="94" t="n">
+      <c r="U41" s="95" t="n">
         <v>79.38</v>
       </c>
-      <c r="Y41" s="94" t="n">
+      <c r="V41" s="95" t="n">
         <v>77.31999999999999</v>
       </c>
-      <c r="Z41" s="94" t="n">
-        <v>77.31999999999999</v>
-      </c>
-      <c r="AA41" s="94" t="n">
+      <c r="W41" s="95" t="n">
         <v>66.75</v>
       </c>
-      <c r="AB41" s="94" t="n">
+      <c r="X41" s="95" t="n">
         <v>64.14</v>
       </c>
-      <c r="AC41" s="94" t="n">
+      <c r="Y41" s="95" t="n">
         <v>66.76000000000001</v>
       </c>
-      <c r="AD41" s="94" t="n">
+      <c r="Z41" s="95" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="AE41" s="94" t="n">
-        <v/>
+      <c r="AA41" s="95" t="n">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="AB41" s="95" t="n">
+        <v>66.14</v>
+      </c>
+      <c r="AC41" s="95" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="AD41" s="95" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="AE41" s="95" t="n">
+        <v>52.02</v>
       </c>
     </row>
     <row r="42">
@@ -10955,12 +10987,12 @@
           <t>red</t>
         </is>
       </c>
-      <c r="D42" s="95" t="inlineStr">
+      <c r="D42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E42" s="95" t="inlineStr">
+      <c r="E42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -10975,123 +11007,125 @@
           <t>red</t>
         </is>
       </c>
-      <c r="H42" s="92" t="inlineStr">
+      <c r="H42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I42" s="95" t="inlineStr">
+      <c r="L42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J42" s="91" t="inlineStr">
+      <c r="M42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="P42" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K42" s="95" t="inlineStr">
+      <c r="Q42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AC42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M42" s="95" t="inlineStr">
+      <c r="AD42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N42" s="95" t="inlineStr">
+      <c r="AE42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
-      </c>
-      <c r="O42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="P42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Q42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="R42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE42" s="91" t="n">
-        <v/>
       </c>
     </row>
     <row r="43">
@@ -11100,95 +11134,95 @@
           <t>fr40:RNG60</t>
         </is>
       </c>
-      <c r="B43" s="94" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="C43" s="94" t="n">
+      <c r="B43" s="95" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="C43" s="95" t="n">
         <v>2.11</v>
       </c>
-      <c r="D43" s="94" t="n">
+      <c r="D43" s="95" t="n">
         <v>-0.29</v>
       </c>
-      <c r="E43" s="94" t="n">
+      <c r="E43" s="95" t="n">
         <v>-1.01</v>
       </c>
-      <c r="F43" s="94" t="n">
+      <c r="F43" s="95" t="n">
         <v>-0.26</v>
       </c>
-      <c r="G43" s="94" t="n">
+      <c r="G43" s="95" t="n">
         <v>0.58</v>
       </c>
-      <c r="H43" s="94" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I43" s="94" t="n">
+      <c r="H43" s="95" t="n">
         <v>-0.59</v>
       </c>
-      <c r="J43" s="94" t="n">
+      <c r="I43" s="95" t="n">
         <v>-0.14</v>
       </c>
-      <c r="K43" s="94" t="n">
+      <c r="J43" s="95" t="n">
         <v>-0.77</v>
       </c>
-      <c r="L43" s="94" t="n">
+      <c r="K43" s="95" t="n">
         <v>-0.74</v>
       </c>
-      <c r="M43" s="94" t="n">
+      <c r="L43" s="95" t="n">
         <v>-2.37</v>
       </c>
-      <c r="N43" s="94" t="n">
-        <v>-2.37</v>
-      </c>
-      <c r="O43" s="94" t="n">
+      <c r="M43" s="95" t="n">
         <v>-1.96</v>
       </c>
-      <c r="P43" s="94" t="n">
+      <c r="N43" s="95" t="n">
         <v>0.05</v>
       </c>
-      <c r="Q43" s="94" t="n">
+      <c r="O43" s="95" t="n">
         <v>0.87</v>
       </c>
-      <c r="R43" s="94" t="n">
+      <c r="P43" s="95" t="n">
         <v>0.11</v>
       </c>
-      <c r="S43" s="94" t="n">
+      <c r="Q43" s="95" t="n">
         <v>1.51</v>
       </c>
-      <c r="T43" s="94" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="U43" s="94" t="n">
+      <c r="R43" s="95" t="n">
         <v>0.6</v>
       </c>
-      <c r="V43" s="94" t="n">
+      <c r="S43" s="95" t="n">
         <v>-0.87</v>
       </c>
-      <c r="W43" s="94" t="n">
+      <c r="T43" s="95" t="n">
         <v>0.87</v>
       </c>
-      <c r="X43" s="94" t="n">
+      <c r="U43" s="95" t="n">
         <v>-0.7</v>
       </c>
-      <c r="Y43" s="94" t="n">
+      <c r="V43" s="95" t="n">
         <v>0.28</v>
       </c>
-      <c r="Z43" s="94" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="AA43" s="94" t="n">
+      <c r="W43" s="95" t="n">
         <v>1.12</v>
       </c>
-      <c r="AB43" s="94" t="n">
+      <c r="X43" s="95" t="n">
         <v>-2.16</v>
       </c>
-      <c r="AC43" s="94" t="n">
+      <c r="Y43" s="95" t="n">
         <v>-2.28</v>
       </c>
-      <c r="AD43" s="94" t="n">
+      <c r="Z43" s="95" t="n">
         <v>-3.34</v>
       </c>
-      <c r="AE43" s="94" t="n">
-        <v/>
+      <c r="AA43" s="95" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="AB43" s="95" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="AC43" s="95" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="AD43" s="95" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="AE43" s="95" t="n">
+        <v>-1.93</v>
       </c>
     </row>
     <row r="44">
@@ -11197,95 +11231,95 @@
           <t>fr40:RNG120</t>
         </is>
       </c>
-      <c r="B44" s="94" t="n">
-        <v>-4.32</v>
-      </c>
-      <c r="C44" s="94" t="n">
+      <c r="B44" s="95" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="C44" s="95" t="n">
         <v>-4.18</v>
       </c>
-      <c r="D44" s="94" t="n">
+      <c r="D44" s="95" t="n">
         <v>-6.17</v>
       </c>
-      <c r="E44" s="94" t="n">
+      <c r="E44" s="95" t="n">
         <v>-6.73</v>
       </c>
-      <c r="F44" s="94" t="n">
+      <c r="F44" s="95" t="n">
         <v>-6.01</v>
       </c>
-      <c r="G44" s="94" t="n">
+      <c r="G44" s="95" t="n">
         <v>-5.47</v>
       </c>
-      <c r="H44" s="94" t="n">
-        <v>-5.47</v>
-      </c>
-      <c r="I44" s="94" t="n">
+      <c r="H44" s="95" t="n">
         <v>-6.8</v>
       </c>
-      <c r="J44" s="94" t="n">
+      <c r="I44" s="95" t="n">
         <v>-6.73</v>
       </c>
-      <c r="K44" s="94" t="n">
+      <c r="J44" s="95" t="n">
         <v>-6.46</v>
       </c>
-      <c r="L44" s="94" t="n">
+      <c r="K44" s="95" t="n">
         <v>-5.56</v>
       </c>
-      <c r="M44" s="94" t="n">
+      <c r="L44" s="95" t="n">
         <v>-6.01</v>
       </c>
-      <c r="N44" s="94" t="n">
+      <c r="M44" s="95" t="n">
+        <v>-6.31</v>
+      </c>
+      <c r="N44" s="95" t="n">
+        <v>-4.48</v>
+      </c>
+      <c r="O44" s="95" t="n">
+        <v>-5.85</v>
+      </c>
+      <c r="P44" s="95" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="Q44" s="95" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="R44" s="95" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="S44" s="95" t="n">
         <v>-6.01</v>
       </c>
-      <c r="O44" s="94" t="n">
-        <v>-6.31</v>
-      </c>
-      <c r="P44" s="94" t="n">
-        <v>-4.48</v>
-      </c>
-      <c r="Q44" s="94" t="n">
-        <v>-5.85</v>
-      </c>
-      <c r="R44" s="94" t="n">
-        <v>-4.68</v>
-      </c>
-      <c r="S44" s="94" t="n">
-        <v>-2.89</v>
-      </c>
-      <c r="T44" s="94" t="n">
-        <v>-2.89</v>
-      </c>
-      <c r="U44" s="94" t="n">
-        <v>-3.77</v>
-      </c>
-      <c r="V44" s="94" t="n">
-        <v>-6.01</v>
-      </c>
-      <c r="W44" s="94" t="n">
+      <c r="T44" s="95" t="n">
         <v>-6.35</v>
       </c>
-      <c r="X44" s="94" t="n">
+      <c r="U44" s="95" t="n">
         <v>-6.86</v>
       </c>
-      <c r="Y44" s="94" t="n">
+      <c r="V44" s="95" t="n">
         <v>-7.99</v>
       </c>
-      <c r="Z44" s="94" t="n">
-        <v>-7.99</v>
-      </c>
-      <c r="AA44" s="94" t="n">
+      <c r="W44" s="95" t="n">
         <v>-6.6</v>
       </c>
-      <c r="AB44" s="94" t="n">
+      <c r="X44" s="95" t="n">
         <v>-8.43</v>
       </c>
-      <c r="AC44" s="94" t="n">
+      <c r="Y44" s="95" t="n">
         <v>-8.75</v>
       </c>
-      <c r="AD44" s="94" t="n">
+      <c r="Z44" s="95" t="n">
         <v>-9.210000000000001</v>
       </c>
-      <c r="AE44" s="94" t="n">
-        <v/>
+      <c r="AA44" s="95" t="n">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="AB44" s="95" t="n">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="AC44" s="95" t="n">
+        <v>-9.26</v>
+      </c>
+      <c r="AD44" s="95" t="n">
+        <v>-9.44</v>
+      </c>
+      <c r="AE44" s="95" t="n">
+        <v>-9.02</v>
       </c>
     </row>
     <row r="45">
@@ -11294,95 +11328,95 @@
           <t>fr40:RS5</t>
         </is>
       </c>
-      <c r="B45" s="94" t="n">
-        <v>61.89</v>
-      </c>
-      <c r="C45" s="94" t="n">
+      <c r="B45" s="95" t="n">
+        <v>61.78</v>
+      </c>
+      <c r="C45" s="95" t="n">
         <v>56.72</v>
       </c>
-      <c r="D45" s="94" t="n">
+      <c r="D45" s="95" t="n">
         <v>35.32</v>
       </c>
-      <c r="E45" s="94" t="n">
+      <c r="E45" s="95" t="n">
         <v>40.56</v>
       </c>
-      <c r="F45" s="94" t="n">
+      <c r="F45" s="95" t="n">
         <v>59.42</v>
       </c>
-      <c r="G45" s="94" t="n">
+      <c r="G45" s="95" t="n">
         <v>54.29</v>
       </c>
-      <c r="H45" s="94" t="n">
-        <v>54.29</v>
-      </c>
-      <c r="I45" s="94" t="n">
+      <c r="H45" s="95" t="n">
         <v>46.1</v>
       </c>
-      <c r="J45" s="94" t="n">
+      <c r="I45" s="95" t="n">
         <v>49.74</v>
       </c>
-      <c r="K45" s="94" t="n">
+      <c r="J45" s="95" t="n">
         <v>42.08</v>
       </c>
-      <c r="L45" s="94" t="n">
+      <c r="K45" s="95" t="n">
         <v>50.81</v>
       </c>
-      <c r="M45" s="94" t="n">
+      <c r="L45" s="95" t="n">
         <v>45.03</v>
       </c>
-      <c r="N45" s="94" t="n">
-        <v>45.03</v>
-      </c>
-      <c r="O45" s="94" t="n">
+      <c r="M45" s="95" t="n">
         <v>33.57</v>
       </c>
-      <c r="P45" s="94" t="n">
+      <c r="N45" s="95" t="n">
         <v>45.48</v>
       </c>
-      <c r="Q45" s="94" t="n">
+      <c r="O45" s="95" t="n">
         <v>44.93</v>
       </c>
-      <c r="R45" s="94" t="n">
+      <c r="P45" s="95" t="n">
         <v>52.35</v>
       </c>
-      <c r="S45" s="94" t="n">
+      <c r="Q45" s="95" t="n">
         <v>78.61</v>
       </c>
-      <c r="T45" s="94" t="n">
-        <v>78.61</v>
-      </c>
-      <c r="U45" s="94" t="n">
+      <c r="R45" s="95" t="n">
         <v>75.48</v>
       </c>
-      <c r="V45" s="94" t="n">
+      <c r="S45" s="95" t="n">
         <v>57.98</v>
       </c>
-      <c r="W45" s="94" t="n">
+      <c r="T45" s="95" t="n">
         <v>66.2</v>
       </c>
-      <c r="X45" s="94" t="n">
+      <c r="U45" s="95" t="n">
         <v>52.83</v>
       </c>
-      <c r="Y45" s="94" t="n">
+      <c r="V45" s="95" t="n">
         <v>51.58</v>
       </c>
-      <c r="Z45" s="94" t="n">
-        <v>51.58</v>
-      </c>
-      <c r="AA45" s="94" t="n">
+      <c r="W45" s="95" t="n">
         <v>74.97</v>
       </c>
-      <c r="AB45" s="94" t="n">
+      <c r="X45" s="95" t="n">
         <v>45.92</v>
       </c>
-      <c r="AC45" s="94" t="n">
+      <c r="Y45" s="95" t="n">
         <v>59.76</v>
       </c>
-      <c r="AD45" s="94" t="n">
+      <c r="Z45" s="95" t="n">
         <v>48.71</v>
       </c>
-      <c r="AE45" s="94" t="n">
-        <v/>
+      <c r="AA45" s="95" t="n">
+        <v>53.61</v>
+      </c>
+      <c r="AB45" s="95" t="n">
+        <v>45.19</v>
+      </c>
+      <c r="AC45" s="95" t="n">
+        <v>32.83</v>
+      </c>
+      <c r="AD45" s="95" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="AE45" s="95" t="n">
+        <v>37.2</v>
       </c>
     </row>
     <row r="46">
@@ -11421,123 +11455,125 @@
           <t>red</t>
         </is>
       </c>
-      <c r="H46" s="92" t="inlineStr">
+      <c r="H46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I46" s="91" t="inlineStr">
+      <c r="J46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J46" s="92" t="inlineStr">
+      <c r="K46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K46" s="91" t="inlineStr">
+      <c r="R46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L46" s="91" t="inlineStr">
+      <c r="T46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O46" s="95" t="inlineStr">
+      <c r="W46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AC46" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE46" s="91" t="n">
-        <v/>
+      <c r="AD46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -11546,95 +11582,95 @@
           <t>dax30:RNG60</t>
         </is>
       </c>
-      <c r="B47" s="94" t="n">
+      <c r="B47" s="95" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="C47" s="95" t="n">
         <v>7.02</v>
       </c>
-      <c r="C47" s="94" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="D47" s="94" t="n">
+      <c r="D47" s="95" t="n">
         <v>5.69</v>
       </c>
-      <c r="E47" s="94" t="n">
+      <c r="E47" s="95" t="n">
         <v>5</v>
       </c>
-      <c r="F47" s="94" t="n">
+      <c r="F47" s="95" t="n">
         <v>5.98</v>
       </c>
-      <c r="G47" s="94" t="n">
+      <c r="G47" s="95" t="n">
         <v>6.61</v>
       </c>
-      <c r="H47" s="94" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="I47" s="94" t="n">
+      <c r="H47" s="95" t="n">
         <v>4.66</v>
       </c>
-      <c r="J47" s="94" t="n">
+      <c r="I47" s="95" t="n">
         <v>4.43</v>
       </c>
-      <c r="K47" s="94" t="n">
+      <c r="J47" s="95" t="n">
         <v>2.96</v>
       </c>
-      <c r="L47" s="94" t="n">
+      <c r="K47" s="95" t="n">
         <v>2.76</v>
       </c>
-      <c r="M47" s="94" t="n">
+      <c r="L47" s="95" t="n">
         <v>1.99</v>
       </c>
-      <c r="N47" s="94" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="O47" s="94" t="n">
+      <c r="M47" s="95" t="n">
         <v>2.59</v>
       </c>
-      <c r="P47" s="94" t="n">
+      <c r="N47" s="95" t="n">
         <v>4.12</v>
       </c>
-      <c r="Q47" s="94" t="n">
+      <c r="O47" s="95" t="n">
         <v>5.36</v>
       </c>
-      <c r="R47" s="94" t="n">
+      <c r="P47" s="95" t="n">
         <v>4.62</v>
       </c>
-      <c r="S47" s="94" t="n">
+      <c r="Q47" s="95" t="n">
         <v>5.4</v>
       </c>
-      <c r="T47" s="94" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="U47" s="94" t="n">
+      <c r="R47" s="95" t="n">
         <v>4.27</v>
       </c>
-      <c r="V47" s="94" t="n">
+      <c r="S47" s="95" t="n">
         <v>2.96</v>
       </c>
-      <c r="W47" s="94" t="n">
+      <c r="T47" s="95" t="n">
         <v>4.58</v>
       </c>
-      <c r="X47" s="94" t="n">
+      <c r="U47" s="95" t="n">
         <v>3.04</v>
       </c>
-      <c r="Y47" s="94" t="n">
+      <c r="V47" s="95" t="n">
         <v>2.66</v>
       </c>
-      <c r="Z47" s="94" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AA47" s="94" t="n">
+      <c r="W47" s="95" t="n">
         <v>4.35</v>
       </c>
-      <c r="AB47" s="94" t="n">
+      <c r="X47" s="95" t="n">
         <v>3.06</v>
       </c>
-      <c r="AC47" s="94" t="n">
+      <c r="Y47" s="95" t="n">
         <v>3.02</v>
       </c>
-      <c r="AD47" s="94" t="n">
+      <c r="Z47" s="95" t="n">
         <v>1.68</v>
       </c>
-      <c r="AE47" s="94" t="n">
-        <v/>
+      <c r="AA47" s="95" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB47" s="95" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC47" s="95" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD47" s="95" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AE47" s="95" t="n">
+        <v>2.08</v>
       </c>
     </row>
     <row r="48">
@@ -11643,95 +11679,95 @@
           <t>dax30:RNG120</t>
         </is>
       </c>
-      <c r="B48" s="94" t="n">
+      <c r="B48" s="95" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="C48" s="95" t="n">
         <v>9.43</v>
       </c>
-      <c r="C48" s="94" t="n">
-        <v>9.43</v>
-      </c>
-      <c r="D48" s="94" t="n">
+      <c r="D48" s="95" t="n">
         <v>8.369999999999999</v>
       </c>
-      <c r="E48" s="94" t="n">
+      <c r="E48" s="95" t="n">
         <v>7.55</v>
       </c>
-      <c r="F48" s="94" t="n">
+      <c r="F48" s="95" t="n">
         <v>7.42</v>
       </c>
-      <c r="G48" s="94" t="n">
+      <c r="G48" s="95" t="n">
         <v>8.130000000000001</v>
       </c>
-      <c r="H48" s="94" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="I48" s="94" t="n">
+      <c r="H48" s="95" t="n">
         <v>6.2</v>
       </c>
-      <c r="J48" s="94" t="n">
+      <c r="I48" s="95" t="n">
         <v>6.16</v>
       </c>
-      <c r="K48" s="94" t="n">
+      <c r="J48" s="95" t="n">
         <v>6.75</v>
       </c>
-      <c r="L48" s="94" t="n">
+      <c r="K48" s="95" t="n">
         <v>7.71</v>
       </c>
-      <c r="M48" s="94" t="n">
+      <c r="L48" s="95" t="n">
         <v>7.2</v>
       </c>
-      <c r="N48" s="94" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O48" s="94" t="n">
+      <c r="M48" s="95" t="n">
         <v>7.01</v>
       </c>
-      <c r="P48" s="94" t="n">
+      <c r="N48" s="95" t="n">
         <v>7.87</v>
       </c>
-      <c r="Q48" s="94" t="n">
+      <c r="O48" s="95" t="n">
         <v>6.58</v>
       </c>
-      <c r="R48" s="94" t="n">
+      <c r="P48" s="95" t="n">
         <v>7.78</v>
       </c>
-      <c r="S48" s="94" t="n">
+      <c r="Q48" s="95" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="T48" s="94" t="n">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="U48" s="94" t="n">
+      <c r="R48" s="95" t="n">
         <v>6.31</v>
       </c>
-      <c r="V48" s="94" t="n">
+      <c r="S48" s="95" t="n">
         <v>4.66</v>
       </c>
-      <c r="W48" s="94" t="n">
+      <c r="T48" s="95" t="n">
         <v>3.7</v>
       </c>
-      <c r="X48" s="94" t="n">
+      <c r="U48" s="95" t="n">
         <v>3.7</v>
       </c>
-      <c r="Y48" s="94" t="n">
+      <c r="V48" s="95" t="n">
         <v>1.72</v>
       </c>
-      <c r="Z48" s="94" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA48" s="94" t="n">
+      <c r="W48" s="95" t="n">
         <v>3.46</v>
       </c>
-      <c r="AB48" s="94" t="n">
+      <c r="X48" s="95" t="n">
         <v>2.34</v>
       </c>
-      <c r="AC48" s="94" t="n">
+      <c r="Y48" s="95" t="n">
         <v>1.26</v>
       </c>
-      <c r="AD48" s="94" t="n">
+      <c r="Z48" s="95" t="n">
         <v>0.84</v>
       </c>
-      <c r="AE48" s="94" t="n">
-        <v/>
+      <c r="AA48" s="95" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB48" s="95" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC48" s="95" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AD48" s="95" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AE48" s="95" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="49">
@@ -11740,95 +11776,95 @@
           <t>dax30:RS6</t>
         </is>
       </c>
-      <c r="B49" s="94" t="n">
+      <c r="B49" s="95" t="n">
+        <v>76.53</v>
+      </c>
+      <c r="C49" s="95" t="n">
         <v>73.2</v>
       </c>
-      <c r="C49" s="94" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="D49" s="94" t="n">
+      <c r="D49" s="95" t="n">
         <v>64.68000000000001</v>
       </c>
-      <c r="E49" s="94" t="n">
+      <c r="E49" s="95" t="n">
         <v>71.38</v>
       </c>
-      <c r="F49" s="94" t="n">
+      <c r="F49" s="95" t="n">
         <v>74.03</v>
       </c>
-      <c r="G49" s="94" t="n">
+      <c r="G49" s="95" t="n">
         <v>68.01000000000001</v>
       </c>
-      <c r="H49" s="94" t="n">
-        <v>68.01000000000001</v>
-      </c>
-      <c r="I49" s="94" t="n">
+      <c r="H49" s="95" t="n">
         <v>58.26</v>
       </c>
-      <c r="J49" s="94" t="n">
+      <c r="I49" s="95" t="n">
         <v>62.55</v>
       </c>
-      <c r="K49" s="94" t="n">
+      <c r="J49" s="95" t="n">
         <v>49.18</v>
       </c>
-      <c r="L49" s="94" t="n">
+      <c r="K49" s="95" t="n">
         <v>52.29</v>
       </c>
-      <c r="M49" s="94" t="n">
+      <c r="L49" s="95" t="n">
         <v>53.55</v>
       </c>
-      <c r="N49" s="94" t="n">
-        <v>53.55</v>
-      </c>
-      <c r="O49" s="94" t="n">
+      <c r="M49" s="95" t="n">
         <v>46.86</v>
       </c>
-      <c r="P49" s="94" t="n">
+      <c r="N49" s="95" t="n">
         <v>56.45</v>
       </c>
-      <c r="Q49" s="94" t="n">
+      <c r="O49" s="95" t="n">
         <v>59.76</v>
       </c>
-      <c r="R49" s="94" t="n">
+      <c r="P49" s="95" t="n">
         <v>67.34999999999999</v>
       </c>
-      <c r="S49" s="94" t="n">
+      <c r="Q49" s="95" t="n">
         <v>78.38</v>
       </c>
-      <c r="T49" s="94" t="n">
-        <v>78.38</v>
-      </c>
-      <c r="U49" s="94" t="n">
+      <c r="R49" s="95" t="n">
         <v>72.42</v>
       </c>
-      <c r="V49" s="94" t="n">
+      <c r="S49" s="95" t="n">
         <v>59.91</v>
       </c>
-      <c r="W49" s="94" t="n">
+      <c r="T49" s="95" t="n">
         <v>66</v>
       </c>
-      <c r="X49" s="94" t="n">
+      <c r="U49" s="95" t="n">
         <v>59.4</v>
       </c>
-      <c r="Y49" s="94" t="n">
+      <c r="V49" s="95" t="n">
         <v>52.95</v>
       </c>
-      <c r="Z49" s="94" t="n">
-        <v>52.95</v>
-      </c>
-      <c r="AA49" s="94" t="n">
+      <c r="W49" s="95" t="n">
         <v>75.06999999999999</v>
       </c>
-      <c r="AB49" s="94" t="n">
+      <c r="X49" s="95" t="n">
         <v>61.14</v>
       </c>
-      <c r="AC49" s="94" t="n">
+      <c r="Y49" s="95" t="n">
         <v>62.6</v>
       </c>
-      <c r="AD49" s="94" t="n">
+      <c r="Z49" s="95" t="n">
         <v>57.16</v>
       </c>
-      <c r="AE49" s="94" t="n">
-        <v/>
+      <c r="AA49" s="95" t="n">
+        <v>62.56</v>
+      </c>
+      <c r="AB49" s="95" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="AC49" s="95" t="n">
+        <v>37.42</v>
+      </c>
+      <c r="AD49" s="95" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="AE49" s="95" t="n">
+        <v>40.38</v>
       </c>
     </row>
     <row r="51">

--- a/report_2410.xlsx
+++ b/report_2410.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.13</v>
+        <v>7.14</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.12</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.12</v>
+        <v>0.29</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.3</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.13</v>
+        <v>0.3</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>-0.14</v>
@@ -8283,9 +8283,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C18" s="92" t="inlineStr">
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="B19" s="93" t="n">
-        <v>8.619999999999999</v>
+        <v>7.23</v>
       </c>
       <c r="C19" s="93" t="n">
         <v>8.619999999999999</v>
@@ -8538,7 +8538,7 @@
         </is>
       </c>
       <c r="B20" s="93" t="n">
-        <v>14.63</v>
+        <v>16.25</v>
       </c>
       <c r="C20" s="93" t="n">
         <v>14.63</v>
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="B21" s="93" t="n">
-        <v>84.39</v>
+        <v>55.4</v>
       </c>
       <c r="C21" s="93" t="n">
         <v>84.39</v>
@@ -8731,9 +8731,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C22" s="92" t="inlineStr">
@@ -8889,7 +8889,7 @@
         </is>
       </c>
       <c r="B23" s="93" t="n">
-        <v>8.369999999999999</v>
+        <v>5.77</v>
       </c>
       <c r="C23" s="93" t="n">
         <v>8.369999999999999</v>
@@ -8986,7 +8986,7 @@
         </is>
       </c>
       <c r="B24" s="93" t="n">
-        <v>12.74</v>
+        <v>13.53</v>
       </c>
       <c r="C24" s="93" t="n">
         <v>12.74</v>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="B25" s="93" t="n">
-        <v>78.72</v>
+        <v>40.25</v>
       </c>
       <c r="C25" s="93" t="n">
         <v>78.72</v>
@@ -9337,7 +9337,7 @@
         </is>
       </c>
       <c r="B27" s="93" t="n">
-        <v>7.61</v>
+        <v>6.81</v>
       </c>
       <c r="C27" s="93" t="n">
         <v>7.61</v>
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="B28" s="93" t="n">
-        <v>15.68</v>
+        <v>18.41</v>
       </c>
       <c r="C28" s="93" t="n">
         <v>15.68</v>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="B29" s="93" t="n">
-        <v>85.89</v>
+        <v>91.14</v>
       </c>
       <c r="C29" s="93" t="n">
         <v>85.89</v>
@@ -10075,9 +10075,9 @@
           <t>vn:EIDE</t>
         </is>
       </c>
-      <c r="B34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B34" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C34" s="92" t="inlineStr">
@@ -10233,7 +10233,7 @@
         </is>
       </c>
       <c r="B35" s="93" t="n">
-        <v>4.4</v>
+        <v>3.78</v>
       </c>
       <c r="C35" s="93" t="n">
         <v>3.79</v>
@@ -10330,7 +10330,7 @@
         </is>
       </c>
       <c r="B36" s="93" t="n">
-        <v>5.44</v>
+        <v>4.81</v>
       </c>
       <c r="C36" s="93" t="n">
         <v>5.68</v>
@@ -10427,7 +10427,7 @@
         </is>
       </c>
       <c r="B37" s="93" t="n">
-        <v>69.05</v>
+        <v>32.52</v>
       </c>
       <c r="C37" s="93" t="n">
         <v>60</v>
@@ -10971,9 +10971,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B42" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C42" s="92" t="inlineStr">
@@ -11129,7 +11129,7 @@
         </is>
       </c>
       <c r="B43" s="93" t="n">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="C43" s="93" t="n">
         <v>1.27</v>
@@ -11226,7 +11226,7 @@
         </is>
       </c>
       <c r="B44" s="93" t="n">
-        <v>-5.3</v>
+        <v>-5.76</v>
       </c>
       <c r="C44" s="93" t="n">
         <v>-4.33</v>
@@ -11323,7 +11323,7 @@
         </is>
       </c>
       <c r="B45" s="93" t="n">
-        <v>51.44</v>
+        <v>44.69</v>
       </c>
       <c r="C45" s="93" t="n">
         <v>61.78</v>
@@ -11577,7 +11577,7 @@
         </is>
       </c>
       <c r="B47" s="93" t="n">
-        <v>6.42</v>
+        <v>6.23</v>
       </c>
       <c r="C47" s="93" t="n">
         <v>6.73</v>
@@ -11674,7 +11674,7 @@
         </is>
       </c>
       <c r="B48" s="93" t="n">
-        <v>7.27</v>
+        <v>7.08</v>
       </c>
       <c r="C48" s="93" t="n">
         <v>9.25</v>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="B49" s="93" t="n">
-        <v>57.72</v>
+        <v>54.82</v>
       </c>
       <c r="C49" s="93" t="n">
         <v>76.53</v>

--- a/report_2410.xlsx
+++ b/report_2410.xlsx
@@ -1060,9 +1060,9 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.14</v>
+        <v>7.13</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.14</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.3</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.31</v>
@@ -6352,142 +6352,142 @@
       </c>
       <c r="D1" s="77" t="inlineStr">
         <is>
-          <t>241020</t>
+          <t>241018</t>
         </is>
       </c>
       <c r="E1" s="77" t="inlineStr">
         <is>
-          <t>241018</t>
+          <t>241017</t>
         </is>
       </c>
       <c r="F1" s="77" t="inlineStr">
         <is>
-          <t>241017</t>
+          <t>241016</t>
         </is>
       </c>
       <c r="G1" s="77" t="inlineStr">
         <is>
-          <t>241016</t>
+          <t>241015</t>
         </is>
       </c>
       <c r="H1" s="77" t="inlineStr">
         <is>
-          <t>241015</t>
+          <t>241014</t>
         </is>
       </c>
       <c r="I1" s="77" t="inlineStr">
         <is>
-          <t>241014</t>
+          <t>241011</t>
         </is>
       </c>
       <c r="J1" s="77" t="inlineStr">
         <is>
-          <t>241013</t>
+          <t>241010</t>
         </is>
       </c>
       <c r="K1" s="77" t="inlineStr">
         <is>
-          <t>241011</t>
+          <t>241009</t>
         </is>
       </c>
       <c r="L1" s="77" t="inlineStr">
         <is>
-          <t>241010</t>
+          <t>241008</t>
         </is>
       </c>
       <c r="M1" s="77" t="inlineStr">
         <is>
-          <t>241009</t>
+          <t>241007</t>
         </is>
       </c>
       <c r="N1" s="77" t="inlineStr">
         <is>
-          <t>241008</t>
+          <t>241004</t>
         </is>
       </c>
       <c r="O1" s="77" t="inlineStr">
         <is>
-          <t>241007</t>
+          <t>241003</t>
         </is>
       </c>
       <c r="P1" s="77" t="inlineStr">
         <is>
-          <t>241006</t>
+          <t>241002</t>
         </is>
       </c>
       <c r="Q1" s="77" t="inlineStr">
         <is>
-          <t>241004</t>
+          <t>241001</t>
         </is>
       </c>
       <c r="R1" s="77" t="inlineStr">
         <is>
-          <t>241003</t>
+          <t>240930</t>
         </is>
       </c>
       <c r="S1" s="77" t="inlineStr">
         <is>
-          <t>241002</t>
+          <t>240927</t>
         </is>
       </c>
       <c r="T1" s="77" t="inlineStr">
         <is>
-          <t>241001</t>
+          <t>240926</t>
         </is>
       </c>
       <c r="U1" s="77" t="inlineStr">
         <is>
-          <t>240930</t>
+          <t>240925</t>
         </is>
       </c>
       <c r="V1" s="77" t="inlineStr">
         <is>
-          <t>240929</t>
+          <t>240924</t>
         </is>
       </c>
       <c r="W1" s="77" t="inlineStr">
         <is>
-          <t>240927</t>
+          <t>240923</t>
         </is>
       </c>
       <c r="X1" s="77" t="inlineStr">
         <is>
-          <t>240926</t>
+          <t>240920</t>
         </is>
       </c>
       <c r="Y1" s="77" t="inlineStr">
         <is>
-          <t>240925</t>
+          <t>240919</t>
         </is>
       </c>
       <c r="Z1" s="77" t="inlineStr">
         <is>
-          <t>240924</t>
+          <t>240918</t>
         </is>
       </c>
       <c r="AA1" s="77" t="inlineStr">
         <is>
-          <t>240923</t>
+          <t>240917</t>
         </is>
       </c>
       <c r="AB1" s="77" t="inlineStr">
         <is>
-          <t>240922</t>
+          <t>240916</t>
         </is>
       </c>
       <c r="AC1" s="77" t="inlineStr">
         <is>
-          <t>240920</t>
+          <t>240913</t>
         </is>
       </c>
       <c r="AD1" s="77" t="inlineStr">
         <is>
-          <t>240919</t>
+          <t>240912</t>
         </is>
       </c>
       <c r="AE1" s="77" t="inlineStr">
         <is>
-          <t>240918</t>
+          <t>240911</t>
         </is>
       </c>
     </row>
@@ -6547,202 +6547,202 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="L2" s="91" t="inlineStr">
+      <c r="L2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M2" s="91" t="inlineStr">
+      <c r="X2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA2" s="91" t="inlineStr">
+      <c r="Y2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB2" s="91" t="inlineStr">
+      <c r="Z2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="AA2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="93" t="inlineStr">
+      <c r="A3" s="94" t="inlineStr">
         <is>
           <t>sh:RNG60</t>
         </is>
       </c>
-      <c r="B3" s="94" t="n">
+      <c r="B3" s="95" t="n">
         <v>10.18</v>
       </c>
-      <c r="C3" s="94" t="n">
+      <c r="C3" s="95" t="n">
         <v>9.77</v>
       </c>
-      <c r="D3" s="94" t="n">
+      <c r="D3" s="95" t="n">
         <v>10.08</v>
       </c>
-      <c r="E3" s="94" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="F3" s="94" t="n">
+      <c r="E3" s="95" t="n">
         <v>6.49</v>
       </c>
-      <c r="G3" s="94" t="n">
+      <c r="F3" s="95" t="n">
         <v>7.7</v>
       </c>
-      <c r="H3" s="94" t="n">
+      <c r="G3" s="95" t="n">
         <v>7.74</v>
       </c>
-      <c r="I3" s="94" t="n">
+      <c r="H3" s="95" t="n">
         <v>10.57</v>
       </c>
-      <c r="J3" s="94" t="n">
+      <c r="I3" s="95" t="n">
         <v>9.470000000000001</v>
       </c>
-      <c r="K3" s="94" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="L3" s="94" t="n">
+      <c r="J3" s="95" t="n">
         <v>11.58</v>
       </c>
-      <c r="M3" s="94" t="n">
+      <c r="K3" s="95" t="n">
         <v>11.51</v>
       </c>
-      <c r="N3" s="94" t="n">
+      <c r="L3" s="95" t="n">
         <v>18.3</v>
       </c>
-      <c r="O3" s="94" t="n">
+      <c r="M3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="P3" s="94" t="n">
+      <c r="N3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="Q3" s="94" t="n">
+      <c r="O3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="R3" s="94" t="n">
+      <c r="P3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="S3" s="94" t="n">
+      <c r="Q3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="T3" s="94" t="n">
+      <c r="R3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="U3" s="94" t="n">
-        <v>12.81</v>
-      </c>
-      <c r="V3" s="94" t="n">
+      <c r="S3" s="95" t="n">
         <v>3.53</v>
       </c>
-      <c r="W3" s="94" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="X3" s="94" t="n">
+      <c r="T3" s="95" t="n">
         <v>0.13</v>
       </c>
-      <c r="Y3" s="94" t="n">
+      <c r="U3" s="95" t="n">
         <v>-3.29</v>
       </c>
-      <c r="Z3" s="94" t="n">
+      <c r="V3" s="95" t="n">
         <v>-3.51</v>
       </c>
-      <c r="AA3" s="94" t="n">
+      <c r="W3" s="95" t="n">
         <v>-6.68</v>
       </c>
-      <c r="AB3" s="94" t="n">
+      <c r="X3" s="95" t="n">
         <v>-7.93</v>
       </c>
-      <c r="AC3" s="94" t="n">
-        <v>-7.93</v>
-      </c>
-      <c r="AD3" s="94" t="n">
+      <c r="Y3" s="95" t="n">
         <v>-7.25</v>
       </c>
-      <c r="AE3" s="94" t="n">
+      <c r="Z3" s="95" t="n">
         <v>-8.300000000000001</v>
+      </c>
+      <c r="AA3" s="95" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="AB3" s="95" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="AC3" s="95" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="AD3" s="95" t="n">
+        <v>-9.59</v>
+      </c>
+      <c r="AE3" s="95" t="n">
+        <v>-9.82</v>
       </c>
     </row>
     <row r="4">
@@ -6751,192 +6751,192 @@
           <t>sh:RNG120</t>
         </is>
       </c>
-      <c r="B4" s="94" t="n">
+      <c r="B4" s="95" t="n">
         <v>7.92</v>
       </c>
-      <c r="C4" s="94" t="n">
+      <c r="C4" s="95" t="n">
         <v>6.62</v>
       </c>
-      <c r="D4" s="94" t="n">
+      <c r="D4" s="95" t="n">
         <v>6.09</v>
       </c>
-      <c r="E4" s="94" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="F4" s="94" t="n">
+      <c r="E4" s="95" t="n">
         <v>3.19</v>
       </c>
-      <c r="G4" s="94" t="n">
+      <c r="F4" s="95" t="n">
         <v>6.51</v>
       </c>
-      <c r="H4" s="94" t="n">
+      <c r="G4" s="95" t="n">
         <v>4.71</v>
       </c>
-      <c r="I4" s="94" t="n">
+      <c r="H4" s="95" t="n">
         <v>8.77</v>
       </c>
-      <c r="J4" s="94" t="n">
+      <c r="I4" s="95" t="n">
         <v>6.05</v>
       </c>
-      <c r="K4" s="94" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="L4" s="94" t="n">
+      <c r="J4" s="95" t="n">
         <v>9.07</v>
       </c>
-      <c r="M4" s="94" t="n">
+      <c r="K4" s="95" t="n">
         <v>6.9</v>
       </c>
-      <c r="N4" s="94" t="n">
+      <c r="L4" s="95" t="n">
         <v>14.53</v>
       </c>
-      <c r="O4" s="94" t="n">
+      <c r="M4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="P4" s="94" t="n">
+      <c r="N4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="Q4" s="94" t="n">
+      <c r="O4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="R4" s="94" t="n">
+      <c r="P4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="S4" s="94" t="n">
+      <c r="Q4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="T4" s="94" t="n">
+      <c r="R4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="U4" s="94" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="V4" s="94" t="n">
+      <c r="S4" s="95" t="n">
         <v>0.41</v>
       </c>
-      <c r="W4" s="94" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="X4" s="94" t="n">
+      <c r="T4" s="95" t="n">
         <v>-2.48</v>
       </c>
-      <c r="Y4" s="94" t="n">
+      <c r="U4" s="95" t="n">
         <v>-4.76</v>
       </c>
-      <c r="Z4" s="94" t="n">
+      <c r="V4" s="95" t="n">
         <v>-4.9</v>
       </c>
-      <c r="AA4" s="94" t="n">
+      <c r="W4" s="95" t="n">
         <v>-8.16</v>
       </c>
-      <c r="AB4" s="94" t="n">
+      <c r="X4" s="95" t="n">
         <v>-9.720000000000001</v>
       </c>
-      <c r="AC4" s="94" t="n">
-        <v>-9.720000000000001</v>
-      </c>
-      <c r="AD4" s="94" t="n">
+      <c r="Y4" s="95" t="n">
         <v>-9.59</v>
       </c>
-      <c r="AE4" s="94" t="n">
+      <c r="Z4" s="95" t="n">
         <v>-10.85</v>
       </c>
+      <c r="AA4" s="95" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="AB4" s="95" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="AC4" s="95" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="AD4" s="95" t="n">
+        <v>-11.77</v>
+      </c>
+      <c r="AE4" s="95" t="n">
+        <v>-11.13</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="93" t="inlineStr">
+      <c r="A5" s="94" t="inlineStr">
         <is>
           <t>sh:RS3</t>
         </is>
       </c>
-      <c r="B5" s="94" t="n">
+      <c r="B5" s="95" t="n">
         <v>71.05</v>
       </c>
-      <c r="C5" s="94" t="n">
+      <c r="C5" s="95" t="n">
         <v>65.47</v>
       </c>
-      <c r="D5" s="94" t="n">
+      <c r="D5" s="95" t="n">
         <v>63.75</v>
       </c>
-      <c r="E5" s="94" t="n">
-        <v>63.75</v>
-      </c>
-      <c r="F5" s="94" t="n">
+      <c r="E5" s="95" t="n">
         <v>32.04</v>
       </c>
-      <c r="G5" s="94" t="n">
+      <c r="F5" s="95" t="n">
         <v>40.69</v>
       </c>
-      <c r="H5" s="94" t="n">
+      <c r="G5" s="95" t="n">
         <v>40.15</v>
       </c>
-      <c r="I5" s="94" t="n">
+      <c r="H5" s="95" t="n">
         <v>57.29</v>
       </c>
-      <c r="J5" s="94" t="n">
+      <c r="I5" s="95" t="n">
         <v>44.67</v>
       </c>
-      <c r="K5" s="94" t="n">
-        <v>44.67</v>
-      </c>
-      <c r="L5" s="94" t="n">
+      <c r="J5" s="95" t="n">
         <v>59.48</v>
       </c>
-      <c r="M5" s="94" t="n">
+      <c r="K5" s="95" t="n">
         <v>54.31</v>
       </c>
-      <c r="N5" s="94" t="n">
+      <c r="L5" s="95" t="n">
         <v>99.84</v>
       </c>
-      <c r="O5" s="94" t="n">
+      <c r="M5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="P5" s="94" t="n">
+      <c r="N5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="Q5" s="94" t="n">
+      <c r="O5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="R5" s="94" t="n">
+      <c r="P5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="S5" s="94" t="n">
+      <c r="Q5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="T5" s="94" t="n">
+      <c r="R5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="U5" s="94" t="n">
-        <v>99.75</v>
-      </c>
-      <c r="V5" s="94" t="n">
+      <c r="S5" s="95" t="n">
         <v>99.31</v>
       </c>
-      <c r="W5" s="94" t="n">
-        <v>99.31</v>
-      </c>
-      <c r="X5" s="94" t="n">
+      <c r="T5" s="95" t="n">
         <v>98.83</v>
       </c>
-      <c r="Y5" s="94" t="n">
+      <c r="U5" s="95" t="n">
         <v>97.34999999999999</v>
       </c>
-      <c r="Z5" s="94" t="n">
+      <c r="V5" s="95" t="n">
         <v>96.38</v>
       </c>
-      <c r="AA5" s="94" t="n">
+      <c r="W5" s="95" t="n">
         <v>77.51000000000001</v>
       </c>
-      <c r="AB5" s="94" t="n">
+      <c r="X5" s="95" t="n">
         <v>64.38</v>
       </c>
-      <c r="AC5" s="94" t="n">
-        <v>64.38</v>
-      </c>
-      <c r="AD5" s="94" t="n">
+      <c r="Y5" s="95" t="n">
         <v>63.45</v>
       </c>
-      <c r="AE5" s="94" t="n">
+      <c r="Z5" s="95" t="n">
         <v>37.85</v>
+      </c>
+      <c r="AA5" s="95" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AB5" s="95" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AC5" s="95" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AD5" s="95" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="AE5" s="95" t="n">
+        <v>12.36</v>
       </c>
     </row>
     <row r="6">
@@ -6960,431 +6960,431 @@
           <t>red</t>
         </is>
       </c>
-      <c r="E6" s="92" t="inlineStr">
+      <c r="E6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F6" s="91" t="inlineStr">
+      <c r="L6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="X6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G6" s="91" t="inlineStr">
+      <c r="Y6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H6" s="91" t="inlineStr">
+      <c r="Z6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I6" s="91" t="inlineStr">
+      <c r="AB6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J6" s="91" t="inlineStr">
+      <c r="AC6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K6" s="91" t="inlineStr">
+      <c r="AD6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L6" s="91" t="inlineStr">
+      <c r="AE6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA6" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE6" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="93" t="inlineStr">
+      <c r="A7" s="94" t="inlineStr">
         <is>
           <t>kc:RNG60</t>
         </is>
       </c>
-      <c r="B7" s="94" t="n">
+      <c r="B7" s="95" t="n">
         <v>31.54</v>
       </c>
-      <c r="C7" s="94" t="n">
+      <c r="C7" s="95" t="n">
         <v>36.03</v>
       </c>
-      <c r="D7" s="94" t="n">
+      <c r="D7" s="95" t="n">
         <v>34.25</v>
       </c>
-      <c r="E7" s="94" t="n">
-        <v>34.25</v>
-      </c>
-      <c r="F7" s="94" t="n">
+      <c r="E7" s="95" t="n">
         <v>20.09</v>
       </c>
-      <c r="G7" s="94" t="n">
+      <c r="F7" s="95" t="n">
         <v>22.33</v>
       </c>
-      <c r="H7" s="94" t="n">
+      <c r="G7" s="95" t="n">
         <v>25.12</v>
       </c>
-      <c r="I7" s="94" t="n">
+      <c r="H7" s="95" t="n">
         <v>28.96</v>
       </c>
-      <c r="J7" s="94" t="n">
+      <c r="I7" s="95" t="n">
         <v>26.54</v>
       </c>
-      <c r="K7" s="94" t="n">
-        <v>26.54</v>
-      </c>
-      <c r="L7" s="94" t="n">
+      <c r="J7" s="95" t="n">
         <v>34.41</v>
       </c>
-      <c r="M7" s="94" t="n">
+      <c r="K7" s="95" t="n">
         <v>44.1</v>
       </c>
-      <c r="N7" s="94" t="n">
+      <c r="L7" s="95" t="n">
         <v>46.52</v>
       </c>
-      <c r="O7" s="94" t="n">
+      <c r="M7" s="95" t="n">
         <v>26.36</v>
       </c>
-      <c r="P7" s="94" t="n">
+      <c r="N7" s="95" t="n">
         <v>26.36</v>
       </c>
-      <c r="Q7" s="94" t="n">
+      <c r="O7" s="95" t="n">
         <v>26.36</v>
       </c>
-      <c r="R7" s="94" t="n">
+      <c r="P7" s="95" t="n">
         <v>26.36</v>
       </c>
-      <c r="S7" s="94" t="n">
+      <c r="Q7" s="95" t="n">
         <v>26.36</v>
       </c>
-      <c r="T7" s="94" t="n">
+      <c r="R7" s="95" t="n">
         <v>26.36</v>
       </c>
-      <c r="U7" s="94" t="n">
-        <v>26.36</v>
-      </c>
-      <c r="V7" s="94" t="n">
+      <c r="S7" s="95" t="n">
         <v>5.45</v>
       </c>
-      <c r="W7" s="94" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="X7" s="94" t="n">
+      <c r="T7" s="95" t="n">
         <v>-0.85</v>
       </c>
-      <c r="Y7" s="94" t="n">
+      <c r="U7" s="95" t="n">
         <v>-5.96</v>
       </c>
-      <c r="Z7" s="94" t="n">
+      <c r="V7" s="95" t="n">
         <v>-6.32</v>
       </c>
-      <c r="AA7" s="94" t="n">
+      <c r="W7" s="95" t="n">
         <v>-10.11</v>
       </c>
-      <c r="AB7" s="94" t="n">
+      <c r="X7" s="95" t="n">
         <v>-11.14</v>
       </c>
-      <c r="AC7" s="94" t="n">
-        <v>-11.14</v>
-      </c>
-      <c r="AD7" s="94" t="n">
+      <c r="Y7" s="95" t="n">
         <v>-9.23</v>
       </c>
-      <c r="AE7" s="94" t="n">
+      <c r="Z7" s="95" t="n">
         <v>-12.41</v>
       </c>
+      <c r="AA7" s="95" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="AB7" s="95" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="AC7" s="95" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="AD7" s="95" t="n">
+        <v>-12.75</v>
+      </c>
+      <c r="AE7" s="95" t="n">
+        <v>-11.62</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="93" t="inlineStr">
+      <c r="A8" s="94" t="inlineStr">
         <is>
           <t>kc:RNG120</t>
         </is>
       </c>
-      <c r="B8" s="94" t="n">
+      <c r="B8" s="95" t="n">
         <v>34.71</v>
       </c>
-      <c r="C8" s="94" t="n">
+      <c r="C8" s="95" t="n">
         <v>36.93</v>
       </c>
-      <c r="D8" s="94" t="n">
+      <c r="D8" s="95" t="n">
         <v>31.24</v>
       </c>
-      <c r="E8" s="94" t="n">
-        <v>31.24</v>
-      </c>
-      <c r="F8" s="94" t="n">
+      <c r="E8" s="95" t="n">
         <v>17.07</v>
       </c>
-      <c r="G8" s="94" t="n">
+      <c r="F8" s="95" t="n">
         <v>19.44</v>
       </c>
-      <c r="H8" s="94" t="n">
+      <c r="G8" s="95" t="n">
         <v>19.7</v>
       </c>
-      <c r="I8" s="94" t="n">
+      <c r="H8" s="95" t="n">
         <v>25.4</v>
       </c>
-      <c r="J8" s="94" t="n">
+      <c r="I8" s="95" t="n">
         <v>21.69</v>
       </c>
-      <c r="K8" s="94" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="L8" s="94" t="n">
+      <c r="J8" s="95" t="n">
         <v>29.69</v>
       </c>
-      <c r="M8" s="94" t="n">
+      <c r="K8" s="95" t="n">
         <v>33.11</v>
       </c>
-      <c r="N8" s="94" t="n">
+      <c r="L8" s="95" t="n">
         <v>38.25</v>
       </c>
-      <c r="O8" s="94" t="n">
+      <c r="M8" s="95" t="n">
         <v>15.28</v>
       </c>
-      <c r="P8" s="94" t="n">
+      <c r="N8" s="95" t="n">
         <v>15.28</v>
       </c>
-      <c r="Q8" s="94" t="n">
+      <c r="O8" s="95" t="n">
         <v>15.28</v>
       </c>
-      <c r="R8" s="94" t="n">
+      <c r="P8" s="95" t="n">
         <v>15.28</v>
       </c>
-      <c r="S8" s="94" t="n">
+      <c r="Q8" s="95" t="n">
         <v>15.28</v>
       </c>
-      <c r="T8" s="94" t="n">
+      <c r="R8" s="95" t="n">
         <v>15.28</v>
       </c>
-      <c r="U8" s="94" t="n">
-        <v>15.28</v>
-      </c>
-      <c r="V8" s="94" t="n">
+      <c r="S8" s="95" t="n">
         <v>-3.74</v>
       </c>
-      <c r="W8" s="94" t="n">
-        <v>-3.74</v>
-      </c>
-      <c r="X8" s="94" t="n">
+      <c r="T8" s="95" t="n">
         <v>-10.62</v>
       </c>
-      <c r="Y8" s="94" t="n">
+      <c r="U8" s="95" t="n">
         <v>-12.51</v>
       </c>
-      <c r="Z8" s="94" t="n">
+      <c r="V8" s="95" t="n">
         <v>-12.61</v>
       </c>
-      <c r="AA8" s="94" t="n">
+      <c r="W8" s="95" t="n">
         <v>-14.58</v>
       </c>
-      <c r="AB8" s="94" t="n">
+      <c r="X8" s="95" t="n">
         <v>-16.03</v>
       </c>
-      <c r="AC8" s="94" t="n">
-        <v>-16.03</v>
-      </c>
-      <c r="AD8" s="94" t="n">
+      <c r="Y8" s="95" t="n">
         <v>-16.65</v>
       </c>
-      <c r="AE8" s="94" t="n">
+      <c r="Z8" s="95" t="n">
         <v>-18.48</v>
       </c>
+      <c r="AA8" s="95" t="n">
+        <v>-18.74</v>
+      </c>
+      <c r="AB8" s="95" t="n">
+        <v>-18.74</v>
+      </c>
+      <c r="AC8" s="95" t="n">
+        <v>-18.74</v>
+      </c>
+      <c r="AD8" s="95" t="n">
+        <v>-19.06</v>
+      </c>
+      <c r="AE8" s="95" t="n">
+        <v>-18.16</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="93" t="inlineStr">
+      <c r="A9" s="94" t="inlineStr">
         <is>
           <t>kc:RS5</t>
         </is>
       </c>
-      <c r="B9" s="94" t="n">
+      <c r="B9" s="95" t="n">
         <v>68.8</v>
       </c>
-      <c r="C9" s="94" t="n">
+      <c r="C9" s="95" t="n">
         <v>74.88</v>
       </c>
-      <c r="D9" s="94" t="n">
+      <c r="D9" s="95" t="n">
         <v>71.91</v>
       </c>
-      <c r="E9" s="94" t="n">
-        <v>71.91</v>
-      </c>
-      <c r="F9" s="94" t="n">
+      <c r="E9" s="95" t="n">
         <v>50.48</v>
       </c>
-      <c r="G9" s="94" t="n">
+      <c r="F9" s="95" t="n">
         <v>49.43</v>
       </c>
-      <c r="H9" s="94" t="n">
+      <c r="G9" s="95" t="n">
         <v>55.91</v>
       </c>
-      <c r="I9" s="94" t="n">
+      <c r="H9" s="95" t="n">
         <v>63.75</v>
       </c>
-      <c r="J9" s="94" t="n">
+      <c r="I9" s="95" t="n">
         <v>59.18</v>
       </c>
-      <c r="K9" s="94" t="n">
-        <v>59.18</v>
-      </c>
-      <c r="L9" s="94" t="n">
+      <c r="J9" s="95" t="n">
         <v>74.52</v>
       </c>
-      <c r="M9" s="94" t="n">
+      <c r="K9" s="95" t="n">
         <v>89.13</v>
       </c>
-      <c r="N9" s="94" t="n">
+      <c r="L9" s="95" t="n">
         <v>98.36</v>
       </c>
-      <c r="O9" s="94" t="n">
+      <c r="M9" s="95" t="n">
         <v>96.84</v>
       </c>
-      <c r="P9" s="94" t="n">
+      <c r="N9" s="95" t="n">
         <v>96.84</v>
       </c>
-      <c r="Q9" s="94" t="n">
+      <c r="O9" s="95" t="n">
         <v>96.84</v>
       </c>
-      <c r="R9" s="94" t="n">
+      <c r="P9" s="95" t="n">
         <v>96.84</v>
       </c>
-      <c r="S9" s="94" t="n">
+      <c r="Q9" s="95" t="n">
         <v>96.84</v>
       </c>
-      <c r="T9" s="94" t="n">
+      <c r="R9" s="95" t="n">
         <v>96.84</v>
       </c>
-      <c r="U9" s="94" t="n">
-        <v>96.84</v>
-      </c>
-      <c r="V9" s="94" t="n">
+      <c r="S9" s="95" t="n">
         <v>91.06999999999999</v>
       </c>
-      <c r="W9" s="94" t="n">
-        <v>91.06999999999999</v>
-      </c>
-      <c r="X9" s="94" t="n">
+      <c r="T9" s="95" t="n">
         <v>81.48999999999999</v>
       </c>
-      <c r="Y9" s="94" t="n">
+      <c r="U9" s="95" t="n">
         <v>64.94</v>
       </c>
-      <c r="Z9" s="94" t="n">
+      <c r="V9" s="95" t="n">
         <v>64.66</v>
       </c>
-      <c r="AA9" s="94" t="n">
+      <c r="W9" s="95" t="n">
         <v>23.69</v>
       </c>
-      <c r="AB9" s="94" t="n">
+      <c r="X9" s="95" t="n">
         <v>29.81</v>
       </c>
-      <c r="AC9" s="94" t="n">
-        <v>29.81</v>
-      </c>
-      <c r="AD9" s="94" t="n">
+      <c r="Y9" s="95" t="n">
         <v>33.91</v>
       </c>
-      <c r="AE9" s="94" t="n">
+      <c r="Z9" s="95" t="n">
         <v>22.82</v>
+      </c>
+      <c r="AA9" s="95" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="AB9" s="95" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="AC9" s="95" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="AD9" s="95" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="AE9" s="95" t="n">
+        <v>42.99</v>
       </c>
     </row>
     <row r="10">
@@ -7408,237 +7408,237 @@
           <t>red</t>
         </is>
       </c>
-      <c r="E10" s="92" t="inlineStr">
+      <c r="E10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F10" s="91" t="inlineStr">
+      <c r="L10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="X10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Y10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G10" s="91" t="inlineStr">
+      <c r="Z10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H10" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="I10" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="J10" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="K10" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="L10" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="M10" s="92" t="inlineStr">
+      <c r="AE10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA10" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB10" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC10" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD10" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE10" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="93" t="inlineStr">
+      <c r="A11" s="94" t="inlineStr">
         <is>
           <t>cy:RNG60</t>
         </is>
       </c>
-      <c r="B11" s="94" t="n">
+      <c r="B11" s="95" t="n">
         <v>28.48</v>
       </c>
-      <c r="C11" s="94" t="n">
+      <c r="C11" s="95" t="n">
         <v>28.68</v>
       </c>
-      <c r="D11" s="94" t="n">
+      <c r="D11" s="95" t="n">
         <v>29.39</v>
       </c>
-      <c r="E11" s="94" t="n">
-        <v>29.39</v>
-      </c>
-      <c r="F11" s="94" t="n">
+      <c r="E11" s="95" t="n">
         <v>19.87</v>
       </c>
-      <c r="G11" s="94" t="n">
+      <c r="F11" s="95" t="n">
         <v>21.93</v>
       </c>
-      <c r="H11" s="94" t="n">
+      <c r="G11" s="95" t="n">
         <v>23.9</v>
       </c>
-      <c r="I11" s="94" t="n">
+      <c r="H11" s="95" t="n">
         <v>27.91</v>
       </c>
-      <c r="J11" s="94" t="n">
+      <c r="I11" s="95" t="n">
         <v>27.24</v>
       </c>
-      <c r="K11" s="94" t="n">
-        <v>27.24</v>
-      </c>
-      <c r="L11" s="94" t="n">
+      <c r="J11" s="95" t="n">
         <v>33.94</v>
       </c>
-      <c r="M11" s="94" t="n">
+      <c r="K11" s="95" t="n">
         <v>39.99</v>
       </c>
-      <c r="N11" s="94" t="n">
+      <c r="L11" s="95" t="n">
         <v>54.04</v>
       </c>
-      <c r="O11" s="94" t="n">
+      <c r="M11" s="95" t="n">
         <v>32.05</v>
       </c>
-      <c r="P11" s="94" t="n">
+      <c r="N11" s="95" t="n">
         <v>32.05</v>
       </c>
-      <c r="Q11" s="94" t="n">
+      <c r="O11" s="95" t="n">
         <v>32.05</v>
       </c>
-      <c r="R11" s="94" t="n">
+      <c r="P11" s="95" t="n">
         <v>32.05</v>
       </c>
-      <c r="S11" s="94" t="n">
+      <c r="Q11" s="95" t="n">
         <v>32.05</v>
       </c>
-      <c r="T11" s="94" t="n">
+      <c r="R11" s="95" t="n">
         <v>32.05</v>
       </c>
-      <c r="U11" s="94" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="V11" s="94" t="n">
+      <c r="S11" s="95" t="n">
         <v>13.58</v>
       </c>
-      <c r="W11" s="94" t="n">
-        <v>13.58</v>
-      </c>
-      <c r="X11" s="94" t="n">
+      <c r="T11" s="95" t="n">
         <v>2.95</v>
       </c>
-      <c r="Y11" s="94" t="n">
+      <c r="U11" s="95" t="n">
         <v>-2.45</v>
       </c>
-      <c r="Z11" s="94" t="n">
+      <c r="V11" s="95" t="n">
         <v>-4.05</v>
       </c>
-      <c r="AA11" s="94" t="n">
+      <c r="W11" s="95" t="n">
         <v>-10.14</v>
       </c>
-      <c r="AB11" s="94" t="n">
+      <c r="X11" s="95" t="n">
         <v>-11.21</v>
       </c>
-      <c r="AC11" s="94" t="n">
-        <v>-11.21</v>
-      </c>
-      <c r="AD11" s="94" t="n">
+      <c r="Y11" s="95" t="n">
         <v>-9.029999999999999</v>
       </c>
-      <c r="AE11" s="94" t="n">
+      <c r="Z11" s="95" t="n">
         <v>-11.44</v>
+      </c>
+      <c r="AA11" s="95" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="AB11" s="95" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="AC11" s="95" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="AD11" s="95" t="n">
+        <v>-11.96</v>
+      </c>
+      <c r="AE11" s="95" t="n">
+        <v>-12.87</v>
       </c>
     </row>
     <row r="12">
@@ -7647,95 +7647,95 @@
           <t>cy:RNG120</t>
         </is>
       </c>
-      <c r="B12" s="94" t="n">
+      <c r="B12" s="95" t="n">
         <v>26.65</v>
       </c>
-      <c r="C12" s="94" t="n">
+      <c r="C12" s="95" t="n">
         <v>25.87</v>
       </c>
-      <c r="D12" s="94" t="n">
+      <c r="D12" s="95" t="n">
         <v>22.8</v>
       </c>
-      <c r="E12" s="94" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="F12" s="94" t="n">
+      <c r="E12" s="95" t="n">
         <v>13.14</v>
       </c>
-      <c r="G12" s="94" t="n">
+      <c r="F12" s="95" t="n">
         <v>15.89</v>
       </c>
-      <c r="H12" s="94" t="n">
+      <c r="G12" s="95" t="n">
         <v>16.18</v>
       </c>
-      <c r="I12" s="94" t="n">
+      <c r="H12" s="95" t="n">
         <v>22.27</v>
       </c>
-      <c r="J12" s="94" t="n">
+      <c r="I12" s="95" t="n">
         <v>17.89</v>
       </c>
-      <c r="K12" s="94" t="n">
-        <v>17.89</v>
-      </c>
-      <c r="L12" s="94" t="n">
+      <c r="J12" s="95" t="n">
         <v>23.63</v>
       </c>
-      <c r="M12" s="94" t="n">
+      <c r="K12" s="95" t="n">
         <v>24.76</v>
       </c>
-      <c r="N12" s="94" t="n">
+      <c r="L12" s="95" t="n">
         <v>41.13</v>
       </c>
-      <c r="O12" s="94" t="n">
+      <c r="M12" s="95" t="n">
         <v>18.19</v>
       </c>
-      <c r="P12" s="94" t="n">
+      <c r="N12" s="95" t="n">
         <v>18.19</v>
       </c>
-      <c r="Q12" s="94" t="n">
+      <c r="O12" s="95" t="n">
         <v>18.19</v>
       </c>
-      <c r="R12" s="94" t="n">
+      <c r="P12" s="95" t="n">
         <v>18.19</v>
       </c>
-      <c r="S12" s="94" t="n">
+      <c r="Q12" s="95" t="n">
         <v>18.19</v>
       </c>
-      <c r="T12" s="94" t="n">
+      <c r="R12" s="95" t="n">
         <v>18.19</v>
       </c>
-      <c r="U12" s="94" t="n">
-        <v>18.19</v>
-      </c>
-      <c r="V12" s="94" t="n">
+      <c r="S12" s="95" t="n">
         <v>1.34</v>
       </c>
-      <c r="W12" s="94" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X12" s="94" t="n">
+      <c r="T12" s="95" t="n">
         <v>-8.44</v>
       </c>
-      <c r="Y12" s="94" t="n">
+      <c r="U12" s="95" t="n">
         <v>-9.720000000000001</v>
       </c>
-      <c r="Z12" s="94" t="n">
+      <c r="V12" s="95" t="n">
         <v>-10.6</v>
       </c>
-      <c r="AA12" s="94" t="n">
+      <c r="W12" s="95" t="n">
         <v>-14.49</v>
       </c>
-      <c r="AB12" s="94" t="n">
+      <c r="X12" s="95" t="n">
         <v>-16.56</v>
       </c>
-      <c r="AC12" s="94" t="n">
-        <v>-16.56</v>
-      </c>
-      <c r="AD12" s="94" t="n">
+      <c r="Y12" s="95" t="n">
         <v>-15.65</v>
       </c>
-      <c r="AE12" s="94" t="n">
+      <c r="Z12" s="95" t="n">
         <v>-17.96</v>
+      </c>
+      <c r="AA12" s="95" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="AB12" s="95" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="AC12" s="95" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="AD12" s="95" t="n">
+        <v>-18.72</v>
+      </c>
+      <c r="AE12" s="95" t="n">
+        <v>-18.28</v>
       </c>
     </row>
     <row r="13">
@@ -7744,95 +7744,95 @@
           <t>cy:RS3</t>
         </is>
       </c>
-      <c r="B13" s="94" t="n">
+      <c r="B13" s="95" t="n">
         <v>74.31</v>
       </c>
-      <c r="C13" s="94" t="n">
+      <c r="C13" s="95" t="n">
         <v>73.05</v>
       </c>
-      <c r="D13" s="94" t="n">
+      <c r="D13" s="95" t="n">
         <v>70.86</v>
       </c>
-      <c r="E13" s="94" t="n">
-        <v>70.86</v>
-      </c>
-      <c r="F13" s="94" t="n">
+      <c r="E13" s="95" t="n">
         <v>31.37</v>
       </c>
-      <c r="G13" s="94" t="n">
+      <c r="F13" s="95" t="n">
         <v>32.55</v>
       </c>
-      <c r="H13" s="94" t="n">
+      <c r="G13" s="95" t="n">
         <v>39.59</v>
       </c>
-      <c r="I13" s="94" t="n">
+      <c r="H13" s="95" t="n">
         <v>50.6</v>
       </c>
-      <c r="J13" s="94" t="n">
+      <c r="I13" s="95" t="n">
         <v>42.18</v>
       </c>
-      <c r="K13" s="94" t="n">
-        <v>42.18</v>
-      </c>
-      <c r="L13" s="94" t="n">
+      <c r="J13" s="95" t="n">
         <v>55.03</v>
       </c>
-      <c r="M13" s="94" t="n">
+      <c r="K13" s="95" t="n">
         <v>62.67</v>
       </c>
-      <c r="N13" s="94" t="n">
+      <c r="L13" s="95" t="n">
         <v>99.77</v>
       </c>
-      <c r="O13" s="94" t="n">
+      <c r="M13" s="95" t="n">
         <v>99.48</v>
       </c>
-      <c r="P13" s="94" t="n">
+      <c r="N13" s="95" t="n">
         <v>99.48</v>
       </c>
-      <c r="Q13" s="94" t="n">
+      <c r="O13" s="95" t="n">
         <v>99.48</v>
       </c>
-      <c r="R13" s="94" t="n">
+      <c r="P13" s="95" t="n">
         <v>99.48</v>
       </c>
-      <c r="S13" s="94" t="n">
+      <c r="Q13" s="95" t="n">
         <v>99.48</v>
       </c>
-      <c r="T13" s="94" t="n">
+      <c r="R13" s="95" t="n">
         <v>99.48</v>
       </c>
-      <c r="U13" s="94" t="n">
-        <v>99.48</v>
-      </c>
-      <c r="V13" s="94" t="n">
+      <c r="S13" s="95" t="n">
         <v>98.62</v>
       </c>
-      <c r="W13" s="94" t="n">
-        <v>98.62</v>
-      </c>
-      <c r="X13" s="94" t="n">
+      <c r="T13" s="95" t="n">
         <v>96</v>
       </c>
-      <c r="Y13" s="94" t="n">
+      <c r="U13" s="95" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="Z13" s="94" t="n">
+      <c r="V13" s="95" t="n">
         <v>88.09</v>
       </c>
-      <c r="AA13" s="94" t="n">
+      <c r="W13" s="95" t="n">
         <v>30.34</v>
       </c>
-      <c r="AB13" s="94" t="n">
+      <c r="X13" s="95" t="n">
         <v>39.51</v>
       </c>
-      <c r="AC13" s="94" t="n">
-        <v>39.51</v>
-      </c>
-      <c r="AD13" s="94" t="n">
+      <c r="Y13" s="95" t="n">
         <v>58.67</v>
       </c>
-      <c r="AE13" s="94" t="n">
+      <c r="Z13" s="95" t="n">
         <v>28.04</v>
+      </c>
+      <c r="AA13" s="95" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="AB13" s="95" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="AC13" s="95" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="AD13" s="95" t="n">
+        <v>54.57</v>
+      </c>
+      <c r="AE13" s="95" t="n">
+        <v>69.45</v>
       </c>
     </row>
     <row r="14">
@@ -7841,12 +7841,12 @@
           <t>hk50:EIDE</t>
         </is>
       </c>
-      <c r="B14" s="95" t="inlineStr">
+      <c r="B14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C14" s="95" t="inlineStr">
+      <c r="C14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -7856,235 +7856,237 @@
           <t>red</t>
         </is>
       </c>
-      <c r="E14" s="92" t="inlineStr">
+      <c r="E14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F14" s="95" t="inlineStr">
+      <c r="N14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AC14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AD14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AE14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G14" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="H14" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="I14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="J14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="K14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="L14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="M14" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE14" s="91" t="n">
-        <v/>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="93" t="inlineStr">
+      <c r="A15" s="94" t="inlineStr">
         <is>
           <t>hk50:RNG60</t>
         </is>
       </c>
-      <c r="B15" s="94" t="n">
+      <c r="B15" s="95" t="n">
         <v>18.42</v>
       </c>
-      <c r="C15" s="94" t="n">
+      <c r="C15" s="95" t="n">
         <v>17.23</v>
       </c>
-      <c r="D15" s="94" t="n">
+      <c r="D15" s="95" t="n">
         <v>17.96</v>
       </c>
-      <c r="E15" s="94" t="n">
+      <c r="E15" s="95" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="F15" s="95" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="G15" s="95" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="H15" s="95" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="I15" s="95" t="n">
         <v>17.96</v>
       </c>
-      <c r="F15" s="94" t="n">
-        <v>15.28</v>
-      </c>
-      <c r="G15" s="94" t="n">
-        <v>14.11</v>
-      </c>
-      <c r="H15" s="94" t="n">
-        <v>14.54</v>
-      </c>
-      <c r="I15" s="94" t="n">
-        <v>18.98</v>
-      </c>
-      <c r="J15" s="94" t="n">
+      <c r="J15" s="95" t="n">
         <v>17.96</v>
       </c>
-      <c r="K15" s="94" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="L15" s="94" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="M15" s="94" t="n">
+      <c r="K15" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="N15" s="94" t="n">
+      <c r="L15" s="95" t="n">
         <v>17.35</v>
       </c>
-      <c r="O15" s="94" t="n">
+      <c r="M15" s="95" t="n">
         <v>32.21</v>
       </c>
-      <c r="P15" s="94" t="n">
+      <c r="N15" s="95" t="n">
         <v>29.75</v>
       </c>
-      <c r="Q15" s="94" t="n">
-        <v>29.75</v>
-      </c>
-      <c r="R15" s="94" t="n">
+      <c r="O15" s="95" t="n">
         <v>26.19</v>
       </c>
-      <c r="S15" s="94" t="n">
+      <c r="P15" s="95" t="n">
         <v>26.09</v>
       </c>
-      <c r="T15" s="94" t="n">
+      <c r="Q15" s="95" t="n">
         <v>17.23</v>
       </c>
-      <c r="U15" s="94" t="n">
+      <c r="R15" s="95" t="n">
         <v>17.23</v>
       </c>
-      <c r="V15" s="94" t="n">
+      <c r="S15" s="95" t="n">
         <v>14.76</v>
       </c>
-      <c r="W15" s="94" t="n">
-        <v>14.76</v>
-      </c>
-      <c r="X15" s="94" t="n">
+      <c r="T15" s="95" t="n">
         <v>12.13</v>
       </c>
-      <c r="Y15" s="94" t="n">
+      <c r="U15" s="95" t="n">
         <v>7.96</v>
       </c>
-      <c r="Z15" s="94" t="n">
+      <c r="V15" s="95" t="n">
         <v>7.25</v>
       </c>
-      <c r="AA15" s="94" t="n">
+      <c r="W15" s="95" t="n">
         <v>0.87</v>
       </c>
-      <c r="AB15" s="94" t="n">
+      <c r="X15" s="95" t="n">
         <v>1.03</v>
       </c>
-      <c r="AC15" s="94" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD15" s="94" t="n">
+      <c r="Y15" s="95" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AE15" s="94" t="n">
-        <v/>
+      <c r="Z15" s="95" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="AA15" s="95" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="AB15" s="95" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="AC15" s="95" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="AD15" s="95" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="AE15" s="95" t="n">
+        <v>-4.61</v>
       </c>
     </row>
     <row r="16">
@@ -8093,95 +8095,95 @@
           <t>hk50:RNG120</t>
         </is>
       </c>
-      <c r="B16" s="94" t="n">
+      <c r="B16" s="95" t="n">
         <v>18.6</v>
       </c>
-      <c r="C16" s="94" t="n">
+      <c r="C16" s="95" t="n">
         <v>19.05</v>
       </c>
-      <c r="D16" s="94" t="n">
+      <c r="D16" s="95" t="n">
         <v>23.62</v>
       </c>
-      <c r="E16" s="94" t="n">
-        <v>23.62</v>
-      </c>
-      <c r="F16" s="94" t="n">
+      <c r="E16" s="95" t="n">
         <v>21.61</v>
       </c>
-      <c r="G16" s="94" t="n">
+      <c r="F16" s="95" t="n">
         <v>25.04</v>
       </c>
-      <c r="H16" s="94" t="n">
+      <c r="G16" s="95" t="n">
         <v>24</v>
       </c>
-      <c r="I16" s="94" t="n">
+      <c r="H16" s="95" t="n">
         <v>29.79</v>
       </c>
-      <c r="J16" s="94" t="n">
+      <c r="I16" s="95" t="n">
         <v>30.79</v>
       </c>
-      <c r="K16" s="94" t="n">
+      <c r="J16" s="95" t="n">
         <v>30.79</v>
       </c>
-      <c r="L16" s="94" t="n">
-        <v>30.79</v>
-      </c>
-      <c r="M16" s="94" t="n">
+      <c r="K16" s="95" t="n">
         <v>24.32</v>
       </c>
-      <c r="N16" s="94" t="n">
+      <c r="L16" s="95" t="n">
         <v>25.15</v>
       </c>
-      <c r="O16" s="94" t="n">
+      <c r="M16" s="95" t="n">
         <v>35.13</v>
       </c>
-      <c r="P16" s="94" t="n">
+      <c r="N16" s="95" t="n">
         <v>32.66</v>
       </c>
-      <c r="Q16" s="94" t="n">
-        <v>32.66</v>
-      </c>
-      <c r="R16" s="94" t="n">
+      <c r="O16" s="95" t="n">
         <v>31.41</v>
       </c>
-      <c r="S16" s="94" t="n">
+      <c r="P16" s="95" t="n">
         <v>34.13</v>
       </c>
-      <c r="T16" s="94" t="n">
+      <c r="Q16" s="95" t="n">
         <v>26.37</v>
       </c>
-      <c r="U16" s="94" t="n">
+      <c r="R16" s="95" t="n">
         <v>26.37</v>
       </c>
-      <c r="V16" s="94" t="n">
+      <c r="S16" s="95" t="n">
         <v>23.36</v>
       </c>
-      <c r="W16" s="94" t="n">
-        <v>23.36</v>
-      </c>
-      <c r="X16" s="94" t="n">
+      <c r="T16" s="95" t="n">
         <v>17.68</v>
       </c>
-      <c r="Y16" s="94" t="n">
+      <c r="U16" s="95" t="n">
         <v>15.64</v>
       </c>
-      <c r="Z16" s="94" t="n">
+      <c r="V16" s="95" t="n">
         <v>15.91</v>
       </c>
-      <c r="AA16" s="94" t="n">
+      <c r="W16" s="95" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AB16" s="94" t="n">
+      <c r="X16" s="95" t="n">
         <v>10.84</v>
       </c>
-      <c r="AC16" s="94" t="n">
-        <v>10.84</v>
-      </c>
-      <c r="AD16" s="94" t="n">
+      <c r="Y16" s="95" t="n">
         <v>9.17</v>
       </c>
-      <c r="AE16" s="94" t="n">
-        <v/>
+      <c r="Z16" s="95" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AA16" s="95" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AB16" s="95" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="AC16" s="95" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AD16" s="95" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AE16" s="95" t="n">
+        <v>2.32</v>
       </c>
     </row>
     <row r="17">
@@ -8190,95 +8192,95 @@
           <t>hk50:RS4</t>
         </is>
       </c>
-      <c r="B17" s="94" t="n">
+      <c r="B17" s="95" t="n">
         <v>45.12</v>
       </c>
-      <c r="C17" s="94" t="n">
+      <c r="C17" s="95" t="n">
         <v>44.29</v>
       </c>
-      <c r="D17" s="94" t="n">
+      <c r="D17" s="95" t="n">
         <v>54</v>
       </c>
-      <c r="E17" s="94" t="n">
-        <v>54</v>
-      </c>
-      <c r="F17" s="94" t="n">
+      <c r="E17" s="95" t="n">
         <v>27.44</v>
       </c>
-      <c r="G17" s="94" t="n">
+      <c r="F17" s="95" t="n">
         <v>31.33</v>
       </c>
-      <c r="H17" s="94" t="n">
+      <c r="G17" s="95" t="n">
         <v>31.85</v>
       </c>
-      <c r="I17" s="94" t="n">
+      <c r="H17" s="95" t="n">
         <v>45.61</v>
       </c>
-      <c r="J17" s="94" t="n">
+      <c r="I17" s="95" t="n">
         <v>48.87</v>
       </c>
-      <c r="K17" s="94" t="n">
+      <c r="J17" s="95" t="n">
         <v>48.87</v>
       </c>
-      <c r="L17" s="94" t="n">
-        <v>48.87</v>
-      </c>
-      <c r="M17" s="94" t="n">
+      <c r="K17" s="95" t="n">
         <v>35.54</v>
       </c>
-      <c r="N17" s="94" t="n">
+      <c r="L17" s="95" t="n">
         <v>39.14</v>
       </c>
-      <c r="O17" s="94" t="n">
+      <c r="M17" s="95" t="n">
         <v>91.23999999999999</v>
       </c>
-      <c r="P17" s="94" t="n">
+      <c r="N17" s="95" t="n">
         <v>89.48999999999999</v>
       </c>
-      <c r="Q17" s="94" t="n">
-        <v>89.48999999999999</v>
-      </c>
-      <c r="R17" s="94" t="n">
+      <c r="O17" s="95" t="n">
         <v>85.84</v>
       </c>
-      <c r="S17" s="94" t="n">
+      <c r="P17" s="95" t="n">
         <v>99.56999999999999</v>
       </c>
-      <c r="T17" s="94" t="n">
+      <c r="Q17" s="95" t="n">
         <v>99.18000000000001</v>
       </c>
-      <c r="U17" s="94" t="n">
+      <c r="R17" s="95" t="n">
         <v>99.18000000000001</v>
       </c>
-      <c r="V17" s="94" t="n">
+      <c r="S17" s="95" t="n">
         <v>98.89</v>
       </c>
-      <c r="W17" s="94" t="n">
-        <v>98.89</v>
-      </c>
-      <c r="X17" s="94" t="n">
+      <c r="T17" s="95" t="n">
         <v>98.23</v>
       </c>
-      <c r="Y17" s="94" t="n">
+      <c r="U17" s="95" t="n">
         <v>96.44</v>
       </c>
-      <c r="Z17" s="94" t="n">
+      <c r="V17" s="95" t="n">
         <v>95.94</v>
       </c>
-      <c r="AA17" s="94" t="n">
+      <c r="W17" s="95" t="n">
         <v>89.48</v>
       </c>
-      <c r="AB17" s="94" t="n">
+      <c r="X17" s="95" t="n">
         <v>91.13</v>
       </c>
-      <c r="AC17" s="94" t="n">
-        <v>91.13</v>
-      </c>
-      <c r="AD17" s="94" t="n">
+      <c r="Y17" s="95" t="n">
         <v>87.39</v>
       </c>
-      <c r="AE17" s="94" t="n">
-        <v/>
+      <c r="Z17" s="95" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="AA17" s="95" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="AB17" s="95" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="AC17" s="95" t="n">
+        <v>54.39</v>
+      </c>
+      <c r="AD17" s="95" t="n">
+        <v>38.93</v>
+      </c>
+      <c r="AE17" s="95" t="n">
+        <v>17.46</v>
       </c>
     </row>
     <row r="18">
@@ -8302,139 +8304,139 @@
           <t>red</t>
         </is>
       </c>
-      <c r="E18" s="92" t="inlineStr">
+      <c r="E18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F18" s="91" t="inlineStr">
+      <c r="G18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G18" s="92" t="inlineStr">
+      <c r="H18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H18" s="91" t="inlineStr">
+      <c r="I18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I18" s="92" t="inlineStr">
+      <c r="P18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J18" s="92" t="inlineStr">
+      <c r="W18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K18" s="92" t="inlineStr">
+      <c r="X18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L18" s="92" t="inlineStr">
+      <c r="Y18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M18" s="92" t="inlineStr">
+      <c r="Z18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N18" s="92" t="inlineStr">
+      <c r="AB18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O18" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="P18" s="92" t="inlineStr">
+      <c r="AC18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q18" s="92" t="inlineStr">
+      <c r="AD18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z18" s="92" t="inlineStr">
+      <c r="AE18" s="92" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AA18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -8444,95 +8446,95 @@
           <t>us500:RNG60</t>
         </is>
       </c>
-      <c r="B19" s="94" t="n">
+      <c r="B19" s="95" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C19" s="95" t="n">
         <v>7.23</v>
       </c>
-      <c r="C19" s="94" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="D19" s="94" t="n">
+      <c r="D19" s="95" t="n">
         <v>8.619999999999999</v>
       </c>
-      <c r="E19" s="94" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="F19" s="94" t="n">
+      <c r="E19" s="95" t="n">
         <v>7.63</v>
       </c>
-      <c r="G19" s="94" t="n">
+      <c r="F19" s="95" t="n">
         <v>5.16</v>
       </c>
-      <c r="H19" s="94" t="n">
+      <c r="G19" s="95" t="n">
         <v>4.51</v>
       </c>
-      <c r="I19" s="94" t="n">
+      <c r="H19" s="95" t="n">
         <v>6.45</v>
       </c>
-      <c r="J19" s="94" t="n">
+      <c r="I19" s="95" t="n">
         <v>4.88</v>
       </c>
-      <c r="K19" s="94" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L19" s="94" t="n">
+      <c r="J19" s="95" t="n">
         <v>3.43</v>
       </c>
-      <c r="M19" s="94" t="n">
+      <c r="K19" s="95" t="n">
         <v>2.2</v>
       </c>
-      <c r="N19" s="94" t="n">
+      <c r="L19" s="95" t="n">
         <v>2.13</v>
       </c>
-      <c r="O19" s="94" t="n">
+      <c r="M19" s="95" t="n">
         <v>1.44</v>
       </c>
-      <c r="P19" s="94" t="n">
+      <c r="N19" s="95" t="n">
         <v>2.98</v>
       </c>
-      <c r="Q19" s="94" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="R19" s="94" t="n">
+      <c r="O19" s="95" t="n">
         <v>1.17</v>
       </c>
-      <c r="S19" s="94" t="n">
+      <c r="P19" s="95" t="n">
         <v>2.38</v>
       </c>
-      <c r="T19" s="94" t="n">
+      <c r="Q19" s="95" t="n">
         <v>2.44</v>
       </c>
-      <c r="U19" s="94" t="n">
+      <c r="R19" s="95" t="n">
         <v>3.51</v>
       </c>
-      <c r="V19" s="94" t="n">
+      <c r="S19" s="95" t="n">
         <v>3.63</v>
       </c>
-      <c r="W19" s="94" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="X19" s="94" t="n">
+      <c r="T19" s="95" t="n">
         <v>4.29</v>
       </c>
-      <c r="Y19" s="94" t="n">
+      <c r="U19" s="95" t="n">
         <v>4.51</v>
       </c>
-      <c r="Z19" s="94" t="n">
+      <c r="V19" s="95" t="n">
         <v>4.99</v>
       </c>
-      <c r="AA19" s="94" t="n">
+      <c r="W19" s="95" t="n">
         <v>4.3</v>
       </c>
-      <c r="AB19" s="94" t="n">
+      <c r="X19" s="95" t="n">
         <v>4.1</v>
       </c>
-      <c r="AC19" s="94" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD19" s="94" t="n">
+      <c r="Y19" s="95" t="n">
         <v>4.47</v>
       </c>
-      <c r="AE19" s="94" t="n">
+      <c r="Z19" s="95" t="n">
         <v>3.13</v>
+      </c>
+      <c r="AA19" s="95" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AB19" s="95" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AC19" s="95" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AD19" s="95" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AE19" s="95" t="n">
+        <v>2.26</v>
       </c>
     </row>
     <row r="20">
@@ -8541,95 +8543,95 @@
           <t>us500:RNG120</t>
         </is>
       </c>
-      <c r="B20" s="94" t="n">
+      <c r="B20" s="95" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="C20" s="95" t="n">
         <v>16.25</v>
       </c>
-      <c r="C20" s="94" t="n">
-        <v>16.25</v>
-      </c>
-      <c r="D20" s="94" t="n">
+      <c r="D20" s="95" t="n">
         <v>14.63</v>
       </c>
-      <c r="E20" s="94" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="F20" s="94" t="n">
+      <c r="E20" s="95" t="n">
         <v>14.54</v>
       </c>
-      <c r="G20" s="94" t="n">
+      <c r="F20" s="95" t="n">
         <v>15.73</v>
       </c>
-      <c r="H20" s="94" t="n">
+      <c r="G20" s="95" t="n">
         <v>14.66</v>
       </c>
-      <c r="I20" s="94" t="n">
+      <c r="H20" s="95" t="n">
         <v>15.57</v>
       </c>
-      <c r="J20" s="94" t="n">
+      <c r="I20" s="95" t="n">
         <v>16.05</v>
       </c>
-      <c r="K20" s="94" t="n">
-        <v>16.05</v>
-      </c>
-      <c r="L20" s="94" t="n">
+      <c r="J20" s="95" t="n">
         <v>16.36</v>
       </c>
-      <c r="M20" s="94" t="n">
+      <c r="K20" s="95" t="n">
         <v>15.58</v>
       </c>
-      <c r="N20" s="94" t="n">
+      <c r="L20" s="95" t="n">
         <v>14.51</v>
       </c>
-      <c r="O20" s="94" t="n">
+      <c r="M20" s="95" t="n">
         <v>12.76</v>
       </c>
-      <c r="P20" s="94" t="n">
+      <c r="N20" s="95" t="n">
         <v>13.62</v>
       </c>
-      <c r="Q20" s="94" t="n">
-        <v>13.62</v>
-      </c>
-      <c r="R20" s="94" t="n">
+      <c r="O20" s="95" t="n">
         <v>11.25</v>
       </c>
-      <c r="S20" s="94" t="n">
+      <c r="P20" s="95" t="n">
         <v>9.82</v>
       </c>
-      <c r="T20" s="94" t="n">
+      <c r="Q20" s="95" t="n">
         <v>10.62</v>
       </c>
-      <c r="U20" s="94" t="n">
+      <c r="R20" s="95" t="n">
         <v>10.61</v>
       </c>
-      <c r="V20" s="94" t="n">
+      <c r="S20" s="95" t="n">
         <v>10.3</v>
       </c>
-      <c r="W20" s="94" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="X20" s="94" t="n">
+      <c r="T20" s="95" t="n">
         <v>10.4</v>
       </c>
-      <c r="Y20" s="94" t="n">
+      <c r="U20" s="95" t="n">
         <v>11.17</v>
       </c>
-      <c r="Z20" s="94" t="n">
+      <c r="V20" s="95" t="n">
         <v>10.01</v>
       </c>
-      <c r="AA20" s="94" t="n">
+      <c r="W20" s="95" t="n">
         <v>9.85</v>
       </c>
-      <c r="AB20" s="94" t="n">
+      <c r="X20" s="95" t="n">
         <v>8.75</v>
       </c>
-      <c r="AC20" s="94" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="AD20" s="94" t="n">
+      <c r="Y20" s="95" t="n">
         <v>8.74</v>
       </c>
-      <c r="AE20" s="94" t="n">
+      <c r="Z20" s="95" t="n">
         <v>7.05</v>
+      </c>
+      <c r="AA20" s="95" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="AB20" s="95" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="AC20" s="95" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="AD20" s="95" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="AE20" s="95" t="n">
+        <v>6.31</v>
       </c>
     </row>
     <row r="21">
@@ -8638,95 +8640,95 @@
           <t>us500:RS2</t>
         </is>
       </c>
-      <c r="B21" s="94" t="n">
+      <c r="B21" s="95" t="n">
+        <v>47</v>
+      </c>
+      <c r="C21" s="95" t="n">
         <v>55.4</v>
       </c>
-      <c r="C21" s="94" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="D21" s="94" t="n">
+      <c r="D21" s="95" t="n">
         <v>84.39</v>
       </c>
-      <c r="E21" s="94" t="n">
+      <c r="E21" s="95" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="F21" s="95" t="n">
+        <v>65.73999999999999</v>
+      </c>
+      <c r="G21" s="95" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="H21" s="95" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="I21" s="95" t="n">
+        <v>84.56999999999999</v>
+      </c>
+      <c r="J21" s="95" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="K21" s="95" t="n">
+        <v>83.12</v>
+      </c>
+      <c r="L21" s="95" t="n">
+        <v>69.18000000000001</v>
+      </c>
+      <c r="M21" s="95" t="n">
+        <v>30.41</v>
+      </c>
+      <c r="N21" s="95" t="n">
+        <v>81.84</v>
+      </c>
+      <c r="O21" s="95" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="P21" s="95" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="Q21" s="95" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="R21" s="95" t="n">
+        <v>86.19</v>
+      </c>
+      <c r="S21" s="95" t="n">
+        <v>60.63</v>
+      </c>
+      <c r="T21" s="95" t="n">
+        <v>83.51000000000001</v>
+      </c>
+      <c r="U21" s="95" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="V21" s="95" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="W21" s="95" t="n">
         <v>84.39</v>
       </c>
-      <c r="F21" s="94" t="n">
-        <v>63.88</v>
-      </c>
-      <c r="G21" s="94" t="n">
-        <v>65.73999999999999</v>
-      </c>
-      <c r="H21" s="94" t="n">
-        <v>43.25</v>
-      </c>
-      <c r="I21" s="94" t="n">
-        <v>93.59999999999999</v>
-      </c>
-      <c r="J21" s="94" t="n">
-        <v>84.56999999999999</v>
-      </c>
-      <c r="K21" s="94" t="n">
-        <v>84.56999999999999</v>
-      </c>
-      <c r="L21" s="94" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="M21" s="94" t="n">
-        <v>83.12</v>
-      </c>
-      <c r="N21" s="94" t="n">
-        <v>69.18000000000001</v>
-      </c>
-      <c r="O21" s="94" t="n">
-        <v>30.41</v>
-      </c>
-      <c r="P21" s="94" t="n">
-        <v>81.84</v>
-      </c>
-      <c r="Q21" s="94" t="n">
-        <v>81.84</v>
-      </c>
-      <c r="R21" s="94" t="n">
-        <v>15.76</v>
-      </c>
-      <c r="S21" s="94" t="n">
-        <v>23.93</v>
-      </c>
-      <c r="T21" s="94" t="n">
-        <v>22.27</v>
-      </c>
-      <c r="U21" s="94" t="n">
-        <v>86.19</v>
-      </c>
-      <c r="V21" s="94" t="n">
-        <v>60.63</v>
-      </c>
-      <c r="W21" s="94" t="n">
-        <v>60.63</v>
-      </c>
-      <c r="X21" s="94" t="n">
-        <v>83.51000000000001</v>
-      </c>
-      <c r="Y21" s="94" t="n">
-        <v>58.19</v>
-      </c>
-      <c r="Z21" s="94" t="n">
-        <v>90.16</v>
-      </c>
-      <c r="AA21" s="94" t="n">
-        <v>84.39</v>
-      </c>
-      <c r="AB21" s="94" t="n">
+      <c r="X21" s="95" t="n">
         <v>76.79000000000001</v>
       </c>
-      <c r="AC21" s="94" t="n">
-        <v>76.79000000000001</v>
-      </c>
-      <c r="AD21" s="94" t="n">
+      <c r="Y21" s="95" t="n">
         <v>92.34</v>
       </c>
-      <c r="AE21" s="94" t="n">
+      <c r="Z21" s="95" t="n">
         <v>40.89</v>
+      </c>
+      <c r="AA21" s="95" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="AB21" s="95" t="n">
+        <v>95.83</v>
+      </c>
+      <c r="AC21" s="95" t="n">
+        <v>95.06</v>
+      </c>
+      <c r="AD21" s="95" t="n">
+        <v>91.83</v>
+      </c>
+      <c r="AE21" s="95" t="n">
+        <v>85.17</v>
       </c>
     </row>
     <row r="22">
@@ -8760,99 +8762,99 @@
           <t>red</t>
         </is>
       </c>
-      <c r="G22" s="92" t="inlineStr">
+      <c r="G22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H22" s="91" t="inlineStr">
+      <c r="I22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I22" s="92" t="inlineStr">
+      <c r="M22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J22" s="92" t="inlineStr">
+      <c r="O22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K22" s="92" t="inlineStr">
+      <c r="W22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L22" s="92" t="inlineStr">
+      <c r="X22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M22" s="92" t="inlineStr">
+      <c r="Y22" s="92" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="N22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O22" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="P22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="Z22" s="92" t="inlineStr">
@@ -8892,95 +8894,95 @@
           <t>us30:RNG60</t>
         </is>
       </c>
-      <c r="B23" s="94" t="n">
+      <c r="B23" s="95" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="C23" s="95" t="n">
         <v>5.77</v>
       </c>
-      <c r="C23" s="94" t="n">
+      <c r="D23" s="95" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="E23" s="95" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="F23" s="95" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="G23" s="95" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H23" s="95" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="I23" s="95" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="J23" s="95" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K23" s="95" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L23" s="95" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="M23" s="95" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="N23" s="95" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="O23" s="95" t="n">
         <v>5.77</v>
       </c>
-      <c r="D23" s="94" t="n">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="E23" s="94" t="n">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="F23" s="94" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="G23" s="94" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="H23" s="94" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="I23" s="94" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="J23" s="94" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="K23" s="94" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="L23" s="94" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="M23" s="94" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N23" s="94" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="O23" s="94" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="P23" s="94" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="Q23" s="94" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="R23" s="94" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="S23" s="94" t="n">
+      <c r="P23" s="95" t="n">
         <v>7.39</v>
       </c>
-      <c r="T23" s="94" t="n">
+      <c r="Q23" s="95" t="n">
         <v>7.15</v>
       </c>
-      <c r="U23" s="94" t="n">
+      <c r="R23" s="95" t="n">
         <v>7.5</v>
       </c>
-      <c r="V23" s="94" t="n">
+      <c r="S23" s="95" t="n">
         <v>7.64</v>
       </c>
-      <c r="W23" s="94" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="X23" s="94" t="n">
+      <c r="T23" s="95" t="n">
         <v>7.23</v>
       </c>
-      <c r="Y23" s="94" t="n">
+      <c r="U23" s="95" t="n">
         <v>7.01</v>
       </c>
-      <c r="Z23" s="94" t="n">
+      <c r="V23" s="95" t="n">
         <v>7.9</v>
       </c>
-      <c r="AA23" s="94" t="n">
+      <c r="W23" s="95" t="n">
         <v>7.56</v>
       </c>
-      <c r="AB23" s="94" t="n">
+      <c r="X23" s="95" t="n">
         <v>7.5</v>
       </c>
-      <c r="AC23" s="94" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD23" s="94" t="n">
+      <c r="Y23" s="95" t="n">
         <v>7.45</v>
       </c>
-      <c r="AE23" s="94" t="n">
+      <c r="Z23" s="95" t="n">
         <v>5.31</v>
+      </c>
+      <c r="AA23" s="95" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="AB23" s="95" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="AC23" s="95" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="AD23" s="95" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AE23" s="95" t="n">
+        <v>5.89</v>
       </c>
     </row>
     <row r="24">
@@ -8989,95 +8991,95 @@
           <t>us30:RNG120</t>
         </is>
       </c>
-      <c r="B24" s="94" t="n">
+      <c r="B24" s="95" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="C24" s="95" t="n">
         <v>13.53</v>
       </c>
-      <c r="C24" s="94" t="n">
-        <v>13.53</v>
-      </c>
-      <c r="D24" s="94" t="n">
+      <c r="D24" s="95" t="n">
         <v>12.74</v>
       </c>
-      <c r="E24" s="94" t="n">
-        <v>12.74</v>
-      </c>
-      <c r="F24" s="94" t="n">
+      <c r="E24" s="95" t="n">
         <v>13.07</v>
       </c>
-      <c r="G24" s="94" t="n">
+      <c r="F24" s="95" t="n">
         <v>13.11</v>
       </c>
-      <c r="H24" s="94" t="n">
+      <c r="G24" s="95" t="n">
         <v>11.13</v>
       </c>
-      <c r="I24" s="94" t="n">
+      <c r="H24" s="95" t="n">
         <v>11.85</v>
       </c>
-      <c r="J24" s="94" t="n">
+      <c r="I24" s="95" t="n">
         <v>12.09</v>
       </c>
-      <c r="K24" s="94" t="n">
-        <v>12.09</v>
-      </c>
-      <c r="L24" s="94" t="n">
+      <c r="J24" s="95" t="n">
         <v>11.76</v>
       </c>
-      <c r="M24" s="94" t="n">
+      <c r="K24" s="95" t="n">
         <v>12.54</v>
       </c>
-      <c r="N24" s="94" t="n">
+      <c r="L24" s="95" t="n">
         <v>11.46</v>
       </c>
-      <c r="O24" s="94" t="n">
+      <c r="M24" s="95" t="n">
         <v>10.99</v>
       </c>
-      <c r="P24" s="94" t="n">
+      <c r="N24" s="95" t="n">
         <v>12.24</v>
       </c>
-      <c r="Q24" s="94" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="R24" s="94" t="n">
+      <c r="O24" s="95" t="n">
         <v>10.61</v>
       </c>
-      <c r="S24" s="94" t="n">
+      <c r="P24" s="95" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="T24" s="94" t="n">
+      <c r="Q24" s="95" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="U24" s="94" t="n">
+      <c r="R24" s="95" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="V24" s="94" t="n">
+      <c r="S24" s="95" t="n">
         <v>8.789999999999999</v>
       </c>
-      <c r="W24" s="94" t="n">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="X24" s="94" t="n">
+      <c r="T24" s="95" t="n">
         <v>8.41</v>
       </c>
-      <c r="Y24" s="94" t="n">
+      <c r="U24" s="95" t="n">
         <v>8.6</v>
       </c>
-      <c r="Z24" s="94" t="n">
+      <c r="V24" s="95" t="n">
         <v>7.87</v>
       </c>
-      <c r="AA24" s="94" t="n">
+      <c r="W24" s="95" t="n">
         <v>7.54</v>
       </c>
-      <c r="AB24" s="94" t="n">
+      <c r="X24" s="95" t="n">
         <v>6.31</v>
       </c>
-      <c r="AC24" s="94" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="AD24" s="94" t="n">
+      <c r="Y24" s="95" t="n">
         <v>5.57</v>
       </c>
-      <c r="AE24" s="94" t="n">
+      <c r="Z24" s="95" t="n">
         <v>4.38</v>
+      </c>
+      <c r="AA24" s="95" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AB24" s="95" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AC24" s="95" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AD24" s="95" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AE24" s="95" t="n">
+        <v>3.42</v>
       </c>
     </row>
     <row r="25">
@@ -9086,95 +9088,95 @@
           <t>us30:RS3</t>
         </is>
       </c>
-      <c r="B25" s="94" t="n">
+      <c r="B25" s="95" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="C25" s="95" t="n">
         <v>40.25</v>
       </c>
-      <c r="C25" s="94" t="n">
-        <v>40.25</v>
-      </c>
-      <c r="D25" s="94" t="n">
+      <c r="D25" s="95" t="n">
         <v>78.72</v>
       </c>
-      <c r="E25" s="94" t="n">
-        <v>78.72</v>
-      </c>
-      <c r="F25" s="94" t="n">
+      <c r="E25" s="95" t="n">
         <v>77.16</v>
       </c>
-      <c r="G25" s="94" t="n">
+      <c r="F25" s="95" t="n">
         <v>70.95999999999999</v>
       </c>
-      <c r="H25" s="94" t="n">
+      <c r="G25" s="95" t="n">
         <v>53.27</v>
       </c>
-      <c r="I25" s="94" t="n">
+      <c r="H25" s="95" t="n">
         <v>87.47</v>
       </c>
-      <c r="J25" s="94" t="n">
+      <c r="I25" s="95" t="n">
         <v>82.94</v>
       </c>
-      <c r="K25" s="94" t="n">
+      <c r="J25" s="95" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="K25" s="95" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="L25" s="95" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="M25" s="95" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="N25" s="95" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="O25" s="95" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="P25" s="95" t="n">
+        <v>52.09</v>
+      </c>
+      <c r="Q25" s="95" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="R25" s="95" t="n">
+        <v>76.02</v>
+      </c>
+      <c r="S25" s="95" t="n">
+        <v>74.91</v>
+      </c>
+      <c r="T25" s="95" t="n">
+        <v>66.62</v>
+      </c>
+      <c r="U25" s="95" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="V25" s="95" t="n">
+        <v>92.18000000000001</v>
+      </c>
+      <c r="W25" s="95" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="X25" s="95" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="Y25" s="95" t="n">
+        <v>87.58</v>
+      </c>
+      <c r="Z25" s="95" t="n">
+        <v>65.31</v>
+      </c>
+      <c r="AA25" s="95" t="n">
+        <v>85.48999999999999</v>
+      </c>
+      <c r="AB25" s="95" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="AC25" s="95" t="n">
         <v>82.94</v>
       </c>
-      <c r="L25" s="94" t="n">
-        <v>66.56</v>
-      </c>
-      <c r="M25" s="94" t="n">
-        <v>73.18000000000001</v>
-      </c>
-      <c r="N25" s="94" t="n">
-        <v>46.98</v>
-      </c>
-      <c r="O25" s="94" t="n">
-        <v>34.52</v>
-      </c>
-      <c r="P25" s="94" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="Q25" s="94" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="R25" s="94" t="n">
-        <v>28.19</v>
-      </c>
-      <c r="S25" s="94" t="n">
-        <v>52.09</v>
-      </c>
-      <c r="T25" s="94" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="U25" s="94" t="n">
-        <v>76.02</v>
-      </c>
-      <c r="V25" s="94" t="n">
-        <v>74.91</v>
-      </c>
-      <c r="W25" s="94" t="n">
-        <v>74.91</v>
-      </c>
-      <c r="X25" s="94" t="n">
-        <v>66.62</v>
-      </c>
-      <c r="Y25" s="94" t="n">
-        <v>42.84</v>
-      </c>
-      <c r="Z25" s="94" t="n">
-        <v>92.18000000000001</v>
-      </c>
-      <c r="AA25" s="94" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="AB25" s="94" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="AC25" s="94" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="AD25" s="94" t="n">
-        <v>87.58</v>
-      </c>
-      <c r="AE25" s="94" t="n">
-        <v>65.31</v>
+      <c r="AD25" s="95" t="n">
+        <v>71.68000000000001</v>
+      </c>
+      <c r="AE25" s="95" t="n">
+        <v>56.57</v>
       </c>
     </row>
     <row r="26">
@@ -9198,139 +9200,139 @@
           <t>red</t>
         </is>
       </c>
-      <c r="E26" s="92" t="inlineStr">
+      <c r="E26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F26" s="91" t="inlineStr">
+      <c r="I26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G26" s="91" t="inlineStr">
+      <c r="P26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H26" s="91" t="inlineStr">
+      <c r="Q26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I26" s="92" t="inlineStr">
+      <c r="R26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J26" s="92" t="inlineStr">
+      <c r="U26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K26" s="92" t="inlineStr">
+      <c r="W26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L26" s="92" t="inlineStr">
+      <c r="X26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M26" s="92" t="inlineStr">
+      <c r="Y26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N26" s="92" t="inlineStr">
+      <c r="Z26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O26" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="P26" s="92" t="inlineStr">
+      <c r="AB26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q26" s="92" t="inlineStr">
+      <c r="AC26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X26" s="92" t="inlineStr">
+      <c r="AD26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z26" s="92" t="inlineStr">
+      <c r="AE26" s="92" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AA26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -9340,95 +9342,95 @@
           <t>ixic:RNG60</t>
         </is>
       </c>
-      <c r="B27" s="94" t="n">
+      <c r="B27" s="95" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="C27" s="95" t="n">
         <v>6.81</v>
       </c>
-      <c r="C27" s="94" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="D27" s="94" t="n">
+      <c r="D27" s="95" t="n">
         <v>7.61</v>
       </c>
-      <c r="E27" s="94" t="n">
-        <v>7.61</v>
-      </c>
-      <c r="F27" s="94" t="n">
+      <c r="E27" s="95" t="n">
         <v>5.95</v>
       </c>
-      <c r="G27" s="94" t="n">
+      <c r="F27" s="95" t="n">
         <v>2.05</v>
       </c>
-      <c r="H27" s="94" t="n">
+      <c r="G27" s="95" t="n">
         <v>1.71</v>
       </c>
-      <c r="I27" s="94" t="n">
+      <c r="H27" s="95" t="n">
         <v>4.38</v>
       </c>
-      <c r="J27" s="94" t="n">
+      <c r="I27" s="95" t="n">
         <v>2.64</v>
       </c>
-      <c r="K27" s="94" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="L27" s="94" t="n">
+      <c r="J27" s="95" t="n">
         <v>1.58</v>
       </c>
-      <c r="M27" s="94" t="n">
+      <c r="K27" s="95" t="n">
         <v>-1.18</v>
       </c>
-      <c r="N27" s="94" t="n">
+      <c r="L27" s="95" t="n">
         <v>-1.57</v>
       </c>
-      <c r="O27" s="94" t="n">
+      <c r="M27" s="95" t="n">
         <v>-2.58</v>
       </c>
-      <c r="P27" s="94" t="n">
+      <c r="N27" s="95" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q27" s="94" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R27" s="94" t="n">
+      <c r="O27" s="95" t="n">
         <v>-3.91</v>
       </c>
-      <c r="S27" s="94" t="n">
+      <c r="P27" s="95" t="n">
         <v>-2.74</v>
       </c>
-      <c r="T27" s="94" t="n">
+      <c r="Q27" s="95" t="n">
         <v>-2.68</v>
       </c>
-      <c r="U27" s="94" t="n">
+      <c r="R27" s="95" t="n">
         <v>-0.89</v>
       </c>
-      <c r="V27" s="94" t="n">
+      <c r="S27" s="95" t="n">
         <v>-0.38</v>
       </c>
-      <c r="W27" s="94" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="X27" s="94" t="n">
+      <c r="T27" s="95" t="n">
         <v>0.9</v>
       </c>
-      <c r="Y27" s="94" t="n">
+      <c r="U27" s="95" t="n">
         <v>1.13</v>
       </c>
-      <c r="Z27" s="94" t="n">
+      <c r="V27" s="95" t="n">
         <v>1.93</v>
       </c>
-      <c r="AA27" s="94" t="n">
+      <c r="W27" s="95" t="n">
         <v>0.65</v>
       </c>
-      <c r="AB27" s="94" t="n">
+      <c r="X27" s="95" t="n">
         <v>0.8</v>
       </c>
-      <c r="AC27" s="94" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AD27" s="94" t="n">
+      <c r="Y27" s="95" t="n">
         <v>1.67</v>
       </c>
-      <c r="AE27" s="94" t="n">
+      <c r="Z27" s="95" t="n">
         <v>0.44</v>
+      </c>
+      <c r="AA27" s="95" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="AB27" s="95" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="AC27" s="95" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD27" s="95" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="AE27" s="95" t="n">
+        <v>-1.66</v>
       </c>
     </row>
     <row r="28">
@@ -9437,95 +9439,95 @@
           <t>ixic:RNG120</t>
         </is>
       </c>
-      <c r="B28" s="94" t="n">
+      <c r="B28" s="95" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="C28" s="95" t="n">
         <v>18.41</v>
       </c>
-      <c r="C28" s="94" t="n">
-        <v>18.41</v>
-      </c>
-      <c r="D28" s="94" t="n">
+      <c r="D28" s="95" t="n">
         <v>15.68</v>
       </c>
-      <c r="E28" s="94" t="n">
-        <v>15.68</v>
-      </c>
-      <c r="F28" s="94" t="n">
+      <c r="E28" s="95" t="n">
         <v>15.35</v>
       </c>
-      <c r="G28" s="94" t="n">
+      <c r="F28" s="95" t="n">
         <v>17.65</v>
       </c>
-      <c r="H28" s="94" t="n">
+      <c r="G28" s="95" t="n">
         <v>16.57</v>
       </c>
-      <c r="I28" s="94" t="n">
+      <c r="H28" s="95" t="n">
         <v>17.88</v>
       </c>
-      <c r="J28" s="94" t="n">
+      <c r="I28" s="95" t="n">
         <v>18.71</v>
       </c>
-      <c r="K28" s="94" t="n">
-        <v>18.71</v>
-      </c>
-      <c r="L28" s="94" t="n">
+      <c r="J28" s="95" t="n">
         <v>19.63</v>
       </c>
-      <c r="M28" s="94" t="n">
+      <c r="K28" s="95" t="n">
         <v>17.24</v>
       </c>
-      <c r="N28" s="94" t="n">
+      <c r="L28" s="95" t="n">
         <v>15.94</v>
       </c>
-      <c r="O28" s="94" t="n">
+      <c r="M28" s="95" t="n">
         <v>12.98</v>
       </c>
-      <c r="P28" s="94" t="n">
+      <c r="N28" s="95" t="n">
         <v>14.18</v>
       </c>
-      <c r="Q28" s="94" t="n">
-        <v>14.18</v>
-      </c>
-      <c r="R28" s="94" t="n">
+      <c r="O28" s="95" t="n">
         <v>10.78</v>
       </c>
-      <c r="S28" s="94" t="n">
+      <c r="P28" s="95" t="n">
         <v>9.02</v>
       </c>
-      <c r="T28" s="94" t="n">
+      <c r="Q28" s="95" t="n">
         <v>10.76</v>
       </c>
-      <c r="U28" s="94" t="n">
+      <c r="R28" s="95" t="n">
         <v>11.54</v>
       </c>
-      <c r="V28" s="94" t="n">
+      <c r="S28" s="95" t="n">
         <v>11.48</v>
       </c>
-      <c r="W28" s="94" t="n">
-        <v>11.48</v>
-      </c>
-      <c r="X28" s="94" t="n">
+      <c r="T28" s="95" t="n">
         <v>11.95</v>
       </c>
-      <c r="Y28" s="94" t="n">
+      <c r="U28" s="95" t="n">
         <v>12.67</v>
       </c>
-      <c r="Z28" s="94" t="n">
+      <c r="V28" s="95" t="n">
         <v>11.04</v>
       </c>
-      <c r="AA28" s="94" t="n">
+      <c r="W28" s="95" t="n">
         <v>10.68</v>
       </c>
-      <c r="AB28" s="94" t="n">
+      <c r="X28" s="95" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="AC28" s="94" t="n">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="AD28" s="94" t="n">
+      <c r="Y28" s="95" t="n">
         <v>9.98</v>
       </c>
-      <c r="AE28" s="94" t="n">
+      <c r="Z28" s="95" t="n">
         <v>7.16</v>
+      </c>
+      <c r="AA28" s="95" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="AB28" s="95" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="AC28" s="95" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="AD28" s="95" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="AE28" s="95" t="n">
+        <v>6.27</v>
       </c>
     </row>
     <row r="29">
@@ -9534,95 +9536,95 @@
           <t>ixic:RS2</t>
         </is>
       </c>
-      <c r="B29" s="94" t="n">
+      <c r="B29" s="95" t="n">
+        <v>94.05</v>
+      </c>
+      <c r="C29" s="95" t="n">
         <v>91.14</v>
       </c>
-      <c r="C29" s="94" t="n">
-        <v>91.14</v>
-      </c>
-      <c r="D29" s="94" t="n">
+      <c r="D29" s="95" t="n">
         <v>85.89</v>
       </c>
-      <c r="E29" s="94" t="n">
-        <v>85.89</v>
-      </c>
-      <c r="F29" s="94" t="n">
+      <c r="E29" s="95" t="n">
         <v>55.65</v>
       </c>
-      <c r="G29" s="94" t="n">
+      <c r="F29" s="95" t="n">
         <v>52.8</v>
       </c>
-      <c r="H29" s="94" t="n">
+      <c r="G29" s="95" t="n">
         <v>36.8</v>
       </c>
-      <c r="I29" s="94" t="n">
+      <c r="H29" s="95" t="n">
         <v>95.84</v>
       </c>
-      <c r="J29" s="94" t="n">
+      <c r="I29" s="95" t="n">
         <v>86.79000000000001</v>
       </c>
-      <c r="K29" s="94" t="n">
-        <v>86.79000000000001</v>
-      </c>
-      <c r="L29" s="94" t="n">
+      <c r="J29" s="95" t="n">
         <v>77.45999999999999</v>
       </c>
-      <c r="M29" s="94" t="n">
+      <c r="K29" s="95" t="n">
         <v>82.01000000000001</v>
       </c>
-      <c r="N29" s="94" t="n">
+      <c r="L29" s="95" t="n">
         <v>72.98999999999999</v>
       </c>
-      <c r="O29" s="94" t="n">
+      <c r="M29" s="95" t="n">
         <v>32.92</v>
       </c>
-      <c r="P29" s="94" t="n">
+      <c r="N29" s="95" t="n">
         <v>85.03</v>
       </c>
-      <c r="Q29" s="94" t="n">
-        <v>85.03</v>
-      </c>
-      <c r="R29" s="94" t="n">
+      <c r="O29" s="95" t="n">
         <v>20.54</v>
       </c>
-      <c r="S29" s="94" t="n">
+      <c r="P29" s="95" t="n">
         <v>21.97</v>
       </c>
-      <c r="T29" s="94" t="n">
+      <c r="Q29" s="95" t="n">
         <v>15.42</v>
       </c>
-      <c r="U29" s="94" t="n">
+      <c r="R29" s="95" t="n">
         <v>74.7</v>
       </c>
-      <c r="V29" s="94" t="n">
+      <c r="S29" s="95" t="n">
         <v>51.35</v>
       </c>
-      <c r="W29" s="94" t="n">
-        <v>51.35</v>
-      </c>
-      <c r="X29" s="94" t="n">
+      <c r="T29" s="95" t="n">
         <v>96.66</v>
       </c>
-      <c r="Y29" s="94" t="n">
+      <c r="U29" s="95" t="n">
         <v>89.75</v>
       </c>
-      <c r="Z29" s="94" t="n">
+      <c r="V29" s="95" t="n">
         <v>88.93000000000001</v>
       </c>
-      <c r="AA29" s="94" t="n">
+      <c r="W29" s="95" t="n">
         <v>77.02</v>
       </c>
-      <c r="AB29" s="94" t="n">
+      <c r="X29" s="95" t="n">
         <v>73.3</v>
       </c>
-      <c r="AC29" s="94" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="AD29" s="94" t="n">
+      <c r="Y29" s="95" t="n">
         <v>92.18000000000001</v>
       </c>
-      <c r="AE29" s="94" t="n">
+      <c r="Z29" s="95" t="n">
         <v>42.32</v>
+      </c>
+      <c r="AA29" s="95" t="n">
+        <v>70.06</v>
+      </c>
+      <c r="AB29" s="95" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="AC29" s="95" t="n">
+        <v>95.17</v>
+      </c>
+      <c r="AD29" s="95" t="n">
+        <v>92.73999999999999</v>
+      </c>
+      <c r="AE29" s="95" t="n">
+        <v>88.20999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -9631,12 +9633,12 @@
           <t>jp225:EIDE</t>
         </is>
       </c>
-      <c r="B30" s="95" t="inlineStr">
+      <c r="B30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C30" s="95" t="inlineStr">
+      <c r="C30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -9646,139 +9648,139 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="E30" s="91" t="inlineStr">
+      <c r="E30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F30" s="95" t="inlineStr">
+      <c r="G30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G30" s="91" t="inlineStr">
+      <c r="Q30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H30" s="92" t="inlineStr">
+      <c r="R30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I30" s="92" t="inlineStr">
+      <c r="T30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J30" s="92" t="inlineStr">
+      <c r="U30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K30" s="92" t="inlineStr">
+      <c r="V30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L30" s="91" t="inlineStr">
+      <c r="W30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M30" s="91" t="inlineStr">
+      <c r="AA30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N30" s="91" t="inlineStr">
+      <c r="AB30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P30" s="91" t="inlineStr">
+      <c r="AC30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q30" s="91" t="inlineStr">
+      <c r="AD30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S30" s="95" t="inlineStr">
+      <c r="AE30" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="T30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -9788,95 +9790,95 @@
           <t>jp225:RNG60</t>
         </is>
       </c>
-      <c r="B31" s="94" t="n">
+      <c r="B31" s="95" t="n">
         <v>1.98</v>
       </c>
-      <c r="C31" s="94" t="n">
+      <c r="C31" s="95" t="n">
         <v>2.87</v>
       </c>
-      <c r="D31" s="94" t="n">
+      <c r="D31" s="95" t="n">
         <v>-0.44</v>
       </c>
-      <c r="E31" s="94" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="F31" s="94" t="n">
+      <c r="E31" s="95" t="n">
         <v>-1.73</v>
       </c>
-      <c r="G31" s="94" t="n">
+      <c r="F31" s="95" t="n">
         <v>-1.06</v>
       </c>
-      <c r="H31" s="94" t="n">
+      <c r="G31" s="95" t="n">
         <v>-0.38</v>
       </c>
-      <c r="I31" s="94" t="n">
+      <c r="H31" s="95" t="n">
         <v>-1.3</v>
       </c>
-      <c r="J31" s="94" t="n">
+      <c r="I31" s="95" t="n">
         <v>-1.3</v>
       </c>
-      <c r="K31" s="94" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="L31" s="94" t="n">
+      <c r="J31" s="95" t="n">
         <v>-4.18</v>
       </c>
-      <c r="M31" s="94" t="n">
+      <c r="K31" s="95" t="n">
         <v>-4.84</v>
       </c>
-      <c r="N31" s="94" t="n">
+      <c r="L31" s="95" t="n">
         <v>-5.47</v>
       </c>
-      <c r="O31" s="94" t="n">
+      <c r="M31" s="95" t="n">
         <v>-6.85</v>
       </c>
-      <c r="P31" s="94" t="n">
+      <c r="N31" s="95" t="n">
         <v>-7.64</v>
       </c>
-      <c r="Q31" s="94" t="n">
-        <v>-7.64</v>
-      </c>
-      <c r="R31" s="94" t="n">
+      <c r="O31" s="95" t="n">
         <v>-7.28</v>
       </c>
-      <c r="S31" s="94" t="n">
+      <c r="P31" s="95" t="n">
         <v>-7.29</v>
       </c>
-      <c r="T31" s="94" t="n">
+      <c r="Q31" s="95" t="n">
         <v>-5.52</v>
       </c>
-      <c r="U31" s="94" t="n">
+      <c r="R31" s="95" t="n">
         <v>-7.32</v>
       </c>
-      <c r="V31" s="94" t="n">
+      <c r="S31" s="95" t="n">
         <v>-1.85</v>
       </c>
-      <c r="W31" s="94" t="n">
-        <v>-1.85</v>
-      </c>
-      <c r="X31" s="94" t="n">
+      <c r="T31" s="95" t="n">
         <v>-2.87</v>
       </c>
-      <c r="Y31" s="94" t="n">
+      <c r="U31" s="95" t="n">
         <v>-4.44</v>
       </c>
-      <c r="Z31" s="94" t="n">
+      <c r="V31" s="95" t="n">
         <v>-4.15</v>
       </c>
-      <c r="AA31" s="94" t="n">
+      <c r="W31" s="95" t="n">
         <v>-4.11</v>
       </c>
-      <c r="AB31" s="94" t="n">
+      <c r="X31" s="95" t="n">
         <v>-4.11</v>
       </c>
-      <c r="AC31" s="94" t="n">
-        <v>-4.11</v>
-      </c>
-      <c r="AD31" s="94" t="n">
+      <c r="Y31" s="95" t="n">
         <v>-6.33</v>
       </c>
-      <c r="AE31" s="94" t="n">
+      <c r="Z31" s="95" t="n">
         <v>-7.13</v>
+      </c>
+      <c r="AA31" s="95" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="AB31" s="95" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="AC31" s="95" t="n">
+        <v>-5.31</v>
+      </c>
+      <c r="AD31" s="95" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AE31" s="95" t="n">
+        <v>-7.44</v>
       </c>
     </row>
     <row r="32">
@@ -9885,95 +9887,95 @@
           <t>jp225:RNG120</t>
         </is>
       </c>
-      <c r="B32" s="94" t="n">
+      <c r="B32" s="95" t="n">
         <v>0.02</v>
       </c>
-      <c r="C32" s="94" t="n">
+      <c r="C32" s="95" t="n">
         <v>2.69</v>
       </c>
-      <c r="D32" s="94" t="n">
+      <c r="D32" s="95" t="n">
         <v>3.6</v>
       </c>
-      <c r="E32" s="94" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F32" s="94" t="n">
+      <c r="E32" s="95" t="n">
         <v>1.17</v>
       </c>
-      <c r="G32" s="94" t="n">
+      <c r="F32" s="95" t="n">
         <v>4.34</v>
       </c>
-      <c r="H32" s="94" t="n">
+      <c r="G32" s="95" t="n">
         <v>6.6</v>
       </c>
-      <c r="I32" s="94" t="n">
+      <c r="H32" s="95" t="n">
         <v>6.85</v>
       </c>
-      <c r="J32" s="94" t="n">
+      <c r="I32" s="95" t="n">
         <v>6.85</v>
       </c>
-      <c r="K32" s="94" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="L32" s="94" t="n">
+      <c r="J32" s="95" t="n">
         <v>3.42</v>
       </c>
-      <c r="M32" s="94" t="n">
+      <c r="K32" s="95" t="n">
         <v>3.47</v>
       </c>
-      <c r="N32" s="94" t="n">
+      <c r="L32" s="95" t="n">
         <v>1.21</v>
       </c>
-      <c r="O32" s="94" t="n">
+      <c r="M32" s="95" t="n">
         <v>0.25</v>
       </c>
-      <c r="P32" s="94" t="n">
+      <c r="N32" s="95" t="n">
         <v>-2.25</v>
       </c>
-      <c r="Q32" s="94" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="R32" s="94" t="n">
+      <c r="O32" s="95" t="n">
         <v>-2.26</v>
       </c>
-      <c r="S32" s="94" t="n">
+      <c r="P32" s="95" t="n">
         <v>-4.48</v>
       </c>
-      <c r="T32" s="94" t="n">
+      <c r="Q32" s="95" t="n">
         <v>-2.82</v>
       </c>
-      <c r="U32" s="94" t="n">
+      <c r="R32" s="95" t="n">
         <v>-3.63</v>
       </c>
-      <c r="V32" s="94" t="n">
+      <c r="S32" s="95" t="n">
         <v>2.15</v>
       </c>
-      <c r="W32" s="94" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="X32" s="94" t="n">
+      <c r="T32" s="95" t="n">
         <v>-2.13</v>
       </c>
-      <c r="Y32" s="94" t="n">
+      <c r="U32" s="95" t="n">
         <v>-4.01</v>
       </c>
-      <c r="Z32" s="94" t="n">
+      <c r="V32" s="95" t="n">
         <v>-4.76</v>
       </c>
-      <c r="AA32" s="94" t="n">
+      <c r="W32" s="95" t="n">
         <v>-5.22</v>
       </c>
-      <c r="AB32" s="94" t="n">
+      <c r="X32" s="95" t="n">
         <v>-5.22</v>
       </c>
-      <c r="AC32" s="94" t="n">
-        <v>-5.22</v>
-      </c>
-      <c r="AD32" s="94" t="n">
+      <c r="Y32" s="95" t="n">
         <v>-7.96</v>
       </c>
-      <c r="AE32" s="94" t="n">
+      <c r="Z32" s="95" t="n">
         <v>-9.43</v>
+      </c>
+      <c r="AA32" s="95" t="n">
+        <v>-11.19</v>
+      </c>
+      <c r="AB32" s="95" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="AC32" s="95" t="n">
+        <v>-9.48</v>
+      </c>
+      <c r="AD32" s="95" t="n">
+        <v>-9.92</v>
+      </c>
+      <c r="AE32" s="95" t="n">
+        <v>-12.73</v>
       </c>
     </row>
     <row r="33">
@@ -9982,95 +9984,95 @@
           <t>jp225:RS9</t>
         </is>
       </c>
-      <c r="B33" s="94" t="n">
+      <c r="B33" s="95" t="n">
         <v>44.35</v>
       </c>
-      <c r="C33" s="94" t="n">
+      <c r="C33" s="95" t="n">
         <v>52.17</v>
       </c>
-      <c r="D33" s="94" t="n">
+      <c r="D33" s="95" t="n">
         <v>52.59</v>
       </c>
-      <c r="E33" s="94" t="n">
-        <v>52.59</v>
-      </c>
-      <c r="F33" s="94" t="n">
+      <c r="E33" s="95" t="n">
         <v>51.7</v>
       </c>
-      <c r="G33" s="94" t="n">
+      <c r="F33" s="95" t="n">
         <v>55.18</v>
       </c>
-      <c r="H33" s="94" t="n">
+      <c r="G33" s="95" t="n">
         <v>65.89</v>
       </c>
-      <c r="I33" s="94" t="n">
+      <c r="H33" s="95" t="n">
         <v>63.24</v>
       </c>
-      <c r="J33" s="94" t="n">
+      <c r="I33" s="95" t="n">
         <v>63.24</v>
       </c>
-      <c r="K33" s="94" t="n">
-        <v>63.24</v>
-      </c>
-      <c r="L33" s="94" t="n">
+      <c r="J33" s="95" t="n">
         <v>61.28</v>
       </c>
-      <c r="M33" s="94" t="n">
+      <c r="K33" s="95" t="n">
         <v>60.41</v>
       </c>
-      <c r="N33" s="94" t="n">
+      <c r="L33" s="95" t="n">
         <v>57.64</v>
       </c>
-      <c r="O33" s="94" t="n">
+      <c r="M33" s="95" t="n">
         <v>62.13</v>
       </c>
-      <c r="P33" s="94" t="n">
+      <c r="N33" s="95" t="n">
         <v>56.86</v>
       </c>
-      <c r="Q33" s="94" t="n">
-        <v>56.86</v>
-      </c>
-      <c r="R33" s="94" t="n">
+      <c r="O33" s="95" t="n">
         <v>56.21</v>
       </c>
-      <c r="S33" s="94" t="n">
+      <c r="P33" s="95" t="n">
         <v>50.28</v>
       </c>
-      <c r="T33" s="94" t="n">
+      <c r="Q33" s="95" t="n">
         <v>58.22</v>
       </c>
-      <c r="U33" s="94" t="n">
+      <c r="R33" s="95" t="n">
         <v>52.42</v>
       </c>
-      <c r="V33" s="94" t="n">
+      <c r="S33" s="95" t="n">
         <v>77.31</v>
       </c>
-      <c r="W33" s="94" t="n">
-        <v>77.31</v>
-      </c>
-      <c r="X33" s="94" t="n">
+      <c r="T33" s="95" t="n">
         <v>71.64</v>
       </c>
-      <c r="Y33" s="94" t="n">
+      <c r="U33" s="95" t="n">
         <v>61.74</v>
       </c>
-      <c r="Z33" s="94" t="n">
+      <c r="V33" s="95" t="n">
         <v>63.04</v>
       </c>
-      <c r="AA33" s="94" t="n">
+      <c r="W33" s="95" t="n">
         <v>60.77</v>
       </c>
-      <c r="AB33" s="94" t="n">
+      <c r="X33" s="95" t="n">
         <v>60.77</v>
       </c>
-      <c r="AC33" s="94" t="n">
-        <v>60.77</v>
-      </c>
-      <c r="AD33" s="94" t="n">
+      <c r="Y33" s="95" t="n">
         <v>54.21</v>
       </c>
-      <c r="AE33" s="94" t="n">
+      <c r="Z33" s="95" t="n">
         <v>42.56</v>
+      </c>
+      <c r="AA33" s="95" t="n">
+        <v>39.44</v>
+      </c>
+      <c r="AB33" s="95" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="AC33" s="95" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="AD33" s="95" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="AE33" s="95" t="n">
+        <v>26.47</v>
       </c>
     </row>
     <row r="34">
@@ -10079,12 +10081,12 @@
           <t>vn:EIDE</t>
         </is>
       </c>
-      <c r="B34" s="95" t="inlineStr">
+      <c r="B34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C34" s="95" t="inlineStr">
+      <c r="C34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -10099,134 +10101,134 @@
           <t>red</t>
         </is>
       </c>
-      <c r="F34" s="92" t="inlineStr">
+      <c r="F34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G34" s="95" t="inlineStr">
+      <c r="I34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H34" s="91" t="inlineStr">
+      <c r="M34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="P34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I34" s="92" t="inlineStr">
+      <c r="Q34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J34" s="92" t="inlineStr">
+      <c r="T34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K34" s="92" t="inlineStr">
+      <c r="U34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L34" s="92" t="inlineStr">
+      <c r="V34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M34" s="92" t="inlineStr">
+      <c r="W34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N34" s="95" t="inlineStr">
+      <c r="X34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AB34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O34" s="95" t="inlineStr">
+      <c r="AC34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P34" s="95" t="inlineStr">
+      <c r="AD34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q34" s="95" t="inlineStr">
+      <c r="AE34" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="R34" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="S34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -10236,95 +10238,95 @@
           <t>vn:RNG60</t>
         </is>
       </c>
-      <c r="B35" s="94" t="n">
+      <c r="B35" s="95" t="n">
         <v>2.24</v>
       </c>
-      <c r="C35" s="94" t="n">
+      <c r="C35" s="95" t="n">
         <v>3.78</v>
       </c>
-      <c r="D35" s="94" t="n">
+      <c r="D35" s="95" t="n">
         <v>3.79</v>
       </c>
-      <c r="E35" s="94" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="F35" s="94" t="n">
+      <c r="E35" s="95" t="n">
         <v>4.44</v>
       </c>
-      <c r="G35" s="94" t="n">
+      <c r="F35" s="95" t="n">
         <v>1.98</v>
       </c>
-      <c r="H35" s="94" t="n">
+      <c r="G35" s="95" t="n">
         <v>1.29</v>
       </c>
-      <c r="I35" s="94" t="n">
+      <c r="H35" s="95" t="n">
         <v>0.93</v>
       </c>
-      <c r="J35" s="94" t="n">
+      <c r="I35" s="95" t="n">
         <v>1.56</v>
       </c>
-      <c r="K35" s="94" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="L35" s="94" t="n">
+      <c r="J35" s="95" t="n">
         <v>0.4</v>
       </c>
-      <c r="M35" s="94" t="n">
+      <c r="K35" s="95" t="n">
         <v>0.16</v>
       </c>
-      <c r="N35" s="94" t="n">
+      <c r="L35" s="95" t="n">
         <v>-0.68</v>
       </c>
-      <c r="O35" s="94" t="n">
+      <c r="M35" s="95" t="n">
         <v>-1.08</v>
       </c>
-      <c r="P35" s="94" t="n">
+      <c r="N35" s="95" t="n">
         <v>-1.19</v>
       </c>
-      <c r="Q35" s="94" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="R35" s="94" t="n">
+      <c r="O35" s="95" t="n">
         <v>-1.21</v>
       </c>
-      <c r="S35" s="94" t="n">
+      <c r="P35" s="95" t="n">
         <v>0.33</v>
       </c>
-      <c r="T35" s="94" t="n">
+      <c r="Q35" s="95" t="n">
         <v>0.71</v>
       </c>
-      <c r="U35" s="94" t="n">
+      <c r="R35" s="95" t="n">
         <v>0.63</v>
       </c>
-      <c r="V35" s="94" t="n">
+      <c r="S35" s="95" t="n">
         <v>1.1</v>
       </c>
-      <c r="W35" s="94" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X35" s="94" t="n">
+      <c r="T35" s="95" t="n">
         <v>1.71</v>
       </c>
-      <c r="Y35" s="94" t="n">
+      <c r="U35" s="95" t="n">
         <v>2.62</v>
       </c>
-      <c r="Z35" s="94" t="n">
+      <c r="V35" s="95" t="n">
         <v>1.79</v>
       </c>
-      <c r="AA35" s="94" t="n">
+      <c r="W35" s="95" t="n">
         <v>1.86</v>
       </c>
-      <c r="AB35" s="94" t="n">
+      <c r="X35" s="95" t="n">
         <v>1.03</v>
       </c>
-      <c r="AC35" s="94" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD35" s="94" t="n">
+      <c r="Y35" s="95" t="n">
         <v>0.8</v>
       </c>
-      <c r="AE35" s="94" t="n">
+      <c r="Z35" s="95" t="n">
         <v>0.66</v>
+      </c>
+      <c r="AA35" s="95" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AB35" s="95" t="n">
+        <v>-3.34</v>
+      </c>
+      <c r="AC35" s="95" t="n">
+        <v>-2.39</v>
+      </c>
+      <c r="AD35" s="95" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="AE35" s="95" t="n">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="36">
@@ -10333,95 +10335,95 @@
           <t>vn:RNG120</t>
         </is>
       </c>
-      <c r="B36" s="94" t="n">
+      <c r="B36" s="95" t="n">
         <v>2.28</v>
       </c>
-      <c r="C36" s="94" t="n">
+      <c r="C36" s="95" t="n">
         <v>4.81</v>
       </c>
-      <c r="D36" s="94" t="n">
+      <c r="D36" s="95" t="n">
         <v>5.68</v>
       </c>
-      <c r="E36" s="94" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="F36" s="94" t="n">
+      <c r="E36" s="95" t="n">
         <v>6.37</v>
       </c>
-      <c r="G36" s="94" t="n">
+      <c r="F36" s="95" t="n">
         <v>6.18</v>
       </c>
-      <c r="H36" s="94" t="n">
+      <c r="G36" s="95" t="n">
         <v>6.26</v>
       </c>
-      <c r="I36" s="94" t="n">
+      <c r="H36" s="95" t="n">
         <v>9.25</v>
       </c>
-      <c r="J36" s="94" t="n">
+      <c r="I36" s="95" t="n">
         <v>8.25</v>
       </c>
-      <c r="K36" s="94" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="L36" s="94" t="n">
+      <c r="J36" s="95" t="n">
         <v>9.49</v>
       </c>
-      <c r="M36" s="94" t="n">
+      <c r="K36" s="95" t="n">
         <v>7.45</v>
       </c>
-      <c r="N36" s="94" t="n">
+      <c r="L36" s="95" t="n">
         <v>4.63</v>
       </c>
-      <c r="O36" s="94" t="n">
+      <c r="M36" s="95" t="n">
         <v>4.38</v>
       </c>
-      <c r="P36" s="94" t="n">
+      <c r="N36" s="95" t="n">
         <v>-0.47</v>
       </c>
-      <c r="Q36" s="94" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="R36" s="94" t="n">
+      <c r="O36" s="95" t="n">
         <v>1.58</v>
       </c>
-      <c r="S36" s="94" t="n">
+      <c r="P36" s="95" t="n">
         <v>2.33</v>
       </c>
-      <c r="T36" s="94" t="n">
+      <c r="Q36" s="95" t="n">
         <v>2.33</v>
       </c>
-      <c r="U36" s="94" t="n">
+      <c r="R36" s="95" t="n">
         <v>3.01</v>
       </c>
-      <c r="V36" s="94" t="n">
+      <c r="S36" s="95" t="n">
         <v>2.85</v>
       </c>
-      <c r="W36" s="94" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X36" s="94" t="n">
+      <c r="T36" s="95" t="n">
         <v>1.83</v>
       </c>
-      <c r="Y36" s="94" t="n">
+      <c r="U36" s="95" t="n">
         <v>1.26</v>
       </c>
-      <c r="Z36" s="94" t="n">
+      <c r="V36" s="95" t="n">
         <v>-0.78</v>
       </c>
-      <c r="AA36" s="94" t="n">
+      <c r="W36" s="95" t="n">
         <v>-1.02</v>
       </c>
-      <c r="AB36" s="94" t="n">
+      <c r="X36" s="95" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="AC36" s="94" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="AD36" s="94" t="n">
+      <c r="Y36" s="95" t="n">
         <v>-1.47</v>
       </c>
-      <c r="AE36" s="94" t="n">
+      <c r="Z36" s="95" t="n">
         <v>-1.42</v>
+      </c>
+      <c r="AA36" s="95" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="AB36" s="95" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="AC36" s="95" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="AD36" s="95" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="AE36" s="95" t="n">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="37">
@@ -10430,95 +10432,95 @@
           <t>vn:RS3</t>
         </is>
       </c>
-      <c r="B37" s="94" t="n">
+      <c r="B37" s="95" t="n">
         <v>14.83</v>
       </c>
-      <c r="C37" s="94" t="n">
+      <c r="C37" s="95" t="n">
         <v>32.52</v>
       </c>
-      <c r="D37" s="94" t="n">
+      <c r="D37" s="95" t="n">
         <v>60</v>
       </c>
-      <c r="E37" s="94" t="n">
-        <v>60</v>
-      </c>
-      <c r="F37" s="94" t="n">
+      <c r="E37" s="95" t="n">
         <v>67.03</v>
       </c>
-      <c r="G37" s="94" t="n">
+      <c r="F37" s="95" t="n">
         <v>31.47</v>
       </c>
-      <c r="H37" s="94" t="n">
+      <c r="G37" s="95" t="n">
         <v>37.61</v>
       </c>
-      <c r="I37" s="94" t="n">
+      <c r="H37" s="95" t="n">
         <v>65.76000000000001</v>
       </c>
-      <c r="J37" s="94" t="n">
+      <c r="I37" s="95" t="n">
         <v>81.64</v>
       </c>
-      <c r="K37" s="94" t="n">
-        <v>81.64</v>
-      </c>
-      <c r="L37" s="94" t="n">
+      <c r="J37" s="95" t="n">
         <v>78.16</v>
       </c>
-      <c r="M37" s="94" t="n">
+      <c r="K37" s="95" t="n">
         <v>69.63</v>
       </c>
-      <c r="N37" s="94" t="n">
+      <c r="L37" s="95" t="n">
         <v>29.45</v>
       </c>
-      <c r="O37" s="94" t="n">
+      <c r="M37" s="95" t="n">
         <v>13.62</v>
       </c>
-      <c r="P37" s="94" t="n">
+      <c r="N37" s="95" t="n">
         <v>14.32</v>
       </c>
-      <c r="Q37" s="94" t="n">
-        <v>14.32</v>
-      </c>
-      <c r="R37" s="94" t="n">
+      <c r="O37" s="95" t="n">
         <v>23.23</v>
       </c>
-      <c r="S37" s="94" t="n">
+      <c r="P37" s="95" t="n">
         <v>50.34</v>
       </c>
-      <c r="T37" s="94" t="n">
+      <c r="Q37" s="95" t="n">
         <v>77.23999999999999</v>
       </c>
-      <c r="U37" s="94" t="n">
+      <c r="R37" s="95" t="n">
         <v>65.09</v>
       </c>
-      <c r="V37" s="94" t="n">
+      <c r="S37" s="95" t="n">
         <v>86.66</v>
       </c>
-      <c r="W37" s="94" t="n">
-        <v>86.66</v>
-      </c>
-      <c r="X37" s="94" t="n">
+      <c r="T37" s="95" t="n">
         <v>90.48999999999999</v>
       </c>
-      <c r="Y37" s="94" t="n">
+      <c r="U37" s="95" t="n">
         <v>88</v>
       </c>
-      <c r="Z37" s="94" t="n">
+      <c r="V37" s="95" t="n">
         <v>77.98</v>
       </c>
-      <c r="AA37" s="94" t="n">
+      <c r="W37" s="95" t="n">
         <v>59.82</v>
       </c>
-      <c r="AB37" s="94" t="n">
+      <c r="X37" s="95" t="n">
         <v>77.68000000000001</v>
       </c>
-      <c r="AC37" s="94" t="n">
-        <v>77.68000000000001</v>
-      </c>
-      <c r="AD37" s="94" t="n">
+      <c r="Y37" s="95" t="n">
         <v>76.68000000000001</v>
       </c>
-      <c r="AE37" s="94" t="n">
+      <c r="Z37" s="95" t="n">
         <v>68.98</v>
+      </c>
+      <c r="AA37" s="95" t="n">
+        <v>60.96</v>
+      </c>
+      <c r="AB37" s="95" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="AC37" s="95" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="AD37" s="95" t="n">
+        <v>30.12</v>
+      </c>
+      <c r="AE37" s="95" t="n">
+        <v>12.08</v>
       </c>
     </row>
     <row r="38">
@@ -10527,7 +10529,7 @@
           <t>sensex:EIDE</t>
         </is>
       </c>
-      <c r="B38" s="95" t="inlineStr">
+      <c r="B38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -10572,109 +10574,109 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="K38" s="91" t="inlineStr">
+      <c r="K38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="P38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L38" s="91" t="inlineStr">
+      <c r="Q38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M38" s="95" t="inlineStr">
+      <c r="R38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AC38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AD38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AE38" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="N38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="O38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="P38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Q38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="R38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="S38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -10684,95 +10686,95 @@
           <t>sensex:RNG60</t>
         </is>
       </c>
-      <c r="B39" s="94" t="n">
+      <c r="B39" s="95" t="n">
         <v>-1.4</v>
       </c>
-      <c r="C39" s="94" t="n">
+      <c r="C39" s="95" t="n">
         <v>-0.22</v>
       </c>
-      <c r="D39" s="94" t="n">
+      <c r="D39" s="95" t="n">
         <v>1.48</v>
       </c>
-      <c r="E39" s="94" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="F39" s="94" t="n">
+      <c r="E39" s="95" t="n">
         <v>1.07</v>
       </c>
-      <c r="G39" s="94" t="n">
+      <c r="F39" s="95" t="n">
         <v>1.33</v>
       </c>
-      <c r="H39" s="94" t="n">
+      <c r="G39" s="95" t="n">
         <v>1.64</v>
       </c>
-      <c r="I39" s="94" t="n">
+      <c r="H39" s="95" t="n">
         <v>1.7</v>
       </c>
-      <c r="J39" s="94" t="n">
+      <c r="I39" s="95" t="n">
         <v>0.05</v>
       </c>
-      <c r="K39" s="94" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L39" s="94" t="n">
+      <c r="J39" s="95" t="n">
         <v>1.11</v>
       </c>
-      <c r="M39" s="94" t="n">
+      <c r="K39" s="95" t="n">
         <v>0.99</v>
       </c>
-      <c r="N39" s="94" t="n">
+      <c r="L39" s="95" t="n">
         <v>1.39</v>
       </c>
-      <c r="O39" s="94" t="n">
+      <c r="M39" s="95" t="n">
         <v>1.44</v>
       </c>
-      <c r="P39" s="94" t="n">
+      <c r="N39" s="95" t="n">
         <v>2.21</v>
       </c>
-      <c r="Q39" s="94" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="R39" s="94" t="n">
+      <c r="O39" s="95" t="n">
         <v>2.67</v>
       </c>
-      <c r="S39" s="94" t="n">
+      <c r="P39" s="95" t="n">
         <v>5.39</v>
       </c>
-      <c r="T39" s="94" t="n">
+      <c r="Q39" s="95" t="n">
         <v>5.39</v>
       </c>
-      <c r="U39" s="94" t="n">
+      <c r="R39" s="95" t="n">
         <v>5.38</v>
       </c>
-      <c r="V39" s="94" t="n">
+      <c r="S39" s="95" t="n">
         <v>6.9</v>
       </c>
-      <c r="W39" s="94" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="X39" s="94" t="n">
+      <c r="T39" s="95" t="n">
         <v>7.31</v>
       </c>
-      <c r="Y39" s="94" t="n">
+      <c r="U39" s="95" t="n">
         <v>7.21</v>
       </c>
-      <c r="Z39" s="94" t="n">
+      <c r="V39" s="95" t="n">
         <v>6.84</v>
       </c>
-      <c r="AA39" s="94" t="n">
+      <c r="W39" s="95" t="n">
         <v>7.46</v>
       </c>
-      <c r="AB39" s="94" t="n">
+      <c r="X39" s="95" t="n">
         <v>6.69</v>
       </c>
-      <c r="AC39" s="94" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="AD39" s="94" t="n">
+      <c r="Y39" s="95" t="n">
         <v>5.73</v>
       </c>
-      <c r="AE39" s="94" t="n">
+      <c r="Z39" s="95" t="n">
         <v>6.27</v>
+      </c>
+      <c r="AA39" s="95" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AB39" s="95" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="AC39" s="95" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="AD39" s="95" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="AE39" s="95" t="n">
+        <v>5.46</v>
       </c>
     </row>
     <row r="40">
@@ -10781,95 +10783,95 @@
           <t>sensex:RNG120</t>
         </is>
       </c>
-      <c r="B40" s="94" t="n">
+      <c r="B40" s="95" t="n">
         <v>7.52</v>
       </c>
-      <c r="C40" s="94" t="n">
+      <c r="C40" s="95" t="n">
         <v>8.949999999999999</v>
       </c>
-      <c r="D40" s="94" t="n">
+      <c r="D40" s="95" t="n">
         <v>8.779999999999999</v>
       </c>
-      <c r="E40" s="94" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="F40" s="94" t="n">
+      <c r="E40" s="95" t="n">
         <v>9.869999999999999</v>
       </c>
-      <c r="G40" s="94" t="n">
+      <c r="F40" s="95" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="H40" s="94" t="n">
+      <c r="G40" s="95" t="n">
         <v>10.79</v>
       </c>
-      <c r="I40" s="94" t="n">
+      <c r="H40" s="95" t="n">
         <v>11.17</v>
       </c>
-      <c r="J40" s="94" t="n">
+      <c r="I40" s="95" t="n">
         <v>10.5</v>
       </c>
-      <c r="K40" s="94" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="L40" s="94" t="n">
+      <c r="J40" s="95" t="n">
         <v>11.66</v>
       </c>
-      <c r="M40" s="94" t="n">
+      <c r="K40" s="95" t="n">
         <v>12.39</v>
       </c>
-      <c r="N40" s="94" t="n">
+      <c r="L40" s="95" t="n">
         <v>11.91</v>
       </c>
-      <c r="O40" s="94" t="n">
+      <c r="M40" s="95" t="n">
         <v>10.42</v>
       </c>
-      <c r="P40" s="94" t="n">
+      <c r="N40" s="95" t="n">
         <v>10.03</v>
       </c>
-      <c r="Q40" s="94" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="R40" s="94" t="n">
+      <c r="O40" s="95" t="n">
         <v>9.94</v>
       </c>
-      <c r="S40" s="94" t="n">
+      <c r="P40" s="95" t="n">
         <v>12.83</v>
       </c>
-      <c r="T40" s="94" t="n">
+      <c r="Q40" s="95" t="n">
         <v>12.83</v>
       </c>
-      <c r="U40" s="94" t="n">
+      <c r="R40" s="95" t="n">
         <v>12.79</v>
       </c>
-      <c r="V40" s="94" t="n">
+      <c r="S40" s="95" t="n">
         <v>15.25</v>
       </c>
-      <c r="W40" s="94" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="X40" s="94" t="n">
+      <c r="T40" s="95" t="n">
         <v>15.64</v>
       </c>
-      <c r="Y40" s="94" t="n">
+      <c r="U40" s="95" t="n">
         <v>15.29</v>
       </c>
-      <c r="Z40" s="94" t="n">
+      <c r="V40" s="95" t="n">
         <v>14.9</v>
       </c>
-      <c r="AA40" s="94" t="n">
+      <c r="W40" s="95" t="n">
         <v>14.75</v>
       </c>
-      <c r="AB40" s="94" t="n">
+      <c r="X40" s="95" t="n">
         <v>14.79</v>
       </c>
-      <c r="AC40" s="94" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="AD40" s="94" t="n">
+      <c r="Y40" s="95" t="n">
         <v>13.96</v>
       </c>
-      <c r="AE40" s="94" t="n">
+      <c r="Z40" s="95" t="n">
         <v>14.46</v>
+      </c>
+      <c r="AA40" s="95" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="AB40" s="95" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="AC40" s="95" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AD40" s="95" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="AE40" s="95" t="n">
+        <v>12.06</v>
       </c>
     </row>
     <row r="41">
@@ -10878,95 +10880,95 @@
           <t>sensex:RS10</t>
         </is>
       </c>
-      <c r="B41" s="94" t="n">
+      <c r="B41" s="95" t="n">
         <v>29.54</v>
       </c>
-      <c r="C41" s="94" t="n">
+      <c r="C41" s="95" t="n">
         <v>37.35</v>
       </c>
-      <c r="D41" s="94" t="n">
+      <c r="D41" s="95" t="n">
         <v>38.06</v>
       </c>
-      <c r="E41" s="94" t="n">
-        <v>38.06</v>
-      </c>
-      <c r="F41" s="94" t="n">
+      <c r="E41" s="95" t="n">
         <v>34.73</v>
       </c>
-      <c r="G41" s="94" t="n">
+      <c r="F41" s="95" t="n">
         <v>39.02</v>
       </c>
-      <c r="H41" s="94" t="n">
+      <c r="G41" s="95" t="n">
         <v>42.03</v>
       </c>
-      <c r="I41" s="94" t="n">
+      <c r="H41" s="95" t="n">
         <v>43.48</v>
       </c>
-      <c r="J41" s="94" t="n">
+      <c r="I41" s="95" t="n">
         <v>35.77</v>
       </c>
-      <c r="K41" s="94" t="n">
-        <v>35.77</v>
-      </c>
-      <c r="L41" s="94" t="n">
+      <c r="J41" s="95" t="n">
         <v>37.56</v>
       </c>
-      <c r="M41" s="94" t="n">
+      <c r="K41" s="95" t="n">
         <v>35.74</v>
       </c>
-      <c r="N41" s="94" t="n">
+      <c r="L41" s="95" t="n">
         <v>36.86</v>
       </c>
-      <c r="O41" s="94" t="n">
+      <c r="M41" s="95" t="n">
         <v>29.96</v>
       </c>
-      <c r="P41" s="94" t="n">
+      <c r="N41" s="95" t="n">
         <v>33.56</v>
       </c>
-      <c r="Q41" s="94" t="n">
-        <v>33.56</v>
-      </c>
-      <c r="R41" s="94" t="n">
+      <c r="O41" s="95" t="n">
         <v>38.91</v>
       </c>
-      <c r="S41" s="94" t="n">
+      <c r="P41" s="95" t="n">
         <v>56.68</v>
       </c>
-      <c r="T41" s="94" t="n">
+      <c r="Q41" s="95" t="n">
         <v>56.68</v>
       </c>
-      <c r="U41" s="94" t="n">
+      <c r="R41" s="95" t="n">
         <v>57.12</v>
       </c>
-      <c r="V41" s="94" t="n">
+      <c r="S41" s="95" t="n">
         <v>78.04000000000001</v>
       </c>
-      <c r="W41" s="94" t="n">
-        <v>78.04000000000001</v>
-      </c>
-      <c r="X41" s="94" t="n">
+      <c r="T41" s="95" t="n">
         <v>83.77</v>
       </c>
-      <c r="Y41" s="94" t="n">
+      <c r="U41" s="95" t="n">
         <v>80.52</v>
       </c>
-      <c r="Z41" s="94" t="n">
+      <c r="V41" s="95" t="n">
         <v>79.08</v>
       </c>
-      <c r="AA41" s="94" t="n">
+      <c r="W41" s="95" t="n">
         <v>79.38</v>
       </c>
-      <c r="AB41" s="94" t="n">
+      <c r="X41" s="95" t="n">
         <v>77.31999999999999</v>
       </c>
-      <c r="AC41" s="94" t="n">
-        <v>77.31999999999999</v>
-      </c>
-      <c r="AD41" s="94" t="n">
+      <c r="Y41" s="95" t="n">
         <v>66.75</v>
       </c>
-      <c r="AE41" s="94" t="n">
+      <c r="Z41" s="95" t="n">
         <v>64.14</v>
+      </c>
+      <c r="AA41" s="95" t="n">
+        <v>66.76000000000001</v>
+      </c>
+      <c r="AB41" s="95" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="AC41" s="95" t="n">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="AD41" s="95" t="n">
+        <v>66.14</v>
+      </c>
+      <c r="AE41" s="95" t="n">
+        <v>50.55</v>
       </c>
     </row>
     <row r="42">
@@ -10975,12 +10977,12 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="95" t="inlineStr">
+      <c r="B42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C42" s="95" t="inlineStr">
+      <c r="C42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -10995,134 +10997,134 @@
           <t>red</t>
         </is>
       </c>
-      <c r="F42" s="92" t="inlineStr">
+      <c r="F42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G42" s="95" t="inlineStr">
+      <c r="I42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H42" s="95" t="inlineStr">
+      <c r="K42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I42" s="92" t="inlineStr">
+      <c r="M42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J42" s="92" t="inlineStr">
+      <c r="N42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="P42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K42" s="92" t="inlineStr">
+      <c r="T42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L42" s="95" t="inlineStr">
+      <c r="U42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AC42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AD42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AE42" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="M42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="O42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Q42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="R42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="S42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="T42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="U42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -11132,95 +11134,95 @@
           <t>fr40:RNG60</t>
         </is>
       </c>
-      <c r="B43" s="94" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C43" s="94" t="n">
+      <c r="B43" s="95" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C43" s="95" t="n">
         <v>1.24</v>
       </c>
-      <c r="D43" s="94" t="n">
+      <c r="D43" s="95" t="n">
         <v>1.27</v>
       </c>
-      <c r="E43" s="94" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="F43" s="94" t="n">
+      <c r="E43" s="95" t="n">
         <v>2.11</v>
       </c>
-      <c r="G43" s="94" t="n">
+      <c r="F43" s="95" t="n">
         <v>-0.29</v>
       </c>
-      <c r="H43" s="94" t="n">
+      <c r="G43" s="95" t="n">
         <v>-1.01</v>
       </c>
-      <c r="I43" s="94" t="n">
+      <c r="H43" s="95" t="n">
         <v>-0.26</v>
       </c>
-      <c r="J43" s="94" t="n">
+      <c r="I43" s="95" t="n">
         <v>0.58</v>
       </c>
-      <c r="K43" s="94" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="L43" s="94" t="n">
+      <c r="J43" s="95" t="n">
         <v>-0.59</v>
       </c>
-      <c r="M43" s="94" t="n">
+      <c r="K43" s="95" t="n">
         <v>-0.14</v>
       </c>
-      <c r="N43" s="94" t="n">
+      <c r="L43" s="95" t="n">
         <v>-0.77</v>
       </c>
-      <c r="O43" s="94" t="n">
+      <c r="M43" s="95" t="n">
         <v>-0.74</v>
       </c>
-      <c r="P43" s="94" t="n">
+      <c r="N43" s="95" t="n">
         <v>-2.37</v>
       </c>
-      <c r="Q43" s="94" t="n">
-        <v>-2.37</v>
-      </c>
-      <c r="R43" s="94" t="n">
+      <c r="O43" s="95" t="n">
         <v>-1.96</v>
       </c>
-      <c r="S43" s="94" t="n">
+      <c r="P43" s="95" t="n">
         <v>0.05</v>
       </c>
-      <c r="T43" s="94" t="n">
+      <c r="Q43" s="95" t="n">
         <v>0.87</v>
       </c>
-      <c r="U43" s="94" t="n">
+      <c r="R43" s="95" t="n">
         <v>0.11</v>
       </c>
-      <c r="V43" s="94" t="n">
+      <c r="S43" s="95" t="n">
         <v>1.51</v>
       </c>
-      <c r="W43" s="94" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X43" s="94" t="n">
+      <c r="T43" s="95" t="n">
         <v>0.6</v>
       </c>
-      <c r="Y43" s="94" t="n">
+      <c r="U43" s="95" t="n">
         <v>-0.87</v>
       </c>
-      <c r="Z43" s="94" t="n">
+      <c r="V43" s="95" t="n">
         <v>0.87</v>
       </c>
-      <c r="AA43" s="94" t="n">
+      <c r="W43" s="95" t="n">
         <v>-0.7</v>
       </c>
-      <c r="AB43" s="94" t="n">
+      <c r="X43" s="95" t="n">
         <v>0.28</v>
       </c>
-      <c r="AC43" s="94" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="AD43" s="94" t="n">
+      <c r="Y43" s="95" t="n">
         <v>1.12</v>
       </c>
-      <c r="AE43" s="94" t="n">
+      <c r="Z43" s="95" t="n">
         <v>-2.16</v>
+      </c>
+      <c r="AA43" s="95" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="AB43" s="95" t="n">
+        <v>-3.34</v>
+      </c>
+      <c r="AC43" s="95" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="AD43" s="95" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="AE43" s="95" t="n">
+        <v>-2.29</v>
       </c>
     </row>
     <row r="44">
@@ -11229,95 +11231,95 @@
           <t>fr40:RNG120</t>
         </is>
       </c>
-      <c r="B44" s="94" t="n">
-        <v>-7.12</v>
-      </c>
-      <c r="C44" s="94" t="n">
+      <c r="B44" s="95" t="n">
+        <v>-6.69</v>
+      </c>
+      <c r="C44" s="95" t="n">
         <v>-5.76</v>
       </c>
-      <c r="D44" s="94" t="n">
+      <c r="D44" s="95" t="n">
         <v>-4.33</v>
       </c>
-      <c r="E44" s="94" t="n">
-        <v>-4.33</v>
-      </c>
-      <c r="F44" s="94" t="n">
+      <c r="E44" s="95" t="n">
         <v>-4.18</v>
       </c>
-      <c r="G44" s="94" t="n">
+      <c r="F44" s="95" t="n">
         <v>-6.17</v>
       </c>
-      <c r="H44" s="94" t="n">
+      <c r="G44" s="95" t="n">
         <v>-6.73</v>
       </c>
-      <c r="I44" s="94" t="n">
+      <c r="H44" s="95" t="n">
         <v>-6.01</v>
       </c>
-      <c r="J44" s="94" t="n">
+      <c r="I44" s="95" t="n">
         <v>-5.47</v>
       </c>
-      <c r="K44" s="94" t="n">
-        <v>-5.47</v>
-      </c>
-      <c r="L44" s="94" t="n">
+      <c r="J44" s="95" t="n">
         <v>-6.8</v>
       </c>
-      <c r="M44" s="94" t="n">
+      <c r="K44" s="95" t="n">
         <v>-6.73</v>
       </c>
-      <c r="N44" s="94" t="n">
+      <c r="L44" s="95" t="n">
         <v>-6.46</v>
       </c>
-      <c r="O44" s="94" t="n">
+      <c r="M44" s="95" t="n">
         <v>-5.56</v>
       </c>
-      <c r="P44" s="94" t="n">
+      <c r="N44" s="95" t="n">
         <v>-6.01</v>
       </c>
-      <c r="Q44" s="94" t="n">
+      <c r="O44" s="95" t="n">
+        <v>-6.31</v>
+      </c>
+      <c r="P44" s="95" t="n">
+        <v>-4.48</v>
+      </c>
+      <c r="Q44" s="95" t="n">
+        <v>-5.85</v>
+      </c>
+      <c r="R44" s="95" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="S44" s="95" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="T44" s="95" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="U44" s="95" t="n">
         <v>-6.01</v>
       </c>
-      <c r="R44" s="94" t="n">
-        <v>-6.31</v>
-      </c>
-      <c r="S44" s="94" t="n">
-        <v>-4.48</v>
-      </c>
-      <c r="T44" s="94" t="n">
-        <v>-5.85</v>
-      </c>
-      <c r="U44" s="94" t="n">
-        <v>-4.68</v>
-      </c>
-      <c r="V44" s="94" t="n">
-        <v>-2.89</v>
-      </c>
-      <c r="W44" s="94" t="n">
-        <v>-2.89</v>
-      </c>
-      <c r="X44" s="94" t="n">
-        <v>-3.77</v>
-      </c>
-      <c r="Y44" s="94" t="n">
-        <v>-6.01</v>
-      </c>
-      <c r="Z44" s="94" t="n">
+      <c r="V44" s="95" t="n">
         <v>-6.35</v>
       </c>
-      <c r="AA44" s="94" t="n">
+      <c r="W44" s="95" t="n">
         <v>-6.86</v>
       </c>
-      <c r="AB44" s="94" t="n">
+      <c r="X44" s="95" t="n">
         <v>-7.99</v>
       </c>
-      <c r="AC44" s="94" t="n">
-        <v>-7.99</v>
-      </c>
-      <c r="AD44" s="94" t="n">
+      <c r="Y44" s="95" t="n">
         <v>-6.6</v>
       </c>
-      <c r="AE44" s="94" t="n">
+      <c r="Z44" s="95" t="n">
         <v>-8.43</v>
+      </c>
+      <c r="AA44" s="95" t="n">
+        <v>-8.75</v>
+      </c>
+      <c r="AB44" s="95" t="n">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="AC44" s="95" t="n">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="AD44" s="95" t="n">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="AE44" s="95" t="n">
+        <v>-9.26</v>
       </c>
     </row>
     <row r="45">
@@ -11326,95 +11328,95 @@
           <t>fr40:RS5</t>
         </is>
       </c>
-      <c r="B45" s="94" t="n">
-        <v>38.58</v>
-      </c>
-      <c r="C45" s="94" t="n">
+      <c r="B45" s="95" t="n">
+        <v>44.46</v>
+      </c>
+      <c r="C45" s="95" t="n">
         <v>44.69</v>
       </c>
-      <c r="D45" s="94" t="n">
+      <c r="D45" s="95" t="n">
         <v>61.78</v>
       </c>
-      <c r="E45" s="94" t="n">
-        <v>61.78</v>
-      </c>
-      <c r="F45" s="94" t="n">
+      <c r="E45" s="95" t="n">
         <v>56.72</v>
       </c>
-      <c r="G45" s="94" t="n">
+      <c r="F45" s="95" t="n">
         <v>35.32</v>
       </c>
-      <c r="H45" s="94" t="n">
+      <c r="G45" s="95" t="n">
         <v>40.56</v>
       </c>
-      <c r="I45" s="94" t="n">
+      <c r="H45" s="95" t="n">
         <v>59.42</v>
       </c>
-      <c r="J45" s="94" t="n">
+      <c r="I45" s="95" t="n">
         <v>54.29</v>
       </c>
-      <c r="K45" s="94" t="n">
-        <v>54.29</v>
-      </c>
-      <c r="L45" s="94" t="n">
+      <c r="J45" s="95" t="n">
         <v>46.1</v>
       </c>
-      <c r="M45" s="94" t="n">
+      <c r="K45" s="95" t="n">
         <v>49.74</v>
       </c>
-      <c r="N45" s="94" t="n">
+      <c r="L45" s="95" t="n">
         <v>42.08</v>
       </c>
-      <c r="O45" s="94" t="n">
+      <c r="M45" s="95" t="n">
         <v>50.81</v>
       </c>
-      <c r="P45" s="94" t="n">
+      <c r="N45" s="95" t="n">
         <v>45.03</v>
       </c>
-      <c r="Q45" s="94" t="n">
-        <v>45.03</v>
-      </c>
-      <c r="R45" s="94" t="n">
+      <c r="O45" s="95" t="n">
         <v>33.57</v>
       </c>
-      <c r="S45" s="94" t="n">
+      <c r="P45" s="95" t="n">
         <v>45.48</v>
       </c>
-      <c r="T45" s="94" t="n">
+      <c r="Q45" s="95" t="n">
         <v>44.93</v>
       </c>
-      <c r="U45" s="94" t="n">
+      <c r="R45" s="95" t="n">
         <v>52.35</v>
       </c>
-      <c r="V45" s="94" t="n">
+      <c r="S45" s="95" t="n">
         <v>78.61</v>
       </c>
-      <c r="W45" s="94" t="n">
-        <v>78.61</v>
-      </c>
-      <c r="X45" s="94" t="n">
+      <c r="T45" s="95" t="n">
         <v>75.48</v>
       </c>
-      <c r="Y45" s="94" t="n">
+      <c r="U45" s="95" t="n">
         <v>57.98</v>
       </c>
-      <c r="Z45" s="94" t="n">
+      <c r="V45" s="95" t="n">
         <v>66.2</v>
       </c>
-      <c r="AA45" s="94" t="n">
+      <c r="W45" s="95" t="n">
         <v>52.83</v>
       </c>
-      <c r="AB45" s="94" t="n">
+      <c r="X45" s="95" t="n">
         <v>51.58</v>
       </c>
-      <c r="AC45" s="94" t="n">
-        <v>51.58</v>
-      </c>
-      <c r="AD45" s="94" t="n">
+      <c r="Y45" s="95" t="n">
         <v>74.97</v>
       </c>
-      <c r="AE45" s="94" t="n">
+      <c r="Z45" s="95" t="n">
         <v>45.92</v>
+      </c>
+      <c r="AA45" s="95" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="AB45" s="95" t="n">
+        <v>48.71</v>
+      </c>
+      <c r="AC45" s="95" t="n">
+        <v>53.61</v>
+      </c>
+      <c r="AD45" s="95" t="n">
+        <v>45.19</v>
+      </c>
+      <c r="AE45" s="95" t="n">
+        <v>32.83</v>
       </c>
     </row>
     <row r="46">
@@ -11443,134 +11445,134 @@
           <t>red</t>
         </is>
       </c>
-      <c r="F46" s="92" t="inlineStr">
+      <c r="F46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G46" s="91" t="inlineStr">
+      <c r="H46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H46" s="92" t="inlineStr">
+      <c r="K46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I46" s="92" t="inlineStr">
+      <c r="L46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="P46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J46" s="92" t="inlineStr">
+      <c r="T46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K46" s="92" t="inlineStr">
+      <c r="U46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L46" s="91" t="inlineStr">
+      <c r="W46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M46" s="92" t="inlineStr">
+      <c r="Y46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R46" s="95" t="inlineStr">
+      <c r="Z46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AC46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AD46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AE46" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="S46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -11580,95 +11582,95 @@
           <t>dax30:RNG60</t>
         </is>
       </c>
-      <c r="B47" s="94" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="C47" s="94" t="n">
+      <c r="B47" s="95" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="C47" s="95" t="n">
         <v>6.23</v>
       </c>
-      <c r="D47" s="94" t="n">
+      <c r="D47" s="95" t="n">
         <v>6.73</v>
       </c>
-      <c r="E47" s="94" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="F47" s="94" t="n">
+      <c r="E47" s="95" t="n">
         <v>7.02</v>
       </c>
-      <c r="G47" s="94" t="n">
+      <c r="F47" s="95" t="n">
         <v>5.69</v>
       </c>
-      <c r="H47" s="94" t="n">
+      <c r="G47" s="95" t="n">
         <v>5</v>
       </c>
-      <c r="I47" s="94" t="n">
+      <c r="H47" s="95" t="n">
         <v>5.98</v>
       </c>
-      <c r="J47" s="94" t="n">
+      <c r="I47" s="95" t="n">
         <v>6.61</v>
       </c>
-      <c r="K47" s="94" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="L47" s="94" t="n">
+      <c r="J47" s="95" t="n">
         <v>4.66</v>
       </c>
-      <c r="M47" s="94" t="n">
+      <c r="K47" s="95" t="n">
         <v>4.43</v>
       </c>
-      <c r="N47" s="94" t="n">
+      <c r="L47" s="95" t="n">
         <v>2.96</v>
       </c>
-      <c r="O47" s="94" t="n">
+      <c r="M47" s="95" t="n">
         <v>2.76</v>
       </c>
-      <c r="P47" s="94" t="n">
+      <c r="N47" s="95" t="n">
         <v>1.99</v>
       </c>
-      <c r="Q47" s="94" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R47" s="94" t="n">
+      <c r="O47" s="95" t="n">
         <v>2.59</v>
       </c>
-      <c r="S47" s="94" t="n">
+      <c r="P47" s="95" t="n">
         <v>4.12</v>
       </c>
-      <c r="T47" s="94" t="n">
+      <c r="Q47" s="95" t="n">
         <v>5.36</v>
       </c>
-      <c r="U47" s="94" t="n">
+      <c r="R47" s="95" t="n">
         <v>4.62</v>
       </c>
-      <c r="V47" s="94" t="n">
+      <c r="S47" s="95" t="n">
         <v>5.4</v>
       </c>
-      <c r="W47" s="94" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="X47" s="94" t="n">
+      <c r="T47" s="95" t="n">
         <v>4.27</v>
       </c>
-      <c r="Y47" s="94" t="n">
+      <c r="U47" s="95" t="n">
         <v>2.96</v>
       </c>
-      <c r="Z47" s="94" t="n">
+      <c r="V47" s="95" t="n">
         <v>4.58</v>
       </c>
-      <c r="AA47" s="94" t="n">
+      <c r="W47" s="95" t="n">
         <v>3.04</v>
       </c>
-      <c r="AB47" s="94" t="n">
+      <c r="X47" s="95" t="n">
         <v>2.66</v>
       </c>
-      <c r="AC47" s="94" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD47" s="94" t="n">
+      <c r="Y47" s="95" t="n">
         <v>4.35</v>
       </c>
-      <c r="AE47" s="94" t="n">
+      <c r="Z47" s="95" t="n">
         <v>3.06</v>
+      </c>
+      <c r="AA47" s="95" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB47" s="95" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC47" s="95" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD47" s="95" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE47" s="95" t="n">
+        <v>1.45</v>
       </c>
     </row>
     <row r="48">
@@ -11677,95 +11679,95 @@
           <t>dax30:RNG120</t>
         </is>
       </c>
-      <c r="B48" s="94" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="C48" s="94" t="n">
+      <c r="B48" s="95" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="C48" s="95" t="n">
         <v>7.08</v>
       </c>
-      <c r="D48" s="94" t="n">
+      <c r="D48" s="95" t="n">
         <v>9.25</v>
       </c>
-      <c r="E48" s="94" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="F48" s="94" t="n">
+      <c r="E48" s="95" t="n">
         <v>9.43</v>
       </c>
-      <c r="G48" s="94" t="n">
+      <c r="F48" s="95" t="n">
         <v>8.369999999999999</v>
       </c>
-      <c r="H48" s="94" t="n">
+      <c r="G48" s="95" t="n">
         <v>7.55</v>
       </c>
-      <c r="I48" s="94" t="n">
+      <c r="H48" s="95" t="n">
         <v>7.42</v>
       </c>
-      <c r="J48" s="94" t="n">
+      <c r="I48" s="95" t="n">
         <v>8.130000000000001</v>
       </c>
-      <c r="K48" s="94" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="L48" s="94" t="n">
+      <c r="J48" s="95" t="n">
         <v>6.2</v>
       </c>
-      <c r="M48" s="94" t="n">
+      <c r="K48" s="95" t="n">
         <v>6.16</v>
       </c>
-      <c r="N48" s="94" t="n">
+      <c r="L48" s="95" t="n">
         <v>6.75</v>
       </c>
-      <c r="O48" s="94" t="n">
+      <c r="M48" s="95" t="n">
         <v>7.71</v>
       </c>
-      <c r="P48" s="94" t="n">
+      <c r="N48" s="95" t="n">
         <v>7.2</v>
       </c>
-      <c r="Q48" s="94" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="R48" s="94" t="n">
+      <c r="O48" s="95" t="n">
         <v>7.01</v>
       </c>
-      <c r="S48" s="94" t="n">
+      <c r="P48" s="95" t="n">
         <v>7.87</v>
       </c>
-      <c r="T48" s="94" t="n">
+      <c r="Q48" s="95" t="n">
         <v>6.58</v>
       </c>
-      <c r="U48" s="94" t="n">
+      <c r="R48" s="95" t="n">
         <v>7.78</v>
       </c>
-      <c r="V48" s="94" t="n">
+      <c r="S48" s="95" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="W48" s="94" t="n">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="X48" s="94" t="n">
+      <c r="T48" s="95" t="n">
         <v>6.31</v>
       </c>
-      <c r="Y48" s="94" t="n">
+      <c r="U48" s="95" t="n">
         <v>4.66</v>
       </c>
-      <c r="Z48" s="94" t="n">
+      <c r="V48" s="95" t="n">
         <v>3.7</v>
       </c>
-      <c r="AA48" s="94" t="n">
+      <c r="W48" s="95" t="n">
         <v>3.7</v>
       </c>
-      <c r="AB48" s="94" t="n">
+      <c r="X48" s="95" t="n">
         <v>1.72</v>
       </c>
-      <c r="AC48" s="94" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD48" s="94" t="n">
+      <c r="Y48" s="95" t="n">
         <v>3.46</v>
       </c>
-      <c r="AE48" s="94" t="n">
+      <c r="Z48" s="95" t="n">
         <v>2.34</v>
+      </c>
+      <c r="AA48" s="95" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AB48" s="95" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AC48" s="95" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD48" s="95" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE48" s="95" t="n">
+        <v>0.68</v>
       </c>
     </row>
     <row r="49">
@@ -11774,95 +11776,95 @@
           <t>dax30:RS6</t>
         </is>
       </c>
-      <c r="B49" s="94" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="C49" s="94" t="n">
+      <c r="B49" s="95" t="n">
+        <v>52.49</v>
+      </c>
+      <c r="C49" s="95" t="n">
         <v>54.82</v>
       </c>
-      <c r="D49" s="94" t="n">
+      <c r="D49" s="95" t="n">
         <v>76.53</v>
       </c>
-      <c r="E49" s="94" t="n">
-        <v>76.53</v>
-      </c>
-      <c r="F49" s="94" t="n">
+      <c r="E49" s="95" t="n">
         <v>73.2</v>
       </c>
-      <c r="G49" s="94" t="n">
+      <c r="F49" s="95" t="n">
         <v>64.68000000000001</v>
       </c>
-      <c r="H49" s="94" t="n">
+      <c r="G49" s="95" t="n">
         <v>71.38</v>
       </c>
-      <c r="I49" s="94" t="n">
+      <c r="H49" s="95" t="n">
         <v>74.03</v>
       </c>
-      <c r="J49" s="94" t="n">
+      <c r="I49" s="95" t="n">
         <v>68.01000000000001</v>
       </c>
-      <c r="K49" s="94" t="n">
-        <v>68.01000000000001</v>
-      </c>
-      <c r="L49" s="94" t="n">
+      <c r="J49" s="95" t="n">
         <v>58.26</v>
       </c>
-      <c r="M49" s="94" t="n">
+      <c r="K49" s="95" t="n">
         <v>62.55</v>
       </c>
-      <c r="N49" s="94" t="n">
+      <c r="L49" s="95" t="n">
         <v>49.18</v>
       </c>
-      <c r="O49" s="94" t="n">
+      <c r="M49" s="95" t="n">
         <v>52.29</v>
       </c>
-      <c r="P49" s="94" t="n">
+      <c r="N49" s="95" t="n">
         <v>53.55</v>
       </c>
-      <c r="Q49" s="94" t="n">
-        <v>53.55</v>
-      </c>
-      <c r="R49" s="94" t="n">
+      <c r="O49" s="95" t="n">
         <v>46.86</v>
       </c>
-      <c r="S49" s="94" t="n">
+      <c r="P49" s="95" t="n">
         <v>56.45</v>
       </c>
-      <c r="T49" s="94" t="n">
+      <c r="Q49" s="95" t="n">
         <v>59.76</v>
       </c>
-      <c r="U49" s="94" t="n">
+      <c r="R49" s="95" t="n">
         <v>67.34999999999999</v>
       </c>
-      <c r="V49" s="94" t="n">
+      <c r="S49" s="95" t="n">
         <v>78.38</v>
       </c>
-      <c r="W49" s="94" t="n">
-        <v>78.38</v>
-      </c>
-      <c r="X49" s="94" t="n">
+      <c r="T49" s="95" t="n">
         <v>72.42</v>
       </c>
-      <c r="Y49" s="94" t="n">
+      <c r="U49" s="95" t="n">
         <v>59.91</v>
       </c>
-      <c r="Z49" s="94" t="n">
+      <c r="V49" s="95" t="n">
         <v>66</v>
       </c>
-      <c r="AA49" s="94" t="n">
+      <c r="W49" s="95" t="n">
         <v>59.4</v>
       </c>
-      <c r="AB49" s="94" t="n">
+      <c r="X49" s="95" t="n">
         <v>52.95</v>
       </c>
-      <c r="AC49" s="94" t="n">
-        <v>52.95</v>
-      </c>
-      <c r="AD49" s="94" t="n">
+      <c r="Y49" s="95" t="n">
         <v>75.06999999999999</v>
       </c>
-      <c r="AE49" s="94" t="n">
+      <c r="Z49" s="95" t="n">
         <v>61.14</v>
+      </c>
+      <c r="AA49" s="95" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="AB49" s="95" t="n">
+        <v>57.16</v>
+      </c>
+      <c r="AC49" s="95" t="n">
+        <v>62.56</v>
+      </c>
+      <c r="AD49" s="95" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="AE49" s="95" t="n">
+        <v>37.42</v>
       </c>
     </row>
     <row r="51">

--- a/report_2410.xlsx
+++ b/report_2410.xlsx
@@ -1060,9 +1060,9 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.14</v>
+        <v>7.13</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.14</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.01</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.55</v>
@@ -6357,137 +6357,137 @@
       </c>
       <c r="E1" s="77" t="inlineStr">
         <is>
-          <t>241020</t>
+          <t>241018</t>
         </is>
       </c>
       <c r="F1" s="77" t="inlineStr">
         <is>
-          <t>241018</t>
+          <t>241017</t>
         </is>
       </c>
       <c r="G1" s="77" t="inlineStr">
         <is>
-          <t>241017</t>
+          <t>241016</t>
         </is>
       </c>
       <c r="H1" s="77" t="inlineStr">
         <is>
-          <t>241016</t>
+          <t>241015</t>
         </is>
       </c>
       <c r="I1" s="77" t="inlineStr">
         <is>
-          <t>241015</t>
+          <t>241014</t>
         </is>
       </c>
       <c r="J1" s="77" t="inlineStr">
         <is>
-          <t>241014</t>
+          <t>241011</t>
         </is>
       </c>
       <c r="K1" s="77" t="inlineStr">
         <is>
-          <t>241013</t>
+          <t>241010</t>
         </is>
       </c>
       <c r="L1" s="77" t="inlineStr">
         <is>
-          <t>241011</t>
+          <t>241009</t>
         </is>
       </c>
       <c r="M1" s="77" t="inlineStr">
         <is>
-          <t>241010</t>
+          <t>241008</t>
         </is>
       </c>
       <c r="N1" s="77" t="inlineStr">
         <is>
-          <t>241009</t>
+          <t>241007</t>
         </is>
       </c>
       <c r="O1" s="77" t="inlineStr">
         <is>
-          <t>241008</t>
+          <t>241004</t>
         </is>
       </c>
       <c r="P1" s="77" t="inlineStr">
         <is>
-          <t>241007</t>
+          <t>241003</t>
         </is>
       </c>
       <c r="Q1" s="77" t="inlineStr">
         <is>
-          <t>241006</t>
+          <t>241002</t>
         </is>
       </c>
       <c r="R1" s="77" t="inlineStr">
         <is>
-          <t>241004</t>
+          <t>241001</t>
         </is>
       </c>
       <c r="S1" s="77" t="inlineStr">
         <is>
-          <t>241003</t>
+          <t>240930</t>
         </is>
       </c>
       <c r="T1" s="77" t="inlineStr">
         <is>
-          <t>241002</t>
+          <t>240927</t>
         </is>
       </c>
       <c r="U1" s="77" t="inlineStr">
         <is>
-          <t>241001</t>
+          <t>240926</t>
         </is>
       </c>
       <c r="V1" s="77" t="inlineStr">
         <is>
-          <t>240930</t>
+          <t>240925</t>
         </is>
       </c>
       <c r="W1" s="77" t="inlineStr">
         <is>
-          <t>240929</t>
+          <t>240924</t>
         </is>
       </c>
       <c r="X1" s="77" t="inlineStr">
         <is>
-          <t>240927</t>
+          <t>240923</t>
         </is>
       </c>
       <c r="Y1" s="77" t="inlineStr">
         <is>
-          <t>240926</t>
+          <t>240920</t>
         </is>
       </c>
       <c r="Z1" s="77" t="inlineStr">
         <is>
-          <t>240925</t>
+          <t>240919</t>
         </is>
       </c>
       <c r="AA1" s="77" t="inlineStr">
         <is>
-          <t>240924</t>
+          <t>240918</t>
         </is>
       </c>
       <c r="AB1" s="77" t="inlineStr">
         <is>
-          <t>240923</t>
+          <t>240917</t>
         </is>
       </c>
       <c r="AC1" s="77" t="inlineStr">
         <is>
-          <t>240922</t>
+          <t>240916</t>
         </is>
       </c>
       <c r="AD1" s="77" t="inlineStr">
         <is>
-          <t>240920</t>
+          <t>240913</t>
         </is>
       </c>
       <c r="AE1" s="77" t="inlineStr">
         <is>
-          <t>240919</t>
+          <t>240912</t>
         </is>
       </c>
     </row>
@@ -6552,197 +6552,197 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="M2" s="91" t="inlineStr">
+      <c r="M2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N2" s="91" t="inlineStr">
+      <c r="Y2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB2" s="91" t="inlineStr">
+      <c r="Z2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC2" s="91" t="inlineStr">
+      <c r="AA2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="AB2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="93" t="inlineStr">
+      <c r="A3" s="94" t="inlineStr">
         <is>
           <t>sh:RNG60</t>
         </is>
       </c>
-      <c r="B3" s="94" t="n">
+      <c r="B3" s="95" t="n">
         <v>11.42</v>
       </c>
-      <c r="C3" s="94" t="n">
+      <c r="C3" s="95" t="n">
         <v>10.18</v>
       </c>
-      <c r="D3" s="94" t="n">
+      <c r="D3" s="95" t="n">
         <v>9.77</v>
       </c>
-      <c r="E3" s="94" t="n">
+      <c r="E3" s="95" t="n">
         <v>10.08</v>
       </c>
-      <c r="F3" s="94" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="G3" s="94" t="n">
+      <c r="F3" s="95" t="n">
         <v>6.49</v>
       </c>
-      <c r="H3" s="94" t="n">
+      <c r="G3" s="95" t="n">
         <v>7.7</v>
       </c>
-      <c r="I3" s="94" t="n">
+      <c r="H3" s="95" t="n">
         <v>7.74</v>
       </c>
-      <c r="J3" s="94" t="n">
+      <c r="I3" s="95" t="n">
         <v>10.57</v>
       </c>
-      <c r="K3" s="94" t="n">
+      <c r="J3" s="95" t="n">
         <v>9.470000000000001</v>
       </c>
-      <c r="L3" s="94" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="M3" s="94" t="n">
+      <c r="K3" s="95" t="n">
         <v>11.58</v>
       </c>
-      <c r="N3" s="94" t="n">
+      <c r="L3" s="95" t="n">
         <v>11.51</v>
       </c>
-      <c r="O3" s="94" t="n">
+      <c r="M3" s="95" t="n">
         <v>18.3</v>
       </c>
-      <c r="P3" s="94" t="n">
+      <c r="N3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="Q3" s="94" t="n">
+      <c r="O3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="R3" s="94" t="n">
+      <c r="P3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="S3" s="94" t="n">
+      <c r="Q3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="T3" s="94" t="n">
+      <c r="R3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="U3" s="94" t="n">
+      <c r="S3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="V3" s="94" t="n">
-        <v>12.81</v>
-      </c>
-      <c r="W3" s="94" t="n">
+      <c r="T3" s="95" t="n">
         <v>3.53</v>
       </c>
-      <c r="X3" s="94" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="Y3" s="94" t="n">
+      <c r="U3" s="95" t="n">
         <v>0.13</v>
       </c>
-      <c r="Z3" s="94" t="n">
+      <c r="V3" s="95" t="n">
         <v>-3.29</v>
       </c>
-      <c r="AA3" s="94" t="n">
+      <c r="W3" s="95" t="n">
         <v>-3.51</v>
       </c>
-      <c r="AB3" s="94" t="n">
+      <c r="X3" s="95" t="n">
         <v>-6.68</v>
       </c>
-      <c r="AC3" s="94" t="n">
+      <c r="Y3" s="95" t="n">
         <v>-7.93</v>
       </c>
-      <c r="AD3" s="94" t="n">
-        <v>-7.93</v>
-      </c>
-      <c r="AE3" s="94" t="n">
+      <c r="Z3" s="95" t="n">
         <v>-7.25</v>
+      </c>
+      <c r="AA3" s="95" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="AB3" s="95" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="AC3" s="95" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="AD3" s="95" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="AE3" s="95" t="n">
+        <v>-9.59</v>
       </c>
     </row>
     <row r="4">
@@ -6751,192 +6751,192 @@
           <t>sh:RNG120</t>
         </is>
       </c>
-      <c r="B4" s="94" t="n">
+      <c r="B4" s="95" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="C4" s="94" t="n">
+      <c r="C4" s="95" t="n">
         <v>7.92</v>
       </c>
-      <c r="D4" s="94" t="n">
+      <c r="D4" s="95" t="n">
         <v>6.62</v>
       </c>
-      <c r="E4" s="94" t="n">
+      <c r="E4" s="95" t="n">
         <v>6.09</v>
       </c>
-      <c r="F4" s="94" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="G4" s="94" t="n">
+      <c r="F4" s="95" t="n">
         <v>3.19</v>
       </c>
-      <c r="H4" s="94" t="n">
+      <c r="G4" s="95" t="n">
         <v>6.51</v>
       </c>
-      <c r="I4" s="94" t="n">
+      <c r="H4" s="95" t="n">
         <v>4.71</v>
       </c>
-      <c r="J4" s="94" t="n">
+      <c r="I4" s="95" t="n">
         <v>8.77</v>
       </c>
-      <c r="K4" s="94" t="n">
+      <c r="J4" s="95" t="n">
         <v>6.05</v>
       </c>
-      <c r="L4" s="94" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="M4" s="94" t="n">
+      <c r="K4" s="95" t="n">
         <v>9.07</v>
       </c>
-      <c r="N4" s="94" t="n">
+      <c r="L4" s="95" t="n">
         <v>6.9</v>
       </c>
-      <c r="O4" s="94" t="n">
+      <c r="M4" s="95" t="n">
         <v>14.53</v>
       </c>
-      <c r="P4" s="94" t="n">
+      <c r="N4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="Q4" s="94" t="n">
+      <c r="O4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="R4" s="94" t="n">
+      <c r="P4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="S4" s="94" t="n">
+      <c r="Q4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="T4" s="94" t="n">
+      <c r="R4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="U4" s="94" t="n">
+      <c r="S4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="V4" s="94" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="W4" s="94" t="n">
+      <c r="T4" s="95" t="n">
         <v>0.41</v>
       </c>
-      <c r="X4" s="94" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="Y4" s="94" t="n">
+      <c r="U4" s="95" t="n">
         <v>-2.48</v>
       </c>
-      <c r="Z4" s="94" t="n">
+      <c r="V4" s="95" t="n">
         <v>-4.76</v>
       </c>
-      <c r="AA4" s="94" t="n">
+      <c r="W4" s="95" t="n">
         <v>-4.9</v>
       </c>
-      <c r="AB4" s="94" t="n">
+      <c r="X4" s="95" t="n">
         <v>-8.16</v>
       </c>
-      <c r="AC4" s="94" t="n">
+      <c r="Y4" s="95" t="n">
         <v>-9.720000000000001</v>
       </c>
-      <c r="AD4" s="94" t="n">
-        <v>-9.720000000000001</v>
-      </c>
-      <c r="AE4" s="94" t="n">
+      <c r="Z4" s="95" t="n">
         <v>-9.59</v>
       </c>
+      <c r="AA4" s="95" t="n">
+        <v>-10.85</v>
+      </c>
+      <c r="AB4" s="95" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="AC4" s="95" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="AD4" s="95" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="AE4" s="95" t="n">
+        <v>-11.77</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="93" t="inlineStr">
+      <c r="A5" s="94" t="inlineStr">
         <is>
           <t>sh:RS3</t>
         </is>
       </c>
-      <c r="B5" s="94" t="n">
+      <c r="B5" s="95" t="n">
         <v>76.48</v>
       </c>
-      <c r="C5" s="94" t="n">
+      <c r="C5" s="95" t="n">
         <v>71.05</v>
       </c>
-      <c r="D5" s="94" t="n">
+      <c r="D5" s="95" t="n">
         <v>65.47</v>
       </c>
-      <c r="E5" s="94" t="n">
+      <c r="E5" s="95" t="n">
         <v>63.75</v>
       </c>
-      <c r="F5" s="94" t="n">
-        <v>63.75</v>
-      </c>
-      <c r="G5" s="94" t="n">
+      <c r="F5" s="95" t="n">
         <v>32.04</v>
       </c>
-      <c r="H5" s="94" t="n">
+      <c r="G5" s="95" t="n">
         <v>40.69</v>
       </c>
-      <c r="I5" s="94" t="n">
+      <c r="H5" s="95" t="n">
         <v>40.15</v>
       </c>
-      <c r="J5" s="94" t="n">
+      <c r="I5" s="95" t="n">
         <v>57.29</v>
       </c>
-      <c r="K5" s="94" t="n">
+      <c r="J5" s="95" t="n">
         <v>44.67</v>
       </c>
-      <c r="L5" s="94" t="n">
-        <v>44.67</v>
-      </c>
-      <c r="M5" s="94" t="n">
+      <c r="K5" s="95" t="n">
         <v>59.48</v>
       </c>
-      <c r="N5" s="94" t="n">
+      <c r="L5" s="95" t="n">
         <v>54.31</v>
       </c>
-      <c r="O5" s="94" t="n">
+      <c r="M5" s="95" t="n">
         <v>99.84</v>
       </c>
-      <c r="P5" s="94" t="n">
+      <c r="N5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="Q5" s="94" t="n">
+      <c r="O5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="R5" s="94" t="n">
+      <c r="P5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="S5" s="94" t="n">
+      <c r="Q5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="T5" s="94" t="n">
+      <c r="R5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="U5" s="94" t="n">
+      <c r="S5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="V5" s="94" t="n">
-        <v>99.75</v>
-      </c>
-      <c r="W5" s="94" t="n">
+      <c r="T5" s="95" t="n">
         <v>99.31</v>
       </c>
-      <c r="X5" s="94" t="n">
-        <v>99.31</v>
-      </c>
-      <c r="Y5" s="94" t="n">
+      <c r="U5" s="95" t="n">
         <v>98.83</v>
       </c>
-      <c r="Z5" s="94" t="n">
+      <c r="V5" s="95" t="n">
         <v>97.34999999999999</v>
       </c>
-      <c r="AA5" s="94" t="n">
+      <c r="W5" s="95" t="n">
         <v>96.38</v>
       </c>
-      <c r="AB5" s="94" t="n">
+      <c r="X5" s="95" t="n">
         <v>77.51000000000001</v>
       </c>
-      <c r="AC5" s="94" t="n">
+      <c r="Y5" s="95" t="n">
         <v>64.38</v>
       </c>
-      <c r="AD5" s="94" t="n">
-        <v>64.38</v>
-      </c>
-      <c r="AE5" s="94" t="n">
+      <c r="Z5" s="95" t="n">
         <v>63.45</v>
+      </c>
+      <c r="AA5" s="95" t="n">
+        <v>37.85</v>
+      </c>
+      <c r="AB5" s="95" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AC5" s="95" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AD5" s="95" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AE5" s="95" t="n">
+        <v>10.95</v>
       </c>
     </row>
     <row r="6">
@@ -6965,426 +6965,426 @@
           <t>red</t>
         </is>
       </c>
-      <c r="F6" s="92" t="inlineStr">
+      <c r="F6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G6" s="91" t="inlineStr">
+      <c r="M6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Y6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H6" s="91" t="inlineStr">
+      <c r="Z6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I6" s="91" t="inlineStr">
+      <c r="AA6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J6" s="91" t="inlineStr">
+      <c r="AC6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K6" s="91" t="inlineStr">
+      <c r="AD6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L6" s="91" t="inlineStr">
+      <c r="AE6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB6" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="93" t="inlineStr">
+      <c r="A7" s="94" t="inlineStr">
         <is>
           <t>kc:RNG60</t>
         </is>
       </c>
-      <c r="B7" s="94" t="n">
+      <c r="B7" s="95" t="n">
         <v>30.21</v>
       </c>
-      <c r="C7" s="94" t="n">
+      <c r="C7" s="95" t="n">
         <v>31.54</v>
       </c>
-      <c r="D7" s="94" t="n">
+      <c r="D7" s="95" t="n">
         <v>36.03</v>
       </c>
-      <c r="E7" s="94" t="n">
+      <c r="E7" s="95" t="n">
         <v>34.25</v>
       </c>
-      <c r="F7" s="94" t="n">
-        <v>34.25</v>
-      </c>
-      <c r="G7" s="94" t="n">
+      <c r="F7" s="95" t="n">
         <v>20.09</v>
       </c>
-      <c r="H7" s="94" t="n">
+      <c r="G7" s="95" t="n">
         <v>22.33</v>
       </c>
-      <c r="I7" s="94" t="n">
+      <c r="H7" s="95" t="n">
         <v>25.12</v>
       </c>
-      <c r="J7" s="94" t="n">
+      <c r="I7" s="95" t="n">
         <v>28.96</v>
       </c>
-      <c r="K7" s="94" t="n">
+      <c r="J7" s="95" t="n">
         <v>26.54</v>
       </c>
-      <c r="L7" s="94" t="n">
-        <v>26.54</v>
-      </c>
-      <c r="M7" s="94" t="n">
+      <c r="K7" s="95" t="n">
         <v>34.41</v>
       </c>
-      <c r="N7" s="94" t="n">
+      <c r="L7" s="95" t="n">
         <v>44.1</v>
       </c>
-      <c r="O7" s="94" t="n">
+      <c r="M7" s="95" t="n">
         <v>46.52</v>
       </c>
-      <c r="P7" s="94" t="n">
+      <c r="N7" s="95" t="n">
         <v>26.36</v>
       </c>
-      <c r="Q7" s="94" t="n">
+      <c r="O7" s="95" t="n">
         <v>26.36</v>
       </c>
-      <c r="R7" s="94" t="n">
+      <c r="P7" s="95" t="n">
         <v>26.36</v>
       </c>
-      <c r="S7" s="94" t="n">
+      <c r="Q7" s="95" t="n">
         <v>26.36</v>
       </c>
-      <c r="T7" s="94" t="n">
+      <c r="R7" s="95" t="n">
         <v>26.36</v>
       </c>
-      <c r="U7" s="94" t="n">
+      <c r="S7" s="95" t="n">
         <v>26.36</v>
       </c>
-      <c r="V7" s="94" t="n">
-        <v>26.36</v>
-      </c>
-      <c r="W7" s="94" t="n">
+      <c r="T7" s="95" t="n">
         <v>5.45</v>
       </c>
-      <c r="X7" s="94" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="Y7" s="94" t="n">
+      <c r="U7" s="95" t="n">
         <v>-0.85</v>
       </c>
-      <c r="Z7" s="94" t="n">
+      <c r="V7" s="95" t="n">
         <v>-5.96</v>
       </c>
-      <c r="AA7" s="94" t="n">
+      <c r="W7" s="95" t="n">
         <v>-6.32</v>
       </c>
-      <c r="AB7" s="94" t="n">
+      <c r="X7" s="95" t="n">
         <v>-10.11</v>
       </c>
-      <c r="AC7" s="94" t="n">
+      <c r="Y7" s="95" t="n">
         <v>-11.14</v>
       </c>
-      <c r="AD7" s="94" t="n">
-        <v>-11.14</v>
-      </c>
-      <c r="AE7" s="94" t="n">
+      <c r="Z7" s="95" t="n">
         <v>-9.23</v>
       </c>
+      <c r="AA7" s="95" t="n">
+        <v>-12.41</v>
+      </c>
+      <c r="AB7" s="95" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="AC7" s="95" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="AD7" s="95" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="AE7" s="95" t="n">
+        <v>-12.75</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="93" t="inlineStr">
+      <c r="A8" s="94" t="inlineStr">
         <is>
           <t>kc:RNG120</t>
         </is>
       </c>
-      <c r="B8" s="94" t="n">
+      <c r="B8" s="95" t="n">
         <v>34.53</v>
       </c>
-      <c r="C8" s="94" t="n">
+      <c r="C8" s="95" t="n">
         <v>34.71</v>
       </c>
-      <c r="D8" s="94" t="n">
+      <c r="D8" s="95" t="n">
         <v>36.93</v>
       </c>
-      <c r="E8" s="94" t="n">
+      <c r="E8" s="95" t="n">
         <v>31.24</v>
       </c>
-      <c r="F8" s="94" t="n">
-        <v>31.24</v>
-      </c>
-      <c r="G8" s="94" t="n">
+      <c r="F8" s="95" t="n">
         <v>17.07</v>
       </c>
-      <c r="H8" s="94" t="n">
+      <c r="G8" s="95" t="n">
         <v>19.44</v>
       </c>
-      <c r="I8" s="94" t="n">
+      <c r="H8" s="95" t="n">
         <v>19.7</v>
       </c>
-      <c r="J8" s="94" t="n">
+      <c r="I8" s="95" t="n">
         <v>25.4</v>
       </c>
-      <c r="K8" s="94" t="n">
+      <c r="J8" s="95" t="n">
         <v>21.69</v>
       </c>
-      <c r="L8" s="94" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="M8" s="94" t="n">
+      <c r="K8" s="95" t="n">
         <v>29.69</v>
       </c>
-      <c r="N8" s="94" t="n">
+      <c r="L8" s="95" t="n">
         <v>33.11</v>
       </c>
-      <c r="O8" s="94" t="n">
+      <c r="M8" s="95" t="n">
         <v>38.25</v>
       </c>
-      <c r="P8" s="94" t="n">
+      <c r="N8" s="95" t="n">
         <v>15.28</v>
       </c>
-      <c r="Q8" s="94" t="n">
+      <c r="O8" s="95" t="n">
         <v>15.28</v>
       </c>
-      <c r="R8" s="94" t="n">
+      <c r="P8" s="95" t="n">
         <v>15.28</v>
       </c>
-      <c r="S8" s="94" t="n">
+      <c r="Q8" s="95" t="n">
         <v>15.28</v>
       </c>
-      <c r="T8" s="94" t="n">
+      <c r="R8" s="95" t="n">
         <v>15.28</v>
       </c>
-      <c r="U8" s="94" t="n">
+      <c r="S8" s="95" t="n">
         <v>15.28</v>
       </c>
-      <c r="V8" s="94" t="n">
-        <v>15.28</v>
-      </c>
-      <c r="W8" s="94" t="n">
+      <c r="T8" s="95" t="n">
         <v>-3.74</v>
       </c>
-      <c r="X8" s="94" t="n">
-        <v>-3.74</v>
-      </c>
-      <c r="Y8" s="94" t="n">
+      <c r="U8" s="95" t="n">
         <v>-10.62</v>
       </c>
-      <c r="Z8" s="94" t="n">
+      <c r="V8" s="95" t="n">
         <v>-12.51</v>
       </c>
-      <c r="AA8" s="94" t="n">
+      <c r="W8" s="95" t="n">
         <v>-12.61</v>
       </c>
-      <c r="AB8" s="94" t="n">
+      <c r="X8" s="95" t="n">
         <v>-14.58</v>
       </c>
-      <c r="AC8" s="94" t="n">
+      <c r="Y8" s="95" t="n">
         <v>-16.03</v>
       </c>
-      <c r="AD8" s="94" t="n">
-        <v>-16.03</v>
-      </c>
-      <c r="AE8" s="94" t="n">
+      <c r="Z8" s="95" t="n">
         <v>-16.65</v>
       </c>
+      <c r="AA8" s="95" t="n">
+        <v>-18.48</v>
+      </c>
+      <c r="AB8" s="95" t="n">
+        <v>-18.74</v>
+      </c>
+      <c r="AC8" s="95" t="n">
+        <v>-18.74</v>
+      </c>
+      <c r="AD8" s="95" t="n">
+        <v>-18.74</v>
+      </c>
+      <c r="AE8" s="95" t="n">
+        <v>-19.06</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="93" t="inlineStr">
+      <c r="A9" s="94" t="inlineStr">
         <is>
           <t>kc:RS5</t>
         </is>
       </c>
-      <c r="B9" s="94" t="n">
+      <c r="B9" s="95" t="n">
         <v>65.73999999999999</v>
       </c>
-      <c r="C9" s="94" t="n">
+      <c r="C9" s="95" t="n">
         <v>68.8</v>
       </c>
-      <c r="D9" s="94" t="n">
+      <c r="D9" s="95" t="n">
         <v>74.88</v>
       </c>
-      <c r="E9" s="94" t="n">
+      <c r="E9" s="95" t="n">
         <v>71.91</v>
       </c>
-      <c r="F9" s="94" t="n">
-        <v>71.91</v>
-      </c>
-      <c r="G9" s="94" t="n">
+      <c r="F9" s="95" t="n">
         <v>50.48</v>
       </c>
-      <c r="H9" s="94" t="n">
+      <c r="G9" s="95" t="n">
         <v>49.43</v>
       </c>
-      <c r="I9" s="94" t="n">
+      <c r="H9" s="95" t="n">
         <v>55.91</v>
       </c>
-      <c r="J9" s="94" t="n">
+      <c r="I9" s="95" t="n">
         <v>63.75</v>
       </c>
-      <c r="K9" s="94" t="n">
+      <c r="J9" s="95" t="n">
         <v>59.18</v>
       </c>
-      <c r="L9" s="94" t="n">
-        <v>59.18</v>
-      </c>
-      <c r="M9" s="94" t="n">
+      <c r="K9" s="95" t="n">
         <v>74.52</v>
       </c>
-      <c r="N9" s="94" t="n">
+      <c r="L9" s="95" t="n">
         <v>89.13</v>
       </c>
-      <c r="O9" s="94" t="n">
+      <c r="M9" s="95" t="n">
         <v>98.36</v>
       </c>
-      <c r="P9" s="94" t="n">
+      <c r="N9" s="95" t="n">
         <v>96.84</v>
       </c>
-      <c r="Q9" s="94" t="n">
+      <c r="O9" s="95" t="n">
         <v>96.84</v>
       </c>
-      <c r="R9" s="94" t="n">
+      <c r="P9" s="95" t="n">
         <v>96.84</v>
       </c>
-      <c r="S9" s="94" t="n">
+      <c r="Q9" s="95" t="n">
         <v>96.84</v>
       </c>
-      <c r="T9" s="94" t="n">
+      <c r="R9" s="95" t="n">
         <v>96.84</v>
       </c>
-      <c r="U9" s="94" t="n">
+      <c r="S9" s="95" t="n">
         <v>96.84</v>
       </c>
-      <c r="V9" s="94" t="n">
-        <v>96.84</v>
-      </c>
-      <c r="W9" s="94" t="n">
+      <c r="T9" s="95" t="n">
         <v>91.06999999999999</v>
       </c>
-      <c r="X9" s="94" t="n">
-        <v>91.06999999999999</v>
-      </c>
-      <c r="Y9" s="94" t="n">
+      <c r="U9" s="95" t="n">
         <v>81.48999999999999</v>
       </c>
-      <c r="Z9" s="94" t="n">
+      <c r="V9" s="95" t="n">
         <v>64.94</v>
       </c>
-      <c r="AA9" s="94" t="n">
+      <c r="W9" s="95" t="n">
         <v>64.66</v>
       </c>
-      <c r="AB9" s="94" t="n">
+      <c r="X9" s="95" t="n">
         <v>23.69</v>
       </c>
-      <c r="AC9" s="94" t="n">
+      <c r="Y9" s="95" t="n">
         <v>29.81</v>
       </c>
-      <c r="AD9" s="94" t="n">
-        <v>29.81</v>
-      </c>
-      <c r="AE9" s="94" t="n">
+      <c r="Z9" s="95" t="n">
         <v>33.91</v>
+      </c>
+      <c r="AA9" s="95" t="n">
+        <v>22.82</v>
+      </c>
+      <c r="AB9" s="95" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="AC9" s="95" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="AD9" s="95" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="AE9" s="95" t="n">
+        <v>35.28</v>
       </c>
     </row>
     <row r="10">
@@ -7413,232 +7413,232 @@
           <t>red</t>
         </is>
       </c>
-      <c r="F10" s="92" t="inlineStr">
+      <c r="F10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K10" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G10" s="91" t="inlineStr">
+      <c r="M10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Y10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H10" s="91" t="inlineStr">
+      <c r="AA10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD10" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I10" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="J10" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="K10" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="L10" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="M10" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA10" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB10" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC10" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD10" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE10" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="93" t="inlineStr">
+      <c r="A11" s="94" t="inlineStr">
         <is>
           <t>cy:RNG60</t>
         </is>
       </c>
-      <c r="B11" s="94" t="n">
+      <c r="B11" s="95" t="n">
         <v>27.92</v>
       </c>
-      <c r="C11" s="94" t="n">
+      <c r="C11" s="95" t="n">
         <v>28.48</v>
       </c>
-      <c r="D11" s="94" t="n">
+      <c r="D11" s="95" t="n">
         <v>28.68</v>
       </c>
-      <c r="E11" s="94" t="n">
+      <c r="E11" s="95" t="n">
         <v>29.39</v>
       </c>
-      <c r="F11" s="94" t="n">
-        <v>29.39</v>
-      </c>
-      <c r="G11" s="94" t="n">
+      <c r="F11" s="95" t="n">
         <v>19.87</v>
       </c>
-      <c r="H11" s="94" t="n">
+      <c r="G11" s="95" t="n">
         <v>21.93</v>
       </c>
-      <c r="I11" s="94" t="n">
+      <c r="H11" s="95" t="n">
         <v>23.9</v>
       </c>
-      <c r="J11" s="94" t="n">
+      <c r="I11" s="95" t="n">
         <v>27.91</v>
       </c>
-      <c r="K11" s="94" t="n">
+      <c r="J11" s="95" t="n">
         <v>27.24</v>
       </c>
-      <c r="L11" s="94" t="n">
-        <v>27.24</v>
-      </c>
-      <c r="M11" s="94" t="n">
+      <c r="K11" s="95" t="n">
         <v>33.94</v>
       </c>
-      <c r="N11" s="94" t="n">
+      <c r="L11" s="95" t="n">
         <v>39.99</v>
       </c>
-      <c r="O11" s="94" t="n">
+      <c r="M11" s="95" t="n">
         <v>54.04</v>
       </c>
-      <c r="P11" s="94" t="n">
+      <c r="N11" s="95" t="n">
         <v>32.05</v>
       </c>
-      <c r="Q11" s="94" t="n">
+      <c r="O11" s="95" t="n">
         <v>32.05</v>
       </c>
-      <c r="R11" s="94" t="n">
+      <c r="P11" s="95" t="n">
         <v>32.05</v>
       </c>
-      <c r="S11" s="94" t="n">
+      <c r="Q11" s="95" t="n">
         <v>32.05</v>
       </c>
-      <c r="T11" s="94" t="n">
+      <c r="R11" s="95" t="n">
         <v>32.05</v>
       </c>
-      <c r="U11" s="94" t="n">
+      <c r="S11" s="95" t="n">
         <v>32.05</v>
       </c>
-      <c r="V11" s="94" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="W11" s="94" t="n">
+      <c r="T11" s="95" t="n">
         <v>13.58</v>
       </c>
-      <c r="X11" s="94" t="n">
-        <v>13.58</v>
-      </c>
-      <c r="Y11" s="94" t="n">
+      <c r="U11" s="95" t="n">
         <v>2.95</v>
       </c>
-      <c r="Z11" s="94" t="n">
+      <c r="V11" s="95" t="n">
         <v>-2.45</v>
       </c>
-      <c r="AA11" s="94" t="n">
+      <c r="W11" s="95" t="n">
         <v>-4.05</v>
       </c>
-      <c r="AB11" s="94" t="n">
+      <c r="X11" s="95" t="n">
         <v>-10.14</v>
       </c>
-      <c r="AC11" s="94" t="n">
+      <c r="Y11" s="95" t="n">
         <v>-11.21</v>
       </c>
-      <c r="AD11" s="94" t="n">
-        <v>-11.21</v>
-      </c>
-      <c r="AE11" s="94" t="n">
+      <c r="Z11" s="95" t="n">
         <v>-9.029999999999999</v>
+      </c>
+      <c r="AA11" s="95" t="n">
+        <v>-11.44</v>
+      </c>
+      <c r="AB11" s="95" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="AC11" s="95" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="AD11" s="95" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="AE11" s="95" t="n">
+        <v>-11.96</v>
       </c>
     </row>
     <row r="12">
@@ -7647,95 +7647,95 @@
           <t>cy:RNG120</t>
         </is>
       </c>
-      <c r="B12" s="94" t="n">
+      <c r="B12" s="95" t="n">
         <v>25.79</v>
       </c>
-      <c r="C12" s="94" t="n">
+      <c r="C12" s="95" t="n">
         <v>26.65</v>
       </c>
-      <c r="D12" s="94" t="n">
+      <c r="D12" s="95" t="n">
         <v>25.87</v>
       </c>
-      <c r="E12" s="94" t="n">
+      <c r="E12" s="95" t="n">
         <v>22.8</v>
       </c>
-      <c r="F12" s="94" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G12" s="94" t="n">
+      <c r="F12" s="95" t="n">
         <v>13.14</v>
       </c>
-      <c r="H12" s="94" t="n">
+      <c r="G12" s="95" t="n">
         <v>15.89</v>
       </c>
-      <c r="I12" s="94" t="n">
+      <c r="H12" s="95" t="n">
         <v>16.18</v>
       </c>
-      <c r="J12" s="94" t="n">
+      <c r="I12" s="95" t="n">
         <v>22.27</v>
       </c>
-      <c r="K12" s="94" t="n">
+      <c r="J12" s="95" t="n">
         <v>17.89</v>
       </c>
-      <c r="L12" s="94" t="n">
-        <v>17.89</v>
-      </c>
-      <c r="M12" s="94" t="n">
+      <c r="K12" s="95" t="n">
         <v>23.63</v>
       </c>
-      <c r="N12" s="94" t="n">
+      <c r="L12" s="95" t="n">
         <v>24.76</v>
       </c>
-      <c r="O12" s="94" t="n">
+      <c r="M12" s="95" t="n">
         <v>41.13</v>
       </c>
-      <c r="P12" s="94" t="n">
+      <c r="N12" s="95" t="n">
         <v>18.19</v>
       </c>
-      <c r="Q12" s="94" t="n">
+      <c r="O12" s="95" t="n">
         <v>18.19</v>
       </c>
-      <c r="R12" s="94" t="n">
+      <c r="P12" s="95" t="n">
         <v>18.19</v>
       </c>
-      <c r="S12" s="94" t="n">
+      <c r="Q12" s="95" t="n">
         <v>18.19</v>
       </c>
-      <c r="T12" s="94" t="n">
+      <c r="R12" s="95" t="n">
         <v>18.19</v>
       </c>
-      <c r="U12" s="94" t="n">
+      <c r="S12" s="95" t="n">
         <v>18.19</v>
       </c>
-      <c r="V12" s="94" t="n">
-        <v>18.19</v>
-      </c>
-      <c r="W12" s="94" t="n">
+      <c r="T12" s="95" t="n">
         <v>1.34</v>
       </c>
-      <c r="X12" s="94" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Y12" s="94" t="n">
+      <c r="U12" s="95" t="n">
         <v>-8.44</v>
       </c>
-      <c r="Z12" s="94" t="n">
+      <c r="V12" s="95" t="n">
         <v>-9.720000000000001</v>
       </c>
-      <c r="AA12" s="94" t="n">
+      <c r="W12" s="95" t="n">
         <v>-10.6</v>
       </c>
-      <c r="AB12" s="94" t="n">
+      <c r="X12" s="95" t="n">
         <v>-14.49</v>
       </c>
-      <c r="AC12" s="94" t="n">
+      <c r="Y12" s="95" t="n">
         <v>-16.56</v>
       </c>
-      <c r="AD12" s="94" t="n">
-        <v>-16.56</v>
-      </c>
-      <c r="AE12" s="94" t="n">
+      <c r="Z12" s="95" t="n">
         <v>-15.65</v>
+      </c>
+      <c r="AA12" s="95" t="n">
+        <v>-17.96</v>
+      </c>
+      <c r="AB12" s="95" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="AC12" s="95" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="AD12" s="95" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="AE12" s="95" t="n">
+        <v>-18.72</v>
       </c>
     </row>
     <row r="13">
@@ -7744,95 +7744,95 @@
           <t>cy:RS3</t>
         </is>
       </c>
-      <c r="B13" s="94" t="n">
+      <c r="B13" s="95" t="n">
         <v>66.13</v>
       </c>
-      <c r="C13" s="94" t="n">
+      <c r="C13" s="95" t="n">
         <v>74.31</v>
       </c>
-      <c r="D13" s="94" t="n">
+      <c r="D13" s="95" t="n">
         <v>73.05</v>
       </c>
-      <c r="E13" s="94" t="n">
+      <c r="E13" s="95" t="n">
         <v>70.86</v>
       </c>
-      <c r="F13" s="94" t="n">
-        <v>70.86</v>
-      </c>
-      <c r="G13" s="94" t="n">
+      <c r="F13" s="95" t="n">
         <v>31.37</v>
       </c>
-      <c r="H13" s="94" t="n">
+      <c r="G13" s="95" t="n">
         <v>32.55</v>
       </c>
-      <c r="I13" s="94" t="n">
+      <c r="H13" s="95" t="n">
         <v>39.59</v>
       </c>
-      <c r="J13" s="94" t="n">
+      <c r="I13" s="95" t="n">
         <v>50.6</v>
       </c>
-      <c r="K13" s="94" t="n">
+      <c r="J13" s="95" t="n">
         <v>42.18</v>
       </c>
-      <c r="L13" s="94" t="n">
-        <v>42.18</v>
-      </c>
-      <c r="M13" s="94" t="n">
+      <c r="K13" s="95" t="n">
         <v>55.03</v>
       </c>
-      <c r="N13" s="94" t="n">
+      <c r="L13" s="95" t="n">
         <v>62.67</v>
       </c>
-      <c r="O13" s="94" t="n">
+      <c r="M13" s="95" t="n">
         <v>99.77</v>
       </c>
-      <c r="P13" s="94" t="n">
+      <c r="N13" s="95" t="n">
         <v>99.48</v>
       </c>
-      <c r="Q13" s="94" t="n">
+      <c r="O13" s="95" t="n">
         <v>99.48</v>
       </c>
-      <c r="R13" s="94" t="n">
+      <c r="P13" s="95" t="n">
         <v>99.48</v>
       </c>
-      <c r="S13" s="94" t="n">
+      <c r="Q13" s="95" t="n">
         <v>99.48</v>
       </c>
-      <c r="T13" s="94" t="n">
+      <c r="R13" s="95" t="n">
         <v>99.48</v>
       </c>
-      <c r="U13" s="94" t="n">
+      <c r="S13" s="95" t="n">
         <v>99.48</v>
       </c>
-      <c r="V13" s="94" t="n">
-        <v>99.48</v>
-      </c>
-      <c r="W13" s="94" t="n">
+      <c r="T13" s="95" t="n">
         <v>98.62</v>
       </c>
-      <c r="X13" s="94" t="n">
-        <v>98.62</v>
-      </c>
-      <c r="Y13" s="94" t="n">
+      <c r="U13" s="95" t="n">
         <v>96</v>
       </c>
-      <c r="Z13" s="94" t="n">
+      <c r="V13" s="95" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="AA13" s="94" t="n">
+      <c r="W13" s="95" t="n">
         <v>88.09</v>
       </c>
-      <c r="AB13" s="94" t="n">
+      <c r="X13" s="95" t="n">
         <v>30.34</v>
       </c>
-      <c r="AC13" s="94" t="n">
+      <c r="Y13" s="95" t="n">
         <v>39.51</v>
       </c>
-      <c r="AD13" s="94" t="n">
-        <v>39.51</v>
-      </c>
-      <c r="AE13" s="94" t="n">
+      <c r="Z13" s="95" t="n">
         <v>58.67</v>
+      </c>
+      <c r="AA13" s="95" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="AB13" s="95" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="AC13" s="95" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="AD13" s="95" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="AE13" s="95" t="n">
+        <v>54.57</v>
       </c>
     </row>
     <row r="14">
@@ -7846,12 +7846,12 @@
           <t>red</t>
         </is>
       </c>
-      <c r="C14" s="95" t="inlineStr">
+      <c r="C14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D14" s="95" t="inlineStr">
+      <c r="D14" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -7861,232 +7861,232 @@
           <t>red</t>
         </is>
       </c>
-      <c r="F14" s="92" t="inlineStr">
+      <c r="F14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L14" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M14" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G14" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="H14" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="I14" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="J14" s="91" t="inlineStr">
+      <c r="O14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AC14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AD14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K14" s="91" t="inlineStr">
+      <c r="AE14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="M14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N14" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="O14" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="93" t="inlineStr">
+      <c r="A15" s="94" t="inlineStr">
         <is>
           <t>hk50:RNG60</t>
         </is>
       </c>
-      <c r="B15" s="94" t="n">
+      <c r="B15" s="95" t="n">
         <v>22.08</v>
       </c>
-      <c r="C15" s="94" t="n">
+      <c r="C15" s="95" t="n">
         <v>18.42</v>
       </c>
-      <c r="D15" s="94" t="n">
+      <c r="D15" s="95" t="n">
         <v>17.23</v>
       </c>
-      <c r="E15" s="94" t="n">
+      <c r="E15" s="95" t="n">
         <v>17.96</v>
       </c>
-      <c r="F15" s="94" t="n">
+      <c r="F15" s="95" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="G15" s="95" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="H15" s="95" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="I15" s="95" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="J15" s="95" t="n">
         <v>17.96</v>
       </c>
-      <c r="G15" s="94" t="n">
-        <v>15.28</v>
-      </c>
-      <c r="H15" s="94" t="n">
-        <v>14.11</v>
-      </c>
-      <c r="I15" s="94" t="n">
-        <v>14.54</v>
-      </c>
-      <c r="J15" s="94" t="n">
-        <v>18.98</v>
-      </c>
-      <c r="K15" s="94" t="n">
+      <c r="K15" s="95" t="n">
         <v>17.96</v>
       </c>
-      <c r="L15" s="94" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="M15" s="94" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="N15" s="94" t="n">
+      <c r="L15" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="O15" s="94" t="n">
+      <c r="M15" s="95" t="n">
         <v>17.35</v>
       </c>
-      <c r="P15" s="94" t="n">
+      <c r="N15" s="95" t="n">
         <v>32.21</v>
       </c>
-      <c r="Q15" s="94" t="n">
+      <c r="O15" s="95" t="n">
         <v>29.75</v>
       </c>
-      <c r="R15" s="94" t="n">
-        <v>29.75</v>
-      </c>
-      <c r="S15" s="94" t="n">
+      <c r="P15" s="95" t="n">
         <v>26.19</v>
       </c>
-      <c r="T15" s="94" t="n">
+      <c r="Q15" s="95" t="n">
         <v>26.09</v>
       </c>
-      <c r="U15" s="94" t="n">
+      <c r="R15" s="95" t="n">
         <v>17.23</v>
       </c>
-      <c r="V15" s="94" t="n">
+      <c r="S15" s="95" t="n">
         <v>17.23</v>
       </c>
-      <c r="W15" s="94" t="n">
+      <c r="T15" s="95" t="n">
         <v>14.76</v>
       </c>
-      <c r="X15" s="94" t="n">
-        <v>14.76</v>
-      </c>
-      <c r="Y15" s="94" t="n">
+      <c r="U15" s="95" t="n">
         <v>12.13</v>
       </c>
-      <c r="Z15" s="94" t="n">
+      <c r="V15" s="95" t="n">
         <v>7.96</v>
       </c>
-      <c r="AA15" s="94" t="n">
+      <c r="W15" s="95" t="n">
         <v>7.25</v>
       </c>
-      <c r="AB15" s="94" t="n">
+      <c r="X15" s="95" t="n">
         <v>0.87</v>
       </c>
-      <c r="AC15" s="94" t="n">
+      <c r="Y15" s="95" t="n">
         <v>1.03</v>
       </c>
-      <c r="AD15" s="94" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AE15" s="94" t="n">
+      <c r="Z15" s="95" t="n">
         <v>-0.08</v>
+      </c>
+      <c r="AA15" s="95" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="AB15" s="95" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="AC15" s="95" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="AD15" s="95" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="AE15" s="95" t="n">
+        <v>-3.77</v>
       </c>
     </row>
     <row r="16">
@@ -8095,95 +8095,95 @@
           <t>hk50:RNG120</t>
         </is>
       </c>
-      <c r="B16" s="94" t="n">
+      <c r="B16" s="95" t="n">
         <v>17.61</v>
       </c>
-      <c r="C16" s="94" t="n">
+      <c r="C16" s="95" t="n">
         <v>18.6</v>
       </c>
-      <c r="D16" s="94" t="n">
+      <c r="D16" s="95" t="n">
         <v>19.05</v>
       </c>
-      <c r="E16" s="94" t="n">
+      <c r="E16" s="95" t="n">
         <v>23.62</v>
       </c>
-      <c r="F16" s="94" t="n">
-        <v>23.62</v>
-      </c>
-      <c r="G16" s="94" t="n">
+      <c r="F16" s="95" t="n">
         <v>21.61</v>
       </c>
-      <c r="H16" s="94" t="n">
+      <c r="G16" s="95" t="n">
         <v>25.04</v>
       </c>
-      <c r="I16" s="94" t="n">
+      <c r="H16" s="95" t="n">
         <v>24</v>
       </c>
-      <c r="J16" s="94" t="n">
+      <c r="I16" s="95" t="n">
         <v>29.79</v>
       </c>
-      <c r="K16" s="94" t="n">
+      <c r="J16" s="95" t="n">
         <v>30.79</v>
       </c>
-      <c r="L16" s="94" t="n">
+      <c r="K16" s="95" t="n">
         <v>30.79</v>
       </c>
-      <c r="M16" s="94" t="n">
-        <v>30.79</v>
-      </c>
-      <c r="N16" s="94" t="n">
+      <c r="L16" s="95" t="n">
         <v>24.32</v>
       </c>
-      <c r="O16" s="94" t="n">
+      <c r="M16" s="95" t="n">
         <v>25.15</v>
       </c>
-      <c r="P16" s="94" t="n">
+      <c r="N16" s="95" t="n">
         <v>35.13</v>
       </c>
-      <c r="Q16" s="94" t="n">
+      <c r="O16" s="95" t="n">
         <v>32.66</v>
       </c>
-      <c r="R16" s="94" t="n">
-        <v>32.66</v>
-      </c>
-      <c r="S16" s="94" t="n">
+      <c r="P16" s="95" t="n">
         <v>31.41</v>
       </c>
-      <c r="T16" s="94" t="n">
+      <c r="Q16" s="95" t="n">
         <v>34.13</v>
       </c>
-      <c r="U16" s="94" t="n">
+      <c r="R16" s="95" t="n">
         <v>26.37</v>
       </c>
-      <c r="V16" s="94" t="n">
+      <c r="S16" s="95" t="n">
         <v>26.37</v>
       </c>
-      <c r="W16" s="94" t="n">
+      <c r="T16" s="95" t="n">
         <v>23.36</v>
       </c>
-      <c r="X16" s="94" t="n">
-        <v>23.36</v>
-      </c>
-      <c r="Y16" s="94" t="n">
+      <c r="U16" s="95" t="n">
         <v>17.68</v>
       </c>
-      <c r="Z16" s="94" t="n">
+      <c r="V16" s="95" t="n">
         <v>15.64</v>
       </c>
-      <c r="AA16" s="94" t="n">
+      <c r="W16" s="95" t="n">
         <v>15.91</v>
       </c>
-      <c r="AB16" s="94" t="n">
+      <c r="X16" s="95" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AC16" s="94" t="n">
+      <c r="Y16" s="95" t="n">
         <v>10.84</v>
       </c>
-      <c r="AD16" s="94" t="n">
-        <v>10.84</v>
-      </c>
-      <c r="AE16" s="94" t="n">
+      <c r="Z16" s="95" t="n">
         <v>9.17</v>
+      </c>
+      <c r="AA16" s="95" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AB16" s="95" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AC16" s="95" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="AD16" s="95" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AE16" s="95" t="n">
+        <v>3.01</v>
       </c>
     </row>
     <row r="17">
@@ -8192,95 +8192,95 @@
           <t>hk50:RS4</t>
         </is>
       </c>
-      <c r="B17" s="94" t="n">
+      <c r="B17" s="95" t="n">
         <v>56.18</v>
       </c>
-      <c r="C17" s="94" t="n">
+      <c r="C17" s="95" t="n">
         <v>45.12</v>
       </c>
-      <c r="D17" s="94" t="n">
+      <c r="D17" s="95" t="n">
         <v>44.29</v>
       </c>
-      <c r="E17" s="94" t="n">
+      <c r="E17" s="95" t="n">
         <v>54</v>
       </c>
-      <c r="F17" s="94" t="n">
-        <v>54</v>
-      </c>
-      <c r="G17" s="94" t="n">
+      <c r="F17" s="95" t="n">
         <v>27.44</v>
       </c>
-      <c r="H17" s="94" t="n">
+      <c r="G17" s="95" t="n">
         <v>31.33</v>
       </c>
-      <c r="I17" s="94" t="n">
+      <c r="H17" s="95" t="n">
         <v>31.85</v>
       </c>
-      <c r="J17" s="94" t="n">
+      <c r="I17" s="95" t="n">
         <v>45.61</v>
       </c>
-      <c r="K17" s="94" t="n">
+      <c r="J17" s="95" t="n">
         <v>48.87</v>
       </c>
-      <c r="L17" s="94" t="n">
+      <c r="K17" s="95" t="n">
         <v>48.87</v>
       </c>
-      <c r="M17" s="94" t="n">
-        <v>48.87</v>
-      </c>
-      <c r="N17" s="94" t="n">
+      <c r="L17" s="95" t="n">
         <v>35.54</v>
       </c>
-      <c r="O17" s="94" t="n">
+      <c r="M17" s="95" t="n">
         <v>39.14</v>
       </c>
-      <c r="P17" s="94" t="n">
+      <c r="N17" s="95" t="n">
         <v>91.23999999999999</v>
       </c>
-      <c r="Q17" s="94" t="n">
+      <c r="O17" s="95" t="n">
         <v>89.48999999999999</v>
       </c>
-      <c r="R17" s="94" t="n">
-        <v>89.48999999999999</v>
-      </c>
-      <c r="S17" s="94" t="n">
+      <c r="P17" s="95" t="n">
         <v>85.84</v>
       </c>
-      <c r="T17" s="94" t="n">
+      <c r="Q17" s="95" t="n">
         <v>99.56999999999999</v>
       </c>
-      <c r="U17" s="94" t="n">
+      <c r="R17" s="95" t="n">
         <v>99.18000000000001</v>
       </c>
-      <c r="V17" s="94" t="n">
+      <c r="S17" s="95" t="n">
         <v>99.18000000000001</v>
       </c>
-      <c r="W17" s="94" t="n">
+      <c r="T17" s="95" t="n">
         <v>98.89</v>
       </c>
-      <c r="X17" s="94" t="n">
-        <v>98.89</v>
-      </c>
-      <c r="Y17" s="94" t="n">
+      <c r="U17" s="95" t="n">
         <v>98.23</v>
       </c>
-      <c r="Z17" s="94" t="n">
+      <c r="V17" s="95" t="n">
         <v>96.44</v>
       </c>
-      <c r="AA17" s="94" t="n">
+      <c r="W17" s="95" t="n">
         <v>95.94</v>
       </c>
-      <c r="AB17" s="94" t="n">
+      <c r="X17" s="95" t="n">
         <v>89.48</v>
       </c>
-      <c r="AC17" s="94" t="n">
+      <c r="Y17" s="95" t="n">
         <v>91.13</v>
       </c>
-      <c r="AD17" s="94" t="n">
-        <v>91.13</v>
-      </c>
-      <c r="AE17" s="94" t="n">
+      <c r="Z17" s="95" t="n">
         <v>87.39</v>
+      </c>
+      <c r="AA17" s="95" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="AB17" s="95" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="AC17" s="95" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="AD17" s="95" t="n">
+        <v>54.39</v>
+      </c>
+      <c r="AE17" s="95" t="n">
+        <v>38.93</v>
       </c>
     </row>
     <row r="18">
@@ -8289,134 +8289,134 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="91" t="inlineStr">
+      <c r="B18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C18" s="91" t="inlineStr">
+      <c r="D18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D18" s="91" t="inlineStr">
+      <c r="E18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E18" s="92" t="inlineStr">
+      <c r="G18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F18" s="92" t="inlineStr">
+      <c r="H18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G18" s="91" t="inlineStr">
+      <c r="J18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N18" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H18" s="92" t="inlineStr">
+      <c r="Q18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I18" s="91" t="inlineStr">
+      <c r="X18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="J18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="K18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="L18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P18" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Q18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z18" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AB18" s="92" t="inlineStr">
@@ -8446,95 +8446,95 @@
           <t>us500:RNG60</t>
         </is>
       </c>
-      <c r="B19" s="94" t="n">
+      <c r="B19" s="95" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="C19" s="95" t="n">
         <v>7.1</v>
       </c>
-      <c r="C19" s="94" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="D19" s="94" t="n">
+      <c r="D19" s="95" t="n">
         <v>7.23</v>
       </c>
-      <c r="E19" s="94" t="n">
+      <c r="E19" s="95" t="n">
         <v>8.619999999999999</v>
       </c>
-      <c r="F19" s="94" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="G19" s="94" t="n">
+      <c r="F19" s="95" t="n">
         <v>7.63</v>
       </c>
-      <c r="H19" s="94" t="n">
+      <c r="G19" s="95" t="n">
         <v>5.16</v>
       </c>
-      <c r="I19" s="94" t="n">
+      <c r="H19" s="95" t="n">
         <v>4.51</v>
       </c>
-      <c r="J19" s="94" t="n">
+      <c r="I19" s="95" t="n">
         <v>6.45</v>
       </c>
-      <c r="K19" s="94" t="n">
+      <c r="J19" s="95" t="n">
         <v>4.88</v>
       </c>
-      <c r="L19" s="94" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M19" s="94" t="n">
+      <c r="K19" s="95" t="n">
         <v>3.43</v>
       </c>
-      <c r="N19" s="94" t="n">
+      <c r="L19" s="95" t="n">
         <v>2.2</v>
       </c>
-      <c r="O19" s="94" t="n">
+      <c r="M19" s="95" t="n">
         <v>2.13</v>
       </c>
-      <c r="P19" s="94" t="n">
+      <c r="N19" s="95" t="n">
         <v>1.44</v>
       </c>
-      <c r="Q19" s="94" t="n">
+      <c r="O19" s="95" t="n">
         <v>2.98</v>
       </c>
-      <c r="R19" s="94" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="S19" s="94" t="n">
+      <c r="P19" s="95" t="n">
         <v>1.17</v>
       </c>
-      <c r="T19" s="94" t="n">
+      <c r="Q19" s="95" t="n">
         <v>2.38</v>
       </c>
-      <c r="U19" s="94" t="n">
+      <c r="R19" s="95" t="n">
         <v>2.44</v>
       </c>
-      <c r="V19" s="94" t="n">
+      <c r="S19" s="95" t="n">
         <v>3.51</v>
       </c>
-      <c r="W19" s="94" t="n">
+      <c r="T19" s="95" t="n">
         <v>3.63</v>
       </c>
-      <c r="X19" s="94" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="Y19" s="94" t="n">
+      <c r="U19" s="95" t="n">
         <v>4.29</v>
       </c>
-      <c r="Z19" s="94" t="n">
+      <c r="V19" s="95" t="n">
         <v>4.51</v>
       </c>
-      <c r="AA19" s="94" t="n">
+      <c r="W19" s="95" t="n">
         <v>4.99</v>
       </c>
-      <c r="AB19" s="94" t="n">
+      <c r="X19" s="95" t="n">
         <v>4.3</v>
       </c>
-      <c r="AC19" s="94" t="n">
+      <c r="Y19" s="95" t="n">
         <v>4.1</v>
       </c>
-      <c r="AD19" s="94" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AE19" s="94" t="n">
+      <c r="Z19" s="95" t="n">
         <v>4.47</v>
+      </c>
+      <c r="AA19" s="95" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AB19" s="95" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AC19" s="95" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AD19" s="95" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AE19" s="95" t="n">
+        <v>2.24</v>
       </c>
     </row>
     <row r="20">
@@ -8543,192 +8543,192 @@
           <t>us500:RNG120</t>
         </is>
       </c>
-      <c r="B20" s="94" t="n">
+      <c r="B20" s="95" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="C20" s="95" t="n">
         <v>16.6</v>
       </c>
-      <c r="C20" s="94" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="D20" s="94" t="n">
+      <c r="D20" s="95" t="n">
         <v>16.25</v>
       </c>
-      <c r="E20" s="94" t="n">
+      <c r="E20" s="95" t="n">
         <v>14.63</v>
       </c>
-      <c r="F20" s="94" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="G20" s="94" t="n">
+      <c r="F20" s="95" t="n">
         <v>14.54</v>
       </c>
-      <c r="H20" s="94" t="n">
+      <c r="G20" s="95" t="n">
         <v>15.73</v>
       </c>
-      <c r="I20" s="94" t="n">
+      <c r="H20" s="95" t="n">
         <v>14.66</v>
       </c>
-      <c r="J20" s="94" t="n">
+      <c r="I20" s="95" t="n">
         <v>15.57</v>
       </c>
-      <c r="K20" s="94" t="n">
+      <c r="J20" s="95" t="n">
         <v>16.05</v>
       </c>
-      <c r="L20" s="94" t="n">
-        <v>16.05</v>
-      </c>
-      <c r="M20" s="94" t="n">
+      <c r="K20" s="95" t="n">
         <v>16.36</v>
       </c>
-      <c r="N20" s="94" t="n">
+      <c r="L20" s="95" t="n">
         <v>15.58</v>
       </c>
-      <c r="O20" s="94" t="n">
+      <c r="M20" s="95" t="n">
         <v>14.51</v>
       </c>
-      <c r="P20" s="94" t="n">
+      <c r="N20" s="95" t="n">
         <v>12.76</v>
       </c>
-      <c r="Q20" s="94" t="n">
+      <c r="O20" s="95" t="n">
         <v>13.62</v>
       </c>
-      <c r="R20" s="94" t="n">
-        <v>13.62</v>
-      </c>
-      <c r="S20" s="94" t="n">
+      <c r="P20" s="95" t="n">
         <v>11.25</v>
       </c>
-      <c r="T20" s="94" t="n">
+      <c r="Q20" s="95" t="n">
         <v>9.82</v>
       </c>
-      <c r="U20" s="94" t="n">
+      <c r="R20" s="95" t="n">
         <v>10.62</v>
       </c>
-      <c r="V20" s="94" t="n">
+      <c r="S20" s="95" t="n">
         <v>10.61</v>
       </c>
-      <c r="W20" s="94" t="n">
+      <c r="T20" s="95" t="n">
         <v>10.3</v>
       </c>
-      <c r="X20" s="94" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="Y20" s="94" t="n">
+      <c r="U20" s="95" t="n">
         <v>10.4</v>
       </c>
-      <c r="Z20" s="94" t="n">
+      <c r="V20" s="95" t="n">
         <v>11.17</v>
       </c>
-      <c r="AA20" s="94" t="n">
+      <c r="W20" s="95" t="n">
         <v>10.01</v>
       </c>
-      <c r="AB20" s="94" t="n">
+      <c r="X20" s="95" t="n">
         <v>9.85</v>
       </c>
-      <c r="AC20" s="94" t="n">
+      <c r="Y20" s="95" t="n">
         <v>8.75</v>
       </c>
-      <c r="AD20" s="94" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="AE20" s="94" t="n">
+      <c r="Z20" s="95" t="n">
         <v>8.74</v>
       </c>
+      <c r="AA20" s="95" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="AB20" s="95" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="AC20" s="95" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="AD20" s="95" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="AE20" s="95" t="n">
+        <v>6.76</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="96" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
-      <c r="B21" s="94" t="n">
+      <c r="B21" s="95" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="C21" s="95" t="n">
         <v>47</v>
       </c>
-      <c r="C21" s="94" t="n">
-        <v>47</v>
-      </c>
-      <c r="D21" s="94" t="n">
+      <c r="D21" s="95" t="n">
         <v>55.4</v>
       </c>
-      <c r="E21" s="94" t="n">
+      <c r="E21" s="95" t="n">
         <v>84.39</v>
       </c>
-      <c r="F21" s="94" t="n">
+      <c r="F21" s="95" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="G21" s="95" t="n">
+        <v>65.73999999999999</v>
+      </c>
+      <c r="H21" s="95" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="I21" s="95" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="J21" s="95" t="n">
+        <v>84.56999999999999</v>
+      </c>
+      <c r="K21" s="95" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="L21" s="95" t="n">
+        <v>83.12</v>
+      </c>
+      <c r="M21" s="95" t="n">
+        <v>69.18000000000001</v>
+      </c>
+      <c r="N21" s="95" t="n">
+        <v>30.41</v>
+      </c>
+      <c r="O21" s="95" t="n">
+        <v>81.84</v>
+      </c>
+      <c r="P21" s="95" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="Q21" s="95" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="R21" s="95" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="S21" s="95" t="n">
+        <v>86.19</v>
+      </c>
+      <c r="T21" s="95" t="n">
+        <v>60.63</v>
+      </c>
+      <c r="U21" s="95" t="n">
+        <v>83.51000000000001</v>
+      </c>
+      <c r="V21" s="95" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="W21" s="95" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="X21" s="95" t="n">
         <v>84.39</v>
       </c>
-      <c r="G21" s="94" t="n">
-        <v>63.88</v>
-      </c>
-      <c r="H21" s="94" t="n">
-        <v>65.73999999999999</v>
-      </c>
-      <c r="I21" s="94" t="n">
-        <v>43.25</v>
-      </c>
-      <c r="J21" s="94" t="n">
-        <v>93.59999999999999</v>
-      </c>
-      <c r="K21" s="94" t="n">
-        <v>84.56999999999999</v>
-      </c>
-      <c r="L21" s="94" t="n">
-        <v>84.56999999999999</v>
-      </c>
-      <c r="M21" s="94" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="N21" s="94" t="n">
-        <v>83.12</v>
-      </c>
-      <c r="O21" s="94" t="n">
-        <v>69.18000000000001</v>
-      </c>
-      <c r="P21" s="94" t="n">
-        <v>30.41</v>
-      </c>
-      <c r="Q21" s="94" t="n">
-        <v>81.84</v>
-      </c>
-      <c r="R21" s="94" t="n">
-        <v>81.84</v>
-      </c>
-      <c r="S21" s="94" t="n">
-        <v>15.76</v>
-      </c>
-      <c r="T21" s="94" t="n">
-        <v>23.93</v>
-      </c>
-      <c r="U21" s="94" t="n">
-        <v>22.27</v>
-      </c>
-      <c r="V21" s="94" t="n">
-        <v>86.19</v>
-      </c>
-      <c r="W21" s="94" t="n">
-        <v>60.63</v>
-      </c>
-      <c r="X21" s="94" t="n">
-        <v>60.63</v>
-      </c>
-      <c r="Y21" s="94" t="n">
-        <v>83.51000000000001</v>
-      </c>
-      <c r="Z21" s="94" t="n">
-        <v>58.19</v>
-      </c>
-      <c r="AA21" s="94" t="n">
-        <v>90.16</v>
-      </c>
-      <c r="AB21" s="94" t="n">
-        <v>84.39</v>
-      </c>
-      <c r="AC21" s="94" t="n">
+      <c r="Y21" s="95" t="n">
         <v>76.79000000000001</v>
       </c>
-      <c r="AD21" s="94" t="n">
-        <v>76.79000000000001</v>
-      </c>
-      <c r="AE21" s="94" t="n">
+      <c r="Z21" s="95" t="n">
         <v>92.34</v>
+      </c>
+      <c r="AA21" s="95" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="AB21" s="95" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="AC21" s="95" t="n">
+        <v>95.83</v>
+      </c>
+      <c r="AD21" s="95" t="n">
+        <v>95.06</v>
+      </c>
+      <c r="AE21" s="95" t="n">
+        <v>91.83</v>
       </c>
     </row>
     <row r="22">
@@ -8737,129 +8737,129 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="91" t="inlineStr">
+      <c r="B22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C22" s="91" t="inlineStr">
+      <c r="D22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D22" s="91" t="inlineStr">
+      <c r="E22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E22" s="92" t="inlineStr">
+      <c r="I22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F22" s="92" t="inlineStr">
+      <c r="J22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G22" s="92" t="inlineStr">
+      <c r="K22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H22" s="92" t="inlineStr">
+      <c r="L22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I22" s="91" t="inlineStr">
+      <c r="M22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J22" s="92" t="inlineStr">
+      <c r="N22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K22" s="92" t="inlineStr">
+      <c r="P22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L22" s="92" t="inlineStr">
+      <c r="X22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M22" s="92" t="inlineStr">
+      <c r="Y22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N22" s="92" t="inlineStr">
+      <c r="Z22" s="92" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="O22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P22" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Q22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z22" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AA22" s="92" t="inlineStr">
@@ -8894,95 +8894,95 @@
           <t>us30:RNG60</t>
         </is>
       </c>
-      <c r="B23" s="94" t="n">
+      <c r="B23" s="95" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="C23" s="95" t="n">
         <v>5.88</v>
       </c>
-      <c r="C23" s="94" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="D23" s="94" t="n">
+      <c r="D23" s="95" t="n">
         <v>5.77</v>
       </c>
-      <c r="E23" s="94" t="n">
+      <c r="E23" s="95" t="n">
         <v>8.369999999999999</v>
       </c>
-      <c r="F23" s="94" t="n">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="G23" s="94" t="n">
+      <c r="F23" s="95" t="n">
         <v>8.49</v>
       </c>
-      <c r="H23" s="94" t="n">
+      <c r="G23" s="95" t="n">
         <v>6.74</v>
       </c>
-      <c r="I23" s="94" t="n">
+      <c r="H23" s="95" t="n">
         <v>5.75</v>
       </c>
-      <c r="J23" s="94" t="n">
+      <c r="I23" s="95" t="n">
         <v>6.89</v>
       </c>
-      <c r="K23" s="94" t="n">
+      <c r="J23" s="95" t="n">
         <v>5.41</v>
       </c>
-      <c r="L23" s="94" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="M23" s="94" t="n">
+      <c r="K23" s="95" t="n">
         <v>3.05</v>
       </c>
-      <c r="N23" s="94" t="n">
+      <c r="L23" s="95" t="n">
         <v>3.8</v>
       </c>
-      <c r="O23" s="94" t="n">
+      <c r="M23" s="95" t="n">
         <v>4.65</v>
       </c>
-      <c r="P23" s="94" t="n">
+      <c r="N23" s="95" t="n">
         <v>4.88</v>
       </c>
-      <c r="Q23" s="94" t="n">
+      <c r="O23" s="95" t="n">
         <v>6.54</v>
       </c>
-      <c r="R23" s="94" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="S23" s="94" t="n">
+      <c r="P23" s="95" t="n">
         <v>5.77</v>
       </c>
-      <c r="T23" s="94" t="n">
+      <c r="Q23" s="95" t="n">
         <v>7.39</v>
       </c>
-      <c r="U23" s="94" t="n">
+      <c r="R23" s="95" t="n">
         <v>7.15</v>
       </c>
-      <c r="V23" s="94" t="n">
+      <c r="S23" s="95" t="n">
         <v>7.5</v>
       </c>
-      <c r="W23" s="94" t="n">
+      <c r="T23" s="95" t="n">
         <v>7.64</v>
       </c>
-      <c r="X23" s="94" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="Y23" s="94" t="n">
+      <c r="U23" s="95" t="n">
         <v>7.23</v>
       </c>
-      <c r="Z23" s="94" t="n">
+      <c r="V23" s="95" t="n">
         <v>7.01</v>
       </c>
-      <c r="AA23" s="94" t="n">
+      <c r="W23" s="95" t="n">
         <v>7.9</v>
       </c>
-      <c r="AB23" s="94" t="n">
+      <c r="X23" s="95" t="n">
         <v>7.56</v>
       </c>
-      <c r="AC23" s="94" t="n">
+      <c r="Y23" s="95" t="n">
         <v>7.5</v>
       </c>
-      <c r="AD23" s="94" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AE23" s="94" t="n">
+      <c r="Z23" s="95" t="n">
         <v>7.45</v>
+      </c>
+      <c r="AA23" s="95" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="AB23" s="95" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="AC23" s="95" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="AD23" s="95" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="AE23" s="95" t="n">
+        <v>5.98</v>
       </c>
     </row>
     <row r="24">
@@ -8991,192 +8991,192 @@
           <t>us30:RNG120</t>
         </is>
       </c>
-      <c r="B24" s="94" t="n">
+      <c r="B24" s="95" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="C24" s="95" t="n">
         <v>13.25</v>
       </c>
-      <c r="C24" s="94" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="D24" s="94" t="n">
+      <c r="D24" s="95" t="n">
         <v>13.53</v>
       </c>
-      <c r="E24" s="94" t="n">
+      <c r="E24" s="95" t="n">
         <v>12.74</v>
       </c>
-      <c r="F24" s="94" t="n">
-        <v>12.74</v>
-      </c>
-      <c r="G24" s="94" t="n">
+      <c r="F24" s="95" t="n">
         <v>13.07</v>
       </c>
-      <c r="H24" s="94" t="n">
+      <c r="G24" s="95" t="n">
         <v>13.11</v>
       </c>
-      <c r="I24" s="94" t="n">
+      <c r="H24" s="95" t="n">
         <v>11.13</v>
       </c>
-      <c r="J24" s="94" t="n">
+      <c r="I24" s="95" t="n">
         <v>11.85</v>
       </c>
-      <c r="K24" s="94" t="n">
+      <c r="J24" s="95" t="n">
         <v>12.09</v>
       </c>
-      <c r="L24" s="94" t="n">
-        <v>12.09</v>
-      </c>
-      <c r="M24" s="94" t="n">
+      <c r="K24" s="95" t="n">
         <v>11.76</v>
       </c>
-      <c r="N24" s="94" t="n">
+      <c r="L24" s="95" t="n">
         <v>12.54</v>
       </c>
-      <c r="O24" s="94" t="n">
+      <c r="M24" s="95" t="n">
         <v>11.46</v>
       </c>
-      <c r="P24" s="94" t="n">
+      <c r="N24" s="95" t="n">
         <v>10.99</v>
       </c>
-      <c r="Q24" s="94" t="n">
+      <c r="O24" s="95" t="n">
         <v>12.24</v>
       </c>
-      <c r="R24" s="94" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="S24" s="94" t="n">
+      <c r="P24" s="95" t="n">
         <v>10.61</v>
       </c>
-      <c r="T24" s="94" t="n">
+      <c r="Q24" s="95" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="U24" s="94" t="n">
+      <c r="R24" s="95" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="V24" s="94" t="n">
+      <c r="S24" s="95" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="W24" s="94" t="n">
+      <c r="T24" s="95" t="n">
         <v>8.789999999999999</v>
       </c>
-      <c r="X24" s="94" t="n">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="Y24" s="94" t="n">
+      <c r="U24" s="95" t="n">
         <v>8.41</v>
       </c>
-      <c r="Z24" s="94" t="n">
+      <c r="V24" s="95" t="n">
         <v>8.6</v>
       </c>
-      <c r="AA24" s="94" t="n">
+      <c r="W24" s="95" t="n">
         <v>7.87</v>
       </c>
-      <c r="AB24" s="94" t="n">
+      <c r="X24" s="95" t="n">
         <v>7.54</v>
       </c>
-      <c r="AC24" s="94" t="n">
+      <c r="Y24" s="95" t="n">
         <v>6.31</v>
       </c>
-      <c r="AD24" s="94" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="AE24" s="94" t="n">
+      <c r="Z24" s="95" t="n">
         <v>5.57</v>
       </c>
+      <c r="AA24" s="95" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AB24" s="95" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AC24" s="95" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AD24" s="95" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AE24" s="95" t="n">
+        <v>3.31</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="76" t="inlineStr">
+      <c r="A25" s="96" t="inlineStr">
         <is>
           <t>us30:RS3</t>
         </is>
       </c>
-      <c r="B25" s="94" t="n">
+      <c r="B25" s="95" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="C25" s="95" t="n">
         <v>39.69</v>
       </c>
-      <c r="C25" s="94" t="n">
-        <v>39.69</v>
-      </c>
-      <c r="D25" s="94" t="n">
+      <c r="D25" s="95" t="n">
         <v>40.25</v>
       </c>
-      <c r="E25" s="94" t="n">
+      <c r="E25" s="95" t="n">
         <v>78.72</v>
       </c>
-      <c r="F25" s="94" t="n">
-        <v>78.72</v>
-      </c>
-      <c r="G25" s="94" t="n">
+      <c r="F25" s="95" t="n">
         <v>77.16</v>
       </c>
-      <c r="H25" s="94" t="n">
+      <c r="G25" s="95" t="n">
         <v>70.95999999999999</v>
       </c>
-      <c r="I25" s="94" t="n">
+      <c r="H25" s="95" t="n">
         <v>53.27</v>
       </c>
-      <c r="J25" s="94" t="n">
+      <c r="I25" s="95" t="n">
         <v>87.47</v>
       </c>
-      <c r="K25" s="94" t="n">
+      <c r="J25" s="95" t="n">
         <v>82.94</v>
       </c>
-      <c r="L25" s="94" t="n">
+      <c r="K25" s="95" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="L25" s="95" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="M25" s="95" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="N25" s="95" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="O25" s="95" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="P25" s="95" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="Q25" s="95" t="n">
+        <v>52.09</v>
+      </c>
+      <c r="R25" s="95" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="S25" s="95" t="n">
+        <v>76.02</v>
+      </c>
+      <c r="T25" s="95" t="n">
+        <v>74.91</v>
+      </c>
+      <c r="U25" s="95" t="n">
+        <v>66.62</v>
+      </c>
+      <c r="V25" s="95" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="W25" s="95" t="n">
+        <v>92.18000000000001</v>
+      </c>
+      <c r="X25" s="95" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="Y25" s="95" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="Z25" s="95" t="n">
+        <v>87.58</v>
+      </c>
+      <c r="AA25" s="95" t="n">
+        <v>65.31</v>
+      </c>
+      <c r="AB25" s="95" t="n">
+        <v>85.48999999999999</v>
+      </c>
+      <c r="AC25" s="95" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="AD25" s="95" t="n">
         <v>82.94</v>
       </c>
-      <c r="M25" s="94" t="n">
-        <v>66.56</v>
-      </c>
-      <c r="N25" s="94" t="n">
-        <v>73.18000000000001</v>
-      </c>
-      <c r="O25" s="94" t="n">
-        <v>46.98</v>
-      </c>
-      <c r="P25" s="94" t="n">
-        <v>34.52</v>
-      </c>
-      <c r="Q25" s="94" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="R25" s="94" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="S25" s="94" t="n">
-        <v>28.19</v>
-      </c>
-      <c r="T25" s="94" t="n">
-        <v>52.09</v>
-      </c>
-      <c r="U25" s="94" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="V25" s="94" t="n">
-        <v>76.02</v>
-      </c>
-      <c r="W25" s="94" t="n">
-        <v>74.91</v>
-      </c>
-      <c r="X25" s="94" t="n">
-        <v>74.91</v>
-      </c>
-      <c r="Y25" s="94" t="n">
-        <v>66.62</v>
-      </c>
-      <c r="Z25" s="94" t="n">
-        <v>42.84</v>
-      </c>
-      <c r="AA25" s="94" t="n">
-        <v>92.18000000000001</v>
-      </c>
-      <c r="AB25" s="94" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="AC25" s="94" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="AD25" s="94" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="AE25" s="94" t="n">
-        <v>87.58</v>
+      <c r="AE25" s="95" t="n">
+        <v>71.68000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -9185,134 +9185,134 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="92" t="inlineStr">
+      <c r="B26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="C26" s="92" t="inlineStr">
+      <c r="D26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D26" s="92" t="inlineStr">
+      <c r="E26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E26" s="92" t="inlineStr">
+      <c r="F26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F26" s="92" t="inlineStr">
+      <c r="J26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G26" s="91" t="inlineStr">
+      <c r="K26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N26" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H26" s="91" t="inlineStr">
+      <c r="Q26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I26" s="91" t="inlineStr">
+      <c r="R26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J26" s="92" t="inlineStr">
+      <c r="S26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K26" s="92" t="inlineStr">
+      <c r="V26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L26" s="92" t="inlineStr">
+      <c r="X26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M26" s="92" t="inlineStr">
+      <c r="Y26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N26" s="92" t="inlineStr">
+      <c r="Z26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P26" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Q26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S26" s="91" t="inlineStr">
+      <c r="AA26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="T26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z26" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AB26" s="92" t="inlineStr">
@@ -9342,95 +9342,95 @@
           <t>ixic:RNG60</t>
         </is>
       </c>
-      <c r="B27" s="94" t="n">
+      <c r="B27" s="95" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="C27" s="95" t="n">
         <v>6.93</v>
       </c>
-      <c r="C27" s="94" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="D27" s="94" t="n">
+      <c r="D27" s="95" t="n">
         <v>6.81</v>
       </c>
-      <c r="E27" s="94" t="n">
+      <c r="E27" s="95" t="n">
         <v>7.61</v>
       </c>
-      <c r="F27" s="94" t="n">
-        <v>7.61</v>
-      </c>
-      <c r="G27" s="94" t="n">
+      <c r="F27" s="95" t="n">
         <v>5.95</v>
       </c>
-      <c r="H27" s="94" t="n">
+      <c r="G27" s="95" t="n">
         <v>2.05</v>
       </c>
-      <c r="I27" s="94" t="n">
+      <c r="H27" s="95" t="n">
         <v>1.71</v>
       </c>
-      <c r="J27" s="94" t="n">
+      <c r="I27" s="95" t="n">
         <v>4.38</v>
       </c>
-      <c r="K27" s="94" t="n">
+      <c r="J27" s="95" t="n">
         <v>2.64</v>
       </c>
-      <c r="L27" s="94" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="M27" s="94" t="n">
+      <c r="K27" s="95" t="n">
         <v>1.58</v>
       </c>
-      <c r="N27" s="94" t="n">
+      <c r="L27" s="95" t="n">
         <v>-1.18</v>
       </c>
-      <c r="O27" s="94" t="n">
+      <c r="M27" s="95" t="n">
         <v>-1.57</v>
       </c>
-      <c r="P27" s="94" t="n">
+      <c r="N27" s="95" t="n">
         <v>-2.58</v>
       </c>
-      <c r="Q27" s="94" t="n">
+      <c r="O27" s="95" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R27" s="94" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="S27" s="94" t="n">
+      <c r="P27" s="95" t="n">
         <v>-3.91</v>
       </c>
-      <c r="T27" s="94" t="n">
+      <c r="Q27" s="95" t="n">
         <v>-2.74</v>
       </c>
-      <c r="U27" s="94" t="n">
+      <c r="R27" s="95" t="n">
         <v>-2.68</v>
       </c>
-      <c r="V27" s="94" t="n">
+      <c r="S27" s="95" t="n">
         <v>-0.89</v>
       </c>
-      <c r="W27" s="94" t="n">
+      <c r="T27" s="95" t="n">
         <v>-0.38</v>
       </c>
-      <c r="X27" s="94" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="Y27" s="94" t="n">
+      <c r="U27" s="95" t="n">
         <v>0.9</v>
       </c>
-      <c r="Z27" s="94" t="n">
+      <c r="V27" s="95" t="n">
         <v>1.13</v>
       </c>
-      <c r="AA27" s="94" t="n">
+      <c r="W27" s="95" t="n">
         <v>1.93</v>
       </c>
-      <c r="AB27" s="94" t="n">
+      <c r="X27" s="95" t="n">
         <v>0.65</v>
       </c>
-      <c r="AC27" s="94" t="n">
+      <c r="Y27" s="95" t="n">
         <v>0.8</v>
       </c>
-      <c r="AD27" s="94" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AE27" s="94" t="n">
+      <c r="Z27" s="95" t="n">
         <v>1.67</v>
+      </c>
+      <c r="AA27" s="95" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AB27" s="95" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="AC27" s="95" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="AD27" s="95" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE27" s="95" t="n">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="28">
@@ -9439,192 +9439,192 @@
           <t>ixic:RNG120</t>
         </is>
       </c>
-      <c r="B28" s="94" t="n">
+      <c r="B28" s="95" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="C28" s="95" t="n">
         <v>19.02</v>
       </c>
-      <c r="C28" s="94" t="n">
-        <v>19.02</v>
-      </c>
-      <c r="D28" s="94" t="n">
+      <c r="D28" s="95" t="n">
         <v>18.41</v>
       </c>
-      <c r="E28" s="94" t="n">
+      <c r="E28" s="95" t="n">
         <v>15.68</v>
       </c>
-      <c r="F28" s="94" t="n">
-        <v>15.68</v>
-      </c>
-      <c r="G28" s="94" t="n">
+      <c r="F28" s="95" t="n">
         <v>15.35</v>
       </c>
-      <c r="H28" s="94" t="n">
+      <c r="G28" s="95" t="n">
         <v>17.65</v>
       </c>
-      <c r="I28" s="94" t="n">
+      <c r="H28" s="95" t="n">
         <v>16.57</v>
       </c>
-      <c r="J28" s="94" t="n">
+      <c r="I28" s="95" t="n">
         <v>17.88</v>
       </c>
-      <c r="K28" s="94" t="n">
+      <c r="J28" s="95" t="n">
         <v>18.71</v>
       </c>
-      <c r="L28" s="94" t="n">
-        <v>18.71</v>
-      </c>
-      <c r="M28" s="94" t="n">
+      <c r="K28" s="95" t="n">
         <v>19.63</v>
       </c>
-      <c r="N28" s="94" t="n">
+      <c r="L28" s="95" t="n">
         <v>17.24</v>
       </c>
-      <c r="O28" s="94" t="n">
+      <c r="M28" s="95" t="n">
         <v>15.94</v>
       </c>
-      <c r="P28" s="94" t="n">
+      <c r="N28" s="95" t="n">
         <v>12.98</v>
       </c>
-      <c r="Q28" s="94" t="n">
+      <c r="O28" s="95" t="n">
         <v>14.18</v>
       </c>
-      <c r="R28" s="94" t="n">
-        <v>14.18</v>
-      </c>
-      <c r="S28" s="94" t="n">
+      <c r="P28" s="95" t="n">
         <v>10.78</v>
       </c>
-      <c r="T28" s="94" t="n">
+      <c r="Q28" s="95" t="n">
         <v>9.02</v>
       </c>
-      <c r="U28" s="94" t="n">
+      <c r="R28" s="95" t="n">
         <v>10.76</v>
       </c>
-      <c r="V28" s="94" t="n">
+      <c r="S28" s="95" t="n">
         <v>11.54</v>
       </c>
-      <c r="W28" s="94" t="n">
+      <c r="T28" s="95" t="n">
         <v>11.48</v>
       </c>
-      <c r="X28" s="94" t="n">
-        <v>11.48</v>
-      </c>
-      <c r="Y28" s="94" t="n">
+      <c r="U28" s="95" t="n">
         <v>11.95</v>
       </c>
-      <c r="Z28" s="94" t="n">
+      <c r="V28" s="95" t="n">
         <v>12.67</v>
       </c>
-      <c r="AA28" s="94" t="n">
+      <c r="W28" s="95" t="n">
         <v>11.04</v>
       </c>
-      <c r="AB28" s="94" t="n">
+      <c r="X28" s="95" t="n">
         <v>10.68</v>
       </c>
-      <c r="AC28" s="94" t="n">
+      <c r="Y28" s="95" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="AD28" s="94" t="n">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="AE28" s="94" t="n">
+      <c r="Z28" s="95" t="n">
         <v>9.98</v>
       </c>
+      <c r="AA28" s="95" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="AB28" s="95" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="AC28" s="95" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="AD28" s="95" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="AE28" s="95" t="n">
+        <v>7.12</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="76" t="inlineStr">
+      <c r="A29" s="96" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
-      <c r="B29" s="94" t="n">
+      <c r="B29" s="95" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="C29" s="95" t="n">
         <v>94.05</v>
       </c>
-      <c r="C29" s="94" t="n">
-        <v>94.05</v>
-      </c>
-      <c r="D29" s="94" t="n">
+      <c r="D29" s="95" t="n">
         <v>91.14</v>
       </c>
-      <c r="E29" s="94" t="n">
+      <c r="E29" s="95" t="n">
         <v>85.89</v>
       </c>
-      <c r="F29" s="94" t="n">
-        <v>85.89</v>
-      </c>
-      <c r="G29" s="94" t="n">
+      <c r="F29" s="95" t="n">
         <v>55.65</v>
       </c>
-      <c r="H29" s="94" t="n">
+      <c r="G29" s="95" t="n">
         <v>52.8</v>
       </c>
-      <c r="I29" s="94" t="n">
+      <c r="H29" s="95" t="n">
         <v>36.8</v>
       </c>
-      <c r="J29" s="94" t="n">
+      <c r="I29" s="95" t="n">
         <v>95.84</v>
       </c>
-      <c r="K29" s="94" t="n">
+      <c r="J29" s="95" t="n">
         <v>86.79000000000001</v>
       </c>
-      <c r="L29" s="94" t="n">
-        <v>86.79000000000001</v>
-      </c>
-      <c r="M29" s="94" t="n">
+      <c r="K29" s="95" t="n">
         <v>77.45999999999999</v>
       </c>
-      <c r="N29" s="94" t="n">
+      <c r="L29" s="95" t="n">
         <v>82.01000000000001</v>
       </c>
-      <c r="O29" s="94" t="n">
+      <c r="M29" s="95" t="n">
         <v>72.98999999999999</v>
       </c>
-      <c r="P29" s="94" t="n">
+      <c r="N29" s="95" t="n">
         <v>32.92</v>
       </c>
-      <c r="Q29" s="94" t="n">
+      <c r="O29" s="95" t="n">
         <v>85.03</v>
       </c>
-      <c r="R29" s="94" t="n">
-        <v>85.03</v>
-      </c>
-      <c r="S29" s="94" t="n">
+      <c r="P29" s="95" t="n">
         <v>20.54</v>
       </c>
-      <c r="T29" s="94" t="n">
+      <c r="Q29" s="95" t="n">
         <v>21.97</v>
       </c>
-      <c r="U29" s="94" t="n">
+      <c r="R29" s="95" t="n">
         <v>15.42</v>
       </c>
-      <c r="V29" s="94" t="n">
+      <c r="S29" s="95" t="n">
         <v>74.7</v>
       </c>
-      <c r="W29" s="94" t="n">
+      <c r="T29" s="95" t="n">
         <v>51.35</v>
       </c>
-      <c r="X29" s="94" t="n">
-        <v>51.35</v>
-      </c>
-      <c r="Y29" s="94" t="n">
+      <c r="U29" s="95" t="n">
         <v>96.66</v>
       </c>
-      <c r="Z29" s="94" t="n">
+      <c r="V29" s="95" t="n">
         <v>89.75</v>
       </c>
-      <c r="AA29" s="94" t="n">
+      <c r="W29" s="95" t="n">
         <v>88.93000000000001</v>
       </c>
-      <c r="AB29" s="94" t="n">
+      <c r="X29" s="95" t="n">
         <v>77.02</v>
       </c>
-      <c r="AC29" s="94" t="n">
+      <c r="Y29" s="95" t="n">
         <v>73.3</v>
       </c>
-      <c r="AD29" s="94" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="AE29" s="94" t="n">
+      <c r="Z29" s="95" t="n">
         <v>92.18000000000001</v>
+      </c>
+      <c r="AA29" s="95" t="n">
+        <v>42.32</v>
+      </c>
+      <c r="AB29" s="95" t="n">
+        <v>70.06</v>
+      </c>
+      <c r="AC29" s="95" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="AD29" s="95" t="n">
+        <v>95.17</v>
+      </c>
+      <c r="AE29" s="95" t="n">
+        <v>92.73999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -9633,17 +9633,17 @@
           <t>jp225:EIDE</t>
         </is>
       </c>
-      <c r="B30" s="95" t="inlineStr">
+      <c r="B30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C30" s="95" t="inlineStr">
+      <c r="C30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D30" s="95" t="inlineStr">
+      <c r="D30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -9653,134 +9653,134 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="F30" s="91" t="inlineStr">
+      <c r="F30" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G30" s="95" t="inlineStr">
+      <c r="H30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q30" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H30" s="91" t="inlineStr">
+      <c r="R30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I30" s="92" t="inlineStr">
+      <c r="S30" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J30" s="92" t="inlineStr">
+      <c r="U30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K30" s="92" t="inlineStr">
+      <c r="V30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L30" s="92" t="inlineStr">
+      <c r="W30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M30" s="91" t="inlineStr">
+      <c r="X30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N30" s="91" t="inlineStr">
+      <c r="AB30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O30" s="91" t="inlineStr">
+      <c r="AC30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q30" s="91" t="inlineStr">
+      <c r="AD30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R30" s="91" t="inlineStr">
+      <c r="AE30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="S30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T30" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="U30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -9790,95 +9790,95 @@
           <t>jp225:RNG60</t>
         </is>
       </c>
-      <c r="B31" s="94" t="n">
+      <c r="B31" s="95" t="n">
         <v>-0.95</v>
       </c>
-      <c r="C31" s="94" t="n">
+      <c r="C31" s="95" t="n">
         <v>1.98</v>
       </c>
-      <c r="D31" s="94" t="n">
+      <c r="D31" s="95" t="n">
         <v>2.87</v>
       </c>
-      <c r="E31" s="94" t="n">
+      <c r="E31" s="95" t="n">
         <v>-0.44</v>
       </c>
-      <c r="F31" s="94" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="G31" s="94" t="n">
+      <c r="F31" s="95" t="n">
         <v>-1.73</v>
       </c>
-      <c r="H31" s="94" t="n">
+      <c r="G31" s="95" t="n">
         <v>-1.06</v>
       </c>
-      <c r="I31" s="94" t="n">
+      <c r="H31" s="95" t="n">
         <v>-0.38</v>
       </c>
-      <c r="J31" s="94" t="n">
+      <c r="I31" s="95" t="n">
         <v>-1.3</v>
       </c>
-      <c r="K31" s="94" t="n">
+      <c r="J31" s="95" t="n">
         <v>-1.3</v>
       </c>
-      <c r="L31" s="94" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="M31" s="94" t="n">
+      <c r="K31" s="95" t="n">
         <v>-4.18</v>
       </c>
-      <c r="N31" s="94" t="n">
+      <c r="L31" s="95" t="n">
         <v>-4.84</v>
       </c>
-      <c r="O31" s="94" t="n">
+      <c r="M31" s="95" t="n">
         <v>-5.47</v>
       </c>
-      <c r="P31" s="94" t="n">
+      <c r="N31" s="95" t="n">
         <v>-6.85</v>
       </c>
-      <c r="Q31" s="94" t="n">
+      <c r="O31" s="95" t="n">
         <v>-7.64</v>
       </c>
-      <c r="R31" s="94" t="n">
-        <v>-7.64</v>
-      </c>
-      <c r="S31" s="94" t="n">
+      <c r="P31" s="95" t="n">
         <v>-7.28</v>
       </c>
-      <c r="T31" s="94" t="n">
+      <c r="Q31" s="95" t="n">
         <v>-7.29</v>
       </c>
-      <c r="U31" s="94" t="n">
+      <c r="R31" s="95" t="n">
         <v>-5.52</v>
       </c>
-      <c r="V31" s="94" t="n">
+      <c r="S31" s="95" t="n">
         <v>-7.32</v>
       </c>
-      <c r="W31" s="94" t="n">
+      <c r="T31" s="95" t="n">
         <v>-1.85</v>
       </c>
-      <c r="X31" s="94" t="n">
-        <v>-1.85</v>
-      </c>
-      <c r="Y31" s="94" t="n">
+      <c r="U31" s="95" t="n">
         <v>-2.87</v>
       </c>
-      <c r="Z31" s="94" t="n">
+      <c r="V31" s="95" t="n">
         <v>-4.44</v>
       </c>
-      <c r="AA31" s="94" t="n">
+      <c r="W31" s="95" t="n">
         <v>-4.15</v>
       </c>
-      <c r="AB31" s="94" t="n">
+      <c r="X31" s="95" t="n">
         <v>-4.11</v>
       </c>
-      <c r="AC31" s="94" t="n">
+      <c r="Y31" s="95" t="n">
         <v>-4.11</v>
       </c>
-      <c r="AD31" s="94" t="n">
-        <v>-4.11</v>
-      </c>
-      <c r="AE31" s="94" t="n">
+      <c r="Z31" s="95" t="n">
         <v>-6.33</v>
+      </c>
+      <c r="AA31" s="95" t="n">
+        <v>-7.13</v>
+      </c>
+      <c r="AB31" s="95" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="AC31" s="95" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="AD31" s="95" t="n">
+        <v>-5.31</v>
+      </c>
+      <c r="AE31" s="95" t="n">
+        <v>-4.5</v>
       </c>
     </row>
     <row r="32">
@@ -9887,95 +9887,95 @@
           <t>jp225:RNG120</t>
         </is>
       </c>
-      <c r="B32" s="94" t="n">
+      <c r="B32" s="95" t="n">
         <v>-0.44</v>
       </c>
-      <c r="C32" s="94" t="n">
+      <c r="C32" s="95" t="n">
         <v>0.02</v>
       </c>
-      <c r="D32" s="94" t="n">
+      <c r="D32" s="95" t="n">
         <v>2.69</v>
       </c>
-      <c r="E32" s="94" t="n">
+      <c r="E32" s="95" t="n">
         <v>3.6</v>
       </c>
-      <c r="F32" s="94" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G32" s="94" t="n">
+      <c r="F32" s="95" t="n">
         <v>1.17</v>
       </c>
-      <c r="H32" s="94" t="n">
+      <c r="G32" s="95" t="n">
         <v>4.34</v>
       </c>
-      <c r="I32" s="94" t="n">
+      <c r="H32" s="95" t="n">
         <v>6.6</v>
       </c>
-      <c r="J32" s="94" t="n">
+      <c r="I32" s="95" t="n">
         <v>6.85</v>
       </c>
-      <c r="K32" s="94" t="n">
+      <c r="J32" s="95" t="n">
         <v>6.85</v>
       </c>
-      <c r="L32" s="94" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="M32" s="94" t="n">
+      <c r="K32" s="95" t="n">
         <v>3.42</v>
       </c>
-      <c r="N32" s="94" t="n">
+      <c r="L32" s="95" t="n">
         <v>3.47</v>
       </c>
-      <c r="O32" s="94" t="n">
+      <c r="M32" s="95" t="n">
         <v>1.21</v>
       </c>
-      <c r="P32" s="94" t="n">
+      <c r="N32" s="95" t="n">
         <v>0.25</v>
       </c>
-      <c r="Q32" s="94" t="n">
+      <c r="O32" s="95" t="n">
         <v>-2.25</v>
       </c>
-      <c r="R32" s="94" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="S32" s="94" t="n">
+      <c r="P32" s="95" t="n">
         <v>-2.26</v>
       </c>
-      <c r="T32" s="94" t="n">
+      <c r="Q32" s="95" t="n">
         <v>-4.48</v>
       </c>
-      <c r="U32" s="94" t="n">
+      <c r="R32" s="95" t="n">
         <v>-2.82</v>
       </c>
-      <c r="V32" s="94" t="n">
+      <c r="S32" s="95" t="n">
         <v>-3.63</v>
       </c>
-      <c r="W32" s="94" t="n">
+      <c r="T32" s="95" t="n">
         <v>2.15</v>
       </c>
-      <c r="X32" s="94" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y32" s="94" t="n">
+      <c r="U32" s="95" t="n">
         <v>-2.13</v>
       </c>
-      <c r="Z32" s="94" t="n">
+      <c r="V32" s="95" t="n">
         <v>-4.01</v>
       </c>
-      <c r="AA32" s="94" t="n">
+      <c r="W32" s="95" t="n">
         <v>-4.76</v>
       </c>
-      <c r="AB32" s="94" t="n">
+      <c r="X32" s="95" t="n">
         <v>-5.22</v>
       </c>
-      <c r="AC32" s="94" t="n">
+      <c r="Y32" s="95" t="n">
         <v>-5.22</v>
       </c>
-      <c r="AD32" s="94" t="n">
-        <v>-5.22</v>
-      </c>
-      <c r="AE32" s="94" t="n">
+      <c r="Z32" s="95" t="n">
         <v>-7.96</v>
+      </c>
+      <c r="AA32" s="95" t="n">
+        <v>-9.43</v>
+      </c>
+      <c r="AB32" s="95" t="n">
+        <v>-11.19</v>
+      </c>
+      <c r="AC32" s="95" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="AD32" s="95" t="n">
+        <v>-9.48</v>
+      </c>
+      <c r="AE32" s="95" t="n">
+        <v>-9.92</v>
       </c>
     </row>
     <row r="33">
@@ -9984,95 +9984,95 @@
           <t>jp225:RS9</t>
         </is>
       </c>
-      <c r="B33" s="94" t="n">
+      <c r="B33" s="95" t="n">
         <v>40.48</v>
       </c>
-      <c r="C33" s="94" t="n">
+      <c r="C33" s="95" t="n">
         <v>44.35</v>
       </c>
-      <c r="D33" s="94" t="n">
+      <c r="D33" s="95" t="n">
         <v>52.17</v>
       </c>
-      <c r="E33" s="94" t="n">
+      <c r="E33" s="95" t="n">
         <v>52.59</v>
       </c>
-      <c r="F33" s="94" t="n">
-        <v>52.59</v>
-      </c>
-      <c r="G33" s="94" t="n">
+      <c r="F33" s="95" t="n">
         <v>51.7</v>
       </c>
-      <c r="H33" s="94" t="n">
+      <c r="G33" s="95" t="n">
         <v>55.18</v>
       </c>
-      <c r="I33" s="94" t="n">
+      <c r="H33" s="95" t="n">
         <v>65.89</v>
       </c>
-      <c r="J33" s="94" t="n">
+      <c r="I33" s="95" t="n">
         <v>63.24</v>
       </c>
-      <c r="K33" s="94" t="n">
+      <c r="J33" s="95" t="n">
         <v>63.24</v>
       </c>
-      <c r="L33" s="94" t="n">
-        <v>63.24</v>
-      </c>
-      <c r="M33" s="94" t="n">
+      <c r="K33" s="95" t="n">
         <v>61.28</v>
       </c>
-      <c r="N33" s="94" t="n">
+      <c r="L33" s="95" t="n">
         <v>60.41</v>
       </c>
-      <c r="O33" s="94" t="n">
+      <c r="M33" s="95" t="n">
         <v>57.64</v>
       </c>
-      <c r="P33" s="94" t="n">
+      <c r="N33" s="95" t="n">
         <v>62.13</v>
       </c>
-      <c r="Q33" s="94" t="n">
+      <c r="O33" s="95" t="n">
         <v>56.86</v>
       </c>
-      <c r="R33" s="94" t="n">
-        <v>56.86</v>
-      </c>
-      <c r="S33" s="94" t="n">
+      <c r="P33" s="95" t="n">
         <v>56.21</v>
       </c>
-      <c r="T33" s="94" t="n">
+      <c r="Q33" s="95" t="n">
         <v>50.28</v>
       </c>
-      <c r="U33" s="94" t="n">
+      <c r="R33" s="95" t="n">
         <v>58.22</v>
       </c>
-      <c r="V33" s="94" t="n">
+      <c r="S33" s="95" t="n">
         <v>52.42</v>
       </c>
-      <c r="W33" s="94" t="n">
+      <c r="T33" s="95" t="n">
         <v>77.31</v>
       </c>
-      <c r="X33" s="94" t="n">
-        <v>77.31</v>
-      </c>
-      <c r="Y33" s="94" t="n">
+      <c r="U33" s="95" t="n">
         <v>71.64</v>
       </c>
-      <c r="Z33" s="94" t="n">
+      <c r="V33" s="95" t="n">
         <v>61.74</v>
       </c>
-      <c r="AA33" s="94" t="n">
+      <c r="W33" s="95" t="n">
         <v>63.04</v>
       </c>
-      <c r="AB33" s="94" t="n">
+      <c r="X33" s="95" t="n">
         <v>60.77</v>
       </c>
-      <c r="AC33" s="94" t="n">
+      <c r="Y33" s="95" t="n">
         <v>60.77</v>
       </c>
-      <c r="AD33" s="94" t="n">
-        <v>60.77</v>
-      </c>
-      <c r="AE33" s="94" t="n">
+      <c r="Z33" s="95" t="n">
         <v>54.21</v>
+      </c>
+      <c r="AA33" s="95" t="n">
+        <v>42.56</v>
+      </c>
+      <c r="AB33" s="95" t="n">
+        <v>39.44</v>
+      </c>
+      <c r="AC33" s="95" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="AD33" s="95" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="AE33" s="95" t="n">
+        <v>46.79</v>
       </c>
     </row>
     <row r="34">
@@ -10081,17 +10081,17 @@
           <t>vn:EIDE</t>
         </is>
       </c>
-      <c r="B34" s="95" t="inlineStr">
+      <c r="B34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C34" s="95" t="inlineStr">
+      <c r="C34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D34" s="95" t="inlineStr">
+      <c r="D34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -10106,129 +10106,129 @@
           <t>red</t>
         </is>
       </c>
-      <c r="G34" s="92" t="inlineStr">
+      <c r="G34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H34" s="95" t="inlineStr">
+      <c r="J34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I34" s="91" t="inlineStr">
+      <c r="N34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="P34" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J34" s="92" t="inlineStr">
+      <c r="R34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K34" s="92" t="inlineStr">
+      <c r="U34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L34" s="92" t="inlineStr">
+      <c r="V34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M34" s="92" t="inlineStr">
+      <c r="W34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N34" s="92" t="inlineStr">
+      <c r="X34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O34" s="95" t="inlineStr">
+      <c r="Y34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA34" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB34" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AC34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P34" s="95" t="inlineStr">
+      <c r="AD34" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q34" s="95" t="inlineStr">
+      <c r="AE34" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="R34" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="S34" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="T34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V34" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -10238,95 +10238,95 @@
           <t>vn:RNG60</t>
         </is>
       </c>
-      <c r="B35" s="94" t="n">
+      <c r="B35" s="95" t="n">
         <v>1.95</v>
       </c>
-      <c r="C35" s="94" t="n">
+      <c r="C35" s="95" t="n">
         <v>2.24</v>
       </c>
-      <c r="D35" s="94" t="n">
+      <c r="D35" s="95" t="n">
         <v>3.78</v>
       </c>
-      <c r="E35" s="94" t="n">
+      <c r="E35" s="95" t="n">
         <v>3.79</v>
       </c>
-      <c r="F35" s="94" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="G35" s="94" t="n">
+      <c r="F35" s="95" t="n">
         <v>4.44</v>
       </c>
-      <c r="H35" s="94" t="n">
+      <c r="G35" s="95" t="n">
         <v>1.98</v>
       </c>
-      <c r="I35" s="94" t="n">
+      <c r="H35" s="95" t="n">
         <v>1.29</v>
       </c>
-      <c r="J35" s="94" t="n">
+      <c r="I35" s="95" t="n">
         <v>0.93</v>
       </c>
-      <c r="K35" s="94" t="n">
+      <c r="J35" s="95" t="n">
         <v>1.56</v>
       </c>
-      <c r="L35" s="94" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M35" s="94" t="n">
+      <c r="K35" s="95" t="n">
         <v>0.4</v>
       </c>
-      <c r="N35" s="94" t="n">
+      <c r="L35" s="95" t="n">
         <v>0.16</v>
       </c>
-      <c r="O35" s="94" t="n">
+      <c r="M35" s="95" t="n">
         <v>-0.68</v>
       </c>
-      <c r="P35" s="94" t="n">
+      <c r="N35" s="95" t="n">
         <v>-1.08</v>
       </c>
-      <c r="Q35" s="94" t="n">
+      <c r="O35" s="95" t="n">
         <v>-1.19</v>
       </c>
-      <c r="R35" s="94" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="S35" s="94" t="n">
+      <c r="P35" s="95" t="n">
         <v>-1.21</v>
       </c>
-      <c r="T35" s="94" t="n">
+      <c r="Q35" s="95" t="n">
         <v>0.33</v>
       </c>
-      <c r="U35" s="94" t="n">
+      <c r="R35" s="95" t="n">
         <v>0.71</v>
       </c>
-      <c r="V35" s="94" t="n">
+      <c r="S35" s="95" t="n">
         <v>0.63</v>
       </c>
-      <c r="W35" s="94" t="n">
+      <c r="T35" s="95" t="n">
         <v>1.1</v>
       </c>
-      <c r="X35" s="94" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y35" s="94" t="n">
+      <c r="U35" s="95" t="n">
         <v>1.71</v>
       </c>
-      <c r="Z35" s="94" t="n">
+      <c r="V35" s="95" t="n">
         <v>2.62</v>
       </c>
-      <c r="AA35" s="94" t="n">
+      <c r="W35" s="95" t="n">
         <v>1.79</v>
       </c>
-      <c r="AB35" s="94" t="n">
+      <c r="X35" s="95" t="n">
         <v>1.86</v>
       </c>
-      <c r="AC35" s="94" t="n">
+      <c r="Y35" s="95" t="n">
         <v>1.03</v>
       </c>
-      <c r="AD35" s="94" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AE35" s="94" t="n">
+      <c r="Z35" s="95" t="n">
         <v>0.8</v>
+      </c>
+      <c r="AA35" s="95" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AB35" s="95" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AC35" s="95" t="n">
+        <v>-3.34</v>
+      </c>
+      <c r="AD35" s="95" t="n">
+        <v>-2.39</v>
+      </c>
+      <c r="AE35" s="95" t="n">
+        <v>-1.83</v>
       </c>
     </row>
     <row r="36">
@@ -10335,95 +10335,95 @@
           <t>vn:RNG120</t>
         </is>
       </c>
-      <c r="B36" s="94" t="n">
+      <c r="B36" s="95" t="n">
         <v>1.78</v>
       </c>
-      <c r="C36" s="94" t="n">
+      <c r="C36" s="95" t="n">
         <v>2.28</v>
       </c>
-      <c r="D36" s="94" t="n">
+      <c r="D36" s="95" t="n">
         <v>4.81</v>
       </c>
-      <c r="E36" s="94" t="n">
+      <c r="E36" s="95" t="n">
         <v>5.68</v>
       </c>
-      <c r="F36" s="94" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="G36" s="94" t="n">
+      <c r="F36" s="95" t="n">
         <v>6.37</v>
       </c>
-      <c r="H36" s="94" t="n">
+      <c r="G36" s="95" t="n">
         <v>6.18</v>
       </c>
-      <c r="I36" s="94" t="n">
+      <c r="H36" s="95" t="n">
         <v>6.26</v>
       </c>
-      <c r="J36" s="94" t="n">
+      <c r="I36" s="95" t="n">
         <v>9.25</v>
       </c>
-      <c r="K36" s="94" t="n">
+      <c r="J36" s="95" t="n">
         <v>8.25</v>
       </c>
-      <c r="L36" s="94" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="M36" s="94" t="n">
+      <c r="K36" s="95" t="n">
         <v>9.49</v>
       </c>
-      <c r="N36" s="94" t="n">
+      <c r="L36" s="95" t="n">
         <v>7.45</v>
       </c>
-      <c r="O36" s="94" t="n">
+      <c r="M36" s="95" t="n">
         <v>4.63</v>
       </c>
-      <c r="P36" s="94" t="n">
+      <c r="N36" s="95" t="n">
         <v>4.38</v>
       </c>
-      <c r="Q36" s="94" t="n">
+      <c r="O36" s="95" t="n">
         <v>-0.47</v>
       </c>
-      <c r="R36" s="94" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S36" s="94" t="n">
+      <c r="P36" s="95" t="n">
         <v>1.58</v>
       </c>
-      <c r="T36" s="94" t="n">
+      <c r="Q36" s="95" t="n">
         <v>2.33</v>
       </c>
-      <c r="U36" s="94" t="n">
+      <c r="R36" s="95" t="n">
         <v>2.33</v>
       </c>
-      <c r="V36" s="94" t="n">
+      <c r="S36" s="95" t="n">
         <v>3.01</v>
       </c>
-      <c r="W36" s="94" t="n">
+      <c r="T36" s="95" t="n">
         <v>2.85</v>
       </c>
-      <c r="X36" s="94" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y36" s="94" t="n">
+      <c r="U36" s="95" t="n">
         <v>1.83</v>
       </c>
-      <c r="Z36" s="94" t="n">
+      <c r="V36" s="95" t="n">
         <v>1.26</v>
       </c>
-      <c r="AA36" s="94" t="n">
+      <c r="W36" s="95" t="n">
         <v>-0.78</v>
       </c>
-      <c r="AB36" s="94" t="n">
+      <c r="X36" s="95" t="n">
         <v>-1.02</v>
       </c>
-      <c r="AC36" s="94" t="n">
+      <c r="Y36" s="95" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="AD36" s="94" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="AE36" s="94" t="n">
+      <c r="Z36" s="95" t="n">
         <v>-1.47</v>
+      </c>
+      <c r="AA36" s="95" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="AB36" s="95" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="AC36" s="95" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="AD36" s="95" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="AE36" s="95" t="n">
+        <v>-1.57</v>
       </c>
     </row>
     <row r="37">
@@ -10432,95 +10432,95 @@
           <t>vn:RS3</t>
         </is>
       </c>
-      <c r="B37" s="94" t="n">
+      <c r="B37" s="95" t="n">
         <v>21.39</v>
       </c>
-      <c r="C37" s="94" t="n">
+      <c r="C37" s="95" t="n">
         <v>14.83</v>
       </c>
-      <c r="D37" s="94" t="n">
+      <c r="D37" s="95" t="n">
         <v>32.52</v>
       </c>
-      <c r="E37" s="94" t="n">
+      <c r="E37" s="95" t="n">
         <v>60</v>
       </c>
-      <c r="F37" s="94" t="n">
-        <v>60</v>
-      </c>
-      <c r="G37" s="94" t="n">
+      <c r="F37" s="95" t="n">
         <v>67.03</v>
       </c>
-      <c r="H37" s="94" t="n">
+      <c r="G37" s="95" t="n">
         <v>31.47</v>
       </c>
-      <c r="I37" s="94" t="n">
+      <c r="H37" s="95" t="n">
         <v>37.61</v>
       </c>
-      <c r="J37" s="94" t="n">
+      <c r="I37" s="95" t="n">
         <v>65.76000000000001</v>
       </c>
-      <c r="K37" s="94" t="n">
+      <c r="J37" s="95" t="n">
         <v>81.64</v>
       </c>
-      <c r="L37" s="94" t="n">
-        <v>81.64</v>
-      </c>
-      <c r="M37" s="94" t="n">
+      <c r="K37" s="95" t="n">
         <v>78.16</v>
       </c>
-      <c r="N37" s="94" t="n">
+      <c r="L37" s="95" t="n">
         <v>69.63</v>
       </c>
-      <c r="O37" s="94" t="n">
+      <c r="M37" s="95" t="n">
         <v>29.45</v>
       </c>
-      <c r="P37" s="94" t="n">
+      <c r="N37" s="95" t="n">
         <v>13.62</v>
       </c>
-      <c r="Q37" s="94" t="n">
+      <c r="O37" s="95" t="n">
         <v>14.32</v>
       </c>
-      <c r="R37" s="94" t="n">
-        <v>14.32</v>
-      </c>
-      <c r="S37" s="94" t="n">
+      <c r="P37" s="95" t="n">
         <v>23.23</v>
       </c>
-      <c r="T37" s="94" t="n">
+      <c r="Q37" s="95" t="n">
         <v>50.34</v>
       </c>
-      <c r="U37" s="94" t="n">
+      <c r="R37" s="95" t="n">
         <v>77.23999999999999</v>
       </c>
-      <c r="V37" s="94" t="n">
+      <c r="S37" s="95" t="n">
         <v>65.09</v>
       </c>
-      <c r="W37" s="94" t="n">
+      <c r="T37" s="95" t="n">
         <v>86.66</v>
       </c>
-      <c r="X37" s="94" t="n">
-        <v>86.66</v>
-      </c>
-      <c r="Y37" s="94" t="n">
+      <c r="U37" s="95" t="n">
         <v>90.48999999999999</v>
       </c>
-      <c r="Z37" s="94" t="n">
+      <c r="V37" s="95" t="n">
         <v>88</v>
       </c>
-      <c r="AA37" s="94" t="n">
+      <c r="W37" s="95" t="n">
         <v>77.98</v>
       </c>
-      <c r="AB37" s="94" t="n">
+      <c r="X37" s="95" t="n">
         <v>59.82</v>
       </c>
-      <c r="AC37" s="94" t="n">
+      <c r="Y37" s="95" t="n">
         <v>77.68000000000001</v>
       </c>
-      <c r="AD37" s="94" t="n">
-        <v>77.68000000000001</v>
-      </c>
-      <c r="AE37" s="94" t="n">
+      <c r="Z37" s="95" t="n">
         <v>76.68000000000001</v>
+      </c>
+      <c r="AA37" s="95" t="n">
+        <v>68.98</v>
+      </c>
+      <c r="AB37" s="95" t="n">
+        <v>60.96</v>
+      </c>
+      <c r="AC37" s="95" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="AD37" s="95" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="AE37" s="95" t="n">
+        <v>30.12</v>
       </c>
     </row>
     <row r="38">
@@ -10529,12 +10529,12 @@
           <t>sensex:EIDE</t>
         </is>
       </c>
-      <c r="B38" s="95" t="inlineStr">
+      <c r="B38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C38" s="95" t="inlineStr">
+      <c r="C38" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -10579,44 +10579,44 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="L38" s="91" t="inlineStr">
+      <c r="L38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="P38" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M38" s="91" t="inlineStr">
+      <c r="R38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="O38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="P38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Q38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="R38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="S38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="S38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="T38" s="91" t="inlineStr">
@@ -10624,39 +10624,39 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="U38" s="91" t="inlineStr">
+      <c r="U38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="V38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AB38" s="92" t="inlineStr">
@@ -10686,95 +10686,95 @@
           <t>sensex:RNG60</t>
         </is>
       </c>
-      <c r="B39" s="94" t="n">
-        <v>-1.51</v>
-      </c>
-      <c r="C39" s="94" t="n">
+      <c r="B39" s="95" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="C39" s="95" t="n">
         <v>-1.4</v>
       </c>
-      <c r="D39" s="94" t="n">
+      <c r="D39" s="95" t="n">
         <v>-0.22</v>
       </c>
-      <c r="E39" s="94" t="n">
+      <c r="E39" s="95" t="n">
         <v>1.48</v>
       </c>
-      <c r="F39" s="94" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="G39" s="94" t="n">
+      <c r="F39" s="95" t="n">
         <v>1.07</v>
       </c>
-      <c r="H39" s="94" t="n">
+      <c r="G39" s="95" t="n">
         <v>1.33</v>
       </c>
-      <c r="I39" s="94" t="n">
+      <c r="H39" s="95" t="n">
         <v>1.64</v>
       </c>
-      <c r="J39" s="94" t="n">
+      <c r="I39" s="95" t="n">
         <v>1.7</v>
       </c>
-      <c r="K39" s="94" t="n">
+      <c r="J39" s="95" t="n">
         <v>0.05</v>
       </c>
-      <c r="L39" s="94" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M39" s="94" t="n">
+      <c r="K39" s="95" t="n">
         <v>1.11</v>
       </c>
-      <c r="N39" s="94" t="n">
+      <c r="L39" s="95" t="n">
         <v>0.99</v>
       </c>
-      <c r="O39" s="94" t="n">
+      <c r="M39" s="95" t="n">
         <v>1.39</v>
       </c>
-      <c r="P39" s="94" t="n">
+      <c r="N39" s="95" t="n">
         <v>1.44</v>
       </c>
-      <c r="Q39" s="94" t="n">
+      <c r="O39" s="95" t="n">
         <v>2.21</v>
       </c>
-      <c r="R39" s="94" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="S39" s="94" t="n">
+      <c r="P39" s="95" t="n">
         <v>2.67</v>
       </c>
-      <c r="T39" s="94" t="n">
+      <c r="Q39" s="95" t="n">
         <v>5.39</v>
       </c>
-      <c r="U39" s="94" t="n">
+      <c r="R39" s="95" t="n">
         <v>5.39</v>
       </c>
-      <c r="V39" s="94" t="n">
+      <c r="S39" s="95" t="n">
         <v>5.38</v>
       </c>
-      <c r="W39" s="94" t="n">
+      <c r="T39" s="95" t="n">
         <v>6.9</v>
       </c>
-      <c r="X39" s="94" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="Y39" s="94" t="n">
+      <c r="U39" s="95" t="n">
         <v>7.31</v>
       </c>
-      <c r="Z39" s="94" t="n">
+      <c r="V39" s="95" t="n">
         <v>7.21</v>
       </c>
-      <c r="AA39" s="94" t="n">
+      <c r="W39" s="95" t="n">
         <v>6.84</v>
       </c>
-      <c r="AB39" s="94" t="n">
+      <c r="X39" s="95" t="n">
         <v>7.46</v>
       </c>
-      <c r="AC39" s="94" t="n">
+      <c r="Y39" s="95" t="n">
         <v>6.69</v>
       </c>
-      <c r="AD39" s="94" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="AE39" s="94" t="n">
+      <c r="Z39" s="95" t="n">
         <v>5.73</v>
+      </c>
+      <c r="AA39" s="95" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="AB39" s="95" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AC39" s="95" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="AD39" s="95" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="AE39" s="95" t="n">
+        <v>7.27</v>
       </c>
     </row>
     <row r="40">
@@ -10783,95 +10783,95 @@
           <t>sensex:RNG120</t>
         </is>
       </c>
-      <c r="B40" s="94" t="n">
-        <v>8.59</v>
-      </c>
-      <c r="C40" s="94" t="n">
+      <c r="B40" s="95" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="C40" s="95" t="n">
         <v>7.52</v>
       </c>
-      <c r="D40" s="94" t="n">
+      <c r="D40" s="95" t="n">
         <v>8.949999999999999</v>
       </c>
-      <c r="E40" s="94" t="n">
+      <c r="E40" s="95" t="n">
         <v>8.779999999999999</v>
       </c>
-      <c r="F40" s="94" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="G40" s="94" t="n">
+      <c r="F40" s="95" t="n">
         <v>9.869999999999999</v>
       </c>
-      <c r="H40" s="94" t="n">
+      <c r="G40" s="95" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="I40" s="94" t="n">
+      <c r="H40" s="95" t="n">
         <v>10.79</v>
       </c>
-      <c r="J40" s="94" t="n">
+      <c r="I40" s="95" t="n">
         <v>11.17</v>
       </c>
-      <c r="K40" s="94" t="n">
+      <c r="J40" s="95" t="n">
         <v>10.5</v>
       </c>
-      <c r="L40" s="94" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="M40" s="94" t="n">
+      <c r="K40" s="95" t="n">
         <v>11.66</v>
       </c>
-      <c r="N40" s="94" t="n">
+      <c r="L40" s="95" t="n">
         <v>12.39</v>
       </c>
-      <c r="O40" s="94" t="n">
+      <c r="M40" s="95" t="n">
         <v>11.91</v>
       </c>
-      <c r="P40" s="94" t="n">
+      <c r="N40" s="95" t="n">
         <v>10.42</v>
       </c>
-      <c r="Q40" s="94" t="n">
+      <c r="O40" s="95" t="n">
         <v>10.03</v>
       </c>
-      <c r="R40" s="94" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="S40" s="94" t="n">
+      <c r="P40" s="95" t="n">
         <v>9.94</v>
       </c>
-      <c r="T40" s="94" t="n">
+      <c r="Q40" s="95" t="n">
         <v>12.83</v>
       </c>
-      <c r="U40" s="94" t="n">
+      <c r="R40" s="95" t="n">
         <v>12.83</v>
       </c>
-      <c r="V40" s="94" t="n">
+      <c r="S40" s="95" t="n">
         <v>12.79</v>
       </c>
-      <c r="W40" s="94" t="n">
+      <c r="T40" s="95" t="n">
         <v>15.25</v>
       </c>
-      <c r="X40" s="94" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="Y40" s="94" t="n">
+      <c r="U40" s="95" t="n">
         <v>15.64</v>
       </c>
-      <c r="Z40" s="94" t="n">
+      <c r="V40" s="95" t="n">
         <v>15.29</v>
       </c>
-      <c r="AA40" s="94" t="n">
+      <c r="W40" s="95" t="n">
         <v>14.9</v>
       </c>
-      <c r="AB40" s="94" t="n">
+      <c r="X40" s="95" t="n">
         <v>14.75</v>
       </c>
-      <c r="AC40" s="94" t="n">
+      <c r="Y40" s="95" t="n">
         <v>14.79</v>
       </c>
-      <c r="AD40" s="94" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="AE40" s="94" t="n">
+      <c r="Z40" s="95" t="n">
         <v>13.96</v>
+      </c>
+      <c r="AA40" s="95" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="AB40" s="95" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="AC40" s="95" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="AD40" s="95" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AE40" s="95" t="n">
+        <v>15.21</v>
       </c>
     </row>
     <row r="41">
@@ -10880,95 +10880,95 @@
           <t>sensex:RS10</t>
         </is>
       </c>
-      <c r="B41" s="94" t="n">
-        <v>29.63</v>
-      </c>
-      <c r="C41" s="94" t="n">
+      <c r="B41" s="95" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="C41" s="95" t="n">
         <v>29.54</v>
       </c>
-      <c r="D41" s="94" t="n">
+      <c r="D41" s="95" t="n">
         <v>37.35</v>
       </c>
-      <c r="E41" s="94" t="n">
+      <c r="E41" s="95" t="n">
         <v>38.06</v>
       </c>
-      <c r="F41" s="94" t="n">
-        <v>38.06</v>
-      </c>
-      <c r="G41" s="94" t="n">
+      <c r="F41" s="95" t="n">
         <v>34.73</v>
       </c>
-      <c r="H41" s="94" t="n">
+      <c r="G41" s="95" t="n">
         <v>39.02</v>
       </c>
-      <c r="I41" s="94" t="n">
+      <c r="H41" s="95" t="n">
         <v>42.03</v>
       </c>
-      <c r="J41" s="94" t="n">
+      <c r="I41" s="95" t="n">
         <v>43.48</v>
       </c>
-      <c r="K41" s="94" t="n">
+      <c r="J41" s="95" t="n">
         <v>35.77</v>
       </c>
-      <c r="L41" s="94" t="n">
-        <v>35.77</v>
-      </c>
-      <c r="M41" s="94" t="n">
+      <c r="K41" s="95" t="n">
         <v>37.56</v>
       </c>
-      <c r="N41" s="94" t="n">
+      <c r="L41" s="95" t="n">
         <v>35.74</v>
       </c>
-      <c r="O41" s="94" t="n">
+      <c r="M41" s="95" t="n">
         <v>36.86</v>
       </c>
-      <c r="P41" s="94" t="n">
+      <c r="N41" s="95" t="n">
         <v>29.96</v>
       </c>
-      <c r="Q41" s="94" t="n">
+      <c r="O41" s="95" t="n">
         <v>33.56</v>
       </c>
-      <c r="R41" s="94" t="n">
-        <v>33.56</v>
-      </c>
-      <c r="S41" s="94" t="n">
+      <c r="P41" s="95" t="n">
         <v>38.91</v>
       </c>
-      <c r="T41" s="94" t="n">
+      <c r="Q41" s="95" t="n">
         <v>56.68</v>
       </c>
-      <c r="U41" s="94" t="n">
+      <c r="R41" s="95" t="n">
         <v>56.68</v>
       </c>
-      <c r="V41" s="94" t="n">
+      <c r="S41" s="95" t="n">
         <v>57.12</v>
       </c>
-      <c r="W41" s="94" t="n">
+      <c r="T41" s="95" t="n">
         <v>78.04000000000001</v>
       </c>
-      <c r="X41" s="94" t="n">
-        <v>78.04000000000001</v>
-      </c>
-      <c r="Y41" s="94" t="n">
+      <c r="U41" s="95" t="n">
         <v>83.77</v>
       </c>
-      <c r="Z41" s="94" t="n">
+      <c r="V41" s="95" t="n">
         <v>80.52</v>
       </c>
-      <c r="AA41" s="94" t="n">
+      <c r="W41" s="95" t="n">
         <v>79.08</v>
       </c>
-      <c r="AB41" s="94" t="n">
+      <c r="X41" s="95" t="n">
         <v>79.38</v>
       </c>
-      <c r="AC41" s="94" t="n">
+      <c r="Y41" s="95" t="n">
         <v>77.31999999999999</v>
       </c>
-      <c r="AD41" s="94" t="n">
-        <v>77.31999999999999</v>
-      </c>
-      <c r="AE41" s="94" t="n">
+      <c r="Z41" s="95" t="n">
         <v>66.75</v>
+      </c>
+      <c r="AA41" s="95" t="n">
+        <v>64.14</v>
+      </c>
+      <c r="AB41" s="95" t="n">
+        <v>66.76000000000001</v>
+      </c>
+      <c r="AC41" s="95" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="AD41" s="95" t="n">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="AE41" s="95" t="n">
+        <v>66.14</v>
       </c>
     </row>
     <row r="42">
@@ -10977,17 +10977,17 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="95" t="inlineStr">
+      <c r="B42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C42" s="95" t="inlineStr">
+      <c r="C42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D42" s="95" t="inlineStr">
+      <c r="D42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -11002,129 +11002,129 @@
           <t>red</t>
         </is>
       </c>
-      <c r="G42" s="92" t="inlineStr">
+      <c r="G42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H42" s="95" t="inlineStr">
+      <c r="J42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I42" s="95" t="inlineStr">
+      <c r="L42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J42" s="92" t="inlineStr">
+      <c r="N42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K42" s="92" t="inlineStr">
+      <c r="O42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="P42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="S42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L42" s="92" t="inlineStr">
+      <c r="U42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N42" s="91" t="inlineStr">
+      <c r="V42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X42" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="P42" s="92" t="inlineStr">
+      <c r="Y42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Z42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="R42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="S42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="T42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="U42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="V42" s="91" t="inlineStr">
+      <c r="AA42" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W42" s="92" t="inlineStr">
+      <c r="AB42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X42" s="92" t="inlineStr">
+      <c r="AC42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AD42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB42" s="91" t="inlineStr">
+      <c r="AE42" s="91" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AC42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD42" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -11134,95 +11134,95 @@
           <t>fr40:RNG60</t>
         </is>
       </c>
-      <c r="B43" s="94" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="C43" s="94" t="n">
+      <c r="B43" s="95" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="C43" s="95" t="n">
         <v>0.8</v>
       </c>
-      <c r="D43" s="94" t="n">
+      <c r="D43" s="95" t="n">
         <v>1.24</v>
       </c>
-      <c r="E43" s="94" t="n">
+      <c r="E43" s="95" t="n">
         <v>1.27</v>
       </c>
-      <c r="F43" s="94" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="G43" s="94" t="n">
+      <c r="F43" s="95" t="n">
         <v>2.11</v>
       </c>
-      <c r="H43" s="94" t="n">
+      <c r="G43" s="95" t="n">
         <v>-0.29</v>
       </c>
-      <c r="I43" s="94" t="n">
+      <c r="H43" s="95" t="n">
         <v>-1.01</v>
       </c>
-      <c r="J43" s="94" t="n">
+      <c r="I43" s="95" t="n">
         <v>-0.26</v>
       </c>
-      <c r="K43" s="94" t="n">
+      <c r="J43" s="95" t="n">
         <v>0.58</v>
       </c>
-      <c r="L43" s="94" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="M43" s="94" t="n">
+      <c r="K43" s="95" t="n">
         <v>-0.59</v>
       </c>
-      <c r="N43" s="94" t="n">
+      <c r="L43" s="95" t="n">
         <v>-0.14</v>
       </c>
-      <c r="O43" s="94" t="n">
+      <c r="M43" s="95" t="n">
         <v>-0.77</v>
       </c>
-      <c r="P43" s="94" t="n">
+      <c r="N43" s="95" t="n">
         <v>-0.74</v>
       </c>
-      <c r="Q43" s="94" t="n">
+      <c r="O43" s="95" t="n">
         <v>-2.37</v>
       </c>
-      <c r="R43" s="94" t="n">
-        <v>-2.37</v>
-      </c>
-      <c r="S43" s="94" t="n">
+      <c r="P43" s="95" t="n">
         <v>-1.96</v>
       </c>
-      <c r="T43" s="94" t="n">
+      <c r="Q43" s="95" t="n">
         <v>0.05</v>
       </c>
-      <c r="U43" s="94" t="n">
+      <c r="R43" s="95" t="n">
         <v>0.87</v>
       </c>
-      <c r="V43" s="94" t="n">
+      <c r="S43" s="95" t="n">
         <v>0.11</v>
       </c>
-      <c r="W43" s="94" t="n">
+      <c r="T43" s="95" t="n">
         <v>1.51</v>
       </c>
-      <c r="X43" s="94" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Y43" s="94" t="n">
+      <c r="U43" s="95" t="n">
         <v>0.6</v>
       </c>
-      <c r="Z43" s="94" t="n">
+      <c r="V43" s="95" t="n">
         <v>-0.87</v>
       </c>
-      <c r="AA43" s="94" t="n">
+      <c r="W43" s="95" t="n">
         <v>0.87</v>
       </c>
-      <c r="AB43" s="94" t="n">
+      <c r="X43" s="95" t="n">
         <v>-0.7</v>
       </c>
-      <c r="AC43" s="94" t="n">
+      <c r="Y43" s="95" t="n">
         <v>0.28</v>
       </c>
-      <c r="AD43" s="94" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="AE43" s="94" t="n">
+      <c r="Z43" s="95" t="n">
         <v>1.12</v>
+      </c>
+      <c r="AA43" s="95" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="AB43" s="95" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="AC43" s="95" t="n">
+        <v>-3.34</v>
+      </c>
+      <c r="AD43" s="95" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="AE43" s="95" t="n">
+        <v>-3.08</v>
       </c>
     </row>
     <row r="44">
@@ -11231,95 +11231,95 @@
           <t>fr40:RNG120</t>
         </is>
       </c>
-      <c r="B44" s="94" t="n">
-        <v>-7.66</v>
-      </c>
-      <c r="C44" s="94" t="n">
+      <c r="B44" s="95" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="C44" s="95" t="n">
         <v>-6.69</v>
       </c>
-      <c r="D44" s="94" t="n">
+      <c r="D44" s="95" t="n">
         <v>-5.76</v>
       </c>
-      <c r="E44" s="94" t="n">
+      <c r="E44" s="95" t="n">
         <v>-4.33</v>
       </c>
-      <c r="F44" s="94" t="n">
-        <v>-4.33</v>
-      </c>
-      <c r="G44" s="94" t="n">
+      <c r="F44" s="95" t="n">
         <v>-4.18</v>
       </c>
-      <c r="H44" s="94" t="n">
+      <c r="G44" s="95" t="n">
         <v>-6.17</v>
       </c>
-      <c r="I44" s="94" t="n">
+      <c r="H44" s="95" t="n">
         <v>-6.73</v>
       </c>
-      <c r="J44" s="94" t="n">
+      <c r="I44" s="95" t="n">
         <v>-6.01</v>
       </c>
-      <c r="K44" s="94" t="n">
+      <c r="J44" s="95" t="n">
         <v>-5.47</v>
       </c>
-      <c r="L44" s="94" t="n">
-        <v>-5.47</v>
-      </c>
-      <c r="M44" s="94" t="n">
+      <c r="K44" s="95" t="n">
         <v>-6.8</v>
       </c>
-      <c r="N44" s="94" t="n">
+      <c r="L44" s="95" t="n">
         <v>-6.73</v>
       </c>
-      <c r="O44" s="94" t="n">
+      <c r="M44" s="95" t="n">
         <v>-6.46</v>
       </c>
-      <c r="P44" s="94" t="n">
+      <c r="N44" s="95" t="n">
         <v>-5.56</v>
       </c>
-      <c r="Q44" s="94" t="n">
+      <c r="O44" s="95" t="n">
         <v>-6.01</v>
       </c>
-      <c r="R44" s="94" t="n">
+      <c r="P44" s="95" t="n">
+        <v>-6.31</v>
+      </c>
+      <c r="Q44" s="95" t="n">
+        <v>-4.48</v>
+      </c>
+      <c r="R44" s="95" t="n">
+        <v>-5.85</v>
+      </c>
+      <c r="S44" s="95" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="T44" s="95" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="U44" s="95" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="V44" s="95" t="n">
         <v>-6.01</v>
       </c>
-      <c r="S44" s="94" t="n">
-        <v>-6.31</v>
-      </c>
-      <c r="T44" s="94" t="n">
-        <v>-4.48</v>
-      </c>
-      <c r="U44" s="94" t="n">
-        <v>-5.85</v>
-      </c>
-      <c r="V44" s="94" t="n">
-        <v>-4.68</v>
-      </c>
-      <c r="W44" s="94" t="n">
-        <v>-2.89</v>
-      </c>
-      <c r="X44" s="94" t="n">
-        <v>-2.89</v>
-      </c>
-      <c r="Y44" s="94" t="n">
-        <v>-3.77</v>
-      </c>
-      <c r="Z44" s="94" t="n">
-        <v>-6.01</v>
-      </c>
-      <c r="AA44" s="94" t="n">
+      <c r="W44" s="95" t="n">
         <v>-6.35</v>
       </c>
-      <c r="AB44" s="94" t="n">
+      <c r="X44" s="95" t="n">
         <v>-6.86</v>
       </c>
-      <c r="AC44" s="94" t="n">
+      <c r="Y44" s="95" t="n">
         <v>-7.99</v>
       </c>
-      <c r="AD44" s="94" t="n">
-        <v>-7.99</v>
-      </c>
-      <c r="AE44" s="94" t="n">
+      <c r="Z44" s="95" t="n">
         <v>-6.6</v>
+      </c>
+      <c r="AA44" s="95" t="n">
+        <v>-8.43</v>
+      </c>
+      <c r="AB44" s="95" t="n">
+        <v>-8.75</v>
+      </c>
+      <c r="AC44" s="95" t="n">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="AD44" s="95" t="n">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="AE44" s="95" t="n">
+        <v>-8.789999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -11328,95 +11328,95 @@
           <t>fr40:RS5</t>
         </is>
       </c>
-      <c r="B45" s="94" t="n">
-        <v>38.64</v>
-      </c>
-      <c r="C45" s="94" t="n">
+      <c r="B45" s="95" t="n">
+        <v>36.72</v>
+      </c>
+      <c r="C45" s="95" t="n">
         <v>44.46</v>
       </c>
-      <c r="D45" s="94" t="n">
+      <c r="D45" s="95" t="n">
         <v>44.69</v>
       </c>
-      <c r="E45" s="94" t="n">
+      <c r="E45" s="95" t="n">
         <v>61.78</v>
       </c>
-      <c r="F45" s="94" t="n">
-        <v>61.78</v>
-      </c>
-      <c r="G45" s="94" t="n">
+      <c r="F45" s="95" t="n">
         <v>56.72</v>
       </c>
-      <c r="H45" s="94" t="n">
+      <c r="G45" s="95" t="n">
         <v>35.32</v>
       </c>
-      <c r="I45" s="94" t="n">
+      <c r="H45" s="95" t="n">
         <v>40.56</v>
       </c>
-      <c r="J45" s="94" t="n">
+      <c r="I45" s="95" t="n">
         <v>59.42</v>
       </c>
-      <c r="K45" s="94" t="n">
+      <c r="J45" s="95" t="n">
         <v>54.29</v>
       </c>
-      <c r="L45" s="94" t="n">
-        <v>54.29</v>
-      </c>
-      <c r="M45" s="94" t="n">
+      <c r="K45" s="95" t="n">
         <v>46.1</v>
       </c>
-      <c r="N45" s="94" t="n">
+      <c r="L45" s="95" t="n">
         <v>49.74</v>
       </c>
-      <c r="O45" s="94" t="n">
+      <c r="M45" s="95" t="n">
         <v>42.08</v>
       </c>
-      <c r="P45" s="94" t="n">
+      <c r="N45" s="95" t="n">
         <v>50.81</v>
       </c>
-      <c r="Q45" s="94" t="n">
+      <c r="O45" s="95" t="n">
         <v>45.03</v>
       </c>
-      <c r="R45" s="94" t="n">
-        <v>45.03</v>
-      </c>
-      <c r="S45" s="94" t="n">
+      <c r="P45" s="95" t="n">
         <v>33.57</v>
       </c>
-      <c r="T45" s="94" t="n">
+      <c r="Q45" s="95" t="n">
         <v>45.48</v>
       </c>
-      <c r="U45" s="94" t="n">
+      <c r="R45" s="95" t="n">
         <v>44.93</v>
       </c>
-      <c r="V45" s="94" t="n">
+      <c r="S45" s="95" t="n">
         <v>52.35</v>
       </c>
-      <c r="W45" s="94" t="n">
+      <c r="T45" s="95" t="n">
         <v>78.61</v>
       </c>
-      <c r="X45" s="94" t="n">
-        <v>78.61</v>
-      </c>
-      <c r="Y45" s="94" t="n">
+      <c r="U45" s="95" t="n">
         <v>75.48</v>
       </c>
-      <c r="Z45" s="94" t="n">
+      <c r="V45" s="95" t="n">
         <v>57.98</v>
       </c>
-      <c r="AA45" s="94" t="n">
+      <c r="W45" s="95" t="n">
         <v>66.2</v>
       </c>
-      <c r="AB45" s="94" t="n">
+      <c r="X45" s="95" t="n">
         <v>52.83</v>
       </c>
-      <c r="AC45" s="94" t="n">
+      <c r="Y45" s="95" t="n">
         <v>51.58</v>
       </c>
-      <c r="AD45" s="94" t="n">
-        <v>51.58</v>
-      </c>
-      <c r="AE45" s="94" t="n">
+      <c r="Z45" s="95" t="n">
         <v>74.97</v>
+      </c>
+      <c r="AA45" s="95" t="n">
+        <v>45.92</v>
+      </c>
+      <c r="AB45" s="95" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="AC45" s="95" t="n">
+        <v>48.71</v>
+      </c>
+      <c r="AD45" s="95" t="n">
+        <v>53.61</v>
+      </c>
+      <c r="AE45" s="95" t="n">
+        <v>45.19</v>
       </c>
     </row>
     <row r="46">
@@ -11425,149 +11425,149 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="91" t="inlineStr">
+      <c r="B46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C46" s="91" t="inlineStr">
+      <c r="D46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D46" s="91" t="inlineStr">
+      <c r="E46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E46" s="92" t="inlineStr">
+      <c r="H46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F46" s="92" t="inlineStr">
+      <c r="I46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G46" s="92" t="inlineStr">
+      <c r="J46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H46" s="91" t="inlineStr">
+      <c r="K46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I46" s="92" t="inlineStr">
+      <c r="L46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J46" s="92" t="inlineStr">
+      <c r="M46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="N46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P46" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K46" s="92" t="inlineStr">
+      <c r="U46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L46" s="92" t="inlineStr">
+      <c r="V46" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M46" s="91" t="inlineStr">
+      <c r="X46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N46" s="92" t="inlineStr">
+      <c r="Z46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S46" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="T46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W46" s="92" t="inlineStr">
+      <c r="AA46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X46" s="92" t="inlineStr">
+      <c r="AB46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y46" s="92" t="inlineStr">
+      <c r="AC46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA46" s="92" t="inlineStr">
+      <c r="AD46" s="92" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AB46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AE46" s="92" t="inlineStr">
@@ -11582,95 +11582,95 @@
           <t>dax30:RNG60</t>
         </is>
       </c>
-      <c r="B47" s="94" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="C47" s="94" t="n">
+      <c r="B47" s="95" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="C47" s="95" t="n">
         <v>5.49</v>
       </c>
-      <c r="D47" s="94" t="n">
+      <c r="D47" s="95" t="n">
         <v>6.23</v>
       </c>
-      <c r="E47" s="94" t="n">
+      <c r="E47" s="95" t="n">
         <v>6.73</v>
       </c>
-      <c r="F47" s="94" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="G47" s="94" t="n">
+      <c r="F47" s="95" t="n">
         <v>7.02</v>
       </c>
-      <c r="H47" s="94" t="n">
+      <c r="G47" s="95" t="n">
         <v>5.69</v>
       </c>
-      <c r="I47" s="94" t="n">
+      <c r="H47" s="95" t="n">
         <v>5</v>
       </c>
-      <c r="J47" s="94" t="n">
+      <c r="I47" s="95" t="n">
         <v>5.98</v>
       </c>
-      <c r="K47" s="94" t="n">
+      <c r="J47" s="95" t="n">
         <v>6.61</v>
       </c>
-      <c r="L47" s="94" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="M47" s="94" t="n">
+      <c r="K47" s="95" t="n">
         <v>4.66</v>
       </c>
-      <c r="N47" s="94" t="n">
+      <c r="L47" s="95" t="n">
         <v>4.43</v>
       </c>
-      <c r="O47" s="94" t="n">
+      <c r="M47" s="95" t="n">
         <v>2.96</v>
       </c>
-      <c r="P47" s="94" t="n">
+      <c r="N47" s="95" t="n">
         <v>2.76</v>
       </c>
-      <c r="Q47" s="94" t="n">
+      <c r="O47" s="95" t="n">
         <v>1.99</v>
       </c>
-      <c r="R47" s="94" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="S47" s="94" t="n">
+      <c r="P47" s="95" t="n">
         <v>2.59</v>
       </c>
-      <c r="T47" s="94" t="n">
+      <c r="Q47" s="95" t="n">
         <v>4.12</v>
       </c>
-      <c r="U47" s="94" t="n">
+      <c r="R47" s="95" t="n">
         <v>5.36</v>
       </c>
-      <c r="V47" s="94" t="n">
+      <c r="S47" s="95" t="n">
         <v>4.62</v>
       </c>
-      <c r="W47" s="94" t="n">
+      <c r="T47" s="95" t="n">
         <v>5.4</v>
       </c>
-      <c r="X47" s="94" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Y47" s="94" t="n">
+      <c r="U47" s="95" t="n">
         <v>4.27</v>
       </c>
-      <c r="Z47" s="94" t="n">
+      <c r="V47" s="95" t="n">
         <v>2.96</v>
       </c>
-      <c r="AA47" s="94" t="n">
+      <c r="W47" s="95" t="n">
         <v>4.58</v>
       </c>
-      <c r="AB47" s="94" t="n">
+      <c r="X47" s="95" t="n">
         <v>3.04</v>
       </c>
-      <c r="AC47" s="94" t="n">
+      <c r="Y47" s="95" t="n">
         <v>2.66</v>
       </c>
-      <c r="AD47" s="94" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AE47" s="94" t="n">
+      <c r="Z47" s="95" t="n">
         <v>4.35</v>
+      </c>
+      <c r="AA47" s="95" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AB47" s="95" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AC47" s="95" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD47" s="95" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE47" s="95" t="n">
+        <v>1.45</v>
       </c>
     </row>
     <row r="48">
@@ -11679,95 +11679,95 @@
           <t>dax30:RNG120</t>
         </is>
       </c>
-      <c r="B48" s="94" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="C48" s="94" t="n">
+      <c r="B48" s="95" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C48" s="95" t="n">
         <v>5.38</v>
       </c>
-      <c r="D48" s="94" t="n">
+      <c r="D48" s="95" t="n">
         <v>7.08</v>
       </c>
-      <c r="E48" s="94" t="n">
+      <c r="E48" s="95" t="n">
         <v>9.25</v>
       </c>
-      <c r="F48" s="94" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="G48" s="94" t="n">
+      <c r="F48" s="95" t="n">
         <v>9.43</v>
       </c>
-      <c r="H48" s="94" t="n">
+      <c r="G48" s="95" t="n">
         <v>8.369999999999999</v>
       </c>
-      <c r="I48" s="94" t="n">
+      <c r="H48" s="95" t="n">
         <v>7.55</v>
       </c>
-      <c r="J48" s="94" t="n">
+      <c r="I48" s="95" t="n">
         <v>7.42</v>
       </c>
-      <c r="K48" s="94" t="n">
+      <c r="J48" s="95" t="n">
         <v>8.130000000000001</v>
       </c>
-      <c r="L48" s="94" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="M48" s="94" t="n">
+      <c r="K48" s="95" t="n">
         <v>6.2</v>
       </c>
-      <c r="N48" s="94" t="n">
+      <c r="L48" s="95" t="n">
         <v>6.16</v>
       </c>
-      <c r="O48" s="94" t="n">
+      <c r="M48" s="95" t="n">
         <v>6.75</v>
       </c>
-      <c r="P48" s="94" t="n">
+      <c r="N48" s="95" t="n">
         <v>7.71</v>
       </c>
-      <c r="Q48" s="94" t="n">
+      <c r="O48" s="95" t="n">
         <v>7.2</v>
       </c>
-      <c r="R48" s="94" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="S48" s="94" t="n">
+      <c r="P48" s="95" t="n">
         <v>7.01</v>
       </c>
-      <c r="T48" s="94" t="n">
+      <c r="Q48" s="95" t="n">
         <v>7.87</v>
       </c>
-      <c r="U48" s="94" t="n">
+      <c r="R48" s="95" t="n">
         <v>6.58</v>
       </c>
-      <c r="V48" s="94" t="n">
+      <c r="S48" s="95" t="n">
         <v>7.78</v>
       </c>
-      <c r="W48" s="94" t="n">
+      <c r="T48" s="95" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="X48" s="94" t="n">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="Y48" s="94" t="n">
+      <c r="U48" s="95" t="n">
         <v>6.31</v>
       </c>
-      <c r="Z48" s="94" t="n">
+      <c r="V48" s="95" t="n">
         <v>4.66</v>
       </c>
-      <c r="AA48" s="94" t="n">
+      <c r="W48" s="95" t="n">
         <v>3.7</v>
       </c>
-      <c r="AB48" s="94" t="n">
+      <c r="X48" s="95" t="n">
         <v>3.7</v>
       </c>
-      <c r="AC48" s="94" t="n">
+      <c r="Y48" s="95" t="n">
         <v>1.72</v>
       </c>
-      <c r="AD48" s="94" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE48" s="94" t="n">
+      <c r="Z48" s="95" t="n">
         <v>3.46</v>
+      </c>
+      <c r="AA48" s="95" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AB48" s="95" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC48" s="95" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AD48" s="95" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE48" s="95" t="n">
+        <v>1.41</v>
       </c>
     </row>
     <row r="49">
@@ -11776,101 +11776,101 @@
           <t>dax30:RS6</t>
         </is>
       </c>
-      <c r="B49" s="94" t="n">
-        <v>49.26</v>
-      </c>
-      <c r="C49" s="94" t="n">
+      <c r="B49" s="95" t="n">
+        <v>47.24</v>
+      </c>
+      <c r="C49" s="95" t="n">
         <v>51.32</v>
       </c>
-      <c r="D49" s="94" t="n">
+      <c r="D49" s="95" t="n">
         <v>54.82</v>
       </c>
-      <c r="E49" s="94" t="n">
+      <c r="E49" s="95" t="n">
         <v>76.53</v>
       </c>
-      <c r="F49" s="94" t="n">
-        <v>76.53</v>
-      </c>
-      <c r="G49" s="94" t="n">
+      <c r="F49" s="95" t="n">
         <v>73.2</v>
       </c>
-      <c r="H49" s="94" t="n">
+      <c r="G49" s="95" t="n">
         <v>64.68000000000001</v>
       </c>
-      <c r="I49" s="94" t="n">
+      <c r="H49" s="95" t="n">
         <v>71.38</v>
       </c>
-      <c r="J49" s="94" t="n">
+      <c r="I49" s="95" t="n">
         <v>74.03</v>
       </c>
-      <c r="K49" s="94" t="n">
+      <c r="J49" s="95" t="n">
         <v>68.01000000000001</v>
       </c>
-      <c r="L49" s="94" t="n">
-        <v>68.01000000000001</v>
-      </c>
-      <c r="M49" s="94" t="n">
+      <c r="K49" s="95" t="n">
         <v>58.26</v>
       </c>
-      <c r="N49" s="94" t="n">
+      <c r="L49" s="95" t="n">
         <v>62.55</v>
       </c>
-      <c r="O49" s="94" t="n">
+      <c r="M49" s="95" t="n">
         <v>49.18</v>
       </c>
-      <c r="P49" s="94" t="n">
+      <c r="N49" s="95" t="n">
         <v>52.29</v>
       </c>
-      <c r="Q49" s="94" t="n">
+      <c r="O49" s="95" t="n">
         <v>53.55</v>
       </c>
-      <c r="R49" s="94" t="n">
-        <v>53.55</v>
-      </c>
-      <c r="S49" s="94" t="n">
+      <c r="P49" s="95" t="n">
         <v>46.86</v>
       </c>
-      <c r="T49" s="94" t="n">
+      <c r="Q49" s="95" t="n">
         <v>56.45</v>
       </c>
-      <c r="U49" s="94" t="n">
+      <c r="R49" s="95" t="n">
         <v>59.76</v>
       </c>
-      <c r="V49" s="94" t="n">
+      <c r="S49" s="95" t="n">
         <v>67.34999999999999</v>
       </c>
-      <c r="W49" s="94" t="n">
+      <c r="T49" s="95" t="n">
         <v>78.38</v>
       </c>
-      <c r="X49" s="94" t="n">
-        <v>78.38</v>
-      </c>
-      <c r="Y49" s="94" t="n">
+      <c r="U49" s="95" t="n">
         <v>72.42</v>
       </c>
-      <c r="Z49" s="94" t="n">
+      <c r="V49" s="95" t="n">
         <v>59.91</v>
       </c>
-      <c r="AA49" s="94" t="n">
+      <c r="W49" s="95" t="n">
         <v>66</v>
       </c>
-      <c r="AB49" s="94" t="n">
+      <c r="X49" s="95" t="n">
         <v>59.4</v>
       </c>
-      <c r="AC49" s="94" t="n">
+      <c r="Y49" s="95" t="n">
         <v>52.95</v>
       </c>
-      <c r="AD49" s="94" t="n">
-        <v>52.95</v>
-      </c>
-      <c r="AE49" s="94" t="n">
+      <c r="Z49" s="95" t="n">
         <v>75.06999999999999</v>
+      </c>
+      <c r="AA49" s="95" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="AB49" s="95" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="AC49" s="95" t="n">
+        <v>57.16</v>
+      </c>
+      <c r="AD49" s="95" t="n">
+        <v>62.56</v>
+      </c>
+      <c r="AE49" s="95" t="n">
+        <v>52.29</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：vn:RS3:21.39&lt;=25;sensex:RS10:29.63&lt;=39</t>
+          <t>今日买报：us500:RS2:6.85&lt;=22;us30:RS3:17.33&lt;=25;ixic:RS2:13.67&lt;=38;vn:RS3:21.39&lt;=25;sensex:RS10:28.55&lt;=39</t>
         </is>
       </c>
     </row>

--- a/report_2410.xlsx
+++ b/report_2410.xlsx
@@ -1060,9 +1060,9 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.21</v>
+        <v>-0.15</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.02</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.55</v>
@@ -6362,132 +6362,132 @@
       </c>
       <c r="F1" s="77" t="inlineStr">
         <is>
-          <t>241020</t>
+          <t>241018</t>
         </is>
       </c>
       <c r="G1" s="77" t="inlineStr">
         <is>
-          <t>241018</t>
+          <t>241017</t>
         </is>
       </c>
       <c r="H1" s="77" t="inlineStr">
         <is>
-          <t>241017</t>
+          <t>241016</t>
         </is>
       </c>
       <c r="I1" s="77" t="inlineStr">
         <is>
-          <t>241016</t>
+          <t>241015</t>
         </is>
       </c>
       <c r="J1" s="77" t="inlineStr">
         <is>
-          <t>241015</t>
+          <t>241014</t>
         </is>
       </c>
       <c r="K1" s="77" t="inlineStr">
         <is>
-          <t>241014</t>
+          <t>241011</t>
         </is>
       </c>
       <c r="L1" s="77" t="inlineStr">
         <is>
-          <t>241013</t>
+          <t>241010</t>
         </is>
       </c>
       <c r="M1" s="77" t="inlineStr">
         <is>
-          <t>241011</t>
+          <t>241009</t>
         </is>
       </c>
       <c r="N1" s="77" t="inlineStr">
         <is>
-          <t>241010</t>
+          <t>241008</t>
         </is>
       </c>
       <c r="O1" s="77" t="inlineStr">
         <is>
-          <t>241009</t>
+          <t>241007</t>
         </is>
       </c>
       <c r="P1" s="77" t="inlineStr">
         <is>
-          <t>241008</t>
+          <t>241004</t>
         </is>
       </c>
       <c r="Q1" s="77" t="inlineStr">
         <is>
-          <t>241007</t>
+          <t>241003</t>
         </is>
       </c>
       <c r="R1" s="77" t="inlineStr">
         <is>
-          <t>241006</t>
+          <t>241002</t>
         </is>
       </c>
       <c r="S1" s="77" t="inlineStr">
         <is>
-          <t>241004</t>
+          <t>241001</t>
         </is>
       </c>
       <c r="T1" s="77" t="inlineStr">
         <is>
-          <t>241003</t>
+          <t>240930</t>
         </is>
       </c>
       <c r="U1" s="77" t="inlineStr">
         <is>
-          <t>241002</t>
+          <t>240927</t>
         </is>
       </c>
       <c r="V1" s="77" t="inlineStr">
         <is>
-          <t>241001</t>
+          <t>240926</t>
         </is>
       </c>
       <c r="W1" s="77" t="inlineStr">
         <is>
-          <t>240930</t>
+          <t>240925</t>
         </is>
       </c>
       <c r="X1" s="77" t="inlineStr">
         <is>
-          <t>240929</t>
+          <t>240924</t>
         </is>
       </c>
       <c r="Y1" s="77" t="inlineStr">
         <is>
-          <t>240927</t>
+          <t>240923</t>
         </is>
       </c>
       <c r="Z1" s="77" t="inlineStr">
         <is>
-          <t>240926</t>
+          <t>240920</t>
         </is>
       </c>
       <c r="AA1" s="77" t="inlineStr">
         <is>
-          <t>240925</t>
+          <t>240919</t>
         </is>
       </c>
       <c r="AB1" s="77" t="inlineStr">
         <is>
-          <t>240924</t>
+          <t>240918</t>
         </is>
       </c>
       <c r="AC1" s="77" t="inlineStr">
         <is>
-          <t>240923</t>
+          <t>240917</t>
         </is>
       </c>
       <c r="AD1" s="77" t="inlineStr">
         <is>
-          <t>240922</t>
+          <t>240916</t>
         </is>
       </c>
       <c r="AE1" s="77" t="inlineStr">
         <is>
-          <t>240920</t>
+          <t>240913</t>
         </is>
       </c>
     </row>
@@ -6557,192 +6557,192 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="N2" s="91" t="inlineStr">
+      <c r="N2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O2" s="91" t="inlineStr">
+      <c r="Z2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB2" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC2" s="91" t="inlineStr">
+      <c r="AA2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD2" s="91" t="inlineStr">
+      <c r="AB2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AE2" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="AC2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AD2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AE2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="93" t="inlineStr">
+      <c r="A3" s="94" t="inlineStr">
         <is>
           <t>sh:RNG60</t>
         </is>
       </c>
-      <c r="B3" s="94" t="n">
+      <c r="B3" s="95" t="n">
         <v>12.52</v>
       </c>
-      <c r="C3" s="94" t="n">
+      <c r="C3" s="95" t="n">
         <v>11.42</v>
       </c>
-      <c r="D3" s="94" t="n">
+      <c r="D3" s="95" t="n">
         <v>10.18</v>
       </c>
-      <c r="E3" s="94" t="n">
+      <c r="E3" s="95" t="n">
         <v>9.77</v>
       </c>
-      <c r="F3" s="94" t="n">
+      <c r="F3" s="95" t="n">
         <v>10.08</v>
       </c>
-      <c r="G3" s="94" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="H3" s="94" t="n">
+      <c r="G3" s="95" t="n">
         <v>6.49</v>
       </c>
-      <c r="I3" s="94" t="n">
+      <c r="H3" s="95" t="n">
         <v>7.7</v>
       </c>
-      <c r="J3" s="94" t="n">
+      <c r="I3" s="95" t="n">
         <v>7.74</v>
       </c>
-      <c r="K3" s="94" t="n">
+      <c r="J3" s="95" t="n">
         <v>10.57</v>
       </c>
-      <c r="L3" s="94" t="n">
+      <c r="K3" s="95" t="n">
         <v>9.470000000000001</v>
       </c>
-      <c r="M3" s="94" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="N3" s="94" t="n">
+      <c r="L3" s="95" t="n">
         <v>11.58</v>
       </c>
-      <c r="O3" s="94" t="n">
+      <c r="M3" s="95" t="n">
         <v>11.51</v>
       </c>
-      <c r="P3" s="94" t="n">
+      <c r="N3" s="95" t="n">
         <v>18.3</v>
       </c>
-      <c r="Q3" s="94" t="n">
+      <c r="O3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="R3" s="94" t="n">
+      <c r="P3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="S3" s="94" t="n">
+      <c r="Q3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="T3" s="94" t="n">
+      <c r="R3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="U3" s="94" t="n">
+      <c r="S3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="V3" s="94" t="n">
+      <c r="T3" s="95" t="n">
         <v>12.81</v>
       </c>
-      <c r="W3" s="94" t="n">
-        <v>12.81</v>
-      </c>
-      <c r="X3" s="94" t="n">
+      <c r="U3" s="95" t="n">
         <v>3.53</v>
       </c>
-      <c r="Y3" s="94" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="Z3" s="94" t="n">
+      <c r="V3" s="95" t="n">
         <v>0.13</v>
       </c>
-      <c r="AA3" s="94" t="n">
+      <c r="W3" s="95" t="n">
         <v>-3.29</v>
       </c>
-      <c r="AB3" s="94" t="n">
+      <c r="X3" s="95" t="n">
         <v>-3.51</v>
       </c>
-      <c r="AC3" s="94" t="n">
+      <c r="Y3" s="95" t="n">
         <v>-6.68</v>
       </c>
-      <c r="AD3" s="94" t="n">
+      <c r="Z3" s="95" t="n">
         <v>-7.93</v>
       </c>
-      <c r="AE3" s="94" t="n">
-        <v>-7.93</v>
+      <c r="AA3" s="95" t="n">
+        <v>-7.25</v>
+      </c>
+      <c r="AB3" s="95" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="AC3" s="95" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="AD3" s="95" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="AE3" s="95" t="n">
+        <v>-9.81</v>
       </c>
     </row>
     <row r="4">
@@ -6751,95 +6751,95 @@
           <t>sh:RNG120</t>
         </is>
       </c>
-      <c r="B4" s="94" t="n">
+      <c r="B4" s="95" t="n">
         <v>7.73</v>
       </c>
-      <c r="C4" s="94" t="n">
+      <c r="C4" s="95" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="D4" s="94" t="n">
+      <c r="D4" s="95" t="n">
         <v>7.92</v>
       </c>
-      <c r="E4" s="94" t="n">
+      <c r="E4" s="95" t="n">
         <v>6.62</v>
       </c>
-      <c r="F4" s="94" t="n">
+      <c r="F4" s="95" t="n">
         <v>6.09</v>
       </c>
-      <c r="G4" s="94" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="H4" s="94" t="n">
+      <c r="G4" s="95" t="n">
         <v>3.19</v>
       </c>
-      <c r="I4" s="94" t="n">
+      <c r="H4" s="95" t="n">
         <v>6.51</v>
       </c>
-      <c r="J4" s="94" t="n">
+      <c r="I4" s="95" t="n">
         <v>4.71</v>
       </c>
-      <c r="K4" s="94" t="n">
+      <c r="J4" s="95" t="n">
         <v>8.77</v>
       </c>
-      <c r="L4" s="94" t="n">
+      <c r="K4" s="95" t="n">
         <v>6.05</v>
       </c>
-      <c r="M4" s="94" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="N4" s="94" t="n">
+      <c r="L4" s="95" t="n">
         <v>9.07</v>
       </c>
-      <c r="O4" s="94" t="n">
+      <c r="M4" s="95" t="n">
         <v>6.9</v>
       </c>
-      <c r="P4" s="94" t="n">
+      <c r="N4" s="95" t="n">
         <v>14.53</v>
       </c>
-      <c r="Q4" s="94" t="n">
+      <c r="O4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="R4" s="94" t="n">
+      <c r="P4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="S4" s="94" t="n">
+      <c r="Q4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="T4" s="94" t="n">
+      <c r="R4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="U4" s="94" t="n">
+      <c r="S4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="V4" s="94" t="n">
+      <c r="T4" s="95" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="W4" s="94" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="X4" s="94" t="n">
+      <c r="U4" s="95" t="n">
         <v>0.41</v>
       </c>
-      <c r="Y4" s="94" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="Z4" s="94" t="n">
+      <c r="V4" s="95" t="n">
         <v>-2.48</v>
       </c>
-      <c r="AA4" s="94" t="n">
+      <c r="W4" s="95" t="n">
         <v>-4.76</v>
       </c>
-      <c r="AB4" s="94" t="n">
+      <c r="X4" s="95" t="n">
         <v>-4.9</v>
       </c>
-      <c r="AC4" s="94" t="n">
+      <c r="Y4" s="95" t="n">
         <v>-8.16</v>
       </c>
-      <c r="AD4" s="94" t="n">
+      <c r="Z4" s="95" t="n">
         <v>-9.720000000000001</v>
       </c>
-      <c r="AE4" s="94" t="n">
-        <v>-9.720000000000001</v>
+      <c r="AA4" s="95" t="n">
+        <v>-9.59</v>
+      </c>
+      <c r="AB4" s="95" t="n">
+        <v>-10.85</v>
+      </c>
+      <c r="AC4" s="95" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="AD4" s="95" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="AE4" s="95" t="n">
+        <v>-12.12</v>
       </c>
     </row>
     <row r="5">
@@ -6848,95 +6848,95 @@
           <t>sh:RS3</t>
         </is>
       </c>
-      <c r="B5" s="94" t="n">
+      <c r="B5" s="95" t="n">
         <v>55.63</v>
       </c>
-      <c r="C5" s="94" t="n">
+      <c r="C5" s="95" t="n">
         <v>76.48</v>
       </c>
-      <c r="D5" s="94" t="n">
+      <c r="D5" s="95" t="n">
         <v>71.05</v>
       </c>
-      <c r="E5" s="94" t="n">
+      <c r="E5" s="95" t="n">
         <v>65.47</v>
       </c>
-      <c r="F5" s="94" t="n">
+      <c r="F5" s="95" t="n">
         <v>63.75</v>
       </c>
-      <c r="G5" s="94" t="n">
-        <v>63.75</v>
-      </c>
-      <c r="H5" s="94" t="n">
+      <c r="G5" s="95" t="n">
         <v>32.04</v>
       </c>
-      <c r="I5" s="94" t="n">
+      <c r="H5" s="95" t="n">
         <v>40.69</v>
       </c>
-      <c r="J5" s="94" t="n">
+      <c r="I5" s="95" t="n">
         <v>40.15</v>
       </c>
-      <c r="K5" s="94" t="n">
+      <c r="J5" s="95" t="n">
         <v>57.29</v>
       </c>
-      <c r="L5" s="94" t="n">
+      <c r="K5" s="95" t="n">
         <v>44.67</v>
       </c>
-      <c r="M5" s="94" t="n">
-        <v>44.67</v>
-      </c>
-      <c r="N5" s="94" t="n">
+      <c r="L5" s="95" t="n">
         <v>59.48</v>
       </c>
-      <c r="O5" s="94" t="n">
+      <c r="M5" s="95" t="n">
         <v>54.31</v>
       </c>
-      <c r="P5" s="94" t="n">
+      <c r="N5" s="95" t="n">
         <v>99.84</v>
       </c>
-      <c r="Q5" s="94" t="n">
+      <c r="O5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="R5" s="94" t="n">
+      <c r="P5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="S5" s="94" t="n">
+      <c r="Q5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="T5" s="94" t="n">
+      <c r="R5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="U5" s="94" t="n">
+      <c r="S5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="V5" s="94" t="n">
+      <c r="T5" s="95" t="n">
         <v>99.75</v>
       </c>
-      <c r="W5" s="94" t="n">
-        <v>99.75</v>
-      </c>
-      <c r="X5" s="94" t="n">
+      <c r="U5" s="95" t="n">
         <v>99.31</v>
       </c>
-      <c r="Y5" s="94" t="n">
-        <v>99.31</v>
-      </c>
-      <c r="Z5" s="94" t="n">
+      <c r="V5" s="95" t="n">
         <v>98.83</v>
       </c>
-      <c r="AA5" s="94" t="n">
+      <c r="W5" s="95" t="n">
         <v>97.34999999999999</v>
       </c>
-      <c r="AB5" s="94" t="n">
+      <c r="X5" s="95" t="n">
         <v>96.38</v>
       </c>
-      <c r="AC5" s="94" t="n">
+      <c r="Y5" s="95" t="n">
         <v>77.51000000000001</v>
       </c>
-      <c r="AD5" s="94" t="n">
+      <c r="Z5" s="95" t="n">
         <v>64.38</v>
       </c>
-      <c r="AE5" s="94" t="n">
-        <v>64.38</v>
+      <c r="AA5" s="95" t="n">
+        <v>63.45</v>
+      </c>
+      <c r="AB5" s="95" t="n">
+        <v>37.85</v>
+      </c>
+      <c r="AC5" s="95" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AD5" s="95" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AE5" s="95" t="n">
+        <v>7.42</v>
       </c>
     </row>
     <row r="6">
@@ -6970,324 +6970,324 @@
           <t>red</t>
         </is>
       </c>
-      <c r="G6" s="92" t="inlineStr">
+      <c r="G6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L6" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H6" s="91" t="inlineStr">
+      <c r="N6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I6" s="91" t="inlineStr">
+      <c r="AA6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J6" s="91" t="inlineStr">
+      <c r="AB6" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AC6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K6" s="91" t="inlineStr">
+      <c r="AD6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L6" s="91" t="inlineStr">
+      <c r="AE6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="N6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB6" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC6" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE6" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="93" t="inlineStr">
+      <c r="A7" s="94" t="inlineStr">
         <is>
           <t>kc:RNG60</t>
         </is>
       </c>
-      <c r="B7" s="94" t="